--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>27.04.2026 18:51:47</t>
+    <t>28.04.2026 18:38:52</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2454,25 +2454,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.060087</v>
+        <v>0.061239</v>
       </c>
       <c r="F6" s="7">
-        <v>0.048285999999999996</v>
+        <v>0.051957</v>
       </c>
       <c r="G6" s="7">
-        <v>0.205684</v>
+        <v>0.20682999999999999</v>
       </c>
       <c r="H6" s="7">
-        <v>0.107674</v>
+        <v>0.109016</v>
       </c>
       <c r="I6" s="7">
-        <v>0.460353</v>
+        <v>0.462123</v>
       </c>
       <c r="J6" s="7">
-        <v>2.172046</v>
+        <v>2.177081</v>
       </c>
       <c r="K6" s="7">
-        <v>5.750565</v>
+        <v>5.748423</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,25 +2489,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.093854</v>
+        <v>0.119036</v>
       </c>
       <c r="F7" s="7">
-        <v>0.059985</v>
+        <v>0.060101</v>
       </c>
       <c r="G7" s="7">
-        <v>0.134201</v>
+        <v>0.130215</v>
       </c>
       <c r="H7" s="7">
-        <v>0.082997</v>
+        <v>0.08940300000000001</v>
       </c>
       <c r="I7" s="7">
-        <v>0.51177</v>
+        <v>0.520713</v>
       </c>
       <c r="J7" s="7">
-        <v>2.8245370000000003</v>
+        <v>2.851056</v>
       </c>
       <c r="K7" s="7">
-        <v>5.579605</v>
+        <v>5.649386</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2524,25 +2524,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.051220999999999996</v>
+        <v>0.049572000000000005</v>
       </c>
       <c r="F8" s="7">
-        <v>0.014931000000000002</v>
+        <v>0.01572</v>
       </c>
       <c r="G8" s="7">
-        <v>0.16326000000000002</v>
+        <v>0.157384</v>
       </c>
       <c r="H8" s="7">
-        <v>0.054572</v>
+        <v>0.053368</v>
       </c>
       <c r="I8" s="7">
-        <v>0.411876</v>
+        <v>0.410264</v>
       </c>
       <c r="J8" s="7">
-        <v>1.7435839999999998</v>
+        <v>1.7487469999999998</v>
       </c>
       <c r="K8" s="7">
-        <v>3.605998</v>
+        <v>3.595865</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2559,25 +2559,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.082544</v>
+        <v>0.09705899999999999</v>
       </c>
       <c r="F9" s="7">
-        <v>0.076519</v>
+        <v>0.092165</v>
       </c>
       <c r="G9" s="7">
-        <v>0.281351</v>
+        <v>0.295739</v>
       </c>
       <c r="H9" s="7">
-        <v>0.240311</v>
+        <v>0.250476</v>
       </c>
       <c r="I9" s="7">
-        <v>0.5285179999999999</v>
+        <v>0.541045</v>
       </c>
       <c r="J9" s="7">
-        <v>3.009087</v>
+        <v>3.032957</v>
       </c>
       <c r="K9" s="7">
-        <v>10.520646</v>
+        <v>10.510965</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,25 +2594,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>0.021351</v>
+        <v>0.019113</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.065597</v>
+        <v>-0.072836</v>
       </c>
       <c r="G10" s="7">
-        <v>0.115925</v>
+        <v>0.13228600000000001</v>
       </c>
       <c r="H10" s="7">
-        <v>0.05535999999999999</v>
+        <v>0.052665</v>
       </c>
       <c r="I10" s="7">
-        <v>0.563879</v>
+        <v>0.559886</v>
       </c>
       <c r="J10" s="7">
-        <v>4.177831</v>
+        <v>4.140904</v>
       </c>
       <c r="K10" s="7">
-        <v>13.710600999999999</v>
+        <v>13.771003</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2629,25 +2629,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.11380900000000001</v>
+        <v>0.127955</v>
       </c>
       <c r="F11" s="7">
-        <v>0.096943</v>
+        <v>0.112809</v>
       </c>
       <c r="G11" s="7">
-        <v>0.32028300000000004</v>
+        <v>0.339617</v>
       </c>
       <c r="H11" s="7">
-        <v>0.28225100000000003</v>
+        <v>0.293092</v>
       </c>
       <c r="I11" s="7">
-        <v>0.56047</v>
+        <v>0.573664</v>
       </c>
       <c r="J11" s="7">
-        <v>2.628104</v>
+        <v>2.648032</v>
       </c>
       <c r="K11" s="7">
-        <v>13.127383</v>
+        <v>13.068493</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2664,25 +2664,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.051928</v>
+        <v>0.05466</v>
       </c>
       <c r="F12" s="7">
-        <v>0.082763</v>
+        <v>0.08721899999999999</v>
       </c>
       <c r="G12" s="7">
-        <v>0.239228</v>
+        <v>0.24519</v>
       </c>
       <c r="H12" s="7">
-        <v>0.142567</v>
+        <v>0.146676</v>
       </c>
       <c r="I12" s="7">
-        <v>0.488199</v>
+        <v>0.493551</v>
       </c>
       <c r="J12" s="7">
-        <v>2.6548110000000005</v>
+        <v>2.6578769999999996</v>
       </c>
       <c r="K12" s="7">
-        <v>4.551686</v>
+        <v>4.566096</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,25 +2699,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.105197</v>
+        <v>0.12048199999999999</v>
       </c>
       <c r="F13" s="7">
-        <v>0.111432</v>
+        <v>0.129012</v>
       </c>
       <c r="G13" s="7">
-        <v>0.339256</v>
+        <v>0.36591500000000005</v>
       </c>
       <c r="H13" s="7">
-        <v>0.28697700000000004</v>
+        <v>0.300335</v>
       </c>
       <c r="I13" s="7">
-        <v>0.563983</v>
+        <v>0.580216</v>
       </c>
       <c r="J13" s="7">
-        <v>2.687078</v>
+        <v>2.7193680000000002</v>
       </c>
       <c r="K13" s="7">
-        <v>10.55386</v>
+        <v>10.517483</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,25 +2734,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.074532</v>
+        <v>0.076029</v>
       </c>
       <c r="F14" s="7">
-        <v>0.039586</v>
+        <v>0.050156</v>
       </c>
       <c r="G14" s="7">
-        <v>0.25558800000000004</v>
+        <v>0.269179</v>
       </c>
       <c r="H14" s="7">
-        <v>0.184662</v>
+        <v>0.186999</v>
       </c>
       <c r="I14" s="7">
-        <v>0.47676</v>
+        <v>0.479673</v>
       </c>
       <c r="J14" s="7">
-        <v>2.67551</v>
+        <v>2.673881</v>
       </c>
       <c r="K14" s="7">
-        <v>8.238811</v>
+        <v>8.166983</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,25 +2769,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.050384000000000005</v>
+        <v>0.051065</v>
       </c>
       <c r="F15" s="7">
-        <v>0.029422999999999998</v>
+        <v>0.033864</v>
       </c>
       <c r="G15" s="7">
-        <v>0.19324200000000002</v>
+        <v>0.19402799999999998</v>
       </c>
       <c r="H15" s="7">
-        <v>0.08274</v>
+        <v>0.08372199999999999</v>
       </c>
       <c r="I15" s="7">
-        <v>0.414991</v>
+        <v>0.41627400000000003</v>
       </c>
       <c r="J15" s="7">
-        <v>2.01363</v>
+        <v>2.014218</v>
       </c>
       <c r="K15" s="7">
-        <v>5.565716</v>
+        <v>5.56231</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,25 +2804,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.047896999999999995</v>
+        <v>0.048617</v>
       </c>
       <c r="F16" s="7">
-        <v>0.09156</v>
+        <v>0.093436</v>
       </c>
       <c r="G16" s="7">
-        <v>0.223432</v>
+        <v>0.22479600000000002</v>
       </c>
       <c r="H16" s="7">
-        <v>0.135731</v>
+        <v>0.138281</v>
       </c>
       <c r="I16" s="7">
-        <v>0.5132030000000001</v>
+        <v>0.516601</v>
       </c>
       <c r="J16" s="7">
-        <v>2.789269</v>
+        <v>2.797335</v>
       </c>
       <c r="K16" s="7">
-        <v>5.051874000000001</v>
+        <v>5.062829</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2839,25 +2839,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.040917</v>
+        <v>0.040008</v>
       </c>
       <c r="F17" s="7">
-        <v>0.081179</v>
+        <v>0.084635</v>
       </c>
       <c r="G17" s="7">
-        <v>0.18751</v>
+        <v>0.19145600000000002</v>
       </c>
       <c r="H17" s="7">
-        <v>0.1291</v>
+        <v>0.131999</v>
       </c>
       <c r="I17" s="7">
-        <v>0.420963</v>
+        <v>0.424611</v>
       </c>
       <c r="J17" s="7">
-        <v>1.654736</v>
+        <v>1.659353</v>
       </c>
       <c r="K17" s="7">
-        <v>4.529464</v>
+        <v>4.53216</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,25 +2874,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>0.028172000000000003</v>
+        <v>0.029462000000000002</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.062377</v>
+        <v>-0.06849</v>
       </c>
       <c r="G18" s="7">
-        <v>0.16957899999999998</v>
+        <v>0.18782800000000002</v>
       </c>
       <c r="H18" s="7">
-        <v>0.07592</v>
+        <v>0.075467</v>
       </c>
       <c r="I18" s="7">
-        <v>0.656835</v>
+        <v>0.656138</v>
       </c>
       <c r="J18" s="7">
-        <v>4.934685</v>
+        <v>4.907018</v>
       </c>
       <c r="K18" s="7">
-        <v>15.979211</v>
+        <v>16.091849</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,25 +2909,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.068214</v>
+        <v>0.07840799999999999</v>
       </c>
       <c r="F19" s="7">
-        <v>0.055807</v>
+        <v>0.06116</v>
       </c>
       <c r="G19" s="7">
-        <v>0.212927</v>
+        <v>0.22360499999999997</v>
       </c>
       <c r="H19" s="7">
-        <v>0.111854</v>
+        <v>0.12097300000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0.42900799999999994</v>
+        <v>0.440729</v>
       </c>
       <c r="J19" s="7">
-        <v>2.149657</v>
+        <v>2.159137</v>
       </c>
       <c r="K19" s="7">
-        <v>7.006992</v>
+        <v>7.012971</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2944,25 +2944,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.045419999999999995</v>
+        <v>0.05012</v>
       </c>
       <c r="F20" s="7">
-        <v>0.089631</v>
+        <v>0.09745799999999999</v>
       </c>
       <c r="G20" s="7">
-        <v>0.238204</v>
+        <v>0.243903</v>
       </c>
       <c r="H20" s="7">
-        <v>0.087407</v>
+        <v>0.093486</v>
       </c>
       <c r="I20" s="7">
-        <v>0.46183100000000005</v>
+        <v>0.470003</v>
       </c>
       <c r="J20" s="7">
-        <v>1.470545</v>
+        <v>1.4772880000000002</v>
       </c>
       <c r="K20" s="7">
-        <v>4.21787</v>
+        <v>4.22082</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,25 +2979,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.044509999999999994</v>
+        <v>0.044355000000000006</v>
       </c>
       <c r="F21" s="7">
-        <v>0.096559</v>
+        <v>0.100135</v>
       </c>
       <c r="G21" s="7">
-        <v>0.212258</v>
+        <v>0.216329</v>
       </c>
       <c r="H21" s="7">
-        <v>0.146654</v>
+        <v>0.14971500000000001</v>
       </c>
       <c r="I21" s="7">
-        <v>0.45643500000000004</v>
+        <v>0.460322</v>
       </c>
       <c r="J21" s="7">
-        <v>1.811481</v>
+        <v>1.815404</v>
       </c>
       <c r="K21" s="7">
-        <v>5.066891</v>
+        <v>5.039433</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,25 +3014,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.101935</v>
+        <v>0.119698</v>
       </c>
       <c r="F22" s="7">
-        <v>0.09323100000000001</v>
+        <v>0.10734</v>
       </c>
       <c r="G22" s="7">
-        <v>0.247237</v>
+        <v>0.259695</v>
       </c>
       <c r="H22" s="7">
-        <v>0.238655</v>
+        <v>0.249944</v>
       </c>
       <c r="I22" s="7">
-        <v>0.570492</v>
+        <v>0.584806</v>
       </c>
       <c r="J22" s="7">
-        <v>2.745779</v>
+        <v>2.7817570000000003</v>
       </c>
       <c r="K22" s="7">
-        <v>10.878986</v>
+        <v>10.829309</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,25 +3049,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.027992</v>
+        <v>0.026452</v>
       </c>
       <c r="F23" s="7">
-        <v>0.081349</v>
+        <v>0.081425</v>
       </c>
       <c r="G23" s="7">
-        <v>0.183974</v>
+        <v>0.184056</v>
       </c>
       <c r="H23" s="7">
-        <v>0.11448</v>
+        <v>0.115724</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40456000000000003</v>
+        <v>0.406128</v>
       </c>
       <c r="J23" s="7">
-        <v>2.161711</v>
+        <v>2.158776</v>
       </c>
       <c r="K23" s="7">
-        <v>4.987557</v>
+        <v>4.986154</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3084,25 +3084,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.050789</v>
+        <v>0.0492</v>
       </c>
       <c r="F24" s="7">
-        <v>0.011568</v>
+        <v>0.013323</v>
       </c>
       <c r="G24" s="7">
-        <v>0.154092</v>
+        <v>0.149129</v>
       </c>
       <c r="H24" s="7">
-        <v>0.041958999999999996</v>
+        <v>0.040845</v>
       </c>
       <c r="I24" s="7">
-        <v>0.398228</v>
+        <v>0.39673200000000003</v>
       </c>
       <c r="J24" s="7">
-        <v>1.607593</v>
+        <v>1.606727</v>
       </c>
       <c r="K24" s="7">
-        <v>3.461074</v>
+        <v>3.453198</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,25 +3119,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.038515</v>
+        <v>0.047893</v>
       </c>
       <c r="F25" s="7">
-        <v>0.040881</v>
+        <v>0.041845999999999994</v>
       </c>
       <c r="G25" s="7">
-        <v>0.119175</v>
+        <v>0.12064399999999999</v>
       </c>
       <c r="H25" s="7">
-        <v>0.054351000000000003</v>
+        <v>0.055851</v>
       </c>
       <c r="I25" s="7">
-        <v>0.34513599999999994</v>
+        <v>0.347049</v>
       </c>
       <c r="J25" s="7">
-        <v>2.128839</v>
+        <v>2.120494</v>
       </c>
       <c r="K25" s="7">
-        <v>6.4237530000000005</v>
+        <v>6.488848000000001</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,25 +3154,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.038157</v>
+        <v>0.052698</v>
       </c>
       <c r="F26" s="7">
-        <v>0.023495</v>
+        <v>0.027589000000000002</v>
       </c>
       <c r="G26" s="7">
-        <v>0.11428</v>
+        <v>0.11793</v>
       </c>
       <c r="H26" s="7">
-        <v>0.049516</v>
+        <v>0.05540199999999999</v>
       </c>
       <c r="I26" s="7">
-        <v>0.307187</v>
+        <v>0.31451799999999996</v>
       </c>
       <c r="J26" s="7">
-        <v>2.049133</v>
+        <v>2.058769</v>
       </c>
       <c r="K26" s="7">
-        <v>5.561159</v>
+        <v>5.672947000000001</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3189,25 +3189,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.092894</v>
+        <v>0.10095499999999999</v>
       </c>
       <c r="F27" s="7">
-        <v>0.044332</v>
+        <v>0.057815000000000005</v>
       </c>
       <c r="G27" s="7">
-        <v>0.226989</v>
+        <v>0.244451</v>
       </c>
       <c r="H27" s="7">
-        <v>0.19980399999999998</v>
+        <v>0.20437999999999998</v>
       </c>
       <c r="I27" s="7">
-        <v>0.395051</v>
+        <v>0.40037100000000003</v>
       </c>
       <c r="J27" s="7">
-        <v>3.2412150000000004</v>
+        <v>3.237899</v>
       </c>
       <c r="K27" s="7">
-        <v>16.749001</v>
+        <v>16.509776</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,25 +3224,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.093353</v>
+        <v>0.117985</v>
       </c>
       <c r="F28" s="7">
-        <v>0.052018</v>
+        <v>0.058103999999999996</v>
       </c>
       <c r="G28" s="7">
-        <v>0.132502</v>
+        <v>0.135974</v>
       </c>
       <c r="H28" s="7">
-        <v>0.10162900000000001</v>
+        <v>0.110649</v>
       </c>
       <c r="I28" s="7">
-        <v>0.421168</v>
+        <v>0.432804</v>
       </c>
       <c r="J28" s="7">
-        <v>2.585288</v>
+        <v>2.59673</v>
       </c>
       <c r="K28" s="7">
-        <v>7.9066920000000005</v>
+        <v>8.038272</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3259,25 +3259,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.039095</v>
+        <v>0.037871999999999996</v>
       </c>
       <c r="F29" s="7">
-        <v>0.059122</v>
+        <v>0.059623</v>
       </c>
       <c r="G29" s="7">
-        <v>0.178042</v>
+        <v>0.17670200000000003</v>
       </c>
       <c r="H29" s="7">
-        <v>0.09896100000000001</v>
+        <v>0.098376</v>
       </c>
       <c r="I29" s="7">
-        <v>0.409518</v>
+        <v>0.408767</v>
       </c>
       <c r="J29" s="7">
-        <v>2.420731</v>
+        <v>2.412494</v>
       </c>
       <c r="K29" s="7">
-        <v>4.585162</v>
+        <v>4.577243</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3294,25 +3294,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.052863</v>
+        <v>0.057895</v>
       </c>
       <c r="F30" s="7">
-        <v>0.040152</v>
+        <v>0.047831</v>
       </c>
       <c r="G30" s="7">
-        <v>0.192377</v>
+        <v>0.20011299999999999</v>
       </c>
       <c r="H30" s="7">
-        <v>0.150038</v>
+        <v>0.152937</v>
       </c>
       <c r="I30" s="7">
-        <v>0.376416</v>
+        <v>0.37988700000000003</v>
       </c>
       <c r="J30" s="7">
-        <v>3.0167219999999997</v>
+        <v>3.0131349999999997</v>
       </c>
       <c r="K30" s="7">
-        <v>9.628103</v>
+        <v>9.572973</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,25 +3329,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.10855000000000001</v>
+        <v>0.120794</v>
       </c>
       <c r="F31" s="7">
-        <v>0.059036</v>
+        <v>0.07258200000000001</v>
       </c>
       <c r="G31" s="7">
-        <v>0.229346</v>
+        <v>0.24970099999999998</v>
       </c>
       <c r="H31" s="7">
-        <v>0.205449</v>
+        <v>0.213902</v>
       </c>
       <c r="I31" s="7">
-        <v>0.345026</v>
+        <v>0.354459</v>
       </c>
       <c r="J31" s="7">
-        <v>2.504706</v>
+        <v>2.517842</v>
       </c>
       <c r="K31" s="7">
-        <v>15.083154</v>
+        <v>14.996533</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3364,25 +3364,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.031946</v>
+        <v>0.030202</v>
       </c>
       <c r="F32" s="7">
-        <v>0.085912</v>
+        <v>0.086154</v>
       </c>
       <c r="G32" s="7">
-        <v>0.193296</v>
+        <v>0.19426100000000002</v>
       </c>
       <c r="H32" s="7">
-        <v>0.111362</v>
+        <v>0.112599</v>
       </c>
       <c r="I32" s="7">
-        <v>0.45122300000000004</v>
+        <v>0.452838</v>
       </c>
       <c r="J32" s="7">
-        <v>2.157038</v>
+        <v>2.1572389999999997</v>
       </c>
       <c r="K32" s="7">
-        <v>3.718406</v>
+        <v>3.721418</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3399,25 +3399,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.079039</v>
+        <v>0.081534</v>
       </c>
       <c r="F33" s="7">
-        <v>0.056066000000000005</v>
+        <v>0.065621</v>
       </c>
       <c r="G33" s="7">
-        <v>0.23433199999999998</v>
+        <v>0.247946</v>
       </c>
       <c r="H33" s="7">
-        <v>0.18225100000000002</v>
+        <v>0.18502</v>
       </c>
       <c r="I33" s="7">
-        <v>0.443839</v>
+        <v>0.447222</v>
       </c>
       <c r="J33" s="7">
-        <v>3.47495</v>
+        <v>3.456451</v>
       </c>
       <c r="K33" s="7">
-        <v>16.96659</v>
+        <v>16.709628</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3434,25 +3434,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.091088</v>
+        <v>0.10757</v>
       </c>
       <c r="F34" s="7">
-        <v>0.113048</v>
+        <v>0.126065</v>
       </c>
       <c r="G34" s="7">
-        <v>0.32394100000000003</v>
+        <v>0.339532</v>
       </c>
       <c r="H34" s="7">
-        <v>0.262375</v>
+        <v>0.276678</v>
       </c>
       <c r="I34" s="7">
-        <v>0.633661</v>
+        <v>0.65217</v>
       </c>
       <c r="J34" s="7">
-        <v>3.1600170000000003</v>
+        <v>3.1708730000000003</v>
       </c>
       <c r="K34" s="7">
-        <v>9.778759</v>
+        <v>9.808775</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3469,25 +3469,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.092927</v>
+        <v>0.108658</v>
       </c>
       <c r="F35" s="7">
-        <v>0.095862</v>
+        <v>0.110654</v>
       </c>
       <c r="G35" s="7">
-        <v>0.329306</v>
+        <v>0.34596</v>
       </c>
       <c r="H35" s="7">
-        <v>0.26644</v>
+        <v>0.282035</v>
       </c>
       <c r="I35" s="7">
-        <v>0.6809919999999999</v>
+        <v>0.701692</v>
       </c>
       <c r="J35" s="7">
-        <v>3.335241</v>
+        <v>3.347779</v>
       </c>
       <c r="K35" s="7">
-        <v>12.313277000000001</v>
+        <v>12.321605</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3504,25 +3504,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.081646</v>
+        <v>0.082378</v>
       </c>
       <c r="F36" s="7">
-        <v>0.061003</v>
+        <v>0.068756</v>
       </c>
       <c r="G36" s="7">
-        <v>0.244028</v>
+        <v>0.255819</v>
       </c>
       <c r="H36" s="7">
-        <v>0.19433</v>
+        <v>0.19546500000000003</v>
       </c>
       <c r="I36" s="7">
-        <v>0.467819</v>
+        <v>0.469215</v>
       </c>
       <c r="J36" s="7">
-        <v>3.564671</v>
+        <v>3.549448</v>
       </c>
       <c r="K36" s="7">
-        <v>17.709032999999998</v>
+        <v>17.436135</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3539,25 +3539,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.07151</v>
+        <v>0.071604</v>
       </c>
       <c r="F37" s="7">
-        <v>0.066088</v>
+        <v>0.070515</v>
       </c>
       <c r="G37" s="7">
-        <v>0.25409400000000004</v>
+        <v>0.260463</v>
       </c>
       <c r="H37" s="7">
-        <v>0.175201</v>
+        <v>0.175227</v>
       </c>
       <c r="I37" s="7">
-        <v>0.458846</v>
+        <v>0.458878</v>
       </c>
       <c r="J37" s="7">
-        <v>3.655974</v>
+        <v>3.641582</v>
       </c>
       <c r="K37" s="7">
-        <v>15.958832</v>
+        <v>15.748729</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3574,25 +3574,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.054264</v>
+        <v>0.052176</v>
       </c>
       <c r="F38" s="7">
-        <v>0.053794</v>
+        <v>0.057013</v>
       </c>
       <c r="G38" s="7">
-        <v>0.22253900000000001</v>
+        <v>0.226985</v>
       </c>
       <c r="H38" s="7">
-        <v>0.15385400000000002</v>
+        <v>0.153999</v>
       </c>
       <c r="I38" s="7">
-        <v>0.456738</v>
+        <v>0.456921</v>
       </c>
       <c r="J38" s="7">
-        <v>3.523664</v>
+        <v>3.5041629999999997</v>
       </c>
       <c r="K38" s="7">
-        <v>11.779214999999999</v>
+        <v>11.685304</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3609,25 +3609,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.037117</v>
+        <v>0.036416</v>
       </c>
       <c r="F39" s="7">
-        <v>0.069348</v>
+        <v>0.07013899999999999</v>
       </c>
       <c r="G39" s="7">
-        <v>0.198572</v>
+        <v>0.198617</v>
       </c>
       <c r="H39" s="7">
-        <v>0.11736</v>
+        <v>0.118385</v>
       </c>
       <c r="I39" s="7">
-        <v>0.466069</v>
+        <v>0.467414</v>
       </c>
       <c r="J39" s="7">
-        <v>2.961999</v>
+        <v>2.9589190000000003</v>
       </c>
       <c r="K39" s="7">
-        <v>5.700105</v>
+        <v>5.701936</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,25 +3644,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.08607300000000001</v>
+        <v>0.093672</v>
       </c>
       <c r="F40" s="7">
-        <v>0.130086</v>
+        <v>0.135387</v>
       </c>
       <c r="G40" s="7">
-        <v>0.306209</v>
+        <v>0.316765</v>
       </c>
       <c r="H40" s="7">
-        <v>0.23689900000000003</v>
+        <v>0.242775</v>
       </c>
       <c r="I40" s="7">
-        <v>0.611692</v>
+        <v>0.619348</v>
       </c>
       <c r="J40" s="7">
-        <v>3.392686</v>
+        <v>3.388379</v>
       </c>
       <c r="K40" s="7">
-        <v>11.921409</v>
+        <v>11.812531</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3679,25 +3679,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.069974</v>
+        <v>0.077082</v>
       </c>
       <c r="F41" s="7">
-        <v>0.12044600000000001</v>
+        <v>0.12609700000000001</v>
       </c>
       <c r="G41" s="7">
-        <v>0.286015</v>
+        <v>0.296261</v>
       </c>
       <c r="H41" s="7">
-        <v>0.213261</v>
+        <v>0.220215</v>
       </c>
       <c r="I41" s="7">
-        <v>0.59961</v>
+        <v>0.608779</v>
       </c>
       <c r="J41" s="7">
-        <v>3.116686</v>
+        <v>3.1268200000000004</v>
       </c>
       <c r="K41" s="7">
-        <v>10.123042</v>
+        <v>10.094076</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,25 +3714,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.08619199999999999</v>
+        <v>0.100165</v>
       </c>
       <c r="F42" s="7">
-        <v>0.078702</v>
+        <v>0.09479599999999999</v>
       </c>
       <c r="G42" s="7">
-        <v>0.2962</v>
+        <v>0.310635</v>
       </c>
       <c r="H42" s="7">
-        <v>0.245064</v>
+        <v>0.256049</v>
       </c>
       <c r="I42" s="7">
-        <v>0.547079</v>
+        <v>0.560728</v>
       </c>
       <c r="J42" s="7">
-        <v>3.101765</v>
+        <v>3.105258</v>
       </c>
       <c r="K42" s="7">
-        <v>10.935085999999998</v>
+        <v>10.948894000000001</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3749,25 +3749,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.093297</v>
+        <v>0.098956</v>
       </c>
       <c r="F43" s="7">
-        <v>0.048605</v>
+        <v>0.060452000000000006</v>
       </c>
       <c r="G43" s="7">
-        <v>0.247928</v>
+        <v>0.264176</v>
       </c>
       <c r="H43" s="7">
-        <v>0.19342800000000002</v>
+        <v>0.19783</v>
       </c>
       <c r="I43" s="7">
-        <v>0.462688</v>
+        <v>0.468083</v>
       </c>
       <c r="J43" s="7">
-        <v>3.9953519999999996</v>
+        <v>3.996061</v>
       </c>
       <c r="K43" s="7">
-        <v>21.995587</v>
+        <v>21.713801</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3784,25 +3784,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.046585999999999995</v>
+        <v>0.04562</v>
       </c>
       <c r="F44" s="7">
-        <v>0.069655</v>
+        <v>0.069543</v>
       </c>
       <c r="G44" s="7">
-        <v>0.20456600000000003</v>
+        <v>0.20369800000000002</v>
       </c>
       <c r="H44" s="7">
-        <v>0.115145</v>
+        <v>0.115663</v>
       </c>
       <c r="I44" s="7">
-        <v>0.478056</v>
+        <v>0.478744</v>
       </c>
       <c r="J44" s="7">
-        <v>2.45357</v>
+        <v>2.455994</v>
       </c>
       <c r="K44" s="7">
-        <v>4.45951</v>
+        <v>4.46001</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3819,25 +3819,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.069073</v>
+        <v>0.081941</v>
       </c>
       <c r="F45" s="7">
-        <v>0.071287</v>
+        <v>0.086463</v>
       </c>
       <c r="G45" s="7">
-        <v>0.27951</v>
+        <v>0.292885</v>
       </c>
       <c r="H45" s="7">
-        <v>0.208377</v>
+        <v>0.218877</v>
       </c>
       <c r="I45" s="7">
-        <v>0.5548879999999999</v>
+        <v>0.568399</v>
       </c>
       <c r="J45" s="7">
-        <v>3.207976</v>
+        <v>3.211895</v>
       </c>
       <c r="K45" s="7">
-        <v>9.550215</v>
+        <v>9.587705999999999</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3854,25 +3854,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.074026</v>
+        <v>0.08108</v>
       </c>
       <c r="F46" s="7">
-        <v>0.13065</v>
+        <v>0.135839</v>
       </c>
       <c r="G46" s="7">
-        <v>0.311575</v>
+        <v>0.322402</v>
       </c>
       <c r="H46" s="7">
-        <v>0.246061</v>
+        <v>0.253689</v>
       </c>
       <c r="I46" s="7">
-        <v>0.610038</v>
+        <v>0.619895</v>
       </c>
       <c r="J46" s="7">
-        <v>3.470183</v>
+        <v>3.486014</v>
       </c>
       <c r="K46" s="7">
-        <v>10.422457</v>
+        <v>10.369219000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3889,25 +3889,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.08755800000000001</v>
+        <v>0.099085</v>
       </c>
       <c r="F47" s="7">
-        <v>0.116618</v>
+        <v>0.125782</v>
       </c>
       <c r="G47" s="7">
-        <v>0.298232</v>
+        <v>0.31497800000000004</v>
       </c>
       <c r="H47" s="7">
-        <v>0.245657</v>
+        <v>0.255521</v>
       </c>
       <c r="I47" s="7">
-        <v>0.5980960000000001</v>
+        <v>0.61075</v>
       </c>
       <c r="J47" s="7">
-        <v>3.5467700000000004</v>
+        <v>3.559368</v>
       </c>
       <c r="K47" s="7">
-        <v>13.336024</v>
+        <v>13.266043999999999</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3924,25 +3924,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.07699600000000001</v>
+        <v>0.07622899999999999</v>
       </c>
       <c r="F48" s="7">
-        <v>0.04657</v>
+        <v>0.048780000000000004</v>
       </c>
       <c r="G48" s="7">
-        <v>0.16200399999999998</v>
+        <v>0.177758</v>
       </c>
       <c r="H48" s="7">
-        <v>0.156759</v>
+        <v>0.158212</v>
       </c>
       <c r="I48" s="7">
-        <v>0.425361</v>
+        <v>0.427151</v>
       </c>
       <c r="J48" s="7">
-        <v>1.7413370000000001</v>
+        <v>1.724159</v>
       </c>
       <c r="K48" s="7">
-        <v>10.572175999999999</v>
+        <v>10.459137</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3959,25 +3959,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.10377</v>
+        <v>0.11817399999999999</v>
       </c>
       <c r="F49" s="7">
-        <v>0.084968</v>
+        <v>0.100051</v>
       </c>
       <c r="G49" s="7">
-        <v>0.316482</v>
+        <v>0.33204</v>
       </c>
       <c r="H49" s="7">
-        <v>0.254009</v>
+        <v>0.26414000000000004</v>
       </c>
       <c r="I49" s="7">
-        <v>0.555758</v>
+        <v>0.5683279999999999</v>
       </c>
       <c r="J49" s="7">
-        <v>3.5773719999999996</v>
+        <v>3.6044439999999995</v>
       </c>
       <c r="K49" s="7">
-        <v>16.291075</v>
+        <v>16.25254</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3994,25 +3994,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.101891</v>
+        <v>0.12551500000000002</v>
       </c>
       <c r="F50" s="7">
-        <v>0.069322</v>
+        <v>0.073517</v>
       </c>
       <c r="G50" s="7">
-        <v>0.157402</v>
+        <v>0.158773</v>
       </c>
       <c r="H50" s="7">
-        <v>0.117016</v>
+        <v>0.123805</v>
       </c>
       <c r="I50" s="7">
-        <v>0.543659</v>
+        <v>0.553041</v>
       </c>
       <c r="J50" s="7">
-        <v>3.057493</v>
+        <v>3.058145</v>
       </c>
       <c r="K50" s="7">
-        <v>8.873721</v>
+        <v>8.972086000000001</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,25 +4029,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.061667</v>
+        <v>0.067296</v>
       </c>
       <c r="F51" s="7">
-        <v>0.038987</v>
+        <v>0.043285</v>
       </c>
       <c r="G51" s="7">
-        <v>0.190686</v>
+        <v>0.197209</v>
       </c>
       <c r="H51" s="7">
-        <v>0.130892</v>
+        <v>0.133706</v>
       </c>
       <c r="I51" s="7">
-        <v>0.36717700000000003</v>
+        <v>0.370579</v>
       </c>
       <c r="J51" s="7">
-        <v>2.543937</v>
+        <v>2.53861</v>
       </c>
       <c r="K51" s="7">
-        <v>8.175655</v>
+        <v>8.179</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.108211</v>
+        <v>0.124347</v>
       </c>
       <c r="F52" s="7">
-        <v>0.049991</v>
+        <v>0.065258</v>
       </c>
       <c r="G52" s="7">
-        <v>0.262554</v>
+        <v>0.282287</v>
       </c>
       <c r="H52" s="7">
-        <v>0.204296</v>
+        <v>0.212767</v>
       </c>
       <c r="I52" s="7">
-        <v>0.469195</v>
+        <v>0.479529</v>
       </c>
       <c r="J52" s="7">
-        <v>2.648562</v>
+        <v>2.661221</v>
       </c>
       <c r="K52" s="7">
-        <v>11.172899</v>
+        <v>11.124423</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4099,25 +4099,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.050570000000000004</v>
+        <v>0.066722</v>
       </c>
       <c r="F53" s="7">
-        <v>0.033925000000000004</v>
+        <v>0.035147</v>
       </c>
       <c r="G53" s="7">
-        <v>0.10008800000000001</v>
+        <v>0.100068</v>
       </c>
       <c r="H53" s="7">
-        <v>0.046816</v>
+        <v>0.048541</v>
       </c>
       <c r="I53" s="7">
-        <v>0.344259</v>
+        <v>0.34647399999999995</v>
       </c>
       <c r="J53" s="7">
-        <v>2.219312</v>
+        <v>2.204005</v>
       </c>
       <c r="K53" s="7">
-        <v>6.4529700000000005</v>
+        <v>6.512219</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4134,25 +4134,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.039396</v>
+        <v>0.049296</v>
       </c>
       <c r="F54" s="7">
-        <v>0.035802</v>
+        <v>0.037469999999999996</v>
       </c>
       <c r="G54" s="7">
-        <v>0.099077</v>
+        <v>0.099579</v>
       </c>
       <c r="H54" s="7">
-        <v>0.051738</v>
+        <v>0.053612</v>
       </c>
       <c r="I54" s="7">
-        <v>0.30845300000000003</v>
+        <v>0.310785</v>
       </c>
       <c r="J54" s="7">
-        <v>2.075336</v>
+        <v>2.071164</v>
       </c>
       <c r="K54" s="7">
-        <v>6.256252</v>
+        <v>6.322551</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4169,25 +4169,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.0378</v>
+        <v>0.040229</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.061482999999999996</v>
+        <v>-0.068524</v>
       </c>
       <c r="G55" s="7">
-        <v>0.162044</v>
+        <v>0.178209</v>
       </c>
       <c r="H55" s="7">
-        <v>0.088463</v>
+        <v>0.088835</v>
       </c>
       <c r="I55" s="7">
-        <v>0.63024</v>
+        <v>0.630797</v>
       </c>
       <c r="J55" s="7">
-        <v>4.0682279999999995</v>
+        <v>4.022743</v>
       </c>
       <c r="K55" s="7">
-        <v>13.261641</v>
+        <v>13.357266</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4204,25 +4204,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.079389</v>
+        <v>0.08680500000000001</v>
       </c>
       <c r="F56" s="7">
-        <v>0.08436</v>
+        <v>0.090358</v>
       </c>
       <c r="G56" s="7">
-        <v>0.249207</v>
+        <v>0.252556</v>
       </c>
       <c r="H56" s="7">
-        <v>0.150031</v>
+        <v>0.15407500000000002</v>
       </c>
       <c r="I56" s="7">
-        <v>0.47720799999999997</v>
+        <v>0.48240299999999997</v>
       </c>
       <c r="J56" s="7">
-        <v>2.035556</v>
+        <v>2.052474</v>
       </c>
       <c r="K56" s="7">
-        <v>5.741592000000001</v>
+        <v>5.743877</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4239,25 +4239,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.058341000000000004</v>
+        <v>0.057512999999999995</v>
       </c>
       <c r="F57" s="7">
-        <v>0.013130999999999999</v>
+        <v>0.015212000000000002</v>
       </c>
       <c r="G57" s="7">
-        <v>0.144401</v>
+        <v>0.143962</v>
       </c>
       <c r="H57" s="7">
-        <v>0.074398</v>
+        <v>0.073102</v>
       </c>
       <c r="I57" s="7">
-        <v>0.373389</v>
+        <v>0.371732</v>
       </c>
       <c r="J57" s="7">
-        <v>1.3421789999999998</v>
+        <v>1.346549</v>
       </c>
       <c r="K57" s="7">
-        <v>3.636886</v>
+        <v>3.616961</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4274,25 +4274,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.075072</v>
+        <v>0.089536</v>
       </c>
       <c r="F58" s="7">
-        <v>0.06816</v>
+        <v>0.081798</v>
       </c>
       <c r="G58" s="7">
-        <v>0.291632</v>
+        <v>0.303</v>
       </c>
       <c r="H58" s="7">
-        <v>0.219711</v>
+        <v>0.22983399999999998</v>
       </c>
       <c r="I58" s="7">
-        <v>0.559964</v>
+        <v>0.572911</v>
       </c>
       <c r="J58" s="7">
-        <v>3.1852229999999997</v>
+        <v>3.1860969999999997</v>
       </c>
       <c r="K58" s="7">
-        <v>9.638825</v>
+        <v>9.67333</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4309,25 +4309,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.085754</v>
+        <v>0.10017899999999999</v>
       </c>
       <c r="F59" s="7">
-        <v>0.08225400000000001</v>
+        <v>0.098277</v>
       </c>
       <c r="G59" s="7">
-        <v>0.306446</v>
+        <v>0.320957</v>
       </c>
       <c r="H59" s="7">
-        <v>0.24897099999999997</v>
+        <v>0.260019</v>
       </c>
       <c r="I59" s="7">
-        <v>0.5536760000000001</v>
+        <v>0.567419</v>
       </c>
       <c r="J59" s="7">
-        <v>3.152557</v>
+        <v>3.182025</v>
       </c>
       <c r="K59" s="7">
-        <v>10.815681</v>
+        <v>10.831698</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4344,25 +4344,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.09863200000000001</v>
+        <v>0.105699</v>
       </c>
       <c r="F60" s="7">
-        <v>0.059756000000000004</v>
+        <v>0.069866</v>
       </c>
       <c r="G60" s="7">
-        <v>0.225468</v>
+        <v>0.232812</v>
       </c>
       <c r="H60" s="7">
-        <v>0.195867</v>
+        <v>0.19957799999999998</v>
       </c>
       <c r="I60" s="7">
-        <v>0.414335</v>
+        <v>0.418724</v>
       </c>
       <c r="J60" s="7">
-        <v>2.3851400000000003</v>
+        <v>2.387928</v>
       </c>
       <c r="K60" s="7">
-        <v>13.503597</v>
+        <v>13.302159999999999</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,25 +4379,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.09001300000000001</v>
+        <v>0.10718899999999999</v>
       </c>
       <c r="F61" s="7">
-        <v>0.067371</v>
+        <v>0.077335</v>
       </c>
       <c r="G61" s="7">
-        <v>0.204466</v>
+        <v>0.21235600000000002</v>
       </c>
       <c r="H61" s="7">
-        <v>0.16331700000000002</v>
+        <v>0.171327</v>
       </c>
       <c r="I61" s="7">
-        <v>0.49979799999999996</v>
+        <v>0.510125</v>
       </c>
       <c r="J61" s="7">
-        <v>2.383442</v>
+        <v>2.4584710000000003</v>
       </c>
       <c r="K61" s="7">
-        <v>7.797484</v>
+        <v>7.768763</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,25 +4414,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.08598499999999999</v>
+        <v>0.080801</v>
       </c>
       <c r="F62" s="7">
-        <v>0.055007</v>
+        <v>0.053893</v>
       </c>
       <c r="G62" s="7">
-        <v>0.172804</v>
+        <v>0.186278</v>
       </c>
       <c r="H62" s="7">
-        <v>0.173274</v>
+        <v>0.161035</v>
       </c>
       <c r="I62" s="7">
-        <v>0.35857999999999995</v>
+        <v>0.344407</v>
       </c>
       <c r="J62" s="7">
-        <v>2.372395</v>
+        <v>2.347966</v>
       </c>
       <c r="K62" s="7">
-        <v>12.924562000000002</v>
+        <v>12.645551000000001</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4449,25 +4449,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.059268</v>
+        <v>0.060439</v>
       </c>
       <c r="F63" s="7">
-        <v>0.021038</v>
+        <v>0.027069</v>
       </c>
       <c r="G63" s="7">
-        <v>0.18787500000000001</v>
+        <v>0.188414</v>
       </c>
       <c r="H63" s="7">
-        <v>0.08971399999999999</v>
+        <v>0.091267</v>
       </c>
       <c r="I63" s="7">
-        <v>0.409655</v>
+        <v>0.41166400000000003</v>
       </c>
       <c r="J63" s="7">
-        <v>1.9176570000000002</v>
+        <v>1.921625</v>
       </c>
       <c r="K63" s="7">
-        <v>4.7206790000000005</v>
+        <v>4.707234000000001</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4484,25 +4484,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.054299999999999994</v>
+        <v>0.057059</v>
       </c>
       <c r="F64" s="7">
-        <v>0.017186</v>
+        <v>0.01914</v>
       </c>
       <c r="G64" s="7">
-        <v>0.17788199999999998</v>
+        <v>0.189334</v>
       </c>
       <c r="H64" s="7">
-        <v>0.143253</v>
+        <v>0.145449</v>
       </c>
       <c r="I64" s="7">
-        <v>0.400723</v>
+        <v>0.40341299999999997</v>
       </c>
       <c r="J64" s="7">
-        <v>2.037765</v>
+        <v>2.039473</v>
       </c>
       <c r="K64" s="7">
-        <v>6.179417</v>
+        <v>6.198828</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,25 +4519,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.036614</v>
+        <v>0.04478</v>
       </c>
       <c r="F65" s="7">
-        <v>0.043486000000000004</v>
+        <v>0.045240999999999996</v>
       </c>
       <c r="G65" s="7">
-        <v>0.104252</v>
+        <v>0.106418</v>
       </c>
       <c r="H65" s="7">
-        <v>0.060441</v>
+        <v>0.062338</v>
       </c>
       <c r="I65" s="7">
-        <v>0.299817</v>
+        <v>0.302141</v>
       </c>
       <c r="J65" s="7">
-        <v>2.078154</v>
+        <v>2.081386</v>
       </c>
       <c r="K65" s="7">
-        <v>5.2785779999999995</v>
+        <v>5.3587</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4554,25 +4554,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.043985</v>
+        <v>0.05766</v>
       </c>
       <c r="F66" s="7">
-        <v>0.035109</v>
+        <v>0.036236000000000004</v>
       </c>
       <c r="G66" s="7">
-        <v>0.09376899999999999</v>
+        <v>0.09457</v>
       </c>
       <c r="H66" s="7">
-        <v>0.04182</v>
+        <v>0.0435</v>
       </c>
       <c r="I66" s="7">
-        <v>0.32565500000000003</v>
+        <v>0.327793</v>
       </c>
       <c r="J66" s="7">
-        <v>2.330626</v>
+        <v>2.313132</v>
       </c>
       <c r="K66" s="7">
-        <v>6.738518</v>
+        <v>6.812385000000001</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4589,25 +4589,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.07284600000000001</v>
+        <v>0.082886</v>
       </c>
       <c r="F67" s="7">
-        <v>0.064105</v>
+        <v>0.072894</v>
       </c>
       <c r="G67" s="7">
-        <v>0.246752</v>
+        <v>0.262869</v>
       </c>
       <c r="H67" s="7">
-        <v>0.195864</v>
+        <v>0.20540299999999997</v>
       </c>
       <c r="I67" s="7">
-        <v>0.5526059999999999</v>
+        <v>0.564991</v>
       </c>
       <c r="J67" s="7">
-        <v>2.5536060000000003</v>
+        <v>2.569757</v>
       </c>
       <c r="K67" s="7">
-        <v>9.488927</v>
+        <v>9.551429</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4624,25 +4624,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.038583</v>
+        <v>0.049227</v>
       </c>
       <c r="F68" s="7">
-        <v>0.035487000000000005</v>
+        <v>0.036934999999999996</v>
       </c>
       <c r="G68" s="7">
-        <v>0.094433</v>
+        <v>0.095976</v>
       </c>
       <c r="H68" s="7">
-        <v>0.046596</v>
+        <v>0.04901900000000001</v>
       </c>
       <c r="I68" s="7">
-        <v>0.298277</v>
+        <v>0.30128299999999997</v>
       </c>
       <c r="J68" s="7">
-        <v>2.0909139999999997</v>
+        <v>2.084766</v>
       </c>
       <c r="K68" s="7">
-        <v>6.103958</v>
+        <v>6.179785000000001</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4659,25 +4659,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.068773</v>
+        <v>0.07241399999999999</v>
       </c>
       <c r="F69" s="7">
-        <v>0.050294</v>
+        <v>0.054869</v>
       </c>
       <c r="G69" s="7">
-        <v>0.217119</v>
+        <v>0.21854700000000002</v>
       </c>
       <c r="H69" s="7">
-        <v>0.126718</v>
+        <v>0.128726</v>
       </c>
       <c r="I69" s="7">
-        <v>0.47308900000000004</v>
+        <v>0.47571399999999997</v>
       </c>
       <c r="J69" s="7">
-        <v>2.167225</v>
+        <v>2.174375</v>
       </c>
       <c r="K69" s="7">
-        <v>5.596254</v>
+        <v>5.586664</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,25 +4694,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.032201</v>
+        <v>0.030271</v>
       </c>
       <c r="F70" s="7">
-        <v>0.09445100000000001</v>
+        <v>0.094634</v>
       </c>
       <c r="G70" s="7">
-        <v>0.201496</v>
+        <v>0.201582</v>
       </c>
       <c r="H70" s="7">
-        <v>0.12201599999999999</v>
+        <v>0.123308</v>
       </c>
       <c r="I70" s="7">
-        <v>0.479126</v>
+        <v>0.480828</v>
       </c>
       <c r="J70" s="7">
-        <v>2.344546</v>
+        <v>2.346101</v>
       </c>
       <c r="K70" s="7">
-        <v>4.041405</v>
+        <v>4.044801</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4729,25 +4729,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.19064599999999998</v>
+        <v>0.242755</v>
       </c>
       <c r="F71" s="7">
-        <v>0.12329499999999999</v>
+        <v>0.11545899999999999</v>
       </c>
       <c r="G71" s="7">
-        <v>0.16396</v>
+        <v>0.154011</v>
       </c>
       <c r="H71" s="7">
-        <v>0.164877</v>
+        <v>0.17112100000000002</v>
       </c>
       <c r="I71" s="7">
-        <v>0.7132970000000001</v>
+        <v>0.722482</v>
       </c>
       <c r="J71" s="7">
-        <v>3.821131</v>
+        <v>3.7664139999999997</v>
       </c>
       <c r="K71" s="7">
-        <v>7.436866</v>
+        <v>7.622401999999999</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4764,25 +4764,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.044319</v>
+        <v>0.047213000000000005</v>
       </c>
       <c r="F72" s="7">
-        <v>0.07622</v>
+        <v>0.080751</v>
       </c>
       <c r="G72" s="7">
-        <v>0.225408</v>
+        <v>0.228991</v>
       </c>
       <c r="H72" s="7">
-        <v>0.133963</v>
+        <v>0.138212</v>
       </c>
       <c r="I72" s="7">
-        <v>0.44847299999999996</v>
+        <v>0.4539</v>
       </c>
       <c r="J72" s="7">
-        <v>1.733671</v>
+        <v>1.741012</v>
       </c>
       <c r="K72" s="7">
-        <v>4.650503</v>
+        <v>4.662631999999999</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,25 +4799,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.056757</v>
+        <v>0.07126299999999999</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.009364</v>
+        <v>-0.0068130000000000005</v>
       </c>
       <c r="G73" s="7">
-        <v>0.051048</v>
+        <v>0.052181</v>
       </c>
       <c r="H73" s="7">
-        <v>-0.000194</v>
+        <v>0.002673</v>
       </c>
       <c r="I73" s="7">
-        <v>0.28210999999999997</v>
+        <v>0.28578600000000004</v>
       </c>
       <c r="J73" s="7">
-        <v>2.069795</v>
+        <v>2.0597630000000002</v>
       </c>
       <c r="K73" s="7">
-        <v>6.0678920000000005</v>
+        <v>6.135706</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,25 +4834,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.109054</v>
+        <v>0.12135</v>
       </c>
       <c r="F74" s="7">
-        <v>0.060073</v>
+        <v>0.073641</v>
       </c>
       <c r="G74" s="7">
-        <v>0.23352699999999998</v>
+        <v>0.254951</v>
       </c>
       <c r="H74" s="7">
-        <v>0.206816</v>
+        <v>0.21532800000000002</v>
       </c>
       <c r="I74" s="7">
-        <v>0.352865</v>
+        <v>0.362407</v>
       </c>
       <c r="J74" s="7">
-        <v>2.535987</v>
+        <v>2.54936</v>
       </c>
       <c r="K74" s="7">
-        <v>15.291927000000001</v>
+        <v>15.205061</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4869,25 +4869,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.04715</v>
+        <v>0.046029999999999995</v>
       </c>
       <c r="F75" s="7">
-        <v>0.013784000000000001</v>
+        <v>0.014138999999999999</v>
       </c>
       <c r="G75" s="7">
-        <v>0.177104</v>
+        <v>0.171735</v>
       </c>
       <c r="H75" s="7">
-        <v>0.053842</v>
+        <v>0.05300099999999999</v>
       </c>
       <c r="I75" s="7">
-        <v>0.425515</v>
+        <v>0.424377</v>
       </c>
       <c r="J75" s="7">
-        <v>1.804883</v>
+        <v>1.8009870000000001</v>
       </c>
       <c r="K75" s="7">
-        <v>3.7347710000000003</v>
+        <v>3.724889</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,25 +4904,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.06603500000000001</v>
+        <v>0.069625</v>
       </c>
       <c r="F76" s="7">
-        <v>0.049242999999999995</v>
+        <v>0.05404</v>
       </c>
       <c r="G76" s="7">
-        <v>0.218782</v>
+        <v>0.22053999999999999</v>
       </c>
       <c r="H76" s="7">
-        <v>0.126779</v>
+        <v>0.12897</v>
       </c>
       <c r="I76" s="7">
-        <v>0.479467</v>
+        <v>0.48234299999999997</v>
       </c>
       <c r="J76" s="7">
-        <v>2.205575</v>
+        <v>2.214633</v>
       </c>
       <c r="K76" s="7">
-        <v>5.684965</v>
+        <v>5.67636</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4939,25 +4939,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.045279</v>
+        <v>0.045899</v>
       </c>
       <c r="F77" s="7">
-        <v>0.08385400000000001</v>
+        <v>0.073708</v>
       </c>
       <c r="G77" s="7">
-        <v>0.27962</v>
+        <v>0.270843</v>
       </c>
       <c r="H77" s="7">
-        <v>0.19114799999999998</v>
+        <v>0.187074</v>
       </c>
       <c r="I77" s="7">
-        <v>0.42619100000000004</v>
+        <v>0.421312</v>
       </c>
       <c r="J77" s="7">
-        <v>1.882306</v>
+        <v>1.865215</v>
       </c>
       <c r="K77" s="7">
-        <v>5.538438</v>
+        <v>5.499129</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4974,25 +4974,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="7">
-        <v>0.075864</v>
+        <v>0.090591</v>
       </c>
       <c r="F78" s="7">
-        <v>0.098521</v>
+        <v>0.106228</v>
       </c>
       <c r="G78" s="7">
-        <v>0.339876</v>
+        <v>0.350691</v>
       </c>
       <c r="H78" s="7">
-        <v>0.244951</v>
+        <v>0.25310900000000003</v>
       </c>
       <c r="I78" s="7">
-        <v>0.658018</v>
+        <v>0.668882</v>
       </c>
       <c r="J78" s="7">
-        <v>2.782288</v>
+        <v>2.8204000000000002</v>
       </c>
       <c r="K78" s="7">
-        <v>8.47837</v>
+        <v>8.515184</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5009,25 +5009,25 @@
         <v>5</v>
       </c>
       <c r="E79" s="7">
-        <v>0.068271</v>
+        <v>0.072617</v>
       </c>
       <c r="F79" s="7">
-        <v>0.079734</v>
+        <v>0.087045</v>
       </c>
       <c r="G79" s="7">
-        <v>0.166718</v>
+        <v>0.17290299999999997</v>
       </c>
       <c r="H79" s="7">
-        <v>0.151975</v>
+        <v>0.157859</v>
       </c>
       <c r="I79" s="7">
-        <v>0.412697</v>
+        <v>0.41991300000000004</v>
       </c>
       <c r="J79" s="7">
-        <v>2.3216900000000003</v>
+        <v>2.339096</v>
       </c>
       <c r="K79" s="7">
-        <v>8.023685</v>
+        <v>8.026372</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,25 +5044,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.123781</v>
+        <v>0.129796</v>
       </c>
       <c r="F80" s="7">
-        <v>0.083778</v>
+        <v>0.0968</v>
       </c>
       <c r="G80" s="7">
-        <v>0.23495999999999997</v>
+        <v>0.245221</v>
       </c>
       <c r="H80" s="7">
-        <v>0.24536999999999998</v>
+        <v>0.248967</v>
       </c>
       <c r="I80" s="7">
-        <v>0.398778</v>
+        <v>0.402819</v>
       </c>
       <c r="J80" s="7">
-        <v>2.288724</v>
+        <v>2.3069550000000003</v>
       </c>
       <c r="K80" s="7">
-        <v>11.624334</v>
+        <v>11.548789999999999</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5079,25 +5079,25 @@
         <v>4</v>
       </c>
       <c r="E81" s="7">
-        <v>0.033971</v>
+        <v>0.035404</v>
       </c>
       <c r="F81" s="7">
-        <v>0.069617</v>
+        <v>0.070594</v>
       </c>
       <c r="G81" s="7">
-        <v>0.17652400000000001</v>
+        <v>0.176351</v>
       </c>
       <c r="H81" s="7">
-        <v>0.11426</v>
+        <v>0.11634399999999999</v>
       </c>
       <c r="I81" s="7">
-        <v>0.37339500000000003</v>
+        <v>0.375963</v>
       </c>
       <c r="J81" s="7">
-        <v>1.511469</v>
+        <v>1.5171510000000001</v>
       </c>
       <c r="K81" s="7">
-        <v>4.3778500000000005</v>
+        <v>4.384298</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,25 +5114,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.049617</v>
+        <v>0.047288</v>
       </c>
       <c r="F82" s="7">
-        <v>0.00617</v>
+        <v>0.00738</v>
       </c>
       <c r="G82" s="7">
-        <v>0.14567</v>
+        <v>0.141951</v>
       </c>
       <c r="H82" s="7">
-        <v>0.046801</v>
+        <v>0.045784000000000005</v>
       </c>
       <c r="I82" s="7">
-        <v>0.391432</v>
+        <v>0.39008000000000004</v>
       </c>
       <c r="J82" s="7">
-        <v>1.496267</v>
+        <v>1.491373</v>
       </c>
       <c r="K82" s="7">
-        <v>3.145276</v>
+        <v>3.136294</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5149,25 +5149,25 @@
         <v>5</v>
       </c>
       <c r="E83" s="7">
-        <v>0.071576</v>
+        <v>0.079635</v>
       </c>
       <c r="F83" s="7">
-        <v>0.075283</v>
+        <v>0.081982</v>
       </c>
       <c r="G83" s="7">
-        <v>0.165489</v>
+        <v>0.17249199999999998</v>
       </c>
       <c r="H83" s="7">
-        <v>0.160534</v>
+        <v>0.16643999999999998</v>
       </c>
       <c r="I83" s="7">
-        <v>0.415675</v>
+        <v>0.42288</v>
       </c>
       <c r="J83" s="7">
-        <v>2.326799</v>
+        <v>2.347169</v>
       </c>
       <c r="K83" s="7">
-        <v>9.031938</v>
+        <v>9.012354</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,22 +5184,22 @@
         <v>6</v>
       </c>
       <c r="E84" s="7">
-        <v>0.02939</v>
+        <v>0.027889</v>
       </c>
       <c r="F84" s="7">
-        <v>-0.074472</v>
+        <v>-0.08211299999999999</v>
       </c>
       <c r="G84" s="7">
-        <v>0.111781</v>
+        <v>0.132699</v>
       </c>
       <c r="H84" s="7">
-        <v>0.035299</v>
+        <v>0.034138</v>
       </c>
       <c r="I84" s="7">
-        <v>0.657339</v>
+        <v>0.6554800000000001</v>
       </c>
       <c r="J84" s="7">
-        <v>3.8990460000000002</v>
+        <v>3.8961669999999997</v>
       </c>
       <c r="K84" s="7"/>
     </row>
@@ -5217,19 +5217,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="7">
-        <v>0.031408</v>
+        <v>0.029435</v>
       </c>
       <c r="F85" s="7">
-        <v>0.09386599999999999</v>
+        <v>0.094064</v>
       </c>
       <c r="G85" s="7">
-        <v>0.19728300000000001</v>
+        <v>0.197488</v>
       </c>
       <c r="H85" s="7">
-        <v>0.120397</v>
+        <v>0.121639</v>
       </c>
       <c r="I85" s="7">
-        <v>0.463498</v>
+        <v>0.46512099999999995</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5248,22 +5248,22 @@
         <v>6</v>
       </c>
       <c r="E86" s="7">
-        <v>0.10638199999999999</v>
+        <v>0.121045</v>
       </c>
       <c r="F86" s="7">
-        <v>0.079197</v>
+        <v>0.090851</v>
       </c>
       <c r="G86" s="7">
-        <v>0.256281</v>
+        <v>0.266838</v>
       </c>
       <c r="H86" s="7">
-        <v>0.20743999999999999</v>
+        <v>0.21390399999999998</v>
       </c>
       <c r="I86" s="7">
-        <v>0.546461</v>
+        <v>0.554739</v>
       </c>
       <c r="J86" s="7">
-        <v>2.755251</v>
+        <v>2.767972</v>
       </c>
       <c r="K86" s="7"/>
     </row>
@@ -5281,22 +5281,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.11318199999999999</v>
+        <v>0.151897</v>
       </c>
       <c r="F87" s="7">
-        <v>0.176877</v>
+        <v>0.198735</v>
       </c>
       <c r="G87" s="7">
-        <v>0.295001</v>
+        <v>0.313685</v>
       </c>
       <c r="H87" s="7">
-        <v>0.294262</v>
+        <v>0.316246</v>
       </c>
       <c r="I87" s="7">
-        <v>0.671159</v>
+        <v>0.699545</v>
       </c>
       <c r="J87" s="7">
-        <v>3.8289190000000004</v>
+        <v>3.901685</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,25 +5314,25 @@
         <v>7</v>
       </c>
       <c r="E88" s="7">
-        <v>0.035588</v>
+        <v>0.039449</v>
       </c>
       <c r="F88" s="7">
-        <v>-0.057903</v>
+        <v>-0.06973900000000001</v>
       </c>
       <c r="G88" s="7">
-        <v>0.177541</v>
+        <v>0.192786</v>
       </c>
       <c r="H88" s="7">
-        <v>0.093808</v>
+        <v>0.095829</v>
       </c>
       <c r="I88" s="7">
-        <v>0.6505540000000001</v>
+        <v>0.653604</v>
       </c>
       <c r="J88" s="7">
-        <v>4.296727000000001</v>
+        <v>4.259374</v>
       </c>
       <c r="K88" s="7">
-        <v>14.131406</v>
+        <v>14.256645</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5349,25 +5349,25 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>0.036041</v>
+        <v>0.034279000000000004</v>
       </c>
       <c r="F89" s="7">
-        <v>0.09420400000000001</v>
+        <v>0.093486</v>
       </c>
       <c r="G89" s="7">
-        <v>0.20884899999999998</v>
+        <v>0.208073</v>
       </c>
       <c r="H89" s="7">
-        <v>0.127132</v>
+        <v>0.128043</v>
       </c>
       <c r="I89" s="7">
-        <v>0.504597</v>
+        <v>0.505814</v>
       </c>
       <c r="J89" s="7">
-        <v>2.381644</v>
+        <v>2.388874</v>
       </c>
       <c r="K89" s="7">
-        <v>4.303839</v>
+        <v>4.313193999999999</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5384,25 +5384,25 @@
         <v>5</v>
       </c>
       <c r="E90" s="7">
-        <v>0.050141</v>
+        <v>0.050012999999999995</v>
       </c>
       <c r="F90" s="7">
-        <v>0.029624</v>
+        <v>0.030188000000000003</v>
       </c>
       <c r="G90" s="7">
-        <v>0.17575500000000002</v>
+        <v>0.176057</v>
       </c>
       <c r="H90" s="7">
-        <v>0.08977299999999999</v>
+        <v>0.088261</v>
       </c>
       <c r="I90" s="7">
-        <v>0.306785</v>
+        <v>0.304972</v>
       </c>
       <c r="J90" s="7">
-        <v>2.042404</v>
+        <v>2.043024</v>
       </c>
       <c r="K90" s="7">
-        <v>5.487329999999999</v>
+        <v>5.462224</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5419,22 +5419,22 @@
         <v>6</v>
       </c>
       <c r="E91" s="7">
-        <v>0.070141</v>
+        <v>0.07108500000000001</v>
       </c>
       <c r="F91" s="7">
-        <v>0.073748</v>
+        <v>0.080655</v>
       </c>
       <c r="G91" s="7">
-        <v>0.224513</v>
+        <v>0.236509</v>
       </c>
       <c r="H91" s="7">
-        <v>0.177342</v>
+        <v>0.178223</v>
       </c>
       <c r="I91" s="7">
-        <v>0.43229300000000004</v>
+        <v>0.433365</v>
       </c>
       <c r="J91" s="7">
-        <v>2.525984</v>
+        <v>2.538218</v>
       </c>
       <c r="K91" s="7"/>
     </row>
@@ -5452,25 +5452,25 @@
         <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>0.060517</v>
+        <v>0.059473000000000005</v>
       </c>
       <c r="F92" s="7">
-        <v>0.032289</v>
+        <v>0.033014</v>
       </c>
       <c r="G92" s="7">
-        <v>0.207986</v>
+        <v>0.208901</v>
       </c>
       <c r="H92" s="7">
-        <v>0.10411799999999999</v>
+        <v>0.102164</v>
       </c>
       <c r="I92" s="7">
-        <v>0.350498</v>
+        <v>0.34810800000000003</v>
       </c>
       <c r="J92" s="7">
-        <v>1.9981309999999999</v>
+        <v>1.989427</v>
       </c>
       <c r="K92" s="7">
-        <v>5.030234</v>
+        <v>4.999139</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,25 +5487,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.038134</v>
+        <v>0.040351</v>
       </c>
       <c r="F93" s="7">
-        <v>0.06794</v>
+        <v>0.068196</v>
       </c>
       <c r="G93" s="7">
-        <v>0.199534</v>
+        <v>0.20136199999999999</v>
       </c>
       <c r="H93" s="7">
-        <v>0.13128</v>
+        <v>0.133199</v>
       </c>
       <c r="I93" s="7">
-        <v>0.34183100000000005</v>
+        <v>0.344108</v>
       </c>
       <c r="J93" s="7">
-        <v>1.7241220000000002</v>
+        <v>1.709101</v>
       </c>
       <c r="K93" s="7">
-        <v>4.649311</v>
+        <v>4.640167</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,25 +5522,25 @@
         <v>4</v>
       </c>
       <c r="E94" s="7">
-        <v>0.072287</v>
+        <v>0.077464</v>
       </c>
       <c r="F94" s="7">
-        <v>0.051176000000000006</v>
+        <v>0.057318</v>
       </c>
       <c r="G94" s="7">
-        <v>0.270737</v>
+        <v>0.28458</v>
       </c>
       <c r="H94" s="7">
-        <v>0.17418199999999998</v>
+        <v>0.176463</v>
       </c>
       <c r="I94" s="7">
-        <v>0.500817</v>
+        <v>0.503734</v>
       </c>
       <c r="J94" s="7">
-        <v>2.792866</v>
+        <v>2.781185</v>
       </c>
       <c r="K94" s="7">
-        <v>8.477095</v>
+        <v>8.446175</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,25 +5557,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.044177</v>
+        <v>0.043037</v>
       </c>
       <c r="F95" s="7">
-        <v>0.016684</v>
+        <v>0.018757</v>
       </c>
       <c r="G95" s="7">
-        <v>0.173117</v>
+        <v>0.174039</v>
       </c>
       <c r="H95" s="7">
-        <v>0.052006</v>
+        <v>0.051527</v>
       </c>
       <c r="I95" s="7">
-        <v>0.43957599999999997</v>
+        <v>0.43892000000000003</v>
       </c>
       <c r="J95" s="7">
-        <v>1.367222</v>
+        <v>1.363433</v>
       </c>
       <c r="K95" s="7">
-        <v>2.784531</v>
+        <v>2.7768360000000003</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,25 +5592,25 @@
         <v>7</v>
       </c>
       <c r="E96" s="7">
-        <v>0.10412800000000001</v>
+        <v>0.111595</v>
       </c>
       <c r="F96" s="7">
-        <v>0.044339</v>
+        <v>0.051933</v>
       </c>
       <c r="G96" s="7">
-        <v>0.286692</v>
+        <v>0.302492</v>
       </c>
       <c r="H96" s="7">
-        <v>0.229707</v>
+        <v>0.22825199999999998</v>
       </c>
       <c r="I96" s="7">
-        <v>0.39718000000000003</v>
+        <v>0.395527</v>
       </c>
       <c r="J96" s="7">
-        <v>2.90958</v>
+        <v>2.87518</v>
       </c>
       <c r="K96" s="7">
-        <v>15.548849</v>
+        <v>15.311259999999999</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,25 +5627,25 @@
         <v>6</v>
       </c>
       <c r="E97" s="7">
-        <v>0.091979</v>
+        <v>0.09632</v>
       </c>
       <c r="F97" s="7">
-        <v>0.029018000000000002</v>
+        <v>0.030884</v>
       </c>
       <c r="G97" s="7">
-        <v>0.39476799999999995</v>
+        <v>0.404202</v>
       </c>
       <c r="H97" s="7">
-        <v>0.229085</v>
+        <v>0.222942</v>
       </c>
       <c r="I97" s="7">
-        <v>0.5097229999999999</v>
+        <v>0.502177</v>
       </c>
       <c r="J97" s="7">
-        <v>4.075838</v>
+        <v>4.013739</v>
       </c>
       <c r="K97" s="7">
-        <v>20.221309</v>
+        <v>19.876399</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,25 +5662,25 @@
         <v>4</v>
       </c>
       <c r="E98" s="7">
-        <v>0.072461</v>
+        <v>0.077262</v>
       </c>
       <c r="F98" s="7">
-        <v>0.079284</v>
+        <v>0.084127</v>
       </c>
       <c r="G98" s="7">
-        <v>0.29565400000000003</v>
+        <v>0.307072</v>
       </c>
       <c r="H98" s="7">
-        <v>0.215588</v>
+        <v>0.217688</v>
       </c>
       <c r="I98" s="7">
-        <v>0.5466</v>
+        <v>0.549272</v>
       </c>
       <c r="J98" s="7">
-        <v>3.434459</v>
+        <v>3.4158600000000003</v>
       </c>
       <c r="K98" s="7">
-        <v>9.380666</v>
+        <v>9.363707</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,25 +5697,25 @@
         <v>6</v>
       </c>
       <c r="E99" s="7">
-        <v>0.027538</v>
+        <v>0.034089999999999995</v>
       </c>
       <c r="F99" s="7">
-        <v>0.041725000000000005</v>
+        <v>0.042668</v>
       </c>
       <c r="G99" s="7">
-        <v>0.09964</v>
+        <v>0.10034000000000001</v>
       </c>
       <c r="H99" s="7">
-        <v>0.056581</v>
+        <v>0.058202</v>
       </c>
       <c r="I99" s="7">
-        <v>0.282033</v>
+        <v>0.284</v>
       </c>
       <c r="J99" s="7">
-        <v>2.000389</v>
+        <v>1.9977850000000001</v>
       </c>
       <c r="K99" s="7">
-        <v>5.710829</v>
+        <v>5.779735</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,25 +5732,25 @@
         <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>0.080422</v>
+        <v>0.087049</v>
       </c>
       <c r="F100" s="7">
-        <v>0.075346</v>
+        <v>0.08191000000000001</v>
       </c>
       <c r="G100" s="7">
-        <v>0.354217</v>
+        <v>0.370664</v>
       </c>
       <c r="H100" s="7">
-        <v>0.225408</v>
+        <v>0.228196</v>
       </c>
       <c r="I100" s="7">
-        <v>0.5866790000000001</v>
+        <v>0.590289</v>
       </c>
       <c r="J100" s="7">
-        <v>3.659316</v>
+        <v>3.646298</v>
       </c>
       <c r="K100" s="7">
-        <v>12.467236</v>
+        <v>12.43386</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,25 +5767,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.084002</v>
+        <v>0.097309</v>
       </c>
       <c r="F101" s="7">
-        <v>0.08558199999999999</v>
+        <v>0.089932</v>
       </c>
       <c r="G101" s="7">
-        <v>0.344877</v>
+        <v>0.35509300000000005</v>
       </c>
       <c r="H101" s="7">
-        <v>0.297095</v>
+        <v>0.304016</v>
       </c>
       <c r="I101" s="7">
-        <v>0.64798</v>
+        <v>0.656772</v>
       </c>
       <c r="J101" s="7">
-        <v>3.504343</v>
+        <v>3.509617</v>
       </c>
       <c r="K101" s="7">
-        <v>11.596089999999998</v>
+        <v>11.514055</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,25 +5802,25 @@
         <v>2</v>
       </c>
       <c r="E102" s="7">
-        <v>0.042986</v>
+        <v>0.043197</v>
       </c>
       <c r="F102" s="7">
-        <v>0.10371499999999999</v>
+        <v>0.105987</v>
       </c>
       <c r="G102" s="7">
-        <v>0.26265</v>
+        <v>0.26508299999999996</v>
       </c>
       <c r="H102" s="7">
-        <v>0.155032</v>
+        <v>0.157448</v>
       </c>
       <c r="I102" s="7">
-        <v>0.571896</v>
+        <v>0.575184</v>
       </c>
       <c r="J102" s="7">
-        <v>3.122457</v>
+        <v>3.1283550000000004</v>
       </c>
       <c r="K102" s="7">
-        <v>5.720656</v>
+        <v>5.729735</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,25 +5837,25 @@
         <v>6</v>
       </c>
       <c r="E103" s="7">
-        <v>0.089263</v>
+        <v>0.103905</v>
       </c>
       <c r="F103" s="7">
-        <v>0.076451</v>
+        <v>0.080191</v>
       </c>
       <c r="G103" s="7">
-        <v>0.350109</v>
+        <v>0.361126</v>
       </c>
       <c r="H103" s="7">
-        <v>0.314226</v>
+        <v>0.321312</v>
       </c>
       <c r="I103" s="7">
-        <v>0.6441849999999999</v>
+        <v>0.65305</v>
       </c>
       <c r="J103" s="7">
-        <v>3.399932</v>
+        <v>3.403082</v>
       </c>
       <c r="K103" s="7">
-        <v>13.767832</v>
+        <v>13.652636</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,25 +5872,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.03646</v>
+        <v>0.049307</v>
       </c>
       <c r="F104" s="7">
-        <v>0.034842</v>
+        <v>0.035542</v>
       </c>
       <c r="G104" s="7">
-        <v>0.096614</v>
+        <v>0.096418</v>
       </c>
       <c r="H104" s="7">
-        <v>0.045454999999999995</v>
+        <v>0.046604</v>
       </c>
       <c r="I104" s="7">
-        <v>0.318964</v>
+        <v>0.32041400000000003</v>
       </c>
       <c r="J104" s="7">
-        <v>2.180074</v>
+        <v>2.164829</v>
       </c>
       <c r="K104" s="7">
-        <v>6.130732</v>
+        <v>6.191096</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,16 +5907,16 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.090382</v>
+        <v>0.10543799999999999</v>
       </c>
       <c r="F105" s="7">
-        <v>0.058358</v>
+        <v>0.065356</v>
       </c>
       <c r="G105" s="7">
-        <v>0.18403099999999997</v>
+        <v>0.190906</v>
       </c>
       <c r="H105" s="7">
-        <v>0.146082</v>
+        <v>0.152344</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
@@ -5936,22 +5936,22 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.16003299999999998</v>
+        <v>0.19633199999999998</v>
       </c>
       <c r="F106" s="7">
-        <v>0.180334</v>
+        <v>0.180984</v>
       </c>
       <c r="G106" s="7">
-        <v>0.310134</v>
+        <v>0.306513</v>
       </c>
       <c r="H106" s="7">
-        <v>0.291135</v>
+        <v>0.301699</v>
       </c>
       <c r="I106" s="7">
-        <v>0.812315</v>
+        <v>0.827144</v>
       </c>
       <c r="J106" s="7">
-        <v>4.184482</v>
+        <v>4.183302</v>
       </c>
       <c r="K106" s="7"/>
     </row>
@@ -5969,25 +5969,25 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.044211</v>
+        <v>0.048049999999999995</v>
       </c>
       <c r="F107" s="7">
-        <v>-0.049241</v>
+        <v>-0.057712000000000006</v>
       </c>
       <c r="G107" s="7">
-        <v>0.196132</v>
+        <v>0.213476</v>
       </c>
       <c r="H107" s="7">
-        <v>0.12163500000000001</v>
+        <v>0.126629</v>
       </c>
       <c r="I107" s="7">
-        <v>0.693271</v>
+        <v>0.70081</v>
       </c>
       <c r="J107" s="7">
-        <v>5.022439</v>
+        <v>4.968293</v>
       </c>
       <c r="K107" s="7">
-        <v>16.215075</v>
+        <v>16.405253000000002</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,25 +6004,25 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.049052</v>
+        <v>0.048285999999999996</v>
       </c>
       <c r="F108" s="7">
-        <v>0.038043</v>
+        <v>0.038543</v>
       </c>
       <c r="G108" s="7">
-        <v>0.195334</v>
+        <v>0.19250699999999998</v>
       </c>
       <c r="H108" s="7">
-        <v>0.076005</v>
+        <v>0.07542900000000001</v>
       </c>
       <c r="I108" s="7">
-        <v>0.47916899999999996</v>
+        <v>0.478376</v>
       </c>
       <c r="J108" s="7">
-        <v>2.061793</v>
+        <v>2.063272</v>
       </c>
       <c r="K108" s="7">
-        <v>3.9113189999999998</v>
+        <v>3.917167</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,25 +6039,25 @@
         <v>6</v>
       </c>
       <c r="E109" s="7">
-        <v>0.035107</v>
+        <v>0.045739</v>
       </c>
       <c r="F109" s="7">
-        <v>0.03373</v>
+        <v>0.032458</v>
       </c>
       <c r="G109" s="7">
-        <v>0.126447</v>
+        <v>0.12638</v>
       </c>
       <c r="H109" s="7">
-        <v>0.053072999999999995</v>
+        <v>0.053984</v>
       </c>
       <c r="I109" s="7">
-        <v>0.34553100000000003</v>
+        <v>0.34669400000000006</v>
       </c>
       <c r="J109" s="7">
-        <v>2.2363720000000002</v>
+        <v>2.21449</v>
       </c>
       <c r="K109" s="7">
-        <v>6.584002000000001</v>
+        <v>6.645268</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,25 +6074,25 @@
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>0.045267</v>
+        <v>0.048817000000000006</v>
       </c>
       <c r="F110" s="7">
-        <v>0.074282</v>
+        <v>0.079469</v>
       </c>
       <c r="G110" s="7">
-        <v>0.198874</v>
+        <v>0.20241299999999998</v>
       </c>
       <c r="H110" s="7">
-        <v>0.144813</v>
+        <v>0.14898</v>
       </c>
       <c r="I110" s="7">
-        <v>0.464343</v>
+        <v>0.469674</v>
       </c>
       <c r="J110" s="7">
-        <v>1.9418250000000001</v>
+        <v>1.9504380000000001</v>
       </c>
       <c r="K110" s="7">
-        <v>5.493611</v>
+        <v>5.499884</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,25 +6109,25 @@
         <v>5</v>
       </c>
       <c r="E111" s="7">
-        <v>0.052282999999999996</v>
+        <v>0.05710200000000001</v>
       </c>
       <c r="F111" s="7">
-        <v>0.024911</v>
+        <v>0.03387</v>
       </c>
       <c r="G111" s="7">
-        <v>0.22395600000000002</v>
+        <v>0.230329</v>
       </c>
       <c r="H111" s="7">
-        <v>0.142732</v>
+        <v>0.145813</v>
       </c>
       <c r="I111" s="7">
-        <v>0.536</v>
+        <v>0.540142</v>
       </c>
       <c r="J111" s="7">
-        <v>3.4479680000000004</v>
+        <v>3.454209</v>
       </c>
       <c r="K111" s="7">
-        <v>14.720310999999999</v>
+        <v>14.661411000000001</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,25 +6144,25 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>0.039769</v>
+        <v>0.039842</v>
       </c>
       <c r="F112" s="7">
-        <v>0.085362</v>
+        <v>0.08818799999999999</v>
       </c>
       <c r="G112" s="7">
-        <v>0.239916</v>
+        <v>0.241773</v>
       </c>
       <c r="H112" s="7">
-        <v>0.137311</v>
+        <v>0.139352</v>
       </c>
       <c r="I112" s="7">
-        <v>0.533513</v>
+        <v>0.536265</v>
       </c>
       <c r="J112" s="7">
-        <v>3.2914190000000003</v>
+        <v>3.29298</v>
       </c>
       <c r="K112" s="7">
-        <v>6.267404</v>
+        <v>6.278185</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6179,25 +6179,25 @@
         <v>6</v>
       </c>
       <c r="E113" s="7">
-        <v>0.102591</v>
+        <v>0.116857</v>
       </c>
       <c r="F113" s="7">
-        <v>0.095788</v>
+        <v>0.10635</v>
       </c>
       <c r="G113" s="7">
-        <v>0.271351</v>
+        <v>0.28945699999999996</v>
       </c>
       <c r="H113" s="7">
-        <v>0.236523</v>
+        <v>0.24870599999999998</v>
       </c>
       <c r="I113" s="7">
-        <v>0.537182</v>
+        <v>0.552327</v>
       </c>
       <c r="J113" s="7">
-        <v>3.341223</v>
+        <v>3.345303</v>
       </c>
       <c r="K113" s="7">
-        <v>17.056431</v>
+        <v>17.054689</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6214,25 +6214,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.09747</v>
+        <v>0.111603</v>
       </c>
       <c r="F114" s="7">
-        <v>0.059519999999999997</v>
+        <v>0.069204</v>
       </c>
       <c r="G114" s="7">
-        <v>0.25726</v>
+        <v>0.274849</v>
       </c>
       <c r="H114" s="7">
-        <v>0.18842199999999998</v>
+        <v>0.19328499999999998</v>
       </c>
       <c r="I114" s="7">
-        <v>0.525447</v>
+        <v>0.531689</v>
       </c>
       <c r="J114" s="7">
-        <v>3.2898140000000002</v>
+        <v>3.292806</v>
       </c>
       <c r="K114" s="7">
-        <v>23.456273</v>
+        <v>23.250246999999998</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6249,25 +6249,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.099615</v>
+        <v>0.110025</v>
       </c>
       <c r="F115" s="7">
-        <v>0.074173</v>
+        <v>0.086396</v>
       </c>
       <c r="G115" s="7">
-        <v>0.274772</v>
+        <v>0.288138</v>
       </c>
       <c r="H115" s="7">
-        <v>0.21757</v>
+        <v>0.220257</v>
       </c>
       <c r="I115" s="7">
-        <v>0.532907</v>
+        <v>0.5362899999999999</v>
       </c>
       <c r="J115" s="7">
-        <v>2.75873</v>
+        <v>2.7567579999999996</v>
       </c>
       <c r="K115" s="7">
-        <v>16.580633</v>
+        <v>16.441858</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6284,25 +6284,25 @@
         <v>5</v>
       </c>
       <c r="E116" s="7">
-        <v>0.079115</v>
+        <v>0.089497</v>
       </c>
       <c r="F116" s="7">
-        <v>0.100607</v>
+        <v>0.109442</v>
       </c>
       <c r="G116" s="7">
-        <v>0.281844</v>
+        <v>0.291863</v>
       </c>
       <c r="H116" s="7">
-        <v>0.244205</v>
+        <v>0.252744</v>
       </c>
       <c r="I116" s="7">
-        <v>0.626387</v>
+        <v>0.637549</v>
       </c>
       <c r="J116" s="7">
-        <v>3.217015</v>
+        <v>3.223116</v>
       </c>
       <c r="K116" s="7">
-        <v>12.417157999999999</v>
+        <v>12.42092</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6319,25 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>0.047571</v>
+        <v>0.046593</v>
       </c>
       <c r="F117" s="7">
-        <v>0.033066</v>
+        <v>0.034174</v>
       </c>
       <c r="G117" s="7">
-        <v>0.191347</v>
+        <v>0.188962</v>
       </c>
       <c r="H117" s="7">
-        <v>0.069688</v>
+        <v>0.069413</v>
       </c>
       <c r="I117" s="7">
-        <v>0.448866</v>
+        <v>0.448494</v>
       </c>
       <c r="J117" s="7">
-        <v>1.8904830000000001</v>
+        <v>1.8881729999999999</v>
       </c>
       <c r="K117" s="7">
-        <v>3.7218590000000003</v>
+        <v>3.714918</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6354,25 +6354,25 @@
         <v>6</v>
       </c>
       <c r="E118" s="7">
-        <v>0.079106</v>
+        <v>0.086015</v>
       </c>
       <c r="F118" s="7">
-        <v>0.053924</v>
+        <v>0.064981</v>
       </c>
       <c r="G118" s="7">
-        <v>0.25934</v>
+        <v>0.269271</v>
       </c>
       <c r="H118" s="7">
-        <v>0.18503799999999998</v>
+        <v>0.187809</v>
       </c>
       <c r="I118" s="7">
-        <v>0.621313</v>
+        <v>0.625105</v>
       </c>
       <c r="J118" s="7">
-        <v>3.514705</v>
+        <v>3.516698</v>
       </c>
       <c r="K118" s="7">
-        <v>16.572895000000003</v>
+        <v>16.502233</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6389,25 +6389,25 @@
         <v>5</v>
       </c>
       <c r="E119" s="7">
-        <v>0.050408</v>
+        <v>0.055579</v>
       </c>
       <c r="F119" s="7">
-        <v>0.018168</v>
+        <v>0.025276999999999997</v>
       </c>
       <c r="G119" s="7">
-        <v>0.187135</v>
+        <v>0.18998400000000001</v>
       </c>
       <c r="H119" s="7">
-        <v>0.106152</v>
+        <v>0.108525</v>
       </c>
       <c r="I119" s="7">
-        <v>0.46356299999999995</v>
+        <v>0.466702</v>
       </c>
       <c r="J119" s="7">
-        <v>2.574574</v>
+        <v>2.55355</v>
       </c>
       <c r="K119" s="7">
-        <v>9.06256</v>
+        <v>9.06296</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,25 +6424,25 @@
         <v>6</v>
       </c>
       <c r="E120" s="7">
-        <v>0.068345</v>
+        <v>0.072839</v>
       </c>
       <c r="F120" s="7">
-        <v>0.012452000000000001</v>
+        <v>0.013054</v>
       </c>
       <c r="G120" s="7">
-        <v>0.184037</v>
+        <v>0.185062</v>
       </c>
       <c r="H120" s="7">
-        <v>0.142177</v>
+        <v>0.136224</v>
       </c>
       <c r="I120" s="7">
-        <v>0.44027</v>
+        <v>0.43276400000000004</v>
       </c>
       <c r="J120" s="7">
-        <v>3.405748</v>
+        <v>3.3764920000000003</v>
       </c>
       <c r="K120" s="7">
-        <v>18.662581</v>
+        <v>18.35544</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,25 +6459,25 @@
         <v>4</v>
       </c>
       <c r="E121" s="7">
-        <v>0.055262000000000006</v>
+        <v>0.057371</v>
       </c>
       <c r="F121" s="7">
-        <v>0.042231</v>
+        <v>0.04785999999999999</v>
       </c>
       <c r="G121" s="7">
-        <v>0.211285</v>
+        <v>0.209724</v>
       </c>
       <c r="H121" s="7">
-        <v>0.117103</v>
+        <v>0.11870900000000001</v>
       </c>
       <c r="I121" s="7">
-        <v>0.486346</v>
+        <v>0.488483</v>
       </c>
       <c r="J121" s="7">
-        <v>2.327575</v>
+        <v>2.328726</v>
       </c>
       <c r="K121" s="7">
-        <v>6.0936</v>
+        <v>6.083111</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6494,25 +6494,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.047077</v>
+        <v>0.048743</v>
       </c>
       <c r="F122" s="7">
-        <v>0.041171</v>
+        <v>0.044855</v>
       </c>
       <c r="G122" s="7">
-        <v>0.18214</v>
+        <v>0.18143499999999999</v>
       </c>
       <c r="H122" s="7">
-        <v>0.10193400000000001</v>
+        <v>0.103368</v>
       </c>
       <c r="I122" s="7">
-        <v>0.43617100000000003</v>
+        <v>0.43804000000000004</v>
       </c>
       <c r="J122" s="7">
-        <v>1.9569130000000001</v>
+        <v>1.964806</v>
       </c>
       <c r="K122" s="7">
-        <v>6.076933</v>
+        <v>6.069981</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,16 +6529,16 @@
         <v>6</v>
       </c>
       <c r="E123" s="7">
-        <v>0.034997</v>
+        <v>0.043587999999999995</v>
       </c>
       <c r="F123" s="7">
-        <v>-0.040677000000000005</v>
+        <v>-0.048996000000000005</v>
       </c>
       <c r="G123" s="7">
-        <v>0.17890499999999998</v>
+        <v>0.194121</v>
       </c>
       <c r="H123" s="7">
-        <v>0.124059</v>
+        <v>0.130217</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
@@ -6558,25 +6558,25 @@
         <v>4</v>
       </c>
       <c r="E124" s="7">
-        <v>0.068471</v>
+        <v>0.070947</v>
       </c>
       <c r="F124" s="7">
-        <v>0.051124</v>
+        <v>0.056167999999999996</v>
       </c>
       <c r="G124" s="7">
-        <v>0.24066600000000002</v>
+        <v>0.247074</v>
       </c>
       <c r="H124" s="7">
-        <v>0.15098699999999998</v>
+        <v>0.15152</v>
       </c>
       <c r="I124" s="7">
-        <v>0.526135</v>
+        <v>0.526841</v>
       </c>
       <c r="J124" s="7">
-        <v>1.966475</v>
+        <v>1.9759929999999999</v>
       </c>
       <c r="K124" s="7">
-        <v>6.600753999999999</v>
+        <v>6.587653</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.12322</v>
+        <v>0.136144</v>
       </c>
       <c r="F125" s="7">
-        <v>0.129237</v>
+        <v>0.14548</v>
       </c>
       <c r="G125" s="7">
-        <v>0.33204999999999996</v>
+        <v>0.350301</v>
       </c>
       <c r="H125" s="7">
-        <v>0.319413</v>
+        <v>0.33603900000000003</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
@@ -6622,25 +6622,25 @@
         <v>7</v>
       </c>
       <c r="E126" s="7">
-        <v>0.0969</v>
+        <v>0.107904</v>
       </c>
       <c r="F126" s="7">
-        <v>0.051026999999999996</v>
+        <v>0.064318</v>
       </c>
       <c r="G126" s="7">
-        <v>0.199964</v>
+        <v>0.215198</v>
       </c>
       <c r="H126" s="7">
-        <v>0.12006800000000001</v>
+        <v>0.128128</v>
       </c>
       <c r="I126" s="7">
-        <v>0.417873</v>
+        <v>0.428077</v>
       </c>
       <c r="J126" s="7">
-        <v>2.3788970000000003</v>
+        <v>2.40937</v>
       </c>
       <c r="K126" s="7">
-        <v>9.390056</v>
+        <v>9.448407999999999</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,25 +6657,25 @@
         <v>5</v>
       </c>
       <c r="E127" s="7">
-        <v>0.034853</v>
+        <v>0.049547999999999995</v>
       </c>
       <c r="F127" s="7">
-        <v>0.026583000000000002</v>
+        <v>0.027318</v>
       </c>
       <c r="G127" s="7">
-        <v>0.090861</v>
+        <v>0.089848</v>
       </c>
       <c r="H127" s="7">
-        <v>0.043867</v>
+        <v>0.046937</v>
       </c>
       <c r="I127" s="7">
-        <v>0.276662</v>
+        <v>0.280416</v>
       </c>
       <c r="J127" s="7">
-        <v>1.982383</v>
+        <v>1.9748869999999998</v>
       </c>
       <c r="K127" s="7">
-        <v>5.525100999999999</v>
+        <v>5.605311</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6692,25 +6692,25 @@
         <v>4</v>
       </c>
       <c r="E128" s="7">
-        <v>0.055206</v>
+        <v>0.051595</v>
       </c>
       <c r="F128" s="7">
-        <v>-0.00096</v>
+        <v>0.0008699999999999999</v>
       </c>
       <c r="G128" s="7">
-        <v>0.151173</v>
+        <v>0.147176</v>
       </c>
       <c r="H128" s="7">
-        <v>0.044194000000000004</v>
+        <v>0.042699999999999995</v>
       </c>
       <c r="I128" s="7">
-        <v>0.396959</v>
+        <v>0.394961</v>
       </c>
       <c r="J128" s="7">
-        <v>1.5640710000000002</v>
+        <v>1.5576949999999998</v>
       </c>
       <c r="K128" s="7">
-        <v>3.378073</v>
+        <v>3.367046</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6727,25 +6727,25 @@
         <v>6</v>
       </c>
       <c r="E129" s="7">
-        <v>0.106036</v>
+        <v>0.112994</v>
       </c>
       <c r="F129" s="7">
-        <v>0.062696</v>
+        <v>0.074218</v>
       </c>
       <c r="G129" s="7">
-        <v>0.293172</v>
+        <v>0.309698</v>
       </c>
       <c r="H129" s="7">
-        <v>0.230514</v>
+        <v>0.232477</v>
       </c>
       <c r="I129" s="7">
-        <v>0.501328</v>
+        <v>0.503723</v>
       </c>
       <c r="J129" s="7">
-        <v>2.7432630000000002</v>
+        <v>2.740514</v>
       </c>
       <c r="K129" s="7">
-        <v>14.996687999999999</v>
+        <v>14.751498999999999</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6762,25 +6762,25 @@
         <v>4</v>
       </c>
       <c r="E130" s="7">
-        <v>0.04035999999999999</v>
+        <v>0.054179000000000005</v>
       </c>
       <c r="F130" s="7">
-        <v>0.030419</v>
+        <v>0.030825</v>
       </c>
       <c r="G130" s="7">
-        <v>0.084797</v>
+        <v>0.08374100000000001</v>
       </c>
       <c r="H130" s="7">
-        <v>0.039026</v>
+        <v>0.039743</v>
       </c>
       <c r="I130" s="7">
-        <v>0.285458</v>
+        <v>0.286344</v>
       </c>
       <c r="J130" s="7">
-        <v>2.06315</v>
+        <v>2.049912</v>
       </c>
       <c r="K130" s="7">
-        <v>6.251633000000001</v>
+        <v>6.318157</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6797,19 +6797,19 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.105215</v>
+        <v>0.134233</v>
       </c>
       <c r="F131" s="7">
-        <v>0.14523</v>
+        <v>0.147568</v>
       </c>
       <c r="G131" s="7">
-        <v>0.248872</v>
+        <v>0.245709</v>
       </c>
       <c r="H131" s="7">
-        <v>0.23952400000000001</v>
+        <v>0.24634899999999998</v>
       </c>
       <c r="I131" s="7">
-        <v>0.6822029999999999</v>
+        <v>0.691465</v>
       </c>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
@@ -6828,25 +6828,25 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.060681000000000006</v>
+        <v>0.060424</v>
       </c>
       <c r="F132" s="7">
-        <v>0.016857999999999998</v>
+        <v>0.020369</v>
       </c>
       <c r="G132" s="7">
-        <v>0.179774</v>
+        <v>0.180454</v>
       </c>
       <c r="H132" s="7">
-        <v>0.077431</v>
+        <v>0.076902</v>
       </c>
       <c r="I132" s="7">
-        <v>0.417287</v>
+        <v>0.41659</v>
       </c>
       <c r="J132" s="7">
-        <v>1.4419739999999999</v>
+        <v>1.447919</v>
       </c>
       <c r="K132" s="7">
-        <v>3.840634</v>
+        <v>3.81923</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6863,25 +6863,25 @@
         <v>3</v>
       </c>
       <c r="E133" s="7">
-        <v>0.032289</v>
+        <v>0.030496</v>
       </c>
       <c r="F133" s="7">
-        <v>0.088932</v>
+        <v>0.088671</v>
       </c>
       <c r="G133" s="7">
-        <v>0.19081199999999998</v>
+        <v>0.18851099999999998</v>
       </c>
       <c r="H133" s="7">
-        <v>0.117581</v>
+        <v>0.117996</v>
       </c>
       <c r="I133" s="7">
-        <v>0.461783</v>
+        <v>0.46232599999999996</v>
       </c>
       <c r="J133" s="7">
-        <v>2.3003839999999998</v>
+        <v>2.299453</v>
       </c>
       <c r="K133" s="7">
-        <v>3.879377</v>
+        <v>3.8587000000000002</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6898,25 +6898,25 @@
         <v>6</v>
       </c>
       <c r="E134" s="7">
-        <v>0.062784</v>
+        <v>0.06587</v>
       </c>
       <c r="F134" s="7">
-        <v>0.076486</v>
+        <v>0.07608</v>
       </c>
       <c r="G134" s="7">
-        <v>0.23979</v>
+        <v>0.24079799999999998</v>
       </c>
       <c r="H134" s="7">
-        <v>0.17010000000000003</v>
+        <v>0.171688</v>
       </c>
       <c r="I134" s="7">
-        <v>0.446317</v>
+        <v>0.44828</v>
       </c>
       <c r="J134" s="7">
-        <v>2.632928</v>
+        <v>2.653004</v>
       </c>
       <c r="K134" s="7">
-        <v>8.044818</v>
+        <v>7.985824</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6933,25 +6933,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.063849</v>
+        <v>0.06082</v>
       </c>
       <c r="F135" s="7">
-        <v>0.016877</v>
+        <v>0.018845</v>
       </c>
       <c r="G135" s="7">
-        <v>0.155363</v>
+        <v>0.152129</v>
       </c>
       <c r="H135" s="7">
-        <v>0.07316600000000001</v>
+        <v>0.070389</v>
       </c>
       <c r="I135" s="7">
-        <v>0.356659</v>
+        <v>0.353149</v>
       </c>
       <c r="J135" s="7">
-        <v>1.02722</v>
+        <v>1.033652</v>
       </c>
       <c r="K135" s="7">
-        <v>2.471986</v>
+        <v>2.4562049999999997</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6968,25 +6968,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.066919</v>
+        <v>0.07793599999999999</v>
       </c>
       <c r="F136" s="7">
-        <v>0.089873</v>
+        <v>0.09787900000000001</v>
       </c>
       <c r="G136" s="7">
-        <v>0.177738</v>
+        <v>0.188599</v>
       </c>
       <c r="H136" s="7">
-        <v>0.14514</v>
+        <v>0.15326800000000002</v>
       </c>
       <c r="I136" s="7">
-        <v>0.41710200000000003</v>
+        <v>0.42716</v>
       </c>
       <c r="J136" s="7">
-        <v>3.056446</v>
+        <v>3.062061</v>
       </c>
       <c r="K136" s="7">
-        <v>9.332928</v>
+        <v>9.423292</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7003,25 +7003,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.051071</v>
+        <v>0.052245</v>
       </c>
       <c r="F137" s="7">
-        <v>0.050334000000000004</v>
+        <v>0.053074</v>
       </c>
       <c r="G137" s="7">
-        <v>0.17693</v>
+        <v>0.178141</v>
       </c>
       <c r="H137" s="7">
-        <v>0.100558</v>
+        <v>0.101819</v>
       </c>
       <c r="I137" s="7">
-        <v>0.430167</v>
+        <v>0.43180599999999997</v>
       </c>
       <c r="J137" s="7">
-        <v>2.165848</v>
+        <v>2.167304</v>
       </c>
       <c r="K137" s="7">
-        <v>4.155212000000001</v>
+        <v>4.160398</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7038,22 +7038,22 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.174866</v>
+        <v>0.220118</v>
       </c>
       <c r="F138" s="7">
-        <v>0.116002</v>
+        <v>0.131344</v>
       </c>
       <c r="G138" s="7">
-        <v>0.262377</v>
+        <v>0.264173</v>
       </c>
       <c r="H138" s="7">
-        <v>0.21575399999999997</v>
+        <v>0.234408</v>
       </c>
       <c r="I138" s="7">
-        <v>0.833508</v>
+        <v>0.8616410000000001</v>
       </c>
       <c r="J138" s="7">
-        <v>5.1732439999999995</v>
+        <v>5.20171</v>
       </c>
       <c r="K138" s="7"/>
     </row>
@@ -7071,22 +7071,22 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.0797</v>
+        <v>0.08767799999999999</v>
       </c>
       <c r="F139" s="7">
-        <v>0.016359</v>
+        <v>0.021563</v>
       </c>
       <c r="G139" s="7">
-        <v>0.193333</v>
+        <v>0.20298200000000002</v>
       </c>
       <c r="H139" s="7">
-        <v>0.109065</v>
+        <v>0.114744</v>
       </c>
       <c r="I139" s="7">
-        <v>0.5229699999999999</v>
+        <v>0.530768</v>
       </c>
       <c r="J139" s="7">
-        <v>4.658306</v>
+        <v>4.711024</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,25 +7104,25 @@
         <v>3</v>
       </c>
       <c r="E140" s="7">
-        <v>0.048278999999999996</v>
+        <v>0.048228</v>
       </c>
       <c r="F140" s="7">
-        <v>0.027149999999999997</v>
+        <v>0.029464</v>
       </c>
       <c r="G140" s="7">
-        <v>0.163578</v>
+        <v>0.16296600000000003</v>
       </c>
       <c r="H140" s="7">
-        <v>0.088014</v>
+        <v>0.087821</v>
       </c>
       <c r="I140" s="7">
-        <v>0.371995</v>
+        <v>0.37175199999999997</v>
       </c>
       <c r="J140" s="7">
-        <v>1.617179</v>
+        <v>1.6188650000000002</v>
       </c>
       <c r="K140" s="7">
-        <v>3.642151</v>
+        <v>3.6351620000000002</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7139,25 +7139,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.035396000000000004</v>
+        <v>0.036978</v>
       </c>
       <c r="F141" s="7">
-        <v>0.056532</v>
+        <v>0.059901</v>
       </c>
       <c r="G141" s="7">
-        <v>0.176942</v>
+        <v>0.178676</v>
       </c>
       <c r="H141" s="7">
-        <v>0.112178</v>
+        <v>0.115207</v>
       </c>
       <c r="I141" s="7">
-        <v>0.347224</v>
+        <v>0.350893</v>
       </c>
       <c r="J141" s="7">
-        <v>1.361284</v>
+        <v>1.367659</v>
       </c>
       <c r="K141" s="7">
-        <v>4.461556</v>
+        <v>4.461825</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,25 +7174,25 @@
         <v>5</v>
       </c>
       <c r="E142" s="7">
-        <v>0.064996</v>
+        <v>0.087984</v>
       </c>
       <c r="F142" s="7">
-        <v>0.028127</v>
+        <v>0.054063</v>
       </c>
       <c r="G142" s="7">
-        <v>0.20324899999999999</v>
+        <v>0.214637</v>
       </c>
       <c r="H142" s="7">
-        <v>0.13857</v>
+        <v>0.16015999999999997</v>
       </c>
       <c r="I142" s="7">
-        <v>0.34538800000000003</v>
+        <v>0.3709</v>
       </c>
       <c r="J142" s="7">
-        <v>3.05387</v>
+        <v>3.1210489999999997</v>
       </c>
       <c r="K142" s="7">
-        <v>13.574173</v>
+        <v>13.746018</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7209,25 +7209,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.077109</v>
+        <v>0.08302899999999999</v>
       </c>
       <c r="F143" s="7">
-        <v>0.17323799999999998</v>
+        <v>0.17784</v>
       </c>
       <c r="G143" s="7">
-        <v>0.17571799999999999</v>
+        <v>0.19139099999999998</v>
       </c>
       <c r="H143" s="7">
-        <v>0.2867</v>
+        <v>0.289727</v>
       </c>
       <c r="I143" s="7">
-        <v>0.280292</v>
+        <v>0.283304</v>
       </c>
       <c r="J143" s="7">
-        <v>3.6054450000000005</v>
+        <v>3.575811</v>
       </c>
       <c r="K143" s="7">
-        <v>11.056383</v>
+        <v>11.061622999999999</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7244,25 +7244,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.08786899999999999</v>
+        <v>0.092172</v>
       </c>
       <c r="F144" s="7">
-        <v>0.09469699999999999</v>
+        <v>0.10269299999999999</v>
       </c>
       <c r="G144" s="7">
-        <v>0.304651</v>
+        <v>0.313739</v>
       </c>
       <c r="H144" s="7">
-        <v>0.19846</v>
+        <v>0.20175</v>
       </c>
       <c r="I144" s="7">
-        <v>0.567389</v>
+        <v>0.571692</v>
       </c>
       <c r="J144" s="7">
-        <v>2.92623</v>
+        <v>2.940766</v>
       </c>
       <c r="K144" s="7">
-        <v>8.226077</v>
+        <v>8.233375</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7279,25 +7279,25 @@
         <v>4</v>
       </c>
       <c r="E145" s="7">
-        <v>0.080294</v>
+        <v>0.083645</v>
       </c>
       <c r="F145" s="7">
-        <v>0.051674</v>
+        <v>0.058521000000000004</v>
       </c>
       <c r="G145" s="7">
-        <v>0.254782</v>
+        <v>0.26213000000000003</v>
       </c>
       <c r="H145" s="7">
-        <v>0.170871</v>
+        <v>0.17211400000000002</v>
       </c>
       <c r="I145" s="7">
-        <v>0.524288</v>
+        <v>0.525907</v>
       </c>
       <c r="J145" s="7">
-        <v>3.393429</v>
+        <v>3.392167</v>
       </c>
       <c r="K145" s="7">
-        <v>9.619115</v>
+        <v>9.524428</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7314,25 +7314,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.027611</v>
+        <v>0.032996</v>
       </c>
       <c r="F146" s="7">
-        <v>0.152277</v>
+        <v>0.159735</v>
       </c>
       <c r="G146" s="7">
-        <v>0.33575499999999997</v>
+        <v>0.36170900000000006</v>
       </c>
       <c r="H146" s="7">
-        <v>0.255474</v>
+        <v>0.26354099999999997</v>
       </c>
       <c r="I146" s="7">
-        <v>0.61562</v>
+        <v>0.626001</v>
       </c>
       <c r="J146" s="7">
-        <v>3.161638</v>
+        <v>3.1759609999999996</v>
       </c>
       <c r="K146" s="7">
-        <v>9.308039</v>
+        <v>9.397463</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7349,25 +7349,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.039247000000000004</v>
+        <v>0.038252</v>
       </c>
       <c r="F147" s="7">
-        <v>0.078198</v>
+        <v>0.079488</v>
       </c>
       <c r="G147" s="7">
-        <v>0.19583899999999999</v>
+        <v>0.196494</v>
       </c>
       <c r="H147" s="7">
-        <v>0.131059</v>
+        <v>0.13109500000000002</v>
       </c>
       <c r="I147" s="7">
-        <v>0.464507</v>
+        <v>0.464553</v>
       </c>
       <c r="J147" s="7">
-        <v>2.18812</v>
+        <v>2.190935</v>
       </c>
       <c r="K147" s="7">
-        <v>6.584722</v>
+        <v>6.535962</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7384,25 +7384,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.051918</v>
+        <v>0.05420899999999999</v>
       </c>
       <c r="F148" s="7">
-        <v>0.018193</v>
+        <v>0.018861000000000003</v>
       </c>
       <c r="G148" s="7">
-        <v>0.216642</v>
+        <v>0.232484</v>
       </c>
       <c r="H148" s="7">
-        <v>0.131962</v>
+        <v>0.13127</v>
       </c>
       <c r="I148" s="7">
-        <v>0.565821</v>
+        <v>0.564863</v>
       </c>
       <c r="J148" s="7">
-        <v>3.305086</v>
+        <v>3.299288</v>
       </c>
       <c r="K148" s="7">
-        <v>9.680376</v>
+        <v>9.658101</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7419,25 +7419,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.044043</v>
+        <v>0.047882999999999995</v>
       </c>
       <c r="F149" s="7">
-        <v>0.064119</v>
+        <v>0.069569</v>
       </c>
       <c r="G149" s="7">
-        <v>0.171214</v>
+        <v>0.17651</v>
       </c>
       <c r="H149" s="7">
-        <v>0.126561</v>
+        <v>0.131601</v>
       </c>
       <c r="I149" s="7">
-        <v>0.381984</v>
+        <v>0.388167</v>
       </c>
       <c r="J149" s="7">
-        <v>1.4200249999999999</v>
+        <v>1.431154</v>
       </c>
       <c r="K149" s="7">
-        <v>4.2365390000000005</v>
+        <v>4.236893</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7454,25 +7454,25 @@
         <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>0.094641</v>
+        <v>0.11089</v>
       </c>
       <c r="F150" s="7">
-        <v>0.081952</v>
+        <v>0.09825400000000001</v>
       </c>
       <c r="G150" s="7">
-        <v>0.240596</v>
+        <v>0.257682</v>
       </c>
       <c r="H150" s="7">
-        <v>0.225548</v>
+        <v>0.239448</v>
       </c>
       <c r="I150" s="7">
-        <v>0.534462</v>
+        <v>0.551866</v>
       </c>
       <c r="J150" s="7">
-        <v>2.596427</v>
+        <v>2.6500869999999996</v>
       </c>
       <c r="K150" s="7">
-        <v>8.572493</v>
+        <v>8.542666</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7489,25 +7489,25 @@
         <v>7</v>
       </c>
       <c r="E151" s="7">
-        <v>0.081113</v>
+        <v>0.09380000000000001</v>
       </c>
       <c r="F151" s="7">
-        <v>0.08458600000000001</v>
+        <v>0.097785</v>
       </c>
       <c r="G151" s="7">
-        <v>0.234528</v>
+        <v>0.248459</v>
       </c>
       <c r="H151" s="7">
-        <v>0.205155</v>
+        <v>0.21651700000000002</v>
       </c>
       <c r="I151" s="7">
-        <v>0.5301100000000001</v>
+        <v>0.544535</v>
       </c>
       <c r="J151" s="7">
-        <v>2.500226</v>
+        <v>2.542554</v>
       </c>
       <c r="K151" s="7">
-        <v>7.3610500000000005</v>
+        <v>7.412177000000001</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7524,25 +7524,25 @@
         <v>3</v>
       </c>
       <c r="E152" s="7">
-        <v>0.045399</v>
+        <v>0.044927999999999996</v>
       </c>
       <c r="F152" s="7">
-        <v>0.074889</v>
+        <v>0.07558</v>
       </c>
       <c r="G152" s="7">
-        <v>0.207899</v>
+        <v>0.207043</v>
       </c>
       <c r="H152" s="7">
-        <v>0.122977</v>
+        <v>0.12375299999999999</v>
       </c>
       <c r="I152" s="7">
-        <v>0.481892</v>
+        <v>0.482916</v>
       </c>
       <c r="J152" s="7">
-        <v>2.955916</v>
+        <v>2.957951</v>
       </c>
       <c r="K152" s="7">
-        <v>5.072681</v>
+        <v>5.075643</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7559,22 +7559,22 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.044379999999999996</v>
+        <v>0.055698</v>
       </c>
       <c r="F153" s="7">
-        <v>0.020415000000000003</v>
+        <v>0.033386</v>
       </c>
       <c r="G153" s="7">
-        <v>0.16856300000000002</v>
+        <v>0.18353999999999998</v>
       </c>
       <c r="H153" s="7">
-        <v>0.113642</v>
+        <v>0.122196</v>
       </c>
       <c r="I153" s="7">
-        <v>0.474853</v>
+        <v>0.486182</v>
       </c>
       <c r="J153" s="7">
-        <v>3.378763</v>
+        <v>3.3895929999999996</v>
       </c>
       <c r="K153" s="7"/>
     </row>
@@ -7592,16 +7592,16 @@
         <v>4</v>
       </c>
       <c r="E154" s="7">
-        <v>0.055129000000000004</v>
+        <v>0.056988000000000004</v>
       </c>
       <c r="F154" s="7">
-        <v>0.08463</v>
+        <v>0.08488899999999999</v>
       </c>
       <c r="G154" s="7">
-        <v>0.254651</v>
+        <v>0.263052</v>
       </c>
       <c r="H154" s="7">
-        <v>0.18500599999999998</v>
+        <v>0.187962</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
@@ -7621,22 +7621,22 @@
         <v>6</v>
       </c>
       <c r="E155" s="7">
-        <v>0.096275</v>
+        <v>0.110738</v>
       </c>
       <c r="F155" s="7">
-        <v>0.08371100000000001</v>
+        <v>0.09342800000000001</v>
       </c>
       <c r="G155" s="7">
-        <v>0.229043</v>
+        <v>0.236051</v>
       </c>
       <c r="H155" s="7">
-        <v>0.183367</v>
+        <v>0.18954000000000001</v>
       </c>
       <c r="I155" s="7">
-        <v>0.449606</v>
+        <v>0.457168</v>
       </c>
       <c r="J155" s="7">
-        <v>1.7902500000000001</v>
+        <v>1.783164</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7654,25 +7654,25 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.058098000000000004</v>
+        <v>0.061981</v>
       </c>
       <c r="F156" s="7">
-        <v>0.090236</v>
+        <v>0.095348</v>
       </c>
       <c r="G156" s="7">
-        <v>0.240517</v>
+        <v>0.24590299999999998</v>
       </c>
       <c r="H156" s="7">
-        <v>0.165333</v>
+        <v>0.170814</v>
       </c>
       <c r="I156" s="7">
-        <v>0.535826</v>
+        <v>0.54305</v>
       </c>
       <c r="J156" s="7">
-        <v>2.362713</v>
+        <v>2.3726830000000003</v>
       </c>
       <c r="K156" s="7">
-        <v>6.456091</v>
+        <v>6.450358</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7689,25 +7689,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.05934300000000001</v>
+        <v>0.062993</v>
       </c>
       <c r="F157" s="7">
-        <v>0.09192700000000001</v>
+        <v>0.09751599999999999</v>
       </c>
       <c r="G157" s="7">
-        <v>0.23078700000000002</v>
+        <v>0.236425</v>
       </c>
       <c r="H157" s="7">
-        <v>0.16438199999999997</v>
+        <v>0.17025400000000002</v>
       </c>
       <c r="I157" s="7">
-        <v>0.49341999999999997</v>
+        <v>0.500951</v>
       </c>
       <c r="J157" s="7">
-        <v>2.140988</v>
+        <v>2.154712</v>
       </c>
       <c r="K157" s="7">
-        <v>5.963711</v>
+        <v>5.960001999999999</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7724,25 +7724,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.04295</v>
+        <v>0.045980999999999994</v>
       </c>
       <c r="F158" s="7">
-        <v>0.067839</v>
+        <v>0.067993</v>
       </c>
       <c r="G158" s="7">
-        <v>0.201416</v>
+        <v>0.20494</v>
       </c>
       <c r="H158" s="7">
-        <v>0.130021</v>
+        <v>0.134723</v>
       </c>
       <c r="I158" s="7">
-        <v>0.431182</v>
+        <v>0.43713700000000005</v>
       </c>
       <c r="J158" s="7">
-        <v>1.806151</v>
+        <v>1.8166229999999999</v>
       </c>
       <c r="K158" s="7">
-        <v>5.048667</v>
+        <v>5.058482000000001</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,22 +7759,22 @@
         <v>5</v>
       </c>
       <c r="E159" s="7">
-        <v>0.130989</v>
+        <v>0.17212700000000003</v>
       </c>
       <c r="F159" s="7">
-        <v>0.142812</v>
+        <v>0.160044</v>
       </c>
       <c r="G159" s="7">
-        <v>0.269446</v>
+        <v>0.27843599999999996</v>
       </c>
       <c r="H159" s="7">
-        <v>0.246024</v>
+        <v>0.266758</v>
       </c>
       <c r="I159" s="7">
-        <v>0.7152670000000001</v>
+        <v>0.74381</v>
       </c>
       <c r="J159" s="7">
-        <v>3.8468669999999996</v>
+        <v>3.924038</v>
       </c>
       <c r="K159" s="7"/>
     </row>
@@ -7792,25 +7792,25 @@
         <v>4</v>
       </c>
       <c r="E160" s="7">
-        <v>0.055207</v>
+        <v>0.056684</v>
       </c>
       <c r="F160" s="7">
-        <v>0.03104</v>
+        <v>0.032818</v>
       </c>
       <c r="G160" s="7">
-        <v>0.2041</v>
+        <v>0.203924</v>
       </c>
       <c r="H160" s="7">
-        <v>0.096073</v>
+        <v>0.096433</v>
       </c>
       <c r="I160" s="7">
-        <v>0.431423</v>
+        <v>0.431893</v>
       </c>
       <c r="J160" s="7">
-        <v>2.040952</v>
+        <v>2.032173</v>
       </c>
       <c r="K160" s="7">
-        <v>5.682847000000001</v>
+        <v>5.673324</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,22 +7827,22 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.032143000000000005</v>
+        <v>0.034249</v>
       </c>
       <c r="F161" s="7">
-        <v>0.08972</v>
+        <v>0.08825</v>
       </c>
       <c r="G161" s="7">
-        <v>0.225414</v>
+        <v>0.225093</v>
       </c>
       <c r="H161" s="7">
-        <v>0.146645</v>
+        <v>0.149875</v>
       </c>
       <c r="I161" s="7">
-        <v>0.529865</v>
+        <v>0.534175</v>
       </c>
       <c r="J161" s="7">
-        <v>3.3429520000000004</v>
+        <v>3.369713</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7860,22 +7860,22 @@
         <v>6</v>
       </c>
       <c r="E162" s="7">
-        <v>0.06375600000000001</v>
+        <v>0.080069</v>
       </c>
       <c r="F162" s="7">
-        <v>0.007496</v>
+        <v>0.006229</v>
       </c>
       <c r="G162" s="7">
-        <v>0.127069</v>
+        <v>0.131731</v>
       </c>
       <c r="H162" s="7">
-        <v>0.07186</v>
+        <v>0.078052</v>
       </c>
       <c r="I162" s="7">
-        <v>0.416071</v>
+        <v>0.42424999999999996</v>
       </c>
       <c r="J162" s="7">
-        <v>2.627273</v>
+        <v>2.6194330000000003</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,25 +7893,25 @@
         <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>0.09351699999999999</v>
+        <v>0.10588800000000001</v>
       </c>
       <c r="F163" s="7">
-        <v>0.103358</v>
+        <v>0.109983</v>
       </c>
       <c r="G163" s="7">
-        <v>0.29404399999999997</v>
+        <v>0.308081</v>
       </c>
       <c r="H163" s="7">
-        <v>0.24563300000000002</v>
+        <v>0.257711</v>
       </c>
       <c r="I163" s="7">
-        <v>0.622313</v>
+        <v>0.638043</v>
       </c>
       <c r="J163" s="7">
-        <v>2.455545</v>
+        <v>2.481781</v>
       </c>
       <c r="K163" s="7">
-        <v>8.672003</v>
+        <v>8.731601000000001</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7928,25 +7928,25 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.105944</v>
+        <v>0.11754400000000001</v>
       </c>
       <c r="F164" s="7">
-        <v>0.091727</v>
+        <v>0.10716799999999999</v>
       </c>
       <c r="G164" s="7">
-        <v>0.328694</v>
+        <v>0.35076799999999997</v>
       </c>
       <c r="H164" s="7">
-        <v>0.27571100000000004</v>
+        <v>0.28527</v>
       </c>
       <c r="I164" s="7">
-        <v>0.620787</v>
+        <v>0.632931</v>
       </c>
       <c r="J164" s="7">
-        <v>1.965543</v>
+        <v>1.9845650000000001</v>
       </c>
       <c r="K164" s="7">
-        <v>3.606317</v>
+        <v>3.6382920000000003</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7963,25 +7963,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.10990899999999999</v>
+        <v>0.116914</v>
       </c>
       <c r="F165" s="7">
-        <v>0.06911400000000001</v>
+        <v>0.07845200000000001</v>
       </c>
       <c r="G165" s="7">
-        <v>0.295979</v>
+        <v>0.31222</v>
       </c>
       <c r="H165" s="7">
-        <v>0.236154</v>
+        <v>0.239433</v>
       </c>
       <c r="I165" s="7">
-        <v>0.464968</v>
+        <v>0.468854</v>
       </c>
       <c r="J165" s="7">
-        <v>2.854275</v>
+        <v>2.8562819999999998</v>
       </c>
       <c r="K165" s="7">
-        <v>16.33059</v>
+        <v>16.104955</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7998,25 +7998,25 @@
         <v>3</v>
       </c>
       <c r="E166" s="7">
-        <v>0.04937299999999999</v>
+        <v>0.047411</v>
       </c>
       <c r="F166" s="7">
-        <v>0.0105</v>
+        <v>0.00966</v>
       </c>
       <c r="G166" s="7">
-        <v>0.156396</v>
+        <v>0.14935</v>
       </c>
       <c r="H166" s="7">
-        <v>0.049370000000000004</v>
+        <v>0.046952999999999995</v>
       </c>
       <c r="I166" s="7">
-        <v>0.405998</v>
+        <v>0.40276</v>
       </c>
       <c r="J166" s="7">
-        <v>1.893385</v>
+        <v>1.881268</v>
       </c>
       <c r="K166" s="7">
-        <v>4.011591</v>
+        <v>3.9907960000000005</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8033,25 +8033,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.048106</v>
+        <v>0.051876</v>
       </c>
       <c r="F167" s="7">
-        <v>0.08299200000000001</v>
+        <v>0.087944</v>
       </c>
       <c r="G167" s="7">
-        <v>0.233375</v>
+        <v>0.23839</v>
       </c>
       <c r="H167" s="7">
-        <v>0.156023</v>
+        <v>0.161053</v>
       </c>
       <c r="I167" s="7">
-        <v>0.459993</v>
+        <v>0.466346</v>
       </c>
       <c r="J167" s="7">
-        <v>1.869161</v>
+        <v>1.880776</v>
       </c>
       <c r="K167" s="7">
-        <v>5.446191</v>
+        <v>5.442304</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8068,25 +8068,25 @@
         <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>0.025009999999999998</v>
+        <v>0.026552</v>
       </c>
       <c r="F168" s="7">
-        <v>0.060808</v>
+        <v>0.061668</v>
       </c>
       <c r="G168" s="7">
-        <v>0.124247</v>
+        <v>0.124998</v>
       </c>
       <c r="H168" s="7">
-        <v>0.078451</v>
+        <v>0.080236</v>
       </c>
       <c r="I168" s="7">
-        <v>0.301541</v>
+        <v>0.303695</v>
       </c>
       <c r="J168" s="7">
-        <v>1.960088</v>
+        <v>1.9583840000000001</v>
       </c>
       <c r="K168" s="7">
-        <v>5.454737</v>
+        <v>5.512133</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8103,22 +8103,22 @@
         <v>6</v>
       </c>
       <c r="E169" s="7">
-        <v>0.035706</v>
+        <v>0.044786</v>
       </c>
       <c r="F169" s="7">
-        <v>-0.059077000000000005</v>
+        <v>-0.068348</v>
       </c>
       <c r="G169" s="7">
-        <v>0.152907</v>
+        <v>0.16606</v>
       </c>
       <c r="H169" s="7">
-        <v>0.101258</v>
+        <v>0.105838</v>
       </c>
       <c r="I169" s="7">
-        <v>0.612178</v>
+        <v>0.6188819999999999</v>
       </c>
       <c r="J169" s="7">
-        <v>4.740181</v>
+        <v>4.758781</v>
       </c>
       <c r="K169" s="7"/>
     </row>
@@ -8136,22 +8136,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>0.112014</v>
+        <v>0.127535</v>
       </c>
       <c r="F170" s="7">
-        <v>0.074477</v>
+        <v>0.08920299999999999</v>
       </c>
       <c r="G170" s="7">
-        <v>0.23366800000000001</v>
+        <v>0.247055</v>
       </c>
       <c r="H170" s="7">
-        <v>0.203487</v>
+        <v>0.211876</v>
       </c>
       <c r="I170" s="7">
-        <v>0.471663</v>
+        <v>0.481922</v>
       </c>
       <c r="J170" s="7">
-        <v>2.450002</v>
+        <v>2.458487</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,16 +8169,16 @@
         <v>7</v>
       </c>
       <c r="E171" s="7">
-        <v>0.090143</v>
+        <v>0.093607</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.238343</v>
+        <v>-0.261261</v>
       </c>
       <c r="G171" s="7">
-        <v>0.6027239999999999</v>
+        <v>0.625799</v>
       </c>
       <c r="H171" s="7">
-        <v>0.070896</v>
+        <v>0.061726</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7"/>
@@ -8198,25 +8198,25 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.027593</v>
+        <v>0.028508</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.061032</v>
+        <v>-0.069379</v>
       </c>
       <c r="G172" s="7">
-        <v>0.135634</v>
+        <v>0.150763</v>
       </c>
       <c r="H172" s="7">
-        <v>0.072852</v>
+        <v>0.072081</v>
       </c>
       <c r="I172" s="7">
-        <v>0.589005</v>
+        <v>0.587864</v>
       </c>
       <c r="J172" s="7">
-        <v>4.175332</v>
+        <v>4.122723</v>
       </c>
       <c r="K172" s="7">
-        <v>13.612381000000001</v>
+        <v>13.69376</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8233,25 +8233,25 @@
         <v>4</v>
       </c>
       <c r="E173" s="7">
-        <v>0.065564</v>
+        <v>0.06697499999999999</v>
       </c>
       <c r="F173" s="7">
-        <v>0.030689</v>
+        <v>0.034285</v>
       </c>
       <c r="G173" s="7">
-        <v>0.21358</v>
+        <v>0.21552800000000003</v>
       </c>
       <c r="H173" s="7">
-        <v>0.107049</v>
+        <v>0.10788600000000001</v>
       </c>
       <c r="I173" s="7">
-        <v>0.452359</v>
+        <v>0.453457</v>
       </c>
       <c r="J173" s="7">
-        <v>2.045259</v>
+        <v>2.038168</v>
       </c>
       <c r="K173" s="7">
-        <v>5.4401779999999995</v>
+        <v>5.4215219999999995</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8268,25 +8268,25 @@
         <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>0.086448</v>
+        <v>0.093105</v>
       </c>
       <c r="F174" s="7">
-        <v>0.067785</v>
+        <v>0.073585</v>
       </c>
       <c r="G174" s="7">
-        <v>0.258815</v>
+        <v>0.26777</v>
       </c>
       <c r="H174" s="7">
-        <v>0.209262</v>
+        <v>0.212246</v>
       </c>
       <c r="I174" s="7">
-        <v>0.46263800000000005</v>
+        <v>0.46624699999999997</v>
       </c>
       <c r="J174" s="7">
-        <v>2.702812</v>
+        <v>2.7047070000000004</v>
       </c>
       <c r="K174" s="7">
-        <v>10.604233999999998</v>
+        <v>10.546201000000002</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8303,25 +8303,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.039524</v>
+        <v>0.053495</v>
       </c>
       <c r="F175" s="7">
-        <v>0.037925</v>
+        <v>0.039452</v>
       </c>
       <c r="G175" s="7">
-        <v>0.101631</v>
+        <v>0.102114</v>
       </c>
       <c r="H175" s="7">
-        <v>0.051619</v>
+        <v>0.054005</v>
       </c>
       <c r="I175" s="7">
-        <v>0.310512</v>
+        <v>0.313485</v>
       </c>
       <c r="J175" s="7">
-        <v>2.115482</v>
+        <v>2.103692</v>
       </c>
       <c r="K175" s="7">
-        <v>6.273201</v>
+        <v>6.347159</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8338,25 +8338,25 @@
         <v>6</v>
       </c>
       <c r="E176" s="7">
-        <v>0.107492</v>
+        <v>0.124479</v>
       </c>
       <c r="F176" s="7">
-        <v>0.081318</v>
+        <v>0.092197</v>
       </c>
       <c r="G176" s="7">
-        <v>0.247038</v>
+        <v>0.252453</v>
       </c>
       <c r="H176" s="7">
-        <v>0.187922</v>
+        <v>0.19587900000000003</v>
       </c>
       <c r="I176" s="7">
-        <v>0.590317</v>
+        <v>0.600969</v>
       </c>
       <c r="J176" s="7">
-        <v>2.920988</v>
+        <v>2.92371</v>
       </c>
       <c r="K176" s="7">
-        <v>12.352285</v>
+        <v>12.42598</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,25 +8373,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.102064</v>
+        <v>0.112018</v>
       </c>
       <c r="F177" s="7">
-        <v>0.08476800000000001</v>
+        <v>0.093842</v>
       </c>
       <c r="G177" s="7">
-        <v>0.332593</v>
+        <v>0.348238</v>
       </c>
       <c r="H177" s="7">
-        <v>0.25139700000000004</v>
+        <v>0.257227</v>
       </c>
       <c r="I177" s="7">
-        <v>0.550739</v>
+        <v>0.557963</v>
       </c>
       <c r="J177" s="7">
-        <v>3.222334</v>
+        <v>3.232072</v>
       </c>
       <c r="K177" s="7">
-        <v>17.661279999999998</v>
+        <v>17.58039</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8408,25 +8408,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.083833</v>
+        <v>0.09028900000000001</v>
       </c>
       <c r="F178" s="7">
-        <v>0.080931</v>
+        <v>0.086701</v>
       </c>
       <c r="G178" s="7">
-        <v>0.30872900000000003</v>
+        <v>0.320154</v>
       </c>
       <c r="H178" s="7">
-        <v>0.21049900000000002</v>
+        <v>0.214007</v>
       </c>
       <c r="I178" s="7">
-        <v>0.5162789999999999</v>
+        <v>0.520674</v>
       </c>
       <c r="J178" s="7">
-        <v>3.120312</v>
+        <v>3.121603</v>
       </c>
       <c r="K178" s="7">
-        <v>13.087851</v>
+        <v>13.04536</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,25 +8443,25 @@
         <v>4</v>
       </c>
       <c r="E179" s="7">
-        <v>0.078373</v>
+        <v>0.081759</v>
       </c>
       <c r="F179" s="7">
-        <v>0.07412099999999999</v>
+        <v>0.07858</v>
       </c>
       <c r="G179" s="7">
-        <v>0.282866</v>
+        <v>0.291525</v>
       </c>
       <c r="H179" s="7">
-        <v>0.17904399999999998</v>
+        <v>0.182331</v>
       </c>
       <c r="I179" s="7">
-        <v>0.53665</v>
+        <v>0.5409349999999999</v>
       </c>
       <c r="J179" s="7">
-        <v>3.386816</v>
+        <v>3.3909269999999996</v>
       </c>
       <c r="K179" s="7">
-        <v>11.361016999999999</v>
+        <v>11.338164999999998</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8478,25 +8478,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.089992</v>
+        <v>0.10837400000000001</v>
       </c>
       <c r="F180" s="7">
-        <v>0.05344</v>
+        <v>0.050092</v>
       </c>
       <c r="G180" s="7">
-        <v>0.153552</v>
+        <v>0.15331899999999998</v>
       </c>
       <c r="H180" s="7">
-        <v>0.11002</v>
+        <v>0.115927</v>
       </c>
       <c r="I180" s="7">
-        <v>0.562257</v>
+        <v>0.5705709999999999</v>
       </c>
       <c r="J180" s="7">
-        <v>3.281997</v>
+        <v>3.269523</v>
       </c>
       <c r="K180" s="7">
-        <v>8.239853</v>
+        <v>8.3633</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8513,25 +8513,25 @@
         <v>2</v>
       </c>
       <c r="E181" s="7">
-        <v>0.043236</v>
+        <v>0.044076000000000004</v>
       </c>
       <c r="F181" s="7">
-        <v>0.081622</v>
+        <v>0.080836</v>
       </c>
       <c r="G181" s="7">
-        <v>0.212499</v>
+        <v>0.21327200000000002</v>
       </c>
       <c r="H181" s="7">
-        <v>0.126453</v>
+        <v>0.12725799999999998</v>
       </c>
       <c r="I181" s="7">
-        <v>0.49264</v>
+        <v>0.49370600000000003</v>
       </c>
       <c r="J181" s="7">
-        <v>3.342325</v>
+        <v>3.338848</v>
       </c>
       <c r="K181" s="7">
-        <v>6.307188</v>
+        <v>6.3094399999999995</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8548,25 +8548,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.07685399999999999</v>
+        <v>0.08326499999999999</v>
       </c>
       <c r="F182" s="7">
-        <v>0.046083</v>
+        <v>0.051628999999999994</v>
       </c>
       <c r="G182" s="7">
-        <v>0.125699</v>
+        <v>0.134566</v>
       </c>
       <c r="H182" s="7">
-        <v>0.15608</v>
+        <v>0.15969</v>
       </c>
       <c r="I182" s="7">
-        <v>0.354805</v>
+        <v>0.35903599999999997</v>
       </c>
       <c r="J182" s="7">
-        <v>2.429229</v>
+        <v>2.436979</v>
       </c>
       <c r="K182" s="7">
-        <v>3.921868</v>
+        <v>3.935333</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8583,25 +8583,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.10239000000000001</v>
+        <v>0.120547</v>
       </c>
       <c r="F183" s="7">
-        <v>0.105194</v>
+        <v>0.11649100000000001</v>
       </c>
       <c r="G183" s="7">
-        <v>0.34919199999999995</v>
+        <v>0.369752</v>
       </c>
       <c r="H183" s="7">
-        <v>0.301805</v>
+        <v>0.319469</v>
       </c>
       <c r="I183" s="7">
-        <v>0.653931</v>
+        <v>0.6763720000000001</v>
       </c>
       <c r="J183" s="7">
-        <v>3.094857</v>
+        <v>3.139801</v>
       </c>
       <c r="K183" s="7">
-        <v>12.987163</v>
+        <v>13.024517000000001</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8618,25 +8618,25 @@
         <v>3</v>
       </c>
       <c r="E184" s="7">
-        <v>0.030817999999999998</v>
+        <v>0.028676</v>
       </c>
       <c r="F184" s="7">
-        <v>0.08917199999999999</v>
+        <v>0.08910299999999999</v>
       </c>
       <c r="G184" s="7">
-        <v>0.194427</v>
+        <v>0.194456</v>
       </c>
       <c r="H184" s="7">
-        <v>0.11610200000000001</v>
+        <v>0.11723499999999999</v>
       </c>
       <c r="I184" s="7">
-        <v>0.454876</v>
+        <v>0.456352</v>
       </c>
       <c r="J184" s="7">
-        <v>1.70859</v>
+        <v>1.7105199999999998</v>
       </c>
       <c r="K184" s="7">
-        <v>3.8073970000000004</v>
+        <v>3.810271</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8653,25 +8653,25 @@
         <v>5</v>
       </c>
       <c r="E185" s="7">
-        <v>0.084103</v>
+        <v>0.097982</v>
       </c>
       <c r="F185" s="7">
-        <v>0.09536</v>
+        <v>0.103382</v>
       </c>
       <c r="G185" s="7">
-        <v>0.273574</v>
+        <v>0.287674</v>
       </c>
       <c r="H185" s="7">
-        <v>0.227323</v>
+        <v>0.23962</v>
       </c>
       <c r="I185" s="7">
-        <v>0.5949949999999999</v>
+        <v>0.6109749999999999</v>
       </c>
       <c r="J185" s="7">
-        <v>2.9064210000000004</v>
+        <v>2.935547</v>
       </c>
       <c r="K185" s="7">
-        <v>11.140324</v>
+        <v>11.162112</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8688,25 +8688,25 @@
         <v>2</v>
       </c>
       <c r="E186" s="7">
-        <v>0.031086999999999997</v>
+        <v>0.028967</v>
       </c>
       <c r="F186" s="7">
-        <v>0.089121</v>
+        <v>0.089109</v>
       </c>
       <c r="G186" s="7">
-        <v>0.191484</v>
+        <v>0.19156199999999998</v>
       </c>
       <c r="H186" s="7">
-        <v>0.11568899999999999</v>
+        <v>0.116829</v>
       </c>
       <c r="I186" s="7">
-        <v>0.44918399999999997</v>
+        <v>0.450664</v>
       </c>
       <c r="J186" s="7">
-        <v>1.821433</v>
+        <v>1.8238489999999998</v>
       </c>
       <c r="K186" s="7">
-        <v>3.318614</v>
+        <v>3.32139</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8723,25 +8723,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.020200999999999997</v>
+        <v>0.019296999999999998</v>
       </c>
       <c r="F187" s="7">
-        <v>0.065625</v>
+        <v>0.061307</v>
       </c>
       <c r="G187" s="7">
-        <v>0.150347</v>
+        <v>0.15027100000000002</v>
       </c>
       <c r="H187" s="7">
-        <v>0.09384100000000001</v>
+        <v>0.094744</v>
       </c>
       <c r="I187" s="7">
-        <v>0.37835500000000005</v>
+        <v>0.379493</v>
       </c>
       <c r="J187" s="7">
-        <v>1.9699119999999999</v>
+        <v>1.972563</v>
       </c>
       <c r="K187" s="7">
-        <v>3.320999</v>
+        <v>3.321001</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,16 +8758,16 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.094482</v>
+        <v>0.095616</v>
       </c>
       <c r="F188" s="7">
-        <v>-0.241559</v>
+        <v>-0.259205</v>
       </c>
       <c r="G188" s="7">
-        <v>0.563041</v>
+        <v>0.598894</v>
       </c>
       <c r="H188" s="7">
-        <v>0.047922</v>
+        <v>0.04093</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
@@ -8787,25 +8787,25 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>0.032191</v>
+        <v>0.039091999999999995</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.063229</v>
+        <v>-0.07126</v>
       </c>
       <c r="G189" s="7">
-        <v>0.151062</v>
+        <v>0.165712</v>
       </c>
       <c r="H189" s="7">
-        <v>0.082749</v>
+        <v>0.084169</v>
       </c>
       <c r="I189" s="7">
-        <v>0.6074069999999999</v>
+        <v>0.609514</v>
       </c>
       <c r="J189" s="7">
-        <v>3.989701</v>
+        <v>3.9686470000000003</v>
       </c>
       <c r="K189" s="7">
-        <v>13.306514</v>
+        <v>13.415393</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>0.02273</v>
+        <v>0.019081</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.057076</v>
+        <v>-0.06555799999999999</v>
       </c>
       <c r="G190" s="7">
-        <v>0.12273400000000001</v>
+        <v>0.139343</v>
       </c>
       <c r="H190" s="7">
-        <v>0.057942999999999995</v>
+        <v>0.054812</v>
       </c>
       <c r="I190" s="7">
-        <v>0.578096</v>
+        <v>0.573425</v>
       </c>
       <c r="J190" s="7">
-        <v>3.949959</v>
+        <v>3.915564</v>
       </c>
       <c r="K190" s="7">
-        <v>13.093241</v>
+        <v>13.144891</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8857,25 @@
         <v>4</v>
       </c>
       <c r="E191" s="7">
-        <v>0.069939</v>
+        <v>0.07377</v>
       </c>
       <c r="F191" s="7">
-        <v>0.055031</v>
+        <v>0.060061</v>
       </c>
       <c r="G191" s="7">
-        <v>0.254296</v>
+        <v>0.260787</v>
       </c>
       <c r="H191" s="7">
-        <v>0.140746</v>
+        <v>0.143263</v>
       </c>
       <c r="I191" s="7">
-        <v>0.492363</v>
+        <v>0.49565600000000004</v>
       </c>
       <c r="J191" s="7">
-        <v>1.8384379999999998</v>
+        <v>1.848848</v>
       </c>
       <c r="K191" s="7">
-        <v>5.114268</v>
+        <v>5.10883</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8892,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.062194</v>
+        <v>0.062797</v>
       </c>
       <c r="F192" s="7">
-        <v>0.047448</v>
+        <v>0.050203</v>
       </c>
       <c r="G192" s="7">
-        <v>0.20110399999999998</v>
+        <v>0.202112</v>
       </c>
       <c r="H192" s="7">
-        <v>0.104446</v>
+        <v>0.105512</v>
       </c>
       <c r="I192" s="7">
-        <v>0.455963</v>
+        <v>0.457368</v>
       </c>
       <c r="J192" s="7">
-        <v>2.196122</v>
+        <v>2.200584</v>
       </c>
       <c r="K192" s="7">
-        <v>5.553419</v>
+        <v>5.550834999999999</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8927,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>0.036218</v>
+        <v>0.049357</v>
       </c>
       <c r="F193" s="7">
-        <v>0.034624</v>
+        <v>0.035297999999999996</v>
       </c>
       <c r="G193" s="7">
-        <v>0.10495499999999999</v>
+        <v>0.102775</v>
       </c>
       <c r="H193" s="7">
-        <v>0.04857</v>
+        <v>0.050728999999999996</v>
       </c>
       <c r="I193" s="7">
-        <v>0.318784</v>
+        <v>0.32149900000000003</v>
       </c>
       <c r="J193" s="7">
-        <v>2.2317</v>
+        <v>2.2208170000000003</v>
       </c>
       <c r="K193" s="7">
-        <v>6.49633</v>
+        <v>6.572184</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8962,25 @@
         <v>3</v>
       </c>
       <c r="E194" s="7">
-        <v>0.048635000000000005</v>
+        <v>0.052334</v>
       </c>
       <c r="F194" s="7">
-        <v>0.09598000000000001</v>
+        <v>0.101729</v>
       </c>
       <c r="G194" s="7">
-        <v>0.234396</v>
+        <v>0.240568</v>
       </c>
       <c r="H194" s="7">
-        <v>0.18029399999999998</v>
+        <v>0.186624</v>
       </c>
       <c r="I194" s="7">
-        <v>0.468122</v>
+        <v>0.47599600000000003</v>
       </c>
       <c r="J194" s="7">
-        <v>1.533534</v>
+        <v>1.545369</v>
       </c>
       <c r="K194" s="7">
-        <v>3.735406</v>
+        <v>3.729413</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +8997,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.04407199999999999</v>
+        <v>0.047641</v>
       </c>
       <c r="F195" s="7">
-        <v>0.07461999999999999</v>
+        <v>0.079333</v>
       </c>
       <c r="G195" s="7">
-        <v>0.22426100000000002</v>
+        <v>0.227992</v>
       </c>
       <c r="H195" s="7">
-        <v>0.130783</v>
+        <v>0.135232</v>
       </c>
       <c r="I195" s="7">
-        <v>0.445816</v>
+        <v>0.451505</v>
       </c>
       <c r="J195" s="7">
-        <v>1.703604</v>
+        <v>1.7115559999999999</v>
       </c>
       <c r="K195" s="7">
-        <v>4.5903480000000005</v>
+        <v>4.602838</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9032,25 @@
         <v>4</v>
       </c>
       <c r="E196" s="7">
-        <v>0.069801</v>
+        <v>0.073844</v>
       </c>
       <c r="F196" s="7">
-        <v>0.051488</v>
+        <v>0.056787000000000004</v>
       </c>
       <c r="G196" s="7">
-        <v>0.22023900000000002</v>
+        <v>0.222146</v>
       </c>
       <c r="H196" s="7">
-        <v>0.1286</v>
+        <v>0.131143</v>
       </c>
       <c r="I196" s="7">
-        <v>0.48115900000000006</v>
+        <v>0.484496</v>
       </c>
       <c r="J196" s="7">
-        <v>2.087941</v>
+        <v>2.097976</v>
       </c>
       <c r="K196" s="7">
-        <v>5.132034</v>
+        <v>5.126385</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9067,25 @@
         <v>6</v>
       </c>
       <c r="E197" s="7">
-        <v>0.090633</v>
+        <v>0.09996600000000001</v>
       </c>
       <c r="F197" s="7">
-        <v>0.050826</v>
+        <v>0.064324</v>
       </c>
       <c r="G197" s="7">
-        <v>0.244835</v>
+        <v>0.260016</v>
       </c>
       <c r="H197" s="7">
-        <v>0.214508</v>
+        <v>0.218238</v>
       </c>
       <c r="I197" s="7">
-        <v>0.441333</v>
+        <v>0.44575899999999996</v>
       </c>
       <c r="J197" s="7">
-        <v>3.893825</v>
+        <v>3.879508</v>
       </c>
       <c r="K197" s="7">
-        <v>21.688382</v>
+        <v>21.398015</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,16 +9102,16 @@
         <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>0.088323</v>
+        <v>0.10049200000000001</v>
       </c>
       <c r="F198" s="7">
-        <v>0.07812999999999999</v>
+        <v>0.087443</v>
       </c>
       <c r="G198" s="7">
-        <v>0.21915600000000002</v>
+        <v>0.22958800000000001</v>
       </c>
       <c r="H198" s="7">
-        <v>0.190079</v>
+        <v>0.197697</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
@@ -9131,25 +9131,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.068705</v>
+        <v>0.08368700000000001</v>
       </c>
       <c r="F199" s="7">
-        <v>-0.003643</v>
+        <v>0.005012</v>
       </c>
       <c r="G199" s="7">
-        <v>0.17149799999999998</v>
+        <v>0.182246</v>
       </c>
       <c r="H199" s="7">
-        <v>0.080364</v>
+        <v>0.088043</v>
       </c>
       <c r="I199" s="7">
-        <v>0.358548</v>
+        <v>0.368204</v>
       </c>
       <c r="J199" s="7">
-        <v>2.052718</v>
+        <v>2.06648</v>
       </c>
       <c r="K199" s="7">
-        <v>10.195561</v>
+        <v>10.100152000000001</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9166,25 +9166,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.076606</v>
+        <v>0.09182499999999999</v>
       </c>
       <c r="F200" s="7">
-        <v>0.061068</v>
+        <v>0.077258</v>
       </c>
       <c r="G200" s="7">
-        <v>0.215733</v>
+        <v>0.227862</v>
       </c>
       <c r="H200" s="7">
-        <v>0.16749099999999997</v>
+        <v>0.178831</v>
       </c>
       <c r="I200" s="7">
-        <v>0.471107</v>
+        <v>0.485397</v>
       </c>
       <c r="J200" s="7">
-        <v>2.291813</v>
+        <v>2.30737</v>
       </c>
       <c r="K200" s="7">
-        <v>9.273039</v>
+        <v>9.206864000000001</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9201,25 +9201,25 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.049874</v>
+        <v>0.057396</v>
       </c>
       <c r="F201" s="7">
-        <v>0.008583</v>
+        <v>0.014384</v>
       </c>
       <c r="G201" s="7">
-        <v>0.17884</v>
+        <v>0.184431</v>
       </c>
       <c r="H201" s="7">
-        <v>0.08938800000000001</v>
+        <v>0.09311799999999999</v>
       </c>
       <c r="I201" s="7">
-        <v>0.669735</v>
+        <v>0.6754519999999999</v>
       </c>
       <c r="J201" s="7">
-        <v>2.9709930000000004</v>
+        <v>2.9609609999999997</v>
       </c>
       <c r="K201" s="7">
-        <v>6.427843</v>
+        <v>6.4452620000000005</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9236,25 +9236,25 @@
         <v>3</v>
       </c>
       <c r="E202" s="7">
-        <v>0.042409</v>
+        <v>0.039245</v>
       </c>
       <c r="F202" s="7">
-        <v>0.024786000000000002</v>
+        <v>0.026446</v>
       </c>
       <c r="G202" s="7">
-        <v>0.16748100000000002</v>
+        <v>0.161841</v>
       </c>
       <c r="H202" s="7">
-        <v>0.057096</v>
+        <v>0.054998</v>
       </c>
       <c r="I202" s="7">
-        <v>0.41274700000000003</v>
+        <v>0.409943</v>
       </c>
       <c r="J202" s="7">
-        <v>1.657343</v>
+        <v>1.656749</v>
       </c>
       <c r="K202" s="7">
-        <v>3.7151</v>
+        <v>3.701836</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,16 +9271,16 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.090547</v>
+        <v>0.10029</v>
       </c>
       <c r="F203" s="7">
-        <v>0.052791</v>
+        <v>0.065517</v>
       </c>
       <c r="G203" s="7">
-        <v>0.263928</v>
+        <v>0.279909</v>
       </c>
       <c r="H203" s="7">
-        <v>0.221094</v>
+        <v>0.22583999999999999</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
@@ -9300,25 +9300,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.035282</v>
+        <v>0.043404</v>
       </c>
       <c r="F204" s="7">
-        <v>0.038651</v>
+        <v>0.040014</v>
       </c>
       <c r="G204" s="7">
-        <v>0.108875</v>
+        <v>0.10942500000000001</v>
       </c>
       <c r="H204" s="7">
-        <v>0.058564</v>
+        <v>0.061177999999999996</v>
       </c>
       <c r="I204" s="7">
-        <v>0.315144</v>
+        <v>0.318391</v>
       </c>
       <c r="J204" s="7">
-        <v>1.95898</v>
+        <v>1.958194</v>
       </c>
       <c r="K204" s="7">
-        <v>5.275561</v>
+        <v>5.342909</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9335,25 +9335,25 @@
         <v>4</v>
       </c>
       <c r="E205" s="7">
-        <v>0.059265</v>
+        <v>0.058127000000000005</v>
       </c>
       <c r="F205" s="7">
-        <v>0.028912</v>
+        <v>0.030085</v>
       </c>
       <c r="G205" s="7">
-        <v>0.204623</v>
+        <v>0.206053</v>
       </c>
       <c r="H205" s="7">
-        <v>0.100834</v>
+        <v>0.099289</v>
       </c>
       <c r="I205" s="7">
-        <v>0.345567</v>
+        <v>0.343679</v>
       </c>
       <c r="J205" s="7">
-        <v>1.992541</v>
+        <v>1.9850299999999999</v>
       </c>
       <c r="K205" s="7">
-        <v>5.006126</v>
+        <v>4.977444</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9370,25 +9370,25 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.070186</v>
+        <v>0.073542</v>
       </c>
       <c r="F206" s="7">
-        <v>0.051655</v>
+        <v>0.055581</v>
       </c>
       <c r="G206" s="7">
-        <v>0.260811</v>
+        <v>0.272036</v>
       </c>
       <c r="H206" s="7">
-        <v>0.175059</v>
+        <v>0.17510799999999999</v>
       </c>
       <c r="I206" s="7">
-        <v>0.491377</v>
+        <v>0.491439</v>
       </c>
       <c r="J206" s="7">
-        <v>2.7297160000000003</v>
+        <v>2.718155</v>
       </c>
       <c r="K206" s="7">
-        <v>8.16847</v>
+        <v>8.123357</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9405,25 +9405,25 @@
         <v>6</v>
       </c>
       <c r="E207" s="7">
-        <v>0.079674</v>
+        <v>0.084273</v>
       </c>
       <c r="F207" s="7">
-        <v>0.043234</v>
+        <v>0.048625999999999996</v>
       </c>
       <c r="G207" s="7">
-        <v>0.310659</v>
+        <v>0.327944</v>
       </c>
       <c r="H207" s="7">
-        <v>0.18374400000000002</v>
+        <v>0.18377</v>
       </c>
       <c r="I207" s="7">
-        <v>0.507768</v>
+        <v>0.507802</v>
       </c>
       <c r="J207" s="7">
-        <v>2.736349</v>
+        <v>2.714828</v>
       </c>
       <c r="K207" s="7">
-        <v>10.022442</v>
+        <v>9.937332</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9440,25 +9440,25 @@
         <v>3</v>
       </c>
       <c r="E208" s="7">
-        <v>0.041689</v>
+        <v>0.040673</v>
       </c>
       <c r="F208" s="7">
-        <v>0.013462</v>
+        <v>0.015298</v>
       </c>
       <c r="G208" s="7">
-        <v>0.170093</v>
+        <v>0.171785</v>
       </c>
       <c r="H208" s="7">
-        <v>0.046144</v>
+        <v>0.045376</v>
       </c>
       <c r="I208" s="7">
-        <v>0.40448</v>
+        <v>0.403448</v>
       </c>
       <c r="J208" s="7">
-        <v>1.5217930000000002</v>
+        <v>1.51721</v>
       </c>
       <c r="K208" s="7">
-        <v>2.9702159999999997</v>
+        <v>2.9617989999999996</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9475,25 +9475,25 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.10487</v>
+        <v>0.11217</v>
       </c>
       <c r="F209" s="7">
-        <v>0.04024200000000001</v>
+        <v>0.047396</v>
       </c>
       <c r="G209" s="7">
-        <v>0.282365</v>
+        <v>0.29764</v>
       </c>
       <c r="H209" s="7">
-        <v>0.225982</v>
+        <v>0.22401700000000002</v>
       </c>
       <c r="I209" s="7">
-        <v>0.389889</v>
+        <v>0.38766</v>
       </c>
       <c r="J209" s="7">
-        <v>2.870669</v>
+        <v>2.835432</v>
       </c>
       <c r="K209" s="7">
-        <v>15.35358</v>
+        <v>15.111319000000002</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9510,25 +9510,25 @@
         <v>4</v>
       </c>
       <c r="E210" s="7">
-        <v>0.071634</v>
+        <v>0.077089</v>
       </c>
       <c r="F210" s="7">
-        <v>0.066932</v>
+        <v>0.074284</v>
       </c>
       <c r="G210" s="7">
-        <v>0.238929</v>
+        <v>0.247119</v>
       </c>
       <c r="H210" s="7">
-        <v>0.171956</v>
+        <v>0.17596599999999998</v>
       </c>
       <c r="I210" s="7">
-        <v>0.507645</v>
+        <v>0.512803</v>
       </c>
       <c r="J210" s="7">
-        <v>1.8453540000000002</v>
+        <v>1.855135</v>
       </c>
       <c r="K210" s="7">
-        <v>5.591984</v>
+        <v>5.570048000000001</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9545,25 +9545,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.055202</v>
+        <v>0.060107</v>
       </c>
       <c r="F211" s="7">
-        <v>0.099093</v>
+        <v>0.109572</v>
       </c>
       <c r="G211" s="7">
-        <v>0.244271</v>
+        <v>0.250572</v>
       </c>
       <c r="H211" s="7">
-        <v>0.17913900000000002</v>
+        <v>0.18614799999999998</v>
       </c>
       <c r="I211" s="7">
-        <v>0.485962</v>
+        <v>0.49479599999999996</v>
       </c>
       <c r="J211" s="7">
-        <v>1.864155</v>
+        <v>1.8789529999999999</v>
       </c>
       <c r="K211" s="7">
-        <v>5.03977</v>
+        <v>5.0380720000000005</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9580,25 +9580,25 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.079771</v>
+        <v>0.09052099999999999</v>
       </c>
       <c r="F212" s="7">
-        <v>0.101053</v>
+        <v>0.11527</v>
       </c>
       <c r="G212" s="7">
-        <v>0.29191500000000004</v>
+        <v>0.304965</v>
       </c>
       <c r="H212" s="7">
-        <v>0.251944</v>
+        <v>0.26184799999999997</v>
       </c>
       <c r="I212" s="7">
-        <v>0.609626</v>
+        <v>0.622361</v>
       </c>
       <c r="J212" s="7">
-        <v>2.9861950000000004</v>
+        <v>3.0025850000000003</v>
       </c>
       <c r="K212" s="7">
-        <v>9.807253</v>
+        <v>9.908239</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,25 +9615,25 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.031632</v>
+        <v>0.033977</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.061417</v>
+        <v>-0.070269</v>
       </c>
       <c r="G213" s="7">
-        <v>0.155877</v>
+        <v>0.170576</v>
       </c>
       <c r="H213" s="7">
-        <v>0.088815</v>
+        <v>0.088947</v>
       </c>
       <c r="I213" s="7">
-        <v>0.628846</v>
+        <v>0.629043</v>
       </c>
       <c r="J213" s="7">
-        <v>4.2163900000000005</v>
+        <v>4.1675130000000005</v>
       </c>
       <c r="K213" s="7">
-        <v>13.659286999999999</v>
+        <v>13.750070000000001</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,25 +9650,25 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.044875</v>
+        <v>0.052439</v>
       </c>
       <c r="F214" s="7">
-        <v>0.04995</v>
+        <v>0.051181000000000004</v>
       </c>
       <c r="G214" s="7">
-        <v>0.165564</v>
+        <v>0.17026700000000003</v>
       </c>
       <c r="H214" s="7">
-        <v>0.11823399999999999</v>
+        <v>0.121978</v>
       </c>
       <c r="I214" s="7">
-        <v>0.40301200000000004</v>
+        <v>0.407709</v>
       </c>
       <c r="J214" s="7">
-        <v>2.2250870000000003</v>
+        <v>2.231163</v>
       </c>
       <c r="K214" s="7">
-        <v>7.215045</v>
+        <v>7.22439</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9685,25 +9685,25 @@
         <v>5</v>
       </c>
       <c r="E215" s="7">
-        <v>0.123775</v>
+        <v>0.131861</v>
       </c>
       <c r="F215" s="7">
-        <v>0.11899100000000001</v>
+        <v>0.129882</v>
       </c>
       <c r="G215" s="7">
-        <v>0.36764899999999995</v>
+        <v>0.38676099999999997</v>
       </c>
       <c r="H215" s="7">
-        <v>0.316784</v>
+        <v>0.327984</v>
       </c>
       <c r="I215" s="7">
-        <v>0.625987</v>
+        <v>0.639817</v>
       </c>
       <c r="J215" s="7">
-        <v>2.630827</v>
+        <v>2.6591340000000003</v>
       </c>
       <c r="K215" s="7">
-        <v>9.976344000000001</v>
+        <v>9.919683</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9720,25 +9720,25 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.022561</v>
+        <v>0.026271</v>
       </c>
       <c r="F216" s="7">
-        <v>0.035152</v>
+        <v>0.036070000000000005</v>
       </c>
       <c r="G216" s="7">
-        <v>0.08295899999999999</v>
+        <v>0.08329700000000001</v>
       </c>
       <c r="H216" s="7">
-        <v>0.047306999999999995</v>
+        <v>0.048651</v>
       </c>
       <c r="I216" s="7">
-        <v>0.230032</v>
+        <v>0.23161</v>
       </c>
       <c r="J216" s="7">
-        <v>1.787159</v>
+        <v>1.7849270000000002</v>
       </c>
       <c r="K216" s="7">
-        <v>5.204111</v>
+        <v>5.283898000000001</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9755,25 +9755,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.067236</v>
+        <v>0.07650699999999999</v>
       </c>
       <c r="F217" s="7">
-        <v>0.117219</v>
+        <v>0.131403</v>
       </c>
       <c r="G217" s="7">
-        <v>0.307782</v>
+        <v>0.319598</v>
       </c>
       <c r="H217" s="7">
-        <v>0.24147400000000002</v>
+        <v>0.250772</v>
       </c>
       <c r="I217" s="7">
-        <v>0.6238750000000001</v>
+        <v>0.6360370000000001</v>
       </c>
       <c r="J217" s="7">
-        <v>3.219896</v>
+        <v>3.217835</v>
       </c>
       <c r="K217" s="7">
-        <v>10.298783</v>
+        <v>10.420955</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,25 +9790,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.108351</v>
+        <v>0.12136</v>
       </c>
       <c r="F218" s="7">
-        <v>0.10891999999999999</v>
+        <v>0.121468</v>
       </c>
       <c r="G218" s="7">
-        <v>0.346188</v>
+        <v>0.371622</v>
       </c>
       <c r="H218" s="7">
-        <v>0.280213</v>
+        <v>0.296575</v>
       </c>
       <c r="I218" s="7">
-        <v>0.5911460000000001</v>
+        <v>0.611483</v>
       </c>
       <c r="J218" s="7">
-        <v>3.841264</v>
+        <v>3.8833949999999997</v>
       </c>
       <c r="K218" s="7">
-        <v>13.346078</v>
+        <v>13.309981</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9825,19 +9825,19 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.06393</v>
+        <v>0.070634</v>
       </c>
       <c r="F219" s="7">
-        <v>0.069647</v>
+        <v>0.07048700000000001</v>
       </c>
       <c r="G219" s="7">
-        <v>0.239186</v>
+        <v>0.24756</v>
       </c>
       <c r="H219" s="7">
-        <v>0.17424199999999998</v>
+        <v>0.17953600000000003</v>
       </c>
       <c r="I219" s="7">
-        <v>0.514238</v>
+        <v>0.521065</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
@@ -9856,16 +9856,16 @@
         <v>6</v>
       </c>
       <c r="E220" s="7">
-        <v>0.085895</v>
+        <v>0.084398</v>
       </c>
       <c r="F220" s="7">
-        <v>-0.216267</v>
+        <v>-0.237211</v>
       </c>
       <c r="G220" s="7">
-        <v>0.6905490000000001</v>
+        <v>0.678872</v>
       </c>
       <c r="H220" s="7">
-        <v>0.143576</v>
+        <v>0.11541399999999999</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
@@ -9906,22 +9906,22 @@
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.058284</v>
+        <v>0.057923</v>
       </c>
       <c r="F222" s="7">
-        <v>-0.145534</v>
+        <v>-0.15667899999999998</v>
       </c>
       <c r="G222" s="7">
-        <v>0.403011</v>
+        <v>0.41113</v>
       </c>
       <c r="H222" s="7">
-        <v>0.105115</v>
+        <v>0.09433899999999999</v>
       </c>
       <c r="I222" s="7">
-        <v>1.068116</v>
+        <v>1.047951</v>
       </c>
       <c r="J222" s="7">
-        <v>4.574176</v>
+        <v>4.48778</v>
       </c>
       <c r="K222" s="7"/>
     </row>
@@ -9939,25 +9939,25 @@
         <v>4</v>
       </c>
       <c r="E223" s="7">
-        <v>0.032355</v>
+        <v>0.030085</v>
       </c>
       <c r="F223" s="7">
-        <v>0.095974</v>
+        <v>0.09615</v>
       </c>
       <c r="G223" s="7">
-        <v>0.197672</v>
+        <v>0.19774</v>
       </c>
       <c r="H223" s="7">
-        <v>0.12032400000000001</v>
+        <v>0.121471</v>
       </c>
       <c r="I223" s="7">
-        <v>0.44607199999999997</v>
+        <v>0.447552</v>
       </c>
       <c r="J223" s="7">
-        <v>1.280612</v>
+        <v>1.282945</v>
       </c>
       <c r="K223" s="7">
-        <v>2.695238</v>
+        <v>2.6979430000000004</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9974,19 +9974,19 @@
         <v>2</v>
       </c>
       <c r="E224" s="7">
-        <v>0.029178000000000003</v>
+        <v>0.027265</v>
       </c>
       <c r="F224" s="7">
-        <v>0.083912</v>
+        <v>0.08387800000000001</v>
       </c>
       <c r="G224" s="7">
-        <v>0.18821000000000002</v>
+        <v>0.188189</v>
       </c>
       <c r="H224" s="7">
-        <v>0.11275600000000001</v>
+        <v>0.11382500000000001</v>
       </c>
       <c r="I224" s="7">
-        <v>0.444452</v>
+        <v>0.445839</v>
       </c>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10005,22 +10005,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.097735</v>
+        <v>0.119617</v>
       </c>
       <c r="F225" s="7">
-        <v>0.08681599999999999</v>
+        <v>0.105247</v>
       </c>
       <c r="G225" s="7">
-        <v>0.226245</v>
+        <v>0.254731</v>
       </c>
       <c r="H225" s="7">
-        <v>0.229757</v>
+        <v>0.25004000000000004</v>
       </c>
       <c r="I225" s="7">
-        <v>0.415732</v>
+        <v>0.43908200000000003</v>
       </c>
       <c r="J225" s="7">
-        <v>2.422736</v>
+        <v>2.482659</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10038,19 +10038,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="7">
-        <v>0.054828999999999996</v>
+        <v>0.070501</v>
       </c>
       <c r="F226" s="7">
-        <v>-0.152062</v>
+        <v>-0.149912</v>
       </c>
       <c r="G226" s="7">
-        <v>0.34741900000000003</v>
+        <v>0.380098</v>
       </c>
       <c r="H226" s="7">
-        <v>0.09664</v>
+        <v>0.110397</v>
       </c>
       <c r="I226" s="7">
-        <v>0.918524</v>
+        <v>0.9425920000000001</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10069,25 +10069,25 @@
         <v>4</v>
       </c>
       <c r="E227" s="7">
-        <v>0.060395000000000004</v>
+        <v>0.061546000000000003</v>
       </c>
       <c r="F227" s="7">
-        <v>0.049849</v>
+        <v>0.053418</v>
       </c>
       <c r="G227" s="7">
-        <v>0.20490200000000003</v>
+        <v>0.20613299999999998</v>
       </c>
       <c r="H227" s="7">
-        <v>0.10702500000000001</v>
+        <v>0.10836499999999999</v>
       </c>
       <c r="I227" s="7">
-        <v>0.45957099999999995</v>
+        <v>0.461338</v>
       </c>
       <c r="J227" s="7">
-        <v>2.164465</v>
+        <v>2.1692850000000004</v>
       </c>
       <c r="K227" s="7">
-        <v>5.635781</v>
+        <v>5.6364469999999995</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10104,25 +10104,25 @@
         <v>3</v>
       </c>
       <c r="E228" s="7">
-        <v>0.043977</v>
+        <v>0.047152</v>
       </c>
       <c r="F228" s="7">
-        <v>0.076407</v>
+        <v>0.08140900000000001</v>
       </c>
       <c r="G228" s="7">
-        <v>0.218304</v>
+        <v>0.222604</v>
       </c>
       <c r="H228" s="7">
-        <v>0.132736</v>
+        <v>0.137543</v>
       </c>
       <c r="I228" s="7">
-        <v>0.43633299999999997</v>
+        <v>0.44242899999999996</v>
       </c>
       <c r="J228" s="7">
-        <v>1.739001</v>
+        <v>1.748064</v>
       </c>
       <c r="K228" s="7">
-        <v>4.5380270000000005</v>
+        <v>4.551394</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.079373</v>
+        <v>0.093813</v>
       </c>
       <c r="F229" s="7">
-        <v>0.117937</v>
+        <v>0.122898</v>
       </c>
       <c r="G229" s="7">
-        <v>0.19991599999999998</v>
+        <v>0.20647</v>
       </c>
       <c r="H229" s="7">
-        <v>0.192106</v>
+        <v>0.20034600000000002</v>
       </c>
       <c r="I229" s="7">
-        <v>0.5452429999999999</v>
+        <v>0.555925</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10191,19 +10191,19 @@
         <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>0.09275499999999999</v>
+        <v>0.123661</v>
       </c>
       <c r="F231" s="7">
-        <v>0.127254</v>
+        <v>0.144052</v>
       </c>
       <c r="G231" s="7">
-        <v>0.325708</v>
+        <v>0.341741</v>
       </c>
       <c r="H231" s="7">
-        <v>0.315408</v>
+        <v>0.33740699999999996</v>
       </c>
       <c r="I231" s="7">
-        <v>0.520178</v>
+        <v>0.545601</v>
       </c>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10222,19 +10222,19 @@
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.098347</v>
+        <v>0.120535</v>
       </c>
       <c r="F232" s="7">
-        <v>0.08240299999999999</v>
+        <v>0.090124</v>
       </c>
       <c r="G232" s="7">
-        <v>0.23441800000000002</v>
+        <v>0.249407</v>
       </c>
       <c r="H232" s="7">
-        <v>0.204589</v>
+        <v>0.215992</v>
       </c>
       <c r="I232" s="7">
-        <v>0.5141640000000001</v>
+        <v>0.528498</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10253,25 +10253,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.034453</v>
+        <v>0.036864</v>
       </c>
       <c r="F233" s="7">
-        <v>0.064305</v>
+        <v>0.065397</v>
       </c>
       <c r="G233" s="7">
-        <v>0.17434899999999998</v>
+        <v>0.173885</v>
       </c>
       <c r="H233" s="7">
-        <v>0.103445</v>
+        <v>0.105479</v>
       </c>
       <c r="I233" s="7">
-        <v>0.3643</v>
+        <v>0.366815</v>
       </c>
       <c r="J233" s="7">
-        <v>1.4844300000000001</v>
+        <v>1.4878909999999999</v>
       </c>
       <c r="K233" s="7">
-        <v>4.320801</v>
+        <v>4.326080999999999</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10288,19 +10288,19 @@
         <v>3</v>
       </c>
       <c r="E234" s="7">
-        <v>0.062566</v>
+        <v>0.061772</v>
       </c>
       <c r="F234" s="7">
-        <v>0.062744</v>
+        <v>0.067306</v>
       </c>
       <c r="G234" s="7">
-        <v>0.230163</v>
+        <v>0.23684899999999998</v>
       </c>
       <c r="H234" s="7">
-        <v>0.173447</v>
+        <v>0.17387799999999998</v>
       </c>
       <c r="I234" s="7">
-        <v>0.46773600000000004</v>
+        <v>0.468275</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10319,19 +10319,19 @@
         <v>4</v>
       </c>
       <c r="E235" s="7">
-        <v>0.057644</v>
+        <v>0.060479000000000005</v>
       </c>
       <c r="F235" s="7">
-        <v>0.061298000000000005</v>
+        <v>0.067686</v>
       </c>
       <c r="G235" s="7">
-        <v>0.214651</v>
+        <v>0.21979800000000002</v>
       </c>
       <c r="H235" s="7">
-        <v>0.107506</v>
+        <v>0.11047499999999999</v>
       </c>
       <c r="I235" s="7">
-        <v>0.481282</v>
+        <v>0.48525199999999996</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10350,19 +10350,19 @@
         <v>2</v>
       </c>
       <c r="E236" s="7">
-        <v>0.03449</v>
+        <v>0.03222</v>
       </c>
       <c r="F236" s="7">
-        <v>0.09585300000000001</v>
+        <v>0.095816</v>
       </c>
       <c r="G236" s="7">
-        <v>0.199681</v>
+        <v>0.19969599999999998</v>
       </c>
       <c r="H236" s="7">
-        <v>0.125321</v>
+        <v>0.126534</v>
       </c>
       <c r="I236" s="7">
-        <v>0.47242199999999995</v>
+        <v>0.474008</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10381,25 +10381,25 @@
         <v>6</v>
       </c>
       <c r="E237" s="7">
-        <v>0.03266</v>
+        <v>0.040833</v>
       </c>
       <c r="F237" s="7">
-        <v>-0.053551</v>
+        <v>-0.058163</v>
       </c>
       <c r="G237" s="7">
-        <v>0.170498</v>
+        <v>0.186588</v>
       </c>
       <c r="H237" s="7">
-        <v>0.093746</v>
+        <v>0.09936600000000001</v>
       </c>
       <c r="I237" s="7">
-        <v>0.624213</v>
+        <v>0.632559</v>
       </c>
       <c r="J237" s="7">
-        <v>4.318264</v>
+        <v>4.308111</v>
       </c>
       <c r="K237" s="7">
-        <v>13.87961</v>
+        <v>14.047754</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10416,14 +10416,14 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.055582</v>
+        <v>0.052706</v>
       </c>
       <c r="F238" s="7">
-        <v>0.016483</v>
+        <v>0.017988999999999998</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7">
-        <v>0.04682</v>
+        <v>0.045048000000000005</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
@@ -10443,19 +10443,19 @@
         <v>6</v>
       </c>
       <c r="E239" s="7">
-        <v>0.120819</v>
+        <v>0.15710000000000002</v>
       </c>
       <c r="F239" s="7">
-        <v>0.145904</v>
+        <v>0.165763</v>
       </c>
       <c r="G239" s="7">
-        <v>0.28496900000000003</v>
+        <v>0.298445</v>
       </c>
       <c r="H239" s="7">
-        <v>0.259867</v>
+        <v>0.28180499999999997</v>
       </c>
       <c r="I239" s="7">
-        <v>0.653604</v>
+        <v>0.682397</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10474,19 +10474,19 @@
         <v>5</v>
       </c>
       <c r="E240" s="7">
-        <v>0.09367800000000001</v>
+        <v>0.107645</v>
       </c>
       <c r="F240" s="7">
-        <v>0.063901</v>
+        <v>0.072195</v>
       </c>
       <c r="G240" s="7">
-        <v>0.211739</v>
+        <v>0.21692599999999998</v>
       </c>
       <c r="H240" s="7">
-        <v>0.16561599999999999</v>
+        <v>0.17112100000000002</v>
       </c>
       <c r="I240" s="7">
-        <v>0.480901</v>
+        <v>0.48789499999999997</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10505,25 +10505,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.026821</v>
+        <v>0.033092</v>
       </c>
       <c r="F241" s="7">
-        <v>0.038121</v>
+        <v>0.039853</v>
       </c>
       <c r="G241" s="7">
-        <v>0.087807</v>
+        <v>0.088974</v>
       </c>
       <c r="H241" s="7">
-        <v>0.05065</v>
+        <v>0.053070000000000006</v>
       </c>
       <c r="I241" s="7">
-        <v>0.22756</v>
+        <v>0.23038599999999998</v>
       </c>
       <c r="J241" s="7">
-        <v>1.840581</v>
+        <v>1.8388069999999999</v>
       </c>
       <c r="K241" s="7">
-        <v>5.804009</v>
+        <v>5.875166</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10540,25 +10540,25 @@
         <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.02384</v>
+        <v>0.023189</v>
       </c>
       <c r="F242" s="7">
-        <v>0.049671</v>
+        <v>0.048149</v>
       </c>
       <c r="G242" s="7">
-        <v>0.201628</v>
+        <v>0.214855</v>
       </c>
       <c r="H242" s="7">
-        <v>0.083033</v>
+        <v>0.08286400000000001</v>
       </c>
       <c r="I242" s="7">
-        <v>0.20511</v>
+        <v>0.204922</v>
       </c>
       <c r="J242" s="7">
-        <v>1.904752</v>
+        <v>1.90714</v>
       </c>
       <c r="K242" s="7">
-        <v>5.883402</v>
+        <v>5.857691999999999</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10575,25 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.103767</v>
+        <v>0.11025</v>
       </c>
       <c r="F243" s="7">
-        <v>0.048140999999999996</v>
+        <v>0.058005</v>
       </c>
       <c r="G243" s="7">
-        <v>0.26599</v>
+        <v>0.277155</v>
       </c>
       <c r="H243" s="7">
-        <v>0.205625</v>
+        <v>0.207887</v>
       </c>
       <c r="I243" s="7">
-        <v>0.44732799999999995</v>
+        <v>0.450043</v>
       </c>
       <c r="J243" s="7">
-        <v>2.7887060000000004</v>
+        <v>2.791404</v>
       </c>
       <c r="K243" s="7">
-        <v>15.229303999999999</v>
+        <v>15.053983</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10610,25 @@
         <v>3</v>
       </c>
       <c r="E244" s="7">
-        <v>0.046716</v>
+        <v>0.050897</v>
       </c>
       <c r="F244" s="7">
-        <v>0.071218</v>
+        <v>0.072694</v>
       </c>
       <c r="G244" s="7">
-        <v>0.21176899999999999</v>
+        <v>0.21559899999999999</v>
       </c>
       <c r="H244" s="7">
-        <v>0.138181</v>
+        <v>0.143125</v>
       </c>
       <c r="I244" s="7">
-        <v>0.44256100000000004</v>
+        <v>0.448828</v>
       </c>
       <c r="J244" s="7">
-        <v>1.757766</v>
+        <v>1.7706540000000002</v>
       </c>
       <c r="K244" s="7">
-        <v>4.573735</v>
+        <v>4.593878</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10645,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.06085</v>
+        <v>0.059617</v>
       </c>
       <c r="F245" s="7">
-        <v>0.014796</v>
+        <v>0.018429</v>
       </c>
       <c r="G245" s="7">
-        <v>0.173249</v>
+        <v>0.172791</v>
       </c>
       <c r="H245" s="7">
-        <v>0.075565</v>
+        <v>0.07485699999999999</v>
       </c>
       <c r="I245" s="7">
-        <v>0.391543</v>
+        <v>0.390627</v>
       </c>
       <c r="J245" s="7">
-        <v>1.4435749999999998</v>
+        <v>1.456626</v>
       </c>
       <c r="K245" s="7">
-        <v>3.883767</v>
+        <v>3.8692399999999996</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10680,25 @@
         <v>2</v>
       </c>
       <c r="E246" s="7">
-        <v>0.044184</v>
+        <v>0.045167</v>
       </c>
       <c r="F246" s="7">
-        <v>0.08855600000000001</v>
+        <v>0.09007899999999999</v>
       </c>
       <c r="G246" s="7">
-        <v>0.21715199999999998</v>
+        <v>0.219707</v>
       </c>
       <c r="H246" s="7">
-        <v>0.128794</v>
+        <v>0.131226</v>
       </c>
       <c r="I246" s="7">
-        <v>0.5151979999999999</v>
+        <v>0.518463</v>
       </c>
       <c r="J246" s="7">
-        <v>4.354132</v>
+        <v>4.342825</v>
       </c>
       <c r="K246" s="7">
-        <v>7.150866</v>
+        <v>7.164917</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10715,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.074445</v>
+        <v>0.077237</v>
       </c>
       <c r="F247" s="7">
-        <v>0.084247</v>
+        <v>0.09014799999999999</v>
       </c>
       <c r="G247" s="7">
-        <v>0.262961</v>
+        <v>0.268432</v>
       </c>
       <c r="H247" s="7">
-        <v>0.18418800000000002</v>
+        <v>0.18579</v>
       </c>
       <c r="I247" s="7">
-        <v>0.510556</v>
+        <v>0.512599</v>
       </c>
       <c r="J247" s="7">
-        <v>3.224731</v>
+        <v>3.214004</v>
       </c>
       <c r="K247" s="7">
-        <v>8.695079</v>
+        <v>8.661194</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10750,25 @@
         <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>0.08310100000000001</v>
+        <v>0.086501</v>
       </c>
       <c r="F248" s="7">
-        <v>0.070761</v>
+        <v>0.07882399999999999</v>
       </c>
       <c r="G248" s="7">
-        <v>0.267996</v>
+        <v>0.275792</v>
       </c>
       <c r="H248" s="7">
-        <v>0.19656600000000002</v>
+        <v>0.198237</v>
       </c>
       <c r="I248" s="7">
-        <v>0.507686</v>
+        <v>0.509791</v>
       </c>
       <c r="J248" s="7">
-        <v>3.7673200000000002</v>
+        <v>3.7826459999999997</v>
       </c>
       <c r="K248" s="7">
-        <v>11.798646000000002</v>
+        <v>11.686286</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10785,25 @@
         <v>6</v>
       </c>
       <c r="E249" s="7">
-        <v>0.090321</v>
+        <v>0.09447</v>
       </c>
       <c r="F249" s="7">
-        <v>0.059002</v>
+        <v>0.066585</v>
       </c>
       <c r="G249" s="7">
-        <v>0.272829</v>
+        <v>0.283163</v>
       </c>
       <c r="H249" s="7">
-        <v>0.20907599999999998</v>
+        <v>0.20978100000000002</v>
       </c>
       <c r="I249" s="7">
-        <v>0.464649</v>
+        <v>0.46550400000000003</v>
       </c>
       <c r="J249" s="7">
-        <v>3.406538</v>
+        <v>3.3948110000000002</v>
       </c>
       <c r="K249" s="7">
-        <v>14.55315</v>
+        <v>14.385547999999998</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10820,25 @@
         <v>3</v>
       </c>
       <c r="E250" s="7">
-        <v>0.052675</v>
+        <v>0.056041999999999995</v>
       </c>
       <c r="F250" s="7">
-        <v>0.087254</v>
+        <v>0.091915</v>
       </c>
       <c r="G250" s="7">
-        <v>0.207406</v>
+        <v>0.211184</v>
       </c>
       <c r="H250" s="7">
-        <v>0.156388</v>
+        <v>0.160564</v>
       </c>
       <c r="I250" s="7">
-        <v>0.44859299999999996</v>
+        <v>0.453825</v>
       </c>
       <c r="J250" s="7">
-        <v>2.005512</v>
+        <v>2.015593</v>
       </c>
       <c r="K250" s="7">
-        <v>5.632562</v>
+        <v>5.6315</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10855,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.086675</v>
+        <v>0.09606400000000001</v>
       </c>
       <c r="F251" s="7">
-        <v>0.10144399999999999</v>
+        <v>0.10964600000000001</v>
       </c>
       <c r="G251" s="7">
-        <v>0.24715800000000002</v>
+        <v>0.256928</v>
       </c>
       <c r="H251" s="7">
-        <v>0.21013300000000001</v>
+        <v>0.21882200000000002</v>
       </c>
       <c r="I251" s="7">
-        <v>0.499523</v>
+        <v>0.51029</v>
       </c>
       <c r="J251" s="7">
-        <v>3.038793</v>
+        <v>3.066642</v>
       </c>
       <c r="K251" s="7">
-        <v>9.91512</v>
+        <v>9.943944</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10890,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.09904299999999999</v>
+        <v>0.110736</v>
       </c>
       <c r="F252" s="7">
-        <v>0.101608</v>
+        <v>0.11168900000000001</v>
       </c>
       <c r="G252" s="7">
-        <v>0.254756</v>
+        <v>0.266029</v>
       </c>
       <c r="H252" s="7">
-        <v>0.22649999999999998</v>
+        <v>0.23646599999999998</v>
       </c>
       <c r="I252" s="7">
-        <v>0.505667</v>
+        <v>0.517902</v>
       </c>
       <c r="J252" s="7">
-        <v>3.210091</v>
+        <v>3.2398520000000004</v>
       </c>
       <c r="K252" s="7">
-        <v>11.046241</v>
+        <v>11.045746999999999</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10925,25 @@
         <v>4</v>
       </c>
       <c r="E253" s="7">
-        <v>0.049537000000000005</v>
+        <v>0.048353</v>
       </c>
       <c r="F253" s="7">
-        <v>0.017988</v>
+        <v>0.020095000000000002</v>
       </c>
       <c r="G253" s="7">
-        <v>0.15915200000000002</v>
+        <v>0.15858</v>
       </c>
       <c r="H253" s="7">
-        <v>0.06761400000000001</v>
+        <v>0.066713</v>
       </c>
       <c r="I253" s="7">
-        <v>0.38182699999999997</v>
+        <v>0.38066099999999997</v>
       </c>
       <c r="J253" s="7">
-        <v>1.825029</v>
+        <v>1.8282640000000001</v>
       </c>
       <c r="K253" s="7">
-        <v>5.064173</v>
+        <v>5.050321</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10960,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.062545</v>
+        <v>0.068966</v>
       </c>
       <c r="F254" s="7">
-        <v>0.056882999999999996</v>
+        <v>0.06087</v>
       </c>
       <c r="G254" s="7">
-        <v>0.22815000000000002</v>
+        <v>0.236695</v>
       </c>
       <c r="H254" s="7">
-        <v>0.16427499999999998</v>
+        <v>0.16836600000000002</v>
       </c>
       <c r="I254" s="7">
-        <v>0.5383100000000001</v>
+        <v>0.543716</v>
       </c>
       <c r="J254" s="7">
-        <v>2.8755889999999997</v>
+        <v>2.8910430000000003</v>
       </c>
       <c r="K254" s="7">
-        <v>6.1538390000000005</v>
+        <v>6.181062</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +10995,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.049825</v>
+        <v>0.052828</v>
       </c>
       <c r="F255" s="7">
-        <v>0.054225</v>
+        <v>0.055005</v>
       </c>
       <c r="G255" s="7">
-        <v>0.21596800000000002</v>
+        <v>0.22311</v>
       </c>
       <c r="H255" s="7">
-        <v>0.149704</v>
+        <v>0.152366</v>
       </c>
       <c r="I255" s="7">
-        <v>0.517333</v>
+        <v>0.520846</v>
       </c>
       <c r="J255" s="7">
-        <v>2.819372</v>
+        <v>2.827546</v>
       </c>
       <c r="K255" s="7">
-        <v>5.316017</v>
+        <v>5.331249000000001</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11030,25 @@
         <v>5</v>
       </c>
       <c r="E256" s="7">
-        <v>0.077361</v>
+        <v>0.087177</v>
       </c>
       <c r="F256" s="7">
-        <v>0.06344999999999999</v>
+        <v>0.069275</v>
       </c>
       <c r="G256" s="7">
-        <v>0.24761399999999997</v>
+        <v>0.25958200000000003</v>
       </c>
       <c r="H256" s="7">
-        <v>0.18574300000000002</v>
+        <v>0.191414</v>
       </c>
       <c r="I256" s="7">
-        <v>0.55875</v>
+        <v>0.566205</v>
       </c>
       <c r="J256" s="7">
-        <v>2.92389</v>
+        <v>2.945711</v>
       </c>
       <c r="K256" s="7">
-        <v>7.471728000000001</v>
+        <v>7.516431</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11065,25 @@
         <v>6</v>
       </c>
       <c r="E257" s="7">
-        <v>0.034906</v>
+        <v>0.038967999999999996</v>
       </c>
       <c r="F257" s="7">
-        <v>-0.058286</v>
+        <v>-0.06665199999999999</v>
       </c>
       <c r="G257" s="7">
-        <v>0.16140100000000002</v>
+        <v>0.175248</v>
       </c>
       <c r="H257" s="7">
-        <v>0.09412000000000001</v>
+        <v>0.096028</v>
       </c>
       <c r="I257" s="7">
-        <v>0.632474</v>
+        <v>0.63532</v>
       </c>
       <c r="J257" s="7">
-        <v>4.215955</v>
+        <v>4.1772089999999995</v>
       </c>
       <c r="K257" s="7">
-        <v>13.865606</v>
+        <v>13.987156</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11100,25 @@
         <v>2</v>
       </c>
       <c r="E258" s="7">
-        <v>0.027498</v>
+        <v>0.027690000000000003</v>
       </c>
       <c r="F258" s="7">
-        <v>0.086513</v>
+        <v>0.08830299999999999</v>
       </c>
       <c r="G258" s="7">
-        <v>0.192885</v>
+        <v>0.191004</v>
       </c>
       <c r="H258" s="7">
-        <v>0.131763</v>
+        <v>0.133979</v>
       </c>
       <c r="I258" s="7">
-        <v>0.42806399999999994</v>
+        <v>0.43085999999999997</v>
       </c>
       <c r="J258" s="7">
-        <v>2.36426</v>
+        <v>2.376293</v>
       </c>
       <c r="K258" s="7">
-        <v>4.4290140000000005</v>
+        <v>4.437237</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11135,25 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.111227</v>
+        <v>0.12517799999999998</v>
       </c>
       <c r="F259" s="7">
-        <v>0.026448</v>
+        <v>0.022717</v>
       </c>
       <c r="G259" s="7">
-        <v>0.21376699999999998</v>
+        <v>0.218693</v>
       </c>
       <c r="H259" s="7">
-        <v>0.133441</v>
+        <v>0.132569</v>
       </c>
       <c r="I259" s="7">
-        <v>0.663478</v>
+        <v>0.6621980000000001</v>
       </c>
       <c r="J259" s="7">
-        <v>4.639073</v>
+        <v>4.59053</v>
       </c>
       <c r="K259" s="7">
-        <v>21.190028</v>
+        <v>20.914043000000003</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,10 +11170,10 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.035291</v>
+        <v>0.040052000000000004</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.032873</v>
+        <v>-0.013083000000000001</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -11195,22 +11195,22 @@
         <v>3</v>
       </c>
       <c r="E261" s="7">
-        <v>0.061649</v>
+        <v>0.064769</v>
       </c>
       <c r="F261" s="7">
-        <v>0.093286</v>
+        <v>0.098238</v>
       </c>
       <c r="G261" s="7">
-        <v>0.235496</v>
+        <v>0.240682</v>
       </c>
       <c r="H261" s="7">
-        <v>0.168517</v>
+        <v>0.17393</v>
       </c>
       <c r="I261" s="7">
-        <v>0.503359</v>
+        <v>0.510323</v>
       </c>
       <c r="J261" s="7">
-        <v>2.219494</v>
+        <v>2.2288140000000003</v>
       </c>
       <c r="K261" s="7"/>
     </row>
@@ -11228,22 +11228,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.029971</v>
+        <v>0.030661</v>
       </c>
       <c r="F262" s="7">
-        <v>0.054173</v>
+        <v>0.055453999999999996</v>
       </c>
       <c r="G262" s="7">
-        <v>0.153667</v>
+        <v>0.153601</v>
       </c>
       <c r="H262" s="7">
-        <v>0.074082</v>
+        <v>0.075932</v>
       </c>
       <c r="I262" s="7">
-        <v>0.506093</v>
+        <v>0.508687</v>
       </c>
       <c r="J262" s="7">
-        <v>2.7249529999999997</v>
+        <v>2.730534</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11261,19 +11261,19 @@
         <v>5</v>
       </c>
       <c r="E263" s="7">
-        <v>0.096538</v>
+        <v>0.101646</v>
       </c>
       <c r="F263" s="7">
-        <v>0.0748</v>
+        <v>0.06565</v>
       </c>
       <c r="G263" s="7">
-        <v>0.27392700000000003</v>
+        <v>0.29027000000000003</v>
       </c>
       <c r="H263" s="7">
-        <v>0.19508299999999998</v>
+        <v>0.197287</v>
       </c>
       <c r="I263" s="7">
-        <v>0.41868</v>
+        <v>0.42129600000000006</v>
       </c>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11292,22 +11292,22 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.123765</v>
+        <v>0.172542</v>
       </c>
       <c r="F264" s="7">
-        <v>0.087332</v>
+        <v>0.10812</v>
       </c>
       <c r="G264" s="7">
-        <v>0.19447399999999998</v>
+        <v>0.206659</v>
       </c>
       <c r="H264" s="7">
-        <v>0.1822</v>
+        <v>0.203777</v>
       </c>
       <c r="I264" s="7">
-        <v>0.505364</v>
+        <v>0.5328390000000001</v>
       </c>
       <c r="J264" s="7">
-        <v>3.282946</v>
+        <v>3.3499849999999998</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11325,16 +11325,16 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.026227999999999998</v>
+        <v>0.028229</v>
       </c>
       <c r="F265" s="7">
-        <v>0.061192</v>
+        <v>0.063054</v>
       </c>
       <c r="G265" s="7">
-        <v>0.145167</v>
+        <v>0.15072</v>
       </c>
       <c r="H265" s="7">
-        <v>0.119975</v>
+        <v>0.123067</v>
       </c>
       <c r="I265" s="7"/>
       <c r="J265" s="7"/>
@@ -11354,16 +11354,16 @@
         <v>2</v>
       </c>
       <c r="E266" s="7">
-        <v>0.032581</v>
+        <v>0.030383</v>
       </c>
       <c r="F266" s="7">
-        <v>0.09936600000000001</v>
+        <v>0.09941900000000001</v>
       </c>
       <c r="G266" s="7">
-        <v>0.207258</v>
+        <v>0.2073</v>
       </c>
       <c r="H266" s="7">
-        <v>0.12668200000000002</v>
+        <v>0.127829</v>
       </c>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
@@ -11383,22 +11383,22 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.037963</v>
+        <v>0.035112000000000004</v>
       </c>
       <c r="F267" s="7">
-        <v>0.07775</v>
+        <v>0.072477</v>
       </c>
       <c r="G267" s="7">
-        <v>0.20023700000000003</v>
+        <v>0.19561399999999998</v>
       </c>
       <c r="H267" s="7">
-        <v>0.124773</v>
+        <v>0.123232</v>
       </c>
       <c r="I267" s="7">
-        <v>0.480415</v>
+        <v>0.478387</v>
       </c>
       <c r="J267" s="7">
-        <v>3.119967</v>
+        <v>3.1013819999999996</v>
       </c>
       <c r="K267" s="7"/>
     </row>
@@ -11416,22 +11416,22 @@
         <v>5</v>
       </c>
       <c r="E268" s="7">
-        <v>0.048337000000000005</v>
+        <v>0.047797</v>
       </c>
       <c r="F268" s="7">
-        <v>0.065273</v>
+        <v>0.060687</v>
       </c>
       <c r="G268" s="7">
-        <v>0.206115</v>
+        <v>0.203301</v>
       </c>
       <c r="H268" s="7">
-        <v>0.13632</v>
+        <v>0.133363</v>
       </c>
       <c r="I268" s="7">
-        <v>0.567227</v>
+        <v>0.563149</v>
       </c>
       <c r="J268" s="7">
-        <v>2.8856939999999995</v>
+        <v>2.879567</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11449,19 +11449,19 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.061123000000000004</v>
+        <v>0.068439</v>
       </c>
       <c r="F269" s="7">
-        <v>0.07696399999999999</v>
+        <v>0.088332</v>
       </c>
       <c r="G269" s="7">
-        <v>0.19134</v>
+        <v>0.20807900000000001</v>
       </c>
       <c r="H269" s="7">
-        <v>0.12720800000000002</v>
+        <v>0.136042</v>
       </c>
       <c r="I269" s="7">
-        <v>0.491852</v>
+        <v>0.503544</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11480,19 +11480,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.078656</v>
+        <v>0.099516</v>
       </c>
       <c r="F270" s="7">
-        <v>0.09513500000000001</v>
+        <v>0.105022</v>
       </c>
       <c r="G270" s="7">
-        <v>0.151667</v>
+        <v>0.16363499999999997</v>
       </c>
       <c r="H270" s="7">
-        <v>0.160414</v>
+        <v>0.168009</v>
       </c>
       <c r="I270" s="7">
-        <v>0.519895</v>
+        <v>0.529843</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11511,19 +11511,19 @@
         <v>4</v>
       </c>
       <c r="E271" s="7">
-        <v>0.068661</v>
+        <v>0.07400999999999999</v>
       </c>
       <c r="F271" s="7">
-        <v>0.074908</v>
+        <v>0.06933500000000001</v>
       </c>
       <c r="G271" s="7">
-        <v>0.23092</v>
+        <v>0.228194</v>
       </c>
       <c r="H271" s="7">
-        <v>0.19819299999999998</v>
+        <v>0.195325</v>
       </c>
       <c r="I271" s="7">
-        <v>0.37309600000000004</v>
+        <v>0.36981</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11542,19 +11542,19 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.046978</v>
+        <v>0.041791</v>
       </c>
       <c r="F272" s="7">
-        <v>0.085914</v>
+        <v>0.072186</v>
       </c>
       <c r="G272" s="7">
-        <v>0.22889299999999999</v>
+        <v>0.212088</v>
       </c>
       <c r="H272" s="7">
-        <v>0.182577</v>
+        <v>0.178527</v>
       </c>
       <c r="I272" s="7">
-        <v>0.339073</v>
+        <v>0.334488</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11573,19 +11573,19 @@
         <v>6</v>
       </c>
       <c r="E273" s="7">
-        <v>0.099859</v>
+        <v>0.14844200000000002</v>
       </c>
       <c r="F273" s="7">
-        <v>0.10452</v>
+        <v>0.13153399999999998</v>
       </c>
       <c r="G273" s="7">
-        <v>0.252888</v>
+        <v>0.287806</v>
       </c>
       <c r="H273" s="7">
-        <v>0.278547</v>
+        <v>0.309526</v>
       </c>
       <c r="I273" s="7">
-        <v>0.478849</v>
+        <v>0.5146809999999999</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11604,22 +11604,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.045291</v>
+        <v>0.042169</v>
       </c>
       <c r="F274" s="7">
-        <v>0.057687</v>
+        <v>0.053621999999999996</v>
       </c>
       <c r="G274" s="7">
-        <v>0.202819</v>
+        <v>0.198123</v>
       </c>
       <c r="H274" s="7">
-        <v>0.128228</v>
+        <v>0.125191</v>
       </c>
       <c r="I274" s="7">
-        <v>0.508794</v>
+        <v>0.504733</v>
       </c>
       <c r="J274" s="7">
-        <v>3.090819</v>
+        <v>3.071045</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -11637,25 +11637,25 @@
         <v>5</v>
       </c>
       <c r="E275" s="7">
-        <v>0.07512400000000001</v>
+        <v>0.08780900000000001</v>
       </c>
       <c r="F275" s="7">
-        <v>0.089823</v>
+        <v>0.109098</v>
       </c>
       <c r="G275" s="7">
-        <v>0.281292</v>
+        <v>0.301997</v>
       </c>
       <c r="H275" s="7">
-        <v>0.201887</v>
+        <v>0.217116</v>
       </c>
       <c r="I275" s="7">
-        <v>0.550551</v>
+        <v>0.570197</v>
       </c>
       <c r="J275" s="7">
-        <v>2.49024</v>
+        <v>2.524995</v>
       </c>
       <c r="K275" s="7">
-        <v>6.541246</v>
+        <v>6.613677</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11672,25 +11672,25 @@
         <v>2</v>
       </c>
       <c r="E276" s="7">
-        <v>0.032608</v>
+        <v>0.031362</v>
       </c>
       <c r="F276" s="7">
-        <v>0.091518</v>
+        <v>0.090821</v>
       </c>
       <c r="G276" s="7">
-        <v>0.20186099999999998</v>
+        <v>0.20092500000000002</v>
       </c>
       <c r="H276" s="7">
-        <v>0.122893</v>
+        <v>0.123903</v>
       </c>
       <c r="I276" s="7">
-        <v>0.47328200000000004</v>
+        <v>0.474607</v>
       </c>
       <c r="J276" s="7">
-        <v>2.200459</v>
+        <v>2.201345</v>
       </c>
       <c r="K276" s="7">
-        <v>4.126558</v>
+        <v>4.128612</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11707,25 +11707,25 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.048037</v>
+        <v>0.064225</v>
       </c>
       <c r="F277" s="7">
-        <v>0.01699</v>
+        <v>0.017265</v>
       </c>
       <c r="G277" s="7">
-        <v>0.110694</v>
+        <v>0.11372299999999999</v>
       </c>
       <c r="H277" s="7">
-        <v>0.043799000000000005</v>
+        <v>0.048703</v>
       </c>
       <c r="I277" s="7">
-        <v>0.304957</v>
+        <v>0.311087</v>
       </c>
       <c r="J277" s="7">
-        <v>1.76804</v>
+        <v>1.776687</v>
       </c>
       <c r="K277" s="7">
-        <v>5.119134</v>
+        <v>5.184622000000001</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11742,25 +11742,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.10563399999999999</v>
+        <v>0.106486</v>
       </c>
       <c r="F278" s="7">
-        <v>0.056313</v>
+        <v>0.062255000000000005</v>
       </c>
       <c r="G278" s="7">
-        <v>0.239479</v>
+        <v>0.248694</v>
       </c>
       <c r="H278" s="7">
-        <v>0.203586</v>
+        <v>0.20272099999999998</v>
       </c>
       <c r="I278" s="7">
-        <v>0.410439</v>
+        <v>0.40942500000000004</v>
       </c>
       <c r="J278" s="7">
-        <v>2.439067</v>
+        <v>2.408601</v>
       </c>
       <c r="K278" s="7">
-        <v>13.040758</v>
+        <v>12.810836</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11777,25 +11777,25 @@
         <v>4</v>
       </c>
       <c r="E279" s="7">
-        <v>0.057469</v>
+        <v>0.060566</v>
       </c>
       <c r="F279" s="7">
-        <v>0.016354</v>
+        <v>0.023081</v>
       </c>
       <c r="G279" s="7">
-        <v>0.172806</v>
+        <v>0.17176</v>
       </c>
       <c r="H279" s="7">
-        <v>0.047335</v>
+        <v>0.048422</v>
       </c>
       <c r="I279" s="7">
-        <v>0.399594</v>
+        <v>0.40104599999999996</v>
       </c>
       <c r="J279" s="7">
-        <v>1.6154359999999999</v>
+        <v>1.634419</v>
       </c>
       <c r="K279" s="7">
-        <v>3.693429</v>
+        <v>3.681506</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11812,25 +11812,25 @@
         <v>6</v>
       </c>
       <c r="E280" s="7">
-        <v>0.082384</v>
+        <v>0.097387</v>
       </c>
       <c r="F280" s="7">
-        <v>0.091388</v>
+        <v>0.110662</v>
       </c>
       <c r="G280" s="7">
-        <v>0.236951</v>
+        <v>0.256961</v>
       </c>
       <c r="H280" s="7">
-        <v>0.193671</v>
+        <v>0.209799</v>
       </c>
       <c r="I280" s="7">
-        <v>0.47497799999999996</v>
+        <v>0.494907</v>
       </c>
       <c r="J280" s="7">
-        <v>2.6640260000000002</v>
+        <v>2.6976479999999996</v>
       </c>
       <c r="K280" s="7">
-        <v>10.187283</v>
+        <v>10.217084</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11847,25 +11847,25 @@
         <v>3</v>
       </c>
       <c r="E281" s="7">
-        <v>0.043487</v>
+        <v>0.042328000000000005</v>
       </c>
       <c r="F281" s="7">
-        <v>0.09108100000000001</v>
+        <v>0.09332599999999999</v>
       </c>
       <c r="G281" s="7">
-        <v>0.210543</v>
+        <v>0.20880500000000002</v>
       </c>
       <c r="H281" s="7">
-        <v>0.13799899999999998</v>
+        <v>0.138626</v>
       </c>
       <c r="I281" s="7">
-        <v>0.475678</v>
+        <v>0.476491</v>
       </c>
       <c r="J281" s="7">
-        <v>2.9687490000000003</v>
+        <v>2.9684559999999998</v>
       </c>
       <c r="K281" s="7">
-        <v>5.299746</v>
+        <v>5.300093</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11882,25 +11882,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.036803</v>
+        <v>0.034359</v>
       </c>
       <c r="F282" s="7">
-        <v>0.06985000000000001</v>
+        <v>0.070115</v>
       </c>
       <c r="G282" s="7">
-        <v>0.186193</v>
+        <v>0.184837</v>
       </c>
       <c r="H282" s="7">
-        <v>0.098827</v>
+        <v>0.099134</v>
       </c>
       <c r="I282" s="7">
-        <v>0.45584800000000003</v>
+        <v>0.456256</v>
       </c>
       <c r="J282" s="7">
-        <v>2.304615</v>
+        <v>2.296149</v>
       </c>
       <c r="K282" s="7">
-        <v>4.222799999999999</v>
+        <v>4.216432</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11917,25 +11917,25 @@
         <v>5</v>
       </c>
       <c r="E283" s="7">
-        <v>0.036352</v>
+        <v>0.049004000000000006</v>
       </c>
       <c r="F283" s="7">
-        <v>0.029925999999999998</v>
+        <v>0.031577</v>
       </c>
       <c r="G283" s="7">
-        <v>0.081087</v>
+        <v>0.0789</v>
       </c>
       <c r="H283" s="7">
-        <v>0.033973</v>
+        <v>0.035162</v>
       </c>
       <c r="I283" s="7">
-        <v>0.282706</v>
+        <v>0.284181</v>
       </c>
       <c r="J283" s="7">
-        <v>1.968397</v>
+        <v>1.9540899999999999</v>
       </c>
       <c r="K283" s="7">
-        <v>5.818452</v>
+        <v>5.893904</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11952,25 +11952,25 @@
         <v>3</v>
       </c>
       <c r="E284" s="7">
-        <v>0.037974</v>
+        <v>0.037485</v>
       </c>
       <c r="F284" s="7">
-        <v>0.051468999999999994</v>
+        <v>0.054207</v>
       </c>
       <c r="G284" s="7">
-        <v>0.223459</v>
+        <v>0.221397</v>
       </c>
       <c r="H284" s="7">
-        <v>0.06281500000000001</v>
+        <v>0.061165000000000004</v>
       </c>
       <c r="I284" s="7">
-        <v>0.433197</v>
+        <v>0.430972</v>
       </c>
       <c r="J284" s="7">
-        <v>1.989476</v>
+        <v>1.983014</v>
       </c>
       <c r="K284" s="7">
-        <v>3.645978</v>
+        <v>3.6356849999999996</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11987,25 +11987,25 @@
         <v>5</v>
       </c>
       <c r="E285" s="7">
-        <v>0.053028000000000006</v>
+        <v>0.054225</v>
       </c>
       <c r="F285" s="7">
-        <v>0.082554</v>
+        <v>0.083652</v>
       </c>
       <c r="G285" s="7">
-        <v>0.24011</v>
+        <v>0.24462399999999998</v>
       </c>
       <c r="H285" s="7">
-        <v>0.159818</v>
+        <v>0.161718</v>
       </c>
       <c r="I285" s="7">
-        <v>0.514316</v>
+        <v>0.516797</v>
       </c>
       <c r="J285" s="7">
-        <v>2.636001</v>
+        <v>2.6336559999999998</v>
       </c>
       <c r="K285" s="7">
-        <v>9.474383</v>
+        <v>9.418493999999999</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12022,25 +12022,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>0.022740999999999997</v>
+        <v>0.021277</v>
       </c>
       <c r="F286" s="7">
-        <v>-0.065623</v>
+        <v>-0.072782</v>
       </c>
       <c r="G286" s="7">
-        <v>0.131494</v>
+        <v>0.150416</v>
       </c>
       <c r="H286" s="7">
-        <v>0.063682</v>
+        <v>0.061729000000000006</v>
       </c>
       <c r="I286" s="7">
-        <v>0.6015630000000001</v>
+        <v>0.598622</v>
       </c>
       <c r="J286" s="7">
-        <v>4.26221</v>
+        <v>4.228126</v>
       </c>
       <c r="K286" s="7">
-        <v>13.90106</v>
+        <v>13.977281</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12057,25 +12057,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.05268900000000001</v>
+        <v>0.057205000000000006</v>
       </c>
       <c r="F287" s="7">
-        <v>0.090119</v>
+        <v>0.09559699999999999</v>
       </c>
       <c r="G287" s="7">
-        <v>0.249137</v>
+        <v>0.255182</v>
       </c>
       <c r="H287" s="7">
-        <v>0.159953</v>
+        <v>0.165993</v>
       </c>
       <c r="I287" s="7">
-        <v>0.479707</v>
+        <v>0.487412</v>
       </c>
       <c r="J287" s="7">
-        <v>1.337904</v>
+        <v>1.3381129999999999</v>
       </c>
       <c r="K287" s="7">
-        <v>3.722949</v>
+        <v>3.7237670000000005</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12092,25 +12092,25 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0.076272</v>
+        <v>0.07556199999999999</v>
       </c>
       <c r="F288" s="7">
-        <v>0.057314</v>
+        <v>0.068697</v>
       </c>
       <c r="G288" s="7">
-        <v>0.277986</v>
+        <v>0.286599</v>
       </c>
       <c r="H288" s="7">
-        <v>0.16421</v>
+        <v>0.165578</v>
       </c>
       <c r="I288" s="7">
-        <v>0.5068549999999999</v>
+        <v>0.508626</v>
       </c>
       <c r="J288" s="7">
-        <v>2.450615</v>
+        <v>2.4396809999999998</v>
       </c>
       <c r="K288" s="7">
-        <v>10.589521</v>
+        <v>10.476984</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12127,25 +12127,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.052111</v>
+        <v>0.054458</v>
       </c>
       <c r="F289" s="7">
-        <v>-0.104713</v>
+        <v>-0.103354</v>
       </c>
       <c r="G289" s="7">
-        <v>0.24749400000000002</v>
+        <v>0.271727</v>
       </c>
       <c r="H289" s="7">
-        <v>0.107353</v>
+        <v>0.112779</v>
       </c>
       <c r="I289" s="7">
-        <v>0.777891</v>
+        <v>0.786603</v>
       </c>
       <c r="J289" s="7">
-        <v>4.26133</v>
+        <v>4.266465999999999</v>
       </c>
       <c r="K289" s="7">
-        <v>8.491655</v>
+        <v>8.525508</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12162,25 +12162,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.08596399999999998</v>
+        <v>0.096991</v>
       </c>
       <c r="F290" s="7">
-        <v>0.073502</v>
+        <v>0.08690099999999999</v>
       </c>
       <c r="G290" s="7">
-        <v>0.247785</v>
+        <v>0.264287</v>
       </c>
       <c r="H290" s="7">
-        <v>0.208096</v>
+        <v>0.217622</v>
       </c>
       <c r="I290" s="7">
-        <v>0.36304000000000003</v>
+        <v>0.37378700000000004</v>
       </c>
       <c r="J290" s="7">
-        <v>2.506627</v>
+        <v>2.511073</v>
       </c>
       <c r="K290" s="7">
-        <v>12.855492</v>
+        <v>12.760313000000002</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12197,25 +12197,25 @@
         <v>4</v>
       </c>
       <c r="E291" s="7">
-        <v>0.049854</v>
+        <v>0.054611</v>
       </c>
       <c r="F291" s="7">
-        <v>0.074096</v>
+        <v>0.074362</v>
       </c>
       <c r="G291" s="7">
-        <v>0.229122</v>
+        <v>0.236115</v>
       </c>
       <c r="H291" s="7">
-        <v>0.161384</v>
+        <v>0.165599</v>
       </c>
       <c r="I291" s="7">
-        <v>0.550747</v>
+        <v>0.5563750000000001</v>
       </c>
       <c r="J291" s="7">
-        <v>2.388693</v>
+        <v>2.392724</v>
       </c>
       <c r="K291" s="7">
-        <v>6.339853000000001</v>
+        <v>6.338695</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12232,25 +12232,25 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0.080512</v>
+        <v>0.098</v>
       </c>
       <c r="F292" s="7">
-        <v>0.06148</v>
+        <v>0.079462</v>
       </c>
       <c r="G292" s="7">
-        <v>0.233445</v>
+        <v>0.24787700000000001</v>
       </c>
       <c r="H292" s="7">
-        <v>0.17287299999999997</v>
+        <v>0.187759</v>
       </c>
       <c r="I292" s="7">
-        <v>0.494238</v>
+        <v>0.513202</v>
       </c>
       <c r="J292" s="7">
-        <v>2.697075</v>
+        <v>2.727819</v>
       </c>
       <c r="K292" s="7">
-        <v>8.461394</v>
+        <v>8.503459</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12267,25 +12267,25 @@
         <v>4</v>
       </c>
       <c r="E293" s="7">
-        <v>0.044777</v>
+        <v>0.048511</v>
       </c>
       <c r="F293" s="7">
-        <v>0.065257</v>
+        <v>0.06856</v>
       </c>
       <c r="G293" s="7">
-        <v>0.225175</v>
+        <v>0.229354</v>
       </c>
       <c r="H293" s="7">
-        <v>0.116771</v>
+        <v>0.12073600000000001</v>
       </c>
       <c r="I293" s="7">
-        <v>0.40350400000000003</v>
+        <v>0.40848799999999996</v>
       </c>
       <c r="J293" s="7">
-        <v>1.418518</v>
+        <v>1.418054</v>
       </c>
       <c r="K293" s="7">
-        <v>4.12702</v>
+        <v>4.136533</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12302,25 +12302,25 @@
         <v>4</v>
       </c>
       <c r="E294" s="7">
-        <v>0.044642999999999995</v>
+        <v>0.043972</v>
       </c>
       <c r="F294" s="7">
-        <v>0.017617</v>
+        <v>0.019864</v>
       </c>
       <c r="G294" s="7">
-        <v>0.203301</v>
+        <v>0.203243</v>
       </c>
       <c r="H294" s="7">
-        <v>0.053689</v>
+        <v>0.052858999999999996</v>
       </c>
       <c r="I294" s="7">
-        <v>0.396591</v>
+        <v>0.39549</v>
       </c>
       <c r="J294" s="7">
-        <v>1.6852070000000001</v>
+        <v>1.69654</v>
       </c>
       <c r="K294" s="7">
-        <v>4.857043</v>
+        <v>4.841341</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12337,25 +12337,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.104977</v>
+        <v>0.119321</v>
       </c>
       <c r="F295" s="7">
-        <v>0.084881</v>
+        <v>0.099931</v>
       </c>
       <c r="G295" s="7">
-        <v>0.307536</v>
+        <v>0.323029</v>
       </c>
       <c r="H295" s="7">
-        <v>0.250063</v>
+        <v>0.25981000000000004</v>
       </c>
       <c r="I295" s="7">
-        <v>0.539793</v>
+        <v>0.551799</v>
       </c>
       <c r="J295" s="7">
-        <v>3.5423039999999997</v>
+        <v>3.560048</v>
       </c>
       <c r="K295" s="7">
-        <v>16.113885</v>
+        <v>16.071493</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12372,25 +12372,25 @@
         <v>5</v>
       </c>
       <c r="E296" s="7">
-        <v>0.085996</v>
+        <v>0.10028100000000001</v>
       </c>
       <c r="F296" s="7">
-        <v>0.082025</v>
+        <v>0.09782099999999999</v>
       </c>
       <c r="G296" s="7">
-        <v>0.30463799999999996</v>
+        <v>0.31878799999999996</v>
       </c>
       <c r="H296" s="7">
-        <v>0.251234</v>
+        <v>0.26213000000000003</v>
       </c>
       <c r="I296" s="7">
-        <v>0.5499069999999999</v>
+        <v>0.563404</v>
       </c>
       <c r="J296" s="7">
-        <v>3.1773399999999996</v>
+        <v>3.206016</v>
       </c>
       <c r="K296" s="7">
-        <v>10.941918000000001</v>
+        <v>10.957681000000001</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12407,25 +12407,25 @@
         <v>4</v>
       </c>
       <c r="E297" s="7">
-        <v>0.07509</v>
+        <v>0.088465</v>
       </c>
       <c r="F297" s="7">
-        <v>0.06381300000000001</v>
+        <v>0.07911</v>
       </c>
       <c r="G297" s="7">
-        <v>0.28563500000000003</v>
+        <v>0.29771000000000003</v>
       </c>
       <c r="H297" s="7">
-        <v>0.215392</v>
+        <v>0.225285</v>
       </c>
       <c r="I297" s="7">
-        <v>0.556623</v>
+        <v>0.569294</v>
       </c>
       <c r="J297" s="7">
-        <v>3.1952999999999996</v>
+        <v>3.213838</v>
       </c>
       <c r="K297" s="7">
-        <v>9.79724</v>
+        <v>9.829422</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12442,25 +12442,25 @@
         <v>2</v>
       </c>
       <c r="E298" s="7">
-        <v>0.048199</v>
+        <v>0.048575999999999994</v>
       </c>
       <c r="F298" s="7">
-        <v>0.09476599999999999</v>
+        <v>0.096584</v>
       </c>
       <c r="G298" s="7">
-        <v>0.22244499999999998</v>
+        <v>0.224036</v>
       </c>
       <c r="H298" s="7">
-        <v>0.13737</v>
+        <v>0.139625</v>
       </c>
       <c r="I298" s="7">
-        <v>0.5148429999999999</v>
+        <v>0.5178470000000001</v>
       </c>
       <c r="J298" s="7">
-        <v>2.823675</v>
+        <v>2.831998</v>
       </c>
       <c r="K298" s="7">
-        <v>5.109655</v>
+        <v>5.119123</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12477,25 +12477,25 @@
         <v>5</v>
       </c>
       <c r="E299" s="7">
-        <v>0.08827199999999999</v>
+        <v>0.104888</v>
       </c>
       <c r="F299" s="7">
-        <v>0.11057700000000001</v>
+        <v>0.123641</v>
       </c>
       <c r="G299" s="7">
-        <v>0.32171999999999995</v>
+        <v>0.337491</v>
       </c>
       <c r="H299" s="7">
-        <v>0.256391</v>
+        <v>0.270521</v>
       </c>
       <c r="I299" s="7">
-        <v>0.6366320000000001</v>
+        <v>0.655039</v>
       </c>
       <c r="J299" s="7">
-        <v>3.1436309999999996</v>
+        <v>3.154794</v>
       </c>
       <c r="K299" s="7">
-        <v>9.771745</v>
+        <v>9.801406</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12512,25 +12512,25 @@
         <v>6</v>
       </c>
       <c r="E300" s="7">
-        <v>0.09178800000000001</v>
+        <v>0.10770400000000001</v>
       </c>
       <c r="F300" s="7">
-        <v>0.094011</v>
+        <v>0.10862</v>
       </c>
       <c r="G300" s="7">
-        <v>0.32919800000000005</v>
+        <v>0.345877</v>
       </c>
       <c r="H300" s="7">
-        <v>0.26605</v>
+        <v>0.281588</v>
       </c>
       <c r="I300" s="7">
-        <v>0.675604</v>
+        <v>0.696168</v>
       </c>
       <c r="J300" s="7">
-        <v>3.330329</v>
+        <v>3.3426729999999996</v>
       </c>
       <c r="K300" s="7">
-        <v>12.424001</v>
+        <v>12.432820999999999</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12547,25 +12547,25 @@
         <v>6</v>
       </c>
       <c r="E301" s="7">
-        <v>0.100733</v>
+        <v>0.11686999999999999</v>
       </c>
       <c r="F301" s="7">
-        <v>0.105083</v>
+        <v>0.128001</v>
       </c>
       <c r="G301" s="7">
-        <v>0.278429</v>
+        <v>0.306789</v>
       </c>
       <c r="H301" s="7">
-        <v>0.264477</v>
+        <v>0.284715</v>
       </c>
       <c r="I301" s="7">
-        <v>0.524343</v>
+        <v>0.548741</v>
       </c>
       <c r="J301" s="7">
-        <v>2.097601</v>
+        <v>2.1249789999999997</v>
       </c>
       <c r="K301" s="7">
-        <v>8.910085</v>
+        <v>8.904163</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12582,22 +12582,22 @@
         <v>4</v>
       </c>
       <c r="E302" s="7">
-        <v>0.144985</v>
+        <v>0.193721</v>
       </c>
       <c r="F302" s="7">
-        <v>0.134518</v>
+        <v>0.150217</v>
       </c>
       <c r="G302" s="7">
-        <v>0.24142600000000003</v>
+        <v>0.250976</v>
       </c>
       <c r="H302" s="7">
-        <v>0.216869</v>
+        <v>0.23722300000000002</v>
       </c>
       <c r="I302" s="7">
-        <v>0.657196</v>
+        <v>0.684915</v>
       </c>
       <c r="J302" s="7">
-        <v>3.502081</v>
+        <v>3.592531</v>
       </c>
       <c r="K302" s="7"/>
     </row>
@@ -12615,25 +12615,25 @@
         <v>5</v>
       </c>
       <c r="E303" s="7">
-        <v>0.10842</v>
+        <v>0.126324</v>
       </c>
       <c r="F303" s="7">
-        <v>0.080016</v>
+        <v>0.094248</v>
       </c>
       <c r="G303" s="7">
-        <v>0.261208</v>
+        <v>0.28041</v>
       </c>
       <c r="H303" s="7">
-        <v>0.186202</v>
+        <v>0.19479500000000002</v>
       </c>
       <c r="I303" s="7">
-        <v>0.489945</v>
+        <v>0.500738</v>
       </c>
       <c r="J303" s="7">
-        <v>2.541358</v>
+        <v>2.549684</v>
       </c>
       <c r="K303" s="7">
-        <v>11.918262</v>
+        <v>11.806793</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12650,25 +12650,25 @@
         <v>6</v>
       </c>
       <c r="E304" s="7">
-        <v>0.024009999999999997</v>
+        <v>0.028547</v>
       </c>
       <c r="F304" s="7">
-        <v>0.035728</v>
+        <v>0.036858</v>
       </c>
       <c r="G304" s="7">
-        <v>0.08183</v>
+        <v>0.08245699999999999</v>
       </c>
       <c r="H304" s="7">
-        <v>0.047663000000000004</v>
+        <v>0.049161</v>
       </c>
       <c r="I304" s="7">
-        <v>0.236039</v>
+        <v>0.237806</v>
       </c>
       <c r="J304" s="7">
-        <v>1.807137</v>
+        <v>1.806687</v>
       </c>
       <c r="K304" s="7">
-        <v>5.568084</v>
+        <v>5.632092</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12685,25 +12685,25 @@
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.095713</v>
+        <v>0.100771</v>
       </c>
       <c r="F305" s="7">
-        <v>0.055219</v>
+        <v>0.068811</v>
       </c>
       <c r="G305" s="7">
-        <v>0.203324</v>
+        <v>0.208712</v>
       </c>
       <c r="H305" s="7">
-        <v>0.106502</v>
+        <v>0.107226</v>
       </c>
       <c r="I305" s="7">
-        <v>0.5026120000000001</v>
+        <v>0.503596</v>
       </c>
       <c r="J305" s="7">
-        <v>2.355993</v>
+        <v>2.333581</v>
       </c>
       <c r="K305" s="7">
-        <v>7.884676</v>
+        <v>7.83732</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12720,25 +12720,25 @@
         <v>3</v>
       </c>
       <c r="E306" s="7">
-        <v>0.040278999999999995</v>
+        <v>0.043319</v>
       </c>
       <c r="F306" s="7">
-        <v>0.079215</v>
+        <v>0.08515800000000001</v>
       </c>
       <c r="G306" s="7">
-        <v>0.203683</v>
+        <v>0.21088300000000001</v>
       </c>
       <c r="H306" s="7">
-        <v>0.136204</v>
+        <v>0.141502</v>
       </c>
       <c r="I306" s="7">
-        <v>0.45882599999999996</v>
+        <v>0.46562800000000004</v>
       </c>
       <c r="J306" s="7">
-        <v>1.948489</v>
+        <v>1.958648</v>
       </c>
       <c r="K306" s="7">
-        <v>5.2509879999999995</v>
+        <v>5.2607539999999995</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12755,25 +12755,25 @@
         <v>3</v>
       </c>
       <c r="E307" s="7">
-        <v>0.037495</v>
+        <v>0.035273</v>
       </c>
       <c r="F307" s="7">
-        <v>0.015298</v>
+        <v>0.016955</v>
       </c>
       <c r="G307" s="7">
-        <v>0.153474</v>
+        <v>0.14780200000000002</v>
       </c>
       <c r="H307" s="7">
-        <v>0.039279</v>
+        <v>0.037477</v>
       </c>
       <c r="I307" s="7">
-        <v>0.39947499999999997</v>
+        <v>0.39704900000000004</v>
       </c>
       <c r="J307" s="7">
-        <v>1.0087380000000001</v>
+        <v>1.013863</v>
       </c>
       <c r="K307" s="7">
-        <v>2.146754</v>
+        <v>2.136787</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>28.04.2026 18:38:52</t>
+    <t>29.04.2026 18:48:48</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2454,25 +2454,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.061239</v>
+        <v>0.055548</v>
       </c>
       <c r="F6" s="7">
-        <v>0.051957</v>
+        <v>0.039912</v>
       </c>
       <c r="G6" s="7">
-        <v>0.20682999999999999</v>
+        <v>0.19777</v>
       </c>
       <c r="H6" s="7">
-        <v>0.109016</v>
+        <v>0.10306900000000001</v>
       </c>
       <c r="I6" s="7">
-        <v>0.462123</v>
+        <v>0.45892099999999997</v>
       </c>
       <c r="J6" s="7">
-        <v>2.177081</v>
+        <v>2.178925</v>
       </c>
       <c r="K6" s="7">
-        <v>5.748423</v>
+        <v>5.718482</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,25 +2489,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.119036</v>
+        <v>0.116214</v>
       </c>
       <c r="F7" s="7">
-        <v>0.060101</v>
+        <v>0.052167000000000005</v>
       </c>
       <c r="G7" s="7">
-        <v>0.130215</v>
+        <v>0.125806</v>
       </c>
       <c r="H7" s="7">
-        <v>0.08940300000000001</v>
+        <v>0.086655</v>
       </c>
       <c r="I7" s="7">
-        <v>0.520713</v>
+        <v>0.500601</v>
       </c>
       <c r="J7" s="7">
-        <v>2.851056</v>
+        <v>2.806612</v>
       </c>
       <c r="K7" s="7">
-        <v>5.649386</v>
+        <v>5.62225</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2524,25 +2524,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.049572000000000005</v>
+        <v>0.044936</v>
       </c>
       <c r="F8" s="7">
-        <v>0.01572</v>
+        <v>0.008736</v>
       </c>
       <c r="G8" s="7">
-        <v>0.157384</v>
+        <v>0.148091</v>
       </c>
       <c r="H8" s="7">
-        <v>0.053368</v>
+        <v>0.04871400000000001</v>
       </c>
       <c r="I8" s="7">
-        <v>0.410264</v>
+        <v>0.405036</v>
       </c>
       <c r="J8" s="7">
-        <v>1.7487469999999998</v>
+        <v>1.725908</v>
       </c>
       <c r="K8" s="7">
-        <v>3.595865</v>
+        <v>3.573864</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2559,25 +2559,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.09705899999999999</v>
+        <v>0.086154</v>
       </c>
       <c r="F9" s="7">
-        <v>0.092165</v>
+        <v>0.052607999999999995</v>
       </c>
       <c r="G9" s="7">
-        <v>0.295739</v>
+        <v>0.280837</v>
       </c>
       <c r="H9" s="7">
-        <v>0.250476</v>
+        <v>0.238046</v>
       </c>
       <c r="I9" s="7">
-        <v>0.541045</v>
+        <v>0.53092</v>
       </c>
       <c r="J9" s="7">
-        <v>3.032957</v>
+        <v>3.083613</v>
       </c>
       <c r="K9" s="7">
-        <v>10.510965</v>
+        <v>10.454377999999998</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,25 +2594,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>0.019113</v>
+        <v>-0.003895</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.072836</v>
+        <v>-0.12430300000000001</v>
       </c>
       <c r="G10" s="7">
-        <v>0.13228600000000001</v>
+        <v>0.115451</v>
       </c>
       <c r="H10" s="7">
-        <v>0.052665</v>
+        <v>0.028898999999999998</v>
       </c>
       <c r="I10" s="7">
-        <v>0.559886</v>
+        <v>0.510806</v>
       </c>
       <c r="J10" s="7">
-        <v>4.140904</v>
+        <v>4.009746</v>
       </c>
       <c r="K10" s="7">
-        <v>13.771003</v>
+        <v>13.626793</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2629,25 +2629,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.127955</v>
+        <v>0.112149</v>
       </c>
       <c r="F11" s="7">
-        <v>0.112809</v>
+        <v>0.066556</v>
       </c>
       <c r="G11" s="7">
-        <v>0.339617</v>
+        <v>0.3193</v>
       </c>
       <c r="H11" s="7">
-        <v>0.293092</v>
+        <v>0.274972</v>
       </c>
       <c r="I11" s="7">
-        <v>0.573664</v>
+        <v>0.56329</v>
       </c>
       <c r="J11" s="7">
-        <v>2.648032</v>
+        <v>2.717987</v>
       </c>
       <c r="K11" s="7">
-        <v>13.068493</v>
+        <v>12.939045</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2664,25 +2664,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.05466</v>
+        <v>0.051308999999999994</v>
       </c>
       <c r="F12" s="7">
-        <v>0.08721899999999999</v>
+        <v>0.077114</v>
       </c>
       <c r="G12" s="7">
-        <v>0.24519</v>
+        <v>0.239819</v>
       </c>
       <c r="H12" s="7">
-        <v>0.146676</v>
+        <v>0.143033</v>
       </c>
       <c r="I12" s="7">
-        <v>0.493551</v>
+        <v>0.49149299999999996</v>
       </c>
       <c r="J12" s="7">
-        <v>2.6578769999999996</v>
+        <v>2.670312</v>
       </c>
       <c r="K12" s="7">
-        <v>4.566096</v>
+        <v>4.548625</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,25 +2699,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.12048199999999999</v>
+        <v>0.107876</v>
       </c>
       <c r="F13" s="7">
-        <v>0.129012</v>
+        <v>0.087743</v>
       </c>
       <c r="G13" s="7">
-        <v>0.36591500000000005</v>
+        <v>0.347503</v>
       </c>
       <c r="H13" s="7">
-        <v>0.300335</v>
+        <v>0.285705</v>
       </c>
       <c r="I13" s="7">
-        <v>0.580216</v>
+        <v>0.583549</v>
       </c>
       <c r="J13" s="7">
-        <v>2.7193680000000002</v>
+        <v>2.8199310000000004</v>
       </c>
       <c r="K13" s="7">
-        <v>10.517483</v>
+        <v>10.487581</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,25 +2734,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.076029</v>
+        <v>0.064762</v>
       </c>
       <c r="F14" s="7">
-        <v>0.050156</v>
+        <v>0.01886</v>
       </c>
       <c r="G14" s="7">
-        <v>0.269179</v>
+        <v>0.258126</v>
       </c>
       <c r="H14" s="7">
-        <v>0.186999</v>
+        <v>0.17457</v>
       </c>
       <c r="I14" s="7">
-        <v>0.479673</v>
+        <v>0.467862</v>
       </c>
       <c r="J14" s="7">
-        <v>2.673881</v>
+        <v>2.657304</v>
       </c>
       <c r="K14" s="7">
-        <v>8.166983</v>
+        <v>8.111453000000001</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,25 +2769,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.051065</v>
+        <v>0.045324</v>
       </c>
       <c r="F15" s="7">
-        <v>0.033864</v>
+        <v>0.023048000000000003</v>
       </c>
       <c r="G15" s="7">
-        <v>0.19402799999999998</v>
+        <v>0.185649</v>
       </c>
       <c r="H15" s="7">
-        <v>0.08372199999999999</v>
+        <v>0.077802</v>
       </c>
       <c r="I15" s="7">
-        <v>0.41627400000000003</v>
+        <v>0.413865</v>
       </c>
       <c r="J15" s="7">
-        <v>2.014218</v>
+        <v>2.017057</v>
       </c>
       <c r="K15" s="7">
-        <v>5.56231</v>
+        <v>5.528891</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,25 +2804,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.048617</v>
+        <v>0.045515999999999994</v>
       </c>
       <c r="F16" s="7">
-        <v>0.093436</v>
+        <v>0.085915</v>
       </c>
       <c r="G16" s="7">
-        <v>0.22479600000000002</v>
+        <v>0.218534</v>
       </c>
       <c r="H16" s="7">
-        <v>0.138281</v>
+        <v>0.134915</v>
       </c>
       <c r="I16" s="7">
-        <v>0.516601</v>
+        <v>0.509962</v>
       </c>
       <c r="J16" s="7">
-        <v>2.797335</v>
+        <v>2.781554</v>
       </c>
       <c r="K16" s="7">
-        <v>5.062829</v>
+        <v>5.041907</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2839,25 +2839,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.040008</v>
+        <v>0.035851</v>
       </c>
       <c r="F17" s="7">
-        <v>0.084635</v>
+        <v>0.075973</v>
       </c>
       <c r="G17" s="7">
-        <v>0.19145600000000002</v>
+        <v>0.18543800000000002</v>
       </c>
       <c r="H17" s="7">
-        <v>0.131999</v>
+        <v>0.127475</v>
       </c>
       <c r="I17" s="7">
-        <v>0.424611</v>
+        <v>0.417381</v>
       </c>
       <c r="J17" s="7">
-        <v>1.659353</v>
+        <v>1.6569</v>
       </c>
       <c r="K17" s="7">
-        <v>4.53216</v>
+        <v>4.515279</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,25 +2874,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>0.029462000000000002</v>
+        <v>0.005801</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.06849</v>
+        <v>-0.12253</v>
       </c>
       <c r="G18" s="7">
-        <v>0.18782800000000002</v>
+        <v>0.168873</v>
       </c>
       <c r="H18" s="7">
-        <v>0.075467</v>
+        <v>0.050747999999999995</v>
       </c>
       <c r="I18" s="7">
-        <v>0.656138</v>
+        <v>0.613468</v>
       </c>
       <c r="J18" s="7">
-        <v>4.907018</v>
+        <v>4.757208</v>
       </c>
       <c r="K18" s="7">
-        <v>16.091849</v>
+        <v>15.902171000000001</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,25 +2909,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.07840799999999999</v>
+        <v>0.065307</v>
       </c>
       <c r="F19" s="7">
-        <v>0.06116</v>
+        <v>0.037815</v>
       </c>
       <c r="G19" s="7">
-        <v>0.22360499999999997</v>
+        <v>0.20958100000000002</v>
       </c>
       <c r="H19" s="7">
-        <v>0.12097300000000001</v>
+        <v>0.107356</v>
       </c>
       <c r="I19" s="7">
-        <v>0.440729</v>
+        <v>0.427677</v>
       </c>
       <c r="J19" s="7">
-        <v>2.159137</v>
+        <v>2.1771700000000003</v>
       </c>
       <c r="K19" s="7">
-        <v>7.012971</v>
+        <v>6.944279</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2944,25 +2944,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.05012</v>
+        <v>0.043461</v>
       </c>
       <c r="F20" s="7">
-        <v>0.09745799999999999</v>
+        <v>0.08739599999999999</v>
       </c>
       <c r="G20" s="7">
-        <v>0.243903</v>
+        <v>0.236041</v>
       </c>
       <c r="H20" s="7">
-        <v>0.093486</v>
+        <v>0.086552</v>
       </c>
       <c r="I20" s="7">
-        <v>0.470003</v>
+        <v>0.466666</v>
       </c>
       <c r="J20" s="7">
-        <v>1.4772880000000002</v>
+        <v>1.471787</v>
       </c>
       <c r="K20" s="7">
-        <v>4.22082</v>
+        <v>4.1970220000000005</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,25 +2979,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.044355000000000006</v>
+        <v>0.041307</v>
       </c>
       <c r="F21" s="7">
-        <v>0.100135</v>
+        <v>0.09130699999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.216329</v>
+        <v>0.211373</v>
       </c>
       <c r="H21" s="7">
-        <v>0.14971500000000001</v>
+        <v>0.146359</v>
       </c>
       <c r="I21" s="7">
-        <v>0.460322</v>
+        <v>0.451832</v>
       </c>
       <c r="J21" s="7">
-        <v>1.815404</v>
+        <v>1.817244</v>
       </c>
       <c r="K21" s="7">
-        <v>5.039433</v>
+        <v>5.030542</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,25 +3014,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.119698</v>
+        <v>0.112174</v>
       </c>
       <c r="F22" s="7">
-        <v>0.10734</v>
+        <v>0.083012</v>
       </c>
       <c r="G22" s="7">
-        <v>0.259695</v>
+        <v>0.25254899999999997</v>
       </c>
       <c r="H22" s="7">
-        <v>0.249944</v>
+        <v>0.24154499999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.584806</v>
+        <v>0.579625</v>
       </c>
       <c r="J22" s="7">
-        <v>2.7817570000000003</v>
+        <v>2.814516</v>
       </c>
       <c r="K22" s="7">
-        <v>10.829309</v>
+        <v>10.834833000000001</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,25 +3049,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.026452</v>
+        <v>0.027268</v>
       </c>
       <c r="F23" s="7">
-        <v>0.081425</v>
+        <v>0.080891</v>
       </c>
       <c r="G23" s="7">
-        <v>0.184056</v>
+        <v>0.183094</v>
       </c>
       <c r="H23" s="7">
-        <v>0.115724</v>
+        <v>0.11661099999999999</v>
       </c>
       <c r="I23" s="7">
-        <v>0.406128</v>
+        <v>0.40732799999999997</v>
       </c>
       <c r="J23" s="7">
-        <v>2.158776</v>
+        <v>2.168707</v>
       </c>
       <c r="K23" s="7">
-        <v>4.986154</v>
+        <v>4.998791</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3084,25 +3084,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.0492</v>
+        <v>0.046036</v>
       </c>
       <c r="F24" s="7">
-        <v>0.013323</v>
+        <v>0.00853</v>
       </c>
       <c r="G24" s="7">
-        <v>0.149129</v>
+        <v>0.141931</v>
       </c>
       <c r="H24" s="7">
-        <v>0.040845</v>
+        <v>0.037705999999999996</v>
       </c>
       <c r="I24" s="7">
-        <v>0.39673200000000003</v>
+        <v>0.39309399999999994</v>
       </c>
       <c r="J24" s="7">
-        <v>1.606727</v>
+        <v>1.597867</v>
       </c>
       <c r="K24" s="7">
-        <v>3.453198</v>
+        <v>3.438195</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,25 +3119,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.047893</v>
+        <v>0.045034</v>
       </c>
       <c r="F25" s="7">
-        <v>0.041845999999999994</v>
+        <v>0.038274</v>
       </c>
       <c r="G25" s="7">
-        <v>0.12064399999999999</v>
+        <v>0.117143</v>
       </c>
       <c r="H25" s="7">
-        <v>0.055851</v>
+        <v>0.052969999999999996</v>
       </c>
       <c r="I25" s="7">
-        <v>0.347049</v>
+        <v>0.347421</v>
       </c>
       <c r="J25" s="7">
-        <v>2.120494</v>
+        <v>2.103355</v>
       </c>
       <c r="K25" s="7">
-        <v>6.488848000000001</v>
+        <v>6.520935</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,25 +3154,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.052698</v>
+        <v>0.046231</v>
       </c>
       <c r="F26" s="7">
-        <v>0.027589000000000002</v>
+        <v>0.012524</v>
       </c>
       <c r="G26" s="7">
-        <v>0.11793</v>
+        <v>0.110153</v>
       </c>
       <c r="H26" s="7">
-        <v>0.05540199999999999</v>
+        <v>0.048919</v>
       </c>
       <c r="I26" s="7">
-        <v>0.31451799999999996</v>
+        <v>0.304681</v>
       </c>
       <c r="J26" s="7">
-        <v>2.058769</v>
+        <v>2.0466409999999997</v>
       </c>
       <c r="K26" s="7">
-        <v>5.672947000000001</v>
+        <v>5.669697</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3189,25 +3189,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.10095499999999999</v>
+        <v>0.08210100000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>0.057815000000000005</v>
+        <v>0.02167</v>
       </c>
       <c r="G27" s="7">
-        <v>0.244451</v>
+        <v>0.227153</v>
       </c>
       <c r="H27" s="7">
-        <v>0.20437999999999998</v>
+        <v>0.183755</v>
       </c>
       <c r="I27" s="7">
-        <v>0.40037100000000003</v>
+        <v>0.396785</v>
       </c>
       <c r="J27" s="7">
-        <v>3.237899</v>
+        <v>3.2820370000000003</v>
       </c>
       <c r="K27" s="7">
-        <v>16.509776</v>
+        <v>16.28605</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,25 +3224,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.117985</v>
+        <v>0.110474</v>
       </c>
       <c r="F28" s="7">
-        <v>0.058103999999999996</v>
+        <v>0.037858</v>
       </c>
       <c r="G28" s="7">
-        <v>0.135974</v>
+        <v>0.127955</v>
       </c>
       <c r="H28" s="7">
-        <v>0.110649</v>
+        <v>0.103187</v>
       </c>
       <c r="I28" s="7">
-        <v>0.432804</v>
+        <v>0.419813</v>
       </c>
       <c r="J28" s="7">
-        <v>2.59673</v>
+        <v>2.582957</v>
       </c>
       <c r="K28" s="7">
-        <v>8.038272</v>
+        <v>8.013611</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3259,25 +3259,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.037871999999999996</v>
+        <v>0.035411</v>
       </c>
       <c r="F29" s="7">
-        <v>0.059623</v>
+        <v>0.05351</v>
       </c>
       <c r="G29" s="7">
-        <v>0.17670200000000003</v>
+        <v>0.172636</v>
       </c>
       <c r="H29" s="7">
-        <v>0.098376</v>
+        <v>0.095771</v>
       </c>
       <c r="I29" s="7">
-        <v>0.408767</v>
+        <v>0.40558999999999995</v>
       </c>
       <c r="J29" s="7">
-        <v>2.412494</v>
+        <v>2.402227</v>
       </c>
       <c r="K29" s="7">
-        <v>4.577243</v>
+        <v>4.562324</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3294,25 +3294,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.057895</v>
+        <v>0.04698</v>
       </c>
       <c r="F30" s="7">
-        <v>0.047831</v>
+        <v>0.027606000000000002</v>
       </c>
       <c r="G30" s="7">
-        <v>0.20011299999999999</v>
+        <v>0.190518</v>
       </c>
       <c r="H30" s="7">
-        <v>0.152937</v>
+        <v>0.141042</v>
       </c>
       <c r="I30" s="7">
-        <v>0.37988700000000003</v>
+        <v>0.377653</v>
       </c>
       <c r="J30" s="7">
-        <v>3.0131349999999997</v>
+        <v>3.029141</v>
       </c>
       <c r="K30" s="7">
-        <v>9.572973</v>
+        <v>9.469059999999999</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,25 +3329,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.120794</v>
+        <v>0.10321799999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>0.07258200000000001</v>
+        <v>0.029654</v>
       </c>
       <c r="G31" s="7">
-        <v>0.24970099999999998</v>
+        <v>0.23129100000000002</v>
       </c>
       <c r="H31" s="7">
-        <v>0.213902</v>
+        <v>0.19486699999999998</v>
       </c>
       <c r="I31" s="7">
-        <v>0.354459</v>
+        <v>0.350067</v>
       </c>
       <c r="J31" s="7">
-        <v>2.517842</v>
+        <v>2.5796660000000005</v>
       </c>
       <c r="K31" s="7">
-        <v>14.996533</v>
+        <v>14.832321</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3364,25 +3364,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.030202</v>
+        <v>0.031244</v>
       </c>
       <c r="F32" s="7">
-        <v>0.086154</v>
+        <v>0.08627800000000001</v>
       </c>
       <c r="G32" s="7">
-        <v>0.19426100000000002</v>
+        <v>0.192884</v>
       </c>
       <c r="H32" s="7">
-        <v>0.112599</v>
+        <v>0.113724</v>
       </c>
       <c r="I32" s="7">
-        <v>0.452838</v>
+        <v>0.45258000000000004</v>
       </c>
       <c r="J32" s="7">
-        <v>2.1572389999999997</v>
+        <v>2.153362</v>
       </c>
       <c r="K32" s="7">
-        <v>3.721418</v>
+        <v>3.7241269999999997</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3399,25 +3399,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.081534</v>
+        <v>0.067471</v>
       </c>
       <c r="F33" s="7">
-        <v>0.065621</v>
+        <v>0.033778999999999997</v>
       </c>
       <c r="G33" s="7">
-        <v>0.247946</v>
+        <v>0.234288</v>
       </c>
       <c r="H33" s="7">
-        <v>0.18502</v>
+        <v>0.169612</v>
       </c>
       <c r="I33" s="7">
-        <v>0.447222</v>
+        <v>0.44052</v>
       </c>
       <c r="J33" s="7">
-        <v>3.456451</v>
+        <v>3.4873849999999997</v>
       </c>
       <c r="K33" s="7">
-        <v>16.709628</v>
+        <v>16.531323</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3434,25 +3434,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.10757</v>
+        <v>0.09641400000000001</v>
       </c>
       <c r="F34" s="7">
-        <v>0.126065</v>
+        <v>0.094559</v>
       </c>
       <c r="G34" s="7">
-        <v>0.339532</v>
+        <v>0.32311799999999996</v>
       </c>
       <c r="H34" s="7">
-        <v>0.276678</v>
+        <v>0.263818</v>
       </c>
       <c r="I34" s="7">
-        <v>0.65217</v>
+        <v>0.636687</v>
       </c>
       <c r="J34" s="7">
-        <v>3.1708730000000003</v>
+        <v>3.1577699999999997</v>
       </c>
       <c r="K34" s="7">
-        <v>9.808775</v>
+        <v>9.768415</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3469,25 +3469,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.108658</v>
+        <v>0.097607</v>
       </c>
       <c r="F35" s="7">
-        <v>0.110654</v>
+        <v>0.07583999999999999</v>
       </c>
       <c r="G35" s="7">
-        <v>0.34596</v>
+        <v>0.328755</v>
       </c>
       <c r="H35" s="7">
-        <v>0.282035</v>
+        <v>0.26925699999999997</v>
       </c>
       <c r="I35" s="7">
-        <v>0.701692</v>
+        <v>0.688035</v>
       </c>
       <c r="J35" s="7">
-        <v>3.347779</v>
+        <v>3.352088</v>
       </c>
       <c r="K35" s="7">
-        <v>12.321605</v>
+        <v>12.302696000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3504,25 +3504,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.082378</v>
+        <v>0.069965</v>
       </c>
       <c r="F36" s="7">
-        <v>0.068756</v>
+        <v>0.037886</v>
       </c>
       <c r="G36" s="7">
-        <v>0.255819</v>
+        <v>0.24370799999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.19546500000000003</v>
+        <v>0.181755</v>
       </c>
       <c r="I36" s="7">
-        <v>0.469215</v>
+        <v>0.46366799999999997</v>
       </c>
       <c r="J36" s="7">
-        <v>3.549448</v>
+        <v>3.593673</v>
       </c>
       <c r="K36" s="7">
-        <v>17.436135</v>
+        <v>17.289585</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3539,25 +3539,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.071604</v>
+        <v>0.061753</v>
       </c>
       <c r="F37" s="7">
-        <v>0.070515</v>
+        <v>0.043158</v>
       </c>
       <c r="G37" s="7">
-        <v>0.260463</v>
+        <v>0.251355</v>
       </c>
       <c r="H37" s="7">
-        <v>0.175227</v>
+        <v>0.164424</v>
       </c>
       <c r="I37" s="7">
-        <v>0.458878</v>
+        <v>0.457961</v>
       </c>
       <c r="J37" s="7">
-        <v>3.641582</v>
+        <v>3.68186</v>
       </c>
       <c r="K37" s="7">
-        <v>15.748729</v>
+        <v>15.630354</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3574,25 +3574,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.052176</v>
+        <v>0.041410999999999996</v>
       </c>
       <c r="F38" s="7">
-        <v>0.057013</v>
+        <v>0.03343</v>
       </c>
       <c r="G38" s="7">
-        <v>0.226985</v>
+        <v>0.21604099999999998</v>
       </c>
       <c r="H38" s="7">
-        <v>0.153999</v>
+        <v>0.142192</v>
       </c>
       <c r="I38" s="7">
-        <v>0.456921</v>
+        <v>0.448954</v>
       </c>
       <c r="J38" s="7">
-        <v>3.5041629999999997</v>
+        <v>3.519602</v>
       </c>
       <c r="K38" s="7">
-        <v>11.685304</v>
+        <v>11.556228</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3609,25 +3609,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.036416</v>
+        <v>0.03211</v>
       </c>
       <c r="F39" s="7">
-        <v>0.07013899999999999</v>
+        <v>0.062389</v>
       </c>
       <c r="G39" s="7">
-        <v>0.198617</v>
+        <v>0.192291</v>
       </c>
       <c r="H39" s="7">
-        <v>0.118385</v>
+        <v>0.113739</v>
       </c>
       <c r="I39" s="7">
-        <v>0.467414</v>
+        <v>0.460177</v>
       </c>
       <c r="J39" s="7">
-        <v>2.9589190000000003</v>
+        <v>2.9408390000000004</v>
       </c>
       <c r="K39" s="7">
-        <v>5.701936</v>
+        <v>5.671753</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,25 +3644,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.093672</v>
+        <v>0.082378</v>
       </c>
       <c r="F40" s="7">
-        <v>0.135387</v>
+        <v>0.10842299999999999</v>
       </c>
       <c r="G40" s="7">
-        <v>0.316765</v>
+        <v>0.300525</v>
       </c>
       <c r="H40" s="7">
-        <v>0.242775</v>
+        <v>0.229941</v>
       </c>
       <c r="I40" s="7">
-        <v>0.619348</v>
+        <v>0.603098</v>
       </c>
       <c r="J40" s="7">
-        <v>3.388379</v>
+        <v>3.390644</v>
       </c>
       <c r="K40" s="7">
-        <v>11.812531</v>
+        <v>11.748692</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3679,25 +3679,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.077082</v>
+        <v>0.064946</v>
       </c>
       <c r="F41" s="7">
-        <v>0.12609700000000001</v>
+        <v>0.10012</v>
       </c>
       <c r="G41" s="7">
-        <v>0.296261</v>
+        <v>0.279312</v>
       </c>
       <c r="H41" s="7">
-        <v>0.220215</v>
+        <v>0.206465</v>
       </c>
       <c r="I41" s="7">
-        <v>0.608779</v>
+        <v>0.589951</v>
       </c>
       <c r="J41" s="7">
-        <v>3.1268200000000004</v>
+        <v>3.1121879999999997</v>
       </c>
       <c r="K41" s="7">
-        <v>10.094076</v>
+        <v>10.004953</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,25 +3714,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.100165</v>
+        <v>0.08855</v>
       </c>
       <c r="F42" s="7">
-        <v>0.09479599999999999</v>
+        <v>0.055248</v>
       </c>
       <c r="G42" s="7">
-        <v>0.310635</v>
+        <v>0.294535</v>
       </c>
       <c r="H42" s="7">
-        <v>0.256049</v>
+        <v>0.242788</v>
       </c>
       <c r="I42" s="7">
-        <v>0.560728</v>
+        <v>0.549941</v>
       </c>
       <c r="J42" s="7">
-        <v>3.105258</v>
+        <v>3.1194</v>
       </c>
       <c r="K42" s="7">
-        <v>10.948894000000001</v>
+        <v>10.873842999999999</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3749,25 +3749,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.098956</v>
+        <v>0.079916</v>
       </c>
       <c r="F43" s="7">
-        <v>0.060452000000000006</v>
+        <v>0.021063000000000002</v>
       </c>
       <c r="G43" s="7">
-        <v>0.264176</v>
+        <v>0.244057</v>
       </c>
       <c r="H43" s="7">
-        <v>0.19783</v>
+        <v>0.17707699999999998</v>
       </c>
       <c r="I43" s="7">
-        <v>0.468083</v>
+        <v>0.45521</v>
       </c>
       <c r="J43" s="7">
-        <v>3.996061</v>
+        <v>4.022273</v>
       </c>
       <c r="K43" s="7">
-        <v>21.713801</v>
+        <v>21.417638</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3784,25 +3784,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.04562</v>
+        <v>0.043289</v>
       </c>
       <c r="F44" s="7">
-        <v>0.069543</v>
+        <v>0.063394</v>
       </c>
       <c r="G44" s="7">
-        <v>0.20369800000000002</v>
+        <v>0.19872499999999998</v>
       </c>
       <c r="H44" s="7">
-        <v>0.115663</v>
+        <v>0.113176</v>
       </c>
       <c r="I44" s="7">
-        <v>0.478744</v>
+        <v>0.475954</v>
       </c>
       <c r="J44" s="7">
-        <v>2.455994</v>
+        <v>2.442594</v>
       </c>
       <c r="K44" s="7">
-        <v>4.46001</v>
+        <v>4.445805</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3819,25 +3819,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.081941</v>
+        <v>0.07222</v>
       </c>
       <c r="F45" s="7">
-        <v>0.086463</v>
+        <v>0.05373700000000001</v>
       </c>
       <c r="G45" s="7">
-        <v>0.292885</v>
+        <v>0.280508</v>
       </c>
       <c r="H45" s="7">
-        <v>0.218877</v>
+        <v>0.207926</v>
       </c>
       <c r="I45" s="7">
-        <v>0.568399</v>
+        <v>0.559337</v>
       </c>
       <c r="J45" s="7">
-        <v>3.211895</v>
+        <v>3.212889</v>
       </c>
       <c r="K45" s="7">
-        <v>9.587705999999999</v>
+        <v>9.525205</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3854,25 +3854,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.08108</v>
+        <v>0.070066</v>
       </c>
       <c r="F46" s="7">
-        <v>0.135839</v>
+        <v>0.11036699999999999</v>
       </c>
       <c r="G46" s="7">
-        <v>0.322402</v>
+        <v>0.3068</v>
       </c>
       <c r="H46" s="7">
-        <v>0.253689</v>
+        <v>0.240917</v>
       </c>
       <c r="I46" s="7">
-        <v>0.619895</v>
+        <v>0.604024</v>
       </c>
       <c r="J46" s="7">
-        <v>3.486014</v>
+        <v>3.4977620000000003</v>
       </c>
       <c r="K46" s="7">
-        <v>10.369219000000001</v>
+        <v>10.302041999999998</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3889,25 +3889,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.099085</v>
+        <v>0.084797</v>
       </c>
       <c r="F47" s="7">
-        <v>0.125782</v>
+        <v>0.094079</v>
       </c>
       <c r="G47" s="7">
-        <v>0.31497800000000004</v>
+        <v>0.296375</v>
       </c>
       <c r="H47" s="7">
-        <v>0.255521</v>
+        <v>0.239199</v>
       </c>
       <c r="I47" s="7">
-        <v>0.61075</v>
+        <v>0.591295</v>
       </c>
       <c r="J47" s="7">
-        <v>3.559368</v>
+        <v>3.548039</v>
       </c>
       <c r="K47" s="7">
-        <v>13.266043999999999</v>
+        <v>13.342174</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3924,25 +3924,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.07622899999999999</v>
+        <v>0.056655</v>
       </c>
       <c r="F48" s="7">
-        <v>0.048780000000000004</v>
+        <v>0.006444999999999999</v>
       </c>
       <c r="G48" s="7">
-        <v>0.177758</v>
+        <v>0.159803</v>
       </c>
       <c r="H48" s="7">
-        <v>0.158212</v>
+        <v>0.13714600000000002</v>
       </c>
       <c r="I48" s="7">
-        <v>0.427151</v>
+        <v>0.435308</v>
       </c>
       <c r="J48" s="7">
-        <v>1.724159</v>
+        <v>1.806054</v>
       </c>
       <c r="K48" s="7">
-        <v>10.459137</v>
+        <v>10.217352</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3959,25 +3959,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.11817399999999999</v>
+        <v>0.10246499999999999</v>
       </c>
       <c r="F49" s="7">
-        <v>0.100051</v>
+        <v>0.058313</v>
       </c>
       <c r="G49" s="7">
-        <v>0.33204</v>
+        <v>0.312216</v>
       </c>
       <c r="H49" s="7">
-        <v>0.26414000000000004</v>
+        <v>0.24638100000000002</v>
       </c>
       <c r="I49" s="7">
-        <v>0.5683279999999999</v>
+        <v>0.555887</v>
       </c>
       <c r="J49" s="7">
-        <v>3.6044439999999995</v>
+        <v>3.665521</v>
       </c>
       <c r="K49" s="7">
-        <v>16.25254</v>
+        <v>16.106084</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3994,25 +3994,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.12551500000000002</v>
+        <v>0.118203</v>
       </c>
       <c r="F50" s="7">
-        <v>0.073517</v>
+        <v>0.058055</v>
       </c>
       <c r="G50" s="7">
-        <v>0.158773</v>
+        <v>0.151639</v>
       </c>
       <c r="H50" s="7">
-        <v>0.123805</v>
+        <v>0.116504</v>
       </c>
       <c r="I50" s="7">
-        <v>0.553041</v>
+        <v>0.534961</v>
       </c>
       <c r="J50" s="7">
-        <v>3.058145</v>
+        <v>3.0334980000000002</v>
       </c>
       <c r="K50" s="7">
-        <v>8.972086000000001</v>
+        <v>8.965287</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,25 +4029,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.067296</v>
+        <v>0.058621999999999994</v>
       </c>
       <c r="F51" s="7">
-        <v>0.043285</v>
+        <v>0.019258</v>
       </c>
       <c r="G51" s="7">
-        <v>0.197209</v>
+        <v>0.18713999999999997</v>
       </c>
       <c r="H51" s="7">
-        <v>0.133706</v>
+        <v>0.12449199999999999</v>
       </c>
       <c r="I51" s="7">
-        <v>0.370579</v>
+        <v>0.366203</v>
       </c>
       <c r="J51" s="7">
-        <v>2.53861</v>
+        <v>2.5442009999999997</v>
       </c>
       <c r="K51" s="7">
-        <v>8.179</v>
+        <v>8.131417</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.124347</v>
+        <v>0.107775</v>
       </c>
       <c r="F52" s="7">
-        <v>0.065258</v>
+        <v>0.028222</v>
       </c>
       <c r="G52" s="7">
-        <v>0.282287</v>
+        <v>0.263933</v>
       </c>
       <c r="H52" s="7">
-        <v>0.212767</v>
+        <v>0.194891</v>
       </c>
       <c r="I52" s="7">
-        <v>0.479529</v>
+        <v>0.468974</v>
       </c>
       <c r="J52" s="7">
-        <v>2.661221</v>
+        <v>2.719981</v>
       </c>
       <c r="K52" s="7">
-        <v>11.124423</v>
+        <v>11.008715</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4099,25 +4099,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.066722</v>
+        <v>0.062205</v>
       </c>
       <c r="F53" s="7">
-        <v>0.035147</v>
+        <v>0.029759</v>
       </c>
       <c r="G53" s="7">
-        <v>0.100068</v>
+        <v>0.09517300000000001</v>
       </c>
       <c r="H53" s="7">
-        <v>0.048541</v>
+        <v>0.044101</v>
       </c>
       <c r="I53" s="7">
-        <v>0.34647399999999995</v>
+        <v>0.343221</v>
       </c>
       <c r="J53" s="7">
-        <v>2.204005</v>
+        <v>2.176726</v>
       </c>
       <c r="K53" s="7">
-        <v>6.512219</v>
+        <v>6.537256999999999</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4134,25 +4134,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.049296</v>
+        <v>0.047270000000000006</v>
       </c>
       <c r="F54" s="7">
-        <v>0.037469999999999996</v>
+        <v>0.034998999999999995</v>
       </c>
       <c r="G54" s="7">
-        <v>0.099579</v>
+        <v>0.097172</v>
       </c>
       <c r="H54" s="7">
-        <v>0.053612</v>
+        <v>0.051578</v>
       </c>
       <c r="I54" s="7">
-        <v>0.310785</v>
+        <v>0.30679</v>
       </c>
       <c r="J54" s="7">
-        <v>2.071164</v>
+        <v>2.056856</v>
       </c>
       <c r="K54" s="7">
-        <v>6.322551</v>
+        <v>6.352445</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4169,25 +4169,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.040229</v>
+        <v>0.014464</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.068524</v>
+        <v>-0.124864</v>
       </c>
       <c r="G55" s="7">
-        <v>0.178209</v>
+        <v>0.153104</v>
       </c>
       <c r="H55" s="7">
-        <v>0.088835</v>
+        <v>0.061867</v>
       </c>
       <c r="I55" s="7">
-        <v>0.630797</v>
+        <v>0.590984</v>
       </c>
       <c r="J55" s="7">
-        <v>4.022743</v>
+        <v>3.903587</v>
       </c>
       <c r="K55" s="7">
-        <v>13.357266</v>
+        <v>13.194327000000001</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4204,25 +4204,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.08680500000000001</v>
+        <v>0.07699399999999999</v>
       </c>
       <c r="F56" s="7">
-        <v>0.090358</v>
+        <v>0.06940299999999999</v>
       </c>
       <c r="G56" s="7">
-        <v>0.252556</v>
+        <v>0.239962</v>
       </c>
       <c r="H56" s="7">
-        <v>0.15407500000000002</v>
+        <v>0.143656</v>
       </c>
       <c r="I56" s="7">
-        <v>0.48240299999999997</v>
+        <v>0.47584000000000004</v>
       </c>
       <c r="J56" s="7">
-        <v>2.052474</v>
+        <v>2.066637</v>
       </c>
       <c r="K56" s="7">
-        <v>5.743877</v>
+        <v>5.692188</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4239,25 +4239,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.057512999999999995</v>
+        <v>0.04918</v>
       </c>
       <c r="F57" s="7">
-        <v>0.015212000000000002</v>
+        <v>0.00022700000000000002</v>
       </c>
       <c r="G57" s="7">
-        <v>0.143962</v>
+        <v>0.133777</v>
       </c>
       <c r="H57" s="7">
-        <v>0.073102</v>
+        <v>0.06464500000000001</v>
       </c>
       <c r="I57" s="7">
-        <v>0.371732</v>
+        <v>0.36789499999999997</v>
       </c>
       <c r="J57" s="7">
-        <v>1.346549</v>
+        <v>1.35464</v>
       </c>
       <c r="K57" s="7">
-        <v>3.616961</v>
+        <v>3.582614</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4274,25 +4274,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.089536</v>
+        <v>0.08060200000000001</v>
       </c>
       <c r="F58" s="7">
-        <v>0.081798</v>
+        <v>0.050323</v>
       </c>
       <c r="G58" s="7">
-        <v>0.303</v>
+        <v>0.29081</v>
       </c>
       <c r="H58" s="7">
-        <v>0.22983399999999998</v>
+        <v>0.21974900000000003</v>
       </c>
       <c r="I58" s="7">
-        <v>0.572911</v>
+        <v>0.565241</v>
       </c>
       <c r="J58" s="7">
-        <v>3.1860969999999997</v>
+        <v>3.192892</v>
       </c>
       <c r="K58" s="7">
-        <v>9.67333</v>
+        <v>9.612776</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4309,25 +4309,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.10017899999999999</v>
+        <v>0.088924</v>
       </c>
       <c r="F59" s="7">
-        <v>0.098277</v>
+        <v>0.05944</v>
       </c>
       <c r="G59" s="7">
-        <v>0.320957</v>
+        <v>0.305531</v>
       </c>
       <c r="H59" s="7">
-        <v>0.260019</v>
+        <v>0.24712900000000002</v>
       </c>
       <c r="I59" s="7">
-        <v>0.567419</v>
+        <v>0.558075</v>
       </c>
       <c r="J59" s="7">
-        <v>3.182025</v>
+        <v>3.2274950000000002</v>
       </c>
       <c r="K59" s="7">
-        <v>10.831698</v>
+        <v>10.755074</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4344,25 +4344,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.105699</v>
+        <v>0.08631</v>
       </c>
       <c r="F60" s="7">
-        <v>0.069866</v>
+        <v>0.026395</v>
       </c>
       <c r="G60" s="7">
-        <v>0.232812</v>
+        <v>0.21593800000000002</v>
       </c>
       <c r="H60" s="7">
-        <v>0.19957799999999998</v>
+        <v>0.17854199999999998</v>
       </c>
       <c r="I60" s="7">
-        <v>0.418724</v>
+        <v>0.41033299999999995</v>
       </c>
       <c r="J60" s="7">
-        <v>2.387928</v>
+        <v>2.441367</v>
       </c>
       <c r="K60" s="7">
-        <v>13.302159999999999</v>
+        <v>13.121297</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,25 +4379,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.10718899999999999</v>
+        <v>0.099068</v>
       </c>
       <c r="F61" s="7">
-        <v>0.077335</v>
+        <v>0.05605400000000001</v>
       </c>
       <c r="G61" s="7">
-        <v>0.21235600000000002</v>
+        <v>0.20389</v>
       </c>
       <c r="H61" s="7">
-        <v>0.171327</v>
+        <v>0.162735</v>
       </c>
       <c r="I61" s="7">
-        <v>0.510125</v>
+        <v>0.498251</v>
       </c>
       <c r="J61" s="7">
-        <v>2.4584710000000003</v>
+        <v>2.406539</v>
       </c>
       <c r="K61" s="7">
-        <v>7.768763</v>
+        <v>7.74111</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,25 +4414,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.080801</v>
+        <v>0.066611</v>
       </c>
       <c r="F62" s="7">
-        <v>0.053893</v>
+        <v>0.021808</v>
       </c>
       <c r="G62" s="7">
-        <v>0.186278</v>
+        <v>0.17748999999999998</v>
       </c>
       <c r="H62" s="7">
-        <v>0.161035</v>
+        <v>0.145791</v>
       </c>
       <c r="I62" s="7">
-        <v>0.344407</v>
+        <v>0.34886</v>
       </c>
       <c r="J62" s="7">
-        <v>2.347966</v>
+        <v>2.416637</v>
       </c>
       <c r="K62" s="7">
-        <v>12.645551000000001</v>
+        <v>12.417800999999999</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4449,25 +4449,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.060439</v>
+        <v>0.053458</v>
       </c>
       <c r="F63" s="7">
-        <v>0.027069</v>
+        <v>0.014018999999999998</v>
       </c>
       <c r="G63" s="7">
-        <v>0.188414</v>
+        <v>0.178064</v>
       </c>
       <c r="H63" s="7">
-        <v>0.091267</v>
+        <v>0.084082</v>
       </c>
       <c r="I63" s="7">
-        <v>0.41166400000000003</v>
+        <v>0.408178</v>
       </c>
       <c r="J63" s="7">
-        <v>1.921625</v>
+        <v>1.918532</v>
       </c>
       <c r="K63" s="7">
-        <v>4.707234000000001</v>
+        <v>4.670522</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4484,25 +4484,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.057059</v>
+        <v>0.041304</v>
       </c>
       <c r="F64" s="7">
-        <v>0.01914</v>
+        <v>-0.020585</v>
       </c>
       <c r="G64" s="7">
-        <v>0.189334</v>
+        <v>0.170987</v>
       </c>
       <c r="H64" s="7">
-        <v>0.145449</v>
+        <v>0.128377</v>
       </c>
       <c r="I64" s="7">
-        <v>0.40341299999999997</v>
+        <v>0.383761</v>
       </c>
       <c r="J64" s="7">
-        <v>2.039473</v>
+        <v>2.035165</v>
       </c>
       <c r="K64" s="7">
-        <v>6.198828</v>
+        <v>6.117795999999999</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,25 +4519,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.04478</v>
+        <v>0.042421</v>
       </c>
       <c r="F65" s="7">
-        <v>0.045240999999999996</v>
+        <v>0.043247</v>
       </c>
       <c r="G65" s="7">
-        <v>0.106418</v>
+        <v>0.10156499999999999</v>
       </c>
       <c r="H65" s="7">
-        <v>0.062338</v>
+        <v>0.059939</v>
       </c>
       <c r="I65" s="7">
-        <v>0.302141</v>
+        <v>0.29662299999999997</v>
       </c>
       <c r="J65" s="7">
-        <v>2.081386</v>
+        <v>2.084155</v>
       </c>
       <c r="K65" s="7">
-        <v>5.3587</v>
+        <v>5.381398000000001</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4554,25 +4554,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.05766</v>
+        <v>0.054421</v>
       </c>
       <c r="F66" s="7">
-        <v>0.036236000000000004</v>
+        <v>0.03318</v>
       </c>
       <c r="G66" s="7">
-        <v>0.09457</v>
+        <v>0.090917</v>
       </c>
       <c r="H66" s="7">
-        <v>0.0435</v>
+        <v>0.040304</v>
       </c>
       <c r="I66" s="7">
-        <v>0.327793</v>
+        <v>0.324664</v>
       </c>
       <c r="J66" s="7">
-        <v>2.313132</v>
+        <v>2.292662</v>
       </c>
       <c r="K66" s="7">
-        <v>6.812385000000001</v>
+        <v>6.847349</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4589,25 +4589,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.082886</v>
+        <v>0.069672</v>
       </c>
       <c r="F67" s="7">
-        <v>0.072894</v>
+        <v>0.038475999999999996</v>
       </c>
       <c r="G67" s="7">
-        <v>0.262869</v>
+        <v>0.246338</v>
       </c>
       <c r="H67" s="7">
-        <v>0.20540299999999997</v>
+        <v>0.19069400000000003</v>
       </c>
       <c r="I67" s="7">
-        <v>0.564991</v>
+        <v>0.552946</v>
       </c>
       <c r="J67" s="7">
-        <v>2.569757</v>
+        <v>2.5638929999999998</v>
       </c>
       <c r="K67" s="7">
-        <v>9.551429</v>
+        <v>9.485654</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4624,25 +4624,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.049227</v>
+        <v>0.046496</v>
       </c>
       <c r="F68" s="7">
-        <v>0.036934999999999996</v>
+        <v>0.032706</v>
       </c>
       <c r="G68" s="7">
-        <v>0.095976</v>
+        <v>0.092816</v>
       </c>
       <c r="H68" s="7">
-        <v>0.04901900000000001</v>
+        <v>0.046289</v>
       </c>
       <c r="I68" s="7">
-        <v>0.30128299999999997</v>
+        <v>0.297443</v>
       </c>
       <c r="J68" s="7">
-        <v>2.084766</v>
+        <v>2.070116</v>
       </c>
       <c r="K68" s="7">
-        <v>6.179785000000001</v>
+        <v>6.212976</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4659,25 +4659,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.07241399999999999</v>
+        <v>0.064873</v>
       </c>
       <c r="F69" s="7">
-        <v>0.054869</v>
+        <v>0.037797</v>
       </c>
       <c r="G69" s="7">
-        <v>0.21854700000000002</v>
+        <v>0.20714200000000002</v>
       </c>
       <c r="H69" s="7">
-        <v>0.128726</v>
+        <v>0.12078900000000001</v>
       </c>
       <c r="I69" s="7">
-        <v>0.47571399999999997</v>
+        <v>0.471347</v>
       </c>
       <c r="J69" s="7">
-        <v>2.174375</v>
+        <v>2.17771</v>
       </c>
       <c r="K69" s="7">
-        <v>5.586664</v>
+        <v>5.545006</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,25 +4694,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.030271</v>
+        <v>0.031326</v>
       </c>
       <c r="F70" s="7">
-        <v>0.094634</v>
+        <v>0.09466</v>
       </c>
       <c r="G70" s="7">
-        <v>0.201582</v>
+        <v>0.200268</v>
       </c>
       <c r="H70" s="7">
-        <v>0.123308</v>
+        <v>0.124457</v>
       </c>
       <c r="I70" s="7">
-        <v>0.480828</v>
+        <v>0.4806</v>
       </c>
       <c r="J70" s="7">
-        <v>2.346101</v>
+        <v>2.340813</v>
       </c>
       <c r="K70" s="7">
-        <v>4.044801</v>
+        <v>4.047559</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4729,25 +4729,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.242755</v>
+        <v>0.224415</v>
       </c>
       <c r="F71" s="7">
-        <v>0.11545899999999999</v>
+        <v>0.07724400000000001</v>
       </c>
       <c r="G71" s="7">
-        <v>0.154011</v>
+        <v>0.136955</v>
       </c>
       <c r="H71" s="7">
-        <v>0.17112100000000002</v>
+        <v>0.153839</v>
       </c>
       <c r="I71" s="7">
-        <v>0.722482</v>
+        <v>0.670999</v>
       </c>
       <c r="J71" s="7">
-        <v>3.7664139999999997</v>
+        <v>3.659652</v>
       </c>
       <c r="K71" s="7">
-        <v>7.622401999999999</v>
+        <v>7.577223</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4764,25 +4764,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.047213000000000005</v>
+        <v>0.044811</v>
       </c>
       <c r="F72" s="7">
-        <v>0.080751</v>
+        <v>0.07129400000000001</v>
       </c>
       <c r="G72" s="7">
-        <v>0.228991</v>
+        <v>0.224148</v>
       </c>
       <c r="H72" s="7">
-        <v>0.138212</v>
+        <v>0.135601</v>
       </c>
       <c r="I72" s="7">
-        <v>0.4539</v>
+        <v>0.452415</v>
       </c>
       <c r="J72" s="7">
-        <v>1.741012</v>
+        <v>1.746971</v>
       </c>
       <c r="K72" s="7">
-        <v>4.662631999999999</v>
+        <v>4.6536480000000005</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,25 +4799,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.07126299999999999</v>
+        <v>0.05961</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.0068130000000000005</v>
+        <v>-0.01772</v>
       </c>
       <c r="G73" s="7">
-        <v>0.052181</v>
+        <v>0.040534999999999995</v>
       </c>
       <c r="H73" s="7">
-        <v>0.002673</v>
+        <v>-0.008234</v>
       </c>
       <c r="I73" s="7">
-        <v>0.28578600000000004</v>
+        <v>0.27400800000000003</v>
       </c>
       <c r="J73" s="7">
-        <v>2.0597630000000002</v>
+        <v>2.013935</v>
       </c>
       <c r="K73" s="7">
-        <v>6.135706</v>
+        <v>6.108777</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,25 +4834,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.12135</v>
+        <v>0.103796</v>
       </c>
       <c r="F74" s="7">
-        <v>0.073641</v>
+        <v>0.030731</v>
       </c>
       <c r="G74" s="7">
-        <v>0.254951</v>
+        <v>0.23672100000000001</v>
       </c>
       <c r="H74" s="7">
-        <v>0.21532800000000002</v>
+        <v>0.19630299999999998</v>
       </c>
       <c r="I74" s="7">
-        <v>0.362407</v>
+        <v>0.358797</v>
       </c>
       <c r="J74" s="7">
-        <v>2.54936</v>
+        <v>2.611955</v>
       </c>
       <c r="K74" s="7">
-        <v>15.205061</v>
+        <v>15.038806999999998</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4869,25 +4869,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.046029999999999995</v>
+        <v>0.041898</v>
       </c>
       <c r="F75" s="7">
-        <v>0.014138999999999999</v>
+        <v>0.007256</v>
       </c>
       <c r="G75" s="7">
-        <v>0.171735</v>
+        <v>0.163936</v>
       </c>
       <c r="H75" s="7">
-        <v>0.05300099999999999</v>
+        <v>0.048841</v>
       </c>
       <c r="I75" s="7">
-        <v>0.424377</v>
+        <v>0.420931</v>
       </c>
       <c r="J75" s="7">
-        <v>1.8009870000000001</v>
+        <v>1.7919239999999999</v>
       </c>
       <c r="K75" s="7">
-        <v>3.724889</v>
+        <v>3.7090410000000005</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,25 +4904,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.069625</v>
+        <v>0.062279</v>
       </c>
       <c r="F76" s="7">
-        <v>0.05404</v>
+        <v>0.036876</v>
       </c>
       <c r="G76" s="7">
-        <v>0.22053999999999999</v>
+        <v>0.209543</v>
       </c>
       <c r="H76" s="7">
-        <v>0.12897</v>
+        <v>0.121217</v>
       </c>
       <c r="I76" s="7">
-        <v>0.48234299999999997</v>
+        <v>0.478622</v>
       </c>
       <c r="J76" s="7">
-        <v>2.214633</v>
+        <v>2.2207310000000002</v>
       </c>
       <c r="K76" s="7">
-        <v>5.67636</v>
+        <v>5.634789</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4939,25 +4939,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.045899</v>
+        <v>0.04101200000000001</v>
       </c>
       <c r="F77" s="7">
-        <v>0.073708</v>
+        <v>0.062104999999999994</v>
       </c>
       <c r="G77" s="7">
-        <v>0.270843</v>
+        <v>0.266573</v>
       </c>
       <c r="H77" s="7">
-        <v>0.187074</v>
+        <v>0.181528</v>
       </c>
       <c r="I77" s="7">
-        <v>0.421312</v>
+        <v>0.41154</v>
       </c>
       <c r="J77" s="7">
-        <v>1.865215</v>
+        <v>1.881138</v>
       </c>
       <c r="K77" s="7">
-        <v>5.499129</v>
+        <v>5.485023999999999</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4974,25 +4974,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="7">
-        <v>0.090591</v>
+        <v>0.0762</v>
       </c>
       <c r="F78" s="7">
-        <v>0.106228</v>
+        <v>0.077851</v>
       </c>
       <c r="G78" s="7">
-        <v>0.350691</v>
+        <v>0.33163800000000004</v>
       </c>
       <c r="H78" s="7">
-        <v>0.25310900000000003</v>
+        <v>0.236573</v>
       </c>
       <c r="I78" s="7">
-        <v>0.668882</v>
+        <v>0.6575449999999999</v>
       </c>
       <c r="J78" s="7">
-        <v>2.8204000000000002</v>
+        <v>2.834047</v>
       </c>
       <c r="K78" s="7">
-        <v>8.515184</v>
+        <v>8.390611999999999</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5009,25 +5009,25 @@
         <v>5</v>
       </c>
       <c r="E79" s="7">
-        <v>0.072617</v>
+        <v>0.06581000000000001</v>
       </c>
       <c r="F79" s="7">
-        <v>0.087045</v>
+        <v>0.070382</v>
       </c>
       <c r="G79" s="7">
-        <v>0.17290299999999997</v>
+        <v>0.166448</v>
       </c>
       <c r="H79" s="7">
-        <v>0.157859</v>
+        <v>0.150512</v>
       </c>
       <c r="I79" s="7">
-        <v>0.41991300000000004</v>
+        <v>0.413427</v>
       </c>
       <c r="J79" s="7">
-        <v>2.339096</v>
+        <v>2.343982</v>
       </c>
       <c r="K79" s="7">
-        <v>8.026372</v>
+        <v>7.987858</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,25 +5044,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.129796</v>
+        <v>0.11264400000000001</v>
       </c>
       <c r="F80" s="7">
-        <v>0.0968</v>
+        <v>0.057009</v>
       </c>
       <c r="G80" s="7">
-        <v>0.245221</v>
+        <v>0.23072800000000002</v>
       </c>
       <c r="H80" s="7">
-        <v>0.248967</v>
+        <v>0.230006</v>
       </c>
       <c r="I80" s="7">
-        <v>0.402819</v>
+        <v>0.397727</v>
       </c>
       <c r="J80" s="7">
-        <v>2.3069550000000003</v>
+        <v>2.360855</v>
       </c>
       <c r="K80" s="7">
-        <v>11.548789999999999</v>
+        <v>11.361244999999998</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5079,25 +5079,25 @@
         <v>4</v>
       </c>
       <c r="E81" s="7">
-        <v>0.035404</v>
+        <v>0.034437999999999996</v>
       </c>
       <c r="F81" s="7">
-        <v>0.070594</v>
+        <v>0.064477</v>
       </c>
       <c r="G81" s="7">
-        <v>0.176351</v>
+        <v>0.174695</v>
       </c>
       <c r="H81" s="7">
-        <v>0.11634399999999999</v>
+        <v>0.115302</v>
       </c>
       <c r="I81" s="7">
-        <v>0.375963</v>
+        <v>0.37660400000000005</v>
       </c>
       <c r="J81" s="7">
-        <v>1.5171510000000001</v>
+        <v>1.5232990000000002</v>
       </c>
       <c r="K81" s="7">
-        <v>4.384298</v>
+        <v>4.372672</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,25 +5114,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.047288</v>
+        <v>0.043258</v>
       </c>
       <c r="F82" s="7">
-        <v>0.00738</v>
+        <v>0.0017449999999999998</v>
       </c>
       <c r="G82" s="7">
-        <v>0.141951</v>
+        <v>0.134428</v>
       </c>
       <c r="H82" s="7">
-        <v>0.045784000000000005</v>
+        <v>0.04176</v>
       </c>
       <c r="I82" s="7">
-        <v>0.39008000000000004</v>
+        <v>0.387367</v>
       </c>
       <c r="J82" s="7">
-        <v>1.491373</v>
+        <v>1.4811189999999999</v>
       </c>
       <c r="K82" s="7">
-        <v>3.136294</v>
+        <v>3.118596</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5149,25 +5149,25 @@
         <v>5</v>
       </c>
       <c r="E83" s="7">
-        <v>0.079635</v>
+        <v>0.07279</v>
       </c>
       <c r="F83" s="7">
-        <v>0.081982</v>
+        <v>0.060621</v>
       </c>
       <c r="G83" s="7">
-        <v>0.17249199999999998</v>
+        <v>0.16727799999999998</v>
       </c>
       <c r="H83" s="7">
-        <v>0.16643999999999998</v>
+        <v>0.159045</v>
       </c>
       <c r="I83" s="7">
-        <v>0.42288</v>
+        <v>0.413184</v>
       </c>
       <c r="J83" s="7">
-        <v>2.347169</v>
+        <v>2.3658959999999998</v>
       </c>
       <c r="K83" s="7">
-        <v>9.012354</v>
+        <v>8.979583</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,22 +5184,22 @@
         <v>6</v>
       </c>
       <c r="E84" s="7">
-        <v>0.027889</v>
+        <v>0.007372999999999999</v>
       </c>
       <c r="F84" s="7">
-        <v>-0.08211299999999999</v>
+        <v>-0.131426</v>
       </c>
       <c r="G84" s="7">
-        <v>0.132699</v>
+        <v>0.1215</v>
       </c>
       <c r="H84" s="7">
-        <v>0.034138</v>
+        <v>0.013496999999999999</v>
       </c>
       <c r="I84" s="7">
-        <v>0.6554800000000001</v>
+        <v>0.628998</v>
       </c>
       <c r="J84" s="7">
-        <v>3.8961669999999997</v>
+        <v>3.764612</v>
       </c>
       <c r="K84" s="7"/>
     </row>
@@ -5217,19 +5217,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="7">
-        <v>0.029435</v>
+        <v>0.030441</v>
       </c>
       <c r="F85" s="7">
-        <v>0.094064</v>
+        <v>0.094041</v>
       </c>
       <c r="G85" s="7">
-        <v>0.197488</v>
+        <v>0.196233</v>
       </c>
       <c r="H85" s="7">
-        <v>0.121639</v>
+        <v>0.122735</v>
       </c>
       <c r="I85" s="7">
-        <v>0.46512099999999995</v>
+        <v>0.464875</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5248,22 +5248,22 @@
         <v>6</v>
       </c>
       <c r="E86" s="7">
-        <v>0.121045</v>
+        <v>0.108498</v>
       </c>
       <c r="F86" s="7">
-        <v>0.090851</v>
+        <v>0.057481</v>
       </c>
       <c r="G86" s="7">
-        <v>0.266838</v>
+        <v>0.25348400000000004</v>
       </c>
       <c r="H86" s="7">
-        <v>0.21390399999999998</v>
+        <v>0.200318</v>
       </c>
       <c r="I86" s="7">
-        <v>0.554739</v>
+        <v>0.549919</v>
       </c>
       <c r="J86" s="7">
-        <v>2.767972</v>
+        <v>2.7761180000000003</v>
       </c>
       <c r="K86" s="7"/>
     </row>
@@ -5281,22 +5281,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.151897</v>
+        <v>0.152661</v>
       </c>
       <c r="F87" s="7">
-        <v>0.198735</v>
+        <v>0.199188</v>
       </c>
       <c r="G87" s="7">
-        <v>0.313685</v>
+        <v>0.312257</v>
       </c>
       <c r="H87" s="7">
-        <v>0.316246</v>
+        <v>0.317119</v>
       </c>
       <c r="I87" s="7">
-        <v>0.699545</v>
+        <v>0.6945910000000001</v>
       </c>
       <c r="J87" s="7">
-        <v>3.901685</v>
+        <v>3.9364179999999998</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,25 +5314,25 @@
         <v>7</v>
       </c>
       <c r="E88" s="7">
-        <v>0.039449</v>
+        <v>0.014306000000000001</v>
       </c>
       <c r="F88" s="7">
-        <v>-0.06973900000000001</v>
+        <v>-0.122338</v>
       </c>
       <c r="G88" s="7">
-        <v>0.192786</v>
+        <v>0.170652</v>
       </c>
       <c r="H88" s="7">
-        <v>0.095829</v>
+        <v>0.069323</v>
       </c>
       <c r="I88" s="7">
-        <v>0.653604</v>
+        <v>0.615413</v>
       </c>
       <c r="J88" s="7">
-        <v>4.259374</v>
+        <v>4.129580000000001</v>
       </c>
       <c r="K88" s="7">
-        <v>14.256645</v>
+        <v>14.093544999999999</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5349,25 +5349,25 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>0.034279000000000004</v>
+        <v>0.034819</v>
       </c>
       <c r="F89" s="7">
-        <v>0.093486</v>
+        <v>0.091776</v>
       </c>
       <c r="G89" s="7">
-        <v>0.208073</v>
+        <v>0.20624199999999998</v>
       </c>
       <c r="H89" s="7">
-        <v>0.128043</v>
+        <v>0.128633</v>
       </c>
       <c r="I89" s="7">
-        <v>0.505814</v>
+        <v>0.511525</v>
       </c>
       <c r="J89" s="7">
-        <v>2.388874</v>
+        <v>2.386428</v>
       </c>
       <c r="K89" s="7">
-        <v>4.313193999999999</v>
+        <v>4.320354</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5384,25 +5384,25 @@
         <v>5</v>
       </c>
       <c r="E90" s="7">
-        <v>0.050012999999999995</v>
+        <v>0.044369</v>
       </c>
       <c r="F90" s="7">
-        <v>0.030188000000000003</v>
+        <v>0.017459</v>
       </c>
       <c r="G90" s="7">
-        <v>0.176057</v>
+        <v>0.16636399999999998</v>
       </c>
       <c r="H90" s="7">
-        <v>0.088261</v>
+        <v>0.082411</v>
       </c>
       <c r="I90" s="7">
-        <v>0.304972</v>
+        <v>0.305934</v>
       </c>
       <c r="J90" s="7">
-        <v>2.043024</v>
+        <v>2.028045</v>
       </c>
       <c r="K90" s="7">
-        <v>5.462224</v>
+        <v>5.431038999999999</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5419,22 +5419,22 @@
         <v>6</v>
       </c>
       <c r="E91" s="7">
-        <v>0.07108500000000001</v>
+        <v>0.061718999999999996</v>
       </c>
       <c r="F91" s="7">
-        <v>0.080655</v>
+        <v>0.055729</v>
       </c>
       <c r="G91" s="7">
-        <v>0.236509</v>
+        <v>0.225664</v>
       </c>
       <c r="H91" s="7">
-        <v>0.178223</v>
+        <v>0.16791899999999998</v>
       </c>
       <c r="I91" s="7">
-        <v>0.433365</v>
+        <v>0.429813</v>
       </c>
       <c r="J91" s="7">
-        <v>2.538218</v>
+        <v>2.553504</v>
       </c>
       <c r="K91" s="7"/>
     </row>
@@ -5452,25 +5452,25 @@
         <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>0.059473000000000005</v>
+        <v>0.052077</v>
       </c>
       <c r="F92" s="7">
-        <v>0.033014</v>
+        <v>0.017419</v>
       </c>
       <c r="G92" s="7">
-        <v>0.208901</v>
+        <v>0.197017</v>
       </c>
       <c r="H92" s="7">
-        <v>0.102164</v>
+        <v>0.09447</v>
       </c>
       <c r="I92" s="7">
-        <v>0.34810800000000003</v>
+        <v>0.347885</v>
       </c>
       <c r="J92" s="7">
-        <v>1.989427</v>
+        <v>1.987935</v>
       </c>
       <c r="K92" s="7">
-        <v>4.999139</v>
+        <v>4.960882</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,25 +5487,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.040351</v>
+        <v>0.038347</v>
       </c>
       <c r="F93" s="7">
-        <v>0.068196</v>
+        <v>0.062206000000000004</v>
       </c>
       <c r="G93" s="7">
-        <v>0.20136199999999999</v>
+        <v>0.195549</v>
       </c>
       <c r="H93" s="7">
-        <v>0.133199</v>
+        <v>0.131016</v>
       </c>
       <c r="I93" s="7">
-        <v>0.344108</v>
+        <v>0.347474</v>
       </c>
       <c r="J93" s="7">
-        <v>1.709101</v>
+        <v>1.70713</v>
       </c>
       <c r="K93" s="7">
-        <v>4.640167</v>
+        <v>4.633171</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,25 +5522,25 @@
         <v>4</v>
       </c>
       <c r="E94" s="7">
-        <v>0.077464</v>
+        <v>0.066095</v>
       </c>
       <c r="F94" s="7">
-        <v>0.057318</v>
+        <v>0.031763</v>
       </c>
       <c r="G94" s="7">
-        <v>0.28458</v>
+        <v>0.26894100000000004</v>
       </c>
       <c r="H94" s="7">
-        <v>0.176463</v>
+        <v>0.16405</v>
       </c>
       <c r="I94" s="7">
-        <v>0.503734</v>
+        <v>0.49952599999999997</v>
       </c>
       <c r="J94" s="7">
-        <v>2.781185</v>
+        <v>2.793235</v>
       </c>
       <c r="K94" s="7">
-        <v>8.446175</v>
+        <v>8.37603</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,25 +5557,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.043037</v>
+        <v>0.038586</v>
       </c>
       <c r="F95" s="7">
-        <v>0.018757</v>
+        <v>0.010891999999999999</v>
       </c>
       <c r="G95" s="7">
-        <v>0.174039</v>
+        <v>0.166127</v>
       </c>
       <c r="H95" s="7">
-        <v>0.051527</v>
+        <v>0.04704</v>
       </c>
       <c r="I95" s="7">
-        <v>0.43892000000000003</v>
+        <v>0.437222</v>
       </c>
       <c r="J95" s="7">
-        <v>1.363433</v>
+        <v>1.351488</v>
       </c>
       <c r="K95" s="7">
-        <v>2.7768360000000003</v>
+        <v>2.7592939999999997</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,25 +5592,25 @@
         <v>7</v>
       </c>
       <c r="E96" s="7">
-        <v>0.111595</v>
+        <v>0.0926</v>
       </c>
       <c r="F96" s="7">
-        <v>0.051933</v>
+        <v>0.011754</v>
       </c>
       <c r="G96" s="7">
-        <v>0.302492</v>
+        <v>0.284087</v>
       </c>
       <c r="H96" s="7">
-        <v>0.22825199999999998</v>
+        <v>0.20726299999999998</v>
       </c>
       <c r="I96" s="7">
-        <v>0.395527</v>
+        <v>0.39037900000000003</v>
       </c>
       <c r="J96" s="7">
-        <v>2.87518</v>
+        <v>2.910646</v>
       </c>
       <c r="K96" s="7">
-        <v>15.311259999999999</v>
+        <v>15.096963</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,25 +5627,25 @@
         <v>6</v>
       </c>
       <c r="E97" s="7">
-        <v>0.09632</v>
+        <v>0.076409</v>
       </c>
       <c r="F97" s="7">
-        <v>0.030884</v>
+        <v>-0.007732</v>
       </c>
       <c r="G97" s="7">
-        <v>0.404202</v>
+        <v>0.382698</v>
       </c>
       <c r="H97" s="7">
-        <v>0.222942</v>
+        <v>0.20073</v>
       </c>
       <c r="I97" s="7">
-        <v>0.502177</v>
+        <v>0.49311</v>
       </c>
       <c r="J97" s="7">
-        <v>4.013739</v>
+        <v>4.037209</v>
       </c>
       <c r="K97" s="7">
-        <v>19.876399</v>
+        <v>19.569942</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,25 +5662,25 @@
         <v>4</v>
       </c>
       <c r="E98" s="7">
-        <v>0.077262</v>
+        <v>0.06677</v>
       </c>
       <c r="F98" s="7">
-        <v>0.084127</v>
+        <v>0.059931</v>
       </c>
       <c r="G98" s="7">
-        <v>0.307072</v>
+        <v>0.294659</v>
       </c>
       <c r="H98" s="7">
-        <v>0.217688</v>
+        <v>0.20582899999999998</v>
       </c>
       <c r="I98" s="7">
-        <v>0.549272</v>
+        <v>0.545861</v>
       </c>
       <c r="J98" s="7">
-        <v>3.4158600000000003</v>
+        <v>3.451561</v>
       </c>
       <c r="K98" s="7">
-        <v>9.363707</v>
+        <v>9.292001</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,25 +5697,25 @@
         <v>6</v>
       </c>
       <c r="E99" s="7">
-        <v>0.034089999999999995</v>
+        <v>0.034252</v>
       </c>
       <c r="F99" s="7">
-        <v>0.042668</v>
+        <v>0.042105</v>
       </c>
       <c r="G99" s="7">
-        <v>0.10034000000000001</v>
+        <v>0.099955</v>
       </c>
       <c r="H99" s="7">
-        <v>0.058202</v>
+        <v>0.058367</v>
       </c>
       <c r="I99" s="7">
-        <v>0.284</v>
+        <v>0.282394</v>
       </c>
       <c r="J99" s="7">
-        <v>1.9977850000000001</v>
+        <v>1.9919049999999998</v>
       </c>
       <c r="K99" s="7">
-        <v>5.779735</v>
+        <v>5.8258469999999996</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,25 +5732,25 @@
         <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>0.087049</v>
+        <v>0.07446900000000001</v>
       </c>
       <c r="F100" s="7">
-        <v>0.08191000000000001</v>
+        <v>0.054028</v>
       </c>
       <c r="G100" s="7">
-        <v>0.370664</v>
+        <v>0.355932</v>
       </c>
       <c r="H100" s="7">
-        <v>0.228196</v>
+        <v>0.213982</v>
       </c>
       <c r="I100" s="7">
-        <v>0.590289</v>
+        <v>0.588159</v>
       </c>
       <c r="J100" s="7">
-        <v>3.646298</v>
+        <v>3.684204</v>
       </c>
       <c r="K100" s="7">
-        <v>12.43386</v>
+        <v>12.329322</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,25 +5767,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.097309</v>
+        <v>0.07918599999999999</v>
       </c>
       <c r="F101" s="7">
-        <v>0.089932</v>
+        <v>0.052351</v>
       </c>
       <c r="G101" s="7">
-        <v>0.35509300000000005</v>
+        <v>0.33419899999999997</v>
       </c>
       <c r="H101" s="7">
-        <v>0.304016</v>
+        <v>0.28247900000000004</v>
       </c>
       <c r="I101" s="7">
-        <v>0.656772</v>
+        <v>0.633536</v>
       </c>
       <c r="J101" s="7">
-        <v>3.509617</v>
+        <v>3.485811</v>
       </c>
       <c r="K101" s="7">
-        <v>11.514055</v>
+        <v>11.373118</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,25 +5802,25 @@
         <v>2</v>
       </c>
       <c r="E102" s="7">
-        <v>0.043197</v>
+        <v>0.041478</v>
       </c>
       <c r="F102" s="7">
-        <v>0.105987</v>
+        <v>0.09959699999999999</v>
       </c>
       <c r="G102" s="7">
-        <v>0.26508299999999996</v>
+        <v>0.259735</v>
       </c>
       <c r="H102" s="7">
-        <v>0.157448</v>
+        <v>0.15554</v>
       </c>
       <c r="I102" s="7">
-        <v>0.575184</v>
+        <v>0.573777</v>
       </c>
       <c r="J102" s="7">
-        <v>3.1283550000000004</v>
+        <v>3.1120569999999996</v>
       </c>
       <c r="K102" s="7">
-        <v>5.729735</v>
+        <v>5.714583</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,25 +5837,25 @@
         <v>6</v>
       </c>
       <c r="E103" s="7">
-        <v>0.103905</v>
+        <v>0.084018</v>
       </c>
       <c r="F103" s="7">
-        <v>0.080191</v>
+        <v>0.036832</v>
       </c>
       <c r="G103" s="7">
-        <v>0.361126</v>
+        <v>0.337958</v>
       </c>
       <c r="H103" s="7">
-        <v>0.321312</v>
+        <v>0.297509</v>
       </c>
       <c r="I103" s="7">
-        <v>0.65305</v>
+        <v>0.6287039999999999</v>
       </c>
       <c r="J103" s="7">
-        <v>3.403082</v>
+        <v>3.380799</v>
       </c>
       <c r="K103" s="7">
-        <v>13.652636</v>
+        <v>13.488331</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,25 +5872,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.049307</v>
+        <v>0.047111</v>
       </c>
       <c r="F104" s="7">
-        <v>0.035542</v>
+        <v>0.03315</v>
       </c>
       <c r="G104" s="7">
-        <v>0.096418</v>
+        <v>0.093961</v>
       </c>
       <c r="H104" s="7">
-        <v>0.046604</v>
+        <v>0.044413999999999995</v>
       </c>
       <c r="I104" s="7">
-        <v>0.32041400000000003</v>
+        <v>0.319113</v>
       </c>
       <c r="J104" s="7">
-        <v>2.164829</v>
+        <v>2.146916</v>
       </c>
       <c r="K104" s="7">
-        <v>6.191096</v>
+        <v>6.228492</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,16 +5907,16 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.10543799999999999</v>
+        <v>0.096586</v>
       </c>
       <c r="F105" s="7">
-        <v>0.065356</v>
+        <v>0.043550000000000005</v>
       </c>
       <c r="G105" s="7">
-        <v>0.190906</v>
+        <v>0.18046500000000001</v>
       </c>
       <c r="H105" s="7">
-        <v>0.152344</v>
+        <v>0.143116</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
@@ -5936,22 +5936,22 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.19633199999999998</v>
+        <v>0.183967</v>
       </c>
       <c r="F106" s="7">
-        <v>0.180984</v>
+        <v>0.15576800000000002</v>
       </c>
       <c r="G106" s="7">
-        <v>0.306513</v>
+        <v>0.290016</v>
       </c>
       <c r="H106" s="7">
-        <v>0.301699</v>
+        <v>0.28824500000000003</v>
       </c>
       <c r="I106" s="7">
-        <v>0.827144</v>
+        <v>0.788133</v>
       </c>
       <c r="J106" s="7">
-        <v>4.183302</v>
+        <v>4.101845</v>
       </c>
       <c r="K106" s="7"/>
     </row>
@@ -5969,25 +5969,25 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.048049999999999995</v>
+        <v>0.025369000000000003</v>
       </c>
       <c r="F107" s="7">
-        <v>-0.057712000000000006</v>
+        <v>-0.112112</v>
       </c>
       <c r="G107" s="7">
-        <v>0.213476</v>
+        <v>0.19128900000000001</v>
       </c>
       <c r="H107" s="7">
-        <v>0.126629</v>
+        <v>0.102247</v>
       </c>
       <c r="I107" s="7">
-        <v>0.70081</v>
+        <v>0.6637050000000001</v>
       </c>
       <c r="J107" s="7">
-        <v>4.968293</v>
+        <v>4.842173</v>
       </c>
       <c r="K107" s="7">
-        <v>16.405253000000002</v>
+        <v>16.263667</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,25 +6004,25 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.048285999999999996</v>
+        <v>0.045397999999999994</v>
       </c>
       <c r="F108" s="7">
-        <v>0.038543</v>
+        <v>0.032667</v>
       </c>
       <c r="G108" s="7">
-        <v>0.19250699999999998</v>
+        <v>0.186292</v>
       </c>
       <c r="H108" s="7">
-        <v>0.07542900000000001</v>
+        <v>0.072465</v>
       </c>
       <c r="I108" s="7">
-        <v>0.478376</v>
+        <v>0.47458500000000003</v>
       </c>
       <c r="J108" s="7">
-        <v>2.063272</v>
+        <v>2.0565629999999997</v>
       </c>
       <c r="K108" s="7">
-        <v>3.917167</v>
+        <v>3.901391</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,25 +6039,25 @@
         <v>6</v>
       </c>
       <c r="E109" s="7">
-        <v>0.045739</v>
+        <v>0.043684</v>
       </c>
       <c r="F109" s="7">
-        <v>0.032458</v>
+        <v>0.028736</v>
       </c>
       <c r="G109" s="7">
-        <v>0.12638</v>
+        <v>0.12395400000000001</v>
       </c>
       <c r="H109" s="7">
-        <v>0.053984</v>
+        <v>0.051913</v>
       </c>
       <c r="I109" s="7">
-        <v>0.34669400000000006</v>
+        <v>0.34368099999999996</v>
       </c>
       <c r="J109" s="7">
-        <v>2.21449</v>
+        <v>2.206902</v>
       </c>
       <c r="K109" s="7">
-        <v>6.645268</v>
+        <v>6.6830359999999995</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,25 +6074,25 @@
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>0.048817000000000006</v>
+        <v>0.045901</v>
       </c>
       <c r="F110" s="7">
-        <v>0.079469</v>
+        <v>0.070003</v>
       </c>
       <c r="G110" s="7">
-        <v>0.20241299999999998</v>
+        <v>0.196007</v>
       </c>
       <c r="H110" s="7">
-        <v>0.14898</v>
+        <v>0.145786</v>
       </c>
       <c r="I110" s="7">
-        <v>0.469674</v>
+        <v>0.465683</v>
       </c>
       <c r="J110" s="7">
-        <v>1.9504380000000001</v>
+        <v>1.951858</v>
       </c>
       <c r="K110" s="7">
-        <v>5.499884</v>
+        <v>5.489706</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,25 +6109,25 @@
         <v>5</v>
       </c>
       <c r="E111" s="7">
-        <v>0.05710200000000001</v>
+        <v>0.04638899999999999</v>
       </c>
       <c r="F111" s="7">
-        <v>0.03387</v>
+        <v>0.008409</v>
       </c>
       <c r="G111" s="7">
-        <v>0.230329</v>
+        <v>0.21644200000000002</v>
       </c>
       <c r="H111" s="7">
-        <v>0.145813</v>
+        <v>0.134202</v>
       </c>
       <c r="I111" s="7">
-        <v>0.540142</v>
+        <v>0.5303450000000001</v>
       </c>
       <c r="J111" s="7">
-        <v>3.454209</v>
+        <v>3.4748419999999998</v>
       </c>
       <c r="K111" s="7">
-        <v>14.661411000000001</v>
+        <v>14.552251000000002</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,25 +6144,25 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>0.039842</v>
+        <v>0.038254</v>
       </c>
       <c r="F112" s="7">
-        <v>0.08818799999999999</v>
+        <v>0.079234</v>
       </c>
       <c r="G112" s="7">
-        <v>0.241773</v>
+        <v>0.237073</v>
       </c>
       <c r="H112" s="7">
-        <v>0.139352</v>
+        <v>0.137612</v>
       </c>
       <c r="I112" s="7">
-        <v>0.536265</v>
+        <v>0.5322330000000001</v>
       </c>
       <c r="J112" s="7">
-        <v>3.29298</v>
+        <v>3.27531</v>
       </c>
       <c r="K112" s="7">
-        <v>6.278185</v>
+        <v>6.266621</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6179,25 +6179,25 @@
         <v>6</v>
       </c>
       <c r="E113" s="7">
-        <v>0.116857</v>
+        <v>0.09922800000000001</v>
       </c>
       <c r="F113" s="7">
-        <v>0.10635</v>
+        <v>0.077154</v>
       </c>
       <c r="G113" s="7">
-        <v>0.28945699999999996</v>
+        <v>0.268347</v>
       </c>
       <c r="H113" s="7">
-        <v>0.24870599999999998</v>
+        <v>0.228996</v>
       </c>
       <c r="I113" s="7">
-        <v>0.552327</v>
+        <v>0.538346</v>
       </c>
       <c r="J113" s="7">
-        <v>3.345303</v>
+        <v>3.360093</v>
       </c>
       <c r="K113" s="7">
-        <v>17.054689</v>
+        <v>16.803811</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6214,25 +6214,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.111603</v>
+        <v>0.08781599999999999</v>
       </c>
       <c r="F114" s="7">
-        <v>0.069204</v>
+        <v>0.018965</v>
       </c>
       <c r="G114" s="7">
-        <v>0.274849</v>
+        <v>0.247707</v>
       </c>
       <c r="H114" s="7">
-        <v>0.19328499999999998</v>
+        <v>0.16774999999999998</v>
       </c>
       <c r="I114" s="7">
-        <v>0.531689</v>
+        <v>0.51627</v>
       </c>
       <c r="J114" s="7">
-        <v>3.292806</v>
+        <v>3.3340410000000005</v>
       </c>
       <c r="K114" s="7">
-        <v>23.250246999999998</v>
+        <v>22.866030000000002</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6249,25 +6249,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.110025</v>
+        <v>0.093363</v>
       </c>
       <c r="F115" s="7">
-        <v>0.086396</v>
+        <v>0.046627</v>
       </c>
       <c r="G115" s="7">
-        <v>0.288138</v>
+        <v>0.26787</v>
       </c>
       <c r="H115" s="7">
-        <v>0.220257</v>
+        <v>0.20194099999999998</v>
       </c>
       <c r="I115" s="7">
-        <v>0.5362899999999999</v>
+        <v>0.527934</v>
       </c>
       <c r="J115" s="7">
-        <v>2.7567579999999996</v>
+        <v>2.824489</v>
       </c>
       <c r="K115" s="7">
-        <v>16.441858</v>
+        <v>16.218173</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6284,25 +6284,25 @@
         <v>5</v>
       </c>
       <c r="E116" s="7">
-        <v>0.089497</v>
+        <v>0.07696900000000001</v>
       </c>
       <c r="F116" s="7">
-        <v>0.109442</v>
+        <v>0.086524</v>
       </c>
       <c r="G116" s="7">
-        <v>0.291863</v>
+        <v>0.274073</v>
       </c>
       <c r="H116" s="7">
-        <v>0.252744</v>
+        <v>0.238338</v>
       </c>
       <c r="I116" s="7">
-        <v>0.637549</v>
+        <v>0.624178</v>
       </c>
       <c r="J116" s="7">
-        <v>3.223116</v>
+        <v>3.216703</v>
       </c>
       <c r="K116" s="7">
-        <v>12.42092</v>
+        <v>12.284599</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6319,25 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>0.046593</v>
+        <v>0.043587</v>
       </c>
       <c r="F117" s="7">
-        <v>0.034174</v>
+        <v>0.028703</v>
       </c>
       <c r="G117" s="7">
-        <v>0.188962</v>
+        <v>0.182527</v>
       </c>
       <c r="H117" s="7">
-        <v>0.069413</v>
+        <v>0.066341</v>
       </c>
       <c r="I117" s="7">
-        <v>0.448494</v>
+        <v>0.44453699999999996</v>
       </c>
       <c r="J117" s="7">
-        <v>1.8881729999999999</v>
+        <v>1.880514</v>
       </c>
       <c r="K117" s="7">
-        <v>3.714918</v>
+        <v>3.69999</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6354,25 +6354,25 @@
         <v>6</v>
       </c>
       <c r="E118" s="7">
-        <v>0.086015</v>
+        <v>0.07548</v>
       </c>
       <c r="F118" s="7">
-        <v>0.064981</v>
+        <v>0.032694</v>
       </c>
       <c r="G118" s="7">
-        <v>0.269271</v>
+        <v>0.255412</v>
       </c>
       <c r="H118" s="7">
-        <v>0.187809</v>
+        <v>0.176286</v>
       </c>
       <c r="I118" s="7">
-        <v>0.625105</v>
+        <v>0.618597</v>
       </c>
       <c r="J118" s="7">
-        <v>3.516698</v>
+        <v>3.5553160000000004</v>
       </c>
       <c r="K118" s="7">
-        <v>16.502233</v>
+        <v>16.356232</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6389,25 +6389,25 @@
         <v>5</v>
       </c>
       <c r="E119" s="7">
-        <v>0.055579</v>
+        <v>0.041534</v>
       </c>
       <c r="F119" s="7">
-        <v>0.025276999999999997</v>
+        <v>-0.0008</v>
       </c>
       <c r="G119" s="7">
-        <v>0.18998400000000001</v>
+        <v>0.172812</v>
       </c>
       <c r="H119" s="7">
-        <v>0.108525</v>
+        <v>0.093775</v>
       </c>
       <c r="I119" s="7">
-        <v>0.466702</v>
+        <v>0.452714</v>
       </c>
       <c r="J119" s="7">
-        <v>2.55355</v>
+        <v>2.593484</v>
       </c>
       <c r="K119" s="7">
-        <v>9.06296</v>
+        <v>8.951819</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,25 +6424,25 @@
         <v>6</v>
       </c>
       <c r="E120" s="7">
-        <v>0.072839</v>
+        <v>0.057150999999999993</v>
       </c>
       <c r="F120" s="7">
-        <v>0.013054</v>
+        <v>-0.026654</v>
       </c>
       <c r="G120" s="7">
-        <v>0.185062</v>
+        <v>0.172547</v>
       </c>
       <c r="H120" s="7">
-        <v>0.136224</v>
+        <v>0.11960900000000001</v>
       </c>
       <c r="I120" s="7">
-        <v>0.43276400000000004</v>
+        <v>0.422844</v>
       </c>
       <c r="J120" s="7">
-        <v>3.3764920000000003</v>
+        <v>3.394269</v>
       </c>
       <c r="K120" s="7">
-        <v>18.35544</v>
+        <v>18.149166</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,25 +6459,25 @@
         <v>4</v>
       </c>
       <c r="E121" s="7">
-        <v>0.057371</v>
+        <v>0.049208</v>
       </c>
       <c r="F121" s="7">
-        <v>0.04785999999999999</v>
+        <v>0.031291</v>
       </c>
       <c r="G121" s="7">
-        <v>0.209724</v>
+        <v>0.19676300000000002</v>
       </c>
       <c r="H121" s="7">
-        <v>0.11870900000000001</v>
+        <v>0.11007199999999999</v>
       </c>
       <c r="I121" s="7">
-        <v>0.488483</v>
+        <v>0.480831</v>
       </c>
       <c r="J121" s="7">
-        <v>2.328726</v>
+        <v>2.334504</v>
       </c>
       <c r="K121" s="7">
-        <v>6.083111</v>
+        <v>6.027734000000001</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6494,25 +6494,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.048743</v>
+        <v>0.041590999999999996</v>
       </c>
       <c r="F122" s="7">
-        <v>0.044855</v>
+        <v>0.030091</v>
       </c>
       <c r="G122" s="7">
-        <v>0.18143499999999999</v>
+        <v>0.17035699999999998</v>
       </c>
       <c r="H122" s="7">
-        <v>0.103368</v>
+        <v>0.09584300000000001</v>
       </c>
       <c r="I122" s="7">
-        <v>0.43804000000000004</v>
+        <v>0.43111600000000005</v>
       </c>
       <c r="J122" s="7">
-        <v>1.964806</v>
+        <v>1.969905</v>
       </c>
       <c r="K122" s="7">
-        <v>6.069981</v>
+        <v>6.031843</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,16 +6529,16 @@
         <v>6</v>
       </c>
       <c r="E123" s="7">
-        <v>0.043587999999999995</v>
+        <v>0.023163</v>
       </c>
       <c r="F123" s="7">
-        <v>-0.048996000000000005</v>
+        <v>-0.09946300000000001</v>
       </c>
       <c r="G123" s="7">
-        <v>0.194121</v>
+        <v>0.172444</v>
       </c>
       <c r="H123" s="7">
-        <v>0.130217</v>
+        <v>0.108096</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
@@ -6558,25 +6558,25 @@
         <v>4</v>
       </c>
       <c r="E124" s="7">
-        <v>0.070947</v>
+        <v>0.06296</v>
       </c>
       <c r="F124" s="7">
-        <v>0.056167999999999996</v>
+        <v>0.034247</v>
       </c>
       <c r="G124" s="7">
-        <v>0.247074</v>
+        <v>0.238201</v>
       </c>
       <c r="H124" s="7">
-        <v>0.15152</v>
+        <v>0.142932</v>
       </c>
       <c r="I124" s="7">
-        <v>0.526841</v>
+        <v>0.525783</v>
       </c>
       <c r="J124" s="7">
-        <v>1.9759929999999999</v>
+        <v>1.9869329999999998</v>
       </c>
       <c r="K124" s="7">
-        <v>6.587653</v>
+        <v>6.531541999999999</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.136144</v>
+        <v>0.122588</v>
       </c>
       <c r="F125" s="7">
-        <v>0.14548</v>
+        <v>0.108301</v>
       </c>
       <c r="G125" s="7">
-        <v>0.350301</v>
+        <v>0.331164</v>
       </c>
       <c r="H125" s="7">
-        <v>0.33603900000000003</v>
+        <v>0.320098</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
@@ -6622,25 +6622,25 @@
         <v>7</v>
       </c>
       <c r="E126" s="7">
-        <v>0.107904</v>
+        <v>0.095334</v>
       </c>
       <c r="F126" s="7">
-        <v>0.064318</v>
+        <v>0.036122</v>
       </c>
       <c r="G126" s="7">
-        <v>0.215198</v>
+        <v>0.200938</v>
       </c>
       <c r="H126" s="7">
-        <v>0.128128</v>
+        <v>0.115328</v>
       </c>
       <c r="I126" s="7">
-        <v>0.428077</v>
+        <v>0.42300899999999997</v>
       </c>
       <c r="J126" s="7">
-        <v>2.40937</v>
+        <v>2.44675</v>
       </c>
       <c r="K126" s="7">
-        <v>9.448407999999999</v>
+        <v>9.337256</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,25 +6657,25 @@
         <v>5</v>
       </c>
       <c r="E127" s="7">
-        <v>0.049547999999999995</v>
+        <v>0.045436</v>
       </c>
       <c r="F127" s="7">
-        <v>0.027318</v>
+        <v>0.020773</v>
       </c>
       <c r="G127" s="7">
-        <v>0.089848</v>
+        <v>0.084015</v>
       </c>
       <c r="H127" s="7">
-        <v>0.046937</v>
+        <v>0.042836</v>
       </c>
       <c r="I127" s="7">
-        <v>0.280416</v>
+        <v>0.276203</v>
       </c>
       <c r="J127" s="7">
-        <v>1.9748869999999998</v>
+        <v>1.964352</v>
       </c>
       <c r="K127" s="7">
-        <v>5.605311</v>
+        <v>5.626402000000001</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6692,25 +6692,25 @@
         <v>4</v>
       </c>
       <c r="E128" s="7">
-        <v>0.051595</v>
+        <v>0.046325000000000005</v>
       </c>
       <c r="F128" s="7">
-        <v>0.0008699999999999999</v>
+        <v>-0.00601</v>
       </c>
       <c r="G128" s="7">
-        <v>0.147176</v>
+        <v>0.13833700000000002</v>
       </c>
       <c r="H128" s="7">
-        <v>0.042699999999999995</v>
+        <v>0.037475</v>
       </c>
       <c r="I128" s="7">
-        <v>0.394961</v>
+        <v>0.392262</v>
       </c>
       <c r="J128" s="7">
-        <v>1.5576949999999998</v>
+        <v>1.539553</v>
       </c>
       <c r="K128" s="7">
-        <v>3.367046</v>
+        <v>3.3431349999999997</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6727,25 +6727,25 @@
         <v>6</v>
       </c>
       <c r="E129" s="7">
-        <v>0.112994</v>
+        <v>0.095524</v>
       </c>
       <c r="F129" s="7">
-        <v>0.074218</v>
+        <v>0.03198</v>
       </c>
       <c r="G129" s="7">
-        <v>0.309698</v>
+        <v>0.292754</v>
       </c>
       <c r="H129" s="7">
-        <v>0.232477</v>
+        <v>0.213132</v>
       </c>
       <c r="I129" s="7">
-        <v>0.503723</v>
+        <v>0.505919</v>
       </c>
       <c r="J129" s="7">
-        <v>2.740514</v>
+        <v>2.8064210000000003</v>
       </c>
       <c r="K129" s="7">
-        <v>14.751498999999999</v>
+        <v>14.580457</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6762,25 +6762,25 @@
         <v>4</v>
       </c>
       <c r="E130" s="7">
-        <v>0.054179000000000005</v>
+        <v>0.051676</v>
       </c>
       <c r="F130" s="7">
-        <v>0.030825</v>
+        <v>0.028815</v>
       </c>
       <c r="G130" s="7">
-        <v>0.08374100000000001</v>
+        <v>0.08012000000000001</v>
       </c>
       <c r="H130" s="7">
-        <v>0.039743</v>
+        <v>0.037274</v>
       </c>
       <c r="I130" s="7">
-        <v>0.286344</v>
+        <v>0.283289</v>
       </c>
       <c r="J130" s="7">
-        <v>2.049912</v>
+        <v>2.036271</v>
       </c>
       <c r="K130" s="7">
-        <v>6.318157</v>
+        <v>6.354709000000001</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6797,19 +6797,19 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.134233</v>
+        <v>0.120542</v>
       </c>
       <c r="F131" s="7">
-        <v>0.147568</v>
+        <v>0.103301</v>
       </c>
       <c r="G131" s="7">
-        <v>0.245709</v>
+        <v>0.224745</v>
       </c>
       <c r="H131" s="7">
-        <v>0.24634899999999998</v>
+        <v>0.231305</v>
       </c>
       <c r="I131" s="7">
-        <v>0.691465</v>
+        <v>0.672548</v>
       </c>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
@@ -6828,25 +6828,25 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.060424</v>
+        <v>0.055362999999999996</v>
       </c>
       <c r="F132" s="7">
-        <v>0.020369</v>
+        <v>0.006579000000000001</v>
       </c>
       <c r="G132" s="7">
-        <v>0.180454</v>
+        <v>0.17299399999999998</v>
       </c>
       <c r="H132" s="7">
-        <v>0.076902</v>
+        <v>0.07176199999999999</v>
       </c>
       <c r="I132" s="7">
-        <v>0.41659</v>
+        <v>0.419019</v>
       </c>
       <c r="J132" s="7">
-        <v>1.447919</v>
+        <v>1.4623089999999999</v>
       </c>
       <c r="K132" s="7">
-        <v>3.81923</v>
+        <v>3.7977800000000004</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6863,25 +6863,25 @@
         <v>3</v>
       </c>
       <c r="E133" s="7">
-        <v>0.030496</v>
+        <v>0.031558</v>
       </c>
       <c r="F133" s="7">
-        <v>0.088671</v>
+        <v>0.087792</v>
       </c>
       <c r="G133" s="7">
-        <v>0.18851099999999998</v>
+        <v>0.18733899999999998</v>
       </c>
       <c r="H133" s="7">
-        <v>0.117996</v>
+        <v>0.11914899999999999</v>
       </c>
       <c r="I133" s="7">
-        <v>0.46232599999999996</v>
+        <v>0.461877</v>
       </c>
       <c r="J133" s="7">
-        <v>2.299453</v>
+        <v>2.295323</v>
       </c>
       <c r="K133" s="7">
-        <v>3.8587000000000002</v>
+        <v>3.867022</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6898,25 +6898,25 @@
         <v>6</v>
       </c>
       <c r="E134" s="7">
-        <v>0.06587</v>
+        <v>0.059634</v>
       </c>
       <c r="F134" s="7">
-        <v>0.07608</v>
+        <v>0.05733</v>
       </c>
       <c r="G134" s="7">
-        <v>0.24079799999999998</v>
+        <v>0.23360399999999998</v>
       </c>
       <c r="H134" s="7">
-        <v>0.171688</v>
+        <v>0.164834</v>
       </c>
       <c r="I134" s="7">
-        <v>0.44828</v>
+        <v>0.44911900000000005</v>
       </c>
       <c r="J134" s="7">
-        <v>2.653004</v>
+        <v>2.73486</v>
       </c>
       <c r="K134" s="7">
-        <v>7.985824</v>
+        <v>7.9625580000000005</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6933,25 +6933,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.06082</v>
+        <v>0.054778</v>
       </c>
       <c r="F135" s="7">
-        <v>0.018845</v>
+        <v>0.007419</v>
       </c>
       <c r="G135" s="7">
-        <v>0.152129</v>
+        <v>0.144232</v>
       </c>
       <c r="H135" s="7">
-        <v>0.070389</v>
+        <v>0.06429299999999999</v>
       </c>
       <c r="I135" s="7">
-        <v>0.353149</v>
+        <v>0.345834</v>
       </c>
       <c r="J135" s="7">
-        <v>1.033652</v>
+        <v>1.044149</v>
       </c>
       <c r="K135" s="7">
-        <v>2.4562049999999997</v>
+        <v>2.438711</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6968,25 +6968,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.07793599999999999</v>
+        <v>0.073598</v>
       </c>
       <c r="F136" s="7">
-        <v>0.09787900000000001</v>
+        <v>0.08691900000000001</v>
       </c>
       <c r="G136" s="7">
-        <v>0.188599</v>
+        <v>0.18134</v>
       </c>
       <c r="H136" s="7">
-        <v>0.15326800000000002</v>
+        <v>0.148626</v>
       </c>
       <c r="I136" s="7">
-        <v>0.42716</v>
+        <v>0.42513199999999995</v>
       </c>
       <c r="J136" s="7">
-        <v>3.062061</v>
+        <v>3.069999</v>
       </c>
       <c r="K136" s="7">
-        <v>9.423292</v>
+        <v>9.40185</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7003,25 +7003,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.052245</v>
+        <v>0.04851</v>
       </c>
       <c r="F137" s="7">
-        <v>0.053074</v>
+        <v>0.04523</v>
       </c>
       <c r="G137" s="7">
-        <v>0.178141</v>
+        <v>0.172043</v>
       </c>
       <c r="H137" s="7">
-        <v>0.101819</v>
+        <v>0.097907</v>
       </c>
       <c r="I137" s="7">
-        <v>0.43180599999999997</v>
+        <v>0.429508</v>
       </c>
       <c r="J137" s="7">
-        <v>2.167304</v>
+        <v>2.157142</v>
       </c>
       <c r="K137" s="7">
-        <v>4.160398</v>
+        <v>4.141363</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7038,22 +7038,22 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.220118</v>
+        <v>0.201388</v>
       </c>
       <c r="F138" s="7">
-        <v>0.131344</v>
+        <v>0.10220000000000001</v>
       </c>
       <c r="G138" s="7">
-        <v>0.264173</v>
+        <v>0.241479</v>
       </c>
       <c r="H138" s="7">
-        <v>0.234408</v>
+        <v>0.21545899999999998</v>
       </c>
       <c r="I138" s="7">
-        <v>0.8616410000000001</v>
+        <v>0.818838</v>
       </c>
       <c r="J138" s="7">
-        <v>5.20171</v>
+        <v>5.0815339999999996</v>
       </c>
       <c r="K138" s="7"/>
     </row>
@@ -7071,22 +7071,22 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.08767799999999999</v>
+        <v>0.074506</v>
       </c>
       <c r="F139" s="7">
-        <v>0.021563</v>
+        <v>-0.0038050000000000002</v>
       </c>
       <c r="G139" s="7">
-        <v>0.20298200000000002</v>
+        <v>0.186713</v>
       </c>
       <c r="H139" s="7">
-        <v>0.114744</v>
+        <v>0.101244</v>
       </c>
       <c r="I139" s="7">
-        <v>0.530768</v>
+        <v>0.51365</v>
       </c>
       <c r="J139" s="7">
-        <v>4.711024</v>
+        <v>4.698272</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,25 +7104,25 @@
         <v>3</v>
       </c>
       <c r="E140" s="7">
-        <v>0.048228</v>
+        <v>0.043822</v>
       </c>
       <c r="F140" s="7">
-        <v>0.029464</v>
+        <v>0.01844</v>
       </c>
       <c r="G140" s="7">
-        <v>0.16296600000000003</v>
+        <v>0.15637</v>
       </c>
       <c r="H140" s="7">
-        <v>0.087821</v>
+        <v>0.083248</v>
       </c>
       <c r="I140" s="7">
-        <v>0.37175199999999997</v>
+        <v>0.370784</v>
       </c>
       <c r="J140" s="7">
-        <v>1.6188650000000002</v>
+        <v>1.62446</v>
       </c>
       <c r="K140" s="7">
-        <v>3.6351620000000002</v>
+        <v>3.615093</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7139,25 +7139,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.036978</v>
+        <v>0.034931000000000004</v>
       </c>
       <c r="F141" s="7">
-        <v>0.059901</v>
+        <v>0.051933</v>
       </c>
       <c r="G141" s="7">
-        <v>0.178676</v>
+        <v>0.176943</v>
       </c>
       <c r="H141" s="7">
-        <v>0.115207</v>
+        <v>0.113006</v>
       </c>
       <c r="I141" s="7">
-        <v>0.350893</v>
+        <v>0.348709</v>
       </c>
       <c r="J141" s="7">
-        <v>1.367659</v>
+        <v>1.370352</v>
       </c>
       <c r="K141" s="7">
-        <v>4.461825</v>
+        <v>4.456199</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,25 +7174,25 @@
         <v>5</v>
       </c>
       <c r="E142" s="7">
-        <v>0.087984</v>
+        <v>0.077011</v>
       </c>
       <c r="F142" s="7">
-        <v>0.054063</v>
+        <v>0.028111</v>
       </c>
       <c r="G142" s="7">
-        <v>0.214637</v>
+        <v>0.207101</v>
       </c>
       <c r="H142" s="7">
-        <v>0.16015999999999997</v>
+        <v>0.148459</v>
       </c>
       <c r="I142" s="7">
-        <v>0.3709</v>
+        <v>0.36972299999999997</v>
       </c>
       <c r="J142" s="7">
-        <v>3.1210489999999997</v>
+        <v>3.2018590000000002</v>
       </c>
       <c r="K142" s="7">
-        <v>13.746018</v>
+        <v>13.654292</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7209,25 +7209,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.08302899999999999</v>
+        <v>0.067509</v>
       </c>
       <c r="F143" s="7">
-        <v>0.17784</v>
+        <v>0.156865</v>
       </c>
       <c r="G143" s="7">
-        <v>0.19139099999999998</v>
+        <v>0.17235199999999998</v>
       </c>
       <c r="H143" s="7">
-        <v>0.289727</v>
+        <v>0.271245</v>
       </c>
       <c r="I143" s="7">
-        <v>0.283304</v>
+        <v>0.273309</v>
       </c>
       <c r="J143" s="7">
-        <v>3.575811</v>
+        <v>3.530899</v>
       </c>
       <c r="K143" s="7">
-        <v>11.061622999999999</v>
+        <v>10.878284</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7244,25 +7244,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.092172</v>
+        <v>0.08404199999999999</v>
       </c>
       <c r="F144" s="7">
-        <v>0.10269299999999999</v>
+        <v>0.083733</v>
       </c>
       <c r="G144" s="7">
-        <v>0.313739</v>
+        <v>0.30211099999999996</v>
       </c>
       <c r="H144" s="7">
-        <v>0.20175</v>
+        <v>0.192804</v>
       </c>
       <c r="I144" s="7">
-        <v>0.571692</v>
+        <v>0.552855</v>
       </c>
       <c r="J144" s="7">
-        <v>2.940766</v>
+        <v>2.926706</v>
       </c>
       <c r="K144" s="7">
-        <v>8.233375</v>
+        <v>8.173055</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7279,25 +7279,25 @@
         <v>4</v>
       </c>
       <c r="E145" s="7">
-        <v>0.083645</v>
+        <v>0.074539</v>
       </c>
       <c r="F145" s="7">
-        <v>0.058521000000000004</v>
+        <v>0.032854</v>
       </c>
       <c r="G145" s="7">
-        <v>0.26213000000000003</v>
+        <v>0.25244099999999997</v>
       </c>
       <c r="H145" s="7">
-        <v>0.17211400000000002</v>
+        <v>0.16226400000000002</v>
       </c>
       <c r="I145" s="7">
-        <v>0.525907</v>
+        <v>0.5296</v>
       </c>
       <c r="J145" s="7">
-        <v>3.392167</v>
+        <v>3.4194709999999997</v>
       </c>
       <c r="K145" s="7">
-        <v>9.524428</v>
+        <v>9.512728</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7314,25 +7314,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.032996</v>
+        <v>0.027729</v>
       </c>
       <c r="F146" s="7">
-        <v>0.159735</v>
+        <v>0.140869</v>
       </c>
       <c r="G146" s="7">
-        <v>0.36170900000000006</v>
+        <v>0.355171</v>
       </c>
       <c r="H146" s="7">
-        <v>0.26354099999999997</v>
+        <v>0.257097</v>
       </c>
       <c r="I146" s="7">
-        <v>0.626001</v>
+        <v>0.61469</v>
       </c>
       <c r="J146" s="7">
-        <v>3.1759609999999996</v>
+        <v>3.149381</v>
       </c>
       <c r="K146" s="7">
-        <v>9.397463</v>
+        <v>9.383303</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7349,25 +7349,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.038252</v>
+        <v>0.034699</v>
       </c>
       <c r="F147" s="7">
-        <v>0.079488</v>
+        <v>0.067706</v>
       </c>
       <c r="G147" s="7">
-        <v>0.196494</v>
+        <v>0.190852</v>
       </c>
       <c r="H147" s="7">
-        <v>0.13109500000000002</v>
+        <v>0.127224</v>
       </c>
       <c r="I147" s="7">
-        <v>0.464553</v>
+        <v>0.457007</v>
       </c>
       <c r="J147" s="7">
-        <v>2.190935</v>
+        <v>2.2030529999999997</v>
       </c>
       <c r="K147" s="7">
-        <v>6.535962</v>
+        <v>6.520966</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7384,25 +7384,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.05420899999999999</v>
+        <v>0.04489099999999999</v>
       </c>
       <c r="F148" s="7">
-        <v>0.018861000000000003</v>
+        <v>-0.013499</v>
       </c>
       <c r="G148" s="7">
-        <v>0.232484</v>
+        <v>0.230538</v>
       </c>
       <c r="H148" s="7">
-        <v>0.13127</v>
+        <v>0.121271</v>
       </c>
       <c r="I148" s="7">
-        <v>0.564863</v>
+        <v>0.543335</v>
       </c>
       <c r="J148" s="7">
-        <v>3.299288</v>
+        <v>3.268035</v>
       </c>
       <c r="K148" s="7">
-        <v>9.658101</v>
+        <v>9.604645</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7419,25 +7419,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.047882999999999995</v>
+        <v>0.046652</v>
       </c>
       <c r="F149" s="7">
-        <v>0.069569</v>
+        <v>0.062935</v>
       </c>
       <c r="G149" s="7">
-        <v>0.17651</v>
+        <v>0.173717</v>
       </c>
       <c r="H149" s="7">
-        <v>0.131601</v>
+        <v>0.130271</v>
       </c>
       <c r="I149" s="7">
-        <v>0.388167</v>
+        <v>0.38821</v>
       </c>
       <c r="J149" s="7">
-        <v>1.431154</v>
+        <v>1.4467109999999999</v>
       </c>
       <c r="K149" s="7">
-        <v>4.236893</v>
+        <v>4.229621</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7454,25 +7454,25 @@
         <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>0.11089</v>
+        <v>0.10106899999999999</v>
       </c>
       <c r="F150" s="7">
-        <v>0.09825400000000001</v>
+        <v>0.071812</v>
       </c>
       <c r="G150" s="7">
-        <v>0.257682</v>
+        <v>0.245946</v>
       </c>
       <c r="H150" s="7">
-        <v>0.239448</v>
+        <v>0.228491</v>
       </c>
       <c r="I150" s="7">
-        <v>0.551866</v>
+        <v>0.541788</v>
       </c>
       <c r="J150" s="7">
-        <v>2.6500869999999996</v>
+        <v>2.679805</v>
       </c>
       <c r="K150" s="7">
-        <v>8.542666</v>
+        <v>8.471303</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7489,25 +7489,25 @@
         <v>7</v>
       </c>
       <c r="E151" s="7">
-        <v>0.09380000000000001</v>
+        <v>0.086202</v>
       </c>
       <c r="F151" s="7">
-        <v>0.097785</v>
+        <v>0.076399</v>
       </c>
       <c r="G151" s="7">
-        <v>0.248459</v>
+        <v>0.23887699999999998</v>
       </c>
       <c r="H151" s="7">
-        <v>0.21651700000000002</v>
+        <v>0.208067</v>
       </c>
       <c r="I151" s="7">
-        <v>0.544535</v>
+        <v>0.535836</v>
       </c>
       <c r="J151" s="7">
-        <v>2.542554</v>
+        <v>2.570531</v>
       </c>
       <c r="K151" s="7">
-        <v>7.412177000000001</v>
+        <v>7.405204</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7524,25 +7524,25 @@
         <v>3</v>
       </c>
       <c r="E152" s="7">
-        <v>0.044927999999999996</v>
+        <v>0.04437</v>
       </c>
       <c r="F152" s="7">
-        <v>0.07558</v>
+        <v>0.071578</v>
       </c>
       <c r="G152" s="7">
-        <v>0.207043</v>
+        <v>0.20474599999999998</v>
       </c>
       <c r="H152" s="7">
-        <v>0.12375299999999999</v>
+        <v>0.12315300000000001</v>
       </c>
       <c r="I152" s="7">
-        <v>0.482916</v>
+        <v>0.48205</v>
       </c>
       <c r="J152" s="7">
-        <v>2.957951</v>
+        <v>2.9441879999999996</v>
       </c>
       <c r="K152" s="7">
-        <v>5.075643</v>
+        <v>5.071984</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7559,22 +7559,22 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.055698</v>
+        <v>0.055911</v>
       </c>
       <c r="F153" s="7">
-        <v>0.033386</v>
+        <v>0.01993</v>
       </c>
       <c r="G153" s="7">
-        <v>0.18353999999999998</v>
+        <v>0.188805</v>
       </c>
       <c r="H153" s="7">
-        <v>0.122196</v>
+        <v>0.122423</v>
       </c>
       <c r="I153" s="7">
-        <v>0.486182</v>
+        <v>0.484359</v>
       </c>
       <c r="J153" s="7">
-        <v>3.3895929999999996</v>
+        <v>3.396191</v>
       </c>
       <c r="K153" s="7"/>
     </row>
@@ -7592,16 +7592,16 @@
         <v>4</v>
       </c>
       <c r="E154" s="7">
-        <v>0.056988000000000004</v>
+        <v>0.050121</v>
       </c>
       <c r="F154" s="7">
-        <v>0.08488899999999999</v>
+        <v>0.0668</v>
       </c>
       <c r="G154" s="7">
-        <v>0.263052</v>
+        <v>0.25627099999999997</v>
       </c>
       <c r="H154" s="7">
-        <v>0.187962</v>
+        <v>0.18024300000000001</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
@@ -7621,22 +7621,22 @@
         <v>6</v>
       </c>
       <c r="E155" s="7">
-        <v>0.110738</v>
+        <v>0.099645</v>
       </c>
       <c r="F155" s="7">
-        <v>0.09342800000000001</v>
+        <v>0.065774</v>
       </c>
       <c r="G155" s="7">
-        <v>0.236051</v>
+        <v>0.22381399999999999</v>
       </c>
       <c r="H155" s="7">
-        <v>0.18954000000000001</v>
+        <v>0.17765899999999998</v>
       </c>
       <c r="I155" s="7">
-        <v>0.457168</v>
+        <v>0.44575899999999996</v>
       </c>
       <c r="J155" s="7">
-        <v>1.783164</v>
+        <v>1.762198</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7654,25 +7654,25 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.061981</v>
+        <v>0.057173</v>
       </c>
       <c r="F156" s="7">
-        <v>0.095348</v>
+        <v>0.08194599999999999</v>
       </c>
       <c r="G156" s="7">
-        <v>0.24590299999999998</v>
+        <v>0.237543</v>
       </c>
       <c r="H156" s="7">
-        <v>0.170814</v>
+        <v>0.16551300000000002</v>
       </c>
       <c r="I156" s="7">
-        <v>0.54305</v>
+        <v>0.53943</v>
       </c>
       <c r="J156" s="7">
-        <v>2.3726830000000003</v>
+        <v>2.380739</v>
       </c>
       <c r="K156" s="7">
-        <v>6.450358</v>
+        <v>6.437593000000001</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7689,25 +7689,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.062993</v>
+        <v>0.058175</v>
       </c>
       <c r="F157" s="7">
-        <v>0.09751599999999999</v>
+        <v>0.084007</v>
       </c>
       <c r="G157" s="7">
-        <v>0.236425</v>
+        <v>0.228434</v>
       </c>
       <c r="H157" s="7">
-        <v>0.17025400000000002</v>
+        <v>0.16495100000000001</v>
       </c>
       <c r="I157" s="7">
-        <v>0.500951</v>
+        <v>0.49674100000000004</v>
       </c>
       <c r="J157" s="7">
-        <v>2.154712</v>
+        <v>2.162836</v>
       </c>
       <c r="K157" s="7">
-        <v>5.960001999999999</v>
+        <v>5.948283</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7724,25 +7724,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.045980999999999994</v>
+        <v>0.042351</v>
       </c>
       <c r="F158" s="7">
-        <v>0.067993</v>
+        <v>0.05755</v>
       </c>
       <c r="G158" s="7">
-        <v>0.20494</v>
+        <v>0.19890899999999997</v>
       </c>
       <c r="H158" s="7">
-        <v>0.134723</v>
+        <v>0.130785</v>
       </c>
       <c r="I158" s="7">
-        <v>0.43713700000000005</v>
+        <v>0.432169</v>
       </c>
       <c r="J158" s="7">
-        <v>1.8166229999999999</v>
+        <v>1.818289</v>
       </c>
       <c r="K158" s="7">
-        <v>5.058482000000001</v>
+        <v>5.038497</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,22 +7759,22 @@
         <v>5</v>
       </c>
       <c r="E159" s="7">
-        <v>0.17212700000000003</v>
+        <v>0.16670400000000002</v>
       </c>
       <c r="F159" s="7">
-        <v>0.160044</v>
+        <v>0.149635</v>
       </c>
       <c r="G159" s="7">
-        <v>0.27843599999999996</v>
+        <v>0.270888</v>
       </c>
       <c r="H159" s="7">
-        <v>0.266758</v>
+        <v>0.260898</v>
       </c>
       <c r="I159" s="7">
-        <v>0.74381</v>
+        <v>0.7232299999999999</v>
       </c>
       <c r="J159" s="7">
-        <v>3.924038</v>
+        <v>3.9310840000000002</v>
       </c>
       <c r="K159" s="7"/>
     </row>
@@ -7792,25 +7792,25 @@
         <v>4</v>
       </c>
       <c r="E160" s="7">
-        <v>0.056684</v>
+        <v>0.051698</v>
       </c>
       <c r="F160" s="7">
-        <v>0.032818</v>
+        <v>0.020665</v>
       </c>
       <c r="G160" s="7">
-        <v>0.203924</v>
+        <v>0.195825</v>
       </c>
       <c r="H160" s="7">
-        <v>0.096433</v>
+        <v>0.09125899999999999</v>
       </c>
       <c r="I160" s="7">
-        <v>0.431893</v>
+        <v>0.42930300000000005</v>
       </c>
       <c r="J160" s="7">
-        <v>2.032173</v>
+        <v>2.043753</v>
       </c>
       <c r="K160" s="7">
-        <v>5.673324</v>
+        <v>5.650576999999999</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,22 +7827,22 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.034249</v>
+        <v>0.034949</v>
       </c>
       <c r="F161" s="7">
-        <v>0.08825</v>
+        <v>0.087759</v>
       </c>
       <c r="G161" s="7">
-        <v>0.225093</v>
+        <v>0.22469</v>
       </c>
       <c r="H161" s="7">
-        <v>0.149875</v>
+        <v>0.150653</v>
       </c>
       <c r="I161" s="7">
-        <v>0.534175</v>
+        <v>0.53362</v>
       </c>
       <c r="J161" s="7">
-        <v>3.369713</v>
+        <v>3.351582</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7860,22 +7860,22 @@
         <v>6</v>
       </c>
       <c r="E162" s="7">
-        <v>0.080069</v>
+        <v>0.067033</v>
       </c>
       <c r="F162" s="7">
-        <v>0.006229</v>
+        <v>-0.020724999999999997</v>
       </c>
       <c r="G162" s="7">
-        <v>0.131731</v>
+        <v>0.117332</v>
       </c>
       <c r="H162" s="7">
-        <v>0.078052</v>
+        <v>0.065039</v>
       </c>
       <c r="I162" s="7">
-        <v>0.42424999999999996</v>
+        <v>0.400458</v>
       </c>
       <c r="J162" s="7">
-        <v>2.6194330000000003</v>
+        <v>2.5856</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,25 +7893,25 @@
         <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>0.10588800000000001</v>
+        <v>0.09488400000000001</v>
       </c>
       <c r="F163" s="7">
-        <v>0.109983</v>
+        <v>0.08071</v>
       </c>
       <c r="G163" s="7">
-        <v>0.308081</v>
+        <v>0.292655</v>
       </c>
       <c r="H163" s="7">
-        <v>0.257711</v>
+        <v>0.245197</v>
       </c>
       <c r="I163" s="7">
-        <v>0.638043</v>
+        <v>0.622514</v>
       </c>
       <c r="J163" s="7">
-        <v>2.481781</v>
+        <v>2.489326</v>
       </c>
       <c r="K163" s="7">
-        <v>8.731601000000001</v>
+        <v>8.660507</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7928,25 +7928,25 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.11754400000000001</v>
+        <v>0.104818</v>
       </c>
       <c r="F164" s="7">
-        <v>0.10716799999999999</v>
+        <v>0.069731</v>
       </c>
       <c r="G164" s="7">
-        <v>0.35076799999999997</v>
+        <v>0.334731</v>
       </c>
       <c r="H164" s="7">
-        <v>0.28527</v>
+        <v>0.27063400000000004</v>
       </c>
       <c r="I164" s="7">
-        <v>0.632931</v>
+        <v>0.624466</v>
       </c>
       <c r="J164" s="7">
-        <v>1.9845650000000001</v>
+        <v>1.94515</v>
       </c>
       <c r="K164" s="7">
-        <v>3.6382920000000003</v>
+        <v>3.585762</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7963,25 +7963,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.116914</v>
+        <v>0.099262</v>
       </c>
       <c r="F165" s="7">
-        <v>0.07845200000000001</v>
+        <v>0.036337</v>
       </c>
       <c r="G165" s="7">
-        <v>0.31222</v>
+        <v>0.29446</v>
       </c>
       <c r="H165" s="7">
-        <v>0.239433</v>
+        <v>0.219845</v>
       </c>
       <c r="I165" s="7">
-        <v>0.468854</v>
+        <v>0.460976</v>
       </c>
       <c r="J165" s="7">
-        <v>2.8562819999999998</v>
+        <v>2.911474</v>
       </c>
       <c r="K165" s="7">
-        <v>16.104955</v>
+        <v>15.953019999999999</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7998,25 +7998,25 @@
         <v>3</v>
       </c>
       <c r="E166" s="7">
-        <v>0.047411</v>
+        <v>0.04415</v>
       </c>
       <c r="F166" s="7">
-        <v>0.00966</v>
+        <v>0.004397</v>
       </c>
       <c r="G166" s="7">
-        <v>0.14935</v>
+        <v>0.141532</v>
       </c>
       <c r="H166" s="7">
-        <v>0.046952999999999995</v>
+        <v>0.043693</v>
       </c>
       <c r="I166" s="7">
-        <v>0.40276</v>
+        <v>0.398512</v>
       </c>
       <c r="J166" s="7">
-        <v>1.881268</v>
+        <v>1.869069</v>
       </c>
       <c r="K166" s="7">
-        <v>3.9907960000000005</v>
+        <v>3.974951</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8033,25 +8033,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.051876</v>
+        <v>0.047725</v>
       </c>
       <c r="F167" s="7">
-        <v>0.087944</v>
+        <v>0.076492</v>
       </c>
       <c r="G167" s="7">
-        <v>0.23839</v>
+        <v>0.231448</v>
       </c>
       <c r="H167" s="7">
-        <v>0.161053</v>
+        <v>0.156471</v>
       </c>
       <c r="I167" s="7">
-        <v>0.466346</v>
+        <v>0.460644</v>
       </c>
       <c r="J167" s="7">
-        <v>1.880776</v>
+        <v>1.885838</v>
       </c>
       <c r="K167" s="7">
-        <v>5.442304</v>
+        <v>5.4193169999999995</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8068,25 +8068,25 @@
         <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>0.026552</v>
+        <v>0.027646999999999998</v>
       </c>
       <c r="F168" s="7">
-        <v>0.061668</v>
+        <v>0.062394</v>
       </c>
       <c r="G168" s="7">
-        <v>0.124998</v>
+        <v>0.125375</v>
       </c>
       <c r="H168" s="7">
-        <v>0.080236</v>
+        <v>0.081388</v>
       </c>
       <c r="I168" s="7">
-        <v>0.303695</v>
+        <v>0.30176200000000003</v>
       </c>
       <c r="J168" s="7">
-        <v>1.9583840000000001</v>
+        <v>1.95867</v>
       </c>
       <c r="K168" s="7">
-        <v>5.512133</v>
+        <v>5.543750999999999</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8103,22 +8103,22 @@
         <v>6</v>
       </c>
       <c r="E169" s="7">
-        <v>0.044786</v>
+        <v>0.021315</v>
       </c>
       <c r="F169" s="7">
-        <v>-0.068348</v>
+        <v>-0.12119999999999999</v>
       </c>
       <c r="G169" s="7">
-        <v>0.16606</v>
+        <v>0.14182</v>
       </c>
       <c r="H169" s="7">
-        <v>0.105838</v>
+        <v>0.08099500000000001</v>
       </c>
       <c r="I169" s="7">
-        <v>0.6188819999999999</v>
+        <v>0.583532</v>
       </c>
       <c r="J169" s="7">
-        <v>4.758781</v>
+        <v>4.586843</v>
       </c>
       <c r="K169" s="7"/>
     </row>
@@ -8136,22 +8136,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>0.127535</v>
+        <v>0.113065</v>
       </c>
       <c r="F170" s="7">
-        <v>0.08920299999999999</v>
+        <v>0.055735</v>
       </c>
       <c r="G170" s="7">
-        <v>0.247055</v>
+        <v>0.23111399999999999</v>
       </c>
       <c r="H170" s="7">
-        <v>0.211876</v>
+        <v>0.196324</v>
       </c>
       <c r="I170" s="7">
-        <v>0.481922</v>
+        <v>0.47375</v>
       </c>
       <c r="J170" s="7">
-        <v>2.458487</v>
+        <v>2.493172</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,16 +8169,16 @@
         <v>7</v>
       </c>
       <c r="E171" s="7">
-        <v>0.093607</v>
+        <v>0.067386</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.261261</v>
+        <v>-0.29783000000000004</v>
       </c>
       <c r="G171" s="7">
-        <v>0.625799</v>
+        <v>0.613532</v>
       </c>
       <c r="H171" s="7">
-        <v>0.061726</v>
+        <v>0.036269</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7"/>
@@ -8198,25 +8198,25 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.028508</v>
+        <v>0.003353</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.069379</v>
+        <v>-0.124094</v>
       </c>
       <c r="G172" s="7">
-        <v>0.150763</v>
+        <v>0.128081</v>
       </c>
       <c r="H172" s="7">
-        <v>0.072081</v>
+        <v>0.045861</v>
       </c>
       <c r="I172" s="7">
-        <v>0.587864</v>
+        <v>0.542543</v>
       </c>
       <c r="J172" s="7">
-        <v>4.122723</v>
+        <v>4.005718</v>
       </c>
       <c r="K172" s="7">
-        <v>13.69376</v>
+        <v>13.528977</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8233,25 +8233,25 @@
         <v>4</v>
       </c>
       <c r="E173" s="7">
-        <v>0.06697499999999999</v>
+        <v>0.060764</v>
       </c>
       <c r="F173" s="7">
-        <v>0.034285</v>
+        <v>0.020200999999999997</v>
       </c>
       <c r="G173" s="7">
-        <v>0.21552800000000003</v>
+        <v>0.20625800000000002</v>
       </c>
       <c r="H173" s="7">
-        <v>0.10788600000000001</v>
+        <v>0.10143700000000001</v>
       </c>
       <c r="I173" s="7">
-        <v>0.453457</v>
+        <v>0.45071599999999995</v>
       </c>
       <c r="J173" s="7">
-        <v>2.038168</v>
+        <v>2.051097</v>
       </c>
       <c r="K173" s="7">
-        <v>5.4215219999999995</v>
+        <v>5.388866</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8268,25 +8268,25 @@
         <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>0.093105</v>
+        <v>0.082623</v>
       </c>
       <c r="F174" s="7">
-        <v>0.073585</v>
+        <v>0.046458000000000006</v>
       </c>
       <c r="G174" s="7">
-        <v>0.26777</v>
+        <v>0.255768</v>
       </c>
       <c r="H174" s="7">
-        <v>0.212246</v>
+        <v>0.20062000000000002</v>
       </c>
       <c r="I174" s="7">
-        <v>0.46624699999999997</v>
+        <v>0.454975</v>
       </c>
       <c r="J174" s="7">
-        <v>2.7047070000000004</v>
+        <v>2.743804</v>
       </c>
       <c r="K174" s="7">
-        <v>10.546201000000002</v>
+        <v>10.473452</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8303,25 +8303,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.053495</v>
+        <v>0.049985</v>
       </c>
       <c r="F175" s="7">
-        <v>0.039452</v>
+        <v>0.033318</v>
       </c>
       <c r="G175" s="7">
-        <v>0.102114</v>
+        <v>0.097835</v>
       </c>
       <c r="H175" s="7">
-        <v>0.054005</v>
+        <v>0.050492999999999996</v>
       </c>
       <c r="I175" s="7">
-        <v>0.313485</v>
+        <v>0.308912</v>
       </c>
       <c r="J175" s="7">
-        <v>2.103692</v>
+        <v>2.089658</v>
       </c>
       <c r="K175" s="7">
-        <v>6.347159</v>
+        <v>6.373005000000001</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8338,25 +8338,25 @@
         <v>6</v>
       </c>
       <c r="E176" s="7">
-        <v>0.124479</v>
+        <v>0.11516299999999999</v>
       </c>
       <c r="F176" s="7">
-        <v>0.092197</v>
+        <v>0.06843</v>
       </c>
       <c r="G176" s="7">
-        <v>0.252453</v>
+        <v>0.241558</v>
       </c>
       <c r="H176" s="7">
-        <v>0.19587900000000003</v>
+        <v>0.185972</v>
       </c>
       <c r="I176" s="7">
-        <v>0.600969</v>
+        <v>0.587967</v>
       </c>
       <c r="J176" s="7">
-        <v>2.92371</v>
+        <v>2.9326049999999997</v>
       </c>
       <c r="K176" s="7">
-        <v>12.42598</v>
+        <v>12.356939</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,25 +8373,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.112018</v>
+        <v>0.098021</v>
       </c>
       <c r="F177" s="7">
-        <v>0.093842</v>
+        <v>0.05878</v>
       </c>
       <c r="G177" s="7">
-        <v>0.348238</v>
+        <v>0.332363</v>
       </c>
       <c r="H177" s="7">
-        <v>0.257227</v>
+        <v>0.241403</v>
       </c>
       <c r="I177" s="7">
-        <v>0.557963</v>
+        <v>0.556176</v>
       </c>
       <c r="J177" s="7">
-        <v>3.232072</v>
+        <v>3.293427</v>
       </c>
       <c r="K177" s="7">
-        <v>17.58039</v>
+        <v>17.449749999999998</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8408,25 +8408,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.09028900000000001</v>
+        <v>0.080363</v>
       </c>
       <c r="F178" s="7">
-        <v>0.086701</v>
+        <v>0.05764300000000001</v>
       </c>
       <c r="G178" s="7">
-        <v>0.320154</v>
+        <v>0.308467</v>
       </c>
       <c r="H178" s="7">
-        <v>0.214007</v>
+        <v>0.202955</v>
       </c>
       <c r="I178" s="7">
-        <v>0.520674</v>
+        <v>0.516938</v>
       </c>
       <c r="J178" s="7">
-        <v>3.121603</v>
+        <v>3.1698340000000003</v>
       </c>
       <c r="K178" s="7">
-        <v>13.04536</v>
+        <v>12.965689</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,25 +8443,25 @@
         <v>4</v>
       </c>
       <c r="E179" s="7">
-        <v>0.081759</v>
+        <v>0.071674</v>
       </c>
       <c r="F179" s="7">
-        <v>0.07858</v>
+        <v>0.05325</v>
       </c>
       <c r="G179" s="7">
-        <v>0.291525</v>
+        <v>0.279057</v>
       </c>
       <c r="H179" s="7">
-        <v>0.182331</v>
+        <v>0.17130800000000002</v>
       </c>
       <c r="I179" s="7">
-        <v>0.5409349999999999</v>
+        <v>0.531792</v>
       </c>
       <c r="J179" s="7">
-        <v>3.3909269999999996</v>
+        <v>3.4068259999999997</v>
       </c>
       <c r="K179" s="7">
-        <v>11.338164999999998</v>
+        <v>11.249922</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8478,25 +8478,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.10837400000000001</v>
+        <v>0.099327</v>
       </c>
       <c r="F180" s="7">
-        <v>0.050092</v>
+        <v>0.025528</v>
       </c>
       <c r="G180" s="7">
-        <v>0.15331899999999998</v>
+        <v>0.142437</v>
       </c>
       <c r="H180" s="7">
-        <v>0.115927</v>
+        <v>0.10681800000000001</v>
       </c>
       <c r="I180" s="7">
-        <v>0.5705709999999999</v>
+        <v>0.54645</v>
       </c>
       <c r="J180" s="7">
-        <v>3.269523</v>
+        <v>3.207041</v>
       </c>
       <c r="K180" s="7">
-        <v>8.3633</v>
+        <v>8.315698</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8513,25 +8513,25 @@
         <v>2</v>
       </c>
       <c r="E181" s="7">
-        <v>0.044076000000000004</v>
+        <v>0.041816000000000006</v>
       </c>
       <c r="F181" s="7">
-        <v>0.080836</v>
+        <v>0.074611</v>
       </c>
       <c r="G181" s="7">
-        <v>0.21327200000000002</v>
+        <v>0.208449</v>
       </c>
       <c r="H181" s="7">
-        <v>0.12725799999999998</v>
+        <v>0.124818</v>
       </c>
       <c r="I181" s="7">
-        <v>0.49370600000000003</v>
+        <v>0.48938000000000004</v>
       </c>
       <c r="J181" s="7">
-        <v>3.338848</v>
+        <v>3.319948</v>
       </c>
       <c r="K181" s="7">
-        <v>6.3094399999999995</v>
+        <v>6.2906629999999994</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8548,25 +8548,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.08326499999999999</v>
+        <v>0.07652</v>
       </c>
       <c r="F182" s="7">
-        <v>0.051628999999999994</v>
+        <v>0.028589000000000003</v>
       </c>
       <c r="G182" s="7">
-        <v>0.134566</v>
+        <v>0.125514</v>
       </c>
       <c r="H182" s="7">
-        <v>0.15969</v>
+        <v>0.152469</v>
       </c>
       <c r="I182" s="7">
-        <v>0.35903599999999997</v>
+        <v>0.35580599999999996</v>
       </c>
       <c r="J182" s="7">
-        <v>2.436979</v>
+        <v>2.418887</v>
       </c>
       <c r="K182" s="7">
-        <v>3.935333</v>
+        <v>3.9114280000000003</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8583,25 +8583,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.120547</v>
+        <v>0.11069699999999999</v>
       </c>
       <c r="F183" s="7">
-        <v>0.11649100000000001</v>
+        <v>0.091375</v>
       </c>
       <c r="G183" s="7">
-        <v>0.369752</v>
+        <v>0.35568</v>
       </c>
       <c r="H183" s="7">
-        <v>0.319469</v>
+        <v>0.30787</v>
       </c>
       <c r="I183" s="7">
-        <v>0.6763720000000001</v>
+        <v>0.661452</v>
       </c>
       <c r="J183" s="7">
-        <v>3.139801</v>
+        <v>3.175906</v>
       </c>
       <c r="K183" s="7">
-        <v>13.024517000000001</v>
+        <v>12.964663</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8618,25 +8618,25 @@
         <v>3</v>
       </c>
       <c r="E184" s="7">
-        <v>0.028676</v>
+        <v>0.029451</v>
       </c>
       <c r="F184" s="7">
-        <v>0.08910299999999999</v>
+        <v>0.08889799999999999</v>
       </c>
       <c r="G184" s="7">
-        <v>0.194456</v>
+        <v>0.192909</v>
       </c>
       <c r="H184" s="7">
-        <v>0.11723499999999999</v>
+        <v>0.118077</v>
       </c>
       <c r="I184" s="7">
-        <v>0.456352</v>
+        <v>0.455956</v>
       </c>
       <c r="J184" s="7">
-        <v>1.7105199999999998</v>
+        <v>1.710203</v>
       </c>
       <c r="K184" s="7">
-        <v>3.810271</v>
+        <v>3.8118950000000003</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8653,25 +8653,25 @@
         <v>5</v>
       </c>
       <c r="E185" s="7">
-        <v>0.097982</v>
+        <v>0.09074299999999999</v>
       </c>
       <c r="F185" s="7">
-        <v>0.103382</v>
+        <v>0.08182</v>
       </c>
       <c r="G185" s="7">
-        <v>0.287674</v>
+        <v>0.277071</v>
       </c>
       <c r="H185" s="7">
-        <v>0.23962</v>
+        <v>0.231448</v>
       </c>
       <c r="I185" s="7">
-        <v>0.6109749999999999</v>
+        <v>0.600492</v>
       </c>
       <c r="J185" s="7">
-        <v>2.935547</v>
+        <v>2.946218</v>
       </c>
       <c r="K185" s="7">
-        <v>11.162112</v>
+        <v>11.120076</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8688,25 +8688,25 @@
         <v>2</v>
       </c>
       <c r="E186" s="7">
-        <v>0.028967</v>
+        <v>0.029747</v>
       </c>
       <c r="F186" s="7">
-        <v>0.089109</v>
+        <v>0.088914</v>
       </c>
       <c r="G186" s="7">
-        <v>0.19156199999999998</v>
+        <v>0.190047</v>
       </c>
       <c r="H186" s="7">
-        <v>0.116829</v>
+        <v>0.117675</v>
       </c>
       <c r="I186" s="7">
-        <v>0.450664</v>
+        <v>0.45023</v>
       </c>
       <c r="J186" s="7">
-        <v>1.8238489999999998</v>
+        <v>1.8204179999999999</v>
       </c>
       <c r="K186" s="7">
-        <v>3.32139</v>
+        <v>3.323031</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8723,25 +8723,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.019296999999999998</v>
+        <v>0.020224000000000002</v>
       </c>
       <c r="F187" s="7">
-        <v>0.061307</v>
+        <v>0.061438</v>
       </c>
       <c r="G187" s="7">
-        <v>0.15027100000000002</v>
+        <v>0.149409</v>
       </c>
       <c r="H187" s="7">
-        <v>0.094744</v>
+        <v>0.09573999999999999</v>
       </c>
       <c r="I187" s="7">
-        <v>0.379493</v>
+        <v>0.38017</v>
       </c>
       <c r="J187" s="7">
-        <v>1.972563</v>
+        <v>1.9713990000000001</v>
       </c>
       <c r="K187" s="7">
-        <v>3.321001</v>
+        <v>3.3235680000000003</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,16 +8758,16 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.095616</v>
+        <v>0.067119</v>
       </c>
       <c r="F188" s="7">
-        <v>-0.259205</v>
+        <v>-0.295344</v>
       </c>
       <c r="G188" s="7">
-        <v>0.598894</v>
+        <v>0.572039</v>
       </c>
       <c r="H188" s="7">
-        <v>0.04093</v>
+        <v>0.013855</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
@@ -8787,25 +8787,25 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>0.039091999999999995</v>
+        <v>0.014014</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.07126</v>
+        <v>-0.12506</v>
       </c>
       <c r="G189" s="7">
-        <v>0.165712</v>
+        <v>0.141704</v>
       </c>
       <c r="H189" s="7">
-        <v>0.084169</v>
+        <v>0.058003</v>
       </c>
       <c r="I189" s="7">
-        <v>0.609514</v>
+        <v>0.565562</v>
       </c>
       <c r="J189" s="7">
-        <v>3.9686470000000003</v>
+        <v>3.850264</v>
       </c>
       <c r="K189" s="7">
-        <v>13.415393</v>
+        <v>13.256404999999999</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>0.019081</v>
+        <v>-0.003196</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.06555799999999999</v>
+        <v>-0.117991</v>
       </c>
       <c r="G190" s="7">
-        <v>0.139343</v>
+        <v>0.123032</v>
       </c>
       <c r="H190" s="7">
-        <v>0.054812</v>
+        <v>0.031753</v>
       </c>
       <c r="I190" s="7">
-        <v>0.573425</v>
+        <v>0.529701</v>
       </c>
       <c r="J190" s="7">
-        <v>3.915564</v>
+        <v>3.7892680000000003</v>
       </c>
       <c r="K190" s="7">
-        <v>13.144891</v>
+        <v>13.012472</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8857,25 @@
         <v>4</v>
       </c>
       <c r="E191" s="7">
-        <v>0.07377</v>
+        <v>0.06591</v>
       </c>
       <c r="F191" s="7">
-        <v>0.060061</v>
+        <v>0.042489</v>
       </c>
       <c r="G191" s="7">
-        <v>0.260787</v>
+        <v>0.24938300000000002</v>
       </c>
       <c r="H191" s="7">
-        <v>0.143263</v>
+        <v>0.134895</v>
       </c>
       <c r="I191" s="7">
-        <v>0.49565600000000004</v>
+        <v>0.49373199999999995</v>
       </c>
       <c r="J191" s="7">
-        <v>1.848848</v>
+        <v>1.852854</v>
       </c>
       <c r="K191" s="7">
-        <v>5.10883</v>
+        <v>5.069145</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8892,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.062797</v>
+        <v>0.056961000000000005</v>
       </c>
       <c r="F192" s="7">
-        <v>0.050203</v>
+        <v>0.037819</v>
       </c>
       <c r="G192" s="7">
-        <v>0.202112</v>
+        <v>0.193208</v>
       </c>
       <c r="H192" s="7">
-        <v>0.105512</v>
+        <v>0.099441</v>
       </c>
       <c r="I192" s="7">
-        <v>0.457368</v>
+        <v>0.454372</v>
       </c>
       <c r="J192" s="7">
-        <v>2.200584</v>
+        <v>2.20084</v>
       </c>
       <c r="K192" s="7">
-        <v>5.550834999999999</v>
+        <v>5.515747999999999</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8927,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>0.049357</v>
+        <v>0.046421000000000004</v>
       </c>
       <c r="F193" s="7">
-        <v>0.035297999999999996</v>
+        <v>0.030055000000000002</v>
       </c>
       <c r="G193" s="7">
-        <v>0.102775</v>
+        <v>0.09859</v>
       </c>
       <c r="H193" s="7">
-        <v>0.050728999999999996</v>
+        <v>0.047789</v>
       </c>
       <c r="I193" s="7">
-        <v>0.32149900000000003</v>
+        <v>0.316619</v>
       </c>
       <c r="J193" s="7">
-        <v>2.2208170000000003</v>
+        <v>2.205788</v>
       </c>
       <c r="K193" s="7">
-        <v>6.572184</v>
+        <v>6.603415999999999</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8962,25 @@
         <v>3</v>
       </c>
       <c r="E194" s="7">
-        <v>0.052334</v>
+        <v>0.047753</v>
       </c>
       <c r="F194" s="7">
-        <v>0.101729</v>
+        <v>0.08925100000000001</v>
       </c>
       <c r="G194" s="7">
-        <v>0.240568</v>
+        <v>0.23268799999999998</v>
       </c>
       <c r="H194" s="7">
-        <v>0.186624</v>
+        <v>0.181459</v>
       </c>
       <c r="I194" s="7">
-        <v>0.47599600000000003</v>
+        <v>0.467661</v>
       </c>
       <c r="J194" s="7">
-        <v>1.545369</v>
+        <v>1.547758</v>
       </c>
       <c r="K194" s="7">
-        <v>3.729413</v>
+        <v>3.720896</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +8997,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.047641</v>
+        <v>0.044977</v>
       </c>
       <c r="F195" s="7">
-        <v>0.079333</v>
+        <v>0.07011099999999999</v>
       </c>
       <c r="G195" s="7">
-        <v>0.227992</v>
+        <v>0.22274000000000002</v>
       </c>
       <c r="H195" s="7">
-        <v>0.135232</v>
+        <v>0.13234500000000002</v>
       </c>
       <c r="I195" s="7">
-        <v>0.451505</v>
+        <v>0.450095</v>
       </c>
       <c r="J195" s="7">
-        <v>1.7115559999999999</v>
+        <v>1.716561</v>
       </c>
       <c r="K195" s="7">
-        <v>4.602838</v>
+        <v>4.590875</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9032,25 @@
         <v>4</v>
       </c>
       <c r="E196" s="7">
-        <v>0.073844</v>
+        <v>0.066518</v>
       </c>
       <c r="F196" s="7">
-        <v>0.056787000000000004</v>
+        <v>0.039699</v>
       </c>
       <c r="G196" s="7">
-        <v>0.222146</v>
+        <v>0.21098</v>
       </c>
       <c r="H196" s="7">
-        <v>0.131143</v>
+        <v>0.123426</v>
       </c>
       <c r="I196" s="7">
-        <v>0.484496</v>
+        <v>0.48039299999999996</v>
       </c>
       <c r="J196" s="7">
-        <v>2.097976</v>
+        <v>2.101223</v>
       </c>
       <c r="K196" s="7">
-        <v>5.126385</v>
+        <v>5.089268000000001</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9067,25 @@
         <v>6</v>
       </c>
       <c r="E197" s="7">
-        <v>0.09996600000000001</v>
+        <v>0.080411</v>
       </c>
       <c r="F197" s="7">
-        <v>0.064324</v>
+        <v>0.02635</v>
       </c>
       <c r="G197" s="7">
-        <v>0.260016</v>
+        <v>0.241656</v>
       </c>
       <c r="H197" s="7">
-        <v>0.218238</v>
+        <v>0.19658</v>
       </c>
       <c r="I197" s="7">
-        <v>0.44575899999999996</v>
+        <v>0.440431</v>
       </c>
       <c r="J197" s="7">
-        <v>3.879508</v>
+        <v>3.936801</v>
       </c>
       <c r="K197" s="7">
-        <v>21.398015</v>
+        <v>21.076028</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,16 +9102,16 @@
         <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>0.10049200000000001</v>
+        <v>0.090076</v>
       </c>
       <c r="F198" s="7">
-        <v>0.087443</v>
+        <v>0.055170000000000004</v>
       </c>
       <c r="G198" s="7">
-        <v>0.22958800000000001</v>
+        <v>0.215912</v>
       </c>
       <c r="H198" s="7">
-        <v>0.197697</v>
+        <v>0.186361</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
@@ -9131,25 +9131,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.08368700000000001</v>
+        <v>0.067299</v>
       </c>
       <c r="F199" s="7">
-        <v>0.005012</v>
+        <v>-0.021172</v>
       </c>
       <c r="G199" s="7">
-        <v>0.182246</v>
+        <v>0.166777</v>
       </c>
       <c r="H199" s="7">
-        <v>0.088043</v>
+        <v>0.071589</v>
       </c>
       <c r="I199" s="7">
-        <v>0.368204</v>
+        <v>0.36429</v>
       </c>
       <c r="J199" s="7">
-        <v>2.06648</v>
+        <v>2.0839529999999997</v>
       </c>
       <c r="K199" s="7">
-        <v>10.100152000000001</v>
+        <v>9.983387</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9166,25 +9166,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.09182499999999999</v>
+        <v>0.08299799999999999</v>
       </c>
       <c r="F200" s="7">
-        <v>0.077258</v>
+        <v>0.055258</v>
       </c>
       <c r="G200" s="7">
-        <v>0.227862</v>
+        <v>0.21758400000000003</v>
       </c>
       <c r="H200" s="7">
-        <v>0.178831</v>
+        <v>0.169301</v>
       </c>
       <c r="I200" s="7">
-        <v>0.485397</v>
+        <v>0.472427</v>
       </c>
       <c r="J200" s="7">
-        <v>2.30737</v>
+        <v>2.350161</v>
       </c>
       <c r="K200" s="7">
-        <v>9.206864000000001</v>
+        <v>9.207158</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9201,25 +9201,25 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.057396</v>
+        <v>0.04891</v>
       </c>
       <c r="F201" s="7">
-        <v>0.014384</v>
+        <v>-0.006159</v>
       </c>
       <c r="G201" s="7">
-        <v>0.184431</v>
+        <v>0.17568799999999998</v>
       </c>
       <c r="H201" s="7">
-        <v>0.09311799999999999</v>
+        <v>0.08434599999999999</v>
       </c>
       <c r="I201" s="7">
-        <v>0.6754519999999999</v>
+        <v>0.66608</v>
       </c>
       <c r="J201" s="7">
-        <v>2.9609609999999997</v>
+        <v>2.91175</v>
       </c>
       <c r="K201" s="7">
-        <v>6.4452620000000005</v>
+        <v>6.382175</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9236,25 +9236,25 @@
         <v>3</v>
       </c>
       <c r="E202" s="7">
-        <v>0.039245</v>
+        <v>0.03599</v>
       </c>
       <c r="F202" s="7">
-        <v>0.026446</v>
+        <v>0.020985</v>
       </c>
       <c r="G202" s="7">
-        <v>0.161841</v>
+        <v>0.153756</v>
       </c>
       <c r="H202" s="7">
-        <v>0.054998</v>
+        <v>0.051694000000000004</v>
       </c>
       <c r="I202" s="7">
-        <v>0.409943</v>
+        <v>0.407212</v>
       </c>
       <c r="J202" s="7">
-        <v>1.656749</v>
+        <v>1.646744</v>
       </c>
       <c r="K202" s="7">
-        <v>3.701836</v>
+        <v>3.684611</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,16 +9271,16 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.10029</v>
+        <v>0.08145899999999999</v>
       </c>
       <c r="F203" s="7">
-        <v>0.065517</v>
+        <v>0.028357999999999998</v>
       </c>
       <c r="G203" s="7">
-        <v>0.279909</v>
+        <v>0.260878</v>
       </c>
       <c r="H203" s="7">
-        <v>0.22583999999999999</v>
+        <v>0.20486000000000001</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
@@ -9300,25 +9300,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.043404</v>
+        <v>0.04089400000000001</v>
       </c>
       <c r="F204" s="7">
-        <v>0.040014</v>
+        <v>0.033703</v>
       </c>
       <c r="G204" s="7">
-        <v>0.10942500000000001</v>
+        <v>0.105753</v>
       </c>
       <c r="H204" s="7">
-        <v>0.061177999999999996</v>
+        <v>0.058625</v>
       </c>
       <c r="I204" s="7">
-        <v>0.318391</v>
+        <v>0.314158</v>
       </c>
       <c r="J204" s="7">
-        <v>1.958194</v>
+        <v>1.9485190000000001</v>
       </c>
       <c r="K204" s="7">
-        <v>5.342909</v>
+        <v>5.3614</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9335,25 +9335,25 @@
         <v>4</v>
       </c>
       <c r="E205" s="7">
-        <v>0.058127000000000005</v>
+        <v>0.050917000000000004</v>
       </c>
       <c r="F205" s="7">
-        <v>0.030085</v>
+        <v>0.014787999999999999</v>
       </c>
       <c r="G205" s="7">
-        <v>0.206053</v>
+        <v>0.194428</v>
       </c>
       <c r="H205" s="7">
-        <v>0.099289</v>
+        <v>0.091798</v>
       </c>
       <c r="I205" s="7">
-        <v>0.343679</v>
+        <v>0.343384</v>
       </c>
       <c r="J205" s="7">
-        <v>1.9850299999999999</v>
+        <v>1.984025</v>
       </c>
       <c r="K205" s="7">
-        <v>4.977444</v>
+        <v>4.940092</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9370,25 +9370,25 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.073542</v>
+        <v>0.062325</v>
       </c>
       <c r="F206" s="7">
-        <v>0.055581</v>
+        <v>0.030619999999999998</v>
       </c>
       <c r="G206" s="7">
-        <v>0.272036</v>
+        <v>0.256817</v>
       </c>
       <c r="H206" s="7">
-        <v>0.17510799999999999</v>
+        <v>0.16283</v>
       </c>
       <c r="I206" s="7">
-        <v>0.491439</v>
+        <v>0.48828499999999997</v>
       </c>
       <c r="J206" s="7">
-        <v>2.718155</v>
+        <v>2.733756</v>
       </c>
       <c r="K206" s="7">
-        <v>8.123357</v>
+        <v>8.055721</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9405,25 +9405,25 @@
         <v>6</v>
       </c>
       <c r="E207" s="7">
-        <v>0.084273</v>
+        <v>0.070645</v>
       </c>
       <c r="F207" s="7">
-        <v>0.048625999999999996</v>
+        <v>0.019039999999999998</v>
       </c>
       <c r="G207" s="7">
-        <v>0.327944</v>
+        <v>0.308956</v>
       </c>
       <c r="H207" s="7">
-        <v>0.18377</v>
+        <v>0.168892</v>
       </c>
       <c r="I207" s="7">
-        <v>0.507802</v>
+        <v>0.505085</v>
       </c>
       <c r="J207" s="7">
-        <v>2.714828</v>
+        <v>2.7423</v>
       </c>
       <c r="K207" s="7">
-        <v>9.937332</v>
+        <v>9.840064</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9440,25 +9440,25 @@
         <v>3</v>
       </c>
       <c r="E208" s="7">
-        <v>0.040673</v>
+        <v>0.036477</v>
       </c>
       <c r="F208" s="7">
-        <v>0.015298</v>
+        <v>0.007841</v>
       </c>
       <c r="G208" s="7">
-        <v>0.171785</v>
+        <v>0.164267</v>
       </c>
       <c r="H208" s="7">
-        <v>0.045376</v>
+        <v>0.041161</v>
       </c>
       <c r="I208" s="7">
-        <v>0.403448</v>
+        <v>0.402274</v>
       </c>
       <c r="J208" s="7">
-        <v>1.51721</v>
+        <v>1.5049430000000001</v>
       </c>
       <c r="K208" s="7">
-        <v>2.9617989999999996</v>
+        <v>2.943912</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9475,25 +9475,25 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.11217</v>
+        <v>0.09354599999999999</v>
       </c>
       <c r="F209" s="7">
-        <v>0.047396</v>
+        <v>0.007475000000000001</v>
       </c>
       <c r="G209" s="7">
-        <v>0.29764</v>
+        <v>0.279721</v>
       </c>
       <c r="H209" s="7">
-        <v>0.22401700000000002</v>
+        <v>0.203519</v>
       </c>
       <c r="I209" s="7">
-        <v>0.38766</v>
+        <v>0.38295</v>
       </c>
       <c r="J209" s="7">
-        <v>2.835432</v>
+        <v>2.872167</v>
       </c>
       <c r="K209" s="7">
-        <v>15.111319000000002</v>
+        <v>14.905677</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9510,25 +9510,25 @@
         <v>4</v>
       </c>
       <c r="E210" s="7">
-        <v>0.077089</v>
+        <v>0.067498</v>
       </c>
       <c r="F210" s="7">
-        <v>0.074284</v>
+        <v>0.05086</v>
       </c>
       <c r="G210" s="7">
-        <v>0.247119</v>
+        <v>0.233523</v>
       </c>
       <c r="H210" s="7">
-        <v>0.17596599999999998</v>
+        <v>0.16549399999999997</v>
       </c>
       <c r="I210" s="7">
-        <v>0.512803</v>
+        <v>0.509537</v>
       </c>
       <c r="J210" s="7">
-        <v>1.855135</v>
+        <v>1.873314</v>
       </c>
       <c r="K210" s="7">
-        <v>5.570048000000001</v>
+        <v>5.515340999999999</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9545,25 +9545,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.060107</v>
+        <v>0.055386</v>
       </c>
       <c r="F211" s="7">
-        <v>0.109572</v>
+        <v>0.098273</v>
       </c>
       <c r="G211" s="7">
-        <v>0.250572</v>
+        <v>0.24239999999999998</v>
       </c>
       <c r="H211" s="7">
-        <v>0.18614799999999998</v>
+        <v>0.180866</v>
       </c>
       <c r="I211" s="7">
-        <v>0.49479599999999996</v>
+        <v>0.48884700000000003</v>
       </c>
       <c r="J211" s="7">
-        <v>1.8789529999999999</v>
+        <v>1.876082</v>
       </c>
       <c r="K211" s="7">
-        <v>5.0380720000000005</v>
+        <v>5.0322949999999995</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9580,25 +9580,25 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.09052099999999999</v>
+        <v>0.077846</v>
       </c>
       <c r="F212" s="7">
-        <v>0.11527</v>
+        <v>0.086776</v>
       </c>
       <c r="G212" s="7">
-        <v>0.304965</v>
+        <v>0.287418</v>
       </c>
       <c r="H212" s="7">
-        <v>0.26184799999999997</v>
+        <v>0.24718199999999999</v>
       </c>
       <c r="I212" s="7">
-        <v>0.622361</v>
+        <v>0.60602</v>
       </c>
       <c r="J212" s="7">
-        <v>3.0025850000000003</v>
+        <v>2.985453</v>
       </c>
       <c r="K212" s="7">
-        <v>9.908239</v>
+        <v>9.802396</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,25 +9615,25 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.033977</v>
+        <v>0.007929</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.070269</v>
+        <v>-0.127605</v>
       </c>
       <c r="G213" s="7">
-        <v>0.170576</v>
+        <v>0.146802</v>
       </c>
       <c r="H213" s="7">
-        <v>0.088947</v>
+        <v>0.061514</v>
       </c>
       <c r="I213" s="7">
-        <v>0.629043</v>
+        <v>0.588357</v>
       </c>
       <c r="J213" s="7">
-        <v>4.1675130000000005</v>
+        <v>4.044404</v>
       </c>
       <c r="K213" s="7">
-        <v>13.750070000000001</v>
+        <v>13.565771</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,25 +9650,25 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.052439</v>
+        <v>0.049656000000000006</v>
       </c>
       <c r="F214" s="7">
-        <v>0.051181000000000004</v>
+        <v>0.040467</v>
       </c>
       <c r="G214" s="7">
-        <v>0.17026700000000003</v>
+        <v>0.168518</v>
       </c>
       <c r="H214" s="7">
-        <v>0.121978</v>
+        <v>0.11901099999999999</v>
       </c>
       <c r="I214" s="7">
-        <v>0.407709</v>
+        <v>0.40883699999999995</v>
       </c>
       <c r="J214" s="7">
-        <v>2.231163</v>
+        <v>2.246665</v>
       </c>
       <c r="K214" s="7">
-        <v>7.22439</v>
+        <v>7.223088000000001</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9685,25 +9685,25 @@
         <v>5</v>
       </c>
       <c r="E215" s="7">
-        <v>0.131861</v>
+        <v>0.11866</v>
       </c>
       <c r="F215" s="7">
-        <v>0.129882</v>
+        <v>0.098727</v>
       </c>
       <c r="G215" s="7">
-        <v>0.38676099999999997</v>
+        <v>0.368271</v>
       </c>
       <c r="H215" s="7">
-        <v>0.327984</v>
+        <v>0.312496</v>
       </c>
       <c r="I215" s="7">
-        <v>0.639817</v>
+        <v>0.630563</v>
       </c>
       <c r="J215" s="7">
-        <v>2.6591340000000003</v>
+        <v>2.6752659999999997</v>
       </c>
       <c r="K215" s="7">
-        <v>9.919683</v>
+        <v>9.876114</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9720,25 +9720,25 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.026271</v>
+        <v>0.026307999999999998</v>
       </c>
       <c r="F216" s="7">
-        <v>0.036070000000000005</v>
+        <v>0.035687</v>
       </c>
       <c r="G216" s="7">
-        <v>0.08329700000000001</v>
+        <v>0.083002</v>
       </c>
       <c r="H216" s="7">
-        <v>0.048651</v>
+        <v>0.048688</v>
       </c>
       <c r="I216" s="7">
-        <v>0.23161</v>
+        <v>0.228294</v>
       </c>
       <c r="J216" s="7">
-        <v>1.7849270000000002</v>
+        <v>1.778418</v>
       </c>
       <c r="K216" s="7">
-        <v>5.283898000000001</v>
+        <v>5.320461</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9755,25 +9755,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.07650699999999999</v>
+        <v>0.06843099999999999</v>
       </c>
       <c r="F217" s="7">
-        <v>0.131403</v>
+        <v>0.114014</v>
       </c>
       <c r="G217" s="7">
-        <v>0.319598</v>
+        <v>0.306257</v>
       </c>
       <c r="H217" s="7">
-        <v>0.250772</v>
+        <v>0.241388</v>
       </c>
       <c r="I217" s="7">
-        <v>0.6360370000000001</v>
+        <v>0.628823</v>
       </c>
       <c r="J217" s="7">
-        <v>3.217835</v>
+        <v>3.241087</v>
       </c>
       <c r="K217" s="7">
-        <v>10.420955</v>
+        <v>10.301253999999998</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,25 +9790,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.12136</v>
+        <v>0.111432</v>
       </c>
       <c r="F218" s="7">
-        <v>0.121468</v>
+        <v>0.093898</v>
       </c>
       <c r="G218" s="7">
-        <v>0.371622</v>
+        <v>0.35749400000000003</v>
       </c>
       <c r="H218" s="7">
-        <v>0.296575</v>
+        <v>0.285096</v>
       </c>
       <c r="I218" s="7">
-        <v>0.611483</v>
+        <v>0.60144</v>
       </c>
       <c r="J218" s="7">
-        <v>3.8833949999999997</v>
+        <v>3.887592</v>
       </c>
       <c r="K218" s="7">
-        <v>13.309981</v>
+        <v>13.300957</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9825,19 +9825,19 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.070634</v>
+        <v>0.06397599999999999</v>
       </c>
       <c r="F219" s="7">
-        <v>0.07048700000000001</v>
+        <v>0.050705</v>
       </c>
       <c r="G219" s="7">
-        <v>0.24756</v>
+        <v>0.23811800000000002</v>
       </c>
       <c r="H219" s="7">
-        <v>0.17953600000000003</v>
+        <v>0.1722</v>
       </c>
       <c r="I219" s="7">
-        <v>0.521065</v>
+        <v>0.512343</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
@@ -9856,16 +9856,16 @@
         <v>6</v>
       </c>
       <c r="E220" s="7">
-        <v>0.084398</v>
+        <v>0.058547</v>
       </c>
       <c r="F220" s="7">
-        <v>-0.237211</v>
+        <v>-0.264657</v>
       </c>
       <c r="G220" s="7">
-        <v>0.678872</v>
+        <v>0.640868</v>
       </c>
       <c r="H220" s="7">
-        <v>0.11541399999999999</v>
+        <v>0.08882300000000001</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
@@ -9906,22 +9906,22 @@
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.057923</v>
+        <v>0.035203000000000005</v>
       </c>
       <c r="F222" s="7">
-        <v>-0.15667899999999998</v>
+        <v>-0.195024</v>
       </c>
       <c r="G222" s="7">
-        <v>0.41113</v>
+        <v>0.384685</v>
       </c>
       <c r="H222" s="7">
-        <v>0.09433899999999999</v>
+        <v>0.070838</v>
       </c>
       <c r="I222" s="7">
-        <v>1.047951</v>
+        <v>0.99698</v>
       </c>
       <c r="J222" s="7">
-        <v>4.48778</v>
+        <v>4.4154349999999996</v>
       </c>
       <c r="K222" s="7"/>
     </row>
@@ -9939,25 +9939,25 @@
         <v>4</v>
       </c>
       <c r="E223" s="7">
-        <v>0.030085</v>
+        <v>0.031218</v>
       </c>
       <c r="F223" s="7">
-        <v>0.09615</v>
+        <v>0.096412</v>
       </c>
       <c r="G223" s="7">
-        <v>0.19774</v>
+        <v>0.196776</v>
       </c>
       <c r="H223" s="7">
-        <v>0.121471</v>
+        <v>0.12270500000000001</v>
       </c>
       <c r="I223" s="7">
-        <v>0.447552</v>
+        <v>0.447868</v>
       </c>
       <c r="J223" s="7">
-        <v>1.282945</v>
+        <v>1.2886410000000001</v>
       </c>
       <c r="K223" s="7">
-        <v>2.6979430000000004</v>
+        <v>2.700937</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9974,19 +9974,19 @@
         <v>2</v>
       </c>
       <c r="E224" s="7">
-        <v>0.027265</v>
+        <v>0.028251</v>
       </c>
       <c r="F224" s="7">
-        <v>0.08387800000000001</v>
+        <v>0.08395200000000001</v>
       </c>
       <c r="G224" s="7">
-        <v>0.188189</v>
+        <v>0.187009</v>
       </c>
       <c r="H224" s="7">
-        <v>0.11382500000000001</v>
+        <v>0.114893</v>
       </c>
       <c r="I224" s="7">
-        <v>0.445839</v>
+        <v>0.445698</v>
       </c>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10005,22 +10005,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.119617</v>
+        <v>0.11003500000000001</v>
       </c>
       <c r="F225" s="7">
-        <v>0.105247</v>
+        <v>0.075479</v>
       </c>
       <c r="G225" s="7">
-        <v>0.254731</v>
+        <v>0.24018</v>
       </c>
       <c r="H225" s="7">
-        <v>0.25004000000000004</v>
+        <v>0.239341</v>
       </c>
       <c r="I225" s="7">
-        <v>0.43908200000000003</v>
+        <v>0.44041800000000003</v>
       </c>
       <c r="J225" s="7">
-        <v>2.482659</v>
+        <v>2.504498</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10038,19 +10038,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="7">
-        <v>0.070501</v>
+        <v>0.046203</v>
       </c>
       <c r="F226" s="7">
-        <v>-0.149912</v>
+        <v>-0.201137</v>
       </c>
       <c r="G226" s="7">
-        <v>0.380098</v>
+        <v>0.354755</v>
       </c>
       <c r="H226" s="7">
-        <v>0.110397</v>
+        <v>0.08519399999999999</v>
       </c>
       <c r="I226" s="7">
-        <v>0.9425920000000001</v>
+        <v>0.8806919999999999</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10069,25 +10069,25 @@
         <v>4</v>
       </c>
       <c r="E227" s="7">
-        <v>0.061546000000000003</v>
+        <v>0.055856</v>
       </c>
       <c r="F227" s="7">
-        <v>0.053418</v>
+        <v>0.041449</v>
       </c>
       <c r="G227" s="7">
-        <v>0.20613299999999998</v>
+        <v>0.19706900000000002</v>
       </c>
       <c r="H227" s="7">
-        <v>0.10836499999999999</v>
+        <v>0.102424</v>
       </c>
       <c r="I227" s="7">
-        <v>0.461338</v>
+        <v>0.458326</v>
       </c>
       <c r="J227" s="7">
-        <v>2.1692850000000004</v>
+        <v>2.1690899999999997</v>
       </c>
       <c r="K227" s="7">
-        <v>5.6364469999999995</v>
+        <v>5.600013000000001</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10104,25 +10104,25 @@
         <v>3</v>
       </c>
       <c r="E228" s="7">
-        <v>0.047152</v>
+        <v>0.044344999999999996</v>
       </c>
       <c r="F228" s="7">
-        <v>0.08140900000000001</v>
+        <v>0.071539</v>
       </c>
       <c r="G228" s="7">
-        <v>0.222604</v>
+        <v>0.21727799999999997</v>
       </c>
       <c r="H228" s="7">
-        <v>0.137543</v>
+        <v>0.134495</v>
       </c>
       <c r="I228" s="7">
-        <v>0.44242899999999996</v>
+        <v>0.43994999999999995</v>
       </c>
       <c r="J228" s="7">
-        <v>1.748064</v>
+        <v>1.7525579999999998</v>
       </c>
       <c r="K228" s="7">
-        <v>4.551394</v>
+        <v>4.541404</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.093813</v>
+        <v>0.088535</v>
       </c>
       <c r="F229" s="7">
-        <v>0.122898</v>
+        <v>0.10287800000000001</v>
       </c>
       <c r="G229" s="7">
-        <v>0.20647</v>
+        <v>0.198777</v>
       </c>
       <c r="H229" s="7">
-        <v>0.20034600000000002</v>
+        <v>0.194554</v>
       </c>
       <c r="I229" s="7">
-        <v>0.555925</v>
+        <v>0.544114</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10191,19 +10191,19 @@
         <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>0.123661</v>
+        <v>0.113246</v>
       </c>
       <c r="F231" s="7">
-        <v>0.144052</v>
+        <v>0.135483</v>
       </c>
       <c r="G231" s="7">
-        <v>0.341741</v>
+        <v>0.327793</v>
       </c>
       <c r="H231" s="7">
-        <v>0.33740699999999996</v>
+        <v>0.325011</v>
       </c>
       <c r="I231" s="7">
-        <v>0.545601</v>
+        <v>0.546566</v>
       </c>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10222,19 +10222,19 @@
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.120535</v>
+        <v>0.10815</v>
       </c>
       <c r="F232" s="7">
-        <v>0.090124</v>
+        <v>0.060584</v>
       </c>
       <c r="G232" s="7">
-        <v>0.249407</v>
+        <v>0.234392</v>
       </c>
       <c r="H232" s="7">
-        <v>0.215992</v>
+        <v>0.20255199999999998</v>
       </c>
       <c r="I232" s="7">
-        <v>0.528498</v>
+        <v>0.505822</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10253,25 +10253,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.036864</v>
+        <v>0.036511</v>
       </c>
       <c r="F233" s="7">
-        <v>0.065397</v>
+        <v>0.059785000000000005</v>
       </c>
       <c r="G233" s="7">
-        <v>0.173885</v>
+        <v>0.173265</v>
       </c>
       <c r="H233" s="7">
-        <v>0.105479</v>
+        <v>0.105103</v>
       </c>
       <c r="I233" s="7">
-        <v>0.366815</v>
+        <v>0.368758</v>
       </c>
       <c r="J233" s="7">
-        <v>1.4878909999999999</v>
+        <v>1.49895</v>
       </c>
       <c r="K233" s="7">
-        <v>4.326080999999999</v>
+        <v>4.323061</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10288,19 +10288,19 @@
         <v>3</v>
       </c>
       <c r="E234" s="7">
-        <v>0.061772</v>
+        <v>0.050956</v>
       </c>
       <c r="F234" s="7">
-        <v>0.067306</v>
+        <v>0.041837</v>
       </c>
       <c r="G234" s="7">
-        <v>0.23684899999999998</v>
+        <v>0.225205</v>
       </c>
       <c r="H234" s="7">
-        <v>0.17387799999999998</v>
+        <v>0.161921</v>
       </c>
       <c r="I234" s="7">
-        <v>0.468275</v>
+        <v>0.462111</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10319,19 +10319,19 @@
         <v>4</v>
       </c>
       <c r="E235" s="7">
-        <v>0.060479000000000005</v>
+        <v>0.050354</v>
       </c>
       <c r="F235" s="7">
-        <v>0.067686</v>
+        <v>0.051916000000000004</v>
       </c>
       <c r="G235" s="7">
-        <v>0.21979800000000002</v>
+        <v>0.207309</v>
       </c>
       <c r="H235" s="7">
-        <v>0.11047499999999999</v>
+        <v>0.09987299999999999</v>
       </c>
       <c r="I235" s="7">
-        <v>0.48525199999999996</v>
+        <v>0.471768</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10350,19 +10350,19 @@
         <v>2</v>
       </c>
       <c r="E236" s="7">
-        <v>0.03222</v>
+        <v>0.032612</v>
       </c>
       <c r="F236" s="7">
-        <v>0.095816</v>
+        <v>0.095169</v>
       </c>
       <c r="G236" s="7">
-        <v>0.19969599999999998</v>
+        <v>0.19778600000000002</v>
       </c>
       <c r="H236" s="7">
-        <v>0.126534</v>
+        <v>0.126961</v>
       </c>
       <c r="I236" s="7">
-        <v>0.474008</v>
+        <v>0.473193</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10381,25 +10381,25 @@
         <v>6</v>
       </c>
       <c r="E237" s="7">
-        <v>0.040833</v>
+        <v>0.020099999999999996</v>
       </c>
       <c r="F237" s="7">
-        <v>-0.058163</v>
+        <v>-0.11335699999999999</v>
       </c>
       <c r="G237" s="7">
-        <v>0.186588</v>
+        <v>0.16460999999999998</v>
       </c>
       <c r="H237" s="7">
-        <v>0.09936600000000001</v>
+        <v>0.077467</v>
       </c>
       <c r="I237" s="7">
-        <v>0.632559</v>
+        <v>0.5946560000000001</v>
       </c>
       <c r="J237" s="7">
-        <v>4.308111</v>
+        <v>4.185021</v>
       </c>
       <c r="K237" s="7">
-        <v>14.047754</v>
+        <v>13.943765</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10416,14 +10416,14 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.052706</v>
+        <v>0.047257</v>
       </c>
       <c r="F238" s="7">
-        <v>0.017988999999999998</v>
+        <v>0.01015</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7">
-        <v>0.045048000000000005</v>
+        <v>0.039638</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
@@ -10443,19 +10443,19 @@
         <v>6</v>
       </c>
       <c r="E239" s="7">
-        <v>0.15710000000000002</v>
+        <v>0.152601</v>
       </c>
       <c r="F239" s="7">
-        <v>0.165763</v>
+        <v>0.158838</v>
       </c>
       <c r="G239" s="7">
-        <v>0.298445</v>
+        <v>0.290256</v>
       </c>
       <c r="H239" s="7">
-        <v>0.28180499999999997</v>
+        <v>0.276821</v>
       </c>
       <c r="I239" s="7">
-        <v>0.682397</v>
+        <v>0.6694209999999999</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10474,19 +10474,19 @@
         <v>5</v>
       </c>
       <c r="E240" s="7">
-        <v>0.107645</v>
+        <v>0.101059</v>
       </c>
       <c r="F240" s="7">
-        <v>0.072195</v>
+        <v>0.050971</v>
       </c>
       <c r="G240" s="7">
-        <v>0.21692599999999998</v>
+        <v>0.20839</v>
       </c>
       <c r="H240" s="7">
-        <v>0.17112100000000002</v>
+        <v>0.164157</v>
       </c>
       <c r="I240" s="7">
-        <v>0.48789499999999997</v>
+        <v>0.482682</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10505,25 +10505,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.033092</v>
+        <v>0.032002</v>
       </c>
       <c r="F241" s="7">
-        <v>0.039853</v>
+        <v>0.038723</v>
       </c>
       <c r="G241" s="7">
-        <v>0.088974</v>
+        <v>0.087447</v>
       </c>
       <c r="H241" s="7">
-        <v>0.053070000000000006</v>
+        <v>0.051959</v>
       </c>
       <c r="I241" s="7">
-        <v>0.23038599999999998</v>
+        <v>0.22602799999999998</v>
       </c>
       <c r="J241" s="7">
-        <v>1.8388069999999999</v>
+        <v>1.831544</v>
       </c>
       <c r="K241" s="7">
-        <v>5.875166</v>
+        <v>5.912767</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10540,25 +10540,25 @@
         <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.023189</v>
+        <v>0.022396</v>
       </c>
       <c r="F242" s="7">
-        <v>0.048149</v>
+        <v>0.046865</v>
       </c>
       <c r="G242" s="7">
-        <v>0.214855</v>
+        <v>0.213387</v>
       </c>
       <c r="H242" s="7">
-        <v>0.08286400000000001</v>
+        <v>0.08202400000000001</v>
       </c>
       <c r="I242" s="7">
-        <v>0.204922</v>
+        <v>0.20683900000000002</v>
       </c>
       <c r="J242" s="7">
-        <v>1.90714</v>
+        <v>1.951939</v>
       </c>
       <c r="K242" s="7">
-        <v>5.857691999999999</v>
+        <v>5.862704</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10575,25 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.11025</v>
+        <v>0.09129300000000001</v>
       </c>
       <c r="F243" s="7">
-        <v>0.058005</v>
+        <v>0.014776000000000001</v>
       </c>
       <c r="G243" s="7">
-        <v>0.277155</v>
+        <v>0.256357</v>
       </c>
       <c r="H243" s="7">
-        <v>0.207887</v>
+        <v>0.18726199999999998</v>
       </c>
       <c r="I243" s="7">
-        <v>0.450043</v>
+        <v>0.44821399999999995</v>
       </c>
       <c r="J243" s="7">
-        <v>2.791404</v>
+        <v>2.853831</v>
       </c>
       <c r="K243" s="7">
-        <v>15.053983</v>
+        <v>14.87759</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10610,25 @@
         <v>3</v>
       </c>
       <c r="E244" s="7">
-        <v>0.050897</v>
+        <v>0.048302</v>
       </c>
       <c r="F244" s="7">
-        <v>0.072694</v>
+        <v>0.062541</v>
       </c>
       <c r="G244" s="7">
-        <v>0.21559899999999999</v>
+        <v>0.21077</v>
       </c>
       <c r="H244" s="7">
-        <v>0.143125</v>
+        <v>0.140302</v>
       </c>
       <c r="I244" s="7">
-        <v>0.448828</v>
+        <v>0.445299</v>
       </c>
       <c r="J244" s="7">
-        <v>1.7706540000000002</v>
+        <v>1.774348</v>
       </c>
       <c r="K244" s="7">
-        <v>4.593878</v>
+        <v>4.58043</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10645,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.059617</v>
+        <v>0.051935</v>
       </c>
       <c r="F245" s="7">
-        <v>0.018429</v>
+        <v>0.002662</v>
       </c>
       <c r="G245" s="7">
-        <v>0.172791</v>
+        <v>0.162094</v>
       </c>
       <c r="H245" s="7">
-        <v>0.07485699999999999</v>
+        <v>0.067065</v>
       </c>
       <c r="I245" s="7">
-        <v>0.390627</v>
+        <v>0.387824</v>
       </c>
       <c r="J245" s="7">
-        <v>1.456626</v>
+        <v>1.4608400000000001</v>
       </c>
       <c r="K245" s="7">
-        <v>3.8692399999999996</v>
+        <v>3.8332960000000003</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10680,25 @@
         <v>2</v>
       </c>
       <c r="E246" s="7">
-        <v>0.045167</v>
+        <v>0.042809999999999994</v>
       </c>
       <c r="F246" s="7">
-        <v>0.09007899999999999</v>
+        <v>0.083757</v>
       </c>
       <c r="G246" s="7">
-        <v>0.219707</v>
+        <v>0.213918</v>
       </c>
       <c r="H246" s="7">
-        <v>0.131226</v>
+        <v>0.12867499999999998</v>
       </c>
       <c r="I246" s="7">
-        <v>0.518463</v>
+        <v>0.516631</v>
       </c>
       <c r="J246" s="7">
-        <v>4.342825</v>
+        <v>4.299912</v>
       </c>
       <c r="K246" s="7">
-        <v>7.164917</v>
+        <v>7.143006000000001</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10715,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.077237</v>
+        <v>0.067786</v>
       </c>
       <c r="F247" s="7">
-        <v>0.09014799999999999</v>
+        <v>0.064813</v>
       </c>
       <c r="G247" s="7">
-        <v>0.268432</v>
+        <v>0.256171</v>
       </c>
       <c r="H247" s="7">
-        <v>0.18579</v>
+        <v>0.175387</v>
       </c>
       <c r="I247" s="7">
-        <v>0.512599</v>
+        <v>0.510229</v>
       </c>
       <c r="J247" s="7">
-        <v>3.214004</v>
+        <v>3.2353620000000003</v>
       </c>
       <c r="K247" s="7">
-        <v>8.661194</v>
+        <v>8.582491</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10750,25 @@
         <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>0.086501</v>
+        <v>0.074195</v>
       </c>
       <c r="F248" s="7">
-        <v>0.07882399999999999</v>
+        <v>0.047082</v>
       </c>
       <c r="G248" s="7">
-        <v>0.275792</v>
+        <v>0.26056999999999997</v>
       </c>
       <c r="H248" s="7">
-        <v>0.198237</v>
+        <v>0.184666</v>
       </c>
       <c r="I248" s="7">
-        <v>0.509791</v>
+        <v>0.506795</v>
       </c>
       <c r="J248" s="7">
-        <v>3.7826459999999997</v>
+        <v>3.8244409999999998</v>
       </c>
       <c r="K248" s="7">
-        <v>11.686286</v>
+        <v>11.593788</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10785,25 @@
         <v>6</v>
       </c>
       <c r="E249" s="7">
-        <v>0.09447</v>
+        <v>0.078683</v>
       </c>
       <c r="F249" s="7">
-        <v>0.066585</v>
+        <v>0.027010999999999997</v>
       </c>
       <c r="G249" s="7">
-        <v>0.283163</v>
+        <v>0.265528</v>
       </c>
       <c r="H249" s="7">
-        <v>0.20978100000000002</v>
+        <v>0.192331</v>
       </c>
       <c r="I249" s="7">
-        <v>0.46550400000000003</v>
+        <v>0.46631900000000004</v>
       </c>
       <c r="J249" s="7">
-        <v>3.3948110000000002</v>
+        <v>3.459728</v>
       </c>
       <c r="K249" s="7">
-        <v>14.385547999999998</v>
+        <v>14.203276</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10820,25 @@
         <v>3</v>
       </c>
       <c r="E250" s="7">
-        <v>0.056041999999999995</v>
+        <v>0.053094999999999996</v>
       </c>
       <c r="F250" s="7">
-        <v>0.091915</v>
+        <v>0.081747</v>
       </c>
       <c r="G250" s="7">
-        <v>0.211184</v>
+        <v>0.206686</v>
       </c>
       <c r="H250" s="7">
-        <v>0.160564</v>
+        <v>0.157325</v>
       </c>
       <c r="I250" s="7">
-        <v>0.453825</v>
+        <v>0.450111</v>
       </c>
       <c r="J250" s="7">
-        <v>2.015593</v>
+        <v>2.024621</v>
       </c>
       <c r="K250" s="7">
-        <v>5.6315</v>
+        <v>5.623259000000001</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10855,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.09606400000000001</v>
+        <v>0.086686</v>
       </c>
       <c r="F251" s="7">
-        <v>0.10964600000000001</v>
+        <v>0.085616</v>
       </c>
       <c r="G251" s="7">
-        <v>0.256928</v>
+        <v>0.246056</v>
       </c>
       <c r="H251" s="7">
-        <v>0.21882200000000002</v>
+        <v>0.20839400000000002</v>
       </c>
       <c r="I251" s="7">
-        <v>0.51029</v>
+        <v>0.50097</v>
       </c>
       <c r="J251" s="7">
-        <v>3.066642</v>
+        <v>3.069284</v>
       </c>
       <c r="K251" s="7">
-        <v>9.943944</v>
+        <v>9.891098</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10890,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.110736</v>
+        <v>0.09951</v>
       </c>
       <c r="F252" s="7">
-        <v>0.11168900000000001</v>
+        <v>0.083483</v>
       </c>
       <c r="G252" s="7">
-        <v>0.266029</v>
+        <v>0.25360099999999997</v>
       </c>
       <c r="H252" s="7">
-        <v>0.23646599999999998</v>
+        <v>0.223968</v>
       </c>
       <c r="I252" s="7">
-        <v>0.517902</v>
+        <v>0.508675</v>
       </c>
       <c r="J252" s="7">
-        <v>3.2398520000000004</v>
+        <v>3.2675929999999997</v>
       </c>
       <c r="K252" s="7">
-        <v>11.045746999999999</v>
+        <v>10.995446</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10925,25 @@
         <v>4</v>
       </c>
       <c r="E253" s="7">
-        <v>0.048353</v>
+        <v>0.04201800000000001</v>
       </c>
       <c r="F253" s="7">
-        <v>0.020095000000000002</v>
+        <v>0.0071330000000000005</v>
       </c>
       <c r="G253" s="7">
-        <v>0.15858</v>
+        <v>0.149027</v>
       </c>
       <c r="H253" s="7">
-        <v>0.066713</v>
+        <v>0.060267</v>
       </c>
       <c r="I253" s="7">
-        <v>0.38066099999999997</v>
+        <v>0.37858400000000003</v>
       </c>
       <c r="J253" s="7">
-        <v>1.8282640000000001</v>
+        <v>1.828849</v>
       </c>
       <c r="K253" s="7">
-        <v>5.050321</v>
+        <v>5.0133659999999995</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10960,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.068966</v>
+        <v>0.058772000000000005</v>
       </c>
       <c r="F254" s="7">
-        <v>0.06087</v>
+        <v>0.028274</v>
       </c>
       <c r="G254" s="7">
-        <v>0.236695</v>
+        <v>0.22427</v>
       </c>
       <c r="H254" s="7">
-        <v>0.16836600000000002</v>
+        <v>0.157225</v>
       </c>
       <c r="I254" s="7">
-        <v>0.543716</v>
+        <v>0.530331</v>
       </c>
       <c r="J254" s="7">
-        <v>2.8910430000000003</v>
+        <v>2.8565660000000004</v>
       </c>
       <c r="K254" s="7">
-        <v>6.181062</v>
+        <v>6.125678000000001</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +10995,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.052828</v>
+        <v>0.043916000000000004</v>
       </c>
       <c r="F255" s="7">
-        <v>0.055005</v>
+        <v>0.026993</v>
       </c>
       <c r="G255" s="7">
-        <v>0.22311</v>
+        <v>0.212397</v>
       </c>
       <c r="H255" s="7">
-        <v>0.152366</v>
+        <v>0.14261200000000002</v>
       </c>
       <c r="I255" s="7">
-        <v>0.520846</v>
+        <v>0.508636</v>
       </c>
       <c r="J255" s="7">
-        <v>2.827546</v>
+        <v>2.7951490000000003</v>
       </c>
       <c r="K255" s="7">
-        <v>5.331249000000001</v>
+        <v>5.283101</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11030,25 @@
         <v>5</v>
       </c>
       <c r="E256" s="7">
-        <v>0.087177</v>
+        <v>0.075371</v>
       </c>
       <c r="F256" s="7">
-        <v>0.069275</v>
+        <v>0.033446</v>
       </c>
       <c r="G256" s="7">
-        <v>0.25958200000000003</v>
+        <v>0.24579499999999999</v>
       </c>
       <c r="H256" s="7">
-        <v>0.191414</v>
+        <v>0.178476</v>
       </c>
       <c r="I256" s="7">
-        <v>0.566205</v>
+        <v>0.553159</v>
       </c>
       <c r="J256" s="7">
-        <v>2.945711</v>
+        <v>2.907672</v>
       </c>
       <c r="K256" s="7">
-        <v>7.516431</v>
+        <v>7.454725</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11065,25 @@
         <v>6</v>
       </c>
       <c r="E257" s="7">
-        <v>0.038967999999999996</v>
+        <v>0.012892999999999998</v>
       </c>
       <c r="F257" s="7">
-        <v>-0.06665199999999999</v>
+        <v>-0.122819</v>
       </c>
       <c r="G257" s="7">
-        <v>0.175248</v>
+        <v>0.150851</v>
       </c>
       <c r="H257" s="7">
-        <v>0.096028</v>
+        <v>0.06852</v>
       </c>
       <c r="I257" s="7">
-        <v>0.63532</v>
+        <v>0.596959</v>
       </c>
       <c r="J257" s="7">
-        <v>4.1772089999999995</v>
+        <v>4.049436</v>
       </c>
       <c r="K257" s="7">
-        <v>13.987156</v>
+        <v>13.81287</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11100,25 @@
         <v>2</v>
       </c>
       <c r="E258" s="7">
-        <v>0.027690000000000003</v>
+        <v>0.030013</v>
       </c>
       <c r="F258" s="7">
-        <v>0.08830299999999999</v>
+        <v>0.08886799999999999</v>
       </c>
       <c r="G258" s="7">
-        <v>0.191004</v>
+        <v>0.190434</v>
       </c>
       <c r="H258" s="7">
-        <v>0.133979</v>
+        <v>0.136542</v>
       </c>
       <c r="I258" s="7">
-        <v>0.43085999999999997</v>
+        <v>0.428994</v>
       </c>
       <c r="J258" s="7">
-        <v>2.376293</v>
+        <v>2.379277</v>
       </c>
       <c r="K258" s="7">
-        <v>4.437237</v>
+        <v>4.446811</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11135,25 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.12517799999999998</v>
+        <v>0.106862</v>
       </c>
       <c r="F259" s="7">
-        <v>0.022717</v>
+        <v>-0.017375</v>
       </c>
       <c r="G259" s="7">
-        <v>0.218693</v>
+        <v>0.204312</v>
       </c>
       <c r="H259" s="7">
-        <v>0.132569</v>
+        <v>0.114133</v>
       </c>
       <c r="I259" s="7">
-        <v>0.6621980000000001</v>
+        <v>0.623912</v>
       </c>
       <c r="J259" s="7">
-        <v>4.59053</v>
+        <v>4.629378</v>
       </c>
       <c r="K259" s="7">
-        <v>20.914043000000003</v>
+        <v>20.632699</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,10 +11170,10 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.040052000000000004</v>
+        <v>0.020932</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.013083000000000001</v>
+        <v>-0.076972</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -11195,22 +11195,22 @@
         <v>3</v>
       </c>
       <c r="E261" s="7">
-        <v>0.064769</v>
+        <v>0.058990999999999995</v>
       </c>
       <c r="F261" s="7">
-        <v>0.098238</v>
+        <v>0.083494</v>
       </c>
       <c r="G261" s="7">
-        <v>0.240682</v>
+        <v>0.23152999999999999</v>
       </c>
       <c r="H261" s="7">
-        <v>0.17393</v>
+        <v>0.16756000000000001</v>
       </c>
       <c r="I261" s="7">
-        <v>0.510323</v>
+        <v>0.504933</v>
       </c>
       <c r="J261" s="7">
-        <v>2.2288140000000003</v>
+        <v>2.221954</v>
       </c>
       <c r="K261" s="7"/>
     </row>
@@ -11228,22 +11228,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.030661</v>
+        <v>0.02689</v>
       </c>
       <c r="F262" s="7">
-        <v>0.055453999999999996</v>
+        <v>0.050617</v>
       </c>
       <c r="G262" s="7">
-        <v>0.153601</v>
+        <v>0.149301</v>
       </c>
       <c r="H262" s="7">
-        <v>0.075932</v>
+        <v>0.071996</v>
       </c>
       <c r="I262" s="7">
-        <v>0.508687</v>
+        <v>0.50113</v>
       </c>
       <c r="J262" s="7">
-        <v>2.730534</v>
+        <v>2.7216039999999997</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11261,19 +11261,19 @@
         <v>5</v>
       </c>
       <c r="E263" s="7">
-        <v>0.101646</v>
+        <v>0.084718</v>
       </c>
       <c r="F263" s="7">
-        <v>0.06565</v>
+        <v>0.0031019999999999997</v>
       </c>
       <c r="G263" s="7">
-        <v>0.29027000000000003</v>
+        <v>0.271838</v>
       </c>
       <c r="H263" s="7">
-        <v>0.197287</v>
+        <v>0.178889</v>
       </c>
       <c r="I263" s="7">
-        <v>0.42129600000000006</v>
+        <v>0.42615400000000003</v>
       </c>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11292,22 +11292,22 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.172542</v>
+        <v>0.163631</v>
       </c>
       <c r="F264" s="7">
-        <v>0.10812</v>
+        <v>0.09772700000000001</v>
       </c>
       <c r="G264" s="7">
-        <v>0.206659</v>
+        <v>0.194006</v>
       </c>
       <c r="H264" s="7">
-        <v>0.203777</v>
+        <v>0.19462900000000002</v>
       </c>
       <c r="I264" s="7">
-        <v>0.5328390000000001</v>
+        <v>0.5151870000000001</v>
       </c>
       <c r="J264" s="7">
-        <v>3.3499849999999998</v>
+        <v>3.271497</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11325,18 +11325,20 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.028229</v>
+        <v>0.029443</v>
       </c>
       <c r="F265" s="7">
-        <v>0.063054</v>
+        <v>0.059170999999999994</v>
       </c>
       <c r="G265" s="7">
-        <v>0.15072</v>
+        <v>0.15239</v>
       </c>
       <c r="H265" s="7">
-        <v>0.123067</v>
-      </c>
-      <c r="I265" s="7"/>
+        <v>0.12439299999999999</v>
+      </c>
+      <c r="I265" s="7">
+        <v>0.2727</v>
+      </c>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
     </row>
@@ -11354,16 +11356,16 @@
         <v>2</v>
       </c>
       <c r="E266" s="7">
-        <v>0.030383</v>
+        <v>0.031641</v>
       </c>
       <c r="F266" s="7">
-        <v>0.09941900000000001</v>
+        <v>0.09904</v>
       </c>
       <c r="G266" s="7">
-        <v>0.2073</v>
+        <v>0.206207</v>
       </c>
       <c r="H266" s="7">
-        <v>0.127829</v>
+        <v>0.12920500000000001</v>
       </c>
       <c r="I266" s="7"/>
       <c r="J266" s="7"/>
@@ -11383,22 +11385,22 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.035112000000000004</v>
+        <v>0.034693999999999996</v>
       </c>
       <c r="F267" s="7">
-        <v>0.072477</v>
+        <v>0.065885</v>
       </c>
       <c r="G267" s="7">
-        <v>0.19561399999999998</v>
+        <v>0.19438199999999997</v>
       </c>
       <c r="H267" s="7">
-        <v>0.123232</v>
+        <v>0.12277900000000001</v>
       </c>
       <c r="I267" s="7">
-        <v>0.478387</v>
+        <v>0.47942300000000004</v>
       </c>
       <c r="J267" s="7">
-        <v>3.1013819999999996</v>
+        <v>3.0882229999999997</v>
       </c>
       <c r="K267" s="7"/>
     </row>
@@ -11416,22 +11418,22 @@
         <v>5</v>
       </c>
       <c r="E268" s="7">
-        <v>0.047797</v>
+        <v>0.043845999999999996</v>
       </c>
       <c r="F268" s="7">
-        <v>0.060687</v>
+        <v>0.046013</v>
       </c>
       <c r="G268" s="7">
-        <v>0.203301</v>
+        <v>0.19941099999999998</v>
       </c>
       <c r="H268" s="7">
-        <v>0.133363</v>
+        <v>0.12908899999999998</v>
       </c>
       <c r="I268" s="7">
-        <v>0.563149</v>
+        <v>0.565084</v>
       </c>
       <c r="J268" s="7">
-        <v>2.879567</v>
+        <v>2.8805880000000004</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11449,19 +11451,19 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.068439</v>
+        <v>0.057119</v>
       </c>
       <c r="F269" s="7">
-        <v>0.088332</v>
+        <v>0.067765</v>
       </c>
       <c r="G269" s="7">
-        <v>0.20807900000000001</v>
+        <v>0.19563</v>
       </c>
       <c r="H269" s="7">
-        <v>0.136042</v>
+        <v>0.124006</v>
       </c>
       <c r="I269" s="7">
-        <v>0.503544</v>
+        <v>0.487723</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11480,19 +11482,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.099516</v>
+        <v>0.090056</v>
       </c>
       <c r="F270" s="7">
-        <v>0.105022</v>
+        <v>0.09060700000000001</v>
       </c>
       <c r="G270" s="7">
-        <v>0.16363499999999997</v>
+        <v>0.149669</v>
       </c>
       <c r="H270" s="7">
-        <v>0.168009</v>
+        <v>0.157959</v>
       </c>
       <c r="I270" s="7">
-        <v>0.529843</v>
+        <v>0.505486</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11511,19 +11513,19 @@
         <v>4</v>
       </c>
       <c r="E271" s="7">
-        <v>0.07400999999999999</v>
+        <v>0.065735</v>
       </c>
       <c r="F271" s="7">
-        <v>0.06933500000000001</v>
+        <v>0.054946</v>
       </c>
       <c r="G271" s="7">
-        <v>0.228194</v>
+        <v>0.221238</v>
       </c>
       <c r="H271" s="7">
-        <v>0.195325</v>
+        <v>0.186115</v>
       </c>
       <c r="I271" s="7">
-        <v>0.36981</v>
+        <v>0.358579</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11542,19 +11544,19 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.041791</v>
+        <v>0.044932999999999994</v>
       </c>
       <c r="F272" s="7">
-        <v>0.072186</v>
+        <v>0.072918</v>
       </c>
       <c r="G272" s="7">
-        <v>0.212088</v>
+        <v>0.213989</v>
       </c>
       <c r="H272" s="7">
-        <v>0.178527</v>
+        <v>0.18208100000000002</v>
       </c>
       <c r="I272" s="7">
-        <v>0.334488</v>
+        <v>0.33079000000000003</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11573,19 +11575,19 @@
         <v>6</v>
       </c>
       <c r="E273" s="7">
-        <v>0.14844200000000002</v>
+        <v>0.142178</v>
       </c>
       <c r="F273" s="7">
-        <v>0.13153399999999998</v>
+        <v>0.129141</v>
       </c>
       <c r="G273" s="7">
-        <v>0.287806</v>
+        <v>0.27991499999999997</v>
       </c>
       <c r="H273" s="7">
-        <v>0.309526</v>
+        <v>0.302384</v>
       </c>
       <c r="I273" s="7">
-        <v>0.5146809999999999</v>
+        <v>0.520494</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11604,22 +11606,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.042169</v>
+        <v>0.037178</v>
       </c>
       <c r="F274" s="7">
-        <v>0.053621999999999996</v>
+        <v>0.03788</v>
       </c>
       <c r="G274" s="7">
-        <v>0.198123</v>
+        <v>0.191111</v>
       </c>
       <c r="H274" s="7">
-        <v>0.125191</v>
+        <v>0.11980299999999999</v>
       </c>
       <c r="I274" s="7">
-        <v>0.504733</v>
+        <v>0.501883</v>
       </c>
       <c r="J274" s="7">
-        <v>3.071045</v>
+        <v>3.0475369999999997</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -11637,25 +11639,25 @@
         <v>5</v>
       </c>
       <c r="E275" s="7">
-        <v>0.08780900000000001</v>
+        <v>0.078231</v>
       </c>
       <c r="F275" s="7">
-        <v>0.109098</v>
+        <v>0.08606</v>
       </c>
       <c r="G275" s="7">
-        <v>0.301997</v>
+        <v>0.287437</v>
       </c>
       <c r="H275" s="7">
-        <v>0.217116</v>
+        <v>0.206399</v>
       </c>
       <c r="I275" s="7">
-        <v>0.570197</v>
+        <v>0.557506</v>
       </c>
       <c r="J275" s="7">
-        <v>2.524995</v>
+        <v>2.526026</v>
       </c>
       <c r="K275" s="7">
-        <v>6.613677</v>
+        <v>6.557569</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11672,25 +11674,25 @@
         <v>2</v>
       </c>
       <c r="E276" s="7">
-        <v>0.031362</v>
+        <v>0.032803</v>
       </c>
       <c r="F276" s="7">
-        <v>0.090821</v>
+        <v>0.09137600000000001</v>
       </c>
       <c r="G276" s="7">
-        <v>0.20092500000000002</v>
+        <v>0.20025600000000002</v>
       </c>
       <c r="H276" s="7">
-        <v>0.123903</v>
+        <v>0.125473</v>
       </c>
       <c r="I276" s="7">
-        <v>0.474607</v>
+        <v>0.47510800000000003</v>
       </c>
       <c r="J276" s="7">
-        <v>2.201345</v>
+        <v>2.197363</v>
       </c>
       <c r="K276" s="7">
-        <v>4.128612</v>
+        <v>4.1335370000000005</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11707,25 +11709,25 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.064225</v>
+        <v>0.056612</v>
       </c>
       <c r="F277" s="7">
-        <v>0.017265</v>
+        <v>0.003172</v>
       </c>
       <c r="G277" s="7">
-        <v>0.11372299999999999</v>
+        <v>0.104879</v>
       </c>
       <c r="H277" s="7">
-        <v>0.048703</v>
+        <v>0.041201</v>
       </c>
       <c r="I277" s="7">
-        <v>0.311087</v>
+        <v>0.300089</v>
       </c>
       <c r="J277" s="7">
-        <v>1.776687</v>
+        <v>1.7480660000000001</v>
       </c>
       <c r="K277" s="7">
-        <v>5.184622000000001</v>
+        <v>5.165854</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11742,25 +11744,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.106486</v>
+        <v>0.09015599999999999</v>
       </c>
       <c r="F278" s="7">
-        <v>0.062255000000000005</v>
+        <v>0.026174</v>
       </c>
       <c r="G278" s="7">
-        <v>0.248694</v>
+        <v>0.232319</v>
       </c>
       <c r="H278" s="7">
-        <v>0.20272099999999998</v>
+        <v>0.184971</v>
       </c>
       <c r="I278" s="7">
-        <v>0.40942500000000004</v>
+        <v>0.41125300000000004</v>
       </c>
       <c r="J278" s="7">
-        <v>2.408601</v>
+        <v>2.473362</v>
       </c>
       <c r="K278" s="7">
-        <v>12.810836</v>
+        <v>12.671492</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11777,25 +11779,25 @@
         <v>4</v>
       </c>
       <c r="E279" s="7">
-        <v>0.060566</v>
+        <v>0.05425</v>
       </c>
       <c r="F279" s="7">
-        <v>0.023081</v>
+        <v>0.010343999999999999</v>
       </c>
       <c r="G279" s="7">
-        <v>0.17176</v>
+        <v>0.165128</v>
       </c>
       <c r="H279" s="7">
-        <v>0.048422</v>
+        <v>0.04217800000000001</v>
       </c>
       <c r="I279" s="7">
-        <v>0.40104599999999996</v>
+        <v>0.397368</v>
       </c>
       <c r="J279" s="7">
-        <v>1.634419</v>
+        <v>1.649863</v>
       </c>
       <c r="K279" s="7">
-        <v>3.681506</v>
+        <v>3.6561950000000003</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11812,25 +11814,25 @@
         <v>6</v>
       </c>
       <c r="E280" s="7">
-        <v>0.097387</v>
+        <v>0.080703</v>
       </c>
       <c r="F280" s="7">
-        <v>0.110662</v>
+        <v>0.08243</v>
       </c>
       <c r="G280" s="7">
-        <v>0.256961</v>
+        <v>0.23431100000000002</v>
       </c>
       <c r="H280" s="7">
-        <v>0.209799</v>
+        <v>0.191406</v>
       </c>
       <c r="I280" s="7">
-        <v>0.494907</v>
+        <v>0.476421</v>
       </c>
       <c r="J280" s="7">
-        <v>2.6976479999999996</v>
+        <v>2.70193</v>
       </c>
       <c r="K280" s="7">
-        <v>10.217084</v>
+        <v>10.095842</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11847,25 +11849,25 @@
         <v>3</v>
       </c>
       <c r="E281" s="7">
-        <v>0.042328000000000005</v>
+        <v>0.041231</v>
       </c>
       <c r="F281" s="7">
-        <v>0.09332599999999999</v>
+        <v>0.08656599999999999</v>
       </c>
       <c r="G281" s="7">
-        <v>0.20880500000000002</v>
+        <v>0.204024</v>
       </c>
       <c r="H281" s="7">
-        <v>0.138626</v>
+        <v>0.137428</v>
       </c>
       <c r="I281" s="7">
-        <v>0.476491</v>
+        <v>0.473311</v>
       </c>
       <c r="J281" s="7">
-        <v>2.9684559999999998</v>
+        <v>2.9536290000000003</v>
       </c>
       <c r="K281" s="7">
-        <v>5.300093</v>
+        <v>5.290343</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11882,25 +11884,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.034359</v>
+        <v>0.033962</v>
       </c>
       <c r="F282" s="7">
-        <v>0.070115</v>
+        <v>0.068501</v>
       </c>
       <c r="G282" s="7">
-        <v>0.184837</v>
+        <v>0.181361</v>
       </c>
       <c r="H282" s="7">
-        <v>0.099134</v>
+        <v>0.098713</v>
       </c>
       <c r="I282" s="7">
-        <v>0.456256</v>
+        <v>0.455152</v>
       </c>
       <c r="J282" s="7">
-        <v>2.296149</v>
+        <v>2.2845969999999998</v>
       </c>
       <c r="K282" s="7">
-        <v>4.216432</v>
+        <v>4.21143</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11917,25 +11919,25 @@
         <v>5</v>
       </c>
       <c r="E283" s="7">
-        <v>0.049004000000000006</v>
+        <v>0.046851000000000004</v>
       </c>
       <c r="F283" s="7">
-        <v>0.031577</v>
+        <v>0.029356</v>
       </c>
       <c r="G283" s="7">
-        <v>0.0789</v>
+        <v>0.075567</v>
       </c>
       <c r="H283" s="7">
-        <v>0.035162</v>
+        <v>0.033037000000000004</v>
       </c>
       <c r="I283" s="7">
-        <v>0.284181</v>
+        <v>0.283795</v>
       </c>
       <c r="J283" s="7">
-        <v>1.9540899999999999</v>
+        <v>1.9380410000000001</v>
       </c>
       <c r="K283" s="7">
-        <v>5.893904</v>
+        <v>5.915166</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11952,25 +11954,25 @@
         <v>3</v>
       </c>
       <c r="E284" s="7">
-        <v>0.037485</v>
+        <v>0.035242</v>
       </c>
       <c r="F284" s="7">
-        <v>0.054207</v>
+        <v>0.049551</v>
       </c>
       <c r="G284" s="7">
-        <v>0.221397</v>
+        <v>0.21677</v>
       </c>
       <c r="H284" s="7">
-        <v>0.061165000000000004</v>
+        <v>0.058871</v>
       </c>
       <c r="I284" s="7">
-        <v>0.430972</v>
+        <v>0.42948300000000006</v>
       </c>
       <c r="J284" s="7">
-        <v>1.983014</v>
+        <v>1.9692560000000001</v>
       </c>
       <c r="K284" s="7">
-        <v>3.6356849999999996</v>
+        <v>3.623618</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11987,25 +11989,25 @@
         <v>5</v>
       </c>
       <c r="E285" s="7">
-        <v>0.054225</v>
+        <v>0.048612999999999996</v>
       </c>
       <c r="F285" s="7">
-        <v>0.083652</v>
+        <v>0.067703</v>
       </c>
       <c r="G285" s="7">
-        <v>0.24462399999999998</v>
+        <v>0.236691</v>
       </c>
       <c r="H285" s="7">
-        <v>0.161718</v>
+        <v>0.155534</v>
       </c>
       <c r="I285" s="7">
-        <v>0.516797</v>
+        <v>0.51315</v>
       </c>
       <c r="J285" s="7">
-        <v>2.6336559999999998</v>
+        <v>2.656767</v>
       </c>
       <c r="K285" s="7">
-        <v>9.418493999999999</v>
+        <v>9.382695</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12022,25 +12024,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>0.021277</v>
+        <v>-0.000877</v>
       </c>
       <c r="F286" s="7">
-        <v>-0.072782</v>
+        <v>-0.125511</v>
       </c>
       <c r="G286" s="7">
-        <v>0.150416</v>
+        <v>0.134651</v>
       </c>
       <c r="H286" s="7">
-        <v>0.061729000000000006</v>
+        <v>0.038697</v>
       </c>
       <c r="I286" s="7">
-        <v>0.598622</v>
+        <v>0.553851</v>
       </c>
       <c r="J286" s="7">
-        <v>4.228126</v>
+        <v>4.097919</v>
       </c>
       <c r="K286" s="7">
-        <v>13.977281</v>
+        <v>13.833300999999999</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12057,25 +12059,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.057205000000000006</v>
+        <v>0.053319</v>
       </c>
       <c r="F287" s="7">
-        <v>0.09559699999999999</v>
+        <v>0.084772</v>
       </c>
       <c r="G287" s="7">
-        <v>0.255182</v>
+        <v>0.248419</v>
       </c>
       <c r="H287" s="7">
-        <v>0.165993</v>
+        <v>0.161707</v>
       </c>
       <c r="I287" s="7">
-        <v>0.487412</v>
+        <v>0.482001</v>
       </c>
       <c r="J287" s="7">
-        <v>1.3381129999999999</v>
+        <v>1.343083</v>
       </c>
       <c r="K287" s="7">
-        <v>3.7237670000000005</v>
+        <v>3.715312</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12092,25 +12094,25 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0.07556199999999999</v>
+        <v>0.06334</v>
       </c>
       <c r="F288" s="7">
-        <v>0.068697</v>
+        <v>0.039812</v>
       </c>
       <c r="G288" s="7">
-        <v>0.286599</v>
+        <v>0.269549</v>
       </c>
       <c r="H288" s="7">
-        <v>0.165578</v>
+        <v>0.152334</v>
       </c>
       <c r="I288" s="7">
-        <v>0.508626</v>
+        <v>0.502089</v>
       </c>
       <c r="J288" s="7">
-        <v>2.4396809999999998</v>
+        <v>2.457043</v>
       </c>
       <c r="K288" s="7">
-        <v>10.476984</v>
+        <v>10.382892</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12127,25 +12129,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.054458</v>
+        <v>0.030177</v>
       </c>
       <c r="F289" s="7">
-        <v>-0.103354</v>
+        <v>-0.157105</v>
       </c>
       <c r="G289" s="7">
-        <v>0.271727</v>
+        <v>0.246839</v>
       </c>
       <c r="H289" s="7">
-        <v>0.112779</v>
+        <v>0.087156</v>
       </c>
       <c r="I289" s="7">
-        <v>0.786603</v>
+        <v>0.745125</v>
       </c>
       <c r="J289" s="7">
-        <v>4.266465999999999</v>
+        <v>4.136573</v>
       </c>
       <c r="K289" s="7">
-        <v>8.525508</v>
+        <v>8.303238</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12162,25 +12164,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.096991</v>
+        <v>0.08445399999999999</v>
       </c>
       <c r="F290" s="7">
-        <v>0.08690099999999999</v>
+        <v>0.049613</v>
       </c>
       <c r="G290" s="7">
-        <v>0.264287</v>
+        <v>0.248329</v>
       </c>
       <c r="H290" s="7">
-        <v>0.217622</v>
+        <v>0.203707</v>
       </c>
       <c r="I290" s="7">
-        <v>0.37378700000000004</v>
+        <v>0.377105</v>
       </c>
       <c r="J290" s="7">
-        <v>2.511073</v>
+        <v>2.544364</v>
       </c>
       <c r="K290" s="7">
-        <v>12.760313000000002</v>
+        <v>12.665700999999999</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12197,25 +12199,25 @@
         <v>4</v>
       </c>
       <c r="E291" s="7">
-        <v>0.054611</v>
+        <v>0.051099</v>
       </c>
       <c r="F291" s="7">
-        <v>0.074362</v>
+        <v>0.061765</v>
       </c>
       <c r="G291" s="7">
-        <v>0.236115</v>
+        <v>0.22919499999999998</v>
       </c>
       <c r="H291" s="7">
-        <v>0.165599</v>
+        <v>0.161718</v>
       </c>
       <c r="I291" s="7">
-        <v>0.5563750000000001</v>
+        <v>0.5538839999999999</v>
       </c>
       <c r="J291" s="7">
-        <v>2.392724</v>
+        <v>2.407349</v>
       </c>
       <c r="K291" s="7">
-        <v>6.338695</v>
+        <v>6.326496</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12232,25 +12234,25 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0.098</v>
+        <v>0.08553100000000001</v>
       </c>
       <c r="F292" s="7">
-        <v>0.079462</v>
+        <v>0.057176</v>
       </c>
       <c r="G292" s="7">
-        <v>0.24787700000000001</v>
+        <v>0.230781</v>
       </c>
       <c r="H292" s="7">
-        <v>0.187759</v>
+        <v>0.174269</v>
       </c>
       <c r="I292" s="7">
-        <v>0.513202</v>
+        <v>0.5002</v>
       </c>
       <c r="J292" s="7">
-        <v>2.727819</v>
+        <v>2.734679</v>
       </c>
       <c r="K292" s="7">
-        <v>8.503459</v>
+        <v>8.436207000000001</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12267,25 +12269,25 @@
         <v>4</v>
       </c>
       <c r="E293" s="7">
-        <v>0.048511</v>
+        <v>0.043113</v>
       </c>
       <c r="F293" s="7">
-        <v>0.06856</v>
+        <v>0.056822</v>
       </c>
       <c r="G293" s="7">
-        <v>0.229354</v>
+        <v>0.221951</v>
       </c>
       <c r="H293" s="7">
-        <v>0.12073600000000001</v>
+        <v>0.11496600000000001</v>
       </c>
       <c r="I293" s="7">
-        <v>0.40848799999999996</v>
+        <v>0.402962</v>
       </c>
       <c r="J293" s="7">
-        <v>1.418054</v>
+        <v>1.41887</v>
       </c>
       <c r="K293" s="7">
-        <v>4.136533</v>
+        <v>4.113663</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12302,25 +12304,25 @@
         <v>4</v>
       </c>
       <c r="E294" s="7">
-        <v>0.043972</v>
+        <v>0.038692000000000004</v>
       </c>
       <c r="F294" s="7">
-        <v>0.019864</v>
+        <v>0.009253</v>
       </c>
       <c r="G294" s="7">
-        <v>0.203243</v>
+        <v>0.196006</v>
       </c>
       <c r="H294" s="7">
-        <v>0.052858999999999996</v>
+        <v>0.047533000000000006</v>
       </c>
       <c r="I294" s="7">
-        <v>0.39549</v>
+        <v>0.39219000000000004</v>
       </c>
       <c r="J294" s="7">
-        <v>1.69654</v>
+        <v>1.701641</v>
       </c>
       <c r="K294" s="7">
-        <v>4.841341</v>
+        <v>4.815098</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12337,25 +12339,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.119321</v>
+        <v>0.103406</v>
       </c>
       <c r="F295" s="7">
-        <v>0.099931</v>
+        <v>0.057405</v>
       </c>
       <c r="G295" s="7">
-        <v>0.323029</v>
+        <v>0.303324</v>
       </c>
       <c r="H295" s="7">
-        <v>0.25981000000000004</v>
+        <v>0.24189699999999997</v>
       </c>
       <c r="I295" s="7">
-        <v>0.551799</v>
+        <v>0.539277</v>
       </c>
       <c r="J295" s="7">
-        <v>3.560048</v>
+        <v>3.611979</v>
       </c>
       <c r="K295" s="7">
-        <v>16.071493</v>
+        <v>15.918267</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12372,25 +12374,25 @@
         <v>5</v>
       </c>
       <c r="E296" s="7">
-        <v>0.10028100000000001</v>
+        <v>0.088881</v>
       </c>
       <c r="F296" s="7">
-        <v>0.09782099999999999</v>
+        <v>0.059364</v>
       </c>
       <c r="G296" s="7">
-        <v>0.31878799999999996</v>
+        <v>0.303307</v>
       </c>
       <c r="H296" s="7">
-        <v>0.26213000000000003</v>
+        <v>0.249053</v>
       </c>
       <c r="I296" s="7">
-        <v>0.563404</v>
+        <v>0.552773</v>
       </c>
       <c r="J296" s="7">
-        <v>3.206016</v>
+        <v>3.2528070000000002</v>
       </c>
       <c r="K296" s="7">
-        <v>10.957681000000001</v>
+        <v>10.877663</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12407,25 +12409,25 @@
         <v>4</v>
       </c>
       <c r="E297" s="7">
-        <v>0.088465</v>
+        <v>0.079651</v>
       </c>
       <c r="F297" s="7">
-        <v>0.07911</v>
+        <v>0.046467</v>
       </c>
       <c r="G297" s="7">
-        <v>0.29771000000000003</v>
+        <v>0.286211</v>
       </c>
       <c r="H297" s="7">
-        <v>0.225285</v>
+        <v>0.215364</v>
       </c>
       <c r="I297" s="7">
-        <v>0.569294</v>
+        <v>0.560723</v>
       </c>
       <c r="J297" s="7">
-        <v>3.213838</v>
+        <v>3.238388</v>
       </c>
       <c r="K297" s="7">
-        <v>9.829422</v>
+        <v>9.767267</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12442,25 +12444,25 @@
         <v>2</v>
       </c>
       <c r="E298" s="7">
-        <v>0.048575999999999994</v>
+        <v>0.045431</v>
       </c>
       <c r="F298" s="7">
-        <v>0.096584</v>
+        <v>0.089496</v>
       </c>
       <c r="G298" s="7">
-        <v>0.224036</v>
+        <v>0.217942</v>
       </c>
       <c r="H298" s="7">
-        <v>0.139625</v>
+        <v>0.136208</v>
       </c>
       <c r="I298" s="7">
-        <v>0.5178470000000001</v>
+        <v>0.511165</v>
       </c>
       <c r="J298" s="7">
-        <v>2.831998</v>
+        <v>2.8143079999999996</v>
       </c>
       <c r="K298" s="7">
-        <v>5.119123</v>
+        <v>5.097758</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12477,25 +12479,25 @@
         <v>5</v>
       </c>
       <c r="E299" s="7">
-        <v>0.104888</v>
+        <v>0.093309</v>
       </c>
       <c r="F299" s="7">
-        <v>0.123641</v>
+        <v>0.09176500000000001</v>
       </c>
       <c r="G299" s="7">
-        <v>0.337491</v>
+        <v>0.32072</v>
       </c>
       <c r="H299" s="7">
-        <v>0.270521</v>
+        <v>0.257207</v>
       </c>
       <c r="I299" s="7">
-        <v>0.655039</v>
+        <v>0.639592</v>
       </c>
       <c r="J299" s="7">
-        <v>3.154794</v>
+        <v>3.139124</v>
       </c>
       <c r="K299" s="7">
-        <v>9.801406</v>
+        <v>9.758775</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12512,25 +12514,25 @@
         <v>6</v>
       </c>
       <c r="E300" s="7">
-        <v>0.10770400000000001</v>
+        <v>0.09666999999999999</v>
       </c>
       <c r="F300" s="7">
-        <v>0.10862</v>
+        <v>0.07347000000000001</v>
       </c>
       <c r="G300" s="7">
-        <v>0.345877</v>
+        <v>0.32874699999999996</v>
       </c>
       <c r="H300" s="7">
-        <v>0.281588</v>
+        <v>0.26882100000000003</v>
       </c>
       <c r="I300" s="7">
-        <v>0.696168</v>
+        <v>0.68336</v>
       </c>
       <c r="J300" s="7">
-        <v>3.3426729999999996</v>
+        <v>3.346375</v>
       </c>
       <c r="K300" s="7">
-        <v>12.432820999999999</v>
+        <v>12.415439</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12547,25 +12549,25 @@
         <v>6</v>
       </c>
       <c r="E301" s="7">
-        <v>0.11686999999999999</v>
+        <v>0.09784599999999999</v>
       </c>
       <c r="F301" s="7">
-        <v>0.128001</v>
+        <v>0.088585</v>
       </c>
       <c r="G301" s="7">
-        <v>0.306789</v>
+        <v>0.28176</v>
       </c>
       <c r="H301" s="7">
-        <v>0.284715</v>
+        <v>0.262832</v>
       </c>
       <c r="I301" s="7">
-        <v>0.548741</v>
+        <v>0.533683</v>
       </c>
       <c r="J301" s="7">
-        <v>2.1249789999999997</v>
+        <v>2.145615</v>
       </c>
       <c r="K301" s="7">
-        <v>8.904163</v>
+        <v>8.815482</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12582,22 +12584,22 @@
         <v>4</v>
       </c>
       <c r="E302" s="7">
-        <v>0.193721</v>
+        <v>0.188643</v>
       </c>
       <c r="F302" s="7">
-        <v>0.150217</v>
+        <v>0.13959</v>
       </c>
       <c r="G302" s="7">
-        <v>0.250976</v>
+        <v>0.24570799999999998</v>
       </c>
       <c r="H302" s="7">
-        <v>0.23722300000000002</v>
+        <v>0.23195900000000003</v>
       </c>
       <c r="I302" s="7">
-        <v>0.684915</v>
+        <v>0.665423</v>
       </c>
       <c r="J302" s="7">
-        <v>3.592531</v>
+        <v>3.532641</v>
       </c>
       <c r="K302" s="7"/>
     </row>
@@ -12615,25 +12617,25 @@
         <v>5</v>
       </c>
       <c r="E303" s="7">
-        <v>0.126324</v>
+        <v>0.11395300000000001</v>
       </c>
       <c r="F303" s="7">
-        <v>0.094248</v>
+        <v>0.060964</v>
       </c>
       <c r="G303" s="7">
-        <v>0.28041</v>
+        <v>0.268196</v>
       </c>
       <c r="H303" s="7">
-        <v>0.19479500000000002</v>
+        <v>0.181672</v>
       </c>
       <c r="I303" s="7">
-        <v>0.500738</v>
+        <v>0.49763399999999997</v>
       </c>
       <c r="J303" s="7">
-        <v>2.549684</v>
+        <v>2.612876</v>
       </c>
       <c r="K303" s="7">
-        <v>11.806793</v>
+        <v>11.725957000000001</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12650,25 +12652,25 @@
         <v>6</v>
       </c>
       <c r="E304" s="7">
-        <v>0.028547</v>
+        <v>0.028283999999999997</v>
       </c>
       <c r="F304" s="7">
-        <v>0.036858</v>
+        <v>0.036141</v>
       </c>
       <c r="G304" s="7">
-        <v>0.08245699999999999</v>
+        <v>0.081988</v>
       </c>
       <c r="H304" s="7">
-        <v>0.049161</v>
+        <v>0.048892</v>
       </c>
       <c r="I304" s="7">
-        <v>0.237806</v>
+        <v>0.23449799999999998</v>
       </c>
       <c r="J304" s="7">
-        <v>1.806687</v>
+        <v>1.802284</v>
       </c>
       <c r="K304" s="7">
-        <v>5.632092</v>
+        <v>5.6693430000000005</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12685,25 +12687,25 @@
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.100771</v>
+        <v>0.082138</v>
       </c>
       <c r="F305" s="7">
-        <v>0.068811</v>
+        <v>0.037513</v>
       </c>
       <c r="G305" s="7">
-        <v>0.208712</v>
+        <v>0.18369</v>
       </c>
       <c r="H305" s="7">
-        <v>0.107226</v>
+        <v>0.088483</v>
       </c>
       <c r="I305" s="7">
-        <v>0.503596</v>
+        <v>0.492813</v>
       </c>
       <c r="J305" s="7">
-        <v>2.333581</v>
+        <v>2.353516</v>
       </c>
       <c r="K305" s="7">
-        <v>7.83732</v>
+        <v>7.713256</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12720,25 +12722,25 @@
         <v>3</v>
       </c>
       <c r="E306" s="7">
-        <v>0.043319</v>
+        <v>0.040011</v>
       </c>
       <c r="F306" s="7">
-        <v>0.08515800000000001</v>
+        <v>0.074906</v>
       </c>
       <c r="G306" s="7">
-        <v>0.21088300000000001</v>
+        <v>0.20521899999999998</v>
       </c>
       <c r="H306" s="7">
-        <v>0.141502</v>
+        <v>0.137883</v>
       </c>
       <c r="I306" s="7">
-        <v>0.46562800000000004</v>
+        <v>0.460349</v>
       </c>
       <c r="J306" s="7">
-        <v>1.958648</v>
+        <v>1.9564340000000002</v>
       </c>
       <c r="K306" s="7">
-        <v>5.2607539999999995</v>
+        <v>5.2492160000000005</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12755,25 +12757,25 @@
         <v>3</v>
       </c>
       <c r="E307" s="7">
-        <v>0.035273</v>
+        <v>0.03372</v>
       </c>
       <c r="F307" s="7">
-        <v>0.016955</v>
+        <v>0.014095</v>
       </c>
       <c r="G307" s="7">
-        <v>0.14780200000000002</v>
+        <v>0.142622</v>
       </c>
       <c r="H307" s="7">
-        <v>0.037477</v>
+        <v>0.035921</v>
       </c>
       <c r="I307" s="7">
-        <v>0.39704900000000004</v>
+        <v>0.398222</v>
       </c>
       <c r="J307" s="7">
-        <v>1.013863</v>
+        <v>1.014622</v>
       </c>
       <c r="K307" s="7">
-        <v>2.136787</v>
+        <v>2.1309970000000003</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>29.04.2026 18:48:48</t>
+    <t>30.04.2026 18:45:33</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2454,25 +2454,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.055548</v>
+        <v>0.059814</v>
       </c>
       <c r="F6" s="7">
-        <v>0.039912</v>
+        <v>0.03115</v>
       </c>
       <c r="G6" s="7">
-        <v>0.19777</v>
+        <v>0.19804</v>
       </c>
       <c r="H6" s="7">
-        <v>0.10306900000000001</v>
+        <v>0.102011</v>
       </c>
       <c r="I6" s="7">
-        <v>0.45892099999999997</v>
+        <v>0.462926</v>
       </c>
       <c r="J6" s="7">
-        <v>2.178925</v>
+        <v>2.175875</v>
       </c>
       <c r="K6" s="7">
-        <v>5.718482</v>
+        <v>5.700458</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,25 +2489,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.116214</v>
+        <v>0.118988</v>
       </c>
       <c r="F7" s="7">
-        <v>0.052167000000000005</v>
+        <v>0.057388</v>
       </c>
       <c r="G7" s="7">
-        <v>0.125806</v>
+        <v>0.124606</v>
       </c>
       <c r="H7" s="7">
-        <v>0.086655</v>
+        <v>0.085338</v>
       </c>
       <c r="I7" s="7">
-        <v>0.500601</v>
+        <v>0.499996</v>
       </c>
       <c r="J7" s="7">
-        <v>2.806612</v>
+        <v>2.801996</v>
       </c>
       <c r="K7" s="7">
-        <v>5.62225</v>
+        <v>5.558279</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2524,25 +2524,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.044936</v>
+        <v>0.048826999999999995</v>
       </c>
       <c r="F8" s="7">
-        <v>0.008736</v>
+        <v>0.004514000000000001</v>
       </c>
       <c r="G8" s="7">
-        <v>0.148091</v>
+        <v>0.144531</v>
       </c>
       <c r="H8" s="7">
-        <v>0.04871400000000001</v>
+        <v>0.045252999999999995</v>
       </c>
       <c r="I8" s="7">
-        <v>0.405036</v>
+        <v>0.405194</v>
       </c>
       <c r="J8" s="7">
-        <v>1.725908</v>
+        <v>1.71691</v>
       </c>
       <c r="K8" s="7">
-        <v>3.573864</v>
+        <v>3.554258</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2559,25 +2559,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.086154</v>
+        <v>0.092647</v>
       </c>
       <c r="F9" s="7">
-        <v>0.052607999999999995</v>
+        <v>0.0421</v>
       </c>
       <c r="G9" s="7">
-        <v>0.280837</v>
+        <v>0.292412</v>
       </c>
       <c r="H9" s="7">
-        <v>0.238046</v>
+        <v>0.24371099999999998</v>
       </c>
       <c r="I9" s="7">
-        <v>0.53092</v>
+        <v>0.548105</v>
       </c>
       <c r="J9" s="7">
-        <v>3.083613</v>
+        <v>3.1022969999999996</v>
       </c>
       <c r="K9" s="7">
-        <v>10.454377999999998</v>
+        <v>10.427442000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,25 +2594,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.003895</v>
+        <v>-0.013467</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.12430300000000001</v>
+        <v>-0.104514</v>
       </c>
       <c r="G10" s="7">
-        <v>0.115451</v>
+        <v>0.122463</v>
       </c>
       <c r="H10" s="7">
-        <v>0.028898999999999998</v>
+        <v>0.024965</v>
       </c>
       <c r="I10" s="7">
-        <v>0.510806</v>
+        <v>0.489529</v>
       </c>
       <c r="J10" s="7">
-        <v>4.009746</v>
+        <v>3.99059</v>
       </c>
       <c r="K10" s="7">
-        <v>13.626793</v>
+        <v>13.557797</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2629,25 +2629,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.112149</v>
+        <v>0.119696</v>
       </c>
       <c r="F11" s="7">
-        <v>0.066556</v>
+        <v>0.044676</v>
       </c>
       <c r="G11" s="7">
-        <v>0.3193</v>
+        <v>0.331982</v>
       </c>
       <c r="H11" s="7">
-        <v>0.274972</v>
+        <v>0.279583</v>
       </c>
       <c r="I11" s="7">
-        <v>0.56329</v>
+        <v>0.588449</v>
       </c>
       <c r="J11" s="7">
-        <v>2.717987</v>
+        <v>2.7314350000000003</v>
       </c>
       <c r="K11" s="7">
-        <v>12.939045</v>
+        <v>12.813725999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2664,25 +2664,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.051308999999999994</v>
+        <v>0.052402</v>
       </c>
       <c r="F12" s="7">
-        <v>0.077114</v>
+        <v>0.067442</v>
       </c>
       <c r="G12" s="7">
-        <v>0.239819</v>
+        <v>0.240868</v>
       </c>
       <c r="H12" s="7">
-        <v>0.143033</v>
+        <v>0.143373</v>
       </c>
       <c r="I12" s="7">
-        <v>0.49149299999999996</v>
+        <v>0.493692</v>
       </c>
       <c r="J12" s="7">
-        <v>2.670312</v>
+        <v>2.671404</v>
       </c>
       <c r="K12" s="7">
-        <v>4.548625</v>
+        <v>4.54772</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,25 +2699,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.107876</v>
+        <v>0.123475</v>
       </c>
       <c r="F13" s="7">
-        <v>0.087743</v>
+        <v>0.05888</v>
       </c>
       <c r="G13" s="7">
-        <v>0.347503</v>
+        <v>0.361541</v>
       </c>
       <c r="H13" s="7">
-        <v>0.285705</v>
+        <v>0.29254</v>
       </c>
       <c r="I13" s="7">
-        <v>0.583549</v>
+        <v>0.603976</v>
       </c>
       <c r="J13" s="7">
-        <v>2.8199310000000004</v>
+        <v>2.840237</v>
       </c>
       <c r="K13" s="7">
-        <v>10.487581</v>
+        <v>10.42055</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,25 +2734,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.064762</v>
+        <v>0.068647</v>
       </c>
       <c r="F14" s="7">
-        <v>0.01886</v>
+        <v>0.00703</v>
       </c>
       <c r="G14" s="7">
-        <v>0.258126</v>
+        <v>0.257907</v>
       </c>
       <c r="H14" s="7">
-        <v>0.17457</v>
+        <v>0.175438</v>
       </c>
       <c r="I14" s="7">
-        <v>0.467862</v>
+        <v>0.476225</v>
       </c>
       <c r="J14" s="7">
-        <v>2.657304</v>
+        <v>2.660005</v>
       </c>
       <c r="K14" s="7">
-        <v>8.111453000000001</v>
+        <v>8.068914</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,25 +2769,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.045324</v>
+        <v>0.04917099999999999</v>
       </c>
       <c r="F15" s="7">
-        <v>0.023048000000000003</v>
+        <v>0.015684</v>
       </c>
       <c r="G15" s="7">
-        <v>0.185649</v>
+        <v>0.185159</v>
       </c>
       <c r="H15" s="7">
-        <v>0.077802</v>
+        <v>0.076545</v>
       </c>
       <c r="I15" s="7">
-        <v>0.413865</v>
+        <v>0.416852</v>
       </c>
       <c r="J15" s="7">
-        <v>2.017057</v>
+        <v>2.013537</v>
       </c>
       <c r="K15" s="7">
-        <v>5.528891</v>
+        <v>5.512803</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,25 +2804,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.045515999999999994</v>
+        <v>0.048984</v>
       </c>
       <c r="F16" s="7">
-        <v>0.085915</v>
+        <v>0.081056</v>
       </c>
       <c r="G16" s="7">
-        <v>0.218534</v>
+        <v>0.219774</v>
       </c>
       <c r="H16" s="7">
-        <v>0.134915</v>
+        <v>0.136383</v>
       </c>
       <c r="I16" s="7">
-        <v>0.509962</v>
+        <v>0.511446</v>
       </c>
       <c r="J16" s="7">
-        <v>2.781554</v>
+        <v>2.786443</v>
       </c>
       <c r="K16" s="7">
-        <v>5.041907</v>
+        <v>5.0467189999999995</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2839,25 +2839,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.035851</v>
+        <v>0.039199000000000005</v>
       </c>
       <c r="F17" s="7">
-        <v>0.075973</v>
+        <v>0.072127</v>
       </c>
       <c r="G17" s="7">
-        <v>0.18543800000000002</v>
+        <v>0.190665</v>
       </c>
       <c r="H17" s="7">
-        <v>0.127475</v>
+        <v>0.130337</v>
       </c>
       <c r="I17" s="7">
-        <v>0.417381</v>
+        <v>0.4202</v>
       </c>
       <c r="J17" s="7">
-        <v>1.6569</v>
+        <v>1.663646</v>
       </c>
       <c r="K17" s="7">
-        <v>4.515279</v>
+        <v>4.522729</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,25 +2874,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>0.005801</v>
+        <v>-0.004746</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.12253</v>
+        <v>-0.10573600000000001</v>
       </c>
       <c r="G18" s="7">
-        <v>0.168873</v>
+        <v>0.180748</v>
       </c>
       <c r="H18" s="7">
-        <v>0.050747999999999995</v>
+        <v>0.0471</v>
       </c>
       <c r="I18" s="7">
-        <v>0.613468</v>
+        <v>0.601783</v>
       </c>
       <c r="J18" s="7">
-        <v>4.757208</v>
+        <v>4.737217</v>
       </c>
       <c r="K18" s="7">
-        <v>15.902171000000001</v>
+        <v>15.829338</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,25 +2909,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.065307</v>
+        <v>0.07281699999999999</v>
       </c>
       <c r="F19" s="7">
-        <v>0.037815</v>
+        <v>0.032625</v>
       </c>
       <c r="G19" s="7">
-        <v>0.20958100000000002</v>
+        <v>0.197729</v>
       </c>
       <c r="H19" s="7">
-        <v>0.107356</v>
+        <v>0.106525</v>
       </c>
       <c r="I19" s="7">
-        <v>0.427677</v>
+        <v>0.432729</v>
       </c>
       <c r="J19" s="7">
-        <v>2.1771700000000003</v>
+        <v>2.174786</v>
       </c>
       <c r="K19" s="7">
-        <v>6.944279</v>
+        <v>6.9094489999999995</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2944,25 +2944,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.043461</v>
+        <v>0.042817</v>
       </c>
       <c r="F20" s="7">
-        <v>0.08739599999999999</v>
+        <v>0.082866</v>
       </c>
       <c r="G20" s="7">
-        <v>0.236041</v>
+        <v>0.235043</v>
       </c>
       <c r="H20" s="7">
-        <v>0.086552</v>
+        <v>0.086936</v>
       </c>
       <c r="I20" s="7">
-        <v>0.466666</v>
+        <v>0.46701099999999995</v>
       </c>
       <c r="J20" s="7">
-        <v>1.471787</v>
+        <v>1.4726599999999999</v>
       </c>
       <c r="K20" s="7">
-        <v>4.1970220000000005</v>
+        <v>4.185661</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,25 +2979,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.041307</v>
+        <v>0.044393</v>
       </c>
       <c r="F21" s="7">
-        <v>0.09130699999999999</v>
+        <v>0.08556</v>
       </c>
       <c r="G21" s="7">
-        <v>0.211373</v>
+        <v>0.213297</v>
       </c>
       <c r="H21" s="7">
-        <v>0.146359</v>
+        <v>0.148171</v>
       </c>
       <c r="I21" s="7">
-        <v>0.451832</v>
+        <v>0.45356</v>
       </c>
       <c r="J21" s="7">
-        <v>1.817244</v>
+        <v>1.8216990000000002</v>
       </c>
       <c r="K21" s="7">
-        <v>5.030542</v>
+        <v>5.027375</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,25 +3014,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.112174</v>
+        <v>0.11699299999999999</v>
       </c>
       <c r="F22" s="7">
-        <v>0.083012</v>
+        <v>0.071982</v>
       </c>
       <c r="G22" s="7">
-        <v>0.25254899999999997</v>
+        <v>0.2566</v>
       </c>
       <c r="H22" s="7">
-        <v>0.24154499999999998</v>
+        <v>0.24096499999999998</v>
       </c>
       <c r="I22" s="7">
-        <v>0.579625</v>
+        <v>0.581307</v>
       </c>
       <c r="J22" s="7">
-        <v>2.814516</v>
+        <v>2.812733</v>
       </c>
       <c r="K22" s="7">
-        <v>10.834833000000001</v>
+        <v>10.734571</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,25 +3049,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.027268</v>
+        <v>0.027376</v>
       </c>
       <c r="F23" s="7">
-        <v>0.080891</v>
+        <v>0.07894899999999999</v>
       </c>
       <c r="G23" s="7">
-        <v>0.183094</v>
+        <v>0.18239</v>
       </c>
       <c r="H23" s="7">
-        <v>0.11661099999999999</v>
+        <v>0.11751099999999999</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40732799999999997</v>
+        <v>0.40882599999999997</v>
       </c>
       <c r="J23" s="7">
-        <v>2.168707</v>
+        <v>2.171261</v>
       </c>
       <c r="K23" s="7">
-        <v>4.998791</v>
+        <v>5.0017059999999995</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3084,25 +3084,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.046036</v>
+        <v>0.048838999999999994</v>
       </c>
       <c r="F24" s="7">
-        <v>0.00853</v>
+        <v>0.006827</v>
       </c>
       <c r="G24" s="7">
-        <v>0.141931</v>
+        <v>0.138529</v>
       </c>
       <c r="H24" s="7">
-        <v>0.037705999999999996</v>
+        <v>0.03438</v>
       </c>
       <c r="I24" s="7">
-        <v>0.39309399999999994</v>
+        <v>0.389529</v>
       </c>
       <c r="J24" s="7">
-        <v>1.597867</v>
+        <v>1.589541</v>
       </c>
       <c r="K24" s="7">
-        <v>3.438195</v>
+        <v>3.420255</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,25 +3119,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.045034</v>
+        <v>0.04258</v>
       </c>
       <c r="F25" s="7">
-        <v>0.038274</v>
+        <v>0.036789999999999996</v>
       </c>
       <c r="G25" s="7">
-        <v>0.117143</v>
+        <v>0.116537</v>
       </c>
       <c r="H25" s="7">
-        <v>0.052969999999999996</v>
+        <v>0.051229</v>
       </c>
       <c r="I25" s="7">
-        <v>0.347421</v>
+        <v>0.344375</v>
       </c>
       <c r="J25" s="7">
-        <v>2.103355</v>
+        <v>2.098225</v>
       </c>
       <c r="K25" s="7">
-        <v>6.520935</v>
+        <v>6.499043</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,25 +3154,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.046231</v>
+        <v>0.047179</v>
       </c>
       <c r="F26" s="7">
-        <v>0.012524</v>
+        <v>0.015493</v>
       </c>
       <c r="G26" s="7">
-        <v>0.110153</v>
+        <v>0.112306</v>
       </c>
       <c r="H26" s="7">
-        <v>0.048919</v>
+        <v>0.049236</v>
       </c>
       <c r="I26" s="7">
-        <v>0.304681</v>
+        <v>0.30075199999999996</v>
       </c>
       <c r="J26" s="7">
-        <v>2.0466409999999997</v>
+        <v>2.0475630000000002</v>
       </c>
       <c r="K26" s="7">
-        <v>5.669697</v>
+        <v>5.644679</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3189,25 +3189,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.08210100000000001</v>
+        <v>0.088824</v>
       </c>
       <c r="F27" s="7">
-        <v>0.02167</v>
+        <v>-0.015434000000000002</v>
       </c>
       <c r="G27" s="7">
-        <v>0.227153</v>
+        <v>0.228342</v>
       </c>
       <c r="H27" s="7">
-        <v>0.183755</v>
+        <v>0.180114</v>
       </c>
       <c r="I27" s="7">
-        <v>0.396785</v>
+        <v>0.407488</v>
       </c>
       <c r="J27" s="7">
-        <v>3.2820370000000003</v>
+        <v>3.268866</v>
       </c>
       <c r="K27" s="7">
-        <v>16.28605</v>
+        <v>16.073108</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,25 +3224,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.110474</v>
+        <v>0.11343199999999999</v>
       </c>
       <c r="F28" s="7">
-        <v>0.037858</v>
+        <v>0.037835</v>
       </c>
       <c r="G28" s="7">
-        <v>0.127955</v>
+        <v>0.124627</v>
       </c>
       <c r="H28" s="7">
-        <v>0.103187</v>
+        <v>0.10151199999999999</v>
       </c>
       <c r="I28" s="7">
-        <v>0.419813</v>
+        <v>0.422094</v>
       </c>
       <c r="J28" s="7">
-        <v>2.582957</v>
+        <v>2.577515</v>
       </c>
       <c r="K28" s="7">
-        <v>8.013611</v>
+        <v>7.962211999999999</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3259,25 +3259,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.035411</v>
+        <v>0.036441</v>
       </c>
       <c r="F29" s="7">
-        <v>0.05351</v>
+        <v>0.046288</v>
       </c>
       <c r="G29" s="7">
-        <v>0.172636</v>
+        <v>0.172052</v>
       </c>
       <c r="H29" s="7">
-        <v>0.095771</v>
+        <v>0.095463</v>
       </c>
       <c r="I29" s="7">
-        <v>0.40558999999999995</v>
+        <v>0.406671</v>
       </c>
       <c r="J29" s="7">
-        <v>2.402227</v>
+        <v>2.401274</v>
       </c>
       <c r="K29" s="7">
-        <v>4.562324</v>
+        <v>4.558415</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3294,25 +3294,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.04698</v>
+        <v>0.053228</v>
       </c>
       <c r="F30" s="7">
-        <v>0.027606000000000002</v>
+        <v>0.004019</v>
       </c>
       <c r="G30" s="7">
-        <v>0.190518</v>
+        <v>0.19177499999999997</v>
       </c>
       <c r="H30" s="7">
-        <v>0.141042</v>
+        <v>0.140897</v>
       </c>
       <c r="I30" s="7">
-        <v>0.377653</v>
+        <v>0.385021</v>
       </c>
       <c r="J30" s="7">
-        <v>3.029141</v>
+        <v>3.028631</v>
       </c>
       <c r="K30" s="7">
-        <v>9.469059999999999</v>
+        <v>9.430741000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,25 +3329,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.10321799999999999</v>
+        <v>0.114711</v>
       </c>
       <c r="F31" s="7">
-        <v>0.029654</v>
+        <v>-0.004476</v>
       </c>
       <c r="G31" s="7">
-        <v>0.23129100000000002</v>
+        <v>0.235024</v>
       </c>
       <c r="H31" s="7">
-        <v>0.19486699999999998</v>
+        <v>0.19736499999999998</v>
       </c>
       <c r="I31" s="7">
-        <v>0.350067</v>
+        <v>0.369646</v>
       </c>
       <c r="J31" s="7">
-        <v>2.5796660000000005</v>
+        <v>2.5871519999999997</v>
       </c>
       <c r="K31" s="7">
-        <v>14.832321</v>
+        <v>14.727048</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3364,25 +3364,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.031244</v>
+        <v>0.030886999999999998</v>
       </c>
       <c r="F32" s="7">
-        <v>0.08627800000000001</v>
+        <v>0.08332700000000001</v>
       </c>
       <c r="G32" s="7">
-        <v>0.192884</v>
+        <v>0.193397</v>
       </c>
       <c r="H32" s="7">
-        <v>0.113724</v>
+        <v>0.114746</v>
       </c>
       <c r="I32" s="7">
-        <v>0.45258000000000004</v>
+        <v>0.451134</v>
       </c>
       <c r="J32" s="7">
-        <v>2.153362</v>
+        <v>2.156255</v>
       </c>
       <c r="K32" s="7">
-        <v>3.7241269999999997</v>
+        <v>3.726568</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3399,25 +3399,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.067471</v>
+        <v>0.072322</v>
       </c>
       <c r="F33" s="7">
-        <v>0.033778999999999997</v>
+        <v>0.0058330000000000005</v>
       </c>
       <c r="G33" s="7">
-        <v>0.234288</v>
+        <v>0.23604</v>
       </c>
       <c r="H33" s="7">
-        <v>0.169612</v>
+        <v>0.166496</v>
       </c>
       <c r="I33" s="7">
-        <v>0.44052</v>
+        <v>0.447082</v>
       </c>
       <c r="J33" s="7">
-        <v>3.4873849999999997</v>
+        <v>3.4754300000000002</v>
       </c>
       <c r="K33" s="7">
-        <v>16.531323</v>
+        <v>16.347299</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3434,25 +3434,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.09641400000000001</v>
+        <v>0.106394</v>
       </c>
       <c r="F34" s="7">
-        <v>0.094559</v>
+        <v>0.093912</v>
       </c>
       <c r="G34" s="7">
-        <v>0.32311799999999996</v>
+        <v>0.338235</v>
       </c>
       <c r="H34" s="7">
-        <v>0.263818</v>
+        <v>0.273173</v>
       </c>
       <c r="I34" s="7">
-        <v>0.636687</v>
+        <v>0.6535</v>
       </c>
       <c r="J34" s="7">
-        <v>3.1577699999999997</v>
+        <v>3.1885449999999995</v>
       </c>
       <c r="K34" s="7">
-        <v>9.768415</v>
+        <v>9.801642000000001</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3469,25 +3469,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.097607</v>
+        <v>0.108139</v>
       </c>
       <c r="F35" s="7">
-        <v>0.07583999999999999</v>
+        <v>0.08099</v>
       </c>
       <c r="G35" s="7">
-        <v>0.328755</v>
+        <v>0.344587</v>
       </c>
       <c r="H35" s="7">
-        <v>0.26925699999999997</v>
+        <v>0.278802</v>
       </c>
       <c r="I35" s="7">
-        <v>0.688035</v>
+        <v>0.706906</v>
       </c>
       <c r="J35" s="7">
-        <v>3.352088</v>
+        <v>3.384819</v>
       </c>
       <c r="K35" s="7">
-        <v>12.302696000000001</v>
+        <v>12.325814000000001</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3504,25 +3504,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.069965</v>
+        <v>0.073895</v>
       </c>
       <c r="F36" s="7">
-        <v>0.037886</v>
+        <v>0.009889</v>
       </c>
       <c r="G36" s="7">
-        <v>0.24370799999999998</v>
+        <v>0.245014</v>
       </c>
       <c r="H36" s="7">
-        <v>0.181755</v>
+        <v>0.178444</v>
       </c>
       <c r="I36" s="7">
-        <v>0.46366799999999997</v>
+        <v>0.46972400000000003</v>
       </c>
       <c r="J36" s="7">
-        <v>3.593673</v>
+        <v>3.5808030000000004</v>
       </c>
       <c r="K36" s="7">
-        <v>17.289585</v>
+        <v>17.089394</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3539,25 +3539,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.061753</v>
+        <v>0.059375</v>
       </c>
       <c r="F37" s="7">
-        <v>0.043158</v>
+        <v>0.014785</v>
       </c>
       <c r="G37" s="7">
-        <v>0.251355</v>
+        <v>0.246134</v>
       </c>
       <c r="H37" s="7">
-        <v>0.164424</v>
+        <v>0.15784399999999998</v>
       </c>
       <c r="I37" s="7">
-        <v>0.457961</v>
+        <v>0.46135</v>
       </c>
       <c r="J37" s="7">
-        <v>3.68186</v>
+        <v>3.6554020000000005</v>
       </c>
       <c r="K37" s="7">
-        <v>15.630354</v>
+        <v>15.435925</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3574,25 +3574,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.041410999999999996</v>
+        <v>0.042566</v>
       </c>
       <c r="F38" s="7">
-        <v>0.03343</v>
+        <v>0.013988</v>
       </c>
       <c r="G38" s="7">
-        <v>0.21604099999999998</v>
+        <v>0.214588</v>
       </c>
       <c r="H38" s="7">
-        <v>0.142192</v>
+        <v>0.139239</v>
       </c>
       <c r="I38" s="7">
-        <v>0.448954</v>
+        <v>0.45446800000000004</v>
       </c>
       <c r="J38" s="7">
-        <v>3.519602</v>
+        <v>3.507917</v>
       </c>
       <c r="K38" s="7">
-        <v>11.556228</v>
+        <v>11.481747</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3609,25 +3609,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.03211</v>
+        <v>0.030496</v>
       </c>
       <c r="F39" s="7">
-        <v>0.062389</v>
+        <v>0.054254</v>
       </c>
       <c r="G39" s="7">
-        <v>0.192291</v>
+        <v>0.188407</v>
       </c>
       <c r="H39" s="7">
-        <v>0.113739</v>
+        <v>0.111816</v>
       </c>
       <c r="I39" s="7">
-        <v>0.460177</v>
+        <v>0.457992</v>
       </c>
       <c r="J39" s="7">
-        <v>2.9408390000000004</v>
+        <v>2.934036</v>
       </c>
       <c r="K39" s="7">
-        <v>5.671753</v>
+        <v>5.661404</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,25 +3644,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.082378</v>
+        <v>0.087658</v>
       </c>
       <c r="F40" s="7">
-        <v>0.10842299999999999</v>
+        <v>0.098191</v>
       </c>
       <c r="G40" s="7">
-        <v>0.300525</v>
+        <v>0.302183</v>
       </c>
       <c r="H40" s="7">
-        <v>0.229941</v>
+        <v>0.231347</v>
       </c>
       <c r="I40" s="7">
-        <v>0.603098</v>
+        <v>0.609173</v>
       </c>
       <c r="J40" s="7">
-        <v>3.390644</v>
+        <v>3.395661</v>
       </c>
       <c r="K40" s="7">
-        <v>11.748692</v>
+        <v>11.682041</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3679,25 +3679,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.064946</v>
+        <v>0.070437</v>
       </c>
       <c r="F41" s="7">
-        <v>0.10012</v>
+        <v>0.090938</v>
       </c>
       <c r="G41" s="7">
-        <v>0.279312</v>
+        <v>0.27943999999999997</v>
       </c>
       <c r="H41" s="7">
-        <v>0.206465</v>
+        <v>0.20717300000000002</v>
       </c>
       <c r="I41" s="7">
-        <v>0.589951</v>
+        <v>0.593446</v>
       </c>
       <c r="J41" s="7">
-        <v>3.1121879999999997</v>
+        <v>3.1146</v>
       </c>
       <c r="K41" s="7">
-        <v>10.004953</v>
+        <v>9.962586</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,25 +3714,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.08855</v>
+        <v>0.095429</v>
       </c>
       <c r="F42" s="7">
-        <v>0.055248</v>
+        <v>0.048133999999999996</v>
       </c>
       <c r="G42" s="7">
-        <v>0.294535</v>
+        <v>0.307713</v>
       </c>
       <c r="H42" s="7">
-        <v>0.242788</v>
+        <v>0.250309</v>
       </c>
       <c r="I42" s="7">
-        <v>0.549941</v>
+        <v>0.569894</v>
       </c>
       <c r="J42" s="7">
-        <v>3.1194</v>
+        <v>3.14433</v>
       </c>
       <c r="K42" s="7">
-        <v>10.873842999999999</v>
+        <v>10.856817000000001</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3749,25 +3749,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.079916</v>
+        <v>0.08055999999999999</v>
       </c>
       <c r="F43" s="7">
-        <v>0.021063000000000002</v>
+        <v>-0.01294</v>
       </c>
       <c r="G43" s="7">
-        <v>0.244057</v>
+        <v>0.242225</v>
       </c>
       <c r="H43" s="7">
-        <v>0.17707699999999998</v>
+        <v>0.172619</v>
       </c>
       <c r="I43" s="7">
-        <v>0.45521</v>
+        <v>0.458523</v>
       </c>
       <c r="J43" s="7">
-        <v>4.022273</v>
+        <v>4.003253</v>
       </c>
       <c r="K43" s="7">
-        <v>21.417638</v>
+        <v>21.154042</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3784,25 +3784,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.043289</v>
+        <v>0.044391</v>
       </c>
       <c r="F44" s="7">
-        <v>0.063394</v>
+        <v>0.05744</v>
       </c>
       <c r="G44" s="7">
-        <v>0.19872499999999998</v>
+        <v>0.197921</v>
       </c>
       <c r="H44" s="7">
-        <v>0.113176</v>
+        <v>0.113252</v>
       </c>
       <c r="I44" s="7">
-        <v>0.475954</v>
+        <v>0.475697</v>
       </c>
       <c r="J44" s="7">
-        <v>2.442594</v>
+        <v>2.44283</v>
       </c>
       <c r="K44" s="7">
-        <v>4.445805</v>
+        <v>4.444146</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3819,25 +3819,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.07222</v>
+        <v>0.077908</v>
       </c>
       <c r="F45" s="7">
-        <v>0.05373700000000001</v>
+        <v>0.050148</v>
       </c>
       <c r="G45" s="7">
-        <v>0.280508</v>
+        <v>0.287964</v>
       </c>
       <c r="H45" s="7">
-        <v>0.207926</v>
+        <v>0.21454399999999998</v>
       </c>
       <c r="I45" s="7">
-        <v>0.559337</v>
+        <v>0.57696</v>
       </c>
       <c r="J45" s="7">
-        <v>3.212889</v>
+        <v>3.23597</v>
       </c>
       <c r="K45" s="7">
-        <v>9.525205</v>
+        <v>9.529091</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3854,25 +3854,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.070066</v>
+        <v>0.074555</v>
       </c>
       <c r="F46" s="7">
-        <v>0.11036699999999999</v>
+        <v>0.100075</v>
       </c>
       <c r="G46" s="7">
-        <v>0.3068</v>
+        <v>0.30396999999999996</v>
       </c>
       <c r="H46" s="7">
-        <v>0.240917</v>
+        <v>0.24084499999999998</v>
       </c>
       <c r="I46" s="7">
-        <v>0.604024</v>
+        <v>0.609088</v>
       </c>
       <c r="J46" s="7">
-        <v>3.4977620000000003</v>
+        <v>3.4974979999999998</v>
       </c>
       <c r="K46" s="7">
-        <v>10.302041999999998</v>
+        <v>10.247300000000001</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3889,25 +3889,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.084797</v>
+        <v>0.092604</v>
       </c>
       <c r="F47" s="7">
-        <v>0.094079</v>
+        <v>0.08380800000000001</v>
       </c>
       <c r="G47" s="7">
-        <v>0.296375</v>
+        <v>0.30017099999999997</v>
       </c>
       <c r="H47" s="7">
-        <v>0.239199</v>
+        <v>0.24152</v>
       </c>
       <c r="I47" s="7">
-        <v>0.591295</v>
+        <v>0.599044</v>
       </c>
       <c r="J47" s="7">
-        <v>3.548039</v>
+        <v>3.5565589999999996</v>
       </c>
       <c r="K47" s="7">
-        <v>13.342174</v>
+        <v>13.268092</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3924,25 +3924,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.056655</v>
+        <v>0.066537</v>
       </c>
       <c r="F48" s="7">
-        <v>0.006444999999999999</v>
+        <v>-0.015325</v>
       </c>
       <c r="G48" s="7">
-        <v>0.159803</v>
+        <v>0.16881000000000002</v>
       </c>
       <c r="H48" s="7">
-        <v>0.13714600000000002</v>
+        <v>0.141265</v>
       </c>
       <c r="I48" s="7">
-        <v>0.435308</v>
+        <v>0.438169</v>
       </c>
       <c r="J48" s="7">
-        <v>1.806054</v>
+        <v>1.816219</v>
       </c>
       <c r="K48" s="7">
-        <v>10.217352</v>
+        <v>10.200609</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3959,25 +3959,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.10246499999999999</v>
+        <v>0.10843799999999999</v>
       </c>
       <c r="F49" s="7">
-        <v>0.058313</v>
+        <v>0.040701999999999995</v>
       </c>
       <c r="G49" s="7">
-        <v>0.312216</v>
+        <v>0.320059</v>
       </c>
       <c r="H49" s="7">
-        <v>0.24638100000000002</v>
+        <v>0.249822</v>
       </c>
       <c r="I49" s="7">
-        <v>0.555887</v>
+        <v>0.5754509999999999</v>
       </c>
       <c r="J49" s="7">
-        <v>3.665521</v>
+        <v>3.678404</v>
       </c>
       <c r="K49" s="7">
-        <v>16.106084</v>
+        <v>15.982069</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3994,25 +3994,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.118203</v>
+        <v>0.120694</v>
       </c>
       <c r="F50" s="7">
-        <v>0.058055</v>
+        <v>0.052803</v>
       </c>
       <c r="G50" s="7">
-        <v>0.151639</v>
+        <v>0.147595</v>
       </c>
       <c r="H50" s="7">
-        <v>0.116504</v>
+        <v>0.11505000000000001</v>
       </c>
       <c r="I50" s="7">
-        <v>0.534961</v>
+        <v>0.5379849999999999</v>
       </c>
       <c r="J50" s="7">
-        <v>3.0334980000000002</v>
+        <v>3.028245</v>
       </c>
       <c r="K50" s="7">
-        <v>8.965287</v>
+        <v>8.923124</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,25 +4029,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.058621999999999994</v>
+        <v>0.060894000000000004</v>
       </c>
       <c r="F51" s="7">
-        <v>0.019258</v>
+        <v>0.00481</v>
       </c>
       <c r="G51" s="7">
-        <v>0.18713999999999997</v>
+        <v>0.186931</v>
       </c>
       <c r="H51" s="7">
-        <v>0.12449199999999999</v>
+        <v>0.122707</v>
       </c>
       <c r="I51" s="7">
-        <v>0.366203</v>
+        <v>0.37127699999999997</v>
       </c>
       <c r="J51" s="7">
-        <v>2.5442009999999997</v>
+        <v>2.538574</v>
       </c>
       <c r="K51" s="7">
-        <v>8.131417</v>
+        <v>8.087619</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.107775</v>
+        <v>0.117024</v>
       </c>
       <c r="F52" s="7">
-        <v>0.028222</v>
+        <v>0.004181000000000001</v>
       </c>
       <c r="G52" s="7">
-        <v>0.263933</v>
+        <v>0.274486</v>
       </c>
       <c r="H52" s="7">
-        <v>0.194891</v>
+        <v>0.19603</v>
       </c>
       <c r="I52" s="7">
-        <v>0.468974</v>
+        <v>0.48170900000000005</v>
       </c>
       <c r="J52" s="7">
-        <v>2.719981</v>
+        <v>2.7235270000000003</v>
       </c>
       <c r="K52" s="7">
-        <v>11.008715</v>
+        <v>10.951318</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4099,25 +4099,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.062205</v>
+        <v>0.060506000000000004</v>
       </c>
       <c r="F53" s="7">
-        <v>0.029759</v>
+        <v>0.030621999999999996</v>
       </c>
       <c r="G53" s="7">
-        <v>0.09517300000000001</v>
+        <v>0.095118</v>
       </c>
       <c r="H53" s="7">
-        <v>0.044101</v>
+        <v>0.042327000000000004</v>
       </c>
       <c r="I53" s="7">
-        <v>0.343221</v>
+        <v>0.33921500000000004</v>
       </c>
       <c r="J53" s="7">
-        <v>2.176726</v>
+        <v>2.171327</v>
       </c>
       <c r="K53" s="7">
-        <v>6.537256999999999</v>
+        <v>6.517974000000001</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4134,25 +4134,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.047270000000000006</v>
+        <v>0.045811000000000004</v>
       </c>
       <c r="F54" s="7">
-        <v>0.034998999999999995</v>
+        <v>0.034419</v>
       </c>
       <c r="G54" s="7">
-        <v>0.097172</v>
+        <v>0.096948</v>
       </c>
       <c r="H54" s="7">
-        <v>0.051578</v>
+        <v>0.050563000000000004</v>
       </c>
       <c r="I54" s="7">
-        <v>0.30679</v>
+        <v>0.305153</v>
       </c>
       <c r="J54" s="7">
-        <v>2.056856</v>
+        <v>2.053906</v>
       </c>
       <c r="K54" s="7">
-        <v>6.352445</v>
+        <v>6.3406709999999995</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4169,25 +4169,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.014464</v>
+        <v>0.000057999999999999994</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.124864</v>
+        <v>-0.10612500000000001</v>
       </c>
       <c r="G55" s="7">
-        <v>0.153104</v>
+        <v>0.17023700000000003</v>
       </c>
       <c r="H55" s="7">
-        <v>0.061867</v>
+        <v>0.058569</v>
       </c>
       <c r="I55" s="7">
-        <v>0.590984</v>
+        <v>0.576095</v>
       </c>
       <c r="J55" s="7">
-        <v>3.903587</v>
+        <v>3.8883609999999997</v>
       </c>
       <c r="K55" s="7">
-        <v>13.194327000000001</v>
+        <v>13.135737999999998</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4204,25 +4204,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.07699399999999999</v>
+        <v>0.077961</v>
       </c>
       <c r="F56" s="7">
-        <v>0.06940299999999999</v>
+        <v>0.05526</v>
       </c>
       <c r="G56" s="7">
-        <v>0.239962</v>
+        <v>0.233804</v>
       </c>
       <c r="H56" s="7">
-        <v>0.143656</v>
+        <v>0.140951</v>
       </c>
       <c r="I56" s="7">
-        <v>0.47584000000000004</v>
+        <v>0.47463900000000003</v>
       </c>
       <c r="J56" s="7">
-        <v>2.066637</v>
+        <v>2.059383</v>
       </c>
       <c r="K56" s="7">
-        <v>5.692188</v>
+        <v>5.6543280000000005</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4239,25 +4239,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.04918</v>
+        <v>0.050875000000000004</v>
       </c>
       <c r="F57" s="7">
-        <v>0.00022700000000000002</v>
+        <v>-0.010737000000000002</v>
       </c>
       <c r="G57" s="7">
-        <v>0.133777</v>
+        <v>0.127529</v>
       </c>
       <c r="H57" s="7">
-        <v>0.06464500000000001</v>
+        <v>0.060629</v>
       </c>
       <c r="I57" s="7">
-        <v>0.36789499999999997</v>
+        <v>0.368344</v>
       </c>
       <c r="J57" s="7">
-        <v>1.35464</v>
+        <v>1.345757</v>
       </c>
       <c r="K57" s="7">
-        <v>3.582614</v>
+        <v>3.550681</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4274,25 +4274,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.08060200000000001</v>
+        <v>0.08637800000000001</v>
       </c>
       <c r="F58" s="7">
-        <v>0.050323</v>
+        <v>0.044457</v>
       </c>
       <c r="G58" s="7">
-        <v>0.29081</v>
+        <v>0.299237</v>
       </c>
       <c r="H58" s="7">
-        <v>0.21974900000000003</v>
+        <v>0.225851</v>
       </c>
       <c r="I58" s="7">
-        <v>0.565241</v>
+        <v>0.581907</v>
       </c>
       <c r="J58" s="7">
-        <v>3.192892</v>
+        <v>3.213866</v>
       </c>
       <c r="K58" s="7">
-        <v>9.612776</v>
+        <v>9.612512</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4309,25 +4309,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.088924</v>
+        <v>0.095883</v>
       </c>
       <c r="F59" s="7">
-        <v>0.05944</v>
+        <v>0.052017</v>
       </c>
       <c r="G59" s="7">
-        <v>0.305531</v>
+        <v>0.317337</v>
       </c>
       <c r="H59" s="7">
-        <v>0.24712900000000002</v>
+        <v>0.254371</v>
       </c>
       <c r="I59" s="7">
-        <v>0.558075</v>
+        <v>0.577628</v>
       </c>
       <c r="J59" s="7">
-        <v>3.2274950000000002</v>
+        <v>3.2520460000000004</v>
       </c>
       <c r="K59" s="7">
-        <v>10.755074</v>
+        <v>10.736658</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4344,25 +4344,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.08631</v>
+        <v>0.093351</v>
       </c>
       <c r="F60" s="7">
-        <v>0.026395</v>
+        <v>-0.00023300000000000003</v>
       </c>
       <c r="G60" s="7">
-        <v>0.21593800000000002</v>
+        <v>0.21229800000000001</v>
       </c>
       <c r="H60" s="7">
-        <v>0.17854199999999998</v>
+        <v>0.17340499999999998</v>
       </c>
       <c r="I60" s="7">
-        <v>0.41033299999999995</v>
+        <v>0.410614</v>
       </c>
       <c r="J60" s="7">
-        <v>2.441367</v>
+        <v>2.426367</v>
       </c>
       <c r="K60" s="7">
-        <v>13.121297</v>
+        <v>12.907238</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,25 +4379,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.099068</v>
+        <v>0.109756</v>
       </c>
       <c r="F61" s="7">
-        <v>0.05605400000000001</v>
+        <v>0.040554</v>
       </c>
       <c r="G61" s="7">
-        <v>0.20389</v>
+        <v>0.20721</v>
       </c>
       <c r="H61" s="7">
-        <v>0.162735</v>
+        <v>0.164016</v>
       </c>
       <c r="I61" s="7">
-        <v>0.498251</v>
+        <v>0.506471</v>
       </c>
       <c r="J61" s="7">
-        <v>2.406539</v>
+        <v>2.4102930000000002</v>
       </c>
       <c r="K61" s="7">
-        <v>7.74111</v>
+        <v>7.667809999999999</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,25 +4414,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.066611</v>
+        <v>0.074947</v>
       </c>
       <c r="F62" s="7">
-        <v>0.021808</v>
+        <v>-0.04616</v>
       </c>
       <c r="G62" s="7">
-        <v>0.17748999999999998</v>
+        <v>0.164086</v>
       </c>
       <c r="H62" s="7">
-        <v>0.145791</v>
+        <v>0.137017</v>
       </c>
       <c r="I62" s="7">
-        <v>0.34886</v>
+        <v>0.353819</v>
       </c>
       <c r="J62" s="7">
-        <v>2.416637</v>
+        <v>2.390474</v>
       </c>
       <c r="K62" s="7">
-        <v>12.417800999999999</v>
+        <v>12.150658</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4449,25 +4449,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.053458</v>
+        <v>0.058410000000000004</v>
       </c>
       <c r="F63" s="7">
-        <v>0.014018999999999998</v>
+        <v>0.0053690000000000005</v>
       </c>
       <c r="G63" s="7">
-        <v>0.178064</v>
+        <v>0.17816500000000002</v>
       </c>
       <c r="H63" s="7">
-        <v>0.084082</v>
+        <v>0.08247600000000001</v>
       </c>
       <c r="I63" s="7">
-        <v>0.408178</v>
+        <v>0.409653</v>
       </c>
       <c r="J63" s="7">
-        <v>1.918532</v>
+        <v>1.9142080000000001</v>
       </c>
       <c r="K63" s="7">
-        <v>4.670522</v>
+        <v>4.649539</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4484,25 +4484,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.041304</v>
+        <v>0.03465</v>
       </c>
       <c r="F64" s="7">
-        <v>-0.020585</v>
+        <v>-0.017641</v>
       </c>
       <c r="G64" s="7">
-        <v>0.170987</v>
+        <v>0.17122800000000002</v>
       </c>
       <c r="H64" s="7">
-        <v>0.128377</v>
+        <v>0.12759</v>
       </c>
       <c r="I64" s="7">
-        <v>0.383761</v>
+        <v>0.38214</v>
       </c>
       <c r="J64" s="7">
-        <v>2.035165</v>
+        <v>2.033047</v>
       </c>
       <c r="K64" s="7">
-        <v>6.117795999999999</v>
+        <v>6.094595000000001</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,25 +4519,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.042421</v>
+        <v>0.037842</v>
       </c>
       <c r="F65" s="7">
-        <v>0.043247</v>
+        <v>0.041783</v>
       </c>
       <c r="G65" s="7">
-        <v>0.10156499999999999</v>
+        <v>0.104518</v>
       </c>
       <c r="H65" s="7">
-        <v>0.059939</v>
+        <v>0.058666</v>
       </c>
       <c r="I65" s="7">
-        <v>0.29662299999999997</v>
+        <v>0.290511</v>
       </c>
       <c r="J65" s="7">
-        <v>2.084155</v>
+        <v>2.080451</v>
       </c>
       <c r="K65" s="7">
-        <v>5.381398000000001</v>
+        <v>5.3475909999999995</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4554,25 +4554,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.054421</v>
+        <v>0.05257100000000001</v>
       </c>
       <c r="F66" s="7">
-        <v>0.03318</v>
+        <v>0.034967</v>
       </c>
       <c r="G66" s="7">
-        <v>0.090917</v>
+        <v>0.090648</v>
       </c>
       <c r="H66" s="7">
-        <v>0.040304</v>
+        <v>0.038467</v>
       </c>
       <c r="I66" s="7">
-        <v>0.324664</v>
+        <v>0.321748</v>
       </c>
       <c r="J66" s="7">
-        <v>2.292662</v>
+        <v>2.286848</v>
       </c>
       <c r="K66" s="7">
-        <v>6.847349</v>
+        <v>6.795286</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4589,25 +4589,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.069672</v>
+        <v>0.06807</v>
       </c>
       <c r="F67" s="7">
-        <v>0.038475999999999996</v>
+        <v>0.028812</v>
       </c>
       <c r="G67" s="7">
-        <v>0.246338</v>
+        <v>0.25572</v>
       </c>
       <c r="H67" s="7">
-        <v>0.19069400000000003</v>
+        <v>0.18834499999999998</v>
       </c>
       <c r="I67" s="7">
-        <v>0.552946</v>
+        <v>0.552889</v>
       </c>
       <c r="J67" s="7">
-        <v>2.5638929999999998</v>
+        <v>2.556862</v>
       </c>
       <c r="K67" s="7">
-        <v>9.485654</v>
+        <v>9.419381</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4624,25 +4624,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.046496</v>
+        <v>0.045175</v>
       </c>
       <c r="F68" s="7">
-        <v>0.032706</v>
+        <v>0.034447</v>
       </c>
       <c r="G68" s="7">
-        <v>0.092816</v>
+        <v>0.09234400000000001</v>
       </c>
       <c r="H68" s="7">
-        <v>0.046289</v>
+        <v>0.044966</v>
       </c>
       <c r="I68" s="7">
-        <v>0.297443</v>
+        <v>0.295022</v>
       </c>
       <c r="J68" s="7">
-        <v>2.070116</v>
+        <v>2.066234</v>
       </c>
       <c r="K68" s="7">
-        <v>6.212976</v>
+        <v>6.174874</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4659,25 +4659,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.064873</v>
+        <v>0.071876</v>
       </c>
       <c r="F69" s="7">
-        <v>0.037797</v>
+        <v>0.031054</v>
       </c>
       <c r="G69" s="7">
-        <v>0.20714200000000002</v>
+        <v>0.208725</v>
       </c>
       <c r="H69" s="7">
-        <v>0.12078900000000001</v>
+        <v>0.12135199999999999</v>
       </c>
       <c r="I69" s="7">
-        <v>0.471347</v>
+        <v>0.479612</v>
       </c>
       <c r="J69" s="7">
-        <v>2.17771</v>
+        <v>2.179306</v>
       </c>
       <c r="K69" s="7">
-        <v>5.545006</v>
+        <v>5.528265</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,25 +4694,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.031326</v>
+        <v>0.031349999999999996</v>
       </c>
       <c r="F70" s="7">
-        <v>0.09466</v>
+        <v>0.09151</v>
       </c>
       <c r="G70" s="7">
-        <v>0.200268</v>
+        <v>0.200334</v>
       </c>
       <c r="H70" s="7">
-        <v>0.124457</v>
+        <v>0.125633</v>
       </c>
       <c r="I70" s="7">
-        <v>0.4806</v>
+        <v>0.48039000000000004</v>
       </c>
       <c r="J70" s="7">
-        <v>2.340813</v>
+        <v>2.344308</v>
       </c>
       <c r="K70" s="7">
-        <v>4.047559</v>
+        <v>4.050433</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4729,25 +4729,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.224415</v>
+        <v>0.239862</v>
       </c>
       <c r="F71" s="7">
-        <v>0.07724400000000001</v>
+        <v>0.116579</v>
       </c>
       <c r="G71" s="7">
-        <v>0.136955</v>
+        <v>0.155796</v>
       </c>
       <c r="H71" s="7">
-        <v>0.153839</v>
+        <v>0.166383</v>
       </c>
       <c r="I71" s="7">
-        <v>0.670999</v>
+        <v>0.690736</v>
       </c>
       <c r="J71" s="7">
-        <v>3.659652</v>
+        <v>3.710308</v>
       </c>
       <c r="K71" s="7">
-        <v>7.577223</v>
+        <v>7.658041</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4764,25 +4764,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.044811</v>
+        <v>0.04856099999999999</v>
       </c>
       <c r="F72" s="7">
-        <v>0.07129400000000001</v>
+        <v>0.071409</v>
       </c>
       <c r="G72" s="7">
-        <v>0.224148</v>
+        <v>0.22896899999999998</v>
       </c>
       <c r="H72" s="7">
-        <v>0.135601</v>
+        <v>0.139066</v>
       </c>
       <c r="I72" s="7">
-        <v>0.452415</v>
+        <v>0.457356</v>
       </c>
       <c r="J72" s="7">
-        <v>1.746971</v>
+        <v>1.755354</v>
       </c>
       <c r="K72" s="7">
-        <v>4.6536480000000005</v>
+        <v>4.6642079999999995</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,25 +4799,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.05961</v>
+        <v>0.053811</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.01772</v>
+        <v>-0.018352999999999998</v>
       </c>
       <c r="G73" s="7">
-        <v>0.040534999999999995</v>
+        <v>0.039384</v>
       </c>
       <c r="H73" s="7">
-        <v>-0.008234</v>
+        <v>-0.010813</v>
       </c>
       <c r="I73" s="7">
-        <v>0.27400800000000003</v>
+        <v>0.269025</v>
       </c>
       <c r="J73" s="7">
-        <v>2.013935</v>
+        <v>2.0060990000000003</v>
       </c>
       <c r="K73" s="7">
-        <v>6.108777</v>
+        <v>6.0839229999999995</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,25 +4834,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.103796</v>
+        <v>0.115339</v>
       </c>
       <c r="F74" s="7">
-        <v>0.030731</v>
+        <v>-0.0034260000000000002</v>
       </c>
       <c r="G74" s="7">
-        <v>0.23672100000000001</v>
+        <v>0.240555</v>
       </c>
       <c r="H74" s="7">
-        <v>0.19630299999999998</v>
+        <v>0.198845</v>
       </c>
       <c r="I74" s="7">
-        <v>0.358797</v>
+        <v>0.378049</v>
       </c>
       <c r="J74" s="7">
-        <v>2.611955</v>
+        <v>2.6196289999999998</v>
       </c>
       <c r="K74" s="7">
-        <v>15.038806999999998</v>
+        <v>14.933343</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4869,25 +4869,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.041898</v>
+        <v>0.045023</v>
       </c>
       <c r="F75" s="7">
-        <v>0.007256</v>
+        <v>0.0032979999999999997</v>
       </c>
       <c r="G75" s="7">
-        <v>0.163936</v>
+        <v>0.160996</v>
       </c>
       <c r="H75" s="7">
-        <v>0.048841</v>
+        <v>0.046432</v>
       </c>
       <c r="I75" s="7">
-        <v>0.420931</v>
+        <v>0.419143</v>
       </c>
       <c r="J75" s="7">
-        <v>1.7919239999999999</v>
+        <v>1.7855109999999998</v>
       </c>
       <c r="K75" s="7">
-        <v>3.7090410000000005</v>
+        <v>3.6906130000000004</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,25 +4904,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.062279</v>
+        <v>0.067526</v>
       </c>
       <c r="F76" s="7">
-        <v>0.036876</v>
+        <v>0.030445000000000003</v>
       </c>
       <c r="G76" s="7">
-        <v>0.209543</v>
+        <v>0.21144200000000002</v>
       </c>
       <c r="H76" s="7">
-        <v>0.121217</v>
+        <v>0.12226200000000001</v>
       </c>
       <c r="I76" s="7">
-        <v>0.478622</v>
+        <v>0.487292</v>
       </c>
       <c r="J76" s="7">
-        <v>2.2207310000000002</v>
+        <v>2.223734</v>
       </c>
       <c r="K76" s="7">
-        <v>5.634789</v>
+        <v>5.620322</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4939,25 +4939,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.04101200000000001</v>
+        <v>0.038003999999999996</v>
       </c>
       <c r="F77" s="7">
-        <v>0.062104999999999994</v>
+        <v>0.061137</v>
       </c>
       <c r="G77" s="7">
-        <v>0.266573</v>
+        <v>0.27716799999999997</v>
       </c>
       <c r="H77" s="7">
-        <v>0.181528</v>
+        <v>0.17928</v>
       </c>
       <c r="I77" s="7">
-        <v>0.41154</v>
+        <v>0.40739400000000003</v>
       </c>
       <c r="J77" s="7">
-        <v>1.881138</v>
+        <v>1.875658</v>
       </c>
       <c r="K77" s="7">
-        <v>5.485023999999999</v>
+        <v>5.448827</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4974,25 +4974,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="7">
-        <v>0.0762</v>
+        <v>0.071476</v>
       </c>
       <c r="F78" s="7">
-        <v>0.077851</v>
+        <v>0.080672</v>
       </c>
       <c r="G78" s="7">
-        <v>0.33163800000000004</v>
+        <v>0.32665500000000003</v>
       </c>
       <c r="H78" s="7">
-        <v>0.236573</v>
+        <v>0.236506</v>
       </c>
       <c r="I78" s="7">
-        <v>0.6575449999999999</v>
+        <v>0.665611</v>
       </c>
       <c r="J78" s="7">
-        <v>2.834047</v>
+        <v>2.8338400000000004</v>
       </c>
       <c r="K78" s="7">
-        <v>8.390611999999999</v>
+        <v>8.328493</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5009,25 +5009,25 @@
         <v>5</v>
       </c>
       <c r="E79" s="7">
-        <v>0.06581000000000001</v>
+        <v>0.070283</v>
       </c>
       <c r="F79" s="7">
-        <v>0.070382</v>
+        <v>0.062218</v>
       </c>
       <c r="G79" s="7">
-        <v>0.166448</v>
+        <v>0.164073</v>
       </c>
       <c r="H79" s="7">
-        <v>0.150512</v>
+        <v>0.149735</v>
       </c>
       <c r="I79" s="7">
-        <v>0.413427</v>
+        <v>0.41286900000000004</v>
       </c>
       <c r="J79" s="7">
-        <v>2.343982</v>
+        <v>2.341723</v>
       </c>
       <c r="K79" s="7">
-        <v>7.987858</v>
+        <v>7.962582</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,25 +5044,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.11264400000000001</v>
+        <v>0.12256</v>
       </c>
       <c r="F80" s="7">
-        <v>0.057009</v>
+        <v>0.019785</v>
       </c>
       <c r="G80" s="7">
-        <v>0.23072800000000002</v>
+        <v>0.23241</v>
       </c>
       <c r="H80" s="7">
-        <v>0.230006</v>
+        <v>0.22974699999999998</v>
       </c>
       <c r="I80" s="7">
-        <v>0.397727</v>
+        <v>0.41103700000000004</v>
       </c>
       <c r="J80" s="7">
-        <v>2.360855</v>
+        <v>2.360147</v>
       </c>
       <c r="K80" s="7">
-        <v>11.361244999999998</v>
+        <v>11.244314</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5079,25 +5079,25 @@
         <v>4</v>
       </c>
       <c r="E81" s="7">
-        <v>0.034437999999999996</v>
+        <v>0.034598</v>
       </c>
       <c r="F81" s="7">
-        <v>0.064477</v>
+        <v>0.060239</v>
       </c>
       <c r="G81" s="7">
-        <v>0.174695</v>
+        <v>0.172163</v>
       </c>
       <c r="H81" s="7">
-        <v>0.115302</v>
+        <v>0.11444499999999999</v>
       </c>
       <c r="I81" s="7">
-        <v>0.37660400000000005</v>
+        <v>0.376471</v>
       </c>
       <c r="J81" s="7">
-        <v>1.5232990000000002</v>
+        <v>1.521361</v>
       </c>
       <c r="K81" s="7">
-        <v>4.372672</v>
+        <v>4.368844</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,25 +5114,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.043258</v>
+        <v>0.045260999999999996</v>
       </c>
       <c r="F82" s="7">
-        <v>0.0017449999999999998</v>
+        <v>-0.00109</v>
       </c>
       <c r="G82" s="7">
-        <v>0.134428</v>
+        <v>0.12934400000000001</v>
       </c>
       <c r="H82" s="7">
-        <v>0.04176</v>
+        <v>0.038483</v>
       </c>
       <c r="I82" s="7">
-        <v>0.387367</v>
+        <v>0.385788</v>
       </c>
       <c r="J82" s="7">
-        <v>1.4811189999999999</v>
+        <v>1.4733150000000002</v>
       </c>
       <c r="K82" s="7">
-        <v>3.118596</v>
+        <v>3.10115</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5149,25 +5149,25 @@
         <v>5</v>
       </c>
       <c r="E83" s="7">
-        <v>0.07279</v>
+        <v>0.07692700000000001</v>
       </c>
       <c r="F83" s="7">
-        <v>0.060621</v>
+        <v>0.05592</v>
       </c>
       <c r="G83" s="7">
-        <v>0.16727799999999998</v>
+        <v>0.163611</v>
       </c>
       <c r="H83" s="7">
-        <v>0.159045</v>
+        <v>0.15792</v>
       </c>
       <c r="I83" s="7">
-        <v>0.413184</v>
+        <v>0.412943</v>
       </c>
       <c r="J83" s="7">
-        <v>2.3658959999999998</v>
+        <v>2.362629</v>
       </c>
       <c r="K83" s="7">
-        <v>8.979583</v>
+        <v>8.946284</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,22 +5184,22 @@
         <v>6</v>
       </c>
       <c r="E84" s="7">
-        <v>0.007372999999999999</v>
+        <v>-0.0052829999999999995</v>
       </c>
       <c r="F84" s="7">
-        <v>-0.131426</v>
+        <v>-0.117392</v>
       </c>
       <c r="G84" s="7">
-        <v>0.1215</v>
+        <v>0.12222899999999999</v>
       </c>
       <c r="H84" s="7">
-        <v>0.013496999999999999</v>
+        <v>0.008111</v>
       </c>
       <c r="I84" s="7">
-        <v>0.628998</v>
+        <v>0.610614</v>
       </c>
       <c r="J84" s="7">
-        <v>3.764612</v>
+        <v>3.739292</v>
       </c>
       <c r="K84" s="7"/>
     </row>
@@ -5217,19 +5217,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="7">
-        <v>0.030441</v>
+        <v>0.030476</v>
       </c>
       <c r="F85" s="7">
-        <v>0.094041</v>
+        <v>0.091057</v>
       </c>
       <c r="G85" s="7">
-        <v>0.196233</v>
+        <v>0.19625199999999998</v>
       </c>
       <c r="H85" s="7">
-        <v>0.122735</v>
+        <v>0.123977</v>
       </c>
       <c r="I85" s="7">
-        <v>0.464875</v>
+        <v>0.464959</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5248,22 +5248,22 @@
         <v>6</v>
       </c>
       <c r="E86" s="7">
-        <v>0.108498</v>
+        <v>0.114963</v>
       </c>
       <c r="F86" s="7">
-        <v>0.057481</v>
+        <v>0.034554999999999995</v>
       </c>
       <c r="G86" s="7">
-        <v>0.25348400000000004</v>
+        <v>0.258959</v>
       </c>
       <c r="H86" s="7">
-        <v>0.200318</v>
+        <v>0.19966899999999999</v>
       </c>
       <c r="I86" s="7">
-        <v>0.549919</v>
+        <v>0.5562469999999999</v>
       </c>
       <c r="J86" s="7">
-        <v>2.7761180000000003</v>
+        <v>2.774076</v>
       </c>
       <c r="K86" s="7"/>
     </row>
@@ -5281,22 +5281,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.152661</v>
+        <v>0.152562</v>
       </c>
       <c r="F87" s="7">
-        <v>0.199188</v>
+        <v>0.220499</v>
       </c>
       <c r="G87" s="7">
-        <v>0.312257</v>
+        <v>0.304162</v>
       </c>
       <c r="H87" s="7">
-        <v>0.317119</v>
+        <v>0.327944</v>
       </c>
       <c r="I87" s="7">
-        <v>0.6945910000000001</v>
+        <v>0.705989</v>
       </c>
       <c r="J87" s="7">
-        <v>3.9364179999999998</v>
+        <v>3.9769889999999997</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,25 +5314,25 @@
         <v>7</v>
       </c>
       <c r="E88" s="7">
-        <v>0.014306000000000001</v>
+        <v>0.000517</v>
       </c>
       <c r="F88" s="7">
-        <v>-0.122338</v>
+        <v>-0.110335</v>
       </c>
       <c r="G88" s="7">
-        <v>0.170652</v>
+        <v>0.188466</v>
       </c>
       <c r="H88" s="7">
-        <v>0.069323</v>
+        <v>0.065965</v>
       </c>
       <c r="I88" s="7">
-        <v>0.615413</v>
+        <v>0.601645</v>
       </c>
       <c r="J88" s="7">
-        <v>4.129580000000001</v>
+        <v>4.113475</v>
       </c>
       <c r="K88" s="7">
-        <v>14.093544999999999</v>
+        <v>14.030733</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5349,25 +5349,25 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>0.034819</v>
+        <v>0.035228999999999996</v>
       </c>
       <c r="F89" s="7">
-        <v>0.091776</v>
+        <v>0.089365</v>
       </c>
       <c r="G89" s="7">
-        <v>0.20624199999999998</v>
+        <v>0.205676</v>
       </c>
       <c r="H89" s="7">
-        <v>0.128633</v>
+        <v>0.12948</v>
       </c>
       <c r="I89" s="7">
-        <v>0.511525</v>
+        <v>0.514527</v>
       </c>
       <c r="J89" s="7">
-        <v>2.386428</v>
+        <v>2.38897</v>
       </c>
       <c r="K89" s="7">
-        <v>4.320354</v>
+        <v>4.320883</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5384,25 +5384,25 @@
         <v>5</v>
       </c>
       <c r="E90" s="7">
-        <v>0.044369</v>
+        <v>0.04533</v>
       </c>
       <c r="F90" s="7">
-        <v>0.017459</v>
+        <v>0.006226000000000001</v>
       </c>
       <c r="G90" s="7">
-        <v>0.16636399999999998</v>
+        <v>0.161799</v>
       </c>
       <c r="H90" s="7">
-        <v>0.082411</v>
+        <v>0.078945</v>
       </c>
       <c r="I90" s="7">
-        <v>0.305934</v>
+        <v>0.30674</v>
       </c>
       <c r="J90" s="7">
-        <v>2.028045</v>
+        <v>2.01835</v>
       </c>
       <c r="K90" s="7">
-        <v>5.431038999999999</v>
+        <v>5.406464</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5419,22 +5419,22 @@
         <v>6</v>
       </c>
       <c r="E91" s="7">
-        <v>0.061718999999999996</v>
+        <v>0.062224</v>
       </c>
       <c r="F91" s="7">
-        <v>0.055729</v>
+        <v>0.03395</v>
       </c>
       <c r="G91" s="7">
-        <v>0.225664</v>
+        <v>0.239777</v>
       </c>
       <c r="H91" s="7">
-        <v>0.16791899999999998</v>
+        <v>0.16649899999999998</v>
       </c>
       <c r="I91" s="7">
-        <v>0.429813</v>
+        <v>0.430303</v>
       </c>
       <c r="J91" s="7">
-        <v>2.553504</v>
+        <v>2.549185</v>
       </c>
       <c r="K91" s="7"/>
     </row>
@@ -5452,25 +5452,25 @@
         <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>0.052077</v>
+        <v>0.054634999999999996</v>
       </c>
       <c r="F92" s="7">
-        <v>0.017419</v>
+        <v>0.005159</v>
       </c>
       <c r="G92" s="7">
-        <v>0.197017</v>
+        <v>0.19350799999999999</v>
       </c>
       <c r="H92" s="7">
-        <v>0.09447</v>
+        <v>0.091195</v>
       </c>
       <c r="I92" s="7">
-        <v>0.347885</v>
+        <v>0.35214</v>
       </c>
       <c r="J92" s="7">
-        <v>1.987935</v>
+        <v>1.9789949999999998</v>
       </c>
       <c r="K92" s="7">
-        <v>4.960882</v>
+        <v>4.928026</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,25 +5487,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.038347</v>
+        <v>0.038395</v>
       </c>
       <c r="F93" s="7">
-        <v>0.062206000000000004</v>
+        <v>0.059025</v>
       </c>
       <c r="G93" s="7">
-        <v>0.195549</v>
+        <v>0.197122</v>
       </c>
       <c r="H93" s="7">
-        <v>0.131016</v>
+        <v>0.130326</v>
       </c>
       <c r="I93" s="7">
-        <v>0.347474</v>
+        <v>0.35217</v>
       </c>
       <c r="J93" s="7">
-        <v>1.70713</v>
+        <v>1.705478</v>
       </c>
       <c r="K93" s="7">
-        <v>4.633171</v>
+        <v>4.621303</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,25 +5522,25 @@
         <v>4</v>
       </c>
       <c r="E94" s="7">
-        <v>0.066095</v>
+        <v>0.06760100000000001</v>
       </c>
       <c r="F94" s="7">
-        <v>0.031763</v>
+        <v>0.007631</v>
       </c>
       <c r="G94" s="7">
-        <v>0.26894100000000004</v>
+        <v>0.26374400000000003</v>
       </c>
       <c r="H94" s="7">
-        <v>0.16405</v>
+        <v>0.159755</v>
       </c>
       <c r="I94" s="7">
-        <v>0.49952599999999997</v>
+        <v>0.500291</v>
       </c>
       <c r="J94" s="7">
-        <v>2.793235</v>
+        <v>2.7792410000000003</v>
       </c>
       <c r="K94" s="7">
-        <v>8.37603</v>
+        <v>8.29903</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,25 +5557,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.038586</v>
+        <v>0.040453</v>
       </c>
       <c r="F95" s="7">
-        <v>0.010891999999999999</v>
+        <v>0.00577</v>
       </c>
       <c r="G95" s="7">
-        <v>0.166127</v>
+        <v>0.162963</v>
       </c>
       <c r="H95" s="7">
-        <v>0.04704</v>
+        <v>0.044152</v>
       </c>
       <c r="I95" s="7">
-        <v>0.437222</v>
+        <v>0.44085599999999997</v>
       </c>
       <c r="J95" s="7">
-        <v>1.351488</v>
+        <v>1.345004</v>
       </c>
       <c r="K95" s="7">
-        <v>2.7592939999999997</v>
+        <v>2.744436</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,25 +5592,25 @@
         <v>7</v>
       </c>
       <c r="E96" s="7">
-        <v>0.0926</v>
+        <v>0.094291</v>
       </c>
       <c r="F96" s="7">
-        <v>0.011754</v>
+        <v>-0.026334</v>
       </c>
       <c r="G96" s="7">
-        <v>0.284087</v>
+        <v>0.272251</v>
       </c>
       <c r="H96" s="7">
-        <v>0.20726299999999998</v>
+        <v>0.198773</v>
       </c>
       <c r="I96" s="7">
-        <v>0.39037900000000003</v>
+        <v>0.398649</v>
       </c>
       <c r="J96" s="7">
-        <v>2.910646</v>
+        <v>2.883143</v>
       </c>
       <c r="K96" s="7">
-        <v>15.096963</v>
+        <v>14.815677</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,25 +5627,25 @@
         <v>6</v>
       </c>
       <c r="E97" s="7">
-        <v>0.076409</v>
+        <v>0.072176</v>
       </c>
       <c r="F97" s="7">
-        <v>-0.007732</v>
+        <v>-0.042382</v>
       </c>
       <c r="G97" s="7">
-        <v>0.382698</v>
+        <v>0.37504899999999997</v>
       </c>
       <c r="H97" s="7">
-        <v>0.20073</v>
+        <v>0.197134</v>
       </c>
       <c r="I97" s="7">
-        <v>0.49311</v>
+        <v>0.506652</v>
       </c>
       <c r="J97" s="7">
-        <v>4.037209</v>
+        <v>4.0221219999999995</v>
       </c>
       <c r="K97" s="7">
-        <v>19.569942</v>
+        <v>19.323295</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,25 +5662,25 @@
         <v>4</v>
       </c>
       <c r="E98" s="7">
-        <v>0.06677</v>
+        <v>0.06953000000000001</v>
       </c>
       <c r="F98" s="7">
-        <v>0.059931</v>
+        <v>0.035166</v>
       </c>
       <c r="G98" s="7">
-        <v>0.294659</v>
+        <v>0.28769300000000003</v>
       </c>
       <c r="H98" s="7">
-        <v>0.20582899999999998</v>
+        <v>0.201909</v>
       </c>
       <c r="I98" s="7">
-        <v>0.545861</v>
+        <v>0.548542</v>
       </c>
       <c r="J98" s="7">
-        <v>3.451561</v>
+        <v>3.4370890000000003</v>
       </c>
       <c r="K98" s="7">
-        <v>9.292001</v>
+        <v>9.216228</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,25 +5697,25 @@
         <v>6</v>
       </c>
       <c r="E99" s="7">
-        <v>0.034252</v>
+        <v>0.030089</v>
       </c>
       <c r="F99" s="7">
-        <v>0.042105</v>
+        <v>0.042515</v>
       </c>
       <c r="G99" s="7">
-        <v>0.099955</v>
+        <v>0.100382</v>
       </c>
       <c r="H99" s="7">
-        <v>0.058367</v>
+        <v>0.057543</v>
       </c>
       <c r="I99" s="7">
-        <v>0.282394</v>
+        <v>0.281556</v>
       </c>
       <c r="J99" s="7">
-        <v>1.9919049999999998</v>
+        <v>1.989575</v>
       </c>
       <c r="K99" s="7">
-        <v>5.8258469999999996</v>
+        <v>5.806404</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,25 +5732,25 @@
         <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>0.07446900000000001</v>
+        <v>0.077096</v>
       </c>
       <c r="F100" s="7">
-        <v>0.054028</v>
+        <v>0.026907999999999998</v>
       </c>
       <c r="G100" s="7">
-        <v>0.355932</v>
+        <v>0.34726399999999996</v>
       </c>
       <c r="H100" s="7">
-        <v>0.213982</v>
+        <v>0.209224</v>
       </c>
       <c r="I100" s="7">
-        <v>0.588159</v>
+        <v>0.592816</v>
       </c>
       <c r="J100" s="7">
-        <v>3.684204</v>
+        <v>3.665846</v>
       </c>
       <c r="K100" s="7">
-        <v>12.329322</v>
+        <v>12.195058</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,25 +5767,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.07918599999999999</v>
+        <v>0.077518</v>
       </c>
       <c r="F101" s="7">
-        <v>0.052351</v>
+        <v>0.042213</v>
       </c>
       <c r="G101" s="7">
-        <v>0.33419899999999997</v>
+        <v>0.335394</v>
       </c>
       <c r="H101" s="7">
-        <v>0.28247900000000004</v>
+        <v>0.280416</v>
       </c>
       <c r="I101" s="7">
-        <v>0.633536</v>
+        <v>0.640467</v>
       </c>
       <c r="J101" s="7">
-        <v>3.485811</v>
+        <v>3.478593</v>
       </c>
       <c r="K101" s="7">
-        <v>11.373118</v>
+        <v>11.288764</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,25 +5802,25 @@
         <v>2</v>
       </c>
       <c r="E102" s="7">
-        <v>0.041478</v>
+        <v>0.042116</v>
       </c>
       <c r="F102" s="7">
-        <v>0.09959699999999999</v>
+        <v>0.092475</v>
       </c>
       <c r="G102" s="7">
-        <v>0.259735</v>
+        <v>0.26017399999999996</v>
       </c>
       <c r="H102" s="7">
-        <v>0.15554</v>
+        <v>0.155899</v>
       </c>
       <c r="I102" s="7">
-        <v>0.573777</v>
+        <v>0.574909</v>
       </c>
       <c r="J102" s="7">
-        <v>3.1120569999999996</v>
+        <v>3.113333</v>
       </c>
       <c r="K102" s="7">
-        <v>5.714583</v>
+        <v>5.713509</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,25 +5837,25 @@
         <v>6</v>
       </c>
       <c r="E103" s="7">
-        <v>0.084018</v>
+        <v>0.082494</v>
       </c>
       <c r="F103" s="7">
-        <v>0.036832</v>
+        <v>0.026568</v>
       </c>
       <c r="G103" s="7">
-        <v>0.337958</v>
+        <v>0.340424</v>
       </c>
       <c r="H103" s="7">
-        <v>0.297509</v>
+        <v>0.294984</v>
       </c>
       <c r="I103" s="7">
-        <v>0.6287039999999999</v>
+        <v>0.635716</v>
       </c>
       <c r="J103" s="7">
-        <v>3.380799</v>
+        <v>3.372274</v>
       </c>
       <c r="K103" s="7">
-        <v>13.488331</v>
+        <v>13.353161</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,25 +5872,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.047111</v>
+        <v>0.0412</v>
       </c>
       <c r="F104" s="7">
-        <v>0.03315</v>
+        <v>0.034079</v>
       </c>
       <c r="G104" s="7">
-        <v>0.093961</v>
+        <v>0.093661</v>
       </c>
       <c r="H104" s="7">
-        <v>0.044413999999999995</v>
+        <v>0.042588999999999995</v>
       </c>
       <c r="I104" s="7">
-        <v>0.319113</v>
+        <v>0.316244</v>
       </c>
       <c r="J104" s="7">
-        <v>2.146916</v>
+        <v>2.1414169999999997</v>
       </c>
       <c r="K104" s="7">
-        <v>6.228492</v>
+        <v>6.208518000000001</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,16 +5907,16 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.096586</v>
+        <v>0.099318</v>
       </c>
       <c r="F105" s="7">
-        <v>0.043550000000000005</v>
+        <v>0.030999</v>
       </c>
       <c r="G105" s="7">
-        <v>0.18046500000000001</v>
+        <v>0.184372</v>
       </c>
       <c r="H105" s="7">
-        <v>0.143116</v>
+        <v>0.142704</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
@@ -5936,22 +5936,22 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.183967</v>
+        <v>0.188053</v>
       </c>
       <c r="F106" s="7">
-        <v>0.15576800000000002</v>
+        <v>0.16736</v>
       </c>
       <c r="G106" s="7">
-        <v>0.290016</v>
+        <v>0.29162</v>
       </c>
       <c r="H106" s="7">
-        <v>0.28824500000000003</v>
+        <v>0.29267</v>
       </c>
       <c r="I106" s="7">
-        <v>0.788133</v>
+        <v>0.789743</v>
       </c>
       <c r="J106" s="7">
-        <v>4.101845</v>
+        <v>4.119368</v>
       </c>
       <c r="K106" s="7"/>
     </row>
@@ -5969,25 +5969,25 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.025369000000000003</v>
+        <v>0.0074399999999999996</v>
       </c>
       <c r="F107" s="7">
-        <v>-0.112112</v>
+        <v>-0.08737299999999999</v>
       </c>
       <c r="G107" s="7">
-        <v>0.19128900000000001</v>
+        <v>0.212403</v>
       </c>
       <c r="H107" s="7">
-        <v>0.102247</v>
+        <v>0.096639</v>
       </c>
       <c r="I107" s="7">
-        <v>0.6637050000000001</v>
+        <v>0.648027</v>
       </c>
       <c r="J107" s="7">
-        <v>4.842173</v>
+        <v>4.812452</v>
       </c>
       <c r="K107" s="7">
-        <v>16.263667</v>
+        <v>16.158919</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,25 +6004,25 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.045397999999999994</v>
+        <v>0.048964999999999995</v>
       </c>
       <c r="F108" s="7">
-        <v>0.032667</v>
+        <v>0.027167</v>
       </c>
       <c r="G108" s="7">
-        <v>0.186292</v>
+        <v>0.181173</v>
       </c>
       <c r="H108" s="7">
-        <v>0.072465</v>
+        <v>0.06844800000000001</v>
       </c>
       <c r="I108" s="7">
-        <v>0.47458500000000003</v>
+        <v>0.47058999999999995</v>
       </c>
       <c r="J108" s="7">
-        <v>2.0565629999999997</v>
+        <v>2.045114</v>
       </c>
       <c r="K108" s="7">
-        <v>3.901391</v>
+        <v>3.8790410000000004</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,25 +6039,25 @@
         <v>6</v>
       </c>
       <c r="E109" s="7">
-        <v>0.043684</v>
+        <v>0.039580000000000004</v>
       </c>
       <c r="F109" s="7">
-        <v>0.028736</v>
+        <v>0.024974</v>
       </c>
       <c r="G109" s="7">
-        <v>0.12395400000000001</v>
+        <v>0.123252</v>
       </c>
       <c r="H109" s="7">
-        <v>0.051913</v>
+        <v>0.050054999999999995</v>
       </c>
       <c r="I109" s="7">
-        <v>0.34368099999999996</v>
+        <v>0.34049799999999997</v>
       </c>
       <c r="J109" s="7">
-        <v>2.206902</v>
+        <v>2.20124</v>
       </c>
       <c r="K109" s="7">
-        <v>6.6830359999999995</v>
+        <v>6.658561</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,25 +6074,25 @@
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>0.045901</v>
+        <v>0.052513</v>
       </c>
       <c r="F110" s="7">
-        <v>0.070003</v>
+        <v>0.071681</v>
       </c>
       <c r="G110" s="7">
-        <v>0.196007</v>
+        <v>0.20353100000000002</v>
       </c>
       <c r="H110" s="7">
-        <v>0.145786</v>
+        <v>0.15027</v>
       </c>
       <c r="I110" s="7">
-        <v>0.465683</v>
+        <v>0.473254</v>
       </c>
       <c r="J110" s="7">
-        <v>1.951858</v>
+        <v>1.963412</v>
       </c>
       <c r="K110" s="7">
-        <v>5.489706</v>
+        <v>5.512841</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,25 +6109,25 @@
         <v>5</v>
       </c>
       <c r="E111" s="7">
-        <v>0.04638899999999999</v>
+        <v>0.048885</v>
       </c>
       <c r="F111" s="7">
-        <v>0.008409</v>
+        <v>-0.0074670000000000005</v>
       </c>
       <c r="G111" s="7">
-        <v>0.21644200000000002</v>
+        <v>0.224481</v>
       </c>
       <c r="H111" s="7">
-        <v>0.134202</v>
+        <v>0.137446</v>
       </c>
       <c r="I111" s="7">
-        <v>0.5303450000000001</v>
+        <v>0.541188</v>
       </c>
       <c r="J111" s="7">
-        <v>3.4748419999999998</v>
+        <v>3.4876389999999997</v>
       </c>
       <c r="K111" s="7">
-        <v>14.552251000000002</v>
+        <v>14.527748999999998</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,25 +6144,25 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>0.038254</v>
+        <v>0.039818</v>
       </c>
       <c r="F112" s="7">
-        <v>0.079234</v>
+        <v>0.076107</v>
       </c>
       <c r="G112" s="7">
-        <v>0.237073</v>
+        <v>0.235592</v>
       </c>
       <c r="H112" s="7">
-        <v>0.137612</v>
+        <v>0.137223</v>
       </c>
       <c r="I112" s="7">
-        <v>0.5322330000000001</v>
+        <v>0.530347</v>
       </c>
       <c r="J112" s="7">
-        <v>3.27531</v>
+        <v>3.27385</v>
       </c>
       <c r="K112" s="7">
-        <v>6.266621</v>
+        <v>6.260082</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6179,25 +6179,25 @@
         <v>6</v>
       </c>
       <c r="E113" s="7">
-        <v>0.09922800000000001</v>
+        <v>0.106643</v>
       </c>
       <c r="F113" s="7">
-        <v>0.077154</v>
+        <v>0.06430799999999999</v>
       </c>
       <c r="G113" s="7">
-        <v>0.268347</v>
+        <v>0.278119</v>
       </c>
       <c r="H113" s="7">
-        <v>0.228996</v>
+        <v>0.23116599999999998</v>
       </c>
       <c r="I113" s="7">
-        <v>0.538346</v>
+        <v>0.552341</v>
       </c>
       <c r="J113" s="7">
-        <v>3.360093</v>
+        <v>3.367793</v>
       </c>
       <c r="K113" s="7">
-        <v>16.803811</v>
+        <v>16.797027</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6214,25 +6214,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.08781599999999999</v>
+        <v>0.090286</v>
       </c>
       <c r="F114" s="7">
-        <v>0.018965</v>
+        <v>-0.014576</v>
       </c>
       <c r="G114" s="7">
-        <v>0.247707</v>
+        <v>0.24140999999999999</v>
       </c>
       <c r="H114" s="7">
-        <v>0.16774999999999998</v>
+        <v>0.16270099999999998</v>
       </c>
       <c r="I114" s="7">
-        <v>0.51627</v>
+        <v>0.518404</v>
       </c>
       <c r="J114" s="7">
-        <v>3.3340410000000005</v>
+        <v>3.315304</v>
       </c>
       <c r="K114" s="7">
-        <v>22.866030000000002</v>
+        <v>22.560011</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6249,25 +6249,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.093363</v>
+        <v>0.10476</v>
       </c>
       <c r="F115" s="7">
-        <v>0.046627</v>
+        <v>0.017686</v>
       </c>
       <c r="G115" s="7">
-        <v>0.26787</v>
+        <v>0.275463</v>
       </c>
       <c r="H115" s="7">
-        <v>0.20194099999999998</v>
+        <v>0.204876</v>
       </c>
       <c r="I115" s="7">
-        <v>0.527934</v>
+        <v>0.547192</v>
       </c>
       <c r="J115" s="7">
-        <v>2.824489</v>
+        <v>2.83383</v>
       </c>
       <c r="K115" s="7">
-        <v>16.218173</v>
+        <v>16.08219</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6284,25 +6284,25 @@
         <v>5</v>
       </c>
       <c r="E116" s="7">
-        <v>0.07696900000000001</v>
+        <v>0.08515</v>
       </c>
       <c r="F116" s="7">
-        <v>0.086524</v>
+        <v>0.08110400000000001</v>
       </c>
       <c r="G116" s="7">
-        <v>0.274073</v>
+        <v>0.286208</v>
       </c>
       <c r="H116" s="7">
-        <v>0.238338</v>
+        <v>0.243586</v>
       </c>
       <c r="I116" s="7">
-        <v>0.624178</v>
+        <v>0.638746</v>
       </c>
       <c r="J116" s="7">
-        <v>3.216703</v>
+        <v>3.2345729999999997</v>
       </c>
       <c r="K116" s="7">
-        <v>12.284599</v>
+        <v>12.324745</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6319,25 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>0.043587</v>
+        <v>0.046525</v>
       </c>
       <c r="F117" s="7">
-        <v>0.028703</v>
+        <v>0.023756</v>
       </c>
       <c r="G117" s="7">
-        <v>0.182527</v>
+        <v>0.177474</v>
       </c>
       <c r="H117" s="7">
-        <v>0.066341</v>
+        <v>0.062363</v>
       </c>
       <c r="I117" s="7">
-        <v>0.44453699999999996</v>
+        <v>0.44109299999999996</v>
       </c>
       <c r="J117" s="7">
-        <v>1.880514</v>
+        <v>1.869767</v>
       </c>
       <c r="K117" s="7">
-        <v>3.69999</v>
+        <v>3.676783</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6354,25 +6354,25 @@
         <v>6</v>
       </c>
       <c r="E118" s="7">
-        <v>0.07548</v>
+        <v>0.08404099999999999</v>
       </c>
       <c r="F118" s="7">
-        <v>0.032694</v>
+        <v>0.017471</v>
       </c>
       <c r="G118" s="7">
-        <v>0.255412</v>
+        <v>0.260101</v>
       </c>
       <c r="H118" s="7">
-        <v>0.176286</v>
+        <v>0.17873899999999998</v>
       </c>
       <c r="I118" s="7">
-        <v>0.618597</v>
+        <v>0.6309239999999999</v>
       </c>
       <c r="J118" s="7">
-        <v>3.5553160000000004</v>
+        <v>3.564815</v>
       </c>
       <c r="K118" s="7">
-        <v>16.356232</v>
+        <v>16.288728000000003</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6389,25 +6389,25 @@
         <v>5</v>
       </c>
       <c r="E119" s="7">
-        <v>0.041534</v>
+        <v>0.042603999999999996</v>
       </c>
       <c r="F119" s="7">
-        <v>-0.0008</v>
+        <v>-0.020658</v>
       </c>
       <c r="G119" s="7">
-        <v>0.172812</v>
+        <v>0.17400500000000002</v>
       </c>
       <c r="H119" s="7">
-        <v>0.093775</v>
+        <v>0.092337</v>
       </c>
       <c r="I119" s="7">
-        <v>0.452714</v>
+        <v>0.452273</v>
       </c>
       <c r="J119" s="7">
-        <v>2.593484</v>
+        <v>2.588759</v>
       </c>
       <c r="K119" s="7">
-        <v>8.951819</v>
+        <v>8.905737</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,25 +6424,25 @@
         <v>6</v>
       </c>
       <c r="E120" s="7">
-        <v>0.057150999999999993</v>
+        <v>0.052022000000000006</v>
       </c>
       <c r="F120" s="7">
-        <v>-0.026654</v>
+        <v>-0.044154</v>
       </c>
       <c r="G120" s="7">
-        <v>0.172547</v>
+        <v>0.16369399999999998</v>
       </c>
       <c r="H120" s="7">
-        <v>0.11960900000000001</v>
+        <v>0.113094</v>
       </c>
       <c r="I120" s="7">
-        <v>0.422844</v>
+        <v>0.41999699999999995</v>
       </c>
       <c r="J120" s="7">
-        <v>3.394269</v>
+        <v>3.368699</v>
       </c>
       <c r="K120" s="7">
-        <v>18.149166</v>
+        <v>17.899445</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,25 +6459,25 @@
         <v>4</v>
       </c>
       <c r="E121" s="7">
-        <v>0.049208</v>
+        <v>0.052752</v>
       </c>
       <c r="F121" s="7">
-        <v>0.031291</v>
+        <v>0.021488</v>
       </c>
       <c r="G121" s="7">
-        <v>0.19676300000000002</v>
+        <v>0.195772</v>
       </c>
       <c r="H121" s="7">
-        <v>0.11007199999999999</v>
+        <v>0.10757699999999999</v>
       </c>
       <c r="I121" s="7">
-        <v>0.480831</v>
+        <v>0.481122</v>
       </c>
       <c r="J121" s="7">
-        <v>2.334504</v>
+        <v>2.327011</v>
       </c>
       <c r="K121" s="7">
-        <v>6.027734000000001</v>
+        <v>5.9905539999999995</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6494,25 +6494,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.041590999999999996</v>
+        <v>0.045134</v>
       </c>
       <c r="F122" s="7">
-        <v>0.030091</v>
+        <v>0.022263</v>
       </c>
       <c r="G122" s="7">
-        <v>0.17035699999999998</v>
+        <v>0.17019700000000001</v>
       </c>
       <c r="H122" s="7">
-        <v>0.09584300000000001</v>
+        <v>0.09449</v>
       </c>
       <c r="I122" s="7">
-        <v>0.43111600000000005</v>
+        <v>0.43193600000000004</v>
       </c>
       <c r="J122" s="7">
-        <v>1.969905</v>
+        <v>1.9662389999999998</v>
       </c>
       <c r="K122" s="7">
-        <v>6.031843</v>
+        <v>6.01584</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,16 +6529,16 @@
         <v>6</v>
       </c>
       <c r="E123" s="7">
-        <v>0.023163</v>
+        <v>0.001941</v>
       </c>
       <c r="F123" s="7">
-        <v>-0.09946300000000001</v>
+        <v>-0.098078</v>
       </c>
       <c r="G123" s="7">
-        <v>0.172444</v>
+        <v>0.191167</v>
       </c>
       <c r="H123" s="7">
-        <v>0.108096</v>
+        <v>0.09889799999999999</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
@@ -6558,25 +6558,25 @@
         <v>4</v>
       </c>
       <c r="E124" s="7">
-        <v>0.06296</v>
+        <v>0.066092</v>
       </c>
       <c r="F124" s="7">
-        <v>0.034247</v>
+        <v>0.011931</v>
       </c>
       <c r="G124" s="7">
-        <v>0.238201</v>
+        <v>0.23559999999999998</v>
       </c>
       <c r="H124" s="7">
-        <v>0.142932</v>
+        <v>0.141051</v>
       </c>
       <c r="I124" s="7">
-        <v>0.525783</v>
+        <v>0.529967</v>
       </c>
       <c r="J124" s="7">
-        <v>1.9869329999999998</v>
+        <v>1.9820160000000002</v>
       </c>
       <c r="K124" s="7">
-        <v>6.531541999999999</v>
+        <v>6.512671</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.122588</v>
+        <v>0.135751</v>
       </c>
       <c r="F125" s="7">
-        <v>0.108301</v>
+        <v>0.115432</v>
       </c>
       <c r="G125" s="7">
-        <v>0.331164</v>
+        <v>0.347213</v>
       </c>
       <c r="H125" s="7">
-        <v>0.320098</v>
+        <v>0.335355</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
@@ -6622,25 +6622,25 @@
         <v>7</v>
       </c>
       <c r="E126" s="7">
-        <v>0.095334</v>
+        <v>0.100529</v>
       </c>
       <c r="F126" s="7">
-        <v>0.036122</v>
+        <v>0.019216999999999998</v>
       </c>
       <c r="G126" s="7">
-        <v>0.200938</v>
+        <v>0.203885</v>
       </c>
       <c r="H126" s="7">
-        <v>0.115328</v>
+        <v>0.114757</v>
       </c>
       <c r="I126" s="7">
-        <v>0.42300899999999997</v>
+        <v>0.434614</v>
       </c>
       <c r="J126" s="7">
-        <v>2.44675</v>
+        <v>2.4449870000000002</v>
       </c>
       <c r="K126" s="7">
-        <v>9.337256</v>
+        <v>9.283529999999999</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,25 +6657,25 @@
         <v>5</v>
       </c>
       <c r="E127" s="7">
-        <v>0.045436</v>
+        <v>0.04249</v>
       </c>
       <c r="F127" s="7">
-        <v>0.020773</v>
+        <v>0.020973000000000002</v>
       </c>
       <c r="G127" s="7">
-        <v>0.084015</v>
+        <v>0.08652599999999999</v>
       </c>
       <c r="H127" s="7">
-        <v>0.042836</v>
+        <v>0.041401</v>
       </c>
       <c r="I127" s="7">
-        <v>0.276203</v>
+        <v>0.274604</v>
       </c>
       <c r="J127" s="7">
-        <v>1.964352</v>
+        <v>1.960274</v>
       </c>
       <c r="K127" s="7">
-        <v>5.626402000000001</v>
+        <v>5.599804000000001</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6692,25 +6692,25 @@
         <v>4</v>
       </c>
       <c r="E128" s="7">
-        <v>0.046325000000000005</v>
+        <v>0.048897</v>
       </c>
       <c r="F128" s="7">
-        <v>-0.00601</v>
+        <v>-0.011566</v>
       </c>
       <c r="G128" s="7">
-        <v>0.13833700000000002</v>
+        <v>0.13151300000000002</v>
       </c>
       <c r="H128" s="7">
-        <v>0.037475</v>
+        <v>0.032837</v>
       </c>
       <c r="I128" s="7">
-        <v>0.392262</v>
+        <v>0.39198</v>
       </c>
       <c r="J128" s="7">
-        <v>1.539553</v>
+        <v>1.5282</v>
       </c>
       <c r="K128" s="7">
-        <v>3.3431349999999997</v>
+        <v>3.319687</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6727,25 +6727,25 @@
         <v>6</v>
       </c>
       <c r="E129" s="7">
-        <v>0.095524</v>
+        <v>0.10251400000000001</v>
       </c>
       <c r="F129" s="7">
-        <v>0.03198</v>
+        <v>-0.0031290000000000003</v>
       </c>
       <c r="G129" s="7">
-        <v>0.292754</v>
+        <v>0.289028</v>
       </c>
       <c r="H129" s="7">
-        <v>0.213132</v>
+        <v>0.211361</v>
       </c>
       <c r="I129" s="7">
-        <v>0.505919</v>
+        <v>0.521014</v>
       </c>
       <c r="J129" s="7">
-        <v>2.8064210000000003</v>
+        <v>2.800863</v>
       </c>
       <c r="K129" s="7">
-        <v>14.580457</v>
+        <v>14.389733000000001</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6762,25 +6762,25 @@
         <v>4</v>
       </c>
       <c r="E130" s="7">
-        <v>0.051676</v>
+        <v>0.046735</v>
       </c>
       <c r="F130" s="7">
-        <v>0.028815</v>
+        <v>0.028652999999999998</v>
       </c>
       <c r="G130" s="7">
-        <v>0.08012000000000001</v>
+        <v>0.078549</v>
       </c>
       <c r="H130" s="7">
-        <v>0.037274</v>
+        <v>0.034647000000000004</v>
       </c>
       <c r="I130" s="7">
-        <v>0.283289</v>
+        <v>0.278779</v>
       </c>
       <c r="J130" s="7">
-        <v>2.036271</v>
+        <v>2.028582</v>
       </c>
       <c r="K130" s="7">
-        <v>6.354709000000001</v>
+        <v>6.329340999999999</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6797,19 +6797,19 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.120542</v>
+        <v>0.128887</v>
       </c>
       <c r="F131" s="7">
-        <v>0.103301</v>
+        <v>0.131663</v>
       </c>
       <c r="G131" s="7">
-        <v>0.224745</v>
+        <v>0.22531700000000002</v>
       </c>
       <c r="H131" s="7">
-        <v>0.231305</v>
+        <v>0.249505</v>
       </c>
       <c r="I131" s="7">
-        <v>0.672548</v>
+        <v>0.7003199999999999</v>
       </c>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
@@ -6828,25 +6828,25 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.055362999999999996</v>
+        <v>0.057078</v>
       </c>
       <c r="F132" s="7">
-        <v>0.006579000000000001</v>
+        <v>-0.009392000000000001</v>
       </c>
       <c r="G132" s="7">
-        <v>0.17299399999999998</v>
+        <v>0.16683599999999998</v>
       </c>
       <c r="H132" s="7">
-        <v>0.07176199999999999</v>
+        <v>0.06643</v>
       </c>
       <c r="I132" s="7">
-        <v>0.419019</v>
+        <v>0.41974200000000006</v>
       </c>
       <c r="J132" s="7">
-        <v>1.4623089999999999</v>
+        <v>1.4500579999999998</v>
       </c>
       <c r="K132" s="7">
-        <v>3.7977800000000004</v>
+        <v>3.758526</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6863,25 +6863,25 @@
         <v>3</v>
       </c>
       <c r="E133" s="7">
-        <v>0.031558</v>
+        <v>0.030939</v>
       </c>
       <c r="F133" s="7">
-        <v>0.087792</v>
+        <v>0.082828</v>
       </c>
       <c r="G133" s="7">
-        <v>0.18733899999999998</v>
+        <v>0.181731</v>
       </c>
       <c r="H133" s="7">
-        <v>0.11914899999999999</v>
+        <v>0.119342</v>
       </c>
       <c r="I133" s="7">
-        <v>0.461877</v>
+        <v>0.460388</v>
       </c>
       <c r="J133" s="7">
-        <v>2.295323</v>
+        <v>2.295893</v>
       </c>
       <c r="K133" s="7">
-        <v>3.867022</v>
+        <v>3.85832</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6898,25 +6898,25 @@
         <v>6</v>
       </c>
       <c r="E134" s="7">
-        <v>0.059634</v>
+        <v>0.060503999999999995</v>
       </c>
       <c r="F134" s="7">
-        <v>0.05733</v>
+        <v>0.047164000000000005</v>
       </c>
       <c r="G134" s="7">
-        <v>0.23360399999999998</v>
+        <v>0.232682</v>
       </c>
       <c r="H134" s="7">
-        <v>0.164834</v>
+        <v>0.161937</v>
       </c>
       <c r="I134" s="7">
-        <v>0.44911900000000005</v>
+        <v>0.45427100000000004</v>
       </c>
       <c r="J134" s="7">
-        <v>2.73486</v>
+        <v>2.725571</v>
       </c>
       <c r="K134" s="7">
-        <v>7.9625580000000005</v>
+        <v>7.851375000000001</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6933,25 +6933,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.054778</v>
+        <v>0.058798</v>
       </c>
       <c r="F135" s="7">
-        <v>0.007419</v>
+        <v>-0.0029170000000000003</v>
       </c>
       <c r="G135" s="7">
-        <v>0.144232</v>
+        <v>0.142668</v>
       </c>
       <c r="H135" s="7">
-        <v>0.06429299999999999</v>
+        <v>0.061598</v>
       </c>
       <c r="I135" s="7">
-        <v>0.345834</v>
+        <v>0.349436</v>
       </c>
       <c r="J135" s="7">
-        <v>1.044149</v>
+        <v>1.038974</v>
       </c>
       <c r="K135" s="7">
-        <v>2.438711</v>
+        <v>2.416944</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6968,25 +6968,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.073598</v>
+        <v>0.081599</v>
       </c>
       <c r="F136" s="7">
-        <v>0.08691900000000001</v>
+        <v>0.08013999999999999</v>
       </c>
       <c r="G136" s="7">
-        <v>0.18134</v>
+        <v>0.18545999999999999</v>
       </c>
       <c r="H136" s="7">
-        <v>0.148626</v>
+        <v>0.156252</v>
       </c>
       <c r="I136" s="7">
-        <v>0.42513199999999995</v>
+        <v>0.436646</v>
       </c>
       <c r="J136" s="7">
-        <v>3.069999</v>
+        <v>3.097021</v>
       </c>
       <c r="K136" s="7">
-        <v>9.40185</v>
+        <v>9.42621</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7003,25 +7003,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.04851</v>
+        <v>0.050393</v>
       </c>
       <c r="F137" s="7">
-        <v>0.04523</v>
+        <v>0.038879000000000004</v>
       </c>
       <c r="G137" s="7">
-        <v>0.172043</v>
+        <v>0.169197</v>
       </c>
       <c r="H137" s="7">
-        <v>0.097907</v>
+        <v>0.097064</v>
       </c>
       <c r="I137" s="7">
-        <v>0.429508</v>
+        <v>0.429628</v>
       </c>
       <c r="J137" s="7">
-        <v>2.157142</v>
+        <v>2.154716</v>
       </c>
       <c r="K137" s="7">
-        <v>4.141363</v>
+        <v>4.134547</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7038,22 +7038,22 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.201388</v>
+        <v>0.23629999999999998</v>
       </c>
       <c r="F138" s="7">
-        <v>0.10220000000000001</v>
+        <v>0.116548</v>
       </c>
       <c r="G138" s="7">
-        <v>0.241479</v>
+        <v>0.260782</v>
       </c>
       <c r="H138" s="7">
-        <v>0.21545899999999998</v>
+        <v>0.232854</v>
       </c>
       <c r="I138" s="7">
-        <v>0.818838</v>
+        <v>0.8340179999999999</v>
       </c>
       <c r="J138" s="7">
-        <v>5.0815339999999996</v>
+        <v>5.168565999999999</v>
       </c>
       <c r="K138" s="7"/>
     </row>
@@ -7071,22 +7071,22 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.074506</v>
+        <v>0.074069</v>
       </c>
       <c r="F139" s="7">
-        <v>-0.0038050000000000002</v>
+        <v>-0.009254</v>
       </c>
       <c r="G139" s="7">
-        <v>0.186713</v>
+        <v>0.180594</v>
       </c>
       <c r="H139" s="7">
-        <v>0.101244</v>
+        <v>0.099088</v>
       </c>
       <c r="I139" s="7">
-        <v>0.51365</v>
+        <v>0.51137</v>
       </c>
       <c r="J139" s="7">
-        <v>4.698272</v>
+        <v>4.687117</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,25 +7104,25 @@
         <v>3</v>
       </c>
       <c r="E140" s="7">
-        <v>0.043822</v>
+        <v>0.045891</v>
       </c>
       <c r="F140" s="7">
-        <v>0.01844</v>
+        <v>0.0059299999999999995</v>
       </c>
       <c r="G140" s="7">
-        <v>0.15637</v>
+        <v>0.153137</v>
       </c>
       <c r="H140" s="7">
-        <v>0.083248</v>
+        <v>0.080442</v>
       </c>
       <c r="I140" s="7">
-        <v>0.370784</v>
+        <v>0.370865</v>
       </c>
       <c r="J140" s="7">
-        <v>1.62446</v>
+        <v>1.617662</v>
       </c>
       <c r="K140" s="7">
-        <v>3.615093</v>
+        <v>3.5941289999999997</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7139,25 +7139,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.034931000000000004</v>
+        <v>0.037875</v>
       </c>
       <c r="F141" s="7">
-        <v>0.051933</v>
+        <v>0.051040999999999996</v>
       </c>
       <c r="G141" s="7">
-        <v>0.176943</v>
+        <v>0.175921</v>
       </c>
       <c r="H141" s="7">
-        <v>0.113006</v>
+        <v>0.11584199999999999</v>
       </c>
       <c r="I141" s="7">
-        <v>0.348709</v>
+        <v>0.35356099999999996</v>
       </c>
       <c r="J141" s="7">
-        <v>1.370352</v>
+        <v>1.3763919999999998</v>
       </c>
       <c r="K141" s="7">
-        <v>4.456199</v>
+        <v>4.461295</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,25 +7174,25 @@
         <v>5</v>
       </c>
       <c r="E142" s="7">
-        <v>0.077011</v>
+        <v>0.085664</v>
       </c>
       <c r="F142" s="7">
-        <v>0.028111</v>
+        <v>-0.010546999999999999</v>
       </c>
       <c r="G142" s="7">
-        <v>0.207101</v>
+        <v>0.20908000000000002</v>
       </c>
       <c r="H142" s="7">
-        <v>0.148459</v>
+        <v>0.149144</v>
       </c>
       <c r="I142" s="7">
-        <v>0.36972299999999997</v>
+        <v>0.371548</v>
       </c>
       <c r="J142" s="7">
-        <v>3.2018590000000002</v>
+        <v>3.204365</v>
       </c>
       <c r="K142" s="7">
-        <v>13.654292</v>
+        <v>13.526187</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7209,25 +7209,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.067509</v>
+        <v>0.071892</v>
       </c>
       <c r="F143" s="7">
-        <v>0.156865</v>
+        <v>0.151829</v>
       </c>
       <c r="G143" s="7">
-        <v>0.17235199999999998</v>
+        <v>0.182738</v>
       </c>
       <c r="H143" s="7">
-        <v>0.271245</v>
+        <v>0.27732500000000004</v>
       </c>
       <c r="I143" s="7">
-        <v>0.273309</v>
+        <v>0.27825700000000003</v>
       </c>
       <c r="J143" s="7">
-        <v>3.530899</v>
+        <v>3.5525700000000002</v>
       </c>
       <c r="K143" s="7">
-        <v>10.878284</v>
+        <v>10.928666</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7244,25 +7244,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.08404199999999999</v>
+        <v>0.089383</v>
       </c>
       <c r="F144" s="7">
-        <v>0.083733</v>
+        <v>0.065885</v>
       </c>
       <c r="G144" s="7">
-        <v>0.30211099999999996</v>
+        <v>0.30471</v>
       </c>
       <c r="H144" s="7">
-        <v>0.192804</v>
+        <v>0.19307300000000002</v>
       </c>
       <c r="I144" s="7">
-        <v>0.552855</v>
+        <v>0.558321</v>
       </c>
       <c r="J144" s="7">
-        <v>2.926706</v>
+        <v>2.927591</v>
       </c>
       <c r="K144" s="7">
-        <v>8.173055</v>
+        <v>8.147826</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7279,25 +7279,25 @@
         <v>4</v>
       </c>
       <c r="E145" s="7">
-        <v>0.074539</v>
+        <v>0.07819899999999999</v>
       </c>
       <c r="F145" s="7">
-        <v>0.032854</v>
+        <v>0.0017410000000000001</v>
       </c>
       <c r="G145" s="7">
-        <v>0.25244099999999997</v>
+        <v>0.249712</v>
       </c>
       <c r="H145" s="7">
-        <v>0.16226400000000002</v>
+        <v>0.16023900000000002</v>
       </c>
       <c r="I145" s="7">
-        <v>0.5296</v>
+        <v>0.53806</v>
       </c>
       <c r="J145" s="7">
-        <v>3.4194709999999997</v>
+        <v>3.4117720000000005</v>
       </c>
       <c r="K145" s="7">
-        <v>9.512728</v>
+        <v>9.432448</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7314,25 +7314,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.027729</v>
+        <v>0.02642</v>
       </c>
       <c r="F146" s="7">
-        <v>0.140869</v>
+        <v>0.130256</v>
       </c>
       <c r="G146" s="7">
-        <v>0.355171</v>
+        <v>0.33321</v>
       </c>
       <c r="H146" s="7">
-        <v>0.257097</v>
+        <v>0.25461500000000004</v>
       </c>
       <c r="I146" s="7">
-        <v>0.61469</v>
+        <v>0.612744</v>
       </c>
       <c r="J146" s="7">
-        <v>3.149381</v>
+        <v>3.1411860000000003</v>
       </c>
       <c r="K146" s="7">
-        <v>9.383303</v>
+        <v>9.341752</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7349,25 +7349,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.034699</v>
+        <v>0.033498</v>
       </c>
       <c r="F147" s="7">
-        <v>0.067706</v>
+        <v>0.064451</v>
       </c>
       <c r="G147" s="7">
-        <v>0.190852</v>
+        <v>0.189181</v>
       </c>
       <c r="H147" s="7">
-        <v>0.127224</v>
+        <v>0.127052</v>
       </c>
       <c r="I147" s="7">
-        <v>0.457007</v>
+        <v>0.457108</v>
       </c>
       <c r="J147" s="7">
-        <v>2.2030529999999997</v>
+        <v>2.202563</v>
       </c>
       <c r="K147" s="7">
-        <v>6.520966</v>
+        <v>6.502199000000001</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7384,25 +7384,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.04489099999999999</v>
+        <v>0.039493</v>
       </c>
       <c r="F148" s="7">
-        <v>-0.013499</v>
+        <v>-0.02205</v>
       </c>
       <c r="G148" s="7">
-        <v>0.230538</v>
+        <v>0.213281</v>
       </c>
       <c r="H148" s="7">
-        <v>0.121271</v>
+        <v>0.116104</v>
       </c>
       <c r="I148" s="7">
-        <v>0.543335</v>
+        <v>0.542205</v>
       </c>
       <c r="J148" s="7">
-        <v>3.268035</v>
+        <v>3.2483690000000003</v>
       </c>
       <c r="K148" s="7">
-        <v>9.604645</v>
+        <v>9.523795</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7419,25 +7419,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.046652</v>
+        <v>0.050026</v>
       </c>
       <c r="F149" s="7">
-        <v>0.062935</v>
+        <v>0.061172000000000004</v>
       </c>
       <c r="G149" s="7">
-        <v>0.173717</v>
+        <v>0.17731000000000002</v>
       </c>
       <c r="H149" s="7">
-        <v>0.130271</v>
+        <v>0.133635</v>
       </c>
       <c r="I149" s="7">
-        <v>0.38821</v>
+        <v>0.394658</v>
       </c>
       <c r="J149" s="7">
-        <v>1.4467109999999999</v>
+        <v>1.453993</v>
       </c>
       <c r="K149" s="7">
-        <v>4.229621</v>
+        <v>4.222281</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7454,25 +7454,25 @@
         <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>0.10106899999999999</v>
+        <v>0.11043599999999999</v>
       </c>
       <c r="F150" s="7">
-        <v>0.071812</v>
+        <v>0.069734</v>
       </c>
       <c r="G150" s="7">
-        <v>0.245946</v>
+        <v>0.252672</v>
       </c>
       <c r="H150" s="7">
-        <v>0.228491</v>
+        <v>0.233797</v>
       </c>
       <c r="I150" s="7">
-        <v>0.541788</v>
+        <v>0.556058</v>
       </c>
       <c r="J150" s="7">
-        <v>2.679805</v>
+        <v>2.6956990000000003</v>
       </c>
       <c r="K150" s="7">
-        <v>8.471303</v>
+        <v>8.422424999999999</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7489,25 +7489,25 @@
         <v>7</v>
       </c>
       <c r="E151" s="7">
-        <v>0.086202</v>
+        <v>0.093558</v>
       </c>
       <c r="F151" s="7">
-        <v>0.076399</v>
+        <v>0.074062</v>
       </c>
       <c r="G151" s="7">
-        <v>0.23887699999999998</v>
+        <v>0.244094</v>
       </c>
       <c r="H151" s="7">
-        <v>0.208067</v>
+        <v>0.21235199999999999</v>
       </c>
       <c r="I151" s="7">
-        <v>0.535836</v>
+        <v>0.546982</v>
       </c>
       <c r="J151" s="7">
-        <v>2.570531</v>
+        <v>2.583197</v>
       </c>
       <c r="K151" s="7">
-        <v>7.405204</v>
+        <v>7.392419</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7524,25 +7524,25 @@
         <v>3</v>
       </c>
       <c r="E152" s="7">
-        <v>0.04437</v>
+        <v>0.043796999999999996</v>
       </c>
       <c r="F152" s="7">
-        <v>0.071578</v>
+        <v>0.06229</v>
       </c>
       <c r="G152" s="7">
-        <v>0.20474599999999998</v>
+        <v>0.20187999999999998</v>
       </c>
       <c r="H152" s="7">
-        <v>0.12315300000000001</v>
+        <v>0.121713</v>
       </c>
       <c r="I152" s="7">
-        <v>0.48205</v>
+        <v>0.481717</v>
       </c>
       <c r="J152" s="7">
-        <v>2.9441879999999996</v>
+        <v>2.939134</v>
       </c>
       <c r="K152" s="7">
-        <v>5.071984</v>
+        <v>5.064614000000001</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7559,22 +7559,22 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.055911</v>
+        <v>0.062723</v>
       </c>
       <c r="F153" s="7">
-        <v>0.01993</v>
+        <v>0.009485</v>
       </c>
       <c r="G153" s="7">
-        <v>0.188805</v>
+        <v>0.189614</v>
       </c>
       <c r="H153" s="7">
-        <v>0.122423</v>
+        <v>0.12659</v>
       </c>
       <c r="I153" s="7">
-        <v>0.484359</v>
+        <v>0.48774700000000004</v>
       </c>
       <c r="J153" s="7">
-        <v>3.396191</v>
+        <v>3.412514</v>
       </c>
       <c r="K153" s="7"/>
     </row>
@@ -7592,16 +7592,16 @@
         <v>4</v>
       </c>
       <c r="E154" s="7">
-        <v>0.050121</v>
+        <v>0.050321</v>
       </c>
       <c r="F154" s="7">
-        <v>0.0668</v>
+        <v>0.059295999999999995</v>
       </c>
       <c r="G154" s="7">
-        <v>0.25627099999999997</v>
+        <v>0.256531</v>
       </c>
       <c r="H154" s="7">
-        <v>0.18024300000000001</v>
+        <v>0.1809</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
@@ -7621,22 +7621,22 @@
         <v>6</v>
       </c>
       <c r="E155" s="7">
-        <v>0.099645</v>
+        <v>0.10479</v>
       </c>
       <c r="F155" s="7">
-        <v>0.065774</v>
+        <v>0.047637</v>
       </c>
       <c r="G155" s="7">
-        <v>0.22381399999999999</v>
+        <v>0.227377</v>
       </c>
       <c r="H155" s="7">
-        <v>0.17765899999999998</v>
+        <v>0.179012</v>
       </c>
       <c r="I155" s="7">
-        <v>0.44575899999999996</v>
+        <v>0.452774</v>
       </c>
       <c r="J155" s="7">
-        <v>1.762198</v>
+        <v>1.765371</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7654,25 +7654,25 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.057173</v>
+        <v>0.061951</v>
       </c>
       <c r="F156" s="7">
-        <v>0.08194599999999999</v>
+        <v>0.08114800000000001</v>
       </c>
       <c r="G156" s="7">
-        <v>0.237543</v>
+        <v>0.24387699999999998</v>
       </c>
       <c r="H156" s="7">
-        <v>0.16551300000000002</v>
+        <v>0.170198</v>
       </c>
       <c r="I156" s="7">
-        <v>0.53943</v>
+        <v>0.5474289999999999</v>
       </c>
       <c r="J156" s="7">
-        <v>2.380739</v>
+        <v>2.394329</v>
       </c>
       <c r="K156" s="7">
-        <v>6.437593000000001</v>
+        <v>6.453563</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7689,25 +7689,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.058175</v>
+        <v>0.063802</v>
       </c>
       <c r="F157" s="7">
-        <v>0.084007</v>
+        <v>0.084638</v>
       </c>
       <c r="G157" s="7">
-        <v>0.228434</v>
+        <v>0.23512899999999998</v>
       </c>
       <c r="H157" s="7">
-        <v>0.16495100000000001</v>
+        <v>0.169917</v>
       </c>
       <c r="I157" s="7">
-        <v>0.49674100000000004</v>
+        <v>0.50465</v>
       </c>
       <c r="J157" s="7">
-        <v>2.162836</v>
+        <v>2.176319</v>
       </c>
       <c r="K157" s="7">
-        <v>5.948283</v>
+        <v>5.964987</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7724,25 +7724,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.042351</v>
+        <v>0.043191</v>
       </c>
       <c r="F158" s="7">
-        <v>0.05755</v>
+        <v>0.055744999999999996</v>
       </c>
       <c r="G158" s="7">
-        <v>0.19890899999999997</v>
+        <v>0.202955</v>
       </c>
       <c r="H158" s="7">
-        <v>0.130785</v>
+        <v>0.133604</v>
       </c>
       <c r="I158" s="7">
-        <v>0.432169</v>
+        <v>0.431954</v>
       </c>
       <c r="J158" s="7">
-        <v>1.818289</v>
+        <v>1.825315</v>
       </c>
       <c r="K158" s="7">
-        <v>5.038497</v>
+        <v>5.045561</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,22 +7759,22 @@
         <v>5</v>
       </c>
       <c r="E159" s="7">
-        <v>0.16670400000000002</v>
+        <v>0.173019</v>
       </c>
       <c r="F159" s="7">
-        <v>0.149635</v>
+        <v>0.16808199999999998</v>
       </c>
       <c r="G159" s="7">
-        <v>0.270888</v>
+        <v>0.267076</v>
       </c>
       <c r="H159" s="7">
-        <v>0.260898</v>
+        <v>0.267486</v>
       </c>
       <c r="I159" s="7">
-        <v>0.7232299999999999</v>
+        <v>0.720261</v>
       </c>
       <c r="J159" s="7">
-        <v>3.9310840000000002</v>
+        <v>3.956848</v>
       </c>
       <c r="K159" s="7"/>
     </row>
@@ -7792,25 +7792,25 @@
         <v>4</v>
       </c>
       <c r="E160" s="7">
-        <v>0.051698</v>
+        <v>0.054838</v>
       </c>
       <c r="F160" s="7">
-        <v>0.020665</v>
+        <v>0.01154</v>
       </c>
       <c r="G160" s="7">
-        <v>0.195825</v>
+        <v>0.194753</v>
       </c>
       <c r="H160" s="7">
-        <v>0.09125899999999999</v>
+        <v>0.08921200000000001</v>
       </c>
       <c r="I160" s="7">
-        <v>0.42930300000000005</v>
+        <v>0.429684</v>
       </c>
       <c r="J160" s="7">
-        <v>2.043753</v>
+        <v>2.038043</v>
       </c>
       <c r="K160" s="7">
-        <v>5.650576999999999</v>
+        <v>5.628545</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,22 +7827,22 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.034949</v>
+        <v>0.032813</v>
       </c>
       <c r="F161" s="7">
-        <v>0.087759</v>
+        <v>0.079139</v>
       </c>
       <c r="G161" s="7">
-        <v>0.22469</v>
+        <v>0.22328</v>
       </c>
       <c r="H161" s="7">
-        <v>0.150653</v>
+        <v>0.151597</v>
       </c>
       <c r="I161" s="7">
-        <v>0.53362</v>
+        <v>0.536541</v>
       </c>
       <c r="J161" s="7">
-        <v>3.351582</v>
+        <v>3.355152</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7860,22 +7860,22 @@
         <v>6</v>
       </c>
       <c r="E162" s="7">
-        <v>0.067033</v>
+        <v>0.060269</v>
       </c>
       <c r="F162" s="7">
-        <v>-0.020724999999999997</v>
+        <v>-0.014127</v>
       </c>
       <c r="G162" s="7">
-        <v>0.117332</v>
+        <v>0.121905</v>
       </c>
       <c r="H162" s="7">
-        <v>0.065039</v>
+        <v>0.06038</v>
       </c>
       <c r="I162" s="7">
-        <v>0.400458</v>
+        <v>0.391413</v>
       </c>
       <c r="J162" s="7">
-        <v>2.5856</v>
+        <v>2.569915</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,25 +7893,25 @@
         <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>0.09488400000000001</v>
+        <v>0.10185000000000001</v>
       </c>
       <c r="F163" s="7">
-        <v>0.08071</v>
+        <v>0.083509</v>
       </c>
       <c r="G163" s="7">
-        <v>0.292655</v>
+        <v>0.306023</v>
       </c>
       <c r="H163" s="7">
-        <v>0.245197</v>
+        <v>0.252867</v>
       </c>
       <c r="I163" s="7">
-        <v>0.622514</v>
+        <v>0.634308</v>
       </c>
       <c r="J163" s="7">
-        <v>2.489326</v>
+        <v>2.51082</v>
       </c>
       <c r="K163" s="7">
-        <v>8.660507</v>
+        <v>8.701333</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7928,25 +7928,25 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.104818</v>
+        <v>0.122421</v>
       </c>
       <c r="F164" s="7">
-        <v>0.069731</v>
+        <v>0.04149</v>
       </c>
       <c r="G164" s="7">
-        <v>0.334731</v>
+        <v>0.34726300000000004</v>
       </c>
       <c r="H164" s="7">
-        <v>0.27063400000000004</v>
+        <v>0.275197</v>
       </c>
       <c r="I164" s="7">
-        <v>0.624466</v>
+        <v>0.6343610000000001</v>
       </c>
       <c r="J164" s="7">
-        <v>1.94515</v>
+        <v>1.955728</v>
       </c>
       <c r="K164" s="7">
-        <v>3.585762</v>
+        <v>3.600295</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7963,25 +7963,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.099262</v>
+        <v>0.104964</v>
       </c>
       <c r="F165" s="7">
-        <v>0.036337</v>
+        <v>0.004562</v>
       </c>
       <c r="G165" s="7">
-        <v>0.29446</v>
+        <v>0.296246</v>
       </c>
       <c r="H165" s="7">
-        <v>0.219845</v>
+        <v>0.21685500000000002</v>
       </c>
       <c r="I165" s="7">
-        <v>0.460976</v>
+        <v>0.470912</v>
       </c>
       <c r="J165" s="7">
-        <v>2.911474</v>
+        <v>2.901887</v>
       </c>
       <c r="K165" s="7">
-        <v>15.953019999999999</v>
+        <v>15.773193000000001</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7998,25 +7998,25 @@
         <v>3</v>
       </c>
       <c r="E166" s="7">
-        <v>0.04415</v>
+        <v>0.045351999999999996</v>
       </c>
       <c r="F166" s="7">
-        <v>0.004397</v>
+        <v>-0.00042</v>
       </c>
       <c r="G166" s="7">
-        <v>0.141532</v>
+        <v>0.137222</v>
       </c>
       <c r="H166" s="7">
-        <v>0.043693</v>
+        <v>0.039534</v>
       </c>
       <c r="I166" s="7">
-        <v>0.398512</v>
+        <v>0.394716</v>
       </c>
       <c r="J166" s="7">
-        <v>1.869069</v>
+        <v>1.857634</v>
       </c>
       <c r="K166" s="7">
-        <v>3.974951</v>
+        <v>3.9494819999999997</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8033,25 +8033,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.047725</v>
+        <v>0.051126</v>
       </c>
       <c r="F167" s="7">
-        <v>0.076492</v>
+        <v>0.077335</v>
       </c>
       <c r="G167" s="7">
-        <v>0.231448</v>
+        <v>0.23561800000000002</v>
       </c>
       <c r="H167" s="7">
-        <v>0.156471</v>
+        <v>0.160529</v>
       </c>
       <c r="I167" s="7">
-        <v>0.460644</v>
+        <v>0.465951</v>
       </c>
       <c r="J167" s="7">
-        <v>1.885838</v>
+        <v>1.895963</v>
       </c>
       <c r="K167" s="7">
-        <v>5.4193169999999995</v>
+        <v>5.430177</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8068,25 +8068,25 @@
         <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>0.027646999999999998</v>
+        <v>0.026034</v>
       </c>
       <c r="F168" s="7">
-        <v>0.062394</v>
+        <v>0.061073</v>
       </c>
       <c r="G168" s="7">
-        <v>0.125375</v>
+        <v>0.125092</v>
       </c>
       <c r="H168" s="7">
-        <v>0.081388</v>
+        <v>0.081855</v>
       </c>
       <c r="I168" s="7">
-        <v>0.30176200000000003</v>
+        <v>0.30185300000000004</v>
       </c>
       <c r="J168" s="7">
-        <v>1.95867</v>
+        <v>1.9599469999999999</v>
       </c>
       <c r="K168" s="7">
-        <v>5.543750999999999</v>
+        <v>5.544842</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8103,22 +8103,22 @@
         <v>6</v>
       </c>
       <c r="E169" s="7">
-        <v>0.021315</v>
+        <v>0.0015</v>
       </c>
       <c r="F169" s="7">
-        <v>-0.12119999999999999</v>
+        <v>-0.10777900000000001</v>
       </c>
       <c r="G169" s="7">
-        <v>0.14182</v>
+        <v>0.168331</v>
       </c>
       <c r="H169" s="7">
-        <v>0.08099500000000001</v>
+        <v>0.07466</v>
       </c>
       <c r="I169" s="7">
-        <v>0.583532</v>
+        <v>0.563063</v>
       </c>
       <c r="J169" s="7">
-        <v>4.586843</v>
+        <v>4.554101999999999</v>
       </c>
       <c r="K169" s="7"/>
     </row>
@@ -8136,22 +8136,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>0.113065</v>
+        <v>0.12282</v>
       </c>
       <c r="F170" s="7">
-        <v>0.055735</v>
+        <v>0.034203000000000004</v>
       </c>
       <c r="G170" s="7">
-        <v>0.23111399999999999</v>
+        <v>0.23637699999999998</v>
       </c>
       <c r="H170" s="7">
-        <v>0.196324</v>
+        <v>0.198123</v>
       </c>
       <c r="I170" s="7">
-        <v>0.47375</v>
+        <v>0.486779</v>
       </c>
       <c r="J170" s="7">
-        <v>2.493172</v>
+        <v>2.498424</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,16 +8169,16 @@
         <v>7</v>
       </c>
       <c r="E171" s="7">
-        <v>0.067386</v>
+        <v>0.036680000000000004</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.29783000000000004</v>
+        <v>-0.268936</v>
       </c>
       <c r="G171" s="7">
-        <v>0.613532</v>
+        <v>0.547402</v>
       </c>
       <c r="H171" s="7">
-        <v>0.036269</v>
+        <v>0.02313</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7"/>
@@ -8198,25 +8198,25 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.003353</v>
+        <v>-0.007268</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.124094</v>
+        <v>-0.107289</v>
       </c>
       <c r="G172" s="7">
-        <v>0.128081</v>
+        <v>0.140154</v>
       </c>
       <c r="H172" s="7">
-        <v>0.045861</v>
+        <v>0.043169000000000006</v>
       </c>
       <c r="I172" s="7">
-        <v>0.542543</v>
+        <v>0.529252</v>
       </c>
       <c r="J172" s="7">
-        <v>4.005718</v>
+        <v>3.992837</v>
       </c>
       <c r="K172" s="7">
-        <v>13.528977</v>
+        <v>13.477013</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8233,25 +8233,25 @@
         <v>4</v>
       </c>
       <c r="E173" s="7">
-        <v>0.060764</v>
+        <v>0.065385</v>
       </c>
       <c r="F173" s="7">
-        <v>0.020200999999999997</v>
+        <v>0.010621</v>
       </c>
       <c r="G173" s="7">
-        <v>0.20625800000000002</v>
+        <v>0.205803</v>
       </c>
       <c r="H173" s="7">
-        <v>0.10143700000000001</v>
+        <v>0.09910999999999999</v>
       </c>
       <c r="I173" s="7">
-        <v>0.45071599999999995</v>
+        <v>0.454369</v>
       </c>
       <c r="J173" s="7">
-        <v>2.051097</v>
+        <v>2.04465</v>
       </c>
       <c r="K173" s="7">
-        <v>5.388866</v>
+        <v>5.360659000000001</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8268,25 +8268,25 @@
         <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>0.082623</v>
+        <v>0.088076</v>
       </c>
       <c r="F174" s="7">
-        <v>0.046458000000000006</v>
+        <v>0.027632</v>
       </c>
       <c r="G174" s="7">
-        <v>0.255768</v>
+        <v>0.257926</v>
       </c>
       <c r="H174" s="7">
-        <v>0.20062000000000002</v>
+        <v>0.19903099999999999</v>
       </c>
       <c r="I174" s="7">
-        <v>0.454975</v>
+        <v>0.457573</v>
       </c>
       <c r="J174" s="7">
-        <v>2.743804</v>
+        <v>2.7388470000000003</v>
       </c>
       <c r="K174" s="7">
-        <v>10.473452</v>
+        <v>10.394443</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8303,25 +8303,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.049985</v>
+        <v>0.045885999999999996</v>
       </c>
       <c r="F175" s="7">
-        <v>0.033318</v>
+        <v>0.033547</v>
       </c>
       <c r="G175" s="7">
-        <v>0.097835</v>
+        <v>0.097321</v>
       </c>
       <c r="H175" s="7">
-        <v>0.050492999999999996</v>
+        <v>0.048837</v>
       </c>
       <c r="I175" s="7">
-        <v>0.308912</v>
+        <v>0.30476</v>
       </c>
       <c r="J175" s="7">
-        <v>2.089658</v>
+        <v>2.0847890000000002</v>
       </c>
       <c r="K175" s="7">
-        <v>6.373005000000001</v>
+        <v>6.343839</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8338,25 +8338,25 @@
         <v>6</v>
       </c>
       <c r="E176" s="7">
-        <v>0.11516299999999999</v>
+        <v>0.12426</v>
       </c>
       <c r="F176" s="7">
-        <v>0.06843</v>
+        <v>0.055268</v>
       </c>
       <c r="G176" s="7">
-        <v>0.241558</v>
+        <v>0.24257</v>
       </c>
       <c r="H176" s="7">
-        <v>0.185972</v>
+        <v>0.187688</v>
       </c>
       <c r="I176" s="7">
-        <v>0.587967</v>
+        <v>0.5997330000000001</v>
       </c>
       <c r="J176" s="7">
-        <v>2.9326049999999997</v>
+        <v>2.938297</v>
       </c>
       <c r="K176" s="7">
-        <v>12.356939</v>
+        <v>12.31606</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,25 +8373,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.098021</v>
+        <v>0.105</v>
       </c>
       <c r="F177" s="7">
-        <v>0.05878</v>
+        <v>0.034711</v>
       </c>
       <c r="G177" s="7">
-        <v>0.332363</v>
+        <v>0.336918</v>
       </c>
       <c r="H177" s="7">
-        <v>0.241403</v>
+        <v>0.23951</v>
       </c>
       <c r="I177" s="7">
-        <v>0.556176</v>
+        <v>0.568307</v>
       </c>
       <c r="J177" s="7">
-        <v>3.293427</v>
+        <v>3.286881</v>
       </c>
       <c r="K177" s="7">
-        <v>17.449749999999998</v>
+        <v>17.257266</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8408,25 +8408,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.080363</v>
+        <v>0.08421300000000001</v>
       </c>
       <c r="F178" s="7">
-        <v>0.05764300000000001</v>
+        <v>0.03567</v>
       </c>
       <c r="G178" s="7">
-        <v>0.308467</v>
+        <v>0.309467</v>
       </c>
       <c r="H178" s="7">
-        <v>0.202955</v>
+        <v>0.20133900000000002</v>
       </c>
       <c r="I178" s="7">
-        <v>0.516938</v>
+        <v>0.523936</v>
       </c>
       <c r="J178" s="7">
-        <v>3.1698340000000003</v>
+        <v>3.164232</v>
       </c>
       <c r="K178" s="7">
-        <v>12.965689</v>
+        <v>12.856205</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,25 +8443,25 @@
         <v>4</v>
       </c>
       <c r="E179" s="7">
-        <v>0.071674</v>
+        <v>0.073197</v>
       </c>
       <c r="F179" s="7">
-        <v>0.05325</v>
+        <v>0.034585</v>
       </c>
       <c r="G179" s="7">
-        <v>0.279057</v>
+        <v>0.278625</v>
       </c>
       <c r="H179" s="7">
-        <v>0.17130800000000002</v>
+        <v>0.168745</v>
       </c>
       <c r="I179" s="7">
-        <v>0.531792</v>
+        <v>0.5323640000000001</v>
       </c>
       <c r="J179" s="7">
-        <v>3.4068259999999997</v>
+        <v>3.3971839999999998</v>
       </c>
       <c r="K179" s="7">
-        <v>11.249922</v>
+        <v>11.170532000000001</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8478,25 +8478,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.099327</v>
+        <v>0.09879500000000001</v>
       </c>
       <c r="F180" s="7">
-        <v>0.025528</v>
+        <v>0.035044</v>
       </c>
       <c r="G180" s="7">
-        <v>0.142437</v>
+        <v>0.14029999999999998</v>
       </c>
       <c r="H180" s="7">
-        <v>0.10681800000000001</v>
+        <v>0.106508</v>
       </c>
       <c r="I180" s="7">
-        <v>0.54645</v>
+        <v>0.544932</v>
       </c>
       <c r="J180" s="7">
-        <v>3.207041</v>
+        <v>3.205863</v>
       </c>
       <c r="K180" s="7">
-        <v>8.315698</v>
+        <v>8.318719999999999</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8513,25 +8513,25 @@
         <v>2</v>
       </c>
       <c r="E181" s="7">
-        <v>0.041816000000000006</v>
+        <v>0.042273</v>
       </c>
       <c r="F181" s="7">
-        <v>0.074611</v>
+        <v>0.066941</v>
       </c>
       <c r="G181" s="7">
-        <v>0.208449</v>
+        <v>0.20747800000000002</v>
       </c>
       <c r="H181" s="7">
-        <v>0.124818</v>
+        <v>0.124389</v>
       </c>
       <c r="I181" s="7">
-        <v>0.48938000000000004</v>
+        <v>0.48761499999999997</v>
       </c>
       <c r="J181" s="7">
-        <v>3.319948</v>
+        <v>3.3183</v>
       </c>
       <c r="K181" s="7">
-        <v>6.2906629999999994</v>
+        <v>6.284928</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8548,25 +8548,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.07652</v>
+        <v>0.081396</v>
       </c>
       <c r="F182" s="7">
-        <v>0.028589000000000003</v>
+        <v>0.014288</v>
       </c>
       <c r="G182" s="7">
-        <v>0.125514</v>
+        <v>0.129917</v>
       </c>
       <c r="H182" s="7">
-        <v>0.152469</v>
+        <v>0.152088</v>
       </c>
       <c r="I182" s="7">
-        <v>0.35580599999999996</v>
+        <v>0.35818399999999995</v>
       </c>
       <c r="J182" s="7">
-        <v>2.418887</v>
+        <v>2.417757</v>
       </c>
       <c r="K182" s="7">
-        <v>3.9114280000000003</v>
+        <v>3.905064</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8583,25 +8583,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.11069699999999999</v>
+        <v>0.117768</v>
       </c>
       <c r="F183" s="7">
-        <v>0.091375</v>
+        <v>0.093626</v>
       </c>
       <c r="G183" s="7">
-        <v>0.35568</v>
+        <v>0.369023</v>
       </c>
       <c r="H183" s="7">
-        <v>0.30787</v>
+        <v>0.318736</v>
       </c>
       <c r="I183" s="7">
-        <v>0.661452</v>
+        <v>0.6774209999999999</v>
       </c>
       <c r="J183" s="7">
-        <v>3.175906</v>
+        <v>3.2106</v>
       </c>
       <c r="K183" s="7">
-        <v>12.964663</v>
+        <v>13.00894</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8618,25 +8618,25 @@
         <v>3</v>
       </c>
       <c r="E184" s="7">
-        <v>0.029451</v>
+        <v>0.029703</v>
       </c>
       <c r="F184" s="7">
-        <v>0.08889799999999999</v>
+        <v>0.08628999999999999</v>
       </c>
       <c r="G184" s="7">
-        <v>0.192909</v>
+        <v>0.193058</v>
       </c>
       <c r="H184" s="7">
-        <v>0.118077</v>
+        <v>0.11940200000000001</v>
       </c>
       <c r="I184" s="7">
-        <v>0.455956</v>
+        <v>0.45632</v>
       </c>
       <c r="J184" s="7">
-        <v>1.710203</v>
+        <v>1.713416</v>
       </c>
       <c r="K184" s="7">
-        <v>3.8118950000000003</v>
+        <v>3.8155959999999998</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8653,25 +8653,25 @@
         <v>5</v>
       </c>
       <c r="E185" s="7">
-        <v>0.09074299999999999</v>
+        <v>0.101121</v>
       </c>
       <c r="F185" s="7">
-        <v>0.08182</v>
+        <v>0.083132</v>
       </c>
       <c r="G185" s="7">
-        <v>0.277071</v>
+        <v>0.288243</v>
       </c>
       <c r="H185" s="7">
-        <v>0.231448</v>
+        <v>0.240338</v>
       </c>
       <c r="I185" s="7">
-        <v>0.600492</v>
+        <v>0.614505</v>
       </c>
       <c r="J185" s="7">
-        <v>2.946218</v>
+        <v>2.974708</v>
       </c>
       <c r="K185" s="7">
-        <v>11.120076</v>
+        <v>11.161865</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8688,25 +8688,25 @@
         <v>2</v>
       </c>
       <c r="E186" s="7">
-        <v>0.029747</v>
+        <v>0.030049000000000003</v>
       </c>
       <c r="F186" s="7">
-        <v>0.088914</v>
+        <v>0.08626899999999998</v>
       </c>
       <c r="G186" s="7">
-        <v>0.190047</v>
+        <v>0.19030999999999998</v>
       </c>
       <c r="H186" s="7">
-        <v>0.117675</v>
+        <v>0.11902599999999999</v>
       </c>
       <c r="I186" s="7">
-        <v>0.45023</v>
+        <v>0.45039</v>
       </c>
       <c r="J186" s="7">
-        <v>1.8204179999999999</v>
+        <v>1.823827</v>
       </c>
       <c r="K186" s="7">
-        <v>3.323031</v>
+        <v>3.3263499999999997</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8723,25 +8723,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.020224000000000002</v>
+        <v>0.021150000000000002</v>
       </c>
       <c r="F187" s="7">
-        <v>0.061438</v>
+        <v>0.054873000000000005</v>
       </c>
       <c r="G187" s="7">
-        <v>0.149409</v>
+        <v>0.150457</v>
       </c>
       <c r="H187" s="7">
-        <v>0.09573999999999999</v>
+        <v>0.09765800000000001</v>
       </c>
       <c r="I187" s="7">
-        <v>0.38017</v>
+        <v>0.38230800000000004</v>
       </c>
       <c r="J187" s="7">
-        <v>1.9713990000000001</v>
+        <v>1.976599</v>
       </c>
       <c r="K187" s="7">
-        <v>3.3235680000000003</v>
+        <v>3.3265179999999996</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,16 +8758,16 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.067119</v>
+        <v>0.029655</v>
       </c>
       <c r="F188" s="7">
-        <v>-0.295344</v>
+        <v>-0.266162</v>
       </c>
       <c r="G188" s="7">
-        <v>0.572039</v>
+        <v>0.5058590000000001</v>
       </c>
       <c r="H188" s="7">
-        <v>0.013855</v>
+        <v>0.0018640000000000002</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
@@ -8787,25 +8787,25 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>0.014014</v>
+        <v>0.001114</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.12506</v>
+        <v>-0.111496</v>
       </c>
       <c r="G189" s="7">
-        <v>0.141704</v>
+        <v>0.160613</v>
       </c>
       <c r="H189" s="7">
-        <v>0.058003</v>
+        <v>0.055</v>
       </c>
       <c r="I189" s="7">
-        <v>0.565562</v>
+        <v>0.5528730000000001</v>
       </c>
       <c r="J189" s="7">
-        <v>3.850264</v>
+        <v>3.836498</v>
       </c>
       <c r="K189" s="7">
-        <v>13.256404999999999</v>
+        <v>13.205755</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>-0.003196</v>
+        <v>-0.012105</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.117991</v>
+        <v>-0.102895</v>
       </c>
       <c r="G190" s="7">
-        <v>0.123032</v>
+        <v>0.128013</v>
       </c>
       <c r="H190" s="7">
-        <v>0.031753</v>
+        <v>0.027490999999999998</v>
       </c>
       <c r="I190" s="7">
-        <v>0.529701</v>
+        <v>0.510956</v>
       </c>
       <c r="J190" s="7">
-        <v>3.7892680000000003</v>
+        <v>3.769483</v>
       </c>
       <c r="K190" s="7">
-        <v>13.012472</v>
+        <v>12.942056000000001</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8857,25 @@
         <v>4</v>
       </c>
       <c r="E191" s="7">
-        <v>0.06591</v>
+        <v>0.071351</v>
       </c>
       <c r="F191" s="7">
-        <v>0.042489</v>
+        <v>0.031093000000000003</v>
       </c>
       <c r="G191" s="7">
-        <v>0.24938300000000002</v>
+        <v>0.250782</v>
       </c>
       <c r="H191" s="7">
-        <v>0.134895</v>
+        <v>0.133626</v>
       </c>
       <c r="I191" s="7">
-        <v>0.49373199999999995</v>
+        <v>0.49830399999999997</v>
       </c>
       <c r="J191" s="7">
-        <v>1.852854</v>
+        <v>1.849664</v>
       </c>
       <c r="K191" s="7">
-        <v>5.069145</v>
+        <v>5.052091</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8892,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.056961000000000005</v>
+        <v>0.061541</v>
       </c>
       <c r="F192" s="7">
-        <v>0.037819</v>
+        <v>0.029802</v>
       </c>
       <c r="G192" s="7">
-        <v>0.193208</v>
+        <v>0.193532</v>
       </c>
       <c r="H192" s="7">
-        <v>0.099441</v>
+        <v>0.098674</v>
       </c>
       <c r="I192" s="7">
-        <v>0.454372</v>
+        <v>0.457885</v>
       </c>
       <c r="J192" s="7">
-        <v>2.20084</v>
+        <v>2.198606</v>
       </c>
       <c r="K192" s="7">
-        <v>5.515747999999999</v>
+        <v>5.50061</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8927,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>0.046421000000000004</v>
+        <v>0.042078</v>
       </c>
       <c r="F193" s="7">
-        <v>0.030055000000000002</v>
+        <v>0.030567999999999998</v>
       </c>
       <c r="G193" s="7">
-        <v>0.09859</v>
+        <v>0.098003</v>
       </c>
       <c r="H193" s="7">
-        <v>0.047789</v>
+        <v>0.046182</v>
       </c>
       <c r="I193" s="7">
-        <v>0.316619</v>
+        <v>0.315485</v>
       </c>
       <c r="J193" s="7">
-        <v>2.205788</v>
+        <v>2.20087</v>
       </c>
       <c r="K193" s="7">
-        <v>6.603415999999999</v>
+        <v>6.573176</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8962,25 @@
         <v>3</v>
       </c>
       <c r="E194" s="7">
-        <v>0.047753</v>
+        <v>0.049703</v>
       </c>
       <c r="F194" s="7">
-        <v>0.08925100000000001</v>
+        <v>0.083451</v>
       </c>
       <c r="G194" s="7">
-        <v>0.23268799999999998</v>
+        <v>0.23602599999999999</v>
       </c>
       <c r="H194" s="7">
-        <v>0.181459</v>
+        <v>0.182666</v>
       </c>
       <c r="I194" s="7">
-        <v>0.467661</v>
+        <v>0.469437</v>
       </c>
       <c r="J194" s="7">
-        <v>1.547758</v>
+        <v>1.55036</v>
       </c>
       <c r="K194" s="7">
-        <v>3.720896</v>
+        <v>3.716017</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +8997,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.044977</v>
+        <v>0.049759000000000005</v>
       </c>
       <c r="F195" s="7">
-        <v>0.07011099999999999</v>
+        <v>0.070956</v>
       </c>
       <c r="G195" s="7">
-        <v>0.22274000000000002</v>
+        <v>0.228296</v>
       </c>
       <c r="H195" s="7">
-        <v>0.13234500000000002</v>
+        <v>0.136545</v>
       </c>
       <c r="I195" s="7">
-        <v>0.450095</v>
+        <v>0.455805</v>
       </c>
       <c r="J195" s="7">
-        <v>1.716561</v>
+        <v>1.7266380000000001</v>
       </c>
       <c r="K195" s="7">
-        <v>4.590875</v>
+        <v>4.605392</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9032,25 @@
         <v>4</v>
       </c>
       <c r="E196" s="7">
-        <v>0.066518</v>
+        <v>0.073656</v>
       </c>
       <c r="F196" s="7">
-        <v>0.039699</v>
+        <v>0.033572000000000005</v>
       </c>
       <c r="G196" s="7">
-        <v>0.21098</v>
+        <v>0.21354099999999998</v>
       </c>
       <c r="H196" s="7">
-        <v>0.123426</v>
+        <v>0.124534</v>
       </c>
       <c r="I196" s="7">
-        <v>0.48039299999999996</v>
+        <v>0.48814100000000005</v>
       </c>
       <c r="J196" s="7">
-        <v>2.101223</v>
+        <v>2.10428</v>
       </c>
       <c r="K196" s="7">
-        <v>5.089268000000001</v>
+        <v>5.076014</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9067,25 @@
         <v>6</v>
       </c>
       <c r="E197" s="7">
-        <v>0.080411</v>
+        <v>0.085455</v>
       </c>
       <c r="F197" s="7">
-        <v>0.02635</v>
+        <v>-0.014332000000000001</v>
       </c>
       <c r="G197" s="7">
-        <v>0.241656</v>
+        <v>0.24064</v>
       </c>
       <c r="H197" s="7">
-        <v>0.19658</v>
+        <v>0.19165500000000002</v>
       </c>
       <c r="I197" s="7">
-        <v>0.440431</v>
+        <v>0.450441</v>
       </c>
       <c r="J197" s="7">
-        <v>3.936801</v>
+        <v>3.916481</v>
       </c>
       <c r="K197" s="7">
-        <v>21.076028</v>
+        <v>20.762793000000002</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,16 +9102,16 @@
         <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>0.090076</v>
+        <v>0.092707</v>
       </c>
       <c r="F198" s="7">
-        <v>0.055170000000000004</v>
+        <v>0.037228</v>
       </c>
       <c r="G198" s="7">
-        <v>0.215912</v>
+        <v>0.220865</v>
       </c>
       <c r="H198" s="7">
-        <v>0.186361</v>
+        <v>0.18754</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
@@ -9131,25 +9131,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.067299</v>
+        <v>0.06618</v>
       </c>
       <c r="F199" s="7">
-        <v>-0.021172</v>
+        <v>-0.035523</v>
       </c>
       <c r="G199" s="7">
-        <v>0.166777</v>
+        <v>0.152807</v>
       </c>
       <c r="H199" s="7">
-        <v>0.071589</v>
+        <v>0.06510200000000001</v>
       </c>
       <c r="I199" s="7">
-        <v>0.36429</v>
+        <v>0.362839</v>
       </c>
       <c r="J199" s="7">
-        <v>2.0839529999999997</v>
+        <v>2.065283</v>
       </c>
       <c r="K199" s="7">
-        <v>9.983387</v>
+        <v>9.81706</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9166,25 +9166,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.08299799999999999</v>
+        <v>0.095282</v>
       </c>
       <c r="F200" s="7">
-        <v>0.055258</v>
+        <v>0.05428</v>
       </c>
       <c r="G200" s="7">
-        <v>0.21758400000000003</v>
+        <v>0.226083</v>
       </c>
       <c r="H200" s="7">
-        <v>0.169301</v>
+        <v>0.173174</v>
       </c>
       <c r="I200" s="7">
-        <v>0.472427</v>
+        <v>0.47976100000000005</v>
       </c>
       <c r="J200" s="7">
-        <v>2.350161</v>
+        <v>2.361259</v>
       </c>
       <c r="K200" s="7">
-        <v>9.207158</v>
+        <v>9.153277000000001</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9201,25 +9201,25 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.04891</v>
+        <v>0.038064</v>
       </c>
       <c r="F201" s="7">
-        <v>-0.006159</v>
+        <v>-0.011878</v>
       </c>
       <c r="G201" s="7">
-        <v>0.17568799999999998</v>
+        <v>0.163729</v>
       </c>
       <c r="H201" s="7">
-        <v>0.08434599999999999</v>
+        <v>0.08216100000000001</v>
       </c>
       <c r="I201" s="7">
-        <v>0.66608</v>
+        <v>0.668537</v>
       </c>
       <c r="J201" s="7">
-        <v>2.91175</v>
+        <v>2.9038690000000003</v>
       </c>
       <c r="K201" s="7">
-        <v>6.382175</v>
+        <v>6.36397</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9236,25 +9236,25 @@
         <v>3</v>
       </c>
       <c r="E202" s="7">
-        <v>0.03599</v>
+        <v>0.035206</v>
       </c>
       <c r="F202" s="7">
-        <v>0.020985</v>
+        <v>0.017147</v>
       </c>
       <c r="G202" s="7">
-        <v>0.153756</v>
+        <v>0.149227</v>
       </c>
       <c r="H202" s="7">
-        <v>0.051694000000000004</v>
+        <v>0.047564999999999996</v>
       </c>
       <c r="I202" s="7">
-        <v>0.407212</v>
+        <v>0.40366199999999997</v>
       </c>
       <c r="J202" s="7">
-        <v>1.646744</v>
+        <v>1.636352</v>
       </c>
       <c r="K202" s="7">
-        <v>3.684611</v>
+        <v>3.6614299999999997</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,16 +9271,16 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.08145899999999999</v>
+        <v>0.08875899999999999</v>
       </c>
       <c r="F203" s="7">
-        <v>0.028357999999999998</v>
+        <v>-0.009003</v>
       </c>
       <c r="G203" s="7">
-        <v>0.260878</v>
+        <v>0.261736</v>
       </c>
       <c r="H203" s="7">
-        <v>0.20486000000000001</v>
+        <v>0.201728</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
@@ -9300,25 +9300,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.04089400000000001</v>
+        <v>0.039865</v>
       </c>
       <c r="F204" s="7">
-        <v>0.033703</v>
+        <v>0.035826</v>
       </c>
       <c r="G204" s="7">
-        <v>0.105753</v>
+        <v>0.10620900000000001</v>
       </c>
       <c r="H204" s="7">
-        <v>0.058625</v>
+        <v>0.05803899999999999</v>
       </c>
       <c r="I204" s="7">
-        <v>0.314158</v>
+        <v>0.311309</v>
       </c>
       <c r="J204" s="7">
-        <v>1.9485190000000001</v>
+        <v>1.946885</v>
       </c>
       <c r="K204" s="7">
-        <v>5.3614</v>
+        <v>5.34842</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9335,25 +9335,25 @@
         <v>4</v>
       </c>
       <c r="E205" s="7">
-        <v>0.050917000000000004</v>
+        <v>0.053367000000000005</v>
       </c>
       <c r="F205" s="7">
-        <v>0.014787999999999999</v>
+        <v>0.0028039999999999996</v>
       </c>
       <c r="G205" s="7">
-        <v>0.194428</v>
+        <v>0.190996</v>
       </c>
       <c r="H205" s="7">
-        <v>0.091798</v>
+        <v>0.088567</v>
       </c>
       <c r="I205" s="7">
-        <v>0.343384</v>
+        <v>0.347959</v>
       </c>
       <c r="J205" s="7">
-        <v>1.984025</v>
+        <v>1.975194</v>
       </c>
       <c r="K205" s="7">
-        <v>4.940092</v>
+        <v>4.907775</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9370,25 +9370,25 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.062325</v>
+        <v>0.063137</v>
       </c>
       <c r="F206" s="7">
-        <v>0.030619999999999998</v>
+        <v>0.0070550000000000005</v>
       </c>
       <c r="G206" s="7">
-        <v>0.256817</v>
+        <v>0.25084</v>
       </c>
       <c r="H206" s="7">
-        <v>0.16283</v>
+        <v>0.157944</v>
       </c>
       <c r="I206" s="7">
-        <v>0.48828499999999997</v>
+        <v>0.487442</v>
       </c>
       <c r="J206" s="7">
-        <v>2.733756</v>
+        <v>2.718069</v>
       </c>
       <c r="K206" s="7">
-        <v>8.055721</v>
+        <v>7.975185</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9405,25 +9405,25 @@
         <v>6</v>
       </c>
       <c r="E207" s="7">
-        <v>0.070645</v>
+        <v>0.072726</v>
       </c>
       <c r="F207" s="7">
-        <v>0.019039999999999998</v>
+        <v>-0.007853</v>
       </c>
       <c r="G207" s="7">
-        <v>0.308956</v>
+        <v>0.298817</v>
       </c>
       <c r="H207" s="7">
-        <v>0.168892</v>
+        <v>0.163167</v>
       </c>
       <c r="I207" s="7">
-        <v>0.505085</v>
+        <v>0.506003</v>
       </c>
       <c r="J207" s="7">
-        <v>2.7423</v>
+        <v>2.72397</v>
       </c>
       <c r="K207" s="7">
-        <v>9.840064</v>
+        <v>9.716237999999999</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9440,25 +9440,25 @@
         <v>3</v>
       </c>
       <c r="E208" s="7">
-        <v>0.036477</v>
+        <v>0.038016999999999995</v>
       </c>
       <c r="F208" s="7">
-        <v>0.007841</v>
+        <v>0.00293</v>
       </c>
       <c r="G208" s="7">
-        <v>0.164267</v>
+        <v>0.16201000000000002</v>
       </c>
       <c r="H208" s="7">
-        <v>0.041161</v>
+        <v>0.038347</v>
       </c>
       <c r="I208" s="7">
-        <v>0.402274</v>
+        <v>0.406775</v>
       </c>
       <c r="J208" s="7">
-        <v>1.5049430000000001</v>
+        <v>1.498173</v>
       </c>
       <c r="K208" s="7">
-        <v>2.943912</v>
+        <v>2.929496</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9475,25 +9475,25 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.09354599999999999</v>
+        <v>0.09540699999999999</v>
       </c>
       <c r="F209" s="7">
-        <v>0.007475000000000001</v>
+        <v>-0.030435</v>
       </c>
       <c r="G209" s="7">
-        <v>0.279721</v>
+        <v>0.268314</v>
       </c>
       <c r="H209" s="7">
-        <v>0.203519</v>
+        <v>0.195303</v>
       </c>
       <c r="I209" s="7">
-        <v>0.38295</v>
+        <v>0.39133</v>
       </c>
       <c r="J209" s="7">
-        <v>2.872167</v>
+        <v>2.845733</v>
       </c>
       <c r="K209" s="7">
-        <v>14.905677</v>
+        <v>14.630576000000001</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9510,25 +9510,25 @@
         <v>4</v>
       </c>
       <c r="E210" s="7">
-        <v>0.067498</v>
+        <v>0.073244</v>
       </c>
       <c r="F210" s="7">
-        <v>0.05086</v>
+        <v>0.037798</v>
       </c>
       <c r="G210" s="7">
-        <v>0.233523</v>
+        <v>0.234683</v>
       </c>
       <c r="H210" s="7">
-        <v>0.16549399999999997</v>
+        <v>0.16545500000000002</v>
       </c>
       <c r="I210" s="7">
-        <v>0.509537</v>
+        <v>0.5139</v>
       </c>
       <c r="J210" s="7">
-        <v>1.873314</v>
+        <v>1.873218</v>
       </c>
       <c r="K210" s="7">
-        <v>5.515340999999999</v>
+        <v>5.48759</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9545,25 +9545,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.055386</v>
+        <v>0.063323</v>
       </c>
       <c r="F211" s="7">
-        <v>0.098273</v>
+        <v>0.098457</v>
       </c>
       <c r="G211" s="7">
-        <v>0.24239999999999998</v>
+        <v>0.251724</v>
       </c>
       <c r="H211" s="7">
-        <v>0.180866</v>
+        <v>0.18718800000000002</v>
       </c>
       <c r="I211" s="7">
-        <v>0.48884700000000003</v>
+        <v>0.500323</v>
       </c>
       <c r="J211" s="7">
-        <v>1.876082</v>
+        <v>1.89148</v>
       </c>
       <c r="K211" s="7">
-        <v>5.0322949999999995</v>
+        <v>5.052407</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9580,25 +9580,25 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.077846</v>
+        <v>0.083896</v>
       </c>
       <c r="F212" s="7">
-        <v>0.086776</v>
+        <v>0.07917</v>
       </c>
       <c r="G212" s="7">
-        <v>0.287418</v>
+        <v>0.302051</v>
       </c>
       <c r="H212" s="7">
-        <v>0.24718199999999999</v>
+        <v>0.25055299999999997</v>
       </c>
       <c r="I212" s="7">
-        <v>0.60602</v>
+        <v>0.61109</v>
       </c>
       <c r="J212" s="7">
-        <v>2.985453</v>
+        <v>2.9962259999999996</v>
       </c>
       <c r="K212" s="7">
-        <v>9.802396</v>
+        <v>9.824588</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,25 +9615,25 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>0.007929</v>
+        <v>-0.003302</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.127605</v>
+        <v>-0.110246</v>
       </c>
       <c r="G213" s="7">
-        <v>0.146802</v>
+        <v>0.16467099999999998</v>
       </c>
       <c r="H213" s="7">
-        <v>0.061514</v>
+        <v>0.059234</v>
       </c>
       <c r="I213" s="7">
-        <v>0.588357</v>
+        <v>0.576281</v>
       </c>
       <c r="J213" s="7">
-        <v>4.044404</v>
+        <v>4.033566</v>
       </c>
       <c r="K213" s="7">
-        <v>13.565771</v>
+        <v>13.520425</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,25 +9650,25 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.049656000000000006</v>
+        <v>0.046039000000000004</v>
       </c>
       <c r="F214" s="7">
-        <v>0.040467</v>
+        <v>0.028983</v>
       </c>
       <c r="G214" s="7">
-        <v>0.168518</v>
+        <v>0.16799399999999998</v>
       </c>
       <c r="H214" s="7">
-        <v>0.11901099999999999</v>
+        <v>0.114383</v>
       </c>
       <c r="I214" s="7">
-        <v>0.40883699999999995</v>
+        <v>0.40132100000000004</v>
       </c>
       <c r="J214" s="7">
-        <v>2.246665</v>
+        <v>2.233237</v>
       </c>
       <c r="K214" s="7">
-        <v>7.223088000000001</v>
+        <v>7.163321999999999</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9685,25 +9685,25 @@
         <v>5</v>
       </c>
       <c r="E215" s="7">
-        <v>0.11866</v>
+        <v>0.12429899999999999</v>
       </c>
       <c r="F215" s="7">
-        <v>0.098727</v>
+        <v>0.09617200000000001</v>
       </c>
       <c r="G215" s="7">
-        <v>0.368271</v>
+        <v>0.375567</v>
       </c>
       <c r="H215" s="7">
-        <v>0.312496</v>
+        <v>0.31946</v>
       </c>
       <c r="I215" s="7">
-        <v>0.630563</v>
+        <v>0.6508710000000001</v>
       </c>
       <c r="J215" s="7">
-        <v>2.6752659999999997</v>
+        <v>2.6947680000000003</v>
       </c>
       <c r="K215" s="7">
-        <v>9.876114</v>
+        <v>9.834802</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9720,25 +9720,25 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.026307999999999998</v>
+        <v>0.025107</v>
       </c>
       <c r="F216" s="7">
-        <v>0.035687</v>
+        <v>0.035354000000000003</v>
       </c>
       <c r="G216" s="7">
-        <v>0.083002</v>
+        <v>0.082468</v>
       </c>
       <c r="H216" s="7">
-        <v>0.048688</v>
+        <v>0.048373</v>
       </c>
       <c r="I216" s="7">
-        <v>0.228294</v>
+        <v>0.22771799999999998</v>
       </c>
       <c r="J216" s="7">
-        <v>1.778418</v>
+        <v>1.777585</v>
       </c>
       <c r="K216" s="7">
-        <v>5.320461</v>
+        <v>5.317145</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9755,25 +9755,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.06843099999999999</v>
+        <v>0.07724199999999999</v>
       </c>
       <c r="F217" s="7">
-        <v>0.114014</v>
+        <v>0.10700799999999999</v>
       </c>
       <c r="G217" s="7">
-        <v>0.306257</v>
+        <v>0.31598299999999996</v>
       </c>
       <c r="H217" s="7">
-        <v>0.241388</v>
+        <v>0.24739899999999998</v>
       </c>
       <c r="I217" s="7">
-        <v>0.628823</v>
+        <v>0.6408020000000001</v>
       </c>
       <c r="J217" s="7">
-        <v>3.241087</v>
+        <v>3.261621</v>
       </c>
       <c r="K217" s="7">
-        <v>10.301253999999998</v>
+        <v>10.337328</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,25 +9790,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.111432</v>
+        <v>0.115377</v>
       </c>
       <c r="F218" s="7">
-        <v>0.093898</v>
+        <v>0.089032</v>
       </c>
       <c r="G218" s="7">
-        <v>0.35749400000000003</v>
+        <v>0.360422</v>
       </c>
       <c r="H218" s="7">
-        <v>0.285096</v>
+        <v>0.289833</v>
       </c>
       <c r="I218" s="7">
-        <v>0.60144</v>
+        <v>0.614663</v>
       </c>
       <c r="J218" s="7">
-        <v>3.887592</v>
+        <v>3.905607</v>
       </c>
       <c r="K218" s="7">
-        <v>13.300957</v>
+        <v>13.293083999999999</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9825,19 +9825,19 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.06397599999999999</v>
+        <v>0.063507</v>
       </c>
       <c r="F219" s="7">
-        <v>0.050705</v>
+        <v>0.050895</v>
       </c>
       <c r="G219" s="7">
-        <v>0.23811800000000002</v>
+        <v>0.239866</v>
       </c>
       <c r="H219" s="7">
-        <v>0.1722</v>
+        <v>0.172729</v>
       </c>
       <c r="I219" s="7">
-        <v>0.512343</v>
+        <v>0.513469</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
@@ -9856,16 +9856,16 @@
         <v>6</v>
       </c>
       <c r="E220" s="7">
-        <v>0.058547</v>
+        <v>0.048696</v>
       </c>
       <c r="F220" s="7">
-        <v>-0.264657</v>
+        <v>-0.25333</v>
       </c>
       <c r="G220" s="7">
-        <v>0.640868</v>
+        <v>0.618568</v>
       </c>
       <c r="H220" s="7">
-        <v>0.08882300000000001</v>
+        <v>0.081657</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
@@ -9906,22 +9906,22 @@
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.035203000000000005</v>
+        <v>0.021588</v>
       </c>
       <c r="F222" s="7">
-        <v>-0.195024</v>
+        <v>-0.181449</v>
       </c>
       <c r="G222" s="7">
-        <v>0.384685</v>
+        <v>0.378461</v>
       </c>
       <c r="H222" s="7">
-        <v>0.070838</v>
+        <v>0.063503</v>
       </c>
       <c r="I222" s="7">
-        <v>0.99698</v>
+        <v>0.974894</v>
       </c>
       <c r="J222" s="7">
-        <v>4.4154349999999996</v>
+        <v>4.378342</v>
       </c>
       <c r="K222" s="7"/>
     </row>
@@ -9939,25 +9939,25 @@
         <v>4</v>
       </c>
       <c r="E223" s="7">
-        <v>0.031218</v>
+        <v>0.031225</v>
       </c>
       <c r="F223" s="7">
-        <v>0.096412</v>
+        <v>0.093828</v>
       </c>
       <c r="G223" s="7">
-        <v>0.196776</v>
+        <v>0.196916</v>
       </c>
       <c r="H223" s="7">
-        <v>0.12270500000000001</v>
+        <v>0.123917</v>
       </c>
       <c r="I223" s="7">
-        <v>0.447868</v>
+        <v>0.448032</v>
       </c>
       <c r="J223" s="7">
-        <v>1.2886410000000001</v>
+        <v>1.291113</v>
       </c>
       <c r="K223" s="7">
-        <v>2.700937</v>
+        <v>2.703588</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9974,19 +9974,19 @@
         <v>2</v>
       </c>
       <c r="E224" s="7">
-        <v>0.028251</v>
+        <v>0.028506999999999998</v>
       </c>
       <c r="F224" s="7">
-        <v>0.08395200000000001</v>
+        <v>0.08133699999999999</v>
       </c>
       <c r="G224" s="7">
-        <v>0.187009</v>
+        <v>0.187334</v>
       </c>
       <c r="H224" s="7">
-        <v>0.114893</v>
+        <v>0.116165</v>
       </c>
       <c r="I224" s="7">
-        <v>0.445698</v>
+        <v>0.445917</v>
       </c>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10005,22 +10005,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.11003500000000001</v>
+        <v>0.113246</v>
       </c>
       <c r="F225" s="7">
-        <v>0.075479</v>
+        <v>0.076757</v>
       </c>
       <c r="G225" s="7">
-        <v>0.24018</v>
+        <v>0.241935</v>
       </c>
       <c r="H225" s="7">
-        <v>0.239341</v>
+        <v>0.24638100000000002</v>
       </c>
       <c r="I225" s="7">
-        <v>0.44041800000000003</v>
+        <v>0.456612</v>
       </c>
       <c r="J225" s="7">
-        <v>2.504498</v>
+        <v>2.524404</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10038,19 +10038,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="7">
-        <v>0.046203</v>
+        <v>0.029931</v>
       </c>
       <c r="F226" s="7">
-        <v>-0.201137</v>
+        <v>-0.159951</v>
       </c>
       <c r="G226" s="7">
-        <v>0.354755</v>
+        <v>0.366327</v>
       </c>
       <c r="H226" s="7">
-        <v>0.08519399999999999</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="I226" s="7">
-        <v>0.8806919999999999</v>
+        <v>0.877114</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10069,25 +10069,25 @@
         <v>4</v>
       </c>
       <c r="E227" s="7">
-        <v>0.055856</v>
+        <v>0.060086</v>
       </c>
       <c r="F227" s="7">
-        <v>0.041449</v>
+        <v>0.032685</v>
       </c>
       <c r="G227" s="7">
-        <v>0.19706900000000002</v>
+        <v>0.19731</v>
       </c>
       <c r="H227" s="7">
-        <v>0.102424</v>
+        <v>0.10143200000000001</v>
       </c>
       <c r="I227" s="7">
-        <v>0.458326</v>
+        <v>0.46273000000000003</v>
       </c>
       <c r="J227" s="7">
-        <v>2.1690899999999997</v>
+        <v>2.166238</v>
       </c>
       <c r="K227" s="7">
-        <v>5.600013000000001</v>
+        <v>5.583333</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10104,25 +10104,25 @@
         <v>3</v>
       </c>
       <c r="E228" s="7">
-        <v>0.044344999999999996</v>
+        <v>0.048728</v>
       </c>
       <c r="F228" s="7">
-        <v>0.071539</v>
+        <v>0.072423</v>
       </c>
       <c r="G228" s="7">
-        <v>0.21727799999999997</v>
+        <v>0.222865</v>
       </c>
       <c r="H228" s="7">
-        <v>0.134495</v>
+        <v>0.1387</v>
       </c>
       <c r="I228" s="7">
-        <v>0.43994999999999995</v>
+        <v>0.445818</v>
       </c>
       <c r="J228" s="7">
-        <v>1.7525579999999998</v>
+        <v>1.7627610000000002</v>
       </c>
       <c r="K228" s="7">
-        <v>4.541404</v>
+        <v>4.556385000000001</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.088535</v>
+        <v>0.09223100000000001</v>
       </c>
       <c r="F229" s="7">
-        <v>0.10287800000000001</v>
+        <v>0.104194</v>
       </c>
       <c r="G229" s="7">
-        <v>0.198777</v>
+        <v>0.209514</v>
       </c>
       <c r="H229" s="7">
-        <v>0.194554</v>
+        <v>0.197958</v>
       </c>
       <c r="I229" s="7">
-        <v>0.544114</v>
+        <v>0.552108</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10191,19 +10191,19 @@
         <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>0.113246</v>
+        <v>0.12185499999999999</v>
       </c>
       <c r="F231" s="7">
-        <v>0.135483</v>
+        <v>0.15254</v>
       </c>
       <c r="G231" s="7">
-        <v>0.327793</v>
+        <v>0.318264</v>
       </c>
       <c r="H231" s="7">
-        <v>0.325011</v>
+        <v>0.338979</v>
       </c>
       <c r="I231" s="7">
-        <v>0.546566</v>
+        <v>0.551173</v>
       </c>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10222,19 +10222,19 @@
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.10815</v>
+        <v>0.11827299999999999</v>
       </c>
       <c r="F232" s="7">
-        <v>0.060584</v>
+        <v>0.06091</v>
       </c>
       <c r="G232" s="7">
-        <v>0.234392</v>
+        <v>0.23848</v>
       </c>
       <c r="H232" s="7">
-        <v>0.20255199999999998</v>
+        <v>0.205946</v>
       </c>
       <c r="I232" s="7">
-        <v>0.505822</v>
+        <v>0.5139330000000001</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10253,25 +10253,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.036511</v>
+        <v>0.035932</v>
       </c>
       <c r="F233" s="7">
-        <v>0.059785000000000005</v>
+        <v>0.053539</v>
       </c>
       <c r="G233" s="7">
-        <v>0.173265</v>
+        <v>0.17022700000000002</v>
       </c>
       <c r="H233" s="7">
-        <v>0.105103</v>
+        <v>0.103645</v>
       </c>
       <c r="I233" s="7">
-        <v>0.368758</v>
+        <v>0.36764899999999995</v>
       </c>
       <c r="J233" s="7">
-        <v>1.49895</v>
+        <v>1.495652</v>
       </c>
       <c r="K233" s="7">
-        <v>4.323061</v>
+        <v>4.3127260000000005</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10288,19 +10288,19 @@
         <v>3</v>
       </c>
       <c r="E234" s="7">
-        <v>0.050956</v>
+        <v>0.052115999999999996</v>
       </c>
       <c r="F234" s="7">
-        <v>0.041837</v>
+        <v>0.018258</v>
       </c>
       <c r="G234" s="7">
-        <v>0.225205</v>
+        <v>0.22299600000000003</v>
       </c>
       <c r="H234" s="7">
-        <v>0.161921</v>
+        <v>0.158469</v>
       </c>
       <c r="I234" s="7">
-        <v>0.462111</v>
+        <v>0.46584000000000003</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10319,19 +10319,19 @@
         <v>4</v>
       </c>
       <c r="E235" s="7">
-        <v>0.050354</v>
+        <v>0.050558</v>
       </c>
       <c r="F235" s="7">
-        <v>0.051916000000000004</v>
+        <v>0.040907</v>
       </c>
       <c r="G235" s="7">
-        <v>0.207309</v>
+        <v>0.20325600000000002</v>
       </c>
       <c r="H235" s="7">
-        <v>0.09987299999999999</v>
+        <v>0.09711600000000001</v>
       </c>
       <c r="I235" s="7">
-        <v>0.471768</v>
+        <v>0.468635</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10350,19 +10350,19 @@
         <v>2</v>
       </c>
       <c r="E236" s="7">
-        <v>0.032612</v>
+        <v>0.033035</v>
       </c>
       <c r="F236" s="7">
-        <v>0.095169</v>
+        <v>0.092824</v>
       </c>
       <c r="G236" s="7">
-        <v>0.19778600000000002</v>
+        <v>0.198349</v>
       </c>
       <c r="H236" s="7">
-        <v>0.126961</v>
+        <v>0.128602</v>
       </c>
       <c r="I236" s="7">
-        <v>0.473193</v>
+        <v>0.475063</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10381,25 +10381,25 @@
         <v>6</v>
       </c>
       <c r="E237" s="7">
-        <v>0.020099999999999996</v>
+        <v>0.0006569999999999999</v>
       </c>
       <c r="F237" s="7">
-        <v>-0.11335699999999999</v>
+        <v>-0.09679299999999999</v>
       </c>
       <c r="G237" s="7">
-        <v>0.16460999999999998</v>
+        <v>0.18194400000000002</v>
       </c>
       <c r="H237" s="7">
-        <v>0.077467</v>
+        <v>0.069848</v>
       </c>
       <c r="I237" s="7">
-        <v>0.5946560000000001</v>
+        <v>0.577338</v>
       </c>
       <c r="J237" s="7">
-        <v>4.185021</v>
+        <v>4.148357</v>
       </c>
       <c r="K237" s="7">
-        <v>13.943765</v>
+        <v>13.823556000000002</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10416,14 +10416,14 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.047257</v>
+        <v>0.049995000000000005</v>
       </c>
       <c r="F238" s="7">
-        <v>0.01015</v>
+        <v>0.004521</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7">
-        <v>0.039638</v>
+        <v>0.036187</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
@@ -10443,19 +10443,19 @@
         <v>6</v>
       </c>
       <c r="E239" s="7">
-        <v>0.152601</v>
+        <v>0.15955</v>
       </c>
       <c r="F239" s="7">
-        <v>0.158838</v>
+        <v>0.182549</v>
       </c>
       <c r="G239" s="7">
-        <v>0.290256</v>
+        <v>0.29386</v>
       </c>
       <c r="H239" s="7">
-        <v>0.276821</v>
+        <v>0.289369</v>
       </c>
       <c r="I239" s="7">
-        <v>0.6694209999999999</v>
+        <v>0.679281</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10474,19 +10474,19 @@
         <v>5</v>
       </c>
       <c r="E240" s="7">
-        <v>0.101059</v>
+        <v>0.108244</v>
       </c>
       <c r="F240" s="7">
-        <v>0.050971</v>
+        <v>0.034617</v>
       </c>
       <c r="G240" s="7">
-        <v>0.20839</v>
+        <v>0.211234</v>
       </c>
       <c r="H240" s="7">
-        <v>0.164157</v>
+        <v>0.16575700000000002</v>
       </c>
       <c r="I240" s="7">
-        <v>0.482682</v>
+        <v>0.495473</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10505,25 +10505,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.032002</v>
+        <v>0.030763</v>
       </c>
       <c r="F241" s="7">
-        <v>0.038723</v>
+        <v>0.039162</v>
       </c>
       <c r="G241" s="7">
-        <v>0.087447</v>
+        <v>0.08775000000000001</v>
       </c>
       <c r="H241" s="7">
-        <v>0.051959</v>
+        <v>0.052428999999999996</v>
       </c>
       <c r="I241" s="7">
-        <v>0.22602799999999998</v>
+        <v>0.226304</v>
       </c>
       <c r="J241" s="7">
-        <v>1.831544</v>
+        <v>1.832808</v>
       </c>
       <c r="K241" s="7">
-        <v>5.912767</v>
+        <v>5.905748999999999</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10540,25 +10540,25 @@
         <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.022396</v>
+        <v>0.024093</v>
       </c>
       <c r="F242" s="7">
-        <v>0.046865</v>
+        <v>0.044751000000000006</v>
       </c>
       <c r="G242" s="7">
-        <v>0.213387</v>
+        <v>0.20805099999999999</v>
       </c>
       <c r="H242" s="7">
-        <v>0.08202400000000001</v>
+        <v>0.08201399999999999</v>
       </c>
       <c r="I242" s="7">
-        <v>0.20683900000000002</v>
+        <v>0.20968499999999998</v>
       </c>
       <c r="J242" s="7">
-        <v>1.951939</v>
+        <v>1.95191</v>
       </c>
       <c r="K242" s="7">
-        <v>5.862704</v>
+        <v>5.837667</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10575,25 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.09129300000000001</v>
+        <v>0.09897399999999999</v>
       </c>
       <c r="F243" s="7">
-        <v>0.014776000000000001</v>
+        <v>-0.014745999999999999</v>
       </c>
       <c r="G243" s="7">
-        <v>0.256357</v>
+        <v>0.255874</v>
       </c>
       <c r="H243" s="7">
-        <v>0.18726199999999998</v>
+        <v>0.184975</v>
       </c>
       <c r="I243" s="7">
-        <v>0.44821399999999995</v>
+        <v>0.459279</v>
       </c>
       <c r="J243" s="7">
-        <v>2.853831</v>
+        <v>2.846406</v>
       </c>
       <c r="K243" s="7">
-        <v>14.87759</v>
+        <v>14.693051</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10610,25 @@
         <v>3</v>
       </c>
       <c r="E244" s="7">
-        <v>0.048302</v>
+        <v>0.048344</v>
       </c>
       <c r="F244" s="7">
-        <v>0.062541</v>
+        <v>0.060393999999999996</v>
       </c>
       <c r="G244" s="7">
-        <v>0.21077</v>
+        <v>0.21489</v>
       </c>
       <c r="H244" s="7">
-        <v>0.140302</v>
+        <v>0.142869</v>
       </c>
       <c r="I244" s="7">
-        <v>0.445299</v>
+        <v>0.44555700000000004</v>
       </c>
       <c r="J244" s="7">
-        <v>1.774348</v>
+        <v>1.780594</v>
       </c>
       <c r="K244" s="7">
-        <v>4.58043</v>
+        <v>4.586712</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10645,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.051935</v>
+        <v>0.054719</v>
       </c>
       <c r="F245" s="7">
-        <v>0.002662</v>
+        <v>-0.008122</v>
       </c>
       <c r="G245" s="7">
-        <v>0.162094</v>
+        <v>0.158222</v>
       </c>
       <c r="H245" s="7">
-        <v>0.067065</v>
+        <v>0.063248</v>
       </c>
       <c r="I245" s="7">
-        <v>0.387824</v>
+        <v>0.38854500000000003</v>
       </c>
       <c r="J245" s="7">
-        <v>1.4608400000000001</v>
+        <v>1.452037</v>
       </c>
       <c r="K245" s="7">
-        <v>3.8332960000000003</v>
+        <v>3.801884</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10680,25 @@
         <v>2</v>
       </c>
       <c r="E246" s="7">
-        <v>0.042809999999999994</v>
+        <v>0.044924</v>
       </c>
       <c r="F246" s="7">
-        <v>0.083757</v>
+        <v>0.077754</v>
       </c>
       <c r="G246" s="7">
-        <v>0.213918</v>
+        <v>0.213568</v>
       </c>
       <c r="H246" s="7">
-        <v>0.12867499999999998</v>
+        <v>0.129763</v>
       </c>
       <c r="I246" s="7">
-        <v>0.516631</v>
+        <v>0.518562</v>
       </c>
       <c r="J246" s="7">
-        <v>4.299912</v>
+        <v>4.305023</v>
       </c>
       <c r="K246" s="7">
-        <v>7.143006000000001</v>
+        <v>7.14736</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10715,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.067786</v>
+        <v>0.070337</v>
       </c>
       <c r="F247" s="7">
-        <v>0.064813</v>
+        <v>0.046403</v>
       </c>
       <c r="G247" s="7">
-        <v>0.256171</v>
+        <v>0.254243</v>
       </c>
       <c r="H247" s="7">
-        <v>0.175387</v>
+        <v>0.173475</v>
       </c>
       <c r="I247" s="7">
-        <v>0.510229</v>
+        <v>0.513634</v>
       </c>
       <c r="J247" s="7">
-        <v>3.2353620000000003</v>
+        <v>3.228473</v>
       </c>
       <c r="K247" s="7">
-        <v>8.582491</v>
+        <v>8.53144</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10750,25 @@
         <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>0.074195</v>
+        <v>0.078547</v>
       </c>
       <c r="F248" s="7">
-        <v>0.047082</v>
+        <v>0.02469</v>
       </c>
       <c r="G248" s="7">
-        <v>0.26056999999999997</v>
+        <v>0.259336</v>
       </c>
       <c r="H248" s="7">
-        <v>0.184666</v>
+        <v>0.182817</v>
       </c>
       <c r="I248" s="7">
-        <v>0.506795</v>
+        <v>0.513848</v>
       </c>
       <c r="J248" s="7">
-        <v>3.8244409999999998</v>
+        <v>3.816913</v>
       </c>
       <c r="K248" s="7">
-        <v>11.593788</v>
+        <v>11.509849999999998</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10785,25 @@
         <v>6</v>
       </c>
       <c r="E249" s="7">
-        <v>0.078683</v>
+        <v>0.085013</v>
       </c>
       <c r="F249" s="7">
-        <v>0.027010999999999997</v>
+        <v>-0.000567</v>
       </c>
       <c r="G249" s="7">
-        <v>0.265528</v>
+        <v>0.265519</v>
       </c>
       <c r="H249" s="7">
-        <v>0.192331</v>
+        <v>0.190552</v>
       </c>
       <c r="I249" s="7">
-        <v>0.46631900000000004</v>
+        <v>0.47761200000000004</v>
       </c>
       <c r="J249" s="7">
-        <v>3.459728</v>
+        <v>3.453073</v>
       </c>
       <c r="K249" s="7">
-        <v>14.203276</v>
+        <v>14.086601</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10820,25 @@
         <v>3</v>
       </c>
       <c r="E250" s="7">
-        <v>0.053094999999999996</v>
+        <v>0.056853999999999995</v>
       </c>
       <c r="F250" s="7">
-        <v>0.081747</v>
+        <v>0.080739</v>
       </c>
       <c r="G250" s="7">
-        <v>0.206686</v>
+        <v>0.20945599999999998</v>
       </c>
       <c r="H250" s="7">
-        <v>0.157325</v>
+        <v>0.159685</v>
       </c>
       <c r="I250" s="7">
-        <v>0.450111</v>
+        <v>0.45549599999999996</v>
       </c>
       <c r="J250" s="7">
-        <v>2.024621</v>
+        <v>2.030787</v>
       </c>
       <c r="K250" s="7">
-        <v>5.623259000000001</v>
+        <v>5.620565</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10855,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.086686</v>
+        <v>0.093711</v>
       </c>
       <c r="F251" s="7">
-        <v>0.085616</v>
+        <v>0.082847</v>
       </c>
       <c r="G251" s="7">
-        <v>0.246056</v>
+        <v>0.25101</v>
       </c>
       <c r="H251" s="7">
-        <v>0.20839400000000002</v>
+        <v>0.21085399999999999</v>
       </c>
       <c r="I251" s="7">
-        <v>0.50097</v>
+        <v>0.5115</v>
       </c>
       <c r="J251" s="7">
-        <v>3.069284</v>
+        <v>3.07757</v>
       </c>
       <c r="K251" s="7">
-        <v>9.891098</v>
+        <v>9.886219</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10890,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.09951</v>
+        <v>0.10800599999999999</v>
       </c>
       <c r="F252" s="7">
-        <v>0.083483</v>
+        <v>0.080653</v>
       </c>
       <c r="G252" s="7">
-        <v>0.25360099999999997</v>
+        <v>0.259274</v>
       </c>
       <c r="H252" s="7">
-        <v>0.223968</v>
+        <v>0.226659</v>
       </c>
       <c r="I252" s="7">
-        <v>0.508675</v>
+        <v>0.521797</v>
       </c>
       <c r="J252" s="7">
-        <v>3.2675929999999997</v>
+        <v>3.276974</v>
       </c>
       <c r="K252" s="7">
-        <v>10.995446</v>
+        <v>10.969453000000001</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10925,25 @@
         <v>4</v>
       </c>
       <c r="E253" s="7">
-        <v>0.04201800000000001</v>
+        <v>0.043972</v>
       </c>
       <c r="F253" s="7">
-        <v>0.0071330000000000005</v>
+        <v>-0.001473</v>
       </c>
       <c r="G253" s="7">
-        <v>0.149027</v>
+        <v>0.145094</v>
       </c>
       <c r="H253" s="7">
-        <v>0.060267</v>
+        <v>0.057020999999999995</v>
       </c>
       <c r="I253" s="7">
-        <v>0.37858400000000003</v>
+        <v>0.37975200000000003</v>
       </c>
       <c r="J253" s="7">
-        <v>1.828849</v>
+        <v>1.820188</v>
       </c>
       <c r="K253" s="7">
-        <v>5.0133659999999995</v>
+        <v>4.988285</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10960,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.058772000000000005</v>
+        <v>0.057367999999999995</v>
       </c>
       <c r="F254" s="7">
-        <v>0.028274</v>
+        <v>0.017065</v>
       </c>
       <c r="G254" s="7">
-        <v>0.22427</v>
+        <v>0.230138</v>
       </c>
       <c r="H254" s="7">
-        <v>0.157225</v>
+        <v>0.156422</v>
       </c>
       <c r="I254" s="7">
-        <v>0.530331</v>
+        <v>0.531405</v>
       </c>
       <c r="J254" s="7">
-        <v>2.8565660000000004</v>
+        <v>2.853891</v>
       </c>
       <c r="K254" s="7">
-        <v>6.125678000000001</v>
+        <v>6.104901999999999</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +10995,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.043916000000000004</v>
+        <v>0.040674</v>
       </c>
       <c r="F255" s="7">
-        <v>0.026993</v>
+        <v>0.018641</v>
       </c>
       <c r="G255" s="7">
-        <v>0.212397</v>
+        <v>0.215883</v>
       </c>
       <c r="H255" s="7">
-        <v>0.14261200000000002</v>
+        <v>0.141596</v>
       </c>
       <c r="I255" s="7">
-        <v>0.508636</v>
+        <v>0.507713</v>
       </c>
       <c r="J255" s="7">
-        <v>2.7951490000000003</v>
+        <v>2.791776</v>
       </c>
       <c r="K255" s="7">
-        <v>5.283101</v>
+        <v>5.267256</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11030,25 @@
         <v>5</v>
       </c>
       <c r="E256" s="7">
-        <v>0.075371</v>
+        <v>0.075883</v>
       </c>
       <c r="F256" s="7">
-        <v>0.033446</v>
+        <v>0.016628</v>
       </c>
       <c r="G256" s="7">
-        <v>0.24579499999999999</v>
+        <v>0.25093499999999996</v>
       </c>
       <c r="H256" s="7">
-        <v>0.178476</v>
+        <v>0.178104</v>
       </c>
       <c r="I256" s="7">
-        <v>0.553159</v>
+        <v>0.559032</v>
       </c>
       <c r="J256" s="7">
-        <v>2.907672</v>
+        <v>2.90644</v>
       </c>
       <c r="K256" s="7">
-        <v>7.454725</v>
+        <v>7.41715</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11065,25 @@
         <v>6</v>
       </c>
       <c r="E257" s="7">
-        <v>0.012892999999999998</v>
+        <v>-0.000065</v>
       </c>
       <c r="F257" s="7">
-        <v>-0.122819</v>
+        <v>-0.107171</v>
       </c>
       <c r="G257" s="7">
-        <v>0.150851</v>
+        <v>0.171688</v>
       </c>
       <c r="H257" s="7">
-        <v>0.06852</v>
+        <v>0.06606200000000001</v>
       </c>
       <c r="I257" s="7">
-        <v>0.596959</v>
+        <v>0.583704</v>
       </c>
       <c r="J257" s="7">
-        <v>4.049436</v>
+        <v>4.037821</v>
       </c>
       <c r="K257" s="7">
-        <v>13.81287</v>
+        <v>13.763669</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11100,25 @@
         <v>2</v>
       </c>
       <c r="E258" s="7">
-        <v>0.030013</v>
+        <v>0.034211</v>
       </c>
       <c r="F258" s="7">
-        <v>0.08886799999999999</v>
+        <v>0.085786</v>
       </c>
       <c r="G258" s="7">
-        <v>0.190434</v>
+        <v>0.191847</v>
       </c>
       <c r="H258" s="7">
-        <v>0.136542</v>
+        <v>0.13897700000000002</v>
       </c>
       <c r="I258" s="7">
-        <v>0.428994</v>
+        <v>0.430666</v>
       </c>
       <c r="J258" s="7">
-        <v>2.379277</v>
+        <v>2.3865190000000003</v>
       </c>
       <c r="K258" s="7">
-        <v>4.446811</v>
+        <v>4.45637</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11135,25 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.106862</v>
+        <v>0.104242</v>
       </c>
       <c r="F259" s="7">
-        <v>-0.017375</v>
+        <v>-0.012362</v>
       </c>
       <c r="G259" s="7">
-        <v>0.204312</v>
+        <v>0.18665299999999999</v>
       </c>
       <c r="H259" s="7">
-        <v>0.114133</v>
+        <v>0.108976</v>
       </c>
       <c r="I259" s="7">
-        <v>0.623912</v>
+        <v>0.620695</v>
       </c>
       <c r="J259" s="7">
-        <v>4.629378</v>
+        <v>4.603324</v>
       </c>
       <c r="K259" s="7">
-        <v>20.632699</v>
+        <v>20.340123000000002</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,10 +11170,10 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.020932</v>
+        <v>0.000199</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.076972</v>
+        <v>-0.060144</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -11195,22 +11195,22 @@
         <v>3</v>
       </c>
       <c r="E261" s="7">
-        <v>0.058990999999999995</v>
+        <v>0.063697</v>
       </c>
       <c r="F261" s="7">
-        <v>0.083494</v>
+        <v>0.08318400000000001</v>
       </c>
       <c r="G261" s="7">
-        <v>0.23152999999999999</v>
+        <v>0.237571</v>
       </c>
       <c r="H261" s="7">
-        <v>0.16756000000000001</v>
+        <v>0.171934</v>
       </c>
       <c r="I261" s="7">
-        <v>0.504933</v>
+        <v>0.513078</v>
       </c>
       <c r="J261" s="7">
-        <v>2.221954</v>
+        <v>2.234025</v>
       </c>
       <c r="K261" s="7"/>
     </row>
@@ -11228,22 +11228,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.02689</v>
+        <v>0.031570999999999995</v>
       </c>
       <c r="F262" s="7">
-        <v>0.050617</v>
+        <v>0.05075</v>
       </c>
       <c r="G262" s="7">
-        <v>0.149301</v>
+        <v>0.14695</v>
       </c>
       <c r="H262" s="7">
-        <v>0.071996</v>
+        <v>0.07466300000000001</v>
       </c>
       <c r="I262" s="7">
-        <v>0.50113</v>
+        <v>0.508272</v>
       </c>
       <c r="J262" s="7">
-        <v>2.7216039999999997</v>
+        <v>2.7308640000000004</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11261,19 +11261,19 @@
         <v>5</v>
       </c>
       <c r="E263" s="7">
-        <v>0.084718</v>
+        <v>0.088686</v>
       </c>
       <c r="F263" s="7">
-        <v>0.0031019999999999997</v>
+        <v>-0.030796999999999998</v>
       </c>
       <c r="G263" s="7">
-        <v>0.271838</v>
+        <v>0.246467</v>
       </c>
       <c r="H263" s="7">
-        <v>0.178889</v>
+        <v>0.17397200000000002</v>
       </c>
       <c r="I263" s="7">
-        <v>0.42615400000000003</v>
+        <v>0.4385</v>
       </c>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11292,22 +11292,22 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.163631</v>
+        <v>0.172422</v>
       </c>
       <c r="F264" s="7">
-        <v>0.09772700000000001</v>
+        <v>0.117483</v>
       </c>
       <c r="G264" s="7">
-        <v>0.194006</v>
+        <v>0.194749</v>
       </c>
       <c r="H264" s="7">
-        <v>0.19462900000000002</v>
+        <v>0.20598</v>
       </c>
       <c r="I264" s="7">
-        <v>0.5151870000000001</v>
+        <v>0.513795</v>
       </c>
       <c r="J264" s="7">
-        <v>3.271497</v>
+        <v>3.312087</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11325,19 +11325,19 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.029443</v>
+        <v>0.035752</v>
       </c>
       <c r="F265" s="7">
-        <v>0.059170999999999994</v>
+        <v>0.068686</v>
       </c>
       <c r="G265" s="7">
-        <v>0.15239</v>
+        <v>0.16802</v>
       </c>
       <c r="H265" s="7">
-        <v>0.12439299999999999</v>
+        <v>0.13128399999999998</v>
       </c>
       <c r="I265" s="7">
-        <v>0.2727</v>
+        <v>0.279221</v>
       </c>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
@@ -11356,18 +11356,20 @@
         <v>2</v>
       </c>
       <c r="E266" s="7">
-        <v>0.031641</v>
+        <v>0.031675</v>
       </c>
       <c r="F266" s="7">
-        <v>0.09904</v>
+        <v>0.095983</v>
       </c>
       <c r="G266" s="7">
-        <v>0.206207</v>
+        <v>0.206314</v>
       </c>
       <c r="H266" s="7">
-        <v>0.12920500000000001</v>
-      </c>
-      <c r="I266" s="7"/>
+        <v>0.13050499999999998</v>
+      </c>
+      <c r="I266" s="7">
+        <v>0.47869999999999996</v>
+      </c>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
     </row>
@@ -11385,22 +11387,22 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.034693999999999996</v>
+        <v>0.033908</v>
       </c>
       <c r="F267" s="7">
-        <v>0.065885</v>
+        <v>0.048732</v>
       </c>
       <c r="G267" s="7">
-        <v>0.19438199999999997</v>
+        <v>0.191855</v>
       </c>
       <c r="H267" s="7">
-        <v>0.12277900000000001</v>
+        <v>0.122348</v>
       </c>
       <c r="I267" s="7">
-        <v>0.47942300000000004</v>
+        <v>0.480447</v>
       </c>
       <c r="J267" s="7">
-        <v>3.0882229999999997</v>
+        <v>3.086655</v>
       </c>
       <c r="K267" s="7"/>
     </row>
@@ -11418,22 +11420,22 @@
         <v>5</v>
       </c>
       <c r="E268" s="7">
-        <v>0.043845999999999996</v>
+        <v>0.045481999999999995</v>
       </c>
       <c r="F268" s="7">
-        <v>0.046013</v>
+        <v>0.008602</v>
       </c>
       <c r="G268" s="7">
-        <v>0.19941099999999998</v>
+        <v>0.1925</v>
       </c>
       <c r="H268" s="7">
-        <v>0.12908899999999998</v>
+        <v>0.126825</v>
       </c>
       <c r="I268" s="7">
-        <v>0.565084</v>
+        <v>0.570343</v>
       </c>
       <c r="J268" s="7">
-        <v>2.8805880000000004</v>
+        <v>2.8728070000000003</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11451,19 +11453,19 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.057119</v>
+        <v>0.058995</v>
       </c>
       <c r="F269" s="7">
-        <v>0.067765</v>
+        <v>0.063032</v>
       </c>
       <c r="G269" s="7">
-        <v>0.19563</v>
+        <v>0.192082</v>
       </c>
       <c r="H269" s="7">
-        <v>0.124006</v>
+        <v>0.12389599999999999</v>
       </c>
       <c r="I269" s="7">
-        <v>0.487723</v>
+        <v>0.489645</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11482,19 +11484,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.090056</v>
+        <v>0.08933400000000001</v>
       </c>
       <c r="F270" s="7">
-        <v>0.09060700000000001</v>
+        <v>0.082037</v>
       </c>
       <c r="G270" s="7">
-        <v>0.149669</v>
+        <v>0.159719</v>
       </c>
       <c r="H270" s="7">
-        <v>0.157959</v>
+        <v>0.152512</v>
       </c>
       <c r="I270" s="7">
-        <v>0.505486</v>
+        <v>0.497657</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11513,19 +11515,19 @@
         <v>4</v>
       </c>
       <c r="E271" s="7">
-        <v>0.065735</v>
+        <v>0.06381</v>
       </c>
       <c r="F271" s="7">
-        <v>0.054946</v>
+        <v>0.05098900000000001</v>
       </c>
       <c r="G271" s="7">
-        <v>0.221238</v>
+        <v>0.24442</v>
       </c>
       <c r="H271" s="7">
-        <v>0.186115</v>
+        <v>0.182031</v>
       </c>
       <c r="I271" s="7">
-        <v>0.358579</v>
+        <v>0.363946</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11544,19 +11546,19 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.044932999999999994</v>
+        <v>0.050136</v>
       </c>
       <c r="F272" s="7">
-        <v>0.072918</v>
+        <v>0.064377</v>
       </c>
       <c r="G272" s="7">
-        <v>0.213989</v>
+        <v>0.216159</v>
       </c>
       <c r="H272" s="7">
-        <v>0.18208100000000002</v>
+        <v>0.18067599999999998</v>
       </c>
       <c r="I272" s="7">
-        <v>0.33079000000000003</v>
+        <v>0.326493</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11575,19 +11577,19 @@
         <v>6</v>
       </c>
       <c r="E273" s="7">
-        <v>0.142178</v>
+        <v>0.142547</v>
       </c>
       <c r="F273" s="7">
-        <v>0.129141</v>
+        <v>0.143404</v>
       </c>
       <c r="G273" s="7">
-        <v>0.27991499999999997</v>
+        <v>0.269253</v>
       </c>
       <c r="H273" s="7">
-        <v>0.302384</v>
+        <v>0.311849</v>
       </c>
       <c r="I273" s="7">
-        <v>0.520494</v>
+        <v>0.52085</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11606,22 +11608,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.037178</v>
+        <v>0.034872</v>
       </c>
       <c r="F274" s="7">
-        <v>0.03788</v>
+        <v>0.010237000000000001</v>
       </c>
       <c r="G274" s="7">
-        <v>0.191111</v>
+        <v>0.18328</v>
       </c>
       <c r="H274" s="7">
-        <v>0.11980299999999999</v>
+        <v>0.115305</v>
       </c>
       <c r="I274" s="7">
-        <v>0.501883</v>
+        <v>0.501691</v>
       </c>
       <c r="J274" s="7">
-        <v>3.0475369999999997</v>
+        <v>3.031278</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -11639,25 +11641,25 @@
         <v>5</v>
       </c>
       <c r="E275" s="7">
-        <v>0.078231</v>
+        <v>0.086773</v>
       </c>
       <c r="F275" s="7">
-        <v>0.08606</v>
+        <v>0.09040200000000001</v>
       </c>
       <c r="G275" s="7">
-        <v>0.287437</v>
+        <v>0.295083</v>
       </c>
       <c r="H275" s="7">
-        <v>0.206399</v>
+        <v>0.21162</v>
       </c>
       <c r="I275" s="7">
-        <v>0.557506</v>
+        <v>0.568013</v>
       </c>
       <c r="J275" s="7">
-        <v>2.526026</v>
+        <v>2.541287</v>
       </c>
       <c r="K275" s="7">
-        <v>6.557569</v>
+        <v>6.57981</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11674,25 +11676,25 @@
         <v>2</v>
       </c>
       <c r="E276" s="7">
-        <v>0.032803</v>
+        <v>0.03199</v>
       </c>
       <c r="F276" s="7">
-        <v>0.09137600000000001</v>
+        <v>0.086089</v>
       </c>
       <c r="G276" s="7">
-        <v>0.20025600000000002</v>
+        <v>0.19893899999999998</v>
       </c>
       <c r="H276" s="7">
-        <v>0.125473</v>
+        <v>0.12543200000000002</v>
       </c>
       <c r="I276" s="7">
-        <v>0.47510800000000003</v>
+        <v>0.473473</v>
       </c>
       <c r="J276" s="7">
-        <v>2.197363</v>
+        <v>2.197247</v>
       </c>
       <c r="K276" s="7">
-        <v>4.1335370000000005</v>
+        <v>4.131114</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11709,25 +11711,25 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.056612</v>
+        <v>0.05742</v>
       </c>
       <c r="F277" s="7">
-        <v>0.003172</v>
+        <v>0.008961</v>
       </c>
       <c r="G277" s="7">
-        <v>0.104879</v>
+        <v>0.107056</v>
       </c>
       <c r="H277" s="7">
-        <v>0.041201</v>
+        <v>0.041871</v>
       </c>
       <c r="I277" s="7">
-        <v>0.300089</v>
+        <v>0.30118500000000004</v>
       </c>
       <c r="J277" s="7">
-        <v>1.7480660000000001</v>
+        <v>1.749834</v>
       </c>
       <c r="K277" s="7">
-        <v>5.165854</v>
+        <v>5.159154999999999</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11744,25 +11746,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.09015599999999999</v>
+        <v>0.096298</v>
       </c>
       <c r="F278" s="7">
-        <v>0.026174</v>
+        <v>-0.010055000000000001</v>
       </c>
       <c r="G278" s="7">
-        <v>0.232319</v>
+        <v>0.22514800000000001</v>
       </c>
       <c r="H278" s="7">
-        <v>0.184971</v>
+        <v>0.179292</v>
       </c>
       <c r="I278" s="7">
-        <v>0.41125300000000004</v>
+        <v>0.419009</v>
       </c>
       <c r="J278" s="7">
-        <v>2.473362</v>
+        <v>2.456714</v>
       </c>
       <c r="K278" s="7">
-        <v>12.671492</v>
+        <v>12.481174000000001</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11779,25 +11781,25 @@
         <v>4</v>
       </c>
       <c r="E279" s="7">
-        <v>0.05425</v>
+        <v>0.057629</v>
       </c>
       <c r="F279" s="7">
-        <v>0.010343999999999999</v>
+        <v>0.000241</v>
       </c>
       <c r="G279" s="7">
-        <v>0.165128</v>
+        <v>0.16097999999999998</v>
       </c>
       <c r="H279" s="7">
-        <v>0.04217800000000001</v>
+        <v>0.039812</v>
       </c>
       <c r="I279" s="7">
-        <v>0.397368</v>
+        <v>0.39775799999999994</v>
       </c>
       <c r="J279" s="7">
-        <v>1.649863</v>
+        <v>1.6438480000000002</v>
       </c>
       <c r="K279" s="7">
-        <v>3.6561950000000003</v>
+        <v>3.633433</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11814,25 +11816,25 @@
         <v>6</v>
       </c>
       <c r="E280" s="7">
-        <v>0.080703</v>
+        <v>0.08708199999999999</v>
       </c>
       <c r="F280" s="7">
-        <v>0.08243</v>
+        <v>0.07609300000000001</v>
       </c>
       <c r="G280" s="7">
-        <v>0.23431100000000002</v>
+        <v>0.240059</v>
       </c>
       <c r="H280" s="7">
-        <v>0.191406</v>
+        <v>0.192903</v>
       </c>
       <c r="I280" s="7">
-        <v>0.476421</v>
+        <v>0.484165</v>
       </c>
       <c r="J280" s="7">
-        <v>2.70193</v>
+        <v>2.706583</v>
       </c>
       <c r="K280" s="7">
-        <v>10.095842</v>
+        <v>10.056523</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11849,25 +11851,25 @@
         <v>3</v>
       </c>
       <c r="E281" s="7">
-        <v>0.041231</v>
+        <v>0.041456</v>
       </c>
       <c r="F281" s="7">
-        <v>0.08656599999999999</v>
+        <v>0.075944</v>
       </c>
       <c r="G281" s="7">
-        <v>0.204024</v>
+        <v>0.201206</v>
       </c>
       <c r="H281" s="7">
-        <v>0.137428</v>
+        <v>0.137685</v>
       </c>
       <c r="I281" s="7">
-        <v>0.473311</v>
+        <v>0.471254</v>
       </c>
       <c r="J281" s="7">
-        <v>2.9536290000000003</v>
+        <v>2.954524</v>
       </c>
       <c r="K281" s="7">
-        <v>5.290343</v>
+        <v>5.288651</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11884,25 +11886,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.033962</v>
+        <v>0.03487</v>
       </c>
       <c r="F282" s="7">
-        <v>0.068501</v>
+        <v>0.065791</v>
       </c>
       <c r="G282" s="7">
-        <v>0.181361</v>
+        <v>0.180409</v>
       </c>
       <c r="H282" s="7">
-        <v>0.098713</v>
+        <v>0.098697</v>
       </c>
       <c r="I282" s="7">
-        <v>0.455152</v>
+        <v>0.454694</v>
       </c>
       <c r="J282" s="7">
-        <v>2.2845969999999998</v>
+        <v>2.284549</v>
       </c>
       <c r="K282" s="7">
-        <v>4.21143</v>
+        <v>4.203958</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11919,25 +11921,25 @@
         <v>5</v>
       </c>
       <c r="E283" s="7">
-        <v>0.046851000000000004</v>
+        <v>0.042054</v>
       </c>
       <c r="F283" s="7">
-        <v>0.029356</v>
+        <v>0.027789</v>
       </c>
       <c r="G283" s="7">
-        <v>0.075567</v>
+        <v>0.074739</v>
       </c>
       <c r="H283" s="7">
-        <v>0.033037000000000004</v>
+        <v>0.030127</v>
       </c>
       <c r="I283" s="7">
-        <v>0.283795</v>
+        <v>0.277094</v>
       </c>
       <c r="J283" s="7">
-        <v>1.9380410000000001</v>
+        <v>1.9297630000000001</v>
       </c>
       <c r="K283" s="7">
-        <v>5.915166</v>
+        <v>5.888524</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11954,25 +11956,25 @@
         <v>3</v>
       </c>
       <c r="E284" s="7">
-        <v>0.035242</v>
+        <v>0.036535000000000005</v>
       </c>
       <c r="F284" s="7">
-        <v>0.049551</v>
+        <v>0.040581</v>
       </c>
       <c r="G284" s="7">
-        <v>0.21677</v>
+        <v>0.21405200000000002</v>
       </c>
       <c r="H284" s="7">
-        <v>0.058871</v>
+        <v>0.057156000000000005</v>
       </c>
       <c r="I284" s="7">
-        <v>0.42948300000000006</v>
+        <v>0.42743200000000003</v>
       </c>
       <c r="J284" s="7">
-        <v>1.9692560000000001</v>
+        <v>1.964447</v>
       </c>
       <c r="K284" s="7">
-        <v>3.623618</v>
+        <v>3.614087</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11989,25 +11991,25 @@
         <v>5</v>
       </c>
       <c r="E285" s="7">
-        <v>0.048612999999999996</v>
+        <v>0.049815</v>
       </c>
       <c r="F285" s="7">
-        <v>0.067703</v>
+        <v>0.0603</v>
       </c>
       <c r="G285" s="7">
-        <v>0.236691</v>
+        <v>0.237044</v>
       </c>
       <c r="H285" s="7">
-        <v>0.155534</v>
+        <v>0.15535</v>
       </c>
       <c r="I285" s="7">
-        <v>0.51315</v>
+        <v>0.519481</v>
       </c>
       <c r="J285" s="7">
-        <v>2.656767</v>
+        <v>2.656185</v>
       </c>
       <c r="K285" s="7">
-        <v>9.382695</v>
+        <v>9.343699</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12024,25 +12026,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>-0.000877</v>
+        <v>-0.009599</v>
       </c>
       <c r="F286" s="7">
-        <v>-0.125511</v>
+        <v>-0.109302</v>
       </c>
       <c r="G286" s="7">
-        <v>0.134651</v>
+        <v>0.137359</v>
       </c>
       <c r="H286" s="7">
-        <v>0.038697</v>
+        <v>0.03469</v>
       </c>
       <c r="I286" s="7">
-        <v>0.553851</v>
+        <v>0.539803</v>
       </c>
       <c r="J286" s="7">
-        <v>4.097919</v>
+        <v>4.078251</v>
       </c>
       <c r="K286" s="7">
-        <v>13.833300999999999</v>
+        <v>13.762991</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12059,25 +12061,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.053319</v>
+        <v>0.057460000000000004</v>
       </c>
       <c r="F287" s="7">
-        <v>0.084772</v>
+        <v>0.086351</v>
       </c>
       <c r="G287" s="7">
-        <v>0.248419</v>
+        <v>0.252815</v>
       </c>
       <c r="H287" s="7">
-        <v>0.161707</v>
+        <v>0.166141</v>
       </c>
       <c r="I287" s="7">
-        <v>0.482001</v>
+        <v>0.487854</v>
       </c>
       <c r="J287" s="7">
-        <v>1.343083</v>
+        <v>1.352026</v>
       </c>
       <c r="K287" s="7">
-        <v>3.715312</v>
+        <v>3.721393</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12094,25 +12096,25 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0.06334</v>
+        <v>0.07048700000000001</v>
       </c>
       <c r="F288" s="7">
-        <v>0.039812</v>
+        <v>0.011573</v>
       </c>
       <c r="G288" s="7">
-        <v>0.269549</v>
+        <v>0.259513</v>
       </c>
       <c r="H288" s="7">
-        <v>0.152334</v>
+        <v>0.152922</v>
       </c>
       <c r="I288" s="7">
-        <v>0.502089</v>
+        <v>0.511582</v>
       </c>
       <c r="J288" s="7">
-        <v>2.457043</v>
+        <v>2.4588069999999997</v>
       </c>
       <c r="K288" s="7">
-        <v>10.382892</v>
+        <v>10.326259</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12129,25 +12131,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.030177</v>
+        <v>0.015645</v>
       </c>
       <c r="F289" s="7">
-        <v>-0.157105</v>
+        <v>-0.130459</v>
       </c>
       <c r="G289" s="7">
-        <v>0.246839</v>
+        <v>0.252585</v>
       </c>
       <c r="H289" s="7">
-        <v>0.087156</v>
+        <v>0.08255499999999999</v>
       </c>
       <c r="I289" s="7">
-        <v>0.745125</v>
+        <v>0.7304609999999999</v>
       </c>
       <c r="J289" s="7">
-        <v>4.136573</v>
+        <v>4.114833</v>
       </c>
       <c r="K289" s="7">
-        <v>8.303238</v>
+        <v>8.254083000000001</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12164,25 +12166,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.08445399999999999</v>
+        <v>0.093474</v>
       </c>
       <c r="F290" s="7">
-        <v>0.049613</v>
+        <v>0.014917</v>
       </c>
       <c r="G290" s="7">
-        <v>0.248329</v>
+        <v>0.255817</v>
       </c>
       <c r="H290" s="7">
-        <v>0.203707</v>
+        <v>0.20711500000000002</v>
       </c>
       <c r="I290" s="7">
-        <v>0.377105</v>
+        <v>0.397002</v>
       </c>
       <c r="J290" s="7">
-        <v>2.544364</v>
+        <v>2.5544</v>
       </c>
       <c r="K290" s="7">
-        <v>12.665700999999999</v>
+        <v>12.603361999999999</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12199,25 +12201,25 @@
         <v>4</v>
       </c>
       <c r="E291" s="7">
-        <v>0.051099</v>
+        <v>0.049599000000000004</v>
       </c>
       <c r="F291" s="7">
-        <v>0.061765</v>
+        <v>0.059396000000000004</v>
       </c>
       <c r="G291" s="7">
-        <v>0.22919499999999998</v>
+        <v>0.22776700000000002</v>
       </c>
       <c r="H291" s="7">
-        <v>0.161718</v>
+        <v>0.16208100000000003</v>
       </c>
       <c r="I291" s="7">
-        <v>0.5538839999999999</v>
+        <v>0.5548190000000001</v>
       </c>
       <c r="J291" s="7">
-        <v>2.407349</v>
+        <v>2.4084149999999998</v>
       </c>
       <c r="K291" s="7">
-        <v>6.326496</v>
+        <v>6.312477</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12234,25 +12236,25 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0.08553100000000001</v>
+        <v>0.092439</v>
       </c>
       <c r="F292" s="7">
-        <v>0.057176</v>
+        <v>0.053621</v>
       </c>
       <c r="G292" s="7">
-        <v>0.230781</v>
+        <v>0.237003</v>
       </c>
       <c r="H292" s="7">
-        <v>0.174269</v>
+        <v>0.178247</v>
       </c>
       <c r="I292" s="7">
-        <v>0.5002</v>
+        <v>0.510312</v>
       </c>
       <c r="J292" s="7">
-        <v>2.734679</v>
+        <v>2.7473289999999997</v>
       </c>
       <c r="K292" s="7">
-        <v>8.436207000000001</v>
+        <v>8.423343</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12269,25 +12271,25 @@
         <v>4</v>
       </c>
       <c r="E293" s="7">
-        <v>0.043113</v>
+        <v>0.046594</v>
       </c>
       <c r="F293" s="7">
-        <v>0.056822</v>
+        <v>0.057926000000000005</v>
       </c>
       <c r="G293" s="7">
-        <v>0.221951</v>
+        <v>0.22662500000000002</v>
       </c>
       <c r="H293" s="7">
-        <v>0.11496600000000001</v>
+        <v>0.11760999999999999</v>
       </c>
       <c r="I293" s="7">
-        <v>0.402962</v>
+        <v>0.407864</v>
       </c>
       <c r="J293" s="7">
-        <v>1.41887</v>
+        <v>1.424605</v>
       </c>
       <c r="K293" s="7">
-        <v>4.113663</v>
+        <v>4.1204149999999995</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12304,25 +12306,25 @@
         <v>4</v>
       </c>
       <c r="E294" s="7">
-        <v>0.038692000000000004</v>
+        <v>0.040938999999999996</v>
       </c>
       <c r="F294" s="7">
-        <v>0.009253</v>
+        <v>0.000196</v>
       </c>
       <c r="G294" s="7">
-        <v>0.196006</v>
+        <v>0.191966</v>
       </c>
       <c r="H294" s="7">
-        <v>0.047533000000000006</v>
+        <v>0.045405</v>
       </c>
       <c r="I294" s="7">
-        <v>0.39219000000000004</v>
+        <v>0.393746</v>
       </c>
       <c r="J294" s="7">
-        <v>1.701641</v>
+        <v>1.6961519999999999</v>
       </c>
       <c r="K294" s="7">
-        <v>4.815098</v>
+        <v>4.795962</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12339,25 +12341,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.103406</v>
+        <v>0.10940899999999999</v>
       </c>
       <c r="F295" s="7">
-        <v>0.057405</v>
+        <v>0.038439</v>
       </c>
       <c r="G295" s="7">
-        <v>0.303324</v>
+        <v>0.311346</v>
       </c>
       <c r="H295" s="7">
-        <v>0.24189699999999997</v>
+        <v>0.24522</v>
       </c>
       <c r="I295" s="7">
-        <v>0.539277</v>
+        <v>0.5586760000000001</v>
       </c>
       <c r="J295" s="7">
-        <v>3.611979</v>
+        <v>3.624321</v>
       </c>
       <c r="K295" s="7">
-        <v>15.918267</v>
+        <v>15.79684</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12374,25 +12376,25 @@
         <v>5</v>
       </c>
       <c r="E296" s="7">
-        <v>0.088881</v>
+        <v>0.09579399999999999</v>
       </c>
       <c r="F296" s="7">
-        <v>0.059364</v>
+        <v>0.051721</v>
       </c>
       <c r="G296" s="7">
-        <v>0.303307</v>
+        <v>0.314798</v>
       </c>
       <c r="H296" s="7">
-        <v>0.249053</v>
+        <v>0.256295</v>
       </c>
       <c r="I296" s="7">
-        <v>0.552773</v>
+        <v>0.572211</v>
       </c>
       <c r="J296" s="7">
-        <v>3.2528070000000002</v>
+        <v>3.277464</v>
       </c>
       <c r="K296" s="7">
-        <v>10.877663</v>
+        <v>10.860083999999999</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12409,25 +12411,25 @@
         <v>4</v>
       </c>
       <c r="E297" s="7">
-        <v>0.079651</v>
+        <v>0.085978</v>
       </c>
       <c r="F297" s="7">
-        <v>0.046467</v>
+        <v>0.045191999999999996</v>
       </c>
       <c r="G297" s="7">
-        <v>0.286211</v>
+        <v>0.294147</v>
       </c>
       <c r="H297" s="7">
-        <v>0.215364</v>
+        <v>0.221995</v>
       </c>
       <c r="I297" s="7">
-        <v>0.560723</v>
+        <v>0.578111</v>
       </c>
       <c r="J297" s="7">
-        <v>3.238388</v>
+        <v>3.261513</v>
       </c>
       <c r="K297" s="7">
-        <v>9.767267</v>
+        <v>9.772770000000001</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12444,25 +12446,25 @@
         <v>2</v>
       </c>
       <c r="E298" s="7">
-        <v>0.045431</v>
+        <v>0.048852</v>
       </c>
       <c r="F298" s="7">
-        <v>0.089496</v>
+        <v>0.08459699999999999</v>
       </c>
       <c r="G298" s="7">
-        <v>0.217942</v>
+        <v>0.218751</v>
       </c>
       <c r="H298" s="7">
-        <v>0.136208</v>
+        <v>0.137439</v>
       </c>
       <c r="I298" s="7">
-        <v>0.511165</v>
+        <v>0.512316</v>
       </c>
       <c r="J298" s="7">
-        <v>2.8143079999999996</v>
+        <v>2.818442</v>
       </c>
       <c r="K298" s="7">
-        <v>5.097758</v>
+        <v>5.100975</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12479,25 +12481,25 @@
         <v>5</v>
       </c>
       <c r="E299" s="7">
-        <v>0.093309</v>
+        <v>0.10294</v>
       </c>
       <c r="F299" s="7">
-        <v>0.09176500000000001</v>
+        <v>0.090465</v>
       </c>
       <c r="G299" s="7">
-        <v>0.32072</v>
+        <v>0.335351</v>
       </c>
       <c r="H299" s="7">
-        <v>0.257207</v>
+        <v>0.265931</v>
       </c>
       <c r="I299" s="7">
-        <v>0.639592</v>
+        <v>0.655571</v>
       </c>
       <c r="J299" s="7">
-        <v>3.139124</v>
+        <v>3.167848</v>
       </c>
       <c r="K299" s="7">
-        <v>9.758775</v>
+        <v>9.785795</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12514,25 +12516,25 @@
         <v>6</v>
       </c>
       <c r="E300" s="7">
-        <v>0.09666999999999999</v>
+        <v>0.107451</v>
       </c>
       <c r="F300" s="7">
-        <v>0.07347000000000001</v>
+        <v>0.078449</v>
       </c>
       <c r="G300" s="7">
-        <v>0.32874699999999996</v>
+        <v>0.344632</v>
       </c>
       <c r="H300" s="7">
-        <v>0.26882100000000003</v>
+        <v>0.27824000000000004</v>
       </c>
       <c r="I300" s="7">
-        <v>0.68336</v>
+        <v>0.7021850000000001</v>
       </c>
       <c r="J300" s="7">
-        <v>3.346375</v>
+        <v>3.378639</v>
       </c>
       <c r="K300" s="7">
-        <v>12.415439</v>
+        <v>12.436976999999999</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12549,25 +12551,25 @@
         <v>6</v>
       </c>
       <c r="E301" s="7">
-        <v>0.09784599999999999</v>
+        <v>0.10665699999999999</v>
       </c>
       <c r="F301" s="7">
-        <v>0.088585</v>
+        <v>0.08354400000000001</v>
       </c>
       <c r="G301" s="7">
-        <v>0.28176</v>
+        <v>0.288998</v>
       </c>
       <c r="H301" s="7">
-        <v>0.262832</v>
+        <v>0.266268</v>
       </c>
       <c r="I301" s="7">
-        <v>0.533683</v>
+        <v>0.5482130000000001</v>
       </c>
       <c r="J301" s="7">
-        <v>2.145615</v>
+        <v>2.154173</v>
       </c>
       <c r="K301" s="7">
-        <v>8.815482</v>
+        <v>8.758412</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12584,22 +12586,22 @@
         <v>4</v>
       </c>
       <c r="E302" s="7">
-        <v>0.188643</v>
+        <v>0.194447</v>
       </c>
       <c r="F302" s="7">
-        <v>0.13959</v>
+        <v>0.16183399999999998</v>
       </c>
       <c r="G302" s="7">
-        <v>0.24570799999999998</v>
+        <v>0.246671</v>
       </c>
       <c r="H302" s="7">
-        <v>0.23195900000000003</v>
+        <v>0.240003</v>
       </c>
       <c r="I302" s="7">
-        <v>0.665423</v>
+        <v>0.6698770000000001</v>
       </c>
       <c r="J302" s="7">
-        <v>3.532641</v>
+        <v>3.562236</v>
       </c>
       <c r="K302" s="7"/>
     </row>
@@ -12617,25 +12619,25 @@
         <v>5</v>
       </c>
       <c r="E303" s="7">
-        <v>0.11395300000000001</v>
+        <v>0.122173</v>
       </c>
       <c r="F303" s="7">
-        <v>0.060964</v>
+        <v>0.039712</v>
       </c>
       <c r="G303" s="7">
-        <v>0.268196</v>
+        <v>0.274315</v>
       </c>
       <c r="H303" s="7">
-        <v>0.181672</v>
+        <v>0.183335</v>
       </c>
       <c r="I303" s="7">
-        <v>0.49763399999999997</v>
+        <v>0.511126</v>
       </c>
       <c r="J303" s="7">
-        <v>2.612876</v>
+        <v>2.617961</v>
       </c>
       <c r="K303" s="7">
-        <v>11.725957000000001</v>
+        <v>11.627438</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12652,25 +12654,25 @@
         <v>6</v>
       </c>
       <c r="E304" s="7">
-        <v>0.028283999999999997</v>
+        <v>0.026812999999999997</v>
       </c>
       <c r="F304" s="7">
-        <v>0.036141</v>
+        <v>0.035322</v>
       </c>
       <c r="G304" s="7">
-        <v>0.081988</v>
+        <v>0.081275</v>
       </c>
       <c r="H304" s="7">
-        <v>0.048892</v>
+        <v>0.048265</v>
       </c>
       <c r="I304" s="7">
-        <v>0.23449799999999998</v>
+        <v>0.23342300000000002</v>
       </c>
       <c r="J304" s="7">
-        <v>1.802284</v>
+        <v>1.800608</v>
       </c>
       <c r="K304" s="7">
-        <v>5.6693430000000005</v>
+        <v>5.656746000000001</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12687,25 +12689,25 @@
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.082138</v>
+        <v>0.07849</v>
       </c>
       <c r="F305" s="7">
-        <v>0.037513</v>
+        <v>0.00244</v>
       </c>
       <c r="G305" s="7">
-        <v>0.18369</v>
+        <v>0.17178000000000002</v>
       </c>
       <c r="H305" s="7">
-        <v>0.088483</v>
+        <v>0.08071400000000001</v>
       </c>
       <c r="I305" s="7">
-        <v>0.492813</v>
+        <v>0.475209</v>
       </c>
       <c r="J305" s="7">
-        <v>2.353516</v>
+        <v>2.329579</v>
       </c>
       <c r="K305" s="7">
-        <v>7.713256</v>
+        <v>7.609471</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12722,25 +12724,25 @@
         <v>3</v>
       </c>
       <c r="E306" s="7">
-        <v>0.040011</v>
+        <v>0.041817</v>
       </c>
       <c r="F306" s="7">
-        <v>0.074906</v>
+        <v>0.076502</v>
       </c>
       <c r="G306" s="7">
-        <v>0.20521899999999998</v>
+        <v>0.207325</v>
       </c>
       <c r="H306" s="7">
-        <v>0.137883</v>
+        <v>0.140039</v>
       </c>
       <c r="I306" s="7">
-        <v>0.460349</v>
+        <v>0.46253</v>
       </c>
       <c r="J306" s="7">
-        <v>1.9564340000000002</v>
+        <v>1.9620339999999998</v>
       </c>
       <c r="K306" s="7">
-        <v>5.2492160000000005</v>
+        <v>5.252730000000001</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12757,25 +12759,25 @@
         <v>3</v>
       </c>
       <c r="E307" s="7">
-        <v>0.03372</v>
+        <v>0.036416</v>
       </c>
       <c r="F307" s="7">
-        <v>0.014095</v>
+        <v>0.011493999999999999</v>
       </c>
       <c r="G307" s="7">
-        <v>0.142622</v>
+        <v>0.13982</v>
       </c>
       <c r="H307" s="7">
-        <v>0.035921</v>
+        <v>0.033530000000000004</v>
       </c>
       <c r="I307" s="7">
-        <v>0.398222</v>
+        <v>0.39820900000000004</v>
       </c>
       <c r="J307" s="7">
-        <v>1.014622</v>
+        <v>1.009971</v>
       </c>
       <c r="K307" s="7">
-        <v>2.1309970000000003</v>
+        <v>2.120216</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>30.04.2026 18:45:33</t>
+    <t>04.05.2026 19:03:35</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -1276,7 +1276,10 @@
     <t>HHM</t>
   </si>
   <si>
-    <t>TÜRKİYE HAYAT VE EMEKLİLİK A.Ş. KATILIM AGRESİF DEĞİŞKEN EMEKLİLİK YATIRIM FONU</t>
+    <t>TÜRKİYE HAYAT VE EMEKLİLİK A.Ş. TEKNOLOJİ SEKTÖRÜ KATILIM EMEKLİLİK YATIRIM FONU</t>
+  </si>
+  <si>
+    <t>Katılım Fonu</t>
   </si>
   <si>
     <t>HHY</t>
@@ -1399,9 +1402,6 @@
     <t>KATILIM EMEKLİLİK VE HAYAT A.Ş. GÜMÜŞ KATILIM EMEKLİLİK YATIRIM FONU</t>
   </si>
   <si>
-    <t>Katılım Fonu</t>
-  </si>
-  <si>
     <t>KHL</t>
   </si>
   <si>
@@ -1636,7 +1636,7 @@
     <t>NHM</t>
   </si>
   <si>
-    <t>ZURICH YAŞAM VE EMEKLİLİK A.Ş. QINVEST PORTFÖY TEMKİNLİ DEĞİŞKEN EMEKLİLİK YATIRIM FONU</t>
+    <t>ZURİCH YAŞAM VE EMEKLİLİK A.Ş. TEMKİNLİ DEĞİŞKEN EMEKLİLİK YATIRIM FONU</t>
   </si>
   <si>
     <t>NHN</t>
@@ -2454,25 +2454,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.059814</v>
+        <v>0.039319</v>
       </c>
       <c r="F6" s="7">
-        <v>0.03115</v>
+        <v>0.030026</v>
       </c>
       <c r="G6" s="7">
-        <v>0.19804</v>
+        <v>0.189614</v>
       </c>
       <c r="H6" s="7">
-        <v>0.102011</v>
+        <v>0.10236</v>
       </c>
       <c r="I6" s="7">
-        <v>0.462926</v>
+        <v>0.452303</v>
       </c>
       <c r="J6" s="7">
-        <v>2.175875</v>
+        <v>2.225156</v>
       </c>
       <c r="K6" s="7">
-        <v>5.700458</v>
+        <v>5.683514</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,25 +2489,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.118988</v>
+        <v>0.103461</v>
       </c>
       <c r="F7" s="7">
-        <v>0.057388</v>
+        <v>0.050415</v>
       </c>
       <c r="G7" s="7">
-        <v>0.124606</v>
+        <v>0.12323</v>
       </c>
       <c r="H7" s="7">
-        <v>0.085338</v>
+        <v>0.087463</v>
       </c>
       <c r="I7" s="7">
-        <v>0.499996</v>
+        <v>0.471289</v>
       </c>
       <c r="J7" s="7">
-        <v>2.801996</v>
+        <v>2.807476</v>
       </c>
       <c r="K7" s="7">
-        <v>5.558279</v>
+        <v>5.632134</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2524,25 +2524,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.048826999999999995</v>
+        <v>0.022337</v>
       </c>
       <c r="F8" s="7">
-        <v>0.004514000000000001</v>
+        <v>0.002323</v>
       </c>
       <c r="G8" s="7">
-        <v>0.144531</v>
+        <v>0.136385</v>
       </c>
       <c r="H8" s="7">
-        <v>0.045252999999999995</v>
+        <v>0.044506</v>
       </c>
       <c r="I8" s="7">
-        <v>0.405194</v>
+        <v>0.383827</v>
       </c>
       <c r="J8" s="7">
-        <v>1.71691</v>
+        <v>1.742226</v>
       </c>
       <c r="K8" s="7">
-        <v>3.554258</v>
+        <v>3.5412090000000003</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2559,25 +2559,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.092647</v>
+        <v>0.076631</v>
       </c>
       <c r="F9" s="7">
-        <v>0.0421</v>
+        <v>0.045957</v>
       </c>
       <c r="G9" s="7">
-        <v>0.292412</v>
+        <v>0.282065</v>
       </c>
       <c r="H9" s="7">
-        <v>0.24371099999999998</v>
+        <v>0.245381</v>
       </c>
       <c r="I9" s="7">
-        <v>0.548105</v>
+        <v>0.557988</v>
       </c>
       <c r="J9" s="7">
-        <v>3.1022969999999996</v>
+        <v>3.165114</v>
       </c>
       <c r="K9" s="7">
-        <v>10.427442000000001</v>
+        <v>10.338115</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,25 +2594,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.013467</v>
+        <v>-0.022014</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.104514</v>
+        <v>-0.10042999999999999</v>
       </c>
       <c r="G10" s="7">
-        <v>0.122463</v>
+        <v>0.15454</v>
       </c>
       <c r="H10" s="7">
-        <v>0.024965</v>
+        <v>0.032014</v>
       </c>
       <c r="I10" s="7">
-        <v>0.489529</v>
+        <v>0.518615</v>
       </c>
       <c r="J10" s="7">
-        <v>3.99059</v>
+        <v>4.035966</v>
       </c>
       <c r="K10" s="7">
-        <v>13.557797</v>
+        <v>13.435705</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2629,25 +2629,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.119696</v>
+        <v>0.098605</v>
       </c>
       <c r="F11" s="7">
-        <v>0.044676</v>
+        <v>0.047779999999999996</v>
       </c>
       <c r="G11" s="7">
-        <v>0.331982</v>
+        <v>0.318239</v>
       </c>
       <c r="H11" s="7">
-        <v>0.279583</v>
+        <v>0.282291</v>
       </c>
       <c r="I11" s="7">
-        <v>0.588449</v>
+        <v>0.5999680000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>2.7314350000000003</v>
+        <v>2.786738</v>
       </c>
       <c r="K11" s="7">
-        <v>12.813725999999999</v>
+        <v>12.63307</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2664,25 +2664,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.052402</v>
+        <v>0.045368000000000006</v>
       </c>
       <c r="F12" s="7">
-        <v>0.067442</v>
+        <v>0.069549</v>
       </c>
       <c r="G12" s="7">
-        <v>0.240868</v>
+        <v>0.237502</v>
       </c>
       <c r="H12" s="7">
-        <v>0.143373</v>
+        <v>0.148115</v>
       </c>
       <c r="I12" s="7">
-        <v>0.493692</v>
+        <v>0.496118</v>
       </c>
       <c r="J12" s="7">
-        <v>2.671404</v>
+        <v>2.690281</v>
       </c>
       <c r="K12" s="7">
-        <v>4.54772</v>
+        <v>4.55072</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,25 +2699,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.123475</v>
+        <v>0.108537</v>
       </c>
       <c r="F13" s="7">
-        <v>0.05888</v>
+        <v>0.062468</v>
       </c>
       <c r="G13" s="7">
-        <v>0.361541</v>
+        <v>0.344652</v>
       </c>
       <c r="H13" s="7">
-        <v>0.29254</v>
+        <v>0.298687</v>
       </c>
       <c r="I13" s="7">
-        <v>0.603976</v>
+        <v>0.628127</v>
       </c>
       <c r="J13" s="7">
-        <v>2.840237</v>
+        <v>2.935883</v>
       </c>
       <c r="K13" s="7">
-        <v>10.42055</v>
+        <v>10.416945</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,25 +2734,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.068647</v>
+        <v>0.050306</v>
       </c>
       <c r="F14" s="7">
-        <v>0.00703</v>
+        <v>0.022138</v>
       </c>
       <c r="G14" s="7">
-        <v>0.257907</v>
+        <v>0.24681799999999998</v>
       </c>
       <c r="H14" s="7">
-        <v>0.175438</v>
+        <v>0.18003699999999997</v>
       </c>
       <c r="I14" s="7">
-        <v>0.476225</v>
+        <v>0.488656</v>
       </c>
       <c r="J14" s="7">
-        <v>2.660005</v>
+        <v>2.6935610000000003</v>
       </c>
       <c r="K14" s="7">
-        <v>8.068914</v>
+        <v>8.023981</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,25 +2769,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.04917099999999999</v>
+        <v>0.030244</v>
       </c>
       <c r="F15" s="7">
-        <v>0.015684</v>
+        <v>0.013037</v>
       </c>
       <c r="G15" s="7">
-        <v>0.185159</v>
+        <v>0.176708</v>
       </c>
       <c r="H15" s="7">
-        <v>0.076545</v>
+        <v>0.076483</v>
       </c>
       <c r="I15" s="7">
-        <v>0.416852</v>
+        <v>0.407115</v>
       </c>
       <c r="J15" s="7">
-        <v>2.013537</v>
+        <v>2.0289680000000003</v>
       </c>
       <c r="K15" s="7">
-        <v>5.512803</v>
+        <v>5.495558</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,25 +2804,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.048984</v>
+        <v>0.034475</v>
       </c>
       <c r="F16" s="7">
-        <v>0.081056</v>
+        <v>0.081683</v>
       </c>
       <c r="G16" s="7">
-        <v>0.219774</v>
+        <v>0.216268</v>
       </c>
       <c r="H16" s="7">
-        <v>0.136383</v>
+        <v>0.139108</v>
       </c>
       <c r="I16" s="7">
-        <v>0.511446</v>
+        <v>0.508598</v>
       </c>
       <c r="J16" s="7">
-        <v>2.786443</v>
+        <v>2.793609</v>
       </c>
       <c r="K16" s="7">
-        <v>5.0467189999999995</v>
+        <v>5.050346</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2839,25 +2839,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.039199000000000005</v>
+        <v>0.037481</v>
       </c>
       <c r="F17" s="7">
-        <v>0.072127</v>
+        <v>0.07420399999999999</v>
       </c>
       <c r="G17" s="7">
-        <v>0.190665</v>
+        <v>0.18986899999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.130337</v>
+        <v>0.134546</v>
       </c>
       <c r="I17" s="7">
-        <v>0.4202</v>
+        <v>0.418785</v>
       </c>
       <c r="J17" s="7">
-        <v>1.663646</v>
+        <v>1.704253</v>
       </c>
       <c r="K17" s="7">
-        <v>4.522729</v>
+        <v>4.528549</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,25 +2874,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.004746</v>
+        <v>-0.016269</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.10573600000000001</v>
+        <v>-0.08362</v>
       </c>
       <c r="G18" s="7">
-        <v>0.180748</v>
+        <v>0.202636</v>
       </c>
       <c r="H18" s="7">
-        <v>0.0471</v>
+        <v>0.053966</v>
       </c>
       <c r="I18" s="7">
-        <v>0.601783</v>
+        <v>0.622584</v>
       </c>
       <c r="J18" s="7">
-        <v>4.737217</v>
+        <v>4.771968</v>
       </c>
       <c r="K18" s="7">
-        <v>15.829338</v>
+        <v>15.681885999999999</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,25 +2909,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.07281699999999999</v>
+        <v>0.066304</v>
       </c>
       <c r="F19" s="7">
-        <v>0.032625</v>
+        <v>0.047431</v>
       </c>
       <c r="G19" s="7">
-        <v>0.197729</v>
+        <v>0.187684</v>
       </c>
       <c r="H19" s="7">
-        <v>0.106525</v>
+        <v>0.11825200000000001</v>
       </c>
       <c r="I19" s="7">
-        <v>0.432729</v>
+        <v>0.45213000000000003</v>
       </c>
       <c r="J19" s="7">
-        <v>2.174786</v>
+        <v>2.316885</v>
       </c>
       <c r="K19" s="7">
-        <v>6.9094489999999995</v>
+        <v>6.920067</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2944,25 +2944,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.042817</v>
+        <v>0.03751</v>
       </c>
       <c r="F20" s="7">
-        <v>0.082866</v>
+        <v>0.091045</v>
       </c>
       <c r="G20" s="7">
-        <v>0.235043</v>
+        <v>0.236022</v>
       </c>
       <c r="H20" s="7">
-        <v>0.086936</v>
+        <v>0.093748</v>
       </c>
       <c r="I20" s="7">
-        <v>0.46701099999999995</v>
+        <v>0.46479</v>
       </c>
       <c r="J20" s="7">
-        <v>1.4726599999999999</v>
+        <v>1.520409</v>
       </c>
       <c r="K20" s="7">
-        <v>4.185661</v>
+        <v>4.18944</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,25 +2979,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.044393</v>
+        <v>0.041902999999999996</v>
       </c>
       <c r="F21" s="7">
-        <v>0.08556</v>
+        <v>0.08931900000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.213297</v>
+        <v>0.207822</v>
       </c>
       <c r="H21" s="7">
-        <v>0.148171</v>
+        <v>0.153714</v>
       </c>
       <c r="I21" s="7">
-        <v>0.45356</v>
+        <v>0.447268</v>
       </c>
       <c r="J21" s="7">
-        <v>1.8216990000000002</v>
+        <v>1.8983809999999999</v>
       </c>
       <c r="K21" s="7">
-        <v>5.027375</v>
+        <v>5.025313</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,25 +3014,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.11699299999999999</v>
+        <v>0.097384</v>
       </c>
       <c r="F22" s="7">
-        <v>0.071982</v>
+        <v>0.080875</v>
       </c>
       <c r="G22" s="7">
-        <v>0.2566</v>
+        <v>0.242806</v>
       </c>
       <c r="H22" s="7">
-        <v>0.24096499999999998</v>
+        <v>0.25342</v>
       </c>
       <c r="I22" s="7">
-        <v>0.581307</v>
+        <v>0.601363</v>
       </c>
       <c r="J22" s="7">
-        <v>2.812733</v>
+        <v>2.9819850000000003</v>
       </c>
       <c r="K22" s="7">
-        <v>10.734571</v>
+        <v>10.65893</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,25 +3049,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.027376</v>
+        <v>0.025447</v>
       </c>
       <c r="F23" s="7">
-        <v>0.07894899999999999</v>
+        <v>0.08036599999999999</v>
       </c>
       <c r="G23" s="7">
-        <v>0.18239</v>
+        <v>0.18290700000000001</v>
       </c>
       <c r="H23" s="7">
-        <v>0.11751099999999999</v>
+        <v>0.121303</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40882599999999997</v>
+        <v>0.40755899999999995</v>
       </c>
       <c r="J23" s="7">
-        <v>2.171261</v>
+        <v>2.2276</v>
       </c>
       <c r="K23" s="7">
-        <v>5.0017059999999995</v>
+        <v>4.999894</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3084,25 +3084,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.048838999999999994</v>
+        <v>0.024238</v>
       </c>
       <c r="F24" s="7">
-        <v>0.006827</v>
+        <v>0.0033239999999999997</v>
       </c>
       <c r="G24" s="7">
-        <v>0.138529</v>
+        <v>0.131782</v>
       </c>
       <c r="H24" s="7">
-        <v>0.03438</v>
+        <v>0.033526</v>
       </c>
       <c r="I24" s="7">
-        <v>0.389529</v>
+        <v>0.371554</v>
       </c>
       <c r="J24" s="7">
-        <v>1.589541</v>
+        <v>1.580796</v>
       </c>
       <c r="K24" s="7">
-        <v>3.420255</v>
+        <v>3.40868</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,25 +3119,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.04258</v>
+        <v>0.028622</v>
       </c>
       <c r="F25" s="7">
-        <v>0.036789999999999996</v>
+        <v>0.033316</v>
       </c>
       <c r="G25" s="7">
-        <v>0.116537</v>
+        <v>0.112174</v>
       </c>
       <c r="H25" s="7">
-        <v>0.051229</v>
+        <v>0.051418</v>
       </c>
       <c r="I25" s="7">
-        <v>0.344375</v>
+        <v>0.338708</v>
       </c>
       <c r="J25" s="7">
-        <v>2.098225</v>
+        <v>2.0966050000000003</v>
       </c>
       <c r="K25" s="7">
-        <v>6.499043</v>
+        <v>6.3948860000000005</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,25 +3154,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.047179</v>
+        <v>0.034607</v>
       </c>
       <c r="F26" s="7">
-        <v>0.015493</v>
+        <v>0.021543</v>
       </c>
       <c r="G26" s="7">
-        <v>0.112306</v>
+        <v>0.114697</v>
       </c>
       <c r="H26" s="7">
-        <v>0.049236</v>
+        <v>0.048388999999999995</v>
       </c>
       <c r="I26" s="7">
-        <v>0.30075199999999996</v>
+        <v>0.30168500000000004</v>
       </c>
       <c r="J26" s="7">
-        <v>2.0475630000000002</v>
+        <v>2.038941</v>
       </c>
       <c r="K26" s="7">
-        <v>5.644679</v>
+        <v>5.584982999999999</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3189,25 +3189,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.088824</v>
+        <v>0.070718</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.015434000000000002</v>
+        <v>-0.020811000000000003</v>
       </c>
       <c r="G27" s="7">
-        <v>0.228342</v>
+        <v>0.210375</v>
       </c>
       <c r="H27" s="7">
-        <v>0.180114</v>
+        <v>0.187234</v>
       </c>
       <c r="I27" s="7">
-        <v>0.407488</v>
+        <v>0.42094000000000004</v>
       </c>
       <c r="J27" s="7">
-        <v>3.268866</v>
+        <v>3.366703</v>
       </c>
       <c r="K27" s="7">
-        <v>16.073108</v>
+        <v>15.931749</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,25 +3224,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.11343199999999999</v>
+        <v>0.094248</v>
       </c>
       <c r="F28" s="7">
-        <v>0.037835</v>
+        <v>0.033564</v>
       </c>
       <c r="G28" s="7">
-        <v>0.124627</v>
+        <v>0.119369</v>
       </c>
       <c r="H28" s="7">
-        <v>0.10151199999999999</v>
+        <v>0.101194</v>
       </c>
       <c r="I28" s="7">
-        <v>0.422094</v>
+        <v>0.410697</v>
       </c>
       <c r="J28" s="7">
-        <v>2.577515</v>
+        <v>2.5830990000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>7.962211999999999</v>
+        <v>7.866052</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3259,25 +3259,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.036441</v>
+        <v>0.027955</v>
       </c>
       <c r="F29" s="7">
-        <v>0.046288</v>
+        <v>0.043653000000000004</v>
       </c>
       <c r="G29" s="7">
-        <v>0.172052</v>
+        <v>0.16724499999999998</v>
       </c>
       <c r="H29" s="7">
-        <v>0.095463</v>
+        <v>0.09791499999999999</v>
       </c>
       <c r="I29" s="7">
-        <v>0.406671</v>
+        <v>0.403557</v>
       </c>
       <c r="J29" s="7">
-        <v>2.401274</v>
+        <v>2.412912</v>
       </c>
       <c r="K29" s="7">
-        <v>4.558415</v>
+        <v>4.561381</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3294,25 +3294,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.053228</v>
+        <v>0.043783</v>
       </c>
       <c r="F30" s="7">
-        <v>0.004019</v>
+        <v>-0.002448</v>
       </c>
       <c r="G30" s="7">
-        <v>0.19177499999999997</v>
+        <v>0.178832</v>
       </c>
       <c r="H30" s="7">
-        <v>0.140897</v>
+        <v>0.14443799999999998</v>
       </c>
       <c r="I30" s="7">
-        <v>0.385021</v>
+        <v>0.390704</v>
       </c>
       <c r="J30" s="7">
-        <v>3.028631</v>
+        <v>3.0796010000000003</v>
       </c>
       <c r="K30" s="7">
-        <v>9.430741000000001</v>
+        <v>9.396824</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,25 +3329,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.114711</v>
+        <v>0.10539799999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>-0.004476</v>
+        <v>0.000518</v>
       </c>
       <c r="G31" s="7">
-        <v>0.235024</v>
+        <v>0.219501</v>
       </c>
       <c r="H31" s="7">
-        <v>0.19736499999999998</v>
+        <v>0.20731100000000002</v>
       </c>
       <c r="I31" s="7">
-        <v>0.369646</v>
+        <v>0.39146099999999995</v>
       </c>
       <c r="J31" s="7">
-        <v>2.5871519999999997</v>
+        <v>2.696908</v>
       </c>
       <c r="K31" s="7">
-        <v>14.727048</v>
+        <v>14.546819000000001</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3364,25 +3364,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.030886999999999998</v>
+        <v>0.028647999999999996</v>
       </c>
       <c r="F32" s="7">
-        <v>0.08332700000000001</v>
+        <v>0.085008</v>
       </c>
       <c r="G32" s="7">
-        <v>0.193397</v>
+        <v>0.192334</v>
       </c>
       <c r="H32" s="7">
-        <v>0.114746</v>
+        <v>0.119057</v>
       </c>
       <c r="I32" s="7">
-        <v>0.451134</v>
+        <v>0.449115</v>
       </c>
       <c r="J32" s="7">
-        <v>2.156255</v>
+        <v>2.1627709999999998</v>
       </c>
       <c r="K32" s="7">
-        <v>3.726568</v>
+        <v>3.7365690000000003</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3399,25 +3399,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.072322</v>
+        <v>0.059025999999999995</v>
       </c>
       <c r="F33" s="7">
-        <v>0.0058330000000000005</v>
+        <v>0.000092</v>
       </c>
       <c r="G33" s="7">
-        <v>0.23604</v>
+        <v>0.219524</v>
       </c>
       <c r="H33" s="7">
-        <v>0.166496</v>
+        <v>0.172081</v>
       </c>
       <c r="I33" s="7">
-        <v>0.447082</v>
+        <v>0.450763</v>
       </c>
       <c r="J33" s="7">
-        <v>3.4754300000000002</v>
+        <v>3.5849189999999997</v>
       </c>
       <c r="K33" s="7">
-        <v>16.347299</v>
+        <v>16.230126</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3434,25 +3434,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.106394</v>
+        <v>0.091202</v>
       </c>
       <c r="F34" s="7">
-        <v>0.093912</v>
+        <v>0.10117599999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.338235</v>
+        <v>0.330133</v>
       </c>
       <c r="H34" s="7">
-        <v>0.273173</v>
+        <v>0.27690000000000003</v>
       </c>
       <c r="I34" s="7">
-        <v>0.6535</v>
+        <v>0.6578879999999999</v>
       </c>
       <c r="J34" s="7">
-        <v>3.1885449999999995</v>
+        <v>3.2815069999999995</v>
       </c>
       <c r="K34" s="7">
-        <v>9.801642000000001</v>
+        <v>9.758091</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3469,25 +3469,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.108139</v>
+        <v>0.09428399999999999</v>
       </c>
       <c r="F35" s="7">
-        <v>0.08099</v>
+        <v>0.09265599999999999</v>
       </c>
       <c r="G35" s="7">
-        <v>0.344587</v>
+        <v>0.33705199999999996</v>
       </c>
       <c r="H35" s="7">
-        <v>0.278802</v>
+        <v>0.283439</v>
       </c>
       <c r="I35" s="7">
-        <v>0.706906</v>
+        <v>0.71418</v>
       </c>
       <c r="J35" s="7">
-        <v>3.384819</v>
+        <v>3.513154</v>
       </c>
       <c r="K35" s="7">
-        <v>12.325814000000001</v>
+        <v>12.255700999999998</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3504,25 +3504,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.073895</v>
+        <v>0.05934300000000001</v>
       </c>
       <c r="F36" s="7">
-        <v>0.009889</v>
+        <v>0.004157</v>
       </c>
       <c r="G36" s="7">
-        <v>0.245014</v>
+        <v>0.22971699999999998</v>
       </c>
       <c r="H36" s="7">
-        <v>0.178444</v>
+        <v>0.185188</v>
       </c>
       <c r="I36" s="7">
-        <v>0.46972400000000003</v>
+        <v>0.47478200000000004</v>
       </c>
       <c r="J36" s="7">
-        <v>3.5808030000000004</v>
+        <v>3.676814</v>
       </c>
       <c r="K36" s="7">
-        <v>17.089394</v>
+        <v>16.94926</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3539,25 +3539,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.059375</v>
+        <v>0.048498</v>
       </c>
       <c r="F37" s="7">
-        <v>0.014785</v>
+        <v>0.008156</v>
       </c>
       <c r="G37" s="7">
-        <v>0.246134</v>
+        <v>0.237704</v>
       </c>
       <c r="H37" s="7">
-        <v>0.15784399999999998</v>
+        <v>0.166909</v>
       </c>
       <c r="I37" s="7">
-        <v>0.46135</v>
+        <v>0.471314</v>
       </c>
       <c r="J37" s="7">
-        <v>3.6554020000000005</v>
+        <v>3.753261</v>
       </c>
       <c r="K37" s="7">
-        <v>15.435925</v>
+        <v>15.396856</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3574,25 +3574,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.042566</v>
+        <v>0.036625</v>
       </c>
       <c r="F38" s="7">
-        <v>0.013988</v>
+        <v>0.009943</v>
       </c>
       <c r="G38" s="7">
-        <v>0.214588</v>
+        <v>0.207611</v>
       </c>
       <c r="H38" s="7">
-        <v>0.139239</v>
+        <v>0.148752</v>
       </c>
       <c r="I38" s="7">
-        <v>0.45446800000000004</v>
+        <v>0.46475099999999997</v>
       </c>
       <c r="J38" s="7">
-        <v>3.507917</v>
+        <v>3.5956770000000002</v>
       </c>
       <c r="K38" s="7">
-        <v>11.481747</v>
+        <v>11.45846</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3609,25 +3609,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.030496</v>
+        <v>0.025559</v>
       </c>
       <c r="F39" s="7">
-        <v>0.054254</v>
+        <v>0.054612</v>
       </c>
       <c r="G39" s="7">
-        <v>0.188407</v>
+        <v>0.188869</v>
       </c>
       <c r="H39" s="7">
-        <v>0.111816</v>
+        <v>0.117331</v>
       </c>
       <c r="I39" s="7">
-        <v>0.457992</v>
+        <v>0.458503</v>
       </c>
       <c r="J39" s="7">
-        <v>2.934036</v>
+        <v>2.9561450000000002</v>
       </c>
       <c r="K39" s="7">
-        <v>5.661404</v>
+        <v>5.68155</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,25 +3644,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.087658</v>
+        <v>0.08058199999999999</v>
       </c>
       <c r="F40" s="7">
-        <v>0.098191</v>
+        <v>0.11149800000000001</v>
       </c>
       <c r="G40" s="7">
-        <v>0.302183</v>
+        <v>0.291461</v>
       </c>
       <c r="H40" s="7">
-        <v>0.231347</v>
+        <v>0.24188600000000002</v>
       </c>
       <c r="I40" s="7">
-        <v>0.609173</v>
+        <v>0.609097</v>
       </c>
       <c r="J40" s="7">
-        <v>3.395661</v>
+        <v>3.5104640000000003</v>
       </c>
       <c r="K40" s="7">
-        <v>11.682041</v>
+        <v>11.669399</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3679,25 +3679,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.070437</v>
+        <v>0.067815</v>
       </c>
       <c r="F41" s="7">
-        <v>0.090938</v>
+        <v>0.10369999999999999</v>
       </c>
       <c r="G41" s="7">
-        <v>0.27943999999999997</v>
+        <v>0.273252</v>
       </c>
       <c r="H41" s="7">
-        <v>0.20717300000000002</v>
+        <v>0.21893</v>
       </c>
       <c r="I41" s="7">
-        <v>0.593446</v>
+        <v>0.5897720000000001</v>
       </c>
       <c r="J41" s="7">
-        <v>3.1146</v>
+        <v>3.220679</v>
       </c>
       <c r="K41" s="7">
-        <v>9.962586</v>
+        <v>9.981912</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,25 +3714,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.095429</v>
+        <v>0.08210800000000001</v>
       </c>
       <c r="F42" s="7">
-        <v>0.048133999999999996</v>
+        <v>0.055053</v>
       </c>
       <c r="G42" s="7">
-        <v>0.307713</v>
+        <v>0.297575</v>
       </c>
       <c r="H42" s="7">
-        <v>0.250309</v>
+        <v>0.25224599999999997</v>
       </c>
       <c r="I42" s="7">
-        <v>0.569894</v>
+        <v>0.57987</v>
       </c>
       <c r="J42" s="7">
-        <v>3.14433</v>
+        <v>3.2005500000000002</v>
       </c>
       <c r="K42" s="7">
-        <v>10.856817000000001</v>
+        <v>10.756188</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3749,25 +3749,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.08055999999999999</v>
+        <v>0.061586999999999996</v>
       </c>
       <c r="F43" s="7">
-        <v>-0.01294</v>
+        <v>-0.013472</v>
       </c>
       <c r="G43" s="7">
-        <v>0.242225</v>
+        <v>0.228942</v>
       </c>
       <c r="H43" s="7">
-        <v>0.172619</v>
+        <v>0.18198699999999998</v>
       </c>
       <c r="I43" s="7">
-        <v>0.458523</v>
+        <v>0.47158700000000003</v>
       </c>
       <c r="J43" s="7">
-        <v>4.003253</v>
+        <v>4.139745</v>
       </c>
       <c r="K43" s="7">
-        <v>21.154042</v>
+        <v>21.010106</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3784,25 +3784,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.044391</v>
+        <v>0.033253</v>
       </c>
       <c r="F44" s="7">
-        <v>0.05744</v>
+        <v>0.057784</v>
       </c>
       <c r="G44" s="7">
-        <v>0.197921</v>
+        <v>0.19438</v>
       </c>
       <c r="H44" s="7">
-        <v>0.113252</v>
+        <v>0.115648</v>
       </c>
       <c r="I44" s="7">
-        <v>0.475697</v>
+        <v>0.47255800000000003</v>
       </c>
       <c r="J44" s="7">
-        <v>2.44283</v>
+        <v>2.4539869999999997</v>
       </c>
       <c r="K44" s="7">
-        <v>4.444146</v>
+        <v>4.447731</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3819,25 +3819,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.077908</v>
+        <v>0.06486</v>
       </c>
       <c r="F45" s="7">
-        <v>0.050148</v>
+        <v>0.055288000000000004</v>
       </c>
       <c r="G45" s="7">
-        <v>0.287964</v>
+        <v>0.278829</v>
       </c>
       <c r="H45" s="7">
-        <v>0.21454399999999998</v>
+        <v>0.215827</v>
       </c>
       <c r="I45" s="7">
-        <v>0.57696</v>
+        <v>0.579862</v>
       </c>
       <c r="J45" s="7">
-        <v>3.23597</v>
+        <v>3.2896319999999997</v>
       </c>
       <c r="K45" s="7">
-        <v>9.529091</v>
+        <v>9.460094</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3854,25 +3854,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.074555</v>
+        <v>0.069207</v>
       </c>
       <c r="F46" s="7">
-        <v>0.100075</v>
+        <v>0.11421900000000001</v>
       </c>
       <c r="G46" s="7">
-        <v>0.30396999999999996</v>
+        <v>0.299636</v>
       </c>
       <c r="H46" s="7">
-        <v>0.24084499999999998</v>
+        <v>0.252697</v>
       </c>
       <c r="I46" s="7">
-        <v>0.609088</v>
+        <v>0.609356</v>
       </c>
       <c r="J46" s="7">
-        <v>3.4974979999999998</v>
+        <v>3.640912</v>
       </c>
       <c r="K46" s="7">
-        <v>10.247300000000001</v>
+        <v>10.260798</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3889,25 +3889,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.092604</v>
+        <v>0.088179</v>
       </c>
       <c r="F47" s="7">
-        <v>0.08380800000000001</v>
+        <v>0.10060600000000001</v>
       </c>
       <c r="G47" s="7">
-        <v>0.30017099999999997</v>
+        <v>0.294649</v>
       </c>
       <c r="H47" s="7">
-        <v>0.24152</v>
+        <v>0.257407</v>
       </c>
       <c r="I47" s="7">
-        <v>0.599044</v>
+        <v>0.611294</v>
       </c>
       <c r="J47" s="7">
-        <v>3.5565589999999996</v>
+        <v>3.6949349999999996</v>
       </c>
       <c r="K47" s="7">
-        <v>13.268092</v>
+        <v>13.108315</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3924,25 +3924,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.066537</v>
+        <v>0.049409</v>
       </c>
       <c r="F48" s="7">
-        <v>-0.015325</v>
+        <v>-0.0143</v>
       </c>
       <c r="G48" s="7">
-        <v>0.16881000000000002</v>
+        <v>0.134961</v>
       </c>
       <c r="H48" s="7">
-        <v>0.141265</v>
+        <v>0.138856</v>
       </c>
       <c r="I48" s="7">
-        <v>0.438169</v>
+        <v>0.451141</v>
       </c>
       <c r="J48" s="7">
-        <v>1.816219</v>
+        <v>1.890053</v>
       </c>
       <c r="K48" s="7">
-        <v>10.200609</v>
+        <v>10.050561</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3959,25 +3959,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.10843799999999999</v>
+        <v>0.092615</v>
       </c>
       <c r="F49" s="7">
-        <v>0.040701999999999995</v>
+        <v>0.045167</v>
       </c>
       <c r="G49" s="7">
-        <v>0.320059</v>
+        <v>0.305037</v>
       </c>
       <c r="H49" s="7">
-        <v>0.249822</v>
+        <v>0.25347200000000003</v>
       </c>
       <c r="I49" s="7">
-        <v>0.5754509999999999</v>
+        <v>0.591006</v>
       </c>
       <c r="J49" s="7">
-        <v>3.678404</v>
+        <v>3.7725510000000004</v>
       </c>
       <c r="K49" s="7">
-        <v>15.982069</v>
+        <v>15.798847</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3994,25 +3994,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.120694</v>
+        <v>0.096593</v>
       </c>
       <c r="F50" s="7">
-        <v>0.052803</v>
+        <v>0.050683</v>
       </c>
       <c r="G50" s="7">
-        <v>0.147595</v>
+        <v>0.139976</v>
       </c>
       <c r="H50" s="7">
-        <v>0.11505000000000001</v>
+        <v>0.118163</v>
       </c>
       <c r="I50" s="7">
-        <v>0.5379849999999999</v>
+        <v>0.5130250000000001</v>
       </c>
       <c r="J50" s="7">
-        <v>3.028245</v>
+        <v>3.0417579999999997</v>
       </c>
       <c r="K50" s="7">
-        <v>8.923124</v>
+        <v>8.868125</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,25 +4029,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.060894000000000004</v>
+        <v>0.046947</v>
       </c>
       <c r="F51" s="7">
-        <v>0.00481</v>
+        <v>0.014071</v>
       </c>
       <c r="G51" s="7">
-        <v>0.186931</v>
+        <v>0.17465699999999998</v>
       </c>
       <c r="H51" s="7">
-        <v>0.122707</v>
+        <v>0.12642799999999998</v>
       </c>
       <c r="I51" s="7">
-        <v>0.37127699999999997</v>
+        <v>0.375794</v>
       </c>
       <c r="J51" s="7">
-        <v>2.538574</v>
+        <v>2.587246</v>
       </c>
       <c r="K51" s="7">
-        <v>8.087619</v>
+        <v>8.021699</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4064,25 +4064,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.117024</v>
+        <v>0.09294600000000001</v>
       </c>
       <c r="F52" s="7">
-        <v>0.004181000000000001</v>
+        <v>0.006861000000000001</v>
       </c>
       <c r="G52" s="7">
-        <v>0.274486</v>
+        <v>0.257302</v>
       </c>
       <c r="H52" s="7">
-        <v>0.19603</v>
+        <v>0.203254</v>
       </c>
       <c r="I52" s="7">
-        <v>0.48170900000000005</v>
+        <v>0.500002</v>
       </c>
       <c r="J52" s="7">
-        <v>2.7235270000000003</v>
+        <v>2.780446</v>
       </c>
       <c r="K52" s="7">
-        <v>10.951318</v>
+        <v>10.914940999999999</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4099,25 +4099,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.060506000000000004</v>
+        <v>0.03771</v>
       </c>
       <c r="F53" s="7">
-        <v>0.030621999999999996</v>
+        <v>0.028433</v>
       </c>
       <c r="G53" s="7">
-        <v>0.095118</v>
+        <v>0.09262100000000001</v>
       </c>
       <c r="H53" s="7">
-        <v>0.042327000000000004</v>
+        <v>0.042699999999999995</v>
       </c>
       <c r="I53" s="7">
-        <v>0.33921500000000004</v>
+        <v>0.33371</v>
       </c>
       <c r="J53" s="7">
-        <v>2.171327</v>
+        <v>2.171744</v>
       </c>
       <c r="K53" s="7">
-        <v>6.517974000000001</v>
+        <v>6.412286</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4134,25 +4134,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.045811000000000004</v>
+        <v>0.030392000000000002</v>
       </c>
       <c r="F54" s="7">
-        <v>0.034419</v>
+        <v>0.031545000000000004</v>
       </c>
       <c r="G54" s="7">
-        <v>0.096948</v>
+        <v>0.094299</v>
       </c>
       <c r="H54" s="7">
-        <v>0.050563000000000004</v>
+        <v>0.050731</v>
       </c>
       <c r="I54" s="7">
-        <v>0.305153</v>
+        <v>0.301349</v>
       </c>
       <c r="J54" s="7">
-        <v>2.053906</v>
+        <v>2.053511</v>
       </c>
       <c r="K54" s="7">
-        <v>6.3406709999999995</v>
+        <v>6.233182</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4169,25 +4169,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.000057999999999999994</v>
+        <v>-0.012971</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.10612500000000001</v>
+        <v>-0.084079</v>
       </c>
       <c r="G55" s="7">
-        <v>0.17023700000000003</v>
+        <v>0.18688500000000002</v>
       </c>
       <c r="H55" s="7">
-        <v>0.058569</v>
+        <v>0.06521300000000001</v>
       </c>
       <c r="I55" s="7">
-        <v>0.576095</v>
+        <v>0.595252</v>
       </c>
       <c r="J55" s="7">
-        <v>3.8883609999999997</v>
+        <v>3.9110250000000004</v>
       </c>
       <c r="K55" s="7">
-        <v>13.135737999999998</v>
+        <v>13.011721999999999</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4204,25 +4204,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.077961</v>
+        <v>0.06687599999999999</v>
       </c>
       <c r="F56" s="7">
-        <v>0.05526</v>
+        <v>0.053895</v>
       </c>
       <c r="G56" s="7">
-        <v>0.233804</v>
+        <v>0.228532</v>
       </c>
       <c r="H56" s="7">
-        <v>0.140951</v>
+        <v>0.14491300000000001</v>
       </c>
       <c r="I56" s="7">
-        <v>0.47463900000000003</v>
+        <v>0.47401000000000004</v>
       </c>
       <c r="J56" s="7">
-        <v>2.059383</v>
+        <v>2.103596</v>
       </c>
       <c r="K56" s="7">
-        <v>5.6543280000000005</v>
+        <v>5.6347320000000005</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4239,25 +4239,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.050875000000000004</v>
+        <v>0.022153</v>
       </c>
       <c r="F57" s="7">
-        <v>-0.010737000000000002</v>
+        <v>-0.014766999999999999</v>
       </c>
       <c r="G57" s="7">
-        <v>0.127529</v>
+        <v>0.12060399999999999</v>
       </c>
       <c r="H57" s="7">
-        <v>0.060629</v>
+        <v>0.059988</v>
       </c>
       <c r="I57" s="7">
-        <v>0.368344</v>
+        <v>0.362286</v>
       </c>
       <c r="J57" s="7">
-        <v>1.345757</v>
+        <v>1.363247</v>
       </c>
       <c r="K57" s="7">
-        <v>3.550681</v>
+        <v>3.521064</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4274,25 +4274,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.08637800000000001</v>
+        <v>0.06935</v>
       </c>
       <c r="F58" s="7">
-        <v>0.044457</v>
+        <v>0.057861</v>
       </c>
       <c r="G58" s="7">
-        <v>0.299237</v>
+        <v>0.28959399999999996</v>
       </c>
       <c r="H58" s="7">
-        <v>0.225851</v>
+        <v>0.225774</v>
       </c>
       <c r="I58" s="7">
-        <v>0.581907</v>
+        <v>0.580613</v>
       </c>
       <c r="J58" s="7">
-        <v>3.213866</v>
+        <v>3.26202</v>
       </c>
       <c r="K58" s="7">
-        <v>9.612512</v>
+        <v>9.532468</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4309,25 +4309,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.095883</v>
+        <v>0.080842</v>
       </c>
       <c r="F59" s="7">
-        <v>0.052017</v>
+        <v>0.060212</v>
       </c>
       <c r="G59" s="7">
-        <v>0.317337</v>
+        <v>0.305862</v>
       </c>
       <c r="H59" s="7">
-        <v>0.254371</v>
+        <v>0.255917</v>
       </c>
       <c r="I59" s="7">
-        <v>0.577628</v>
+        <v>0.5864889999999999</v>
       </c>
       <c r="J59" s="7">
-        <v>3.2520460000000004</v>
+        <v>3.3068579999999996</v>
       </c>
       <c r="K59" s="7">
-        <v>10.736658</v>
+        <v>10.630516</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4344,25 +4344,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.093351</v>
+        <v>0.08080399999999999</v>
       </c>
       <c r="F60" s="7">
-        <v>-0.00023300000000000003</v>
+        <v>0.004497</v>
       </c>
       <c r="G60" s="7">
-        <v>0.21229800000000001</v>
+        <v>0.210212</v>
       </c>
       <c r="H60" s="7">
-        <v>0.17340499999999998</v>
+        <v>0.18711099999999997</v>
       </c>
       <c r="I60" s="7">
-        <v>0.410614</v>
+        <v>0.435453</v>
       </c>
       <c r="J60" s="7">
-        <v>2.426367</v>
+        <v>2.569369</v>
       </c>
       <c r="K60" s="7">
-        <v>12.907238</v>
+        <v>12.830228</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,25 +4379,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.109756</v>
+        <v>0.088922</v>
       </c>
       <c r="F61" s="7">
-        <v>0.040554</v>
+        <v>0.035388</v>
       </c>
       <c r="G61" s="7">
-        <v>0.20721</v>
+        <v>0.19626100000000002</v>
       </c>
       <c r="H61" s="7">
-        <v>0.164016</v>
+        <v>0.165676</v>
       </c>
       <c r="I61" s="7">
-        <v>0.506471</v>
+        <v>0.49167099999999997</v>
       </c>
       <c r="J61" s="7">
-        <v>2.4102930000000002</v>
+        <v>2.517716</v>
       </c>
       <c r="K61" s="7">
-        <v>7.667809999999999</v>
+        <v>7.558089</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,25 +4414,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.074947</v>
+        <v>0.060732</v>
       </c>
       <c r="F62" s="7">
-        <v>-0.04616</v>
+        <v>-0.042156</v>
       </c>
       <c r="G62" s="7">
-        <v>0.164086</v>
+        <v>0.151975</v>
       </c>
       <c r="H62" s="7">
-        <v>0.137017</v>
+        <v>0.155302</v>
       </c>
       <c r="I62" s="7">
-        <v>0.353819</v>
+        <v>0.38249099999999997</v>
       </c>
       <c r="J62" s="7">
-        <v>2.390474</v>
+        <v>2.496355</v>
       </c>
       <c r="K62" s="7">
-        <v>12.150658</v>
+        <v>12.071266000000001</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4449,25 +4449,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.058410000000000004</v>
+        <v>0.037637000000000004</v>
       </c>
       <c r="F63" s="7">
-        <v>0.0053690000000000005</v>
+        <v>0.0027960000000000003</v>
       </c>
       <c r="G63" s="7">
-        <v>0.17816500000000002</v>
+        <v>0.169423</v>
       </c>
       <c r="H63" s="7">
-        <v>0.08247600000000001</v>
+        <v>0.082766</v>
       </c>
       <c r="I63" s="7">
-        <v>0.409653</v>
+        <v>0.397851</v>
       </c>
       <c r="J63" s="7">
-        <v>1.9142080000000001</v>
+        <v>1.931292</v>
       </c>
       <c r="K63" s="7">
-        <v>4.649539</v>
+        <v>4.623226</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4484,25 +4484,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.03465</v>
+        <v>0.023540000000000002</v>
       </c>
       <c r="F64" s="7">
-        <v>-0.017641</v>
+        <v>0.0025069999999999997</v>
       </c>
       <c r="G64" s="7">
-        <v>0.17122800000000002</v>
+        <v>0.17380099999999998</v>
       </c>
       <c r="H64" s="7">
-        <v>0.12759</v>
+        <v>0.135069</v>
       </c>
       <c r="I64" s="7">
-        <v>0.38214</v>
+        <v>0.391449</v>
       </c>
       <c r="J64" s="7">
-        <v>2.033047</v>
+        <v>2.075043</v>
       </c>
       <c r="K64" s="7">
-        <v>6.094595000000001</v>
+        <v>6.083786</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,25 +4519,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.037842</v>
+        <v>0.028188</v>
       </c>
       <c r="F65" s="7">
-        <v>0.041783</v>
+        <v>0.040979</v>
       </c>
       <c r="G65" s="7">
-        <v>0.104518</v>
+        <v>0.102925</v>
       </c>
       <c r="H65" s="7">
-        <v>0.058666</v>
+        <v>0.059273</v>
       </c>
       <c r="I65" s="7">
-        <v>0.290511</v>
+        <v>0.291699</v>
       </c>
       <c r="J65" s="7">
-        <v>2.080451</v>
+        <v>2.078696</v>
       </c>
       <c r="K65" s="7">
-        <v>5.3475909999999995</v>
+        <v>5.296734</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4554,25 +4554,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.05257100000000001</v>
+        <v>0.030133999999999998</v>
       </c>
       <c r="F66" s="7">
-        <v>0.034967</v>
+        <v>0.028197999999999997</v>
       </c>
       <c r="G66" s="7">
-        <v>0.090648</v>
+        <v>0.086922</v>
       </c>
       <c r="H66" s="7">
-        <v>0.038467</v>
+        <v>0.036252</v>
       </c>
       <c r="I66" s="7">
-        <v>0.321748</v>
+        <v>0.31339300000000003</v>
       </c>
       <c r="J66" s="7">
-        <v>2.286848</v>
+        <v>2.282</v>
       </c>
       <c r="K66" s="7">
-        <v>6.795286</v>
+        <v>6.688713</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4589,25 +4589,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.06807</v>
+        <v>0.054071</v>
       </c>
       <c r="F67" s="7">
-        <v>0.028812</v>
+        <v>0.035787</v>
       </c>
       <c r="G67" s="7">
-        <v>0.25572</v>
+        <v>0.255449</v>
       </c>
       <c r="H67" s="7">
-        <v>0.18834499999999998</v>
+        <v>0.19250699999999998</v>
       </c>
       <c r="I67" s="7">
-        <v>0.552889</v>
+        <v>0.563604</v>
       </c>
       <c r="J67" s="7">
-        <v>2.556862</v>
+        <v>2.595498</v>
       </c>
       <c r="K67" s="7">
-        <v>9.419381</v>
+        <v>9.359162</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4624,25 +4624,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.045175</v>
+        <v>0.028896</v>
       </c>
       <c r="F68" s="7">
-        <v>0.034447</v>
+        <v>0.031004999999999998</v>
       </c>
       <c r="G68" s="7">
-        <v>0.09234400000000001</v>
+        <v>0.089778</v>
       </c>
       <c r="H68" s="7">
-        <v>0.044966</v>
+        <v>0.043353</v>
       </c>
       <c r="I68" s="7">
-        <v>0.295022</v>
+        <v>0.289642</v>
       </c>
       <c r="J68" s="7">
-        <v>2.066234</v>
+        <v>2.059906</v>
       </c>
       <c r="K68" s="7">
-        <v>6.174874</v>
+        <v>6.083094999999999</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4659,25 +4659,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.071876</v>
+        <v>0.049441</v>
       </c>
       <c r="F69" s="7">
-        <v>0.031054</v>
+        <v>0.028671000000000002</v>
       </c>
       <c r="G69" s="7">
-        <v>0.208725</v>
+        <v>0.19950199999999998</v>
       </c>
       <c r="H69" s="7">
-        <v>0.12135199999999999</v>
+        <v>0.12153900000000001</v>
       </c>
       <c r="I69" s="7">
-        <v>0.479612</v>
+        <v>0.46621</v>
       </c>
       <c r="J69" s="7">
-        <v>2.179306</v>
+        <v>2.226961</v>
       </c>
       <c r="K69" s="7">
-        <v>5.528265</v>
+        <v>5.500598</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,25 +4694,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.031349999999999996</v>
+        <v>0.029234</v>
       </c>
       <c r="F70" s="7">
-        <v>0.09151</v>
+        <v>0.09382099999999999</v>
       </c>
       <c r="G70" s="7">
-        <v>0.200334</v>
+        <v>0.200064</v>
       </c>
       <c r="H70" s="7">
-        <v>0.125633</v>
+        <v>0.130241</v>
       </c>
       <c r="I70" s="7">
-        <v>0.48039000000000004</v>
+        <v>0.477685</v>
       </c>
       <c r="J70" s="7">
-        <v>2.344308</v>
+        <v>2.3520079999999997</v>
       </c>
       <c r="K70" s="7">
-        <v>4.050433</v>
+        <v>4.061666</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4729,25 +4729,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.239862</v>
+        <v>0.219387</v>
       </c>
       <c r="F71" s="7">
-        <v>0.116579</v>
+        <v>0.135988</v>
       </c>
       <c r="G71" s="7">
-        <v>0.155796</v>
+        <v>0.153051</v>
       </c>
       <c r="H71" s="7">
-        <v>0.166383</v>
+        <v>0.172651</v>
       </c>
       <c r="I71" s="7">
-        <v>0.690736</v>
+        <v>0.6515810000000001</v>
       </c>
       <c r="J71" s="7">
-        <v>3.710308</v>
+        <v>3.8157530000000004</v>
       </c>
       <c r="K71" s="7">
-        <v>7.658041</v>
+        <v>7.838273</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4764,25 +4764,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.04856099999999999</v>
+        <v>0.04402300000000001</v>
       </c>
       <c r="F72" s="7">
-        <v>0.071409</v>
+        <v>0.075442</v>
       </c>
       <c r="G72" s="7">
-        <v>0.22896899999999998</v>
+        <v>0.227974</v>
       </c>
       <c r="H72" s="7">
-        <v>0.139066</v>
+        <v>0.143813</v>
       </c>
       <c r="I72" s="7">
-        <v>0.457356</v>
+        <v>0.458756</v>
       </c>
       <c r="J72" s="7">
-        <v>1.755354</v>
+        <v>1.807293</v>
       </c>
       <c r="K72" s="7">
-        <v>4.6642079999999995</v>
+        <v>4.672081</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,25 +4799,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.053811</v>
+        <v>0.032986</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.018352999999999998</v>
+        <v>-0.021640000000000003</v>
       </c>
       <c r="G73" s="7">
-        <v>0.039384</v>
+        <v>0.037006000000000004</v>
       </c>
       <c r="H73" s="7">
-        <v>-0.010813</v>
+        <v>-0.010576</v>
       </c>
       <c r="I73" s="7">
-        <v>0.269025</v>
+        <v>0.263535</v>
       </c>
       <c r="J73" s="7">
-        <v>2.0060990000000003</v>
+        <v>2.006082</v>
       </c>
       <c r="K73" s="7">
-        <v>6.0839229999999995</v>
+        <v>5.984853</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,25 +4834,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.115339</v>
+        <v>0.10602299999999999</v>
       </c>
       <c r="F74" s="7">
-        <v>-0.0034260000000000002</v>
+        <v>0.001512</v>
       </c>
       <c r="G74" s="7">
-        <v>0.240555</v>
+        <v>0.22334900000000002</v>
       </c>
       <c r="H74" s="7">
-        <v>0.198845</v>
+        <v>0.20883700000000002</v>
       </c>
       <c r="I74" s="7">
-        <v>0.378049</v>
+        <v>0.40088</v>
       </c>
       <c r="J74" s="7">
-        <v>2.6196289999999998</v>
+        <v>2.730362</v>
       </c>
       <c r="K74" s="7">
-        <v>14.933343</v>
+        <v>14.75037</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4869,25 +4869,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.045023</v>
+        <v>0.023135</v>
       </c>
       <c r="F75" s="7">
-        <v>0.0032979999999999997</v>
+        <v>0.002708</v>
       </c>
       <c r="G75" s="7">
-        <v>0.160996</v>
+        <v>0.153945</v>
       </c>
       <c r="H75" s="7">
-        <v>0.046432</v>
+        <v>0.045385999999999996</v>
       </c>
       <c r="I75" s="7">
-        <v>0.419143</v>
+        <v>0.399726</v>
       </c>
       <c r="J75" s="7">
-        <v>1.7855109999999998</v>
+        <v>1.774041</v>
       </c>
       <c r="K75" s="7">
-        <v>3.6906130000000004</v>
+        <v>3.670232</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,25 +4904,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.067526</v>
+        <v>0.045820999999999994</v>
       </c>
       <c r="F76" s="7">
-        <v>0.030445000000000003</v>
+        <v>0.028083999999999998</v>
       </c>
       <c r="G76" s="7">
-        <v>0.21144200000000002</v>
+        <v>0.202003</v>
       </c>
       <c r="H76" s="7">
-        <v>0.12226200000000001</v>
+        <v>0.122335</v>
       </c>
       <c r="I76" s="7">
-        <v>0.487292</v>
+        <v>0.473842</v>
       </c>
       <c r="J76" s="7">
-        <v>2.223734</v>
+        <v>2.268749</v>
       </c>
       <c r="K76" s="7">
-        <v>5.620322</v>
+        <v>5.590712999999999</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4939,25 +4939,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.038003999999999996</v>
+        <v>0.036732999999999995</v>
       </c>
       <c r="F77" s="7">
-        <v>0.061137</v>
+        <v>0.06274</v>
       </c>
       <c r="G77" s="7">
-        <v>0.27716799999999997</v>
+        <v>0.294435</v>
       </c>
       <c r="H77" s="7">
-        <v>0.17928</v>
+        <v>0.19238600000000003</v>
       </c>
       <c r="I77" s="7">
-        <v>0.40739400000000003</v>
+        <v>0.417719</v>
       </c>
       <c r="J77" s="7">
-        <v>1.875658</v>
+        <v>1.9358469999999999</v>
       </c>
       <c r="K77" s="7">
-        <v>5.448827</v>
+        <v>5.472622</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4974,25 +4974,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="7">
-        <v>0.071476</v>
+        <v>0.050004</v>
       </c>
       <c r="F78" s="7">
-        <v>0.080672</v>
+        <v>0.11448399999999999</v>
       </c>
       <c r="G78" s="7">
-        <v>0.32665500000000003</v>
+        <v>0.325652</v>
       </c>
       <c r="H78" s="7">
-        <v>0.236506</v>
+        <v>0.248514</v>
       </c>
       <c r="I78" s="7">
-        <v>0.665611</v>
+        <v>0.676529</v>
       </c>
       <c r="J78" s="7">
-        <v>2.8338400000000004</v>
+        <v>2.938285</v>
       </c>
       <c r="K78" s="7">
-        <v>8.328493</v>
+        <v>8.286103</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5009,25 +5009,25 @@
         <v>5</v>
       </c>
       <c r="E79" s="7">
-        <v>0.070283</v>
+        <v>0.061369</v>
       </c>
       <c r="F79" s="7">
-        <v>0.062218</v>
+        <v>0.069546</v>
       </c>
       <c r="G79" s="7">
-        <v>0.164073</v>
+        <v>0.15637299999999998</v>
       </c>
       <c r="H79" s="7">
-        <v>0.149735</v>
+        <v>0.161327</v>
       </c>
       <c r="I79" s="7">
-        <v>0.41286900000000004</v>
+        <v>0.429489</v>
       </c>
       <c r="J79" s="7">
-        <v>2.341723</v>
+        <v>2.458862</v>
       </c>
       <c r="K79" s="7">
-        <v>7.962582</v>
+        <v>8.003442999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,25 +5044,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.12256</v>
+        <v>0.092912</v>
       </c>
       <c r="F80" s="7">
-        <v>0.019785</v>
+        <v>0.017787</v>
       </c>
       <c r="G80" s="7">
-        <v>0.23241</v>
+        <v>0.222112</v>
       </c>
       <c r="H80" s="7">
-        <v>0.22974699999999998</v>
+        <v>0.233571</v>
       </c>
       <c r="I80" s="7">
-        <v>0.41103700000000004</v>
+        <v>0.420471</v>
       </c>
       <c r="J80" s="7">
-        <v>2.360147</v>
+        <v>2.465043</v>
       </c>
       <c r="K80" s="7">
-        <v>11.244314</v>
+        <v>10.995308999999999</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5079,25 +5079,25 @@
         <v>4</v>
       </c>
       <c r="E81" s="7">
-        <v>0.034598</v>
+        <v>0.030945999999999998</v>
       </c>
       <c r="F81" s="7">
-        <v>0.060239</v>
+        <v>0.064476</v>
       </c>
       <c r="G81" s="7">
-        <v>0.172163</v>
+        <v>0.17018799999999998</v>
       </c>
       <c r="H81" s="7">
-        <v>0.11444499999999999</v>
+        <v>0.12086000000000001</v>
       </c>
       <c r="I81" s="7">
-        <v>0.376471</v>
+        <v>0.382594</v>
       </c>
       <c r="J81" s="7">
-        <v>1.521361</v>
+        <v>1.6055549999999998</v>
       </c>
       <c r="K81" s="7">
-        <v>4.368844</v>
+        <v>4.387124</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,25 +5114,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.045260999999999996</v>
+        <v>0.019562</v>
       </c>
       <c r="F82" s="7">
-        <v>-0.00109</v>
+        <v>-0.0037080000000000004</v>
       </c>
       <c r="G82" s="7">
-        <v>0.12934400000000001</v>
+        <v>0.121875</v>
       </c>
       <c r="H82" s="7">
-        <v>0.038483</v>
+        <v>0.038006000000000005</v>
       </c>
       <c r="I82" s="7">
-        <v>0.385788</v>
+        <v>0.369418</v>
       </c>
       <c r="J82" s="7">
-        <v>1.4733150000000002</v>
+        <v>1.465329</v>
       </c>
       <c r="K82" s="7">
-        <v>3.10115</v>
+        <v>3.088612</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5149,25 +5149,25 @@
         <v>5</v>
       </c>
       <c r="E83" s="7">
-        <v>0.07692700000000001</v>
+        <v>0.065746</v>
       </c>
       <c r="F83" s="7">
-        <v>0.05592</v>
+        <v>0.062082</v>
       </c>
       <c r="G83" s="7">
-        <v>0.163611</v>
+        <v>0.15221</v>
       </c>
       <c r="H83" s="7">
-        <v>0.15792</v>
+        <v>0.1703</v>
       </c>
       <c r="I83" s="7">
-        <v>0.412943</v>
+        <v>0.43367400000000006</v>
       </c>
       <c r="J83" s="7">
-        <v>2.362629</v>
+        <v>2.5040780000000002</v>
       </c>
       <c r="K83" s="7">
-        <v>8.946284</v>
+        <v>8.992984</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,22 +5184,22 @@
         <v>6</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.0052829999999999995</v>
+        <v>-0.017651</v>
       </c>
       <c r="F84" s="7">
-        <v>-0.117392</v>
+        <v>-0.098404</v>
       </c>
       <c r="G84" s="7">
-        <v>0.12222899999999999</v>
+        <v>0.132827</v>
       </c>
       <c r="H84" s="7">
-        <v>0.008111</v>
+        <v>0.012352</v>
       </c>
       <c r="I84" s="7">
-        <v>0.610614</v>
+        <v>0.620229</v>
       </c>
       <c r="J84" s="7">
-        <v>3.739292</v>
+        <v>3.7777019999999997</v>
       </c>
       <c r="K84" s="7"/>
     </row>
@@ -5217,19 +5217,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="7">
-        <v>0.030476</v>
+        <v>0.028433</v>
       </c>
       <c r="F85" s="7">
-        <v>0.091057</v>
+        <v>0.093297</v>
       </c>
       <c r="G85" s="7">
-        <v>0.19625199999999998</v>
+        <v>0.196081</v>
       </c>
       <c r="H85" s="7">
-        <v>0.123977</v>
+        <v>0.128361</v>
       </c>
       <c r="I85" s="7">
-        <v>0.464959</v>
+        <v>0.462733</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5248,22 +5248,22 @@
         <v>6</v>
       </c>
       <c r="E86" s="7">
-        <v>0.114963</v>
+        <v>0.087408</v>
       </c>
       <c r="F86" s="7">
-        <v>0.034554999999999995</v>
+        <v>0.029745</v>
       </c>
       <c r="G86" s="7">
-        <v>0.258959</v>
+        <v>0.242727</v>
       </c>
       <c r="H86" s="7">
-        <v>0.19966899999999999</v>
+        <v>0.199988</v>
       </c>
       <c r="I86" s="7">
-        <v>0.5562469999999999</v>
+        <v>0.544334</v>
       </c>
       <c r="J86" s="7">
-        <v>2.774076</v>
+        <v>2.811684</v>
       </c>
       <c r="K86" s="7"/>
     </row>
@@ -5281,22 +5281,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.152562</v>
+        <v>0.139697</v>
       </c>
       <c r="F87" s="7">
-        <v>0.220499</v>
+        <v>0.236238</v>
       </c>
       <c r="G87" s="7">
-        <v>0.304162</v>
+        <v>0.280565</v>
       </c>
       <c r="H87" s="7">
-        <v>0.327944</v>
+        <v>0.337918</v>
       </c>
       <c r="I87" s="7">
-        <v>0.705989</v>
+        <v>0.685268</v>
       </c>
       <c r="J87" s="7">
-        <v>3.9769889999999997</v>
+        <v>4.27189</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,25 +5314,25 @@
         <v>7</v>
       </c>
       <c r="E88" s="7">
-        <v>0.000517</v>
+        <v>-0.012073</v>
       </c>
       <c r="F88" s="7">
-        <v>-0.110335</v>
+        <v>-0.079031</v>
       </c>
       <c r="G88" s="7">
-        <v>0.188466</v>
+        <v>0.198265</v>
       </c>
       <c r="H88" s="7">
-        <v>0.065965</v>
+        <v>0.071742</v>
       </c>
       <c r="I88" s="7">
-        <v>0.601645</v>
+        <v>0.62235</v>
       </c>
       <c r="J88" s="7">
-        <v>4.113475</v>
+        <v>4.145385</v>
       </c>
       <c r="K88" s="7">
-        <v>14.030733</v>
+        <v>13.875522</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5349,25 +5349,25 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>0.035228999999999996</v>
+        <v>0.031000999999999997</v>
       </c>
       <c r="F89" s="7">
-        <v>0.089365</v>
+        <v>0.090059</v>
       </c>
       <c r="G89" s="7">
-        <v>0.205676</v>
+        <v>0.20366700000000001</v>
       </c>
       <c r="H89" s="7">
-        <v>0.12948</v>
+        <v>0.132187</v>
       </c>
       <c r="I89" s="7">
-        <v>0.514527</v>
+        <v>0.510306</v>
       </c>
       <c r="J89" s="7">
-        <v>2.38897</v>
+        <v>2.405185</v>
       </c>
       <c r="K89" s="7">
-        <v>4.320883</v>
+        <v>4.313124</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5384,25 +5384,25 @@
         <v>5</v>
       </c>
       <c r="E90" s="7">
-        <v>0.04533</v>
+        <v>0.027328</v>
       </c>
       <c r="F90" s="7">
-        <v>0.006226000000000001</v>
+        <v>0.005965000000000001</v>
       </c>
       <c r="G90" s="7">
-        <v>0.161799</v>
+        <v>0.15303699999999998</v>
       </c>
       <c r="H90" s="7">
-        <v>0.078945</v>
+        <v>0.080771</v>
       </c>
       <c r="I90" s="7">
-        <v>0.30674</v>
+        <v>0.308527</v>
       </c>
       <c r="J90" s="7">
-        <v>2.01835</v>
+        <v>2.0721350000000003</v>
       </c>
       <c r="K90" s="7">
-        <v>5.406464</v>
+        <v>5.394784</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5419,22 +5419,22 @@
         <v>6</v>
       </c>
       <c r="E91" s="7">
-        <v>0.062224</v>
+        <v>0.053329</v>
       </c>
       <c r="F91" s="7">
-        <v>0.03395</v>
+        <v>0.033295</v>
       </c>
       <c r="G91" s="7">
-        <v>0.239777</v>
+        <v>0.23268699999999998</v>
       </c>
       <c r="H91" s="7">
-        <v>0.16649899999999998</v>
+        <v>0.17274</v>
       </c>
       <c r="I91" s="7">
-        <v>0.430303</v>
+        <v>0.429334</v>
       </c>
       <c r="J91" s="7">
-        <v>2.549185</v>
+        <v>2.6364120000000004</v>
       </c>
       <c r="K91" s="7"/>
     </row>
@@ -5452,25 +5452,25 @@
         <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>0.054634999999999996</v>
+        <v>0.035973000000000005</v>
       </c>
       <c r="F92" s="7">
-        <v>0.005159</v>
+        <v>0.00471</v>
       </c>
       <c r="G92" s="7">
-        <v>0.19350799999999999</v>
+        <v>0.18294899999999997</v>
       </c>
       <c r="H92" s="7">
-        <v>0.091195</v>
+        <v>0.09342800000000001</v>
       </c>
       <c r="I92" s="7">
-        <v>0.35214</v>
+        <v>0.35283299999999995</v>
       </c>
       <c r="J92" s="7">
-        <v>1.9789949999999998</v>
+        <v>1.991168</v>
       </c>
       <c r="K92" s="7">
-        <v>4.928026</v>
+        <v>4.911771</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,25 +5487,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.038395</v>
+        <v>0.037071</v>
       </c>
       <c r="F93" s="7">
-        <v>0.059025</v>
+        <v>0.067096</v>
       </c>
       <c r="G93" s="7">
-        <v>0.197122</v>
+        <v>0.19652999999999998</v>
       </c>
       <c r="H93" s="7">
-        <v>0.130326</v>
+        <v>0.13622299999999998</v>
       </c>
       <c r="I93" s="7">
-        <v>0.35217</v>
+        <v>0.363625</v>
       </c>
       <c r="J93" s="7">
-        <v>1.705478</v>
+        <v>1.7889439999999999</v>
       </c>
       <c r="K93" s="7">
-        <v>4.621303</v>
+        <v>4.629904</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,25 +5522,25 @@
         <v>4</v>
       </c>
       <c r="E94" s="7">
-        <v>0.06760100000000001</v>
+        <v>0.051948999999999995</v>
       </c>
       <c r="F94" s="7">
-        <v>0.007631</v>
+        <v>0.018813</v>
       </c>
       <c r="G94" s="7">
-        <v>0.26374400000000003</v>
+        <v>0.250418</v>
       </c>
       <c r="H94" s="7">
-        <v>0.159755</v>
+        <v>0.164179</v>
       </c>
       <c r="I94" s="7">
-        <v>0.500291</v>
+        <v>0.507241</v>
       </c>
       <c r="J94" s="7">
-        <v>2.7792410000000003</v>
+        <v>2.867379</v>
       </c>
       <c r="K94" s="7">
-        <v>8.29903</v>
+        <v>8.256237</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,25 +5557,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.040453</v>
+        <v>0.019382999999999997</v>
       </c>
       <c r="F95" s="7">
-        <v>0.00577</v>
+        <v>0.00231</v>
       </c>
       <c r="G95" s="7">
-        <v>0.162963</v>
+        <v>0.15071199999999998</v>
       </c>
       <c r="H95" s="7">
-        <v>0.044152</v>
+        <v>0.042908</v>
       </c>
       <c r="I95" s="7">
-        <v>0.44085599999999997</v>
+        <v>0.409829</v>
       </c>
       <c r="J95" s="7">
-        <v>1.345004</v>
+        <v>1.342395</v>
       </c>
       <c r="K95" s="7">
-        <v>2.744436</v>
+        <v>2.73139</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,25 +5592,25 @@
         <v>7</v>
       </c>
       <c r="E96" s="7">
-        <v>0.094291</v>
+        <v>0.064573</v>
       </c>
       <c r="F96" s="7">
-        <v>-0.026334</v>
+        <v>-0.026277</v>
       </c>
       <c r="G96" s="7">
-        <v>0.272251</v>
+        <v>0.24715199999999998</v>
       </c>
       <c r="H96" s="7">
-        <v>0.198773</v>
+        <v>0.202974</v>
       </c>
       <c r="I96" s="7">
-        <v>0.398649</v>
+        <v>0.41411000000000003</v>
       </c>
       <c r="J96" s="7">
-        <v>2.883143</v>
+        <v>2.9873559999999997</v>
       </c>
       <c r="K96" s="7">
-        <v>14.815677</v>
+        <v>14.656436000000001</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,25 +5627,25 @@
         <v>6</v>
       </c>
       <c r="E97" s="7">
-        <v>0.072176</v>
+        <v>0.053669</v>
       </c>
       <c r="F97" s="7">
-        <v>-0.042382</v>
+        <v>-0.018577999999999997</v>
       </c>
       <c r="G97" s="7">
-        <v>0.37504899999999997</v>
+        <v>0.366509</v>
       </c>
       <c r="H97" s="7">
-        <v>0.197134</v>
+        <v>0.215129</v>
       </c>
       <c r="I97" s="7">
-        <v>0.506652</v>
+        <v>0.5449069999999999</v>
       </c>
       <c r="J97" s="7">
-        <v>4.0221219999999995</v>
+        <v>4.202305</v>
       </c>
       <c r="K97" s="7">
-        <v>19.323295</v>
+        <v>19.387493</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,25 +5662,25 @@
         <v>4</v>
       </c>
       <c r="E98" s="7">
-        <v>0.06953000000000001</v>
+        <v>0.053819</v>
       </c>
       <c r="F98" s="7">
-        <v>0.035166</v>
+        <v>0.042754</v>
       </c>
       <c r="G98" s="7">
-        <v>0.28769300000000003</v>
+        <v>0.27510999999999997</v>
       </c>
       <c r="H98" s="7">
-        <v>0.201909</v>
+        <v>0.205556</v>
       </c>
       <c r="I98" s="7">
-        <v>0.548542</v>
+        <v>0.553211</v>
       </c>
       <c r="J98" s="7">
-        <v>3.4370890000000003</v>
+        <v>3.563867</v>
       </c>
       <c r="K98" s="7">
-        <v>9.216228</v>
+        <v>9.171838000000001</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,25 +5697,25 @@
         <v>6</v>
       </c>
       <c r="E99" s="7">
-        <v>0.030089</v>
+        <v>0.023035</v>
       </c>
       <c r="F99" s="7">
-        <v>0.042515</v>
+        <v>0.039592999999999996</v>
       </c>
       <c r="G99" s="7">
-        <v>0.100382</v>
+        <v>0.09708399999999999</v>
       </c>
       <c r="H99" s="7">
-        <v>0.057543</v>
+        <v>0.057865</v>
       </c>
       <c r="I99" s="7">
-        <v>0.281556</v>
+        <v>0.27947700000000003</v>
       </c>
       <c r="J99" s="7">
-        <v>1.989575</v>
+        <v>1.985586</v>
       </c>
       <c r="K99" s="7">
-        <v>5.806404</v>
+        <v>5.721490999999999</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,25 +5732,25 @@
         <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>0.077096</v>
+        <v>0.059051</v>
       </c>
       <c r="F100" s="7">
-        <v>0.026907999999999998</v>
+        <v>0.034408</v>
       </c>
       <c r="G100" s="7">
-        <v>0.34726399999999996</v>
+        <v>0.33053899999999997</v>
       </c>
       <c r="H100" s="7">
-        <v>0.209224</v>
+        <v>0.213109</v>
       </c>
       <c r="I100" s="7">
-        <v>0.592816</v>
+        <v>0.600599</v>
       </c>
       <c r="J100" s="7">
-        <v>3.665846</v>
+        <v>3.76015</v>
       </c>
       <c r="K100" s="7">
-        <v>12.195058</v>
+        <v>12.118471</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,25 +5767,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.077518</v>
+        <v>0.07307000000000001</v>
       </c>
       <c r="F101" s="7">
-        <v>0.042213</v>
+        <v>0.060476</v>
       </c>
       <c r="G101" s="7">
-        <v>0.335394</v>
+        <v>0.337377</v>
       </c>
       <c r="H101" s="7">
-        <v>0.280416</v>
+        <v>0.302415</v>
       </c>
       <c r="I101" s="7">
-        <v>0.640467</v>
+        <v>0.6835469999999999</v>
       </c>
       <c r="J101" s="7">
-        <v>3.478593</v>
+        <v>3.6782549999999996</v>
       </c>
       <c r="K101" s="7">
-        <v>11.288764</v>
+        <v>11.360783</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,25 +5802,25 @@
         <v>2</v>
       </c>
       <c r="E102" s="7">
-        <v>0.042116</v>
+        <v>0.035977999999999996</v>
       </c>
       <c r="F102" s="7">
-        <v>0.092475</v>
+        <v>0.093125</v>
       </c>
       <c r="G102" s="7">
-        <v>0.26017399999999996</v>
+        <v>0.255722</v>
       </c>
       <c r="H102" s="7">
-        <v>0.155899</v>
+        <v>0.159378</v>
       </c>
       <c r="I102" s="7">
-        <v>0.574909</v>
+        <v>0.569662</v>
       </c>
       <c r="J102" s="7">
-        <v>3.113333</v>
+        <v>3.126903</v>
       </c>
       <c r="K102" s="7">
-        <v>5.713509</v>
+        <v>5.721083</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,25 +5837,25 @@
         <v>6</v>
       </c>
       <c r="E103" s="7">
-        <v>0.082494</v>
+        <v>0.078654</v>
       </c>
       <c r="F103" s="7">
-        <v>0.026568</v>
+        <v>0.046654</v>
       </c>
       <c r="G103" s="7">
-        <v>0.340424</v>
+        <v>0.34385599999999994</v>
       </c>
       <c r="H103" s="7">
-        <v>0.294984</v>
+        <v>0.319778</v>
       </c>
       <c r="I103" s="7">
-        <v>0.635716</v>
+        <v>0.683319</v>
       </c>
       <c r="J103" s="7">
-        <v>3.372274</v>
+        <v>3.5977499999999996</v>
       </c>
       <c r="K103" s="7">
-        <v>13.353161</v>
+        <v>13.403554</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,25 +5872,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.0412</v>
+        <v>0.027816999999999998</v>
       </c>
       <c r="F104" s="7">
-        <v>0.034079</v>
+        <v>0.030968</v>
       </c>
       <c r="G104" s="7">
-        <v>0.093661</v>
+        <v>0.09057399999999999</v>
       </c>
       <c r="H104" s="7">
-        <v>0.042588999999999995</v>
+        <v>0.043525</v>
       </c>
       <c r="I104" s="7">
-        <v>0.316244</v>
+        <v>0.313093</v>
       </c>
       <c r="J104" s="7">
-        <v>2.1414169999999997</v>
+        <v>2.140996</v>
       </c>
       <c r="K104" s="7">
-        <v>6.208518000000001</v>
+        <v>6.108465</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,16 +5907,16 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.099318</v>
+        <v>0.080526</v>
       </c>
       <c r="F105" s="7">
-        <v>0.030999</v>
+        <v>0.027751</v>
       </c>
       <c r="G105" s="7">
-        <v>0.184372</v>
+        <v>0.173171</v>
       </c>
       <c r="H105" s="7">
-        <v>0.142704</v>
+        <v>0.14427</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
@@ -5936,22 +5936,22 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.188053</v>
+        <v>0.162088</v>
       </c>
       <c r="F106" s="7">
-        <v>0.16736</v>
+        <v>0.18682500000000002</v>
       </c>
       <c r="G106" s="7">
-        <v>0.29162</v>
+        <v>0.28759599999999996</v>
       </c>
       <c r="H106" s="7">
-        <v>0.29267</v>
+        <v>0.300851</v>
       </c>
       <c r="I106" s="7">
-        <v>0.789743</v>
+        <v>0.789971</v>
       </c>
       <c r="J106" s="7">
-        <v>4.119368</v>
+        <v>4.308962</v>
       </c>
       <c r="K106" s="7"/>
     </row>
@@ -5969,25 +5969,25 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.0074399999999999996</v>
+        <v>-0.00819</v>
       </c>
       <c r="F107" s="7">
-        <v>-0.08737299999999999</v>
+        <v>-0.073533</v>
       </c>
       <c r="G107" s="7">
-        <v>0.212403</v>
+        <v>0.22143100000000002</v>
       </c>
       <c r="H107" s="7">
-        <v>0.096639</v>
+        <v>0.09935100000000001</v>
       </c>
       <c r="I107" s="7">
-        <v>0.648027</v>
+        <v>0.669567</v>
       </c>
       <c r="J107" s="7">
-        <v>4.812452</v>
+        <v>4.833027</v>
       </c>
       <c r="K107" s="7">
-        <v>16.158919</v>
+        <v>15.938519</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,25 +6004,25 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.048964999999999995</v>
+        <v>0.025695000000000003</v>
       </c>
       <c r="F108" s="7">
-        <v>0.027167</v>
+        <v>0.031326</v>
       </c>
       <c r="G108" s="7">
-        <v>0.181173</v>
+        <v>0.17506799999999997</v>
       </c>
       <c r="H108" s="7">
-        <v>0.06844800000000001</v>
+        <v>0.068488</v>
       </c>
       <c r="I108" s="7">
-        <v>0.47058999999999995</v>
+        <v>0.452476</v>
       </c>
       <c r="J108" s="7">
-        <v>2.045114</v>
+        <v>2.032338</v>
       </c>
       <c r="K108" s="7">
-        <v>3.8790410000000004</v>
+        <v>3.873027</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,25 +6039,25 @@
         <v>6</v>
       </c>
       <c r="E109" s="7">
-        <v>0.039580000000000004</v>
+        <v>0.027440000000000003</v>
       </c>
       <c r="F109" s="7">
-        <v>0.024974</v>
+        <v>0.02886</v>
       </c>
       <c r="G109" s="7">
-        <v>0.123252</v>
+        <v>0.123764</v>
       </c>
       <c r="H109" s="7">
-        <v>0.050054999999999995</v>
+        <v>0.050826</v>
       </c>
       <c r="I109" s="7">
-        <v>0.34049799999999997</v>
+        <v>0.339846</v>
       </c>
       <c r="J109" s="7">
-        <v>2.20124</v>
+        <v>2.205133</v>
       </c>
       <c r="K109" s="7">
-        <v>6.658561</v>
+        <v>6.548129</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,25 +6074,25 @@
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>0.052513</v>
+        <v>0.048079000000000004</v>
       </c>
       <c r="F110" s="7">
-        <v>0.071681</v>
+        <v>0.080166</v>
       </c>
       <c r="G110" s="7">
-        <v>0.20353100000000002</v>
+        <v>0.20149899999999998</v>
       </c>
       <c r="H110" s="7">
-        <v>0.15027</v>
+        <v>0.15710000000000002</v>
       </c>
       <c r="I110" s="7">
-        <v>0.473254</v>
+        <v>0.482176</v>
       </c>
       <c r="J110" s="7">
-        <v>1.963412</v>
+        <v>2.012877</v>
       </c>
       <c r="K110" s="7">
-        <v>5.512841</v>
+        <v>5.523147</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,25 +6109,25 @@
         <v>5</v>
       </c>
       <c r="E111" s="7">
-        <v>0.048885</v>
+        <v>0.046379000000000004</v>
       </c>
       <c r="F111" s="7">
-        <v>-0.0074670000000000005</v>
+        <v>0.0005920000000000001</v>
       </c>
       <c r="G111" s="7">
-        <v>0.224481</v>
+        <v>0.215111</v>
       </c>
       <c r="H111" s="7">
-        <v>0.137446</v>
+        <v>0.142467</v>
       </c>
       <c r="I111" s="7">
-        <v>0.541188</v>
+        <v>0.546237</v>
       </c>
       <c r="J111" s="7">
-        <v>3.4876389999999997</v>
+        <v>3.526855</v>
       </c>
       <c r="K111" s="7">
-        <v>14.527748999999998</v>
+        <v>14.390441000000001</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,25 +6144,25 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>0.039818</v>
+        <v>0.031289</v>
       </c>
       <c r="F112" s="7">
-        <v>0.076107</v>
+        <v>0.079188</v>
       </c>
       <c r="G112" s="7">
-        <v>0.235592</v>
+        <v>0.232128</v>
       </c>
       <c r="H112" s="7">
-        <v>0.137223</v>
+        <v>0.140333</v>
       </c>
       <c r="I112" s="7">
-        <v>0.530347</v>
+        <v>0.525277</v>
       </c>
       <c r="J112" s="7">
-        <v>3.27385</v>
+        <v>3.277101</v>
       </c>
       <c r="K112" s="7">
-        <v>6.260082</v>
+        <v>6.253832999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6179,25 +6179,25 @@
         <v>6</v>
       </c>
       <c r="E113" s="7">
-        <v>0.106643</v>
+        <v>0.096443</v>
       </c>
       <c r="F113" s="7">
-        <v>0.06430799999999999</v>
+        <v>0.077598</v>
       </c>
       <c r="G113" s="7">
-        <v>0.278119</v>
+        <v>0.264605</v>
       </c>
       <c r="H113" s="7">
-        <v>0.23116599999999998</v>
+        <v>0.24766200000000002</v>
       </c>
       <c r="I113" s="7">
-        <v>0.552341</v>
+        <v>0.5849989999999999</v>
       </c>
       <c r="J113" s="7">
-        <v>3.367793</v>
+        <v>3.6029050000000002</v>
       </c>
       <c r="K113" s="7">
-        <v>16.797027</v>
+        <v>16.765698999999998</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6214,25 +6214,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.090286</v>
+        <v>0.070133</v>
       </c>
       <c r="F114" s="7">
-        <v>-0.014576</v>
+        <v>-0.009201</v>
       </c>
       <c r="G114" s="7">
-        <v>0.24140999999999999</v>
+        <v>0.22591799999999998</v>
       </c>
       <c r="H114" s="7">
-        <v>0.16270099999999998</v>
+        <v>0.171187</v>
       </c>
       <c r="I114" s="7">
-        <v>0.518404</v>
+        <v>0.541315</v>
       </c>
       <c r="J114" s="7">
-        <v>3.315304</v>
+        <v>3.4136059999999997</v>
       </c>
       <c r="K114" s="7">
-        <v>22.560011</v>
+        <v>21.950469</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6249,25 +6249,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.10476</v>
+        <v>0.08602800000000001</v>
       </c>
       <c r="F115" s="7">
-        <v>0.017686</v>
+        <v>0.027090999999999997</v>
       </c>
       <c r="G115" s="7">
-        <v>0.275463</v>
+        <v>0.26802</v>
       </c>
       <c r="H115" s="7">
-        <v>0.204876</v>
+        <v>0.214271</v>
       </c>
       <c r="I115" s="7">
-        <v>0.547192</v>
+        <v>0.564639</v>
       </c>
       <c r="J115" s="7">
-        <v>2.83383</v>
+        <v>2.915849</v>
       </c>
       <c r="K115" s="7">
-        <v>16.08219</v>
+        <v>15.814993</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6284,25 +6284,25 @@
         <v>5</v>
       </c>
       <c r="E116" s="7">
-        <v>0.08515</v>
+        <v>0.075377</v>
       </c>
       <c r="F116" s="7">
-        <v>0.08110400000000001</v>
+        <v>0.095147</v>
       </c>
       <c r="G116" s="7">
-        <v>0.286208</v>
+        <v>0.282818</v>
       </c>
       <c r="H116" s="7">
-        <v>0.243586</v>
+        <v>0.255072</v>
       </c>
       <c r="I116" s="7">
-        <v>0.638746</v>
+        <v>0.664131</v>
       </c>
       <c r="J116" s="7">
-        <v>3.2345729999999997</v>
+        <v>3.3462</v>
       </c>
       <c r="K116" s="7">
-        <v>12.324745</v>
+        <v>12.281846</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6319,25 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>0.046525</v>
+        <v>0.024735</v>
       </c>
       <c r="F117" s="7">
-        <v>0.023756</v>
+        <v>0.026687</v>
       </c>
       <c r="G117" s="7">
-        <v>0.177474</v>
+        <v>0.17150300000000002</v>
       </c>
       <c r="H117" s="7">
-        <v>0.062363</v>
+        <v>0.061976</v>
       </c>
       <c r="I117" s="7">
-        <v>0.44109299999999996</v>
+        <v>0.422106</v>
       </c>
       <c r="J117" s="7">
-        <v>1.869767</v>
+        <v>1.840647</v>
       </c>
       <c r="K117" s="7">
-        <v>3.676783</v>
+        <v>3.665153</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6354,25 +6354,25 @@
         <v>6</v>
       </c>
       <c r="E118" s="7">
-        <v>0.08404099999999999</v>
+        <v>0.068454</v>
       </c>
       <c r="F118" s="7">
-        <v>0.017471</v>
+        <v>0.029044</v>
       </c>
       <c r="G118" s="7">
-        <v>0.260101</v>
+        <v>0.256629</v>
       </c>
       <c r="H118" s="7">
-        <v>0.17873899999999998</v>
+        <v>0.185601</v>
       </c>
       <c r="I118" s="7">
-        <v>0.6309239999999999</v>
+        <v>0.639918</v>
       </c>
       <c r="J118" s="7">
-        <v>3.564815</v>
+        <v>3.648063</v>
       </c>
       <c r="K118" s="7">
-        <v>16.288728000000003</v>
+        <v>16.092722000000002</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6389,25 +6389,25 @@
         <v>5</v>
       </c>
       <c r="E119" s="7">
-        <v>0.042603999999999996</v>
+        <v>0.032074</v>
       </c>
       <c r="F119" s="7">
-        <v>-0.020658</v>
+        <v>-0.00901</v>
       </c>
       <c r="G119" s="7">
-        <v>0.17400500000000002</v>
+        <v>0.16931100000000002</v>
       </c>
       <c r="H119" s="7">
-        <v>0.092337</v>
+        <v>0.098798</v>
       </c>
       <c r="I119" s="7">
-        <v>0.452273</v>
+        <v>0.46142099999999997</v>
       </c>
       <c r="J119" s="7">
-        <v>2.588759</v>
+        <v>2.6487130000000003</v>
       </c>
       <c r="K119" s="7">
-        <v>8.905737</v>
+        <v>8.866062</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,25 +6424,25 @@
         <v>6</v>
       </c>
       <c r="E120" s="7">
-        <v>0.052022000000000006</v>
+        <v>0.037566</v>
       </c>
       <c r="F120" s="7">
-        <v>-0.044154</v>
+        <v>-0.039608</v>
       </c>
       <c r="G120" s="7">
-        <v>0.16369399999999998</v>
+        <v>0.151314</v>
       </c>
       <c r="H120" s="7">
-        <v>0.113094</v>
+        <v>0.11857699999999999</v>
       </c>
       <c r="I120" s="7">
-        <v>0.41999699999999995</v>
+        <v>0.432149</v>
       </c>
       <c r="J120" s="7">
-        <v>3.368699</v>
+        <v>3.4257799999999996</v>
       </c>
       <c r="K120" s="7">
-        <v>17.899445</v>
+        <v>17.591244</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,25 +6459,25 @@
         <v>4</v>
       </c>
       <c r="E121" s="7">
-        <v>0.052752</v>
+        <v>0.03614</v>
       </c>
       <c r="F121" s="7">
-        <v>0.021488</v>
+        <v>0.021999</v>
       </c>
       <c r="G121" s="7">
-        <v>0.195772</v>
+        <v>0.189218</v>
       </c>
       <c r="H121" s="7">
-        <v>0.10757699999999999</v>
+        <v>0.110267</v>
       </c>
       <c r="I121" s="7">
-        <v>0.481122</v>
+        <v>0.470145</v>
       </c>
       <c r="J121" s="7">
-        <v>2.327011</v>
+        <v>2.359316</v>
       </c>
       <c r="K121" s="7">
-        <v>5.9905539999999995</v>
+        <v>5.957211999999999</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6494,25 +6494,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.045134</v>
+        <v>0.031986</v>
       </c>
       <c r="F122" s="7">
-        <v>0.022263</v>
+        <v>0.023081</v>
       </c>
       <c r="G122" s="7">
-        <v>0.17019700000000001</v>
+        <v>0.165498</v>
       </c>
       <c r="H122" s="7">
-        <v>0.09449</v>
+        <v>0.097124</v>
       </c>
       <c r="I122" s="7">
-        <v>0.43193600000000004</v>
+        <v>0.424823</v>
       </c>
       <c r="J122" s="7">
-        <v>1.9662389999999998</v>
+        <v>1.9737049999999998</v>
       </c>
       <c r="K122" s="7">
-        <v>6.01584</v>
+        <v>5.9966930000000005</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,16 +6529,16 @@
         <v>6</v>
       </c>
       <c r="E123" s="7">
-        <v>0.001941</v>
+        <v>-0.011007</v>
       </c>
       <c r="F123" s="7">
-        <v>-0.098078</v>
+        <v>-0.092358</v>
       </c>
       <c r="G123" s="7">
-        <v>0.191167</v>
+        <v>0.207109</v>
       </c>
       <c r="H123" s="7">
-        <v>0.09889799999999999</v>
+        <v>0.099658</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
@@ -6558,25 +6558,25 @@
         <v>4</v>
       </c>
       <c r="E124" s="7">
-        <v>0.066092</v>
+        <v>0.050217</v>
       </c>
       <c r="F124" s="7">
-        <v>0.011931</v>
+        <v>0.014584</v>
       </c>
       <c r="G124" s="7">
-        <v>0.23559999999999998</v>
+        <v>0.222893</v>
       </c>
       <c r="H124" s="7">
-        <v>0.141051</v>
+        <v>0.14469300000000002</v>
       </c>
       <c r="I124" s="7">
-        <v>0.529967</v>
+        <v>0.529807</v>
       </c>
       <c r="J124" s="7">
-        <v>1.9820160000000002</v>
+        <v>2.053705</v>
       </c>
       <c r="K124" s="7">
-        <v>6.512671</v>
+        <v>6.484788999999999</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6593,16 +6593,16 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.135751</v>
+        <v>0.12224299999999999</v>
       </c>
       <c r="F125" s="7">
-        <v>0.115432</v>
+        <v>0.12895</v>
       </c>
       <c r="G125" s="7">
-        <v>0.347213</v>
+        <v>0.34291</v>
       </c>
       <c r="H125" s="7">
-        <v>0.335355</v>
+        <v>0.348557</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
@@ -6622,25 +6622,25 @@
         <v>7</v>
       </c>
       <c r="E126" s="7">
-        <v>0.100529</v>
+        <v>0.078133</v>
       </c>
       <c r="F126" s="7">
-        <v>0.019216999999999998</v>
+        <v>0.019013</v>
       </c>
       <c r="G126" s="7">
-        <v>0.203885</v>
+        <v>0.187591</v>
       </c>
       <c r="H126" s="7">
-        <v>0.114757</v>
+        <v>0.119038</v>
       </c>
       <c r="I126" s="7">
-        <v>0.434614</v>
+        <v>0.439837</v>
       </c>
       <c r="J126" s="7">
-        <v>2.4449870000000002</v>
+        <v>2.5525040000000003</v>
       </c>
       <c r="K126" s="7">
-        <v>9.283529999999999</v>
+        <v>9.176501</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,25 +6657,25 @@
         <v>5</v>
       </c>
       <c r="E127" s="7">
-        <v>0.04249</v>
+        <v>0.026742</v>
       </c>
       <c r="F127" s="7">
-        <v>0.020973000000000002</v>
+        <v>0.023769</v>
       </c>
       <c r="G127" s="7">
-        <v>0.08652599999999999</v>
+        <v>0.08683</v>
       </c>
       <c r="H127" s="7">
-        <v>0.041401</v>
+        <v>0.041461</v>
       </c>
       <c r="I127" s="7">
-        <v>0.274604</v>
+        <v>0.27498100000000003</v>
       </c>
       <c r="J127" s="7">
-        <v>1.960274</v>
+        <v>1.956712</v>
       </c>
       <c r="K127" s="7">
-        <v>5.599804000000001</v>
+        <v>5.527842000000001</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6692,25 +6692,25 @@
         <v>4</v>
       </c>
       <c r="E128" s="7">
-        <v>0.048897</v>
+        <v>0.018226</v>
       </c>
       <c r="F128" s="7">
-        <v>-0.011566</v>
+        <v>-0.013986</v>
       </c>
       <c r="G128" s="7">
-        <v>0.13151300000000002</v>
+        <v>0.12194</v>
       </c>
       <c r="H128" s="7">
-        <v>0.032837</v>
+        <v>0.03228</v>
       </c>
       <c r="I128" s="7">
-        <v>0.39198</v>
+        <v>0.369215</v>
       </c>
       <c r="J128" s="7">
-        <v>1.5282</v>
+        <v>1.5233009999999998</v>
       </c>
       <c r="K128" s="7">
-        <v>3.319687</v>
+        <v>3.3071789999999996</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6727,25 +6727,25 @@
         <v>6</v>
       </c>
       <c r="E129" s="7">
-        <v>0.10251400000000001</v>
+        <v>0.080842</v>
       </c>
       <c r="F129" s="7">
-        <v>-0.0031290000000000003</v>
+        <v>-0.001348</v>
       </c>
       <c r="G129" s="7">
-        <v>0.289028</v>
+        <v>0.264262</v>
       </c>
       <c r="H129" s="7">
-        <v>0.211361</v>
+        <v>0.216537</v>
       </c>
       <c r="I129" s="7">
-        <v>0.521014</v>
+        <v>0.530377</v>
       </c>
       <c r="J129" s="7">
-        <v>2.800863</v>
+        <v>2.933602</v>
       </c>
       <c r="K129" s="7">
-        <v>14.389733000000001</v>
+        <v>14.192372</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6762,25 +6762,25 @@
         <v>4</v>
       </c>
       <c r="E130" s="7">
-        <v>0.046735</v>
+        <v>0.031076000000000003</v>
       </c>
       <c r="F130" s="7">
-        <v>0.028652999999999998</v>
+        <v>0.025611000000000002</v>
       </c>
       <c r="G130" s="7">
-        <v>0.078549</v>
+        <v>0.074253</v>
       </c>
       <c r="H130" s="7">
-        <v>0.034647000000000004</v>
+        <v>0.035297999999999996</v>
       </c>
       <c r="I130" s="7">
-        <v>0.278779</v>
+        <v>0.276716</v>
       </c>
       <c r="J130" s="7">
-        <v>2.028582</v>
+        <v>2.027166</v>
       </c>
       <c r="K130" s="7">
-        <v>6.329340999999999</v>
+        <v>6.2263459999999995</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6797,19 +6797,19 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.128887</v>
+        <v>0.109242</v>
       </c>
       <c r="F131" s="7">
-        <v>0.131663</v>
+        <v>0.127029</v>
       </c>
       <c r="G131" s="7">
-        <v>0.22531700000000002</v>
+        <v>0.198947</v>
       </c>
       <c r="H131" s="7">
-        <v>0.249505</v>
+        <v>0.253321</v>
       </c>
       <c r="I131" s="7">
-        <v>0.7003199999999999</v>
+        <v>0.7330289999999999</v>
       </c>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
@@ -6828,25 +6828,25 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.057078</v>
+        <v>0.033902</v>
       </c>
       <c r="F132" s="7">
-        <v>-0.009392000000000001</v>
+        <v>-0.0084</v>
       </c>
       <c r="G132" s="7">
-        <v>0.16683599999999998</v>
+        <v>0.157111</v>
       </c>
       <c r="H132" s="7">
-        <v>0.06643</v>
+        <v>0.068572</v>
       </c>
       <c r="I132" s="7">
-        <v>0.41974200000000006</v>
+        <v>0.40301200000000004</v>
       </c>
       <c r="J132" s="7">
-        <v>1.4500579999999998</v>
+        <v>1.4785579999999998</v>
       </c>
       <c r="K132" s="7">
-        <v>3.758526</v>
+        <v>3.7400819999999997</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6863,25 +6863,25 @@
         <v>3</v>
       </c>
       <c r="E133" s="7">
-        <v>0.030939</v>
+        <v>0.027738</v>
       </c>
       <c r="F133" s="7">
-        <v>0.082828</v>
+        <v>0.085854</v>
       </c>
       <c r="G133" s="7">
-        <v>0.181731</v>
+        <v>0.1867</v>
       </c>
       <c r="H133" s="7">
-        <v>0.119342</v>
+        <v>0.123371</v>
       </c>
       <c r="I133" s="7">
-        <v>0.460388</v>
+        <v>0.457598</v>
       </c>
       <c r="J133" s="7">
-        <v>2.295893</v>
+        <v>2.3028239999999998</v>
       </c>
       <c r="K133" s="7">
-        <v>3.85832</v>
+        <v>3.864905</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6898,25 +6898,25 @@
         <v>6</v>
       </c>
       <c r="E134" s="7">
-        <v>0.060503999999999995</v>
+        <v>0.050092</v>
       </c>
       <c r="F134" s="7">
-        <v>0.047164000000000005</v>
+        <v>0.047442000000000005</v>
       </c>
       <c r="G134" s="7">
-        <v>0.232682</v>
+        <v>0.22698000000000002</v>
       </c>
       <c r="H134" s="7">
-        <v>0.161937</v>
+        <v>0.166513</v>
       </c>
       <c r="I134" s="7">
-        <v>0.45427100000000004</v>
+        <v>0.47138399999999997</v>
       </c>
       <c r="J134" s="7">
-        <v>2.725571</v>
+        <v>2.93906</v>
       </c>
       <c r="K134" s="7">
-        <v>7.851375000000001</v>
+        <v>7.776771999999999</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6933,25 +6933,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.058798</v>
+        <v>0.031492</v>
       </c>
       <c r="F135" s="7">
-        <v>-0.0029170000000000003</v>
+        <v>-0.007769000000000001</v>
       </c>
       <c r="G135" s="7">
-        <v>0.142668</v>
+        <v>0.135408</v>
       </c>
       <c r="H135" s="7">
-        <v>0.061598</v>
+        <v>0.061812</v>
       </c>
       <c r="I135" s="7">
-        <v>0.349436</v>
+        <v>0.33578600000000003</v>
       </c>
       <c r="J135" s="7">
-        <v>1.038974</v>
+        <v>1.018743</v>
       </c>
       <c r="K135" s="7">
-        <v>2.416944</v>
+        <v>2.406103</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6968,25 +6968,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.081599</v>
+        <v>0.069189</v>
       </c>
       <c r="F136" s="7">
-        <v>0.08013999999999999</v>
+        <v>0.072489</v>
       </c>
       <c r="G136" s="7">
-        <v>0.18545999999999999</v>
+        <v>0.16704799999999997</v>
       </c>
       <c r="H136" s="7">
-        <v>0.156252</v>
+        <v>0.154892</v>
       </c>
       <c r="I136" s="7">
-        <v>0.436646</v>
+        <v>0.435321</v>
       </c>
       <c r="J136" s="7">
-        <v>3.097021</v>
+        <v>3.106724</v>
       </c>
       <c r="K136" s="7">
-        <v>9.42621</v>
+        <v>9.292463</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7003,25 +7003,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.050393</v>
+        <v>0.038267999999999996</v>
       </c>
       <c r="F137" s="7">
-        <v>0.038879000000000004</v>
+        <v>0.040227000000000006</v>
       </c>
       <c r="G137" s="7">
-        <v>0.169197</v>
+        <v>0.162155</v>
       </c>
       <c r="H137" s="7">
-        <v>0.097064</v>
+        <v>0.10045899999999999</v>
       </c>
       <c r="I137" s="7">
-        <v>0.429628</v>
+        <v>0.426946</v>
       </c>
       <c r="J137" s="7">
-        <v>2.154716</v>
+        <v>2.171993</v>
       </c>
       <c r="K137" s="7">
-        <v>4.134547</v>
+        <v>4.137786</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7038,22 +7038,22 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.23629999999999998</v>
+        <v>0.16935099999999997</v>
       </c>
       <c r="F138" s="7">
-        <v>0.116548</v>
+        <v>0.12584</v>
       </c>
       <c r="G138" s="7">
-        <v>0.260782</v>
+        <v>0.241608</v>
       </c>
       <c r="H138" s="7">
-        <v>0.232854</v>
+        <v>0.22085999999999997</v>
       </c>
       <c r="I138" s="7">
-        <v>0.8340179999999999</v>
+        <v>0.785528</v>
       </c>
       <c r="J138" s="7">
-        <v>5.168565999999999</v>
+        <v>5.285132999999999</v>
       </c>
       <c r="K138" s="7"/>
     </row>
@@ -7071,22 +7071,22 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.074069</v>
+        <v>0.060378</v>
       </c>
       <c r="F139" s="7">
-        <v>-0.009254</v>
+        <v>-0.000619</v>
       </c>
       <c r="G139" s="7">
-        <v>0.180594</v>
+        <v>0.178947</v>
       </c>
       <c r="H139" s="7">
-        <v>0.099088</v>
+        <v>0.10418799999999999</v>
       </c>
       <c r="I139" s="7">
-        <v>0.51137</v>
+        <v>0.513268</v>
       </c>
       <c r="J139" s="7">
-        <v>4.687117</v>
+        <v>4.877003</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,25 +7104,25 @@
         <v>3</v>
       </c>
       <c r="E140" s="7">
-        <v>0.045891</v>
+        <v>0.028277</v>
       </c>
       <c r="F140" s="7">
-        <v>0.0059299999999999995</v>
+        <v>0.004917</v>
       </c>
       <c r="G140" s="7">
-        <v>0.153137</v>
+        <v>0.144824</v>
       </c>
       <c r="H140" s="7">
-        <v>0.080442</v>
+        <v>0.080353</v>
       </c>
       <c r="I140" s="7">
-        <v>0.370865</v>
+        <v>0.360399</v>
       </c>
       <c r="J140" s="7">
-        <v>1.617662</v>
+        <v>1.601072</v>
       </c>
       <c r="K140" s="7">
-        <v>3.5941289999999997</v>
+        <v>3.578431</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7139,25 +7139,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.037875</v>
+        <v>0.035441</v>
       </c>
       <c r="F141" s="7">
-        <v>0.051040999999999996</v>
+        <v>0.059345999999999996</v>
       </c>
       <c r="G141" s="7">
-        <v>0.175921</v>
+        <v>0.177332</v>
       </c>
       <c r="H141" s="7">
-        <v>0.11584199999999999</v>
+        <v>0.121402</v>
       </c>
       <c r="I141" s="7">
-        <v>0.35356099999999996</v>
+        <v>0.35690600000000006</v>
       </c>
       <c r="J141" s="7">
-        <v>1.3763919999999998</v>
+        <v>1.4370500000000002</v>
       </c>
       <c r="K141" s="7">
-        <v>4.461295</v>
+        <v>4.462117</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,25 +7174,25 @@
         <v>5</v>
       </c>
       <c r="E142" s="7">
-        <v>0.085664</v>
+        <v>0.11337799999999999</v>
       </c>
       <c r="F142" s="7">
-        <v>-0.010546999999999999</v>
+        <v>0.005078</v>
       </c>
       <c r="G142" s="7">
-        <v>0.20908000000000002</v>
+        <v>0.212593</v>
       </c>
       <c r="H142" s="7">
-        <v>0.149144</v>
+        <v>0.165245</v>
       </c>
       <c r="I142" s="7">
-        <v>0.371548</v>
+        <v>0.374251</v>
       </c>
       <c r="J142" s="7">
-        <v>3.204365</v>
+        <v>3.4012439999999997</v>
       </c>
       <c r="K142" s="7">
-        <v>13.526187</v>
+        <v>13.360289999999999</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7209,25 +7209,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.071892</v>
+        <v>0.063275</v>
       </c>
       <c r="F143" s="7">
-        <v>0.151829</v>
+        <v>0.142564</v>
       </c>
       <c r="G143" s="7">
-        <v>0.182738</v>
+        <v>0.17516500000000002</v>
       </c>
       <c r="H143" s="7">
-        <v>0.27732500000000004</v>
+        <v>0.283222</v>
       </c>
       <c r="I143" s="7">
-        <v>0.27825700000000003</v>
+        <v>0.274709</v>
       </c>
       <c r="J143" s="7">
-        <v>3.5525700000000002</v>
+        <v>3.629595</v>
       </c>
       <c r="K143" s="7">
-        <v>10.928666</v>
+        <v>10.884748</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7244,25 +7244,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.089383</v>
+        <v>0.070012</v>
       </c>
       <c r="F144" s="7">
-        <v>0.065885</v>
+        <v>0.062805</v>
       </c>
       <c r="G144" s="7">
-        <v>0.30471</v>
+        <v>0.29408</v>
       </c>
       <c r="H144" s="7">
-        <v>0.19307300000000002</v>
+        <v>0.197333</v>
       </c>
       <c r="I144" s="7">
-        <v>0.558321</v>
+        <v>0.570605</v>
       </c>
       <c r="J144" s="7">
-        <v>2.927591</v>
+        <v>2.9778640000000003</v>
       </c>
       <c r="K144" s="7">
-        <v>8.147826</v>
+        <v>8.111685</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7279,25 +7279,25 @@
         <v>4</v>
       </c>
       <c r="E145" s="7">
-        <v>0.07819899999999999</v>
+        <v>0.058346</v>
       </c>
       <c r="F145" s="7">
-        <v>0.0017410000000000001</v>
+        <v>0.006443</v>
       </c>
       <c r="G145" s="7">
-        <v>0.249712</v>
+        <v>0.235688</v>
       </c>
       <c r="H145" s="7">
-        <v>0.16023900000000002</v>
+        <v>0.163796</v>
       </c>
       <c r="I145" s="7">
-        <v>0.53806</v>
+        <v>0.539823</v>
       </c>
       <c r="J145" s="7">
-        <v>3.4117720000000005</v>
+        <v>3.5019810000000002</v>
       </c>
       <c r="K145" s="7">
-        <v>9.432448</v>
+        <v>9.355245</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7314,25 +7314,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.02642</v>
+        <v>0.02306</v>
       </c>
       <c r="F146" s="7">
-        <v>0.130256</v>
+        <v>0.139182</v>
       </c>
       <c r="G146" s="7">
-        <v>0.33321</v>
+        <v>0.32036200000000004</v>
       </c>
       <c r="H146" s="7">
-        <v>0.25461500000000004</v>
+        <v>0.261191</v>
       </c>
       <c r="I146" s="7">
-        <v>0.612744</v>
+        <v>0.6146159999999999</v>
       </c>
       <c r="J146" s="7">
-        <v>3.1411860000000003</v>
+        <v>3.1822519999999996</v>
       </c>
       <c r="K146" s="7">
-        <v>9.341752</v>
+        <v>9.279271</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7349,25 +7349,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.033498</v>
+        <v>0.028637000000000003</v>
       </c>
       <c r="F147" s="7">
-        <v>0.064451</v>
+        <v>0.071454</v>
       </c>
       <c r="G147" s="7">
-        <v>0.189181</v>
+        <v>0.187618</v>
       </c>
       <c r="H147" s="7">
-        <v>0.127052</v>
+        <v>0.133128</v>
       </c>
       <c r="I147" s="7">
-        <v>0.457108</v>
+        <v>0.461409</v>
       </c>
       <c r="J147" s="7">
-        <v>2.202563</v>
+        <v>2.2721199999999997</v>
       </c>
       <c r="K147" s="7">
-        <v>6.502199000000001</v>
+        <v>6.483256</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7384,25 +7384,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.039493</v>
+        <v>0.025456</v>
       </c>
       <c r="F148" s="7">
-        <v>-0.02205</v>
+        <v>0.01214</v>
       </c>
       <c r="G148" s="7">
-        <v>0.213281</v>
+        <v>0.214969</v>
       </c>
       <c r="H148" s="7">
-        <v>0.116104</v>
+        <v>0.122948</v>
       </c>
       <c r="I148" s="7">
-        <v>0.542205</v>
+        <v>0.554724</v>
       </c>
       <c r="J148" s="7">
-        <v>3.2483690000000003</v>
+        <v>3.313724</v>
       </c>
       <c r="K148" s="7">
-        <v>9.523795</v>
+        <v>9.462726</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7419,25 +7419,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.050026</v>
+        <v>0.048288000000000005</v>
       </c>
       <c r="F149" s="7">
-        <v>0.061172000000000004</v>
+        <v>0.07013899999999999</v>
       </c>
       <c r="G149" s="7">
-        <v>0.17731000000000002</v>
+        <v>0.177669</v>
       </c>
       <c r="H149" s="7">
-        <v>0.133635</v>
+        <v>0.141878</v>
       </c>
       <c r="I149" s="7">
-        <v>0.394658</v>
+        <v>0.403361</v>
       </c>
       <c r="J149" s="7">
-        <v>1.453993</v>
+        <v>1.526266</v>
       </c>
       <c r="K149" s="7">
-        <v>4.222281</v>
+        <v>4.224914</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7454,25 +7454,25 @@
         <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>0.11043599999999999</v>
+        <v>0.105877</v>
       </c>
       <c r="F150" s="7">
-        <v>0.069734</v>
+        <v>0.09711399999999999</v>
       </c>
       <c r="G150" s="7">
-        <v>0.252672</v>
+        <v>0.255175</v>
       </c>
       <c r="H150" s="7">
-        <v>0.233797</v>
+        <v>0.256004</v>
       </c>
       <c r="I150" s="7">
-        <v>0.556058</v>
+        <v>0.59254</v>
       </c>
       <c r="J150" s="7">
-        <v>2.6956990000000003</v>
+        <v>2.9460879999999996</v>
       </c>
       <c r="K150" s="7">
-        <v>8.422424999999999</v>
+        <v>8.45995</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7489,25 +7489,25 @@
         <v>7</v>
       </c>
       <c r="E151" s="7">
-        <v>0.093558</v>
+        <v>0.08998900000000001</v>
       </c>
       <c r="F151" s="7">
-        <v>0.074062</v>
+        <v>0.09686199999999999</v>
       </c>
       <c r="G151" s="7">
-        <v>0.244094</v>
+        <v>0.24600999999999998</v>
       </c>
       <c r="H151" s="7">
-        <v>0.21235199999999999</v>
+        <v>0.231095</v>
       </c>
       <c r="I151" s="7">
-        <v>0.546982</v>
+        <v>0.576712</v>
       </c>
       <c r="J151" s="7">
-        <v>2.583197</v>
+        <v>2.803002</v>
       </c>
       <c r="K151" s="7">
-        <v>7.392419</v>
+        <v>7.407556</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7524,25 +7524,25 @@
         <v>3</v>
       </c>
       <c r="E152" s="7">
-        <v>0.043796999999999996</v>
+        <v>0.032383999999999996</v>
       </c>
       <c r="F152" s="7">
-        <v>0.06229</v>
+        <v>0.063106</v>
       </c>
       <c r="G152" s="7">
-        <v>0.20187999999999998</v>
+        <v>0.19656500000000002</v>
       </c>
       <c r="H152" s="7">
-        <v>0.121713</v>
+        <v>0.123027</v>
       </c>
       <c r="I152" s="7">
-        <v>0.481717</v>
+        <v>0.475696</v>
       </c>
       <c r="J152" s="7">
-        <v>2.939134</v>
+        <v>2.947392</v>
       </c>
       <c r="K152" s="7">
-        <v>5.064614000000001</v>
+        <v>5.066383</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7559,22 +7559,22 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.062723</v>
+        <v>0.072736</v>
       </c>
       <c r="F153" s="7">
-        <v>0.009485</v>
+        <v>0.027548</v>
       </c>
       <c r="G153" s="7">
-        <v>0.189614</v>
+        <v>0.17887699999999998</v>
       </c>
       <c r="H153" s="7">
-        <v>0.12659</v>
+        <v>0.13631500000000002</v>
       </c>
       <c r="I153" s="7">
-        <v>0.48774700000000004</v>
+        <v>0.48808100000000004</v>
       </c>
       <c r="J153" s="7">
-        <v>3.412514</v>
+        <v>3.45838</v>
       </c>
       <c r="K153" s="7"/>
     </row>
@@ -7592,16 +7592,16 @@
         <v>4</v>
       </c>
       <c r="E154" s="7">
-        <v>0.050321</v>
+        <v>0.042286000000000004</v>
       </c>
       <c r="F154" s="7">
-        <v>0.059295999999999995</v>
+        <v>0.063466</v>
       </c>
       <c r="G154" s="7">
-        <v>0.256531</v>
+        <v>0.24904900000000002</v>
       </c>
       <c r="H154" s="7">
-        <v>0.1809</v>
+        <v>0.186073</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
@@ -7621,22 +7621,22 @@
         <v>6</v>
       </c>
       <c r="E155" s="7">
-        <v>0.10479</v>
+        <v>0.07887</v>
       </c>
       <c r="F155" s="7">
-        <v>0.047637</v>
+        <v>0.043818</v>
       </c>
       <c r="G155" s="7">
-        <v>0.227377</v>
+        <v>0.20997699999999997</v>
       </c>
       <c r="H155" s="7">
-        <v>0.179012</v>
+        <v>0.180408</v>
       </c>
       <c r="I155" s="7">
-        <v>0.452774</v>
+        <v>0.442768</v>
       </c>
       <c r="J155" s="7">
-        <v>1.765371</v>
+        <v>1.8028309999999999</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7654,25 +7654,25 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.061951</v>
+        <v>0.054688999999999995</v>
       </c>
       <c r="F156" s="7">
-        <v>0.08114800000000001</v>
+        <v>0.084276</v>
       </c>
       <c r="G156" s="7">
-        <v>0.24387699999999998</v>
+        <v>0.24052800000000002</v>
       </c>
       <c r="H156" s="7">
-        <v>0.170198</v>
+        <v>0.173885</v>
       </c>
       <c r="I156" s="7">
-        <v>0.5474289999999999</v>
+        <v>0.547235</v>
       </c>
       <c r="J156" s="7">
-        <v>2.394329</v>
+        <v>2.463788</v>
       </c>
       <c r="K156" s="7">
-        <v>6.453563</v>
+        <v>6.441102</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7689,25 +7689,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.063802</v>
+        <v>0.057674</v>
       </c>
       <c r="F157" s="7">
-        <v>0.084638</v>
+        <v>0.087606</v>
       </c>
       <c r="G157" s="7">
-        <v>0.23512899999999998</v>
+        <v>0.232395</v>
       </c>
       <c r="H157" s="7">
-        <v>0.169917</v>
+        <v>0.174181</v>
       </c>
       <c r="I157" s="7">
-        <v>0.50465</v>
+        <v>0.504925</v>
       </c>
       <c r="J157" s="7">
-        <v>2.176319</v>
+        <v>2.247586</v>
       </c>
       <c r="K157" s="7">
-        <v>5.964987</v>
+        <v>5.956523999999999</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7724,25 +7724,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.043191</v>
+        <v>0.043494000000000005</v>
       </c>
       <c r="F158" s="7">
-        <v>0.055744999999999996</v>
+        <v>0.071447</v>
       </c>
       <c r="G158" s="7">
-        <v>0.202955</v>
+        <v>0.205825</v>
       </c>
       <c r="H158" s="7">
-        <v>0.133604</v>
+        <v>0.14177</v>
       </c>
       <c r="I158" s="7">
-        <v>0.431954</v>
+        <v>0.440469</v>
       </c>
       <c r="J158" s="7">
-        <v>1.825315</v>
+        <v>1.868206</v>
       </c>
       <c r="K158" s="7">
-        <v>5.045561</v>
+        <v>5.056101</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,22 +7759,22 @@
         <v>5</v>
       </c>
       <c r="E159" s="7">
-        <v>0.173019</v>
+        <v>0.141008</v>
       </c>
       <c r="F159" s="7">
-        <v>0.16808199999999998</v>
+        <v>0.177102</v>
       </c>
       <c r="G159" s="7">
-        <v>0.267076</v>
+        <v>0.261898</v>
       </c>
       <c r="H159" s="7">
-        <v>0.267486</v>
+        <v>0.271588</v>
       </c>
       <c r="I159" s="7">
-        <v>0.720261</v>
+        <v>0.705018</v>
       </c>
       <c r="J159" s="7">
-        <v>3.956848</v>
+        <v>4.138168</v>
       </c>
       <c r="K159" s="7"/>
     </row>
@@ -7792,25 +7792,25 @@
         <v>4</v>
       </c>
       <c r="E160" s="7">
-        <v>0.054838</v>
+        <v>0.036969</v>
       </c>
       <c r="F160" s="7">
-        <v>0.01154</v>
+        <v>0.01222</v>
       </c>
       <c r="G160" s="7">
-        <v>0.194753</v>
+        <v>0.187284</v>
       </c>
       <c r="H160" s="7">
-        <v>0.08921200000000001</v>
+        <v>0.090621</v>
       </c>
       <c r="I160" s="7">
-        <v>0.429684</v>
+        <v>0.421134</v>
       </c>
       <c r="J160" s="7">
-        <v>2.038043</v>
+        <v>2.0542420000000003</v>
       </c>
       <c r="K160" s="7">
-        <v>5.628545</v>
+        <v>5.611461</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,22 +7827,22 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.032813</v>
+        <v>0.029022000000000003</v>
       </c>
       <c r="F161" s="7">
-        <v>0.079139</v>
+        <v>0.07708</v>
       </c>
       <c r="G161" s="7">
-        <v>0.22328</v>
+        <v>0.219782</v>
       </c>
       <c r="H161" s="7">
-        <v>0.151597</v>
+        <v>0.15279</v>
       </c>
       <c r="I161" s="7">
-        <v>0.536541</v>
+        <v>0.536705</v>
       </c>
       <c r="J161" s="7">
-        <v>3.355152</v>
+        <v>3.425075</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7860,22 +7860,22 @@
         <v>6</v>
       </c>
       <c r="E162" s="7">
-        <v>0.060269</v>
+        <v>0.032458999999999995</v>
       </c>
       <c r="F162" s="7">
-        <v>-0.014127</v>
+        <v>-0.014649</v>
       </c>
       <c r="G162" s="7">
-        <v>0.121905</v>
+        <v>0.128013</v>
       </c>
       <c r="H162" s="7">
-        <v>0.06038</v>
+        <v>0.058743</v>
       </c>
       <c r="I162" s="7">
-        <v>0.391413</v>
+        <v>0.384765</v>
       </c>
       <c r="J162" s="7">
-        <v>2.569915</v>
+        <v>2.5681849999999997</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,25 +7893,25 @@
         <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>0.10185000000000001</v>
+        <v>0.08964</v>
       </c>
       <c r="F163" s="7">
-        <v>0.083509</v>
+        <v>0.10830000000000001</v>
       </c>
       <c r="G163" s="7">
-        <v>0.306023</v>
+        <v>0.304636</v>
       </c>
       <c r="H163" s="7">
-        <v>0.252867</v>
+        <v>0.26351199999999997</v>
       </c>
       <c r="I163" s="7">
-        <v>0.634308</v>
+        <v>0.65641</v>
       </c>
       <c r="J163" s="7">
-        <v>2.51082</v>
+        <v>2.6024380000000003</v>
       </c>
       <c r="K163" s="7">
-        <v>8.701333</v>
+        <v>8.676375</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7928,25 +7928,25 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.122421</v>
+        <v>0.104129</v>
       </c>
       <c r="F164" s="7">
-        <v>0.04149</v>
+        <v>0.050187</v>
       </c>
       <c r="G164" s="7">
-        <v>0.34726300000000004</v>
+        <v>0.337909</v>
       </c>
       <c r="H164" s="7">
-        <v>0.275197</v>
+        <v>0.284184</v>
       </c>
       <c r="I164" s="7">
-        <v>0.6343610000000001</v>
+        <v>0.658482</v>
       </c>
       <c r="J164" s="7">
-        <v>1.955728</v>
+        <v>1.973502</v>
       </c>
       <c r="K164" s="7">
-        <v>3.600295</v>
+        <v>3.6251209999999996</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7963,25 +7963,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.104964</v>
+        <v>0.08147700000000001</v>
       </c>
       <c r="F165" s="7">
-        <v>0.004562</v>
+        <v>0.001983</v>
       </c>
       <c r="G165" s="7">
-        <v>0.296246</v>
+        <v>0.27728400000000003</v>
       </c>
       <c r="H165" s="7">
-        <v>0.21685500000000002</v>
+        <v>0.21991499999999997</v>
       </c>
       <c r="I165" s="7">
-        <v>0.470912</v>
+        <v>0.483748</v>
       </c>
       <c r="J165" s="7">
-        <v>2.901887</v>
+        <v>2.987584</v>
       </c>
       <c r="K165" s="7">
-        <v>15.773193000000001</v>
+        <v>15.569567</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7998,25 +7998,25 @@
         <v>3</v>
       </c>
       <c r="E166" s="7">
-        <v>0.045351999999999996</v>
+        <v>0.022215</v>
       </c>
       <c r="F166" s="7">
-        <v>-0.00042</v>
+        <v>-0.003675</v>
       </c>
       <c r="G166" s="7">
-        <v>0.137222</v>
+        <v>0.129434</v>
       </c>
       <c r="H166" s="7">
-        <v>0.039534</v>
+        <v>0.03858</v>
       </c>
       <c r="I166" s="7">
-        <v>0.394716</v>
+        <v>0.375966</v>
       </c>
       <c r="J166" s="7">
-        <v>1.857634</v>
+        <v>1.863999</v>
       </c>
       <c r="K166" s="7">
-        <v>3.9494819999999997</v>
+        <v>3.929673</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8033,25 +8033,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.051126</v>
+        <v>0.047118</v>
       </c>
       <c r="F167" s="7">
-        <v>0.077335</v>
+        <v>0.08372199999999999</v>
       </c>
       <c r="G167" s="7">
-        <v>0.23561800000000002</v>
+        <v>0.23465499999999997</v>
       </c>
       <c r="H167" s="7">
-        <v>0.160529</v>
+        <v>0.167663</v>
       </c>
       <c r="I167" s="7">
-        <v>0.465951</v>
+        <v>0.471602</v>
       </c>
       <c r="J167" s="7">
-        <v>1.895963</v>
+        <v>1.952733</v>
       </c>
       <c r="K167" s="7">
-        <v>5.430177</v>
+        <v>5.424809</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8068,25 +8068,25 @@
         <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>0.026034</v>
+        <v>0.023096000000000002</v>
       </c>
       <c r="F168" s="7">
-        <v>0.061073</v>
+        <v>0.060079</v>
       </c>
       <c r="G168" s="7">
-        <v>0.125092</v>
+        <v>0.123367</v>
       </c>
       <c r="H168" s="7">
-        <v>0.081855</v>
+        <v>0.083018</v>
       </c>
       <c r="I168" s="7">
-        <v>0.30185300000000004</v>
+        <v>0.30009</v>
       </c>
       <c r="J168" s="7">
-        <v>1.9599469999999999</v>
+        <v>1.9633150000000001</v>
       </c>
       <c r="K168" s="7">
-        <v>5.544842</v>
+        <v>5.477304</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8103,22 +8103,22 @@
         <v>6</v>
       </c>
       <c r="E169" s="7">
-        <v>0.0015</v>
+        <v>-0.012008000000000001</v>
       </c>
       <c r="F169" s="7">
-        <v>-0.10777900000000001</v>
+        <v>-0.08907899999999999</v>
       </c>
       <c r="G169" s="7">
-        <v>0.168331</v>
+        <v>0.194972</v>
       </c>
       <c r="H169" s="7">
-        <v>0.07466</v>
+        <v>0.078552</v>
       </c>
       <c r="I169" s="7">
-        <v>0.563063</v>
+        <v>0.581206</v>
       </c>
       <c r="J169" s="7">
-        <v>4.554101999999999</v>
+        <v>4.605155</v>
       </c>
       <c r="K169" s="7"/>
     </row>
@@ -8136,22 +8136,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>0.12282</v>
+        <v>0.096432</v>
       </c>
       <c r="F170" s="7">
-        <v>0.034203000000000004</v>
+        <v>0.032367</v>
       </c>
       <c r="G170" s="7">
-        <v>0.23637699999999998</v>
+        <v>0.21945900000000002</v>
       </c>
       <c r="H170" s="7">
-        <v>0.198123</v>
+        <v>0.19967600000000002</v>
       </c>
       <c r="I170" s="7">
-        <v>0.486779</v>
+        <v>0.48916</v>
       </c>
       <c r="J170" s="7">
-        <v>2.498424</v>
+        <v>2.561635</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,16 +8169,16 @@
         <v>7</v>
       </c>
       <c r="E171" s="7">
-        <v>0.036680000000000004</v>
+        <v>0.019592000000000002</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.268936</v>
+        <v>-0.108354</v>
       </c>
       <c r="G171" s="7">
-        <v>0.547402</v>
+        <v>0.533428</v>
       </c>
       <c r="H171" s="7">
-        <v>0.02313</v>
+        <v>0.032778999999999996</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7"/>
@@ -8198,25 +8198,25 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>-0.007268</v>
+        <v>-0.018373999999999998</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.107289</v>
+        <v>-0.091246</v>
       </c>
       <c r="G172" s="7">
-        <v>0.140154</v>
+        <v>0.17721900000000002</v>
       </c>
       <c r="H172" s="7">
-        <v>0.043169000000000006</v>
+        <v>0.049950999999999995</v>
       </c>
       <c r="I172" s="7">
-        <v>0.529252</v>
+        <v>0.549434</v>
       </c>
       <c r="J172" s="7">
-        <v>3.992837</v>
+        <v>4.024583</v>
       </c>
       <c r="K172" s="7">
-        <v>13.477013</v>
+        <v>13.342158999999999</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8233,25 +8233,25 @@
         <v>4</v>
       </c>
       <c r="E173" s="7">
-        <v>0.065385</v>
+        <v>0.042298999999999996</v>
       </c>
       <c r="F173" s="7">
-        <v>0.010621</v>
+        <v>0.008394</v>
       </c>
       <c r="G173" s="7">
-        <v>0.205803</v>
+        <v>0.194478</v>
       </c>
       <c r="H173" s="7">
-        <v>0.09910999999999999</v>
+        <v>0.099413</v>
       </c>
       <c r="I173" s="7">
-        <v>0.454369</v>
+        <v>0.440969</v>
       </c>
       <c r="J173" s="7">
-        <v>2.04465</v>
+        <v>2.0761920000000003</v>
       </c>
       <c r="K173" s="7">
-        <v>5.360659000000001</v>
+        <v>5.337560999999999</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8268,25 +8268,25 @@
         <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>0.088076</v>
+        <v>0.068464</v>
       </c>
       <c r="F174" s="7">
-        <v>0.027632</v>
+        <v>0.027301000000000002</v>
       </c>
       <c r="G174" s="7">
-        <v>0.257926</v>
+        <v>0.245613</v>
       </c>
       <c r="H174" s="7">
-        <v>0.19903099999999999</v>
+        <v>0.20285799999999998</v>
       </c>
       <c r="I174" s="7">
-        <v>0.457573</v>
+        <v>0.45441899999999996</v>
       </c>
       <c r="J174" s="7">
-        <v>2.7388470000000003</v>
+        <v>2.806356</v>
       </c>
       <c r="K174" s="7">
-        <v>10.394443</v>
+        <v>10.330867000000001</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8303,25 +8303,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.045885999999999996</v>
+        <v>0.030807</v>
       </c>
       <c r="F175" s="7">
-        <v>0.033547</v>
+        <v>0.034491999999999995</v>
       </c>
       <c r="G175" s="7">
-        <v>0.097321</v>
+        <v>0.097073</v>
       </c>
       <c r="H175" s="7">
-        <v>0.048837</v>
+        <v>0.049601</v>
       </c>
       <c r="I175" s="7">
-        <v>0.30476</v>
+        <v>0.30303599999999997</v>
       </c>
       <c r="J175" s="7">
-        <v>2.0847890000000002</v>
+        <v>2.082099</v>
       </c>
       <c r="K175" s="7">
-        <v>6.343839</v>
+        <v>6.257223</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8338,25 +8338,25 @@
         <v>6</v>
       </c>
       <c r="E176" s="7">
-        <v>0.12426</v>
+        <v>0.097904</v>
       </c>
       <c r="F176" s="7">
-        <v>0.055268</v>
+        <v>0.050339999999999996</v>
       </c>
       <c r="G176" s="7">
-        <v>0.24257</v>
+        <v>0.234254</v>
       </c>
       <c r="H176" s="7">
-        <v>0.187688</v>
+        <v>0.189487</v>
       </c>
       <c r="I176" s="7">
-        <v>0.5997330000000001</v>
+        <v>0.589492</v>
       </c>
       <c r="J176" s="7">
-        <v>2.938297</v>
+        <v>2.982672</v>
       </c>
       <c r="K176" s="7">
-        <v>12.31606</v>
+        <v>12.135102</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,25 +8373,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.105</v>
+        <v>0.08453</v>
       </c>
       <c r="F177" s="7">
-        <v>0.034711</v>
+        <v>0.03786</v>
       </c>
       <c r="G177" s="7">
-        <v>0.336918</v>
+        <v>0.32032200000000005</v>
       </c>
       <c r="H177" s="7">
-        <v>0.23951</v>
+        <v>0.24481000000000003</v>
       </c>
       <c r="I177" s="7">
-        <v>0.568307</v>
+        <v>0.583269</v>
       </c>
       <c r="J177" s="7">
-        <v>3.286881</v>
+        <v>3.3667439999999997</v>
       </c>
       <c r="K177" s="7">
-        <v>17.257266</v>
+        <v>17.110637</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8408,25 +8408,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.08421300000000001</v>
+        <v>0.06861</v>
       </c>
       <c r="F178" s="7">
-        <v>0.03567</v>
+        <v>0.034398</v>
       </c>
       <c r="G178" s="7">
-        <v>0.309467</v>
+        <v>0.296063</v>
       </c>
       <c r="H178" s="7">
-        <v>0.20133900000000002</v>
+        <v>0.205439</v>
       </c>
       <c r="I178" s="7">
-        <v>0.523936</v>
+        <v>0.5244489999999999</v>
       </c>
       <c r="J178" s="7">
-        <v>3.164232</v>
+        <v>3.2231360000000002</v>
       </c>
       <c r="K178" s="7">
-        <v>12.856205</v>
+        <v>12.765730000000001</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,25 +8443,25 @@
         <v>4</v>
       </c>
       <c r="E179" s="7">
-        <v>0.073197</v>
+        <v>0.06046</v>
       </c>
       <c r="F179" s="7">
-        <v>0.034585</v>
+        <v>0.037309999999999996</v>
       </c>
       <c r="G179" s="7">
-        <v>0.278625</v>
+        <v>0.269638</v>
       </c>
       <c r="H179" s="7">
-        <v>0.168745</v>
+        <v>0.172793</v>
       </c>
       <c r="I179" s="7">
-        <v>0.5323640000000001</v>
+        <v>0.533193</v>
       </c>
       <c r="J179" s="7">
-        <v>3.3971839999999998</v>
+        <v>3.445763</v>
       </c>
       <c r="K179" s="7">
-        <v>11.170532000000001</v>
+        <v>11.127988</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8478,25 +8478,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.09879500000000001</v>
+        <v>0.07624399999999999</v>
       </c>
       <c r="F180" s="7">
-        <v>0.035044</v>
+        <v>0.040170000000000004</v>
       </c>
       <c r="G180" s="7">
-        <v>0.14029999999999998</v>
+        <v>0.144434</v>
       </c>
       <c r="H180" s="7">
-        <v>0.106508</v>
+        <v>0.10960900000000001</v>
       </c>
       <c r="I180" s="7">
-        <v>0.544932</v>
+        <v>0.52481</v>
       </c>
       <c r="J180" s="7">
-        <v>3.205863</v>
+        <v>3.22168</v>
       </c>
       <c r="K180" s="7">
-        <v>8.318719999999999</v>
+        <v>8.245472</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8513,25 +8513,25 @@
         <v>2</v>
       </c>
       <c r="E181" s="7">
-        <v>0.042273</v>
+        <v>0.035412</v>
       </c>
       <c r="F181" s="7">
-        <v>0.066941</v>
+        <v>0.07133099999999999</v>
       </c>
       <c r="G181" s="7">
-        <v>0.20747800000000002</v>
+        <v>0.206016</v>
       </c>
       <c r="H181" s="7">
-        <v>0.124389</v>
+        <v>0.129063</v>
       </c>
       <c r="I181" s="7">
-        <v>0.48761499999999997</v>
+        <v>0.485578</v>
       </c>
       <c r="J181" s="7">
-        <v>3.3183</v>
+        <v>3.331048</v>
       </c>
       <c r="K181" s="7">
-        <v>6.284928</v>
+        <v>6.30337</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8548,25 +8548,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.081396</v>
+        <v>0.065795</v>
       </c>
       <c r="F182" s="7">
-        <v>0.014288</v>
+        <v>0.015771999999999998</v>
       </c>
       <c r="G182" s="7">
-        <v>0.129917</v>
+        <v>0.11743</v>
       </c>
       <c r="H182" s="7">
-        <v>0.152088</v>
+        <v>0.155626</v>
       </c>
       <c r="I182" s="7">
-        <v>0.35818399999999995</v>
+        <v>0.357318</v>
       </c>
       <c r="J182" s="7">
-        <v>2.417757</v>
+        <v>2.437318</v>
       </c>
       <c r="K182" s="7">
-        <v>3.905064</v>
+        <v>3.90214</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8583,25 +8583,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.117768</v>
+        <v>0.10886100000000001</v>
       </c>
       <c r="F183" s="7">
-        <v>0.093626</v>
+        <v>0.125952</v>
       </c>
       <c r="G183" s="7">
-        <v>0.369023</v>
+        <v>0.367172</v>
       </c>
       <c r="H183" s="7">
-        <v>0.318736</v>
+        <v>0.33305599999999996</v>
       </c>
       <c r="I183" s="7">
-        <v>0.6774209999999999</v>
+        <v>0.7038949999999999</v>
       </c>
       <c r="J183" s="7">
-        <v>3.2106</v>
+        <v>3.357449</v>
       </c>
       <c r="K183" s="7">
-        <v>13.00894</v>
+        <v>12.979104</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8618,25 +8618,25 @@
         <v>3</v>
       </c>
       <c r="E184" s="7">
-        <v>0.029703</v>
+        <v>0.027978</v>
       </c>
       <c r="F184" s="7">
-        <v>0.08628999999999999</v>
+        <v>0.088238</v>
       </c>
       <c r="G184" s="7">
-        <v>0.193058</v>
+        <v>0.192716</v>
       </c>
       <c r="H184" s="7">
-        <v>0.11940200000000001</v>
+        <v>0.123544</v>
       </c>
       <c r="I184" s="7">
-        <v>0.45632</v>
+        <v>0.45358899999999996</v>
       </c>
       <c r="J184" s="7">
-        <v>1.713416</v>
+        <v>1.733425</v>
       </c>
       <c r="K184" s="7">
-        <v>3.8155959999999998</v>
+        <v>3.825388</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8653,25 +8653,25 @@
         <v>5</v>
       </c>
       <c r="E185" s="7">
-        <v>0.101121</v>
+        <v>0.090916</v>
       </c>
       <c r="F185" s="7">
-        <v>0.083132</v>
+        <v>0.105959</v>
       </c>
       <c r="G185" s="7">
-        <v>0.288243</v>
+        <v>0.28729</v>
       </c>
       <c r="H185" s="7">
-        <v>0.240338</v>
+        <v>0.251357</v>
       </c>
       <c r="I185" s="7">
-        <v>0.614505</v>
+        <v>0.633362</v>
       </c>
       <c r="J185" s="7">
-        <v>2.974708</v>
+        <v>3.063594</v>
       </c>
       <c r="K185" s="7">
-        <v>11.161865</v>
+        <v>11.147998</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8688,25 +8688,25 @@
         <v>2</v>
       </c>
       <c r="E186" s="7">
-        <v>0.030049000000000003</v>
+        <v>0.028155</v>
       </c>
       <c r="F186" s="7">
-        <v>0.08626899999999998</v>
+        <v>0.088284</v>
       </c>
       <c r="G186" s="7">
-        <v>0.19030999999999998</v>
+        <v>0.19002400000000003</v>
       </c>
       <c r="H186" s="7">
-        <v>0.11902599999999999</v>
+        <v>0.12319200000000001</v>
       </c>
       <c r="I186" s="7">
-        <v>0.45039</v>
+        <v>0.44800199999999996</v>
       </c>
       <c r="J186" s="7">
-        <v>1.823827</v>
+        <v>1.8350380000000002</v>
       </c>
       <c r="K186" s="7">
-        <v>3.3263499999999997</v>
+        <v>3.3356369999999997</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8723,25 +8723,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.021150000000000002</v>
+        <v>0.020739999999999998</v>
       </c>
       <c r="F187" s="7">
-        <v>0.054873000000000005</v>
+        <v>0.068831</v>
       </c>
       <c r="G187" s="7">
-        <v>0.150457</v>
+        <v>0.150328</v>
       </c>
       <c r="H187" s="7">
-        <v>0.09765800000000001</v>
+        <v>0.10138799999999999</v>
       </c>
       <c r="I187" s="7">
-        <v>0.38230800000000004</v>
+        <v>0.380041</v>
       </c>
       <c r="J187" s="7">
-        <v>1.976599</v>
+        <v>1.982143</v>
       </c>
       <c r="K187" s="7">
-        <v>3.3265179999999996</v>
+        <v>3.332616</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,16 +8758,16 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.029655</v>
+        <v>0.034054</v>
       </c>
       <c r="F188" s="7">
-        <v>-0.266162</v>
+        <v>-0.11831</v>
       </c>
       <c r="G188" s="7">
-        <v>0.5058590000000001</v>
+        <v>0.504196</v>
       </c>
       <c r="H188" s="7">
-        <v>0.0018640000000000002</v>
+        <v>0.017710999999999998</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
@@ -8787,25 +8787,25 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>0.001114</v>
+        <v>-0.013502</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.111496</v>
+        <v>-0.08307600000000001</v>
       </c>
       <c r="G189" s="7">
-        <v>0.160613</v>
+        <v>0.190052</v>
       </c>
       <c r="H189" s="7">
-        <v>0.055</v>
+        <v>0.060764</v>
       </c>
       <c r="I189" s="7">
-        <v>0.5528730000000001</v>
+        <v>0.569601</v>
       </c>
       <c r="J189" s="7">
-        <v>3.836498</v>
+        <v>3.888384</v>
       </c>
       <c r="K189" s="7">
-        <v>13.205755</v>
+        <v>13.073786</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>-0.012105</v>
+        <v>-0.020762</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.102895</v>
+        <v>-0.09671400000000001</v>
       </c>
       <c r="G190" s="7">
-        <v>0.128013</v>
+        <v>0.152808</v>
       </c>
       <c r="H190" s="7">
-        <v>0.027490999999999998</v>
+        <v>0.034885</v>
       </c>
       <c r="I190" s="7">
-        <v>0.510956</v>
+        <v>0.5378269999999999</v>
       </c>
       <c r="J190" s="7">
-        <v>3.769483</v>
+        <v>3.8181380000000003</v>
       </c>
       <c r="K190" s="7">
-        <v>12.942056000000001</v>
+        <v>12.835761</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8857,25 @@
         <v>4</v>
       </c>
       <c r="E191" s="7">
-        <v>0.071351</v>
+        <v>0.052848</v>
       </c>
       <c r="F191" s="7">
-        <v>0.031093000000000003</v>
+        <v>0.032001</v>
       </c>
       <c r="G191" s="7">
-        <v>0.250782</v>
+        <v>0.234022</v>
       </c>
       <c r="H191" s="7">
-        <v>0.133626</v>
+        <v>0.135409</v>
       </c>
       <c r="I191" s="7">
-        <v>0.49830399999999997</v>
+        <v>0.492263</v>
       </c>
       <c r="J191" s="7">
-        <v>1.849664</v>
+        <v>1.858606</v>
       </c>
       <c r="K191" s="7">
-        <v>5.052091</v>
+        <v>5.034359</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8892,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.061541</v>
+        <v>0.04027</v>
       </c>
       <c r="F192" s="7">
-        <v>0.029802</v>
+        <v>0.028028</v>
       </c>
       <c r="G192" s="7">
-        <v>0.193532</v>
+        <v>0.18482099999999999</v>
       </c>
       <c r="H192" s="7">
-        <v>0.098674</v>
+        <v>0.09859299999999999</v>
       </c>
       <c r="I192" s="7">
-        <v>0.457885</v>
+        <v>0.447636</v>
       </c>
       <c r="J192" s="7">
-        <v>2.198606</v>
+        <v>2.247097</v>
       </c>
       <c r="K192" s="7">
-        <v>5.50061</v>
+        <v>5.482563</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8927,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>0.042078</v>
+        <v>0.027971</v>
       </c>
       <c r="F193" s="7">
-        <v>0.030567999999999998</v>
+        <v>0.029781</v>
       </c>
       <c r="G193" s="7">
-        <v>0.098003</v>
+        <v>0.09723599999999999</v>
       </c>
       <c r="H193" s="7">
-        <v>0.046182</v>
+        <v>0.046204</v>
       </c>
       <c r="I193" s="7">
-        <v>0.315485</v>
+        <v>0.314401</v>
       </c>
       <c r="J193" s="7">
-        <v>2.20087</v>
+        <v>2.197226</v>
       </c>
       <c r="K193" s="7">
-        <v>6.573176</v>
+        <v>6.474302</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8962,25 @@
         <v>3</v>
       </c>
       <c r="E194" s="7">
-        <v>0.049703</v>
+        <v>0.045801999999999995</v>
       </c>
       <c r="F194" s="7">
-        <v>0.083451</v>
+        <v>0.09027400000000001</v>
       </c>
       <c r="G194" s="7">
-        <v>0.23602599999999999</v>
+        <v>0.235291</v>
       </c>
       <c r="H194" s="7">
-        <v>0.182666</v>
+        <v>0.19057400000000002</v>
       </c>
       <c r="I194" s="7">
-        <v>0.469437</v>
+        <v>0.473992</v>
       </c>
       <c r="J194" s="7">
-        <v>1.55036</v>
+        <v>1.5924209999999999</v>
       </c>
       <c r="K194" s="7">
-        <v>3.716017</v>
+        <v>3.719596</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +8997,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.049759000000000005</v>
+        <v>0.043958000000000004</v>
       </c>
       <c r="F195" s="7">
-        <v>0.070956</v>
+        <v>0.07418</v>
       </c>
       <c r="G195" s="7">
-        <v>0.228296</v>
+        <v>0.226812</v>
       </c>
       <c r="H195" s="7">
-        <v>0.136545</v>
+        <v>0.140616</v>
       </c>
       <c r="I195" s="7">
-        <v>0.455805</v>
+        <v>0.456911</v>
       </c>
       <c r="J195" s="7">
-        <v>1.7266380000000001</v>
+        <v>1.772926</v>
       </c>
       <c r="K195" s="7">
-        <v>4.605392</v>
+        <v>4.611713</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9032,25 @@
         <v>4</v>
       </c>
       <c r="E196" s="7">
-        <v>0.073656</v>
+        <v>0.051026999999999996</v>
       </c>
       <c r="F196" s="7">
-        <v>0.033572000000000005</v>
+        <v>0.030268000000000003</v>
       </c>
       <c r="G196" s="7">
-        <v>0.21354099999999998</v>
+        <v>0.20363</v>
       </c>
       <c r="H196" s="7">
-        <v>0.124534</v>
+        <v>0.123869</v>
       </c>
       <c r="I196" s="7">
-        <v>0.48814100000000005</v>
+        <v>0.475396</v>
       </c>
       <c r="J196" s="7">
-        <v>2.10428</v>
+        <v>2.1465389999999998</v>
       </c>
       <c r="K196" s="7">
-        <v>5.076014</v>
+        <v>5.046663</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9067,25 @@
         <v>6</v>
       </c>
       <c r="E197" s="7">
-        <v>0.085455</v>
+        <v>0.065593</v>
       </c>
       <c r="F197" s="7">
-        <v>-0.014332000000000001</v>
+        <v>-0.020375</v>
       </c>
       <c r="G197" s="7">
-        <v>0.24064</v>
+        <v>0.21959900000000002</v>
       </c>
       <c r="H197" s="7">
-        <v>0.19165500000000002</v>
+        <v>0.198204</v>
       </c>
       <c r="I197" s="7">
-        <v>0.450441</v>
+        <v>0.46204900000000004</v>
       </c>
       <c r="J197" s="7">
-        <v>3.916481</v>
+        <v>4.037406</v>
       </c>
       <c r="K197" s="7">
-        <v>20.762793000000002</v>
+        <v>20.586955</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,16 +9102,16 @@
         <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>0.092707</v>
+        <v>0.086312</v>
       </c>
       <c r="F198" s="7">
-        <v>0.037228</v>
+        <v>0.046908000000000005</v>
       </c>
       <c r="G198" s="7">
-        <v>0.220865</v>
+        <v>0.21589200000000003</v>
       </c>
       <c r="H198" s="7">
-        <v>0.18754</v>
+        <v>0.196155</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
@@ -9131,25 +9131,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.06618</v>
+        <v>0.064997</v>
       </c>
       <c r="F199" s="7">
-        <v>-0.035523</v>
+        <v>-0.023056999999999998</v>
       </c>
       <c r="G199" s="7">
-        <v>0.152807</v>
+        <v>0.13123100000000001</v>
       </c>
       <c r="H199" s="7">
-        <v>0.06510200000000001</v>
+        <v>0.076264</v>
       </c>
       <c r="I199" s="7">
-        <v>0.362839</v>
+        <v>0.387975</v>
       </c>
       <c r="J199" s="7">
-        <v>2.065283</v>
+        <v>2.280224</v>
       </c>
       <c r="K199" s="7">
-        <v>9.81706</v>
+        <v>9.781476</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9160,39 +9160,39 @@
         <v>421</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>85</v>
+        <v>422</v>
       </c>
       <c r="D200" s="6">
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.095282</v>
+        <v>0.081065</v>
       </c>
       <c r="F200" s="7">
-        <v>0.05428</v>
+        <v>0.06525299999999999</v>
       </c>
       <c r="G200" s="7">
-        <v>0.226083</v>
+        <v>0.215953</v>
       </c>
       <c r="H200" s="7">
-        <v>0.173174</v>
+        <v>0.179634</v>
       </c>
       <c r="I200" s="7">
-        <v>0.47976100000000005</v>
+        <v>0.489391</v>
       </c>
       <c r="J200" s="7">
-        <v>2.361259</v>
+        <v>2.4933899999999998</v>
       </c>
       <c r="K200" s="7">
-        <v>9.153277000000001</v>
+        <v>9.009284000000001</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C201" s="5" t="s">
         <v>73</v>
@@ -9201,33 +9201,33 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.038064</v>
+        <v>0.020436999999999997</v>
       </c>
       <c r="F201" s="7">
-        <v>-0.011878</v>
+        <v>-0.008947</v>
       </c>
       <c r="G201" s="7">
-        <v>0.163729</v>
+        <v>0.15491</v>
       </c>
       <c r="H201" s="7">
-        <v>0.08216100000000001</v>
+        <v>0.08295899999999999</v>
       </c>
       <c r="I201" s="7">
-        <v>0.668537</v>
+        <v>0.65537</v>
       </c>
       <c r="J201" s="7">
-        <v>2.9038690000000003</v>
+        <v>2.970157</v>
       </c>
       <c r="K201" s="7">
-        <v>6.36397</v>
+        <v>6.355676</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C202" s="5" t="s">
         <v>23</v>
@@ -9236,33 +9236,33 @@
         <v>3</v>
       </c>
       <c r="E202" s="7">
-        <v>0.035206</v>
+        <v>0.01626</v>
       </c>
       <c r="F202" s="7">
-        <v>0.017147</v>
+        <v>0.014403999999999998</v>
       </c>
       <c r="G202" s="7">
-        <v>0.149227</v>
+        <v>0.141743</v>
       </c>
       <c r="H202" s="7">
-        <v>0.047564999999999996</v>
+        <v>0.046962000000000004</v>
       </c>
       <c r="I202" s="7">
-        <v>0.40366199999999997</v>
+        <v>0.38427900000000004</v>
       </c>
       <c r="J202" s="7">
-        <v>1.636352</v>
+        <v>1.627737</v>
       </c>
       <c r="K202" s="7">
-        <v>3.6614299999999997</v>
+        <v>3.648838</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>32</v>
@@ -9271,16 +9271,16 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.08875899999999999</v>
+        <v>0.07105</v>
       </c>
       <c r="F203" s="7">
-        <v>-0.009003</v>
+        <v>-0.014621</v>
       </c>
       <c r="G203" s="7">
-        <v>0.261736</v>
+        <v>0.242368</v>
       </c>
       <c r="H203" s="7">
-        <v>0.201728</v>
+        <v>0.209227</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
@@ -9288,10 +9288,10 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>26</v>
@@ -9300,33 +9300,33 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.039865</v>
+        <v>0.031034000000000003</v>
       </c>
       <c r="F204" s="7">
-        <v>0.035826</v>
+        <v>0.036438</v>
       </c>
       <c r="G204" s="7">
-        <v>0.10620900000000001</v>
+        <v>0.10627800000000001</v>
       </c>
       <c r="H204" s="7">
-        <v>0.05803899999999999</v>
+        <v>0.058041</v>
       </c>
       <c r="I204" s="7">
-        <v>0.311309</v>
+        <v>0.310242</v>
       </c>
       <c r="J204" s="7">
-        <v>1.946885</v>
+        <v>1.944303</v>
       </c>
       <c r="K204" s="7">
-        <v>5.34842</v>
+        <v>5.2828729999999995</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>133</v>
@@ -9335,33 +9335,33 @@
         <v>4</v>
       </c>
       <c r="E205" s="7">
-        <v>0.053367000000000005</v>
+        <v>0.035028000000000004</v>
       </c>
       <c r="F205" s="7">
-        <v>0.0028039999999999996</v>
+        <v>0.002439</v>
       </c>
       <c r="G205" s="7">
-        <v>0.190996</v>
+        <v>0.180424</v>
       </c>
       <c r="H205" s="7">
-        <v>0.088567</v>
+        <v>0.09077299999999999</v>
       </c>
       <c r="I205" s="7">
-        <v>0.347959</v>
+        <v>0.34799100000000005</v>
       </c>
       <c r="J205" s="7">
-        <v>1.975194</v>
+        <v>1.987295</v>
       </c>
       <c r="K205" s="7">
-        <v>4.907775</v>
+        <v>4.892154</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>26</v>
@@ -9370,33 +9370,33 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.063137</v>
+        <v>0.046496</v>
       </c>
       <c r="F206" s="7">
-        <v>0.0070550000000000005</v>
+        <v>0.016165</v>
       </c>
       <c r="G206" s="7">
-        <v>0.25084</v>
+        <v>0.237712</v>
       </c>
       <c r="H206" s="7">
-        <v>0.157944</v>
+        <v>0.162225</v>
       </c>
       <c r="I206" s="7">
-        <v>0.487442</v>
+        <v>0.49338</v>
       </c>
       <c r="J206" s="7">
-        <v>2.718069</v>
+        <v>2.799282</v>
       </c>
       <c r="K206" s="7">
-        <v>7.975185</v>
+        <v>7.933441</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>26</v>
@@ -9405,33 +9405,33 @@
         <v>6</v>
       </c>
       <c r="E207" s="7">
-        <v>0.072726</v>
+        <v>0.052663</v>
       </c>
       <c r="F207" s="7">
-        <v>-0.007853</v>
+        <v>0.00111</v>
       </c>
       <c r="G207" s="7">
-        <v>0.298817</v>
+        <v>0.28114</v>
       </c>
       <c r="H207" s="7">
-        <v>0.163167</v>
+        <v>0.167631</v>
       </c>
       <c r="I207" s="7">
-        <v>0.506003</v>
+        <v>0.5147780000000001</v>
       </c>
       <c r="J207" s="7">
-        <v>2.72397</v>
+        <v>2.8161720000000003</v>
       </c>
       <c r="K207" s="7">
-        <v>9.716237999999999</v>
+        <v>9.64128</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>23</v>
@@ -9440,33 +9440,33 @@
         <v>3</v>
       </c>
       <c r="E208" s="7">
-        <v>0.038016999999999995</v>
+        <v>0.017154</v>
       </c>
       <c r="F208" s="7">
-        <v>0.00293</v>
+        <v>-0.000335</v>
       </c>
       <c r="G208" s="7">
-        <v>0.16201000000000002</v>
+        <v>0.149376</v>
       </c>
       <c r="H208" s="7">
-        <v>0.038347</v>
+        <v>0.037209</v>
       </c>
       <c r="I208" s="7">
-        <v>0.406775</v>
+        <v>0.375039</v>
       </c>
       <c r="J208" s="7">
-        <v>1.498173</v>
+        <v>1.494931</v>
       </c>
       <c r="K208" s="7">
-        <v>2.929496</v>
+        <v>2.9161349999999997</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>32</v>
@@ -9475,33 +9475,33 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.09540699999999999</v>
+        <v>0.06557</v>
       </c>
       <c r="F209" s="7">
-        <v>-0.030435</v>
+        <v>-0.030299999999999997</v>
       </c>
       <c r="G209" s="7">
-        <v>0.268314</v>
+        <v>0.24310700000000002</v>
       </c>
       <c r="H209" s="7">
-        <v>0.195303</v>
+        <v>0.199269</v>
       </c>
       <c r="I209" s="7">
-        <v>0.39133</v>
+        <v>0.405869</v>
       </c>
       <c r="J209" s="7">
-        <v>2.845733</v>
+        <v>2.948478</v>
       </c>
       <c r="K209" s="7">
-        <v>14.630576000000001</v>
+        <v>14.469937</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>73</v>
@@ -9510,33 +9510,33 @@
         <v>4</v>
       </c>
       <c r="E210" s="7">
-        <v>0.073244</v>
+        <v>0.057365000000000006</v>
       </c>
       <c r="F210" s="7">
-        <v>0.037798</v>
+        <v>0.039852</v>
       </c>
       <c r="G210" s="7">
-        <v>0.234683</v>
+        <v>0.225065</v>
       </c>
       <c r="H210" s="7">
-        <v>0.16545500000000002</v>
+        <v>0.168871</v>
       </c>
       <c r="I210" s="7">
-        <v>0.5139</v>
+        <v>0.516489</v>
       </c>
       <c r="J210" s="7">
-        <v>1.873218</v>
+        <v>1.907446</v>
       </c>
       <c r="K210" s="7">
-        <v>5.48759</v>
+        <v>5.460572</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>53</v>
@@ -9545,33 +9545,33 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.063323</v>
+        <v>0.05455</v>
       </c>
       <c r="F211" s="7">
-        <v>0.098457</v>
+        <v>0.103301</v>
       </c>
       <c r="G211" s="7">
-        <v>0.251724</v>
+        <v>0.247847</v>
       </c>
       <c r="H211" s="7">
-        <v>0.18718800000000002</v>
+        <v>0.19185</v>
       </c>
       <c r="I211" s="7">
-        <v>0.500323</v>
+        <v>0.504684</v>
       </c>
       <c r="J211" s="7">
-        <v>1.89148</v>
+        <v>1.931692</v>
       </c>
       <c r="K211" s="7">
-        <v>5.052407</v>
+        <v>5.05495</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>85</v>
@@ -9580,33 +9580,33 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.083896</v>
+        <v>0.070592</v>
       </c>
       <c r="F212" s="7">
-        <v>0.07917</v>
+        <v>0.09217800000000001</v>
       </c>
       <c r="G212" s="7">
-        <v>0.302051</v>
+        <v>0.29519300000000004</v>
       </c>
       <c r="H212" s="7">
-        <v>0.25055299999999997</v>
+        <v>0.25849900000000003</v>
       </c>
       <c r="I212" s="7">
-        <v>0.61109</v>
+        <v>0.625491</v>
       </c>
       <c r="J212" s="7">
-        <v>2.9962259999999996</v>
+        <v>3.112889</v>
       </c>
       <c r="K212" s="7">
-        <v>9.824588</v>
+        <v>9.805276</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>29</v>
@@ -9615,33 +9615,33 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>-0.003302</v>
+        <v>-0.015193000000000002</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.110246</v>
+        <v>-0.087772</v>
       </c>
       <c r="G213" s="7">
-        <v>0.16467099999999998</v>
+        <v>0.18811499999999998</v>
       </c>
       <c r="H213" s="7">
-        <v>0.059234</v>
+        <v>0.066165</v>
       </c>
       <c r="I213" s="7">
-        <v>0.576281</v>
+        <v>0.597635</v>
       </c>
       <c r="J213" s="7">
-        <v>4.033566</v>
+        <v>4.067353</v>
       </c>
       <c r="K213" s="7">
-        <v>13.520425</v>
+        <v>13.392498</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>26</v>
@@ -9650,33 +9650,33 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.046039000000000004</v>
+        <v>0.037327</v>
       </c>
       <c r="F214" s="7">
-        <v>0.028983</v>
+        <v>0.035825</v>
       </c>
       <c r="G214" s="7">
-        <v>0.16799399999999998</v>
+        <v>0.160355</v>
       </c>
       <c r="H214" s="7">
-        <v>0.114383</v>
+        <v>0.121064</v>
       </c>
       <c r="I214" s="7">
-        <v>0.40132100000000004</v>
+        <v>0.402196</v>
       </c>
       <c r="J214" s="7">
-        <v>2.233237</v>
+        <v>2.344824</v>
       </c>
       <c r="K214" s="7">
-        <v>7.163321999999999</v>
+        <v>7.152773</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>32</v>
@@ -9685,33 +9685,33 @@
         <v>5</v>
       </c>
       <c r="E215" s="7">
-        <v>0.12429899999999999</v>
+        <v>0.11914899999999999</v>
       </c>
       <c r="F215" s="7">
-        <v>0.09617200000000001</v>
+        <v>0.128143</v>
       </c>
       <c r="G215" s="7">
-        <v>0.375567</v>
+        <v>0.37437800000000004</v>
       </c>
       <c r="H215" s="7">
-        <v>0.31946</v>
+        <v>0.34192500000000003</v>
       </c>
       <c r="I215" s="7">
-        <v>0.6508710000000001</v>
+        <v>0.688866</v>
       </c>
       <c r="J215" s="7">
-        <v>2.6947680000000003</v>
+        <v>2.890464</v>
       </c>
       <c r="K215" s="7">
-        <v>9.834802</v>
+        <v>9.837527</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C216" s="5" t="s">
         <v>26</v>
@@ -9720,33 +9720,33 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.025107</v>
+        <v>0.02073</v>
       </c>
       <c r="F216" s="7">
-        <v>0.035354000000000003</v>
+        <v>0.033307</v>
       </c>
       <c r="G216" s="7">
-        <v>0.082468</v>
+        <v>0.080111</v>
       </c>
       <c r="H216" s="7">
-        <v>0.048373</v>
+        <v>0.048272</v>
       </c>
       <c r="I216" s="7">
-        <v>0.22771799999999998</v>
+        <v>0.226757</v>
       </c>
       <c r="J216" s="7">
-        <v>1.777585</v>
+        <v>1.781441</v>
       </c>
       <c r="K216" s="7">
-        <v>5.317145</v>
+        <v>5.224765</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>26</v>
@@ -9755,33 +9755,33 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.07724199999999999</v>
+        <v>0.06746</v>
       </c>
       <c r="F217" s="7">
-        <v>0.10700799999999999</v>
+        <v>0.117838</v>
       </c>
       <c r="G217" s="7">
-        <v>0.31598299999999996</v>
+        <v>0.307513</v>
       </c>
       <c r="H217" s="7">
-        <v>0.24739899999999998</v>
+        <v>0.253328</v>
       </c>
       <c r="I217" s="7">
-        <v>0.6408020000000001</v>
+        <v>0.6472410000000001</v>
       </c>
       <c r="J217" s="7">
-        <v>3.261621</v>
+        <v>3.3726089999999997</v>
       </c>
       <c r="K217" s="7">
-        <v>10.337328</v>
+        <v>10.301234</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>26</v>
@@ -9790,33 +9790,33 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.115377</v>
+        <v>0.110262</v>
       </c>
       <c r="F218" s="7">
-        <v>0.089032</v>
+        <v>0.1226</v>
       </c>
       <c r="G218" s="7">
-        <v>0.360422</v>
+        <v>0.36058</v>
       </c>
       <c r="H218" s="7">
-        <v>0.289833</v>
+        <v>0.31021699999999996</v>
       </c>
       <c r="I218" s="7">
-        <v>0.614663</v>
+        <v>0.645729</v>
       </c>
       <c r="J218" s="7">
-        <v>3.905607</v>
+        <v>4.171334</v>
       </c>
       <c r="K218" s="7">
-        <v>13.293083999999999</v>
+        <v>13.372072000000001</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C219" s="5" t="s">
         <v>20</v>
@@ -9825,47 +9825,47 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.063507</v>
+        <v>0.057605</v>
       </c>
       <c r="F219" s="7">
-        <v>0.050895</v>
+        <v>0.064958</v>
       </c>
       <c r="G219" s="7">
-        <v>0.239866</v>
+        <v>0.239705</v>
       </c>
       <c r="H219" s="7">
-        <v>0.172729</v>
+        <v>0.18157800000000002</v>
       </c>
       <c r="I219" s="7">
-        <v>0.513469</v>
+        <v>0.525632</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="D220" s="6">
         <v>6</v>
       </c>
       <c r="E220" s="7">
-        <v>0.048696</v>
+        <v>0.013734</v>
       </c>
       <c r="F220" s="7">
-        <v>-0.25333</v>
+        <v>-0.093446</v>
       </c>
       <c r="G220" s="7">
-        <v>0.618568</v>
+        <v>0.607898</v>
       </c>
       <c r="H220" s="7">
-        <v>0.081657</v>
+        <v>0.090395</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
@@ -9900,28 +9900,28 @@
         <v>467</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="D222" s="6">
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.021588</v>
+        <v>0.001463</v>
       </c>
       <c r="F222" s="7">
-        <v>-0.181449</v>
+        <v>-0.094895</v>
       </c>
       <c r="G222" s="7">
-        <v>0.378461</v>
+        <v>0.38267</v>
       </c>
       <c r="H222" s="7">
-        <v>0.063503</v>
+        <v>0.06938</v>
       </c>
       <c r="I222" s="7">
-        <v>0.974894</v>
+        <v>1.000909</v>
       </c>
       <c r="J222" s="7">
-        <v>4.378342</v>
+        <v>4.41405</v>
       </c>
       <c r="K222" s="7"/>
     </row>
@@ -9939,25 +9939,25 @@
         <v>4</v>
       </c>
       <c r="E223" s="7">
-        <v>0.031225</v>
+        <v>0.029184</v>
       </c>
       <c r="F223" s="7">
-        <v>0.093828</v>
+        <v>0.096396</v>
       </c>
       <c r="G223" s="7">
-        <v>0.196916</v>
+        <v>0.197022</v>
       </c>
       <c r="H223" s="7">
-        <v>0.123917</v>
+        <v>0.128634</v>
       </c>
       <c r="I223" s="7">
-        <v>0.448032</v>
+        <v>0.443736</v>
       </c>
       <c r="J223" s="7">
-        <v>1.291113</v>
+        <v>1.366767</v>
       </c>
       <c r="K223" s="7">
-        <v>2.703588</v>
+        <v>2.712929</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9974,19 +9974,19 @@
         <v>2</v>
       </c>
       <c r="E224" s="7">
-        <v>0.028506999999999998</v>
+        <v>0.02706</v>
       </c>
       <c r="F224" s="7">
-        <v>0.08133699999999999</v>
+        <v>0.083206</v>
       </c>
       <c r="G224" s="7">
-        <v>0.187334</v>
+        <v>0.186995</v>
       </c>
       <c r="H224" s="7">
-        <v>0.116165</v>
+        <v>0.120134</v>
       </c>
       <c r="I224" s="7">
-        <v>0.445917</v>
+        <v>0.443446</v>
       </c>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10005,22 +10005,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.113246</v>
+        <v>0.10106</v>
       </c>
       <c r="F225" s="7">
-        <v>0.076757</v>
+        <v>0.09856999999999999</v>
       </c>
       <c r="G225" s="7">
-        <v>0.241935</v>
+        <v>0.23297</v>
       </c>
       <c r="H225" s="7">
-        <v>0.24638100000000002</v>
+        <v>0.256164</v>
       </c>
       <c r="I225" s="7">
-        <v>0.456612</v>
+        <v>0.461254</v>
       </c>
       <c r="J225" s="7">
-        <v>2.524404</v>
+        <v>2.816918</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10038,19 +10038,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="7">
-        <v>0.029931</v>
+        <v>0.007873999999999999</v>
       </c>
       <c r="F226" s="7">
-        <v>-0.159951</v>
+        <v>-0.095368</v>
       </c>
       <c r="G226" s="7">
-        <v>0.366327</v>
+        <v>0.355574</v>
       </c>
       <c r="H226" s="7">
-        <v>0.08259999999999999</v>
+        <v>0.08248799999999999</v>
       </c>
       <c r="I226" s="7">
-        <v>0.877114</v>
+        <v>0.8971339999999999</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10069,25 +10069,25 @@
         <v>4</v>
       </c>
       <c r="E227" s="7">
-        <v>0.060086</v>
+        <v>0.039428</v>
       </c>
       <c r="F227" s="7">
-        <v>0.032685</v>
+        <v>0.031631</v>
       </c>
       <c r="G227" s="7">
-        <v>0.19731</v>
+        <v>0.188826</v>
       </c>
       <c r="H227" s="7">
-        <v>0.10143200000000001</v>
+        <v>0.101792</v>
       </c>
       <c r="I227" s="7">
-        <v>0.46273000000000003</v>
+        <v>0.451712</v>
       </c>
       <c r="J227" s="7">
-        <v>2.166238</v>
+        <v>2.216049</v>
       </c>
       <c r="K227" s="7">
-        <v>5.583333</v>
+        <v>5.567938000000001</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10104,25 +10104,25 @@
         <v>3</v>
       </c>
       <c r="E228" s="7">
-        <v>0.048728</v>
+        <v>0.044396000000000005</v>
       </c>
       <c r="F228" s="7">
-        <v>0.072423</v>
+        <v>0.076206</v>
       </c>
       <c r="G228" s="7">
-        <v>0.222865</v>
+        <v>0.221265</v>
       </c>
       <c r="H228" s="7">
-        <v>0.1387</v>
+        <v>0.14317</v>
       </c>
       <c r="I228" s="7">
-        <v>0.445818</v>
+        <v>0.446757</v>
       </c>
       <c r="J228" s="7">
-        <v>1.7627610000000002</v>
+        <v>1.810249</v>
       </c>
       <c r="K228" s="7">
-        <v>4.556385000000001</v>
+        <v>4.5625</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,19 +10139,19 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.09223100000000001</v>
+        <v>0.076985</v>
       </c>
       <c r="F229" s="7">
-        <v>0.104194</v>
+        <v>0.11027100000000001</v>
       </c>
       <c r="G229" s="7">
-        <v>0.209514</v>
+        <v>0.205911</v>
       </c>
       <c r="H229" s="7">
-        <v>0.197958</v>
+        <v>0.20130199999999998</v>
       </c>
       <c r="I229" s="7">
-        <v>0.552108</v>
+        <v>0.546153</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10185,25 +10185,25 @@
         <v>486</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="D231" s="6">
         <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>0.12185499999999999</v>
+        <v>0.10922599999999999</v>
       </c>
       <c r="F231" s="7">
-        <v>0.15254</v>
+        <v>0.161247</v>
       </c>
       <c r="G231" s="7">
-        <v>0.318264</v>
+        <v>0.298703</v>
       </c>
       <c r="H231" s="7">
-        <v>0.338979</v>
+        <v>0.346661</v>
       </c>
       <c r="I231" s="7">
-        <v>0.551173</v>
+        <v>0.5613360000000001</v>
       </c>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10216,25 +10216,25 @@
         <v>488</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="D232" s="6">
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.11827299999999999</v>
+        <v>0.10718899999999999</v>
       </c>
       <c r="F232" s="7">
-        <v>0.06091</v>
+        <v>0.083664</v>
       </c>
       <c r="G232" s="7">
-        <v>0.23848</v>
+        <v>0.243198</v>
       </c>
       <c r="H232" s="7">
-        <v>0.205946</v>
+        <v>0.222102</v>
       </c>
       <c r="I232" s="7">
-        <v>0.5139330000000001</v>
+        <v>0.528094</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10253,25 +10253,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.035932</v>
+        <v>0.031234</v>
       </c>
       <c r="F233" s="7">
-        <v>0.053539</v>
+        <v>0.058032</v>
       </c>
       <c r="G233" s="7">
-        <v>0.17022700000000002</v>
+        <v>0.166382</v>
       </c>
       <c r="H233" s="7">
-        <v>0.103645</v>
+        <v>0.108949</v>
       </c>
       <c r="I233" s="7">
-        <v>0.36764899999999995</v>
+        <v>0.371364</v>
       </c>
       <c r="J233" s="7">
-        <v>1.495652</v>
+        <v>1.5864719999999999</v>
       </c>
       <c r="K233" s="7">
-        <v>4.3127260000000005</v>
+        <v>4.325295</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10288,19 +10288,19 @@
         <v>3</v>
       </c>
       <c r="E234" s="7">
-        <v>0.052115999999999996</v>
+        <v>0.042512999999999995</v>
       </c>
       <c r="F234" s="7">
-        <v>0.018258</v>
+        <v>0.015013</v>
       </c>
       <c r="G234" s="7">
-        <v>0.22299600000000003</v>
+        <v>0.21602</v>
       </c>
       <c r="H234" s="7">
-        <v>0.158469</v>
+        <v>0.16685199999999997</v>
       </c>
       <c r="I234" s="7">
-        <v>0.46584000000000003</v>
+        <v>0.471283</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10319,19 +10319,19 @@
         <v>4</v>
       </c>
       <c r="E235" s="7">
-        <v>0.050558</v>
+        <v>0.038060000000000004</v>
       </c>
       <c r="F235" s="7">
-        <v>0.040907</v>
+        <v>0.046611</v>
       </c>
       <c r="G235" s="7">
-        <v>0.20325600000000002</v>
+        <v>0.199386</v>
       </c>
       <c r="H235" s="7">
-        <v>0.09711600000000001</v>
+        <v>0.104608</v>
       </c>
       <c r="I235" s="7">
-        <v>0.468635</v>
+        <v>0.47045499999999996</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10350,19 +10350,19 @@
         <v>2</v>
       </c>
       <c r="E236" s="7">
-        <v>0.033035</v>
+        <v>0.03138</v>
       </c>
       <c r="F236" s="7">
-        <v>0.092824</v>
+        <v>0.094299</v>
       </c>
       <c r="G236" s="7">
-        <v>0.198349</v>
+        <v>0.19757100000000002</v>
       </c>
       <c r="H236" s="7">
-        <v>0.128602</v>
+        <v>0.13231099999999998</v>
       </c>
       <c r="I236" s="7">
-        <v>0.475063</v>
+        <v>0.47031599999999996</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10381,25 +10381,25 @@
         <v>6</v>
       </c>
       <c r="E237" s="7">
-        <v>0.0006569999999999999</v>
+        <v>-0.011970000000000001</v>
       </c>
       <c r="F237" s="7">
-        <v>-0.09679299999999999</v>
+        <v>-0.083255</v>
       </c>
       <c r="G237" s="7">
-        <v>0.18194400000000002</v>
+        <v>0.20251999999999998</v>
       </c>
       <c r="H237" s="7">
-        <v>0.069848</v>
+        <v>0.070993</v>
       </c>
       <c r="I237" s="7">
-        <v>0.577338</v>
+        <v>0.591774</v>
       </c>
       <c r="J237" s="7">
-        <v>4.148357</v>
+        <v>4.1572640000000005</v>
       </c>
       <c r="K237" s="7">
-        <v>13.823556000000002</v>
+        <v>13.622594</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10416,14 +10416,14 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.049995000000000005</v>
+        <v>0.019756</v>
       </c>
       <c r="F238" s="7">
-        <v>0.004521</v>
+        <v>0.0023480000000000003</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7">
-        <v>0.036187</v>
+        <v>0.035068</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
@@ -10443,19 +10443,19 @@
         <v>6</v>
       </c>
       <c r="E239" s="7">
-        <v>0.15955</v>
+        <v>0.153441</v>
       </c>
       <c r="F239" s="7">
-        <v>0.182549</v>
+        <v>0.193707</v>
       </c>
       <c r="G239" s="7">
-        <v>0.29386</v>
+        <v>0.278346</v>
       </c>
       <c r="H239" s="7">
-        <v>0.289369</v>
+        <v>0.294843</v>
       </c>
       <c r="I239" s="7">
-        <v>0.679281</v>
+        <v>0.6725490000000001</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10474,19 +10474,19 @@
         <v>5</v>
       </c>
       <c r="E240" s="7">
-        <v>0.108244</v>
+        <v>0.088415</v>
       </c>
       <c r="F240" s="7">
-        <v>0.034617</v>
+        <v>0.027094</v>
       </c>
       <c r="G240" s="7">
-        <v>0.211234</v>
+        <v>0.20213</v>
       </c>
       <c r="H240" s="7">
-        <v>0.16575700000000002</v>
+        <v>0.16825099999999998</v>
       </c>
       <c r="I240" s="7">
-        <v>0.495473</v>
+        <v>0.486737</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10505,25 +10505,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.030763</v>
+        <v>0.023485999999999996</v>
       </c>
       <c r="F241" s="7">
-        <v>0.039162</v>
+        <v>0.03494</v>
       </c>
       <c r="G241" s="7">
-        <v>0.08775000000000001</v>
+        <v>0.083831</v>
       </c>
       <c r="H241" s="7">
-        <v>0.052428999999999996</v>
+        <v>0.050865</v>
       </c>
       <c r="I241" s="7">
-        <v>0.226304</v>
+        <v>0.22595500000000002</v>
       </c>
       <c r="J241" s="7">
-        <v>1.832808</v>
+        <v>1.8278550000000002</v>
       </c>
       <c r="K241" s="7">
-        <v>5.905748999999999</v>
+        <v>5.7929759999999995</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10540,25 +10540,25 @@
         <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.024093</v>
+        <v>0.020550000000000002</v>
       </c>
       <c r="F242" s="7">
-        <v>0.044751000000000006</v>
+        <v>0.044501</v>
       </c>
       <c r="G242" s="7">
-        <v>0.20805099999999999</v>
+        <v>0.186779</v>
       </c>
       <c r="H242" s="7">
-        <v>0.08201399999999999</v>
+        <v>0.082626</v>
       </c>
       <c r="I242" s="7">
-        <v>0.20968499999999998</v>
+        <v>0.207838</v>
       </c>
       <c r="J242" s="7">
-        <v>1.95191</v>
+        <v>1.963147</v>
       </c>
       <c r="K242" s="7">
-        <v>5.837667</v>
+        <v>5.8029340000000005</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10575,25 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.09897399999999999</v>
+        <v>0.076391</v>
       </c>
       <c r="F243" s="7">
-        <v>-0.014745999999999999</v>
+        <v>-0.015318</v>
       </c>
       <c r="G243" s="7">
-        <v>0.255874</v>
+        <v>0.23603000000000002</v>
       </c>
       <c r="H243" s="7">
-        <v>0.184975</v>
+        <v>0.191848</v>
       </c>
       <c r="I243" s="7">
-        <v>0.459279</v>
+        <v>0.47975</v>
       </c>
       <c r="J243" s="7">
-        <v>2.846406</v>
+        <v>2.965163</v>
       </c>
       <c r="K243" s="7">
-        <v>14.693051</v>
+        <v>14.513322</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10610,25 @@
         <v>3</v>
       </c>
       <c r="E244" s="7">
-        <v>0.048344</v>
+        <v>0.045441</v>
       </c>
       <c r="F244" s="7">
-        <v>0.060393999999999996</v>
+        <v>0.079741</v>
       </c>
       <c r="G244" s="7">
-        <v>0.21489</v>
+        <v>0.217306</v>
       </c>
       <c r="H244" s="7">
-        <v>0.142869</v>
+        <v>0.15065099999999998</v>
       </c>
       <c r="I244" s="7">
-        <v>0.44555700000000004</v>
+        <v>0.45299100000000003</v>
       </c>
       <c r="J244" s="7">
-        <v>1.780594</v>
+        <v>1.830791</v>
       </c>
       <c r="K244" s="7">
-        <v>4.586712</v>
+        <v>4.604764</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10645,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.054719</v>
+        <v>0.027634</v>
       </c>
       <c r="F245" s="7">
-        <v>-0.008122</v>
+        <v>-0.009979</v>
       </c>
       <c r="G245" s="7">
-        <v>0.158222</v>
+        <v>0.147325</v>
       </c>
       <c r="H245" s="7">
-        <v>0.063248</v>
+        <v>0.063878</v>
       </c>
       <c r="I245" s="7">
-        <v>0.38854500000000003</v>
+        <v>0.37815899999999997</v>
       </c>
       <c r="J245" s="7">
-        <v>1.452037</v>
+        <v>1.4392660000000002</v>
       </c>
       <c r="K245" s="7">
-        <v>3.801884</v>
+        <v>3.776924</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10680,25 @@
         <v>2</v>
       </c>
       <c r="E246" s="7">
-        <v>0.044924</v>
+        <v>0.037868</v>
       </c>
       <c r="F246" s="7">
-        <v>0.077754</v>
+        <v>0.08025499999999999</v>
       </c>
       <c r="G246" s="7">
-        <v>0.213568</v>
+        <v>0.211561</v>
       </c>
       <c r="H246" s="7">
-        <v>0.129763</v>
+        <v>0.134066</v>
       </c>
       <c r="I246" s="7">
-        <v>0.518562</v>
+        <v>0.5114070000000001</v>
       </c>
       <c r="J246" s="7">
-        <v>4.305023</v>
+        <v>4.300465</v>
       </c>
       <c r="K246" s="7">
-        <v>7.14736</v>
+        <v>7.164371</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10715,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.070337</v>
+        <v>0.055987</v>
       </c>
       <c r="F247" s="7">
-        <v>0.046403</v>
+        <v>0.045632</v>
       </c>
       <c r="G247" s="7">
-        <v>0.254243</v>
+        <v>0.243599</v>
       </c>
       <c r="H247" s="7">
-        <v>0.173475</v>
+        <v>0.179012</v>
       </c>
       <c r="I247" s="7">
-        <v>0.513634</v>
+        <v>0.520051</v>
       </c>
       <c r="J247" s="7">
-        <v>3.228473</v>
+        <v>3.330666</v>
       </c>
       <c r="K247" s="7">
-        <v>8.53144</v>
+        <v>8.530419</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10750,25 @@
         <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>0.078547</v>
+        <v>0.061912</v>
       </c>
       <c r="F248" s="7">
-        <v>0.02469</v>
+        <v>0.024107</v>
       </c>
       <c r="G248" s="7">
-        <v>0.259336</v>
+        <v>0.24415099999999998</v>
       </c>
       <c r="H248" s="7">
-        <v>0.182817</v>
+        <v>0.188995</v>
       </c>
       <c r="I248" s="7">
-        <v>0.513848</v>
+        <v>0.5238349999999999</v>
       </c>
       <c r="J248" s="7">
-        <v>3.816913</v>
+        <v>3.9361040000000003</v>
       </c>
       <c r="K248" s="7">
-        <v>11.509849999999998</v>
+        <v>11.440494000000001</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10785,25 @@
         <v>6</v>
       </c>
       <c r="E249" s="7">
-        <v>0.085013</v>
+        <v>0.066644</v>
       </c>
       <c r="F249" s="7">
-        <v>-0.000567</v>
+        <v>-0.000624</v>
       </c>
       <c r="G249" s="7">
-        <v>0.265519</v>
+        <v>0.242747</v>
       </c>
       <c r="H249" s="7">
-        <v>0.190552</v>
+        <v>0.19728300000000001</v>
       </c>
       <c r="I249" s="7">
-        <v>0.47761200000000004</v>
+        <v>0.49648699999999996</v>
       </c>
       <c r="J249" s="7">
-        <v>3.453073</v>
+        <v>3.600519</v>
       </c>
       <c r="K249" s="7">
-        <v>14.086601</v>
+        <v>13.960355999999999</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10820,25 @@
         <v>3</v>
       </c>
       <c r="E250" s="7">
-        <v>0.056853999999999995</v>
+        <v>0.05206</v>
       </c>
       <c r="F250" s="7">
-        <v>0.080739</v>
+        <v>0.086229</v>
       </c>
       <c r="G250" s="7">
-        <v>0.20945599999999998</v>
+        <v>0.20666299999999999</v>
       </c>
       <c r="H250" s="7">
-        <v>0.159685</v>
+        <v>0.166549</v>
       </c>
       <c r="I250" s="7">
-        <v>0.45549599999999996</v>
+        <v>0.46225499999999997</v>
       </c>
       <c r="J250" s="7">
-        <v>2.030787</v>
+        <v>2.0983840000000002</v>
       </c>
       <c r="K250" s="7">
-        <v>5.620565</v>
+        <v>5.609502</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10855,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.093711</v>
+        <v>0.084748</v>
       </c>
       <c r="F251" s="7">
-        <v>0.082847</v>
+        <v>0.09626</v>
       </c>
       <c r="G251" s="7">
-        <v>0.25101</v>
+        <v>0.24561</v>
       </c>
       <c r="H251" s="7">
-        <v>0.21085399999999999</v>
+        <v>0.22324100000000002</v>
       </c>
       <c r="I251" s="7">
-        <v>0.5115</v>
+        <v>0.531219</v>
       </c>
       <c r="J251" s="7">
-        <v>3.07757</v>
+        <v>3.191637</v>
       </c>
       <c r="K251" s="7">
-        <v>9.886219</v>
+        <v>9.880699</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10890,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.10800599999999999</v>
+        <v>0.09717599999999998</v>
       </c>
       <c r="F252" s="7">
-        <v>0.080653</v>
+        <v>0.096021</v>
       </c>
       <c r="G252" s="7">
-        <v>0.259274</v>
+        <v>0.25234</v>
       </c>
       <c r="H252" s="7">
-        <v>0.226659</v>
+        <v>0.24089300000000002</v>
       </c>
       <c r="I252" s="7">
-        <v>0.521797</v>
+        <v>0.5479569999999999</v>
       </c>
       <c r="J252" s="7">
-        <v>3.276974</v>
+        <v>3.430889</v>
       </c>
       <c r="K252" s="7">
-        <v>10.969453000000001</v>
+        <v>10.972627</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10925,25 @@
         <v>4</v>
       </c>
       <c r="E253" s="7">
-        <v>0.043972</v>
+        <v>0.022401</v>
       </c>
       <c r="F253" s="7">
-        <v>-0.001473</v>
+        <v>-0.002875</v>
       </c>
       <c r="G253" s="7">
-        <v>0.145094</v>
+        <v>0.136623</v>
       </c>
       <c r="H253" s="7">
-        <v>0.057020999999999995</v>
+        <v>0.057645</v>
       </c>
       <c r="I253" s="7">
-        <v>0.37975200000000003</v>
+        <v>0.370379</v>
       </c>
       <c r="J253" s="7">
-        <v>1.820188</v>
+        <v>1.810677</v>
       </c>
       <c r="K253" s="7">
-        <v>4.988285</v>
+        <v>4.975395</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10960,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.057367999999999995</v>
+        <v>0.044707</v>
       </c>
       <c r="F254" s="7">
-        <v>0.017065</v>
+        <v>0.025091000000000002</v>
       </c>
       <c r="G254" s="7">
-        <v>0.230138</v>
+        <v>0.228039</v>
       </c>
       <c r="H254" s="7">
-        <v>0.156422</v>
+        <v>0.15982100000000002</v>
       </c>
       <c r="I254" s="7">
-        <v>0.531405</v>
+        <v>0.533797</v>
       </c>
       <c r="J254" s="7">
-        <v>2.853891</v>
+        <v>2.9190679999999998</v>
       </c>
       <c r="K254" s="7">
-        <v>6.104901999999999</v>
+        <v>6.079243</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +10995,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.040674</v>
+        <v>0.030993</v>
       </c>
       <c r="F255" s="7">
-        <v>0.018641</v>
+        <v>0.030749</v>
       </c>
       <c r="G255" s="7">
-        <v>0.215883</v>
+        <v>0.21495799999999998</v>
       </c>
       <c r="H255" s="7">
-        <v>0.141596</v>
+        <v>0.145239</v>
       </c>
       <c r="I255" s="7">
-        <v>0.507713</v>
+        <v>0.510672</v>
       </c>
       <c r="J255" s="7">
-        <v>2.791776</v>
+        <v>2.8371269999999997</v>
       </c>
       <c r="K255" s="7">
-        <v>5.267256</v>
+        <v>5.258972</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11030,25 @@
         <v>5</v>
       </c>
       <c r="E256" s="7">
-        <v>0.075883</v>
+        <v>0.060712999999999996</v>
       </c>
       <c r="F256" s="7">
-        <v>0.016628</v>
+        <v>0.023895</v>
       </c>
       <c r="G256" s="7">
-        <v>0.25093499999999996</v>
+        <v>0.243502</v>
       </c>
       <c r="H256" s="7">
-        <v>0.178104</v>
+        <v>0.181903</v>
       </c>
       <c r="I256" s="7">
-        <v>0.559032</v>
+        <v>0.562267</v>
       </c>
       <c r="J256" s="7">
-        <v>2.90644</v>
+        <v>2.9974860000000003</v>
       </c>
       <c r="K256" s="7">
-        <v>7.41715</v>
+        <v>7.354738</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11065,25 @@
         <v>6</v>
       </c>
       <c r="E257" s="7">
-        <v>-0.000065</v>
+        <v>-0.012782</v>
       </c>
       <c r="F257" s="7">
-        <v>-0.107171</v>
+        <v>-0.081023</v>
       </c>
       <c r="G257" s="7">
-        <v>0.171688</v>
+        <v>0.18855899999999998</v>
       </c>
       <c r="H257" s="7">
-        <v>0.06606200000000001</v>
+        <v>0.071834</v>
       </c>
       <c r="I257" s="7">
-        <v>0.583704</v>
+        <v>0.603352</v>
       </c>
       <c r="J257" s="7">
-        <v>4.037821</v>
+        <v>4.064982</v>
       </c>
       <c r="K257" s="7">
-        <v>13.763669</v>
+        <v>13.610133000000001</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11100,25 @@
         <v>2</v>
       </c>
       <c r="E258" s="7">
-        <v>0.034211</v>
+        <v>0.031103000000000002</v>
       </c>
       <c r="F258" s="7">
-        <v>0.085786</v>
+        <v>0.089124</v>
       </c>
       <c r="G258" s="7">
-        <v>0.191847</v>
+        <v>0.191192</v>
       </c>
       <c r="H258" s="7">
-        <v>0.13897700000000002</v>
+        <v>0.14455199999999999</v>
       </c>
       <c r="I258" s="7">
-        <v>0.430666</v>
+        <v>0.431256</v>
       </c>
       <c r="J258" s="7">
-        <v>2.3865190000000003</v>
+        <v>2.4443520000000003</v>
       </c>
       <c r="K258" s="7">
-        <v>4.45637</v>
+        <v>4.473394</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11135,25 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.104242</v>
+        <v>0.06667200000000001</v>
       </c>
       <c r="F259" s="7">
-        <v>-0.012362</v>
+        <v>0.007068</v>
       </c>
       <c r="G259" s="7">
-        <v>0.18665299999999999</v>
+        <v>0.181871</v>
       </c>
       <c r="H259" s="7">
-        <v>0.108976</v>
+        <v>0.112869</v>
       </c>
       <c r="I259" s="7">
-        <v>0.620695</v>
+        <v>0.6169319999999999</v>
       </c>
       <c r="J259" s="7">
-        <v>4.603324</v>
+        <v>4.734407</v>
       </c>
       <c r="K259" s="7">
-        <v>20.340123000000002</v>
+        <v>20.156475</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,10 +11170,10 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.000199</v>
+        <v>-0.012159999999999999</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.060144</v>
+        <v>-0.064282</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -11195,22 +11195,22 @@
         <v>3</v>
       </c>
       <c r="E261" s="7">
-        <v>0.063697</v>
+        <v>0.058818</v>
       </c>
       <c r="F261" s="7">
-        <v>0.08318400000000001</v>
+        <v>0.08759299999999999</v>
       </c>
       <c r="G261" s="7">
-        <v>0.237571</v>
+        <v>0.235687</v>
       </c>
       <c r="H261" s="7">
-        <v>0.171934</v>
+        <v>0.17721</v>
       </c>
       <c r="I261" s="7">
-        <v>0.513078</v>
+        <v>0.515343</v>
       </c>
       <c r="J261" s="7">
-        <v>2.234025</v>
+        <v>2.301894</v>
       </c>
       <c r="K261" s="7"/>
     </row>
@@ -11228,22 +11228,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.031570999999999995</v>
+        <v>0.022135</v>
       </c>
       <c r="F262" s="7">
-        <v>0.05075</v>
+        <v>0.046237</v>
       </c>
       <c r="G262" s="7">
-        <v>0.14695</v>
+        <v>0.13662000000000002</v>
       </c>
       <c r="H262" s="7">
-        <v>0.07466300000000001</v>
+        <v>0.07178</v>
       </c>
       <c r="I262" s="7">
-        <v>0.508272</v>
+        <v>0.49018999999999996</v>
       </c>
       <c r="J262" s="7">
-        <v>2.7308640000000004</v>
+        <v>2.735643</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11261,19 +11261,19 @@
         <v>5</v>
       </c>
       <c r="E263" s="7">
-        <v>0.088686</v>
+        <v>0.076237</v>
       </c>
       <c r="F263" s="7">
-        <v>-0.030796999999999998</v>
+        <v>-0.021092</v>
       </c>
       <c r="G263" s="7">
-        <v>0.246467</v>
+        <v>0.241901</v>
       </c>
       <c r="H263" s="7">
-        <v>0.17397200000000002</v>
+        <v>0.17651499999999998</v>
       </c>
       <c r="I263" s="7">
-        <v>0.4385</v>
+        <v>0.44191600000000003</v>
       </c>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11292,22 +11292,22 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.172422</v>
+        <v>0.128004</v>
       </c>
       <c r="F264" s="7">
-        <v>0.117483</v>
+        <v>0.109606</v>
       </c>
       <c r="G264" s="7">
-        <v>0.194749</v>
+        <v>0.162586</v>
       </c>
       <c r="H264" s="7">
-        <v>0.20598</v>
+        <v>0.194494</v>
       </c>
       <c r="I264" s="7">
-        <v>0.513795</v>
+        <v>0.485392</v>
       </c>
       <c r="J264" s="7">
-        <v>3.312087</v>
+        <v>3.53065</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11325,19 +11325,19 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.035752</v>
+        <v>0.032663000000000005</v>
       </c>
       <c r="F265" s="7">
-        <v>0.068686</v>
+        <v>0.06514</v>
       </c>
       <c r="G265" s="7">
-        <v>0.16802</v>
+        <v>0.16226</v>
       </c>
       <c r="H265" s="7">
-        <v>0.13128399999999998</v>
+        <v>0.134022</v>
       </c>
       <c r="I265" s="7">
-        <v>0.279221</v>
+        <v>0.275437</v>
       </c>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
@@ -11356,19 +11356,19 @@
         <v>2</v>
       </c>
       <c r="E266" s="7">
-        <v>0.031675</v>
+        <v>0.029609999999999997</v>
       </c>
       <c r="F266" s="7">
-        <v>0.095983</v>
+        <v>0.09822499999999999</v>
       </c>
       <c r="G266" s="7">
-        <v>0.206314</v>
+        <v>0.20627199999999998</v>
       </c>
       <c r="H266" s="7">
-        <v>0.13050499999999998</v>
+        <v>0.135168</v>
       </c>
       <c r="I266" s="7">
-        <v>0.47869999999999996</v>
+        <v>0.480507</v>
       </c>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
@@ -11387,22 +11387,22 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.033908</v>
+        <v>0.024585</v>
       </c>
       <c r="F267" s="7">
-        <v>0.048732</v>
+        <v>0.055573</v>
       </c>
       <c r="G267" s="7">
-        <v>0.191855</v>
+        <v>0.182837</v>
       </c>
       <c r="H267" s="7">
-        <v>0.122348</v>
+        <v>0.124071</v>
       </c>
       <c r="I267" s="7">
-        <v>0.480447</v>
+        <v>0.47874099999999997</v>
       </c>
       <c r="J267" s="7">
-        <v>3.086655</v>
+        <v>3.085846</v>
       </c>
       <c r="K267" s="7"/>
     </row>
@@ -11420,22 +11420,22 @@
         <v>5</v>
       </c>
       <c r="E268" s="7">
-        <v>0.045481999999999995</v>
+        <v>0.032844000000000005</v>
       </c>
       <c r="F268" s="7">
-        <v>0.008602</v>
+        <v>0.000696</v>
       </c>
       <c r="G268" s="7">
-        <v>0.1925</v>
+        <v>0.171581</v>
       </c>
       <c r="H268" s="7">
-        <v>0.126825</v>
+        <v>0.12892699999999999</v>
       </c>
       <c r="I268" s="7">
-        <v>0.570343</v>
+        <v>0.577488</v>
       </c>
       <c r="J268" s="7">
-        <v>2.8728070000000003</v>
+        <v>2.907957</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11453,19 +11453,19 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.058995</v>
+        <v>0.048294</v>
       </c>
       <c r="F269" s="7">
-        <v>0.063032</v>
+        <v>0.073645</v>
       </c>
       <c r="G269" s="7">
-        <v>0.192082</v>
+        <v>0.18711</v>
       </c>
       <c r="H269" s="7">
-        <v>0.12389599999999999</v>
+        <v>0.134938</v>
       </c>
       <c r="I269" s="7">
-        <v>0.489645</v>
+        <v>0.49792299999999995</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11484,19 +11484,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.08933400000000001</v>
+        <v>0.079983</v>
       </c>
       <c r="F270" s="7">
-        <v>0.082037</v>
+        <v>0.084413</v>
       </c>
       <c r="G270" s="7">
-        <v>0.159719</v>
+        <v>0.15906499999999998</v>
       </c>
       <c r="H270" s="7">
-        <v>0.152512</v>
+        <v>0.156041</v>
       </c>
       <c r="I270" s="7">
-        <v>0.497657</v>
+        <v>0.481857</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11515,19 +11515,19 @@
         <v>4</v>
       </c>
       <c r="E271" s="7">
-        <v>0.06381</v>
+        <v>0.053684</v>
       </c>
       <c r="F271" s="7">
-        <v>0.05098900000000001</v>
+        <v>0.047401</v>
       </c>
       <c r="G271" s="7">
-        <v>0.24442</v>
+        <v>0.251484</v>
       </c>
       <c r="H271" s="7">
-        <v>0.182031</v>
+        <v>0.190373</v>
       </c>
       <c r="I271" s="7">
-        <v>0.363946</v>
+        <v>0.353889</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11546,19 +11546,19 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.050136</v>
+        <v>0.039489</v>
       </c>
       <c r="F272" s="7">
-        <v>0.064377</v>
+        <v>0.066587</v>
       </c>
       <c r="G272" s="7">
-        <v>0.216159</v>
+        <v>0.235548</v>
       </c>
       <c r="H272" s="7">
-        <v>0.18067599999999998</v>
+        <v>0.18356899999999998</v>
       </c>
       <c r="I272" s="7">
-        <v>0.326493</v>
+        <v>0.343844</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11577,19 +11577,19 @@
         <v>6</v>
       </c>
       <c r="E273" s="7">
-        <v>0.142547</v>
+        <v>0.133629</v>
       </c>
       <c r="F273" s="7">
-        <v>0.143404</v>
+        <v>0.151435</v>
       </c>
       <c r="G273" s="7">
-        <v>0.269253</v>
+        <v>0.24207499999999998</v>
       </c>
       <c r="H273" s="7">
-        <v>0.311849</v>
+        <v>0.318389</v>
       </c>
       <c r="I273" s="7">
-        <v>0.52085</v>
+        <v>0.526909</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11608,22 +11608,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.034872</v>
+        <v>0.024869</v>
       </c>
       <c r="F274" s="7">
-        <v>0.010237000000000001</v>
+        <v>0.017147</v>
       </c>
       <c r="G274" s="7">
-        <v>0.18328</v>
+        <v>0.16611499999999998</v>
       </c>
       <c r="H274" s="7">
-        <v>0.115305</v>
+        <v>0.11877499999999999</v>
       </c>
       <c r="I274" s="7">
-        <v>0.501691</v>
+        <v>0.506086</v>
       </c>
       <c r="J274" s="7">
-        <v>3.031278</v>
+        <v>3.03849</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -11641,25 +11641,25 @@
         <v>5</v>
       </c>
       <c r="E275" s="7">
-        <v>0.086773</v>
+        <v>0.074199</v>
       </c>
       <c r="F275" s="7">
-        <v>0.09040200000000001</v>
+        <v>0.100373</v>
       </c>
       <c r="G275" s="7">
-        <v>0.295083</v>
+        <v>0.28733000000000003</v>
       </c>
       <c r="H275" s="7">
-        <v>0.21162</v>
+        <v>0.21807300000000002</v>
       </c>
       <c r="I275" s="7">
-        <v>0.568013</v>
+        <v>0.580157</v>
       </c>
       <c r="J275" s="7">
-        <v>2.541287</v>
+        <v>2.63586</v>
       </c>
       <c r="K275" s="7">
-        <v>6.57981</v>
+        <v>6.588015</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11676,25 +11676,25 @@
         <v>2</v>
       </c>
       <c r="E276" s="7">
-        <v>0.03199</v>
+        <v>0.029168</v>
       </c>
       <c r="F276" s="7">
-        <v>0.086089</v>
+        <v>0.089215</v>
       </c>
       <c r="G276" s="7">
-        <v>0.19893899999999998</v>
+        <v>0.198402</v>
       </c>
       <c r="H276" s="7">
-        <v>0.12543200000000002</v>
+        <v>0.129786</v>
       </c>
       <c r="I276" s="7">
-        <v>0.473473</v>
+        <v>0.47092</v>
       </c>
       <c r="J276" s="7">
-        <v>2.197247</v>
+        <v>2.205763</v>
       </c>
       <c r="K276" s="7">
-        <v>4.131114</v>
+        <v>4.141686</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11711,25 +11711,25 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.05742</v>
+        <v>0.037452</v>
       </c>
       <c r="F277" s="7">
-        <v>0.008961</v>
+        <v>0.014454</v>
       </c>
       <c r="G277" s="7">
-        <v>0.107056</v>
+        <v>0.104617</v>
       </c>
       <c r="H277" s="7">
-        <v>0.041871</v>
+        <v>0.042303</v>
       </c>
       <c r="I277" s="7">
-        <v>0.30118500000000004</v>
+        <v>0.29408</v>
       </c>
       <c r="J277" s="7">
-        <v>1.749834</v>
+        <v>1.7480879999999999</v>
       </c>
       <c r="K277" s="7">
-        <v>5.159154999999999</v>
+        <v>5.094568</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11746,25 +11746,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.096298</v>
+        <v>0.07980000000000001</v>
       </c>
       <c r="F278" s="7">
-        <v>-0.010055000000000001</v>
+        <v>-0.011975</v>
       </c>
       <c r="G278" s="7">
-        <v>0.22514800000000001</v>
+        <v>0.200259</v>
       </c>
       <c r="H278" s="7">
-        <v>0.179292</v>
+        <v>0.186053</v>
       </c>
       <c r="I278" s="7">
-        <v>0.419009</v>
+        <v>0.441865</v>
       </c>
       <c r="J278" s="7">
-        <v>2.456714</v>
+        <v>2.5756330000000003</v>
       </c>
       <c r="K278" s="7">
-        <v>12.481174000000001</v>
+        <v>12.375649000000001</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11781,25 +11781,25 @@
         <v>4</v>
       </c>
       <c r="E279" s="7">
-        <v>0.057629</v>
+        <v>0.034496</v>
       </c>
       <c r="F279" s="7">
-        <v>0.000241</v>
+        <v>0.00145</v>
       </c>
       <c r="G279" s="7">
-        <v>0.16097999999999998</v>
+        <v>0.153514</v>
       </c>
       <c r="H279" s="7">
-        <v>0.039812</v>
+        <v>0.040512</v>
       </c>
       <c r="I279" s="7">
-        <v>0.39775799999999994</v>
+        <v>0.379944</v>
       </c>
       <c r="J279" s="7">
-        <v>1.6438480000000002</v>
+        <v>1.678491</v>
       </c>
       <c r="K279" s="7">
-        <v>3.633433</v>
+        <v>3.614404</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11816,25 +11816,25 @@
         <v>6</v>
       </c>
       <c r="E280" s="7">
-        <v>0.08708199999999999</v>
+        <v>0.08566000000000001</v>
       </c>
       <c r="F280" s="7">
-        <v>0.07609300000000001</v>
+        <v>0.09204000000000001</v>
       </c>
       <c r="G280" s="7">
-        <v>0.240059</v>
+        <v>0.237339</v>
       </c>
       <c r="H280" s="7">
-        <v>0.192903</v>
+        <v>0.20517600000000003</v>
       </c>
       <c r="I280" s="7">
-        <v>0.484165</v>
+        <v>0.499201</v>
       </c>
       <c r="J280" s="7">
-        <v>2.706583</v>
+        <v>2.835034</v>
       </c>
       <c r="K280" s="7">
-        <v>10.056523</v>
+        <v>10.05203</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11851,25 +11851,25 @@
         <v>3</v>
       </c>
       <c r="E281" s="7">
-        <v>0.041456</v>
+        <v>0.035529000000000005</v>
       </c>
       <c r="F281" s="7">
-        <v>0.075944</v>
+        <v>0.07821</v>
       </c>
       <c r="G281" s="7">
-        <v>0.201206</v>
+        <v>0.194015</v>
       </c>
       <c r="H281" s="7">
-        <v>0.137685</v>
+        <v>0.141012</v>
       </c>
       <c r="I281" s="7">
-        <v>0.471254</v>
+        <v>0.46695</v>
       </c>
       <c r="J281" s="7">
-        <v>2.954524</v>
+        <v>2.9609989999999997</v>
       </c>
       <c r="K281" s="7">
-        <v>5.288651</v>
+        <v>5.294957</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11886,25 +11886,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.03487</v>
+        <v>0.026217</v>
       </c>
       <c r="F282" s="7">
-        <v>0.065791</v>
+        <v>0.066341</v>
       </c>
       <c r="G282" s="7">
-        <v>0.180409</v>
+        <v>0.17836</v>
       </c>
       <c r="H282" s="7">
-        <v>0.098697</v>
+        <v>0.10174200000000001</v>
       </c>
       <c r="I282" s="7">
-        <v>0.454694</v>
+        <v>0.447382</v>
       </c>
       <c r="J282" s="7">
-        <v>2.284549</v>
+        <v>2.299001</v>
       </c>
       <c r="K282" s="7">
-        <v>4.203958</v>
+        <v>4.202217999999999</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11921,25 +11921,25 @@
         <v>5</v>
       </c>
       <c r="E283" s="7">
-        <v>0.042054</v>
+        <v>0.028681</v>
       </c>
       <c r="F283" s="7">
-        <v>0.027789</v>
+        <v>0.027111</v>
       </c>
       <c r="G283" s="7">
-        <v>0.074739</v>
+        <v>0.070759</v>
       </c>
       <c r="H283" s="7">
-        <v>0.030127</v>
+        <v>0.031303</v>
       </c>
       <c r="I283" s="7">
-        <v>0.277094</v>
+        <v>0.27456800000000003</v>
       </c>
       <c r="J283" s="7">
-        <v>1.9297630000000001</v>
+        <v>1.9305459999999999</v>
       </c>
       <c r="K283" s="7">
-        <v>5.888524</v>
+        <v>5.797496</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11956,25 +11956,25 @@
         <v>3</v>
       </c>
       <c r="E284" s="7">
-        <v>0.036535000000000005</v>
+        <v>0.029757</v>
       </c>
       <c r="F284" s="7">
-        <v>0.040581</v>
+        <v>0.045466</v>
       </c>
       <c r="G284" s="7">
-        <v>0.21405200000000002</v>
+        <v>0.209179</v>
       </c>
       <c r="H284" s="7">
-        <v>0.057156000000000005</v>
+        <v>0.060832</v>
       </c>
       <c r="I284" s="7">
-        <v>0.42743200000000003</v>
+        <v>0.424919</v>
       </c>
       <c r="J284" s="7">
-        <v>1.964447</v>
+        <v>1.971258</v>
       </c>
       <c r="K284" s="7">
-        <v>3.614087</v>
+        <v>3.621812</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11991,25 +11991,25 @@
         <v>5</v>
       </c>
       <c r="E285" s="7">
-        <v>0.049815</v>
+        <v>0.042899</v>
       </c>
       <c r="F285" s="7">
-        <v>0.0603</v>
+        <v>0.060651000000000004</v>
       </c>
       <c r="G285" s="7">
-        <v>0.237044</v>
+        <v>0.235193</v>
       </c>
       <c r="H285" s="7">
-        <v>0.15535</v>
+        <v>0.161915</v>
       </c>
       <c r="I285" s="7">
-        <v>0.519481</v>
+        <v>0.527212</v>
       </c>
       <c r="J285" s="7">
-        <v>2.656185</v>
+        <v>2.709822</v>
       </c>
       <c r="K285" s="7">
-        <v>9.343699</v>
+        <v>9.328168</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12026,25 +12026,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>-0.009599</v>
+        <v>-0.019748</v>
       </c>
       <c r="F286" s="7">
-        <v>-0.109302</v>
+        <v>-0.093102</v>
       </c>
       <c r="G286" s="7">
-        <v>0.137359</v>
+        <v>0.176345</v>
       </c>
       <c r="H286" s="7">
-        <v>0.03469</v>
+        <v>0.041429</v>
       </c>
       <c r="I286" s="7">
-        <v>0.539803</v>
+        <v>0.559678</v>
       </c>
       <c r="J286" s="7">
-        <v>4.078251</v>
+        <v>4.109262</v>
       </c>
       <c r="K286" s="7">
-        <v>13.762991</v>
+        <v>13.634942</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12061,25 +12061,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.057460000000000004</v>
+        <v>0.053663999999999996</v>
       </c>
       <c r="F287" s="7">
-        <v>0.086351</v>
+        <v>0.093543</v>
       </c>
       <c r="G287" s="7">
-        <v>0.252815</v>
+        <v>0.252168</v>
       </c>
       <c r="H287" s="7">
-        <v>0.166141</v>
+        <v>0.17378799999999997</v>
       </c>
       <c r="I287" s="7">
-        <v>0.487854</v>
+        <v>0.494674</v>
       </c>
       <c r="J287" s="7">
-        <v>1.352026</v>
+        <v>1.4008209999999999</v>
       </c>
       <c r="K287" s="7">
-        <v>3.721393</v>
+        <v>3.7269940000000004</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12096,25 +12096,25 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0.07048700000000001</v>
+        <v>0.069386</v>
       </c>
       <c r="F288" s="7">
-        <v>0.011573</v>
+        <v>0.012931999999999999</v>
       </c>
       <c r="G288" s="7">
-        <v>0.259513</v>
+        <v>0.25142</v>
       </c>
       <c r="H288" s="7">
-        <v>0.152922</v>
+        <v>0.16389800000000002</v>
       </c>
       <c r="I288" s="7">
-        <v>0.511582</v>
+        <v>0.530114</v>
       </c>
       <c r="J288" s="7">
-        <v>2.4588069999999997</v>
+        <v>2.536496</v>
       </c>
       <c r="K288" s="7">
-        <v>10.326259</v>
+        <v>10.319306999999998</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12131,25 +12131,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.015645</v>
+        <v>0.001031</v>
       </c>
       <c r="F289" s="7">
-        <v>-0.130459</v>
+        <v>-0.073934</v>
       </c>
       <c r="G289" s="7">
-        <v>0.252585</v>
+        <v>0.269578</v>
       </c>
       <c r="H289" s="7">
-        <v>0.08255499999999999</v>
+        <v>0.08905099999999999</v>
       </c>
       <c r="I289" s="7">
-        <v>0.7304609999999999</v>
+        <v>0.756524</v>
       </c>
       <c r="J289" s="7">
-        <v>4.114833</v>
+        <v>4.136151</v>
       </c>
       <c r="K289" s="7">
-        <v>8.254083000000001</v>
+        <v>8.285833</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12166,25 +12166,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.093474</v>
+        <v>0.105192</v>
       </c>
       <c r="F290" s="7">
-        <v>0.014917</v>
+        <v>0.022427000000000002</v>
       </c>
       <c r="G290" s="7">
-        <v>0.255817</v>
+        <v>0.238721</v>
       </c>
       <c r="H290" s="7">
-        <v>0.20711500000000002</v>
+        <v>0.21892399999999998</v>
       </c>
       <c r="I290" s="7">
-        <v>0.397002</v>
+        <v>0.416523</v>
       </c>
       <c r="J290" s="7">
-        <v>2.5544</v>
+        <v>2.659955</v>
       </c>
       <c r="K290" s="7">
-        <v>12.603361999999999</v>
+        <v>12.56048</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12201,25 +12201,25 @@
         <v>4</v>
       </c>
       <c r="E291" s="7">
-        <v>0.049599000000000004</v>
+        <v>0.042661</v>
       </c>
       <c r="F291" s="7">
-        <v>0.059396000000000004</v>
+        <v>0.069352</v>
       </c>
       <c r="G291" s="7">
-        <v>0.22776700000000002</v>
+        <v>0.226274</v>
       </c>
       <c r="H291" s="7">
-        <v>0.16208100000000003</v>
+        <v>0.168537</v>
       </c>
       <c r="I291" s="7">
-        <v>0.5548190000000001</v>
+        <v>0.556968</v>
       </c>
       <c r="J291" s="7">
-        <v>2.4084149999999998</v>
+        <v>2.499765</v>
       </c>
       <c r="K291" s="7">
-        <v>6.312477</v>
+        <v>6.316456</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12236,25 +12236,25 @@
         <v>5</v>
       </c>
       <c r="E292" s="7">
-        <v>0.092439</v>
+        <v>0.09329000000000001</v>
       </c>
       <c r="F292" s="7">
-        <v>0.053621</v>
+        <v>0.06879400000000001</v>
       </c>
       <c r="G292" s="7">
-        <v>0.237003</v>
+        <v>0.234599</v>
       </c>
       <c r="H292" s="7">
-        <v>0.178247</v>
+        <v>0.19077200000000002</v>
       </c>
       <c r="I292" s="7">
-        <v>0.510312</v>
+        <v>0.520456</v>
       </c>
       <c r="J292" s="7">
-        <v>2.7473289999999997</v>
+        <v>2.865836</v>
       </c>
       <c r="K292" s="7">
-        <v>8.423343</v>
+        <v>8.44862</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12271,25 +12271,25 @@
         <v>4</v>
       </c>
       <c r="E293" s="7">
-        <v>0.046594</v>
+        <v>0.040911</v>
       </c>
       <c r="F293" s="7">
-        <v>0.057926000000000005</v>
+        <v>0.062948</v>
       </c>
       <c r="G293" s="7">
-        <v>0.22662500000000002</v>
+        <v>0.22580999999999998</v>
       </c>
       <c r="H293" s="7">
-        <v>0.11760999999999999</v>
+        <v>0.12496800000000001</v>
       </c>
       <c r="I293" s="7">
-        <v>0.407864</v>
+        <v>0.41708799999999996</v>
       </c>
       <c r="J293" s="7">
-        <v>1.424605</v>
+        <v>1.4763460000000002</v>
       </c>
       <c r="K293" s="7">
-        <v>4.1204149999999995</v>
+        <v>4.139465</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12306,25 +12306,25 @@
         <v>4</v>
       </c>
       <c r="E294" s="7">
-        <v>0.040938999999999996</v>
+        <v>0.02239</v>
       </c>
       <c r="F294" s="7">
-        <v>0.000196</v>
+        <v>-0.0006090000000000001</v>
       </c>
       <c r="G294" s="7">
-        <v>0.191966</v>
+        <v>0.183247</v>
       </c>
       <c r="H294" s="7">
-        <v>0.045405</v>
+        <v>0.045473</v>
       </c>
       <c r="I294" s="7">
-        <v>0.393746</v>
+        <v>0.38315600000000005</v>
       </c>
       <c r="J294" s="7">
-        <v>1.6961519999999999</v>
+        <v>1.7056989999999999</v>
       </c>
       <c r="K294" s="7">
-        <v>4.795962</v>
+        <v>4.779567</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12341,25 +12341,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.10940899999999999</v>
+        <v>0.09350199999999999</v>
       </c>
       <c r="F295" s="7">
-        <v>0.038439</v>
+        <v>0.043827</v>
       </c>
       <c r="G295" s="7">
-        <v>0.311346</v>
+        <v>0.297201</v>
       </c>
       <c r="H295" s="7">
-        <v>0.24522</v>
+        <v>0.24895399999999998</v>
       </c>
       <c r="I295" s="7">
-        <v>0.5586760000000001</v>
+        <v>0.574895</v>
       </c>
       <c r="J295" s="7">
-        <v>3.624321</v>
+        <v>3.718367</v>
       </c>
       <c r="K295" s="7">
-        <v>15.79684</v>
+        <v>15.619819999999999</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12376,25 +12376,25 @@
         <v>5</v>
       </c>
       <c r="E296" s="7">
-        <v>0.09579399999999999</v>
+        <v>0.080894</v>
       </c>
       <c r="F296" s="7">
-        <v>0.051721</v>
+        <v>0.061219</v>
       </c>
       <c r="G296" s="7">
-        <v>0.314798</v>
+        <v>0.303491</v>
       </c>
       <c r="H296" s="7">
-        <v>0.256295</v>
+        <v>0.25778199999999996</v>
       </c>
       <c r="I296" s="7">
-        <v>0.572211</v>
+        <v>0.581473</v>
       </c>
       <c r="J296" s="7">
-        <v>3.277464</v>
+        <v>3.332332</v>
       </c>
       <c r="K296" s="7">
-        <v>10.860083999999999</v>
+        <v>10.752422999999999</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12411,25 +12411,25 @@
         <v>4</v>
       </c>
       <c r="E297" s="7">
-        <v>0.085978</v>
+        <v>0.06976399999999999</v>
       </c>
       <c r="F297" s="7">
-        <v>0.045191999999999996</v>
+        <v>0.055267</v>
       </c>
       <c r="G297" s="7">
-        <v>0.294147</v>
+        <v>0.28366199999999997</v>
       </c>
       <c r="H297" s="7">
-        <v>0.221995</v>
+        <v>0.222447</v>
       </c>
       <c r="I297" s="7">
-        <v>0.578111</v>
+        <v>0.578997</v>
       </c>
       <c r="J297" s="7">
-        <v>3.261513</v>
+        <v>3.3124740000000004</v>
       </c>
       <c r="K297" s="7">
-        <v>9.772770000000001</v>
+        <v>9.69486</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12446,25 +12446,25 @@
         <v>2</v>
       </c>
       <c r="E298" s="7">
-        <v>0.048852</v>
+        <v>0.034366</v>
       </c>
       <c r="F298" s="7">
-        <v>0.08459699999999999</v>
+        <v>0.08551500000000001</v>
       </c>
       <c r="G298" s="7">
-        <v>0.218751</v>
+        <v>0.21578</v>
       </c>
       <c r="H298" s="7">
-        <v>0.137439</v>
+        <v>0.1405</v>
       </c>
       <c r="I298" s="7">
-        <v>0.512316</v>
+        <v>0.509595</v>
       </c>
       <c r="J298" s="7">
-        <v>2.818442</v>
+        <v>2.8312329999999997</v>
       </c>
       <c r="K298" s="7">
-        <v>5.100975</v>
+        <v>5.106087</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12481,25 +12481,25 @@
         <v>5</v>
       </c>
       <c r="E299" s="7">
-        <v>0.10294</v>
+        <v>0.08788</v>
       </c>
       <c r="F299" s="7">
-        <v>0.090465</v>
+        <v>0.098019</v>
       </c>
       <c r="G299" s="7">
-        <v>0.335351</v>
+        <v>0.327593</v>
       </c>
       <c r="H299" s="7">
-        <v>0.265931</v>
+        <v>0.269849</v>
       </c>
       <c r="I299" s="7">
-        <v>0.655571</v>
+        <v>0.660177</v>
       </c>
       <c r="J299" s="7">
-        <v>3.167848</v>
+        <v>3.26102</v>
       </c>
       <c r="K299" s="7">
-        <v>9.785795</v>
+        <v>9.742981</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12516,25 +12516,25 @@
         <v>6</v>
       </c>
       <c r="E300" s="7">
-        <v>0.107451</v>
+        <v>0.093597</v>
       </c>
       <c r="F300" s="7">
-        <v>0.078449</v>
+        <v>0.090559</v>
       </c>
       <c r="G300" s="7">
-        <v>0.344632</v>
+        <v>0.33720799999999995</v>
       </c>
       <c r="H300" s="7">
-        <v>0.27824000000000004</v>
+        <v>0.282846</v>
       </c>
       <c r="I300" s="7">
-        <v>0.7021850000000001</v>
+        <v>0.709669</v>
       </c>
       <c r="J300" s="7">
-        <v>3.378639</v>
+        <v>3.506888</v>
       </c>
       <c r="K300" s="7">
-        <v>12.436976999999999</v>
+        <v>12.365145</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12551,25 +12551,25 @@
         <v>6</v>
       </c>
       <c r="E301" s="7">
-        <v>0.10665699999999999</v>
+        <v>0.097817</v>
       </c>
       <c r="F301" s="7">
-        <v>0.08354400000000001</v>
+        <v>0.102856</v>
       </c>
       <c r="G301" s="7">
-        <v>0.288998</v>
+        <v>0.282346</v>
       </c>
       <c r="H301" s="7">
-        <v>0.266268</v>
+        <v>0.282798</v>
       </c>
       <c r="I301" s="7">
-        <v>0.5482130000000001</v>
+        <v>0.5845859999999999</v>
       </c>
       <c r="J301" s="7">
-        <v>2.154173</v>
+        <v>2.3331749999999998</v>
       </c>
       <c r="K301" s="7">
-        <v>8.758412</v>
+        <v>8.692709</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12586,22 +12586,22 @@
         <v>4</v>
       </c>
       <c r="E302" s="7">
-        <v>0.194447</v>
+        <v>0.169599</v>
       </c>
       <c r="F302" s="7">
-        <v>0.16183399999999998</v>
+        <v>0.169786</v>
       </c>
       <c r="G302" s="7">
-        <v>0.246671</v>
+        <v>0.23058</v>
       </c>
       <c r="H302" s="7">
-        <v>0.240003</v>
+        <v>0.240322</v>
       </c>
       <c r="I302" s="7">
-        <v>0.6698770000000001</v>
+        <v>0.6507729999999999</v>
       </c>
       <c r="J302" s="7">
-        <v>3.562236</v>
+        <v>3.658721</v>
       </c>
       <c r="K302" s="7"/>
     </row>
@@ -12619,25 +12619,25 @@
         <v>5</v>
       </c>
       <c r="E303" s="7">
-        <v>0.122173</v>
+        <v>0.09077299999999999</v>
       </c>
       <c r="F303" s="7">
-        <v>0.039712</v>
+        <v>0.033658</v>
       </c>
       <c r="G303" s="7">
-        <v>0.274315</v>
+        <v>0.24752400000000002</v>
       </c>
       <c r="H303" s="7">
-        <v>0.183335</v>
+        <v>0.18190699999999999</v>
       </c>
       <c r="I303" s="7">
-        <v>0.511126</v>
+        <v>0.500294</v>
       </c>
       <c r="J303" s="7">
-        <v>2.617961</v>
+        <v>2.6895119999999997</v>
       </c>
       <c r="K303" s="7">
-        <v>11.627438</v>
+        <v>11.440776000000001</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12654,25 +12654,25 @@
         <v>6</v>
       </c>
       <c r="E304" s="7">
-        <v>0.026812999999999997</v>
+        <v>0.02176</v>
       </c>
       <c r="F304" s="7">
-        <v>0.035322</v>
+        <v>0.033367</v>
       </c>
       <c r="G304" s="7">
-        <v>0.081275</v>
+        <v>0.078988</v>
       </c>
       <c r="H304" s="7">
-        <v>0.048265</v>
+        <v>0.048270999999999994</v>
       </c>
       <c r="I304" s="7">
-        <v>0.23342300000000002</v>
+        <v>0.232267</v>
       </c>
       <c r="J304" s="7">
-        <v>1.800608</v>
+        <v>1.8024639999999998</v>
       </c>
       <c r="K304" s="7">
-        <v>5.656746000000001</v>
+        <v>5.56875</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12689,25 +12689,25 @@
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.07849</v>
+        <v>0.047967</v>
       </c>
       <c r="F305" s="7">
-        <v>0.00244</v>
+        <v>0.005299000000000001</v>
       </c>
       <c r="G305" s="7">
-        <v>0.17178000000000002</v>
+        <v>0.158556</v>
       </c>
       <c r="H305" s="7">
-        <v>0.08071400000000001</v>
+        <v>0.084842</v>
       </c>
       <c r="I305" s="7">
-        <v>0.475209</v>
+        <v>0.486282</v>
       </c>
       <c r="J305" s="7">
-        <v>2.329579</v>
+        <v>2.4107320000000003</v>
       </c>
       <c r="K305" s="7">
-        <v>7.609471</v>
+        <v>7.573665999999999</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12724,25 +12724,25 @@
         <v>3</v>
       </c>
       <c r="E306" s="7">
-        <v>0.041817</v>
+        <v>0.036668</v>
       </c>
       <c r="F306" s="7">
-        <v>0.076502</v>
+        <v>0.080844</v>
       </c>
       <c r="G306" s="7">
-        <v>0.207325</v>
+        <v>0.20613099999999998</v>
       </c>
       <c r="H306" s="7">
-        <v>0.140039</v>
+        <v>0.144393</v>
       </c>
       <c r="I306" s="7">
-        <v>0.46253</v>
+        <v>0.464133</v>
       </c>
       <c r="J306" s="7">
-        <v>1.9620339999999998</v>
+        <v>2.0008850000000002</v>
       </c>
       <c r="K306" s="7">
-        <v>5.252730000000001</v>
+        <v>5.251383</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12759,25 +12759,25 @@
         <v>3</v>
       </c>
       <c r="E307" s="7">
-        <v>0.036416</v>
+        <v>0.020510999999999998</v>
       </c>
       <c r="F307" s="7">
-        <v>0.011493999999999999</v>
+        <v>0.010661</v>
       </c>
       <c r="G307" s="7">
-        <v>0.13982</v>
+        <v>0.134741</v>
       </c>
       <c r="H307" s="7">
-        <v>0.033530000000000004</v>
+        <v>0.034185</v>
       </c>
       <c r="I307" s="7">
-        <v>0.39820900000000004</v>
+        <v>0.376734</v>
       </c>
       <c r="J307" s="7">
-        <v>1.009971</v>
+        <v>0.9971850000000001</v>
       </c>
       <c r="K307" s="7">
-        <v>2.120216</v>
+        <v>2.1146469999999997</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="924" uniqueCount="644">
   <si>
     <t>Rapor Bilgileri</t>
   </si>
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>04.05.2026 19:03:35</t>
+    <t>05.05.2026 18:23:33</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -1826,6 +1826,12 @@
   </si>
   <si>
     <t>TÜRKİYE HAYAT VE EMEKLİLİK A.Ş. KIYMETLİ MADENLER KATILIM EMEKLİLİK YATIRIM FONU</t>
+  </si>
+  <si>
+    <t>VGE</t>
+  </si>
+  <si>
+    <t>TÜRKİYE HAYAT VE EMEKLİLİK A.Ş. GÜMÜŞ KATILIM EMEKLİLİK YATIRIM FONU</t>
   </si>
   <si>
     <t>VGF</t>
@@ -2373,7 +2379,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K307"/>
+  <dimension ref="A1:K308"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -2402,7 +2408,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2454,25 +2460,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.039319</v>
+        <v>0.038917</v>
       </c>
       <c r="F6" s="7">
-        <v>0.030026</v>
+        <v>0.031488999999999996</v>
       </c>
       <c r="G6" s="7">
-        <v>0.189614</v>
+        <v>0.192413</v>
       </c>
       <c r="H6" s="7">
-        <v>0.10236</v>
+        <v>0.101935</v>
       </c>
       <c r="I6" s="7">
-        <v>0.452303</v>
+        <v>0.451742</v>
       </c>
       <c r="J6" s="7">
-        <v>2.225156</v>
+        <v>2.2222649999999997</v>
       </c>
       <c r="K6" s="7">
-        <v>5.683514</v>
+        <v>5.6765170000000005</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2489,25 +2495,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.103461</v>
+        <v>0.11784700000000001</v>
       </c>
       <c r="F7" s="7">
-        <v>0.050415</v>
+        <v>0.073898</v>
       </c>
       <c r="G7" s="7">
-        <v>0.12323</v>
+        <v>0.15137</v>
       </c>
       <c r="H7" s="7">
-        <v>0.087463</v>
+        <v>0.101639</v>
       </c>
       <c r="I7" s="7">
-        <v>0.471289</v>
+        <v>0.490469</v>
       </c>
       <c r="J7" s="7">
-        <v>2.807476</v>
+        <v>2.8901100000000004</v>
       </c>
       <c r="K7" s="7">
-        <v>5.632134</v>
+        <v>5.708324</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2524,25 +2530,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.022337</v>
+        <v>0.024689000000000003</v>
       </c>
       <c r="F8" s="7">
-        <v>0.002323</v>
+        <v>0.005453</v>
       </c>
       <c r="G8" s="7">
-        <v>0.136385</v>
+        <v>0.140285</v>
       </c>
       <c r="H8" s="7">
-        <v>0.044506</v>
+        <v>0.046908000000000005</v>
       </c>
       <c r="I8" s="7">
-        <v>0.383827</v>
+        <v>0.387009</v>
       </c>
       <c r="J8" s="7">
-        <v>1.742226</v>
+        <v>1.748124</v>
       </c>
       <c r="K8" s="7">
-        <v>3.5412090000000003</v>
+        <v>3.547851</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2559,25 +2565,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.076631</v>
+        <v>0.077171</v>
       </c>
       <c r="F9" s="7">
-        <v>0.045957</v>
+        <v>0.045554</v>
       </c>
       <c r="G9" s="7">
-        <v>0.282065</v>
+        <v>0.298551</v>
       </c>
       <c r="H9" s="7">
-        <v>0.245381</v>
+        <v>0.246006</v>
       </c>
       <c r="I9" s="7">
-        <v>0.557988</v>
+        <v>0.55877</v>
       </c>
       <c r="J9" s="7">
-        <v>3.165114</v>
+        <v>3.161962</v>
       </c>
       <c r="K9" s="7">
-        <v>10.338115</v>
+        <v>10.333897</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2594,25 +2600,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.022014</v>
+        <v>-0.02557</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.10042999999999999</v>
+        <v>-0.12457599999999999</v>
       </c>
       <c r="G10" s="7">
-        <v>0.15454</v>
+        <v>0.15655</v>
       </c>
       <c r="H10" s="7">
-        <v>0.032014</v>
+        <v>0.028262</v>
       </c>
       <c r="I10" s="7">
-        <v>0.518615</v>
+        <v>0.5130939999999999</v>
       </c>
       <c r="J10" s="7">
-        <v>4.035966</v>
+        <v>3.931222</v>
       </c>
       <c r="K10" s="7">
-        <v>13.435705</v>
+        <v>13.260193</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2629,25 +2635,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.098605</v>
+        <v>0.096413</v>
       </c>
       <c r="F11" s="7">
-        <v>0.047779999999999996</v>
+        <v>0.048745000000000004</v>
       </c>
       <c r="G11" s="7">
-        <v>0.318239</v>
+        <v>0.33750100000000005</v>
       </c>
       <c r="H11" s="7">
-        <v>0.282291</v>
+        <v>0.279732</v>
       </c>
       <c r="I11" s="7">
-        <v>0.5999680000000001</v>
+        <v>0.596775</v>
       </c>
       <c r="J11" s="7">
-        <v>2.786738</v>
+        <v>2.780693</v>
       </c>
       <c r="K11" s="7">
-        <v>12.63307</v>
+        <v>12.597224</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2664,25 +2670,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.045368000000000006</v>
+        <v>0.045354</v>
       </c>
       <c r="F12" s="7">
-        <v>0.069549</v>
+        <v>0.069306</v>
       </c>
       <c r="G12" s="7">
-        <v>0.237502</v>
+        <v>0.24080400000000002</v>
       </c>
       <c r="H12" s="7">
-        <v>0.148115</v>
+        <v>0.148099</v>
       </c>
       <c r="I12" s="7">
-        <v>0.496118</v>
+        <v>0.49609699999999995</v>
       </c>
       <c r="J12" s="7">
-        <v>2.690281</v>
+        <v>2.6844279999999996</v>
       </c>
       <c r="K12" s="7">
-        <v>4.55072</v>
+        <v>4.54916</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2699,25 +2705,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.108537</v>
+        <v>0.104644</v>
       </c>
       <c r="F13" s="7">
-        <v>0.062468</v>
+        <v>0.060715000000000005</v>
       </c>
       <c r="G13" s="7">
-        <v>0.344652</v>
+        <v>0.36518900000000004</v>
       </c>
       <c r="H13" s="7">
-        <v>0.298687</v>
+        <v>0.294126</v>
       </c>
       <c r="I13" s="7">
-        <v>0.628127</v>
+        <v>0.622409</v>
       </c>
       <c r="J13" s="7">
-        <v>2.935883</v>
+        <v>2.9246839999999996</v>
       </c>
       <c r="K13" s="7">
-        <v>10.416945</v>
+        <v>10.394722</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2734,25 +2740,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.050306</v>
+        <v>0.045551</v>
       </c>
       <c r="F14" s="7">
-        <v>0.022138</v>
+        <v>0.017903</v>
       </c>
       <c r="G14" s="7">
-        <v>0.24681799999999998</v>
+        <v>0.25757</v>
       </c>
       <c r="H14" s="7">
-        <v>0.18003699999999997</v>
+        <v>0.174695</v>
       </c>
       <c r="I14" s="7">
-        <v>0.488656</v>
+        <v>0.481918</v>
       </c>
       <c r="J14" s="7">
-        <v>2.6935610000000003</v>
+        <v>2.66521</v>
       </c>
       <c r="K14" s="7">
-        <v>8.023981</v>
+        <v>7.974525</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2769,25 +2775,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.030244</v>
+        <v>0.030635</v>
       </c>
       <c r="F15" s="7">
-        <v>0.013037</v>
+        <v>0.014183</v>
       </c>
       <c r="G15" s="7">
-        <v>0.176708</v>
+        <v>0.17832699999999999</v>
       </c>
       <c r="H15" s="7">
-        <v>0.076483</v>
+        <v>0.076892</v>
       </c>
       <c r="I15" s="7">
-        <v>0.407115</v>
+        <v>0.407649</v>
       </c>
       <c r="J15" s="7">
-        <v>2.0289680000000003</v>
+        <v>2.025506</v>
       </c>
       <c r="K15" s="7">
-        <v>5.495558</v>
+        <v>5.494020000000001</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2804,25 +2810,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.034475</v>
+        <v>0.036082</v>
       </c>
       <c r="F16" s="7">
-        <v>0.081683</v>
+        <v>0.08326800000000001</v>
       </c>
       <c r="G16" s="7">
-        <v>0.216268</v>
+        <v>0.218612</v>
       </c>
       <c r="H16" s="7">
-        <v>0.139108</v>
+        <v>0.140878</v>
       </c>
       <c r="I16" s="7">
-        <v>0.508598</v>
+        <v>0.510942</v>
       </c>
       <c r="J16" s="7">
-        <v>2.793609</v>
+        <v>2.792591</v>
       </c>
       <c r="K16" s="7">
-        <v>5.050346</v>
+        <v>5.0575</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2839,25 +2845,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.037481</v>
+        <v>0.037991000000000004</v>
       </c>
       <c r="F17" s="7">
-        <v>0.07420399999999999</v>
+        <v>0.073536</v>
       </c>
       <c r="G17" s="7">
-        <v>0.18986899999999998</v>
+        <v>0.192076</v>
       </c>
       <c r="H17" s="7">
-        <v>0.134546</v>
+        <v>0.135104</v>
       </c>
       <c r="I17" s="7">
-        <v>0.418785</v>
+        <v>0.41948300000000005</v>
       </c>
       <c r="J17" s="7">
-        <v>1.704253</v>
+        <v>1.685704</v>
       </c>
       <c r="K17" s="7">
-        <v>4.528549</v>
+        <v>4.529634</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2874,25 +2880,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.016269</v>
+        <v>-0.017539</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.08362</v>
+        <v>-0.110752</v>
       </c>
       <c r="G18" s="7">
-        <v>0.202636</v>
+        <v>0.20613199999999998</v>
       </c>
       <c r="H18" s="7">
-        <v>0.053966</v>
+        <v>0.052605000000000006</v>
       </c>
       <c r="I18" s="7">
-        <v>0.622584</v>
+        <v>0.6204890000000001</v>
       </c>
       <c r="J18" s="7">
-        <v>4.771968</v>
+        <v>4.654992</v>
       </c>
       <c r="K18" s="7">
-        <v>15.681885999999999</v>
+        <v>15.522093</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2909,25 +2915,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.066304</v>
+        <v>0.067925</v>
       </c>
       <c r="F19" s="7">
-        <v>0.047431</v>
+        <v>0.048524000000000005</v>
       </c>
       <c r="G19" s="7">
-        <v>0.187684</v>
+        <v>0.194529</v>
       </c>
       <c r="H19" s="7">
-        <v>0.11825200000000001</v>
+        <v>0.119952</v>
       </c>
       <c r="I19" s="7">
-        <v>0.45213000000000003</v>
+        <v>0.45433799999999996</v>
       </c>
       <c r="J19" s="7">
-        <v>2.316885</v>
+        <v>2.310479</v>
       </c>
       <c r="K19" s="7">
-        <v>6.920067</v>
+        <v>6.924018</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2944,25 +2950,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.03751</v>
+        <v>0.037924</v>
       </c>
       <c r="F20" s="7">
-        <v>0.091045</v>
+        <v>0.09168</v>
       </c>
       <c r="G20" s="7">
-        <v>0.236022</v>
+        <v>0.236356</v>
       </c>
       <c r="H20" s="7">
-        <v>0.093748</v>
+        <v>0.094184</v>
       </c>
       <c r="I20" s="7">
-        <v>0.46479</v>
+        <v>0.46537399999999995</v>
       </c>
       <c r="J20" s="7">
-        <v>1.520409</v>
+        <v>1.5086080000000002</v>
       </c>
       <c r="K20" s="7">
-        <v>4.18944</v>
+        <v>4.186787</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2979,25 +2985,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.041902999999999996</v>
+        <v>0.040622</v>
       </c>
       <c r="F21" s="7">
-        <v>0.08931900000000001</v>
+        <v>0.087737</v>
       </c>
       <c r="G21" s="7">
-        <v>0.207822</v>
+        <v>0.209297</v>
       </c>
       <c r="H21" s="7">
-        <v>0.153714</v>
+        <v>0.152296</v>
       </c>
       <c r="I21" s="7">
-        <v>0.447268</v>
+        <v>0.445489</v>
       </c>
       <c r="J21" s="7">
-        <v>1.8983809999999999</v>
+        <v>1.86018</v>
       </c>
       <c r="K21" s="7">
-        <v>5.025313</v>
+        <v>5.011306</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3014,25 +3020,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.097384</v>
+        <v>0.101277</v>
       </c>
       <c r="F22" s="7">
-        <v>0.080875</v>
+        <v>0.08906800000000001</v>
       </c>
       <c r="G22" s="7">
-        <v>0.242806</v>
+        <v>0.25978999999999997</v>
       </c>
       <c r="H22" s="7">
-        <v>0.25342</v>
+        <v>0.257866</v>
       </c>
       <c r="I22" s="7">
-        <v>0.601363</v>
+        <v>0.607044</v>
       </c>
       <c r="J22" s="7">
-        <v>2.9819850000000003</v>
+        <v>2.989793</v>
       </c>
       <c r="K22" s="7">
-        <v>10.65893</v>
+        <v>10.677909</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3049,25 +3055,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.025447</v>
+        <v>0.026712</v>
       </c>
       <c r="F23" s="7">
-        <v>0.08036599999999999</v>
+        <v>0.079819</v>
       </c>
       <c r="G23" s="7">
-        <v>0.18290700000000001</v>
+        <v>0.183581</v>
       </c>
       <c r="H23" s="7">
-        <v>0.121303</v>
+        <v>0.12268599999999999</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40755899999999995</v>
+        <v>0.40929499999999996</v>
       </c>
       <c r="J23" s="7">
-        <v>2.2276</v>
+        <v>2.202182</v>
       </c>
       <c r="K23" s="7">
-        <v>4.999894</v>
+        <v>4.996042</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3084,25 +3090,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.024238</v>
+        <v>0.02673</v>
       </c>
       <c r="F24" s="7">
-        <v>0.0033239999999999997</v>
+        <v>0.006291</v>
       </c>
       <c r="G24" s="7">
-        <v>0.131782</v>
+        <v>0.135139</v>
       </c>
       <c r="H24" s="7">
-        <v>0.033526</v>
+        <v>0.036042</v>
       </c>
       <c r="I24" s="7">
-        <v>0.371554</v>
+        <v>0.37489199999999995</v>
       </c>
       <c r="J24" s="7">
-        <v>1.580796</v>
+        <v>1.588308</v>
       </c>
       <c r="K24" s="7">
-        <v>3.40868</v>
+        <v>3.416169</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3119,25 +3125,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.028622</v>
+        <v>0.032528</v>
       </c>
       <c r="F25" s="7">
-        <v>0.033316</v>
+        <v>0.037114</v>
       </c>
       <c r="G25" s="7">
-        <v>0.112174</v>
+        <v>0.118995</v>
       </c>
       <c r="H25" s="7">
-        <v>0.051418</v>
+        <v>0.055411999999999996</v>
       </c>
       <c r="I25" s="7">
-        <v>0.338708</v>
+        <v>0.343792</v>
       </c>
       <c r="J25" s="7">
-        <v>2.0966050000000003</v>
+        <v>2.101521</v>
       </c>
       <c r="K25" s="7">
-        <v>6.3948860000000005</v>
+        <v>6.394386</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,25 +3160,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.034607</v>
+        <v>0.040302</v>
       </c>
       <c r="F26" s="7">
-        <v>0.021543</v>
+        <v>0.026057999999999998</v>
       </c>
       <c r="G26" s="7">
-        <v>0.114697</v>
+        <v>0.1222</v>
       </c>
       <c r="H26" s="7">
-        <v>0.048388999999999995</v>
+        <v>0.05416000000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.30168500000000004</v>
+        <v>0.308851</v>
       </c>
       <c r="J26" s="7">
-        <v>2.038941</v>
+        <v>2.056388</v>
       </c>
       <c r="K26" s="7">
-        <v>5.584982999999999</v>
+        <v>5.619266</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3189,25 +3195,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.070718</v>
+        <v>0.06494799999999999</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.020811000000000003</v>
+        <v>-0.018417</v>
       </c>
       <c r="G27" s="7">
-        <v>0.210375</v>
+        <v>0.21108000000000002</v>
       </c>
       <c r="H27" s="7">
-        <v>0.187234</v>
+        <v>0.180836</v>
       </c>
       <c r="I27" s="7">
-        <v>0.42094000000000004</v>
+        <v>0.41328200000000004</v>
       </c>
       <c r="J27" s="7">
-        <v>3.366703</v>
+        <v>3.345001</v>
       </c>
       <c r="K27" s="7">
-        <v>15.931749</v>
+        <v>15.827774999999999</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3224,25 +3230,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.094248</v>
+        <v>0.101789</v>
       </c>
       <c r="F28" s="7">
-        <v>0.033564</v>
+        <v>0.048957</v>
       </c>
       <c r="G28" s="7">
-        <v>0.119369</v>
+        <v>0.14065899999999998</v>
       </c>
       <c r="H28" s="7">
-        <v>0.101194</v>
+        <v>0.10878299999999999</v>
       </c>
       <c r="I28" s="7">
-        <v>0.410697</v>
+        <v>0.420419</v>
       </c>
       <c r="J28" s="7">
-        <v>2.5830990000000003</v>
+        <v>2.619209</v>
       </c>
       <c r="K28" s="7">
-        <v>7.866052</v>
+        <v>7.937609999999999</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3259,25 +3265,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.027955</v>
+        <v>0.028415</v>
       </c>
       <c r="F29" s="7">
-        <v>0.043653000000000004</v>
+        <v>0.043398000000000006</v>
       </c>
       <c r="G29" s="7">
-        <v>0.16724499999999998</v>
+        <v>0.167891</v>
       </c>
       <c r="H29" s="7">
-        <v>0.09791499999999999</v>
+        <v>0.098407</v>
       </c>
       <c r="I29" s="7">
-        <v>0.403557</v>
+        <v>0.404186</v>
       </c>
       <c r="J29" s="7">
-        <v>2.412912</v>
+        <v>2.414193</v>
       </c>
       <c r="K29" s="7">
-        <v>4.561381</v>
+        <v>4.561307</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3294,25 +3300,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.043783</v>
+        <v>0.045115999999999996</v>
       </c>
       <c r="F30" s="7">
-        <v>-0.002448</v>
+        <v>0.003686</v>
       </c>
       <c r="G30" s="7">
-        <v>0.178832</v>
+        <v>0.18250699999999997</v>
       </c>
       <c r="H30" s="7">
-        <v>0.14443799999999998</v>
+        <v>0.145899</v>
       </c>
       <c r="I30" s="7">
-        <v>0.390704</v>
+        <v>0.392479</v>
       </c>
       <c r="J30" s="7">
-        <v>3.0796010000000003</v>
+        <v>3.090094</v>
       </c>
       <c r="K30" s="7">
-        <v>9.396824</v>
+        <v>9.385102</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3329,25 +3335,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.10539799999999999</v>
+        <v>0.09855399999999999</v>
       </c>
       <c r="F31" s="7">
-        <v>0.000518</v>
+        <v>0.002223</v>
       </c>
       <c r="G31" s="7">
-        <v>0.219501</v>
+        <v>0.228913</v>
       </c>
       <c r="H31" s="7">
-        <v>0.20731100000000002</v>
+        <v>0.19983599999999999</v>
       </c>
       <c r="I31" s="7">
-        <v>0.39146099999999995</v>
+        <v>0.38284599999999996</v>
       </c>
       <c r="J31" s="7">
-        <v>2.696908</v>
+        <v>2.6748360000000004</v>
       </c>
       <c r="K31" s="7">
-        <v>14.546819000000001</v>
+        <v>14.433313</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3364,25 +3370,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.028647999999999996</v>
+        <v>0.029643000000000003</v>
       </c>
       <c r="F32" s="7">
-        <v>0.085008</v>
+        <v>0.084829</v>
       </c>
       <c r="G32" s="7">
-        <v>0.192334</v>
+        <v>0.19319199999999997</v>
       </c>
       <c r="H32" s="7">
-        <v>0.119057</v>
+        <v>0.120139</v>
       </c>
       <c r="I32" s="7">
-        <v>0.449115</v>
+        <v>0.45051699999999995</v>
       </c>
       <c r="J32" s="7">
-        <v>2.1627709999999998</v>
+        <v>2.165445</v>
       </c>
       <c r="K32" s="7">
-        <v>3.7365690000000003</v>
+        <v>3.738909</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3399,25 +3405,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.059025999999999995</v>
+        <v>0.053458</v>
       </c>
       <c r="F33" s="7">
-        <v>0.000092</v>
+        <v>-0.0011200000000000001</v>
       </c>
       <c r="G33" s="7">
-        <v>0.219524</v>
+        <v>0.219851</v>
       </c>
       <c r="H33" s="7">
-        <v>0.172081</v>
+        <v>0.16591799999999998</v>
       </c>
       <c r="I33" s="7">
-        <v>0.450763</v>
+        <v>0.443135</v>
       </c>
       <c r="J33" s="7">
-        <v>3.5849189999999997</v>
+        <v>3.5443290000000003</v>
       </c>
       <c r="K33" s="7">
-        <v>16.230126</v>
+        <v>16.125092</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3434,25 +3440,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.091202</v>
+        <v>0.094582</v>
       </c>
       <c r="F34" s="7">
-        <v>0.10117599999999999</v>
+        <v>0.105418</v>
       </c>
       <c r="G34" s="7">
-        <v>0.330133</v>
+        <v>0.348219</v>
       </c>
       <c r="H34" s="7">
-        <v>0.27690000000000003</v>
+        <v>0.280856</v>
       </c>
       <c r="I34" s="7">
-        <v>0.6578879999999999</v>
+        <v>0.6630240000000001</v>
       </c>
       <c r="J34" s="7">
-        <v>3.2815069999999995</v>
+        <v>3.284235</v>
       </c>
       <c r="K34" s="7">
-        <v>9.758091</v>
+        <v>9.789234</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3469,25 +3475,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.09428399999999999</v>
+        <v>0.100096</v>
       </c>
       <c r="F35" s="7">
-        <v>0.09265599999999999</v>
+        <v>0.097282</v>
       </c>
       <c r="G35" s="7">
-        <v>0.33705199999999996</v>
+        <v>0.361207</v>
       </c>
       <c r="H35" s="7">
-        <v>0.283439</v>
+        <v>0.290254</v>
       </c>
       <c r="I35" s="7">
-        <v>0.71418</v>
+        <v>0.723283</v>
       </c>
       <c r="J35" s="7">
-        <v>3.513154</v>
+        <v>3.522192</v>
       </c>
       <c r="K35" s="7">
-        <v>12.255700999999998</v>
+        <v>12.322799</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3504,25 +3510,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.05934300000000001</v>
+        <v>0.050289</v>
       </c>
       <c r="F36" s="7">
-        <v>0.004157</v>
+        <v>-0.000786</v>
       </c>
       <c r="G36" s="7">
-        <v>0.22971699999999998</v>
+        <v>0.227051</v>
       </c>
       <c r="H36" s="7">
-        <v>0.185188</v>
+        <v>0.17505800000000002</v>
       </c>
       <c r="I36" s="7">
-        <v>0.47478200000000004</v>
+        <v>0.462177</v>
       </c>
       <c r="J36" s="7">
-        <v>3.676814</v>
+        <v>3.619735</v>
       </c>
       <c r="K36" s="7">
-        <v>16.94926</v>
+        <v>16.78132</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3539,25 +3545,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.048498</v>
+        <v>0.042703</v>
       </c>
       <c r="F37" s="7">
-        <v>0.008156</v>
+        <v>0.005248</v>
       </c>
       <c r="G37" s="7">
-        <v>0.237704</v>
+        <v>0.237987</v>
       </c>
       <c r="H37" s="7">
-        <v>0.166909</v>
+        <v>0.16046</v>
       </c>
       <c r="I37" s="7">
-        <v>0.471314</v>
+        <v>0.463183</v>
       </c>
       <c r="J37" s="7">
-        <v>3.753261</v>
+        <v>3.703904</v>
       </c>
       <c r="K37" s="7">
-        <v>15.396856</v>
+        <v>15.286482000000001</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3574,25 +3580,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.036625</v>
+        <v>0.030615999999999997</v>
       </c>
       <c r="F38" s="7">
-        <v>0.009943</v>
+        <v>0.006734</v>
       </c>
       <c r="G38" s="7">
-        <v>0.207611</v>
+        <v>0.205855</v>
       </c>
       <c r="H38" s="7">
-        <v>0.148752</v>
+        <v>0.142093</v>
       </c>
       <c r="I38" s="7">
-        <v>0.46475099999999997</v>
+        <v>0.45626</v>
       </c>
       <c r="J38" s="7">
-        <v>3.5956770000000002</v>
+        <v>3.557304</v>
       </c>
       <c r="K38" s="7">
-        <v>11.45846</v>
+        <v>11.370229</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3609,25 +3615,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.025559</v>
+        <v>0.02702</v>
       </c>
       <c r="F39" s="7">
-        <v>0.054612</v>
+        <v>0.055968</v>
       </c>
       <c r="G39" s="7">
-        <v>0.188869</v>
+        <v>0.18970900000000002</v>
       </c>
       <c r="H39" s="7">
-        <v>0.117331</v>
+        <v>0.11892200000000001</v>
       </c>
       <c r="I39" s="7">
-        <v>0.458503</v>
+        <v>0.46058</v>
       </c>
       <c r="J39" s="7">
-        <v>2.9561450000000002</v>
+        <v>2.9604090000000003</v>
       </c>
       <c r="K39" s="7">
-        <v>5.68155</v>
+        <v>5.6879409999999995</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3644,25 +3650,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.08058199999999999</v>
+        <v>0.07787</v>
       </c>
       <c r="F40" s="7">
-        <v>0.11149800000000001</v>
+        <v>0.110245</v>
       </c>
       <c r="G40" s="7">
-        <v>0.291461</v>
+        <v>0.298251</v>
       </c>
       <c r="H40" s="7">
-        <v>0.24188600000000002</v>
+        <v>0.23876899999999998</v>
       </c>
       <c r="I40" s="7">
-        <v>0.609097</v>
+        <v>0.605057</v>
       </c>
       <c r="J40" s="7">
-        <v>3.5104640000000003</v>
+        <v>3.4700990000000003</v>
       </c>
       <c r="K40" s="7">
-        <v>11.669399</v>
+        <v>11.604881</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3679,25 +3685,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.067815</v>
+        <v>0.064476</v>
       </c>
       <c r="F41" s="7">
-        <v>0.10369999999999999</v>
+        <v>0.100304</v>
       </c>
       <c r="G41" s="7">
-        <v>0.273252</v>
+        <v>0.277233</v>
       </c>
       <c r="H41" s="7">
-        <v>0.21893</v>
+        <v>0.215119</v>
       </c>
       <c r="I41" s="7">
-        <v>0.5897720000000001</v>
+        <v>0.584801</v>
       </c>
       <c r="J41" s="7">
-        <v>3.220679</v>
+        <v>3.179223</v>
       </c>
       <c r="K41" s="7">
-        <v>9.981912</v>
+        <v>9.918174</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,25 +3720,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.08210800000000001</v>
+        <v>0.084575</v>
       </c>
       <c r="F42" s="7">
-        <v>0.055053</v>
+        <v>0.056101</v>
       </c>
       <c r="G42" s="7">
-        <v>0.297575</v>
+        <v>0.315449</v>
       </c>
       <c r="H42" s="7">
-        <v>0.25224599999999997</v>
+        <v>0.255102</v>
       </c>
       <c r="I42" s="7">
-        <v>0.57987</v>
+        <v>0.583473</v>
       </c>
       <c r="J42" s="7">
-        <v>3.2005500000000002</v>
+        <v>3.214827</v>
       </c>
       <c r="K42" s="7">
-        <v>10.756188</v>
+        <v>10.771280999999998</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3749,25 +3755,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.061586999999999996</v>
+        <v>0.054707</v>
       </c>
       <c r="F43" s="7">
-        <v>-0.013472</v>
+        <v>-0.013566</v>
       </c>
       <c r="G43" s="7">
-        <v>0.228942</v>
+        <v>0.228139</v>
       </c>
       <c r="H43" s="7">
-        <v>0.18198699999999998</v>
+        <v>0.174326</v>
       </c>
       <c r="I43" s="7">
-        <v>0.47158700000000003</v>
+        <v>0.46204900000000004</v>
       </c>
       <c r="J43" s="7">
-        <v>4.139745</v>
+        <v>4.084721</v>
       </c>
       <c r="K43" s="7">
-        <v>21.010106</v>
+        <v>20.863618000000002</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3784,25 +3790,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.033253</v>
+        <v>0.035344</v>
       </c>
       <c r="F44" s="7">
-        <v>0.057784</v>
+        <v>0.059925</v>
       </c>
       <c r="G44" s="7">
-        <v>0.19438</v>
+        <v>0.196036</v>
       </c>
       <c r="H44" s="7">
-        <v>0.115648</v>
+        <v>0.117906</v>
       </c>
       <c r="I44" s="7">
-        <v>0.47255800000000003</v>
+        <v>0.475539</v>
       </c>
       <c r="J44" s="7">
-        <v>2.4539869999999997</v>
+        <v>2.459508</v>
       </c>
       <c r="K44" s="7">
-        <v>4.447731</v>
+        <v>4.456726</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3819,25 +3825,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.06486</v>
+        <v>0.067375</v>
       </c>
       <c r="F45" s="7">
-        <v>0.055288000000000004</v>
+        <v>0.05556199999999999</v>
       </c>
       <c r="G45" s="7">
-        <v>0.278829</v>
+        <v>0.29462</v>
       </c>
       <c r="H45" s="7">
-        <v>0.215827</v>
+        <v>0.218698</v>
       </c>
       <c r="I45" s="7">
-        <v>0.579862</v>
+        <v>0.5835940000000001</v>
       </c>
       <c r="J45" s="7">
-        <v>3.2896319999999997</v>
+        <v>3.3038909999999997</v>
       </c>
       <c r="K45" s="7">
-        <v>9.460094</v>
+        <v>9.476375</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3854,25 +3860,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.069207</v>
+        <v>0.067847</v>
       </c>
       <c r="F46" s="7">
-        <v>0.11421900000000001</v>
+        <v>0.11279199999999999</v>
       </c>
       <c r="G46" s="7">
-        <v>0.299636</v>
+        <v>0.30557300000000004</v>
       </c>
       <c r="H46" s="7">
-        <v>0.252697</v>
+        <v>0.25110299999999997</v>
       </c>
       <c r="I46" s="7">
-        <v>0.609356</v>
+        <v>0.607309</v>
       </c>
       <c r="J46" s="7">
-        <v>3.640912</v>
+        <v>3.6248009999999997</v>
       </c>
       <c r="K46" s="7">
-        <v>10.260798</v>
+        <v>10.214249</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3889,25 +3895,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.088179</v>
+        <v>0.083735</v>
       </c>
       <c r="F47" s="7">
-        <v>0.10060600000000001</v>
+        <v>0.099606</v>
       </c>
       <c r="G47" s="7">
-        <v>0.294649</v>
+        <v>0.29945299999999997</v>
       </c>
       <c r="H47" s="7">
-        <v>0.257407</v>
+        <v>0.25227299999999997</v>
       </c>
       <c r="I47" s="7">
-        <v>0.611294</v>
+        <v>0.604715</v>
       </c>
       <c r="J47" s="7">
-        <v>3.6949349999999996</v>
+        <v>3.643641</v>
       </c>
       <c r="K47" s="7">
-        <v>13.108315</v>
+        <v>13.003565000000002</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3924,25 +3930,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.049409</v>
+        <v>0.032448000000000005</v>
       </c>
       <c r="F48" s="7">
-        <v>-0.0143</v>
+        <v>-0.027121</v>
       </c>
       <c r="G48" s="7">
-        <v>0.134961</v>
+        <v>0.138674</v>
       </c>
       <c r="H48" s="7">
-        <v>0.138856</v>
+        <v>0.12045</v>
       </c>
       <c r="I48" s="7">
-        <v>0.451141</v>
+        <v>0.427688</v>
       </c>
       <c r="J48" s="7">
-        <v>1.890053</v>
+        <v>1.8441040000000002</v>
       </c>
       <c r="K48" s="7">
-        <v>10.050561</v>
+        <v>9.982643000000001</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3959,25 +3965,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.092615</v>
+        <v>0.089016</v>
       </c>
       <c r="F49" s="7">
-        <v>0.045167</v>
+        <v>0.044482</v>
       </c>
       <c r="G49" s="7">
-        <v>0.305037</v>
+        <v>0.32151</v>
       </c>
       <c r="H49" s="7">
-        <v>0.25347200000000003</v>
+        <v>0.249344</v>
       </c>
       <c r="I49" s="7">
-        <v>0.591006</v>
+        <v>0.585767</v>
       </c>
       <c r="J49" s="7">
-        <v>3.7725510000000004</v>
+        <v>3.7564830000000002</v>
       </c>
       <c r="K49" s="7">
-        <v>15.798847</v>
+        <v>15.725102</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -3994,25 +4000,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.096593</v>
+        <v>0.10604</v>
       </c>
       <c r="F50" s="7">
-        <v>0.050683</v>
+        <v>0.06661500000000001</v>
       </c>
       <c r="G50" s="7">
-        <v>0.139976</v>
+        <v>0.163265</v>
       </c>
       <c r="H50" s="7">
-        <v>0.118163</v>
+        <v>0.127796</v>
       </c>
       <c r="I50" s="7">
-        <v>0.5130250000000001</v>
+        <v>0.5260589999999999</v>
       </c>
       <c r="J50" s="7">
-        <v>3.0417579999999997</v>
+        <v>3.098122</v>
       </c>
       <c r="K50" s="7">
-        <v>8.868125</v>
+        <v>9.030616</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4029,25 +4035,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.046947</v>
+        <v>0.047139</v>
       </c>
       <c r="F51" s="7">
-        <v>0.014071</v>
+        <v>0.013137000000000001</v>
       </c>
       <c r="G51" s="7">
-        <v>0.17465699999999998</v>
+        <v>0.184025</v>
       </c>
       <c r="H51" s="7">
-        <v>0.12642799999999998</v>
+        <v>0.126635</v>
       </c>
       <c r="I51" s="7">
-        <v>0.375794</v>
+        <v>0.376047</v>
       </c>
       <c r="J51" s="7">
-        <v>2.587246</v>
+        <v>2.598571</v>
       </c>
       <c r="K51" s="7">
-        <v>8.021699</v>
+        <v>7.999459000000001</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4064,25 +4070,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.09294600000000001</v>
+        <v>0.08883200000000001</v>
       </c>
       <c r="F52" s="7">
-        <v>0.006861000000000001</v>
+        <v>0.010069999999999999</v>
       </c>
       <c r="G52" s="7">
-        <v>0.257302</v>
+        <v>0.26791899999999996</v>
       </c>
       <c r="H52" s="7">
-        <v>0.203254</v>
+        <v>0.19872499999999998</v>
       </c>
       <c r="I52" s="7">
-        <v>0.500002</v>
+        <v>0.494356</v>
       </c>
       <c r="J52" s="7">
-        <v>2.780446</v>
+        <v>2.757034</v>
       </c>
       <c r="K52" s="7">
-        <v>10.914940999999999</v>
+        <v>10.872715000000001</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4099,25 +4105,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.03771</v>
+        <v>0.04179</v>
       </c>
       <c r="F53" s="7">
-        <v>0.028433</v>
+        <v>0.03128</v>
       </c>
       <c r="G53" s="7">
-        <v>0.09262100000000001</v>
+        <v>0.098134</v>
       </c>
       <c r="H53" s="7">
-        <v>0.042699999999999995</v>
+        <v>0.046801</v>
       </c>
       <c r="I53" s="7">
-        <v>0.33371</v>
+        <v>0.338955</v>
       </c>
       <c r="J53" s="7">
-        <v>2.171744</v>
+        <v>2.1758539999999997</v>
       </c>
       <c r="K53" s="7">
-        <v>6.412286</v>
+        <v>6.414069</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4134,25 +4140,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.030392000000000002</v>
+        <v>0.033443</v>
       </c>
       <c r="F54" s="7">
-        <v>0.031545000000000004</v>
+        <v>0.033481000000000004</v>
       </c>
       <c r="G54" s="7">
-        <v>0.094299</v>
+        <v>0.09756500000000001</v>
       </c>
       <c r="H54" s="7">
-        <v>0.050731</v>
+        <v>0.053842</v>
       </c>
       <c r="I54" s="7">
-        <v>0.301349</v>
+        <v>0.305202</v>
       </c>
       <c r="J54" s="7">
-        <v>2.053511</v>
+        <v>2.061078</v>
       </c>
       <c r="K54" s="7">
-        <v>6.233182</v>
+        <v>6.227598</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4169,25 +4175,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.012971</v>
+        <v>-0.013302000000000001</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.084079</v>
+        <v>-0.109059</v>
       </c>
       <c r="G55" s="7">
-        <v>0.18688500000000002</v>
+        <v>0.19107</v>
       </c>
       <c r="H55" s="7">
-        <v>0.06521300000000001</v>
+        <v>0.064855</v>
       </c>
       <c r="I55" s="7">
-        <v>0.595252</v>
+        <v>0.594716</v>
       </c>
       <c r="J55" s="7">
-        <v>3.9110250000000004</v>
+        <v>3.8103230000000003</v>
       </c>
       <c r="K55" s="7">
-        <v>13.011721999999999</v>
+        <v>12.881887999999998</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4204,25 +4210,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.06687599999999999</v>
+        <v>0.060212</v>
       </c>
       <c r="F56" s="7">
-        <v>0.053895</v>
+        <v>0.048085</v>
       </c>
       <c r="G56" s="7">
-        <v>0.228532</v>
+        <v>0.222442</v>
       </c>
       <c r="H56" s="7">
-        <v>0.14491300000000001</v>
+        <v>0.137762</v>
       </c>
       <c r="I56" s="7">
-        <v>0.47401000000000004</v>
+        <v>0.464803</v>
       </c>
       <c r="J56" s="7">
-        <v>2.103596</v>
+        <v>2.087828</v>
       </c>
       <c r="K56" s="7">
-        <v>5.6347320000000005</v>
+        <v>5.599764</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4239,25 +4245,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.022153</v>
+        <v>0.020347</v>
       </c>
       <c r="F57" s="7">
-        <v>-0.014766999999999999</v>
+        <v>-0.013654999999999999</v>
       </c>
       <c r="G57" s="7">
-        <v>0.12060399999999999</v>
+        <v>0.122363</v>
       </c>
       <c r="H57" s="7">
-        <v>0.059988</v>
+        <v>0.058115</v>
       </c>
       <c r="I57" s="7">
-        <v>0.362286</v>
+        <v>0.35987900000000006</v>
       </c>
       <c r="J57" s="7">
-        <v>1.363247</v>
+        <v>1.3561170000000002</v>
       </c>
       <c r="K57" s="7">
-        <v>3.521064</v>
+        <v>3.5145150000000003</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4274,25 +4280,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.06935</v>
+        <v>0.072066</v>
       </c>
       <c r="F58" s="7">
-        <v>0.057861</v>
+        <v>0.057138999999999995</v>
       </c>
       <c r="G58" s="7">
-        <v>0.28959399999999996</v>
+        <v>0.304989</v>
       </c>
       <c r="H58" s="7">
-        <v>0.225774</v>
+        <v>0.228886</v>
       </c>
       <c r="I58" s="7">
-        <v>0.580613</v>
+        <v>0.584626</v>
       </c>
       <c r="J58" s="7">
-        <v>3.26202</v>
+        <v>3.27433</v>
       </c>
       <c r="K58" s="7">
-        <v>9.532468</v>
+        <v>9.55083</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4309,25 +4315,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.080842</v>
+        <v>0.082683</v>
       </c>
       <c r="F59" s="7">
-        <v>0.060212</v>
+        <v>0.062404</v>
       </c>
       <c r="G59" s="7">
-        <v>0.305862</v>
+        <v>0.323641</v>
       </c>
       <c r="H59" s="7">
-        <v>0.255917</v>
+        <v>0.258056</v>
       </c>
       <c r="I59" s="7">
-        <v>0.5864889999999999</v>
+        <v>0.58919</v>
       </c>
       <c r="J59" s="7">
-        <v>3.3068579999999996</v>
+        <v>3.320049</v>
       </c>
       <c r="K59" s="7">
-        <v>10.630516</v>
+        <v>10.639671</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4344,25 +4350,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.08080399999999999</v>
+        <v>0.066401</v>
       </c>
       <c r="F60" s="7">
-        <v>0.004497</v>
+        <v>-0.0033179999999999998</v>
       </c>
       <c r="G60" s="7">
-        <v>0.210212</v>
+        <v>0.19828600000000002</v>
       </c>
       <c r="H60" s="7">
-        <v>0.18711099999999997</v>
+        <v>0.171292</v>
       </c>
       <c r="I60" s="7">
-        <v>0.435453</v>
+        <v>0.41632399999999997</v>
       </c>
       <c r="J60" s="7">
-        <v>2.569369</v>
+        <v>2.51909</v>
       </c>
       <c r="K60" s="7">
-        <v>12.830228</v>
+        <v>12.629996</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4379,25 +4385,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.088922</v>
+        <v>0.08975300000000001</v>
       </c>
       <c r="F61" s="7">
-        <v>0.035388</v>
+        <v>0.041124</v>
       </c>
       <c r="G61" s="7">
-        <v>0.19626100000000002</v>
+        <v>0.21035</v>
       </c>
       <c r="H61" s="7">
-        <v>0.165676</v>
+        <v>0.16656600000000002</v>
       </c>
       <c r="I61" s="7">
-        <v>0.49167099999999997</v>
+        <v>0.49280999999999997</v>
       </c>
       <c r="J61" s="7">
-        <v>2.517716</v>
+        <v>2.520911</v>
       </c>
       <c r="K61" s="7">
-        <v>7.558089</v>
+        <v>7.5870820000000005</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,25 +4420,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.060732</v>
+        <v>0.049345999999999994</v>
       </c>
       <c r="F62" s="7">
-        <v>-0.042156</v>
+        <v>-0.042243</v>
       </c>
       <c r="G62" s="7">
-        <v>0.151975</v>
+        <v>0.142348</v>
       </c>
       <c r="H62" s="7">
-        <v>0.155302</v>
+        <v>0.142901</v>
       </c>
       <c r="I62" s="7">
-        <v>0.38249099999999997</v>
+        <v>0.367652</v>
       </c>
       <c r="J62" s="7">
-        <v>2.496355</v>
+        <v>2.454562</v>
       </c>
       <c r="K62" s="7">
-        <v>12.071266000000001</v>
+        <v>12.018523</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4449,25 +4455,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.037637000000000004</v>
+        <v>0.036946</v>
       </c>
       <c r="F63" s="7">
-        <v>0.0027960000000000003</v>
+        <v>0.003648</v>
       </c>
       <c r="G63" s="7">
-        <v>0.169423</v>
+        <v>0.171399</v>
       </c>
       <c r="H63" s="7">
-        <v>0.082766</v>
+        <v>0.082046</v>
       </c>
       <c r="I63" s="7">
-        <v>0.397851</v>
+        <v>0.396921</v>
       </c>
       <c r="J63" s="7">
-        <v>1.931292</v>
+        <v>1.93199</v>
       </c>
       <c r="K63" s="7">
-        <v>4.623226</v>
+        <v>4.618917</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4484,25 +4490,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.023540000000000002</v>
+        <v>0.023988</v>
       </c>
       <c r="F64" s="7">
-        <v>0.0025069999999999997</v>
+        <v>-0.0067469999999999995</v>
       </c>
       <c r="G64" s="7">
-        <v>0.17380099999999998</v>
+        <v>0.182312</v>
       </c>
       <c r="H64" s="7">
-        <v>0.135069</v>
+        <v>0.135566</v>
       </c>
       <c r="I64" s="7">
-        <v>0.391449</v>
+        <v>0.392059</v>
       </c>
       <c r="J64" s="7">
-        <v>2.075043</v>
+        <v>2.066294</v>
       </c>
       <c r="K64" s="7">
-        <v>6.083786</v>
+        <v>6.090250999999999</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4519,25 +4525,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.028188</v>
+        <v>0.030688</v>
       </c>
       <c r="F65" s="7">
-        <v>0.040979</v>
+        <v>0.041881</v>
       </c>
       <c r="G65" s="7">
-        <v>0.102925</v>
+        <v>0.104547</v>
       </c>
       <c r="H65" s="7">
-        <v>0.059273</v>
+        <v>0.061849</v>
       </c>
       <c r="I65" s="7">
-        <v>0.291699</v>
+        <v>0.29484</v>
       </c>
       <c r="J65" s="7">
-        <v>2.078696</v>
+        <v>2.084279</v>
       </c>
       <c r="K65" s="7">
-        <v>5.296734</v>
+        <v>5.3101009999999995</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4554,25 +4560,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.030133999999999998</v>
+        <v>0.03645</v>
       </c>
       <c r="F66" s="7">
-        <v>0.028197999999999997</v>
+        <v>0.034677</v>
       </c>
       <c r="G66" s="7">
-        <v>0.086922</v>
+        <v>0.094985</v>
       </c>
       <c r="H66" s="7">
-        <v>0.036252</v>
+        <v>0.042605000000000004</v>
       </c>
       <c r="I66" s="7">
-        <v>0.31339300000000003</v>
+        <v>0.321445</v>
       </c>
       <c r="J66" s="7">
-        <v>2.282</v>
+        <v>2.286222</v>
       </c>
       <c r="K66" s="7">
-        <v>6.688713</v>
+        <v>6.709756</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4589,25 +4595,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.054071</v>
+        <v>0.053923</v>
       </c>
       <c r="F67" s="7">
-        <v>0.035787</v>
+        <v>0.029477000000000003</v>
       </c>
       <c r="G67" s="7">
-        <v>0.255449</v>
+        <v>0.262472</v>
       </c>
       <c r="H67" s="7">
-        <v>0.19250699999999998</v>
+        <v>0.19234</v>
       </c>
       <c r="I67" s="7">
-        <v>0.563604</v>
+        <v>0.5633859999999999</v>
       </c>
       <c r="J67" s="7">
-        <v>2.595498</v>
+        <v>2.5769290000000002</v>
       </c>
       <c r="K67" s="7">
-        <v>9.359162</v>
+        <v>9.343831999999999</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4624,25 +4630,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.028896</v>
+        <v>0.033965</v>
       </c>
       <c r="F68" s="7">
-        <v>0.031004999999999998</v>
+        <v>0.026751</v>
       </c>
       <c r="G68" s="7">
-        <v>0.089778</v>
+        <v>0.095931</v>
       </c>
       <c r="H68" s="7">
-        <v>0.043353</v>
+        <v>0.048492</v>
       </c>
       <c r="I68" s="7">
-        <v>0.289642</v>
+        <v>0.295994</v>
       </c>
       <c r="J68" s="7">
-        <v>2.059906</v>
+        <v>2.0648429999999998</v>
       </c>
       <c r="K68" s="7">
-        <v>6.083094999999999</v>
+        <v>6.097042</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4659,25 +4665,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.049441</v>
+        <v>0.049976</v>
       </c>
       <c r="F69" s="7">
-        <v>0.028671000000000002</v>
+        <v>0.03034</v>
       </c>
       <c r="G69" s="7">
-        <v>0.19950199999999998</v>
+        <v>0.20633600000000002</v>
       </c>
       <c r="H69" s="7">
-        <v>0.12153900000000001</v>
+        <v>0.122112</v>
       </c>
       <c r="I69" s="7">
-        <v>0.46621</v>
+        <v>0.466959</v>
       </c>
       <c r="J69" s="7">
-        <v>2.226961</v>
+        <v>2.231661</v>
       </c>
       <c r="K69" s="7">
-        <v>5.500598</v>
+        <v>5.498968</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4694,25 +4700,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.029234</v>
+        <v>0.030289</v>
       </c>
       <c r="F70" s="7">
-        <v>0.09382099999999999</v>
+        <v>0.09387499999999999</v>
       </c>
       <c r="G70" s="7">
-        <v>0.200064</v>
+        <v>0.199919</v>
       </c>
       <c r="H70" s="7">
-        <v>0.130241</v>
+        <v>0.13140000000000002</v>
       </c>
       <c r="I70" s="7">
-        <v>0.477685</v>
+        <v>0.479199</v>
       </c>
       <c r="J70" s="7">
-        <v>2.3520079999999997</v>
+        <v>2.353245</v>
       </c>
       <c r="K70" s="7">
-        <v>4.061666</v>
+        <v>4.064447</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4729,25 +4735,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.219387</v>
+        <v>0.268943</v>
       </c>
       <c r="F71" s="7">
-        <v>0.135988</v>
+        <v>0.23386600000000002</v>
       </c>
       <c r="G71" s="7">
-        <v>0.153051</v>
+        <v>0.22761099999999998</v>
       </c>
       <c r="H71" s="7">
-        <v>0.172651</v>
+        <v>0.220307</v>
       </c>
       <c r="I71" s="7">
-        <v>0.6515810000000001</v>
+        <v>0.718702</v>
       </c>
       <c r="J71" s="7">
-        <v>3.8157530000000004</v>
+        <v>3.9983969999999998</v>
       </c>
       <c r="K71" s="7">
-        <v>7.838273</v>
+        <v>8.340944</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4764,25 +4770,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.04402300000000001</v>
+        <v>0.044954</v>
       </c>
       <c r="F72" s="7">
-        <v>0.075442</v>
+        <v>0.075849</v>
       </c>
       <c r="G72" s="7">
-        <v>0.227974</v>
+        <v>0.232824</v>
       </c>
       <c r="H72" s="7">
-        <v>0.143813</v>
+        <v>0.144834</v>
       </c>
       <c r="I72" s="7">
-        <v>0.458756</v>
+        <v>0.460058</v>
       </c>
       <c r="J72" s="7">
-        <v>1.807293</v>
+        <v>1.788679</v>
       </c>
       <c r="K72" s="7">
-        <v>4.672081</v>
+        <v>4.674137</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4799,25 +4805,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.032986</v>
+        <v>0.040446</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.021640000000000003</v>
+        <v>-0.014991</v>
       </c>
       <c r="G73" s="7">
-        <v>0.037006000000000004</v>
+        <v>0.045771</v>
       </c>
       <c r="H73" s="7">
-        <v>-0.010576</v>
+        <v>-0.003431</v>
       </c>
       <c r="I73" s="7">
-        <v>0.263535</v>
+        <v>0.27265999999999996</v>
       </c>
       <c r="J73" s="7">
-        <v>2.006082</v>
+        <v>2.0215289999999997</v>
       </c>
       <c r="K73" s="7">
-        <v>5.984853</v>
+        <v>6.0093179999999995</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,25 +4840,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.10602299999999999</v>
+        <v>0.09920899999999999</v>
       </c>
       <c r="F74" s="7">
-        <v>0.001512</v>
+        <v>0.0032519999999999997</v>
       </c>
       <c r="G74" s="7">
-        <v>0.22334900000000002</v>
+        <v>0.233009</v>
       </c>
       <c r="H74" s="7">
-        <v>0.20883700000000002</v>
+        <v>0.20138999999999999</v>
       </c>
       <c r="I74" s="7">
-        <v>0.40088</v>
+        <v>0.39225</v>
       </c>
       <c r="J74" s="7">
-        <v>2.730362</v>
+        <v>2.7082170000000003</v>
       </c>
       <c r="K74" s="7">
-        <v>14.75037</v>
+        <v>14.635791</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4869,25 +4875,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.023135</v>
+        <v>0.025783</v>
       </c>
       <c r="F75" s="7">
-        <v>0.002708</v>
+        <v>0.005620000000000001</v>
       </c>
       <c r="G75" s="7">
-        <v>0.153945</v>
+        <v>0.15629099999999999</v>
       </c>
       <c r="H75" s="7">
-        <v>0.045385999999999996</v>
+        <v>0.048091</v>
       </c>
       <c r="I75" s="7">
-        <v>0.399726</v>
+        <v>0.40334800000000004</v>
       </c>
       <c r="J75" s="7">
-        <v>1.774041</v>
+        <v>1.782883</v>
       </c>
       <c r="K75" s="7">
-        <v>3.670232</v>
+        <v>3.679777</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4904,25 +4910,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.045820999999999994</v>
+        <v>0.046397</v>
       </c>
       <c r="F76" s="7">
-        <v>0.028083999999999998</v>
+        <v>0.029807999999999998</v>
       </c>
       <c r="G76" s="7">
-        <v>0.202003</v>
+        <v>0.20893799999999998</v>
       </c>
       <c r="H76" s="7">
-        <v>0.122335</v>
+        <v>0.12295299999999999</v>
       </c>
       <c r="I76" s="7">
-        <v>0.473842</v>
+        <v>0.474654</v>
       </c>
       <c r="J76" s="7">
-        <v>2.268749</v>
+        <v>2.273669</v>
       </c>
       <c r="K76" s="7">
-        <v>5.590712999999999</v>
+        <v>5.589417999999999</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4939,25 +4945,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.036732999999999995</v>
+        <v>0.043045</v>
       </c>
       <c r="F77" s="7">
-        <v>0.06274</v>
+        <v>0.059551999999999994</v>
       </c>
       <c r="G77" s="7">
-        <v>0.294435</v>
+        <v>0.305133</v>
       </c>
       <c r="H77" s="7">
-        <v>0.19238600000000003</v>
+        <v>0.19964600000000002</v>
       </c>
       <c r="I77" s="7">
-        <v>0.417719</v>
+        <v>0.42635</v>
       </c>
       <c r="J77" s="7">
-        <v>1.9358469999999999</v>
+        <v>1.9507320000000001</v>
       </c>
       <c r="K77" s="7">
-        <v>5.472622</v>
+        <v>5.497668999999999</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4974,25 +4980,25 @@
         <v>4</v>
       </c>
       <c r="E78" s="7">
-        <v>0.050004</v>
+        <v>0.049272</v>
       </c>
       <c r="F78" s="7">
-        <v>0.11448399999999999</v>
+        <v>0.11888299999999999</v>
       </c>
       <c r="G78" s="7">
-        <v>0.325652</v>
+        <v>0.330513</v>
       </c>
       <c r="H78" s="7">
-        <v>0.248514</v>
+        <v>0.24764299999999997</v>
       </c>
       <c r="I78" s="7">
-        <v>0.676529</v>
+        <v>0.6753589999999999</v>
       </c>
       <c r="J78" s="7">
-        <v>2.938285</v>
+        <v>2.938874</v>
       </c>
       <c r="K78" s="7">
-        <v>8.286103</v>
+        <v>8.268242</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5009,25 +5015,25 @@
         <v>5</v>
       </c>
       <c r="E79" s="7">
-        <v>0.061369</v>
+        <v>0.063344</v>
       </c>
       <c r="F79" s="7">
-        <v>0.069546</v>
+        <v>0.075431</v>
       </c>
       <c r="G79" s="7">
-        <v>0.15637299999999998</v>
+        <v>0.162448</v>
       </c>
       <c r="H79" s="7">
-        <v>0.161327</v>
+        <v>0.163488</v>
       </c>
       <c r="I79" s="7">
-        <v>0.429489</v>
+        <v>0.43215000000000003</v>
       </c>
       <c r="J79" s="7">
-        <v>2.458862</v>
+        <v>2.443865</v>
       </c>
       <c r="K79" s="7">
-        <v>8.003442999999999</v>
+        <v>8.014724</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5044,25 +5050,25 @@
         <v>6</v>
       </c>
       <c r="E80" s="7">
-        <v>0.092912</v>
+        <v>0.084058</v>
       </c>
       <c r="F80" s="7">
-        <v>0.017787</v>
+        <v>0.014804999999999999</v>
       </c>
       <c r="G80" s="7">
-        <v>0.222112</v>
+        <v>0.23146999999999998</v>
       </c>
       <c r="H80" s="7">
-        <v>0.233571</v>
+        <v>0.223578</v>
       </c>
       <c r="I80" s="7">
-        <v>0.420471</v>
+        <v>0.408964</v>
       </c>
       <c r="J80" s="7">
-        <v>2.465043</v>
+        <v>2.443552</v>
       </c>
       <c r="K80" s="7">
-        <v>10.995308999999999</v>
+        <v>10.903362</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5079,25 +5085,25 @@
         <v>4</v>
       </c>
       <c r="E81" s="7">
-        <v>0.030945999999999998</v>
+        <v>0.030966999999999998</v>
       </c>
       <c r="F81" s="7">
-        <v>0.064476</v>
+        <v>0.063528</v>
       </c>
       <c r="G81" s="7">
-        <v>0.17018799999999998</v>
+        <v>0.172636</v>
       </c>
       <c r="H81" s="7">
-        <v>0.12086000000000001</v>
+        <v>0.120883</v>
       </c>
       <c r="I81" s="7">
-        <v>0.382594</v>
+        <v>0.38262300000000005</v>
       </c>
       <c r="J81" s="7">
-        <v>1.6055549999999998</v>
+        <v>1.5761420000000002</v>
       </c>
       <c r="K81" s="7">
-        <v>4.387124</v>
+        <v>4.38364</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5114,25 +5120,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.019562</v>
+        <v>0.022494</v>
       </c>
       <c r="F82" s="7">
-        <v>-0.0037080000000000004</v>
+        <v>0.00038899999999999997</v>
       </c>
       <c r="G82" s="7">
-        <v>0.121875</v>
+        <v>0.12548199999999998</v>
       </c>
       <c r="H82" s="7">
-        <v>0.038006000000000005</v>
+        <v>0.040991</v>
       </c>
       <c r="I82" s="7">
-        <v>0.369418</v>
+        <v>0.373356</v>
       </c>
       <c r="J82" s="7">
-        <v>1.465329</v>
+        <v>1.470964</v>
       </c>
       <c r="K82" s="7">
-        <v>3.088612</v>
+        <v>3.0974880000000002</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5149,25 +5155,25 @@
         <v>5</v>
       </c>
       <c r="E83" s="7">
-        <v>0.065746</v>
+        <v>0.069789</v>
       </c>
       <c r="F83" s="7">
-        <v>0.062082</v>
+        <v>0.06925200000000001</v>
       </c>
       <c r="G83" s="7">
-        <v>0.15221</v>
+        <v>0.161848</v>
       </c>
       <c r="H83" s="7">
-        <v>0.1703</v>
+        <v>0.174739</v>
       </c>
       <c r="I83" s="7">
-        <v>0.43367400000000006</v>
+        <v>0.439112</v>
       </c>
       <c r="J83" s="7">
-        <v>2.5040780000000002</v>
+        <v>2.497275</v>
       </c>
       <c r="K83" s="7">
-        <v>8.992984</v>
+        <v>9.02381</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5184,22 +5190,22 @@
         <v>6</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.017651</v>
+        <v>-0.017588</v>
       </c>
       <c r="F84" s="7">
-        <v>-0.098404</v>
+        <v>-0.120748</v>
       </c>
       <c r="G84" s="7">
-        <v>0.132827</v>
+        <v>0.142589</v>
       </c>
       <c r="H84" s="7">
-        <v>0.012352</v>
+        <v>0.012417000000000001</v>
       </c>
       <c r="I84" s="7">
-        <v>0.620229</v>
+        <v>0.620332</v>
       </c>
       <c r="J84" s="7">
-        <v>3.7777019999999997</v>
+        <v>3.713438</v>
       </c>
       <c r="K84" s="7"/>
     </row>
@@ -5217,19 +5223,19 @@
         <v>2</v>
       </c>
       <c r="E85" s="7">
-        <v>0.028433</v>
+        <v>0.029630999999999998</v>
       </c>
       <c r="F85" s="7">
-        <v>0.093297</v>
+        <v>0.09340999999999999</v>
       </c>
       <c r="G85" s="7">
-        <v>0.196081</v>
+        <v>0.19627099999999997</v>
       </c>
       <c r="H85" s="7">
-        <v>0.128361</v>
+        <v>0.12967599999999999</v>
       </c>
       <c r="I85" s="7">
-        <v>0.462733</v>
+        <v>0.464438</v>
       </c>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
@@ -5248,22 +5254,22 @@
         <v>6</v>
       </c>
       <c r="E86" s="7">
-        <v>0.087408</v>
+        <v>0.08316599999999999</v>
       </c>
       <c r="F86" s="7">
-        <v>0.029745</v>
+        <v>0.031466</v>
       </c>
       <c r="G86" s="7">
-        <v>0.242727</v>
+        <v>0.254141</v>
       </c>
       <c r="H86" s="7">
-        <v>0.199988</v>
+        <v>0.19530799999999998</v>
       </c>
       <c r="I86" s="7">
-        <v>0.544334</v>
+        <v>0.538311</v>
       </c>
       <c r="J86" s="7">
-        <v>2.811684</v>
+        <v>2.819271</v>
       </c>
       <c r="K86" s="7"/>
     </row>
@@ -5281,22 +5287,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.139697</v>
+        <v>0.161571</v>
       </c>
       <c r="F87" s="7">
-        <v>0.236238</v>
+        <v>0.266355</v>
       </c>
       <c r="G87" s="7">
-        <v>0.280565</v>
+        <v>0.324936</v>
       </c>
       <c r="H87" s="7">
-        <v>0.337918</v>
+        <v>0.36359699999999995</v>
       </c>
       <c r="I87" s="7">
-        <v>0.685268</v>
+        <v>0.717614</v>
       </c>
       <c r="J87" s="7">
-        <v>4.27189</v>
+        <v>4.338633</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,25 +5320,25 @@
         <v>7</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.012073</v>
+        <v>-0.011240000000000002</v>
       </c>
       <c r="F88" s="7">
-        <v>-0.079031</v>
+        <v>-0.10585900000000001</v>
       </c>
       <c r="G88" s="7">
-        <v>0.198265</v>
+        <v>0.204522</v>
       </c>
       <c r="H88" s="7">
-        <v>0.071742</v>
+        <v>0.072646</v>
       </c>
       <c r="I88" s="7">
-        <v>0.62235</v>
+        <v>0.6237189999999999</v>
       </c>
       <c r="J88" s="7">
-        <v>4.145385</v>
+        <v>4.043439</v>
       </c>
       <c r="K88" s="7">
-        <v>13.875522</v>
+        <v>13.754674999999999</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5349,25 +5355,25 @@
         <v>3</v>
       </c>
       <c r="E89" s="7">
-        <v>0.031000999999999997</v>
+        <v>0.032234</v>
       </c>
       <c r="F89" s="7">
-        <v>0.090059</v>
+        <v>0.090405</v>
       </c>
       <c r="G89" s="7">
-        <v>0.20366700000000001</v>
+        <v>0.20295100000000002</v>
       </c>
       <c r="H89" s="7">
-        <v>0.132187</v>
+        <v>0.13354100000000002</v>
       </c>
       <c r="I89" s="7">
-        <v>0.510306</v>
+        <v>0.512112</v>
       </c>
       <c r="J89" s="7">
-        <v>2.405185</v>
+        <v>2.402189</v>
       </c>
       <c r="K89" s="7">
-        <v>4.313124</v>
+        <v>4.31213</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5384,25 +5390,25 @@
         <v>5</v>
       </c>
       <c r="E90" s="7">
-        <v>0.027328</v>
+        <v>0.02421</v>
       </c>
       <c r="F90" s="7">
-        <v>0.005965000000000001</v>
+        <v>0.007272999999999999</v>
       </c>
       <c r="G90" s="7">
-        <v>0.15303699999999998</v>
+        <v>0.15512700000000001</v>
       </c>
       <c r="H90" s="7">
-        <v>0.080771</v>
+        <v>0.077491</v>
       </c>
       <c r="I90" s="7">
-        <v>0.308527</v>
+        <v>0.304557</v>
       </c>
       <c r="J90" s="7">
-        <v>2.0721350000000003</v>
+        <v>2.047599</v>
       </c>
       <c r="K90" s="7">
-        <v>5.394784</v>
+        <v>5.358314</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5419,22 +5425,22 @@
         <v>6</v>
       </c>
       <c r="E91" s="7">
-        <v>0.053329</v>
+        <v>0.046799999999999994</v>
       </c>
       <c r="F91" s="7">
-        <v>0.033295</v>
+        <v>0.023294000000000002</v>
       </c>
       <c r="G91" s="7">
-        <v>0.23268699999999998</v>
+        <v>0.237269</v>
       </c>
       <c r="H91" s="7">
-        <v>0.17274</v>
+        <v>0.165471</v>
       </c>
       <c r="I91" s="7">
-        <v>0.429334</v>
+        <v>0.420475</v>
       </c>
       <c r="J91" s="7">
-        <v>2.6364120000000004</v>
+        <v>2.640673</v>
       </c>
       <c r="K91" s="7"/>
     </row>
@@ -5452,25 +5458,25 @@
         <v>5</v>
       </c>
       <c r="E92" s="7">
-        <v>0.035973000000000005</v>
+        <v>0.032818</v>
       </c>
       <c r="F92" s="7">
-        <v>0.00471</v>
+        <v>0.0058379999999999994</v>
       </c>
       <c r="G92" s="7">
-        <v>0.18294899999999997</v>
+        <v>0.184844</v>
       </c>
       <c r="H92" s="7">
-        <v>0.09342800000000001</v>
+        <v>0.09009700000000001</v>
       </c>
       <c r="I92" s="7">
-        <v>0.35283299999999995</v>
+        <v>0.348712</v>
       </c>
       <c r="J92" s="7">
-        <v>1.991168</v>
+        <v>1.9801609999999998</v>
       </c>
       <c r="K92" s="7">
-        <v>4.911771</v>
+        <v>4.897619000000001</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -5487,25 +5493,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.037071</v>
+        <v>0.038193000000000005</v>
       </c>
       <c r="F93" s="7">
-        <v>0.067096</v>
+        <v>0.068113</v>
       </c>
       <c r="G93" s="7">
-        <v>0.19652999999999998</v>
+        <v>0.2028</v>
       </c>
       <c r="H93" s="7">
-        <v>0.13622299999999998</v>
+        <v>0.137453</v>
       </c>
       <c r="I93" s="7">
-        <v>0.363625</v>
+        <v>0.365101</v>
       </c>
       <c r="J93" s="7">
-        <v>1.7889439999999999</v>
+        <v>1.7541319999999998</v>
       </c>
       <c r="K93" s="7">
-        <v>4.629904</v>
+        <v>4.632845</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5522,25 +5528,25 @@
         <v>4</v>
       </c>
       <c r="E94" s="7">
-        <v>0.051948999999999995</v>
+        <v>0.045155</v>
       </c>
       <c r="F94" s="7">
-        <v>0.018813</v>
+        <v>0.012157</v>
       </c>
       <c r="G94" s="7">
-        <v>0.250418</v>
+        <v>0.252778</v>
       </c>
       <c r="H94" s="7">
-        <v>0.164179</v>
+        <v>0.15666</v>
       </c>
       <c r="I94" s="7">
-        <v>0.507241</v>
+        <v>0.49750500000000003</v>
       </c>
       <c r="J94" s="7">
-        <v>2.867379</v>
+        <v>2.8352640000000005</v>
       </c>
       <c r="K94" s="7">
-        <v>8.256237</v>
+        <v>8.191322</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5557,25 +5563,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.019382999999999997</v>
+        <v>0.021368</v>
       </c>
       <c r="F95" s="7">
-        <v>0.00231</v>
+        <v>0.00637</v>
       </c>
       <c r="G95" s="7">
-        <v>0.15071199999999998</v>
+        <v>0.155541</v>
       </c>
       <c r="H95" s="7">
-        <v>0.042908</v>
+        <v>0.044939</v>
       </c>
       <c r="I95" s="7">
-        <v>0.409829</v>
+        <v>0.412574</v>
       </c>
       <c r="J95" s="7">
-        <v>1.342395</v>
+        <v>1.3446639999999999</v>
       </c>
       <c r="K95" s="7">
-        <v>2.73139</v>
+        <v>2.734427</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5592,25 +5598,25 @@
         <v>7</v>
       </c>
       <c r="E96" s="7">
-        <v>0.064573</v>
+        <v>0.052142999999999995</v>
       </c>
       <c r="F96" s="7">
-        <v>-0.026277</v>
+        <v>-0.030139999999999997</v>
       </c>
       <c r="G96" s="7">
-        <v>0.24715199999999998</v>
+        <v>0.25186</v>
       </c>
       <c r="H96" s="7">
-        <v>0.202974</v>
+        <v>0.188928</v>
       </c>
       <c r="I96" s="7">
-        <v>0.41411000000000003</v>
+        <v>0.397598</v>
       </c>
       <c r="J96" s="7">
-        <v>2.9873559999999997</v>
+        <v>2.922257</v>
       </c>
       <c r="K96" s="7">
-        <v>14.656436000000001</v>
+        <v>14.489949999999999</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5627,25 +5633,25 @@
         <v>6</v>
       </c>
       <c r="E97" s="7">
-        <v>0.053669</v>
+        <v>0.045721</v>
       </c>
       <c r="F97" s="7">
-        <v>-0.018577999999999997</v>
+        <v>-0.011603</v>
       </c>
       <c r="G97" s="7">
-        <v>0.366509</v>
+        <v>0.374288</v>
       </c>
       <c r="H97" s="7">
-        <v>0.215129</v>
+        <v>0.205962</v>
       </c>
       <c r="I97" s="7">
-        <v>0.5449069999999999</v>
+        <v>0.533253</v>
       </c>
       <c r="J97" s="7">
-        <v>4.202305</v>
+        <v>4.144136</v>
       </c>
       <c r="K97" s="7">
-        <v>19.387493</v>
+        <v>19.238388</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5662,25 +5668,25 @@
         <v>4</v>
       </c>
       <c r="E98" s="7">
-        <v>0.053819</v>
+        <v>0.047397</v>
       </c>
       <c r="F98" s="7">
-        <v>0.042754</v>
+        <v>0.040076</v>
       </c>
       <c r="G98" s="7">
-        <v>0.27510999999999997</v>
+        <v>0.276315</v>
       </c>
       <c r="H98" s="7">
-        <v>0.205556</v>
+        <v>0.19820900000000002</v>
       </c>
       <c r="I98" s="7">
-        <v>0.553211</v>
+        <v>0.5437449999999999</v>
       </c>
       <c r="J98" s="7">
-        <v>3.563867</v>
+        <v>3.5298110000000005</v>
       </c>
       <c r="K98" s="7">
-        <v>9.171838000000001</v>
+        <v>9.11567</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5697,25 +5703,25 @@
         <v>6</v>
       </c>
       <c r="E99" s="7">
-        <v>0.023035</v>
+        <v>0.025698</v>
       </c>
       <c r="F99" s="7">
-        <v>0.039592999999999996</v>
+        <v>0.040510000000000004</v>
       </c>
       <c r="G99" s="7">
-        <v>0.09708399999999999</v>
+        <v>0.10114000000000001</v>
       </c>
       <c r="H99" s="7">
-        <v>0.057865</v>
+        <v>0.060619</v>
       </c>
       <c r="I99" s="7">
-        <v>0.27947700000000003</v>
+        <v>0.282808</v>
       </c>
       <c r="J99" s="7">
-        <v>1.985586</v>
+        <v>1.9948830000000002</v>
       </c>
       <c r="K99" s="7">
-        <v>5.721490999999999</v>
+        <v>5.719147</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5732,25 +5738,25 @@
         <v>5</v>
       </c>
       <c r="E100" s="7">
-        <v>0.059051</v>
+        <v>0.051143999999999995</v>
       </c>
       <c r="F100" s="7">
-        <v>0.034408</v>
+        <v>0.030888</v>
       </c>
       <c r="G100" s="7">
-        <v>0.33053899999999997</v>
+        <v>0.333562</v>
       </c>
       <c r="H100" s="7">
-        <v>0.213109</v>
+        <v>0.204051</v>
       </c>
       <c r="I100" s="7">
-        <v>0.600599</v>
+        <v>0.5886480000000001</v>
       </c>
       <c r="J100" s="7">
-        <v>3.76015</v>
+        <v>3.7255000000000003</v>
       </c>
       <c r="K100" s="7">
-        <v>12.118471</v>
+        <v>12.032399</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5767,25 +5773,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.07307000000000001</v>
+        <v>0.069948</v>
       </c>
       <c r="F101" s="7">
-        <v>0.060476</v>
+        <v>0.06078</v>
       </c>
       <c r="G101" s="7">
-        <v>0.337377</v>
+        <v>0.34891300000000003</v>
       </c>
       <c r="H101" s="7">
-        <v>0.302415</v>
+        <v>0.29862500000000003</v>
       </c>
       <c r="I101" s="7">
-        <v>0.6835469999999999</v>
+        <v>0.678648</v>
       </c>
       <c r="J101" s="7">
-        <v>3.6782549999999996</v>
+        <v>3.6056909999999998</v>
       </c>
       <c r="K101" s="7">
-        <v>11.360783</v>
+        <v>11.313052</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5802,25 +5808,25 @@
         <v>2</v>
       </c>
       <c r="E102" s="7">
-        <v>0.035977999999999996</v>
+        <v>0.036081</v>
       </c>
       <c r="F102" s="7">
-        <v>0.093125</v>
+        <v>0.093925</v>
       </c>
       <c r="G102" s="7">
-        <v>0.255722</v>
+        <v>0.256886</v>
       </c>
       <c r="H102" s="7">
-        <v>0.159378</v>
+        <v>0.159494</v>
       </c>
       <c r="I102" s="7">
-        <v>0.569662</v>
+        <v>0.5698190000000001</v>
       </c>
       <c r="J102" s="7">
-        <v>3.126903</v>
+        <v>3.1235820000000003</v>
       </c>
       <c r="K102" s="7">
-        <v>5.721083</v>
+        <v>5.715453</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5837,25 +5843,25 @@
         <v>6</v>
       </c>
       <c r="E103" s="7">
-        <v>0.078654</v>
+        <v>0.074949</v>
       </c>
       <c r="F103" s="7">
-        <v>0.046654</v>
+        <v>0.046898</v>
       </c>
       <c r="G103" s="7">
-        <v>0.34385599999999994</v>
+        <v>0.356656</v>
       </c>
       <c r="H103" s="7">
-        <v>0.319778</v>
+        <v>0.315244</v>
       </c>
       <c r="I103" s="7">
-        <v>0.683319</v>
+        <v>0.677536</v>
       </c>
       <c r="J103" s="7">
-        <v>3.5977499999999996</v>
+        <v>3.522417</v>
       </c>
       <c r="K103" s="7">
-        <v>13.403554</v>
+        <v>13.324558999999999</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5872,25 +5878,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.027816999999999998</v>
+        <v>0.031181999999999998</v>
       </c>
       <c r="F104" s="7">
-        <v>0.030968</v>
+        <v>0.03298</v>
       </c>
       <c r="G104" s="7">
-        <v>0.09057399999999999</v>
+        <v>0.095984</v>
       </c>
       <c r="H104" s="7">
-        <v>0.043525</v>
+        <v>0.046942000000000005</v>
       </c>
       <c r="I104" s="7">
-        <v>0.313093</v>
+        <v>0.317392</v>
       </c>
       <c r="J104" s="7">
-        <v>2.140996</v>
+        <v>2.144174</v>
       </c>
       <c r="K104" s="7">
-        <v>6.108465</v>
+        <v>6.104048000000001</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5907,16 +5913,16 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.080526</v>
+        <v>0.08285999999999999</v>
       </c>
       <c r="F105" s="7">
-        <v>0.027751</v>
+        <v>0.037109</v>
       </c>
       <c r="G105" s="7">
-        <v>0.173171</v>
+        <v>0.18734</v>
       </c>
       <c r="H105" s="7">
-        <v>0.14427</v>
+        <v>0.14674099999999998</v>
       </c>
       <c r="I105" s="7"/>
       <c r="J105" s="7"/>
@@ -5936,22 +5942,22 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.162088</v>
+        <v>0.184512</v>
       </c>
       <c r="F106" s="7">
-        <v>0.18682500000000002</v>
+        <v>0.227669</v>
       </c>
       <c r="G106" s="7">
-        <v>0.28759599999999996</v>
+        <v>0.31509899999999996</v>
       </c>
       <c r="H106" s="7">
-        <v>0.300851</v>
+        <v>0.325953</v>
       </c>
       <c r="I106" s="7">
-        <v>0.789971</v>
+        <v>0.824512</v>
       </c>
       <c r="J106" s="7">
-        <v>4.308962</v>
+        <v>4.420998</v>
       </c>
       <c r="K106" s="7"/>
     </row>
@@ -5969,25 +5975,25 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>-0.00819</v>
+        <v>-0.004424</v>
       </c>
       <c r="F107" s="7">
-        <v>-0.073533</v>
+        <v>-0.09498200000000001</v>
       </c>
       <c r="G107" s="7">
-        <v>0.22143100000000002</v>
+        <v>0.229829</v>
       </c>
       <c r="H107" s="7">
-        <v>0.09935100000000001</v>
+        <v>0.103526</v>
       </c>
       <c r="I107" s="7">
-        <v>0.669567</v>
+        <v>0.6759080000000001</v>
       </c>
       <c r="J107" s="7">
-        <v>4.833027</v>
+        <v>4.733434</v>
       </c>
       <c r="K107" s="7">
-        <v>15.938519</v>
+        <v>15.84657</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -6004,25 +6010,25 @@
         <v>3</v>
       </c>
       <c r="E108" s="7">
-        <v>0.025695000000000003</v>
+        <v>0.02726</v>
       </c>
       <c r="F108" s="7">
-        <v>0.031326</v>
+        <v>0.030901</v>
       </c>
       <c r="G108" s="7">
-        <v>0.17506799999999997</v>
+        <v>0.175576</v>
       </c>
       <c r="H108" s="7">
-        <v>0.068488</v>
+        <v>0.070119</v>
       </c>
       <c r="I108" s="7">
-        <v>0.452476</v>
+        <v>0.45469299999999996</v>
       </c>
       <c r="J108" s="7">
-        <v>2.032338</v>
+        <v>2.034739</v>
       </c>
       <c r="K108" s="7">
-        <v>3.873027</v>
+        <v>3.87781</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6039,25 +6045,25 @@
         <v>6</v>
       </c>
       <c r="E109" s="7">
-        <v>0.027440000000000003</v>
+        <v>0.031154</v>
       </c>
       <c r="F109" s="7">
-        <v>0.02886</v>
+        <v>0.030704</v>
       </c>
       <c r="G109" s="7">
-        <v>0.123764</v>
+        <v>0.130261</v>
       </c>
       <c r="H109" s="7">
-        <v>0.050826</v>
+        <v>0.054624</v>
       </c>
       <c r="I109" s="7">
-        <v>0.339846</v>
+        <v>0.34468899999999997</v>
       </c>
       <c r="J109" s="7">
-        <v>2.205133</v>
+        <v>2.207088</v>
       </c>
       <c r="K109" s="7">
-        <v>6.548129</v>
+        <v>6.5442100000000005</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,25 +6080,25 @@
         <v>3</v>
       </c>
       <c r="E110" s="7">
-        <v>0.048079000000000004</v>
+        <v>0.048792999999999996</v>
       </c>
       <c r="F110" s="7">
-        <v>0.080166</v>
+        <v>0.08084</v>
       </c>
       <c r="G110" s="7">
-        <v>0.20149899999999998</v>
+        <v>0.205548</v>
       </c>
       <c r="H110" s="7">
-        <v>0.15710000000000002</v>
+        <v>0.157888</v>
       </c>
       <c r="I110" s="7">
-        <v>0.482176</v>
+        <v>0.48318600000000006</v>
       </c>
       <c r="J110" s="7">
-        <v>2.012877</v>
+        <v>2.000371</v>
       </c>
       <c r="K110" s="7">
-        <v>5.523147</v>
+        <v>5.516307</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6109,25 +6115,25 @@
         <v>5</v>
       </c>
       <c r="E111" s="7">
-        <v>0.046379000000000004</v>
+        <v>0.045738</v>
       </c>
       <c r="F111" s="7">
-        <v>0.0005920000000000001</v>
+        <v>0.004491</v>
       </c>
       <c r="G111" s="7">
-        <v>0.215111</v>
+        <v>0.222096</v>
       </c>
       <c r="H111" s="7">
-        <v>0.142467</v>
+        <v>0.141768</v>
       </c>
       <c r="I111" s="7">
-        <v>0.546237</v>
+        <v>0.54529</v>
       </c>
       <c r="J111" s="7">
-        <v>3.526855</v>
+        <v>3.4805270000000004</v>
       </c>
       <c r="K111" s="7">
-        <v>14.390441000000001</v>
+        <v>14.333687</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6144,25 +6150,25 @@
         <v>3</v>
       </c>
       <c r="E112" s="7">
-        <v>0.031289</v>
+        <v>0.032062</v>
       </c>
       <c r="F112" s="7">
-        <v>0.079188</v>
+        <v>0.079204</v>
       </c>
       <c r="G112" s="7">
-        <v>0.232128</v>
+        <v>0.231888</v>
       </c>
       <c r="H112" s="7">
-        <v>0.140333</v>
+        <v>0.141188</v>
       </c>
       <c r="I112" s="7">
-        <v>0.525277</v>
+        <v>0.52642</v>
       </c>
       <c r="J112" s="7">
-        <v>3.277101</v>
+        <v>3.278126</v>
       </c>
       <c r="K112" s="7">
-        <v>6.253832999999999</v>
+        <v>6.248966</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6179,25 +6185,25 @@
         <v>6</v>
       </c>
       <c r="E113" s="7">
-        <v>0.096443</v>
+        <v>0.102547</v>
       </c>
       <c r="F113" s="7">
-        <v>0.077598</v>
+        <v>0.088643</v>
       </c>
       <c r="G113" s="7">
-        <v>0.264605</v>
+        <v>0.280188</v>
       </c>
       <c r="H113" s="7">
-        <v>0.24766200000000002</v>
+        <v>0.254608</v>
       </c>
       <c r="I113" s="7">
-        <v>0.5849989999999999</v>
+        <v>0.593824</v>
       </c>
       <c r="J113" s="7">
-        <v>3.6029050000000002</v>
+        <v>3.588534</v>
       </c>
       <c r="K113" s="7">
-        <v>16.765698999999998</v>
+        <v>16.756932</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6214,25 +6220,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.070133</v>
+        <v>0.060677</v>
       </c>
       <c r="F114" s="7">
-        <v>-0.009201</v>
+        <v>-0.008331</v>
       </c>
       <c r="G114" s="7">
-        <v>0.22591799999999998</v>
+        <v>0.225864</v>
       </c>
       <c r="H114" s="7">
-        <v>0.171187</v>
+        <v>0.160838</v>
       </c>
       <c r="I114" s="7">
-        <v>0.541315</v>
+        <v>0.5276959999999999</v>
       </c>
       <c r="J114" s="7">
-        <v>3.4136059999999997</v>
+        <v>3.3511509999999998</v>
       </c>
       <c r="K114" s="7">
-        <v>21.950469</v>
+        <v>21.6021</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6249,25 +6255,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.08602800000000001</v>
+        <v>0.080629</v>
       </c>
       <c r="F115" s="7">
-        <v>0.027090999999999997</v>
+        <v>0.029703</v>
       </c>
       <c r="G115" s="7">
-        <v>0.26802</v>
+        <v>0.272862</v>
       </c>
       <c r="H115" s="7">
-        <v>0.214271</v>
+        <v>0.208234</v>
       </c>
       <c r="I115" s="7">
-        <v>0.564639</v>
+        <v>0.55686</v>
       </c>
       <c r="J115" s="7">
-        <v>2.915849</v>
+        <v>2.897373</v>
       </c>
       <c r="K115" s="7">
-        <v>15.814993</v>
+        <v>15.6438</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6284,25 +6290,25 @@
         <v>5</v>
       </c>
       <c r="E116" s="7">
-        <v>0.075377</v>
+        <v>0.076403</v>
       </c>
       <c r="F116" s="7">
-        <v>0.095147</v>
+        <v>0.09766</v>
       </c>
       <c r="G116" s="7">
-        <v>0.282818</v>
+        <v>0.294003</v>
       </c>
       <c r="H116" s="7">
-        <v>0.255072</v>
+        <v>0.25627</v>
       </c>
       <c r="I116" s="7">
-        <v>0.664131</v>
+        <v>0.66572</v>
       </c>
       <c r="J116" s="7">
-        <v>3.3462</v>
+        <v>3.340158</v>
       </c>
       <c r="K116" s="7">
-        <v>12.281846</v>
+        <v>12.235641000000001</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6319,25 +6325,25 @@
         <v>3</v>
       </c>
       <c r="E117" s="7">
-        <v>0.024735</v>
+        <v>0.026715</v>
       </c>
       <c r="F117" s="7">
-        <v>0.026687</v>
+        <v>0.026767</v>
       </c>
       <c r="G117" s="7">
-        <v>0.17150300000000002</v>
+        <v>0.172363</v>
       </c>
       <c r="H117" s="7">
-        <v>0.061976</v>
+        <v>0.064029</v>
       </c>
       <c r="I117" s="7">
-        <v>0.422106</v>
+        <v>0.424854</v>
       </c>
       <c r="J117" s="7">
-        <v>1.840647</v>
+        <v>1.844666</v>
       </c>
       <c r="K117" s="7">
-        <v>3.665153</v>
+        <v>3.669441</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6354,25 +6360,25 @@
         <v>6</v>
       </c>
       <c r="E118" s="7">
-        <v>0.068454</v>
+        <v>0.06682</v>
       </c>
       <c r="F118" s="7">
-        <v>0.029044</v>
+        <v>0.030053999999999997</v>
       </c>
       <c r="G118" s="7">
-        <v>0.256629</v>
+        <v>0.26287</v>
       </c>
       <c r="H118" s="7">
-        <v>0.185601</v>
+        <v>0.18378699999999998</v>
       </c>
       <c r="I118" s="7">
-        <v>0.639918</v>
+        <v>0.63741</v>
       </c>
       <c r="J118" s="7">
-        <v>3.648063</v>
+        <v>3.633132</v>
       </c>
       <c r="K118" s="7">
-        <v>16.092722000000002</v>
+        <v>15.994412</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6389,25 +6395,25 @@
         <v>5</v>
       </c>
       <c r="E119" s="7">
-        <v>0.032074</v>
+        <v>0.027014999999999997</v>
       </c>
       <c r="F119" s="7">
-        <v>-0.00901</v>
+        <v>-0.009811</v>
       </c>
       <c r="G119" s="7">
-        <v>0.16931100000000002</v>
+        <v>0.17195799999999997</v>
       </c>
       <c r="H119" s="7">
-        <v>0.098798</v>
+        <v>0.09341100000000001</v>
       </c>
       <c r="I119" s="7">
-        <v>0.46142099999999997</v>
+        <v>0.45425699999999997</v>
       </c>
       <c r="J119" s="7">
-        <v>2.6487130000000003</v>
+        <v>2.609413</v>
       </c>
       <c r="K119" s="7">
-        <v>8.866062</v>
+        <v>8.797601</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6424,25 +6430,25 @@
         <v>6</v>
       </c>
       <c r="E120" s="7">
-        <v>0.037566</v>
+        <v>0.030038</v>
       </c>
       <c r="F120" s="7">
-        <v>-0.039608</v>
+        <v>-0.044013</v>
       </c>
       <c r="G120" s="7">
-        <v>0.151314</v>
+        <v>0.144789</v>
       </c>
       <c r="H120" s="7">
-        <v>0.11857699999999999</v>
+        <v>0.11045999999999999</v>
       </c>
       <c r="I120" s="7">
-        <v>0.432149</v>
+        <v>0.421758</v>
       </c>
       <c r="J120" s="7">
-        <v>3.4257799999999996</v>
+        <v>3.3641180000000004</v>
       </c>
       <c r="K120" s="7">
-        <v>17.591244</v>
+        <v>17.351952</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6459,25 +6465,25 @@
         <v>4</v>
       </c>
       <c r="E121" s="7">
-        <v>0.03614</v>
+        <v>0.03483</v>
       </c>
       <c r="F121" s="7">
-        <v>0.021999</v>
+        <v>0.022704</v>
       </c>
       <c r="G121" s="7">
-        <v>0.189218</v>
+        <v>0.19250399999999998</v>
       </c>
       <c r="H121" s="7">
-        <v>0.110267</v>
+        <v>0.108864</v>
       </c>
       <c r="I121" s="7">
-        <v>0.470145</v>
+        <v>0.46828699999999995</v>
       </c>
       <c r="J121" s="7">
-        <v>2.359316</v>
+        <v>2.347176</v>
       </c>
       <c r="K121" s="7">
-        <v>5.957211999999999</v>
+        <v>5.932505</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6494,25 +6500,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.031986</v>
+        <v>0.031086999999999997</v>
       </c>
       <c r="F122" s="7">
-        <v>0.023081</v>
+        <v>0.023860000000000003</v>
       </c>
       <c r="G122" s="7">
-        <v>0.165498</v>
+        <v>0.167712</v>
       </c>
       <c r="H122" s="7">
-        <v>0.097124</v>
+        <v>0.09616799999999999</v>
       </c>
       <c r="I122" s="7">
-        <v>0.424823</v>
+        <v>0.423581</v>
       </c>
       <c r="J122" s="7">
-        <v>1.9737049999999998</v>
+        <v>1.969641</v>
       </c>
       <c r="K122" s="7">
-        <v>5.9966930000000005</v>
+        <v>5.9824459999999995</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6529,16 +6535,16 @@
         <v>6</v>
       </c>
       <c r="E123" s="7">
-        <v>-0.011007</v>
+        <v>-0.004854</v>
       </c>
       <c r="F123" s="7">
-        <v>-0.092358</v>
+        <v>-0.113628</v>
       </c>
       <c r="G123" s="7">
-        <v>0.207109</v>
+        <v>0.21199</v>
       </c>
       <c r="H123" s="7">
-        <v>0.099658</v>
+        <v>0.10649900000000001</v>
       </c>
       <c r="I123" s="7"/>
       <c r="J123" s="7"/>
@@ -6558,25 +6564,25 @@
         <v>4</v>
       </c>
       <c r="E124" s="7">
-        <v>0.050217</v>
+        <v>0.045931</v>
       </c>
       <c r="F124" s="7">
-        <v>0.014584</v>
+        <v>0.015115</v>
       </c>
       <c r="G124" s="7">
-        <v>0.222893</v>
+        <v>0.226568</v>
       </c>
       <c r="H124" s="7">
-        <v>0.14469300000000002</v>
+        <v>0.140021</v>
       </c>
       <c r="I124" s="7">
-        <v>0.529807</v>
+        <v>0.523563</v>
       </c>
       <c r="J124" s="7">
-        <v>2.053705</v>
+        <v>2.036773</v>
       </c>
       <c r="K124" s="7">
-        <v>6.484788999999999</v>
+        <v>6.443688</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -6593,16 +6599,16 @@
         <v>6</v>
       </c>
       <c r="E125" s="7">
-        <v>0.12224299999999999</v>
+        <v>0.12794</v>
       </c>
       <c r="F125" s="7">
-        <v>0.12895</v>
+        <v>0.132827</v>
       </c>
       <c r="G125" s="7">
-        <v>0.34291</v>
+        <v>0.36851999999999996</v>
       </c>
       <c r="H125" s="7">
-        <v>0.348557</v>
+        <v>0.355403</v>
       </c>
       <c r="I125" s="7"/>
       <c r="J125" s="7"/>
@@ -6622,25 +6628,25 @@
         <v>7</v>
       </c>
       <c r="E126" s="7">
-        <v>0.078133</v>
+        <v>0.072114</v>
       </c>
       <c r="F126" s="7">
-        <v>0.019013</v>
+        <v>0.018462</v>
       </c>
       <c r="G126" s="7">
-        <v>0.187591</v>
+        <v>0.19386</v>
       </c>
       <c r="H126" s="7">
-        <v>0.119038</v>
+        <v>0.11279</v>
       </c>
       <c r="I126" s="7">
-        <v>0.439837</v>
+        <v>0.431798</v>
       </c>
       <c r="J126" s="7">
-        <v>2.5525040000000003</v>
+        <v>2.533849</v>
       </c>
       <c r="K126" s="7">
-        <v>9.176501</v>
+        <v>9.115143</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -6657,25 +6663,25 @@
         <v>5</v>
       </c>
       <c r="E127" s="7">
-        <v>0.026742</v>
+        <v>0.030513</v>
       </c>
       <c r="F127" s="7">
-        <v>0.023769</v>
+        <v>0.026617000000000002</v>
       </c>
       <c r="G127" s="7">
-        <v>0.08683</v>
+        <v>0.09251</v>
       </c>
       <c r="H127" s="7">
-        <v>0.041461</v>
+        <v>0.045285</v>
       </c>
       <c r="I127" s="7">
-        <v>0.27498100000000003</v>
+        <v>0.279663</v>
       </c>
       <c r="J127" s="7">
-        <v>1.956712</v>
+        <v>1.9615850000000001</v>
       </c>
       <c r="K127" s="7">
-        <v>5.527842000000001</v>
+        <v>5.533636</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6692,25 +6698,25 @@
         <v>4</v>
       </c>
       <c r="E128" s="7">
-        <v>0.018226</v>
+        <v>0.021496</v>
       </c>
       <c r="F128" s="7">
-        <v>-0.013986</v>
+        <v>-0.008976</v>
       </c>
       <c r="G128" s="7">
-        <v>0.12194</v>
+        <v>0.125953</v>
       </c>
       <c r="H128" s="7">
-        <v>0.03228</v>
+        <v>0.035595</v>
       </c>
       <c r="I128" s="7">
-        <v>0.369215</v>
+        <v>0.37361199999999994</v>
       </c>
       <c r="J128" s="7">
-        <v>1.5233009999999998</v>
+        <v>1.53053</v>
       </c>
       <c r="K128" s="7">
-        <v>3.3071789999999996</v>
+        <v>3.3181990000000003</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6727,25 +6733,25 @@
         <v>6</v>
       </c>
       <c r="E129" s="7">
-        <v>0.080842</v>
+        <v>0.069246</v>
       </c>
       <c r="F129" s="7">
-        <v>-0.001348</v>
+        <v>-0.004463</v>
       </c>
       <c r="G129" s="7">
-        <v>0.264262</v>
+        <v>0.266709</v>
       </c>
       <c r="H129" s="7">
-        <v>0.216537</v>
+        <v>0.20348500000000003</v>
       </c>
       <c r="I129" s="7">
-        <v>0.530377</v>
+        <v>0.513957</v>
       </c>
       <c r="J129" s="7">
-        <v>2.933602</v>
+        <v>2.887009</v>
       </c>
       <c r="K129" s="7">
-        <v>14.192372</v>
+        <v>14.012589</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6762,25 +6768,25 @@
         <v>4</v>
       </c>
       <c r="E130" s="7">
-        <v>0.031076000000000003</v>
+        <v>0.032802</v>
       </c>
       <c r="F130" s="7">
-        <v>0.025611000000000002</v>
+        <v>0.027014</v>
       </c>
       <c r="G130" s="7">
-        <v>0.074253</v>
+        <v>0.076559</v>
       </c>
       <c r="H130" s="7">
-        <v>0.035297999999999996</v>
+        <v>0.03703</v>
       </c>
       <c r="I130" s="7">
-        <v>0.276716</v>
+        <v>0.278853</v>
       </c>
       <c r="J130" s="7">
-        <v>2.027166</v>
+        <v>2.024619</v>
       </c>
       <c r="K130" s="7">
-        <v>6.2263459999999995</v>
+        <v>6.212858</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6797,19 +6803,19 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.109242</v>
+        <v>0.12983</v>
       </c>
       <c r="F131" s="7">
-        <v>0.127029</v>
+        <v>0.123047</v>
       </c>
       <c r="G131" s="7">
-        <v>0.198947</v>
+        <v>0.23183700000000002</v>
       </c>
       <c r="H131" s="7">
-        <v>0.253321</v>
+        <v>0.276583</v>
       </c>
       <c r="I131" s="7">
-        <v>0.7330289999999999</v>
+        <v>0.765195</v>
       </c>
       <c r="J131" s="7"/>
       <c r="K131" s="7"/>
@@ -6828,25 +6834,25 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.033902</v>
+        <v>0.031899000000000004</v>
       </c>
       <c r="F132" s="7">
-        <v>-0.0084</v>
+        <v>-0.006424999999999999</v>
       </c>
       <c r="G132" s="7">
-        <v>0.157111</v>
+        <v>0.159099</v>
       </c>
       <c r="H132" s="7">
-        <v>0.068572</v>
+        <v>0.066502</v>
       </c>
       <c r="I132" s="7">
-        <v>0.40301200000000004</v>
+        <v>0.40029400000000004</v>
       </c>
       <c r="J132" s="7">
-        <v>1.4785579999999998</v>
+        <v>1.471479</v>
       </c>
       <c r="K132" s="7">
-        <v>3.7400819999999997</v>
+        <v>3.7324149999999996</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -6863,25 +6869,25 @@
         <v>3</v>
       </c>
       <c r="E133" s="7">
-        <v>0.027738</v>
+        <v>0.02897</v>
       </c>
       <c r="F133" s="7">
-        <v>0.085854</v>
+        <v>0.085868</v>
       </c>
       <c r="G133" s="7">
-        <v>0.1867</v>
+        <v>0.18723099999999998</v>
       </c>
       <c r="H133" s="7">
-        <v>0.123371</v>
+        <v>0.12471700000000001</v>
       </c>
       <c r="I133" s="7">
-        <v>0.457598</v>
+        <v>0.459344</v>
       </c>
       <c r="J133" s="7">
-        <v>2.3028239999999998</v>
+        <v>2.306423</v>
       </c>
       <c r="K133" s="7">
-        <v>3.864905</v>
+        <v>3.8678179999999998</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6898,25 +6904,25 @@
         <v>6</v>
       </c>
       <c r="E134" s="7">
-        <v>0.050092</v>
+        <v>0.049042</v>
       </c>
       <c r="F134" s="7">
-        <v>0.047442000000000005</v>
+        <v>0.045103</v>
       </c>
       <c r="G134" s="7">
-        <v>0.22698000000000002</v>
+        <v>0.23066099999999998</v>
       </c>
       <c r="H134" s="7">
-        <v>0.166513</v>
+        <v>0.16534700000000002</v>
       </c>
       <c r="I134" s="7">
-        <v>0.47138399999999997</v>
+        <v>0.469914</v>
       </c>
       <c r="J134" s="7">
-        <v>2.93906</v>
+        <v>2.923928</v>
       </c>
       <c r="K134" s="7">
-        <v>7.776771999999999</v>
+        <v>7.760045</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6933,25 +6939,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.031492</v>
+        <v>0.032688999999999996</v>
       </c>
       <c r="F135" s="7">
-        <v>-0.007769000000000001</v>
+        <v>-0.0044469999999999996</v>
       </c>
       <c r="G135" s="7">
-        <v>0.135408</v>
+        <v>0.139548</v>
       </c>
       <c r="H135" s="7">
-        <v>0.061812</v>
+        <v>0.063044</v>
       </c>
       <c r="I135" s="7">
-        <v>0.33578600000000003</v>
+        <v>0.337336</v>
       </c>
       <c r="J135" s="7">
-        <v>1.018743</v>
+        <v>1.0224760000000002</v>
       </c>
       <c r="K135" s="7">
-        <v>2.406103</v>
+        <v>2.405748</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6968,25 +6974,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.069189</v>
+        <v>0.063985</v>
       </c>
       <c r="F136" s="7">
-        <v>0.072489</v>
+        <v>0.069847</v>
       </c>
       <c r="G136" s="7">
-        <v>0.16704799999999997</v>
+        <v>0.164076</v>
       </c>
       <c r="H136" s="7">
-        <v>0.154892</v>
+        <v>0.149271</v>
       </c>
       <c r="I136" s="7">
-        <v>0.435321</v>
+        <v>0.428335</v>
       </c>
       <c r="J136" s="7">
-        <v>3.106724</v>
+        <v>3.098236</v>
       </c>
       <c r="K136" s="7">
-        <v>9.292463</v>
+        <v>9.264873</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7003,25 +7009,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.038267999999999996</v>
+        <v>0.038531</v>
       </c>
       <c r="F137" s="7">
-        <v>0.040227000000000006</v>
+        <v>0.041672</v>
       </c>
       <c r="G137" s="7">
-        <v>0.162155</v>
+        <v>0.16558900000000001</v>
       </c>
       <c r="H137" s="7">
-        <v>0.10045899999999999</v>
+        <v>0.10073700000000001</v>
       </c>
       <c r="I137" s="7">
-        <v>0.426946</v>
+        <v>0.427306</v>
       </c>
       <c r="J137" s="7">
-        <v>2.171993</v>
+        <v>2.172069</v>
       </c>
       <c r="K137" s="7">
-        <v>4.137786</v>
+        <v>4.136703</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7038,22 +7044,22 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.16935099999999997</v>
+        <v>0.201029</v>
       </c>
       <c r="F138" s="7">
-        <v>0.12584</v>
+        <v>0.160412</v>
       </c>
       <c r="G138" s="7">
-        <v>0.241608</v>
+        <v>0.29702100000000003</v>
       </c>
       <c r="H138" s="7">
-        <v>0.22085999999999997</v>
+        <v>0.253933</v>
       </c>
       <c r="I138" s="7">
-        <v>0.785528</v>
+        <v>0.8338979999999999</v>
       </c>
       <c r="J138" s="7">
-        <v>5.285132999999999</v>
+        <v>5.446948</v>
       </c>
       <c r="K138" s="7"/>
     </row>
@@ -7071,22 +7077,22 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.060378</v>
+        <v>0.058712</v>
       </c>
       <c r="F139" s="7">
-        <v>-0.000619</v>
+        <v>-0.001227</v>
       </c>
       <c r="G139" s="7">
-        <v>0.178947</v>
+        <v>0.183673</v>
       </c>
       <c r="H139" s="7">
-        <v>0.10418799999999999</v>
+        <v>0.102453</v>
       </c>
       <c r="I139" s="7">
-        <v>0.513268</v>
+        <v>0.51089</v>
       </c>
       <c r="J139" s="7">
-        <v>4.877003</v>
+        <v>4.883822</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,25 +7110,25 @@
         <v>3</v>
       </c>
       <c r="E140" s="7">
-        <v>0.028277</v>
+        <v>0.027034</v>
       </c>
       <c r="F140" s="7">
-        <v>0.004917</v>
+        <v>0.005785</v>
       </c>
       <c r="G140" s="7">
-        <v>0.144824</v>
+        <v>0.14553000000000002</v>
       </c>
       <c r="H140" s="7">
-        <v>0.080353</v>
+        <v>0.079046</v>
       </c>
       <c r="I140" s="7">
-        <v>0.360399</v>
+        <v>0.35875300000000004</v>
       </c>
       <c r="J140" s="7">
-        <v>1.601072</v>
+        <v>1.600343</v>
       </c>
       <c r="K140" s="7">
-        <v>3.578431</v>
+        <v>3.570306</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7139,25 +7145,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.035441</v>
+        <v>0.035892</v>
       </c>
       <c r="F141" s="7">
-        <v>0.059345999999999996</v>
+        <v>0.059829999999999994</v>
       </c>
       <c r="G141" s="7">
-        <v>0.177332</v>
+        <v>0.182973</v>
       </c>
       <c r="H141" s="7">
-        <v>0.121402</v>
+        <v>0.12189</v>
       </c>
       <c r="I141" s="7">
-        <v>0.35690600000000006</v>
+        <v>0.35749600000000004</v>
       </c>
       <c r="J141" s="7">
-        <v>1.4370500000000002</v>
+        <v>1.41536</v>
       </c>
       <c r="K141" s="7">
-        <v>4.462117</v>
+        <v>4.460268</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7174,25 +7180,25 @@
         <v>5</v>
       </c>
       <c r="E142" s="7">
-        <v>0.11337799999999999</v>
+        <v>0.10963300000000001</v>
       </c>
       <c r="F142" s="7">
-        <v>0.005078</v>
+        <v>0.011469</v>
       </c>
       <c r="G142" s="7">
-        <v>0.212593</v>
+        <v>0.224463</v>
       </c>
       <c r="H142" s="7">
-        <v>0.165245</v>
+        <v>0.161325</v>
       </c>
       <c r="I142" s="7">
-        <v>0.374251</v>
+        <v>0.369628</v>
       </c>
       <c r="J142" s="7">
-        <v>3.4012439999999997</v>
+        <v>3.367928</v>
       </c>
       <c r="K142" s="7">
-        <v>13.360289999999999</v>
+        <v>13.346333999999999</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7209,25 +7215,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.063275</v>
+        <v>0.056233000000000005</v>
       </c>
       <c r="F143" s="7">
-        <v>0.142564</v>
+        <v>0.132109</v>
       </c>
       <c r="G143" s="7">
-        <v>0.17516500000000002</v>
+        <v>0.18787600000000002</v>
       </c>
       <c r="H143" s="7">
-        <v>0.283222</v>
+        <v>0.274723</v>
       </c>
       <c r="I143" s="7">
-        <v>0.274709</v>
+        <v>0.266266</v>
       </c>
       <c r="J143" s="7">
-        <v>3.629595</v>
+        <v>3.579948</v>
       </c>
       <c r="K143" s="7">
-        <v>10.884748</v>
+        <v>10.85731</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7244,25 +7250,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.070012</v>
+        <v>0.065604</v>
       </c>
       <c r="F144" s="7">
-        <v>0.062805</v>
+        <v>0.061422</v>
       </c>
       <c r="G144" s="7">
-        <v>0.29408</v>
+        <v>0.291833</v>
       </c>
       <c r="H144" s="7">
-        <v>0.197333</v>
+        <v>0.19240200000000002</v>
       </c>
       <c r="I144" s="7">
-        <v>0.570605</v>
+        <v>0.564136</v>
       </c>
       <c r="J144" s="7">
-        <v>2.9778640000000003</v>
+        <v>2.9362079999999997</v>
       </c>
       <c r="K144" s="7">
-        <v>8.111685</v>
+        <v>8.075185</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7279,25 +7285,25 @@
         <v>4</v>
       </c>
       <c r="E145" s="7">
-        <v>0.058346</v>
+        <v>0.052929000000000004</v>
       </c>
       <c r="F145" s="7">
-        <v>0.006443</v>
+        <v>0.006387</v>
       </c>
       <c r="G145" s="7">
-        <v>0.235688</v>
+        <v>0.236599</v>
       </c>
       <c r="H145" s="7">
-        <v>0.163796</v>
+        <v>0.15783899999999998</v>
       </c>
       <c r="I145" s="7">
-        <v>0.539823</v>
+        <v>0.531941</v>
       </c>
       <c r="J145" s="7">
-        <v>3.5019810000000002</v>
+        <v>3.47853</v>
       </c>
       <c r="K145" s="7">
-        <v>9.355245</v>
+        <v>9.290787</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7314,25 +7320,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.02306</v>
+        <v>0.021880999999999998</v>
       </c>
       <c r="F146" s="7">
-        <v>0.139182</v>
+        <v>0.13863</v>
       </c>
       <c r="G146" s="7">
-        <v>0.32036200000000004</v>
+        <v>0.345574</v>
       </c>
       <c r="H146" s="7">
-        <v>0.261191</v>
+        <v>0.259738</v>
       </c>
       <c r="I146" s="7">
-        <v>0.6146159999999999</v>
+        <v>0.612756</v>
       </c>
       <c r="J146" s="7">
-        <v>3.1822519999999996</v>
+        <v>3.1849740000000004</v>
       </c>
       <c r="K146" s="7">
-        <v>9.279271</v>
+        <v>9.323773</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7349,25 +7355,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.028637000000000003</v>
+        <v>0.028813</v>
       </c>
       <c r="F147" s="7">
-        <v>0.071454</v>
+        <v>0.07061200000000001</v>
       </c>
       <c r="G147" s="7">
-        <v>0.187618</v>
+        <v>0.19098600000000002</v>
       </c>
       <c r="H147" s="7">
-        <v>0.133128</v>
+        <v>0.133322</v>
       </c>
       <c r="I147" s="7">
-        <v>0.461409</v>
+        <v>0.461659</v>
       </c>
       <c r="J147" s="7">
-        <v>2.2721199999999997</v>
+        <v>2.2588239999999997</v>
       </c>
       <c r="K147" s="7">
-        <v>6.483256</v>
+        <v>6.472485000000001</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7384,25 +7390,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.025456</v>
+        <v>0.023605</v>
       </c>
       <c r="F148" s="7">
-        <v>0.01214</v>
+        <v>-0.002157</v>
       </c>
       <c r="G148" s="7">
-        <v>0.214969</v>
+        <v>0.22589700000000001</v>
       </c>
       <c r="H148" s="7">
-        <v>0.122948</v>
+        <v>0.120921</v>
       </c>
       <c r="I148" s="7">
-        <v>0.554724</v>
+        <v>0.551917</v>
       </c>
       <c r="J148" s="7">
-        <v>3.313724</v>
+        <v>3.279656</v>
       </c>
       <c r="K148" s="7">
-        <v>9.462726</v>
+        <v>9.435426</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7419,25 +7425,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.048288000000000005</v>
+        <v>0.049094</v>
       </c>
       <c r="F149" s="7">
-        <v>0.07013899999999999</v>
+        <v>0.072694</v>
       </c>
       <c r="G149" s="7">
-        <v>0.177669</v>
+        <v>0.181265</v>
       </c>
       <c r="H149" s="7">
-        <v>0.141878</v>
+        <v>0.142756</v>
       </c>
       <c r="I149" s="7">
-        <v>0.403361</v>
+        <v>0.404441</v>
       </c>
       <c r="J149" s="7">
-        <v>1.526266</v>
+        <v>1.511063</v>
       </c>
       <c r="K149" s="7">
-        <v>4.224914</v>
+        <v>4.2444690000000005</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7454,25 +7460,25 @@
         <v>5</v>
       </c>
       <c r="E150" s="7">
-        <v>0.105877</v>
+        <v>0.11297800000000001</v>
       </c>
       <c r="F150" s="7">
-        <v>0.09711399999999999</v>
+        <v>0.108736</v>
       </c>
       <c r="G150" s="7">
-        <v>0.255175</v>
+        <v>0.276212</v>
       </c>
       <c r="H150" s="7">
-        <v>0.256004</v>
+        <v>0.26407</v>
       </c>
       <c r="I150" s="7">
-        <v>0.59254</v>
+        <v>0.6027669999999999</v>
       </c>
       <c r="J150" s="7">
-        <v>2.9460879999999996</v>
+        <v>2.928431</v>
       </c>
       <c r="K150" s="7">
-        <v>8.45995</v>
+        <v>8.526884</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7489,25 +7495,25 @@
         <v>7</v>
       </c>
       <c r="E151" s="7">
-        <v>0.08998900000000001</v>
+        <v>0.095847</v>
       </c>
       <c r="F151" s="7">
-        <v>0.09686199999999999</v>
+        <v>0.1061</v>
       </c>
       <c r="G151" s="7">
-        <v>0.24600999999999998</v>
+        <v>0.263138</v>
       </c>
       <c r="H151" s="7">
-        <v>0.231095</v>
+        <v>0.23771</v>
       </c>
       <c r="I151" s="7">
-        <v>0.576712</v>
+        <v>0.585186</v>
       </c>
       <c r="J151" s="7">
-        <v>2.803002</v>
+        <v>2.782962</v>
       </c>
       <c r="K151" s="7">
-        <v>7.407556</v>
+        <v>7.418935</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7524,25 +7530,25 @@
         <v>3</v>
       </c>
       <c r="E152" s="7">
-        <v>0.032383999999999996</v>
+        <v>0.03365</v>
       </c>
       <c r="F152" s="7">
-        <v>0.063106</v>
+        <v>0.063402</v>
       </c>
       <c r="G152" s="7">
-        <v>0.19656500000000002</v>
+        <v>0.19825600000000002</v>
       </c>
       <c r="H152" s="7">
-        <v>0.123027</v>
+        <v>0.124404</v>
       </c>
       <c r="I152" s="7">
-        <v>0.475696</v>
+        <v>0.477504</v>
       </c>
       <c r="J152" s="7">
-        <v>2.947392</v>
+        <v>2.9442489999999997</v>
       </c>
       <c r="K152" s="7">
-        <v>5.066383</v>
+        <v>5.070126</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7559,22 +7565,22 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.072736</v>
+        <v>0.077719</v>
       </c>
       <c r="F153" s="7">
-        <v>0.027548</v>
+        <v>0.033117</v>
       </c>
       <c r="G153" s="7">
-        <v>0.17887699999999998</v>
+        <v>0.19069400000000003</v>
       </c>
       <c r="H153" s="7">
-        <v>0.13631500000000002</v>
+        <v>0.141592</v>
       </c>
       <c r="I153" s="7">
-        <v>0.48808100000000004</v>
+        <v>0.49499200000000004</v>
       </c>
       <c r="J153" s="7">
-        <v>3.45838</v>
+        <v>3.47776</v>
       </c>
       <c r="K153" s="7"/>
     </row>
@@ -7592,16 +7598,16 @@
         <v>4</v>
       </c>
       <c r="E154" s="7">
-        <v>0.042286000000000004</v>
+        <v>0.043008</v>
       </c>
       <c r="F154" s="7">
-        <v>0.063466</v>
+        <v>0.062247000000000004</v>
       </c>
       <c r="G154" s="7">
-        <v>0.24904900000000002</v>
+        <v>0.25895</v>
       </c>
       <c r="H154" s="7">
-        <v>0.186073</v>
+        <v>0.186894</v>
       </c>
       <c r="I154" s="7"/>
       <c r="J154" s="7"/>
@@ -7621,22 +7627,22 @@
         <v>6</v>
       </c>
       <c r="E155" s="7">
-        <v>0.07887</v>
+        <v>0.076822</v>
       </c>
       <c r="F155" s="7">
-        <v>0.043818</v>
+        <v>0.045197</v>
       </c>
       <c r="G155" s="7">
-        <v>0.20997699999999997</v>
+        <v>0.219519</v>
       </c>
       <c r="H155" s="7">
-        <v>0.180408</v>
+        <v>0.17816700000000002</v>
       </c>
       <c r="I155" s="7">
-        <v>0.442768</v>
+        <v>0.44002899999999995</v>
       </c>
       <c r="J155" s="7">
-        <v>1.8028309999999999</v>
+        <v>1.794424</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7654,25 +7660,25 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.054688999999999995</v>
+        <v>0.056524</v>
       </c>
       <c r="F156" s="7">
-        <v>0.084276</v>
+        <v>0.085831</v>
       </c>
       <c r="G156" s="7">
-        <v>0.24052800000000002</v>
+        <v>0.247557</v>
       </c>
       <c r="H156" s="7">
-        <v>0.173885</v>
+        <v>0.175927</v>
       </c>
       <c r="I156" s="7">
-        <v>0.547235</v>
+        <v>0.5499269999999999</v>
       </c>
       <c r="J156" s="7">
-        <v>2.463788</v>
+        <v>2.447056</v>
       </c>
       <c r="K156" s="7">
-        <v>6.441102</v>
+        <v>6.446605</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -7689,25 +7695,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.057674</v>
+        <v>0.059482999999999994</v>
       </c>
       <c r="F157" s="7">
-        <v>0.087606</v>
+        <v>0.08918799999999999</v>
       </c>
       <c r="G157" s="7">
-        <v>0.232395</v>
+        <v>0.239461</v>
       </c>
       <c r="H157" s="7">
-        <v>0.174181</v>
+        <v>0.176189</v>
       </c>
       <c r="I157" s="7">
-        <v>0.504925</v>
+        <v>0.507498</v>
       </c>
       <c r="J157" s="7">
-        <v>2.247586</v>
+        <v>2.230043</v>
       </c>
       <c r="K157" s="7">
-        <v>5.956523999999999</v>
+        <v>5.961824</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7724,25 +7730,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.043494000000000005</v>
+        <v>0.04552</v>
       </c>
       <c r="F158" s="7">
-        <v>0.071447</v>
+        <v>0.070338</v>
       </c>
       <c r="G158" s="7">
-        <v>0.205825</v>
+        <v>0.211359</v>
       </c>
       <c r="H158" s="7">
-        <v>0.14177</v>
+        <v>0.143987</v>
       </c>
       <c r="I158" s="7">
-        <v>0.440469</v>
+        <v>0.443265</v>
       </c>
       <c r="J158" s="7">
-        <v>1.868206</v>
+        <v>1.8574000000000002</v>
       </c>
       <c r="K158" s="7">
-        <v>5.056101</v>
+        <v>5.067511</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7759,22 +7765,22 @@
         <v>5</v>
       </c>
       <c r="E159" s="7">
-        <v>0.141008</v>
+        <v>0.163947</v>
       </c>
       <c r="F159" s="7">
-        <v>0.177102</v>
+        <v>0.21368600000000001</v>
       </c>
       <c r="G159" s="7">
-        <v>0.261898</v>
+        <v>0.307484</v>
       </c>
       <c r="H159" s="7">
-        <v>0.271588</v>
+        <v>0.297153</v>
       </c>
       <c r="I159" s="7">
-        <v>0.705018</v>
+        <v>0.739297</v>
       </c>
       <c r="J159" s="7">
-        <v>4.138168</v>
+        <v>4.246179000000001</v>
       </c>
       <c r="K159" s="7"/>
     </row>
@@ -7792,25 +7798,25 @@
         <v>4</v>
       </c>
       <c r="E160" s="7">
-        <v>0.036969</v>
+        <v>0.036234999999999996</v>
       </c>
       <c r="F160" s="7">
-        <v>0.01222</v>
+        <v>0.012354</v>
       </c>
       <c r="G160" s="7">
-        <v>0.187284</v>
+        <v>0.189668</v>
       </c>
       <c r="H160" s="7">
-        <v>0.090621</v>
+        <v>0.08985</v>
       </c>
       <c r="I160" s="7">
-        <v>0.421134</v>
+        <v>0.42012900000000003</v>
       </c>
       <c r="J160" s="7">
-        <v>2.0542420000000003</v>
+        <v>2.044801</v>
       </c>
       <c r="K160" s="7">
-        <v>5.611461</v>
+        <v>5.598555</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7827,22 +7833,22 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.029022000000000003</v>
+        <v>0.032792</v>
       </c>
       <c r="F161" s="7">
-        <v>0.07708</v>
+        <v>0.077807</v>
       </c>
       <c r="G161" s="7">
-        <v>0.219782</v>
+        <v>0.22300799999999998</v>
       </c>
       <c r="H161" s="7">
-        <v>0.15279</v>
+        <v>0.15701299999999999</v>
       </c>
       <c r="I161" s="7">
-        <v>0.536705</v>
+        <v>0.542335</v>
       </c>
       <c r="J161" s="7">
-        <v>3.425075</v>
+        <v>3.4348020000000004</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7860,22 +7866,22 @@
         <v>6</v>
       </c>
       <c r="E162" s="7">
-        <v>0.032458999999999995</v>
+        <v>0.040011</v>
       </c>
       <c r="F162" s="7">
-        <v>-0.014649</v>
+        <v>-0.012111</v>
       </c>
       <c r="G162" s="7">
-        <v>0.128013</v>
+        <v>0.142652</v>
       </c>
       <c r="H162" s="7">
-        <v>0.058743</v>
+        <v>0.06648799999999999</v>
       </c>
       <c r="I162" s="7">
-        <v>0.384765</v>
+        <v>0.394894</v>
       </c>
       <c r="J162" s="7">
-        <v>2.5681849999999997</v>
+        <v>2.5770800000000005</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,25 +7899,25 @@
         <v>5</v>
       </c>
       <c r="E163" s="7">
-        <v>0.08964</v>
+        <v>0.095298</v>
       </c>
       <c r="F163" s="7">
-        <v>0.10830000000000001</v>
+        <v>0.108153</v>
       </c>
       <c r="G163" s="7">
-        <v>0.304636</v>
+        <v>0.322894</v>
       </c>
       <c r="H163" s="7">
-        <v>0.26351199999999997</v>
+        <v>0.270073</v>
       </c>
       <c r="I163" s="7">
-        <v>0.65641</v>
+        <v>0.6650119999999999</v>
       </c>
       <c r="J163" s="7">
-        <v>2.6024380000000003</v>
+        <v>2.601946</v>
       </c>
       <c r="K163" s="7">
-        <v>8.676375</v>
+        <v>8.729905</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7928,25 +7934,25 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.104129</v>
+        <v>0.09859</v>
       </c>
       <c r="F164" s="7">
-        <v>0.050187</v>
+        <v>0.046166</v>
       </c>
       <c r="G164" s="7">
-        <v>0.337909</v>
+        <v>0.35136</v>
       </c>
       <c r="H164" s="7">
-        <v>0.284184</v>
+        <v>0.277742</v>
       </c>
       <c r="I164" s="7">
-        <v>0.658482</v>
+        <v>0.650161</v>
       </c>
       <c r="J164" s="7">
-        <v>1.973502</v>
+        <v>1.954711</v>
       </c>
       <c r="K164" s="7">
-        <v>3.6251209999999996</v>
+        <v>3.5931319999999998</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7963,25 +7969,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.08147700000000001</v>
+        <v>0.07254</v>
       </c>
       <c r="F165" s="7">
-        <v>0.001983</v>
+        <v>-0.001115</v>
       </c>
       <c r="G165" s="7">
-        <v>0.27728400000000003</v>
+        <v>0.282808</v>
       </c>
       <c r="H165" s="7">
-        <v>0.21991499999999997</v>
+        <v>0.209833</v>
       </c>
       <c r="I165" s="7">
-        <v>0.483748</v>
+        <v>0.471486</v>
       </c>
       <c r="J165" s="7">
-        <v>2.987584</v>
+        <v>2.938285</v>
       </c>
       <c r="K165" s="7">
-        <v>15.569567</v>
+        <v>15.444251</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7998,25 +8004,25 @@
         <v>3</v>
       </c>
       <c r="E166" s="7">
-        <v>0.022215</v>
+        <v>0.024353</v>
       </c>
       <c r="F166" s="7">
-        <v>-0.003675</v>
+        <v>-0.00031099999999999997</v>
       </c>
       <c r="G166" s="7">
-        <v>0.129434</v>
+        <v>0.131781</v>
       </c>
       <c r="H166" s="7">
-        <v>0.03858</v>
+        <v>0.040752</v>
       </c>
       <c r="I166" s="7">
-        <v>0.375966</v>
+        <v>0.378844</v>
       </c>
       <c r="J166" s="7">
-        <v>1.863999</v>
+        <v>1.865277</v>
       </c>
       <c r="K166" s="7">
-        <v>3.929673</v>
+        <v>3.935047</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8033,25 +8039,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.047118</v>
+        <v>0.048827999999999996</v>
       </c>
       <c r="F167" s="7">
-        <v>0.08372199999999999</v>
+        <v>0.08519299999999999</v>
       </c>
       <c r="G167" s="7">
-        <v>0.23465499999999997</v>
+        <v>0.241279</v>
       </c>
       <c r="H167" s="7">
-        <v>0.167663</v>
+        <v>0.16957</v>
       </c>
       <c r="I167" s="7">
-        <v>0.471602</v>
+        <v>0.474006</v>
       </c>
       <c r="J167" s="7">
-        <v>1.952733</v>
+        <v>1.947193</v>
       </c>
       <c r="K167" s="7">
-        <v>5.424809</v>
+        <v>5.443654</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8068,25 +8074,25 @@
         <v>5</v>
       </c>
       <c r="E168" s="7">
-        <v>0.023096000000000002</v>
+        <v>0.025779999999999997</v>
       </c>
       <c r="F168" s="7">
-        <v>0.060079</v>
+        <v>0.061985</v>
       </c>
       <c r="G168" s="7">
-        <v>0.123367</v>
+        <v>0.125438</v>
       </c>
       <c r="H168" s="7">
-        <v>0.083018</v>
+        <v>0.08586</v>
       </c>
       <c r="I168" s="7">
-        <v>0.30009</v>
+        <v>0.3035</v>
       </c>
       <c r="J168" s="7">
-        <v>1.9633150000000001</v>
+        <v>1.968194</v>
       </c>
       <c r="K168" s="7">
-        <v>5.477304</v>
+        <v>5.4763720000000005</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8103,22 +8109,22 @@
         <v>6</v>
       </c>
       <c r="E169" s="7">
-        <v>-0.012008000000000001</v>
+        <v>-0.009408</v>
       </c>
       <c r="F169" s="7">
-        <v>-0.08907899999999999</v>
+        <v>-0.113126</v>
       </c>
       <c r="G169" s="7">
-        <v>0.194972</v>
+        <v>0.195056</v>
       </c>
       <c r="H169" s="7">
-        <v>0.078552</v>
+        <v>0.08138999999999999</v>
       </c>
       <c r="I169" s="7">
-        <v>0.581206</v>
+        <v>0.5853670000000001</v>
       </c>
       <c r="J169" s="7">
-        <v>4.605155</v>
+        <v>4.554862</v>
       </c>
       <c r="K169" s="7"/>
     </row>
@@ -8136,22 +8142,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>0.096432</v>
+        <v>0.09339800000000001</v>
       </c>
       <c r="F170" s="7">
-        <v>0.032367</v>
+        <v>0.035163</v>
       </c>
       <c r="G170" s="7">
-        <v>0.21945900000000002</v>
+        <v>0.23081600000000002</v>
       </c>
       <c r="H170" s="7">
-        <v>0.19967600000000002</v>
+        <v>0.196356</v>
       </c>
       <c r="I170" s="7">
-        <v>0.48916</v>
+        <v>0.485039</v>
       </c>
       <c r="J170" s="7">
-        <v>2.561635</v>
+        <v>2.564412</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,16 +8175,16 @@
         <v>7</v>
       </c>
       <c r="E171" s="7">
-        <v>0.019592000000000002</v>
+        <v>0.02628</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.108354</v>
+        <v>-0.142865</v>
       </c>
       <c r="G171" s="7">
-        <v>0.533428</v>
+        <v>0.5709409999999999</v>
       </c>
       <c r="H171" s="7">
-        <v>0.032778999999999996</v>
+        <v>0.039554</v>
       </c>
       <c r="I171" s="7"/>
       <c r="J171" s="7"/>
@@ -8198,25 +8204,25 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>-0.018373999999999998</v>
+        <v>-0.020133</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.091246</v>
+        <v>-0.11688499999999999</v>
       </c>
       <c r="G172" s="7">
-        <v>0.17721900000000002</v>
+        <v>0.18067699999999998</v>
       </c>
       <c r="H172" s="7">
-        <v>0.049950999999999995</v>
+        <v>0.048069</v>
       </c>
       <c r="I172" s="7">
-        <v>0.549434</v>
+        <v>0.5466570000000001</v>
       </c>
       <c r="J172" s="7">
-        <v>4.024583</v>
+        <v>3.910662</v>
       </c>
       <c r="K172" s="7">
-        <v>13.342158999999999</v>
+        <v>13.188973</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -8233,25 +8239,25 @@
         <v>4</v>
       </c>
       <c r="E173" s="7">
-        <v>0.042298999999999996</v>
+        <v>0.041921</v>
       </c>
       <c r="F173" s="7">
-        <v>0.008394</v>
+        <v>0.009904</v>
       </c>
       <c r="G173" s="7">
-        <v>0.194478</v>
+        <v>0.19862300000000002</v>
       </c>
       <c r="H173" s="7">
-        <v>0.099413</v>
+        <v>0.099014</v>
       </c>
       <c r="I173" s="7">
-        <v>0.440969</v>
+        <v>0.440446</v>
       </c>
       <c r="J173" s="7">
-        <v>2.0761920000000003</v>
+        <v>2.065164</v>
       </c>
       <c r="K173" s="7">
-        <v>5.337560999999999</v>
+        <v>5.332063000000001</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8268,25 +8274,25 @@
         <v>5</v>
       </c>
       <c r="E174" s="7">
-        <v>0.068464</v>
+        <v>0.0647</v>
       </c>
       <c r="F174" s="7">
-        <v>0.027301000000000002</v>
+        <v>0.027688</v>
       </c>
       <c r="G174" s="7">
-        <v>0.245613</v>
+        <v>0.257992</v>
       </c>
       <c r="H174" s="7">
-        <v>0.20285799999999998</v>
+        <v>0.19862</v>
       </c>
       <c r="I174" s="7">
-        <v>0.45441899999999996</v>
+        <v>0.449295</v>
       </c>
       <c r="J174" s="7">
-        <v>2.806356</v>
+        <v>2.772321</v>
       </c>
       <c r="K174" s="7">
-        <v>10.330867000000001</v>
+        <v>10.301152</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8303,25 +8309,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.030807</v>
+        <v>0.035137999999999996</v>
       </c>
       <c r="F175" s="7">
-        <v>0.034491999999999995</v>
+        <v>0.037996</v>
       </c>
       <c r="G175" s="7">
-        <v>0.097073</v>
+        <v>0.10223</v>
       </c>
       <c r="H175" s="7">
-        <v>0.049601</v>
+        <v>0.054009999999999996</v>
       </c>
       <c r="I175" s="7">
-        <v>0.30303599999999997</v>
+        <v>0.308511</v>
       </c>
       <c r="J175" s="7">
-        <v>2.082099</v>
+        <v>2.086521</v>
       </c>
       <c r="K175" s="7">
-        <v>6.257223</v>
+        <v>6.267318</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8338,25 +8344,25 @@
         <v>6</v>
       </c>
       <c r="E176" s="7">
-        <v>0.097904</v>
+        <v>0.099252</v>
       </c>
       <c r="F176" s="7">
-        <v>0.050339999999999996</v>
+        <v>0.059071</v>
       </c>
       <c r="G176" s="7">
-        <v>0.234254</v>
+        <v>0.248623</v>
       </c>
       <c r="H176" s="7">
-        <v>0.189487</v>
+        <v>0.190948</v>
       </c>
       <c r="I176" s="7">
-        <v>0.589492</v>
+        <v>0.591444</v>
       </c>
       <c r="J176" s="7">
-        <v>2.982672</v>
+        <v>2.996277</v>
       </c>
       <c r="K176" s="7">
-        <v>12.135102</v>
+        <v>12.210261000000001</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,25 +8379,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.08453</v>
+        <v>0.07896399999999999</v>
       </c>
       <c r="F177" s="7">
-        <v>0.03786</v>
+        <v>0.037014</v>
       </c>
       <c r="G177" s="7">
-        <v>0.32032200000000005</v>
+        <v>0.32878599999999997</v>
       </c>
       <c r="H177" s="7">
-        <v>0.24481000000000003</v>
+        <v>0.238422</v>
       </c>
       <c r="I177" s="7">
-        <v>0.583269</v>
+        <v>0.575144</v>
       </c>
       <c r="J177" s="7">
-        <v>3.3667439999999997</v>
+        <v>3.324235</v>
       </c>
       <c r="K177" s="7">
-        <v>17.110637</v>
+        <v>16.989208</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8408,25 +8414,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.06861</v>
+        <v>0.065081</v>
       </c>
       <c r="F178" s="7">
-        <v>0.034398</v>
+        <v>0.03426</v>
       </c>
       <c r="G178" s="7">
-        <v>0.296063</v>
+        <v>0.30437000000000003</v>
       </c>
       <c r="H178" s="7">
-        <v>0.205439</v>
+        <v>0.201459</v>
       </c>
       <c r="I178" s="7">
-        <v>0.5244489999999999</v>
+        <v>0.519415</v>
       </c>
       <c r="J178" s="7">
-        <v>3.2231360000000002</v>
+        <v>3.1967529999999997</v>
       </c>
       <c r="K178" s="7">
-        <v>12.765730000000001</v>
+        <v>12.701608</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8443,25 +8449,25 @@
         <v>4</v>
       </c>
       <c r="E179" s="7">
-        <v>0.06046</v>
+        <v>0.056692</v>
       </c>
       <c r="F179" s="7">
-        <v>0.037309999999999996</v>
+        <v>0.035</v>
       </c>
       <c r="G179" s="7">
-        <v>0.269638</v>
+        <v>0.273073</v>
       </c>
       <c r="H179" s="7">
-        <v>0.172793</v>
+        <v>0.168626</v>
       </c>
       <c r="I179" s="7">
-        <v>0.533193</v>
+        <v>0.527745</v>
       </c>
       <c r="J179" s="7">
-        <v>3.445763</v>
+        <v>3.4144349999999997</v>
       </c>
       <c r="K179" s="7">
-        <v>11.127988</v>
+        <v>11.076666</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8478,25 +8484,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.07624399999999999</v>
+        <v>0.08879799999999999</v>
       </c>
       <c r="F180" s="7">
-        <v>0.040170000000000004</v>
+        <v>0.057173999999999996</v>
       </c>
       <c r="G180" s="7">
-        <v>0.144434</v>
+        <v>0.165682</v>
       </c>
       <c r="H180" s="7">
-        <v>0.10960900000000001</v>
+        <v>0.12255200000000001</v>
       </c>
       <c r="I180" s="7">
-        <v>0.52481</v>
+        <v>0.542597</v>
       </c>
       <c r="J180" s="7">
-        <v>3.22168</v>
+        <v>3.275119</v>
       </c>
       <c r="K180" s="7">
-        <v>8.245472</v>
+        <v>8.442419</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8513,25 +8519,25 @@
         <v>2</v>
       </c>
       <c r="E181" s="7">
-        <v>0.035412</v>
+        <v>0.035666</v>
       </c>
       <c r="F181" s="7">
-        <v>0.07133099999999999</v>
+        <v>0.070713</v>
       </c>
       <c r="G181" s="7">
-        <v>0.206016</v>
+        <v>0.206565</v>
       </c>
       <c r="H181" s="7">
-        <v>0.129063</v>
+        <v>0.12933999999999998</v>
       </c>
       <c r="I181" s="7">
-        <v>0.485578</v>
+        <v>0.48594299999999996</v>
       </c>
       <c r="J181" s="7">
-        <v>3.331048</v>
+        <v>3.329439</v>
       </c>
       <c r="K181" s="7">
-        <v>6.30337</v>
+        <v>6.300520000000001</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8548,25 +8554,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.065795</v>
+        <v>0.06116</v>
       </c>
       <c r="F182" s="7">
-        <v>0.015771999999999998</v>
+        <v>0.013181</v>
       </c>
       <c r="G182" s="7">
-        <v>0.11743</v>
+        <v>0.125304</v>
       </c>
       <c r="H182" s="7">
-        <v>0.155626</v>
+        <v>0.150601</v>
       </c>
       <c r="I182" s="7">
-        <v>0.357318</v>
+        <v>0.35141500000000003</v>
       </c>
       <c r="J182" s="7">
-        <v>2.437318</v>
+        <v>2.4082980000000003</v>
       </c>
       <c r="K182" s="7">
-        <v>3.90214</v>
+        <v>3.878943</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8583,25 +8589,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.10886100000000001</v>
+        <v>0.11751899999999998</v>
       </c>
       <c r="F183" s="7">
-        <v>0.125952</v>
+        <v>0.13175499999999998</v>
       </c>
       <c r="G183" s="7">
-        <v>0.367172</v>
+        <v>0.398472</v>
       </c>
       <c r="H183" s="7">
-        <v>0.33305599999999996</v>
+        <v>0.34346400000000005</v>
       </c>
       <c r="I183" s="7">
-        <v>0.7038949999999999</v>
+        <v>0.7171980000000001</v>
       </c>
       <c r="J183" s="7">
-        <v>3.357449</v>
+        <v>3.372898</v>
       </c>
       <c r="K183" s="7">
-        <v>12.979104</v>
+        <v>13.088893</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8618,25 +8624,25 @@
         <v>3</v>
       </c>
       <c r="E184" s="7">
-        <v>0.027978</v>
+        <v>0.028988</v>
       </c>
       <c r="F184" s="7">
-        <v>0.088238</v>
+        <v>0.08829000000000001</v>
       </c>
       <c r="G184" s="7">
-        <v>0.192716</v>
+        <v>0.19263000000000002</v>
       </c>
       <c r="H184" s="7">
-        <v>0.123544</v>
+        <v>0.12464800000000001</v>
       </c>
       <c r="I184" s="7">
-        <v>0.45358899999999996</v>
+        <v>0.45501800000000003</v>
       </c>
       <c r="J184" s="7">
-        <v>1.733425</v>
+        <v>1.7271360000000002</v>
       </c>
       <c r="K184" s="7">
-        <v>3.825388</v>
+        <v>3.827842</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8653,25 +8659,25 @@
         <v>5</v>
       </c>
       <c r="E185" s="7">
-        <v>0.090916</v>
+        <v>0.097926</v>
       </c>
       <c r="F185" s="7">
-        <v>0.105959</v>
+        <v>0.10946</v>
       </c>
       <c r="G185" s="7">
-        <v>0.28729</v>
+        <v>0.308183</v>
       </c>
       <c r="H185" s="7">
-        <v>0.251357</v>
+        <v>0.259397</v>
       </c>
       <c r="I185" s="7">
-        <v>0.633362</v>
+        <v>0.643856</v>
       </c>
       <c r="J185" s="7">
-        <v>3.063594</v>
+        <v>3.074142</v>
       </c>
       <c r="K185" s="7">
-        <v>11.147998</v>
+        <v>11.229678</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8688,25 +8694,25 @@
         <v>2</v>
       </c>
       <c r="E186" s="7">
-        <v>0.028155</v>
+        <v>0.029168</v>
       </c>
       <c r="F186" s="7">
-        <v>0.088284</v>
+        <v>0.088327</v>
       </c>
       <c r="G186" s="7">
-        <v>0.19002400000000003</v>
+        <v>0.189986</v>
       </c>
       <c r="H186" s="7">
-        <v>0.12319200000000001</v>
+        <v>0.124298</v>
       </c>
       <c r="I186" s="7">
-        <v>0.44800199999999996</v>
+        <v>0.449428</v>
       </c>
       <c r="J186" s="7">
-        <v>1.8350380000000002</v>
+        <v>1.835385</v>
       </c>
       <c r="K186" s="7">
-        <v>3.3356369999999997</v>
+        <v>3.3377280000000003</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8723,25 +8729,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.020739999999999998</v>
+        <v>0.021332</v>
       </c>
       <c r="F187" s="7">
-        <v>0.068831</v>
+        <v>0.065695</v>
       </c>
       <c r="G187" s="7">
-        <v>0.150328</v>
+        <v>0.149962</v>
       </c>
       <c r="H187" s="7">
-        <v>0.10138799999999999</v>
+        <v>0.102028</v>
       </c>
       <c r="I187" s="7">
-        <v>0.380041</v>
+        <v>0.380842</v>
       </c>
       <c r="J187" s="7">
-        <v>1.982143</v>
+        <v>1.983676</v>
       </c>
       <c r="K187" s="7">
-        <v>3.332616</v>
+        <v>3.332512</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8758,16 +8764,16 @@
         <v>6</v>
       </c>
       <c r="E188" s="7">
-        <v>0.034054</v>
+        <v>0.041459</v>
       </c>
       <c r="F188" s="7">
-        <v>-0.11831</v>
+        <v>-0.146521</v>
       </c>
       <c r="G188" s="7">
-        <v>0.504196</v>
+        <v>0.5440740000000001</v>
       </c>
       <c r="H188" s="7">
-        <v>0.017710999999999998</v>
+        <v>0.024998999999999997</v>
       </c>
       <c r="I188" s="7"/>
       <c r="J188" s="7"/>
@@ -8787,25 +8793,25 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>-0.013502</v>
+        <v>-0.012792</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.08307600000000001</v>
+        <v>-0.10898</v>
       </c>
       <c r="G189" s="7">
-        <v>0.190052</v>
+        <v>0.192335</v>
       </c>
       <c r="H189" s="7">
-        <v>0.060764</v>
+        <v>0.061528</v>
       </c>
       <c r="I189" s="7">
-        <v>0.569601</v>
+        <v>0.570731</v>
       </c>
       <c r="J189" s="7">
-        <v>3.888384</v>
+        <v>3.800996</v>
       </c>
       <c r="K189" s="7">
-        <v>13.073786</v>
+        <v>12.958998999999999</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8822,25 +8828,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>-0.020762</v>
+        <v>-0.023752</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.09671400000000001</v>
+        <v>-0.120661</v>
       </c>
       <c r="G190" s="7">
-        <v>0.152808</v>
+        <v>0.159311</v>
       </c>
       <c r="H190" s="7">
-        <v>0.034885</v>
+        <v>0.031724999999999996</v>
       </c>
       <c r="I190" s="7">
-        <v>0.5378269999999999</v>
+        <v>0.533131</v>
       </c>
       <c r="J190" s="7">
-        <v>3.8181380000000003</v>
+        <v>3.7237799999999996</v>
       </c>
       <c r="K190" s="7">
-        <v>12.835761</v>
+        <v>12.676072</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8863,25 @@
         <v>4</v>
       </c>
       <c r="E191" s="7">
-        <v>0.052848</v>
+        <v>0.05222</v>
       </c>
       <c r="F191" s="7">
-        <v>0.032001</v>
+        <v>0.032980999999999996</v>
       </c>
       <c r="G191" s="7">
-        <v>0.234022</v>
+        <v>0.23967</v>
       </c>
       <c r="H191" s="7">
-        <v>0.135409</v>
+        <v>0.134733</v>
       </c>
       <c r="I191" s="7">
-        <v>0.492263</v>
+        <v>0.491374</v>
       </c>
       <c r="J191" s="7">
-        <v>1.858606</v>
+        <v>1.863713</v>
       </c>
       <c r="K191" s="7">
-        <v>5.034359</v>
+        <v>5.0355110000000005</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8898,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.04027</v>
+        <v>0.040064</v>
       </c>
       <c r="F192" s="7">
-        <v>0.028028</v>
+        <v>0.029567</v>
       </c>
       <c r="G192" s="7">
-        <v>0.18482099999999999</v>
+        <v>0.187314</v>
       </c>
       <c r="H192" s="7">
-        <v>0.09859299999999999</v>
+        <v>0.098376</v>
       </c>
       <c r="I192" s="7">
-        <v>0.447636</v>
+        <v>0.44734900000000005</v>
       </c>
       <c r="J192" s="7">
-        <v>2.247097</v>
+        <v>2.245904</v>
       </c>
       <c r="K192" s="7">
-        <v>5.482563</v>
+        <v>5.477339</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8933,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>0.027971</v>
+        <v>0.03238</v>
       </c>
       <c r="F193" s="7">
-        <v>0.029781</v>
+        <v>0.033585</v>
       </c>
       <c r="G193" s="7">
-        <v>0.09723599999999999</v>
+        <v>0.10125</v>
       </c>
       <c r="H193" s="7">
-        <v>0.046204</v>
+        <v>0.050691</v>
       </c>
       <c r="I193" s="7">
-        <v>0.314401</v>
+        <v>0.320037</v>
       </c>
       <c r="J193" s="7">
-        <v>2.197226</v>
+        <v>2.205222</v>
       </c>
       <c r="K193" s="7">
-        <v>6.474302</v>
+        <v>6.480792</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8968,25 @@
         <v>3</v>
       </c>
       <c r="E194" s="7">
-        <v>0.045801999999999995</v>
+        <v>0.047677</v>
       </c>
       <c r="F194" s="7">
-        <v>0.09027400000000001</v>
+        <v>0.091276</v>
       </c>
       <c r="G194" s="7">
-        <v>0.235291</v>
+        <v>0.241398</v>
       </c>
       <c r="H194" s="7">
-        <v>0.19057400000000002</v>
+        <v>0.19271000000000002</v>
       </c>
       <c r="I194" s="7">
-        <v>0.473992</v>
+        <v>0.476636</v>
       </c>
       <c r="J194" s="7">
-        <v>1.5924209999999999</v>
+        <v>1.590548</v>
       </c>
       <c r="K194" s="7">
-        <v>3.719596</v>
+        <v>3.7193759999999996</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +9003,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.043958000000000004</v>
+        <v>0.046145</v>
       </c>
       <c r="F195" s="7">
-        <v>0.07418</v>
+        <v>0.075616</v>
       </c>
       <c r="G195" s="7">
-        <v>0.226812</v>
+        <v>0.23283500000000001</v>
       </c>
       <c r="H195" s="7">
-        <v>0.140616</v>
+        <v>0.143006</v>
       </c>
       <c r="I195" s="7">
-        <v>0.456911</v>
+        <v>0.45996400000000004</v>
       </c>
       <c r="J195" s="7">
-        <v>1.772926</v>
+        <v>1.758818</v>
       </c>
       <c r="K195" s="7">
-        <v>4.611713</v>
+        <v>4.620527</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9038,25 @@
         <v>4</v>
       </c>
       <c r="E196" s="7">
-        <v>0.051026999999999996</v>
+        <v>0.05203</v>
       </c>
       <c r="F196" s="7">
-        <v>0.030268000000000003</v>
+        <v>0.032568</v>
       </c>
       <c r="G196" s="7">
-        <v>0.20363</v>
+        <v>0.210613</v>
       </c>
       <c r="H196" s="7">
-        <v>0.123869</v>
+        <v>0.124941</v>
       </c>
       <c r="I196" s="7">
-        <v>0.475396</v>
+        <v>0.476804</v>
       </c>
       <c r="J196" s="7">
-        <v>2.1465389999999998</v>
+        <v>2.153451</v>
       </c>
       <c r="K196" s="7">
-        <v>5.046663</v>
+        <v>5.047531</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9073,25 @@
         <v>6</v>
       </c>
       <c r="E197" s="7">
-        <v>0.065593</v>
+        <v>0.059396000000000004</v>
       </c>
       <c r="F197" s="7">
-        <v>-0.020375</v>
+        <v>-0.019406</v>
       </c>
       <c r="G197" s="7">
-        <v>0.21959900000000002</v>
+        <v>0.217415</v>
       </c>
       <c r="H197" s="7">
-        <v>0.198204</v>
+        <v>0.191236</v>
       </c>
       <c r="I197" s="7">
-        <v>0.46204900000000004</v>
+        <v>0.453546</v>
       </c>
       <c r="J197" s="7">
-        <v>4.037406</v>
+        <v>3.991726</v>
       </c>
       <c r="K197" s="7">
-        <v>20.586955</v>
+        <v>20.455365</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,16 +9108,16 @@
         <v>5</v>
       </c>
       <c r="E198" s="7">
-        <v>0.086312</v>
+        <v>0.08746499999999999</v>
       </c>
       <c r="F198" s="7">
-        <v>0.046908000000000005</v>
+        <v>0.050856000000000005</v>
       </c>
       <c r="G198" s="7">
-        <v>0.21589200000000003</v>
+        <v>0.231257</v>
       </c>
       <c r="H198" s="7">
-        <v>0.196155</v>
+        <v>0.197425</v>
       </c>
       <c r="I198" s="7"/>
       <c r="J198" s="7"/>
@@ -9131,25 +9137,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.064997</v>
+        <v>0.071522</v>
       </c>
       <c r="F199" s="7">
-        <v>-0.023056999999999998</v>
+        <v>-0.015122</v>
       </c>
       <c r="G199" s="7">
-        <v>0.13123100000000001</v>
+        <v>0.14610599999999999</v>
       </c>
       <c r="H199" s="7">
-        <v>0.076264</v>
+        <v>0.082858</v>
       </c>
       <c r="I199" s="7">
-        <v>0.387975</v>
+        <v>0.39648000000000005</v>
       </c>
       <c r="J199" s="7">
-        <v>2.280224</v>
+        <v>2.267808</v>
       </c>
       <c r="K199" s="7">
-        <v>9.781476</v>
+        <v>9.858372000000001</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9166,25 +9172,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.081065</v>
+        <v>0.087282</v>
       </c>
       <c r="F200" s="7">
-        <v>0.06525299999999999</v>
+        <v>0.070405</v>
       </c>
       <c r="G200" s="7">
-        <v>0.215953</v>
+        <v>0.23397600000000002</v>
       </c>
       <c r="H200" s="7">
-        <v>0.179634</v>
+        <v>0.186418</v>
       </c>
       <c r="I200" s="7">
-        <v>0.489391</v>
+        <v>0.497955</v>
       </c>
       <c r="J200" s="7">
-        <v>2.4933899999999998</v>
+        <v>2.503274</v>
       </c>
       <c r="K200" s="7">
-        <v>9.009284000000001</v>
+        <v>9.05071</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9201,25 +9207,25 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.020436999999999997</v>
+        <v>0.022636</v>
       </c>
       <c r="F201" s="7">
-        <v>-0.008947</v>
+        <v>-0.011559999999999999</v>
       </c>
       <c r="G201" s="7">
-        <v>0.15491</v>
+        <v>0.17136600000000002</v>
       </c>
       <c r="H201" s="7">
-        <v>0.08295899999999999</v>
+        <v>0.085293</v>
       </c>
       <c r="I201" s="7">
-        <v>0.65537</v>
+        <v>0.658938</v>
       </c>
       <c r="J201" s="7">
-        <v>2.970157</v>
+        <v>2.9992959999999997</v>
       </c>
       <c r="K201" s="7">
-        <v>6.355676</v>
+        <v>6.367373</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9236,25 +9242,25 @@
         <v>3</v>
       </c>
       <c r="E202" s="7">
-        <v>0.01626</v>
+        <v>0.018993</v>
       </c>
       <c r="F202" s="7">
-        <v>0.014403999999999998</v>
+        <v>0.017972</v>
       </c>
       <c r="G202" s="7">
-        <v>0.141743</v>
+        <v>0.146173</v>
       </c>
       <c r="H202" s="7">
-        <v>0.046962000000000004</v>
+        <v>0.049778</v>
       </c>
       <c r="I202" s="7">
-        <v>0.38427900000000004</v>
+        <v>0.38800199999999996</v>
       </c>
       <c r="J202" s="7">
-        <v>1.627737</v>
+        <v>1.6330170000000002</v>
       </c>
       <c r="K202" s="7">
-        <v>3.648838</v>
+        <v>3.657674</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,16 +9277,16 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.07105</v>
+        <v>0.065248</v>
       </c>
       <c r="F203" s="7">
-        <v>-0.014621</v>
+        <v>-0.012856000000000001</v>
       </c>
       <c r="G203" s="7">
-        <v>0.242368</v>
+        <v>0.242912</v>
       </c>
       <c r="H203" s="7">
-        <v>0.209227</v>
+        <v>0.20267700000000002</v>
       </c>
       <c r="I203" s="7"/>
       <c r="J203" s="7"/>
@@ -9300,25 +9306,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.031034000000000003</v>
+        <v>0.034595</v>
       </c>
       <c r="F204" s="7">
-        <v>0.036438</v>
+        <v>0.038354</v>
       </c>
       <c r="G204" s="7">
-        <v>0.10627800000000001</v>
+        <v>0.110133</v>
       </c>
       <c r="H204" s="7">
-        <v>0.058041</v>
+        <v>0.061695</v>
       </c>
       <c r="I204" s="7">
-        <v>0.310242</v>
+        <v>0.314767</v>
       </c>
       <c r="J204" s="7">
-        <v>1.944303</v>
+        <v>1.952696</v>
       </c>
       <c r="K204" s="7">
-        <v>5.2828729999999995</v>
+        <v>5.2921450000000005</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9335,25 +9341,25 @@
         <v>4</v>
       </c>
       <c r="E205" s="7">
-        <v>0.035028000000000004</v>
+        <v>0.031825</v>
       </c>
       <c r="F205" s="7">
-        <v>0.002439</v>
+        <v>0.0037619999999999997</v>
       </c>
       <c r="G205" s="7">
-        <v>0.180424</v>
+        <v>0.182277</v>
       </c>
       <c r="H205" s="7">
-        <v>0.09077299999999999</v>
+        <v>0.08739699999999999</v>
       </c>
       <c r="I205" s="7">
-        <v>0.34799100000000005</v>
+        <v>0.34381999999999996</v>
       </c>
       <c r="J205" s="7">
-        <v>1.987295</v>
+        <v>1.976137</v>
       </c>
       <c r="K205" s="7">
-        <v>4.892154</v>
+        <v>4.878162</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9370,25 +9376,25 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.046496</v>
+        <v>0.040655000000000004</v>
       </c>
       <c r="F206" s="7">
-        <v>0.016165</v>
+        <v>0.013151</v>
       </c>
       <c r="G206" s="7">
-        <v>0.237712</v>
+        <v>0.24022300000000002</v>
       </c>
       <c r="H206" s="7">
-        <v>0.162225</v>
+        <v>0.155739</v>
       </c>
       <c r="I206" s="7">
-        <v>0.49338</v>
+        <v>0.485045</v>
       </c>
       <c r="J206" s="7">
-        <v>2.799282</v>
+        <v>2.7779320000000003</v>
       </c>
       <c r="K206" s="7">
-        <v>7.933441</v>
+        <v>7.875371</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9405,25 +9411,25 @@
         <v>6</v>
       </c>
       <c r="E207" s="7">
-        <v>0.052663</v>
+        <v>0.044771</v>
       </c>
       <c r="F207" s="7">
-        <v>0.00111</v>
+        <v>-0.002523</v>
       </c>
       <c r="G207" s="7">
-        <v>0.28114</v>
+        <v>0.28785299999999997</v>
       </c>
       <c r="H207" s="7">
-        <v>0.167631</v>
+        <v>0.15887700000000002</v>
       </c>
       <c r="I207" s="7">
-        <v>0.5147780000000001</v>
+        <v>0.503422</v>
       </c>
       <c r="J207" s="7">
-        <v>2.8161720000000003</v>
+        <v>2.785888</v>
       </c>
       <c r="K207" s="7">
-        <v>9.64128</v>
+        <v>9.554889</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9440,25 +9446,25 @@
         <v>3</v>
       </c>
       <c r="E208" s="7">
-        <v>0.017154</v>
+        <v>0.019375</v>
       </c>
       <c r="F208" s="7">
-        <v>-0.000335</v>
+        <v>0.004025</v>
       </c>
       <c r="G208" s="7">
-        <v>0.149376</v>
+        <v>0.155855</v>
       </c>
       <c r="H208" s="7">
-        <v>0.037209</v>
+        <v>0.039474</v>
       </c>
       <c r="I208" s="7">
-        <v>0.375039</v>
+        <v>0.37804099999999996</v>
       </c>
       <c r="J208" s="7">
-        <v>1.494931</v>
+        <v>1.498004</v>
       </c>
       <c r="K208" s="7">
-        <v>2.9161349999999997</v>
+        <v>2.9204610000000004</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9475,25 +9481,25 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.06557</v>
+        <v>0.053298</v>
       </c>
       <c r="F209" s="7">
-        <v>-0.030299999999999997</v>
+        <v>-0.033799</v>
       </c>
       <c r="G209" s="7">
-        <v>0.24310700000000002</v>
+        <v>0.24807099999999999</v>
       </c>
       <c r="H209" s="7">
-        <v>0.199269</v>
+        <v>0.185457</v>
       </c>
       <c r="I209" s="7">
-        <v>0.405869</v>
+        <v>0.38967799999999997</v>
       </c>
       <c r="J209" s="7">
-        <v>2.948478</v>
+        <v>2.884678</v>
       </c>
       <c r="K209" s="7">
-        <v>14.469937</v>
+        <v>14.308053</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9510,25 +9516,25 @@
         <v>4</v>
       </c>
       <c r="E210" s="7">
-        <v>0.057365000000000006</v>
+        <v>0.055045000000000004</v>
       </c>
       <c r="F210" s="7">
-        <v>0.039852</v>
+        <v>0.039901</v>
       </c>
       <c r="G210" s="7">
-        <v>0.225065</v>
+        <v>0.230596</v>
       </c>
       <c r="H210" s="7">
-        <v>0.168871</v>
+        <v>0.166307</v>
       </c>
       <c r="I210" s="7">
-        <v>0.516489</v>
+        <v>0.513163</v>
       </c>
       <c r="J210" s="7">
-        <v>1.907446</v>
+        <v>1.9036099999999998</v>
       </c>
       <c r="K210" s="7">
-        <v>5.460572</v>
+        <v>5.459239999999999</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9545,25 +9551,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.05455</v>
+        <v>0.057496</v>
       </c>
       <c r="F211" s="7">
-        <v>0.103301</v>
+        <v>0.105319</v>
       </c>
       <c r="G211" s="7">
-        <v>0.247847</v>
+        <v>0.256085</v>
       </c>
       <c r="H211" s="7">
-        <v>0.19185</v>
+        <v>0.19517900000000002</v>
       </c>
       <c r="I211" s="7">
-        <v>0.504684</v>
+        <v>0.508887</v>
       </c>
       <c r="J211" s="7">
-        <v>1.931692</v>
+        <v>1.9315360000000001</v>
       </c>
       <c r="K211" s="7">
-        <v>5.05495</v>
+        <v>5.075225</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9580,25 +9586,25 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.070592</v>
+        <v>0.075139</v>
       </c>
       <c r="F212" s="7">
-        <v>0.09217800000000001</v>
+        <v>0.095501</v>
       </c>
       <c r="G212" s="7">
-        <v>0.29519300000000004</v>
+        <v>0.309265</v>
       </c>
       <c r="H212" s="7">
-        <v>0.25849900000000003</v>
+        <v>0.26384399999999997</v>
       </c>
       <c r="I212" s="7">
-        <v>0.625491</v>
+        <v>0.632395</v>
       </c>
       <c r="J212" s="7">
-        <v>3.112889</v>
+        <v>3.0896929999999996</v>
       </c>
       <c r="K212" s="7">
-        <v>9.805276</v>
+        <v>9.833088</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,25 +9621,25 @@
         <v>6</v>
       </c>
       <c r="E213" s="7">
-        <v>-0.015193000000000002</v>
+        <v>-0.016203000000000002</v>
       </c>
       <c r="F213" s="7">
-        <v>-0.087772</v>
+        <v>-0.115175</v>
       </c>
       <c r="G213" s="7">
-        <v>0.18811499999999998</v>
+        <v>0.19225799999999998</v>
       </c>
       <c r="H213" s="7">
-        <v>0.066165</v>
+        <v>0.065072</v>
       </c>
       <c r="I213" s="7">
-        <v>0.597635</v>
+        <v>0.595996</v>
       </c>
       <c r="J213" s="7">
-        <v>4.067353</v>
+        <v>3.956814</v>
       </c>
       <c r="K213" s="7">
-        <v>13.392498</v>
+        <v>13.256422</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,25 +9656,25 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.037327</v>
+        <v>0.038868</v>
       </c>
       <c r="F214" s="7">
-        <v>0.035825</v>
+        <v>0.03609</v>
       </c>
       <c r="G214" s="7">
-        <v>0.160355</v>
+        <v>0.16346</v>
       </c>
       <c r="H214" s="7">
-        <v>0.121064</v>
+        <v>0.122729</v>
       </c>
       <c r="I214" s="7">
-        <v>0.402196</v>
+        <v>0.40428</v>
       </c>
       <c r="J214" s="7">
-        <v>2.344824</v>
+        <v>2.318676</v>
       </c>
       <c r="K214" s="7">
-        <v>7.152773</v>
+        <v>7.151906</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9685,25 +9691,25 @@
         <v>5</v>
       </c>
       <c r="E215" s="7">
-        <v>0.11914899999999999</v>
+        <v>0.121782</v>
       </c>
       <c r="F215" s="7">
-        <v>0.128143</v>
+        <v>0.137157</v>
       </c>
       <c r="G215" s="7">
-        <v>0.37437800000000004</v>
+        <v>0.389267</v>
       </c>
       <c r="H215" s="7">
-        <v>0.34192500000000003</v>
+        <v>0.345083</v>
       </c>
       <c r="I215" s="7">
-        <v>0.688866</v>
+        <v>0.69284</v>
       </c>
       <c r="J215" s="7">
-        <v>2.890464</v>
+        <v>2.885964</v>
       </c>
       <c r="K215" s="7">
-        <v>9.837527</v>
+        <v>9.849997</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9720,25 +9726,25 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.02073</v>
+        <v>0.02346</v>
       </c>
       <c r="F216" s="7">
-        <v>0.033307</v>
+        <v>0.03582</v>
       </c>
       <c r="G216" s="7">
-        <v>0.080111</v>
+        <v>0.082685</v>
       </c>
       <c r="H216" s="7">
-        <v>0.048272</v>
+        <v>0.051075999999999996</v>
       </c>
       <c r="I216" s="7">
-        <v>0.226757</v>
+        <v>0.230038</v>
       </c>
       <c r="J216" s="7">
-        <v>1.781441</v>
+        <v>1.78754</v>
       </c>
       <c r="K216" s="7">
-        <v>5.224765</v>
+        <v>5.22447</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9755,25 +9761,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.06746</v>
+        <v>0.07202499999999999</v>
       </c>
       <c r="F217" s="7">
-        <v>0.117838</v>
+        <v>0.122619</v>
       </c>
       <c r="G217" s="7">
-        <v>0.307513</v>
+        <v>0.32130899999999996</v>
       </c>
       <c r="H217" s="7">
-        <v>0.253328</v>
+        <v>0.25868800000000003</v>
       </c>
       <c r="I217" s="7">
-        <v>0.6472410000000001</v>
+        <v>0.654286</v>
       </c>
       <c r="J217" s="7">
-        <v>3.3726089999999997</v>
+        <v>3.375936</v>
       </c>
       <c r="K217" s="7">
-        <v>10.301234</v>
+        <v>10.351877</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,25 +9796,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.110262</v>
+        <v>0.11248699999999999</v>
       </c>
       <c r="F218" s="7">
-        <v>0.1226</v>
+        <v>0.126688</v>
       </c>
       <c r="G218" s="7">
-        <v>0.36058</v>
+        <v>0.37449800000000005</v>
       </c>
       <c r="H218" s="7">
-        <v>0.31021699999999996</v>
+        <v>0.312842</v>
       </c>
       <c r="I218" s="7">
-        <v>0.645729</v>
+        <v>0.6490269999999999</v>
       </c>
       <c r="J218" s="7">
-        <v>4.171334</v>
+        <v>4.130623</v>
       </c>
       <c r="K218" s="7">
-        <v>13.372072000000001</v>
+        <v>13.420669</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9825,19 +9831,19 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.057605</v>
+        <v>0.060719</v>
       </c>
       <c r="F219" s="7">
-        <v>0.064958</v>
+        <v>0.067366</v>
       </c>
       <c r="G219" s="7">
-        <v>0.239705</v>
+        <v>0.245529</v>
       </c>
       <c r="H219" s="7">
-        <v>0.18157800000000002</v>
+        <v>0.185056</v>
       </c>
       <c r="I219" s="7">
-        <v>0.525632</v>
+        <v>0.530124</v>
       </c>
       <c r="J219" s="7"/>
       <c r="K219" s="7"/>
@@ -9856,16 +9862,16 @@
         <v>6</v>
       </c>
       <c r="E220" s="7">
-        <v>0.013734</v>
+        <v>0.028344</v>
       </c>
       <c r="F220" s="7">
-        <v>-0.093446</v>
+        <v>-0.120376</v>
       </c>
       <c r="G220" s="7">
-        <v>0.607898</v>
+        <v>0.652362</v>
       </c>
       <c r="H220" s="7">
-        <v>0.090395</v>
+        <v>0.10611000000000001</v>
       </c>
       <c r="I220" s="7"/>
       <c r="J220" s="7"/>
@@ -9906,22 +9912,22 @@
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.001463</v>
+        <v>0.009559999999999999</v>
       </c>
       <c r="F222" s="7">
-        <v>-0.094895</v>
+        <v>-0.116513</v>
       </c>
       <c r="G222" s="7">
-        <v>0.38267</v>
+        <v>0.40519</v>
       </c>
       <c r="H222" s="7">
-        <v>0.06938</v>
+        <v>0.078027</v>
       </c>
       <c r="I222" s="7">
-        <v>1.000909</v>
+        <v>1.0170869999999999</v>
       </c>
       <c r="J222" s="7">
-        <v>4.41405</v>
+        <v>4.340927</v>
       </c>
       <c r="K222" s="7"/>
     </row>
@@ -9939,25 +9945,25 @@
         <v>4</v>
       </c>
       <c r="E223" s="7">
-        <v>0.029184</v>
+        <v>0.03031</v>
       </c>
       <c r="F223" s="7">
-        <v>0.096396</v>
+        <v>0.096633</v>
       </c>
       <c r="G223" s="7">
-        <v>0.197022</v>
+        <v>0.19679200000000002</v>
       </c>
       <c r="H223" s="7">
-        <v>0.128634</v>
+        <v>0.129868</v>
       </c>
       <c r="I223" s="7">
-        <v>0.443736</v>
+        <v>0.445315</v>
       </c>
       <c r="J223" s="7">
-        <v>1.366767</v>
+        <v>1.331105</v>
       </c>
       <c r="K223" s="7">
-        <v>2.712929</v>
+        <v>2.7175279999999997</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -9974,19 +9980,19 @@
         <v>2</v>
       </c>
       <c r="E224" s="7">
-        <v>0.02706</v>
+        <v>0.027013</v>
       </c>
       <c r="F224" s="7">
-        <v>0.083206</v>
+        <v>0.082145</v>
       </c>
       <c r="G224" s="7">
-        <v>0.186995</v>
+        <v>0.185726</v>
       </c>
       <c r="H224" s="7">
-        <v>0.120134</v>
+        <v>0.120083</v>
       </c>
       <c r="I224" s="7">
-        <v>0.443446</v>
+        <v>0.44338099999999997</v>
       </c>
       <c r="J224" s="7"/>
       <c r="K224" s="7"/>
@@ -10005,22 +10011,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.10106</v>
+        <v>0.10464999999999999</v>
       </c>
       <c r="F225" s="7">
-        <v>0.09856999999999999</v>
+        <v>0.10863099999999999</v>
       </c>
       <c r="G225" s="7">
-        <v>0.23297</v>
+        <v>0.2516</v>
       </c>
       <c r="H225" s="7">
-        <v>0.256164</v>
+        <v>0.260261</v>
       </c>
       <c r="I225" s="7">
-        <v>0.461254</v>
+        <v>0.466019</v>
       </c>
       <c r="J225" s="7">
-        <v>2.816918</v>
+        <v>2.788618</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10038,19 +10044,19 @@
         <v>5</v>
       </c>
       <c r="E226" s="7">
-        <v>0.007873999999999999</v>
+        <v>0.022677999999999997</v>
       </c>
       <c r="F226" s="7">
-        <v>-0.095368</v>
+        <v>-0.106745</v>
       </c>
       <c r="G226" s="7">
-        <v>0.355574</v>
+        <v>0.383299</v>
       </c>
       <c r="H226" s="7">
-        <v>0.08248799999999999</v>
+        <v>0.09838699999999999</v>
       </c>
       <c r="I226" s="7">
-        <v>0.8971339999999999</v>
+        <v>0.925</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10069,25 +10075,25 @@
         <v>4</v>
       </c>
       <c r="E227" s="7">
-        <v>0.039428</v>
+        <v>0.039027</v>
       </c>
       <c r="F227" s="7">
-        <v>0.031631</v>
+        <v>0.033098999999999996</v>
       </c>
       <c r="G227" s="7">
-        <v>0.188826</v>
+        <v>0.191703</v>
       </c>
       <c r="H227" s="7">
-        <v>0.101792</v>
+        <v>0.101367</v>
       </c>
       <c r="I227" s="7">
-        <v>0.451712</v>
+        <v>0.451152</v>
       </c>
       <c r="J227" s="7">
-        <v>2.216049</v>
+        <v>2.212968</v>
       </c>
       <c r="K227" s="7">
-        <v>5.567938000000001</v>
+        <v>5.56114</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -10104,25 +10110,25 @@
         <v>3</v>
       </c>
       <c r="E228" s="7">
-        <v>0.044396000000000005</v>
+        <v>0.045937</v>
       </c>
       <c r="F228" s="7">
-        <v>0.076206</v>
+        <v>0.077293</v>
       </c>
       <c r="G228" s="7">
-        <v>0.221265</v>
+        <v>0.22699999999999998</v>
       </c>
       <c r="H228" s="7">
-        <v>0.14317</v>
+        <v>0.14485699999999999</v>
       </c>
       <c r="I228" s="7">
-        <v>0.446757</v>
+        <v>0.448892</v>
       </c>
       <c r="J228" s="7">
-        <v>1.810249</v>
+        <v>1.7956809999999999</v>
       </c>
       <c r="K228" s="7">
-        <v>4.5625</v>
+        <v>4.5667919999999995</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,19 +10145,19 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.076985</v>
+        <v>0.086996</v>
       </c>
       <c r="F229" s="7">
-        <v>0.11027100000000001</v>
+        <v>0.12518700000000002</v>
       </c>
       <c r="G229" s="7">
-        <v>0.205911</v>
+        <v>0.228164</v>
       </c>
       <c r="H229" s="7">
-        <v>0.20130199999999998</v>
+        <v>0.212469</v>
       </c>
       <c r="I229" s="7">
-        <v>0.546153</v>
+        <v>0.560526</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10191,19 +10197,19 @@
         <v>5</v>
       </c>
       <c r="E231" s="7">
-        <v>0.10922599999999999</v>
+        <v>0.132379</v>
       </c>
       <c r="F231" s="7">
-        <v>0.161247</v>
+        <v>0.19294</v>
       </c>
       <c r="G231" s="7">
-        <v>0.298703</v>
+        <v>0.33220500000000003</v>
       </c>
       <c r="H231" s="7">
-        <v>0.346661</v>
+        <v>0.374771</v>
       </c>
       <c r="I231" s="7">
-        <v>0.5613360000000001</v>
+        <v>0.593927</v>
       </c>
       <c r="J231" s="7"/>
       <c r="K231" s="7"/>
@@ -10222,19 +10228,19 @@
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.10718899999999999</v>
+        <v>0.115799</v>
       </c>
       <c r="F232" s="7">
-        <v>0.083664</v>
+        <v>0.099703</v>
       </c>
       <c r="G232" s="7">
-        <v>0.243198</v>
+        <v>0.266951</v>
       </c>
       <c r="H232" s="7">
-        <v>0.222102</v>
+        <v>0.23160499999999998</v>
       </c>
       <c r="I232" s="7">
-        <v>0.528094</v>
+        <v>0.539976</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10253,25 +10259,25 @@
         <v>4</v>
       </c>
       <c r="E233" s="7">
-        <v>0.031234</v>
+        <v>0.03142</v>
       </c>
       <c r="F233" s="7">
-        <v>0.058032</v>
+        <v>0.057416</v>
       </c>
       <c r="G233" s="7">
-        <v>0.166382</v>
+        <v>0.167878</v>
       </c>
       <c r="H233" s="7">
-        <v>0.108949</v>
+        <v>0.109148</v>
       </c>
       <c r="I233" s="7">
-        <v>0.371364</v>
+        <v>0.37161099999999997</v>
       </c>
       <c r="J233" s="7">
-        <v>1.5864719999999999</v>
+        <v>1.5487659999999999</v>
       </c>
       <c r="K233" s="7">
-        <v>4.325295</v>
+        <v>4.32385</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -10288,19 +10294,19 @@
         <v>3</v>
       </c>
       <c r="E234" s="7">
-        <v>0.042512999999999995</v>
+        <v>0.037888000000000005</v>
       </c>
       <c r="F234" s="7">
-        <v>0.015013</v>
+        <v>0.013715999999999999</v>
       </c>
       <c r="G234" s="7">
-        <v>0.21602</v>
+        <v>0.216563</v>
       </c>
       <c r="H234" s="7">
-        <v>0.16685199999999997</v>
+        <v>0.161674</v>
       </c>
       <c r="I234" s="7">
-        <v>0.471283</v>
+        <v>0.464755</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10319,19 +10325,19 @@
         <v>4</v>
       </c>
       <c r="E235" s="7">
-        <v>0.038060000000000004</v>
+        <v>0.034739</v>
       </c>
       <c r="F235" s="7">
-        <v>0.046611</v>
+        <v>0.044662</v>
       </c>
       <c r="G235" s="7">
-        <v>0.199386</v>
+        <v>0.19481500000000002</v>
       </c>
       <c r="H235" s="7">
-        <v>0.104608</v>
+        <v>0.101074</v>
       </c>
       <c r="I235" s="7">
-        <v>0.47045499999999996</v>
+        <v>0.46575099999999997</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10350,19 +10356,19 @@
         <v>2</v>
       </c>
       <c r="E236" s="7">
-        <v>0.03138</v>
+        <v>0.032354</v>
       </c>
       <c r="F236" s="7">
-        <v>0.094299</v>
+        <v>0.094277</v>
       </c>
       <c r="G236" s="7">
-        <v>0.19757100000000002</v>
+        <v>0.197528</v>
       </c>
       <c r="H236" s="7">
-        <v>0.13231099999999998</v>
+        <v>0.133381</v>
       </c>
       <c r="I236" s="7">
-        <v>0.47031599999999996</v>
+        <v>0.471705</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10381,25 +10387,25 @@
         <v>6</v>
       </c>
       <c r="E237" s="7">
-        <v>-0.011970000000000001</v>
+        <v>-0.006663</v>
       </c>
       <c r="F237" s="7">
-        <v>-0.083255</v>
+        <v>-0.102265</v>
       </c>
       <c r="G237" s="7">
-        <v>0.20251999999999998</v>
+        <v>0.208869</v>
       </c>
       <c r="H237" s="7">
-        <v>0.070993</v>
+        <v>0.07674500000000001</v>
       </c>
       <c r="I237" s="7">
-        <v>0.591774</v>
+        <v>0.600322</v>
       </c>
       <c r="J237" s="7">
-        <v>4.1572640000000005</v>
+        <v>4.090199999999999</v>
       </c>
       <c r="K237" s="7">
-        <v>13.622594</v>
+        <v>13.573542999999999</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10416,14 +10422,14 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.019756</v>
+        <v>0.022053</v>
       </c>
       <c r="F238" s="7">
-        <v>0.0023480000000000003</v>
+        <v>0.005514</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="7">
-        <v>0.035068</v>
+        <v>0.0374</v>
       </c>
       <c r="I238" s="7"/>
       <c r="J238" s="7"/>
@@ -10443,19 +10449,19 @@
         <v>6</v>
       </c>
       <c r="E239" s="7">
-        <v>0.153441</v>
+        <v>0.17995899999999998</v>
       </c>
       <c r="F239" s="7">
-        <v>0.193707</v>
+        <v>0.233804</v>
       </c>
       <c r="G239" s="7">
-        <v>0.278346</v>
+        <v>0.3297</v>
       </c>
       <c r="H239" s="7">
-        <v>0.294843</v>
+        <v>0.32461199999999996</v>
       </c>
       <c r="I239" s="7">
-        <v>0.6725490000000001</v>
+        <v>0.711001</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10474,19 +10480,19 @@
         <v>5</v>
       </c>
       <c r="E240" s="7">
-        <v>0.088415</v>
+        <v>0.087099</v>
       </c>
       <c r="F240" s="7">
-        <v>0.027094</v>
+        <v>0.030243000000000003</v>
       </c>
       <c r="G240" s="7">
-        <v>0.20213</v>
+        <v>0.214555</v>
       </c>
       <c r="H240" s="7">
-        <v>0.16825099999999998</v>
+        <v>0.16683900000000002</v>
       </c>
       <c r="I240" s="7">
-        <v>0.486737</v>
+        <v>0.484941</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10505,25 +10511,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.023485999999999996</v>
+        <v>0.027582</v>
       </c>
       <c r="F241" s="7">
-        <v>0.03494</v>
+        <v>0.038646</v>
       </c>
       <c r="G241" s="7">
-        <v>0.083831</v>
+        <v>0.087739</v>
       </c>
       <c r="H241" s="7">
-        <v>0.050865</v>
+        <v>0.055071</v>
       </c>
       <c r="I241" s="7">
-        <v>0.22595500000000002</v>
+        <v>0.230862</v>
       </c>
       <c r="J241" s="7">
-        <v>1.8278550000000002</v>
+        <v>1.838758</v>
       </c>
       <c r="K241" s="7">
-        <v>5.7929759999999995</v>
+        <v>5.796187</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10540,25 +10546,25 @@
         <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.020550000000000002</v>
+        <v>0.020172</v>
       </c>
       <c r="F242" s="7">
-        <v>0.044501</v>
+        <v>0.043981000000000006</v>
       </c>
       <c r="G242" s="7">
-        <v>0.186779</v>
+        <v>0.200844</v>
       </c>
       <c r="H242" s="7">
-        <v>0.082626</v>
+        <v>0.082225</v>
       </c>
       <c r="I242" s="7">
-        <v>0.207838</v>
+        <v>0.20739000000000002</v>
       </c>
       <c r="J242" s="7">
-        <v>1.963147</v>
+        <v>1.968228</v>
       </c>
       <c r="K242" s="7">
-        <v>5.8029340000000005</v>
+        <v>5.8028949999999995</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10581,25 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.076391</v>
+        <v>0.065705</v>
       </c>
       <c r="F243" s="7">
-        <v>-0.015318</v>
+        <v>-0.016705</v>
       </c>
       <c r="G243" s="7">
-        <v>0.23603000000000002</v>
+        <v>0.23519600000000002</v>
       </c>
       <c r="H243" s="7">
-        <v>0.191848</v>
+        <v>0.180015</v>
       </c>
       <c r="I243" s="7">
-        <v>0.47975</v>
+        <v>0.46505899999999994</v>
       </c>
       <c r="J243" s="7">
-        <v>2.965163</v>
+        <v>2.917563</v>
       </c>
       <c r="K243" s="7">
-        <v>14.513322</v>
+        <v>14.375335</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10616,25 @@
         <v>3</v>
       </c>
       <c r="E244" s="7">
-        <v>0.045441</v>
+        <v>0.047295</v>
       </c>
       <c r="F244" s="7">
-        <v>0.079741</v>
+        <v>0.077258</v>
       </c>
       <c r="G244" s="7">
-        <v>0.217306</v>
+        <v>0.222592</v>
       </c>
       <c r="H244" s="7">
-        <v>0.15065099999999998</v>
+        <v>0.152691</v>
       </c>
       <c r="I244" s="7">
-        <v>0.45299100000000003</v>
+        <v>0.455567</v>
       </c>
       <c r="J244" s="7">
-        <v>1.830791</v>
+        <v>1.820622</v>
       </c>
       <c r="K244" s="7">
-        <v>4.604764</v>
+        <v>4.611009</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10651,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.027634</v>
+        <v>0.026475</v>
       </c>
       <c r="F245" s="7">
-        <v>-0.009979</v>
+        <v>-0.007716</v>
       </c>
       <c r="G245" s="7">
-        <v>0.147325</v>
+        <v>0.148981</v>
       </c>
       <c r="H245" s="7">
-        <v>0.063878</v>
+        <v>0.062678</v>
       </c>
       <c r="I245" s="7">
-        <v>0.37815899999999997</v>
+        <v>0.37660400000000005</v>
       </c>
       <c r="J245" s="7">
-        <v>1.4392660000000002</v>
+        <v>1.4314689999999999</v>
       </c>
       <c r="K245" s="7">
-        <v>3.776924</v>
+        <v>3.771745</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10686,25 @@
         <v>2</v>
       </c>
       <c r="E246" s="7">
-        <v>0.037868</v>
+        <v>0.037066</v>
       </c>
       <c r="F246" s="7">
-        <v>0.08025499999999999</v>
+        <v>0.079683</v>
       </c>
       <c r="G246" s="7">
-        <v>0.211561</v>
+        <v>0.210394</v>
       </c>
       <c r="H246" s="7">
-        <v>0.134066</v>
+        <v>0.13319</v>
       </c>
       <c r="I246" s="7">
-        <v>0.5114070000000001</v>
+        <v>0.510239</v>
       </c>
       <c r="J246" s="7">
-        <v>4.300465</v>
+        <v>4.294478</v>
       </c>
       <c r="K246" s="7">
-        <v>7.164371</v>
+        <v>7.153573</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10721,25 @@
         <v>4</v>
       </c>
       <c r="E247" s="7">
-        <v>0.055987</v>
+        <v>0.050664999999999995</v>
       </c>
       <c r="F247" s="7">
-        <v>0.045632</v>
+        <v>0.045248</v>
       </c>
       <c r="G247" s="7">
-        <v>0.243599</v>
+        <v>0.242206</v>
       </c>
       <c r="H247" s="7">
-        <v>0.179012</v>
+        <v>0.17307099999999997</v>
       </c>
       <c r="I247" s="7">
-        <v>0.520051</v>
+        <v>0.51239</v>
       </c>
       <c r="J247" s="7">
-        <v>3.330666</v>
+        <v>3.301086</v>
       </c>
       <c r="K247" s="7">
-        <v>8.530419</v>
+        <v>8.502895</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10756,25 @@
         <v>5</v>
       </c>
       <c r="E248" s="7">
-        <v>0.061912</v>
+        <v>0.054934000000000004</v>
       </c>
       <c r="F248" s="7">
-        <v>0.024107</v>
+        <v>0.023866000000000002</v>
       </c>
       <c r="G248" s="7">
-        <v>0.24415099999999998</v>
+        <v>0.243701</v>
       </c>
       <c r="H248" s="7">
-        <v>0.188995</v>
+        <v>0.181182</v>
       </c>
       <c r="I248" s="7">
-        <v>0.5238349999999999</v>
+        <v>0.513822</v>
       </c>
       <c r="J248" s="7">
-        <v>3.9361040000000003</v>
+        <v>3.902077</v>
       </c>
       <c r="K248" s="7">
-        <v>11.440494000000001</v>
+        <v>11.363344999999999</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10791,25 @@
         <v>6</v>
       </c>
       <c r="E249" s="7">
-        <v>0.066644</v>
+        <v>0.057246</v>
       </c>
       <c r="F249" s="7">
-        <v>-0.000624</v>
+        <v>-0.00098</v>
       </c>
       <c r="G249" s="7">
-        <v>0.242747</v>
+        <v>0.242712</v>
       </c>
       <c r="H249" s="7">
-        <v>0.19728300000000001</v>
+        <v>0.186734</v>
       </c>
       <c r="I249" s="7">
-        <v>0.49648699999999996</v>
+        <v>0.48330100000000004</v>
       </c>
       <c r="J249" s="7">
-        <v>3.600519</v>
+        <v>3.502174</v>
       </c>
       <c r="K249" s="7">
-        <v>13.960355999999999</v>
+        <v>13.883501</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10826,25 @@
         <v>3</v>
       </c>
       <c r="E250" s="7">
-        <v>0.05206</v>
+        <v>0.053742</v>
       </c>
       <c r="F250" s="7">
-        <v>0.086229</v>
+        <v>0.087958</v>
       </c>
       <c r="G250" s="7">
-        <v>0.20666299999999999</v>
+        <v>0.211251</v>
       </c>
       <c r="H250" s="7">
-        <v>0.166549</v>
+        <v>0.168415</v>
       </c>
       <c r="I250" s="7">
-        <v>0.46225499999999997</v>
+        <v>0.464594</v>
       </c>
       <c r="J250" s="7">
-        <v>2.0983840000000002</v>
+        <v>2.088505</v>
       </c>
       <c r="K250" s="7">
-        <v>5.609502</v>
+        <v>5.613606</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10861,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.084748</v>
+        <v>0.08727399999999999</v>
       </c>
       <c r="F251" s="7">
-        <v>0.09626</v>
+        <v>0.10094099999999999</v>
       </c>
       <c r="G251" s="7">
-        <v>0.24561</v>
+        <v>0.25639</v>
       </c>
       <c r="H251" s="7">
-        <v>0.22324100000000002</v>
+        <v>0.22609</v>
       </c>
       <c r="I251" s="7">
-        <v>0.531219</v>
+        <v>0.534786</v>
       </c>
       <c r="J251" s="7">
-        <v>3.191637</v>
+        <v>3.196723</v>
       </c>
       <c r="K251" s="7">
-        <v>9.880699</v>
+        <v>9.897134999999999</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10896,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.09717599999999998</v>
+        <v>0.099588</v>
       </c>
       <c r="F252" s="7">
-        <v>0.096021</v>
+        <v>0.10139200000000001</v>
       </c>
       <c r="G252" s="7">
-        <v>0.25234</v>
+        <v>0.264849</v>
       </c>
       <c r="H252" s="7">
-        <v>0.24089300000000002</v>
+        <v>0.24361999999999998</v>
       </c>
       <c r="I252" s="7">
-        <v>0.5479569999999999</v>
+        <v>0.551359</v>
       </c>
       <c r="J252" s="7">
-        <v>3.430889</v>
+        <v>3.431725</v>
       </c>
       <c r="K252" s="7">
-        <v>10.972627</v>
+        <v>10.969985999999999</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10931,25 @@
         <v>4</v>
       </c>
       <c r="E253" s="7">
-        <v>0.022401</v>
+        <v>0.021541</v>
       </c>
       <c r="F253" s="7">
-        <v>-0.002875</v>
+        <v>-0.0009170000000000001</v>
       </c>
       <c r="G253" s="7">
-        <v>0.136623</v>
+        <v>0.138013</v>
       </c>
       <c r="H253" s="7">
-        <v>0.057645</v>
+        <v>0.05675500000000001</v>
       </c>
       <c r="I253" s="7">
-        <v>0.370379</v>
+        <v>0.36922600000000005</v>
       </c>
       <c r="J253" s="7">
-        <v>1.810677</v>
+        <v>1.808572</v>
       </c>
       <c r="K253" s="7">
-        <v>4.975395</v>
+        <v>4.966086000000001</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10966,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.044707</v>
+        <v>0.046762</v>
       </c>
       <c r="F254" s="7">
-        <v>0.025091000000000002</v>
+        <v>0.022911</v>
       </c>
       <c r="G254" s="7">
-        <v>0.228039</v>
+        <v>0.23535399999999998</v>
       </c>
       <c r="H254" s="7">
-        <v>0.15982100000000002</v>
+        <v>0.162103</v>
       </c>
       <c r="I254" s="7">
-        <v>0.533797</v>
+        <v>0.536814</v>
       </c>
       <c r="J254" s="7">
-        <v>2.9190679999999998</v>
+        <v>2.9169889999999996</v>
       </c>
       <c r="K254" s="7">
-        <v>6.079243</v>
+        <v>6.078213</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +11001,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.030993</v>
+        <v>0.032963</v>
       </c>
       <c r="F255" s="7">
-        <v>0.030749</v>
+        <v>0.024885</v>
       </c>
       <c r="G255" s="7">
-        <v>0.21495799999999998</v>
+        <v>0.219864</v>
       </c>
       <c r="H255" s="7">
-        <v>0.145239</v>
+        <v>0.147428</v>
       </c>
       <c r="I255" s="7">
-        <v>0.510672</v>
+        <v>0.513559</v>
       </c>
       <c r="J255" s="7">
-        <v>2.8371269999999997</v>
+        <v>2.834787</v>
       </c>
       <c r="K255" s="7">
-        <v>5.258972</v>
+        <v>5.261946</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11036,25 @@
         <v>5</v>
       </c>
       <c r="E256" s="7">
-        <v>0.060712999999999996</v>
+        <v>0.06278800000000001</v>
       </c>
       <c r="F256" s="7">
-        <v>0.023895</v>
+        <v>0.024848</v>
       </c>
       <c r="G256" s="7">
-        <v>0.243502</v>
+        <v>0.25531400000000004</v>
       </c>
       <c r="H256" s="7">
-        <v>0.181903</v>
+        <v>0.18421600000000002</v>
       </c>
       <c r="I256" s="7">
-        <v>0.562267</v>
+        <v>0.565323</v>
       </c>
       <c r="J256" s="7">
-        <v>2.9974860000000003</v>
+        <v>2.999907</v>
       </c>
       <c r="K256" s="7">
-        <v>7.354738</v>
+        <v>7.346721</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11071,25 @@
         <v>6</v>
       </c>
       <c r="E257" s="7">
-        <v>-0.012782</v>
+        <v>-0.012099</v>
       </c>
       <c r="F257" s="7">
-        <v>-0.081023</v>
+        <v>-0.107953</v>
       </c>
       <c r="G257" s="7">
-        <v>0.18855899999999998</v>
+        <v>0.192922</v>
       </c>
       <c r="H257" s="7">
-        <v>0.071834</v>
+        <v>0.072576</v>
       </c>
       <c r="I257" s="7">
-        <v>0.603352</v>
+        <v>0.604461</v>
       </c>
       <c r="J257" s="7">
-        <v>4.064982</v>
+        <v>3.962705</v>
       </c>
       <c r="K257" s="7">
-        <v>13.610133000000001</v>
+        <v>13.488407</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11106,25 @@
         <v>2</v>
       </c>
       <c r="E258" s="7">
-        <v>0.031103000000000002</v>
+        <v>0.031737</v>
       </c>
       <c r="F258" s="7">
-        <v>0.089124</v>
+        <v>0.087024</v>
       </c>
       <c r="G258" s="7">
-        <v>0.191192</v>
+        <v>0.19162400000000002</v>
       </c>
       <c r="H258" s="7">
-        <v>0.14455199999999999</v>
+        <v>0.145256</v>
       </c>
       <c r="I258" s="7">
-        <v>0.431256</v>
+        <v>0.43213700000000005</v>
       </c>
       <c r="J258" s="7">
-        <v>2.4443520000000003</v>
+        <v>2.442883</v>
       </c>
       <c r="K258" s="7">
-        <v>4.473394</v>
+        <v>4.474041000000001</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11141,25 @@
         <v>6</v>
       </c>
       <c r="E259" s="7">
-        <v>0.06667200000000001</v>
+        <v>0.07302</v>
       </c>
       <c r="F259" s="7">
-        <v>0.007068</v>
+        <v>0.011228</v>
       </c>
       <c r="G259" s="7">
-        <v>0.181871</v>
+        <v>0.204768</v>
       </c>
       <c r="H259" s="7">
-        <v>0.112869</v>
+        <v>0.11949199999999999</v>
       </c>
       <c r="I259" s="7">
-        <v>0.6169319999999999</v>
+        <v>0.626554</v>
       </c>
       <c r="J259" s="7">
-        <v>4.734407</v>
+        <v>4.747663999999999</v>
       </c>
       <c r="K259" s="7">
-        <v>20.156475</v>
+        <v>20.297728</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,10 +11176,10 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>-0.012159999999999999</v>
+        <v>-0.008238</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.064282</v>
+        <v>-0.084216</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -11195,22 +11201,22 @@
         <v>3</v>
       </c>
       <c r="E261" s="7">
-        <v>0.058818</v>
+        <v>0.060662</v>
       </c>
       <c r="F261" s="7">
-        <v>0.08759299999999999</v>
+        <v>0.089185</v>
       </c>
       <c r="G261" s="7">
-        <v>0.235687</v>
+        <v>0.242546</v>
       </c>
       <c r="H261" s="7">
-        <v>0.17721</v>
+        <v>0.179261</v>
       </c>
       <c r="I261" s="7">
-        <v>0.515343</v>
+        <v>0.517983</v>
       </c>
       <c r="J261" s="7">
-        <v>2.301894</v>
+        <v>2.288481</v>
       </c>
       <c r="K261" s="7"/>
     </row>
@@ -11228,22 +11234,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.022135</v>
+        <v>0.021171000000000002</v>
       </c>
       <c r="F262" s="7">
-        <v>0.046237</v>
+        <v>0.044635999999999995</v>
       </c>
       <c r="G262" s="7">
-        <v>0.13662000000000002</v>
+        <v>0.140961</v>
       </c>
       <c r="H262" s="7">
-        <v>0.07178</v>
+        <v>0.070769</v>
       </c>
       <c r="I262" s="7">
-        <v>0.49018999999999996</v>
+        <v>0.488785</v>
       </c>
       <c r="J262" s="7">
-        <v>2.735643</v>
+        <v>2.714296</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11261,19 +11267,19 @@
         <v>5</v>
       </c>
       <c r="E263" s="7">
-        <v>0.076237</v>
+        <v>0.06631000000000001</v>
       </c>
       <c r="F263" s="7">
-        <v>-0.021092</v>
+        <v>-0.01919</v>
       </c>
       <c r="G263" s="7">
-        <v>0.241901</v>
+        <v>0.23998899999999998</v>
       </c>
       <c r="H263" s="7">
-        <v>0.17651499999999998</v>
+        <v>0.16566299999999998</v>
       </c>
       <c r="I263" s="7">
-        <v>0.44191600000000003</v>
+        <v>0.42861600000000005</v>
       </c>
       <c r="J263" s="7"/>
       <c r="K263" s="7"/>
@@ -11292,22 +11298,22 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.128004</v>
+        <v>0.157638</v>
       </c>
       <c r="F264" s="7">
-        <v>0.109606</v>
+        <v>0.148373</v>
       </c>
       <c r="G264" s="7">
-        <v>0.162586</v>
+        <v>0.21171299999999998</v>
       </c>
       <c r="H264" s="7">
-        <v>0.194494</v>
+        <v>0.225875</v>
       </c>
       <c r="I264" s="7">
-        <v>0.485392</v>
+        <v>0.524416</v>
       </c>
       <c r="J264" s="7">
-        <v>3.53065</v>
+        <v>3.6088139999999997</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11325,19 +11331,19 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.032663000000000005</v>
+        <v>0.038616000000000004</v>
       </c>
       <c r="F265" s="7">
-        <v>0.06514</v>
+        <v>0.067471</v>
       </c>
       <c r="G265" s="7">
-        <v>0.16226</v>
+        <v>0.16949000000000003</v>
       </c>
       <c r="H265" s="7">
-        <v>0.134022</v>
+        <v>0.14056</v>
       </c>
       <c r="I265" s="7">
-        <v>0.275437</v>
+        <v>0.28279</v>
       </c>
       <c r="J265" s="7"/>
       <c r="K265" s="7"/>
@@ -11356,19 +11362,19 @@
         <v>2</v>
       </c>
       <c r="E266" s="7">
-        <v>0.029609999999999997</v>
+        <v>0.030858</v>
       </c>
       <c r="F266" s="7">
-        <v>0.09822499999999999</v>
+        <v>0.098419</v>
       </c>
       <c r="G266" s="7">
-        <v>0.20627199999999998</v>
+        <v>0.206558</v>
       </c>
       <c r="H266" s="7">
-        <v>0.135168</v>
+        <v>0.136544</v>
       </c>
       <c r="I266" s="7">
-        <v>0.480507</v>
+        <v>0.482301</v>
       </c>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
@@ -11387,22 +11393,22 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.024585</v>
+        <v>0.026403</v>
       </c>
       <c r="F267" s="7">
-        <v>0.055573</v>
+        <v>0.054999</v>
       </c>
       <c r="G267" s="7">
-        <v>0.182837</v>
+        <v>0.186407</v>
       </c>
       <c r="H267" s="7">
-        <v>0.124071</v>
+        <v>0.126065</v>
       </c>
       <c r="I267" s="7">
-        <v>0.47874099999999997</v>
+        <v>0.481364</v>
       </c>
       <c r="J267" s="7">
-        <v>3.085846</v>
+        <v>3.091411</v>
       </c>
       <c r="K267" s="7"/>
     </row>
@@ -11420,22 +11426,22 @@
         <v>5</v>
       </c>
       <c r="E268" s="7">
-        <v>0.032844000000000005</v>
+        <v>0.024559</v>
       </c>
       <c r="F268" s="7">
-        <v>0.000696</v>
+        <v>-0.005396</v>
       </c>
       <c r="G268" s="7">
-        <v>0.171581</v>
+        <v>0.174118</v>
       </c>
       <c r="H268" s="7">
-        <v>0.12892699999999999</v>
+        <v>0.11987199999999999</v>
       </c>
       <c r="I268" s="7">
-        <v>0.577488</v>
+        <v>0.5648340000000001</v>
       </c>
       <c r="J268" s="7">
-        <v>2.907957</v>
+        <v>2.874441</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11453,19 +11459,19 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.048294</v>
+        <v>0.048600000000000004</v>
       </c>
       <c r="F269" s="7">
-        <v>0.073645</v>
+        <v>0.075137</v>
       </c>
       <c r="G269" s="7">
-        <v>0.18711</v>
+        <v>0.192899</v>
       </c>
       <c r="H269" s="7">
-        <v>0.134938</v>
+        <v>0.135269</v>
       </c>
       <c r="I269" s="7">
-        <v>0.49792299999999995</v>
+        <v>0.49835999999999997</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11484,19 +11490,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.079983</v>
+        <v>0.07453599999999999</v>
       </c>
       <c r="F270" s="7">
-        <v>0.084413</v>
+        <v>0.073613</v>
       </c>
       <c r="G270" s="7">
-        <v>0.15906499999999998</v>
+        <v>0.156778</v>
       </c>
       <c r="H270" s="7">
-        <v>0.156041</v>
+        <v>0.150211</v>
       </c>
       <c r="I270" s="7">
-        <v>0.481857</v>
+        <v>0.474383</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11515,19 +11521,19 @@
         <v>4</v>
       </c>
       <c r="E271" s="7">
-        <v>0.053684</v>
+        <v>0.05976</v>
       </c>
       <c r="F271" s="7">
-        <v>0.047401</v>
+        <v>0.044337999999999995</v>
       </c>
       <c r="G271" s="7">
-        <v>0.251484</v>
+        <v>0.271243</v>
       </c>
       <c r="H271" s="7">
-        <v>0.190373</v>
+        <v>0.197237</v>
       </c>
       <c r="I271" s="7">
-        <v>0.353889</v>
+        <v>0.361696</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11546,19 +11552,19 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.039489</v>
+        <v>0.045804</v>
       </c>
       <c r="F272" s="7">
-        <v>0.066587</v>
+        <v>0.064347</v>
       </c>
       <c r="G272" s="7">
-        <v>0.235548</v>
+        <v>0.23400400000000002</v>
       </c>
       <c r="H272" s="7">
-        <v>0.18356899999999998</v>
+        <v>0.19076</v>
       </c>
       <c r="I272" s="7">
-        <v>0.343844</v>
+        <v>0.352008</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11577,19 +11583,19 @@
         <v>6</v>
       </c>
       <c r="E273" s="7">
-        <v>0.133629</v>
+        <v>0.163818</v>
       </c>
       <c r="F273" s="7">
-        <v>0.151435</v>
+        <v>0.181832</v>
       </c>
       <c r="G273" s="7">
-        <v>0.24207499999999998</v>
+        <v>0.29032</v>
       </c>
       <c r="H273" s="7">
-        <v>0.318389</v>
+        <v>0.35349800000000003</v>
       </c>
       <c r="I273" s="7">
-        <v>0.526909</v>
+        <v>0.56757</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11608,22 +11614,22 @@
         <v>4</v>
       </c>
       <c r="E274" s="7">
-        <v>0.024869</v>
+        <v>0.020623</v>
       </c>
       <c r="F274" s="7">
-        <v>0.017147</v>
+        <v>0.01226</v>
       </c>
       <c r="G274" s="7">
-        <v>0.16611499999999998</v>
+        <v>0.167061</v>
       </c>
       <c r="H274" s="7">
-        <v>0.11877499999999999</v>
+        <v>0.11413999999999999</v>
       </c>
       <c r="I274" s="7">
-        <v>0.506086</v>
+        <v>0.499846</v>
       </c>
       <c r="J274" s="7">
-        <v>3.03849</v>
+        <v>3.021427</v>
       </c>
       <c r="K274" s="7"/>
     </row>
@@ -11641,25 +11647,25 @@
         <v>5</v>
       </c>
       <c r="E275" s="7">
-        <v>0.074199</v>
+        <v>0.080497</v>
       </c>
       <c r="F275" s="7">
-        <v>0.100373</v>
+        <v>0.104565</v>
       </c>
       <c r="G275" s="7">
-        <v>0.28733000000000003</v>
+        <v>0.304499</v>
       </c>
       <c r="H275" s="7">
-        <v>0.21807300000000002</v>
+        <v>0.225214</v>
       </c>
       <c r="I275" s="7">
-        <v>0.580157</v>
+        <v>0.5894210000000001</v>
       </c>
       <c r="J275" s="7">
-        <v>2.63586</v>
+        <v>2.650262</v>
       </c>
       <c r="K275" s="7">
-        <v>6.588015</v>
+        <v>6.635824</v>
       </c>
     </row>
     <row r="276" spans="1:11" x14ac:dyDescent="0.25">
@@ -11676,25 +11682,25 @@
         <v>2</v>
       </c>
       <c r="E276" s="7">
-        <v>0.029168</v>
+        <v>0.03061</v>
       </c>
       <c r="F276" s="7">
-        <v>0.089215</v>
+        <v>0.089208</v>
       </c>
       <c r="G276" s="7">
-        <v>0.198402</v>
+        <v>0.19871</v>
       </c>
       <c r="H276" s="7">
-        <v>0.129786</v>
+        <v>0.131369</v>
       </c>
       <c r="I276" s="7">
-        <v>0.47092</v>
+        <v>0.472981</v>
       </c>
       <c r="J276" s="7">
-        <v>2.205763</v>
+        <v>2.2082669999999998</v>
       </c>
       <c r="K276" s="7">
-        <v>4.141686</v>
+        <v>4.1463339999999995</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11711,25 +11717,25 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.037452</v>
+        <v>0.041213</v>
       </c>
       <c r="F277" s="7">
-        <v>0.014454</v>
+        <v>0.016519</v>
       </c>
       <c r="G277" s="7">
-        <v>0.104617</v>
+        <v>0.110446</v>
       </c>
       <c r="H277" s="7">
-        <v>0.042303</v>
+        <v>0.046081000000000004</v>
       </c>
       <c r="I277" s="7">
-        <v>0.29408</v>
+        <v>0.298771</v>
       </c>
       <c r="J277" s="7">
-        <v>1.7480879999999999</v>
+        <v>1.7562200000000001</v>
       </c>
       <c r="K277" s="7">
-        <v>5.094568</v>
+        <v>5.108278</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11746,25 +11752,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.07980000000000001</v>
+        <v>0.072872</v>
       </c>
       <c r="F278" s="7">
-        <v>-0.011975</v>
+        <v>-0.011128</v>
       </c>
       <c r="G278" s="7">
-        <v>0.200259</v>
+        <v>0.205644</v>
       </c>
       <c r="H278" s="7">
-        <v>0.186053</v>
+        <v>0.17844300000000002</v>
       </c>
       <c r="I278" s="7">
-        <v>0.441865</v>
+        <v>0.432614</v>
       </c>
       <c r="J278" s="7">
-        <v>2.5756330000000003</v>
+        <v>2.549219</v>
       </c>
       <c r="K278" s="7">
-        <v>12.375649000000001</v>
+        <v>12.302231999999998</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11781,25 +11787,25 @@
         <v>4</v>
       </c>
       <c r="E279" s="7">
-        <v>0.034496</v>
+        <v>0.036544</v>
       </c>
       <c r="F279" s="7">
-        <v>0.00145</v>
+        <v>0.004386</v>
       </c>
       <c r="G279" s="7">
-        <v>0.153514</v>
+        <v>0.155255</v>
       </c>
       <c r="H279" s="7">
-        <v>0.040512</v>
+        <v>0.042571000000000005</v>
       </c>
       <c r="I279" s="7">
-        <v>0.379944</v>
+        <v>0.382676</v>
       </c>
       <c r="J279" s="7">
-        <v>1.678491</v>
+        <v>1.68</v>
       </c>
       <c r="K279" s="7">
-        <v>3.614404</v>
+        <v>3.6226049999999996</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11816,25 +11822,25 @@
         <v>6</v>
       </c>
       <c r="E280" s="7">
-        <v>0.08566000000000001</v>
+        <v>0.08904999999999999</v>
       </c>
       <c r="F280" s="7">
-        <v>0.09204000000000001</v>
+        <v>0.093453</v>
       </c>
       <c r="G280" s="7">
-        <v>0.237339</v>
+        <v>0.254747</v>
       </c>
       <c r="H280" s="7">
-        <v>0.20517600000000003</v>
+        <v>0.20893799999999998</v>
       </c>
       <c r="I280" s="7">
-        <v>0.499201</v>
+        <v>0.503881</v>
       </c>
       <c r="J280" s="7">
-        <v>2.835034</v>
+        <v>2.8410840000000004</v>
       </c>
       <c r="K280" s="7">
-        <v>10.05203</v>
+        <v>10.093734</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11851,25 +11857,25 @@
         <v>3</v>
       </c>
       <c r="E281" s="7">
-        <v>0.035529000000000005</v>
+        <v>0.035092</v>
       </c>
       <c r="F281" s="7">
-        <v>0.07821</v>
+        <v>0.0782</v>
       </c>
       <c r="G281" s="7">
-        <v>0.194015</v>
+        <v>0.19683599999999998</v>
       </c>
       <c r="H281" s="7">
-        <v>0.141012</v>
+        <v>0.14053000000000002</v>
       </c>
       <c r="I281" s="7">
-        <v>0.46695</v>
+        <v>0.466331</v>
       </c>
       <c r="J281" s="7">
-        <v>2.9609989999999997</v>
+        <v>2.956865</v>
       </c>
       <c r="K281" s="7">
-        <v>5.294957</v>
+        <v>5.2880259999999994</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11886,25 +11892,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.026217</v>
+        <v>0.027732999999999997</v>
       </c>
       <c r="F282" s="7">
-        <v>0.066341</v>
+        <v>0.067581</v>
       </c>
       <c r="G282" s="7">
-        <v>0.17836</v>
+        <v>0.179049</v>
       </c>
       <c r="H282" s="7">
-        <v>0.10174200000000001</v>
+        <v>0.103369</v>
       </c>
       <c r="I282" s="7">
-        <v>0.447382</v>
+        <v>0.44952</v>
       </c>
       <c r="J282" s="7">
-        <v>2.299001</v>
+        <v>2.302914</v>
       </c>
       <c r="K282" s="7">
-        <v>4.202217999999999</v>
+        <v>4.208509</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11921,25 +11927,25 @@
         <v>5</v>
       </c>
       <c r="E283" s="7">
-        <v>0.028681</v>
+        <v>0.032536999999999996</v>
       </c>
       <c r="F283" s="7">
-        <v>0.027111</v>
+        <v>0.030686</v>
       </c>
       <c r="G283" s="7">
-        <v>0.070759</v>
+        <v>0.076764</v>
       </c>
       <c r="H283" s="7">
-        <v>0.031303</v>
+        <v>0.035169</v>
       </c>
       <c r="I283" s="7">
-        <v>0.27456800000000003</v>
+        <v>0.279346</v>
       </c>
       <c r="J283" s="7">
-        <v>1.9305459999999999</v>
+        <v>1.9333699999999998</v>
       </c>
       <c r="K283" s="7">
-        <v>5.797496</v>
+        <v>5.806268</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11956,25 +11962,25 @@
         <v>3</v>
       </c>
       <c r="E284" s="7">
-        <v>0.029757</v>
+        <v>0.030649000000000003</v>
       </c>
       <c r="F284" s="7">
-        <v>0.045466</v>
+        <v>0.047709</v>
       </c>
       <c r="G284" s="7">
-        <v>0.209179</v>
+        <v>0.211066</v>
       </c>
       <c r="H284" s="7">
-        <v>0.060832</v>
+        <v>0.06175099999999999</v>
       </c>
       <c r="I284" s="7">
-        <v>0.424919</v>
+        <v>0.42615400000000003</v>
       </c>
       <c r="J284" s="7">
-        <v>1.971258</v>
+        <v>1.972025</v>
       </c>
       <c r="K284" s="7">
-        <v>3.621812</v>
+        <v>3.623629</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11991,25 +11997,25 @@
         <v>5</v>
       </c>
       <c r="E285" s="7">
-        <v>0.042899</v>
+        <v>0.042025</v>
       </c>
       <c r="F285" s="7">
-        <v>0.060651000000000004</v>
+        <v>0.059775</v>
       </c>
       <c r="G285" s="7">
-        <v>0.235193</v>
+        <v>0.237041</v>
       </c>
       <c r="H285" s="7">
-        <v>0.161915</v>
+        <v>0.160941</v>
       </c>
       <c r="I285" s="7">
-        <v>0.527212</v>
+        <v>0.5259320000000001</v>
       </c>
       <c r="J285" s="7">
-        <v>2.709822</v>
+        <v>2.700276</v>
       </c>
       <c r="K285" s="7">
-        <v>9.328168</v>
+        <v>9.305163</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12026,25 +12032,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>-0.019748</v>
+        <v>-0.021959</v>
       </c>
       <c r="F286" s="7">
-        <v>-0.093102</v>
+        <v>-0.118245</v>
       </c>
       <c r="G286" s="7">
-        <v>0.176345</v>
+        <v>0.181125</v>
       </c>
       <c r="H286" s="7">
-        <v>0.041429</v>
+        <v>0.039079</v>
       </c>
       <c r="I286" s="7">
-        <v>0.559678</v>
+        <v>0.5561590000000001</v>
       </c>
       <c r="J286" s="7">
-        <v>4.109262</v>
+        <v>4.002461</v>
       </c>
       <c r="K286" s="7">
-        <v>13.634942</v>
+        <v>13.479512</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12061,25 +12067,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.053663999999999996</v>
+        <v>0.055159</v>
       </c>
       <c r="F287" s="7">
-        <v>0.093543</v>
+        <v>0.094657</v>
       </c>
       <c r="G287" s="7">
-        <v>0.252168</v>
+        <v>0.258526</v>
       </c>
       <c r="H287" s="7">
-        <v>0.17378799999999997</v>
+        <v>0.175453</v>
       </c>
       <c r="I287" s="7">
-        <v>0.494674</v>
+        <v>0.496795</v>
       </c>
       <c r="J287" s="7">
-        <v>1.4008209999999999</v>
+        <v>1.394475</v>
       </c>
       <c r="K287" s="7">
-        <v>3.7269940000000004</v>
+        <v>3.7296120000000004</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12096,25 +12102,25 @@
         <v>6</v>
       </c>
       <c r="E288" s="7">
-        <v>0.069386</v>
+        <v>0.064374</v>
       </c>
       <c r="F288" s="7">
-        <v>0.012931999999999999</v>
+        <v>0.012414000000000001</v>
       </c>
       <c r="G288" s="7">
-        <v>0.25142</v>
+        <v>0.25533100000000003</v>
       </c>
       <c r="H288" s="7">
-        <v>0.16389800000000002</v>
+        <v>0.158443</v>
       </c>
       <c r="I288" s="7">
-        <v>0.530114</v>
+        <v>0.522942</v>
       </c>
       <c r="J288" s="7">
-        <v>2.536496</v>
+        <v>2.5143459999999997</v>
       </c>
       <c r="K288" s="7">
-        <v>10.319306999999998</v>
+        <v>10.245252</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12131,25 +12137,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.001031</v>
+        <v>0.006029</v>
       </c>
       <c r="F289" s="7">
-        <v>-0.073934</v>
+        <v>-0.09924200000000001</v>
       </c>
       <c r="G289" s="7">
-        <v>0.269578</v>
+        <v>0.282059</v>
       </c>
       <c r="H289" s="7">
-        <v>0.08905099999999999</v>
+        <v>0.094487</v>
       </c>
       <c r="I289" s="7">
-        <v>0.756524</v>
+        <v>0.7652930000000001</v>
       </c>
       <c r="J289" s="7">
-        <v>4.136151</v>
+        <v>4.089633</v>
       </c>
       <c r="K289" s="7">
-        <v>8.285833</v>
+        <v>8.322373</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12160,31 +12166,31 @@
         <v>606</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>26</v>
+        <v>422</v>
       </c>
       <c r="D290" s="6">
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>0.105192</v>
+        <v>0.065517</v>
       </c>
       <c r="F290" s="7">
-        <v>0.022427000000000002</v>
+        <v>0.058216000000000004</v>
       </c>
       <c r="G290" s="7">
-        <v>0.238721</v>
+        <v>0.185266</v>
       </c>
       <c r="H290" s="7">
-        <v>0.21892399999999998</v>
+        <v>0.151311</v>
       </c>
       <c r="I290" s="7">
-        <v>0.416523</v>
+        <v>0.42756700000000003</v>
       </c>
       <c r="J290" s="7">
-        <v>2.659955</v>
+        <v>2.491488</v>
       </c>
       <c r="K290" s="7">
-        <v>12.56048</v>
+        <v>9.149666999999999</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12195,31 +12201,31 @@
         <v>608</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D291" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E291" s="7">
-        <v>0.042661</v>
+        <v>0.09951499999999999</v>
       </c>
       <c r="F291" s="7">
-        <v>0.069352</v>
+        <v>0.024297</v>
       </c>
       <c r="G291" s="7">
-        <v>0.226274</v>
+        <v>0.25417100000000004</v>
       </c>
       <c r="H291" s="7">
-        <v>0.168537</v>
+        <v>0.21266300000000002</v>
       </c>
       <c r="I291" s="7">
-        <v>0.556968</v>
+        <v>0.409248</v>
       </c>
       <c r="J291" s="7">
-        <v>2.499765</v>
+        <v>2.6336619999999997</v>
       </c>
       <c r="K291" s="7">
-        <v>6.316456</v>
+        <v>12.460460000000001</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12233,28 +12239,28 @@
         <v>85</v>
       </c>
       <c r="D292" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E292" s="7">
-        <v>0.09329000000000001</v>
+        <v>0.044923000000000005</v>
       </c>
       <c r="F292" s="7">
-        <v>0.06879400000000001</v>
+        <v>0.072868</v>
       </c>
       <c r="G292" s="7">
-        <v>0.234599</v>
+        <v>0.23398599999999997</v>
       </c>
       <c r="H292" s="7">
-        <v>0.19077200000000002</v>
+        <v>0.171072</v>
       </c>
       <c r="I292" s="7">
-        <v>0.520456</v>
+        <v>0.560346</v>
       </c>
       <c r="J292" s="7">
-        <v>2.865836</v>
+        <v>2.501072</v>
       </c>
       <c r="K292" s="7">
-        <v>8.44862</v>
+        <v>6.3318769999999995</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12265,31 +12271,31 @@
         <v>612</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="D293" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E293" s="7">
-        <v>0.040911</v>
+        <v>0.098341</v>
       </c>
       <c r="F293" s="7">
-        <v>0.062948</v>
+        <v>0.07431499999999999</v>
       </c>
       <c r="G293" s="7">
-        <v>0.22580999999999998</v>
+        <v>0.252961</v>
       </c>
       <c r="H293" s="7">
-        <v>0.12496800000000001</v>
+        <v>0.19627199999999997</v>
       </c>
       <c r="I293" s="7">
-        <v>0.41708799999999996</v>
+        <v>0.527479</v>
       </c>
       <c r="J293" s="7">
-        <v>1.4763460000000002</v>
+        <v>2.876078</v>
       </c>
       <c r="K293" s="7">
-        <v>4.139465</v>
+        <v>8.496278</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12300,31 +12306,31 @@
         <v>614</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D294" s="6">
         <v>4</v>
       </c>
       <c r="E294" s="7">
-        <v>0.02239</v>
+        <v>0.041181999999999996</v>
       </c>
       <c r="F294" s="7">
-        <v>-0.0006090000000000001</v>
+        <v>0.063863</v>
       </c>
       <c r="G294" s="7">
-        <v>0.183247</v>
+        <v>0.22846</v>
       </c>
       <c r="H294" s="7">
-        <v>0.045473</v>
+        <v>0.12526099999999998</v>
       </c>
       <c r="I294" s="7">
-        <v>0.38315600000000005</v>
+        <v>0.41745600000000005</v>
       </c>
       <c r="J294" s="7">
-        <v>1.7056989999999999</v>
+        <v>1.4613589999999999</v>
       </c>
       <c r="K294" s="7">
-        <v>4.779567</v>
+        <v>4.1369229999999995</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12335,31 +12341,31 @@
         <v>616</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D295" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E295" s="7">
-        <v>0.09350199999999999</v>
+        <v>0.022045</v>
       </c>
       <c r="F295" s="7">
-        <v>0.043827</v>
+        <v>0.001691</v>
       </c>
       <c r="G295" s="7">
-        <v>0.297201</v>
+        <v>0.184556</v>
       </c>
       <c r="H295" s="7">
-        <v>0.24895399999999998</v>
+        <v>0.04511999999999999</v>
       </c>
       <c r="I295" s="7">
-        <v>0.574895</v>
+        <v>0.382689</v>
       </c>
       <c r="J295" s="7">
-        <v>3.718367</v>
+        <v>1.702796</v>
       </c>
       <c r="K295" s="7">
-        <v>15.619819999999999</v>
+        <v>4.775074</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12373,28 +12379,28 @@
         <v>26</v>
       </c>
       <c r="D296" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E296" s="7">
-        <v>0.080894</v>
+        <v>0.089642</v>
       </c>
       <c r="F296" s="7">
-        <v>0.061219</v>
+        <v>0.04294</v>
       </c>
       <c r="G296" s="7">
-        <v>0.303491</v>
+        <v>0.31309000000000003</v>
       </c>
       <c r="H296" s="7">
-        <v>0.25778199999999996</v>
+        <v>0.24454399999999998</v>
       </c>
       <c r="I296" s="7">
-        <v>0.581473</v>
+        <v>0.569335</v>
       </c>
       <c r="J296" s="7">
-        <v>3.332332</v>
+        <v>3.701794</v>
       </c>
       <c r="K296" s="7">
-        <v>10.752422999999999</v>
+        <v>15.544373</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12408,28 +12414,28 @@
         <v>26</v>
       </c>
       <c r="D297" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E297" s="7">
-        <v>0.06976399999999999</v>
+        <v>0.08264200000000001</v>
       </c>
       <c r="F297" s="7">
-        <v>0.055267</v>
+        <v>0.062663</v>
       </c>
       <c r="G297" s="7">
-        <v>0.28366199999999997</v>
+        <v>0.320868</v>
       </c>
       <c r="H297" s="7">
-        <v>0.222447</v>
+        <v>0.259817</v>
       </c>
       <c r="I297" s="7">
-        <v>0.578997</v>
+        <v>0.584032</v>
       </c>
       <c r="J297" s="7">
-        <v>3.3124740000000004</v>
+        <v>3.343494</v>
       </c>
       <c r="K297" s="7">
-        <v>9.69486</v>
+        <v>10.762724</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12443,28 +12449,28 @@
         <v>26</v>
       </c>
       <c r="D298" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E298" s="7">
-        <v>0.034366</v>
+        <v>0.072285</v>
       </c>
       <c r="F298" s="7">
-        <v>0.08551500000000001</v>
+        <v>0.055553</v>
       </c>
       <c r="G298" s="7">
-        <v>0.21578</v>
+        <v>0.299631</v>
       </c>
       <c r="H298" s="7">
-        <v>0.1405</v>
+        <v>0.22532800000000003</v>
       </c>
       <c r="I298" s="7">
-        <v>0.509595</v>
+        <v>0.582718</v>
       </c>
       <c r="J298" s="7">
-        <v>2.8312329999999997</v>
+        <v>3.324793</v>
       </c>
       <c r="K298" s="7">
-        <v>5.106087</v>
+        <v>9.712125</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12478,28 +12484,28 @@
         <v>26</v>
       </c>
       <c r="D299" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E299" s="7">
-        <v>0.08788</v>
+        <v>0.035775</v>
       </c>
       <c r="F299" s="7">
-        <v>0.098019</v>
+        <v>0.086684</v>
       </c>
       <c r="G299" s="7">
-        <v>0.327593</v>
+        <v>0.217988</v>
       </c>
       <c r="H299" s="7">
-        <v>0.269849</v>
+        <v>0.14205299999999998</v>
       </c>
       <c r="I299" s="7">
-        <v>0.660177</v>
+        <v>0.511652</v>
       </c>
       <c r="J299" s="7">
-        <v>3.26102</v>
+        <v>2.8294940000000004</v>
       </c>
       <c r="K299" s="7">
-        <v>9.742981</v>
+        <v>5.112144</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12513,28 +12519,28 @@
         <v>26</v>
       </c>
       <c r="D300" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E300" s="7">
-        <v>0.093597</v>
+        <v>0.092059</v>
       </c>
       <c r="F300" s="7">
-        <v>0.090559</v>
+        <v>0.10245900000000001</v>
       </c>
       <c r="G300" s="7">
-        <v>0.33720799999999995</v>
+        <v>0.346719</v>
       </c>
       <c r="H300" s="7">
-        <v>0.282846</v>
+        <v>0.27472799999999997</v>
       </c>
       <c r="I300" s="7">
-        <v>0.709669</v>
+        <v>0.666555</v>
       </c>
       <c r="J300" s="7">
-        <v>3.506888</v>
+        <v>3.2662670000000005</v>
       </c>
       <c r="K300" s="7">
-        <v>12.365145</v>
+        <v>9.782227</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12545,31 +12551,31 @@
         <v>628</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D301" s="6">
         <v>6</v>
       </c>
       <c r="E301" s="7">
-        <v>0.097817</v>
+        <v>0.09939</v>
       </c>
       <c r="F301" s="7">
-        <v>0.102856</v>
+        <v>0.094957</v>
       </c>
       <c r="G301" s="7">
-        <v>0.282346</v>
+        <v>0.361763</v>
       </c>
       <c r="H301" s="7">
-        <v>0.282798</v>
+        <v>0.289641</v>
       </c>
       <c r="I301" s="7">
-        <v>0.5845859999999999</v>
+        <v>0.7187260000000001</v>
       </c>
       <c r="J301" s="7">
-        <v>2.3331749999999998</v>
+        <v>3.51529</v>
       </c>
       <c r="K301" s="7">
-        <v>8.692709</v>
+        <v>12.432042</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12580,30 +12586,32 @@
         <v>630</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D302" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E302" s="7">
-        <v>0.169599</v>
+        <v>0.101754</v>
       </c>
       <c r="F302" s="7">
-        <v>0.169786</v>
+        <v>0.106566</v>
       </c>
       <c r="G302" s="7">
-        <v>0.23058</v>
+        <v>0.301796</v>
       </c>
       <c r="H302" s="7">
-        <v>0.240322</v>
+        <v>0.28739899999999996</v>
       </c>
       <c r="I302" s="7">
-        <v>0.6507729999999999</v>
+        <v>0.59027</v>
       </c>
       <c r="J302" s="7">
-        <v>3.658721</v>
-      </c>
-      <c r="K302" s="7"/>
+        <v>2.334177</v>
+      </c>
+      <c r="K302" s="7">
+        <v>8.711956</v>
+      </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
@@ -12613,32 +12621,30 @@
         <v>632</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D303" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E303" s="7">
-        <v>0.09077299999999999</v>
+        <v>0.19889900000000002</v>
       </c>
       <c r="F303" s="7">
-        <v>0.033658</v>
+        <v>0.219871</v>
       </c>
       <c r="G303" s="7">
-        <v>0.24752400000000002</v>
+        <v>0.282582</v>
       </c>
       <c r="H303" s="7">
-        <v>0.18190699999999999</v>
+        <v>0.27139399999999997</v>
       </c>
       <c r="I303" s="7">
-        <v>0.500294</v>
+        <v>0.6921269999999999</v>
       </c>
       <c r="J303" s="7">
-        <v>2.6895119999999997</v>
-      </c>
-      <c r="K303" s="7">
-        <v>11.440776000000001</v>
-      </c>
+        <v>3.7884089999999997</v>
+      </c>
+      <c r="K303" s="7"/>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
@@ -12648,31 +12654,31 @@
         <v>634</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>191</v>
+        <v>32</v>
       </c>
       <c r="D304" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E304" s="7">
-        <v>0.02176</v>
+        <v>0.09376200000000001</v>
       </c>
       <c r="F304" s="7">
-        <v>0.033367</v>
+        <v>0.04402300000000001</v>
       </c>
       <c r="G304" s="7">
-        <v>0.078988</v>
+        <v>0.26405100000000004</v>
       </c>
       <c r="H304" s="7">
-        <v>0.048270999999999994</v>
+        <v>0.185146</v>
       </c>
       <c r="I304" s="7">
-        <v>0.232267</v>
+        <v>0.504405</v>
       </c>
       <c r="J304" s="7">
-        <v>1.8024639999999998</v>
+        <v>2.7088440000000005</v>
       </c>
       <c r="K304" s="7">
-        <v>5.56875</v>
+        <v>11.486857</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12683,31 +12689,31 @@
         <v>636</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>26</v>
+        <v>191</v>
       </c>
       <c r="D305" s="6">
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.047967</v>
+        <v>0.024665</v>
       </c>
       <c r="F305" s="7">
-        <v>0.005299000000000001</v>
+        <v>0.036137999999999997</v>
       </c>
       <c r="G305" s="7">
-        <v>0.158556</v>
+        <v>0.082081</v>
       </c>
       <c r="H305" s="7">
-        <v>0.084842</v>
+        <v>0.051251</v>
       </c>
       <c r="I305" s="7">
-        <v>0.486282</v>
+        <v>0.23577</v>
       </c>
       <c r="J305" s="7">
-        <v>2.4107320000000003</v>
+        <v>1.807209</v>
       </c>
       <c r="K305" s="7">
-        <v>7.573665999999999</v>
+        <v>5.57474</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12718,31 +12724,31 @@
         <v>638</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D306" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E306" s="7">
-        <v>0.036668</v>
+        <v>0.039243</v>
       </c>
       <c r="F306" s="7">
-        <v>0.080844</v>
+        <v>0.00215</v>
       </c>
       <c r="G306" s="7">
-        <v>0.20613099999999998</v>
+        <v>0.157533</v>
       </c>
       <c r="H306" s="7">
-        <v>0.144393</v>
+        <v>0.075811</v>
       </c>
       <c r="I306" s="7">
-        <v>0.464133</v>
+        <v>0.473908</v>
       </c>
       <c r="J306" s="7">
-        <v>2.0008850000000002</v>
+        <v>2.382764</v>
       </c>
       <c r="K306" s="7">
-        <v>5.251383</v>
+        <v>7.5141290000000005</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12753,35 +12759,70 @@
         <v>640</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>641</v>
+        <v>85</v>
       </c>
       <c r="D307" s="6">
         <v>3</v>
       </c>
       <c r="E307" s="7">
-        <v>0.020510999999999998</v>
+        <v>0.039428</v>
       </c>
       <c r="F307" s="7">
-        <v>0.010661</v>
+        <v>0.080876</v>
       </c>
       <c r="G307" s="7">
-        <v>0.134741</v>
+        <v>0.211587</v>
       </c>
       <c r="H307" s="7">
-        <v>0.034185</v>
+        <v>0.14744</v>
       </c>
       <c r="I307" s="7">
-        <v>0.376734</v>
+        <v>0.46803100000000003</v>
       </c>
       <c r="J307" s="7">
-        <v>0.9971850000000001</v>
+        <v>2.003898</v>
       </c>
       <c r="K307" s="7">
-        <v>2.1146469999999997</v>
+        <v>5.271291</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A308" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>643</v>
+      </c>
+      <c r="D308" s="6">
+        <v>3</v>
+      </c>
+      <c r="E308" s="7">
+        <v>0.022677</v>
+      </c>
+      <c r="F308" s="7">
+        <v>0.014137</v>
+      </c>
+      <c r="G308" s="7">
+        <v>0.137129</v>
+      </c>
+      <c r="H308" s="7">
+        <v>0.036379999999999996</v>
+      </c>
+      <c r="I308" s="7">
+        <v>0.37965499999999996</v>
+      </c>
+      <c r="J308" s="7">
+        <v>1.000917</v>
+      </c>
+      <c r="K308" s="7">
+        <v>2.118642</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K307"/>
+  <autoFilter ref="A5:K308"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>06.05.2026 18:18:13</t>
+    <t>07.05.2026 18:21:16</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2466,25 +2466,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.041355</v>
+        <v>0.050809</v>
       </c>
       <c r="F6" s="7">
-        <v>0.040692000000000006</v>
+        <v>0.052968</v>
       </c>
       <c r="G6" s="7">
-        <v>0.19328099999999998</v>
+        <v>0.204767</v>
       </c>
       <c r="H6" s="7">
-        <v>0.104521</v>
+        <v>0.1184</v>
       </c>
       <c r="I6" s="7">
-        <v>0.455128</v>
+        <v>0.46881</v>
       </c>
       <c r="J6" s="7">
-        <v>2.228282</v>
+        <v>2.268848</v>
       </c>
       <c r="K6" s="7">
-        <v>5.692186</v>
+        <v>5.76242</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2501,25 +2501,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.120665</v>
+        <v>0.116213</v>
       </c>
       <c r="F7" s="7">
-        <v>0.08974399999999999</v>
+        <v>0.102138</v>
       </c>
       <c r="G7" s="7">
-        <v>0.15526099999999998</v>
+        <v>0.16031199999999998</v>
       </c>
       <c r="H7" s="7">
-        <v>0.10441700000000001</v>
+        <v>0.115098</v>
       </c>
       <c r="I7" s="7">
-        <v>0.492244</v>
+        <v>0.516504</v>
       </c>
       <c r="J7" s="7">
-        <v>2.884126</v>
+        <v>2.9216919999999997</v>
       </c>
       <c r="K7" s="7">
-        <v>5.64116</v>
+        <v>5.661022</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2536,25 +2536,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.023967000000000002</v>
+        <v>0.033592</v>
       </c>
       <c r="F8" s="7">
-        <v>0.009642</v>
+        <v>0.019423</v>
       </c>
       <c r="G8" s="7">
-        <v>0.139435</v>
+        <v>0.151649</v>
       </c>
       <c r="H8" s="7">
-        <v>0.04617</v>
+        <v>0.05733</v>
       </c>
       <c r="I8" s="7">
-        <v>0.38476</v>
+        <v>0.398097</v>
       </c>
       <c r="J8" s="7">
-        <v>1.7388659999999998</v>
+        <v>1.768084</v>
       </c>
       <c r="K8" s="7">
-        <v>3.5436509999999997</v>
+        <v>3.582772</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2571,25 +2571,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.085532</v>
+        <v>0.100964</v>
       </c>
       <c r="F9" s="7">
-        <v>0.078385</v>
+        <v>0.099636</v>
       </c>
       <c r="G9" s="7">
-        <v>0.305684</v>
+        <v>0.32218</v>
       </c>
       <c r="H9" s="7">
-        <v>0.255677</v>
+        <v>0.282463</v>
       </c>
       <c r="I9" s="7">
-        <v>0.576033</v>
+        <v>0.599583</v>
       </c>
       <c r="J9" s="7">
-        <v>3.228017</v>
+        <v>3.3182069999999997</v>
       </c>
       <c r="K9" s="7">
-        <v>10.415655999999998</v>
+        <v>10.603539000000001</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2606,25 +2606,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.028172000000000003</v>
+        <v>-0.008579</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.09840199999999999</v>
+        <v>-0.083233</v>
       </c>
       <c r="G10" s="7">
-        <v>0.147983</v>
+        <v>0.164165</v>
       </c>
       <c r="H10" s="7">
-        <v>0.025515</v>
+        <v>0.050159</v>
       </c>
       <c r="I10" s="7">
-        <v>0.490202</v>
+        <v>0.521605</v>
       </c>
       <c r="J10" s="7">
-        <v>3.930345</v>
+        <v>4.048821</v>
       </c>
       <c r="K10" s="7">
-        <v>13.223847000000001</v>
+        <v>13.578712000000001</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2641,25 +2641,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.108903</v>
+        <v>0.12086000000000001</v>
       </c>
       <c r="F11" s="7">
-        <v>0.08594099999999999</v>
+        <v>0.113034</v>
       </c>
       <c r="G11" s="7">
-        <v>0.346443</v>
+        <v>0.361916</v>
       </c>
       <c r="H11" s="7">
-        <v>0.29431</v>
+        <v>0.327055</v>
       </c>
       <c r="I11" s="7">
-        <v>0.627669</v>
+        <v>0.66365</v>
       </c>
       <c r="J11" s="7">
-        <v>2.875959</v>
+        <v>2.9740159999999998</v>
       </c>
       <c r="K11" s="7">
-        <v>12.723386</v>
+        <v>12.974264</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2676,25 +2676,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.047995</v>
+        <v>0.051763</v>
       </c>
       <c r="F12" s="7">
-        <v>0.077312</v>
+        <v>0.084199</v>
       </c>
       <c r="G12" s="7">
-        <v>0.24295100000000003</v>
+        <v>0.24813500000000002</v>
       </c>
       <c r="H12" s="7">
-        <v>0.150999</v>
+        <v>0.159677</v>
       </c>
       <c r="I12" s="7">
-        <v>0.499861</v>
+        <v>0.506762</v>
       </c>
       <c r="J12" s="7">
-        <v>2.7053879999999997</v>
+        <v>2.733323</v>
       </c>
       <c r="K12" s="7">
-        <v>4.562966</v>
+        <v>4.584427</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2711,25 +2711,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.114564</v>
+        <v>0.13140000000000002</v>
       </c>
       <c r="F13" s="7">
-        <v>0.089363</v>
+        <v>0.120639</v>
       </c>
       <c r="G13" s="7">
-        <v>0.37432699999999997</v>
+        <v>0.401072</v>
       </c>
       <c r="H13" s="7">
-        <v>0.305749</v>
+        <v>0.33917700000000006</v>
       </c>
       <c r="I13" s="7">
-        <v>0.6534399999999999</v>
+        <v>0.6830620000000001</v>
       </c>
       <c r="J13" s="7">
-        <v>3.0326889999999995</v>
+        <v>3.1359269999999997</v>
       </c>
       <c r="K13" s="7">
-        <v>10.454201000000001</v>
+        <v>10.708784000000001</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2746,25 +2746,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.051334</v>
+        <v>0.067142</v>
       </c>
       <c r="F14" s="7">
-        <v>0.043407</v>
+        <v>0.058571</v>
       </c>
       <c r="G14" s="7">
-        <v>0.260927</v>
+        <v>0.273667</v>
       </c>
       <c r="H14" s="7">
-        <v>0.181192</v>
+        <v>0.204743</v>
       </c>
       <c r="I14" s="7">
-        <v>0.48679</v>
+        <v>0.501664</v>
       </c>
       <c r="J14" s="7">
-        <v>2.718467</v>
+        <v>2.792606</v>
       </c>
       <c r="K14" s="7">
-        <v>7.995423</v>
+        <v>8.165652999999999</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2781,25 +2781,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.031056</v>
+        <v>0.040629</v>
       </c>
       <c r="F15" s="7">
-        <v>0.023136999999999998</v>
+        <v>0.033989</v>
       </c>
       <c r="G15" s="7">
-        <v>0.176531</v>
+        <v>0.187108</v>
       </c>
       <c r="H15" s="7">
-        <v>0.077332</v>
+        <v>0.09011200000000001</v>
       </c>
       <c r="I15" s="7">
-        <v>0.407453</v>
+        <v>0.42392</v>
       </c>
       <c r="J15" s="7">
-        <v>2.0295259999999997</v>
+        <v>2.065463</v>
       </c>
       <c r="K15" s="7">
-        <v>5.49587</v>
+        <v>5.563216</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2816,25 +2816,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.037732</v>
+        <v>0.042037000000000005</v>
       </c>
       <c r="F16" s="7">
-        <v>0.087458</v>
+        <v>0.092574</v>
       </c>
       <c r="G16" s="7">
-        <v>0.218885</v>
+        <v>0.225146</v>
       </c>
       <c r="H16" s="7">
-        <v>0.142694</v>
+        <v>0.150589</v>
       </c>
       <c r="I16" s="7">
-        <v>0.511227</v>
+        <v>0.518604</v>
       </c>
       <c r="J16" s="7">
-        <v>2.784274</v>
+        <v>2.8104199999999997</v>
       </c>
       <c r="K16" s="7">
-        <v>5.064895</v>
+        <v>5.103404</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2851,25 +2851,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.038901</v>
+        <v>0.038834</v>
       </c>
       <c r="F17" s="7">
-        <v>0.077741</v>
+        <v>0.08155200000000001</v>
       </c>
       <c r="G17" s="7">
-        <v>0.19456700000000002</v>
+        <v>0.19779699999999997</v>
       </c>
       <c r="H17" s="7">
-        <v>0.136099</v>
+        <v>0.141206</v>
       </c>
       <c r="I17" s="7">
-        <v>0.420274</v>
+        <v>0.423335</v>
       </c>
       <c r="J17" s="7">
-        <v>1.688984</v>
+        <v>1.701071</v>
       </c>
       <c r="K17" s="7">
-        <v>4.530231</v>
+        <v>4.551812</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2886,25 +2886,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.020666000000000004</v>
+        <v>-0.0015609999999999999</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.0861</v>
+        <v>-0.069086</v>
       </c>
       <c r="G18" s="7">
-        <v>0.203687</v>
+        <v>0.221198</v>
       </c>
       <c r="H18" s="7">
-        <v>0.04925500000000001</v>
+        <v>0.074438</v>
       </c>
       <c r="I18" s="7">
-        <v>0.597875</v>
+        <v>0.602313</v>
       </c>
       <c r="J18" s="7">
-        <v>4.64881</v>
+        <v>4.784384</v>
       </c>
       <c r="K18" s="7">
-        <v>15.480452</v>
+        <v>15.869397</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2921,25 +2921,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.070836</v>
+        <v>0.068912</v>
       </c>
       <c r="F19" s="7">
-        <v>0.062567</v>
+        <v>0.07599</v>
       </c>
       <c r="G19" s="7">
-        <v>0.19988</v>
+        <v>0.213275</v>
       </c>
       <c r="H19" s="7">
-        <v>0.123004</v>
+        <v>0.135439</v>
       </c>
       <c r="I19" s="7">
-        <v>0.452146</v>
+        <v>0.463643</v>
       </c>
       <c r="J19" s="7">
-        <v>2.346172</v>
+        <v>2.383224</v>
       </c>
       <c r="K19" s="7">
-        <v>6.9299159999999995</v>
+        <v>7.003586</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2956,25 +2956,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.040505000000000006</v>
+        <v>0.045262000000000004</v>
       </c>
       <c r="F20" s="7">
-        <v>0.09689500000000001</v>
+        <v>0.103795</v>
       </c>
       <c r="G20" s="7">
-        <v>0.24351199999999998</v>
+        <v>0.249451</v>
       </c>
       <c r="H20" s="7">
-        <v>0.096905</v>
+        <v>0.10574</v>
       </c>
       <c r="I20" s="7">
-        <v>0.461032</v>
+        <v>0.472954</v>
       </c>
       <c r="J20" s="7">
-        <v>1.519885</v>
+        <v>1.5401820000000002</v>
       </c>
       <c r="K20" s="7">
-        <v>4.194103</v>
+        <v>4.225148</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2991,25 +2991,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.042538</v>
+        <v>0.039087000000000004</v>
       </c>
       <c r="F21" s="7">
-        <v>0.09456400000000001</v>
+        <v>0.09924799999999999</v>
       </c>
       <c r="G21" s="7">
-        <v>0.20758600000000002</v>
+        <v>0.21214200000000002</v>
       </c>
       <c r="H21" s="7">
-        <v>0.154417</v>
+        <v>0.158765</v>
       </c>
       <c r="I21" s="7">
-        <v>0.44815</v>
+        <v>0.449484</v>
       </c>
       <c r="J21" s="7">
-        <v>1.8652119999999999</v>
+        <v>1.876002</v>
       </c>
       <c r="K21" s="7">
-        <v>5.015572000000001</v>
+        <v>5.025442</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3026,25 +3026,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.112947</v>
+        <v>0.112814</v>
       </c>
       <c r="F22" s="7">
-        <v>0.118743</v>
+        <v>0.139932</v>
       </c>
       <c r="G22" s="7">
-        <v>0.278696</v>
+        <v>0.296158</v>
       </c>
       <c r="H22" s="7">
-        <v>0.27119499999999996</v>
+        <v>0.291755</v>
       </c>
       <c r="I22" s="7">
-        <v>0.609737</v>
+        <v>0.631363</v>
       </c>
       <c r="J22" s="7">
-        <v>3.0509730000000004</v>
+        <v>3.1164929999999997</v>
       </c>
       <c r="K22" s="7">
-        <v>10.795350000000001</v>
+        <v>10.937125000000002</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3061,25 +3061,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.028195</v>
+        <v>0.028436</v>
       </c>
       <c r="F23" s="7">
-        <v>0.08063599999999999</v>
+        <v>0.079252</v>
       </c>
       <c r="G23" s="7">
-        <v>0.183902</v>
+        <v>0.184197</v>
       </c>
       <c r="H23" s="7">
-        <v>0.124307</v>
+        <v>0.125809</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40834699999999996</v>
+        <v>0.40869900000000003</v>
       </c>
       <c r="J23" s="7">
-        <v>2.201187</v>
+        <v>2.205464</v>
       </c>
       <c r="K23" s="7">
-        <v>5.000247</v>
+        <v>5.006991</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3096,25 +3096,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.025619999999999997</v>
+        <v>0.035329</v>
       </c>
       <c r="F24" s="7">
-        <v>0.011032</v>
+        <v>0.020748000000000003</v>
       </c>
       <c r="G24" s="7">
-        <v>0.133553</v>
+        <v>0.146789</v>
       </c>
       <c r="H24" s="7">
-        <v>0.034921</v>
+        <v>0.046406</v>
       </c>
       <c r="I24" s="7">
-        <v>0.370751</v>
+        <v>0.38591299999999995</v>
       </c>
       <c r="J24" s="7">
-        <v>1.582951</v>
+        <v>1.6116169999999999</v>
       </c>
       <c r="K24" s="7">
-        <v>3.411218</v>
+        <v>3.450678</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3131,25 +3131,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.032555</v>
+        <v>0.037467</v>
       </c>
       <c r="F25" s="7">
-        <v>0.035602</v>
+        <v>0.042581</v>
       </c>
       <c r="G25" s="7">
-        <v>0.117133</v>
+        <v>0.124734</v>
       </c>
       <c r="H25" s="7">
-        <v>0.055438999999999995</v>
+        <v>0.063427</v>
       </c>
       <c r="I25" s="7">
-        <v>0.340685</v>
+        <v>0.34832500000000005</v>
       </c>
       <c r="J25" s="7">
-        <v>2.11766</v>
+        <v>2.1412549999999997</v>
       </c>
       <c r="K25" s="7">
-        <v>6.34347</v>
+        <v>6.390988</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3166,25 +3166,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.037876</v>
+        <v>0.046725</v>
       </c>
       <c r="F26" s="7">
-        <v>0.024933999999999998</v>
+        <v>0.035707</v>
       </c>
       <c r="G26" s="7">
-        <v>0.120173</v>
+        <v>0.129525</v>
       </c>
       <c r="H26" s="7">
-        <v>0.051701</v>
+        <v>0.063235</v>
       </c>
       <c r="I26" s="7">
-        <v>0.30044699999999996</v>
+        <v>0.314634</v>
       </c>
       <c r="J26" s="7">
-        <v>2.066681</v>
+        <v>2.100313</v>
       </c>
       <c r="K26" s="7">
-        <v>5.574822</v>
+        <v>5.636093</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3201,25 +3201,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.07319099999999999</v>
+        <v>0.09341300000000001</v>
       </c>
       <c r="F27" s="7">
-        <v>0.012838</v>
+        <v>0.044271000000000005</v>
       </c>
       <c r="G27" s="7">
-        <v>0.21192599999999998</v>
+        <v>0.23485399999999998</v>
       </c>
       <c r="H27" s="7">
-        <v>0.18997699999999998</v>
+        <v>0.227464</v>
       </c>
       <c r="I27" s="7">
-        <v>0.42863999999999997</v>
+        <v>0.47173099999999996</v>
       </c>
       <c r="J27" s="7">
-        <v>3.4155029999999997</v>
+        <v>3.554602</v>
       </c>
       <c r="K27" s="7">
-        <v>15.920053000000001</v>
+        <v>16.315573999999998</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3236,25 +3236,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.10479</v>
+        <v>0.114424</v>
       </c>
       <c r="F28" s="7">
-        <v>0.064694</v>
+        <v>0.084826</v>
       </c>
       <c r="G28" s="7">
-        <v>0.143279</v>
+        <v>0.157501</v>
       </c>
       <c r="H28" s="7">
-        <v>0.111802</v>
+        <v>0.131336</v>
       </c>
       <c r="I28" s="7">
-        <v>0.419041</v>
+        <v>0.445458</v>
       </c>
       <c r="J28" s="7">
-        <v>2.635709</v>
+        <v>2.6995850000000003</v>
       </c>
       <c r="K28" s="7">
-        <v>7.9236450000000005</v>
+        <v>8.066373</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3271,25 +3271,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.029434000000000002</v>
+        <v>0.033979</v>
       </c>
       <c r="F29" s="7">
-        <v>0.048782</v>
+        <v>0.054607</v>
       </c>
       <c r="G29" s="7">
-        <v>0.166305</v>
+        <v>0.17142600000000002</v>
       </c>
       <c r="H29" s="7">
-        <v>0.099495</v>
+        <v>0.107097</v>
       </c>
       <c r="I29" s="7">
-        <v>0.40281799999999995</v>
+        <v>0.41179499999999997</v>
       </c>
       <c r="J29" s="7">
-        <v>2.4108140000000002</v>
+        <v>2.4343969999999997</v>
       </c>
       <c r="K29" s="7">
-        <v>4.563734999999999</v>
+        <v>4.599034</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3306,25 +3306,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.048876</v>
+        <v>0.061514</v>
       </c>
       <c r="F30" s="7">
-        <v>0.024515</v>
+        <v>0.041696</v>
       </c>
       <c r="G30" s="7">
-        <v>0.181943</v>
+        <v>0.193805</v>
       </c>
       <c r="H30" s="7">
-        <v>0.150023</v>
+        <v>0.17042100000000002</v>
       </c>
       <c r="I30" s="7">
-        <v>0.396659</v>
+        <v>0.420101</v>
       </c>
       <c r="J30" s="7">
-        <v>3.1230770000000003</v>
+        <v>3.1962099999999998</v>
       </c>
       <c r="K30" s="7">
-        <v>9.420089</v>
+        <v>9.568779</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3341,25 +3341,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.11055300000000001</v>
+        <v>0.127298</v>
       </c>
       <c r="F31" s="7">
-        <v>0.031121</v>
+        <v>0.06310500000000001</v>
       </c>
       <c r="G31" s="7">
-        <v>0.240328</v>
+        <v>0.266516</v>
       </c>
       <c r="H31" s="7">
-        <v>0.212941</v>
+        <v>0.246999</v>
       </c>
       <c r="I31" s="7">
-        <v>0.408379</v>
+        <v>0.442396</v>
       </c>
       <c r="J31" s="7">
-        <v>2.774137</v>
+        <v>2.88011</v>
       </c>
       <c r="K31" s="7">
-        <v>14.575879</v>
+        <v>14.82086</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3376,25 +3376,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.030882</v>
+        <v>0.030763</v>
       </c>
       <c r="F32" s="7">
-        <v>0.08535</v>
+        <v>0.08411400000000001</v>
       </c>
       <c r="G32" s="7">
-        <v>0.1931</v>
+        <v>0.19273800000000002</v>
       </c>
       <c r="H32" s="7">
-        <v>0.121487</v>
+        <v>0.122827</v>
       </c>
       <c r="I32" s="7">
-        <v>0.44929699999999995</v>
+        <v>0.449709</v>
       </c>
       <c r="J32" s="7">
-        <v>2.165184</v>
+        <v>2.168965</v>
       </c>
       <c r="K32" s="7">
-        <v>3.742546</v>
+        <v>3.746143</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3411,25 +3411,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.057256</v>
+        <v>0.067772</v>
       </c>
       <c r="F33" s="7">
-        <v>0.020663</v>
+        <v>0.046807</v>
       </c>
       <c r="G33" s="7">
-        <v>0.21325</v>
+        <v>0.234011</v>
       </c>
       <c r="H33" s="7">
-        <v>0.170121</v>
+        <v>0.198445</v>
       </c>
       <c r="I33" s="7">
-        <v>0.453066</v>
+        <v>0.484547</v>
       </c>
       <c r="J33" s="7">
-        <v>3.5915890000000004</v>
+        <v>3.7027330000000003</v>
       </c>
       <c r="K33" s="7">
-        <v>16.154318</v>
+        <v>16.468581999999998</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3446,25 +3446,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.10020799999999999</v>
+        <v>0.102887</v>
       </c>
       <c r="F34" s="7">
-        <v>0.123439</v>
+        <v>0.138436</v>
       </c>
       <c r="G34" s="7">
-        <v>0.353641</v>
+        <v>0.365811</v>
       </c>
       <c r="H34" s="7">
-        <v>0.287439</v>
+        <v>0.304146</v>
       </c>
       <c r="I34" s="7">
-        <v>0.670385</v>
+        <v>0.68647</v>
       </c>
       <c r="J34" s="7">
-        <v>3.3291489999999997</v>
+        <v>3.385328</v>
       </c>
       <c r="K34" s="7">
-        <v>9.823309</v>
+        <v>9.952138</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3481,25 +3481,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.108696</v>
+        <v>0.111837</v>
       </c>
       <c r="F35" s="7">
-        <v>0.12410199999999999</v>
+        <v>0.140654</v>
       </c>
       <c r="G35" s="7">
-        <v>0.36784</v>
+        <v>0.383359</v>
       </c>
       <c r="H35" s="7">
-        <v>0.30034099999999997</v>
+        <v>0.32120899999999997</v>
       </c>
       <c r="I35" s="7">
-        <v>0.735012</v>
+        <v>0.7563460000000001</v>
       </c>
       <c r="J35" s="7">
-        <v>3.591925</v>
+        <v>3.6656180000000003</v>
       </c>
       <c r="K35" s="7">
-        <v>12.393172999999999</v>
+        <v>12.584655</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3516,25 +3516,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.054858000000000004</v>
+        <v>0.06389</v>
       </c>
       <c r="F36" s="7">
-        <v>0.021927</v>
+        <v>0.046904</v>
       </c>
       <c r="G36" s="7">
-        <v>0.221603</v>
+        <v>0.240724</v>
       </c>
       <c r="H36" s="7">
-        <v>0.180169</v>
+        <v>0.207339</v>
       </c>
       <c r="I36" s="7">
-        <v>0.474255</v>
+        <v>0.5038130000000001</v>
       </c>
       <c r="J36" s="7">
-        <v>3.6705270000000003</v>
+        <v>3.7780509999999996</v>
       </c>
       <c r="K36" s="7">
-        <v>16.79768</v>
+        <v>17.084863</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3551,25 +3551,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.047931</v>
+        <v>0.055066</v>
       </c>
       <c r="F37" s="7">
-        <v>0.028355</v>
+        <v>0.048112</v>
       </c>
       <c r="G37" s="7">
-        <v>0.23742999999999997</v>
+        <v>0.249921</v>
       </c>
       <c r="H37" s="7">
-        <v>0.166278</v>
+        <v>0.188425</v>
       </c>
       <c r="I37" s="7">
-        <v>0.472275</v>
+        <v>0.499529</v>
       </c>
       <c r="J37" s="7">
-        <v>3.7518540000000002</v>
+        <v>3.842089</v>
       </c>
       <c r="K37" s="7">
-        <v>15.328568</v>
+        <v>15.56031</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3586,25 +3586,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.036873</v>
+        <v>0.043668</v>
       </c>
       <c r="F38" s="7">
-        <v>0.026974</v>
+        <v>0.043891</v>
       </c>
       <c r="G38" s="7">
-        <v>0.206952</v>
+        <v>0.217541</v>
       </c>
       <c r="H38" s="7">
-        <v>0.149027</v>
+        <v>0.16772700000000001</v>
       </c>
       <c r="I38" s="7">
-        <v>0.463881</v>
+        <v>0.488265</v>
       </c>
       <c r="J38" s="7">
-        <v>3.606342</v>
+        <v>3.681307</v>
       </c>
       <c r="K38" s="7">
-        <v>11.438339000000001</v>
+        <v>11.591952000000001</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3621,25 +3621,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.028328000000000002</v>
+        <v>0.032045</v>
       </c>
       <c r="F39" s="7">
-        <v>0.060429000000000004</v>
+        <v>0.066399</v>
       </c>
       <c r="G39" s="7">
-        <v>0.18941</v>
+        <v>0.19544899999999998</v>
       </c>
       <c r="H39" s="7">
-        <v>0.12034700000000001</v>
+        <v>0.128194</v>
       </c>
       <c r="I39" s="7">
-        <v>0.457815</v>
+        <v>0.468194</v>
       </c>
       <c r="J39" s="7">
-        <v>2.9638099999999996</v>
+        <v>2.991574</v>
       </c>
       <c r="K39" s="7">
-        <v>5.693725</v>
+        <v>5.735897</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3656,25 +3656,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.08573</v>
+        <v>0.078894</v>
       </c>
       <c r="F40" s="7">
-        <v>0.130257</v>
+        <v>0.141756</v>
       </c>
       <c r="G40" s="7">
-        <v>0.302685</v>
+        <v>0.312866</v>
       </c>
       <c r="H40" s="7">
-        <v>0.247802</v>
+        <v>0.258419</v>
       </c>
       <c r="I40" s="7">
-        <v>0.618294</v>
+        <v>0.622115</v>
       </c>
       <c r="J40" s="7">
-        <v>3.530024</v>
+        <v>3.568566</v>
       </c>
       <c r="K40" s="7">
-        <v>11.675445</v>
+        <v>11.723268000000001</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3691,25 +3691,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.068112</v>
+        <v>0.063031</v>
       </c>
       <c r="F41" s="7">
-        <v>0.11387499999999999</v>
+        <v>0.125595</v>
       </c>
       <c r="G41" s="7">
-        <v>0.277715</v>
+        <v>0.288323</v>
       </c>
       <c r="H41" s="7">
-        <v>0.219269</v>
+        <v>0.230617</v>
       </c>
       <c r="I41" s="7">
-        <v>0.591775</v>
+        <v>0.596436</v>
       </c>
       <c r="J41" s="7">
-        <v>3.2100869999999997</v>
+        <v>3.249273</v>
       </c>
       <c r="K41" s="7">
-        <v>9.940769</v>
+        <v>9.995905</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3726,25 +3726,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.092131</v>
+        <v>0.10402499999999999</v>
       </c>
       <c r="F42" s="7">
-        <v>0.08951599999999998</v>
+        <v>0.108727</v>
       </c>
       <c r="G42" s="7">
-        <v>0.321051</v>
+        <v>0.336154</v>
       </c>
       <c r="H42" s="7">
-        <v>0.26384599999999997</v>
+        <v>0.28809799999999997</v>
       </c>
       <c r="I42" s="7">
-        <v>0.598739</v>
+        <v>0.618708</v>
       </c>
       <c r="J42" s="7">
-        <v>3.2854919999999996</v>
+        <v>3.367728</v>
       </c>
       <c r="K42" s="7">
-        <v>10.840727999999999</v>
+        <v>11.013053</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3761,25 +3761,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.062416</v>
+        <v>0.069649</v>
       </c>
       <c r="F43" s="7">
-        <v>0.016378</v>
+        <v>0.04090099999999999</v>
       </c>
       <c r="G43" s="7">
-        <v>0.228542</v>
+        <v>0.244686</v>
       </c>
       <c r="H43" s="7">
-        <v>0.18290900000000002</v>
+        <v>0.210363</v>
       </c>
       <c r="I43" s="7">
-        <v>0.47601</v>
+        <v>0.508146</v>
       </c>
       <c r="J43" s="7">
-        <v>4.173184</v>
+        <v>4.2932440000000005</v>
       </c>
       <c r="K43" s="7">
-        <v>20.963129</v>
+        <v>21.323323000000002</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3796,25 +3796,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.037139000000000005</v>
+        <v>0.040510000000000004</v>
       </c>
       <c r="F44" s="7">
-        <v>0.063347</v>
+        <v>0.066994</v>
       </c>
       <c r="G44" s="7">
-        <v>0.197074</v>
+        <v>0.202202</v>
       </c>
       <c r="H44" s="7">
-        <v>0.119844</v>
+        <v>0.126421</v>
       </c>
       <c r="I44" s="7">
-        <v>0.476759</v>
+        <v>0.48253799999999997</v>
       </c>
       <c r="J44" s="7">
-        <v>2.459298</v>
+        <v>2.479613</v>
       </c>
       <c r="K44" s="7">
-        <v>4.46415</v>
+        <v>4.493377</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3831,25 +3831,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.073811</v>
+        <v>0.08355</v>
       </c>
       <c r="F45" s="7">
-        <v>0.08355800000000001</v>
+        <v>0.099156</v>
       </c>
       <c r="G45" s="7">
-        <v>0.29786999999999997</v>
+        <v>0.314071</v>
       </c>
       <c r="H45" s="7">
-        <v>0.226047</v>
+        <v>0.247413</v>
       </c>
       <c r="I45" s="7">
-        <v>0.5946560000000001</v>
+        <v>0.61648</v>
       </c>
       <c r="J45" s="7">
-        <v>3.367185</v>
+        <v>3.443291</v>
       </c>
       <c r="K45" s="7">
-        <v>9.531854</v>
+        <v>9.677987</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3866,25 +3866,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.071745</v>
+        <v>0.067977</v>
       </c>
       <c r="F46" s="7">
-        <v>0.127791</v>
+        <v>0.137487</v>
       </c>
       <c r="G46" s="7">
-        <v>0.30534500000000003</v>
+        <v>0.315536</v>
       </c>
       <c r="H46" s="7">
-        <v>0.25567</v>
+        <v>0.267353</v>
       </c>
       <c r="I46" s="7">
-        <v>0.612835</v>
+        <v>0.618687</v>
       </c>
       <c r="J46" s="7">
-        <v>3.672638</v>
+        <v>3.716111</v>
       </c>
       <c r="K46" s="7">
-        <v>10.239573</v>
+        <v>10.296637</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3901,25 +3901,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.08936</v>
+        <v>0.08631</v>
       </c>
       <c r="F47" s="7">
-        <v>0.118035</v>
+        <v>0.132816</v>
       </c>
       <c r="G47" s="7">
-        <v>0.300625</v>
+        <v>0.312771</v>
       </c>
       <c r="H47" s="7">
-        <v>0.258772</v>
+        <v>0.27326</v>
       </c>
       <c r="I47" s="7">
-        <v>0.611316</v>
+        <v>0.617661</v>
       </c>
       <c r="J47" s="7">
-        <v>3.695035</v>
+        <v>3.749073</v>
       </c>
       <c r="K47" s="7">
-        <v>13.040326</v>
+        <v>13.122171000000002</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3936,25 +3936,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.044474</v>
+        <v>0.049104999999999996</v>
       </c>
       <c r="F48" s="7">
-        <v>-0.008113</v>
+        <v>0.006797</v>
       </c>
       <c r="G48" s="7">
-        <v>0.135208</v>
+        <v>0.152218</v>
       </c>
       <c r="H48" s="7">
-        <v>0.13350099999999998</v>
+        <v>0.154215</v>
       </c>
       <c r="I48" s="7">
-        <v>0.462162</v>
+        <v>0.490839</v>
       </c>
       <c r="J48" s="7">
-        <v>1.9364750000000002</v>
+        <v>1.990137</v>
       </c>
       <c r="K48" s="7">
-        <v>10.069898</v>
+        <v>10.383756</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3971,25 +3971,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.099298</v>
+        <v>0.113473</v>
       </c>
       <c r="F49" s="7">
-        <v>0.075501</v>
+        <v>0.10442299999999999</v>
       </c>
       <c r="G49" s="7">
-        <v>0.321988</v>
+        <v>0.347166</v>
       </c>
       <c r="H49" s="7">
-        <v>0.261139</v>
+        <v>0.29589</v>
       </c>
       <c r="I49" s="7">
-        <v>0.609259</v>
+        <v>0.6452500000000001</v>
       </c>
       <c r="J49" s="7">
-        <v>3.860605</v>
+        <v>3.994541</v>
       </c>
       <c r="K49" s="7">
-        <v>15.855731</v>
+        <v>16.205699</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4006,25 +4006,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.110565</v>
+        <v>0.11743100000000001</v>
       </c>
       <c r="F50" s="7">
-        <v>0.086331</v>
+        <v>0.103463</v>
       </c>
       <c r="G50" s="7">
-        <v>0.164523</v>
+        <v>0.18243099999999998</v>
       </c>
       <c r="H50" s="7">
-        <v>0.13241</v>
+        <v>0.152124</v>
       </c>
       <c r="I50" s="7">
-        <v>0.533418</v>
+        <v>0.569266</v>
       </c>
       <c r="J50" s="7">
-        <v>3.116767</v>
+        <v>3.188437</v>
       </c>
       <c r="K50" s="7">
-        <v>9.011076000000001</v>
+        <v>9.234077</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4041,25 +4041,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.05028</v>
+        <v>0.059013</v>
       </c>
       <c r="F51" s="7">
-        <v>0.025316</v>
+        <v>0.038267999999999996</v>
       </c>
       <c r="G51" s="7">
-        <v>0.18568300000000001</v>
+        <v>0.19499</v>
       </c>
       <c r="H51" s="7">
-        <v>0.130014</v>
+        <v>0.143898</v>
       </c>
       <c r="I51" s="7">
-        <v>0.381027</v>
+        <v>0.395646</v>
       </c>
       <c r="J51" s="7">
-        <v>2.632937</v>
+        <v>2.677572</v>
       </c>
       <c r="K51" s="7">
-        <v>8.007867</v>
+        <v>8.068395</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4076,25 +4076,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.100725</v>
+        <v>0.11287599999999999</v>
       </c>
       <c r="F52" s="7">
-        <v>0.044406</v>
+        <v>0.07302</v>
       </c>
       <c r="G52" s="7">
-        <v>0.275636</v>
+        <v>0.293179</v>
       </c>
       <c r="H52" s="7">
-        <v>0.21181799999999998</v>
+        <v>0.244443</v>
       </c>
       <c r="I52" s="7">
-        <v>0.514783</v>
+        <v>0.543486</v>
       </c>
       <c r="J52" s="7">
-        <v>2.8336669999999997</v>
+        <v>2.9368790000000002</v>
       </c>
       <c r="K52" s="7">
-        <v>10.998415</v>
+        <v>11.210305</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4111,25 +4111,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.040967</v>
+        <v>0.048639999999999996</v>
       </c>
       <c r="F53" s="7">
-        <v>0.029684</v>
+        <v>0.039749</v>
       </c>
       <c r="G53" s="7">
-        <v>0.09586800000000001</v>
+        <v>0.107712</v>
       </c>
       <c r="H53" s="7">
-        <v>0.045973</v>
+        <v>0.057191</v>
       </c>
       <c r="I53" s="7">
-        <v>0.332619</v>
+        <v>0.344256</v>
       </c>
       <c r="J53" s="7">
-        <v>2.186436</v>
+        <v>2.220609</v>
       </c>
       <c r="K53" s="7">
-        <v>6.352392999999999</v>
+        <v>6.419596</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4146,25 +4146,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.033173</v>
+        <v>0.035903</v>
       </c>
       <c r="F54" s="7">
-        <v>0.032064</v>
+        <v>0.037628</v>
       </c>
       <c r="G54" s="7">
-        <v>0.096174</v>
+        <v>0.102279</v>
       </c>
       <c r="H54" s="7">
-        <v>0.053567000000000004</v>
+        <v>0.05946</v>
       </c>
       <c r="I54" s="7">
-        <v>0.301239</v>
+        <v>0.30472899999999997</v>
       </c>
       <c r="J54" s="7">
-        <v>2.0672900000000003</v>
+        <v>2.0844460000000002</v>
       </c>
       <c r="K54" s="7">
-        <v>6.178394</v>
+        <v>6.221499</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4181,25 +4181,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.016514</v>
+        <v>0.00521</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.08067500000000001</v>
+        <v>-0.061413</v>
       </c>
       <c r="G55" s="7">
-        <v>0.189052</v>
+        <v>0.209866</v>
       </c>
       <c r="H55" s="7">
-        <v>0.061389</v>
+        <v>0.088191</v>
       </c>
       <c r="I55" s="7">
-        <v>0.579043</v>
+        <v>0.589521</v>
       </c>
       <c r="J55" s="7">
-        <v>3.797163</v>
+        <v>3.9183030000000003</v>
       </c>
       <c r="K55" s="7">
-        <v>12.838642</v>
+        <v>13.20375</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4216,25 +4216,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.066037</v>
+        <v>0.083167</v>
       </c>
       <c r="F56" s="7">
-        <v>0.065352</v>
+        <v>0.08996</v>
       </c>
       <c r="G56" s="7">
-        <v>0.224188</v>
+        <v>0.24564599999999998</v>
       </c>
       <c r="H56" s="7">
-        <v>0.144013</v>
+        <v>0.16989</v>
       </c>
       <c r="I56" s="7">
-        <v>0.474568</v>
+        <v>0.508093</v>
       </c>
       <c r="J56" s="7">
-        <v>2.115489</v>
+        <v>2.1859610000000003</v>
       </c>
       <c r="K56" s="7">
-        <v>5.631428</v>
+        <v>5.767207</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4251,25 +4251,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.022324</v>
+        <v>0.033668000000000003</v>
       </c>
       <c r="F57" s="7">
-        <v>-0.002983</v>
+        <v>0.011452</v>
       </c>
       <c r="G57" s="7">
-        <v>0.121899</v>
+        <v>0.13311299999999998</v>
       </c>
       <c r="H57" s="7">
-        <v>0.060166000000000004</v>
+        <v>0.076424</v>
       </c>
       <c r="I57" s="7">
-        <v>0.363862</v>
+        <v>0.384403</v>
       </c>
       <c r="J57" s="7">
-        <v>1.367346</v>
+        <v>1.4036490000000001</v>
       </c>
       <c r="K57" s="7">
-        <v>3.518735</v>
+        <v>3.567028</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4286,25 +4286,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.07865899999999999</v>
+        <v>0.08997</v>
       </c>
       <c r="F58" s="7">
-        <v>0.08259499999999999</v>
+        <v>0.099176</v>
       </c>
       <c r="G58" s="7">
-        <v>0.308626</v>
+        <v>0.324531</v>
       </c>
       <c r="H58" s="7">
-        <v>0.23644300000000001</v>
+        <v>0.257328</v>
       </c>
       <c r="I58" s="7">
-        <v>0.596195</v>
+        <v>0.618906</v>
       </c>
       <c r="J58" s="7">
-        <v>3.336404</v>
+        <v>3.409651</v>
       </c>
       <c r="K58" s="7">
-        <v>9.606595</v>
+        <v>9.747399</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4321,25 +4321,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.09078099999999999</v>
+        <v>0.103271</v>
       </c>
       <c r="F59" s="7">
-        <v>0.09332499999999999</v>
+        <v>0.11296400000000001</v>
       </c>
       <c r="G59" s="7">
-        <v>0.32943399999999995</v>
+        <v>0.345895</v>
       </c>
       <c r="H59" s="7">
-        <v>0.267466</v>
+        <v>0.29307</v>
       </c>
       <c r="I59" s="7">
-        <v>0.606147</v>
+        <v>0.627701</v>
       </c>
       <c r="J59" s="7">
-        <v>3.379006</v>
+        <v>3.4674650000000002</v>
       </c>
       <c r="K59" s="7">
-        <v>10.715254999999999</v>
+        <v>10.894481</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4356,25 +4356,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.08002100000000001</v>
+        <v>0.096359</v>
       </c>
       <c r="F60" s="7">
-        <v>0.024214000000000003</v>
+        <v>0.053445</v>
       </c>
       <c r="G60" s="7">
-        <v>0.203991</v>
+        <v>0.22838999999999998</v>
       </c>
       <c r="H60" s="7">
-        <v>0.186251</v>
+        <v>0.220948</v>
       </c>
       <c r="I60" s="7">
-        <v>0.441533</v>
+        <v>0.479501</v>
       </c>
       <c r="J60" s="7">
-        <v>2.616791</v>
+        <v>2.722577</v>
       </c>
       <c r="K60" s="7">
-        <v>12.774961000000001</v>
+        <v>13.027436</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4391,25 +4391,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.09322699999999999</v>
+        <v>0.10030099999999999</v>
       </c>
       <c r="F61" s="7">
-        <v>0.062525</v>
+        <v>0.080481</v>
       </c>
       <c r="G61" s="7">
-        <v>0.211086</v>
+        <v>0.22546</v>
       </c>
       <c r="H61" s="7">
-        <v>0.17028400000000002</v>
+        <v>0.192329</v>
       </c>
       <c r="I61" s="7">
-        <v>0.498801</v>
+        <v>0.532456</v>
       </c>
       <c r="J61" s="7">
-        <v>2.5372339999999998</v>
+        <v>2.6038650000000003</v>
       </c>
       <c r="K61" s="7">
-        <v>7.594666</v>
+        <v>7.699394999999999</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4426,25 +4426,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.060233</v>
+        <v>0.078864</v>
       </c>
       <c r="F62" s="7">
-        <v>-0.020735999999999997</v>
+        <v>0.010917</v>
       </c>
       <c r="G62" s="7">
-        <v>0.144583</v>
+        <v>0.16616499999999998</v>
       </c>
       <c r="H62" s="7">
-        <v>0.15475899999999998</v>
+        <v>0.184656</v>
       </c>
       <c r="I62" s="7">
-        <v>0.396503</v>
+        <v>0.427933</v>
       </c>
       <c r="J62" s="7">
-        <v>2.5368440000000003</v>
+        <v>2.628416</v>
       </c>
       <c r="K62" s="7">
-        <v>12.124729</v>
+        <v>12.429219</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4461,25 +4461,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.037697</v>
+        <v>0.047712000000000004</v>
       </c>
       <c r="F63" s="7">
-        <v>0.014951</v>
+        <v>0.027705</v>
       </c>
       <c r="G63" s="7">
-        <v>0.16902699999999998</v>
+        <v>0.181086</v>
       </c>
       <c r="H63" s="7">
-        <v>0.082829</v>
+        <v>0.09794800000000001</v>
       </c>
       <c r="I63" s="7">
-        <v>0.399086</v>
+        <v>0.41708799999999996</v>
       </c>
       <c r="J63" s="7">
-        <v>1.9401650000000001</v>
+        <v>1.981215</v>
       </c>
       <c r="K63" s="7">
-        <v>4.621292</v>
+        <v>4.681654</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4496,25 +4496,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.027021000000000003</v>
+        <v>0.040343</v>
       </c>
       <c r="F64" s="7">
-        <v>0.016964</v>
+        <v>0.028392</v>
       </c>
       <c r="G64" s="7">
-        <v>0.184085</v>
+        <v>0.19700199999999998</v>
       </c>
       <c r="H64" s="7">
-        <v>0.13893</v>
+        <v>0.15991</v>
       </c>
       <c r="I64" s="7">
-        <v>0.39279800000000004</v>
+        <v>0.40908900000000004</v>
       </c>
       <c r="J64" s="7">
-        <v>2.112875</v>
+        <v>2.170218</v>
       </c>
       <c r="K64" s="7">
-        <v>6.092288999999999</v>
+        <v>6.22356</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4531,25 +4531,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.030888</v>
+        <v>0.032831</v>
       </c>
       <c r="F65" s="7">
-        <v>0.039295</v>
+        <v>0.043455</v>
       </c>
       <c r="G65" s="7">
-        <v>0.104525</v>
+        <v>0.11011900000000001</v>
       </c>
       <c r="H65" s="7">
-        <v>0.062055</v>
+        <v>0.068163</v>
       </c>
       <c r="I65" s="7">
-        <v>0.29370799999999997</v>
+        <v>0.29918500000000003</v>
       </c>
       <c r="J65" s="7">
-        <v>2.097744</v>
+        <v>2.115561</v>
       </c>
       <c r="K65" s="7">
-        <v>5.281789</v>
+        <v>5.305381</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4566,25 +4566,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.034566</v>
+        <v>0.04313500000000001</v>
       </c>
       <c r="F66" s="7">
-        <v>0.030749</v>
+        <v>0.041021</v>
       </c>
       <c r="G66" s="7">
-        <v>0.091158</v>
+        <v>0.10379300000000001</v>
       </c>
       <c r="H66" s="7">
-        <v>0.040709999999999996</v>
+        <v>0.051833</v>
       </c>
       <c r="I66" s="7">
-        <v>0.313195</v>
+        <v>0.326139</v>
       </c>
       <c r="J66" s="7">
-        <v>2.287224</v>
+        <v>2.322358</v>
       </c>
       <c r="K66" s="7">
-        <v>6.6488819999999995</v>
+        <v>6.7087</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4601,25 +4601,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.056424</v>
+        <v>0.067403</v>
       </c>
       <c r="F67" s="7">
-        <v>0.049561</v>
+        <v>0.069612</v>
       </c>
       <c r="G67" s="7">
-        <v>0.263729</v>
+        <v>0.278872</v>
       </c>
       <c r="H67" s="7">
-        <v>0.19516999999999998</v>
+        <v>0.21875599999999998</v>
       </c>
       <c r="I67" s="7">
-        <v>0.569424</v>
+        <v>0.587617</v>
       </c>
       <c r="J67" s="7">
-        <v>2.599598</v>
+        <v>2.670634</v>
       </c>
       <c r="K67" s="7">
-        <v>9.367151</v>
+        <v>9.533132</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4636,25 +4636,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.032628</v>
+        <v>0.039034</v>
       </c>
       <c r="F68" s="7">
-        <v>0.033325</v>
+        <v>0.042052</v>
       </c>
       <c r="G68" s="7">
-        <v>0.092897</v>
+        <v>0.102757</v>
       </c>
       <c r="H68" s="7">
-        <v>0.047137000000000005</v>
+        <v>0.056326</v>
       </c>
       <c r="I68" s="7">
-        <v>0.289233</v>
+        <v>0.299486</v>
       </c>
       <c r="J68" s="7">
-        <v>2.068542</v>
+        <v>2.095471</v>
       </c>
       <c r="K68" s="7">
-        <v>6.046397</v>
+        <v>6.092419</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4671,25 +4671,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.0529</v>
+        <v>0.062443</v>
       </c>
       <c r="F69" s="7">
-        <v>0.042793</v>
+        <v>0.055682</v>
       </c>
       <c r="G69" s="7">
-        <v>0.207101</v>
+        <v>0.220091</v>
       </c>
       <c r="H69" s="7">
-        <v>0.12523600000000001</v>
+        <v>0.140847</v>
       </c>
       <c r="I69" s="7">
-        <v>0.472885</v>
+        <v>0.48916800000000005</v>
       </c>
       <c r="J69" s="7">
-        <v>2.245745</v>
+        <v>2.290775</v>
       </c>
       <c r="K69" s="7">
-        <v>5.516707</v>
+        <v>5.579591000000001</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4706,25 +4706,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.03136</v>
+        <v>0.031368</v>
       </c>
       <c r="F70" s="7">
-        <v>0.093927</v>
+        <v>0.09185600000000001</v>
       </c>
       <c r="G70" s="7">
-        <v>0.199929</v>
+        <v>0.20008800000000002</v>
       </c>
       <c r="H70" s="7">
-        <v>0.132576</v>
+        <v>0.133734</v>
       </c>
       <c r="I70" s="7">
-        <v>0.478942</v>
+        <v>0.478662</v>
       </c>
       <c r="J70" s="7">
-        <v>2.3502330000000002</v>
+        <v>2.35366</v>
       </c>
       <c r="K70" s="7">
-        <v>4.067105000000001</v>
+        <v>4.069881</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4741,25 +4741,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.28333600000000003</v>
+        <v>0.265985</v>
       </c>
       <c r="F71" s="7">
-        <v>0.276812</v>
+        <v>0.286015</v>
       </c>
       <c r="G71" s="7">
-        <v>0.252583</v>
+        <v>0.260795</v>
       </c>
       <c r="H71" s="7">
-        <v>0.234148</v>
+        <v>0.253722</v>
       </c>
       <c r="I71" s="7">
-        <v>0.730373</v>
+        <v>0.783044</v>
       </c>
       <c r="J71" s="7">
-        <v>3.981452</v>
+        <v>4.060458</v>
       </c>
       <c r="K71" s="7">
-        <v>8.42167</v>
+        <v>8.611114</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4776,25 +4776,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.047782</v>
+        <v>0.049649</v>
       </c>
       <c r="F72" s="7">
-        <v>0.083024</v>
+        <v>0.087438</v>
       </c>
       <c r="G72" s="7">
-        <v>0.234771</v>
+        <v>0.239041</v>
       </c>
       <c r="H72" s="7">
-        <v>0.147931</v>
+        <v>0.153901</v>
       </c>
       <c r="I72" s="7">
-        <v>0.462834</v>
+        <v>0.46740099999999996</v>
       </c>
       <c r="J72" s="7">
-        <v>1.796144</v>
+        <v>1.810684</v>
       </c>
       <c r="K72" s="7">
-        <v>4.686144</v>
+        <v>4.712355</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4811,25 +4811,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.040202</v>
+        <v>0.052029</v>
       </c>
       <c r="F73" s="7">
-        <v>-0.015872999999999998</v>
+        <v>0.002352</v>
       </c>
       <c r="G73" s="7">
-        <v>0.044142</v>
+        <v>0.06516</v>
       </c>
       <c r="H73" s="7">
-        <v>-0.003665</v>
+        <v>0.016188</v>
       </c>
       <c r="I73" s="7">
-        <v>0.267187</v>
+        <v>0.290183</v>
       </c>
       <c r="J73" s="7">
-        <v>2.0337549999999998</v>
+        <v>2.0942060000000002</v>
       </c>
       <c r="K73" s="7">
-        <v>5.957564</v>
+        <v>6.087006</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4846,25 +4846,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.111264</v>
+        <v>0.12798299999999999</v>
       </c>
       <c r="F74" s="7">
-        <v>0.032235</v>
+        <v>0.064346</v>
       </c>
       <c r="G74" s="7">
-        <v>0.243989</v>
+        <v>0.270123</v>
       </c>
       <c r="H74" s="7">
-        <v>0.21456499999999998</v>
+        <v>0.24879</v>
       </c>
       <c r="I74" s="7">
-        <v>0.41761899999999996</v>
+        <v>0.45201500000000006</v>
       </c>
       <c r="J74" s="7">
-        <v>2.808709</v>
+        <v>2.916032</v>
       </c>
       <c r="K74" s="7">
-        <v>14.781253999999999</v>
+        <v>15.031014</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4881,25 +4881,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.025861000000000002</v>
+        <v>0.031072000000000002</v>
       </c>
       <c r="F75" s="7">
-        <v>0.011023</v>
+        <v>0.017017</v>
       </c>
       <c r="G75" s="7">
-        <v>0.158007</v>
+        <v>0.165312</v>
       </c>
       <c r="H75" s="7">
-        <v>0.048171</v>
+        <v>0.055567000000000005</v>
       </c>
       <c r="I75" s="7">
-        <v>0.402393</v>
+        <v>0.411364</v>
       </c>
       <c r="J75" s="7">
-        <v>1.779596</v>
+        <v>1.7992080000000001</v>
       </c>
       <c r="K75" s="7">
-        <v>3.678278</v>
+        <v>3.69168</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4916,25 +4916,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.049599000000000004</v>
+        <v>0.059359</v>
       </c>
       <c r="F76" s="7">
-        <v>0.042342000000000005</v>
+        <v>0.054981999999999996</v>
       </c>
       <c r="G76" s="7">
-        <v>0.210079</v>
+        <v>0.222423</v>
       </c>
       <c r="H76" s="7">
-        <v>0.126388</v>
+        <v>0.14166800000000002</v>
       </c>
       <c r="I76" s="7">
-        <v>0.481145</v>
+        <v>0.49689</v>
       </c>
       <c r="J76" s="7">
-        <v>2.289263</v>
+        <v>2.333882</v>
       </c>
       <c r="K76" s="7">
-        <v>5.609932</v>
+        <v>5.671482</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4951,25 +4951,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.056791999999999995</v>
+        <v>0.059663</v>
       </c>
       <c r="F77" s="7">
-        <v>0.068714</v>
+        <v>0.078563</v>
       </c>
       <c r="G77" s="7">
-        <v>0.316166</v>
+        <v>0.321874</v>
       </c>
       <c r="H77" s="7">
-        <v>0.215457</v>
+        <v>0.22534099999999999</v>
       </c>
       <c r="I77" s="7">
-        <v>0.44006799999999996</v>
+        <v>0.451873</v>
       </c>
       <c r="J77" s="7">
-        <v>2.004444</v>
+        <v>2.0288749999999998</v>
       </c>
       <c r="K77" s="7">
-        <v>5.5774170000000005</v>
+        <v>5.5966949999999995</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5007,25 +5007,25 @@
         <v>4</v>
       </c>
       <c r="E79" s="7">
-        <v>0.059336</v>
+        <v>0.066138</v>
       </c>
       <c r="F79" s="7">
-        <v>0.13819599999999999</v>
+        <v>0.146183</v>
       </c>
       <c r="G79" s="7">
-        <v>0.34155</v>
+        <v>0.34600000000000003</v>
       </c>
       <c r="H79" s="7">
-        <v>0.25961</v>
+        <v>0.271365</v>
       </c>
       <c r="I79" s="7">
-        <v>0.6972539999999999</v>
+        <v>0.7107479999999999</v>
       </c>
       <c r="J79" s="7">
-        <v>3.005327</v>
+        <v>3.042705</v>
       </c>
       <c r="K79" s="7">
-        <v>8.346461</v>
+        <v>8.418797</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5042,25 +5042,25 @@
         <v>5</v>
       </c>
       <c r="E80" s="7">
-        <v>0.072201</v>
+        <v>0.071146</v>
       </c>
       <c r="F80" s="7">
-        <v>0.09456400000000001</v>
+        <v>0.104242</v>
       </c>
       <c r="G80" s="7">
-        <v>0.177201</v>
+        <v>0.184068</v>
       </c>
       <c r="H80" s="7">
-        <v>0.17318</v>
+        <v>0.18263000000000001</v>
       </c>
       <c r="I80" s="7">
-        <v>0.43411900000000003</v>
+        <v>0.44481699999999996</v>
       </c>
       <c r="J80" s="7">
-        <v>2.4803550000000003</v>
+        <v>2.5083889999999998</v>
       </c>
       <c r="K80" s="7">
-        <v>8.087055</v>
+        <v>8.140369</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5077,25 +5077,25 @@
         <v>6</v>
       </c>
       <c r="E81" s="7">
-        <v>0.09370200000000001</v>
+        <v>0.108426</v>
       </c>
       <c r="F81" s="7">
-        <v>0.04442</v>
+        <v>0.07465</v>
       </c>
       <c r="G81" s="7">
-        <v>0.244398</v>
+        <v>0.265985</v>
       </c>
       <c r="H81" s="7">
-        <v>0.234463</v>
+        <v>0.268475</v>
       </c>
       <c r="I81" s="7">
-        <v>0.43099699999999996</v>
+        <v>0.463523</v>
       </c>
       <c r="J81" s="7">
-        <v>2.5180789999999997</v>
+        <v>2.6150080000000004</v>
       </c>
       <c r="K81" s="7">
-        <v>10.955916</v>
+        <v>11.2907</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5112,25 +5112,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.035919</v>
+        <v>0.039994</v>
       </c>
       <c r="F82" s="7">
-        <v>0.072323</v>
+        <v>0.076082</v>
       </c>
       <c r="G82" s="7">
-        <v>0.178811</v>
+        <v>0.183115</v>
       </c>
       <c r="H82" s="7">
-        <v>0.126266</v>
+        <v>0.13200900000000002</v>
       </c>
       <c r="I82" s="7">
-        <v>0.385504</v>
+        <v>0.39381900000000003</v>
       </c>
       <c r="J82" s="7">
-        <v>1.5828110000000002</v>
+        <v>1.5959800000000002</v>
       </c>
       <c r="K82" s="7">
-        <v>4.406791999999999</v>
+        <v>4.431643</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5147,25 +5147,25 @@
         <v>4</v>
       </c>
       <c r="E83" s="7">
-        <v>0.022952</v>
+        <v>0.02918</v>
       </c>
       <c r="F83" s="7">
-        <v>0.006513</v>
+        <v>0.013146</v>
       </c>
       <c r="G83" s="7">
-        <v>0.126426</v>
+        <v>0.13483</v>
       </c>
       <c r="H83" s="7">
-        <v>0.041458</v>
+        <v>0.050067</v>
       </c>
       <c r="I83" s="7">
-        <v>0.374276</v>
+        <v>0.385043</v>
       </c>
       <c r="J83" s="7">
-        <v>1.466609</v>
+        <v>1.4869990000000002</v>
       </c>
       <c r="K83" s="7">
-        <v>3.0976190000000003</v>
+        <v>3.120973</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5182,25 +5182,25 @@
         <v>5</v>
       </c>
       <c r="E84" s="7">
-        <v>0.080204</v>
+        <v>0.080063</v>
       </c>
       <c r="F84" s="7">
-        <v>0.09160700000000001</v>
+        <v>0.104677</v>
       </c>
       <c r="G84" s="7">
-        <v>0.179412</v>
+        <v>0.190481</v>
       </c>
       <c r="H84" s="7">
-        <v>0.186176</v>
+        <v>0.199422</v>
       </c>
       <c r="I84" s="7">
-        <v>0.44010599999999994</v>
+        <v>0.449917</v>
       </c>
       <c r="J84" s="7">
-        <v>2.541324</v>
+        <v>2.5808690000000003</v>
       </c>
       <c r="K84" s="7">
-        <v>9.115213</v>
+        <v>9.208486</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5217,22 +5217,22 @@
         <v>6</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.020984</v>
+        <v>-0.002026</v>
       </c>
       <c r="F85" s="7">
-        <v>-0.096755</v>
+        <v>-0.080038</v>
       </c>
       <c r="G85" s="7">
-        <v>0.13733599999999999</v>
+        <v>0.154234</v>
       </c>
       <c r="H85" s="7">
-        <v>0.008917000000000001</v>
+        <v>0.032767</v>
       </c>
       <c r="I85" s="7">
-        <v>0.6029</v>
+        <v>0.618729</v>
       </c>
       <c r="J85" s="7">
-        <v>3.728743</v>
+        <v>3.8405259999999997</v>
       </c>
       <c r="K85" s="7"/>
     </row>
@@ -5250,19 +5250,19 @@
         <v>2</v>
       </c>
       <c r="E86" s="7">
-        <v>0.030830000000000003</v>
+        <v>0.030732</v>
       </c>
       <c r="F86" s="7">
-        <v>0.093677</v>
+        <v>0.09150499999999999</v>
       </c>
       <c r="G86" s="7">
-        <v>0.19646</v>
+        <v>0.196248</v>
       </c>
       <c r="H86" s="7">
-        <v>0.130991</v>
+        <v>0.132013</v>
       </c>
       <c r="I86" s="7">
-        <v>0.464617</v>
+        <v>0.46441699999999997</v>
       </c>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5281,22 +5281,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.089858</v>
+        <v>0.101011</v>
       </c>
       <c r="F87" s="7">
-        <v>0.056353</v>
+        <v>0.079967</v>
       </c>
       <c r="G87" s="7">
-        <v>0.25444</v>
+        <v>0.274326</v>
       </c>
       <c r="H87" s="7">
-        <v>0.202692</v>
+        <v>0.231995</v>
       </c>
       <c r="I87" s="7">
-        <v>0.556608</v>
+        <v>0.596356</v>
       </c>
       <c r="J87" s="7">
-        <v>2.862838</v>
+        <v>2.956956</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5314,22 +5314,22 @@
         <v>6</v>
       </c>
       <c r="E88" s="7">
-        <v>0.186024</v>
+        <v>0.184106</v>
       </c>
       <c r="F88" s="7">
-        <v>0.31568999999999997</v>
+        <v>0.32994300000000004</v>
       </c>
       <c r="G88" s="7">
-        <v>0.347666</v>
+        <v>0.35064</v>
       </c>
       <c r="H88" s="7">
-        <v>0.392303</v>
+        <v>0.404119</v>
       </c>
       <c r="I88" s="7">
-        <v>0.765051</v>
+        <v>0.7683920000000001</v>
       </c>
       <c r="J88" s="7">
-        <v>4.457693</v>
+        <v>4.504011</v>
       </c>
       <c r="K88" s="7"/>
     </row>
@@ -5347,25 +5347,25 @@
         <v>7</v>
       </c>
       <c r="E89" s="7">
-        <v>-0.014778</v>
+        <v>0.003517</v>
       </c>
       <c r="F89" s="7">
-        <v>-0.080701</v>
+        <v>-0.057172</v>
       </c>
       <c r="G89" s="7">
-        <v>0.20833200000000002</v>
+        <v>0.22867200000000001</v>
       </c>
       <c r="H89" s="7">
-        <v>0.068808</v>
+        <v>0.09473699999999999</v>
       </c>
       <c r="I89" s="7">
-        <v>0.6054809999999999</v>
+        <v>0.610218</v>
       </c>
       <c r="J89" s="7">
-        <v>4.022129</v>
+        <v>4.143966</v>
       </c>
       <c r="K89" s="7">
-        <v>13.703344</v>
+        <v>14.078444999999999</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5382,25 +5382,25 @@
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>0.03303</v>
+        <v>0.034329</v>
       </c>
       <c r="F90" s="7">
-        <v>0.09052199999999999</v>
+        <v>0.09060700000000001</v>
       </c>
       <c r="G90" s="7">
-        <v>0.202129</v>
+        <v>0.203136</v>
       </c>
       <c r="H90" s="7">
-        <v>0.13441599999999998</v>
+        <v>0.137537</v>
       </c>
       <c r="I90" s="7">
-        <v>0.509829</v>
+        <v>0.510836</v>
       </c>
       <c r="J90" s="7">
-        <v>2.39356</v>
+        <v>2.402898</v>
       </c>
       <c r="K90" s="7">
-        <v>4.307755</v>
+        <v>4.319153</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5417,25 +5417,25 @@
         <v>5</v>
       </c>
       <c r="E91" s="7">
-        <v>0.027273000000000002</v>
+        <v>0.036097000000000004</v>
       </c>
       <c r="F91" s="7">
-        <v>0.019742</v>
+        <v>0.029878000000000002</v>
       </c>
       <c r="G91" s="7">
-        <v>0.156706</v>
+        <v>0.162657</v>
       </c>
       <c r="H91" s="7">
-        <v>0.08071300000000001</v>
+        <v>0.091587</v>
       </c>
       <c r="I91" s="7">
-        <v>0.308457</v>
+        <v>0.318355</v>
       </c>
       <c r="J91" s="7">
-        <v>2.0603350000000002</v>
+        <v>2.091128</v>
       </c>
       <c r="K91" s="7">
-        <v>5.373388</v>
+        <v>5.416393</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5452,22 +5452,22 @@
         <v>6</v>
       </c>
       <c r="E92" s="7">
-        <v>0.053373</v>
+        <v>0.061369999999999994</v>
       </c>
       <c r="F92" s="7">
-        <v>0.035057</v>
+        <v>0.055652</v>
       </c>
       <c r="G92" s="7">
-        <v>0.235503</v>
+        <v>0.245704</v>
       </c>
       <c r="H92" s="7">
-        <v>0.172789</v>
+        <v>0.19405799999999998</v>
       </c>
       <c r="I92" s="7">
-        <v>0.441</v>
+        <v>0.46260199999999996</v>
       </c>
       <c r="J92" s="7">
-        <v>2.6806970000000003</v>
+        <v>2.747446</v>
       </c>
       <c r="K92" s="7"/>
     </row>
@@ -5485,25 +5485,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.036626</v>
+        <v>0.045107</v>
       </c>
       <c r="F93" s="7">
-        <v>0.020036</v>
+        <v>0.031851</v>
       </c>
       <c r="G93" s="7">
-        <v>0.18717099999999998</v>
+        <v>0.19548</v>
       </c>
       <c r="H93" s="7">
-        <v>0.094116</v>
+        <v>0.107346</v>
       </c>
       <c r="I93" s="7">
-        <v>0.353825</v>
+        <v>0.366796</v>
       </c>
       <c r="J93" s="7">
-        <v>1.995339</v>
+        <v>2.031558</v>
       </c>
       <c r="K93" s="7">
-        <v>4.917874</v>
+        <v>4.9717020000000005</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5520,25 +5520,25 @@
         <v>5</v>
       </c>
       <c r="E94" s="7">
-        <v>0.040724</v>
+        <v>0.048743999999999996</v>
       </c>
       <c r="F94" s="7">
-        <v>0.072676</v>
+        <v>0.0788</v>
       </c>
       <c r="G94" s="7">
-        <v>0.208249</v>
+        <v>0.21131</v>
       </c>
       <c r="H94" s="7">
-        <v>0.14022600000000002</v>
+        <v>0.146763</v>
       </c>
       <c r="I94" s="7">
-        <v>0.370265</v>
+        <v>0.38440399999999997</v>
       </c>
       <c r="J94" s="7">
-        <v>1.7668979999999999</v>
+        <v>1.782761</v>
       </c>
       <c r="K94" s="7">
-        <v>4.643771</v>
+        <v>4.677538</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5555,25 +5555,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.051104000000000004</v>
+        <v>0.06282499999999999</v>
       </c>
       <c r="F95" s="7">
-        <v>0.032145</v>
+        <v>0.053729</v>
       </c>
       <c r="G95" s="7">
-        <v>0.25624600000000003</v>
+        <v>0.26867599999999997</v>
       </c>
       <c r="H95" s="7">
-        <v>0.163244</v>
+        <v>0.185339</v>
       </c>
       <c r="I95" s="7">
-        <v>0.510773</v>
+        <v>0.5308160000000001</v>
       </c>
       <c r="J95" s="7">
-        <v>2.8807389999999997</v>
+        <v>2.954452</v>
       </c>
       <c r="K95" s="7">
-        <v>8.228754</v>
+        <v>8.349488000000001</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5590,25 +5590,25 @@
         <v>4</v>
       </c>
       <c r="E96" s="7">
-        <v>0.021174</v>
+        <v>0.027791999999999997</v>
       </c>
       <c r="F96" s="7">
-        <v>0.013054</v>
+        <v>0.019482</v>
       </c>
       <c r="G96" s="7">
-        <v>0.15495699999999998</v>
+        <v>0.160884</v>
       </c>
       <c r="H96" s="7">
-        <v>0.044741</v>
+        <v>0.052424</v>
       </c>
       <c r="I96" s="7">
-        <v>0.41288600000000003</v>
+        <v>0.42499499999999996</v>
       </c>
       <c r="J96" s="7">
-        <v>1.34168</v>
+        <v>1.3588999999999998</v>
       </c>
       <c r="K96" s="7">
-        <v>2.73284</v>
+        <v>2.7513360000000002</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5625,25 +5625,25 @@
         <v>7</v>
       </c>
       <c r="E97" s="7">
-        <v>0.061044999999999995</v>
+        <v>0.081556</v>
       </c>
       <c r="F97" s="7">
-        <v>0.002461</v>
+        <v>0.038018</v>
       </c>
       <c r="G97" s="7">
-        <v>0.257777</v>
+        <v>0.28150400000000003</v>
       </c>
       <c r="H97" s="7">
-        <v>0.19898800000000003</v>
+        <v>0.236999</v>
       </c>
       <c r="I97" s="7">
-        <v>0.423347</v>
+        <v>0.45809300000000003</v>
       </c>
       <c r="J97" s="7">
-        <v>2.983321</v>
+        <v>3.109604</v>
       </c>
       <c r="K97" s="7">
-        <v>14.588937000000001</v>
+        <v>14.938576000000001</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5660,25 +5660,25 @@
         <v>6</v>
       </c>
       <c r="E98" s="7">
-        <v>0.050789999999999995</v>
+        <v>0.059413999999999995</v>
       </c>
       <c r="F98" s="7">
-        <v>0.01517</v>
+        <v>0.043451000000000004</v>
       </c>
       <c r="G98" s="7">
-        <v>0.376764</v>
+        <v>0.386116</v>
       </c>
       <c r="H98" s="7">
-        <v>0.21180900000000003</v>
+        <v>0.233458</v>
       </c>
       <c r="I98" s="7">
-        <v>0.552196</v>
+        <v>0.570781</v>
       </c>
       <c r="J98" s="7">
-        <v>4.202157000000001</v>
+        <v>4.295095</v>
       </c>
       <c r="K98" s="7">
-        <v>19.304748</v>
+        <v>19.513287000000002</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5695,25 +5695,25 @@
         <v>4</v>
       </c>
       <c r="E99" s="7">
-        <v>0.053693</v>
+        <v>0.064826</v>
       </c>
       <c r="F99" s="7">
-        <v>0.059917</v>
+        <v>0.082096</v>
       </c>
       <c r="G99" s="7">
-        <v>0.280854</v>
+        <v>0.29462900000000003</v>
       </c>
       <c r="H99" s="7">
-        <v>0.205412</v>
+        <v>0.22777999999999998</v>
       </c>
       <c r="I99" s="7">
-        <v>0.559653</v>
+        <v>0.581735</v>
       </c>
       <c r="J99" s="7">
-        <v>3.5973680000000003</v>
+        <v>3.682678</v>
       </c>
       <c r="K99" s="7">
-        <v>9.165420000000001</v>
+        <v>9.294151000000001</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5730,25 +5730,25 @@
         <v>6</v>
       </c>
       <c r="E100" s="7">
-        <v>0.025945</v>
+        <v>0.026143999999999997</v>
       </c>
       <c r="F100" s="7">
-        <v>0.040741</v>
+        <v>0.042585</v>
       </c>
       <c r="G100" s="7">
-        <v>0.100076</v>
+        <v>0.10291499999999999</v>
       </c>
       <c r="H100" s="7">
-        <v>0.060874</v>
+        <v>0.06409</v>
       </c>
       <c r="I100" s="7">
-        <v>0.27789400000000003</v>
+        <v>0.28021799999999997</v>
       </c>
       <c r="J100" s="7">
-        <v>2.001902</v>
+        <v>2.011001</v>
       </c>
       <c r="K100" s="7">
-        <v>5.678391</v>
+        <v>5.690398</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5765,25 +5765,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.05821</v>
+        <v>0.071345</v>
       </c>
       <c r="F101" s="7">
-        <v>0.053308999999999995</v>
+        <v>0.07900800000000001</v>
       </c>
       <c r="G101" s="7">
-        <v>0.338893</v>
+        <v>0.35490499999999997</v>
       </c>
       <c r="H101" s="7">
-        <v>0.212145</v>
+        <v>0.23839300000000002</v>
       </c>
       <c r="I101" s="7">
-        <v>0.6093160000000001</v>
+        <v>0.6357</v>
       </c>
       <c r="J101" s="7">
-        <v>3.804282</v>
+        <v>3.9083120000000005</v>
       </c>
       <c r="K101" s="7">
-        <v>12.10805</v>
+        <v>12.298344</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5800,25 +5800,25 @@
         <v>5</v>
       </c>
       <c r="E102" s="7">
-        <v>0.084308</v>
+        <v>0.095374</v>
       </c>
       <c r="F102" s="7">
-        <v>0.091058</v>
+        <v>0.109237</v>
       </c>
       <c r="G102" s="7">
-        <v>0.365083</v>
+        <v>0.381947</v>
       </c>
       <c r="H102" s="7">
-        <v>0.316055</v>
+        <v>0.34013800000000005</v>
       </c>
       <c r="I102" s="7">
-        <v>0.697181</v>
+        <v>0.7216119999999999</v>
       </c>
       <c r="J102" s="7">
-        <v>3.684396</v>
+        <v>3.770118</v>
       </c>
       <c r="K102" s="7">
-        <v>11.467601</v>
+        <v>11.715759</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5835,25 +5835,25 @@
         <v>2</v>
       </c>
       <c r="E103" s="7">
-        <v>0.038013</v>
+        <v>0.041619</v>
       </c>
       <c r="F103" s="7">
-        <v>0.09888899999999999</v>
+        <v>0.101591</v>
       </c>
       <c r="G103" s="7">
-        <v>0.257543</v>
+        <v>0.262496</v>
       </c>
       <c r="H103" s="7">
-        <v>0.16165500000000002</v>
+        <v>0.16913499999999998</v>
       </c>
       <c r="I103" s="7">
-        <v>0.569969</v>
+        <v>0.578203</v>
       </c>
       <c r="J103" s="7">
-        <v>3.122118</v>
+        <v>3.1486590000000003</v>
       </c>
       <c r="K103" s="7">
-        <v>5.7248209999999995</v>
+        <v>5.764044999999999</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5870,25 +5870,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.091628</v>
+        <v>0.103358</v>
       </c>
       <c r="F104" s="7">
-        <v>0.08147700000000001</v>
+        <v>0.10192899999999999</v>
       </c>
       <c r="G104" s="7">
-        <v>0.37717100000000003</v>
+        <v>0.39589599999999997</v>
       </c>
       <c r="H104" s="7">
-        <v>0.335653</v>
+        <v>0.362048</v>
       </c>
       <c r="I104" s="7">
-        <v>0.70097</v>
+        <v>0.7284480000000001</v>
       </c>
       <c r="J104" s="7">
-        <v>3.617909</v>
+        <v>3.709169</v>
       </c>
       <c r="K104" s="7">
-        <v>13.537223</v>
+        <v>13.873624</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5905,25 +5905,25 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.030989</v>
+        <v>0.036309999999999995</v>
       </c>
       <c r="F105" s="7">
-        <v>0.032767</v>
+        <v>0.038546</v>
       </c>
       <c r="G105" s="7">
-        <v>0.09411</v>
+        <v>0.102384</v>
       </c>
       <c r="H105" s="7">
-        <v>0.046745</v>
+        <v>0.054892</v>
       </c>
       <c r="I105" s="7">
-        <v>0.310879</v>
+        <v>0.31921099999999997</v>
       </c>
       <c r="J105" s="7">
-        <v>2.1556960000000003</v>
+        <v>2.180257</v>
       </c>
       <c r="K105" s="7">
-        <v>6.051543000000001</v>
+        <v>6.097305</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5940,16 +5940,16 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.086672</v>
+        <v>0.102158</v>
       </c>
       <c r="F106" s="7">
-        <v>0.055308</v>
+        <v>0.076842</v>
       </c>
       <c r="G106" s="7">
-        <v>0.18888300000000002</v>
+        <v>0.20412299999999997</v>
       </c>
       <c r="H106" s="7">
-        <v>0.150779</v>
+        <v>0.17426100000000003</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
@@ -5969,22 +5969,22 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.208115</v>
+        <v>0.218763</v>
       </c>
       <c r="F107" s="7">
-        <v>0.277509</v>
+        <v>0.30482</v>
       </c>
       <c r="G107" s="7">
-        <v>0.355458</v>
+        <v>0.380379</v>
       </c>
       <c r="H107" s="7">
-        <v>0.352374</v>
+        <v>0.37928199999999995</v>
       </c>
       <c r="I107" s="7">
-        <v>0.851618</v>
+        <v>0.892954</v>
       </c>
       <c r="J107" s="7">
-        <v>4.478054</v>
+        <v>4.587052</v>
       </c>
       <c r="K107" s="7"/>
     </row>
@@ -6002,25 +6002,25 @@
         <v>6</v>
       </c>
       <c r="E108" s="7">
-        <v>-0.009007</v>
+        <v>0.008727</v>
       </c>
       <c r="F108" s="7">
-        <v>-0.07145</v>
+        <v>-0.048437</v>
       </c>
       <c r="G108" s="7">
-        <v>0.23124099999999997</v>
+        <v>0.253234</v>
       </c>
       <c r="H108" s="7">
-        <v>0.09844599999999999</v>
+        <v>0.126672</v>
       </c>
       <c r="I108" s="7">
-        <v>0.651982</v>
+        <v>0.6531359999999999</v>
       </c>
       <c r="J108" s="7">
-        <v>4.691447</v>
+        <v>4.8377</v>
       </c>
       <c r="K108" s="7">
-        <v>15.776068</v>
+        <v>16.233055999999998</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6037,25 +6037,25 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.026172</v>
+        <v>0.035264000000000004</v>
       </c>
       <c r="F109" s="7">
-        <v>0.034108</v>
+        <v>0.042977</v>
       </c>
       <c r="G109" s="7">
-        <v>0.173613</v>
+        <v>0.183939</v>
       </c>
       <c r="H109" s="7">
-        <v>0.068985</v>
+        <v>0.080062</v>
       </c>
       <c r="I109" s="7">
-        <v>0.45236699999999996</v>
+        <v>0.466505</v>
       </c>
       <c r="J109" s="7">
-        <v>2.016724</v>
+        <v>2.047982</v>
       </c>
       <c r="K109" s="7">
-        <v>3.8730849999999997</v>
+        <v>3.91289</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6072,25 +6072,25 @@
         <v>6</v>
       </c>
       <c r="E110" s="7">
-        <v>0.030654</v>
+        <v>0.036019999999999996</v>
       </c>
       <c r="F110" s="7">
-        <v>0.030879</v>
+        <v>0.036312000000000004</v>
       </c>
       <c r="G110" s="7">
-        <v>0.12759299999999998</v>
+        <v>0.135095</v>
       </c>
       <c r="H110" s="7">
-        <v>0.054114</v>
+        <v>0.061738</v>
       </c>
       <c r="I110" s="7">
-        <v>0.34029200000000004</v>
+        <v>0.345855</v>
       </c>
       <c r="J110" s="7">
-        <v>2.213248</v>
+        <v>2.23649</v>
       </c>
       <c r="K110" s="7">
-        <v>6.484865999999999</v>
+        <v>6.535526</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6107,25 +6107,25 @@
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>0.052605000000000006</v>
+        <v>0.057291999999999996</v>
       </c>
       <c r="F111" s="7">
-        <v>0.094086</v>
+        <v>0.099151</v>
       </c>
       <c r="G111" s="7">
-        <v>0.21144</v>
+        <v>0.21858</v>
       </c>
       <c r="H111" s="7">
-        <v>0.16209700000000002</v>
+        <v>0.170605</v>
       </c>
       <c r="I111" s="7">
-        <v>0.487679</v>
+        <v>0.49046300000000004</v>
       </c>
       <c r="J111" s="7">
-        <v>1.9998150000000001</v>
+        <v>2.021779</v>
       </c>
       <c r="K111" s="7">
-        <v>5.544516</v>
+        <v>5.579535</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6142,25 +6142,25 @@
         <v>5</v>
       </c>
       <c r="E112" s="7">
-        <v>0.052353</v>
+        <v>0.068154</v>
       </c>
       <c r="F112" s="7">
-        <v>0.029783</v>
+        <v>0.050809</v>
       </c>
       <c r="G112" s="7">
-        <v>0.225122</v>
+        <v>0.24808</v>
       </c>
       <c r="H112" s="7">
-        <v>0.14898999999999998</v>
+        <v>0.17505800000000002</v>
       </c>
       <c r="I112" s="7">
-        <v>0.561779</v>
+        <v>0.5941810000000001</v>
       </c>
       <c r="J112" s="7">
-        <v>3.483013</v>
+        <v>3.584721</v>
       </c>
       <c r="K112" s="7">
-        <v>14.490679</v>
+        <v>14.7883</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6177,25 +6177,25 @@
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>0.032766</v>
+        <v>0.03624</v>
       </c>
       <c r="F113" s="7">
-        <v>0.08350400000000001</v>
+        <v>0.08500400000000001</v>
       </c>
       <c r="G113" s="7">
-        <v>0.23107399999999997</v>
+        <v>0.235047</v>
       </c>
       <c r="H113" s="7">
-        <v>0.141966</v>
+        <v>0.14768</v>
       </c>
       <c r="I113" s="7">
-        <v>0.525378</v>
+        <v>0.531222</v>
       </c>
       <c r="J113" s="7">
-        <v>3.25839</v>
+        <v>3.2796980000000002</v>
       </c>
       <c r="K113" s="7">
-        <v>6.257041</v>
+        <v>6.286155</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6212,25 +6212,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.11353400000000001</v>
+        <v>0.111396</v>
       </c>
       <c r="F114" s="7">
-        <v>0.119299</v>
+        <v>0.13406</v>
       </c>
       <c r="G114" s="7">
-        <v>0.294574</v>
+        <v>0.303872</v>
       </c>
       <c r="H114" s="7">
-        <v>0.26710999999999996</v>
+        <v>0.282088</v>
       </c>
       <c r="I114" s="7">
-        <v>0.616696</v>
+        <v>0.616612</v>
       </c>
       <c r="J114" s="7">
-        <v>3.660281</v>
+        <v>3.7153699999999996</v>
       </c>
       <c r="K114" s="7">
-        <v>17.002195999999998</v>
+        <v>17.07887</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6247,25 +6247,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.072384</v>
+        <v>0.080518</v>
       </c>
       <c r="F115" s="7">
-        <v>0.023194</v>
+        <v>0.051485</v>
       </c>
       <c r="G115" s="7">
-        <v>0.226796</v>
+        <v>0.244503</v>
       </c>
       <c r="H115" s="7">
-        <v>0.17364999999999997</v>
+        <v>0.202516</v>
       </c>
       <c r="I115" s="7">
-        <v>0.559424</v>
+        <v>0.593808</v>
       </c>
       <c r="J115" s="7">
-        <v>3.4393830000000003</v>
+        <v>3.5485700000000002</v>
       </c>
       <c r="K115" s="7">
-        <v>22.038438999999997</v>
+        <v>22.400928</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6282,25 +6282,25 @@
         <v>6</v>
       </c>
       <c r="E116" s="7">
-        <v>0.093497</v>
+        <v>0.108977</v>
       </c>
       <c r="F116" s="7">
-        <v>0.066867</v>
+        <v>0.102203</v>
       </c>
       <c r="G116" s="7">
-        <v>0.276754</v>
+        <v>0.303348</v>
       </c>
       <c r="H116" s="7">
-        <v>0.222622</v>
+        <v>0.258721</v>
       </c>
       <c r="I116" s="7">
-        <v>0.590768</v>
+        <v>0.634056</v>
       </c>
       <c r="J116" s="7">
-        <v>2.9964839999999997</v>
+        <v>3.114484</v>
       </c>
       <c r="K116" s="7">
-        <v>15.862346</v>
+        <v>16.164682</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6317,25 +6317,25 @@
         <v>5</v>
       </c>
       <c r="E117" s="7">
-        <v>0.086295</v>
+        <v>0.08485200000000001</v>
       </c>
       <c r="F117" s="7">
-        <v>0.12453099999999999</v>
+        <v>0.132797</v>
       </c>
       <c r="G117" s="7">
-        <v>0.30729399999999996</v>
+        <v>0.31778300000000004</v>
       </c>
       <c r="H117" s="7">
-        <v>0.267814</v>
+        <v>0.28026700000000004</v>
       </c>
       <c r="I117" s="7">
-        <v>0.680523</v>
+        <v>0.681665</v>
       </c>
       <c r="J117" s="7">
-        <v>3.3788110000000002</v>
+        <v>3.421823</v>
       </c>
       <c r="K117" s="7">
-        <v>12.398748000000001</v>
+        <v>12.444935000000001</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6352,25 +6352,25 @@
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>0.025345</v>
+        <v>0.034446</v>
       </c>
       <c r="F118" s="7">
-        <v>0.029296000000000003</v>
+        <v>0.039502999999999996</v>
       </c>
       <c r="G118" s="7">
-        <v>0.17014600000000002</v>
+        <v>0.18084499999999998</v>
       </c>
       <c r="H118" s="7">
-        <v>0.062608</v>
+        <v>0.073756</v>
       </c>
       <c r="I118" s="7">
-        <v>0.422117</v>
+        <v>0.435792</v>
       </c>
       <c r="J118" s="7">
-        <v>1.835007</v>
+        <v>1.8647470000000002</v>
       </c>
       <c r="K118" s="7">
-        <v>3.6654910000000003</v>
+        <v>3.703531</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6387,25 +6387,25 @@
         <v>6</v>
       </c>
       <c r="E119" s="7">
-        <v>0.07683</v>
+        <v>0.0889</v>
       </c>
       <c r="F119" s="7">
-        <v>0.060621999999999995</v>
+        <v>0.08180300000000001</v>
       </c>
       <c r="G119" s="7">
-        <v>0.26332</v>
+        <v>0.28300000000000003</v>
       </c>
       <c r="H119" s="7">
-        <v>0.19489499999999998</v>
+        <v>0.219529</v>
       </c>
       <c r="I119" s="7">
-        <v>0.662239</v>
+        <v>0.692569</v>
       </c>
       <c r="J119" s="7">
-        <v>3.726276</v>
+        <v>3.823713</v>
       </c>
       <c r="K119" s="7">
-        <v>16.179788000000002</v>
+        <v>16.370075</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6422,25 +6422,25 @@
         <v>5</v>
       </c>
       <c r="E120" s="7">
-        <v>0.030853000000000002</v>
+        <v>0.046826999999999994</v>
       </c>
       <c r="F120" s="7">
-        <v>0.007082000000000001</v>
+        <v>0.028156</v>
       </c>
       <c r="G120" s="7">
-        <v>0.171143</v>
+        <v>0.192471</v>
       </c>
       <c r="H120" s="7">
-        <v>0.097497</v>
+        <v>0.12142099999999999</v>
       </c>
       <c r="I120" s="7">
-        <v>0.466128</v>
+        <v>0.49363399999999996</v>
       </c>
       <c r="J120" s="7">
-        <v>2.6267579999999997</v>
+        <v>2.7058139999999997</v>
       </c>
       <c r="K120" s="7">
-        <v>8.831116</v>
+        <v>8.98412</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6457,25 +6457,25 @@
         <v>6</v>
       </c>
       <c r="E121" s="7">
-        <v>0.03912</v>
+        <v>0.059978</v>
       </c>
       <c r="F121" s="7">
-        <v>-0.0029920000000000003</v>
+        <v>0.026636000000000003</v>
       </c>
       <c r="G121" s="7">
-        <v>0.15328799999999998</v>
+        <v>0.176708</v>
       </c>
       <c r="H121" s="7">
-        <v>0.120251</v>
+        <v>0.150746</v>
       </c>
       <c r="I121" s="7">
-        <v>0.442772</v>
+        <v>0.478624</v>
       </c>
       <c r="J121" s="7">
-        <v>3.400747</v>
+        <v>3.5205399999999996</v>
       </c>
       <c r="K121" s="7">
-        <v>17.625699</v>
+        <v>18.034068</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6492,25 +6492,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.036831</v>
+        <v>0.048474</v>
       </c>
       <c r="F122" s="7">
-        <v>0.03356</v>
+        <v>0.048792999999999996</v>
       </c>
       <c r="G122" s="7">
-        <v>0.19121400000000002</v>
+        <v>0.20815799999999998</v>
       </c>
       <c r="H122" s="7">
-        <v>0.111007</v>
+        <v>0.128787</v>
       </c>
       <c r="I122" s="7">
-        <v>0.473041</v>
+        <v>0.494422</v>
       </c>
       <c r="J122" s="7">
-        <v>2.346403</v>
+        <v>2.399958</v>
       </c>
       <c r="K122" s="7">
-        <v>5.95404</v>
+        <v>6.030684</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6527,25 +6527,25 @@
         <v>4</v>
       </c>
       <c r="E123" s="7">
-        <v>0.033029</v>
+        <v>0.045432</v>
       </c>
       <c r="F123" s="7">
-        <v>0.032417</v>
+        <v>0.045701</v>
       </c>
       <c r="G123" s="7">
-        <v>0.167155</v>
+        <v>0.181231</v>
       </c>
       <c r="H123" s="7">
-        <v>0.098233</v>
+        <v>0.113832</v>
       </c>
       <c r="I123" s="7">
-        <v>0.42675199999999996</v>
+        <v>0.444975</v>
       </c>
       <c r="J123" s="7">
-        <v>1.976874</v>
+        <v>2.019157</v>
       </c>
       <c r="K123" s="7">
-        <v>6.002853</v>
+        <v>6.0729690000000005</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6562,16 +6562,16 @@
         <v>6</v>
       </c>
       <c r="E124" s="7">
-        <v>-0.010391999999999998</v>
+        <v>0.006023</v>
       </c>
       <c r="F124" s="7">
-        <v>-0.092875</v>
+        <v>-0.065271</v>
       </c>
       <c r="G124" s="7">
-        <v>0.20876799999999998</v>
+        <v>0.231464</v>
       </c>
       <c r="H124" s="7">
-        <v>0.100342</v>
+        <v>0.12998900000000002</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
@@ -6591,25 +6591,25 @@
         <v>4</v>
       </c>
       <c r="E125" s="7">
-        <v>0.051143999999999995</v>
+        <v>0.059439</v>
       </c>
       <c r="F125" s="7">
-        <v>0.033685</v>
+        <v>0.05051</v>
       </c>
       <c r="G125" s="7">
-        <v>0.228039</v>
+        <v>0.23894500000000002</v>
       </c>
       <c r="H125" s="7">
-        <v>0.145703</v>
+        <v>0.163488</v>
       </c>
       <c r="I125" s="7">
-        <v>0.53429</v>
+        <v>0.557747</v>
       </c>
       <c r="J125" s="7">
-        <v>2.0620279999999998</v>
+        <v>2.109559</v>
       </c>
       <c r="K125" s="7">
-        <v>6.469905</v>
+        <v>6.575148</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6626,16 +6626,16 @@
         <v>6</v>
       </c>
       <c r="E126" s="7">
-        <v>0.137707</v>
+        <v>0.13833700000000002</v>
       </c>
       <c r="F126" s="7">
-        <v>0.162495</v>
+        <v>0.18267299999999997</v>
       </c>
       <c r="G126" s="7">
-        <v>0.38091500000000006</v>
+        <v>0.399409</v>
       </c>
       <c r="H126" s="7">
-        <v>0.36713900000000005</v>
+        <v>0.389829</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
@@ -6655,25 +6655,25 @@
         <v>7</v>
       </c>
       <c r="E127" s="7">
-        <v>0.0819</v>
+        <v>0.092804</v>
       </c>
       <c r="F127" s="7">
-        <v>0.041594</v>
+        <v>0.067626</v>
       </c>
       <c r="G127" s="7">
-        <v>0.203817</v>
+        <v>0.22116599999999997</v>
       </c>
       <c r="H127" s="7">
-        <v>0.122947</v>
+        <v>0.147418</v>
       </c>
       <c r="I127" s="7">
-        <v>0.45210700000000004</v>
+        <v>0.478797</v>
       </c>
       <c r="J127" s="7">
-        <v>2.5961380000000003</v>
+        <v>2.674504</v>
       </c>
       <c r="K127" s="7">
-        <v>9.176436</v>
+        <v>9.407038</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6690,25 +6690,25 @@
         <v>5</v>
       </c>
       <c r="E128" s="7">
-        <v>0.028997000000000002</v>
+        <v>0.036159</v>
       </c>
       <c r="F128" s="7">
-        <v>0.0245</v>
+        <v>0.033905</v>
       </c>
       <c r="G128" s="7">
-        <v>0.09164699999999999</v>
+        <v>0.099323</v>
       </c>
       <c r="H128" s="7">
-        <v>0.043747999999999995</v>
+        <v>0.05374399999999999</v>
       </c>
       <c r="I128" s="7">
-        <v>0.271985</v>
+        <v>0.284036</v>
       </c>
       <c r="J128" s="7">
-        <v>1.9751400000000001</v>
+        <v>2.003634</v>
       </c>
       <c r="K128" s="7">
-        <v>5.485182999999999</v>
+        <v>5.533778</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6725,25 +6725,25 @@
         <v>4</v>
       </c>
       <c r="E129" s="7">
-        <v>0.021738</v>
+        <v>0.031291</v>
       </c>
       <c r="F129" s="7">
-        <v>-0.002384</v>
+        <v>0.007526000000000001</v>
       </c>
       <c r="G129" s="7">
-        <v>0.126975</v>
+        <v>0.138315</v>
       </c>
       <c r="H129" s="7">
-        <v>0.035840000000000004</v>
+        <v>0.04771</v>
       </c>
       <c r="I129" s="7">
-        <v>0.375022</v>
+        <v>0.390875</v>
       </c>
       <c r="J129" s="7">
-        <v>1.525213</v>
+        <v>1.55415</v>
       </c>
       <c r="K129" s="7">
-        <v>3.317749</v>
+        <v>3.3576420000000002</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6760,25 +6760,25 @@
         <v>6</v>
       </c>
       <c r="E130" s="7">
-        <v>0.08166999999999999</v>
+        <v>0.095952</v>
       </c>
       <c r="F130" s="7">
-        <v>0.029952999999999997</v>
+        <v>0.060422000000000003</v>
       </c>
       <c r="G130" s="7">
-        <v>0.277506</v>
+        <v>0.298923</v>
       </c>
       <c r="H130" s="7">
-        <v>0.217469</v>
+        <v>0.252483</v>
       </c>
       <c r="I130" s="7">
-        <v>0.5426639999999999</v>
+        <v>0.584823</v>
       </c>
       <c r="J130" s="7">
-        <v>2.990888</v>
+        <v>3.105666</v>
       </c>
       <c r="K130" s="7">
-        <v>14.154674</v>
+        <v>14.427886</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6795,25 +6795,25 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.034724</v>
+        <v>0.040754</v>
       </c>
       <c r="F131" s="7">
-        <v>0.028902999999999998</v>
+        <v>0.034548999999999996</v>
       </c>
       <c r="G131" s="7">
-        <v>0.079169</v>
+        <v>0.091547</v>
       </c>
       <c r="H131" s="7">
-        <v>0.038961</v>
+        <v>0.047879</v>
       </c>
       <c r="I131" s="7">
-        <v>0.275314</v>
+        <v>0.285621</v>
       </c>
       <c r="J131" s="7">
-        <v>2.040005</v>
+        <v>2.0661</v>
       </c>
       <c r="K131" s="7">
-        <v>6.181001999999999</v>
+        <v>6.237795</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6830,19 +6830,19 @@
         <v>4</v>
       </c>
       <c r="E132" s="7">
-        <v>0.135351</v>
+        <v>0.135156</v>
       </c>
       <c r="F132" s="7">
-        <v>0.167268</v>
+        <v>0.174755</v>
       </c>
       <c r="G132" s="7">
-        <v>0.23244499999999998</v>
+        <v>0.224142</v>
       </c>
       <c r="H132" s="7">
-        <v>0.282821</v>
+        <v>0.294929</v>
       </c>
       <c r="I132" s="7">
-        <v>0.768974</v>
+        <v>0.7697320000000001</v>
       </c>
       <c r="J132" s="7"/>
       <c r="K132" s="7"/>
@@ -6861,25 +6861,25 @@
         <v>4</v>
       </c>
       <c r="E133" s="7">
-        <v>0.034927</v>
+        <v>0.044203</v>
       </c>
       <c r="F133" s="7">
-        <v>0.007448</v>
+        <v>0.019876</v>
       </c>
       <c r="G133" s="7">
-        <v>0.159648</v>
+        <v>0.170025</v>
       </c>
       <c r="H133" s="7">
-        <v>0.069632</v>
+        <v>0.08390700000000001</v>
       </c>
       <c r="I133" s="7">
-        <v>0.40607</v>
+        <v>0.42716099999999996</v>
       </c>
       <c r="J133" s="7">
-        <v>1.485109</v>
+        <v>1.5182749999999998</v>
       </c>
       <c r="K133" s="7">
-        <v>3.740984</v>
+        <v>3.7833319999999997</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -6896,25 +6896,25 @@
         <v>3</v>
       </c>
       <c r="E134" s="7">
-        <v>0.03015</v>
+        <v>0.030159</v>
       </c>
       <c r="F134" s="7">
-        <v>0.08588599999999999</v>
+        <v>0.08404400000000001</v>
       </c>
       <c r="G134" s="7">
-        <v>0.187473</v>
+        <v>0.187247</v>
       </c>
       <c r="H134" s="7">
-        <v>0.126007</v>
+        <v>0.126975</v>
       </c>
       <c r="I134" s="7">
-        <v>0.458837</v>
+        <v>0.45835000000000004</v>
       </c>
       <c r="J134" s="7">
-        <v>2.304039</v>
+        <v>2.3068790000000003</v>
       </c>
       <c r="K134" s="7">
-        <v>3.870683</v>
+        <v>3.8729270000000002</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6931,25 +6931,25 @@
         <v>6</v>
       </c>
       <c r="E135" s="7">
-        <v>0.057542</v>
+        <v>0.068483</v>
       </c>
       <c r="F135" s="7">
-        <v>0.06061</v>
+        <v>0.07397999999999999</v>
       </c>
       <c r="G135" s="7">
-        <v>0.238063</v>
+        <v>0.24696400000000002</v>
       </c>
       <c r="H135" s="7">
-        <v>0.174789</v>
+        <v>0.19159500000000002</v>
       </c>
       <c r="I135" s="7">
-        <v>0.482564</v>
+        <v>0.501036</v>
       </c>
       <c r="J135" s="7">
-        <v>2.9910039999999998</v>
+        <v>3.0480959999999997</v>
       </c>
       <c r="K135" s="7">
-        <v>7.811781999999999</v>
+        <v>7.949484</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6966,25 +6966,25 @@
         <v>4</v>
       </c>
       <c r="E136" s="7">
-        <v>0.033519</v>
+        <v>0.045245</v>
       </c>
       <c r="F136" s="7">
-        <v>0.004811</v>
+        <v>0.016557</v>
       </c>
       <c r="G136" s="7">
-        <v>0.13902</v>
+        <v>0.152611</v>
       </c>
       <c r="H136" s="7">
-        <v>0.063899</v>
+        <v>0.078374</v>
       </c>
       <c r="I136" s="7">
-        <v>0.336009</v>
+        <v>0.355865</v>
       </c>
       <c r="J136" s="7">
-        <v>1.03722</v>
+        <v>1.064938</v>
       </c>
       <c r="K136" s="7">
-        <v>2.4108199999999997</v>
+        <v>2.442178</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7001,25 +7001,25 @@
         <v>6</v>
       </c>
       <c r="E137" s="7">
-        <v>0.06873800000000001</v>
+        <v>0.071565</v>
       </c>
       <c r="F137" s="7">
-        <v>0.079275</v>
+        <v>0.090716</v>
       </c>
       <c r="G137" s="7">
-        <v>0.168985</v>
+        <v>0.18183800000000003</v>
       </c>
       <c r="H137" s="7">
-        <v>0.15440500000000001</v>
+        <v>0.17136600000000002</v>
       </c>
       <c r="I137" s="7">
-        <v>0.43435899999999994</v>
+        <v>0.45503</v>
       </c>
       <c r="J137" s="7">
-        <v>3.095797</v>
+        <v>3.1559730000000004</v>
       </c>
       <c r="K137" s="7">
-        <v>9.285992</v>
+        <v>9.433663000000001</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7036,25 +7036,25 @@
         <v>4</v>
       </c>
       <c r="E138" s="7">
-        <v>0.041884</v>
+        <v>0.046364</v>
       </c>
       <c r="F138" s="7">
-        <v>0.049779</v>
+        <v>0.057153</v>
       </c>
       <c r="G138" s="7">
-        <v>0.168689</v>
+        <v>0.176213</v>
       </c>
       <c r="H138" s="7">
-        <v>0.10429000000000001</v>
+        <v>0.113443</v>
       </c>
       <c r="I138" s="7">
-        <v>0.430478</v>
+        <v>0.44000100000000003</v>
       </c>
       <c r="J138" s="7">
-        <v>2.177946</v>
+        <v>2.204285</v>
       </c>
       <c r="K138" s="7">
-        <v>4.1501850000000005</v>
+        <v>4.190467</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7071,22 +7071,22 @@
         <v>6</v>
       </c>
       <c r="E139" s="7">
-        <v>0.22930599999999998</v>
+        <v>0.239049</v>
       </c>
       <c r="F139" s="7">
-        <v>0.228187</v>
+        <v>0.24372</v>
       </c>
       <c r="G139" s="7">
-        <v>0.32248</v>
+        <v>0.33879800000000004</v>
       </c>
       <c r="H139" s="7">
-        <v>0.283455</v>
+        <v>0.304387</v>
       </c>
       <c r="I139" s="7">
-        <v>0.865231</v>
+        <v>0.9079130000000001</v>
       </c>
       <c r="J139" s="7">
-        <v>5.559863</v>
+        <v>5.666849</v>
       </c>
       <c r="K139" s="7"/>
     </row>
@@ -7104,22 +7104,22 @@
         <v>4</v>
       </c>
       <c r="E140" s="7">
-        <v>0.062297000000000005</v>
+        <v>0.075358</v>
       </c>
       <c r="F140" s="7">
-        <v>0.02182</v>
+        <v>0.045481999999999995</v>
       </c>
       <c r="G140" s="7">
-        <v>0.18627500000000002</v>
+        <v>0.2034</v>
       </c>
       <c r="H140" s="7">
-        <v>0.106186</v>
+        <v>0.129795</v>
       </c>
       <c r="I140" s="7">
-        <v>0.515733</v>
+        <v>0.5399</v>
       </c>
       <c r="J140" s="7">
-        <v>4.933719</v>
+        <v>5.060358</v>
       </c>
       <c r="K140" s="7"/>
     </row>
@@ -7137,25 +7137,25 @@
         <v>3</v>
       </c>
       <c r="E141" s="7">
-        <v>0.029408</v>
+        <v>0.038381</v>
       </c>
       <c r="F141" s="7">
-        <v>0.016493999999999998</v>
+        <v>0.025941000000000002</v>
       </c>
       <c r="G141" s="7">
-        <v>0.148431</v>
+        <v>0.15513</v>
       </c>
       <c r="H141" s="7">
-        <v>0.081541</v>
+        <v>0.092171</v>
       </c>
       <c r="I141" s="7">
-        <v>0.362429</v>
+        <v>0.374921</v>
       </c>
       <c r="J141" s="7">
-        <v>1.6223990000000001</v>
+        <v>1.648175</v>
       </c>
       <c r="K141" s="7">
-        <v>3.581158</v>
+        <v>3.6168959999999997</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -7172,25 +7172,25 @@
         <v>3</v>
       </c>
       <c r="E142" s="7">
-        <v>0.039988</v>
+        <v>0.043955</v>
       </c>
       <c r="F142" s="7">
-        <v>0.068476</v>
+        <v>0.071522</v>
       </c>
       <c r="G142" s="7">
-        <v>0.186189</v>
+        <v>0.190074</v>
       </c>
       <c r="H142" s="7">
-        <v>0.126326</v>
+        <v>0.130717</v>
       </c>
       <c r="I142" s="7">
-        <v>0.36161099999999996</v>
+        <v>0.36344099999999996</v>
       </c>
       <c r="J142" s="7">
-        <v>1.4237270000000002</v>
+        <v>1.4331749999999999</v>
       </c>
       <c r="K142" s="7">
-        <v>4.477625</v>
+        <v>4.4956439999999995</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7207,25 +7207,25 @@
         <v>5</v>
       </c>
       <c r="E143" s="7">
-        <v>0.11732300000000001</v>
+        <v>0.13214</v>
       </c>
       <c r="F143" s="7">
-        <v>0.029277</v>
+        <v>0.047148</v>
       </c>
       <c r="G143" s="7">
-        <v>0.229831</v>
+        <v>0.247933</v>
       </c>
       <c r="H143" s="7">
-        <v>0.169374</v>
+        <v>0.19559300000000002</v>
       </c>
       <c r="I143" s="7">
-        <v>0.37449</v>
+        <v>0.41458</v>
       </c>
       <c r="J143" s="7">
-        <v>3.4470240000000003</v>
+        <v>3.546732</v>
       </c>
       <c r="K143" s="7">
-        <v>13.428443</v>
+        <v>13.777631</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7242,25 +7242,25 @@
         <v>5</v>
       </c>
       <c r="E144" s="7">
-        <v>0.063053</v>
+        <v>0.055114</v>
       </c>
       <c r="F144" s="7">
-        <v>0.138433</v>
+        <v>0.145821</v>
       </c>
       <c r="G144" s="7">
-        <v>0.21503</v>
+        <v>0.22719699999999998</v>
       </c>
       <c r="H144" s="7">
-        <v>0.282954</v>
+        <v>0.292885</v>
       </c>
       <c r="I144" s="7">
-        <v>0.266713</v>
+        <v>0.27876999999999996</v>
       </c>
       <c r="J144" s="7">
-        <v>3.606484</v>
+        <v>3.6421409999999996</v>
       </c>
       <c r="K144" s="7">
-        <v>10.944952</v>
+        <v>11.024493999999999</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7277,25 +7277,25 @@
         <v>3</v>
       </c>
       <c r="E145" s="7">
-        <v>0.072619</v>
+        <v>0.079469</v>
       </c>
       <c r="F145" s="7">
-        <v>0.078545</v>
+        <v>0.096915</v>
       </c>
       <c r="G145" s="7">
-        <v>0.294227</v>
+        <v>0.305826</v>
       </c>
       <c r="H145" s="7">
-        <v>0.20025099999999998</v>
+        <v>0.22044799999999998</v>
       </c>
       <c r="I145" s="7">
-        <v>0.558085</v>
+        <v>0.569497</v>
       </c>
       <c r="J145" s="7">
-        <v>2.9690600000000003</v>
+        <v>3.03585</v>
       </c>
       <c r="K145" s="7">
-        <v>8.131294</v>
+        <v>8.281791</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7312,25 +7312,25 @@
         <v>4</v>
       </c>
       <c r="E146" s="7">
-        <v>0.059932</v>
+        <v>0.069492</v>
       </c>
       <c r="F146" s="7">
-        <v>0.029150999999999996</v>
+        <v>0.04935</v>
       </c>
       <c r="G146" s="7">
-        <v>0.239875</v>
+        <v>0.25305099999999997</v>
       </c>
       <c r="H146" s="7">
-        <v>0.16554</v>
+        <v>0.186546</v>
       </c>
       <c r="I146" s="7">
-        <v>0.547765</v>
+        <v>0.577592</v>
       </c>
       <c r="J146" s="7">
-        <v>3.5414120000000002</v>
+        <v>3.62326</v>
       </c>
       <c r="K146" s="7">
-        <v>9.345569000000001</v>
+        <v>9.506507000000001</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7347,25 +7347,25 @@
         <v>3</v>
       </c>
       <c r="E147" s="7">
-        <v>0.028184</v>
+        <v>0.044425</v>
       </c>
       <c r="F147" s="7">
-        <v>0.13750199999999999</v>
+        <v>0.1432</v>
       </c>
       <c r="G147" s="7">
-        <v>0.341679</v>
+        <v>0.34757599999999994</v>
       </c>
       <c r="H147" s="7">
-        <v>0.267508</v>
+        <v>0.291204</v>
       </c>
       <c r="I147" s="7">
-        <v>0.619259</v>
+        <v>0.6464610000000001</v>
       </c>
       <c r="J147" s="7">
-        <v>3.209639</v>
+        <v>3.2883370000000003</v>
       </c>
       <c r="K147" s="7">
-        <v>9.344074</v>
+        <v>9.538541</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7382,25 +7382,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.032536</v>
+        <v>0.036971</v>
       </c>
       <c r="F148" s="7">
-        <v>0.078379</v>
+        <v>0.082133</v>
       </c>
       <c r="G148" s="7">
-        <v>0.19525099999999998</v>
+        <v>0.20095300000000002</v>
       </c>
       <c r="H148" s="7">
-        <v>0.137423</v>
+        <v>0.14429</v>
       </c>
       <c r="I148" s="7">
-        <v>0.46314</v>
+        <v>0.468716</v>
       </c>
       <c r="J148" s="7">
-        <v>2.277996</v>
+        <v>2.297785</v>
       </c>
       <c r="K148" s="7">
-        <v>6.493139</v>
+        <v>6.519162</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7417,25 +7417,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.025874</v>
+        <v>0.037391</v>
       </c>
       <c r="F149" s="7">
-        <v>0.011583000000000001</v>
+        <v>0.023783</v>
       </c>
       <c r="G149" s="7">
-        <v>0.223909</v>
+        <v>0.23647500000000002</v>
       </c>
       <c r="H149" s="7">
-        <v>0.123405</v>
+        <v>0.139539</v>
       </c>
       <c r="I149" s="7">
-        <v>0.541482</v>
+        <v>0.549899</v>
       </c>
       <c r="J149" s="7">
-        <v>3.297388</v>
+        <v>3.3591070000000003</v>
       </c>
       <c r="K149" s="7">
-        <v>9.434941</v>
+        <v>9.560557</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7452,25 +7452,25 @@
         <v>4</v>
       </c>
       <c r="E150" s="7">
-        <v>0.05405</v>
+        <v>0.055702</v>
       </c>
       <c r="F150" s="7">
-        <v>0.082271</v>
+        <v>0.087484</v>
       </c>
       <c r="G150" s="7">
-        <v>0.18656199999999998</v>
+        <v>0.191572</v>
       </c>
       <c r="H150" s="7">
-        <v>0.148155</v>
+        <v>0.154201</v>
       </c>
       <c r="I150" s="7">
-        <v>0.411357</v>
+        <v>0.41563</v>
       </c>
       <c r="J150" s="7">
-        <v>1.530124</v>
+        <v>1.5434469999999998</v>
       </c>
       <c r="K150" s="7">
-        <v>4.260872</v>
+        <v>4.286335</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7487,25 +7487,25 @@
         <v>5</v>
       </c>
       <c r="E151" s="7">
-        <v>0.127414</v>
+        <v>0.13261900000000001</v>
       </c>
       <c r="F151" s="7">
-        <v>0.140022</v>
+        <v>0.159459</v>
       </c>
       <c r="G151" s="7">
-        <v>0.29465</v>
+        <v>0.312731</v>
       </c>
       <c r="H151" s="7">
-        <v>0.280465</v>
+        <v>0.300597</v>
       </c>
       <c r="I151" s="7">
-        <v>0.623105</v>
+        <v>0.641186</v>
       </c>
       <c r="J151" s="7">
-        <v>2.999964</v>
+        <v>3.062852</v>
       </c>
       <c r="K151" s="7">
-        <v>8.637087000000001</v>
+        <v>8.775915</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7522,25 +7522,25 @@
         <v>7</v>
       </c>
       <c r="E152" s="7">
-        <v>0.107713</v>
+        <v>0.11226000000000001</v>
       </c>
       <c r="F152" s="7">
-        <v>0.131216</v>
+        <v>0.146708</v>
       </c>
       <c r="G152" s="7">
-        <v>0.278155</v>
+        <v>0.29285</v>
       </c>
       <c r="H152" s="7">
-        <v>0.251112</v>
+        <v>0.267538</v>
       </c>
       <c r="I152" s="7">
-        <v>0.600955</v>
+        <v>0.615576</v>
       </c>
       <c r="J152" s="7">
-        <v>2.840469</v>
+        <v>2.890892</v>
       </c>
       <c r="K152" s="7">
-        <v>7.507225</v>
+        <v>7.619334</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7557,25 +7557,25 @@
         <v>3</v>
       </c>
       <c r="E153" s="7">
-        <v>0.034628</v>
+        <v>0.03746</v>
       </c>
       <c r="F153" s="7">
-        <v>0.067022</v>
+        <v>0.071852</v>
       </c>
       <c r="G153" s="7">
-        <v>0.198382</v>
+        <v>0.201313</v>
       </c>
       <c r="H153" s="7">
-        <v>0.125468</v>
+        <v>0.130911</v>
       </c>
       <c r="I153" s="7">
-        <v>0.476498</v>
+        <v>0.48252</v>
       </c>
       <c r="J153" s="7">
-        <v>2.945902</v>
+        <v>2.964988</v>
       </c>
       <c r="K153" s="7">
-        <v>5.073816</v>
+        <v>5.100311</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7592,22 +7592,22 @@
         <v>3</v>
       </c>
       <c r="E154" s="7">
-        <v>0.081703</v>
+        <v>0.08973</v>
       </c>
       <c r="F154" s="7">
-        <v>0.04137</v>
+        <v>0.051976</v>
       </c>
       <c r="G154" s="7">
-        <v>0.191203</v>
+        <v>0.197272</v>
       </c>
       <c r="H154" s="7">
-        <v>0.145812</v>
+        <v>0.159063</v>
       </c>
       <c r="I154" s="7">
-        <v>0.493152</v>
+        <v>0.509736</v>
       </c>
       <c r="J154" s="7">
-        <v>3.490059</v>
+        <v>3.541982</v>
       </c>
       <c r="K154" s="7"/>
     </row>
@@ -7625,16 +7625,16 @@
         <v>4</v>
       </c>
       <c r="E155" s="7">
-        <v>0.049935</v>
+        <v>0.056073000000000005</v>
       </c>
       <c r="F155" s="7">
-        <v>0.076582</v>
+        <v>0.08918799999999999</v>
       </c>
       <c r="G155" s="7">
-        <v>0.262473</v>
+        <v>0.26910799999999996</v>
       </c>
       <c r="H155" s="7">
-        <v>0.19477699999999998</v>
+        <v>0.209394</v>
       </c>
       <c r="I155" s="7"/>
       <c r="J155" s="7"/>
@@ -7654,22 +7654,22 @@
         <v>6</v>
       </c>
       <c r="E156" s="7">
-        <v>0.082618</v>
+        <v>0.09840199999999999</v>
       </c>
       <c r="F156" s="7">
-        <v>0.068946</v>
+        <v>0.088719</v>
       </c>
       <c r="G156" s="7">
-        <v>0.23055299999999998</v>
+        <v>0.254444</v>
       </c>
       <c r="H156" s="7">
-        <v>0.184509</v>
+        <v>0.21148299999999998</v>
       </c>
       <c r="I156" s="7">
-        <v>0.447033</v>
+        <v>0.481516</v>
       </c>
       <c r="J156" s="7">
-        <v>1.780468</v>
+        <v>1.843787</v>
       </c>
       <c r="K156" s="7"/>
     </row>
@@ -7687,25 +7687,25 @@
         <v>3</v>
       </c>
       <c r="E157" s="7">
-        <v>0.060916</v>
+        <v>0.06321</v>
       </c>
       <c r="F157" s="7">
-        <v>0.096074</v>
+        <v>0.10234</v>
       </c>
       <c r="G157" s="7">
-        <v>0.250929</v>
+        <v>0.25747800000000004</v>
       </c>
       <c r="H157" s="7">
-        <v>0.18081499999999998</v>
+        <v>0.18966000000000002</v>
       </c>
       <c r="I157" s="7">
-        <v>0.555092</v>
+        <v>0.564003</v>
       </c>
       <c r="J157" s="7">
-        <v>2.473463</v>
+        <v>2.4994810000000003</v>
       </c>
       <c r="K157" s="7">
-        <v>6.470454</v>
+        <v>6.516414</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -7722,25 +7722,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.063732</v>
+        <v>0.066007</v>
       </c>
       <c r="F158" s="7">
-        <v>0.099345</v>
+        <v>0.106122</v>
       </c>
       <c r="G158" s="7">
-        <v>0.242768</v>
+        <v>0.250014</v>
       </c>
       <c r="H158" s="7">
-        <v>0.18090599999999998</v>
+        <v>0.19027899999999998</v>
       </c>
       <c r="I158" s="7">
-        <v>0.512408</v>
+        <v>0.5218659999999999</v>
       </c>
       <c r="J158" s="7">
-        <v>2.2514060000000002</v>
+        <v>2.277212</v>
       </c>
       <c r="K158" s="7">
-        <v>5.983135999999999</v>
+        <v>6.030066000000001</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7757,25 +7757,25 @@
         <v>3</v>
       </c>
       <c r="E159" s="7">
-        <v>0.048745000000000004</v>
+        <v>0.049284999999999995</v>
       </c>
       <c r="F159" s="7">
-        <v>0.078025</v>
+        <v>0.08474500000000001</v>
       </c>
       <c r="G159" s="7">
-        <v>0.217274</v>
+        <v>0.221535</v>
       </c>
       <c r="H159" s="7">
-        <v>0.147516</v>
+        <v>0.153176</v>
       </c>
       <c r="I159" s="7">
-        <v>0.44630400000000003</v>
+        <v>0.448546</v>
       </c>
       <c r="J159" s="7">
-        <v>1.8721590000000001</v>
+        <v>1.886324</v>
       </c>
       <c r="K159" s="7">
-        <v>5.079984</v>
+        <v>5.107882</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7792,22 +7792,22 @@
         <v>5</v>
       </c>
       <c r="E160" s="7">
-        <v>0.184274</v>
+        <v>0.19476</v>
       </c>
       <c r="F160" s="7">
-        <v>0.25997</v>
+        <v>0.278917</v>
       </c>
       <c r="G160" s="7">
-        <v>0.326697</v>
+        <v>0.34129</v>
       </c>
       <c r="H160" s="7">
-        <v>0.319807</v>
+        <v>0.34001600000000004</v>
       </c>
       <c r="I160" s="7">
-        <v>0.7773789999999999</v>
+        <v>0.804692</v>
       </c>
       <c r="J160" s="7">
-        <v>4.32996</v>
+        <v>4.411573000000001</v>
       </c>
       <c r="K160" s="7"/>
     </row>
@@ -7825,25 +7825,25 @@
         <v>4</v>
       </c>
       <c r="E161" s="7">
-        <v>0.039101</v>
+        <v>0.047222999999999994</v>
       </c>
       <c r="F161" s="7">
-        <v>0.022097000000000002</v>
+        <v>0.033665</v>
       </c>
       <c r="G161" s="7">
-        <v>0.192168</v>
+        <v>0.202527</v>
       </c>
       <c r="H161" s="7">
-        <v>0.092863</v>
+        <v>0.10540200000000001</v>
       </c>
       <c r="I161" s="7">
-        <v>0.42526</v>
+        <v>0.439527</v>
       </c>
       <c r="J161" s="7">
-        <v>2.058847</v>
+        <v>2.093943</v>
       </c>
       <c r="K161" s="7">
-        <v>5.613918999999999</v>
+        <v>5.675259</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7860,22 +7860,22 @@
         <v>4</v>
       </c>
       <c r="E162" s="7">
-        <v>0.03396</v>
+        <v>0.031785</v>
       </c>
       <c r="F162" s="7">
-        <v>0.077845</v>
+        <v>0.08005599999999999</v>
       </c>
       <c r="G162" s="7">
-        <v>0.22308499999999998</v>
+        <v>0.223335</v>
       </c>
       <c r="H162" s="7">
-        <v>0.158322</v>
+        <v>0.159713</v>
       </c>
       <c r="I162" s="7">
-        <v>0.536785</v>
+        <v>0.537583</v>
       </c>
       <c r="J162" s="7">
-        <v>3.437282</v>
+        <v>3.4426119999999996</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7893,22 +7893,22 @@
         <v>6</v>
       </c>
       <c r="E163" s="7">
-        <v>0.03774</v>
+        <v>0.059337</v>
       </c>
       <c r="F163" s="7">
-        <v>-0.00185</v>
+        <v>0.023752</v>
       </c>
       <c r="G163" s="7">
-        <v>0.13995100000000002</v>
+        <v>0.162681</v>
       </c>
       <c r="H163" s="7">
-        <v>0.06415799999999999</v>
+        <v>0.09181900000000001</v>
       </c>
       <c r="I163" s="7">
-        <v>0.383795</v>
+        <v>0.414399</v>
       </c>
       <c r="J163" s="7">
-        <v>2.562245</v>
+        <v>2.6548410000000002</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -7926,25 +7926,25 @@
         <v>5</v>
       </c>
       <c r="E164" s="7">
-        <v>0.103187</v>
+        <v>0.103797</v>
       </c>
       <c r="F164" s="7">
-        <v>0.129907</v>
+        <v>0.147442</v>
       </c>
       <c r="G164" s="7">
-        <v>0.334592</v>
+        <v>0.34752000000000005</v>
       </c>
       <c r="H164" s="7">
-        <v>0.27922</v>
+        <v>0.294245</v>
       </c>
       <c r="I164" s="7">
-        <v>0.674367</v>
+        <v>0.681888</v>
       </c>
       <c r="J164" s="7">
-        <v>2.6586250000000002</v>
+        <v>2.7015949999999997</v>
       </c>
       <c r="K164" s="7">
-        <v>8.778689</v>
+        <v>8.898687</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -7961,25 +7961,25 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.111048</v>
+        <v>0.13376</v>
       </c>
       <c r="F165" s="7">
-        <v>0.078562</v>
+        <v>0.11661300000000001</v>
       </c>
       <c r="G165" s="7">
-        <v>0.35842599999999997</v>
+        <v>0.387593</v>
       </c>
       <c r="H165" s="7">
-        <v>0.292232</v>
+        <v>0.333905</v>
       </c>
       <c r="I165" s="7">
-        <v>0.6759860000000001</v>
+        <v>0.725621</v>
       </c>
       <c r="J165" s="7">
-        <v>1.984232</v>
+        <v>2.080471</v>
       </c>
       <c r="K165" s="7">
-        <v>3.642007</v>
+        <v>3.7907029999999997</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -7996,25 +7996,25 @@
         <v>6</v>
       </c>
       <c r="E166" s="7">
-        <v>0.0874</v>
+        <v>0.108575</v>
       </c>
       <c r="F166" s="7">
-        <v>0.034068999999999995</v>
+        <v>0.067157</v>
       </c>
       <c r="G166" s="7">
-        <v>0.294399</v>
+        <v>0.32297800000000004</v>
       </c>
       <c r="H166" s="7">
-        <v>0.22659600000000002</v>
+        <v>0.267103</v>
       </c>
       <c r="I166" s="7">
-        <v>0.499748</v>
+        <v>0.5445340000000001</v>
       </c>
       <c r="J166" s="7">
-        <v>3.0296760000000003</v>
+        <v>3.16275</v>
       </c>
       <c r="K166" s="7">
-        <v>15.618618</v>
+        <v>15.989366</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8031,25 +8031,25 @@
         <v>3</v>
       </c>
       <c r="E167" s="7">
-        <v>0.02331</v>
+        <v>0.030390999999999998</v>
       </c>
       <c r="F167" s="7">
-        <v>0.003442</v>
+        <v>0.011189</v>
       </c>
       <c r="G167" s="7">
-        <v>0.130784</v>
+        <v>0.14007899999999998</v>
       </c>
       <c r="H167" s="7">
-        <v>0.039693</v>
+        <v>0.048342</v>
       </c>
       <c r="I167" s="7">
-        <v>0.376456</v>
+        <v>0.386589</v>
       </c>
       <c r="J167" s="7">
-        <v>1.8574860000000002</v>
+        <v>1.8812559999999998</v>
       </c>
       <c r="K167" s="7">
-        <v>3.9271409999999998</v>
+        <v>3.9528</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8066,25 +8066,25 @@
         <v>3</v>
       </c>
       <c r="E168" s="7">
-        <v>0.052698</v>
+        <v>0.053579999999999996</v>
       </c>
       <c r="F168" s="7">
-        <v>0.094359</v>
+        <v>0.098626</v>
       </c>
       <c r="G168" s="7">
-        <v>0.24593900000000002</v>
+        <v>0.249439</v>
       </c>
       <c r="H168" s="7">
-        <v>0.173886</v>
+        <v>0.180041</v>
       </c>
       <c r="I168" s="7">
-        <v>0.477846</v>
+        <v>0.481541</v>
       </c>
       <c r="J168" s="7">
-        <v>1.9694399999999999</v>
+        <v>1.9850079999999999</v>
       </c>
       <c r="K168" s="7">
-        <v>5.456079999999999</v>
+        <v>5.488573</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8101,25 +8101,25 @@
         <v>5</v>
       </c>
       <c r="E169" s="7">
-        <v>0.0263</v>
+        <v>0.025353</v>
       </c>
       <c r="F169" s="7">
-        <v>0.061654999999999995</v>
+        <v>0.061458000000000006</v>
       </c>
       <c r="G169" s="7">
-        <v>0.12504300000000002</v>
+        <v>0.125816</v>
       </c>
       <c r="H169" s="7">
-        <v>0.08641</v>
+        <v>0.087567</v>
       </c>
       <c r="I169" s="7">
-        <v>0.299693</v>
+        <v>0.30028900000000003</v>
       </c>
       <c r="J169" s="7">
-        <v>1.9649340000000002</v>
+        <v>1.968092</v>
       </c>
       <c r="K169" s="7">
-        <v>5.4527790000000005</v>
+        <v>5.466696</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8136,22 +8136,22 @@
         <v>6</v>
       </c>
       <c r="E170" s="7">
-        <v>-0.014112</v>
+        <v>0.0037099999999999998</v>
       </c>
       <c r="F170" s="7">
-        <v>-0.089252</v>
+        <v>-0.064189</v>
       </c>
       <c r="G170" s="7">
-        <v>0.19648</v>
+        <v>0.21732500000000002</v>
       </c>
       <c r="H170" s="7">
-        <v>0.076255</v>
+        <v>0.104462</v>
       </c>
       <c r="I170" s="7">
-        <v>0.566682</v>
+        <v>0.578925</v>
       </c>
       <c r="J170" s="7">
-        <v>4.569082</v>
+        <v>4.715043</v>
       </c>
       <c r="K170" s="7"/>
     </row>
@@ -8169,22 +8169,22 @@
         <v>6</v>
       </c>
       <c r="E171" s="7">
-        <v>0.100647</v>
+        <v>0.112327</v>
       </c>
       <c r="F171" s="7">
-        <v>0.061630000000000004</v>
+        <v>0.087141</v>
       </c>
       <c r="G171" s="7">
-        <v>0.234945</v>
+        <v>0.257196</v>
       </c>
       <c r="H171" s="7">
-        <v>0.204288</v>
+        <v>0.233512</v>
       </c>
       <c r="I171" s="7">
-        <v>0.500978</v>
+        <v>0.536525</v>
       </c>
       <c r="J171" s="7">
-        <v>2.6123320000000003</v>
+        <v>2.69999</v>
       </c>
       <c r="K171" s="7"/>
     </row>
@@ -8202,16 +8202,16 @@
         <v>7</v>
       </c>
       <c r="E172" s="7">
-        <v>0.028037</v>
+        <v>0.060272</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.058237</v>
+        <v>0.027534</v>
       </c>
       <c r="G172" s="7">
-        <v>0.576075</v>
+        <v>0.612883</v>
       </c>
       <c r="H172" s="7">
-        <v>0.041333</v>
+        <v>0.072607</v>
       </c>
       <c r="I172" s="7"/>
       <c r="J172" s="7"/>
@@ -8231,25 +8231,25 @@
         <v>6</v>
       </c>
       <c r="E173" s="7">
-        <v>-0.023287</v>
+        <v>-0.003387</v>
       </c>
       <c r="F173" s="7">
-        <v>-0.09100799999999999</v>
+        <v>-0.073305</v>
       </c>
       <c r="G173" s="7">
-        <v>0.178036</v>
+        <v>0.195929</v>
       </c>
       <c r="H173" s="7">
-        <v>0.044696</v>
+        <v>0.069842</v>
       </c>
       <c r="I173" s="7">
-        <v>0.526341</v>
+        <v>0.543087</v>
       </c>
       <c r="J173" s="7">
-        <v>3.890889</v>
+        <v>4.008616</v>
       </c>
       <c r="K173" s="7">
-        <v>13.144077</v>
+        <v>13.501929</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -8266,25 +8266,25 @@
         <v>4</v>
       </c>
       <c r="E174" s="7">
-        <v>0.045042</v>
+        <v>0.05628999999999999</v>
       </c>
       <c r="F174" s="7">
-        <v>0.022320000000000003</v>
+        <v>0.037453</v>
       </c>
       <c r="G174" s="7">
-        <v>0.20150300000000002</v>
+        <v>0.21557400000000002</v>
       </c>
       <c r="H174" s="7">
-        <v>0.10230600000000001</v>
+        <v>0.119062</v>
       </c>
       <c r="I174" s="7">
-        <v>0.44669600000000004</v>
+        <v>0.466019</v>
       </c>
       <c r="J174" s="7">
-        <v>2.08312</v>
+        <v>2.129986</v>
       </c>
       <c r="K174" s="7">
-        <v>5.346367</v>
+        <v>5.419563</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8301,25 +8301,25 @@
         <v>5</v>
       </c>
       <c r="E175" s="7">
-        <v>0.073169</v>
+        <v>0.085702</v>
       </c>
       <c r="F175" s="7">
-        <v>0.051573</v>
+        <v>0.07383200000000001</v>
       </c>
       <c r="G175" s="7">
-        <v>0.26832</v>
+        <v>0.288751</v>
       </c>
       <c r="H175" s="7">
-        <v>0.208155</v>
+        <v>0.23392</v>
       </c>
       <c r="I175" s="7">
-        <v>0.464433</v>
+        <v>0.49144</v>
       </c>
       <c r="J175" s="7">
-        <v>2.814872</v>
+        <v>2.896227</v>
       </c>
       <c r="K175" s="7">
-        <v>10.369793999999999</v>
+        <v>10.560824</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8336,25 +8336,25 @@
         <v>5</v>
       </c>
       <c r="E176" s="7">
-        <v>0.03438</v>
+        <v>0.040908</v>
       </c>
       <c r="F176" s="7">
-        <v>0.037463</v>
+        <v>0.045008</v>
       </c>
       <c r="G176" s="7">
-        <v>0.10066800000000001</v>
+        <v>0.10961</v>
       </c>
       <c r="H176" s="7">
-        <v>0.053239</v>
+        <v>0.06249</v>
       </c>
       <c r="I176" s="7">
-        <v>0.303246</v>
+        <v>0.31273</v>
       </c>
       <c r="J176" s="7">
-        <v>2.09747</v>
+        <v>2.1246780000000003</v>
       </c>
       <c r="K176" s="7">
-        <v>6.218428</v>
+        <v>6.266557000000001</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8371,25 +8371,25 @@
         <v>6</v>
       </c>
       <c r="E177" s="7">
-        <v>0.106448</v>
+        <v>0.11916299999999999</v>
       </c>
       <c r="F177" s="7">
-        <v>0.08395899999999999</v>
+        <v>0.104056</v>
       </c>
       <c r="G177" s="7">
-        <v>0.25380400000000003</v>
+        <v>0.274099</v>
       </c>
       <c r="H177" s="7">
-        <v>0.198744</v>
+        <v>0.22482500000000002</v>
       </c>
       <c r="I177" s="7">
-        <v>0.6018950000000001</v>
+        <v>0.6415890000000001</v>
       </c>
       <c r="J177" s="7">
-        <v>3.030089</v>
+        <v>3.117773</v>
       </c>
       <c r="K177" s="7">
-        <v>12.236857</v>
+        <v>12.498467</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8406,25 +8406,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.089242</v>
+        <v>0.103079</v>
       </c>
       <c r="F178" s="7">
-        <v>0.066841</v>
+        <v>0.094954</v>
       </c>
       <c r="G178" s="7">
-        <v>0.338236</v>
+        <v>0.359931</v>
       </c>
       <c r="H178" s="7">
-        <v>0.25021899999999997</v>
+        <v>0.282501</v>
       </c>
       <c r="I178" s="7">
-        <v>0.5997290000000001</v>
+        <v>0.636458</v>
       </c>
       <c r="J178" s="7">
-        <v>3.397763</v>
+        <v>3.511319</v>
       </c>
       <c r="K178" s="7">
-        <v>17.145604000000002</v>
+        <v>17.445654</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8441,25 +8441,25 @@
         <v>6</v>
       </c>
       <c r="E179" s="7">
-        <v>0.072831</v>
+        <v>0.08463</v>
       </c>
       <c r="F179" s="7">
-        <v>0.060236</v>
+        <v>0.08220100000000001</v>
       </c>
       <c r="G179" s="7">
-        <v>0.310165</v>
+        <v>0.324523</v>
       </c>
       <c r="H179" s="7">
-        <v>0.2102</v>
+        <v>0.23425100000000001</v>
       </c>
       <c r="I179" s="7">
-        <v>0.536</v>
+        <v>0.5616559999999999</v>
       </c>
       <c r="J179" s="7">
-        <v>3.250152</v>
+        <v>3.3346159999999996</v>
       </c>
       <c r="K179" s="7">
-        <v>12.791916</v>
+        <v>12.96417</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8476,25 +8476,25 @@
         <v>4</v>
       </c>
       <c r="E180" s="7">
-        <v>0.06431</v>
+        <v>0.07657</v>
       </c>
       <c r="F180" s="7">
-        <v>0.057098</v>
+        <v>0.07900299999999999</v>
       </c>
       <c r="G180" s="7">
-        <v>0.279821</v>
+        <v>0.29722899999999997</v>
       </c>
       <c r="H180" s="7">
-        <v>0.17704999999999999</v>
+        <v>0.200672</v>
       </c>
       <c r="I180" s="7">
-        <v>0.541426</v>
+        <v>0.568743</v>
       </c>
       <c r="J180" s="7">
-        <v>3.451091</v>
+        <v>3.5404180000000003</v>
       </c>
       <c r="K180" s="7">
-        <v>11.156206</v>
+        <v>11.348996</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8511,25 +8511,25 @@
         <v>6</v>
       </c>
       <c r="E181" s="7">
-        <v>0.09114699999999999</v>
+        <v>0.09959</v>
       </c>
       <c r="F181" s="7">
-        <v>0.07747</v>
+        <v>0.09068799999999999</v>
       </c>
       <c r="G181" s="7">
-        <v>0.17168299999999997</v>
+        <v>0.183151</v>
       </c>
       <c r="H181" s="7">
-        <v>0.124974</v>
+        <v>0.140124</v>
       </c>
       <c r="I181" s="7">
-        <v>0.542486</v>
+        <v>0.563931</v>
       </c>
       <c r="J181" s="7">
-        <v>3.259459</v>
+        <v>3.3168200000000003</v>
       </c>
       <c r="K181" s="7">
-        <v>8.423982</v>
+        <v>8.602083</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8546,25 +8546,25 @@
         <v>2</v>
       </c>
       <c r="E182" s="7">
-        <v>0.037363</v>
+        <v>0.040366</v>
       </c>
       <c r="F182" s="7">
-        <v>0.074506</v>
+        <v>0.078854</v>
       </c>
       <c r="G182" s="7">
-        <v>0.20712399999999997</v>
+        <v>0.211874</v>
       </c>
       <c r="H182" s="7">
-        <v>0.13119</v>
+        <v>0.137579</v>
       </c>
       <c r="I182" s="7">
-        <v>0.487048</v>
+        <v>0.493465</v>
       </c>
       <c r="J182" s="7">
-        <v>3.324235</v>
+        <v>3.3486610000000003</v>
       </c>
       <c r="K182" s="7">
-        <v>6.310367</v>
+        <v>6.3482650000000005</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8581,25 +8581,25 @@
         <v>4</v>
       </c>
       <c r="E183" s="7">
-        <v>0.067686</v>
+        <v>0.077498</v>
       </c>
       <c r="F183" s="7">
-        <v>0.035753</v>
+        <v>0.049964</v>
       </c>
       <c r="G183" s="7">
-        <v>0.128589</v>
+        <v>0.137735</v>
       </c>
       <c r="H183" s="7">
-        <v>0.15767699999999998</v>
+        <v>0.176419</v>
       </c>
       <c r="I183" s="7">
-        <v>0.36172800000000005</v>
+        <v>0.381577</v>
       </c>
       <c r="J183" s="7">
-        <v>2.440816</v>
+        <v>2.496522</v>
       </c>
       <c r="K183" s="7">
-        <v>3.8991480000000003</v>
+        <v>3.976361</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8616,25 +8616,25 @@
         <v>6</v>
       </c>
       <c r="E184" s="7">
-        <v>0.131606</v>
+        <v>0.130905</v>
       </c>
       <c r="F184" s="7">
-        <v>0.16187200000000002</v>
+        <v>0.18299800000000002</v>
       </c>
       <c r="G184" s="7">
-        <v>0.415375</v>
+        <v>0.43236199999999997</v>
       </c>
       <c r="H184" s="7">
-        <v>0.360399</v>
+        <v>0.37750100000000003</v>
       </c>
       <c r="I184" s="7">
-        <v>0.736049</v>
+        <v>0.746135</v>
       </c>
       <c r="J184" s="7">
-        <v>3.481771</v>
+        <v>3.5381099999999996</v>
       </c>
       <c r="K184" s="7">
-        <v>13.227461</v>
+        <v>13.373538000000002</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8651,25 +8651,25 @@
         <v>3</v>
       </c>
       <c r="E185" s="7">
-        <v>0.030188000000000003</v>
+        <v>0.030240999999999997</v>
       </c>
       <c r="F185" s="7">
-        <v>0.08840999999999999</v>
+        <v>0.086669</v>
       </c>
       <c r="G185" s="7">
-        <v>0.19281600000000002</v>
+        <v>0.193037</v>
       </c>
       <c r="H185" s="7">
-        <v>0.12595900000000002</v>
+        <v>0.127354</v>
       </c>
       <c r="I185" s="7">
-        <v>0.455077</v>
+        <v>0.45527</v>
       </c>
       <c r="J185" s="7">
-        <v>1.7278499999999999</v>
+        <v>1.7312280000000002</v>
       </c>
       <c r="K185" s="7">
-        <v>3.831467</v>
+        <v>3.8354450000000004</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8686,25 +8686,25 @@
         <v>5</v>
       </c>
       <c r="E186" s="7">
-        <v>0.108673</v>
+        <v>0.107911</v>
       </c>
       <c r="F186" s="7">
-        <v>0.131747</v>
+        <v>0.146697</v>
       </c>
       <c r="G186" s="7">
-        <v>0.320472</v>
+        <v>0.33171799999999996</v>
       </c>
       <c r="H186" s="7">
-        <v>0.271725</v>
+        <v>0.28457699999999997</v>
       </c>
       <c r="I186" s="7">
-        <v>0.6580849999999999</v>
+        <v>0.664487</v>
       </c>
       <c r="J186" s="7">
-        <v>3.1393180000000003</v>
+        <v>3.1811489999999996</v>
       </c>
       <c r="K186" s="7">
-        <v>11.321969999999999</v>
+        <v>11.426876</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8721,25 +8721,25 @@
         <v>2</v>
       </c>
       <c r="E187" s="7">
-        <v>0.030389</v>
+        <v>0.030428</v>
       </c>
       <c r="F187" s="7">
-        <v>0.088521</v>
+        <v>0.08681599999999999</v>
       </c>
       <c r="G187" s="7">
-        <v>0.19024999999999997</v>
+        <v>0.190487</v>
       </c>
       <c r="H187" s="7">
-        <v>0.125633</v>
+        <v>0.127</v>
       </c>
       <c r="I187" s="7">
-        <v>0.449658</v>
+        <v>0.44986899999999996</v>
       </c>
       <c r="J187" s="7">
-        <v>1.8334020000000002</v>
+        <v>1.836843</v>
       </c>
       <c r="K187" s="7">
-        <v>3.340969</v>
+        <v>3.343787</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8756,25 +8756,25 @@
         <v>2</v>
       </c>
       <c r="E188" s="7">
-        <v>0.022164000000000003</v>
+        <v>0.024057</v>
       </c>
       <c r="F188" s="7">
-        <v>0.064153</v>
+        <v>0.06622499999999999</v>
       </c>
       <c r="G188" s="7">
-        <v>0.156573</v>
+        <v>0.156506</v>
       </c>
       <c r="H188" s="7">
-        <v>0.102925</v>
+        <v>0.103835</v>
       </c>
       <c r="I188" s="7">
-        <v>0.380436</v>
+        <v>0.379675</v>
       </c>
       <c r="J188" s="7">
-        <v>1.9844169999999999</v>
+        <v>1.9868780000000001</v>
       </c>
       <c r="K188" s="7">
-        <v>3.3360399999999997</v>
+        <v>3.3303030000000002</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8791,19 +8791,19 @@
         <v>6</v>
       </c>
       <c r="E189" s="7">
-        <v>0.041845999999999994</v>
+        <v>0.061266999999999995</v>
       </c>
       <c r="F189" s="7">
-        <v>-0.039949</v>
+        <v>0.019607</v>
       </c>
       <c r="G189" s="7">
-        <v>0.546524</v>
+        <v>0.591631</v>
       </c>
       <c r="H189" s="7">
-        <v>0.02538</v>
+        <v>0.062031</v>
       </c>
       <c r="I189" s="7">
-        <v>1.4214529999999999</v>
+        <v>1.4561490000000001</v>
       </c>
       <c r="J189" s="7"/>
       <c r="K189" s="7"/>
@@ -8822,25 +8822,25 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>-0.016102</v>
+        <v>0.0014269999999999999</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.08555</v>
+        <v>-0.06448999999999999</v>
       </c>
       <c r="G190" s="7">
-        <v>0.191181</v>
+        <v>0.207093</v>
       </c>
       <c r="H190" s="7">
-        <v>0.057968</v>
+        <v>0.08089299999999999</v>
       </c>
       <c r="I190" s="7">
-        <v>0.553214</v>
+        <v>0.5617179999999999</v>
       </c>
       <c r="J190" s="7">
-        <v>3.780793</v>
+        <v>3.884385</v>
       </c>
       <c r="K190" s="7">
-        <v>12.910351</v>
+        <v>13.227908</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8857,25 +8857,25 @@
         <v>6</v>
       </c>
       <c r="E191" s="7">
-        <v>-0.026014</v>
+        <v>-0.005606</v>
       </c>
       <c r="F191" s="7">
-        <v>-0.094816</v>
+        <v>-0.079845</v>
       </c>
       <c r="G191" s="7">
-        <v>0.152935</v>
+        <v>0.17048300000000002</v>
       </c>
       <c r="H191" s="7">
-        <v>0.029335</v>
+        <v>0.054268000000000004</v>
       </c>
       <c r="I191" s="7">
-        <v>0.515208</v>
+        <v>0.534048</v>
       </c>
       <c r="J191" s="7">
-        <v>3.731576</v>
+        <v>3.8461849999999997</v>
       </c>
       <c r="K191" s="7">
-        <v>12.649354</v>
+        <v>12.986255000000002</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8892,25 +8892,25 @@
         <v>4</v>
       </c>
       <c r="E192" s="7">
-        <v>0.053350999999999996</v>
+        <v>0.06077</v>
       </c>
       <c r="F192" s="7">
-        <v>0.042744</v>
+        <v>0.055277</v>
       </c>
       <c r="G192" s="7">
-        <v>0.233657</v>
+        <v>0.243319</v>
       </c>
       <c r="H192" s="7">
-        <v>0.135952</v>
+        <v>0.15087</v>
       </c>
       <c r="I192" s="7">
-        <v>0.496221</v>
+        <v>0.514632</v>
       </c>
       <c r="J192" s="7">
-        <v>1.876567</v>
+        <v>1.9143430000000001</v>
       </c>
       <c r="K192" s="7">
-        <v>5.046306</v>
+        <v>5.107831</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8927,25 +8927,25 @@
         <v>4</v>
       </c>
       <c r="E193" s="7">
-        <v>0.042492999999999996</v>
+        <v>0.05253</v>
       </c>
       <c r="F193" s="7">
-        <v>0.038686</v>
+        <v>0.051234</v>
       </c>
       <c r="G193" s="7">
-        <v>0.188293</v>
+        <v>0.199874</v>
       </c>
       <c r="H193" s="7">
-        <v>0.10094099999999999</v>
+        <v>0.115121</v>
       </c>
       <c r="I193" s="7">
-        <v>0.45116799999999996</v>
+        <v>0.46505899999999994</v>
       </c>
       <c r="J193" s="7">
-        <v>2.2516149999999997</v>
+        <v>2.293495</v>
       </c>
       <c r="K193" s="7">
-        <v>5.492907</v>
+        <v>5.564561</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8962,25 +8962,25 @@
         <v>6</v>
       </c>
       <c r="E194" s="7">
-        <v>0.031728</v>
+        <v>0.037643</v>
       </c>
       <c r="F194" s="7">
-        <v>0.031948</v>
+        <v>0.040132</v>
       </c>
       <c r="G194" s="7">
-        <v>0.09998100000000001</v>
+        <v>0.108272</v>
       </c>
       <c r="H194" s="7">
-        <v>0.050027</v>
+        <v>0.058889</v>
       </c>
       <c r="I194" s="7">
-        <v>0.312468</v>
+        <v>0.323719</v>
       </c>
       <c r="J194" s="7">
-        <v>2.214456</v>
+        <v>2.241585</v>
       </c>
       <c r="K194" s="7">
-        <v>6.4269989999999995</v>
+        <v>6.478548</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -8997,25 +8997,25 @@
         <v>3</v>
       </c>
       <c r="E195" s="7">
-        <v>0.050331</v>
+        <v>0.05021899999999999</v>
       </c>
       <c r="F195" s="7">
-        <v>0.100192</v>
+        <v>0.10447</v>
       </c>
       <c r="G195" s="7">
-        <v>0.250463</v>
+        <v>0.256564</v>
       </c>
       <c r="H195" s="7">
-        <v>0.195731</v>
+        <v>0.201639</v>
       </c>
       <c r="I195" s="7">
-        <v>0.47826</v>
+        <v>0.48082099999999994</v>
       </c>
       <c r="J195" s="7">
-        <v>1.602072</v>
+        <v>1.614928</v>
       </c>
       <c r="K195" s="7">
-        <v>3.72502</v>
+        <v>3.7385680000000003</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9032,25 +9032,25 @@
         <v>3</v>
       </c>
       <c r="E196" s="7">
-        <v>0.049372</v>
+        <v>0.051809</v>
       </c>
       <c r="F196" s="7">
-        <v>0.08299799999999999</v>
+        <v>0.08805400000000001</v>
       </c>
       <c r="G196" s="7">
-        <v>0.23539200000000002</v>
+        <v>0.240616</v>
       </c>
       <c r="H196" s="7">
-        <v>0.146532</v>
+        <v>0.15328799999999998</v>
       </c>
       <c r="I196" s="7">
-        <v>0.463362</v>
+        <v>0.469013</v>
       </c>
       <c r="J196" s="7">
-        <v>1.770176</v>
+        <v>1.7865</v>
       </c>
       <c r="K196" s="7">
-        <v>4.6349149999999995</v>
+        <v>4.664497</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9067,25 +9067,25 @@
         <v>4</v>
       </c>
       <c r="E197" s="7">
-        <v>0.055062</v>
+        <v>0.064722</v>
       </c>
       <c r="F197" s="7">
-        <v>0.045542</v>
+        <v>0.058376000000000004</v>
       </c>
       <c r="G197" s="7">
-        <v>0.21183800000000003</v>
+        <v>0.22420600000000002</v>
       </c>
       <c r="H197" s="7">
-        <v>0.128184</v>
+        <v>0.143776</v>
       </c>
       <c r="I197" s="7">
-        <v>0.482992</v>
+        <v>0.500639</v>
       </c>
       <c r="J197" s="7">
-        <v>2.168047</v>
+        <v>2.211832</v>
       </c>
       <c r="K197" s="7">
-        <v>5.064673</v>
+        <v>5.12225</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9102,25 +9102,25 @@
         <v>6</v>
       </c>
       <c r="E198" s="7">
-        <v>0.068633</v>
+        <v>0.08784399999999999</v>
       </c>
       <c r="F198" s="7">
-        <v>0.013633</v>
+        <v>0.04414799999999999</v>
       </c>
       <c r="G198" s="7">
-        <v>0.21795799999999999</v>
+        <v>0.24341100000000002</v>
       </c>
       <c r="H198" s="7">
-        <v>0.201622</v>
+        <v>0.23788499999999999</v>
       </c>
       <c r="I198" s="7">
-        <v>0.470985</v>
+        <v>0.512737</v>
       </c>
       <c r="J198" s="7">
-        <v>4.08055</v>
+        <v>4.23387</v>
       </c>
       <c r="K198" s="7">
-        <v>20.607737</v>
+        <v>21.082752</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9137,16 +9137,16 @@
         <v>5</v>
       </c>
       <c r="E199" s="7">
-        <v>0.09454800000000001</v>
+        <v>0.105388</v>
       </c>
       <c r="F199" s="7">
-        <v>0.073159</v>
+        <v>0.091643</v>
       </c>
       <c r="G199" s="7">
-        <v>0.239623</v>
+        <v>0.258963</v>
       </c>
       <c r="H199" s="7">
-        <v>0.20522400000000002</v>
+        <v>0.226081</v>
       </c>
       <c r="I199" s="7"/>
       <c r="J199" s="7"/>
@@ -9166,25 +9166,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.085252</v>
+        <v>0.096328</v>
       </c>
       <c r="F200" s="7">
-        <v>0.012809999999999998</v>
+        <v>0.042706999999999995</v>
       </c>
       <c r="G200" s="7">
-        <v>0.159052</v>
+        <v>0.186421</v>
       </c>
       <c r="H200" s="7">
-        <v>0.096733</v>
+        <v>0.12273899999999999</v>
       </c>
       <c r="I200" s="7">
-        <v>0.414079</v>
+        <v>0.4385</v>
       </c>
       <c r="J200" s="7">
-        <v>2.347927</v>
+        <v>2.427315</v>
       </c>
       <c r="K200" s="7">
-        <v>9.977678</v>
+        <v>10.154136</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9201,25 +9201,25 @@
         <v>6</v>
       </c>
       <c r="E201" s="7">
-        <v>0.101803</v>
+        <v>0.09813599999999999</v>
       </c>
       <c r="F201" s="7">
-        <v>0.09858</v>
+        <v>0.107628</v>
       </c>
       <c r="G201" s="7">
-        <v>0.255858</v>
+        <v>0.264848</v>
       </c>
       <c r="H201" s="7">
-        <v>0.20226299999999997</v>
+        <v>0.210376</v>
       </c>
       <c r="I201" s="7">
-        <v>0.509046</v>
+        <v>0.514042</v>
       </c>
       <c r="J201" s="7">
-        <v>2.57959</v>
+        <v>2.6037459999999997</v>
       </c>
       <c r="K201" s="7">
-        <v>9.157897</v>
+        <v>9.196362</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9236,25 +9236,25 @@
         <v>5</v>
       </c>
       <c r="E202" s="7">
-        <v>0.022746</v>
+        <v>0.033704</v>
       </c>
       <c r="F202" s="7">
-        <v>0.005425</v>
+        <v>0.013763000000000001</v>
       </c>
       <c r="G202" s="7">
-        <v>0.169468</v>
+        <v>0.17174299999999998</v>
       </c>
       <c r="H202" s="7">
-        <v>0.08540900000000001</v>
+        <v>0.09702999999999999</v>
       </c>
       <c r="I202" s="7">
-        <v>0.661204</v>
+        <v>0.6691020000000001</v>
       </c>
       <c r="J202" s="7">
-        <v>3.029823</v>
+        <v>3.0729680000000004</v>
       </c>
       <c r="K202" s="7">
-        <v>6.36484</v>
+        <v>6.440338000000001</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,25 +9271,25 @@
         <v>3</v>
       </c>
       <c r="E203" s="7">
-        <v>0.018352</v>
+        <v>0.024961999999999998</v>
       </c>
       <c r="F203" s="7">
-        <v>0.023542999999999998</v>
+        <v>0.029474</v>
       </c>
       <c r="G203" s="7">
-        <v>0.145285</v>
+        <v>0.153843</v>
       </c>
       <c r="H203" s="7">
-        <v>0.049118</v>
+        <v>0.056768</v>
       </c>
       <c r="I203" s="7">
-        <v>0.385837</v>
+        <v>0.395444</v>
       </c>
       <c r="J203" s="7">
-        <v>1.63177</v>
+        <v>1.6509610000000001</v>
       </c>
       <c r="K203" s="7">
-        <v>3.6550170000000004</v>
+        <v>3.678283</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9306,16 +9306,16 @@
         <v>6</v>
       </c>
       <c r="E204" s="7">
-        <v>0.074498</v>
+        <v>0.094051</v>
       </c>
       <c r="F204" s="7">
-        <v>0.020442000000000002</v>
+        <v>0.051589</v>
       </c>
       <c r="G204" s="7">
-        <v>0.24369800000000003</v>
+        <v>0.268593</v>
       </c>
       <c r="H204" s="7">
-        <v>0.213119</v>
+        <v>0.250047</v>
       </c>
       <c r="I204" s="7"/>
       <c r="J204" s="7"/>
@@ -9335,25 +9335,25 @@
         <v>5</v>
       </c>
       <c r="E205" s="7">
-        <v>0.034714999999999996</v>
+        <v>0.038858000000000004</v>
       </c>
       <c r="F205" s="7">
-        <v>0.038915000000000005</v>
+        <v>0.044955999999999996</v>
       </c>
       <c r="G205" s="7">
-        <v>0.109912</v>
+        <v>0.11638</v>
       </c>
       <c r="H205" s="7">
-        <v>0.061817000000000004</v>
+        <v>0.068708</v>
       </c>
       <c r="I205" s="7">
-        <v>0.308805</v>
+        <v>0.31556</v>
       </c>
       <c r="J205" s="7">
-        <v>1.9596449999999999</v>
+        <v>1.978851</v>
       </c>
       <c r="K205" s="7">
-        <v>5.26511</v>
+        <v>5.3040329999999996</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9370,25 +9370,25 @@
         <v>4</v>
       </c>
       <c r="E206" s="7">
-        <v>0.035847000000000004</v>
+        <v>0.044013</v>
       </c>
       <c r="F206" s="7">
-        <v>0.0183</v>
+        <v>0.029801</v>
       </c>
       <c r="G206" s="7">
-        <v>0.184853</v>
+        <v>0.192704</v>
       </c>
       <c r="H206" s="7">
-        <v>0.09163500000000001</v>
+        <v>0.104466</v>
       </c>
       <c r="I206" s="7">
-        <v>0.34907</v>
+        <v>0.361343</v>
       </c>
       <c r="J206" s="7">
-        <v>1.992054</v>
+        <v>2.027222</v>
       </c>
       <c r="K206" s="7">
-        <v>4.898426</v>
+        <v>4.952543</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9405,25 +9405,25 @@
         <v>4</v>
       </c>
       <c r="E207" s="7">
-        <v>0.046601</v>
+        <v>0.056655</v>
       </c>
       <c r="F207" s="7">
-        <v>0.032754</v>
+        <v>0.053403</v>
       </c>
       <c r="G207" s="7">
-        <v>0.243612</v>
+        <v>0.25446</v>
       </c>
       <c r="H207" s="7">
-        <v>0.16234200000000001</v>
+        <v>0.182788</v>
       </c>
       <c r="I207" s="7">
-        <v>0.498008</v>
+        <v>0.5165460000000001</v>
       </c>
       <c r="J207" s="7">
-        <v>2.825165</v>
+        <v>2.89245</v>
       </c>
       <c r="K207" s="7">
-        <v>7.913061</v>
+        <v>8.017428</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9440,25 +9440,25 @@
         <v>6</v>
       </c>
       <c r="E208" s="7">
-        <v>0.052715</v>
+        <v>0.067509</v>
       </c>
       <c r="F208" s="7">
-        <v>0.021753</v>
+        <v>0.04861</v>
       </c>
       <c r="G208" s="7">
-        <v>0.292175</v>
+        <v>0.306077</v>
       </c>
       <c r="H208" s="7">
-        <v>0.16768799999999998</v>
+        <v>0.195145</v>
       </c>
       <c r="I208" s="7">
-        <v>0.521769</v>
+        <v>0.54753</v>
       </c>
       <c r="J208" s="7">
-        <v>2.846127</v>
+        <v>2.936564</v>
       </c>
       <c r="K208" s="7">
-        <v>9.62013</v>
+        <v>9.787184</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9475,25 +9475,25 @@
         <v>3</v>
       </c>
       <c r="E209" s="7">
-        <v>0.019098999999999998</v>
+        <v>0.027632</v>
       </c>
       <c r="F209" s="7">
-        <v>0.010854999999999998</v>
+        <v>0.018189999999999998</v>
       </c>
       <c r="G209" s="7">
-        <v>0.155749</v>
+        <v>0.162913</v>
       </c>
       <c r="H209" s="7">
-        <v>0.039192</v>
+        <v>0.047732000000000004</v>
       </c>
       <c r="I209" s="7">
-        <v>0.378537</v>
+        <v>0.391432</v>
       </c>
       <c r="J209" s="7">
-        <v>1.495068</v>
+        <v>1.515571</v>
       </c>
       <c r="K209" s="7">
-        <v>2.917345</v>
+        <v>2.941327</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9510,25 +9510,25 @@
         <v>6</v>
       </c>
       <c r="E210" s="7">
-        <v>0.06271499999999999</v>
+        <v>0.083074</v>
       </c>
       <c r="F210" s="7">
-        <v>-0.000332</v>
+        <v>0.035161</v>
       </c>
       <c r="G210" s="7">
-        <v>0.254533</v>
+        <v>0.2779</v>
       </c>
       <c r="H210" s="7">
-        <v>0.19605599999999998</v>
+        <v>0.233786</v>
       </c>
       <c r="I210" s="7">
-        <v>0.415886</v>
+        <v>0.450449</v>
       </c>
       <c r="J210" s="7">
-        <v>2.9471030000000003</v>
+        <v>3.071616</v>
       </c>
       <c r="K210" s="7">
-        <v>14.413087</v>
+        <v>14.7556</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9545,25 +9545,25 @@
         <v>4</v>
       </c>
       <c r="E211" s="7">
-        <v>0.06075</v>
+        <v>0.069448</v>
       </c>
       <c r="F211" s="7">
-        <v>0.057893</v>
+        <v>0.073185</v>
       </c>
       <c r="G211" s="7">
-        <v>0.234022</v>
+        <v>0.245954</v>
       </c>
       <c r="H211" s="7">
-        <v>0.172613</v>
+        <v>0.19115100000000002</v>
       </c>
       <c r="I211" s="7">
-        <v>0.525559</v>
+        <v>0.546923</v>
       </c>
       <c r="J211" s="7">
-        <v>1.947946</v>
+        <v>1.9945490000000001</v>
       </c>
       <c r="K211" s="7">
-        <v>5.479407999999999</v>
+        <v>5.554854000000001</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9580,25 +9580,25 @@
         <v>3</v>
       </c>
       <c r="E212" s="7">
-        <v>0.060159000000000004</v>
+        <v>0.06318</v>
       </c>
       <c r="F212" s="7">
-        <v>0.11557600000000001</v>
+        <v>0.1207</v>
       </c>
       <c r="G212" s="7">
-        <v>0.263077</v>
+        <v>0.271875</v>
       </c>
       <c r="H212" s="7">
-        <v>0.198189</v>
+        <v>0.20538299999999998</v>
       </c>
       <c r="I212" s="7">
-        <v>0.511663</v>
+        <v>0.515401</v>
       </c>
       <c r="J212" s="7">
-        <v>1.939886</v>
+        <v>1.9575380000000002</v>
       </c>
       <c r="K212" s="7">
-        <v>5.096502</v>
+        <v>5.132059000000001</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,25 +9615,25 @@
         <v>4</v>
       </c>
       <c r="E213" s="7">
-        <v>0.080677</v>
+        <v>0.08682000000000001</v>
       </c>
       <c r="F213" s="7">
-        <v>0.11726</v>
+        <v>0.133566</v>
       </c>
       <c r="G213" s="7">
-        <v>0.319925</v>
+        <v>0.33840400000000004</v>
       </c>
       <c r="H213" s="7">
-        <v>0.270355</v>
+        <v>0.28843</v>
       </c>
       <c r="I213" s="7">
-        <v>0.636286</v>
+        <v>0.6492140000000001</v>
       </c>
       <c r="J213" s="7">
-        <v>3.11305</v>
+        <v>3.171572</v>
       </c>
       <c r="K213" s="7">
-        <v>9.881227</v>
+        <v>10.015594</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,25 +9650,25 @@
         <v>6</v>
       </c>
       <c r="E214" s="7">
-        <v>-0.019355999999999998</v>
+        <v>0.000027000000000000002</v>
       </c>
       <c r="F214" s="7">
-        <v>-0.08837999999999999</v>
+        <v>-0.069119</v>
       </c>
       <c r="G214" s="7">
-        <v>0.19294</v>
+        <v>0.211146</v>
       </c>
       <c r="H214" s="7">
-        <v>0.061658</v>
+        <v>0.08736700000000001</v>
       </c>
       <c r="I214" s="7">
-        <v>0.5780080000000001</v>
+        <v>0.5839</v>
       </c>
       <c r="J214" s="7">
-        <v>3.935292</v>
+        <v>4.054804</v>
       </c>
       <c r="K214" s="7">
-        <v>13.211848999999999</v>
+        <v>13.572627</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9685,25 +9685,25 @@
         <v>4</v>
       </c>
       <c r="E215" s="7">
-        <v>0.043771000000000004</v>
+        <v>0.048208</v>
       </c>
       <c r="F215" s="7">
-        <v>0.050821</v>
+        <v>0.062991</v>
       </c>
       <c r="G215" s="7">
-        <v>0.17157699999999998</v>
+        <v>0.179284</v>
       </c>
       <c r="H215" s="7">
-        <v>0.128027</v>
+        <v>0.13936199999999999</v>
       </c>
       <c r="I215" s="7">
-        <v>0.40403799999999995</v>
+        <v>0.41578499999999996</v>
       </c>
       <c r="J215" s="7">
-        <v>2.343203</v>
+        <v>2.376796</v>
       </c>
       <c r="K215" s="7">
-        <v>7.185271</v>
+        <v>7.251835</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9720,25 +9720,25 @@
         <v>5</v>
       </c>
       <c r="E216" s="7">
-        <v>0.132384</v>
+        <v>0.134236</v>
       </c>
       <c r="F216" s="7">
-        <v>0.16499199999999997</v>
+        <v>0.186429</v>
       </c>
       <c r="G216" s="7">
-        <v>0.39306800000000003</v>
+        <v>0.415128</v>
       </c>
       <c r="H216" s="7">
-        <v>0.357795</v>
+        <v>0.37990999999999997</v>
       </c>
       <c r="I216" s="7">
-        <v>0.703017</v>
+        <v>0.720667</v>
       </c>
       <c r="J216" s="7">
-        <v>2.945915</v>
+        <v>3.0101850000000003</v>
       </c>
       <c r="K216" s="7">
-        <v>9.944004999999999</v>
+        <v>10.088367</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9755,25 +9755,25 @@
         <v>5</v>
       </c>
       <c r="E217" s="7">
-        <v>0.024457</v>
+        <v>0.024435</v>
       </c>
       <c r="F217" s="7">
-        <v>0.036399</v>
+        <v>0.038003999999999996</v>
       </c>
       <c r="G217" s="7">
-        <v>0.08243700000000001</v>
+        <v>0.084423</v>
       </c>
       <c r="H217" s="7">
-        <v>0.052099</v>
+        <v>0.054365</v>
       </c>
       <c r="I217" s="7">
-        <v>0.227209</v>
+        <v>0.22821000000000002</v>
       </c>
       <c r="J217" s="7">
-        <v>1.7930179999999998</v>
+        <v>1.799032</v>
       </c>
       <c r="K217" s="7">
-        <v>5.210339</v>
+        <v>5.240795</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,25 +9790,25 @@
         <v>4</v>
       </c>
       <c r="E218" s="7">
-        <v>0.075144</v>
+        <v>0.077643</v>
       </c>
       <c r="F218" s="7">
-        <v>0.137041</v>
+        <v>0.146608</v>
       </c>
       <c r="G218" s="7">
-        <v>0.3246</v>
+        <v>0.3378</v>
       </c>
       <c r="H218" s="7">
-        <v>0.262351</v>
+        <v>0.273256</v>
       </c>
       <c r="I218" s="7">
-        <v>0.65846</v>
+        <v>0.66646</v>
       </c>
       <c r="J218" s="7">
-        <v>3.404572</v>
+        <v>3.4426240000000004</v>
       </c>
       <c r="K218" s="7">
-        <v>10.377493</v>
+        <v>10.445039999999999</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9825,25 +9825,25 @@
         <v>5</v>
       </c>
       <c r="E219" s="7">
-        <v>0.124388</v>
+        <v>0.126969</v>
       </c>
       <c r="F219" s="7">
-        <v>0.154172</v>
+        <v>0.169297</v>
       </c>
       <c r="G219" s="7">
-        <v>0.38154000000000005</v>
+        <v>0.39710999999999996</v>
       </c>
       <c r="H219" s="7">
-        <v>0.326887</v>
+        <v>0.34354300000000004</v>
       </c>
       <c r="I219" s="7">
-        <v>0.6664570000000001</v>
+        <v>0.679897</v>
       </c>
       <c r="J219" s="7">
-        <v>4.192521</v>
+        <v>4.257703</v>
       </c>
       <c r="K219" s="7">
-        <v>13.62038</v>
+        <v>13.824797</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9860,19 +9860,19 @@
         <v>4</v>
       </c>
       <c r="E220" s="7">
-        <v>0.064307</v>
+        <v>0.067425</v>
       </c>
       <c r="F220" s="7">
-        <v>0.080693</v>
+        <v>0.089043</v>
       </c>
       <c r="G220" s="7">
-        <v>0.24667000000000003</v>
+        <v>0.255481</v>
       </c>
       <c r="H220" s="7">
-        <v>0.189065</v>
+        <v>0.199652</v>
       </c>
       <c r="I220" s="7">
-        <v>0.533802</v>
+        <v>0.539499</v>
       </c>
       <c r="J220" s="7"/>
       <c r="K220" s="7"/>
@@ -9891,16 +9891,16 @@
         <v>6</v>
       </c>
       <c r="E221" s="7">
-        <v>0.012857</v>
+        <v>0.016896</v>
       </c>
       <c r="F221" s="7">
-        <v>-0.103507</v>
+        <v>-0.09894299999999999</v>
       </c>
       <c r="G221" s="7">
-        <v>0.62595</v>
+        <v>0.6162420000000001</v>
       </c>
       <c r="H221" s="7">
-        <v>0.089452</v>
+        <v>0.09341200000000001</v>
       </c>
       <c r="I221" s="7"/>
       <c r="J221" s="7"/>
@@ -9941,22 +9941,22 @@
         <v>6</v>
       </c>
       <c r="E223" s="7">
-        <v>0.0007729999999999999</v>
+        <v>0.015346</v>
       </c>
       <c r="F223" s="7">
-        <v>-0.097355</v>
+        <v>-0.08054</v>
       </c>
       <c r="G223" s="7">
-        <v>0.39169600000000004</v>
+        <v>0.40653</v>
       </c>
       <c r="H223" s="7">
-        <v>0.068644</v>
+        <v>0.089474</v>
       </c>
       <c r="I223" s="7">
-        <v>1.003476</v>
+        <v>1.0011</v>
       </c>
       <c r="J223" s="7">
-        <v>4.347851</v>
+        <v>4.452093</v>
       </c>
       <c r="K223" s="7"/>
     </row>
@@ -9974,25 +9974,25 @@
         <v>4</v>
       </c>
       <c r="E224" s="7">
-        <v>0.031375</v>
+        <v>0.031487</v>
       </c>
       <c r="F224" s="7">
-        <v>0.096805</v>
+        <v>0.09522399999999999</v>
       </c>
       <c r="G224" s="7">
-        <v>0.196828</v>
+        <v>0.196785</v>
       </c>
       <c r="H224" s="7">
-        <v>0.131037</v>
+        <v>0.132183</v>
       </c>
       <c r="I224" s="7">
-        <v>0.44534300000000004</v>
+        <v>0.44534199999999996</v>
       </c>
       <c r="J224" s="7">
-        <v>1.331289</v>
+        <v>1.3336510000000001</v>
       </c>
       <c r="K224" s="7">
-        <v>2.720023</v>
+        <v>2.722444</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -10009,19 +10009,19 @@
         <v>2</v>
       </c>
       <c r="E225" s="7">
-        <v>0.02818</v>
+        <v>0.02896</v>
       </c>
       <c r="F225" s="7">
-        <v>0.082363</v>
+        <v>0.08082700000000001</v>
       </c>
       <c r="G225" s="7">
-        <v>0.185923</v>
+        <v>0.18623699999999999</v>
       </c>
       <c r="H225" s="7">
-        <v>0.121356</v>
+        <v>0.122678</v>
       </c>
       <c r="I225" s="7">
-        <v>0.443506</v>
+        <v>0.443696</v>
       </c>
       <c r="J225" s="7"/>
       <c r="K225" s="7"/>
@@ -10040,22 +10040,22 @@
         <v>6</v>
       </c>
       <c r="E226" s="7">
-        <v>0.12323100000000001</v>
+        <v>0.120734</v>
       </c>
       <c r="F226" s="7">
-        <v>0.143156</v>
+        <v>0.164102</v>
       </c>
       <c r="G226" s="7">
-        <v>0.264015</v>
+        <v>0.283757</v>
       </c>
       <c r="H226" s="7">
-        <v>0.281459</v>
+        <v>0.29693</v>
       </c>
       <c r="I226" s="7">
-        <v>0.483335</v>
+        <v>0.479381</v>
       </c>
       <c r="J226" s="7">
-        <v>2.897073</v>
+        <v>2.9441219999999997</v>
       </c>
       <c r="K226" s="7"/>
     </row>
@@ -10073,19 +10073,19 @@
         <v>5</v>
       </c>
       <c r="E227" s="7">
-        <v>0.007822</v>
+        <v>0.015053</v>
       </c>
       <c r="F227" s="7">
-        <v>-0.05045</v>
+        <v>-0.038532000000000004</v>
       </c>
       <c r="G227" s="7">
-        <v>0.37236400000000003</v>
+        <v>0.37851</v>
       </c>
       <c r="H227" s="7">
-        <v>0.082431</v>
+        <v>0.098782</v>
       </c>
       <c r="I227" s="7">
-        <v>0.8768210000000001</v>
+        <v>0.89259</v>
       </c>
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
@@ -10104,25 +10104,25 @@
         <v>4</v>
       </c>
       <c r="E228" s="7">
-        <v>0.041422999999999995</v>
+        <v>0.050987</v>
       </c>
       <c r="F228" s="7">
-        <v>0.042108999999999994</v>
+        <v>0.054478</v>
       </c>
       <c r="G228" s="7">
-        <v>0.19242599999999999</v>
+        <v>0.20392600000000002</v>
       </c>
       <c r="H228" s="7">
-        <v>0.10390700000000001</v>
+        <v>0.11785999999999999</v>
       </c>
       <c r="I228" s="7">
-        <v>0.454812</v>
+        <v>0.468643</v>
       </c>
       <c r="J228" s="7">
-        <v>2.218024</v>
+        <v>2.258699</v>
       </c>
       <c r="K228" s="7">
-        <v>5.576698</v>
+        <v>5.647307</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -10139,25 +10139,25 @@
         <v>3</v>
       </c>
       <c r="E229" s="7">
-        <v>0.048689</v>
+        <v>0.050021</v>
       </c>
       <c r="F229" s="7">
-        <v>0.08441900000000001</v>
+        <v>0.088859</v>
       </c>
       <c r="G229" s="7">
-        <v>0.230102</v>
+        <v>0.234298</v>
       </c>
       <c r="H229" s="7">
-        <v>0.14787</v>
+        <v>0.153882</v>
       </c>
       <c r="I229" s="7">
-        <v>0.45148699999999997</v>
+        <v>0.45618400000000003</v>
       </c>
       <c r="J229" s="7">
-        <v>1.802707</v>
+        <v>1.8173869999999999</v>
       </c>
       <c r="K229" s="7">
-        <v>4.578171</v>
+        <v>4.6037799999999995</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -10174,19 +10174,19 @@
         <v>3</v>
       </c>
       <c r="E230" s="7">
-        <v>0.09224299999999999</v>
+        <v>0.097094</v>
       </c>
       <c r="F230" s="7">
-        <v>0.144765</v>
+        <v>0.148317</v>
       </c>
       <c r="G230" s="7">
-        <v>0.23656</v>
+        <v>0.24742799999999998</v>
       </c>
       <c r="H230" s="7">
-        <v>0.21832100000000002</v>
+        <v>0.230742</v>
       </c>
       <c r="I230" s="7">
-        <v>0.565291</v>
+        <v>0.575809</v>
       </c>
       <c r="J230" s="7"/>
       <c r="K230" s="7"/>
@@ -10226,19 +10226,19 @@
         <v>5</v>
       </c>
       <c r="E232" s="7">
-        <v>0.156396</v>
+        <v>0.16999099999999998</v>
       </c>
       <c r="F232" s="7">
-        <v>0.23517700000000002</v>
+        <v>0.259397</v>
       </c>
       <c r="G232" s="7">
-        <v>0.367052</v>
+        <v>0.394371</v>
       </c>
       <c r="H232" s="7">
-        <v>0.403928</v>
+        <v>0.418595</v>
       </c>
       <c r="I232" s="7">
-        <v>0.6290520000000001</v>
+        <v>0.632838</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10257,19 +10257,19 @@
         <v>5</v>
       </c>
       <c r="E233" s="7">
-        <v>0.12471600000000001</v>
+        <v>0.13115</v>
       </c>
       <c r="F233" s="7">
-        <v>0.12909</v>
+        <v>0.146083</v>
       </c>
       <c r="G233" s="7">
-        <v>0.274051</v>
+        <v>0.290228</v>
       </c>
       <c r="H233" s="7">
-        <v>0.241447</v>
+        <v>0.261064</v>
       </c>
       <c r="I233" s="7">
-        <v>0.5505720000000001</v>
+        <v>0.568823</v>
       </c>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
@@ -10288,25 +10288,25 @@
         <v>4</v>
       </c>
       <c r="E234" s="7">
-        <v>0.035794</v>
+        <v>0.038853</v>
       </c>
       <c r="F234" s="7">
-        <v>0.066493</v>
+        <v>0.070659</v>
       </c>
       <c r="G234" s="7">
-        <v>0.17499900000000002</v>
+        <v>0.179354</v>
       </c>
       <c r="H234" s="7">
-        <v>0.11385300000000001</v>
+        <v>0.119451</v>
       </c>
       <c r="I234" s="7">
-        <v>0.37445</v>
+        <v>0.382281</v>
       </c>
       <c r="J234" s="7">
-        <v>1.555915</v>
+        <v>1.568761</v>
       </c>
       <c r="K234" s="7">
-        <v>4.341906</v>
+        <v>4.366635</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -10323,19 +10323,19 @@
         <v>3</v>
       </c>
       <c r="E235" s="7">
-        <v>0.041797</v>
+        <v>0.051258</v>
       </c>
       <c r="F235" s="7">
-        <v>0.032304</v>
+        <v>0.050284</v>
       </c>
       <c r="G235" s="7">
-        <v>0.21557500000000002</v>
+        <v>0.22787600000000002</v>
       </c>
       <c r="H235" s="7">
-        <v>0.16605</v>
+        <v>0.187007</v>
       </c>
       <c r="I235" s="7">
-        <v>0.471073</v>
+        <v>0.496464</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10354,19 +10354,19 @@
         <v>4</v>
       </c>
       <c r="E236" s="7">
-        <v>0.036001</v>
+        <v>0.043962</v>
       </c>
       <c r="F236" s="7">
-        <v>0.050728</v>
+        <v>0.060105000000000006</v>
       </c>
       <c r="G236" s="7">
-        <v>0.19215800000000002</v>
+        <v>0.199909</v>
       </c>
       <c r="H236" s="7">
-        <v>0.102417</v>
+        <v>0.114504</v>
       </c>
       <c r="I236" s="7">
-        <v>0.464507</v>
+        <v>0.479174</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10385,19 +10385,19 @@
         <v>2</v>
       </c>
       <c r="E237" s="7">
-        <v>0.033849</v>
+        <v>0.032174</v>
       </c>
       <c r="F237" s="7">
-        <v>0.09458</v>
+        <v>0.091658</v>
       </c>
       <c r="G237" s="7">
-        <v>0.198178</v>
+        <v>0.19693100000000002</v>
       </c>
       <c r="H237" s="7">
-        <v>0.135021</v>
+        <v>0.13495</v>
       </c>
       <c r="I237" s="7">
-        <v>0.472063</v>
+        <v>0.47061</v>
       </c>
       <c r="J237" s="7"/>
       <c r="K237" s="7"/>
@@ -10416,25 +10416,25 @@
         <v>6</v>
       </c>
       <c r="E238" s="7">
-        <v>-0.01187</v>
+        <v>0.004997</v>
       </c>
       <c r="F238" s="7">
-        <v>-0.079988</v>
+        <v>-0.057987000000000004</v>
       </c>
       <c r="G238" s="7">
-        <v>0.208264</v>
+        <v>0.22973</v>
       </c>
       <c r="H238" s="7">
-        <v>0.071102</v>
+        <v>0.098933</v>
       </c>
       <c r="I238" s="7">
-        <v>0.574863</v>
+        <v>0.5850719999999999</v>
       </c>
       <c r="J238" s="7">
-        <v>4.0771</v>
+        <v>4.20902</v>
       </c>
       <c r="K238" s="7">
-        <v>13.498086</v>
+        <v>13.891899</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -10451,14 +10451,14 @@
         <v>3</v>
       </c>
       <c r="E239" s="7">
-        <v>0.021042</v>
+        <v>0.027999999999999997</v>
       </c>
       <c r="F239" s="7">
-        <v>0.011101000000000001</v>
+        <v>0.017815</v>
       </c>
       <c r="G239" s="7"/>
       <c r="H239" s="7">
-        <v>0.036374</v>
+        <v>0.044395</v>
       </c>
       <c r="I239" s="7"/>
       <c r="J239" s="7"/>
@@ -10478,19 +10478,19 @@
         <v>6</v>
       </c>
       <c r="E240" s="7">
-        <v>0.203623</v>
+        <v>0.20413900000000001</v>
       </c>
       <c r="F240" s="7">
-        <v>0.28236</v>
+        <v>0.300668</v>
       </c>
       <c r="G240" s="7">
-        <v>0.357277</v>
+        <v>0.37308199999999997</v>
       </c>
       <c r="H240" s="7">
-        <v>0.351177</v>
+        <v>0.36959899999999996</v>
       </c>
       <c r="I240" s="7">
-        <v>0.7515569999999999</v>
+        <v>0.771046</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10509,19 +10509,19 @@
         <v>5</v>
       </c>
       <c r="E241" s="7">
-        <v>0.09222799999999999</v>
+        <v>0.10048</v>
       </c>
       <c r="F241" s="7">
-        <v>0.052371</v>
+        <v>0.072687</v>
       </c>
       <c r="G241" s="7">
-        <v>0.215108</v>
+        <v>0.232357</v>
       </c>
       <c r="H241" s="7">
-        <v>0.172344</v>
+        <v>0.197045</v>
       </c>
       <c r="I241" s="7">
-        <v>0.495349</v>
+        <v>0.527498</v>
       </c>
       <c r="J241" s="7"/>
       <c r="K241" s="7"/>
@@ -10540,25 +10540,25 @@
         <v>6</v>
       </c>
       <c r="E242" s="7">
-        <v>0.027371</v>
+        <v>0.02765</v>
       </c>
       <c r="F242" s="7">
-        <v>0.037334</v>
+        <v>0.041131</v>
       </c>
       <c r="G242" s="7">
-        <v>0.086533</v>
+        <v>0.090804</v>
       </c>
       <c r="H242" s="7">
-        <v>0.054854</v>
+        <v>0.058929</v>
       </c>
       <c r="I242" s="7">
-        <v>0.228433</v>
+        <v>0.232774</v>
       </c>
       <c r="J242" s="7">
-        <v>1.845428</v>
+        <v>1.856422</v>
       </c>
       <c r="K242" s="7">
-        <v>5.748519</v>
+        <v>5.779068</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -10575,25 +10575,25 @@
         <v>4</v>
       </c>
       <c r="E243" s="7">
-        <v>0.021486</v>
+        <v>0.028671000000000002</v>
       </c>
       <c r="F243" s="7">
-        <v>0.045811000000000004</v>
+        <v>0.050910000000000004</v>
       </c>
       <c r="G243" s="7">
-        <v>0.198857</v>
+        <v>0.195116</v>
       </c>
       <c r="H243" s="7">
-        <v>0.083619</v>
+        <v>0.091274</v>
       </c>
       <c r="I243" s="7">
-        <v>0.20579799999999998</v>
+        <v>0.213652</v>
       </c>
       <c r="J243" s="7">
-        <v>1.9969759999999999</v>
+        <v>2.018145</v>
       </c>
       <c r="K243" s="7">
-        <v>5.80398</v>
+        <v>5.825553</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -10610,25 +10610,25 @@
         <v>6</v>
       </c>
       <c r="E244" s="7">
-        <v>0.076995</v>
+        <v>0.094659</v>
       </c>
       <c r="F244" s="7">
-        <v>0.01365</v>
+        <v>0.045495</v>
       </c>
       <c r="G244" s="7">
-        <v>0.243999</v>
+        <v>0.26715900000000004</v>
       </c>
       <c r="H244" s="7">
-        <v>0.192516</v>
+        <v>0.229407</v>
       </c>
       <c r="I244" s="7">
-        <v>0.494553</v>
+        <v>0.53112</v>
       </c>
       <c r="J244" s="7">
-        <v>3.008977</v>
+        <v>3.132994</v>
       </c>
       <c r="K244" s="7">
-        <v>14.524212</v>
+        <v>14.885418999999999</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10645,25 +10645,25 @@
         <v>3</v>
       </c>
       <c r="E245" s="7">
-        <v>0.050425000000000005</v>
+        <v>0.051165</v>
       </c>
       <c r="F245" s="7">
-        <v>0.08460000000000001</v>
+        <v>0.092564</v>
       </c>
       <c r="G245" s="7">
-        <v>0.228199</v>
+        <v>0.23276599999999997</v>
       </c>
       <c r="H245" s="7">
-        <v>0.156136</v>
+        <v>0.16185</v>
       </c>
       <c r="I245" s="7">
-        <v>0.45844999999999997</v>
+        <v>0.46102699999999996</v>
       </c>
       <c r="J245" s="7">
-        <v>1.831486</v>
+        <v>1.845482</v>
       </c>
       <c r="K245" s="7">
-        <v>4.625559</v>
+        <v>4.651508</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10680,25 +10680,25 @@
         <v>4</v>
       </c>
       <c r="E246" s="7">
-        <v>0.029459</v>
+        <v>0.039768</v>
       </c>
       <c r="F246" s="7">
-        <v>0.004665</v>
+        <v>0.018207</v>
       </c>
       <c r="G246" s="7">
-        <v>0.152677</v>
+        <v>0.165765</v>
       </c>
       <c r="H246" s="7">
-        <v>0.06576699999999999</v>
+        <v>0.08111399999999999</v>
       </c>
       <c r="I246" s="7">
-        <v>0.383621</v>
+        <v>0.401362</v>
       </c>
       <c r="J246" s="7">
-        <v>1.4572319999999999</v>
+        <v>1.4926169999999999</v>
       </c>
       <c r="K246" s="7">
-        <v>3.7866739999999997</v>
+        <v>3.836583</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10715,25 +10715,25 @@
         <v>2</v>
       </c>
       <c r="E247" s="7">
-        <v>0.03814</v>
+        <v>0.039811</v>
       </c>
       <c r="F247" s="7">
-        <v>0.082327</v>
+        <v>0.084825</v>
       </c>
       <c r="G247" s="7">
-        <v>0.209637</v>
+        <v>0.212893</v>
       </c>
       <c r="H247" s="7">
-        <v>0.13436299999999998</v>
+        <v>0.139593</v>
       </c>
       <c r="I247" s="7">
-        <v>0.512763</v>
+        <v>0.517552</v>
       </c>
       <c r="J247" s="7">
-        <v>4.28045</v>
+        <v>4.304794</v>
       </c>
       <c r="K247" s="7">
-        <v>7.1585220000000005</v>
+        <v>7.192627</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10750,25 +10750,25 @@
         <v>4</v>
       </c>
       <c r="E248" s="7">
-        <v>0.057545</v>
+        <v>0.067625</v>
       </c>
       <c r="F248" s="7">
-        <v>0.065053</v>
+        <v>0.079649</v>
       </c>
       <c r="G248" s="7">
-        <v>0.247257</v>
+        <v>0.261451</v>
       </c>
       <c r="H248" s="7">
-        <v>0.180752</v>
+        <v>0.201944</v>
       </c>
       <c r="I248" s="7">
-        <v>0.528879</v>
+        <v>0.5500630000000001</v>
       </c>
       <c r="J248" s="7">
-        <v>3.3528890000000002</v>
+        <v>3.431016</v>
       </c>
       <c r="K248" s="7">
-        <v>8.553125</v>
+        <v>8.705653</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10785,25 +10785,25 @@
         <v>5</v>
       </c>
       <c r="E249" s="7">
-        <v>0.063486</v>
+        <v>0.07646</v>
       </c>
       <c r="F249" s="7">
-        <v>0.047916999999999994</v>
+        <v>0.069447</v>
       </c>
       <c r="G249" s="7">
-        <v>0.249892</v>
+        <v>0.266455</v>
       </c>
       <c r="H249" s="7">
-        <v>0.190758</v>
+        <v>0.21716100000000002</v>
       </c>
       <c r="I249" s="7">
-        <v>0.534483</v>
+        <v>0.562111</v>
       </c>
       <c r="J249" s="7">
-        <v>3.97012</v>
+        <v>4.080324</v>
       </c>
       <c r="K249" s="7">
-        <v>11.458014</v>
+        <v>11.704957</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10820,25 +10820,25 @@
         <v>6</v>
       </c>
       <c r="E250" s="7">
-        <v>0.068187</v>
+        <v>0.083964</v>
       </c>
       <c r="F250" s="7">
-        <v>0.027414</v>
+        <v>0.054535</v>
       </c>
       <c r="G250" s="7">
-        <v>0.251108</v>
+        <v>0.26987</v>
       </c>
       <c r="H250" s="7">
-        <v>0.199014</v>
+        <v>0.231442</v>
       </c>
       <c r="I250" s="7">
-        <v>0.512586</v>
+        <v>0.543965</v>
       </c>
       <c r="J250" s="7">
-        <v>3.599176</v>
+        <v>3.72356</v>
       </c>
       <c r="K250" s="7">
-        <v>14.013670999999999</v>
+        <v>14.365169000000002</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10855,25 +10855,25 @@
         <v>3</v>
       </c>
       <c r="E251" s="7">
-        <v>0.058598</v>
+        <v>0.060829</v>
       </c>
       <c r="F251" s="7">
-        <v>0.097432</v>
+        <v>0.103719</v>
       </c>
       <c r="G251" s="7">
-        <v>0.21695699999999998</v>
+        <v>0.222694</v>
       </c>
       <c r="H251" s="7">
-        <v>0.17379899999999998</v>
+        <v>0.181313</v>
       </c>
       <c r="I251" s="7">
-        <v>0.470616</v>
+        <v>0.47559199999999996</v>
       </c>
       <c r="J251" s="7">
-        <v>2.110375</v>
+        <v>2.130285</v>
       </c>
       <c r="K251" s="7">
-        <v>5.636055</v>
+        <v>5.677292</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10890,25 +10890,25 @@
         <v>5</v>
       </c>
       <c r="E252" s="7">
-        <v>0.09676</v>
+        <v>0.09867100000000001</v>
       </c>
       <c r="F252" s="7">
-        <v>0.123117</v>
+        <v>0.135708</v>
       </c>
       <c r="G252" s="7">
-        <v>0.268887</v>
+        <v>0.281435</v>
       </c>
       <c r="H252" s="7">
-        <v>0.236788</v>
+        <v>0.25266</v>
       </c>
       <c r="I252" s="7">
-        <v>0.546001</v>
+        <v>0.554548</v>
       </c>
       <c r="J252" s="7">
-        <v>3.2511360000000002</v>
+        <v>3.305694</v>
       </c>
       <c r="K252" s="7">
-        <v>9.982546</v>
+        <v>10.114422</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10925,25 +10925,25 @@
         <v>6</v>
       </c>
       <c r="E253" s="7">
-        <v>0.110713</v>
+        <v>0.11289500000000001</v>
       </c>
       <c r="F253" s="7">
-        <v>0.128386</v>
+        <v>0.144569</v>
       </c>
       <c r="G253" s="7">
-        <v>0.280051</v>
+        <v>0.294751</v>
       </c>
       <c r="H253" s="7">
-        <v>0.256203</v>
+        <v>0.275157</v>
       </c>
       <c r="I253" s="7">
-        <v>0.563823</v>
+        <v>0.572589</v>
       </c>
       <c r="J253" s="7">
-        <v>3.5212909999999997</v>
+        <v>3.5895119999999996</v>
       </c>
       <c r="K253" s="7">
-        <v>11.088967</v>
+        <v>11.247592</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10960,25 +10960,25 @@
         <v>4</v>
       </c>
       <c r="E254" s="7">
-        <v>0.023885999999999998</v>
+        <v>0.033047</v>
       </c>
       <c r="F254" s="7">
-        <v>0.008991</v>
+        <v>0.020316</v>
       </c>
       <c r="G254" s="7">
-        <v>0.140455</v>
+        <v>0.151171</v>
       </c>
       <c r="H254" s="7">
-        <v>0.059181</v>
+        <v>0.07216499999999999</v>
       </c>
       <c r="I254" s="7">
-        <v>0.374571</v>
+        <v>0.389214</v>
       </c>
       <c r="J254" s="7">
-        <v>1.822124</v>
+        <v>1.856721</v>
       </c>
       <c r="K254" s="7">
-        <v>4.978612</v>
+        <v>5.042841</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10995,25 +10995,25 @@
         <v>4</v>
       </c>
       <c r="E255" s="7">
-        <v>0.049385000000000005</v>
+        <v>0.057204</v>
       </c>
       <c r="F255" s="7">
-        <v>0.042748</v>
+        <v>0.05847</v>
       </c>
       <c r="G255" s="7">
-        <v>0.237124</v>
+        <v>0.24806</v>
       </c>
       <c r="H255" s="7">
-        <v>0.165014</v>
+        <v>0.182246</v>
       </c>
       <c r="I255" s="7">
-        <v>0.538999</v>
+        <v>0.552852</v>
       </c>
       <c r="J255" s="7">
-        <v>2.916415</v>
+        <v>2.974343</v>
       </c>
       <c r="K255" s="7">
-        <v>6.0850800000000005</v>
+        <v>6.184374</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11030,25 +11030,25 @@
         <v>4</v>
       </c>
       <c r="E256" s="7">
-        <v>0.034209</v>
+        <v>0.040777</v>
       </c>
       <c r="F256" s="7">
-        <v>0.040491</v>
+        <v>0.051712</v>
       </c>
       <c r="G256" s="7">
-        <v>0.22013100000000002</v>
+        <v>0.228676</v>
       </c>
       <c r="H256" s="7">
-        <v>0.148811</v>
+        <v>0.162085</v>
       </c>
       <c r="I256" s="7">
-        <v>0.512763</v>
+        <v>0.521541</v>
       </c>
       <c r="J256" s="7">
-        <v>2.8288780000000004</v>
+        <v>2.873118</v>
       </c>
       <c r="K256" s="7">
-        <v>5.262314</v>
+        <v>5.331044</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11065,25 +11065,25 @@
         <v>5</v>
       </c>
       <c r="E257" s="7">
-        <v>0.066988</v>
+        <v>0.074866</v>
       </c>
       <c r="F257" s="7">
-        <v>0.048875</v>
+        <v>0.06805699999999999</v>
       </c>
       <c r="G257" s="7">
-        <v>0.25735800000000003</v>
+        <v>0.268951</v>
       </c>
       <c r="H257" s="7">
-        <v>0.188895</v>
+        <v>0.20918299999999998</v>
       </c>
       <c r="I257" s="7">
-        <v>0.572625</v>
+        <v>0.591233</v>
       </c>
       <c r="J257" s="7">
-        <v>3.006958</v>
+        <v>3.075335</v>
       </c>
       <c r="K257" s="7">
-        <v>7.356196</v>
+        <v>7.487296</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11100,25 +11100,25 @@
         <v>6</v>
       </c>
       <c r="E258" s="7">
-        <v>-0.015817</v>
+        <v>0.0027050000000000004</v>
       </c>
       <c r="F258" s="7">
-        <v>-0.080455</v>
+        <v>-0.058792</v>
       </c>
       <c r="G258" s="7">
-        <v>0.19700600000000001</v>
+        <v>0.216333</v>
       </c>
       <c r="H258" s="7">
-        <v>0.068539</v>
+        <v>0.094201</v>
       </c>
       <c r="I258" s="7">
-        <v>0.585138</v>
+        <v>0.590205</v>
       </c>
       <c r="J258" s="7">
-        <v>3.942449</v>
+        <v>4.061146</v>
       </c>
       <c r="K258" s="7">
-        <v>13.43528</v>
+        <v>13.799593999999999</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11135,25 +11135,25 @@
         <v>2</v>
       </c>
       <c r="E259" s="7">
-        <v>0.033214</v>
+        <v>0.042686</v>
       </c>
       <c r="F259" s="7">
-        <v>0.09004799999999999</v>
+        <v>0.095045</v>
       </c>
       <c r="G259" s="7">
-        <v>0.194391</v>
+        <v>0.200744</v>
       </c>
       <c r="H259" s="7">
-        <v>0.146896</v>
+        <v>0.154618</v>
       </c>
       <c r="I259" s="7">
-        <v>0.426813</v>
+        <v>0.43471</v>
       </c>
       <c r="J259" s="7">
-        <v>2.436601</v>
+        <v>2.45974</v>
       </c>
       <c r="K259" s="7">
-        <v>4.4785509999999995</v>
+        <v>4.512703</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11170,25 +11170,25 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.081106</v>
+        <v>0.098246</v>
       </c>
       <c r="F260" s="7">
-        <v>0.04612</v>
+        <v>0.06521</v>
       </c>
       <c r="G260" s="7">
-        <v>0.216921</v>
+        <v>0.23939800000000003</v>
       </c>
       <c r="H260" s="7">
-        <v>0.127928</v>
+        <v>0.15366</v>
       </c>
       <c r="I260" s="7">
-        <v>0.629758</v>
+        <v>0.65315</v>
       </c>
       <c r="J260" s="7">
-        <v>4.836901</v>
+        <v>4.9700619999999995</v>
       </c>
       <c r="K260" s="7">
-        <v>20.419597</v>
+        <v>20.741277</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11205,10 +11205,10 @@
         <v>6</v>
       </c>
       <c r="E261" s="7">
-        <v>-0.012357</v>
+        <v>0.005437</v>
       </c>
       <c r="F261" s="7">
-        <v>-0.052497999999999996</v>
+        <v>-0.032424</v>
       </c>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
@@ -11230,22 +11230,22 @@
         <v>3</v>
       </c>
       <c r="E262" s="7">
-        <v>0.065481</v>
+        <v>0.068071</v>
       </c>
       <c r="F262" s="7">
-        <v>0.098935</v>
+        <v>0.106599</v>
       </c>
       <c r="G262" s="7">
-        <v>0.246756</v>
+        <v>0.25532</v>
       </c>
       <c r="H262" s="7">
-        <v>0.184619</v>
+        <v>0.19509</v>
       </c>
       <c r="I262" s="7">
-        <v>0.5237539999999999</v>
+        <v>0.534363</v>
       </c>
       <c r="J262" s="7">
-        <v>2.313528</v>
+        <v>2.342816</v>
       </c>
       <c r="K262" s="7"/>
     </row>
@@ -11263,22 +11263,22 @@
         <v>3</v>
       </c>
       <c r="E263" s="7">
-        <v>0.020863</v>
+        <v>0.022446999999999998</v>
       </c>
       <c r="F263" s="7">
-        <v>0.044168000000000006</v>
+        <v>0.04518</v>
       </c>
       <c r="G263" s="7">
-        <v>0.13897299999999999</v>
+        <v>0.139873</v>
       </c>
       <c r="H263" s="7">
-        <v>0.070447</v>
+        <v>0.073867</v>
       </c>
       <c r="I263" s="7">
-        <v>0.48753500000000005</v>
+        <v>0.487885</v>
       </c>
       <c r="J263" s="7">
-        <v>2.7104090000000003</v>
+        <v>2.722264</v>
       </c>
       <c r="K263" s="7"/>
     </row>
@@ -11296,19 +11296,19 @@
         <v>5</v>
       </c>
       <c r="E264" s="7">
-        <v>0.061424000000000006</v>
+        <v>0.0674</v>
       </c>
       <c r="F264" s="7">
-        <v>-0.008117</v>
+        <v>0.024253</v>
       </c>
       <c r="G264" s="7">
-        <v>0.233195</v>
+        <v>0.254057</v>
       </c>
       <c r="H264" s="7">
-        <v>0.160322</v>
+        <v>0.192285</v>
       </c>
       <c r="I264" s="7">
-        <v>0.443671</v>
+        <v>0.4738</v>
       </c>
       <c r="J264" s="7"/>
       <c r="K264" s="7"/>
@@ -11327,22 +11327,22 @@
         <v>6</v>
       </c>
       <c r="E265" s="7">
-        <v>0.173599</v>
+        <v>0.183855</v>
       </c>
       <c r="F265" s="7">
-        <v>0.184244</v>
+        <v>0.209741</v>
       </c>
       <c r="G265" s="7">
-        <v>0.22903199999999999</v>
+        <v>0.248762</v>
       </c>
       <c r="H265" s="7">
-        <v>0.242777</v>
+        <v>0.25983</v>
       </c>
       <c r="I265" s="7">
-        <v>0.5471159999999999</v>
+        <v>0.560569</v>
       </c>
       <c r="J265" s="7">
-        <v>3.657633</v>
+        <v>3.7215429999999996</v>
       </c>
       <c r="K265" s="7"/>
     </row>
@@ -11360,19 +11360,19 @@
         <v>6</v>
       </c>
       <c r="E266" s="7">
-        <v>0.048914</v>
+        <v>0.045382</v>
       </c>
       <c r="F266" s="7">
-        <v>0.077699</v>
+        <v>0.075353</v>
       </c>
       <c r="G266" s="7">
-        <v>0.177246</v>
+        <v>0.177189</v>
       </c>
       <c r="H266" s="7">
-        <v>0.151869</v>
+        <v>0.149837</v>
       </c>
       <c r="I266" s="7">
-        <v>0.293581</v>
+        <v>0.289635</v>
       </c>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
@@ -11391,19 +11391,19 @@
         <v>2</v>
       </c>
       <c r="E267" s="7">
-        <v>0.031966999999999995</v>
+        <v>0.031863</v>
       </c>
       <c r="F267" s="7">
-        <v>0.09846500000000001</v>
+        <v>0.096335</v>
       </c>
       <c r="G267" s="7">
-        <v>0.20658300000000002</v>
+        <v>0.206528</v>
       </c>
       <c r="H267" s="7">
-        <v>0.137768</v>
+        <v>0.138914</v>
       </c>
       <c r="I267" s="7">
-        <v>0.482271</v>
+        <v>0.481994</v>
       </c>
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
@@ -11422,22 +11422,22 @@
         <v>2</v>
       </c>
       <c r="E268" s="7">
-        <v>0.026299000000000003</v>
+        <v>0.025566</v>
       </c>
       <c r="F268" s="7">
-        <v>0.054534</v>
+        <v>0.054974999999999996</v>
       </c>
       <c r="G268" s="7">
-        <v>0.186742</v>
+        <v>0.185385</v>
       </c>
       <c r="H268" s="7">
-        <v>0.125952</v>
+        <v>0.126519</v>
       </c>
       <c r="I268" s="7">
-        <v>0.480068</v>
+        <v>0.479711</v>
       </c>
       <c r="J268" s="7">
-        <v>3.0825940000000003</v>
+        <v>3.084648</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11455,22 +11455,22 @@
         <v>5</v>
       </c>
       <c r="E269" s="7">
-        <v>0.028025</v>
+        <v>0.031422</v>
       </c>
       <c r="F269" s="7">
-        <v>0.00035000000000000005</v>
+        <v>0.010348999999999999</v>
       </c>
       <c r="G269" s="7">
-        <v>0.176068</v>
+        <v>0.17548200000000003</v>
       </c>
       <c r="H269" s="7">
-        <v>0.12365999999999999</v>
+        <v>0.13211499999999998</v>
       </c>
       <c r="I269" s="7">
-        <v>0.574295</v>
+        <v>0.579241</v>
       </c>
       <c r="J269" s="7">
-        <v>2.8863060000000003</v>
+        <v>2.915548</v>
       </c>
       <c r="K269" s="7"/>
     </row>
@@ -11488,19 +11488,19 @@
         <v>5</v>
       </c>
       <c r="E270" s="7">
-        <v>0.053037</v>
+        <v>0.058242</v>
       </c>
       <c r="F270" s="7">
-        <v>0.091442</v>
+        <v>0.100121</v>
       </c>
       <c r="G270" s="7">
-        <v>0.19538</v>
+        <v>0.20564800000000003</v>
       </c>
       <c r="H270" s="7">
-        <v>0.140073</v>
+        <v>0.152661</v>
       </c>
       <c r="I270" s="7">
-        <v>0.5002179999999999</v>
+        <v>0.5134839999999999</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11519,19 +11519,19 @@
         <v>5</v>
       </c>
       <c r="E271" s="7">
-        <v>0.076471</v>
+        <v>0.08446300000000001</v>
       </c>
       <c r="F271" s="7">
-        <v>0.077707</v>
+        <v>0.10102499999999999</v>
       </c>
       <c r="G271" s="7">
-        <v>0.150693</v>
+        <v>0.171588</v>
       </c>
       <c r="H271" s="7">
-        <v>0.152282</v>
+        <v>0.17805900000000002</v>
       </c>
       <c r="I271" s="7">
-        <v>0.471539</v>
+        <v>0.500049</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11550,19 +11550,19 @@
         <v>4</v>
       </c>
       <c r="E272" s="7">
-        <v>0.069605</v>
+        <v>0.08244</v>
       </c>
       <c r="F272" s="7">
-        <v>0.051886999999999996</v>
+        <v>0.069829</v>
       </c>
       <c r="G272" s="7">
-        <v>0.264963</v>
+        <v>0.283212</v>
       </c>
       <c r="H272" s="7">
-        <v>0.208359</v>
+        <v>0.228691</v>
       </c>
       <c r="I272" s="7">
-        <v>0.375297</v>
+        <v>0.398853</v>
       </c>
       <c r="J272" s="7"/>
       <c r="K272" s="7"/>
@@ -11581,19 +11581,19 @@
         <v>5</v>
       </c>
       <c r="E273" s="7">
-        <v>0.054007</v>
+        <v>0.059054</v>
       </c>
       <c r="F273" s="7">
-        <v>0.06749</v>
+        <v>0.07330300000000001</v>
       </c>
       <c r="G273" s="7">
-        <v>0.248495</v>
+        <v>0.245776</v>
       </c>
       <c r="H273" s="7">
-        <v>0.20009899999999997</v>
+        <v>0.20654599999999998</v>
       </c>
       <c r="I273" s="7">
-        <v>0.34233199999999997</v>
+        <v>0.348545</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11612,19 +11612,19 @@
         <v>6</v>
       </c>
       <c r="E274" s="7">
-        <v>0.19023299999999999</v>
+        <v>0.197674</v>
       </c>
       <c r="F274" s="7">
-        <v>0.2256</v>
+        <v>0.25309899999999996</v>
       </c>
       <c r="G274" s="7">
-        <v>0.31658200000000003</v>
+        <v>0.32783900000000005</v>
       </c>
       <c r="H274" s="7">
-        <v>0.38421799999999995</v>
+        <v>0.400396</v>
       </c>
       <c r="I274" s="7">
-        <v>0.6089220000000001</v>
+        <v>0.612085</v>
       </c>
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
@@ -11643,22 +11643,22 @@
         <v>4</v>
       </c>
       <c r="E275" s="7">
-        <v>0.023719</v>
+        <v>0.028441</v>
       </c>
       <c r="F275" s="7">
-        <v>0.018415</v>
+        <v>0.026427999999999997</v>
       </c>
       <c r="G275" s="7">
-        <v>0.170713</v>
+        <v>0.174899</v>
       </c>
       <c r="H275" s="7">
-        <v>0.11751899999999998</v>
+        <v>0.125351</v>
       </c>
       <c r="I275" s="7">
-        <v>0.506247</v>
+        <v>0.513636</v>
       </c>
       <c r="J275" s="7">
-        <v>3.027318</v>
+        <v>3.055542</v>
       </c>
       <c r="K275" s="7"/>
     </row>
@@ -11676,25 +11676,25 @@
         <v>5</v>
       </c>
       <c r="E276" s="7">
-        <v>0.084608</v>
+        <v>0.087922</v>
       </c>
       <c r="F276" s="7">
-        <v>0.123114</v>
+        <v>0.130475</v>
       </c>
       <c r="G276" s="7">
-        <v>0.31272500000000003</v>
+        <v>0.32339199999999996</v>
       </c>
       <c r="H276" s="7">
-        <v>0.229876</v>
+        <v>0.240033</v>
       </c>
       <c r="I276" s="7">
-        <v>0.5932569999999999</v>
+        <v>0.596838</v>
       </c>
       <c r="J276" s="7">
-        <v>2.685466</v>
+        <v>2.715904</v>
       </c>
       <c r="K276" s="7">
-        <v>6.656668</v>
+        <v>6.726371</v>
       </c>
     </row>
     <row r="277" spans="1:11" x14ac:dyDescent="0.25">
@@ -11711,25 +11711,25 @@
         <v>2</v>
       </c>
       <c r="E277" s="7">
-        <v>0.03163</v>
+        <v>0.032302</v>
       </c>
       <c r="F277" s="7">
-        <v>0.08938399999999999</v>
+        <v>0.08830500000000001</v>
       </c>
       <c r="G277" s="7">
-        <v>0.19902899999999998</v>
+        <v>0.199524</v>
       </c>
       <c r="H277" s="7">
-        <v>0.132488</v>
+        <v>0.134085</v>
       </c>
       <c r="I277" s="7">
-        <v>0.472868</v>
+        <v>0.47334899999999996</v>
       </c>
       <c r="J277" s="7">
-        <v>2.204991</v>
+        <v>2.20951</v>
       </c>
       <c r="K277" s="7">
-        <v>4.149187</v>
+        <v>4.1538889999999995</v>
       </c>
     </row>
     <row r="278" spans="1:11" x14ac:dyDescent="0.25">
@@ -11746,25 +11746,25 @@
         <v>6</v>
       </c>
       <c r="E278" s="7">
-        <v>0.040346</v>
+        <v>0.057694999999999996</v>
       </c>
       <c r="F278" s="7">
-        <v>0.023568</v>
+        <v>0.038907</v>
       </c>
       <c r="G278" s="7">
-        <v>0.10793799999999999</v>
+        <v>0.128559</v>
       </c>
       <c r="H278" s="7">
-        <v>0.045210999999999994</v>
+        <v>0.064856</v>
       </c>
       <c r="I278" s="7">
-        <v>0.294095</v>
+        <v>0.318451</v>
       </c>
       <c r="J278" s="7">
-        <v>1.7580779999999998</v>
+        <v>1.809917</v>
       </c>
       <c r="K278" s="7">
-        <v>5.083746</v>
+        <v>5.194904</v>
       </c>
     </row>
     <row r="279" spans="1:11" x14ac:dyDescent="0.25">
@@ -11781,25 +11781,25 @@
         <v>6</v>
       </c>
       <c r="E279" s="7">
-        <v>0.08204399999999999</v>
+        <v>0.093076</v>
       </c>
       <c r="F279" s="7">
-        <v>0.016268</v>
+        <v>0.042249</v>
       </c>
       <c r="G279" s="7">
-        <v>0.21222000000000002</v>
+        <v>0.23331600000000002</v>
       </c>
       <c r="H279" s="7">
-        <v>0.18851700000000002</v>
+        <v>0.21943000000000001</v>
       </c>
       <c r="I279" s="7">
-        <v>0.453301</v>
+        <v>0.48282800000000003</v>
       </c>
       <c r="J279" s="7">
-        <v>2.63197</v>
+        <v>2.726434</v>
       </c>
       <c r="K279" s="7">
-        <v>12.392138</v>
+        <v>12.641079</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11816,25 +11816,25 @@
         <v>4</v>
       </c>
       <c r="E280" s="7">
-        <v>0.039388</v>
+        <v>0.050397</v>
       </c>
       <c r="F280" s="7">
-        <v>0.012648999999999999</v>
+        <v>0.028822</v>
       </c>
       <c r="G280" s="7">
-        <v>0.159445</v>
+        <v>0.16733699999999999</v>
       </c>
       <c r="H280" s="7">
-        <v>0.045432</v>
+        <v>0.060244</v>
       </c>
       <c r="I280" s="7">
-        <v>0.383401</v>
+        <v>0.402911</v>
       </c>
       <c r="J280" s="7">
-        <v>1.697732</v>
+        <v>1.7359540000000002</v>
       </c>
       <c r="K280" s="7">
-        <v>3.634017</v>
+        <v>3.679828</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11851,25 +11851,25 @@
         <v>6</v>
       </c>
       <c r="E281" s="7">
-        <v>0.093886</v>
+        <v>0.098498</v>
       </c>
       <c r="F281" s="7">
-        <v>0.112621</v>
+        <v>0.129763</v>
       </c>
       <c r="G281" s="7">
-        <v>0.269567</v>
+        <v>0.288451</v>
       </c>
       <c r="H281" s="7">
-        <v>0.21430700000000003</v>
+        <v>0.23197600000000002</v>
       </c>
       <c r="I281" s="7">
-        <v>0.502945</v>
+        <v>0.526192</v>
       </c>
       <c r="J281" s="7">
-        <v>2.89099</v>
+        <v>2.947606</v>
       </c>
       <c r="K281" s="7">
-        <v>10.114123</v>
+        <v>10.255645999999999</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11886,25 +11886,25 @@
         <v>3</v>
       </c>
       <c r="E282" s="7">
-        <v>0.036576</v>
+        <v>0.039695999999999995</v>
       </c>
       <c r="F282" s="7">
-        <v>0.082222</v>
+        <v>0.086912</v>
       </c>
       <c r="G282" s="7">
-        <v>0.196569</v>
+        <v>0.200914</v>
       </c>
       <c r="H282" s="7">
-        <v>0.142166</v>
+        <v>0.147968</v>
       </c>
       <c r="I282" s="7">
-        <v>0.46689100000000006</v>
+        <v>0.471021</v>
       </c>
       <c r="J282" s="7">
-        <v>2.954241</v>
+        <v>2.974328</v>
       </c>
       <c r="K282" s="7">
-        <v>5.294321</v>
+        <v>5.323174</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11921,25 +11921,25 @@
         <v>3</v>
       </c>
       <c r="E283" s="7">
-        <v>0.028351</v>
+        <v>0.030308</v>
       </c>
       <c r="F283" s="7">
-        <v>0.069003</v>
+        <v>0.06982300000000001</v>
       </c>
       <c r="G283" s="7">
-        <v>0.178983</v>
+        <v>0.18159</v>
       </c>
       <c r="H283" s="7">
-        <v>0.104033</v>
+        <v>0.10766099999999999</v>
       </c>
       <c r="I283" s="7">
-        <v>0.448912</v>
+        <v>0.45246899999999995</v>
       </c>
       <c r="J283" s="7">
-        <v>2.2922130000000003</v>
+        <v>2.30303</v>
       </c>
       <c r="K283" s="7">
-        <v>4.2110449999999995</v>
+        <v>4.214615</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11956,25 +11956,25 @@
         <v>5</v>
       </c>
       <c r="E284" s="7">
-        <v>0.032374</v>
+        <v>0.038235</v>
       </c>
       <c r="F284" s="7">
-        <v>0.030588</v>
+        <v>0.036944</v>
       </c>
       <c r="G284" s="7">
-        <v>0.074192</v>
+        <v>0.084835</v>
       </c>
       <c r="H284" s="7">
-        <v>0.035006</v>
+        <v>0.04337</v>
       </c>
       <c r="I284" s="7">
-        <v>0.27664</v>
+        <v>0.28238800000000003</v>
       </c>
       <c r="J284" s="7">
-        <v>1.9379920000000002</v>
+        <v>1.961735</v>
       </c>
       <c r="K284" s="7">
-        <v>5.759477</v>
+        <v>5.805699</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11991,25 +11991,25 @@
         <v>3</v>
       </c>
       <c r="E285" s="7">
-        <v>0.031351</v>
+        <v>0.032466</v>
       </c>
       <c r="F285" s="7">
-        <v>0.049945</v>
+        <v>0.053811</v>
       </c>
       <c r="G285" s="7">
-        <v>0.213594</v>
+        <v>0.21863600000000002</v>
       </c>
       <c r="H285" s="7">
-        <v>0.062474999999999996</v>
+        <v>0.06644800000000001</v>
       </c>
       <c r="I285" s="7">
-        <v>0.426654</v>
+        <v>0.42997399999999997</v>
       </c>
       <c r="J285" s="7">
-        <v>1.968759</v>
+        <v>1.97986</v>
       </c>
       <c r="K285" s="7">
-        <v>3.624594</v>
+        <v>3.639841</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12026,25 +12026,25 @@
         <v>5</v>
       </c>
       <c r="E286" s="7">
-        <v>0.048827999999999996</v>
+        <v>0.056417999999999996</v>
       </c>
       <c r="F286" s="7">
-        <v>0.071738</v>
+        <v>0.080716</v>
       </c>
       <c r="G286" s="7">
-        <v>0.242224</v>
+        <v>0.249854</v>
       </c>
       <c r="H286" s="7">
-        <v>0.168521</v>
+        <v>0.18238</v>
       </c>
       <c r="I286" s="7">
-        <v>0.535153</v>
+        <v>0.55035</v>
       </c>
       <c r="J286" s="7">
-        <v>2.7468830000000004</v>
+        <v>2.791322</v>
       </c>
       <c r="K286" s="7">
-        <v>9.369938</v>
+        <v>9.461946000000001</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12061,25 +12061,25 @@
         <v>6</v>
       </c>
       <c r="E287" s="7">
-        <v>-0.024761000000000002</v>
+        <v>-0.005262</v>
       </c>
       <c r="F287" s="7">
-        <v>-0.092476</v>
+        <v>-0.07747799999999999</v>
       </c>
       <c r="G287" s="7">
-        <v>0.179272</v>
+        <v>0.19511900000000001</v>
       </c>
       <c r="H287" s="7">
-        <v>0.036101999999999995</v>
+        <v>0.060521000000000005</v>
       </c>
       <c r="I287" s="7">
-        <v>0.535159</v>
+        <v>0.547743</v>
       </c>
       <c r="J287" s="7">
-        <v>4.000273</v>
+        <v>4.118118</v>
       </c>
       <c r="K287" s="7">
-        <v>13.445903000000001</v>
+        <v>13.784689</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12096,25 +12096,25 @@
         <v>3</v>
       </c>
       <c r="E288" s="7">
-        <v>0.0592</v>
+        <v>0.059828</v>
       </c>
       <c r="F288" s="7">
-        <v>0.104008</v>
+        <v>0.10813800000000001</v>
       </c>
       <c r="G288" s="7">
-        <v>0.26326499999999997</v>
+        <v>0.268158</v>
       </c>
       <c r="H288" s="7">
-        <v>0.179954</v>
+        <v>0.185558</v>
       </c>
       <c r="I288" s="7">
-        <v>0.501111</v>
+        <v>0.504189</v>
       </c>
       <c r="J288" s="7">
-        <v>1.4116069999999998</v>
+        <v>1.4230600000000002</v>
       </c>
       <c r="K288" s="7">
-        <v>3.742636</v>
+        <v>3.755538</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12131,25 +12131,25 @@
         <v>6</v>
       </c>
       <c r="E289" s="7">
-        <v>0.076367</v>
+        <v>0.092528</v>
       </c>
       <c r="F289" s="7">
-        <v>0.041931</v>
+        <v>0.068107</v>
       </c>
       <c r="G289" s="7">
-        <v>0.26557400000000003</v>
+        <v>0.289366</v>
       </c>
       <c r="H289" s="7">
-        <v>0.17149599999999998</v>
+        <v>0.20269600000000002</v>
       </c>
       <c r="I289" s="7">
-        <v>0.545149</v>
+        <v>0.579549</v>
       </c>
       <c r="J289" s="7">
-        <v>2.5748349999999998</v>
+        <v>2.6700420000000005</v>
       </c>
       <c r="K289" s="7">
-        <v>10.364674</v>
+        <v>10.614604</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12166,25 +12166,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>-0.000319</v>
+        <v>0.029828999999999998</v>
       </c>
       <c r="F290" s="7">
-        <v>-0.049360999999999995</v>
+        <v>-0.018712</v>
       </c>
       <c r="G290" s="7">
-        <v>0.275253</v>
+        <v>0.30964600000000003</v>
       </c>
       <c r="H290" s="7">
-        <v>0.08758200000000001</v>
+        <v>0.125159</v>
       </c>
       <c r="I290" s="7">
-        <v>0.7422880000000001</v>
+        <v>0.765183</v>
       </c>
       <c r="J290" s="7">
-        <v>4.0800529999999995</v>
+        <v>4.255576</v>
       </c>
       <c r="K290" s="7">
-        <v>8.267079</v>
+        <v>8.560937000000001</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12201,25 +12201,25 @@
         <v>6</v>
       </c>
       <c r="E291" s="7">
-        <v>0.067143</v>
+        <v>0.090138</v>
       </c>
       <c r="F291" s="7">
-        <v>0.071359</v>
+        <v>0.102381</v>
       </c>
       <c r="G291" s="7">
-        <v>0.204455</v>
+        <v>0.23014800000000002</v>
       </c>
       <c r="H291" s="7">
-        <v>0.153068</v>
+        <v>0.18689499999999998</v>
       </c>
       <c r="I291" s="7">
-        <v>0.432378</v>
+        <v>0.470298</v>
       </c>
       <c r="J291" s="7">
-        <v>2.526055</v>
+        <v>2.629499</v>
       </c>
       <c r="K291" s="7">
-        <v>9.170461</v>
+        <v>9.430298</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12236,25 +12236,25 @@
         <v>6</v>
       </c>
       <c r="E292" s="7">
-        <v>0.111918</v>
+        <v>0.125065</v>
       </c>
       <c r="F292" s="7">
-        <v>0.051281</v>
+        <v>0.07792</v>
       </c>
       <c r="G292" s="7">
-        <v>0.269496</v>
+        <v>0.29207</v>
       </c>
       <c r="H292" s="7">
-        <v>0.226342</v>
+        <v>0.256416</v>
       </c>
       <c r="I292" s="7">
-        <v>0.428468</v>
+        <v>0.466897</v>
       </c>
       <c r="J292" s="7">
-        <v>2.697921</v>
+        <v>2.7886059999999997</v>
       </c>
       <c r="K292" s="7">
-        <v>12.599463</v>
+        <v>12.847574</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12271,25 +12271,25 @@
         <v>4</v>
       </c>
       <c r="E293" s="7">
-        <v>0.049473</v>
+        <v>0.052281</v>
       </c>
       <c r="F293" s="7">
-        <v>0.08138400000000001</v>
+        <v>0.08701700000000001</v>
       </c>
       <c r="G293" s="7">
-        <v>0.23332</v>
+        <v>0.238066</v>
       </c>
       <c r="H293" s="7">
-        <v>0.176171</v>
+        <v>0.183216</v>
       </c>
       <c r="I293" s="7">
-        <v>0.560135</v>
+        <v>0.566498</v>
       </c>
       <c r="J293" s="7">
-        <v>2.532714</v>
+        <v>2.5538730000000003</v>
       </c>
       <c r="K293" s="7">
-        <v>6.355659</v>
+        <v>6.391088</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12306,25 +12306,25 @@
         <v>5</v>
       </c>
       <c r="E294" s="7">
-        <v>0.10770300000000001</v>
+        <v>0.110354</v>
       </c>
       <c r="F294" s="7">
-        <v>0.096738</v>
+        <v>0.114953</v>
       </c>
       <c r="G294" s="7">
-        <v>0.267075</v>
+        <v>0.286143</v>
       </c>
       <c r="H294" s="7">
-        <v>0.20646899999999999</v>
+        <v>0.22655</v>
       </c>
       <c r="I294" s="7">
-        <v>0.530155</v>
+        <v>0.556766</v>
       </c>
       <c r="J294" s="7">
-        <v>2.934214</v>
+        <v>2.999696</v>
       </c>
       <c r="K294" s="7">
-        <v>8.55754</v>
+        <v>8.701284000000001</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12341,25 +12341,25 @@
         <v>4</v>
       </c>
       <c r="E295" s="7">
-        <v>0.04647300000000001</v>
+        <v>0.050308</v>
       </c>
       <c r="F295" s="7">
-        <v>0.072479</v>
+        <v>0.078512</v>
       </c>
       <c r="G295" s="7">
-        <v>0.236007</v>
+        <v>0.24079</v>
       </c>
       <c r="H295" s="7">
-        <v>0.13098</v>
+        <v>0.137754</v>
       </c>
       <c r="I295" s="7">
-        <v>0.42115699999999995</v>
+        <v>0.425911</v>
       </c>
       <c r="J295" s="7">
-        <v>1.4799350000000002</v>
+        <v>1.4947890000000001</v>
       </c>
       <c r="K295" s="7">
-        <v>4.15914</v>
+        <v>4.18463</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12376,25 +12376,25 @@
         <v>4</v>
       </c>
       <c r="E296" s="7">
-        <v>0.024939</v>
+        <v>0.031248</v>
       </c>
       <c r="F296" s="7">
-        <v>0.010079</v>
+        <v>0.01876</v>
       </c>
       <c r="G296" s="7">
-        <v>0.18735800000000002</v>
+        <v>0.195038</v>
       </c>
       <c r="H296" s="7">
-        <v>0.048079000000000004</v>
+        <v>0.057945</v>
       </c>
       <c r="I296" s="7">
-        <v>0.38474800000000003</v>
+        <v>0.396566</v>
       </c>
       <c r="J296" s="7">
-        <v>1.7196520000000002</v>
+        <v>1.745253</v>
       </c>
       <c r="K296" s="7">
-        <v>4.7921510000000005</v>
+        <v>4.836033</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12411,25 +12411,25 @@
         <v>6</v>
       </c>
       <c r="E297" s="7">
-        <v>0.100098</v>
+        <v>0.114252</v>
       </c>
       <c r="F297" s="7">
-        <v>0.074051</v>
+        <v>0.10299799999999999</v>
       </c>
       <c r="G297" s="7">
-        <v>0.313731</v>
+        <v>0.33903700000000003</v>
       </c>
       <c r="H297" s="7">
-        <v>0.256487</v>
+        <v>0.291128</v>
       </c>
       <c r="I297" s="7">
-        <v>0.5930599999999999</v>
+        <v>0.628564</v>
       </c>
       <c r="J297" s="7">
-        <v>3.805347</v>
+        <v>3.937829</v>
       </c>
       <c r="K297" s="7">
-        <v>15.680952999999999</v>
+        <v>16.021406</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12446,25 +12446,25 @@
         <v>5</v>
       </c>
       <c r="E298" s="7">
-        <v>0.09075699999999999</v>
+        <v>0.10334199999999999</v>
       </c>
       <c r="F298" s="7">
-        <v>0.09324</v>
+        <v>0.11285500000000001</v>
       </c>
       <c r="G298" s="7">
-        <v>0.32663200000000003</v>
+        <v>0.342963</v>
       </c>
       <c r="H298" s="7">
-        <v>0.26925899999999997</v>
+        <v>0.294672</v>
       </c>
       <c r="I298" s="7">
-        <v>0.600638</v>
+        <v>0.622385</v>
       </c>
       <c r="J298" s="7">
-        <v>3.401214</v>
+        <v>3.489334</v>
       </c>
       <c r="K298" s="7">
-        <v>10.839199</v>
+        <v>11.014778</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12481,25 +12481,25 @@
         <v>4</v>
       </c>
       <c r="E299" s="7">
-        <v>0.078489</v>
+        <v>0.08931599999999999</v>
       </c>
       <c r="F299" s="7">
-        <v>0.083041</v>
+        <v>0.097381</v>
       </c>
       <c r="G299" s="7">
-        <v>0.302682</v>
+        <v>0.318192</v>
       </c>
       <c r="H299" s="7">
-        <v>0.232418</v>
+        <v>0.252975</v>
       </c>
       <c r="I299" s="7">
-        <v>0.593373</v>
+        <v>0.61535</v>
       </c>
       <c r="J299" s="7">
-        <v>3.3843490000000003</v>
+        <v>3.45748</v>
       </c>
       <c r="K299" s="7">
-        <v>9.76414</v>
+        <v>9.904007</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12516,25 +12516,25 @@
         <v>2</v>
       </c>
       <c r="E300" s="7">
-        <v>0.037528</v>
+        <v>0.042106000000000005</v>
       </c>
       <c r="F300" s="7">
-        <v>0.09056499999999999</v>
+        <v>0.09559200000000001</v>
       </c>
       <c r="G300" s="7">
-        <v>0.218316</v>
+        <v>0.22456399999999999</v>
       </c>
       <c r="H300" s="7">
-        <v>0.143986</v>
+        <v>0.151995</v>
       </c>
       <c r="I300" s="7">
-        <v>0.512115</v>
+        <v>0.519742</v>
       </c>
       <c r="J300" s="7">
-        <v>2.8200580000000004</v>
+        <v>2.8468009999999997</v>
       </c>
       <c r="K300" s="7">
-        <v>5.120229</v>
+        <v>5.159663</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12551,25 +12551,25 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.097651</v>
+        <v>0.100377</v>
       </c>
       <c r="F301" s="7">
-        <v>0.120686</v>
+        <v>0.135327</v>
       </c>
       <c r="G301" s="7">
-        <v>0.350953</v>
+        <v>0.362774</v>
       </c>
       <c r="H301" s="7">
-        <v>0.281255</v>
+        <v>0.297616</v>
       </c>
       <c r="I301" s="7">
-        <v>0.674032</v>
+        <v>0.6898449999999999</v>
       </c>
       <c r="J301" s="7">
-        <v>3.31069</v>
+        <v>3.365736</v>
       </c>
       <c r="K301" s="7">
-        <v>9.816108</v>
+        <v>9.940897999999999</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12586,25 +12586,25 @@
         <v>6</v>
       </c>
       <c r="E302" s="7">
-        <v>0.10796900000000001</v>
+        <v>0.111167</v>
       </c>
       <c r="F302" s="7">
-        <v>0.121769</v>
+        <v>0.138531</v>
       </c>
       <c r="G302" s="7">
-        <v>0.367241</v>
+        <v>0.38264899999999996</v>
       </c>
       <c r="H302" s="7">
-        <v>0.299705</v>
+        <v>0.32051699999999994</v>
       </c>
       <c r="I302" s="7">
-        <v>0.730283</v>
+        <v>0.751511</v>
       </c>
       <c r="J302" s="7">
-        <v>3.584649</v>
+        <v>3.6580630000000003</v>
       </c>
       <c r="K302" s="7">
-        <v>12.503267000000001</v>
+        <v>12.695706</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -12621,25 +12621,25 @@
         <v>6</v>
       </c>
       <c r="E303" s="7">
-        <v>0.108154</v>
+        <v>0.109762</v>
       </c>
       <c r="F303" s="7">
-        <v>0.13264099999999998</v>
+        <v>0.150124</v>
       </c>
       <c r="G303" s="7">
-        <v>0.309008</v>
+        <v>0.326406</v>
       </c>
       <c r="H303" s="7">
-        <v>0.294877</v>
+        <v>0.313869</v>
       </c>
       <c r="I303" s="7">
-        <v>0.594932</v>
+        <v>0.611042</v>
       </c>
       <c r="J303" s="7">
-        <v>2.393319</v>
+        <v>2.443091</v>
       </c>
       <c r="K303" s="7">
-        <v>8.741081000000001</v>
+        <v>8.85469</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12656,22 +12656,22 @@
         <v>4</v>
       </c>
       <c r="E304" s="7">
-        <v>0.215551</v>
+        <v>0.213252</v>
       </c>
       <c r="F304" s="7">
-        <v>0.260899</v>
+        <v>0.279241</v>
       </c>
       <c r="G304" s="7">
-        <v>0.303019</v>
+        <v>0.315297</v>
       </c>
       <c r="H304" s="7">
-        <v>0.289053</v>
+        <v>0.307369</v>
       </c>
       <c r="I304" s="7">
-        <v>0.718348</v>
+        <v>0.742616</v>
       </c>
       <c r="J304" s="7">
-        <v>3.857634</v>
+        <v>3.9266579999999998</v>
       </c>
       <c r="K304" s="7"/>
     </row>
@@ -12689,25 +12689,25 @@
         <v>5</v>
       </c>
       <c r="E305" s="7">
-        <v>0.099633</v>
+        <v>0.11303800000000001</v>
       </c>
       <c r="F305" s="7">
-        <v>0.070243</v>
+        <v>0.093405</v>
       </c>
       <c r="G305" s="7">
-        <v>0.266726</v>
+        <v>0.28034</v>
       </c>
       <c r="H305" s="7">
-        <v>0.191507</v>
+        <v>0.21762399999999998</v>
       </c>
       <c r="I305" s="7">
-        <v>0.514605</v>
+        <v>0.550702</v>
       </c>
       <c r="J305" s="7">
-        <v>2.7847750000000002</v>
+        <v>2.867733</v>
       </c>
       <c r="K305" s="7">
-        <v>11.531183</v>
+        <v>11.71203</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12724,25 +12724,25 @@
         <v>6</v>
       </c>
       <c r="E306" s="7">
-        <v>0.025464</v>
+        <v>0.025903</v>
       </c>
       <c r="F306" s="7">
-        <v>0.036509</v>
+        <v>0.038618</v>
       </c>
       <c r="G306" s="7">
-        <v>0.081362</v>
+        <v>0.08402799999999999</v>
       </c>
       <c r="H306" s="7">
-        <v>0.05207</v>
+        <v>0.054692</v>
       </c>
       <c r="I306" s="7">
-        <v>0.23257000000000003</v>
+        <v>0.23392700000000002</v>
       </c>
       <c r="J306" s="7">
-        <v>1.812325</v>
+        <v>1.819333</v>
       </c>
       <c r="K306" s="7">
-        <v>5.5412609999999995</v>
+        <v>5.550428</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12759,25 +12759,25 @@
         <v>6</v>
       </c>
       <c r="E307" s="7">
-        <v>0.042871</v>
+        <v>0.059409000000000003</v>
       </c>
       <c r="F307" s="7">
-        <v>0.020081</v>
+        <v>0.044664999999999996</v>
       </c>
       <c r="G307" s="7">
-        <v>0.170499</v>
+        <v>0.192555</v>
       </c>
       <c r="H307" s="7">
-        <v>0.079567</v>
+        <v>0.103394</v>
       </c>
       <c r="I307" s="7">
-        <v>0.491582</v>
+        <v>0.511564</v>
       </c>
       <c r="J307" s="7">
-        <v>2.426763</v>
+        <v>2.502394</v>
       </c>
       <c r="K307" s="7">
-        <v>7.54046</v>
+        <v>7.687136000000001</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -12794,25 +12794,25 @@
         <v>3</v>
       </c>
       <c r="E308" s="7">
-        <v>0.041146</v>
+        <v>0.044941</v>
       </c>
       <c r="F308" s="7">
-        <v>0.088842</v>
+        <v>0.090657</v>
       </c>
       <c r="G308" s="7">
-        <v>0.21437699999999998</v>
+        <v>0.21851199999999998</v>
       </c>
       <c r="H308" s="7">
-        <v>0.149336</v>
+        <v>0.15454700000000002</v>
       </c>
       <c r="I308" s="7">
-        <v>0.468115</v>
+        <v>0.46996099999999996</v>
       </c>
       <c r="J308" s="7">
-        <v>2.013163</v>
+        <v>2.026825</v>
       </c>
       <c r="K308" s="7">
-        <v>5.273045</v>
+        <v>5.307449</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -12829,25 +12829,25 @@
         <v>3</v>
       </c>
       <c r="E309" s="7">
-        <v>0.02237</v>
+        <v>0.029824000000000003</v>
       </c>
       <c r="F309" s="7">
-        <v>0.018469</v>
+        <v>0.022835</v>
       </c>
       <c r="G309" s="7">
-        <v>0.137462</v>
+        <v>0.145131</v>
       </c>
       <c r="H309" s="7">
-        <v>0.036069</v>
+        <v>0.041835000000000004</v>
       </c>
       <c r="I309" s="7">
-        <v>0.380385</v>
+        <v>0.387007</v>
       </c>
       <c r="J309" s="7">
-        <v>0.9997469999999999</v>
+        <v>1.0108759999999999</v>
       </c>
       <c r="K309" s="7">
-        <v>2.1183199999999998</v>
+        <v>2.127655</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>11.05.2026 18:27:04</t>
+    <t>12.05.2026 14:58:21</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -1066,7 +1066,7 @@
     <t>GEA</t>
   </si>
   <si>
-    <t>GARANTİ EMEKLİLİK VE HAYAT A.Ş. KATILIM DEĞİŞKEN EMEKLİLİK YATIRIM FONU</t>
+    <t>GARANTİ EMEKLİLİK VE HAYAT A.Ş. KATILIM HİSSE SENEDİ EMEKLİLİK YATIRIM FONU</t>
   </si>
   <si>
     <t>GED</t>
@@ -1405,7 +1405,7 @@
     <t>KFE</t>
   </si>
   <si>
-    <t>KATILIM EMEKLİLİK VE HAYAT A.Ş. KATILIM FON SEPETİ EMEKLİLİK YATIRIM FONU</t>
+    <t>KATILIM EMEKLİLİK VE HAYAT A.Ş. KUVEYT TÜRK KATILIM FON SEPETİ EMEKLİLİK YATIRIM FONU</t>
   </si>
   <si>
     <t>KGC</t>
@@ -2484,25 +2484,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.025527</v>
+        <v>0.024266</v>
       </c>
       <c r="F6" s="7">
-        <v>0.05579100000000001</v>
+        <v>0.054698000000000004</v>
       </c>
       <c r="G6" s="7">
-        <v>0.219388</v>
+        <v>0.221985</v>
       </c>
       <c r="H6" s="7">
-        <v>0.127009</v>
+        <v>0.125623</v>
       </c>
       <c r="I6" s="7">
-        <v>0.46307200000000004</v>
+        <v>0.461273</v>
       </c>
       <c r="J6" s="7">
-        <v>2.294956</v>
+        <v>2.253335</v>
       </c>
       <c r="K6" s="7">
-        <v>5.788498</v>
+        <v>5.782380000000001</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2519,25 +2519,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.08716499999999999</v>
+        <v>0.092752</v>
       </c>
       <c r="F7" s="7">
-        <v>0.08852399999999999</v>
+        <v>0.09267099999999999</v>
       </c>
       <c r="G7" s="7">
-        <v>0.167851</v>
+        <v>0.168655</v>
       </c>
       <c r="H7" s="7">
-        <v>0.125425</v>
+        <v>0.13120900000000002</v>
       </c>
       <c r="I7" s="7">
-        <v>0.513127</v>
+        <v>0.520904</v>
       </c>
       <c r="J7" s="7">
-        <v>2.917787</v>
+        <v>2.937361</v>
       </c>
       <c r="K7" s="7">
-        <v>5.6251</v>
+        <v>5.729076</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2554,25 +2554,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.016182000000000002</v>
+        <v>0.012994</v>
       </c>
       <c r="F8" s="7">
-        <v>0.026886</v>
+        <v>0.02726</v>
       </c>
       <c r="G8" s="7">
-        <v>0.16385100000000002</v>
+        <v>0.161269</v>
       </c>
       <c r="H8" s="7">
-        <v>0.067094</v>
+        <v>0.063746</v>
       </c>
       <c r="I8" s="7">
-        <v>0.403559</v>
+        <v>0.39915500000000004</v>
       </c>
       <c r="J8" s="7">
-        <v>1.815605</v>
+        <v>1.804532</v>
       </c>
       <c r="K8" s="7">
-        <v>3.612737</v>
+        <v>3.597073</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2589,25 +2589,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.061913</v>
+        <v>0.064585</v>
       </c>
       <c r="F9" s="7">
-        <v>0.09478400000000001</v>
+        <v>0.091173</v>
       </c>
       <c r="G9" s="7">
-        <v>0.352372</v>
+        <v>0.371498</v>
       </c>
       <c r="H9" s="7">
-        <v>0.29344000000000003</v>
+        <v>0.296695</v>
       </c>
       <c r="I9" s="7">
-        <v>0.575213</v>
+        <v>0.579177</v>
       </c>
       <c r="J9" s="7">
-        <v>3.254397</v>
+        <v>3.055917</v>
       </c>
       <c r="K9" s="7">
-        <v>10.545166</v>
+        <v>10.621160999999999</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2624,25 +2624,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.009007</v>
+        <v>-0.015244</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.084011</v>
+        <v>-0.09185</v>
       </c>
       <c r="G10" s="7">
-        <v>0.145247</v>
+        <v>0.125101</v>
       </c>
       <c r="H10" s="7">
-        <v>0.057952000000000004</v>
+        <v>0.051294000000000006</v>
       </c>
       <c r="I10" s="7">
-        <v>0.5408120000000001</v>
+        <v>0.531115</v>
       </c>
       <c r="J10" s="7">
-        <v>4.00853</v>
+        <v>4.019864999999999</v>
       </c>
       <c r="K10" s="7">
-        <v>13.387147</v>
+        <v>13.22982</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2659,25 +2659,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.069909</v>
+        <v>0.075911</v>
       </c>
       <c r="F11" s="7">
-        <v>0.11482799999999999</v>
+        <v>0.112996</v>
       </c>
       <c r="G11" s="7">
-        <v>0.412746</v>
+        <v>0.44459000000000004</v>
       </c>
       <c r="H11" s="7">
-        <v>0.347856</v>
+        <v>0.355417</v>
       </c>
       <c r="I11" s="7">
-        <v>0.637471</v>
+        <v>0.6466580000000001</v>
       </c>
       <c r="J11" s="7">
-        <v>2.886422</v>
+        <v>2.621531</v>
       </c>
       <c r="K11" s="7">
-        <v>12.883773000000001</v>
+        <v>13.061630000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2694,25 +2694,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.033885</v>
+        <v>0.035976</v>
       </c>
       <c r="F12" s="7">
-        <v>0.08348900000000001</v>
+        <v>0.084683</v>
       </c>
       <c r="G12" s="7">
-        <v>0.25949500000000003</v>
+        <v>0.265534</v>
       </c>
       <c r="H12" s="7">
-        <v>0.164877</v>
+        <v>0.167232</v>
       </c>
       <c r="I12" s="7">
-        <v>0.49608199999999997</v>
+        <v>0.49910699999999997</v>
       </c>
       <c r="J12" s="7">
-        <v>2.709203</v>
+        <v>2.6203149999999997</v>
       </c>
       <c r="K12" s="7">
-        <v>4.592442</v>
+        <v>4.602686</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2729,25 +2729,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.059613</v>
+        <v>0.05862</v>
       </c>
       <c r="F13" s="7">
-        <v>0.10535800000000001</v>
+        <v>0.09661199999999999</v>
       </c>
       <c r="G13" s="7">
-        <v>0.440379</v>
+        <v>0.46814300000000003</v>
       </c>
       <c r="H13" s="7">
-        <v>0.34274099999999996</v>
+        <v>0.341483</v>
       </c>
       <c r="I13" s="7">
-        <v>0.637326</v>
+        <v>0.635792</v>
       </c>
       <c r="J13" s="7">
-        <v>3.0532190000000003</v>
+        <v>2.729246</v>
       </c>
       <c r="K13" s="7">
-        <v>10.548348</v>
+        <v>10.639487999999998</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2764,25 +2764,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.034543</v>
+        <v>0.035168</v>
       </c>
       <c r="F14" s="7">
-        <v>0.045555000000000005</v>
+        <v>0.043868</v>
       </c>
       <c r="G14" s="7">
-        <v>0.290076</v>
+        <v>0.296931</v>
       </c>
       <c r="H14" s="7">
-        <v>0.21060099999999998</v>
+        <v>0.211333</v>
       </c>
       <c r="I14" s="7">
-        <v>0.48747399999999996</v>
+        <v>0.488373</v>
       </c>
       <c r="J14" s="7">
-        <v>2.735333</v>
+        <v>2.6203570000000003</v>
       </c>
       <c r="K14" s="7">
-        <v>8.135037</v>
+        <v>8.15247</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2799,25 +2799,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.018872</v>
+        <v>0.01761</v>
       </c>
       <c r="F15" s="7">
-        <v>0.037807</v>
+        <v>0.037605</v>
       </c>
       <c r="G15" s="7">
-        <v>0.201268</v>
+        <v>0.203049</v>
       </c>
       <c r="H15" s="7">
-        <v>0.098424</v>
+        <v>0.097064</v>
       </c>
       <c r="I15" s="7">
-        <v>0.422167</v>
+        <v>0.420406</v>
       </c>
       <c r="J15" s="7">
-        <v>2.072583</v>
+        <v>2.025261</v>
       </c>
       <c r="K15" s="7">
-        <v>5.596206</v>
+        <v>5.594113</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2834,25 +2834,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.030022000000000004</v>
+        <v>0.030623</v>
       </c>
       <c r="F16" s="7">
-        <v>0.09485099999999999</v>
+        <v>0.095273</v>
       </c>
       <c r="G16" s="7">
-        <v>0.228443</v>
+        <v>0.230258</v>
       </c>
       <c r="H16" s="7">
-        <v>0.15581799999999998</v>
+        <v>0.156493</v>
       </c>
       <c r="I16" s="7">
-        <v>0.512534</v>
+        <v>0.513418</v>
       </c>
       <c r="J16" s="7">
-        <v>2.8159620000000003</v>
+        <v>2.822895</v>
       </c>
       <c r="K16" s="7">
-        <v>5.117535</v>
+        <v>5.118469999999999</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2869,25 +2869,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.0304</v>
+        <v>0.031924</v>
       </c>
       <c r="F17" s="7">
-        <v>0.082347</v>
+        <v>0.082104</v>
       </c>
       <c r="G17" s="7">
-        <v>0.206294</v>
+        <v>0.208819</v>
       </c>
       <c r="H17" s="7">
-        <v>0.147926</v>
+        <v>0.149624</v>
       </c>
       <c r="I17" s="7">
-        <v>0.42148</v>
+        <v>0.42358199999999996</v>
       </c>
       <c r="J17" s="7">
-        <v>1.761373</v>
+        <v>1.7637639999999999</v>
       </c>
       <c r="K17" s="7">
-        <v>4.571681</v>
+        <v>4.585843</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2904,25 +2904,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.001109</v>
+        <v>-0.006449</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.066673</v>
+        <v>-0.073079</v>
       </c>
       <c r="G18" s="7">
-        <v>0.19709800000000002</v>
+        <v>0.174128</v>
       </c>
       <c r="H18" s="7">
-        <v>0.083096</v>
+        <v>0.077307</v>
       </c>
       <c r="I18" s="7">
-        <v>0.63662</v>
+        <v>0.627872</v>
       </c>
       <c r="J18" s="7">
-        <v>4.7637540000000005</v>
+        <v>4.787192999999999</v>
       </c>
       <c r="K18" s="7">
-        <v>15.666475</v>
+        <v>15.50221</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2939,25 +2939,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.051714</v>
+        <v>0.056907</v>
       </c>
       <c r="F19" s="7">
-        <v>0.078833</v>
+        <v>0.076278</v>
       </c>
       <c r="G19" s="7">
-        <v>0.25573599999999996</v>
+        <v>0.29319</v>
       </c>
       <c r="H19" s="7">
-        <v>0.15917199999999998</v>
+        <v>0.164896</v>
       </c>
       <c r="I19" s="7">
-        <v>0.47238199999999997</v>
+        <v>0.479652</v>
       </c>
       <c r="J19" s="7">
-        <v>2.469237</v>
+        <v>2.334353</v>
       </c>
       <c r="K19" s="7">
-        <v>7.105478000000001</v>
+        <v>7.182127</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2974,25 +2974,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.037341</v>
+        <v>0.040359</v>
       </c>
       <c r="F20" s="7">
-        <v>0.102277</v>
+        <v>0.103743</v>
       </c>
       <c r="G20" s="7">
-        <v>0.258642</v>
+        <v>0.265492</v>
       </c>
       <c r="H20" s="7">
-        <v>0.115246</v>
+        <v>0.11849</v>
       </c>
       <c r="I20" s="7">
-        <v>0.470616</v>
+        <v>0.47489400000000004</v>
       </c>
       <c r="J20" s="7">
-        <v>1.597461</v>
+        <v>1.5866280000000001</v>
       </c>
       <c r="K20" s="7">
-        <v>4.240267</v>
+        <v>4.267817</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3009,25 +3009,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.030687000000000002</v>
+        <v>0.035992</v>
       </c>
       <c r="F21" s="7">
-        <v>0.101001</v>
+        <v>0.10423600000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.224528</v>
+        <v>0.236601</v>
       </c>
       <c r="H21" s="7">
-        <v>0.168675</v>
+        <v>0.174691</v>
       </c>
       <c r="I21" s="7">
-        <v>0.449922</v>
+        <v>0.45738500000000004</v>
       </c>
       <c r="J21" s="7">
-        <v>2.002548</v>
+        <v>2.021675</v>
       </c>
       <c r="K21" s="7">
-        <v>5.0554689999999995</v>
+        <v>5.10159</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3044,25 +3044,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.085165</v>
+        <v>0.092874</v>
       </c>
       <c r="F22" s="7">
-        <v>0.144212</v>
+        <v>0.147901</v>
       </c>
       <c r="G22" s="7">
-        <v>0.35579700000000003</v>
+        <v>0.393491</v>
       </c>
       <c r="H22" s="7">
-        <v>0.32480800000000004</v>
+        <v>0.334219</v>
       </c>
       <c r="I22" s="7">
-        <v>0.630531</v>
+        <v>0.642114</v>
       </c>
       <c r="J22" s="7">
-        <v>3.257133</v>
+        <v>3.073668</v>
       </c>
       <c r="K22" s="7">
-        <v>11.028694</v>
+        <v>11.200405</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3079,25 +3079,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.027259000000000002</v>
+        <v>0.028805</v>
       </c>
       <c r="F23" s="7">
-        <v>0.081987</v>
+        <v>0.082155</v>
       </c>
       <c r="G23" s="7">
-        <v>0.185348</v>
+        <v>0.186366</v>
       </c>
       <c r="H23" s="7">
-        <v>0.13065300000000002</v>
+        <v>0.132354</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40469900000000003</v>
+        <v>0.40681199999999995</v>
       </c>
       <c r="J23" s="7">
-        <v>2.27372</v>
+        <v>2.299252</v>
       </c>
       <c r="K23" s="7">
-        <v>5.016479</v>
+        <v>5.0195940000000006</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3114,25 +3114,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.017888</v>
+        <v>0.014521</v>
       </c>
       <c r="F24" s="7">
-        <v>0.027089</v>
+        <v>0.026793</v>
       </c>
       <c r="G24" s="7">
-        <v>0.156519</v>
+        <v>0.153564</v>
       </c>
       <c r="H24" s="7">
-        <v>0.05483</v>
+        <v>0.051341</v>
       </c>
       <c r="I24" s="7">
-        <v>0.39255</v>
+        <v>0.387944</v>
       </c>
       <c r="J24" s="7">
-        <v>1.635206</v>
+        <v>1.628345</v>
       </c>
       <c r="K24" s="7">
-        <v>3.4761</v>
+        <v>3.46025</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3149,25 +3149,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.018702</v>
+        <v>0.020451999999999998</v>
       </c>
       <c r="F25" s="7">
-        <v>0.036392</v>
+        <v>0.036497</v>
       </c>
       <c r="G25" s="7">
-        <v>0.12925599999999998</v>
+        <v>0.132432</v>
       </c>
       <c r="H25" s="7">
-        <v>0.065651</v>
+        <v>0.067482</v>
       </c>
       <c r="I25" s="7">
-        <v>0.344385</v>
+        <v>0.346695</v>
       </c>
       <c r="J25" s="7">
-        <v>2.1247190000000002</v>
+        <v>2.056578</v>
       </c>
       <c r="K25" s="7">
-        <v>6.395269</v>
+        <v>6.387944</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3184,25 +3184,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.018266</v>
+        <v>0.020691</v>
       </c>
       <c r="F26" s="7">
-        <v>0.024263</v>
+        <v>0.025266</v>
       </c>
       <c r="G26" s="7">
-        <v>0.12663</v>
+        <v>0.129547</v>
       </c>
       <c r="H26" s="7">
-        <v>0.065178</v>
+        <v>0.067715</v>
       </c>
       <c r="I26" s="7">
-        <v>0.31816700000000003</v>
+        <v>0.32130600000000004</v>
       </c>
       <c r="J26" s="7">
-        <v>2.114494</v>
+        <v>2.102598</v>
       </c>
       <c r="K26" s="7">
-        <v>5.6092830000000005</v>
+        <v>5.597390000000001</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3219,25 +3219,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.03381</v>
+        <v>0.038748</v>
       </c>
       <c r="F27" s="7">
-        <v>0.036779</v>
+        <v>0.037157</v>
       </c>
       <c r="G27" s="7">
-        <v>0.279906</v>
+        <v>0.308765</v>
       </c>
       <c r="H27" s="7">
-        <v>0.241862</v>
+        <v>0.247794</v>
       </c>
       <c r="I27" s="7">
-        <v>0.45478999999999997</v>
+        <v>0.461738</v>
       </c>
       <c r="J27" s="7">
-        <v>3.429794</v>
+        <v>3.11976</v>
       </c>
       <c r="K27" s="7">
-        <v>16.250398</v>
+        <v>16.474303</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3254,25 +3254,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.06922299999999999</v>
+        <v>0.069786</v>
       </c>
       <c r="F28" s="7">
-        <v>0.069542</v>
+        <v>0.068456</v>
       </c>
       <c r="G28" s="7">
-        <v>0.17367100000000002</v>
+        <v>0.17878699999999997</v>
       </c>
       <c r="H28" s="7">
-        <v>0.138278</v>
+        <v>0.138878</v>
       </c>
       <c r="I28" s="7">
-        <v>0.439018</v>
+        <v>0.439776</v>
       </c>
       <c r="J28" s="7">
-        <v>2.669966</v>
+        <v>2.578481</v>
       </c>
       <c r="K28" s="7">
-        <v>8.041376</v>
+        <v>8.110295</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3289,25 +3289,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.022012999999999998</v>
+        <v>0.022071</v>
       </c>
       <c r="F29" s="7">
-        <v>0.055084999999999995</v>
+        <v>0.054762000000000005</v>
       </c>
       <c r="G29" s="7">
-        <v>0.177638</v>
+        <v>0.180792</v>
       </c>
       <c r="H29" s="7">
-        <v>0.113093</v>
+        <v>0.11315599999999999</v>
       </c>
       <c r="I29" s="7">
-        <v>0.41005899999999995</v>
+        <v>0.41013800000000006</v>
       </c>
       <c r="J29" s="7">
-        <v>2.436242</v>
+        <v>2.402888</v>
       </c>
       <c r="K29" s="7">
-        <v>4.619006</v>
+        <v>4.621093</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3324,25 +3324,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.030171999999999997</v>
+        <v>0.034523</v>
       </c>
       <c r="F30" s="7">
-        <v>0.037674</v>
+        <v>0.040606</v>
       </c>
       <c r="G30" s="7">
-        <v>0.216811</v>
+        <v>0.233841</v>
       </c>
       <c r="H30" s="7">
-        <v>0.180141</v>
+        <v>0.18512599999999999</v>
       </c>
       <c r="I30" s="7">
-        <v>0.41293599999999997</v>
+        <v>0.418905</v>
       </c>
       <c r="J30" s="7">
-        <v>3.144979</v>
+        <v>2.969637</v>
       </c>
       <c r="K30" s="7">
-        <v>9.611923</v>
+        <v>9.687834</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3359,25 +3359,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.073878</v>
+        <v>0.073411</v>
       </c>
       <c r="F31" s="7">
-        <v>0.064028</v>
+        <v>0.057301000000000005</v>
       </c>
       <c r="G31" s="7">
-        <v>0.331624</v>
+        <v>0.360894</v>
       </c>
       <c r="H31" s="7">
-        <v>0.27142499999999997</v>
+        <v>0.270871</v>
       </c>
       <c r="I31" s="7">
-        <v>0.429105</v>
+        <v>0.428482</v>
       </c>
       <c r="J31" s="7">
-        <v>2.8270229999999996</v>
+        <v>2.528322</v>
       </c>
       <c r="K31" s="7">
-        <v>14.780989</v>
+        <v>14.92108</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3394,25 +3394,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.027987</v>
+        <v>0.029068</v>
       </c>
       <c r="F32" s="7">
-        <v>0.085264</v>
+        <v>0.08570499999999999</v>
       </c>
       <c r="G32" s="7">
-        <v>0.194751</v>
+        <v>0.196083</v>
       </c>
       <c r="H32" s="7">
-        <v>0.127113</v>
+        <v>0.128298</v>
       </c>
       <c r="I32" s="7">
-        <v>0.44742600000000005</v>
+        <v>0.44894799999999996</v>
       </c>
       <c r="J32" s="7">
-        <v>2.1700720000000002</v>
+        <v>2.168202</v>
       </c>
       <c r="K32" s="7">
-        <v>3.75666</v>
+        <v>3.759591</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3429,25 +3429,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.022358</v>
+        <v>0.02659</v>
       </c>
       <c r="F33" s="7">
-        <v>0.040233</v>
+        <v>0.038903</v>
       </c>
       <c r="G33" s="7">
-        <v>0.27842500000000003</v>
+        <v>0.307811</v>
       </c>
       <c r="H33" s="7">
-        <v>0.212683</v>
+        <v>0.21770299999999998</v>
       </c>
       <c r="I33" s="7">
-        <v>0.46638199999999996</v>
+        <v>0.472453</v>
       </c>
       <c r="J33" s="7">
-        <v>3.666707</v>
+        <v>3.373531</v>
       </c>
       <c r="K33" s="7">
-        <v>16.527147</v>
+        <v>16.692591</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3464,25 +3464,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.076264</v>
+        <v>0.082126</v>
       </c>
       <c r="F34" s="7">
-        <v>0.13715</v>
+        <v>0.139096</v>
       </c>
       <c r="G34" s="7">
-        <v>0.39482799999999996</v>
+        <v>0.417132</v>
       </c>
       <c r="H34" s="7">
-        <v>0.317925</v>
+        <v>0.32510300000000003</v>
       </c>
       <c r="I34" s="7">
-        <v>0.672307</v>
+        <v>0.6814149999999999</v>
       </c>
       <c r="J34" s="7">
-        <v>3.440549</v>
+        <v>3.288814</v>
       </c>
       <c r="K34" s="7">
-        <v>9.996789999999999</v>
+        <v>10.089505</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3499,25 +3499,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.08002100000000001</v>
+        <v>0.090293</v>
       </c>
       <c r="F35" s="7">
-        <v>0.136702</v>
+        <v>0.141492</v>
       </c>
       <c r="G35" s="7">
-        <v>0.41804</v>
+        <v>0.449994</v>
       </c>
       <c r="H35" s="7">
-        <v>0.33645</v>
+        <v>0.349161</v>
       </c>
       <c r="I35" s="7">
-        <v>0.7376510000000001</v>
+        <v>0.754179</v>
       </c>
       <c r="J35" s="7">
-        <v>3.736018</v>
+        <v>3.5433229999999996</v>
       </c>
       <c r="K35" s="7">
-        <v>12.62594</v>
+        <v>12.8122</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3534,25 +3534,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.018068</v>
+        <v>0.023979</v>
       </c>
       <c r="F36" s="7">
-        <v>0.041550000000000004</v>
+        <v>0.041906</v>
       </c>
       <c r="G36" s="7">
-        <v>0.286963</v>
+        <v>0.318819</v>
       </c>
       <c r="H36" s="7">
-        <v>0.222837</v>
+        <v>0.229936</v>
       </c>
       <c r="I36" s="7">
-        <v>0.484121</v>
+        <v>0.492738</v>
       </c>
       <c r="J36" s="7">
-        <v>3.729572</v>
+        <v>3.456399</v>
       </c>
       <c r="K36" s="7">
-        <v>17.074655</v>
+        <v>17.256230000000002</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3569,25 +3569,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.018487</v>
+        <v>0.024829</v>
       </c>
       <c r="F37" s="7">
-        <v>0.046993</v>
+        <v>0.048251999999999996</v>
       </c>
       <c r="G37" s="7">
-        <v>0.289977</v>
+        <v>0.315734</v>
       </c>
       <c r="H37" s="7">
-        <v>0.20379999999999998</v>
+        <v>0.211296</v>
       </c>
       <c r="I37" s="7">
-        <v>0.489351</v>
+        <v>0.498625</v>
       </c>
       <c r="J37" s="7">
-        <v>3.7587360000000003</v>
+        <v>3.5429880000000002</v>
       </c>
       <c r="K37" s="7">
-        <v>15.60089</v>
+        <v>15.740662</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3604,25 +3604,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.017159</v>
+        <v>0.023085</v>
       </c>
       <c r="F38" s="7">
-        <v>0.040670000000000005</v>
+        <v>0.041990999999999994</v>
       </c>
       <c r="G38" s="7">
-        <v>0.249539</v>
+        <v>0.273574</v>
       </c>
       <c r="H38" s="7">
-        <v>0.17863700000000002</v>
+        <v>0.185503</v>
       </c>
       <c r="I38" s="7">
-        <v>0.475601</v>
+        <v>0.484198</v>
       </c>
       <c r="J38" s="7">
-        <v>3.61219</v>
+        <v>3.431429</v>
       </c>
       <c r="K38" s="7">
-        <v>11.605884000000001</v>
+        <v>11.720275999999998</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3639,25 +3639,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.023243</v>
+        <v>0.024412</v>
       </c>
       <c r="F39" s="7">
-        <v>0.06835</v>
+        <v>0.068414</v>
       </c>
       <c r="G39" s="7">
-        <v>0.201844</v>
+        <v>0.203814</v>
       </c>
       <c r="H39" s="7">
-        <v>0.136129</v>
+        <v>0.137428</v>
       </c>
       <c r="I39" s="7">
-        <v>0.467098</v>
+        <v>0.468774</v>
       </c>
       <c r="J39" s="7">
-        <v>3.002373</v>
+        <v>2.974692</v>
       </c>
       <c r="K39" s="7">
-        <v>5.7675</v>
+        <v>5.775232999999999</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3674,25 +3674,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.058522</v>
+        <v>0.067799</v>
       </c>
       <c r="F40" s="7">
-        <v>0.145483</v>
+        <v>0.15157299999999999</v>
       </c>
       <c r="G40" s="7">
-        <v>0.35379399999999994</v>
+        <v>0.384326</v>
       </c>
       <c r="H40" s="7">
-        <v>0.284267</v>
+        <v>0.295521</v>
       </c>
       <c r="I40" s="7">
-        <v>0.630465</v>
+        <v>0.644753</v>
       </c>
       <c r="J40" s="7">
-        <v>3.636914</v>
+        <v>3.4532220000000002</v>
       </c>
       <c r="K40" s="7">
-        <v>11.866934</v>
+        <v>12.027654</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3709,25 +3709,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.048773</v>
+        <v>0.055576999999999994</v>
       </c>
       <c r="F41" s="7">
-        <v>0.131596</v>
+        <v>0.134521</v>
       </c>
       <c r="G41" s="7">
-        <v>0.323911</v>
+        <v>0.34749899999999995</v>
       </c>
       <c r="H41" s="7">
-        <v>0.255596</v>
+        <v>0.263741</v>
       </c>
       <c r="I41" s="7">
-        <v>0.608066</v>
+        <v>0.618498</v>
       </c>
       <c r="J41" s="7">
-        <v>3.3547759999999998</v>
+        <v>3.230546</v>
       </c>
       <c r="K41" s="7">
-        <v>10.137296</v>
+        <v>10.234366999999999</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3744,25 +3744,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.063268</v>
+        <v>0.067206</v>
       </c>
       <c r="F42" s="7">
-        <v>0.10286300000000001</v>
+        <v>0.099899</v>
       </c>
       <c r="G42" s="7">
-        <v>0.36568399999999995</v>
+        <v>0.38886000000000004</v>
       </c>
       <c r="H42" s="7">
-        <v>0.297945</v>
+        <v>0.302752</v>
       </c>
       <c r="I42" s="7">
-        <v>0.590271</v>
+        <v>0.59616</v>
       </c>
       <c r="J42" s="7">
-        <v>3.292872</v>
+        <v>3.087359</v>
       </c>
       <c r="K42" s="7">
-        <v>10.956696999999998</v>
+        <v>11.047261</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3779,25 +3779,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.017224</v>
+        <v>0.026444000000000002</v>
       </c>
       <c r="F43" s="7">
-        <v>0.034034</v>
+        <v>0.037952</v>
       </c>
       <c r="G43" s="7">
-        <v>0.295641</v>
+        <v>0.331387</v>
       </c>
       <c r="H43" s="7">
-        <v>0.226701</v>
+        <v>0.237819</v>
       </c>
       <c r="I43" s="7">
-        <v>0.489863</v>
+        <v>0.503366</v>
       </c>
       <c r="J43" s="7">
-        <v>4.2050209999999995</v>
+        <v>3.9182420000000002</v>
       </c>
       <c r="K43" s="7">
-        <v>21.317332999999998</v>
+        <v>21.625495</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3814,25 +3814,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.031742</v>
+        <v>0.032006</v>
       </c>
       <c r="F44" s="7">
-        <v>0.072468</v>
+        <v>0.072882</v>
       </c>
       <c r="G44" s="7">
-        <v>0.20710599999999998</v>
+        <v>0.207493</v>
       </c>
       <c r="H44" s="7">
-        <v>0.134295</v>
+        <v>0.134585</v>
       </c>
       <c r="I44" s="7">
-        <v>0.479912</v>
+        <v>0.480291</v>
       </c>
       <c r="J44" s="7">
-        <v>2.499976</v>
+        <v>2.501036</v>
       </c>
       <c r="K44" s="7">
-        <v>4.5210930000000005</v>
+        <v>4.520045</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3849,25 +3849,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.053044</v>
+        <v>0.055888999999999994</v>
       </c>
       <c r="F45" s="7">
-        <v>0.092636</v>
+        <v>0.090931</v>
       </c>
       <c r="G45" s="7">
-        <v>0.332491</v>
+        <v>0.348044</v>
       </c>
       <c r="H45" s="7">
-        <v>0.25494900000000004</v>
+        <v>0.258338</v>
       </c>
       <c r="I45" s="7">
-        <v>0.594147</v>
+        <v>0.598452</v>
       </c>
       <c r="J45" s="7">
-        <v>3.3784460000000003</v>
+        <v>3.2016000000000004</v>
       </c>
       <c r="K45" s="7">
-        <v>9.653397</v>
+        <v>9.709204</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3884,25 +3884,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.04842</v>
+        <v>0.054336999999999996</v>
       </c>
       <c r="F46" s="7">
-        <v>0.13741899999999999</v>
+        <v>0.137554</v>
       </c>
       <c r="G46" s="7">
-        <v>0.34771599999999997</v>
+        <v>0.36875199999999997</v>
       </c>
       <c r="H46" s="7">
-        <v>0.292558</v>
+        <v>0.299852</v>
       </c>
       <c r="I46" s="7">
-        <v>0.629042</v>
+        <v>0.638235</v>
       </c>
       <c r="J46" s="7">
-        <v>3.800302</v>
+        <v>3.640339</v>
       </c>
       <c r="K46" s="7">
-        <v>10.418767</v>
+        <v>10.511775</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3919,25 +3919,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.066269</v>
+        <v>0.073204</v>
       </c>
       <c r="F47" s="7">
-        <v>0.139409</v>
+        <v>0.140255</v>
       </c>
       <c r="G47" s="7">
-        <v>0.36121200000000003</v>
+        <v>0.38698</v>
       </c>
       <c r="H47" s="7">
-        <v>0.302712</v>
+        <v>0.311185</v>
       </c>
       <c r="I47" s="7">
-        <v>0.627923</v>
+        <v>0.638511</v>
       </c>
       <c r="J47" s="7">
-        <v>3.85058</v>
+        <v>3.656672</v>
       </c>
       <c r="K47" s="7">
-        <v>13.307192</v>
+        <v>13.441878999999998</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3954,25 +3954,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>0.010456</v>
+        <v>0.009925</v>
       </c>
       <c r="F48" s="7">
-        <v>0.024657</v>
+        <v>0.017963</v>
       </c>
       <c r="G48" s="7">
-        <v>0.19499300000000003</v>
+        <v>0.21716100000000002</v>
       </c>
       <c r="H48" s="7">
-        <v>0.162952</v>
+        <v>0.162341</v>
       </c>
       <c r="I48" s="7">
-        <v>0.45321199999999995</v>
+        <v>0.452449</v>
       </c>
       <c r="J48" s="7">
-        <v>1.8626580000000001</v>
+        <v>1.629279</v>
       </c>
       <c r="K48" s="7">
-        <v>10.188141</v>
+        <v>10.343978</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -3989,25 +3989,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.067389</v>
+        <v>0.06839400000000001</v>
       </c>
       <c r="F49" s="7">
-        <v>0.104712</v>
+        <v>0.101002</v>
       </c>
       <c r="G49" s="7">
-        <v>0.39061100000000004</v>
+        <v>0.41790799999999995</v>
       </c>
       <c r="H49" s="7">
-        <v>0.31447600000000003</v>
+        <v>0.315714</v>
       </c>
       <c r="I49" s="7">
-        <v>0.616294</v>
+        <v>0.6178159999999999</v>
       </c>
       <c r="J49" s="7">
-        <v>3.901087</v>
+        <v>3.591791</v>
       </c>
       <c r="K49" s="7">
-        <v>16.130339</v>
+        <v>16.232225</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4024,25 +4024,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.079663</v>
+        <v>0.08546300000000001</v>
       </c>
       <c r="F50" s="7">
-        <v>0.096687</v>
+        <v>0.10129899999999999</v>
       </c>
       <c r="G50" s="7">
-        <v>0.20345400000000002</v>
+        <v>0.212361</v>
       </c>
       <c r="H50" s="7">
-        <v>0.164135</v>
+        <v>0.170389</v>
       </c>
       <c r="I50" s="7">
-        <v>0.551056</v>
+        <v>0.5593889999999999</v>
       </c>
       <c r="J50" s="7">
-        <v>3.1619979999999996</v>
+        <v>3.082262</v>
       </c>
       <c r="K50" s="7">
-        <v>9.269584</v>
+        <v>9.44196</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4059,25 +4059,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.036468</v>
+        <v>0.035682</v>
       </c>
       <c r="F51" s="7">
-        <v>0.039445</v>
+        <v>0.036159</v>
       </c>
       <c r="G51" s="7">
-        <v>0.232642</v>
+        <v>0.24500699999999997</v>
       </c>
       <c r="H51" s="7">
-        <v>0.1582</v>
+        <v>0.157323</v>
       </c>
       <c r="I51" s="7">
-        <v>0.396749</v>
+        <v>0.395691</v>
       </c>
       <c r="J51" s="7">
-        <v>2.656709</v>
+        <v>2.5006180000000002</v>
       </c>
       <c r="K51" s="7">
-        <v>8.098146</v>
+        <v>8.113863</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4094,25 +4094,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.060677</v>
+        <v>0.069589</v>
       </c>
       <c r="F52" s="7">
-        <v>0.069975</v>
+        <v>0.07375899999999999</v>
       </c>
       <c r="G52" s="7">
-        <v>0.348413</v>
+        <v>0.38387</v>
       </c>
       <c r="H52" s="7">
-        <v>0.266506</v>
+        <v>0.27714700000000003</v>
       </c>
       <c r="I52" s="7">
-        <v>0.525002</v>
+        <v>0.537814</v>
       </c>
       <c r="J52" s="7">
-        <v>2.898978</v>
+        <v>2.675482</v>
       </c>
       <c r="K52" s="7">
-        <v>11.237306</v>
+        <v>11.425463</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4129,25 +4129,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.018231999999999998</v>
+        <v>0.020225</v>
       </c>
       <c r="F53" s="7">
-        <v>0.033082</v>
+        <v>0.034228999999999996</v>
       </c>
       <c r="G53" s="7">
-        <v>0.107571</v>
+        <v>0.10818199999999999</v>
       </c>
       <c r="H53" s="7">
-        <v>0.059347000000000004</v>
+        <v>0.06142</v>
       </c>
       <c r="I53" s="7">
-        <v>0.33752699999999997</v>
+        <v>0.340145</v>
       </c>
       <c r="J53" s="7">
-        <v>2.201495</v>
+        <v>2.126348</v>
       </c>
       <c r="K53" s="7">
-        <v>6.421901</v>
+        <v>6.417922999999999</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4164,25 +4164,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.01692</v>
+        <v>0.019015</v>
       </c>
       <c r="F54" s="7">
-        <v>0.034592</v>
+        <v>0.035926</v>
       </c>
       <c r="G54" s="7">
-        <v>0.100908</v>
+        <v>0.101729</v>
       </c>
       <c r="H54" s="7">
-        <v>0.060857999999999995</v>
+        <v>0.063043</v>
       </c>
       <c r="I54" s="7">
-        <v>0.298679</v>
+        <v>0.301355</v>
       </c>
       <c r="J54" s="7">
-        <v>2.0785839999999998</v>
+        <v>2.0396870000000002</v>
       </c>
       <c r="K54" s="7">
-        <v>6.240843</v>
+        <v>6.225318</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4199,25 +4199,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.001114</v>
+        <v>-0.0044469999999999996</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.064726</v>
+        <v>-0.071903</v>
       </c>
       <c r="G55" s="7">
-        <v>0.191957</v>
+        <v>0.172937</v>
       </c>
       <c r="H55" s="7">
-        <v>0.097711</v>
+        <v>0.091613</v>
       </c>
       <c r="I55" s="7">
-        <v>0.617735</v>
+        <v>0.608748</v>
       </c>
       <c r="J55" s="7">
-        <v>3.8913580000000003</v>
+        <v>3.915438</v>
       </c>
       <c r="K55" s="7">
-        <v>13.020408999999999</v>
+        <v>12.877437</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4234,25 +4234,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.039747</v>
+        <v>0.039752</v>
       </c>
       <c r="F56" s="7">
-        <v>0.09240399999999999</v>
+        <v>0.093494</v>
       </c>
       <c r="G56" s="7">
-        <v>0.270443</v>
+        <v>0.27869499999999997</v>
       </c>
       <c r="H56" s="7">
-        <v>0.180897</v>
+        <v>0.18090299999999998</v>
       </c>
       <c r="I56" s="7">
-        <v>0.505797</v>
+        <v>0.5058039999999999</v>
       </c>
       <c r="J56" s="7">
-        <v>2.237574</v>
+        <v>2.164584</v>
       </c>
       <c r="K56" s="7">
-        <v>5.771414999999999</v>
+        <v>5.787577</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4269,25 +4269,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>0.0072829999999999995</v>
+        <v>0.003221</v>
       </c>
       <c r="F57" s="7">
-        <v>0.017294</v>
+        <v>0.016223</v>
       </c>
       <c r="G57" s="7">
-        <v>0.156868</v>
+        <v>0.15878</v>
       </c>
       <c r="H57" s="7">
-        <v>0.087885</v>
+        <v>0.083499</v>
       </c>
       <c r="I57" s="7">
-        <v>0.384429</v>
+        <v>0.37884700000000004</v>
       </c>
       <c r="J57" s="7">
-        <v>1.431834</v>
+        <v>1.382621</v>
       </c>
       <c r="K57" s="7">
-        <v>3.574128</v>
+        <v>3.560736</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4304,25 +4304,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.05619</v>
+        <v>0.059241</v>
       </c>
       <c r="F58" s="7">
-        <v>0.094418</v>
+        <v>0.09339499999999999</v>
       </c>
       <c r="G58" s="7">
-        <v>0.346421</v>
+        <v>0.361841</v>
       </c>
       <c r="H58" s="7">
-        <v>0.26675</v>
+        <v>0.270409</v>
       </c>
       <c r="I58" s="7">
-        <v>0.599341</v>
+        <v>0.603961</v>
       </c>
       <c r="J58" s="7">
-        <v>3.349044</v>
+        <v>3.1762610000000002</v>
       </c>
       <c r="K58" s="7">
-        <v>9.722726</v>
+        <v>9.775484</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4339,25 +4339,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.063873</v>
+        <v>0.06703100000000001</v>
       </c>
       <c r="F59" s="7">
-        <v>0.107595</v>
+        <v>0.10489699999999999</v>
       </c>
       <c r="G59" s="7">
-        <v>0.37723799999999996</v>
+        <v>0.400312</v>
       </c>
       <c r="H59" s="7">
-        <v>0.303009</v>
+        <v>0.306878</v>
       </c>
       <c r="I59" s="7">
-        <v>0.598938</v>
+        <v>0.603685</v>
       </c>
       <c r="J59" s="7">
-        <v>3.3949380000000002</v>
+        <v>3.179879</v>
       </c>
       <c r="K59" s="7">
-        <v>10.823149</v>
+        <v>10.900174</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4374,25 +4374,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.057944</v>
+        <v>0.06127</v>
       </c>
       <c r="F60" s="7">
-        <v>0.052563000000000006</v>
+        <v>0.053295</v>
       </c>
       <c r="G60" s="7">
-        <v>0.295159</v>
+        <v>0.32711799999999996</v>
       </c>
       <c r="H60" s="7">
-        <v>0.248281</v>
+        <v>0.252206</v>
       </c>
       <c r="I60" s="7">
-        <v>0.474463</v>
+        <v>0.479099</v>
       </c>
       <c r="J60" s="7">
-        <v>2.706954</v>
+        <v>2.466164</v>
       </c>
       <c r="K60" s="7">
-        <v>13.018531000000001</v>
+        <v>13.180748000000001</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4409,25 +4409,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.054972</v>
+        <v>0.058852</v>
       </c>
       <c r="F61" s="7">
-        <v>0.070935</v>
+        <v>0.072631</v>
       </c>
       <c r="G61" s="7">
-        <v>0.252355</v>
+        <v>0.265005</v>
       </c>
       <c r="H61" s="7">
-        <v>0.203575</v>
+        <v>0.208001</v>
       </c>
       <c r="I61" s="7">
-        <v>0.515868</v>
+        <v>0.521443</v>
       </c>
       <c r="J61" s="7">
-        <v>2.560674</v>
+        <v>2.577309</v>
       </c>
       <c r="K61" s="7">
-        <v>7.569869</v>
+        <v>7.6889959999999995</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4444,25 +4444,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.036261999999999996</v>
+        <v>0.046052</v>
       </c>
       <c r="F62" s="7">
-        <v>0.008421999999999999</v>
+        <v>0.014375</v>
       </c>
       <c r="G62" s="7">
-        <v>0.243971</v>
+        <v>0.28518</v>
       </c>
       <c r="H62" s="7">
-        <v>0.20316299999999998</v>
+        <v>0.21453</v>
       </c>
       <c r="I62" s="7">
-        <v>0.423051</v>
+        <v>0.436495</v>
       </c>
       <c r="J62" s="7">
-        <v>2.430747</v>
+        <v>2.16517</v>
       </c>
       <c r="K62" s="7">
-        <v>12.380332000000001</v>
+        <v>12.632724000000001</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4479,25 +4479,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.021297999999999997</v>
+        <v>0.019964</v>
       </c>
       <c r="F63" s="7">
-        <v>0.03105</v>
+        <v>0.03118</v>
       </c>
       <c r="G63" s="7">
-        <v>0.197882</v>
+        <v>0.201113</v>
       </c>
       <c r="H63" s="7">
-        <v>0.107517</v>
+        <v>0.10607100000000001</v>
       </c>
       <c r="I63" s="7">
-        <v>0.41404</v>
+        <v>0.412193</v>
       </c>
       <c r="J63" s="7">
-        <v>1.9995150000000002</v>
+        <v>1.941448</v>
       </c>
       <c r="K63" s="7">
-        <v>4.706316</v>
+        <v>4.710536</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4514,25 +4514,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.024754</v>
+        <v>0.027134000000000002</v>
       </c>
       <c r="F64" s="7">
-        <v>0.026496</v>
+        <v>0.025238999999999998</v>
       </c>
       <c r="G64" s="7">
-        <v>0.21881599999999998</v>
+        <v>0.226493</v>
       </c>
       <c r="H64" s="7">
-        <v>0.17159500000000003</v>
+        <v>0.174316</v>
       </c>
       <c r="I64" s="7">
-        <v>0.414185</v>
+        <v>0.417469</v>
       </c>
       <c r="J64" s="7">
-        <v>2.1432990000000003</v>
+        <v>2.027149</v>
       </c>
       <c r="K64" s="7">
-        <v>6.242134</v>
+        <v>6.280087</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4549,25 +4549,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.019287000000000002</v>
+        <v>0.020325000000000003</v>
       </c>
       <c r="F65" s="7">
-        <v>0.040447</v>
+        <v>0.04229</v>
       </c>
       <c r="G65" s="7">
-        <v>0.10957</v>
+        <v>0.109642</v>
       </c>
       <c r="H65" s="7">
-        <v>0.07041</v>
+        <v>0.07150000000000001</v>
       </c>
       <c r="I65" s="7">
-        <v>0.296628</v>
+        <v>0.29794899999999996</v>
       </c>
       <c r="J65" s="7">
-        <v>2.100032</v>
+        <v>2.030824</v>
       </c>
       <c r="K65" s="7">
-        <v>5.280381</v>
+        <v>5.261585</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4584,25 +4584,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.016549</v>
+        <v>0.018743</v>
       </c>
       <c r="F66" s="7">
-        <v>0.033637</v>
+        <v>0.034381</v>
       </c>
       <c r="G66" s="7">
-        <v>0.10366</v>
+        <v>0.10484</v>
       </c>
       <c r="H66" s="7">
-        <v>0.054372</v>
+        <v>0.056648</v>
       </c>
       <c r="I66" s="7">
-        <v>0.318732</v>
+        <v>0.32157800000000003</v>
       </c>
       <c r="J66" s="7">
-        <v>2.321787</v>
+        <v>2.250539</v>
       </c>
       <c r="K66" s="7">
-        <v>6.704679</v>
+        <v>6.686616</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4619,25 +4619,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.034054</v>
+        <v>0.034423</v>
       </c>
       <c r="F67" s="7">
-        <v>0.06416000000000001</v>
+        <v>0.061509999999999995</v>
       </c>
       <c r="G67" s="7">
-        <v>0.29134899999999997</v>
+        <v>0.29663</v>
       </c>
       <c r="H67" s="7">
-        <v>0.224145</v>
+        <v>0.224583</v>
       </c>
       <c r="I67" s="7">
-        <v>0.578368</v>
+        <v>0.578933</v>
       </c>
       <c r="J67" s="7">
-        <v>2.633819</v>
+        <v>2.54222</v>
       </c>
       <c r="K67" s="7">
-        <v>9.403483</v>
+        <v>9.442151</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4654,25 +4654,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.016936</v>
+        <v>0.019111</v>
       </c>
       <c r="F68" s="7">
-        <v>0.034148</v>
+        <v>0.034628</v>
       </c>
       <c r="G68" s="7">
-        <v>0.101539</v>
+        <v>0.102714</v>
       </c>
       <c r="H68" s="7">
-        <v>0.058246</v>
+        <v>0.06050900000000001</v>
       </c>
       <c r="I68" s="7">
-        <v>0.293585</v>
+        <v>0.29635100000000003</v>
       </c>
       <c r="J68" s="7">
-        <v>2.097644</v>
+        <v>2.049571</v>
       </c>
       <c r="K68" s="7">
-        <v>6.091334000000001</v>
+        <v>6.075611</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4689,25 +4689,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.029468</v>
+        <v>0.028517999999999998</v>
       </c>
       <c r="F69" s="7">
-        <v>0.057794</v>
+        <v>0.057384000000000004</v>
       </c>
       <c r="G69" s="7">
-        <v>0.234982</v>
+        <v>0.24075</v>
       </c>
       <c r="H69" s="7">
-        <v>0.148746</v>
+        <v>0.14768599999999998</v>
       </c>
       <c r="I69" s="7">
-        <v>0.481088</v>
+        <v>0.47972099999999995</v>
       </c>
       <c r="J69" s="7">
-        <v>2.307206</v>
+        <v>2.238293</v>
       </c>
       <c r="K69" s="7">
-        <v>5.583472</v>
+        <v>5.58554</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4724,25 +4724,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.029289</v>
+        <v>0.030369</v>
       </c>
       <c r="F70" s="7">
-        <v>0.094237</v>
+        <v>0.09432399999999999</v>
       </c>
       <c r="G70" s="7">
-        <v>0.19994</v>
+        <v>0.19994599999999998</v>
       </c>
       <c r="H70" s="7">
-        <v>0.138413</v>
+        <v>0.139606</v>
       </c>
       <c r="I70" s="7">
-        <v>0.475776</v>
+        <v>0.477323</v>
       </c>
       <c r="J70" s="7">
-        <v>2.3606409999999998</v>
+        <v>2.359605</v>
       </c>
       <c r="K70" s="7">
-        <v>4.080955</v>
+        <v>4.083475</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4759,25 +4759,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.270864</v>
+        <v>0.301065</v>
       </c>
       <c r="F71" s="7">
-        <v>0.278839</v>
+        <v>0.303351</v>
       </c>
       <c r="G71" s="7">
-        <v>0.295548</v>
+        <v>0.328604</v>
       </c>
       <c r="H71" s="7">
-        <v>0.285714</v>
+        <v>0.316268</v>
       </c>
       <c r="I71" s="7">
-        <v>0.7718659999999999</v>
+        <v>0.8139740000000001</v>
       </c>
       <c r="J71" s="7">
-        <v>4.105909</v>
+        <v>4.229904</v>
       </c>
       <c r="K71" s="7">
-        <v>9.136606</v>
+        <v>9.268070999999999</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4794,25 +4794,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.039805</v>
+        <v>0.042518</v>
       </c>
       <c r="F72" s="7">
-        <v>0.08713900000000001</v>
+        <v>0.087713</v>
       </c>
       <c r="G72" s="7">
-        <v>0.248566</v>
+        <v>0.256125</v>
       </c>
       <c r="H72" s="7">
-        <v>0.159764</v>
+        <v>0.16279</v>
       </c>
       <c r="I72" s="7">
-        <v>0.45704500000000003</v>
+        <v>0.460847</v>
       </c>
       <c r="J72" s="7">
-        <v>1.881524</v>
+        <v>1.888191</v>
       </c>
       <c r="K72" s="7">
-        <v>4.724897</v>
+        <v>4.743537</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4829,25 +4829,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.035291</v>
+        <v>0.033983</v>
       </c>
       <c r="F73" s="7">
-        <v>0.0040550000000000004</v>
+        <v>0.002056</v>
       </c>
       <c r="G73" s="7">
-        <v>0.07184</v>
+        <v>0.069005</v>
       </c>
       <c r="H73" s="7">
-        <v>0.024714999999999997</v>
+        <v>0.02342</v>
       </c>
       <c r="I73" s="7">
-        <v>0.291922</v>
+        <v>0.290291</v>
       </c>
       <c r="J73" s="7">
-        <v>2.0998159999999997</v>
+        <v>2.018008</v>
       </c>
       <c r="K73" s="7">
-        <v>6.131699</v>
+        <v>6.1046000000000005</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4864,25 +4864,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.074279</v>
+        <v>0.073834</v>
       </c>
       <c r="F74" s="7">
-        <v>0.065281</v>
+        <v>0.058600000000000006</v>
       </c>
       <c r="G74" s="7">
-        <v>0.338294</v>
+        <v>0.368596</v>
       </c>
       <c r="H74" s="7">
-        <v>0.273254</v>
+        <v>0.272727</v>
       </c>
       <c r="I74" s="7">
-        <v>0.439048</v>
+        <v>0.43845100000000004</v>
       </c>
       <c r="J74" s="7">
-        <v>2.862683</v>
+        <v>2.5621409999999996</v>
       </c>
       <c r="K74" s="7">
-        <v>14.990586</v>
+        <v>15.131575</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4899,25 +4899,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.019639</v>
+        <v>0.016905</v>
       </c>
       <c r="F75" s="7">
-        <v>0.025573000000000002</v>
+        <v>0.026794</v>
       </c>
       <c r="G75" s="7">
-        <v>0.177384</v>
+        <v>0.175184</v>
       </c>
       <c r="H75" s="7">
-        <v>0.066195</v>
+        <v>0.063336</v>
       </c>
       <c r="I75" s="7">
-        <v>0.421655</v>
+        <v>0.417842</v>
       </c>
       <c r="J75" s="7">
-        <v>1.8211410000000001</v>
+        <v>1.808621</v>
       </c>
       <c r="K75" s="7">
-        <v>3.720703</v>
+        <v>3.708784</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4934,25 +4934,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.03056</v>
+        <v>0.029500000000000002</v>
       </c>
       <c r="F76" s="7">
-        <v>0.057013</v>
+        <v>0.056562</v>
       </c>
       <c r="G76" s="7">
-        <v>0.237496</v>
+        <v>0.243305</v>
       </c>
       <c r="H76" s="7">
-        <v>0.149457</v>
+        <v>0.148276</v>
       </c>
       <c r="I76" s="7">
-        <v>0.48861699999999997</v>
+        <v>0.487087</v>
       </c>
       <c r="J76" s="7">
-        <v>2.348807</v>
+        <v>2.277664</v>
       </c>
       <c r="K76" s="7">
-        <v>5.674813</v>
+        <v>5.67535</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4969,25 +4969,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.02377</v>
+        <v>0.030988</v>
       </c>
       <c r="F77" s="7">
-        <v>0.053598999999999994</v>
+        <v>0.053452</v>
       </c>
       <c r="G77" s="7">
-        <v>0.322128</v>
+        <v>0.329747</v>
       </c>
       <c r="H77" s="7">
-        <v>0.221389</v>
+        <v>0.23</v>
       </c>
       <c r="I77" s="7">
-        <v>0.443376</v>
+        <v>0.453553</v>
       </c>
       <c r="J77" s="7">
-        <v>1.994905</v>
+        <v>1.932245</v>
       </c>
       <c r="K77" s="7">
-        <v>5.500485</v>
+        <v>5.574806</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5025,25 +5025,25 @@
         <v>4</v>
       </c>
       <c r="E79" s="7">
-        <v>0.052747</v>
+        <v>0.067625</v>
       </c>
       <c r="F79" s="7">
-        <v>0.129163</v>
+        <v>0.131957</v>
       </c>
       <c r="G79" s="7">
-        <v>0.38370600000000005</v>
+        <v>0.41080800000000006</v>
       </c>
       <c r="H79" s="7">
-        <v>0.29192799999999997</v>
+        <v>0.310187</v>
       </c>
       <c r="I79" s="7">
-        <v>0.709673</v>
+        <v>0.733836</v>
       </c>
       <c r="J79" s="7">
-        <v>3.0287759999999997</v>
+        <v>2.93736</v>
       </c>
       <c r="K79" s="7">
-        <v>8.497437999999999</v>
+        <v>8.668936</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5060,25 +5060,25 @@
         <v>5</v>
       </c>
       <c r="E80" s="7">
-        <v>0.060816999999999996</v>
+        <v>0.067968</v>
       </c>
       <c r="F80" s="7">
-        <v>0.109329</v>
+        <v>0.114836</v>
       </c>
       <c r="G80" s="7">
-        <v>0.225124</v>
+        <v>0.249439</v>
       </c>
       <c r="H80" s="7">
-        <v>0.209066</v>
+        <v>0.217216</v>
       </c>
       <c r="I80" s="7">
-        <v>0.45624699999999996</v>
+        <v>0.46606299999999995</v>
       </c>
       <c r="J80" s="7">
-        <v>2.655294</v>
+        <v>2.6061720000000004</v>
       </c>
       <c r="K80" s="7">
-        <v>8.295425999999999</v>
+        <v>8.375503</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5095,25 +5095,25 @@
         <v>6</v>
       </c>
       <c r="E81" s="7">
-        <v>0.039629</v>
+        <v>0.045732999999999996</v>
       </c>
       <c r="F81" s="7">
-        <v>0.072023</v>
+        <v>0.075354</v>
       </c>
       <c r="G81" s="7">
-        <v>0.326494</v>
+        <v>0.35781799999999997</v>
       </c>
       <c r="H81" s="7">
-        <v>0.282528</v>
+        <v>0.290059</v>
       </c>
       <c r="I81" s="7">
-        <v>0.440724</v>
+        <v>0.44918399999999997</v>
       </c>
       <c r="J81" s="7">
-        <v>2.513498</v>
+        <v>2.2800700000000003</v>
       </c>
       <c r="K81" s="7">
-        <v>11.239852</v>
+        <v>11.407810999999999</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5130,25 +5130,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.039496</v>
+        <v>0.04379400000000001</v>
       </c>
       <c r="F82" s="7">
-        <v>0.08241899999999999</v>
+        <v>0.08488799999999999</v>
       </c>
       <c r="G82" s="7">
-        <v>0.199205</v>
+        <v>0.208307</v>
       </c>
       <c r="H82" s="7">
-        <v>0.145404</v>
+        <v>0.15014</v>
       </c>
       <c r="I82" s="7">
-        <v>0.39482300000000004</v>
+        <v>0.40058900000000003</v>
       </c>
       <c r="J82" s="7">
-        <v>1.734666</v>
+        <v>1.801969</v>
       </c>
       <c r="K82" s="7">
-        <v>4.490731</v>
+        <v>4.509762</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5165,25 +5165,25 @@
         <v>4</v>
       </c>
       <c r="E83" s="7">
-        <v>0.018781000000000003</v>
+        <v>0.016605</v>
       </c>
       <c r="F83" s="7">
-        <v>0.022322</v>
+        <v>0.024003999999999998</v>
       </c>
       <c r="G83" s="7">
-        <v>0.14958</v>
+        <v>0.14824199999999998</v>
       </c>
       <c r="H83" s="7">
-        <v>0.062722</v>
+        <v>0.060451</v>
       </c>
       <c r="I83" s="7">
-        <v>0.396057</v>
+        <v>0.39307400000000003</v>
       </c>
       <c r="J83" s="7">
-        <v>1.519212</v>
+        <v>1.516743</v>
       </c>
       <c r="K83" s="7">
-        <v>3.158681</v>
+        <v>3.147843</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5200,25 +5200,25 @@
         <v>5</v>
       </c>
       <c r="E84" s="7">
-        <v>0.073549</v>
+        <v>0.084629</v>
       </c>
       <c r="F84" s="7">
-        <v>0.11215299999999999</v>
+        <v>0.119324</v>
       </c>
       <c r="G84" s="7">
-        <v>0.239827</v>
+        <v>0.27247499999999997</v>
       </c>
       <c r="H84" s="7">
-        <v>0.230563</v>
+        <v>0.243263</v>
       </c>
       <c r="I84" s="7">
-        <v>0.461566</v>
+        <v>0.47665</v>
       </c>
       <c r="J84" s="7">
-        <v>2.7280349999999998</v>
+        <v>2.651518</v>
       </c>
       <c r="K84" s="7">
-        <v>9.417301</v>
+        <v>9.545489</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5235,22 +5235,22 @@
         <v>6</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.004577</v>
+        <v>-0.011372</v>
       </c>
       <c r="F85" s="7">
-        <v>-0.079657</v>
+        <v>-0.087553</v>
       </c>
       <c r="G85" s="7">
-        <v>0.135013</v>
+        <v>0.115252</v>
       </c>
       <c r="H85" s="7">
-        <v>0.041669</v>
+        <v>0.034557000000000004</v>
       </c>
       <c r="I85" s="7">
-        <v>0.648387</v>
+        <v>0.637134</v>
       </c>
       <c r="J85" s="7">
-        <v>3.793485</v>
+        <v>3.783834</v>
       </c>
       <c r="K85" s="7"/>
     </row>
@@ -5268,19 +5268,19 @@
         <v>2</v>
       </c>
       <c r="E86" s="7">
-        <v>0.028768</v>
+        <v>0.029958</v>
       </c>
       <c r="F86" s="7">
-        <v>0.093721</v>
+        <v>0.09391</v>
       </c>
       <c r="G86" s="7">
-        <v>0.196155</v>
+        <v>0.196344</v>
       </c>
       <c r="H86" s="7">
-        <v>0.13647</v>
+        <v>0.137785</v>
       </c>
       <c r="I86" s="7">
-        <v>0.46189300000000005</v>
+        <v>0.46358400000000005</v>
       </c>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5299,22 +5299,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.039830000000000004</v>
+        <v>0.04136599999999999</v>
       </c>
       <c r="F87" s="7">
-        <v>0.07282899999999999</v>
+        <v>0.070732</v>
       </c>
       <c r="G87" s="7">
-        <v>0.301432</v>
+        <v>0.316575</v>
       </c>
       <c r="H87" s="7">
-        <v>0.23961200000000002</v>
+        <v>0.24144300000000002</v>
       </c>
       <c r="I87" s="7">
-        <v>0.57879</v>
+        <v>0.581122</v>
       </c>
       <c r="J87" s="7">
-        <v>2.873168</v>
+        <v>2.6979559999999996</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5332,22 +5332,22 @@
         <v>6</v>
       </c>
       <c r="E88" s="7">
-        <v>0.170409</v>
+        <v>0.172307</v>
       </c>
       <c r="F88" s="7">
-        <v>0.333905</v>
+        <v>0.34069299999999997</v>
       </c>
       <c r="G88" s="7">
-        <v>0.392532</v>
+        <v>0.422837</v>
       </c>
       <c r="H88" s="7">
-        <v>0.441205</v>
+        <v>0.443542</v>
       </c>
       <c r="I88" s="7">
-        <v>0.791117</v>
+        <v>0.7940219999999999</v>
       </c>
       <c r="J88" s="7">
-        <v>4.592476</v>
+        <v>4.454719</v>
       </c>
       <c r="K88" s="7"/>
     </row>
@@ -5365,25 +5365,25 @@
         <v>7</v>
       </c>
       <c r="E89" s="7">
-        <v>0.0017460000000000002</v>
+        <v>-0.004178</v>
       </c>
       <c r="F89" s="7">
-        <v>-0.058279</v>
+        <v>-0.066366</v>
       </c>
       <c r="G89" s="7">
-        <v>0.207517</v>
+        <v>0.186038</v>
       </c>
       <c r="H89" s="7">
-        <v>0.10348399999999999</v>
+        <v>0.096959</v>
       </c>
       <c r="I89" s="7">
-        <v>0.641969</v>
+        <v>0.632259</v>
       </c>
       <c r="J89" s="7">
-        <v>4.113553</v>
+        <v>4.132804</v>
       </c>
       <c r="K89" s="7">
-        <v>13.870443999999999</v>
+        <v>13.712167999999998</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5400,25 +5400,25 @@
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>0.029415</v>
+        <v>0.030310999999999998</v>
       </c>
       <c r="F90" s="7">
-        <v>0.093377</v>
+        <v>0.093558</v>
       </c>
       <c r="G90" s="7">
-        <v>0.201518</v>
+        <v>0.201354</v>
       </c>
       <c r="H90" s="7">
-        <v>0.143044</v>
+        <v>0.144038</v>
       </c>
       <c r="I90" s="7">
-        <v>0.518466</v>
+        <v>0.519787</v>
       </c>
       <c r="J90" s="7">
-        <v>2.4285319999999997</v>
+        <v>2.440924</v>
       </c>
       <c r="K90" s="7">
-        <v>4.348356</v>
+        <v>4.34817</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5435,25 +5435,25 @@
         <v>5</v>
       </c>
       <c r="E91" s="7">
-        <v>0.018268</v>
+        <v>0.016699</v>
       </c>
       <c r="F91" s="7">
-        <v>0.031669</v>
+        <v>0.031674</v>
       </c>
       <c r="G91" s="7">
-        <v>0.18167999999999998</v>
+        <v>0.18374300000000002</v>
       </c>
       <c r="H91" s="7">
-        <v>0.101379</v>
+        <v>0.09968099999999999</v>
       </c>
       <c r="I91" s="7">
-        <v>0.32543500000000003</v>
+        <v>0.32339199999999996</v>
       </c>
       <c r="J91" s="7">
-        <v>2.119577</v>
+        <v>2.11826</v>
       </c>
       <c r="K91" s="7">
-        <v>5.45366</v>
+        <v>5.446785</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5470,22 +5470,22 @@
         <v>6</v>
       </c>
       <c r="E92" s="7">
-        <v>0.021343</v>
+        <v>0.025127</v>
       </c>
       <c r="F92" s="7">
-        <v>0.046299</v>
+        <v>0.040438999999999996</v>
       </c>
       <c r="G92" s="7">
-        <v>0.262709</v>
+        <v>0.276692</v>
       </c>
       <c r="H92" s="7">
-        <v>0.19577100000000003</v>
+        <v>0.200201</v>
       </c>
       <c r="I92" s="7">
-        <v>0.438608</v>
+        <v>0.443937</v>
       </c>
       <c r="J92" s="7">
-        <v>2.669947</v>
+        <v>2.53078</v>
       </c>
       <c r="K92" s="7"/>
     </row>
@@ -5503,25 +5503,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.022362000000000003</v>
+        <v>0.020398</v>
       </c>
       <c r="F93" s="7">
-        <v>0.035778</v>
+        <v>0.035528</v>
       </c>
       <c r="G93" s="7">
-        <v>0.220184</v>
+        <v>0.22459900000000002</v>
       </c>
       <c r="H93" s="7">
-        <v>0.119115</v>
+        <v>0.116966</v>
       </c>
       <c r="I93" s="7">
-        <v>0.375353</v>
+        <v>0.372712</v>
       </c>
       <c r="J93" s="7">
-        <v>2.0387020000000002</v>
+        <v>1.982832</v>
       </c>
       <c r="K93" s="7">
-        <v>4.992776</v>
+        <v>4.990818</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5538,25 +5538,25 @@
         <v>5</v>
       </c>
       <c r="E94" s="7">
-        <v>0.04196</v>
+        <v>0.042751000000000004</v>
       </c>
       <c r="F94" s="7">
-        <v>0.082475</v>
+        <v>0.081913</v>
       </c>
       <c r="G94" s="7">
-        <v>0.225895</v>
+        <v>0.230015</v>
       </c>
       <c r="H94" s="7">
-        <v>0.156863</v>
+        <v>0.157742</v>
       </c>
       <c r="I94" s="7">
-        <v>0.38582900000000003</v>
+        <v>0.386882</v>
       </c>
       <c r="J94" s="7">
-        <v>1.868494</v>
+        <v>1.8804400000000001</v>
       </c>
       <c r="K94" s="7">
-        <v>4.722212</v>
+        <v>4.7276229999999995</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5573,25 +5573,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.023330000000000004</v>
+        <v>0.025514000000000002</v>
       </c>
       <c r="F95" s="7">
-        <v>0.04777</v>
+        <v>0.046471</v>
       </c>
       <c r="G95" s="7">
-        <v>0.29422</v>
+        <v>0.309963</v>
       </c>
       <c r="H95" s="7">
-        <v>0.195725</v>
+        <v>0.198276</v>
       </c>
       <c r="I95" s="7">
-        <v>0.515649</v>
+        <v>0.518883</v>
       </c>
       <c r="J95" s="7">
-        <v>2.918749</v>
+        <v>2.776239</v>
       </c>
       <c r="K95" s="7">
-        <v>8.330432</v>
+        <v>8.383756</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5608,25 +5608,25 @@
         <v>4</v>
       </c>
       <c r="E96" s="7">
-        <v>0.015566</v>
+        <v>0.012098</v>
       </c>
       <c r="F96" s="7">
-        <v>0.026618</v>
+        <v>0.027639999999999998</v>
       </c>
       <c r="G96" s="7">
-        <v>0.18002400000000002</v>
+        <v>0.181674</v>
       </c>
       <c r="H96" s="7">
-        <v>0.06182000000000001</v>
+        <v>0.058193999999999996</v>
       </c>
       <c r="I96" s="7">
-        <v>0.433665</v>
+        <v>0.42877000000000004</v>
       </c>
       <c r="J96" s="7">
-        <v>1.372739</v>
+        <v>1.358406</v>
       </c>
       <c r="K96" s="7">
-        <v>2.777668</v>
+        <v>2.763474</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5643,25 +5643,25 @@
         <v>7</v>
       </c>
       <c r="E97" s="7">
-        <v>0.020835</v>
+        <v>0.024773</v>
       </c>
       <c r="F97" s="7">
-        <v>0.028584000000000002</v>
+        <v>0.028254</v>
       </c>
       <c r="G97" s="7">
-        <v>0.34232999999999997</v>
+        <v>0.377729</v>
       </c>
       <c r="H97" s="7">
-        <v>0.257731</v>
+        <v>0.262583</v>
       </c>
       <c r="I97" s="7">
-        <v>0.447201</v>
+        <v>0.45278399999999996</v>
       </c>
       <c r="J97" s="7">
-        <v>3.0139389999999997</v>
+        <v>2.737113</v>
       </c>
       <c r="K97" s="7">
-        <v>14.814359999999999</v>
+        <v>15.006507999999998</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5678,25 +5678,25 @@
         <v>6</v>
       </c>
       <c r="E98" s="7">
-        <v>0.020577</v>
+        <v>0.038458</v>
       </c>
       <c r="F98" s="7">
-        <v>0.017225</v>
+        <v>0.028806</v>
       </c>
       <c r="G98" s="7">
-        <v>0.43814</v>
+        <v>0.491869</v>
       </c>
       <c r="H98" s="7">
-        <v>0.246479</v>
+        <v>0.268318</v>
       </c>
       <c r="I98" s="7">
-        <v>0.546196</v>
+        <v>0.573287</v>
       </c>
       <c r="J98" s="7">
-        <v>4.170219</v>
+        <v>3.9135489999999997</v>
       </c>
       <c r="K98" s="7">
-        <v>19.306758</v>
+        <v>19.799366</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5713,25 +5713,25 @@
         <v>4</v>
       </c>
       <c r="E99" s="7">
-        <v>0.02572</v>
+        <v>0.028206000000000002</v>
       </c>
       <c r="F99" s="7">
-        <v>0.075782</v>
+        <v>0.075041</v>
       </c>
       <c r="G99" s="7">
-        <v>0.32351599999999997</v>
+        <v>0.340167</v>
       </c>
       <c r="H99" s="7">
-        <v>0.238577</v>
+        <v>0.24158000000000002</v>
       </c>
       <c r="I99" s="7">
-        <v>0.572315</v>
+        <v>0.576127</v>
       </c>
       <c r="J99" s="7">
-        <v>3.64699</v>
+        <v>3.41438</v>
       </c>
       <c r="K99" s="7">
-        <v>9.275587</v>
+        <v>9.361111</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5748,25 +5748,25 @@
         <v>6</v>
       </c>
       <c r="E100" s="7">
-        <v>0.018335</v>
+        <v>0.019936</v>
       </c>
       <c r="F100" s="7">
-        <v>0.040345000000000006</v>
+        <v>0.042113</v>
       </c>
       <c r="G100" s="7">
-        <v>0.104814</v>
+        <v>0.107309</v>
       </c>
       <c r="H100" s="7">
-        <v>0.066221</v>
+        <v>0.067896</v>
       </c>
       <c r="I100" s="7">
-        <v>0.277182</v>
+        <v>0.279189</v>
       </c>
       <c r="J100" s="7">
-        <v>2.002185</v>
+        <v>1.9689340000000002</v>
       </c>
       <c r="K100" s="7">
-        <v>5.685022</v>
+        <v>5.672624</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5783,25 +5783,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.025216</v>
+        <v>0.028082</v>
       </c>
       <c r="F101" s="7">
-        <v>0.07119</v>
+        <v>0.070548</v>
       </c>
       <c r="G101" s="7">
-        <v>0.39397</v>
+        <v>0.417115</v>
       </c>
       <c r="H101" s="7">
-        <v>0.249794</v>
+        <v>0.25328700000000004</v>
       </c>
       <c r="I101" s="7">
-        <v>0.6198210000000001</v>
+        <v>0.624348</v>
       </c>
       <c r="J101" s="7">
-        <v>3.830804</v>
+        <v>3.553934</v>
       </c>
       <c r="K101" s="7">
-        <v>12.235028</v>
+        <v>12.369226000000001</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5818,25 +5818,25 @@
         <v>5</v>
       </c>
       <c r="E102" s="7">
-        <v>0.074489</v>
+        <v>0.07681</v>
       </c>
       <c r="F102" s="7">
-        <v>0.120244</v>
+        <v>0.115969</v>
       </c>
       <c r="G102" s="7">
-        <v>0.434084</v>
+        <v>0.454309</v>
       </c>
       <c r="H102" s="7">
-        <v>0.370402</v>
+        <v>0.373361</v>
       </c>
       <c r="I102" s="7">
-        <v>0.721358</v>
+        <v>0.7250759999999999</v>
       </c>
       <c r="J102" s="7">
-        <v>3.869291</v>
+        <v>3.718631</v>
       </c>
       <c r="K102" s="7">
-        <v>11.961441</v>
+        <v>12.022286999999999</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5853,25 +5853,25 @@
         <v>2</v>
       </c>
       <c r="E103" s="7">
-        <v>0.02993</v>
+        <v>0.030934</v>
       </c>
       <c r="F103" s="7">
-        <v>0.097317</v>
+        <v>0.09481400000000001</v>
       </c>
       <c r="G103" s="7">
-        <v>0.269696</v>
+        <v>0.27321</v>
       </c>
       <c r="H103" s="7">
-        <v>0.17390899999999998</v>
+        <v>0.175053</v>
       </c>
       <c r="I103" s="7">
-        <v>0.5756</v>
+        <v>0.577136</v>
       </c>
       <c r="J103" s="7">
-        <v>3.157074</v>
+        <v>3.153306</v>
       </c>
       <c r="K103" s="7">
-        <v>5.7789719999999996</v>
+        <v>5.7819590000000005</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5888,25 +5888,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.079746</v>
+        <v>0.08226000000000001</v>
       </c>
       <c r="F104" s="7">
-        <v>0.11623100000000001</v>
+        <v>0.111771</v>
       </c>
       <c r="G104" s="7">
-        <v>0.45697899999999997</v>
+        <v>0.480872</v>
       </c>
       <c r="H104" s="7">
-        <v>0.397461</v>
+        <v>0.40071399999999996</v>
       </c>
       <c r="I104" s="7">
-        <v>0.7305240000000001</v>
+        <v>0.7345520000000001</v>
       </c>
       <c r="J104" s="7">
-        <v>3.807345</v>
+        <v>3.627443</v>
       </c>
       <c r="K104" s="7">
-        <v>14.158219999999998</v>
+        <v>14.261028</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5923,25 +5923,25 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.0182</v>
+        <v>0.019185</v>
       </c>
       <c r="F105" s="7">
-        <v>0.034485</v>
+        <v>0.035503</v>
       </c>
       <c r="G105" s="7">
-        <v>0.104034</v>
+        <v>0.10597300000000001</v>
       </c>
       <c r="H105" s="7">
-        <v>0.057950999999999996</v>
+        <v>0.058976</v>
       </c>
       <c r="I105" s="7">
-        <v>0.31448899999999996</v>
+        <v>0.315762</v>
       </c>
       <c r="J105" s="7">
-        <v>2.16661</v>
+        <v>2.095339</v>
       </c>
       <c r="K105" s="7">
-        <v>6.104034</v>
+        <v>6.090744999999999</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5958,16 +5958,16 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.054737</v>
+        <v>0.058034999999999996</v>
       </c>
       <c r="F106" s="7">
-        <v>0.070743</v>
+        <v>0.071938</v>
       </c>
       <c r="G106" s="7">
-        <v>0.23278500000000002</v>
+        <v>0.246461</v>
       </c>
       <c r="H106" s="7">
-        <v>0.18596000000000001</v>
+        <v>0.189668</v>
       </c>
       <c r="I106" s="7"/>
       <c r="J106" s="7"/>
@@ -5987,22 +5987,22 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.20104</v>
+        <v>0.22389099999999998</v>
       </c>
       <c r="F107" s="7">
-        <v>0.31196999999999997</v>
+        <v>0.32955599999999996</v>
       </c>
       <c r="G107" s="7">
-        <v>0.44766</v>
+        <v>0.46502099999999996</v>
       </c>
       <c r="H107" s="7">
-        <v>0.41809199999999996</v>
+        <v>0.445073</v>
       </c>
       <c r="I107" s="7">
-        <v>0.8906870000000001</v>
+        <v>0.9266589999999999</v>
       </c>
       <c r="J107" s="7">
-        <v>4.72917</v>
+        <v>4.736057</v>
       </c>
       <c r="K107" s="7"/>
     </row>
@@ -6020,25 +6020,25 @@
         <v>6</v>
       </c>
       <c r="E108" s="7">
-        <v>0.006242</v>
+        <v>-0.000157</v>
       </c>
       <c r="F108" s="7">
-        <v>-0.048441</v>
+        <v>-0.057204</v>
       </c>
       <c r="G108" s="7">
-        <v>0.228195</v>
+        <v>0.207502</v>
       </c>
       <c r="H108" s="7">
-        <v>0.13617200000000002</v>
+        <v>0.128947</v>
       </c>
       <c r="I108" s="7">
-        <v>0.6889780000000001</v>
+        <v>0.678238</v>
       </c>
       <c r="J108" s="7">
-        <v>4.815186</v>
+        <v>4.836751</v>
       </c>
       <c r="K108" s="7">
-        <v>15.985762999999999</v>
+        <v>15.811485</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6055,25 +6055,25 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.017259</v>
+        <v>0.014249000000000001</v>
       </c>
       <c r="F109" s="7">
-        <v>0.045080999999999996</v>
+        <v>0.04185</v>
       </c>
       <c r="G109" s="7">
-        <v>0.19037400000000002</v>
+        <v>0.186001</v>
       </c>
       <c r="H109" s="7">
-        <v>0.08889200000000001</v>
+        <v>0.08567</v>
       </c>
       <c r="I109" s="7">
-        <v>0.471896</v>
+        <v>0.467541</v>
       </c>
       <c r="J109" s="7">
-        <v>2.0974090000000003</v>
+        <v>2.100346</v>
       </c>
       <c r="K109" s="7">
-        <v>3.942323</v>
+        <v>3.9263670000000004</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6090,25 +6090,25 @@
         <v>6</v>
       </c>
       <c r="E110" s="7">
-        <v>0.019248</v>
+        <v>0.020421</v>
       </c>
       <c r="F110" s="7">
-        <v>0.030316999999999997</v>
+        <v>0.03116</v>
       </c>
       <c r="G110" s="7">
-        <v>0.134971</v>
+        <v>0.13457</v>
       </c>
       <c r="H110" s="7">
-        <v>0.06517400000000001</v>
+        <v>0.0664</v>
       </c>
       <c r="I110" s="7">
-        <v>0.342278</v>
+        <v>0.343823</v>
       </c>
       <c r="J110" s="7">
-        <v>2.242375</v>
+        <v>2.2007749999999997</v>
       </c>
       <c r="K110" s="7">
-        <v>6.552446</v>
+        <v>6.5348429999999995</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6125,25 +6125,25 @@
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>0.044054</v>
+        <v>0.047768</v>
       </c>
       <c r="F111" s="7">
-        <v>0.10285399999999999</v>
+        <v>0.105448</v>
       </c>
       <c r="G111" s="7">
-        <v>0.23833100000000002</v>
+        <v>0.247147</v>
       </c>
       <c r="H111" s="7">
-        <v>0.182985</v>
+        <v>0.187193</v>
       </c>
       <c r="I111" s="7">
-        <v>0.49087000000000003</v>
+        <v>0.49617400000000006</v>
       </c>
       <c r="J111" s="7">
-        <v>2.095544</v>
+        <v>2.100658</v>
       </c>
       <c r="K111" s="7">
-        <v>5.6296550000000005</v>
+        <v>5.6597360000000005</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6160,25 +6160,25 @@
         <v>5</v>
       </c>
       <c r="E112" s="7">
-        <v>0.033243999999999996</v>
+        <v>0.034162</v>
       </c>
       <c r="F112" s="7">
-        <v>0.051094999999999995</v>
+        <v>0.047451999999999994</v>
       </c>
       <c r="G112" s="7">
-        <v>0.278132</v>
+        <v>0.29157900000000003</v>
       </c>
       <c r="H112" s="7">
-        <v>0.18814699999999998</v>
+        <v>0.189202</v>
       </c>
       <c r="I112" s="7">
-        <v>0.579887</v>
+        <v>0.5812890000000001</v>
       </c>
       <c r="J112" s="7">
-        <v>3.582808</v>
+        <v>3.476635</v>
       </c>
       <c r="K112" s="7">
-        <v>14.852248</v>
+        <v>14.873852999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6195,25 +6195,25 @@
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>0.027863000000000002</v>
+        <v>0.027871</v>
       </c>
       <c r="F113" s="7">
-        <v>0.085843</v>
+        <v>0.084265</v>
       </c>
       <c r="G113" s="7">
-        <v>0.23878699999999997</v>
+        <v>0.23841</v>
       </c>
       <c r="H113" s="7">
-        <v>0.153696</v>
+        <v>0.153706</v>
       </c>
       <c r="I113" s="7">
-        <v>0.529058</v>
+        <v>0.529071</v>
       </c>
       <c r="J113" s="7">
-        <v>3.269484</v>
+        <v>3.25834</v>
       </c>
       <c r="K113" s="7">
-        <v>6.3085640000000005</v>
+        <v>6.3059270000000005</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6230,25 +6230,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.070976</v>
+        <v>0.070826</v>
       </c>
       <c r="F114" s="7">
-        <v>0.131867</v>
+        <v>0.13011799999999998</v>
       </c>
       <c r="G114" s="7">
-        <v>0.354083</v>
+        <v>0.37727200000000005</v>
       </c>
       <c r="H114" s="7">
-        <v>0.306518</v>
+        <v>0.306335</v>
       </c>
       <c r="I114" s="7">
-        <v>0.615302</v>
+        <v>0.615076</v>
       </c>
       <c r="J114" s="7">
-        <v>3.8228449999999996</v>
+        <v>3.5745679999999997</v>
       </c>
       <c r="K114" s="7">
-        <v>17.199104</v>
+        <v>17.307573</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6265,25 +6265,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.034532</v>
+        <v>0.040844</v>
       </c>
       <c r="F115" s="7">
-        <v>0.057602</v>
+        <v>0.056704</v>
       </c>
       <c r="G115" s="7">
-        <v>0.30483499999999997</v>
+        <v>0.34745899999999996</v>
       </c>
       <c r="H115" s="7">
-        <v>0.231814</v>
+        <v>0.23933</v>
       </c>
       <c r="I115" s="7">
-        <v>0.580329</v>
+        <v>0.589971</v>
       </c>
       <c r="J115" s="7">
-        <v>3.491632</v>
+        <v>3.214185</v>
       </c>
       <c r="K115" s="7">
-        <v>22.563516</v>
+        <v>22.820135</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6300,25 +6300,25 @@
         <v>6</v>
       </c>
       <c r="E116" s="7">
-        <v>0.042484</v>
+        <v>0.044321</v>
       </c>
       <c r="F116" s="7">
-        <v>0.10270099999999999</v>
+        <v>0.098025</v>
       </c>
       <c r="G116" s="7">
-        <v>0.350475</v>
+        <v>0.381982</v>
       </c>
       <c r="H116" s="7">
-        <v>0.278795</v>
+        <v>0.281048</v>
       </c>
       <c r="I116" s="7">
-        <v>0.603457</v>
+        <v>0.606282</v>
       </c>
       <c r="J116" s="7">
-        <v>3.024379</v>
+        <v>2.731509</v>
       </c>
       <c r="K116" s="7">
-        <v>16.073679</v>
+        <v>16.230169</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6335,25 +6335,25 @@
         <v>5</v>
       </c>
       <c r="E117" s="7">
-        <v>0.048353</v>
+        <v>0.053299000000000006</v>
       </c>
       <c r="F117" s="7">
-        <v>0.12923199999999999</v>
+        <v>0.13237</v>
       </c>
       <c r="G117" s="7">
-        <v>0.350488</v>
+        <v>0.371238</v>
       </c>
       <c r="H117" s="7">
-        <v>0.296396</v>
+        <v>0.30251100000000003</v>
       </c>
       <c r="I117" s="7">
-        <v>0.6773640000000001</v>
+        <v>0.6852769999999999</v>
       </c>
       <c r="J117" s="7">
-        <v>3.470895</v>
+        <v>3.3424509999999996</v>
       </c>
       <c r="K117" s="7">
-        <v>12.47993</v>
+        <v>12.610051</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6370,25 +6370,25 @@
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>0.017509</v>
+        <v>0.014512</v>
       </c>
       <c r="F118" s="7">
-        <v>0.044781</v>
+        <v>0.042324</v>
       </c>
       <c r="G118" s="7">
-        <v>0.187885</v>
+        <v>0.18387399999999998</v>
       </c>
       <c r="H118" s="7">
-        <v>0.082984</v>
+        <v>0.079794</v>
       </c>
       <c r="I118" s="7">
-        <v>0.44276699999999997</v>
+        <v>0.438517</v>
       </c>
       <c r="J118" s="7">
-        <v>1.895516</v>
+        <v>1.889917</v>
       </c>
       <c r="K118" s="7">
-        <v>3.73178</v>
+        <v>3.7164620000000004</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6405,25 +6405,25 @@
         <v>6</v>
       </c>
       <c r="E119" s="7">
-        <v>0.041493</v>
+        <v>0.045792</v>
       </c>
       <c r="F119" s="7">
-        <v>0.08591599999999999</v>
+        <v>0.084959</v>
       </c>
       <c r="G119" s="7">
-        <v>0.31686</v>
+        <v>0.34112299999999995</v>
       </c>
       <c r="H119" s="7">
-        <v>0.238928</v>
+        <v>0.24404199999999998</v>
       </c>
       <c r="I119" s="7">
-        <v>0.676488</v>
+        <v>0.683407</v>
       </c>
       <c r="J119" s="7">
-        <v>3.7882279999999997</v>
+        <v>3.557087</v>
       </c>
       <c r="K119" s="7">
-        <v>16.417357</v>
+        <v>16.577353000000002</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6440,25 +6440,25 @@
         <v>5</v>
       </c>
       <c r="E120" s="7">
-        <v>0.016019000000000002</v>
+        <v>0.014842</v>
       </c>
       <c r="F120" s="7">
-        <v>0.031271</v>
+        <v>0.028738</v>
       </c>
       <c r="G120" s="7">
-        <v>0.212849</v>
+        <v>0.224073</v>
       </c>
       <c r="H120" s="7">
-        <v>0.132805</v>
+        <v>0.131493</v>
       </c>
       <c r="I120" s="7">
-        <v>0.479059</v>
+        <v>0.477346</v>
       </c>
       <c r="J120" s="7">
-        <v>2.669769</v>
+        <v>2.529616</v>
       </c>
       <c r="K120" s="7">
-        <v>8.992972</v>
+        <v>9.006476</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6475,25 +6475,25 @@
         <v>6</v>
       </c>
       <c r="E121" s="7">
-        <v>0.031213</v>
+        <v>0.040365000000000005</v>
       </c>
       <c r="F121" s="7">
-        <v>0.029504000000000002</v>
+        <v>0.030684</v>
       </c>
       <c r="G121" s="7">
-        <v>0.211845</v>
+        <v>0.240015</v>
       </c>
       <c r="H121" s="7">
-        <v>0.176565</v>
+        <v>0.187006</v>
       </c>
       <c r="I121" s="7">
-        <v>0.475214</v>
+        <v>0.48830599999999996</v>
       </c>
       <c r="J121" s="7">
-        <v>3.5369479999999998</v>
+        <v>3.400444</v>
       </c>
       <c r="K121" s="7">
-        <v>18.236523</v>
+        <v>18.450976</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6510,25 +6510,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.021714999999999998</v>
+        <v>0.020072</v>
       </c>
       <c r="F122" s="7">
-        <v>0.05332</v>
+        <v>0.052446</v>
       </c>
       <c r="G122" s="7">
-        <v>0.223157</v>
+        <v>0.227302</v>
       </c>
       <c r="H122" s="7">
-        <v>0.139178</v>
+        <v>0.137346</v>
       </c>
       <c r="I122" s="7">
-        <v>0.493796</v>
+        <v>0.491394</v>
       </c>
       <c r="J122" s="7">
-        <v>2.406541</v>
+        <v>2.344159</v>
       </c>
       <c r="K122" s="7">
-        <v>6.056006</v>
+        <v>6.052492</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6545,25 +6545,25 @@
         <v>4</v>
       </c>
       <c r="E123" s="7">
-        <v>0.022324</v>
+        <v>0.021195</v>
       </c>
       <c r="F123" s="7">
-        <v>0.050838</v>
+        <v>0.050017</v>
       </c>
       <c r="G123" s="7">
-        <v>0.193915</v>
+        <v>0.197072</v>
       </c>
       <c r="H123" s="7">
-        <v>0.123716</v>
+        <v>0.122476</v>
       </c>
       <c r="I123" s="7">
-        <v>0.444893</v>
+        <v>0.44329799999999997</v>
       </c>
       <c r="J123" s="7">
-        <v>2.032409</v>
+        <v>1.976138</v>
       </c>
       <c r="K123" s="7">
-        <v>6.1063670000000005</v>
+        <v>6.099891</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6580,16 +6580,16 @@
         <v>6</v>
       </c>
       <c r="E124" s="7">
-        <v>0.006239</v>
+        <v>-0.0005369999999999999</v>
       </c>
       <c r="F124" s="7">
-        <v>-0.063733</v>
+        <v>-0.071255</v>
       </c>
       <c r="G124" s="7">
-        <v>0.212726</v>
+        <v>0.19136299999999998</v>
       </c>
       <c r="H124" s="7">
-        <v>0.140175</v>
+        <v>0.132497</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
@@ -6609,25 +6609,25 @@
         <v>4</v>
       </c>
       <c r="E125" s="7">
-        <v>0.023253</v>
+        <v>0.025562</v>
       </c>
       <c r="F125" s="7">
-        <v>0.049114000000000005</v>
+        <v>0.04944</v>
       </c>
       <c r="G125" s="7">
-        <v>0.264233</v>
+        <v>0.27797</v>
       </c>
       <c r="H125" s="7">
-        <v>0.174403</v>
+        <v>0.17705300000000002</v>
       </c>
       <c r="I125" s="7">
-        <v>0.549674</v>
+        <v>0.5531710000000001</v>
       </c>
       <c r="J125" s="7">
-        <v>2.132032</v>
+        <v>2.073082</v>
       </c>
       <c r="K125" s="7">
-        <v>6.603278</v>
+        <v>6.6191759999999995</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6644,16 +6644,16 @@
         <v>6</v>
       </c>
       <c r="E126" s="7">
-        <v>0.108549</v>
+        <v>0.116439</v>
       </c>
       <c r="F126" s="7">
-        <v>0.185662</v>
+        <v>0.186421</v>
       </c>
       <c r="G126" s="7">
-        <v>0.454372</v>
+        <v>0.501545</v>
       </c>
       <c r="H126" s="7">
-        <v>0.415257</v>
+        <v>0.42533</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
@@ -6673,25 +6673,25 @@
         <v>7</v>
       </c>
       <c r="E127" s="7">
-        <v>0.046467999999999995</v>
+        <v>0.050673</v>
       </c>
       <c r="F127" s="7">
-        <v>0.066375</v>
+        <v>0.067386</v>
       </c>
       <c r="G127" s="7">
-        <v>0.268345</v>
+        <v>0.294866</v>
       </c>
       <c r="H127" s="7">
-        <v>0.16298200000000002</v>
+        <v>0.167654</v>
       </c>
       <c r="I127" s="7">
-        <v>0.470403</v>
+        <v>0.47631</v>
       </c>
       <c r="J127" s="7">
-        <v>2.6293599999999997</v>
+        <v>2.4663</v>
       </c>
       <c r="K127" s="7">
-        <v>9.45942</v>
+        <v>9.536508</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6708,25 +6708,25 @@
         <v>5</v>
       </c>
       <c r="E128" s="7">
-        <v>0.015949</v>
+        <v>0.017997</v>
       </c>
       <c r="F128" s="7">
-        <v>0.025752999999999998</v>
+        <v>0.025743000000000002</v>
       </c>
       <c r="G128" s="7">
-        <v>0.096485</v>
+        <v>0.097023</v>
       </c>
       <c r="H128" s="7">
-        <v>0.055396</v>
+        <v>0.057523</v>
       </c>
       <c r="I128" s="7">
-        <v>0.28267600000000004</v>
+        <v>0.285262</v>
       </c>
       <c r="J128" s="7">
-        <v>2.006207</v>
+        <v>1.971192</v>
       </c>
       <c r="K128" s="7">
-        <v>5.508405</v>
+        <v>5.48569</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6743,25 +6743,25 @@
         <v>4</v>
       </c>
       <c r="E129" s="7">
-        <v>0.020587</v>
+        <v>0.019400999999999998</v>
       </c>
       <c r="F129" s="7">
-        <v>0.017296</v>
+        <v>0.020203000000000002</v>
       </c>
       <c r="G129" s="7">
-        <v>0.157296</v>
+        <v>0.158672</v>
       </c>
       <c r="H129" s="7">
-        <v>0.062314999999999995</v>
+        <v>0.061081</v>
       </c>
       <c r="I129" s="7">
-        <v>0.405507</v>
+        <v>0.40387500000000004</v>
       </c>
       <c r="J129" s="7">
-        <v>1.591963</v>
+        <v>1.592761</v>
       </c>
       <c r="K129" s="7">
-        <v>3.406536</v>
+        <v>3.399926</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6778,25 +6778,25 @@
         <v>6</v>
       </c>
       <c r="E130" s="7">
-        <v>0.029315</v>
+        <v>0.032943</v>
       </c>
       <c r="F130" s="7">
-        <v>0.054485</v>
+        <v>0.052717</v>
       </c>
       <c r="G130" s="7">
-        <v>0.350536</v>
+        <v>0.382718</v>
       </c>
       <c r="H130" s="7">
-        <v>0.26839999999999997</v>
+        <v>0.272872</v>
       </c>
       <c r="I130" s="7">
-        <v>0.55943</v>
+        <v>0.564928</v>
       </c>
       <c r="J130" s="7">
-        <v>3.052793</v>
+        <v>2.789778</v>
       </c>
       <c r="K130" s="7">
-        <v>14.273819000000001</v>
+        <v>14.457840000000001</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6813,25 +6813,25 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.019173</v>
+        <v>0.020192</v>
       </c>
       <c r="F131" s="7">
-        <v>0.030083000000000002</v>
+        <v>0.030753</v>
       </c>
       <c r="G131" s="7">
-        <v>0.090092</v>
+        <v>0.092087</v>
       </c>
       <c r="H131" s="7">
-        <v>0.051112000000000005</v>
+        <v>0.052163</v>
       </c>
       <c r="I131" s="7">
-        <v>0.282338</v>
+        <v>0.28362</v>
       </c>
       <c r="J131" s="7">
-        <v>2.058793</v>
+        <v>2.0062510000000002</v>
       </c>
       <c r="K131" s="7">
-        <v>6.251797</v>
+        <v>6.222525000000001</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6869,19 +6869,19 @@
         <v>4</v>
       </c>
       <c r="E133" s="7">
-        <v>0.09481099999999999</v>
+        <v>0.129215</v>
       </c>
       <c r="F133" s="7">
-        <v>0.14645</v>
+        <v>0.175583</v>
       </c>
       <c r="G133" s="7">
-        <v>0.239558</v>
+        <v>0.305827</v>
       </c>
       <c r="H133" s="7">
-        <v>0.29140699999999997</v>
+        <v>0.331988</v>
       </c>
       <c r="I133" s="7">
-        <v>0.729533</v>
+        <v>0.783882</v>
       </c>
       <c r="J133" s="7"/>
       <c r="K133" s="7"/>
@@ -6900,25 +6900,25 @@
         <v>4</v>
       </c>
       <c r="E134" s="7">
-        <v>0.017314</v>
+        <v>0.016295999999999998</v>
       </c>
       <c r="F134" s="7">
-        <v>0.023707</v>
+        <v>0.0252</v>
       </c>
       <c r="G134" s="7">
-        <v>0.18942699999999998</v>
+        <v>0.192606</v>
       </c>
       <c r="H134" s="7">
-        <v>0.094078</v>
+        <v>0.092983</v>
       </c>
       <c r="I134" s="7">
-        <v>0.428553</v>
+        <v>0.427123</v>
       </c>
       <c r="J134" s="7">
-        <v>1.54575</v>
+        <v>1.504068</v>
       </c>
       <c r="K134" s="7">
-        <v>3.786015</v>
+        <v>3.786264</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -6935,25 +6935,25 @@
         <v>3</v>
       </c>
       <c r="E135" s="7">
-        <v>0.02921</v>
+        <v>0.030156000000000002</v>
       </c>
       <c r="F135" s="7">
-        <v>0.088115</v>
+        <v>0.088047</v>
       </c>
       <c r="G135" s="7">
-        <v>0.189382</v>
+        <v>0.189072</v>
       </c>
       <c r="H135" s="7">
-        <v>0.13358499999999998</v>
+        <v>0.134626</v>
       </c>
       <c r="I135" s="7">
-        <v>0.458499</v>
+        <v>0.45984</v>
       </c>
       <c r="J135" s="7">
-        <v>2.316853</v>
+        <v>2.317127</v>
       </c>
       <c r="K135" s="7">
-        <v>3.893315</v>
+        <v>3.8948899999999997</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6970,25 +6970,25 @@
         <v>6</v>
       </c>
       <c r="E136" s="7">
-        <v>0.053155</v>
+        <v>0.053549</v>
       </c>
       <c r="F136" s="7">
-        <v>0.080785</v>
+        <v>0.076575</v>
       </c>
       <c r="G136" s="7">
-        <v>0.27709</v>
+        <v>0.28468699999999997</v>
       </c>
       <c r="H136" s="7">
-        <v>0.210117</v>
+        <v>0.21056899999999998</v>
       </c>
       <c r="I136" s="7">
-        <v>0.493406</v>
+        <v>0.493964</v>
       </c>
       <c r="J136" s="7">
-        <v>3.02584</v>
+        <v>2.7884379999999998</v>
       </c>
       <c r="K136" s="7">
-        <v>8.086791</v>
+        <v>8.096632</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7005,25 +7005,25 @@
         <v>4</v>
       </c>
       <c r="E137" s="7">
-        <v>0.018518</v>
+        <v>0.016966000000000002</v>
       </c>
       <c r="F137" s="7">
-        <v>0.02051</v>
+        <v>0.021661</v>
       </c>
       <c r="G137" s="7">
-        <v>0.17082999999999998</v>
+        <v>0.172941</v>
       </c>
       <c r="H137" s="7">
-        <v>0.088955</v>
+        <v>0.087296</v>
       </c>
       <c r="I137" s="7">
-        <v>0.36578299999999997</v>
+        <v>0.36370199999999997</v>
       </c>
       <c r="J137" s="7">
-        <v>1.078595</v>
+        <v>1.057169</v>
       </c>
       <c r="K137" s="7">
-        <v>2.451695</v>
+        <v>2.452909</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7040,25 +7040,25 @@
         <v>6</v>
       </c>
       <c r="E138" s="7">
-        <v>0.055042</v>
+        <v>0.059764</v>
       </c>
       <c r="F138" s="7">
-        <v>0.094843</v>
+        <v>0.101012</v>
       </c>
       <c r="G138" s="7">
-        <v>0.21296299999999999</v>
+        <v>0.22979399999999997</v>
       </c>
       <c r="H138" s="7">
-        <v>0.187324</v>
+        <v>0.192638</v>
       </c>
       <c r="I138" s="7">
-        <v>0.466566</v>
+        <v>0.47313099999999997</v>
       </c>
       <c r="J138" s="7">
-        <v>3.153493</v>
+        <v>3.048562</v>
       </c>
       <c r="K138" s="7">
-        <v>9.502854</v>
+        <v>9.584198</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7075,25 +7075,25 @@
         <v>4</v>
       </c>
       <c r="E139" s="7">
-        <v>0.034281</v>
+        <v>0.036844999999999996</v>
       </c>
       <c r="F139" s="7">
-        <v>0.06257</v>
+        <v>0.06611399999999999</v>
       </c>
       <c r="G139" s="7">
-        <v>0.19142099999999998</v>
+        <v>0.198154</v>
       </c>
       <c r="H139" s="7">
-        <v>0.124918</v>
+        <v>0.127708</v>
       </c>
       <c r="I139" s="7">
-        <v>0.44431</v>
+        <v>0.447891</v>
       </c>
       <c r="J139" s="7">
-        <v>2.22726</v>
+        <v>2.2160290000000002</v>
       </c>
       <c r="K139" s="7">
-        <v>4.235724</v>
+        <v>4.24604</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -7110,22 +7110,22 @@
         <v>6</v>
       </c>
       <c r="E140" s="7">
-        <v>0.176794</v>
+        <v>0.20235199999999998</v>
       </c>
       <c r="F140" s="7">
-        <v>0.248879</v>
+        <v>0.257839</v>
       </c>
       <c r="G140" s="7">
-        <v>0.37245199999999995</v>
+        <v>0.41328000000000004</v>
       </c>
       <c r="H140" s="7">
-        <v>0.332744</v>
+        <v>0.36168999999999996</v>
       </c>
       <c r="I140" s="7">
-        <v>0.9191819999999999</v>
+        <v>0.960865</v>
       </c>
       <c r="J140" s="7">
-        <v>5.743423</v>
+        <v>5.815023</v>
       </c>
       <c r="K140" s="7"/>
     </row>
@@ -7143,22 +7143,22 @@
         <v>4</v>
       </c>
       <c r="E141" s="7">
-        <v>0.04731900000000001</v>
+        <v>0.056407</v>
       </c>
       <c r="F141" s="7">
-        <v>0.041502</v>
+        <v>0.046280999999999996</v>
       </c>
       <c r="G141" s="7">
-        <v>0.22286999999999998</v>
+        <v>0.233777</v>
       </c>
       <c r="H141" s="7">
-        <v>0.143702</v>
+        <v>0.153627</v>
       </c>
       <c r="I141" s="7">
-        <v>0.548645</v>
+        <v>0.562084</v>
       </c>
       <c r="J141" s="7">
-        <v>4.979794</v>
+        <v>4.839443999999999</v>
       </c>
       <c r="K141" s="7"/>
     </row>
@@ -7176,25 +7176,25 @@
         <v>3</v>
       </c>
       <c r="E142" s="7">
-        <v>0.016735</v>
+        <v>0.016722</v>
       </c>
       <c r="F142" s="7">
-        <v>0.028073999999999998</v>
+        <v>0.028673</v>
       </c>
       <c r="G142" s="7">
-        <v>0.169122</v>
+        <v>0.17284300000000002</v>
       </c>
       <c r="H142" s="7">
-        <v>0.100471</v>
+        <v>0.100456</v>
       </c>
       <c r="I142" s="7">
-        <v>0.379054</v>
+        <v>0.379035</v>
       </c>
       <c r="J142" s="7">
-        <v>1.673689</v>
+        <v>1.6522219999999999</v>
       </c>
       <c r="K142" s="7">
-        <v>3.6330790000000004</v>
+        <v>3.6356240000000004</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -7211,25 +7211,25 @@
         <v>3</v>
       </c>
       <c r="E143" s="7">
-        <v>0.033287</v>
+        <v>0.03402</v>
       </c>
       <c r="F143" s="7">
-        <v>0.07063799999999999</v>
+        <v>0.07033299999999999</v>
       </c>
       <c r="G143" s="7">
-        <v>0.198264</v>
+        <v>0.20336400000000002</v>
       </c>
       <c r="H143" s="7">
-        <v>0.135494</v>
+        <v>0.136299</v>
       </c>
       <c r="I143" s="7">
-        <v>0.36024999999999996</v>
+        <v>0.36121499999999995</v>
       </c>
       <c r="J143" s="7">
-        <v>1.512969</v>
+        <v>1.540782</v>
       </c>
       <c r="K143" s="7">
-        <v>4.498544</v>
+        <v>4.508498</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7246,25 +7246,25 @@
         <v>5</v>
       </c>
       <c r="E144" s="7">
-        <v>0.092828</v>
+        <v>0.097545</v>
       </c>
       <c r="F144" s="7">
-        <v>0.035651999999999996</v>
+        <v>0.041546</v>
       </c>
       <c r="G144" s="7">
-        <v>0.287914</v>
+        <v>0.318756</v>
       </c>
       <c r="H144" s="7">
-        <v>0.19971599999999998</v>
+        <v>0.204894</v>
       </c>
       <c r="I144" s="7">
-        <v>0.40563699999999997</v>
+        <v>0.411704</v>
       </c>
       <c r="J144" s="7">
-        <v>3.4689710000000002</v>
+        <v>3.181616</v>
       </c>
       <c r="K144" s="7">
-        <v>13.683152999999999</v>
+        <v>13.85692</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7281,25 +7281,25 @@
         <v>5</v>
       </c>
       <c r="E145" s="7">
-        <v>0.014740999999999999</v>
+        <v>0.021976</v>
       </c>
       <c r="F145" s="7">
-        <v>0.13123300000000002</v>
+        <v>0.138016</v>
       </c>
       <c r="G145" s="7">
-        <v>0.252358</v>
+        <v>0.281997</v>
       </c>
       <c r="H145" s="7">
-        <v>0.29576</v>
+        <v>0.304999</v>
       </c>
       <c r="I145" s="7">
-        <v>0.27176100000000003</v>
+        <v>0.280829</v>
       </c>
       <c r="J145" s="7">
-        <v>3.521556</v>
+        <v>3.3981580000000005</v>
       </c>
       <c r="K145" s="7">
-        <v>11.017808</v>
+        <v>11.122368</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7316,25 +7316,25 @@
         <v>3</v>
       </c>
       <c r="E146" s="7">
-        <v>0.034739</v>
+        <v>0.040096999999999994</v>
       </c>
       <c r="F146" s="7">
-        <v>0.094755</v>
+        <v>0.098215</v>
       </c>
       <c r="G146" s="7">
-        <v>0.32799999999999996</v>
+        <v>0.345658</v>
       </c>
       <c r="H146" s="7">
-        <v>0.230551</v>
+        <v>0.236922</v>
       </c>
       <c r="I146" s="7">
-        <v>0.57766</v>
+        <v>0.585829</v>
       </c>
       <c r="J146" s="7">
-        <v>3.0451040000000003</v>
+        <v>3.011348</v>
       </c>
       <c r="K146" s="7">
-        <v>8.328978</v>
+        <v>8.385247</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7351,25 +7351,25 @@
         <v>4</v>
       </c>
       <c r="E147" s="7">
-        <v>0.024596</v>
+        <v>0.026764</v>
       </c>
       <c r="F147" s="7">
-        <v>0.04635500000000001</v>
+        <v>0.045761</v>
       </c>
       <c r="G147" s="7">
-        <v>0.279125</v>
+        <v>0.293228</v>
       </c>
       <c r="H147" s="7">
-        <v>0.19714700000000002</v>
+        <v>0.199679</v>
       </c>
       <c r="I147" s="7">
-        <v>0.560512</v>
+        <v>0.563813</v>
       </c>
       <c r="J147" s="7">
-        <v>3.60786</v>
+        <v>3.459922</v>
       </c>
       <c r="K147" s="7">
-        <v>9.492874</v>
+        <v>9.571576</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7386,25 +7386,25 @@
         <v>3</v>
       </c>
       <c r="E148" s="7">
-        <v>0.037182</v>
+        <v>0.0392</v>
       </c>
       <c r="F148" s="7">
-        <v>0.11841499999999999</v>
+        <v>0.103872</v>
       </c>
       <c r="G148" s="7">
-        <v>0.37272700000000003</v>
+        <v>0.388311</v>
       </c>
       <c r="H148" s="7">
-        <v>0.305234</v>
+        <v>0.307774</v>
       </c>
       <c r="I148" s="7">
-        <v>0.6547280000000001</v>
+        <v>0.657948</v>
       </c>
       <c r="J148" s="7">
-        <v>3.294212</v>
+        <v>3.199233</v>
       </c>
       <c r="K148" s="7">
-        <v>9.591346999999999</v>
+        <v>9.662237</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7421,25 +7421,25 @@
         <v>4</v>
       </c>
       <c r="E149" s="7">
-        <v>0.032097</v>
+        <v>0.034331</v>
       </c>
       <c r="F149" s="7">
-        <v>0.08509399999999999</v>
+        <v>0.085494</v>
       </c>
       <c r="G149" s="7">
-        <v>0.212863</v>
+        <v>0.217086</v>
       </c>
       <c r="H149" s="7">
-        <v>0.154575</v>
+        <v>0.157074</v>
       </c>
       <c r="I149" s="7">
-        <v>0.471135</v>
+        <v>0.47432</v>
       </c>
       <c r="J149" s="7">
-        <v>2.332048</v>
+        <v>2.288546</v>
       </c>
       <c r="K149" s="7">
-        <v>6.535887</v>
+        <v>6.574928</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7456,25 +7456,25 @@
         <v>4</v>
       </c>
       <c r="E150" s="7">
-        <v>0.025996000000000002</v>
+        <v>0.02844</v>
       </c>
       <c r="F150" s="7">
-        <v>0.023348</v>
+        <v>0.022615</v>
       </c>
       <c r="G150" s="7">
-        <v>0.241339</v>
+        <v>0.239628</v>
       </c>
       <c r="H150" s="7">
-        <v>0.151759</v>
+        <v>0.154503</v>
       </c>
       <c r="I150" s="7">
-        <v>0.5613750000000001</v>
+        <v>0.565095</v>
       </c>
       <c r="J150" s="7">
-        <v>3.377086</v>
+        <v>3.3267450000000003</v>
       </c>
       <c r="K150" s="7">
-        <v>9.612619</v>
+        <v>9.634269</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7491,25 +7491,25 @@
         <v>4</v>
       </c>
       <c r="E151" s="7">
-        <v>0.041326</v>
+        <v>0.042900999999999995</v>
       </c>
       <c r="F151" s="7">
-        <v>0.08803699999999999</v>
+        <v>0.08838599999999999</v>
       </c>
       <c r="G151" s="7">
-        <v>0.20222</v>
+        <v>0.208318</v>
       </c>
       <c r="H151" s="7">
-        <v>0.16168</v>
+        <v>0.16343800000000003</v>
       </c>
       <c r="I151" s="7">
-        <v>0.413819</v>
+        <v>0.415957</v>
       </c>
       <c r="J151" s="7">
-        <v>1.612369</v>
+        <v>1.598487</v>
       </c>
       <c r="K151" s="7">
-        <v>4.288112</v>
+        <v>4.319626</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7526,25 +7526,25 @@
         <v>5</v>
       </c>
       <c r="E152" s="7">
-        <v>0.087476</v>
+        <v>0.08777499999999999</v>
       </c>
       <c r="F152" s="7">
-        <v>0.157793</v>
+        <v>0.155402</v>
       </c>
       <c r="G152" s="7">
-        <v>0.349433</v>
+        <v>0.366464</v>
       </c>
       <c r="H152" s="7">
-        <v>0.317038</v>
+        <v>0.31739999999999996</v>
       </c>
       <c r="I152" s="7">
-        <v>0.636445</v>
+        <v>0.636895</v>
       </c>
       <c r="J152" s="7">
-        <v>3.167346</v>
+        <v>3.048386</v>
       </c>
       <c r="K152" s="7">
-        <v>8.785751</v>
+        <v>8.894094</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7561,25 +7561,25 @@
         <v>7</v>
       </c>
       <c r="E153" s="7">
-        <v>0.076333</v>
+        <v>0.076975</v>
       </c>
       <c r="F153" s="7">
-        <v>0.146311</v>
+        <v>0.144587</v>
       </c>
       <c r="G153" s="7">
-        <v>0.322536</v>
+        <v>0.33630499999999997</v>
       </c>
       <c r="H153" s="7">
-        <v>0.281748</v>
+        <v>0.282513</v>
       </c>
       <c r="I153" s="7">
-        <v>0.611413</v>
+        <v>0.612375</v>
       </c>
       <c r="J153" s="7">
-        <v>3.0007960000000002</v>
+        <v>2.888829</v>
       </c>
       <c r="K153" s="7">
-        <v>7.601198</v>
+        <v>7.614931</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7596,25 +7596,25 @@
         <v>3</v>
       </c>
       <c r="E154" s="7">
-        <v>0.027434</v>
+        <v>0.028484</v>
       </c>
       <c r="F154" s="7">
-        <v>0.074477</v>
+        <v>0.075474</v>
       </c>
       <c r="G154" s="7">
-        <v>0.20846900000000002</v>
+        <v>0.210428</v>
       </c>
       <c r="H154" s="7">
-        <v>0.138858</v>
+        <v>0.140022</v>
       </c>
       <c r="I154" s="7">
-        <v>0.482649</v>
+        <v>0.48416400000000004</v>
       </c>
       <c r="J154" s="7">
-        <v>2.9835849999999997</v>
+        <v>2.978774</v>
       </c>
       <c r="K154" s="7">
-        <v>5.1319989999999995</v>
+        <v>5.136612</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7631,22 +7631,22 @@
         <v>3</v>
       </c>
       <c r="E155" s="7">
-        <v>0.087409</v>
+        <v>0.09986800000000001</v>
       </c>
       <c r="F155" s="7">
-        <v>0.057538</v>
+        <v>0.066673</v>
       </c>
       <c r="G155" s="7">
-        <v>0.23847000000000002</v>
+        <v>0.268426</v>
       </c>
       <c r="H155" s="7">
-        <v>0.17951499999999998</v>
+        <v>0.19303</v>
       </c>
       <c r="I155" s="7">
-        <v>0.527335</v>
+        <v>0.544834</v>
       </c>
       <c r="J155" s="7">
-        <v>3.5844240000000003</v>
+        <v>3.5761200000000004</v>
       </c>
       <c r="K155" s="7"/>
     </row>
@@ -7664,16 +7664,16 @@
         <v>4</v>
       </c>
       <c r="E156" s="7">
-        <v>0.042846999999999996</v>
+        <v>0.045862999999999994</v>
       </c>
       <c r="F156" s="7">
-        <v>0.09088900000000001</v>
+        <v>0.090364</v>
       </c>
       <c r="G156" s="7">
-        <v>0.286753</v>
+        <v>0.299695</v>
       </c>
       <c r="H156" s="7">
-        <v>0.22113600000000003</v>
+        <v>0.224667</v>
       </c>
       <c r="I156" s="7"/>
       <c r="J156" s="7"/>
@@ -7693,22 +7693,22 @@
         <v>6</v>
       </c>
       <c r="E157" s="7">
-        <v>0.047127</v>
+        <v>0.049701</v>
       </c>
       <c r="F157" s="7">
-        <v>0.079047</v>
+        <v>0.075831</v>
       </c>
       <c r="G157" s="7">
-        <v>0.274713</v>
+        <v>0.284194</v>
       </c>
       <c r="H157" s="7">
-        <v>0.22125</v>
+        <v>0.224252</v>
       </c>
       <c r="I157" s="7">
-        <v>0.474477</v>
+        <v>0.478101</v>
       </c>
       <c r="J157" s="7">
-        <v>1.850306</v>
+        <v>1.8277340000000002</v>
       </c>
       <c r="K157" s="7"/>
     </row>
@@ -7726,25 +7726,25 @@
         <v>3</v>
       </c>
       <c r="E158" s="7">
-        <v>0.048742</v>
+        <v>0.05122</v>
       </c>
       <c r="F158" s="7">
-        <v>0.104242</v>
+        <v>0.104542</v>
       </c>
       <c r="G158" s="7">
-        <v>0.26995</v>
+        <v>0.27770700000000004</v>
       </c>
       <c r="H158" s="7">
-        <v>0.198369</v>
+        <v>0.20120000000000002</v>
       </c>
       <c r="I158" s="7">
-        <v>0.554402</v>
+        <v>0.558074</v>
       </c>
       <c r="J158" s="7">
-        <v>2.584638</v>
+        <v>2.559608</v>
       </c>
       <c r="K158" s="7">
-        <v>6.538541</v>
+        <v>6.569577000000001</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -7761,25 +7761,25 @@
         <v>3</v>
       </c>
       <c r="E159" s="7">
-        <v>0.052209000000000005</v>
+        <v>0.055175999999999996</v>
       </c>
       <c r="F159" s="7">
-        <v>0.10872</v>
+        <v>0.109271</v>
       </c>
       <c r="G159" s="7">
-        <v>0.26450399999999996</v>
+        <v>0.273506</v>
       </c>
       <c r="H159" s="7">
-        <v>0.200167</v>
+        <v>0.203552</v>
       </c>
       <c r="I159" s="7">
-        <v>0.514332</v>
+        <v>0.518602</v>
       </c>
       <c r="J159" s="7">
-        <v>2.3698859999999997</v>
+        <v>2.351384</v>
       </c>
       <c r="K159" s="7">
-        <v>6.058098</v>
+        <v>6.091342</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7796,25 +7796,25 @@
         <v>3</v>
       </c>
       <c r="E160" s="7">
-        <v>0.042308000000000005</v>
+        <v>0.044124</v>
       </c>
       <c r="F160" s="7">
-        <v>0.086621</v>
+        <v>0.08615199999999999</v>
       </c>
       <c r="G160" s="7">
-        <v>0.231021</v>
+        <v>0.23677900000000002</v>
       </c>
       <c r="H160" s="7">
-        <v>0.160794</v>
+        <v>0.16281600000000002</v>
       </c>
       <c r="I160" s="7">
-        <v>0.443116</v>
+        <v>0.445631</v>
       </c>
       <c r="J160" s="7">
-        <v>1.9384700000000001</v>
+        <v>1.9316929999999999</v>
       </c>
       <c r="K160" s="7">
-        <v>5.120327</v>
+        <v>5.134472</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7831,22 +7831,22 @@
         <v>5</v>
       </c>
       <c r="E161" s="7">
-        <v>0.172939</v>
+        <v>0.182993</v>
       </c>
       <c r="F161" s="7">
-        <v>0.27249</v>
+        <v>0.277665</v>
       </c>
       <c r="G161" s="7">
-        <v>0.3786</v>
+        <v>0.40565399999999996</v>
       </c>
       <c r="H161" s="7">
-        <v>0.369824</v>
+        <v>0.381565</v>
       </c>
       <c r="I161" s="7">
-        <v>0.801159</v>
+        <v>0.816597</v>
       </c>
       <c r="J161" s="7">
-        <v>4.461966</v>
+        <v>4.390207</v>
       </c>
       <c r="K161" s="7"/>
     </row>
@@ -7864,25 +7864,25 @@
         <v>4</v>
       </c>
       <c r="E162" s="7">
-        <v>0.024914000000000002</v>
+        <v>0.024573</v>
       </c>
       <c r="F162" s="7">
-        <v>0.037306</v>
+        <v>0.038005</v>
       </c>
       <c r="G162" s="7">
-        <v>0.218711</v>
+        <v>0.222361</v>
       </c>
       <c r="H162" s="7">
-        <v>0.114588</v>
+        <v>0.11421799999999999</v>
       </c>
       <c r="I162" s="7">
-        <v>0.44006900000000004</v>
+        <v>0.439591</v>
       </c>
       <c r="J162" s="7">
-        <v>2.103835</v>
+        <v>2.058561</v>
       </c>
       <c r="K162" s="7">
-        <v>5.691244</v>
+        <v>5.690673</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -7899,22 +7899,22 @@
         <v>4</v>
       </c>
       <c r="E163" s="7">
-        <v>0.028176999999999997</v>
+        <v>0.031077</v>
       </c>
       <c r="F163" s="7">
-        <v>0.077307</v>
+        <v>0.08039500000000001</v>
       </c>
       <c r="G163" s="7">
-        <v>0.221586</v>
+        <v>0.223711</v>
       </c>
       <c r="H163" s="7">
-        <v>0.16280999999999998</v>
+        <v>0.16609000000000002</v>
       </c>
       <c r="I163" s="7">
-        <v>0.535788</v>
+        <v>0.540119</v>
       </c>
       <c r="J163" s="7">
-        <v>3.410264</v>
+        <v>3.350822</v>
       </c>
       <c r="K163" s="7"/>
     </row>
@@ -7932,22 +7932,22 @@
         <v>6</v>
       </c>
       <c r="E164" s="7">
-        <v>0.019657</v>
+        <v>0.016593</v>
       </c>
       <c r="F164" s="7">
-        <v>0.004313</v>
+        <v>0.002226</v>
       </c>
       <c r="G164" s="7">
-        <v>0.148478</v>
+        <v>0.137605</v>
       </c>
       <c r="H164" s="7">
-        <v>0.08976200000000001</v>
+        <v>0.086488</v>
       </c>
       <c r="I164" s="7">
-        <v>0.409818</v>
+        <v>0.405582</v>
       </c>
       <c r="J164" s="7">
-        <v>2.649237</v>
+        <v>2.6518759999999997</v>
       </c>
       <c r="K164" s="7"/>
     </row>
@@ -7959,31 +7959,31 @@
         <v>351</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D165" s="6">
         <v>5</v>
       </c>
       <c r="E165" s="7">
-        <v>0.079698</v>
+        <v>0.08406000000000001</v>
       </c>
       <c r="F165" s="7">
-        <v>0.150935</v>
+        <v>0.152686</v>
       </c>
       <c r="G165" s="7">
-        <v>0.38223599999999996</v>
+        <v>0.40303</v>
       </c>
       <c r="H165" s="7">
-        <v>0.313904</v>
+        <v>0.31921299999999997</v>
       </c>
       <c r="I165" s="7">
-        <v>0.677692</v>
+        <v>0.68447</v>
       </c>
       <c r="J165" s="7">
-        <v>2.7344349999999995</v>
+        <v>2.622093</v>
       </c>
       <c r="K165" s="7">
-        <v>8.987584</v>
+        <v>9.036792</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -8000,25 +8000,25 @@
         <v>6</v>
       </c>
       <c r="E166" s="7">
-        <v>0.065885</v>
+        <v>0.067375</v>
       </c>
       <c r="F166" s="7">
-        <v>0.109519</v>
+        <v>0.103392</v>
       </c>
       <c r="G166" s="7">
-        <v>0.428771</v>
+        <v>0.45146000000000003</v>
       </c>
       <c r="H166" s="7">
-        <v>0.344591</v>
+        <v>0.34647</v>
       </c>
       <c r="I166" s="7">
-        <v>0.693121</v>
+        <v>0.695487</v>
       </c>
       <c r="J166" s="7">
-        <v>2.096051</v>
+        <v>2.093477</v>
       </c>
       <c r="K166" s="7">
-        <v>3.826044</v>
+        <v>3.827632</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8035,25 +8035,25 @@
         <v>6</v>
       </c>
       <c r="E167" s="7">
-        <v>0.047672</v>
+        <v>0.053067</v>
       </c>
       <c r="F167" s="7">
-        <v>0.063253</v>
+        <v>0.065329</v>
       </c>
       <c r="G167" s="7">
-        <v>0.372811</v>
+        <v>0.403669</v>
       </c>
       <c r="H167" s="7">
-        <v>0.28322800000000004</v>
+        <v>0.289836</v>
       </c>
       <c r="I167" s="7">
-        <v>0.5180279999999999</v>
+        <v>0.525846</v>
       </c>
       <c r="J167" s="7">
-        <v>3.0928050000000002</v>
+        <v>2.817121</v>
       </c>
       <c r="K167" s="7">
-        <v>15.803752999999999</v>
+        <v>16.015404</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8070,25 +8070,25 @@
         <v>3</v>
       </c>
       <c r="E168" s="7">
-        <v>0.016189</v>
+        <v>0.012927</v>
       </c>
       <c r="F168" s="7">
-        <v>0.01936</v>
+        <v>0.020168</v>
       </c>
       <c r="G168" s="7">
-        <v>0.15065</v>
+        <v>0.147261</v>
       </c>
       <c r="H168" s="7">
-        <v>0.058988</v>
+        <v>0.055589000000000006</v>
       </c>
       <c r="I168" s="7">
-        <v>0.398872</v>
+        <v>0.394383</v>
       </c>
       <c r="J168" s="7">
-        <v>1.918538</v>
+        <v>1.9144370000000002</v>
       </c>
       <c r="K168" s="7">
-        <v>3.9875279999999997</v>
+        <v>3.9705579999999996</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8105,25 +8105,25 @@
         <v>3</v>
       </c>
       <c r="E169" s="7">
-        <v>0.047338</v>
+        <v>0.049513999999999996</v>
       </c>
       <c r="F169" s="7">
-        <v>0.101013</v>
+        <v>0.101788</v>
       </c>
       <c r="G169" s="7">
-        <v>0.266128</v>
+        <v>0.275156</v>
       </c>
       <c r="H169" s="7">
-        <v>0.188703</v>
+        <v>0.191172</v>
       </c>
       <c r="I169" s="7">
-        <v>0.473773</v>
+        <v>0.476835</v>
       </c>
       <c r="J169" s="7">
-        <v>2.035743</v>
+        <v>1.9999619999999998</v>
       </c>
       <c r="K169" s="7">
-        <v>5.5033259999999995</v>
+        <v>5.529049</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8140,25 +8140,25 @@
         <v>5</v>
       </c>
       <c r="E170" s="7">
-        <v>0.022706</v>
+        <v>0.02474</v>
       </c>
       <c r="F170" s="7">
-        <v>0.061468999999999996</v>
+        <v>0.062838</v>
       </c>
       <c r="G170" s="7">
-        <v>0.12561999999999998</v>
+        <v>0.12681800000000001</v>
       </c>
       <c r="H170" s="7">
-        <v>0.090124</v>
+        <v>0.092292</v>
       </c>
       <c r="I170" s="7">
-        <v>0.298328</v>
+        <v>0.30091</v>
       </c>
       <c r="J170" s="7">
-        <v>1.9695310000000001</v>
+        <v>1.967802</v>
       </c>
       <c r="K170" s="7">
-        <v>5.497043</v>
+        <v>5.484266</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -8175,22 +8175,22 @@
         <v>6</v>
       </c>
       <c r="E171" s="7">
-        <v>0.003715</v>
+        <v>-0.0046110000000000005</v>
       </c>
       <c r="F171" s="7">
-        <v>-0.062513</v>
+        <v>-0.071684</v>
       </c>
       <c r="G171" s="7">
-        <v>0.19500900000000002</v>
+        <v>0.171442</v>
       </c>
       <c r="H171" s="7">
-        <v>0.11460100000000001</v>
+        <v>0.105355</v>
       </c>
       <c r="I171" s="7">
-        <v>0.610124</v>
+        <v>0.596766</v>
       </c>
       <c r="J171" s="7">
-        <v>4.665006</v>
+        <v>4.654592</v>
       </c>
       <c r="K171" s="7"/>
     </row>
@@ -8208,22 +8208,22 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.051965000000000004</v>
+        <v>0.054035</v>
       </c>
       <c r="F172" s="7">
-        <v>0.080792</v>
+        <v>0.080162</v>
       </c>
       <c r="G172" s="7">
-        <v>0.297889</v>
+        <v>0.317762</v>
       </c>
       <c r="H172" s="7">
-        <v>0.24675799999999998</v>
+        <v>0.249211</v>
       </c>
       <c r="I172" s="7">
-        <v>0.518958</v>
+        <v>0.521946</v>
       </c>
       <c r="J172" s="7">
-        <v>2.643741</v>
+        <v>2.441986</v>
       </c>
       <c r="K172" s="7"/>
     </row>
@@ -8241,16 +8241,16 @@
         <v>7</v>
       </c>
       <c r="E173" s="7">
-        <v>0.074714</v>
+        <v>0.102651</v>
       </c>
       <c r="F173" s="7">
-        <v>0.016156</v>
+        <v>0.019095</v>
       </c>
       <c r="G173" s="7">
-        <v>0.65818</v>
+        <v>0.666045</v>
       </c>
       <c r="H173" s="7">
-        <v>0.13200599999999998</v>
+        <v>0.161432</v>
       </c>
       <c r="I173" s="7"/>
       <c r="J173" s="7"/>
@@ -8270,25 +8270,25 @@
         <v>6</v>
       </c>
       <c r="E174" s="7">
-        <v>-0.0031530000000000004</v>
+        <v>-0.009843</v>
       </c>
       <c r="F174" s="7">
-        <v>-0.071576</v>
+        <v>-0.079474</v>
       </c>
       <c r="G174" s="7">
-        <v>0.17671</v>
+        <v>0.155809</v>
       </c>
       <c r="H174" s="7">
-        <v>0.078865</v>
+        <v>0.071625</v>
       </c>
       <c r="I174" s="7">
-        <v>0.573379</v>
+        <v>0.56282</v>
       </c>
       <c r="J174" s="7">
-        <v>3.972057</v>
+        <v>3.987063</v>
       </c>
       <c r="K174" s="7">
-        <v>13.310733</v>
+        <v>13.147437</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -8305,25 +8305,25 @@
         <v>4</v>
       </c>
       <c r="E175" s="7">
-        <v>0.027922</v>
+        <v>0.027652999999999997</v>
       </c>
       <c r="F175" s="7">
-        <v>0.041101</v>
+        <v>0.042123</v>
       </c>
       <c r="G175" s="7">
-        <v>0.236649</v>
+        <v>0.24243099999999998</v>
       </c>
       <c r="H175" s="7">
-        <v>0.129553</v>
+        <v>0.129258</v>
       </c>
       <c r="I175" s="7">
-        <v>0.470074</v>
+        <v>0.46969099999999997</v>
       </c>
       <c r="J175" s="7">
-        <v>2.150967</v>
+        <v>2.098401</v>
       </c>
       <c r="K175" s="7">
-        <v>5.43706</v>
+        <v>5.443868</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8340,25 +8340,25 @@
         <v>5</v>
       </c>
       <c r="E176" s="7">
-        <v>0.040491</v>
+        <v>0.045919</v>
       </c>
       <c r="F176" s="7">
-        <v>0.073637</v>
+        <v>0.077859</v>
       </c>
       <c r="G176" s="7">
-        <v>0.33305500000000005</v>
+        <v>0.357031</v>
       </c>
       <c r="H176" s="7">
-        <v>0.24743400000000002</v>
+        <v>0.25394100000000003</v>
       </c>
       <c r="I176" s="7">
-        <v>0.482105</v>
+        <v>0.48983699999999997</v>
       </c>
       <c r="J176" s="7">
-        <v>2.8878769999999996</v>
+        <v>2.694195</v>
       </c>
       <c r="K176" s="7">
-        <v>10.53904</v>
+        <v>10.645235</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8375,25 +8375,25 @@
         <v>5</v>
       </c>
       <c r="E177" s="7">
-        <v>0.019314</v>
+        <v>0.020962</v>
       </c>
       <c r="F177" s="7">
-        <v>0.039316</v>
+        <v>0.039958999999999995</v>
       </c>
       <c r="G177" s="7">
-        <v>0.108033</v>
+        <v>0.109222</v>
       </c>
       <c r="H177" s="7">
-        <v>0.06527999999999999</v>
+        <v>0.06700300000000001</v>
       </c>
       <c r="I177" s="7">
-        <v>0.310566</v>
+        <v>0.312685</v>
       </c>
       <c r="J177" s="7">
-        <v>2.120916</v>
+        <v>2.066649</v>
       </c>
       <c r="K177" s="7">
-        <v>6.27122</v>
+        <v>6.254451</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8410,25 +8410,25 @@
         <v>6</v>
       </c>
       <c r="E178" s="7">
-        <v>0.07115</v>
+        <v>0.07422100000000001</v>
       </c>
       <c r="F178" s="7">
-        <v>0.10198399999999999</v>
+        <v>0.101941</v>
       </c>
       <c r="G178" s="7">
-        <v>0.305501</v>
+        <v>0.319079</v>
       </c>
       <c r="H178" s="7">
-        <v>0.239396</v>
+        <v>0.24294899999999997</v>
       </c>
       <c r="I178" s="7">
-        <v>0.625287</v>
+        <v>0.629947</v>
       </c>
       <c r="J178" s="7">
-        <v>3.091357</v>
+        <v>2.9453899999999997</v>
       </c>
       <c r="K178" s="7">
-        <v>12.439443</v>
+        <v>12.613309999999998</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8445,25 +8445,25 @@
         <v>6</v>
       </c>
       <c r="E179" s="7">
-        <v>0.047992</v>
+        <v>0.055244999999999995</v>
       </c>
       <c r="F179" s="7">
-        <v>0.093048</v>
+        <v>0.097957</v>
       </c>
       <c r="G179" s="7">
-        <v>0.40929299999999996</v>
+        <v>0.441124</v>
       </c>
       <c r="H179" s="7">
-        <v>0.298496</v>
+        <v>0.30748200000000003</v>
       </c>
       <c r="I179" s="7">
-        <v>0.611097</v>
+        <v>0.6222460000000001</v>
       </c>
       <c r="J179" s="7">
-        <v>3.4360700000000004</v>
+        <v>3.169511</v>
       </c>
       <c r="K179" s="7">
-        <v>17.360789999999998</v>
+        <v>17.616157</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8480,25 +8480,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.042967000000000005</v>
+        <v>0.047813999999999995</v>
       </c>
       <c r="F180" s="7">
-        <v>0.08181699999999999</v>
+        <v>0.084513</v>
       </c>
       <c r="G180" s="7">
-        <v>0.366747</v>
+        <v>0.39079200000000003</v>
       </c>
       <c r="H180" s="7">
-        <v>0.247352</v>
+        <v>0.253149</v>
       </c>
       <c r="I180" s="7">
-        <v>0.552005</v>
+        <v>0.559218</v>
       </c>
       <c r="J180" s="7">
-        <v>3.283309</v>
+        <v>3.068147</v>
       </c>
       <c r="K180" s="7">
-        <v>12.931197</v>
+        <v>13.067511</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8515,25 +8515,25 @@
         <v>4</v>
       </c>
       <c r="E181" s="7">
-        <v>0.042607</v>
+        <v>0.046398999999999996</v>
       </c>
       <c r="F181" s="7">
-        <v>0.082325</v>
+        <v>0.083879</v>
       </c>
       <c r="G181" s="7">
-        <v>0.327695</v>
+        <v>0.342416</v>
       </c>
       <c r="H181" s="7">
-        <v>0.214815</v>
+        <v>0.219234</v>
       </c>
       <c r="I181" s="7">
-        <v>0.568545</v>
+        <v>0.5742499999999999</v>
       </c>
       <c r="J181" s="7">
-        <v>3.5321230000000003</v>
+        <v>3.3824759999999996</v>
       </c>
       <c r="K181" s="7">
-        <v>11.388411000000001</v>
+        <v>11.470786</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8550,25 +8550,25 @@
         <v>6</v>
       </c>
       <c r="E182" s="7">
-        <v>0.08793100000000001</v>
+        <v>0.094168</v>
       </c>
       <c r="F182" s="7">
-        <v>0.08962500000000001</v>
+        <v>0.095363</v>
       </c>
       <c r="G182" s="7">
-        <v>0.194131</v>
+        <v>0.19750900000000002</v>
       </c>
       <c r="H182" s="7">
-        <v>0.155499</v>
+        <v>0.162124</v>
       </c>
       <c r="I182" s="7">
-        <v>0.569214</v>
+        <v>0.578212</v>
       </c>
       <c r="J182" s="7">
-        <v>3.3319959999999997</v>
+        <v>3.337516</v>
       </c>
       <c r="K182" s="7">
-        <v>8.719816</v>
+        <v>8.828972</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8585,25 +8585,25 @@
         <v>2</v>
       </c>
       <c r="E183" s="7">
-        <v>0.029136000000000002</v>
+        <v>0.030052</v>
       </c>
       <c r="F183" s="7">
-        <v>0.08233800000000001</v>
+        <v>0.082871</v>
       </c>
       <c r="G183" s="7">
-        <v>0.21624500000000002</v>
+        <v>0.217409</v>
       </c>
       <c r="H183" s="7">
-        <v>0.14489000000000002</v>
+        <v>0.145908</v>
       </c>
       <c r="I183" s="7">
-        <v>0.495762</v>
+        <v>0.497093</v>
       </c>
       <c r="J183" s="7">
-        <v>3.365272</v>
+        <v>3.359353</v>
       </c>
       <c r="K183" s="7">
-        <v>6.380999</v>
+        <v>6.383737999999999</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8620,25 +8620,25 @@
         <v>4</v>
       </c>
       <c r="E184" s="7">
-        <v>0.038773</v>
+        <v>0.043438</v>
       </c>
       <c r="F184" s="7">
-        <v>0.040773000000000004</v>
+        <v>0.042407</v>
       </c>
       <c r="G184" s="7">
-        <v>0.167665</v>
+        <v>0.19260100000000002</v>
       </c>
       <c r="H184" s="7">
-        <v>0.18169000000000002</v>
+        <v>0.186997</v>
       </c>
       <c r="I184" s="7">
-        <v>0.371244</v>
+        <v>0.377403</v>
       </c>
       <c r="J184" s="7">
-        <v>2.482422</v>
+        <v>2.409908</v>
       </c>
       <c r="K184" s="7">
-        <v>3.979548</v>
+        <v>4.00459</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8655,25 +8655,25 @@
         <v>6</v>
       </c>
       <c r="E185" s="7">
-        <v>0.10498900000000001</v>
+        <v>0.11470599999999999</v>
       </c>
       <c r="F185" s="7">
-        <v>0.19194199999999997</v>
+        <v>0.198382</v>
       </c>
       <c r="G185" s="7">
-        <v>0.48944499999999996</v>
+        <v>0.5261330000000001</v>
       </c>
       <c r="H185" s="7">
-        <v>0.409615</v>
+        <v>0.42201099999999997</v>
       </c>
       <c r="I185" s="7">
-        <v>0.74858</v>
+        <v>0.7639579999999999</v>
       </c>
       <c r="J185" s="7">
-        <v>3.605274</v>
+        <v>3.420043</v>
       </c>
       <c r="K185" s="7">
-        <v>13.539285</v>
+        <v>13.762086</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8690,25 +8690,25 @@
         <v>3</v>
       </c>
       <c r="E186" s="7">
-        <v>0.028797000000000003</v>
+        <v>0.029751</v>
       </c>
       <c r="F186" s="7">
-        <v>0.08893000000000001</v>
+        <v>0.08891299999999999</v>
       </c>
       <c r="G186" s="7">
-        <v>0.19315200000000002</v>
+        <v>0.19302499999999997</v>
       </c>
       <c r="H186" s="7">
-        <v>0.13191</v>
+        <v>0.132959</v>
       </c>
       <c r="I186" s="7">
-        <v>0.452891</v>
+        <v>0.454238</v>
       </c>
       <c r="J186" s="7">
-        <v>1.759803</v>
+        <v>1.7619900000000002</v>
       </c>
       <c r="K186" s="7">
-        <v>3.8438</v>
+        <v>3.846286</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8725,25 +8725,25 @@
         <v>5</v>
       </c>
       <c r="E187" s="7">
-        <v>0.089421</v>
+        <v>0.097692</v>
       </c>
       <c r="F187" s="7">
-        <v>0.15637700000000002</v>
+        <v>0.16059400000000001</v>
       </c>
       <c r="G187" s="7">
-        <v>0.374493</v>
+        <v>0.40063000000000004</v>
       </c>
       <c r="H187" s="7">
-        <v>0.309181</v>
+        <v>0.31912</v>
       </c>
       <c r="I187" s="7">
-        <v>0.665393</v>
+        <v>0.6780370000000001</v>
       </c>
       <c r="J187" s="7">
-        <v>3.2452609999999997</v>
+        <v>3.11824</v>
       </c>
       <c r="K187" s="7">
-        <v>11.553586000000001</v>
+        <v>11.705969</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,25 +8760,25 @@
         <v>2</v>
       </c>
       <c r="E188" s="7">
-        <v>0.028885</v>
+        <v>0.029832</v>
       </c>
       <c r="F188" s="7">
-        <v>0.08905900000000001</v>
+        <v>0.089055</v>
       </c>
       <c r="G188" s="7">
-        <v>0.19064</v>
+        <v>0.190533</v>
       </c>
       <c r="H188" s="7">
-        <v>0.131524</v>
+        <v>0.13256500000000002</v>
       </c>
       <c r="I188" s="7">
-        <v>0.447748</v>
+        <v>0.44908099999999995</v>
       </c>
       <c r="J188" s="7">
-        <v>1.854076</v>
+        <v>1.8585800000000001</v>
       </c>
       <c r="K188" s="7">
-        <v>3.353033</v>
+        <v>3.355131</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8795,25 +8795,25 @@
         <v>2</v>
       </c>
       <c r="E189" s="7">
-        <v>0.028657</v>
+        <v>0.029485</v>
       </c>
       <c r="F189" s="7">
-        <v>0.066254</v>
+        <v>0.066368</v>
       </c>
       <c r="G189" s="7">
-        <v>0.155289</v>
+        <v>0.155152</v>
       </c>
       <c r="H189" s="7">
-        <v>0.10665</v>
+        <v>0.107541</v>
       </c>
       <c r="I189" s="7">
-        <v>0.37758400000000003</v>
+        <v>0.378694</v>
       </c>
       <c r="J189" s="7">
-        <v>1.992106</v>
+        <v>2.0005</v>
       </c>
       <c r="K189" s="7">
-        <v>3.3304869999999998</v>
+        <v>3.3322030000000002</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8830,19 +8830,19 @@
         <v>6</v>
       </c>
       <c r="E190" s="7">
-        <v>0.06740499999999999</v>
+        <v>0.106016</v>
       </c>
       <c r="F190" s="7">
-        <v>-0.001258</v>
+        <v>0.009142</v>
       </c>
       <c r="G190" s="7">
-        <v>0.616082</v>
+        <v>0.6398550000000001</v>
       </c>
       <c r="H190" s="7">
-        <v>0.11046099999999999</v>
+        <v>0.150629</v>
       </c>
       <c r="I190" s="7">
-        <v>1.5984530000000001</v>
+        <v>1.692445</v>
       </c>
       <c r="J190" s="7"/>
       <c r="K190" s="7"/>
@@ -8861,25 +8861,25 @@
         <v>6</v>
       </c>
       <c r="E191" s="7">
-        <v>0.002553</v>
+        <v>-0.003759</v>
       </c>
       <c r="F191" s="7">
-        <v>-0.061093</v>
+        <v>-0.068105</v>
       </c>
       <c r="G191" s="7">
-        <v>0.187998</v>
+        <v>0.165515</v>
       </c>
       <c r="H191" s="7">
-        <v>0.092098</v>
+        <v>0.08522199999999999</v>
       </c>
       <c r="I191" s="7">
-        <v>0.592086</v>
+        <v>0.5820620000000001</v>
       </c>
       <c r="J191" s="7">
-        <v>3.884702</v>
+        <v>3.890313</v>
       </c>
       <c r="K191" s="7">
-        <v>13.069367999999999</v>
+        <v>12.914531</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -8896,25 +8896,25 @@
         <v>6</v>
       </c>
       <c r="E192" s="7">
-        <v>-0.007192</v>
+        <v>-0.012881</v>
       </c>
       <c r="F192" s="7">
-        <v>-0.077719</v>
+        <v>-0.084928</v>
       </c>
       <c r="G192" s="7">
-        <v>0.150546</v>
+        <v>0.131128</v>
       </c>
       <c r="H192" s="7">
-        <v>0.061535</v>
+        <v>0.055452</v>
       </c>
       <c r="I192" s="7">
-        <v>0.557025</v>
+        <v>0.548103</v>
       </c>
       <c r="J192" s="7">
-        <v>3.806669</v>
+        <v>3.820482</v>
       </c>
       <c r="K192" s="7">
-        <v>12.794412999999999</v>
+        <v>12.652666</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8931,25 +8931,25 @@
         <v>4</v>
       </c>
       <c r="E193" s="7">
-        <v>0.029304</v>
+        <v>0.027538</v>
       </c>
       <c r="F193" s="7">
-        <v>0.057369</v>
+        <v>0.056853999999999995</v>
       </c>
       <c r="G193" s="7">
-        <v>0.260306</v>
+        <v>0.26676</v>
       </c>
       <c r="H193" s="7">
-        <v>0.15866</v>
+        <v>0.156672</v>
       </c>
       <c r="I193" s="7">
-        <v>0.510241</v>
+        <v>0.50765</v>
       </c>
       <c r="J193" s="7">
-        <v>1.928424</v>
+        <v>1.864948</v>
       </c>
       <c r="K193" s="7">
-        <v>5.10101</v>
+        <v>5.111186</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8966,25 +8966,25 @@
         <v>4</v>
       </c>
       <c r="E194" s="7">
-        <v>0.027563</v>
+        <v>0.026087</v>
       </c>
       <c r="F194" s="7">
-        <v>0.054405999999999996</v>
+        <v>0.053265</v>
       </c>
       <c r="G194" s="7">
-        <v>0.21436599999999997</v>
+        <v>0.216762</v>
       </c>
       <c r="H194" s="7">
-        <v>0.12386</v>
+        <v>0.122245</v>
       </c>
       <c r="I194" s="7">
-        <v>0.458694</v>
+        <v>0.45659799999999995</v>
       </c>
       <c r="J194" s="7">
-        <v>2.3199799999999997</v>
+        <v>2.274438</v>
       </c>
       <c r="K194" s="7">
-        <v>5.5906769999999995</v>
+        <v>5.58386</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -9001,25 +9001,25 @@
         <v>6</v>
       </c>
       <c r="E195" s="7">
-        <v>0.018344</v>
+        <v>0.020118</v>
       </c>
       <c r="F195" s="7">
-        <v>0.034425</v>
+        <v>0.034103</v>
       </c>
       <c r="G195" s="7">
-        <v>0.107101</v>
+        <v>0.10795400000000001</v>
       </c>
       <c r="H195" s="7">
-        <v>0.061131000000000005</v>
+        <v>0.062981</v>
       </c>
       <c r="I195" s="7">
-        <v>0.31488</v>
+        <v>0.317172</v>
       </c>
       <c r="J195" s="7">
-        <v>2.231821</v>
+        <v>2.175041</v>
       </c>
       <c r="K195" s="7">
-        <v>6.4550909999999995</v>
+        <v>6.430794</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9036,25 +9036,25 @@
         <v>3</v>
       </c>
       <c r="E196" s="7">
-        <v>0.037061000000000004</v>
+        <v>0.0408</v>
       </c>
       <c r="F196" s="7">
-        <v>0.109795</v>
+        <v>0.11175700000000001</v>
       </c>
       <c r="G196" s="7">
-        <v>0.27377300000000004</v>
+        <v>0.284038</v>
       </c>
       <c r="H196" s="7">
-        <v>0.214645</v>
+        <v>0.219025</v>
       </c>
       <c r="I196" s="7">
-        <v>0.479339</v>
+        <v>0.484674</v>
       </c>
       <c r="J196" s="7">
-        <v>1.657729</v>
+        <v>1.633801</v>
       </c>
       <c r="K196" s="7">
-        <v>3.766693</v>
+        <v>3.7911829999999997</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9071,25 +9071,25 @@
         <v>3</v>
       </c>
       <c r="E197" s="7">
-        <v>0.042664</v>
+        <v>0.044971</v>
       </c>
       <c r="F197" s="7">
-        <v>0.08924</v>
+        <v>0.08930300000000001</v>
       </c>
       <c r="G197" s="7">
-        <v>0.251075</v>
+        <v>0.257693</v>
       </c>
       <c r="H197" s="7">
-        <v>0.16043500000000002</v>
+        <v>0.163003</v>
       </c>
       <c r="I197" s="7">
-        <v>0.461791</v>
+        <v>0.46502499999999997</v>
       </c>
       <c r="J197" s="7">
-        <v>1.853531</v>
+        <v>1.85652</v>
       </c>
       <c r="K197" s="7">
-        <v>4.683414</v>
+        <v>4.699623</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9106,25 +9106,25 @@
         <v>4</v>
       </c>
       <c r="E198" s="7">
-        <v>0.031675</v>
+        <v>0.030659000000000002</v>
       </c>
       <c r="F198" s="7">
-        <v>0.060441</v>
+        <v>0.059492</v>
       </c>
       <c r="G198" s="7">
-        <v>0.23924900000000002</v>
+        <v>0.24495999999999998</v>
       </c>
       <c r="H198" s="7">
-        <v>0.151616</v>
+        <v>0.150482</v>
       </c>
       <c r="I198" s="7">
-        <v>0.49282800000000004</v>
+        <v>0.491358</v>
       </c>
       <c r="J198" s="7">
-        <v>2.228467</v>
+        <v>2.168472</v>
       </c>
       <c r="K198" s="7">
-        <v>5.126161</v>
+        <v>5.127636</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9141,25 +9141,25 @@
         <v>6</v>
       </c>
       <c r="E199" s="7">
-        <v>0.028956</v>
+        <v>0.035133</v>
       </c>
       <c r="F199" s="7">
-        <v>0.037412</v>
+        <v>0.039388</v>
       </c>
       <c r="G199" s="7">
-        <v>0.288518</v>
+        <v>0.32014699999999996</v>
       </c>
       <c r="H199" s="7">
-        <v>0.254193</v>
+        <v>0.261723</v>
       </c>
       <c r="I199" s="7">
-        <v>0.498146</v>
+        <v>0.5071410000000001</v>
       </c>
       <c r="J199" s="7">
-        <v>4.060947</v>
+        <v>3.6986489999999996</v>
       </c>
       <c r="K199" s="7">
-        <v>21.01788</v>
+        <v>21.329771</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9176,16 +9176,16 @@
         <v>5</v>
       </c>
       <c r="E200" s="7">
-        <v>0.07853399999999999</v>
+        <v>0.079868</v>
       </c>
       <c r="F200" s="7">
-        <v>0.096427</v>
+        <v>0.093596</v>
       </c>
       <c r="G200" s="7">
-        <v>0.299338</v>
+        <v>0.31348400000000004</v>
       </c>
       <c r="H200" s="7">
-        <v>0.246667</v>
+        <v>0.248209</v>
       </c>
       <c r="I200" s="7"/>
       <c r="J200" s="7"/>
@@ -9205,25 +9205,25 @@
         <v>6</v>
       </c>
       <c r="E201" s="7">
-        <v>0.06457099999999999</v>
+        <v>0.071552</v>
       </c>
       <c r="F201" s="7">
-        <v>0.038373</v>
+        <v>0.04261</v>
       </c>
       <c r="G201" s="7">
-        <v>0.237818</v>
+        <v>0.275566</v>
       </c>
       <c r="H201" s="7">
-        <v>0.143569</v>
+        <v>0.151068</v>
       </c>
       <c r="I201" s="7">
-        <v>0.438839</v>
+        <v>0.44827399999999995</v>
       </c>
       <c r="J201" s="7">
-        <v>2.478409</v>
+        <v>2.306451</v>
       </c>
       <c r="K201" s="7">
-        <v>10.13597</v>
+        <v>10.291148</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -9240,25 +9240,25 @@
         <v>6</v>
       </c>
       <c r="E202" s="7">
-        <v>0.082454</v>
+        <v>0.093346</v>
       </c>
       <c r="F202" s="7">
-        <v>0.12148400000000001</v>
+        <v>0.126061</v>
       </c>
       <c r="G202" s="7">
-        <v>0.33476999999999996</v>
+        <v>0.370904</v>
       </c>
       <c r="H202" s="7">
-        <v>0.24732800000000002</v>
+        <v>0.25987899999999997</v>
       </c>
       <c r="I202" s="7">
-        <v>0.520837</v>
+        <v>0.53614</v>
       </c>
       <c r="J202" s="7">
-        <v>2.713637</v>
+        <v>2.572798</v>
       </c>
       <c r="K202" s="7">
-        <v>9.349833</v>
+        <v>9.561082</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9275,25 +9275,25 @@
         <v>5</v>
       </c>
       <c r="E203" s="7">
-        <v>0.008291</v>
+        <v>0.012571</v>
       </c>
       <c r="F203" s="7">
-        <v>-0.0040160000000000005</v>
+        <v>-0.001229</v>
       </c>
       <c r="G203" s="7">
-        <v>0.181449</v>
+        <v>0.186707</v>
       </c>
       <c r="H203" s="7">
-        <v>0.096009</v>
+        <v>0.10066000000000001</v>
       </c>
       <c r="I203" s="7">
-        <v>0.6512690000000001</v>
+        <v>0.6582769999999999</v>
       </c>
       <c r="J203" s="7">
-        <v>3.0011829999999997</v>
+        <v>2.910835</v>
       </c>
       <c r="K203" s="7">
-        <v>6.4292229999999995</v>
+        <v>6.457395</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9310,25 +9310,25 @@
         <v>3</v>
       </c>
       <c r="E204" s="7">
-        <v>0.012512</v>
+        <v>0.009553</v>
       </c>
       <c r="F204" s="7">
-        <v>0.036943000000000004</v>
+        <v>0.036458</v>
       </c>
       <c r="G204" s="7">
-        <v>0.164862</v>
+        <v>0.16354500000000002</v>
       </c>
       <c r="H204" s="7">
-        <v>0.065594</v>
+        <v>0.06248</v>
       </c>
       <c r="I204" s="7">
-        <v>0.400798</v>
+        <v>0.396705</v>
       </c>
       <c r="J204" s="7">
-        <v>1.674648</v>
+        <v>1.6708770000000002</v>
       </c>
       <c r="K204" s="7">
-        <v>3.705068</v>
+        <v>3.689852</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9345,16 +9345,16 @@
         <v>6</v>
       </c>
       <c r="E205" s="7">
-        <v>0.032853</v>
+        <v>0.038354</v>
       </c>
       <c r="F205" s="7">
-        <v>0.044425</v>
+        <v>0.044912</v>
       </c>
       <c r="G205" s="7">
-        <v>0.31343</v>
+        <v>0.343593</v>
       </c>
       <c r="H205" s="7">
-        <v>0.265426</v>
+        <v>0.272166</v>
       </c>
       <c r="I205" s="7"/>
       <c r="J205" s="7"/>
@@ -9374,25 +9374,25 @@
         <v>5</v>
       </c>
       <c r="E206" s="7">
-        <v>0.021655</v>
+        <v>0.023644</v>
       </c>
       <c r="F206" s="7">
-        <v>0.039583</v>
+        <v>0.041048999999999995</v>
       </c>
       <c r="G206" s="7">
-        <v>0.11475300000000001</v>
+        <v>0.115731</v>
       </c>
       <c r="H206" s="7">
-        <v>0.071506</v>
+        <v>0.073592</v>
       </c>
       <c r="I206" s="7">
-        <v>0.316732</v>
+        <v>0.319296</v>
       </c>
       <c r="J206" s="7">
-        <v>1.9815459999999998</v>
+        <v>1.961327</v>
       </c>
       <c r="K206" s="7">
-        <v>5.3081640000000005</v>
+        <v>5.298690000000001</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -9409,25 +9409,25 @@
         <v>4</v>
       </c>
       <c r="E207" s="7">
-        <v>0.022434</v>
+        <v>0.020470000000000002</v>
       </c>
       <c r="F207" s="7">
-        <v>0.033886</v>
+        <v>0.033628</v>
       </c>
       <c r="G207" s="7">
-        <v>0.218613</v>
+        <v>0.223112</v>
       </c>
       <c r="H207" s="7">
-        <v>0.116373</v>
+        <v>0.11422800000000001</v>
       </c>
       <c r="I207" s="7">
-        <v>0.37053600000000003</v>
+        <v>0.36790300000000004</v>
       </c>
       <c r="J207" s="7">
-        <v>2.033561</v>
+        <v>1.976602</v>
       </c>
       <c r="K207" s="7">
-        <v>4.975555</v>
+        <v>4.973657</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9444,25 +9444,25 @@
         <v>4</v>
       </c>
       <c r="E208" s="7">
-        <v>0.017838</v>
+        <v>0.021150000000000002</v>
       </c>
       <c r="F208" s="7">
-        <v>0.046704999999999997</v>
+        <v>0.046127</v>
       </c>
       <c r="G208" s="7">
-        <v>0.278497</v>
+        <v>0.295224</v>
       </c>
       <c r="H208" s="7">
-        <v>0.192443</v>
+        <v>0.196324</v>
       </c>
       <c r="I208" s="7">
-        <v>0.49861</v>
+        <v>0.503487</v>
       </c>
       <c r="J208" s="7">
-        <v>2.8707190000000002</v>
+        <v>2.735098</v>
       </c>
       <c r="K208" s="7">
-        <v>7.9982500000000005</v>
+        <v>8.060256</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9479,25 +9479,25 @@
         <v>6</v>
       </c>
       <c r="E209" s="7">
-        <v>0.020556</v>
+        <v>0.023969</v>
       </c>
       <c r="F209" s="7">
-        <v>0.041402999999999995</v>
+        <v>0.040686</v>
       </c>
       <c r="G209" s="7">
-        <v>0.34637999999999997</v>
+        <v>0.371524</v>
       </c>
       <c r="H209" s="7">
-        <v>0.207271</v>
+        <v>0.211309</v>
       </c>
       <c r="I209" s="7">
-        <v>0.5299280000000001</v>
+        <v>0.535045</v>
       </c>
       <c r="J209" s="7">
-        <v>2.9146370000000004</v>
+        <v>2.7354629999999998</v>
       </c>
       <c r="K209" s="7">
-        <v>9.735498</v>
+        <v>9.831628</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9514,25 +9514,25 @@
         <v>3</v>
       </c>
       <c r="E210" s="7">
-        <v>0.015290999999999999</v>
+        <v>0.011724000000000002</v>
       </c>
       <c r="F210" s="7">
-        <v>0.02428</v>
+        <v>0.025175</v>
       </c>
       <c r="G210" s="7">
-        <v>0.184536</v>
+        <v>0.187774</v>
       </c>
       <c r="H210" s="7">
-        <v>0.056044000000000004</v>
+        <v>0.052334</v>
       </c>
       <c r="I210" s="7">
-        <v>0.399249</v>
+        <v>0.39433300000000004</v>
       </c>
       <c r="J210" s="7">
-        <v>1.5265620000000002</v>
+        <v>1.511421</v>
       </c>
       <c r="K210" s="7">
-        <v>2.969702</v>
+        <v>2.953852</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9549,25 +9549,25 @@
         <v>6</v>
       </c>
       <c r="E211" s="7">
-        <v>0.021697</v>
+        <v>0.025688</v>
       </c>
       <c r="F211" s="7">
-        <v>0.025872000000000003</v>
+        <v>0.025575</v>
       </c>
       <c r="G211" s="7">
-        <v>0.338357</v>
+        <v>0.373556</v>
       </c>
       <c r="H211" s="7">
-        <v>0.254431</v>
+        <v>0.259331</v>
       </c>
       <c r="I211" s="7">
-        <v>0.439913</v>
+        <v>0.445537</v>
       </c>
       <c r="J211" s="7">
-        <v>2.977427</v>
+        <v>2.703339</v>
       </c>
       <c r="K211" s="7">
-        <v>14.631596</v>
+        <v>14.821905999999998</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9584,25 +9584,25 @@
         <v>4</v>
       </c>
       <c r="E212" s="7">
-        <v>0.034991</v>
+        <v>0.038126</v>
       </c>
       <c r="F212" s="7">
-        <v>0.072019</v>
+        <v>0.07312</v>
       </c>
       <c r="G212" s="7">
-        <v>0.268572</v>
+        <v>0.28295200000000004</v>
       </c>
       <c r="H212" s="7">
-        <v>0.200299</v>
+        <v>0.203934</v>
       </c>
       <c r="I212" s="7">
-        <v>0.531303</v>
+        <v>0.535941</v>
       </c>
       <c r="J212" s="7">
-        <v>1.979162</v>
+        <v>1.8895330000000001</v>
       </c>
       <c r="K212" s="7">
-        <v>5.539695</v>
+        <v>5.576683</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9619,25 +9619,25 @@
         <v>3</v>
       </c>
       <c r="E213" s="7">
-        <v>0.044135</v>
+        <v>0.044539999999999996</v>
       </c>
       <c r="F213" s="7">
-        <v>0.119794</v>
+        <v>0.119595</v>
       </c>
       <c r="G213" s="7">
-        <v>0.284026</v>
+        <v>0.29084</v>
       </c>
       <c r="H213" s="7">
-        <v>0.21218299999999998</v>
+        <v>0.212652</v>
       </c>
       <c r="I213" s="7">
-        <v>0.49822299999999997</v>
+        <v>0.498803</v>
       </c>
       <c r="J213" s="7">
-        <v>1.9864490000000001</v>
+        <v>1.952596</v>
       </c>
       <c r="K213" s="7">
-        <v>5.148818</v>
+        <v>5.167726</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9654,25 +9654,25 @@
         <v>4</v>
       </c>
       <c r="E214" s="7">
-        <v>0.051725</v>
+        <v>0.049375999999999996</v>
       </c>
       <c r="F214" s="7">
-        <v>0.126607</v>
+        <v>0.121748</v>
       </c>
       <c r="G214" s="7">
-        <v>0.364597</v>
+        <v>0.37319899999999995</v>
       </c>
       <c r="H214" s="7">
-        <v>0.302281</v>
+        <v>0.29937400000000003</v>
       </c>
       <c r="I214" s="7">
-        <v>0.632715</v>
+        <v>0.62907</v>
       </c>
       <c r="J214" s="7">
-        <v>3.291091</v>
+        <v>3.176377</v>
       </c>
       <c r="K214" s="7">
-        <v>10.106337</v>
+        <v>10.075889</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9689,25 +9689,25 @@
         <v>6</v>
       </c>
       <c r="E215" s="7">
-        <v>-0.000332</v>
+        <v>-0.006379</v>
       </c>
       <c r="F215" s="7">
-        <v>-0.067305</v>
+        <v>-0.07422100000000001</v>
       </c>
       <c r="G215" s="7">
-        <v>0.189499</v>
+        <v>0.168353</v>
       </c>
       <c r="H215" s="7">
-        <v>0.096967</v>
+        <v>0.090331</v>
       </c>
       <c r="I215" s="7">
-        <v>0.617566</v>
+        <v>0.607781</v>
       </c>
       <c r="J215" s="7">
-        <v>4.037015</v>
+        <v>4.056493</v>
       </c>
       <c r="K215" s="7">
-        <v>13.390682</v>
+        <v>13.238031000000001</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9724,25 +9724,25 @@
         <v>4</v>
       </c>
       <c r="E216" s="7">
-        <v>0.042756999999999996</v>
+        <v>0.044996999999999995</v>
       </c>
       <c r="F216" s="7">
-        <v>0.066899</v>
+        <v>0.06680900000000001</v>
       </c>
       <c r="G216" s="7">
-        <v>0.203723</v>
+        <v>0.215309</v>
       </c>
       <c r="H216" s="7">
-        <v>0.156999</v>
+        <v>0.159485</v>
       </c>
       <c r="I216" s="7">
-        <v>0.42178</v>
+        <v>0.424835</v>
       </c>
       <c r="J216" s="7">
-        <v>2.514528</v>
+        <v>2.468967</v>
       </c>
       <c r="K216" s="7">
-        <v>7.319811</v>
+        <v>7.344126999999999</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9759,25 +9759,25 @@
         <v>5</v>
       </c>
       <c r="E217" s="7">
-        <v>0.10076299999999999</v>
+        <v>0.105157</v>
       </c>
       <c r="F217" s="7">
-        <v>0.182943</v>
+        <v>0.184482</v>
       </c>
       <c r="G217" s="7">
-        <v>0.46684600000000004</v>
+        <v>0.49695500000000004</v>
       </c>
       <c r="H217" s="7">
-        <v>0.4122</v>
+        <v>0.417836</v>
       </c>
       <c r="I217" s="7">
-        <v>0.7146370000000001</v>
+        <v>0.72148</v>
       </c>
       <c r="J217" s="7">
-        <v>3.138541</v>
+        <v>2.927203</v>
       </c>
       <c r="K217" s="7">
-        <v>10.139076</v>
+        <v>10.271230000000001</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9794,25 +9794,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.020411000000000002</v>
+        <v>0.022505</v>
       </c>
       <c r="F218" s="7">
-        <v>0.037759</v>
+        <v>0.0394</v>
       </c>
       <c r="G218" s="7">
-        <v>0.084794</v>
+        <v>0.08622999999999999</v>
       </c>
       <c r="H218" s="7">
-        <v>0.057131</v>
+        <v>0.059301000000000006</v>
       </c>
       <c r="I218" s="7">
-        <v>0.227166</v>
+        <v>0.229684</v>
       </c>
       <c r="J218" s="7">
-        <v>1.805701</v>
+        <v>1.7840850000000001</v>
       </c>
       <c r="K218" s="7">
-        <v>5.282541999999999</v>
+        <v>5.265464</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9829,25 +9829,25 @@
         <v>4</v>
       </c>
       <c r="E219" s="7">
-        <v>0.044749</v>
+        <v>0.045198</v>
       </c>
       <c r="F219" s="7">
-        <v>0.13558299999999998</v>
+        <v>0.13473100000000002</v>
       </c>
       <c r="G219" s="7">
-        <v>0.35419199999999995</v>
+        <v>0.365404</v>
       </c>
       <c r="H219" s="7">
-        <v>0.281177</v>
+        <v>0.281728</v>
       </c>
       <c r="I219" s="7">
-        <v>0.648302</v>
+        <v>0.649011</v>
       </c>
       <c r="J219" s="7">
-        <v>3.4734320000000003</v>
+        <v>3.346513</v>
       </c>
       <c r="K219" s="7">
-        <v>10.46968</v>
+        <v>10.488544999999998</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9864,25 +9864,25 @@
         <v>5</v>
       </c>
       <c r="E220" s="7">
-        <v>0.103244</v>
+        <v>0.108757</v>
       </c>
       <c r="F220" s="7">
-        <v>0.166279</v>
+        <v>0.167549</v>
       </c>
       <c r="G220" s="7">
-        <v>0.44366700000000003</v>
+        <v>0.472325</v>
       </c>
       <c r="H220" s="7">
-        <v>0.37048699999999996</v>
+        <v>0.377335</v>
       </c>
       <c r="I220" s="7">
-        <v>0.6789499999999999</v>
+        <v>0.68734</v>
       </c>
       <c r="J220" s="7">
-        <v>4.33836</v>
+        <v>4.153558</v>
       </c>
       <c r="K220" s="7">
-        <v>14.127545</v>
+        <v>14.290845</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9899,19 +9899,19 @@
         <v>4</v>
       </c>
       <c r="E221" s="7">
-        <v>0.055253</v>
+        <v>0.058471999999999996</v>
       </c>
       <c r="F221" s="7">
-        <v>0.088654</v>
+        <v>0.088949</v>
       </c>
       <c r="G221" s="7">
-        <v>0.272238</v>
+        <v>0.28200800000000004</v>
       </c>
       <c r="H221" s="7">
-        <v>0.21470199999999998</v>
+        <v>0.218407</v>
       </c>
       <c r="I221" s="7">
-        <v>0.540572</v>
+        <v>0.545271</v>
       </c>
       <c r="J221" s="7"/>
       <c r="K221" s="7"/>
@@ -9930,16 +9930,16 @@
         <v>6</v>
       </c>
       <c r="E222" s="7">
-        <v>0.06362899999999999</v>
+        <v>0.07084399999999999</v>
       </c>
       <c r="F222" s="7">
-        <v>0.03021</v>
+        <v>0.031465</v>
       </c>
       <c r="G222" s="7">
-        <v>0.691543</v>
+        <v>0.65589</v>
       </c>
       <c r="H222" s="7">
-        <v>0.176892</v>
+        <v>0.184876</v>
       </c>
       <c r="I222" s="7"/>
       <c r="J222" s="7"/>
@@ -9959,7 +9959,7 @@
         <v>6</v>
       </c>
       <c r="E223" s="7">
-        <v>0.076063</v>
+        <v>0.086957</v>
       </c>
       <c r="F223" s="7"/>
       <c r="G223" s="7"/>
@@ -9982,22 +9982,22 @@
         <v>6</v>
       </c>
       <c r="E224" s="7">
-        <v>0.033415</v>
+        <v>0.036019999999999996</v>
       </c>
       <c r="F224" s="7">
-        <v>-0.025731</v>
+        <v>-0.026846000000000002</v>
       </c>
       <c r="G224" s="7">
-        <v>0.42035200000000006</v>
+        <v>0.397055</v>
       </c>
       <c r="H224" s="7">
-        <v>0.13020400000000001</v>
+        <v>0.133053</v>
       </c>
       <c r="I224" s="7">
-        <v>1.102833</v>
+        <v>1.108135</v>
       </c>
       <c r="J224" s="7">
-        <v>4.609103999999999</v>
+        <v>4.656199</v>
       </c>
       <c r="K224" s="7"/>
     </row>
@@ -10015,25 +10015,25 @@
         <v>4</v>
       </c>
       <c r="E225" s="7">
-        <v>0.029299</v>
+        <v>0.030357</v>
       </c>
       <c r="F225" s="7">
-        <v>0.097697</v>
+        <v>0.097867</v>
       </c>
       <c r="G225" s="7">
-        <v>0.196649</v>
+        <v>0.19654699999999997</v>
       </c>
       <c r="H225" s="7">
-        <v>0.136723</v>
+        <v>0.137892</v>
       </c>
       <c r="I225" s="7">
-        <v>0.436106</v>
+        <v>0.437582</v>
       </c>
       <c r="J225" s="7">
-        <v>1.480019</v>
+        <v>1.571991</v>
       </c>
       <c r="K225" s="7">
-        <v>2.732503</v>
+        <v>2.734988</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -10050,19 +10050,19 @@
         <v>2</v>
       </c>
       <c r="E226" s="7">
-        <v>0.027221000000000002</v>
+        <v>0.028195</v>
       </c>
       <c r="F226" s="7">
-        <v>0.083231</v>
+        <v>0.083252</v>
       </c>
       <c r="G226" s="7">
-        <v>0.18632200000000002</v>
+        <v>0.186176</v>
       </c>
       <c r="H226" s="7">
-        <v>0.127105</v>
+        <v>0.12817399999999998</v>
       </c>
       <c r="I226" s="7">
-        <v>0.441747</v>
+        <v>0.443114</v>
       </c>
       <c r="J226" s="7"/>
       <c r="K226" s="7"/>
@@ -10081,22 +10081,22 @@
         <v>6</v>
       </c>
       <c r="E227" s="7">
-        <v>0.093084</v>
+        <v>0.111324</v>
       </c>
       <c r="F227" s="7">
-        <v>0.150249</v>
+        <v>0.167818</v>
       </c>
       <c r="G227" s="7">
-        <v>0.32108600000000004</v>
+        <v>0.367655</v>
       </c>
       <c r="H227" s="7">
-        <v>0.315622</v>
+        <v>0.337576</v>
       </c>
       <c r="I227" s="7">
-        <v>0.478172</v>
+        <v>0.502837</v>
       </c>
       <c r="J227" s="7">
-        <v>2.9489080000000003</v>
+        <v>2.821384</v>
       </c>
       <c r="K227" s="7"/>
     </row>
@@ -10114,19 +10114,19 @@
         <v>5</v>
       </c>
       <c r="E228" s="7">
-        <v>0.045921000000000003</v>
+        <v>0.045614999999999996</v>
       </c>
       <c r="F228" s="7">
-        <v>-0.016806</v>
+        <v>-0.029811999999999998</v>
       </c>
       <c r="G228" s="7">
-        <v>0.412138</v>
+        <v>0.394889</v>
       </c>
       <c r="H228" s="7">
-        <v>0.15448800000000001</v>
+        <v>0.15414999999999998</v>
       </c>
       <c r="I228" s="7">
-        <v>1.0177370000000001</v>
+        <v>1.017146</v>
       </c>
       <c r="J228" s="7"/>
       <c r="K228" s="7"/>
@@ -10166,25 +10166,25 @@
         <v>4</v>
       </c>
       <c r="E230" s="7">
-        <v>0.025707</v>
+        <v>0.024357000000000004</v>
       </c>
       <c r="F230" s="7">
-        <v>0.05733799999999999</v>
+        <v>0.05612</v>
       </c>
       <c r="G230" s="7">
-        <v>0.218661</v>
+        <v>0.22120499999999998</v>
       </c>
       <c r="H230" s="7">
-        <v>0.126493</v>
+        <v>0.12501099999999998</v>
       </c>
       <c r="I230" s="7">
-        <v>0.46231</v>
+        <v>0.460386</v>
       </c>
       <c r="J230" s="7">
-        <v>2.2827189999999997</v>
+        <v>2.241128</v>
       </c>
       <c r="K230" s="7">
-        <v>5.672693000000001</v>
+        <v>5.666494</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -10201,25 +10201,25 @@
         <v>3</v>
       </c>
       <c r="E231" s="7">
-        <v>0.040101000000000005</v>
+        <v>0.04289</v>
       </c>
       <c r="F231" s="7">
-        <v>0.08848</v>
+        <v>0.089169</v>
       </c>
       <c r="G231" s="7">
-        <v>0.24340699999999998</v>
+        <v>0.251089</v>
       </c>
       <c r="H231" s="7">
-        <v>0.159461</v>
+        <v>0.16257000000000002</v>
       </c>
       <c r="I231" s="7">
-        <v>0.44587699999999997</v>
+        <v>0.449754</v>
       </c>
       <c r="J231" s="7">
-        <v>1.8816220000000001</v>
+        <v>1.8852010000000001</v>
       </c>
       <c r="K231" s="7">
-        <v>4.615756999999999</v>
+        <v>4.633115</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -10236,19 +10236,19 @@
         <v>3</v>
       </c>
       <c r="E232" s="7">
-        <v>0.082937</v>
+        <v>0.090223</v>
       </c>
       <c r="F232" s="7">
-        <v>0.14475300000000002</v>
+        <v>0.146755</v>
       </c>
       <c r="G232" s="7">
-        <v>0.282009</v>
+        <v>0.298498</v>
       </c>
       <c r="H232" s="7">
-        <v>0.251463</v>
+        <v>0.259883</v>
       </c>
       <c r="I232" s="7">
-        <v>0.582975</v>
+        <v>0.593625</v>
       </c>
       <c r="J232" s="7"/>
       <c r="K232" s="7"/>
@@ -10267,7 +10267,7 @@
         <v>2</v>
       </c>
       <c r="E233" s="7">
-        <v>0.035114</v>
+        <v>0.036208</v>
       </c>
       <c r="F233" s="7"/>
       <c r="G233" s="7"/>
@@ -10290,19 +10290,19 @@
         <v>5</v>
       </c>
       <c r="E234" s="7">
-        <v>0.142808</v>
+        <v>0.162885</v>
       </c>
       <c r="F234" s="7">
-        <v>0.261843</v>
+        <v>0.27703099999999997</v>
       </c>
       <c r="G234" s="7">
-        <v>0.442795</v>
+        <v>0.497919</v>
       </c>
       <c r="H234" s="7">
-        <v>0.450982</v>
+        <v>0.47647300000000004</v>
       </c>
       <c r="I234" s="7">
-        <v>0.648091</v>
+        <v>0.677045</v>
       </c>
       <c r="J234" s="7"/>
       <c r="K234" s="7"/>
@@ -10321,19 +10321,19 @@
         <v>5</v>
       </c>
       <c r="E235" s="7">
-        <v>0.08767799999999999</v>
+        <v>0.092706</v>
       </c>
       <c r="F235" s="7">
-        <v>0.140131</v>
+        <v>0.140909</v>
       </c>
       <c r="G235" s="7">
-        <v>0.32007599999999997</v>
+        <v>0.338099</v>
       </c>
       <c r="H235" s="7">
-        <v>0.277423</v>
+        <v>0.283329</v>
       </c>
       <c r="I235" s="7">
-        <v>0.57113</v>
+        <v>0.578394</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10352,25 +10352,25 @@
         <v>4</v>
       </c>
       <c r="E236" s="7">
-        <v>0.035972</v>
+        <v>0.039313</v>
       </c>
       <c r="F236" s="7">
-        <v>0.07460499999999999</v>
+        <v>0.07613299999999999</v>
       </c>
       <c r="G236" s="7">
-        <v>0.19325199999999998</v>
+        <v>0.20138</v>
       </c>
       <c r="H236" s="7">
-        <v>0.130552</v>
+        <v>0.134198</v>
       </c>
       <c r="I236" s="7">
-        <v>0.38176299999999996</v>
+        <v>0.386219</v>
       </c>
       <c r="J236" s="7">
-        <v>1.726375</v>
+        <v>1.794367</v>
       </c>
       <c r="K236" s="7">
-        <v>4.412533</v>
+        <v>4.4293759999999995</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -10387,19 +10387,19 @@
         <v>3</v>
       </c>
       <c r="E237" s="7">
-        <v>0.02105</v>
+        <v>0.025722000000000002</v>
       </c>
       <c r="F237" s="7">
-        <v>0.048232</v>
+        <v>0.04929700000000001</v>
       </c>
       <c r="G237" s="7">
-        <v>0.261168</v>
+        <v>0.282068</v>
       </c>
       <c r="H237" s="7">
-        <v>0.198903</v>
+        <v>0.20438900000000002</v>
       </c>
       <c r="I237" s="7">
-        <v>0.484583</v>
+        <v>0.491375</v>
       </c>
       <c r="J237" s="7"/>
       <c r="K237" s="7"/>
@@ -10418,19 +10418,19 @@
         <v>4</v>
       </c>
       <c r="E238" s="7">
-        <v>0.024798</v>
+        <v>0.026211</v>
       </c>
       <c r="F238" s="7">
-        <v>0.061485000000000005</v>
+        <v>0.06203</v>
       </c>
       <c r="G238" s="7">
-        <v>0.20921800000000002</v>
+        <v>0.21254</v>
       </c>
       <c r="H238" s="7">
-        <v>0.12750899999999998</v>
+        <v>0.12906399999999998</v>
       </c>
       <c r="I238" s="7">
-        <v>0.482528</v>
+        <v>0.484572</v>
       </c>
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
@@ -10449,19 +10449,19 @@
         <v>2</v>
       </c>
       <c r="E239" s="7">
-        <v>0.031979</v>
+        <v>0.033011</v>
       </c>
       <c r="F239" s="7">
-        <v>0.099842</v>
+        <v>0.09627100000000001</v>
       </c>
       <c r="G239" s="7">
-        <v>0.19940100000000002</v>
+        <v>0.19934100000000002</v>
       </c>
       <c r="H239" s="7">
-        <v>0.141655</v>
+        <v>0.142796</v>
       </c>
       <c r="I239" s="7">
-        <v>0.46911400000000003</v>
+        <v>0.47058300000000003</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10480,25 +10480,25 @@
         <v>6</v>
       </c>
       <c r="E240" s="7">
-        <v>0.005475</v>
+        <v>-0.0010689999999999999</v>
       </c>
       <c r="F240" s="7">
-        <v>-0.056165</v>
+        <v>-0.063691</v>
       </c>
       <c r="G240" s="7">
-        <v>0.20919000000000001</v>
+        <v>0.18646000000000001</v>
       </c>
       <c r="H240" s="7">
-        <v>0.10832900000000001</v>
+        <v>0.101115</v>
       </c>
       <c r="I240" s="7">
-        <v>0.619182</v>
+        <v>0.6086440000000001</v>
       </c>
       <c r="J240" s="7">
-        <v>4.168774</v>
+        <v>4.182076</v>
       </c>
       <c r="K240" s="7">
-        <v>13.702671</v>
+        <v>13.537877000000002</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -10515,14 +10515,14 @@
         <v>3</v>
       </c>
       <c r="E241" s="7">
-        <v>0.009825</v>
+        <v>0.005806</v>
       </c>
       <c r="F241" s="7">
-        <v>0.024836999999999998</v>
+        <v>0.024472</v>
       </c>
       <c r="G241" s="7"/>
       <c r="H241" s="7">
-        <v>0.054467</v>
+        <v>0.05027</v>
       </c>
       <c r="I241" s="7"/>
       <c r="J241" s="7"/>
@@ -10542,19 +10542,19 @@
         <v>6</v>
       </c>
       <c r="E242" s="7">
-        <v>0.18501599999999999</v>
+        <v>0.193236</v>
       </c>
       <c r="F242" s="7">
-        <v>0.302232</v>
+        <v>0.31408400000000003</v>
       </c>
       <c r="G242" s="7">
-        <v>0.41964199999999996</v>
+        <v>0.45360999999999996</v>
       </c>
       <c r="H242" s="7">
-        <v>0.404797</v>
+        <v>0.414542</v>
       </c>
       <c r="I242" s="7">
-        <v>0.773994</v>
+        <v>0.7863</v>
       </c>
       <c r="J242" s="7"/>
       <c r="K242" s="7"/>
@@ -10573,19 +10573,19 @@
         <v>5</v>
       </c>
       <c r="E243" s="7">
-        <v>0.055180999999999994</v>
+        <v>0.058506999999999997</v>
       </c>
       <c r="F243" s="7">
-        <v>0.066479</v>
+        <v>0.065463</v>
       </c>
       <c r="G243" s="7">
-        <v>0.262403</v>
+        <v>0.279835</v>
       </c>
       <c r="H243" s="7">
-        <v>0.20918399999999998</v>
+        <v>0.212995</v>
       </c>
       <c r="I243" s="7">
-        <v>0.513456</v>
+        <v>0.518226</v>
       </c>
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
@@ -10604,25 +10604,25 @@
         <v>6</v>
       </c>
       <c r="E244" s="7">
-        <v>0.017828999999999998</v>
+        <v>0.020266000000000003</v>
       </c>
       <c r="F244" s="7">
-        <v>0.037991000000000004</v>
+        <v>0.039405</v>
       </c>
       <c r="G244" s="7">
-        <v>0.090094</v>
+        <v>0.09161</v>
       </c>
       <c r="H244" s="7">
-        <v>0.060406</v>
+        <v>0.062945</v>
       </c>
       <c r="I244" s="7">
-        <v>0.231124</v>
+        <v>0.234071</v>
       </c>
       <c r="J244" s="7">
-        <v>1.8535300000000001</v>
+        <v>1.8217050000000001</v>
       </c>
       <c r="K244" s="7">
-        <v>5.793483999999999</v>
+        <v>5.779675</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -10639,25 +10639,25 @@
         <v>4</v>
       </c>
       <c r="E245" s="7">
-        <v>0.021016</v>
+        <v>0.021846</v>
       </c>
       <c r="F245" s="7">
-        <v>0.055707000000000007</v>
+        <v>0.057035999999999996</v>
       </c>
       <c r="G245" s="7">
-        <v>0.232482</v>
+        <v>0.254533</v>
       </c>
       <c r="H245" s="7">
-        <v>0.09887</v>
+        <v>0.099762</v>
       </c>
       <c r="I245" s="7">
-        <v>0.238308</v>
+        <v>0.239314</v>
       </c>
       <c r="J245" s="7">
-        <v>2.0087360000000003</v>
+        <v>1.910652</v>
       </c>
       <c r="K245" s="7">
-        <v>5.814077999999999</v>
+        <v>5.842251</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10674,25 +10674,25 @@
         <v>6</v>
       </c>
       <c r="E246" s="7">
-        <v>0.034123</v>
+        <v>0.038425</v>
       </c>
       <c r="F246" s="7">
-        <v>0.043392999999999994</v>
+        <v>0.043017</v>
       </c>
       <c r="G246" s="7">
-        <v>0.318402</v>
+        <v>0.34822899999999996</v>
       </c>
       <c r="H246" s="7">
-        <v>0.24783000000000002</v>
+        <v>0.253021</v>
       </c>
       <c r="I246" s="7">
-        <v>0.512894</v>
+        <v>0.5191870000000001</v>
       </c>
       <c r="J246" s="7">
-        <v>3.061473</v>
+        <v>2.783684</v>
       </c>
       <c r="K246" s="7">
-        <v>14.786252</v>
+        <v>15.01059</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10709,25 +10709,25 @@
         <v>3</v>
       </c>
       <c r="E247" s="7">
-        <v>0.046305</v>
+        <v>0.048505</v>
       </c>
       <c r="F247" s="7">
-        <v>0.093781</v>
+        <v>0.093552</v>
       </c>
       <c r="G247" s="7">
-        <v>0.241658</v>
+        <v>0.24712900000000002</v>
       </c>
       <c r="H247" s="7">
-        <v>0.16979399999999997</v>
+        <v>0.17225300000000002</v>
       </c>
       <c r="I247" s="7">
-        <v>0.45735</v>
+        <v>0.460413</v>
       </c>
       <c r="J247" s="7">
-        <v>1.904434</v>
+        <v>1.901585</v>
       </c>
       <c r="K247" s="7">
-        <v>4.675231</v>
+        <v>4.689024</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10744,25 +10744,25 @@
         <v>4</v>
       </c>
       <c r="E248" s="7">
-        <v>0.015215000000000001</v>
+        <v>0.014027000000000001</v>
       </c>
       <c r="F248" s="7">
-        <v>0.023351</v>
+        <v>0.023946000000000002</v>
       </c>
       <c r="G248" s="7">
-        <v>0.18738</v>
+        <v>0.19267</v>
       </c>
       <c r="H248" s="7">
-        <v>0.092959</v>
+        <v>0.09168</v>
       </c>
       <c r="I248" s="7">
-        <v>0.40233800000000003</v>
+        <v>0.40069699999999997</v>
       </c>
       <c r="J248" s="7">
-        <v>1.542766</v>
+        <v>1.5162360000000001</v>
       </c>
       <c r="K248" s="7">
-        <v>3.8545339999999997</v>
+        <v>3.856493</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10779,25 +10779,25 @@
         <v>2</v>
       </c>
       <c r="E249" s="7">
-        <v>0.026954</v>
+        <v>0.027700999999999996</v>
       </c>
       <c r="F249" s="7">
-        <v>0.086677</v>
+        <v>0.087004</v>
       </c>
       <c r="G249" s="7">
-        <v>0.21688</v>
+        <v>0.21732500000000002</v>
       </c>
       <c r="H249" s="7">
-        <v>0.144653</v>
+        <v>0.145486</v>
       </c>
       <c r="I249" s="7">
-        <v>0.5143610000000001</v>
+        <v>0.515463</v>
       </c>
       <c r="J249" s="7">
-        <v>4.2987720000000005</v>
+        <v>4.2928370000000005</v>
       </c>
       <c r="K249" s="7">
-        <v>7.213937</v>
+        <v>7.216407</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10814,25 +10814,25 @@
         <v>4</v>
       </c>
       <c r="E250" s="7">
-        <v>0.028534999999999998</v>
+        <v>0.030331</v>
       </c>
       <c r="F250" s="7">
-        <v>0.072826</v>
+        <v>0.070062</v>
       </c>
       <c r="G250" s="7">
-        <v>0.285929</v>
+        <v>0.298309</v>
       </c>
       <c r="H250" s="7">
-        <v>0.21300999999999998</v>
+        <v>0.21512799999999999</v>
       </c>
       <c r="I250" s="7">
-        <v>0.540368</v>
+        <v>0.5430579999999999</v>
       </c>
       <c r="J250" s="7">
-        <v>3.391097</v>
+        <v>3.216333</v>
       </c>
       <c r="K250" s="7">
-        <v>8.711272000000001</v>
+        <v>8.756482</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10849,25 +10849,25 @@
         <v>5</v>
       </c>
       <c r="E251" s="7">
-        <v>0.028972</v>
+        <v>0.031429</v>
       </c>
       <c r="F251" s="7">
-        <v>0.065955</v>
+        <v>0.06438100000000001</v>
       </c>
       <c r="G251" s="7">
-        <v>0.300194</v>
+        <v>0.31813800000000003</v>
       </c>
       <c r="H251" s="7">
-        <v>0.22984400000000002</v>
+        <v>0.23278</v>
       </c>
       <c r="I251" s="7">
-        <v>0.548354</v>
+        <v>0.5520499999999999</v>
       </c>
       <c r="J251" s="7">
-        <v>3.997573</v>
+        <v>3.7342</v>
       </c>
       <c r="K251" s="7">
-        <v>11.686712</v>
+        <v>11.758167</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10884,25 +10884,25 @@
         <v>6</v>
       </c>
       <c r="E252" s="7">
-        <v>0.028134000000000003</v>
+        <v>0.031676</v>
       </c>
       <c r="F252" s="7">
-        <v>0.049729</v>
+        <v>0.04807</v>
       </c>
       <c r="G252" s="7">
-        <v>0.317974</v>
+        <v>0.345285</v>
       </c>
       <c r="H252" s="7">
-        <v>0.24652100000000002</v>
+        <v>0.25081600000000004</v>
       </c>
       <c r="I252" s="7">
-        <v>0.51966</v>
+        <v>0.524895</v>
       </c>
       <c r="J252" s="7">
-        <v>3.569025</v>
+        <v>3.292376</v>
       </c>
       <c r="K252" s="7">
-        <v>14.29886</v>
+        <v>14.413186000000001</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10919,25 +10919,25 @@
         <v>3</v>
       </c>
       <c r="E253" s="7">
-        <v>0.05476</v>
+        <v>0.056207</v>
       </c>
       <c r="F253" s="7">
-        <v>0.104062</v>
+        <v>0.102572</v>
       </c>
       <c r="G253" s="7">
-        <v>0.240611</v>
+        <v>0.24748599999999998</v>
       </c>
       <c r="H253" s="7">
-        <v>0.192616</v>
+        <v>0.194252</v>
       </c>
       <c r="I253" s="7">
-        <v>0.47401499999999996</v>
+        <v>0.47603700000000004</v>
       </c>
       <c r="J253" s="7">
-        <v>2.199687</v>
+        <v>2.168921</v>
       </c>
       <c r="K253" s="7">
-        <v>5.701635</v>
+        <v>5.727921</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10954,25 +10954,25 @@
         <v>5</v>
       </c>
       <c r="E254" s="7">
-        <v>0.080444</v>
+        <v>0.083513</v>
       </c>
       <c r="F254" s="7">
-        <v>0.137939</v>
+        <v>0.136331</v>
       </c>
       <c r="G254" s="7">
-        <v>0.326976</v>
+        <v>0.347091</v>
       </c>
       <c r="H254" s="7">
-        <v>0.276642</v>
+        <v>0.280269</v>
       </c>
       <c r="I254" s="7">
-        <v>0.5535049999999999</v>
+        <v>0.5579189999999999</v>
       </c>
       <c r="J254" s="7">
-        <v>3.381631</v>
+        <v>3.253</v>
       </c>
       <c r="K254" s="7">
-        <v>10.247476999999998</v>
+        <v>10.313258000000001</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10989,25 +10989,25 @@
         <v>6</v>
       </c>
       <c r="E255" s="7">
-        <v>0.088783</v>
+        <v>0.09194200000000001</v>
       </c>
       <c r="F255" s="7">
-        <v>0.146488</v>
+        <v>0.144633</v>
       </c>
       <c r="G255" s="7">
-        <v>0.349729</v>
+        <v>0.37469499999999994</v>
       </c>
       <c r="H255" s="7">
-        <v>0.302152</v>
+        <v>0.305931</v>
       </c>
       <c r="I255" s="7">
-        <v>0.566107</v>
+        <v>0.570651</v>
       </c>
       <c r="J255" s="7">
-        <v>3.646485</v>
+        <v>3.449131</v>
       </c>
       <c r="K255" s="7">
-        <v>11.389726000000001</v>
+        <v>11.465565999999999</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11024,25 +11024,25 @@
         <v>4</v>
       </c>
       <c r="E256" s="7">
-        <v>0.014119</v>
+        <v>0.013274999999999999</v>
       </c>
       <c r="F256" s="7">
-        <v>0.025794</v>
+        <v>0.026153</v>
       </c>
       <c r="G256" s="7">
-        <v>0.169074</v>
+        <v>0.173134</v>
       </c>
       <c r="H256" s="7">
-        <v>0.08281599999999999</v>
+        <v>0.081915</v>
       </c>
       <c r="I256" s="7">
-        <v>0.39360700000000004</v>
+        <v>0.392447</v>
       </c>
       <c r="J256" s="7">
-        <v>1.877483</v>
+        <v>1.865325</v>
       </c>
       <c r="K256" s="7">
-        <v>5.080701</v>
+        <v>5.076035</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11059,25 +11059,25 @@
         <v>4</v>
       </c>
       <c r="E257" s="7">
-        <v>0.038199000000000004</v>
+        <v>0.040005</v>
       </c>
       <c r="F257" s="7">
-        <v>0.057271</v>
+        <v>0.056048999999999995</v>
       </c>
       <c r="G257" s="7">
-        <v>0.26189</v>
+        <v>0.267713</v>
       </c>
       <c r="H257" s="7">
-        <v>0.193718</v>
+        <v>0.195795</v>
       </c>
       <c r="I257" s="7">
-        <v>0.553789</v>
+        <v>0.556493</v>
       </c>
       <c r="J257" s="7">
-        <v>2.9549529999999997</v>
+        <v>2.924189</v>
       </c>
       <c r="K257" s="7">
-        <v>6.249235</v>
+        <v>6.259075</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11094,25 +11094,25 @@
         <v>4</v>
       </c>
       <c r="E258" s="7">
-        <v>0.029397000000000003</v>
+        <v>0.030259</v>
       </c>
       <c r="F258" s="7">
-        <v>0.052004999999999996</v>
+        <v>0.050606</v>
       </c>
       <c r="G258" s="7">
-        <v>0.23704999999999998</v>
+        <v>0.23950600000000002</v>
       </c>
       <c r="H258" s="7">
-        <v>0.17180299999999998</v>
+        <v>0.17278400000000002</v>
       </c>
       <c r="I258" s="7">
-        <v>0.5244789999999999</v>
+        <v>0.525755</v>
       </c>
       <c r="J258" s="7">
-        <v>2.866023</v>
+        <v>2.847475</v>
       </c>
       <c r="K258" s="7">
-        <v>5.377299000000001</v>
+        <v>5.379596</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11129,25 +11129,25 @@
         <v>5</v>
       </c>
       <c r="E259" s="7">
-        <v>0.047374</v>
+        <v>0.050214999999999996</v>
       </c>
       <c r="F259" s="7">
-        <v>0.065476</v>
+        <v>0.064384</v>
       </c>
       <c r="G259" s="7">
-        <v>0.29620799999999997</v>
+        <v>0.310355</v>
       </c>
       <c r="H259" s="7">
-        <v>0.222686</v>
+        <v>0.226003</v>
       </c>
       <c r="I259" s="7">
-        <v>0.585143</v>
+        <v>0.5894429999999999</v>
       </c>
       <c r="J259" s="7">
-        <v>3.036396</v>
+        <v>2.987555</v>
       </c>
       <c r="K259" s="7">
-        <v>7.579583</v>
+        <v>7.602028000000001</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11164,25 +11164,25 @@
         <v>6</v>
       </c>
       <c r="E260" s="7">
-        <v>0.0014219999999999999</v>
+        <v>-0.005109</v>
       </c>
       <c r="F260" s="7">
-        <v>-0.05901</v>
+        <v>-0.067757</v>
       </c>
       <c r="G260" s="7">
-        <v>0.194379</v>
+        <v>0.172939</v>
       </c>
       <c r="H260" s="7">
-        <v>0.10322300000000001</v>
+        <v>0.096028</v>
       </c>
       <c r="I260" s="7">
-        <v>0.6229520000000001</v>
+        <v>0.612367</v>
       </c>
       <c r="J260" s="7">
-        <v>4.037162</v>
+        <v>4.0548779999999995</v>
       </c>
       <c r="K260" s="7">
-        <v>13.5973</v>
+        <v>13.433348</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11199,25 +11199,25 @@
         <v>2</v>
       </c>
       <c r="E261" s="7">
-        <v>0.04362</v>
+        <v>0.046883999999999995</v>
       </c>
       <c r="F261" s="7">
-        <v>0.102424</v>
+        <v>0.103926</v>
       </c>
       <c r="G261" s="7">
-        <v>0.21550999999999998</v>
+        <v>0.22004300000000002</v>
       </c>
       <c r="H261" s="7">
-        <v>0.16985399999999998</v>
+        <v>0.17351400000000003</v>
       </c>
       <c r="I261" s="7">
-        <v>0.44475299999999995</v>
+        <v>0.449272</v>
       </c>
       <c r="J261" s="7">
-        <v>2.5196389999999997</v>
+        <v>2.524283</v>
       </c>
       <c r="K261" s="7">
-        <v>4.575311</v>
+        <v>4.590289</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -11234,25 +11234,25 @@
         <v>6</v>
       </c>
       <c r="E262" s="7">
-        <v>0.08128</v>
+        <v>0.094918</v>
       </c>
       <c r="F262" s="7">
-        <v>0.058331999999999995</v>
+        <v>0.065009</v>
       </c>
       <c r="G262" s="7">
-        <v>0.251262</v>
+        <v>0.263282</v>
       </c>
       <c r="H262" s="7">
-        <v>0.176172</v>
+        <v>0.191007</v>
       </c>
       <c r="I262" s="7">
-        <v>0.675035</v>
+        <v>0.696161</v>
       </c>
       <c r="J262" s="7">
-        <v>4.880788</v>
+        <v>4.557746</v>
       </c>
       <c r="K262" s="7">
-        <v>20.704157</v>
+        <v>21.12886</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -11269,10 +11269,10 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.002884</v>
+        <v>-0.0016339999999999998</v>
       </c>
       <c r="F263" s="7">
-        <v>-0.055490000000000005</v>
+        <v>-0.06415</v>
       </c>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
@@ -11294,22 +11294,22 @@
         <v>3</v>
       </c>
       <c r="E264" s="7">
-        <v>0.053989</v>
+        <v>0.055972</v>
       </c>
       <c r="F264" s="7">
-        <v>0.1108</v>
+        <v>0.110207</v>
       </c>
       <c r="G264" s="7">
-        <v>0.270959</v>
+        <v>0.27902699999999997</v>
       </c>
       <c r="H264" s="7">
-        <v>0.20567</v>
+        <v>0.207939</v>
       </c>
       <c r="I264" s="7">
-        <v>0.528419</v>
+        <v>0.531295</v>
       </c>
       <c r="J264" s="7">
-        <v>2.419477</v>
+        <v>2.3875640000000002</v>
       </c>
       <c r="K264" s="7"/>
     </row>
@@ -11327,22 +11327,22 @@
         <v>3</v>
       </c>
       <c r="E265" s="7">
-        <v>0.010351999999999998</v>
+        <v>0.010433</v>
       </c>
       <c r="F265" s="7">
-        <v>0.040556</v>
+        <v>0.039987</v>
       </c>
       <c r="G265" s="7">
-        <v>0.131687</v>
+        <v>0.130519</v>
       </c>
       <c r="H265" s="7">
-        <v>0.070683</v>
+        <v>0.070769</v>
       </c>
       <c r="I265" s="7">
-        <v>0.468159</v>
+        <v>0.468277</v>
       </c>
       <c r="J265" s="7">
-        <v>2.655626</v>
+        <v>2.6723719999999997</v>
       </c>
       <c r="K265" s="7"/>
     </row>
@@ -11360,19 +11360,19 @@
         <v>5</v>
       </c>
       <c r="E266" s="7">
-        <v>0.005620000000000001</v>
+        <v>0.0066159999999999995</v>
       </c>
       <c r="F266" s="7">
-        <v>0.021315</v>
+        <v>0.016524</v>
       </c>
       <c r="G266" s="7">
-        <v>0.302165</v>
+        <v>0.329668</v>
       </c>
       <c r="H266" s="7">
-        <v>0.19838899999999998</v>
+        <v>0.199576</v>
       </c>
       <c r="I266" s="7">
-        <v>0.459775</v>
+        <v>0.46122100000000005</v>
       </c>
       <c r="J266" s="7"/>
       <c r="K266" s="7"/>
@@ -11412,22 +11412,22 @@
         <v>6</v>
       </c>
       <c r="E268" s="7">
-        <v>0.162893</v>
+        <v>0.173315</v>
       </c>
       <c r="F268" s="7">
-        <v>0.22342800000000002</v>
+        <v>0.23641600000000002</v>
       </c>
       <c r="G268" s="7">
-        <v>0.30196</v>
+        <v>0.33608499999999997</v>
       </c>
       <c r="H268" s="7">
-        <v>0.294844</v>
+        <v>0.306448</v>
       </c>
       <c r="I268" s="7">
-        <v>0.5736829999999999</v>
+        <v>0.5877859999999999</v>
       </c>
       <c r="J268" s="7">
-        <v>3.819957</v>
+        <v>3.7204230000000003</v>
       </c>
       <c r="K268" s="7"/>
     </row>
@@ -11445,19 +11445,19 @@
         <v>6</v>
       </c>
       <c r="E269" s="7">
-        <v>0.030133999999999998</v>
+        <v>0.039358</v>
       </c>
       <c r="F269" s="7">
-        <v>0.061184</v>
+        <v>0.069284</v>
       </c>
       <c r="G269" s="7">
-        <v>0.17217</v>
+        <v>0.179145</v>
       </c>
       <c r="H269" s="7">
-        <v>0.144624</v>
+        <v>0.154872</v>
       </c>
       <c r="I269" s="7">
-        <v>0.275699</v>
+        <v>0.287121</v>
       </c>
       <c r="J269" s="7"/>
       <c r="K269" s="7"/>
@@ -11476,19 +11476,19 @@
         <v>2</v>
       </c>
       <c r="E270" s="7">
-        <v>0.029948000000000002</v>
+        <v>0.031256</v>
       </c>
       <c r="F270" s="7">
-        <v>0.09870699999999999</v>
+        <v>0.09897299999999999</v>
       </c>
       <c r="G270" s="7">
-        <v>0.206646</v>
+        <v>0.20691299999999999</v>
       </c>
       <c r="H270" s="7">
-        <v>0.143731</v>
+        <v>0.145183</v>
       </c>
       <c r="I270" s="7">
-        <v>0.47972299999999996</v>
+        <v>0.48160200000000003</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11507,22 +11507,22 @@
         <v>2</v>
       </c>
       <c r="E271" s="7">
-        <v>0.018068999999999998</v>
+        <v>0.019314</v>
       </c>
       <c r="F271" s="7">
-        <v>0.054010999999999997</v>
+        <v>0.055789</v>
       </c>
       <c r="G271" s="7">
-        <v>0.187389</v>
+        <v>0.190567</v>
       </c>
       <c r="H271" s="7">
-        <v>0.131437</v>
+        <v>0.13282</v>
       </c>
       <c r="I271" s="7">
-        <v>0.47519100000000003</v>
+        <v>0.476994</v>
       </c>
       <c r="J271" s="7">
-        <v>3.076684</v>
+        <v>3.0846679999999997</v>
       </c>
       <c r="K271" s="7"/>
     </row>
@@ -11540,22 +11540,22 @@
         <v>5</v>
       </c>
       <c r="E272" s="7">
-        <v>0.003944</v>
+        <v>0.003903</v>
       </c>
       <c r="F272" s="7">
-        <v>0.002305</v>
+        <v>0.001488</v>
       </c>
       <c r="G272" s="7">
-        <v>0.194602</v>
+        <v>0.20474799999999999</v>
       </c>
       <c r="H272" s="7">
-        <v>0.13491</v>
+        <v>0.13486399999999998</v>
       </c>
       <c r="I272" s="7">
-        <v>0.549681</v>
+        <v>0.5496179999999999</v>
       </c>
       <c r="J272" s="7">
-        <v>2.863479</v>
+        <v>2.791757</v>
       </c>
       <c r="K272" s="7"/>
     </row>
@@ -11573,19 +11573,19 @@
         <v>5</v>
       </c>
       <c r="E273" s="7">
-        <v>0.043392999999999994</v>
+        <v>0.051059</v>
       </c>
       <c r="F273" s="7">
-        <v>0.10135899999999999</v>
+        <v>0.10749800000000001</v>
       </c>
       <c r="G273" s="7">
-        <v>0.235784</v>
+        <v>0.255606</v>
       </c>
       <c r="H273" s="7">
-        <v>0.172261</v>
+        <v>0.18087499999999998</v>
       </c>
       <c r="I273" s="7">
-        <v>0.522771</v>
+        <v>0.53396</v>
       </c>
       <c r="J273" s="7"/>
       <c r="K273" s="7"/>
@@ -11604,19 +11604,19 @@
         <v>5</v>
       </c>
       <c r="E274" s="7">
-        <v>0.055765</v>
+        <v>0.055353000000000006</v>
       </c>
       <c r="F274" s="7">
-        <v>0.075411</v>
+        <v>0.068191</v>
       </c>
       <c r="G274" s="7">
-        <v>0.185548</v>
+        <v>0.19281199999999998</v>
       </c>
       <c r="H274" s="7">
-        <v>0.179363</v>
+        <v>0.178903</v>
       </c>
       <c r="I274" s="7">
-        <v>0.495865</v>
+        <v>0.495281</v>
       </c>
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
@@ -11635,19 +11635,19 @@
         <v>4</v>
       </c>
       <c r="E275" s="7">
-        <v>0.036945</v>
+        <v>0.039798</v>
       </c>
       <c r="F275" s="7">
-        <v>0.053516</v>
+        <v>0.051569000000000004</v>
       </c>
       <c r="G275" s="7">
-        <v>0.30132200000000003</v>
+        <v>0.315288</v>
       </c>
       <c r="H275" s="7">
-        <v>0.23155799999999999</v>
+        <v>0.23494700000000002</v>
       </c>
       <c r="I275" s="7">
-        <v>0.38499099999999997</v>
+        <v>0.38880200000000004</v>
       </c>
       <c r="J275" s="7"/>
       <c r="K275" s="7"/>
@@ -11666,19 +11666,19 @@
         <v>5</v>
       </c>
       <c r="E276" s="7">
-        <v>0.045970000000000004</v>
+        <v>0.052313</v>
       </c>
       <c r="F276" s="7">
-        <v>0.06843300000000001</v>
+        <v>0.070548</v>
       </c>
       <c r="G276" s="7">
-        <v>0.265609</v>
+        <v>0.269343</v>
       </c>
       <c r="H276" s="7">
-        <v>0.212993</v>
+        <v>0.22034900000000002</v>
       </c>
       <c r="I276" s="7">
-        <v>0.36141</v>
+        <v>0.369666</v>
       </c>
       <c r="J276" s="7"/>
       <c r="K276" s="7"/>
@@ -11697,19 +11697,19 @@
         <v>6</v>
       </c>
       <c r="E277" s="7">
-        <v>0.199958</v>
+        <v>0.195708</v>
       </c>
       <c r="F277" s="7">
-        <v>0.275678</v>
+        <v>0.27423</v>
       </c>
       <c r="G277" s="7">
-        <v>0.392831</v>
+        <v>0.42588099999999995</v>
       </c>
       <c r="H277" s="7">
-        <v>0.45779200000000003</v>
+        <v>0.452629</v>
       </c>
       <c r="I277" s="7">
-        <v>0.660394</v>
+        <v>0.654513</v>
       </c>
       <c r="J277" s="7"/>
       <c r="K277" s="7"/>
@@ -11728,22 +11728,22 @@
         <v>4</v>
       </c>
       <c r="E278" s="7">
-        <v>0.011557</v>
+        <v>0.014145000000000001</v>
       </c>
       <c r="F278" s="7">
-        <v>0.026474</v>
+        <v>0.027719</v>
       </c>
       <c r="G278" s="7">
-        <v>0.189545</v>
+        <v>0.19917100000000001</v>
       </c>
       <c r="H278" s="7">
-        <v>0.13316</v>
+        <v>0.13606</v>
       </c>
       <c r="I278" s="7">
-        <v>0.502725</v>
+        <v>0.506571</v>
       </c>
       <c r="J278" s="7">
-        <v>3.0358620000000003</v>
+        <v>3.025566</v>
       </c>
       <c r="K278" s="7"/>
     </row>
@@ -11761,25 +11761,25 @@
         <v>5</v>
       </c>
       <c r="E279" s="7">
-        <v>0.054118000000000006</v>
+        <v>0.058385</v>
       </c>
       <c r="F279" s="7">
-        <v>0.131566</v>
+        <v>0.132657</v>
       </c>
       <c r="G279" s="7">
-        <v>0.357371</v>
+        <v>0.375508</v>
       </c>
       <c r="H279" s="7">
-        <v>0.25790199999999996</v>
+        <v>0.262994</v>
       </c>
       <c r="I279" s="7">
-        <v>0.5914280000000001</v>
+        <v>0.597871</v>
       </c>
       <c r="J279" s="7">
-        <v>2.784205</v>
+        <v>2.675498</v>
       </c>
       <c r="K279" s="7">
-        <v>6.8084050000000005</v>
+        <v>6.855748</v>
       </c>
     </row>
     <row r="280" spans="1:11" x14ac:dyDescent="0.25">
@@ -11796,25 +11796,25 @@
         <v>2</v>
       </c>
       <c r="E280" s="7">
-        <v>0.031244</v>
+        <v>0.03254</v>
       </c>
       <c r="F280" s="7">
-        <v>0.091501</v>
+        <v>0.091945</v>
       </c>
       <c r="G280" s="7">
-        <v>0.201571</v>
+        <v>0.202095</v>
       </c>
       <c r="H280" s="7">
-        <v>0.140186</v>
+        <v>0.141619</v>
       </c>
       <c r="I280" s="7">
-        <v>0.472918</v>
+        <v>0.474769</v>
       </c>
       <c r="J280" s="7">
-        <v>2.2209280000000002</v>
+        <v>2.222864</v>
       </c>
       <c r="K280" s="7">
-        <v>4.1723110000000005</v>
+        <v>4.176249</v>
       </c>
     </row>
     <row r="281" spans="1:11" x14ac:dyDescent="0.25">
@@ -11831,25 +11831,25 @@
         <v>6</v>
       </c>
       <c r="E281" s="7">
-        <v>0.019639</v>
+        <v>0.020528</v>
       </c>
       <c r="F281" s="7">
-        <v>0.018108</v>
+        <v>0.017495</v>
       </c>
       <c r="G281" s="7">
-        <v>0.12232799999999999</v>
+        <v>0.121874</v>
       </c>
       <c r="H281" s="7">
-        <v>0.060934999999999996</v>
+        <v>0.06186</v>
       </c>
       <c r="I281" s="7">
-        <v>0.30720600000000003</v>
+        <v>0.308346</v>
       </c>
       <c r="J281" s="7">
-        <v>1.7910810000000001</v>
+        <v>1.773441</v>
       </c>
       <c r="K281" s="7">
-        <v>5.1468</v>
+        <v>5.143686</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11866,25 +11866,25 @@
         <v>6</v>
       </c>
       <c r="E282" s="7">
-        <v>0.031271</v>
+        <v>0.037485</v>
       </c>
       <c r="F282" s="7">
-        <v>0.039051</v>
+        <v>0.038653</v>
       </c>
       <c r="G282" s="7">
-        <v>0.292711</v>
+        <v>0.327401</v>
       </c>
       <c r="H282" s="7">
-        <v>0.237504</v>
+        <v>0.24495999999999998</v>
       </c>
       <c r="I282" s="7">
-        <v>0.453677</v>
+        <v>0.462436</v>
       </c>
       <c r="J282" s="7">
-        <v>2.667606</v>
+        <v>2.411181</v>
       </c>
       <c r="K282" s="7">
-        <v>12.570476000000001</v>
+        <v>12.750392</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11901,25 +11901,25 @@
         <v>4</v>
       </c>
       <c r="E283" s="7">
-        <v>0.027000000000000003</v>
+        <v>0.02323</v>
       </c>
       <c r="F283" s="7">
-        <v>0.029216000000000002</v>
+        <v>0.026046</v>
       </c>
       <c r="G283" s="7">
-        <v>0.18871400000000002</v>
+        <v>0.191044</v>
       </c>
       <c r="H283" s="7">
-        <v>0.068125</v>
+        <v>0.064204</v>
       </c>
       <c r="I283" s="7">
-        <v>0.403771</v>
+        <v>0.39861800000000003</v>
       </c>
       <c r="J283" s="7">
-        <v>1.7534710000000002</v>
+        <v>1.7078829999999998</v>
       </c>
       <c r="K283" s="7">
-        <v>3.6929770000000004</v>
+        <v>3.683182</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11936,25 +11936,25 @@
         <v>6</v>
       </c>
       <c r="E284" s="7">
-        <v>0.066134</v>
+        <v>0.07168000000000001</v>
       </c>
       <c r="F284" s="7">
-        <v>0.135762</v>
+        <v>0.13861700000000002</v>
       </c>
       <c r="G284" s="7">
-        <v>0.34546</v>
+        <v>0.37018500000000004</v>
       </c>
       <c r="H284" s="7">
-        <v>0.261183</v>
+        <v>0.267744</v>
       </c>
       <c r="I284" s="7">
-        <v>0.53573</v>
+        <v>0.54372</v>
       </c>
       <c r="J284" s="7">
-        <v>3.040911</v>
+        <v>2.854482</v>
       </c>
       <c r="K284" s="7">
-        <v>10.410099</v>
+        <v>10.543954000000001</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11971,25 +11971,25 @@
         <v>3</v>
       </c>
       <c r="E285" s="7">
-        <v>0.028961999999999998</v>
+        <v>0.030390999999999998</v>
       </c>
       <c r="F285" s="7">
-        <v>0.087236</v>
+        <v>0.08734600000000001</v>
       </c>
       <c r="G285" s="7">
-        <v>0.20411300000000002</v>
+        <v>0.20888</v>
       </c>
       <c r="H285" s="7">
-        <v>0.15367</v>
+        <v>0.15527100000000002</v>
       </c>
       <c r="I285" s="7">
-        <v>0.472409</v>
+        <v>0.474453</v>
       </c>
       <c r="J285" s="7">
-        <v>2.986029</v>
+        <v>2.988784</v>
       </c>
       <c r="K285" s="7">
-        <v>5.361643</v>
+        <v>5.36615</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -12006,25 +12006,25 @@
         <v>3</v>
       </c>
       <c r="E286" s="7">
-        <v>0.024302999999999998</v>
+        <v>0.024281</v>
       </c>
       <c r="F286" s="7">
-        <v>0.07392800000000001</v>
+        <v>0.073972</v>
       </c>
       <c r="G286" s="7">
-        <v>0.184656</v>
+        <v>0.18351900000000002</v>
       </c>
       <c r="H286" s="7">
-        <v>0.113912</v>
+        <v>0.113888</v>
       </c>
       <c r="I286" s="7">
-        <v>0.452891</v>
+        <v>0.45285899999999996</v>
       </c>
       <c r="J286" s="7">
-        <v>2.322473</v>
+        <v>2.315514</v>
       </c>
       <c r="K286" s="7">
-        <v>4.230486</v>
+        <v>4.230371</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12041,25 +12041,25 @@
         <v>5</v>
       </c>
       <c r="E287" s="7">
-        <v>0.020459</v>
+        <v>0.021797</v>
       </c>
       <c r="F287" s="7">
-        <v>0.032804</v>
+        <v>0.03339</v>
       </c>
       <c r="G287" s="7">
-        <v>0.08695499999999999</v>
+        <v>0.08880800000000001</v>
       </c>
       <c r="H287" s="7">
-        <v>0.04782600000000001</v>
+        <v>0.0492</v>
       </c>
       <c r="I287" s="7">
-        <v>0.27674299999999996</v>
+        <v>0.278418</v>
       </c>
       <c r="J287" s="7">
-        <v>1.9677269999999998</v>
+        <v>1.915359</v>
       </c>
       <c r="K287" s="7">
-        <v>5.820013</v>
+        <v>5.795011</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12076,25 +12076,25 @@
         <v>3</v>
       </c>
       <c r="E288" s="7">
-        <v>0.023272</v>
+        <v>0.022692999999999998</v>
       </c>
       <c r="F288" s="7">
-        <v>0.054168</v>
+        <v>0.051993</v>
       </c>
       <c r="G288" s="7">
-        <v>0.221968</v>
+        <v>0.227585</v>
       </c>
       <c r="H288" s="7">
-        <v>0.07359</v>
+        <v>0.07298199999999999</v>
       </c>
       <c r="I288" s="7">
-        <v>0.430088</v>
+        <v>0.429278</v>
       </c>
       <c r="J288" s="7">
-        <v>1.994248</v>
+        <v>1.990681</v>
       </c>
       <c r="K288" s="7">
-        <v>3.664749</v>
+        <v>3.6599090000000003</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12111,25 +12111,25 @@
         <v>5</v>
       </c>
       <c r="E289" s="7">
-        <v>0.041946000000000004</v>
+        <v>0.043169000000000006</v>
       </c>
       <c r="F289" s="7">
-        <v>0.08427199999999999</v>
+        <v>0.081548</v>
       </c>
       <c r="G289" s="7">
-        <v>0.267902</v>
+        <v>0.273542</v>
       </c>
       <c r="H289" s="7">
-        <v>0.19484300000000002</v>
+        <v>0.196246</v>
       </c>
       <c r="I289" s="7">
-        <v>0.541678</v>
+        <v>0.543488</v>
       </c>
       <c r="J289" s="7">
-        <v>2.7637240000000003</v>
+        <v>2.6244560000000003</v>
       </c>
       <c r="K289" s="7">
-        <v>9.48691</v>
+        <v>9.525647</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12146,25 +12146,25 @@
         <v>6</v>
       </c>
       <c r="E290" s="7">
-        <v>-0.004337</v>
+        <v>-0.010304</v>
       </c>
       <c r="F290" s="7">
-        <v>-0.074353</v>
+        <v>-0.081472</v>
       </c>
       <c r="G290" s="7">
-        <v>0.17485900000000001</v>
+        <v>0.15360200000000002</v>
       </c>
       <c r="H290" s="7">
-        <v>0.069033</v>
+        <v>0.062626</v>
       </c>
       <c r="I290" s="7">
-        <v>0.581395</v>
+        <v>0.571917</v>
       </c>
       <c r="J290" s="7">
-        <v>4.091749</v>
+        <v>4.107863</v>
       </c>
       <c r="K290" s="7">
-        <v>13.602414000000001</v>
+        <v>13.448875000000001</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12181,25 +12181,25 @@
         <v>3</v>
       </c>
       <c r="E291" s="7">
-        <v>0.053684</v>
+        <v>0.056315</v>
       </c>
       <c r="F291" s="7">
-        <v>0.109616</v>
+        <v>0.110585</v>
       </c>
       <c r="G291" s="7">
-        <v>0.283389</v>
+        <v>0.293039</v>
       </c>
       <c r="H291" s="7">
-        <v>0.19488499999999997</v>
+        <v>0.197868</v>
       </c>
       <c r="I291" s="7">
-        <v>0.497153</v>
+        <v>0.50089</v>
       </c>
       <c r="J291" s="7">
-        <v>1.461225</v>
+        <v>1.439289</v>
       </c>
       <c r="K291" s="7">
-        <v>3.766344</v>
+        <v>3.789841</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12216,25 +12216,25 @@
         <v>6</v>
       </c>
       <c r="E292" s="7">
-        <v>0.051980000000000005</v>
+        <v>0.055957</v>
       </c>
       <c r="F292" s="7">
-        <v>0.062159000000000006</v>
+        <v>0.059656</v>
       </c>
       <c r="G292" s="7">
-        <v>0.310047</v>
+        <v>0.331415</v>
       </c>
       <c r="H292" s="7">
-        <v>0.217333</v>
+        <v>0.221935</v>
       </c>
       <c r="I292" s="7">
-        <v>0.569043</v>
+        <v>0.5749759999999999</v>
       </c>
       <c r="J292" s="7">
-        <v>2.6343099999999997</v>
+        <v>2.4743790000000003</v>
       </c>
       <c r="K292" s="7">
-        <v>10.613271</v>
+        <v>10.706779</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12251,25 +12251,25 @@
         <v>6</v>
       </c>
       <c r="E293" s="7">
-        <v>0.022987999999999998</v>
+        <v>0.023467</v>
       </c>
       <c r="F293" s="7">
-        <v>-0.023323999999999998</v>
+        <v>-0.030962999999999997</v>
       </c>
       <c r="G293" s="7">
-        <v>0.290439</v>
+        <v>0.27642</v>
       </c>
       <c r="H293" s="7">
-        <v>0.138658</v>
+        <v>0.139191</v>
       </c>
       <c r="I293" s="7">
-        <v>0.803679</v>
+        <v>0.804524</v>
       </c>
       <c r="J293" s="7">
-        <v>4.237942</v>
+        <v>4.279132000000001</v>
       </c>
       <c r="K293" s="7">
-        <v>8.646779</v>
+        <v>8.648719999999999</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12286,25 +12286,25 @@
         <v>6</v>
       </c>
       <c r="E294" s="7">
-        <v>0.053625</v>
+        <v>0.058452000000000004</v>
       </c>
       <c r="F294" s="7">
-        <v>0.098398</v>
+        <v>0.101825</v>
       </c>
       <c r="G294" s="7">
-        <v>0.259806</v>
+        <v>0.27531700000000003</v>
       </c>
       <c r="H294" s="7">
-        <v>0.19559200000000002</v>
+        <v>0.20107</v>
       </c>
       <c r="I294" s="7">
-        <v>0.462177</v>
+        <v>0.468876</v>
       </c>
       <c r="J294" s="7">
-        <v>2.5663869999999998</v>
+        <v>2.409483</v>
       </c>
       <c r="K294" s="7">
-        <v>9.364516</v>
+        <v>9.448351</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12321,25 +12321,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.08388899999999999</v>
+        <v>0.083353</v>
       </c>
       <c r="F295" s="7">
-        <v>0.078973</v>
+        <v>0.073224</v>
       </c>
       <c r="G295" s="7">
-        <v>0.363174</v>
+        <v>0.39115900000000003</v>
       </c>
       <c r="H295" s="7">
-        <v>0.283965</v>
+        <v>0.28332999999999997</v>
       </c>
       <c r="I295" s="7">
-        <v>0.469915</v>
+        <v>0.469188</v>
       </c>
       <c r="J295" s="7">
-        <v>2.770301</v>
+        <v>2.5535390000000002</v>
       </c>
       <c r="K295" s="7">
-        <v>12.929241</v>
+        <v>13.001856</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12356,25 +12356,25 @@
         <v>4</v>
       </c>
       <c r="E296" s="7">
-        <v>0.04724300000000001</v>
+        <v>0.047785</v>
       </c>
       <c r="F296" s="7">
-        <v>0.088507</v>
+        <v>0.086263</v>
       </c>
       <c r="G296" s="7">
-        <v>0.255651</v>
+        <v>0.259822</v>
       </c>
       <c r="H296" s="7">
-        <v>0.19594999999999999</v>
+        <v>0.196569</v>
       </c>
       <c r="I296" s="7">
-        <v>0.5621820000000001</v>
+        <v>0.562991</v>
       </c>
       <c r="J296" s="7">
-        <v>2.6133409999999997</v>
+        <v>2.512605</v>
       </c>
       <c r="K296" s="7">
-        <v>6.434129</v>
+        <v>6.45665</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12391,25 +12391,25 @@
         <v>5</v>
       </c>
       <c r="E297" s="7">
-        <v>0.071775</v>
+        <v>0.076165</v>
       </c>
       <c r="F297" s="7">
-        <v>0.113483</v>
+        <v>0.11704</v>
       </c>
       <c r="G297" s="7">
-        <v>0.32555999999999996</v>
+        <v>0.34708799999999995</v>
       </c>
       <c r="H297" s="7">
-        <v>0.24392399999999997</v>
+        <v>0.24901900000000002</v>
       </c>
       <c r="I297" s="7">
-        <v>0.554486</v>
+        <v>0.5608529999999999</v>
       </c>
       <c r="J297" s="7">
-        <v>3.065433</v>
+        <v>2.9235270000000004</v>
       </c>
       <c r="K297" s="7">
-        <v>8.759119</v>
+        <v>8.845331</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12426,25 +12426,25 @@
         <v>4</v>
       </c>
       <c r="E298" s="7">
-        <v>0.041923</v>
+        <v>0.046750999999999994</v>
       </c>
       <c r="F298" s="7">
-        <v>0.081867</v>
+        <v>0.08299300000000001</v>
       </c>
       <c r="G298" s="7">
-        <v>0.260782</v>
+        <v>0.272801</v>
       </c>
       <c r="H298" s="7">
-        <v>0.149115</v>
+        <v>0.154441</v>
       </c>
       <c r="I298" s="7">
-        <v>0.420021</v>
+        <v>0.42660200000000004</v>
       </c>
       <c r="J298" s="7">
-        <v>1.564657</v>
+        <v>1.569545</v>
       </c>
       <c r="K298" s="7">
-        <v>4.221587</v>
+        <v>4.2500290000000005</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12461,25 +12461,25 @@
         <v>4</v>
       </c>
       <c r="E299" s="7">
-        <v>0.015536000000000001</v>
+        <v>0.016067</v>
       </c>
       <c r="F299" s="7">
-        <v>0.022721</v>
+        <v>0.023469000000000004</v>
       </c>
       <c r="G299" s="7">
-        <v>0.20958400000000002</v>
+        <v>0.214892</v>
       </c>
       <c r="H299" s="7">
-        <v>0.065922</v>
+        <v>0.06648</v>
       </c>
       <c r="I299" s="7">
-        <v>0.399047</v>
+        <v>0.399779</v>
       </c>
       <c r="J299" s="7">
-        <v>1.779083</v>
+        <v>1.761773</v>
       </c>
       <c r="K299" s="7">
-        <v>4.858707</v>
+        <v>4.865073</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12496,25 +12496,25 @@
         <v>6</v>
       </c>
       <c r="E300" s="7">
-        <v>0.06745899999999999</v>
+        <v>0.068325</v>
       </c>
       <c r="F300" s="7">
-        <v>0.103713</v>
+        <v>0.10004400000000001</v>
       </c>
       <c r="G300" s="7">
-        <v>0.382892</v>
+        <v>0.409724</v>
       </c>
       <c r="H300" s="7">
-        <v>0.30991199999999997</v>
+        <v>0.31097400000000003</v>
       </c>
       <c r="I300" s="7">
-        <v>0.600335</v>
+        <v>0.6016320000000001</v>
       </c>
       <c r="J300" s="7">
-        <v>3.846396</v>
+        <v>3.540895</v>
       </c>
       <c r="K300" s="7">
-        <v>15.941495</v>
+        <v>16.049728</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12531,25 +12531,25 @@
         <v>5</v>
       </c>
       <c r="E301" s="7">
-        <v>0.063472</v>
+        <v>0.066451</v>
       </c>
       <c r="F301" s="7">
-        <v>0.10747</v>
+        <v>0.1045</v>
       </c>
       <c r="G301" s="7">
-        <v>0.372172</v>
+        <v>0.39392299999999997</v>
       </c>
       <c r="H301" s="7">
-        <v>0.30428</v>
+        <v>0.307934</v>
       </c>
       <c r="I301" s="7">
-        <v>0.594087</v>
+        <v>0.598553</v>
       </c>
       <c r="J301" s="7">
-        <v>3.415313</v>
+        <v>3.1999579999999996</v>
       </c>
       <c r="K301" s="7">
-        <v>10.937046</v>
+        <v>11.014081000000001</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12566,25 +12566,25 @@
         <v>4</v>
       </c>
       <c r="E302" s="7">
-        <v>0.054606</v>
+        <v>0.057754</v>
       </c>
       <c r="F302" s="7">
-        <v>0.091181</v>
+        <v>0.09010199999999999</v>
       </c>
       <c r="G302" s="7">
-        <v>0.337513</v>
+        <v>0.353879</v>
       </c>
       <c r="H302" s="7">
-        <v>0.260884</v>
+        <v>0.264648</v>
       </c>
       <c r="I302" s="7">
-        <v>0.594438</v>
+        <v>0.599198</v>
       </c>
       <c r="J302" s="7">
-        <v>3.391726</v>
+        <v>3.216793</v>
       </c>
       <c r="K302" s="7">
-        <v>9.863349</v>
+        <v>9.917698</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -12601,25 +12601,25 @@
         <v>2</v>
       </c>
       <c r="E303" s="7">
-        <v>0.029937000000000002</v>
+        <v>0.030142000000000002</v>
       </c>
       <c r="F303" s="7">
-        <v>0.098162</v>
+        <v>0.097853</v>
       </c>
       <c r="G303" s="7">
-        <v>0.228458</v>
+        <v>0.22994900000000001</v>
       </c>
       <c r="H303" s="7">
-        <v>0.157553</v>
+        <v>0.157783</v>
       </c>
       <c r="I303" s="7">
-        <v>0.513792</v>
+        <v>0.514093</v>
       </c>
       <c r="J303" s="7">
-        <v>2.851154</v>
+        <v>2.855906</v>
       </c>
       <c r="K303" s="7">
-        <v>5.17646</v>
+        <v>5.1746550000000004</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12636,25 +12636,25 @@
         <v>5</v>
       </c>
       <c r="E304" s="7">
-        <v>0.073613</v>
+        <v>0.079623</v>
       </c>
       <c r="F304" s="7">
-        <v>0.134742</v>
+        <v>0.13655699999999998</v>
       </c>
       <c r="G304" s="7">
-        <v>0.392617</v>
+        <v>0.414128</v>
       </c>
       <c r="H304" s="7">
-        <v>0.31258400000000003</v>
+        <v>0.319932</v>
       </c>
       <c r="I304" s="7">
-        <v>0.677274</v>
+        <v>0.6866639999999999</v>
       </c>
       <c r="J304" s="7">
-        <v>3.428914</v>
+        <v>3.281332</v>
       </c>
       <c r="K304" s="7">
-        <v>9.993028</v>
+        <v>10.087551999999999</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12671,25 +12671,25 @@
         <v>6</v>
       </c>
       <c r="E305" s="7">
-        <v>0.07960099999999999</v>
+        <v>0.08992800000000001</v>
       </c>
       <c r="F305" s="7">
-        <v>0.134699</v>
+        <v>0.139619</v>
       </c>
       <c r="G305" s="7">
-        <v>0.417865</v>
+        <v>0.449822</v>
       </c>
       <c r="H305" s="7">
-        <v>0.33597499999999997</v>
+        <v>0.348754</v>
       </c>
       <c r="I305" s="7">
-        <v>0.733462</v>
+        <v>0.750043</v>
       </c>
       <c r="J305" s="7">
-        <v>3.7328609999999998</v>
+        <v>3.541717</v>
       </c>
       <c r="K305" s="7">
-        <v>12.739734</v>
+        <v>12.929326000000001</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12706,25 +12706,25 @@
         <v>6</v>
       </c>
       <c r="E306" s="7">
-        <v>0.076303</v>
+        <v>0.081899</v>
       </c>
       <c r="F306" s="7">
-        <v>0.161917</v>
+        <v>0.162457</v>
       </c>
       <c r="G306" s="7">
-        <v>0.39783</v>
+        <v>0.435715</v>
       </c>
       <c r="H306" s="7">
-        <v>0.35218299999999997</v>
+        <v>0.359215</v>
       </c>
       <c r="I306" s="7">
-        <v>0.612352</v>
+        <v>0.620736</v>
       </c>
       <c r="J306" s="7">
-        <v>2.550537</v>
+        <v>2.370269</v>
       </c>
       <c r="K306" s="7">
-        <v>8.990624</v>
+        <v>9.143669</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12741,22 +12741,22 @@
         <v>4</v>
       </c>
       <c r="E307" s="7">
-        <v>0.205675</v>
+        <v>0.218478</v>
       </c>
       <c r="F307" s="7">
-        <v>0.288427</v>
+        <v>0.303639</v>
       </c>
       <c r="G307" s="7">
-        <v>0.36615499999999995</v>
+        <v>0.39189500000000005</v>
       </c>
       <c r="H307" s="7">
-        <v>0.35104799999999997</v>
+        <v>0.365396</v>
       </c>
       <c r="I307" s="7">
-        <v>0.7627379999999999</v>
+        <v>0.781458</v>
       </c>
       <c r="J307" s="7">
-        <v>3.983247</v>
+        <v>3.968489</v>
       </c>
       <c r="K307" s="7"/>
     </row>
@@ -12774,25 +12774,25 @@
         <v>5</v>
       </c>
       <c r="E308" s="7">
-        <v>0.057449</v>
+        <v>0.059036</v>
       </c>
       <c r="F308" s="7">
-        <v>0.083252</v>
+        <v>0.08123100000000001</v>
       </c>
       <c r="G308" s="7">
-        <v>0.329797</v>
+        <v>0.354056</v>
       </c>
       <c r="H308" s="7">
-        <v>0.22715699999999997</v>
+        <v>0.22899899999999998</v>
       </c>
       <c r="I308" s="7">
-        <v>0.530226</v>
+        <v>0.532523</v>
       </c>
       <c r="J308" s="7">
-        <v>2.794031</v>
+        <v>2.5219210000000003</v>
       </c>
       <c r="K308" s="7">
-        <v>11.558532</v>
+        <v>11.669283</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -12809,25 +12809,25 @@
         <v>6</v>
       </c>
       <c r="E309" s="7">
-        <v>0.020339999999999997</v>
+        <v>0.022428</v>
       </c>
       <c r="F309" s="7">
-        <v>0.038142</v>
+        <v>0.039756</v>
       </c>
       <c r="G309" s="7">
-        <v>0.084588</v>
+        <v>0.085855</v>
       </c>
       <c r="H309" s="7">
-        <v>0.057379</v>
+        <v>0.059543</v>
       </c>
       <c r="I309" s="7">
-        <v>0.232483</v>
+        <v>0.235005</v>
       </c>
       <c r="J309" s="7">
-        <v>1.8275190000000001</v>
+        <v>1.795461</v>
       </c>
       <c r="K309" s="7">
-        <v>5.550908</v>
+        <v>5.538907</v>
       </c>
     </row>
     <row r="310" spans="1:11" x14ac:dyDescent="0.25">
@@ -12844,25 +12844,25 @@
         <v>6</v>
       </c>
       <c r="E310" s="7">
-        <v>0.008872999999999999</v>
+        <v>0.015322</v>
       </c>
       <c r="F310" s="7">
-        <v>0.029456000000000003</v>
+        <v>0.036152000000000004</v>
       </c>
       <c r="G310" s="7">
-        <v>0.206542</v>
+        <v>0.22624199999999997</v>
       </c>
       <c r="H310" s="7">
-        <v>0.11094699999999999</v>
+        <v>0.118048</v>
       </c>
       <c r="I310" s="7">
-        <v>0.486079</v>
+        <v>0.495577</v>
       </c>
       <c r="J310" s="7">
-        <v>2.441227</v>
+        <v>2.270928</v>
       </c>
       <c r="K310" s="7">
-        <v>7.618305</v>
+        <v>7.713843000000001</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -12879,25 +12879,25 @@
         <v>3</v>
       </c>
       <c r="E311" s="7">
-        <v>0.032795</v>
+        <v>0.034825</v>
       </c>
       <c r="F311" s="7">
-        <v>0.092135</v>
+        <v>0.09278</v>
       </c>
       <c r="G311" s="7">
-        <v>0.22477799999999998</v>
+        <v>0.228464</v>
       </c>
       <c r="H311" s="7">
-        <v>0.162191</v>
+        <v>0.164477</v>
       </c>
       <c r="I311" s="7">
-        <v>0.46676</v>
+        <v>0.46964399999999995</v>
       </c>
       <c r="J311" s="7">
-        <v>2.057829</v>
+        <v>2.0315280000000002</v>
       </c>
       <c r="K311" s="7">
-        <v>5.324979</v>
+        <v>5.349681</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -12914,25 +12914,25 @@
         <v>3</v>
       </c>
       <c r="E312" s="7">
-        <v>0.018854</v>
+        <v>0.01701</v>
       </c>
       <c r="F312" s="7">
-        <v>0.028352</v>
+        <v>0.029148999999999998</v>
       </c>
       <c r="G312" s="7">
-        <v>0.150812</v>
+        <v>0.150133</v>
       </c>
       <c r="H312" s="7">
-        <v>0.049812</v>
+        <v>0.047911999999999996</v>
       </c>
       <c r="I312" s="7">
-        <v>0.393555</v>
+        <v>0.39103299999999996</v>
       </c>
       <c r="J312" s="7">
-        <v>1.04053</v>
+        <v>1.054894</v>
       </c>
       <c r="K312" s="7">
-        <v>2.1427940000000003</v>
+        <v>2.136337</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>13.05.2026 10:27:02</t>
+    <t>14.05.2026 21:28:14</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2496,25 +2496,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.018974</v>
+        <v>0.020655999999999997</v>
       </c>
       <c r="F6" s="7">
-        <v>0.038493</v>
+        <v>0.033801</v>
       </c>
       <c r="G6" s="7">
-        <v>0.213917</v>
+        <v>0.211974</v>
       </c>
       <c r="H6" s="7">
-        <v>0.119808</v>
+        <v>0.117658</v>
       </c>
       <c r="I6" s="7">
-        <v>0.440702</v>
+        <v>0.43826</v>
       </c>
       <c r="J6" s="7">
-        <v>2.239795</v>
+        <v>2.233576</v>
       </c>
       <c r="K6" s="7">
-        <v>5.738918999999999</v>
+        <v>5.725983</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2531,25 +2531,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.090409</v>
+        <v>0.094871</v>
       </c>
       <c r="F7" s="7">
-        <v>0.090633</v>
+        <v>0.11196300000000001</v>
       </c>
       <c r="G7" s="7">
-        <v>0.15712099999999998</v>
+        <v>0.16547</v>
       </c>
       <c r="H7" s="7">
-        <v>0.12878399999999998</v>
+        <v>0.13107</v>
       </c>
       <c r="I7" s="7">
-        <v>0.479304</v>
+        <v>0.470998</v>
       </c>
       <c r="J7" s="7">
-        <v>2.907212</v>
+        <v>2.915127</v>
       </c>
       <c r="K7" s="7">
-        <v>5.707028</v>
+        <v>5.720612999999999</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2566,25 +2566,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.011748000000000001</v>
+        <v>0.01542</v>
       </c>
       <c r="F8" s="7">
-        <v>0.020581000000000002</v>
+        <v>0.015537</v>
       </c>
       <c r="G8" s="7">
-        <v>0.161019</v>
+        <v>0.160215</v>
       </c>
       <c r="H8" s="7">
-        <v>0.062438</v>
+        <v>0.060823999999999996</v>
       </c>
       <c r="I8" s="7">
-        <v>0.392825</v>
+        <v>0.389451</v>
       </c>
       <c r="J8" s="7">
-        <v>1.794671</v>
+        <v>1.790425</v>
       </c>
       <c r="K8" s="7">
-        <v>3.585235</v>
+        <v>3.578269</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2601,25 +2601,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.047985</v>
+        <v>0.038133</v>
       </c>
       <c r="F9" s="7">
-        <v>0.046881000000000006</v>
+        <v>0.042096999999999996</v>
       </c>
       <c r="G9" s="7">
-        <v>0.340665</v>
+        <v>0.334445</v>
       </c>
       <c r="H9" s="7">
-        <v>0.276476</v>
+        <v>0.269434</v>
       </c>
       <c r="I9" s="7">
-        <v>0.529975</v>
+        <v>0.5288309999999999</v>
       </c>
       <c r="J9" s="7">
-        <v>3.014731</v>
+        <v>2.992582</v>
       </c>
       <c r="K9" s="7">
-        <v>10.443149</v>
+        <v>10.380018</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2636,25 +2636,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.014998000000000001</v>
+        <v>-0.010363</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.088886</v>
+        <v>-0.07707499999999999</v>
       </c>
       <c r="G10" s="7">
-        <v>0.123255</v>
+        <v>0.09890399999999999</v>
       </c>
       <c r="H10" s="7">
-        <v>0.051557000000000006</v>
+        <v>0.050789999999999995</v>
       </c>
       <c r="I10" s="7">
-        <v>0.572457</v>
+        <v>0.560421</v>
       </c>
       <c r="J10" s="7">
-        <v>4.077877</v>
+        <v>4.074175</v>
       </c>
       <c r="K10" s="7">
-        <v>13.232246</v>
+        <v>13.221871</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2671,25 +2671,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.052248</v>
+        <v>0.037932</v>
       </c>
       <c r="F11" s="7">
-        <v>0.050957</v>
+        <v>0.039367</v>
       </c>
       <c r="G11" s="7">
-        <v>0.400391</v>
+        <v>0.39021</v>
       </c>
       <c r="H11" s="7">
-        <v>0.325606</v>
+        <v>0.311977</v>
       </c>
       <c r="I11" s="7">
-        <v>0.555418</v>
+        <v>0.545792</v>
       </c>
       <c r="J11" s="7">
-        <v>2.571789</v>
+        <v>2.535066</v>
       </c>
       <c r="K11" s="7">
-        <v>12.763558</v>
+        <v>12.622046000000001</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2706,25 +2706,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.031816</v>
+        <v>0.029859</v>
       </c>
       <c r="F12" s="7">
-        <v>0.072843</v>
+        <v>0.068462</v>
       </c>
       <c r="G12" s="7">
-        <v>0.25871700000000003</v>
+        <v>0.25712399999999996</v>
       </c>
       <c r="H12" s="7">
-        <v>0.162545</v>
+        <v>0.16034800000000002</v>
       </c>
       <c r="I12" s="7">
-        <v>0.480555</v>
+        <v>0.47856099999999996</v>
       </c>
       <c r="J12" s="7">
-        <v>2.610293</v>
+        <v>2.6034699999999997</v>
       </c>
       <c r="K12" s="7">
-        <v>4.570049</v>
+        <v>4.5595229999999995</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2741,25 +2741,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.037622</v>
+        <v>0.030361</v>
       </c>
       <c r="F13" s="7">
-        <v>0.042141000000000005</v>
+        <v>0.03872</v>
       </c>
       <c r="G13" s="7">
-        <v>0.429345</v>
+        <v>0.431406</v>
       </c>
       <c r="H13" s="7">
-        <v>0.314874</v>
+        <v>0.313654</v>
       </c>
       <c r="I13" s="7">
-        <v>0.542567</v>
+        <v>0.5500849999999999</v>
       </c>
       <c r="J13" s="7">
-        <v>2.693073</v>
+        <v>2.689647</v>
       </c>
       <c r="K13" s="7">
-        <v>10.458277</v>
+        <v>10.447648</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2776,25 +2776,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.023757</v>
+        <v>0.027707000000000002</v>
       </c>
       <c r="F14" s="7">
-        <v>0.015583</v>
+        <v>0.014162</v>
       </c>
       <c r="G14" s="7">
-        <v>0.271978</v>
+        <v>0.261057</v>
       </c>
       <c r="H14" s="7">
-        <v>0.197979</v>
+        <v>0.193981</v>
       </c>
       <c r="I14" s="7">
-        <v>0.45671700000000004</v>
+        <v>0.45217799999999997</v>
       </c>
       <c r="J14" s="7">
-        <v>2.577987</v>
+        <v>2.566045</v>
       </c>
       <c r="K14" s="7">
-        <v>8.049072</v>
+        <v>8.018871</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2811,25 +2811,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.013286</v>
+        <v>0.014542999999999999</v>
       </c>
       <c r="F15" s="7">
-        <v>0.025029</v>
+        <v>0.020571000000000002</v>
       </c>
       <c r="G15" s="7">
-        <v>0.197736</v>
+        <v>0.19528500000000001</v>
       </c>
       <c r="H15" s="7">
-        <v>0.092402</v>
+        <v>0.09052099999999999</v>
       </c>
       <c r="I15" s="7">
-        <v>0.39556399999999997</v>
+        <v>0.39299799999999996</v>
       </c>
       <c r="J15" s="7">
-        <v>2.01947</v>
+        <v>2.014271</v>
       </c>
       <c r="K15" s="7">
-        <v>5.555617</v>
+        <v>5.544328</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2846,25 +2846,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.028319999999999998</v>
+        <v>0.030364</v>
       </c>
       <c r="F16" s="7">
-        <v>0.087906</v>
+        <v>0.086328</v>
       </c>
       <c r="G16" s="7">
-        <v>0.226323</v>
+        <v>0.22738499999999998</v>
       </c>
       <c r="H16" s="7">
-        <v>0.15390800000000002</v>
+        <v>0.155422</v>
       </c>
       <c r="I16" s="7">
-        <v>0.503459</v>
+        <v>0.5050209999999999</v>
       </c>
       <c r="J16" s="7">
-        <v>2.796958</v>
+        <v>2.801939</v>
       </c>
       <c r="K16" s="7">
-        <v>5.089411999999999</v>
+        <v>5.097401</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2881,25 +2881,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.030737</v>
+        <v>0.029660000000000002</v>
       </c>
       <c r="F17" s="7">
-        <v>0.076508</v>
+        <v>0.075106</v>
       </c>
       <c r="G17" s="7">
-        <v>0.20661300000000002</v>
+        <v>0.20718699999999998</v>
       </c>
       <c r="H17" s="7">
-        <v>0.148302</v>
+        <v>0.148775</v>
       </c>
       <c r="I17" s="7">
-        <v>0.415334</v>
+        <v>0.414225</v>
       </c>
       <c r="J17" s="7">
-        <v>1.794816</v>
+        <v>1.795967</v>
       </c>
       <c r="K17" s="7">
-        <v>4.568588</v>
+        <v>4.570882</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2916,25 +2916,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.005012</v>
+        <v>-0.000841</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.06914</v>
+        <v>-0.05867</v>
       </c>
       <c r="G18" s="7">
-        <v>0.174826</v>
+        <v>0.150045</v>
       </c>
       <c r="H18" s="7">
-        <v>0.078864</v>
+        <v>0.078709</v>
       </c>
       <c r="I18" s="7">
-        <v>0.6824410000000001</v>
+        <v>0.679279</v>
       </c>
       <c r="J18" s="7">
-        <v>4.861836</v>
+        <v>4.8609919999999995</v>
       </c>
       <c r="K18" s="7">
-        <v>15.519457</v>
+        <v>15.517076</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2951,25 +2951,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.047867</v>
+        <v>0.041035</v>
       </c>
       <c r="F19" s="7">
-        <v>0.054193</v>
+        <v>0.045988</v>
       </c>
       <c r="G19" s="7">
-        <v>0.28560800000000003</v>
+        <v>0.279481</v>
       </c>
       <c r="H19" s="7">
-        <v>0.154933</v>
+        <v>0.14644500000000002</v>
       </c>
       <c r="I19" s="7">
-        <v>0.446226</v>
+        <v>0.44242800000000004</v>
       </c>
       <c r="J19" s="7">
-        <v>2.355596</v>
+        <v>2.330935</v>
       </c>
       <c r="K19" s="7">
-        <v>7.108283</v>
+        <v>7.048695</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2986,25 +2986,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.036895</v>
+        <v>0.035663</v>
       </c>
       <c r="F20" s="7">
-        <v>0.095599</v>
+        <v>0.09562799999999999</v>
       </c>
       <c r="G20" s="7">
-        <v>0.257804</v>
+        <v>0.266696</v>
       </c>
       <c r="H20" s="7">
-        <v>0.11476599999999999</v>
+        <v>0.116947</v>
       </c>
       <c r="I20" s="7">
-        <v>0.460961</v>
+        <v>0.457571</v>
       </c>
       <c r="J20" s="7">
-        <v>1.607307</v>
+        <v>1.612406</v>
       </c>
       <c r="K20" s="7">
-        <v>4.24726</v>
+        <v>4.257523</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3021,25 +3021,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.034481000000000005</v>
+        <v>0.029763</v>
       </c>
       <c r="F21" s="7">
-        <v>0.09622299999999999</v>
+        <v>0.090406</v>
       </c>
       <c r="G21" s="7">
-        <v>0.233202</v>
+        <v>0.230988</v>
       </c>
       <c r="H21" s="7">
-        <v>0.172977</v>
+        <v>0.16886600000000002</v>
       </c>
       <c r="I21" s="7">
-        <v>0.44474600000000003</v>
+        <v>0.435676</v>
       </c>
       <c r="J21" s="7">
-        <v>2.089074</v>
+        <v>2.078247</v>
       </c>
       <c r="K21" s="7">
-        <v>5.082726</v>
+        <v>5.061406</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3056,25 +3056,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.08805400000000001</v>
+        <v>0.074552</v>
       </c>
       <c r="F22" s="7">
-        <v>0.123171</v>
+        <v>0.10754799999999999</v>
       </c>
       <c r="G22" s="7">
-        <v>0.39081200000000005</v>
+        <v>0.381113</v>
       </c>
       <c r="H22" s="7">
-        <v>0.328335</v>
+        <v>0.313956</v>
       </c>
       <c r="I22" s="7">
-        <v>0.6097670000000001</v>
+        <v>0.592186</v>
       </c>
       <c r="J22" s="7">
-        <v>3.0951400000000002</v>
+        <v>3.050812</v>
       </c>
       <c r="K22" s="7">
-        <v>11.15249</v>
+        <v>11.020942999999999</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3091,25 +3091,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.029580000000000002</v>
+        <v>0.030417</v>
       </c>
       <c r="F23" s="7">
-        <v>0.081821</v>
+        <v>0.081509</v>
       </c>
       <c r="G23" s="7">
-        <v>0.18586200000000003</v>
+        <v>0.18694299999999997</v>
       </c>
       <c r="H23" s="7">
-        <v>0.133207</v>
+        <v>0.135206</v>
       </c>
       <c r="I23" s="7">
-        <v>0.406231</v>
+        <v>0.40713900000000003</v>
       </c>
       <c r="J23" s="7">
-        <v>2.3485460000000002</v>
+        <v>2.354451</v>
       </c>
       <c r="K23" s="7">
-        <v>5.016724</v>
+        <v>5.027335</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3126,25 +3126,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.012716</v>
+        <v>0.015124</v>
       </c>
       <c r="F24" s="7">
-        <v>0.02239</v>
+        <v>0.015347999999999999</v>
       </c>
       <c r="G24" s="7">
-        <v>0.152253</v>
+        <v>0.151297</v>
       </c>
       <c r="H24" s="7">
-        <v>0.049471</v>
+        <v>0.046931</v>
       </c>
       <c r="I24" s="7">
-        <v>0.38321500000000003</v>
+        <v>0.377604</v>
       </c>
       <c r="J24" s="7">
-        <v>1.619888</v>
+        <v>1.6135480000000002</v>
       </c>
       <c r="K24" s="7">
-        <v>3.447158</v>
+        <v>3.436396</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3161,25 +3161,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.017593</v>
+        <v>0.016696</v>
       </c>
       <c r="F25" s="7">
-        <v>0.032496</v>
+        <v>0.031318</v>
       </c>
       <c r="G25" s="7">
-        <v>0.127444</v>
+        <v>0.12349199999999999</v>
       </c>
       <c r="H25" s="7">
-        <v>0.06449099999999999</v>
+        <v>0.063999</v>
       </c>
       <c r="I25" s="7">
-        <v>0.33305599999999996</v>
+        <v>0.332988</v>
       </c>
       <c r="J25" s="7">
-        <v>2.0426759999999997</v>
+        <v>2.0412690000000002</v>
       </c>
       <c r="K25" s="7">
-        <v>6.362518</v>
+        <v>6.359114</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3196,25 +3196,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.017349</v>
+        <v>0.015470999999999999</v>
       </c>
       <c r="F26" s="7">
-        <v>0.022713</v>
+        <v>0.019370000000000002</v>
       </c>
       <c r="G26" s="7">
-        <v>0.123249</v>
+        <v>0.11583199999999999</v>
       </c>
       <c r="H26" s="7">
-        <v>0.064219</v>
+        <v>0.061581000000000004</v>
       </c>
       <c r="I26" s="7">
-        <v>0.32271500000000003</v>
+        <v>0.319787</v>
       </c>
       <c r="J26" s="7">
-        <v>2.094224</v>
+        <v>2.0865549999999997</v>
       </c>
       <c r="K26" s="7">
-        <v>5.573741</v>
+        <v>5.557449</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3231,25 +3231,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.017439</v>
+        <v>0.026810999999999998</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.016033</v>
+        <v>-0.017363</v>
       </c>
       <c r="G27" s="7">
-        <v>0.277238</v>
+        <v>0.278856</v>
       </c>
       <c r="H27" s="7">
-        <v>0.222196</v>
+        <v>0.22367</v>
       </c>
       <c r="I27" s="7">
-        <v>0.376122</v>
+        <v>0.379295</v>
       </c>
       <c r="J27" s="7">
-        <v>3.0690910000000002</v>
+        <v>3.073997</v>
       </c>
       <c r="K27" s="7">
-        <v>16.134921</v>
+        <v>16.155577</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3266,25 +3266,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.06023</v>
+        <v>0.058266</v>
       </c>
       <c r="F28" s="7">
-        <v>0.05106</v>
+        <v>0.057795</v>
       </c>
       <c r="G28" s="7">
-        <v>0.160915</v>
+        <v>0.160246</v>
       </c>
       <c r="H28" s="7">
-        <v>0.128704</v>
+        <v>0.125593</v>
       </c>
       <c r="I28" s="7">
-        <v>0.40393900000000005</v>
+        <v>0.397196</v>
       </c>
       <c r="J28" s="7">
-        <v>2.539659</v>
+        <v>2.529902</v>
       </c>
       <c r="K28" s="7">
-        <v>8.029548</v>
+        <v>8.004658</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3301,25 +3301,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.020049</v>
+        <v>0.023124</v>
       </c>
       <c r="F29" s="7">
-        <v>0.047203</v>
+        <v>0.045011</v>
       </c>
       <c r="G29" s="7">
-        <v>0.17662199999999997</v>
+        <v>0.177714</v>
       </c>
       <c r="H29" s="7">
-        <v>0.110954</v>
+        <v>0.11166999999999999</v>
       </c>
       <c r="I29" s="7">
-        <v>0.401237</v>
+        <v>0.400439</v>
       </c>
       <c r="J29" s="7">
-        <v>2.393835</v>
+        <v>2.396021</v>
       </c>
       <c r="K29" s="7">
-        <v>4.599231</v>
+        <v>4.602839</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3336,25 +3336,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.023617</v>
+        <v>0.032129</v>
       </c>
       <c r="F30" s="7">
-        <v>0.01195</v>
+        <v>0.012541</v>
       </c>
       <c r="G30" s="7">
-        <v>0.220098</v>
+        <v>0.223751</v>
       </c>
       <c r="H30" s="7">
-        <v>0.172632</v>
+        <v>0.176883</v>
       </c>
       <c r="I30" s="7">
-        <v>0.37189300000000003</v>
+        <v>0.377794</v>
       </c>
       <c r="J30" s="7">
-        <v>2.9491340000000004</v>
+        <v>2.9634500000000004</v>
       </c>
       <c r="K30" s="7">
-        <v>9.57264</v>
+        <v>9.610966</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3371,25 +3371,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.049318</v>
+        <v>0.042823</v>
       </c>
       <c r="F31" s="7">
-        <v>-0.004555</v>
+        <v>-0.016268</v>
       </c>
       <c r="G31" s="7">
-        <v>0.32496400000000003</v>
+        <v>0.315874</v>
       </c>
       <c r="H31" s="7">
-        <v>0.242346</v>
+        <v>0.234024</v>
       </c>
       <c r="I31" s="7">
-        <v>0.34948599999999996</v>
+        <v>0.347651</v>
       </c>
       <c r="J31" s="7">
-        <v>2.4852819999999998</v>
+        <v>2.461935</v>
       </c>
       <c r="K31" s="7">
-        <v>14.553091</v>
+        <v>14.448904</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3406,25 +3406,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.030085999999999998</v>
+        <v>0.030042</v>
       </c>
       <c r="F32" s="7">
-        <v>0.087606</v>
+        <v>0.08585100000000001</v>
       </c>
       <c r="G32" s="7">
-        <v>0.19533</v>
+        <v>0.19513000000000003</v>
       </c>
       <c r="H32" s="7">
-        <v>0.129414</v>
+        <v>0.130436</v>
       </c>
       <c r="I32" s="7">
-        <v>0.44876800000000006</v>
+        <v>0.448164</v>
       </c>
       <c r="J32" s="7">
-        <v>2.164241</v>
+        <v>2.167104</v>
       </c>
       <c r="K32" s="7">
-        <v>3.7541390000000003</v>
+        <v>3.7584410000000004</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3441,25 +3441,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.011574</v>
+        <v>0.020323</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.004875</v>
+        <v>-0.008365000000000001</v>
       </c>
       <c r="G33" s="7">
-        <v>0.282051</v>
+        <v>0.28474299999999997</v>
       </c>
       <c r="H33" s="7">
-        <v>0.199891</v>
+        <v>0.198512</v>
       </c>
       <c r="I33" s="7">
-        <v>0.40222</v>
+        <v>0.400194</v>
       </c>
       <c r="J33" s="7">
-        <v>3.334257</v>
+        <v>3.3292759999999997</v>
       </c>
       <c r="K33" s="7">
-        <v>16.461678</v>
+        <v>16.441612</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3476,25 +3476,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.074835</v>
+        <v>0.059632</v>
       </c>
       <c r="F34" s="7">
-        <v>0.114357</v>
+        <v>0.106192</v>
       </c>
       <c r="G34" s="7">
-        <v>0.40196</v>
+        <v>0.39900399999999997</v>
       </c>
       <c r="H34" s="7">
-        <v>0.316175</v>
+        <v>0.30949000000000004</v>
       </c>
       <c r="I34" s="7">
-        <v>0.6533880000000001</v>
+        <v>0.644071</v>
       </c>
       <c r="J34" s="7">
-        <v>3.297211</v>
+        <v>3.2753840000000003</v>
       </c>
       <c r="K34" s="7">
-        <v>10.007038999999999</v>
+        <v>9.951131</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3511,25 +3511,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.080567</v>
+        <v>0.06472800000000001</v>
       </c>
       <c r="F35" s="7">
-        <v>0.111751</v>
+        <v>0.103497</v>
       </c>
       <c r="G35" s="7">
-        <v>0.43046100000000004</v>
+        <v>0.42563</v>
       </c>
       <c r="H35" s="7">
-        <v>0.337125</v>
+        <v>0.328001</v>
       </c>
       <c r="I35" s="7">
-        <v>0.718146</v>
+        <v>0.706202</v>
       </c>
       <c r="J35" s="7">
-        <v>3.555844</v>
+        <v>3.524756</v>
       </c>
       <c r="K35" s="7">
-        <v>12.685622</v>
+        <v>12.592235</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3546,25 +3546,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.008317</v>
+        <v>0.012683</v>
       </c>
       <c r="F36" s="7">
-        <v>-0.003128</v>
+        <v>-0.010883</v>
       </c>
       <c r="G36" s="7">
-        <v>0.292634</v>
+        <v>0.289251</v>
       </c>
       <c r="H36" s="7">
-        <v>0.211125</v>
+        <v>0.204988</v>
       </c>
       <c r="I36" s="7">
-        <v>0.419979</v>
+        <v>0.412748</v>
       </c>
       <c r="J36" s="7">
-        <v>3.411394</v>
+        <v>3.3890429999999996</v>
       </c>
       <c r="K36" s="7">
-        <v>17.004863</v>
+        <v>16.913638000000002</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3581,25 +3581,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.01755</v>
+        <v>0.021505</v>
       </c>
       <c r="F37" s="7">
-        <v>0.015505</v>
+        <v>0.008239999999999999</v>
       </c>
       <c r="G37" s="7">
-        <v>0.301956</v>
+        <v>0.297196</v>
       </c>
       <c r="H37" s="7">
-        <v>0.202693</v>
+        <v>0.197468</v>
       </c>
       <c r="I37" s="7">
-        <v>0.451039</v>
+        <v>0.44445999999999997</v>
       </c>
       <c r="J37" s="7">
-        <v>3.5319670000000003</v>
+        <v>3.5122780000000002</v>
       </c>
       <c r="K37" s="7">
-        <v>15.623482</v>
+        <v>15.551261</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3616,25 +3616,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.015596</v>
+        <v>0.021653</v>
       </c>
       <c r="F38" s="7">
-        <v>0.015437000000000001</v>
+        <v>0.010383</v>
       </c>
       <c r="G38" s="7">
-        <v>0.260204</v>
+        <v>0.259006</v>
       </c>
       <c r="H38" s="7">
-        <v>0.176825</v>
+        <v>0.174713</v>
       </c>
       <c r="I38" s="7">
-        <v>0.444168</v>
+        <v>0.44210900000000003</v>
       </c>
       <c r="J38" s="7">
-        <v>3.422414</v>
+        <v>3.414476</v>
       </c>
       <c r="K38" s="7">
-        <v>11.594901</v>
+        <v>11.572294</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3651,25 +3651,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.022618</v>
+        <v>0.020981999999999997</v>
       </c>
       <c r="F39" s="7">
-        <v>0.06125</v>
+        <v>0.055617</v>
       </c>
       <c r="G39" s="7">
-        <v>0.199909</v>
+        <v>0.196133</v>
       </c>
       <c r="H39" s="7">
-        <v>0.135436</v>
+        <v>0.132284</v>
       </c>
       <c r="I39" s="7">
-        <v>0.459617</v>
+        <v>0.45426900000000003</v>
       </c>
       <c r="J39" s="7">
-        <v>2.970036</v>
+        <v>2.959013</v>
       </c>
       <c r="K39" s="7">
-        <v>5.74768</v>
+        <v>5.728944</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3686,25 +3686,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.059804</v>
+        <v>0.049532999999999994</v>
       </c>
       <c r="F40" s="7">
-        <v>0.12692</v>
+        <v>0.116016</v>
       </c>
       <c r="G40" s="7">
-        <v>0.373902</v>
+        <v>0.37331600000000004</v>
       </c>
       <c r="H40" s="7">
-        <v>0.285822</v>
+        <v>0.277459</v>
       </c>
       <c r="I40" s="7">
-        <v>0.6025659999999999</v>
+        <v>0.589095</v>
       </c>
       <c r="J40" s="7">
-        <v>3.470077</v>
+        <v>3.4410030000000003</v>
       </c>
       <c r="K40" s="7">
-        <v>11.917001</v>
+        <v>11.832989</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3721,25 +3721,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.05055</v>
+        <v>0.039091999999999995</v>
       </c>
       <c r="F41" s="7">
-        <v>0.115523</v>
+        <v>0.10230800000000001</v>
       </c>
       <c r="G41" s="7">
-        <v>0.340149</v>
+        <v>0.334557</v>
       </c>
       <c r="H41" s="7">
-        <v>0.25772300000000004</v>
+        <v>0.246464</v>
       </c>
       <c r="I41" s="7">
-        <v>0.583472</v>
+        <v>0.566978</v>
       </c>
       <c r="J41" s="7">
-        <v>3.2648110000000004</v>
+        <v>3.226633</v>
       </c>
       <c r="K41" s="7">
-        <v>10.170479</v>
+        <v>10.070484</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3756,25 +3756,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.051832</v>
+        <v>0.04441900000000001</v>
       </c>
       <c r="F42" s="7">
-        <v>0.057238</v>
+        <v>0.054664000000000004</v>
       </c>
       <c r="G42" s="7">
-        <v>0.35726399999999997</v>
+        <v>0.35531399999999996</v>
       </c>
       <c r="H42" s="7">
-        <v>0.283984</v>
+        <v>0.27979299999999996</v>
       </c>
       <c r="I42" s="7">
-        <v>0.548291</v>
+        <v>0.551196</v>
       </c>
       <c r="J42" s="7">
-        <v>3.0507560000000002</v>
+        <v>3.037532</v>
       </c>
       <c r="K42" s="7">
-        <v>10.865952</v>
+        <v>10.827215</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3791,25 +3791,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.011491</v>
+        <v>0.009926</v>
       </c>
       <c r="F43" s="7">
-        <v>-0.007325000000000001</v>
+        <v>-0.016546</v>
       </c>
       <c r="G43" s="7">
-        <v>0.306143</v>
+        <v>0.297964</v>
       </c>
       <c r="H43" s="7">
-        <v>0.219787</v>
+        <v>0.20904499999999998</v>
       </c>
       <c r="I43" s="7">
-        <v>0.431336</v>
+        <v>0.418997</v>
       </c>
       <c r="J43" s="7">
-        <v>3.8888249999999998</v>
+        <v>3.845773</v>
       </c>
       <c r="K43" s="7">
-        <v>21.342010000000002</v>
+        <v>21.145262</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3826,25 +3826,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.030035</v>
+        <v>0.030363</v>
       </c>
       <c r="F44" s="7">
-        <v>0.066677</v>
+        <v>0.064013</v>
       </c>
       <c r="G44" s="7">
-        <v>0.204092</v>
+        <v>0.20434000000000002</v>
       </c>
       <c r="H44" s="7">
-        <v>0.132418</v>
+        <v>0.132982</v>
       </c>
       <c r="I44" s="7">
-        <v>0.471984</v>
+        <v>0.47216299999999994</v>
       </c>
       <c r="J44" s="7">
-        <v>2.489093</v>
+        <v>2.490832</v>
       </c>
       <c r="K44" s="7">
-        <v>4.497666</v>
+        <v>4.500407</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3861,25 +3861,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.042473000000000004</v>
+        <v>0.034032</v>
       </c>
       <c r="F45" s="7">
-        <v>0.054842</v>
+        <v>0.050786</v>
       </c>
       <c r="G45" s="7">
-        <v>0.325355</v>
+        <v>0.32055100000000003</v>
       </c>
       <c r="H45" s="7">
-        <v>0.24234999999999998</v>
+        <v>0.23693799999999998</v>
       </c>
       <c r="I45" s="7">
-        <v>0.548579</v>
+        <v>0.546156</v>
       </c>
       <c r="J45" s="7">
-        <v>3.166534</v>
+        <v>3.148385</v>
       </c>
       <c r="K45" s="7">
-        <v>9.559391</v>
+        <v>9.513394</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3896,25 +3896,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.049249</v>
+        <v>0.040351</v>
       </c>
       <c r="F46" s="7">
-        <v>0.117364</v>
+        <v>0.10702099999999999</v>
       </c>
       <c r="G46" s="7">
-        <v>0.36024700000000004</v>
+        <v>0.357046</v>
       </c>
       <c r="H46" s="7">
-        <v>0.29358</v>
+        <v>0.284726</v>
       </c>
       <c r="I46" s="7">
-        <v>0.600848</v>
+        <v>0.588225</v>
       </c>
       <c r="J46" s="7">
-        <v>3.652377</v>
+        <v>3.620534</v>
       </c>
       <c r="K46" s="7">
-        <v>10.440033000000001</v>
+        <v>10.361732</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3931,25 +3931,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.066862</v>
+        <v>0.051980000000000005</v>
       </c>
       <c r="F47" s="7">
-        <v>0.11675100000000001</v>
+        <v>0.100834</v>
       </c>
       <c r="G47" s="7">
-        <v>0.37822</v>
+        <v>0.371265</v>
       </c>
       <c r="H47" s="7">
-        <v>0.303436</v>
+        <v>0.29025</v>
       </c>
       <c r="I47" s="7">
-        <v>0.596886</v>
+        <v>0.579518</v>
       </c>
       <c r="J47" s="7">
-        <v>3.693546</v>
+        <v>3.646063</v>
       </c>
       <c r="K47" s="7">
-        <v>13.341724</v>
+        <v>13.196632999999999</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3966,25 +3966,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.005601</v>
+        <v>-0.027195</v>
       </c>
       <c r="F48" s="7">
-        <v>-0.043299000000000004</v>
+        <v>-0.057493999999999996</v>
       </c>
       <c r="G48" s="7">
-        <v>0.199818</v>
+        <v>0.18062899999999998</v>
       </c>
       <c r="H48" s="7">
-        <v>0.14447100000000002</v>
+        <v>0.13018000000000002</v>
       </c>
       <c r="I48" s="7">
-        <v>0.366594</v>
+        <v>0.34307699999999997</v>
       </c>
       <c r="J48" s="7">
-        <v>1.628404</v>
+        <v>1.5955840000000001</v>
       </c>
       <c r="K48" s="7">
-        <v>10.196031</v>
+        <v>10.056227</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4001,25 +4001,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.046346</v>
+        <v>0.033739</v>
       </c>
       <c r="F49" s="7">
-        <v>0.044705</v>
+        <v>0.033654</v>
       </c>
       <c r="G49" s="7">
-        <v>0.378956</v>
+        <v>0.37065</v>
       </c>
       <c r="H49" s="7">
-        <v>0.288561</v>
+        <v>0.277129</v>
       </c>
       <c r="I49" s="7">
-        <v>0.538363</v>
+        <v>0.536937</v>
       </c>
       <c r="J49" s="7">
-        <v>3.540694</v>
+        <v>3.5004090000000003</v>
       </c>
       <c r="K49" s="7">
-        <v>15.888368</v>
+        <v>15.738533</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4036,25 +4036,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.076879</v>
+        <v>0.076028</v>
       </c>
       <c r="F50" s="7">
-        <v>0.08745599999999999</v>
+        <v>0.096678</v>
       </c>
       <c r="G50" s="7">
-        <v>0.19735399999999997</v>
+        <v>0.200402</v>
       </c>
       <c r="H50" s="7">
-        <v>0.161132</v>
+        <v>0.16005299999999997</v>
       </c>
       <c r="I50" s="7">
-        <v>0.499398</v>
+        <v>0.48136</v>
       </c>
       <c r="J50" s="7">
-        <v>3.045713</v>
+        <v>3.041953</v>
       </c>
       <c r="K50" s="7">
-        <v>9.316246</v>
+        <v>9.306658</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4071,25 +4071,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.025619999999999997</v>
+        <v>0.021658</v>
       </c>
       <c r="F51" s="7">
-        <v>0.009939</v>
+        <v>0.0024560000000000003</v>
       </c>
       <c r="G51" s="7">
-        <v>0.230023</v>
+        <v>0.224827</v>
       </c>
       <c r="H51" s="7">
-        <v>0.14607799999999999</v>
+        <v>0.141859</v>
       </c>
       <c r="I51" s="7">
-        <v>0.359373</v>
+        <v>0.353466</v>
       </c>
       <c r="J51" s="7">
-        <v>2.474691</v>
+        <v>2.4618979999999997</v>
       </c>
       <c r="K51" s="7">
-        <v>8.018186</v>
+        <v>7.984983</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4106,25 +4106,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.048711000000000004</v>
+        <v>0.047759</v>
       </c>
       <c r="F52" s="7">
-        <v>0.021353</v>
+        <v>0.013139000000000001</v>
       </c>
       <c r="G52" s="7">
-        <v>0.34957</v>
+        <v>0.35090699999999997</v>
       </c>
       <c r="H52" s="7">
-        <v>0.252218</v>
+        <v>0.246636</v>
       </c>
       <c r="I52" s="7">
-        <v>0.460274</v>
+        <v>0.45651400000000003</v>
       </c>
       <c r="J52" s="7">
-        <v>2.632179</v>
+        <v>2.615986</v>
       </c>
       <c r="K52" s="7">
-        <v>11.176317</v>
+        <v>11.122031999999999</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4141,25 +4141,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.016819</v>
+        <v>0.015164</v>
       </c>
       <c r="F53" s="7">
-        <v>0.028469</v>
+        <v>0.027709</v>
       </c>
       <c r="G53" s="7">
-        <v>0.10282999999999999</v>
+        <v>0.09934699999999999</v>
       </c>
       <c r="H53" s="7">
-        <v>0.057877</v>
+        <v>0.057276999999999995</v>
       </c>
       <c r="I53" s="7">
-        <v>0.32615</v>
+        <v>0.324754</v>
       </c>
       <c r="J53" s="7">
-        <v>2.104758</v>
+        <v>2.102999</v>
       </c>
       <c r="K53" s="7">
-        <v>6.39563</v>
+        <v>6.391439</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4176,25 +4176,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.017512</v>
+        <v>0.015811</v>
       </c>
       <c r="F54" s="7">
-        <v>0.032957</v>
+        <v>0.0334</v>
       </c>
       <c r="G54" s="7">
-        <v>0.09927799999999999</v>
+        <v>0.09798899999999999</v>
       </c>
       <c r="H54" s="7">
-        <v>0.061475</v>
+        <v>0.061757</v>
       </c>
       <c r="I54" s="7">
-        <v>0.293584</v>
+        <v>0.292993</v>
       </c>
       <c r="J54" s="7">
-        <v>2.0267250000000003</v>
+        <v>2.027528</v>
       </c>
       <c r="K54" s="7">
-        <v>6.2153719999999995</v>
+        <v>6.217287</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4211,25 +4211,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.001494</v>
+        <v>0.001545</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.068368</v>
+        <v>-0.055507999999999995</v>
       </c>
       <c r="G55" s="7">
-        <v>0.17395499999999997</v>
+        <v>0.149868</v>
       </c>
       <c r="H55" s="7">
-        <v>0.094852</v>
+        <v>0.093919</v>
       </c>
       <c r="I55" s="7">
-        <v>0.653975</v>
+        <v>0.649637</v>
       </c>
       <c r="J55" s="7">
-        <v>4.010723</v>
+        <v>4.006455</v>
       </c>
       <c r="K55" s="7">
-        <v>12.917795000000002</v>
+        <v>12.905939</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4246,25 +4246,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.025526</v>
+        <v>0.026962</v>
       </c>
       <c r="F56" s="7">
-        <v>0.057915</v>
+        <v>0.053132</v>
       </c>
       <c r="G56" s="7">
-        <v>0.258696</v>
+        <v>0.25871099999999997</v>
       </c>
       <c r="H56" s="7">
-        <v>0.164745</v>
+        <v>0.165932</v>
       </c>
       <c r="I56" s="7">
-        <v>0.46742100000000003</v>
+        <v>0.469318</v>
       </c>
       <c r="J56" s="7">
-        <v>2.116692</v>
+        <v>2.119869</v>
       </c>
       <c r="K56" s="7">
-        <v>5.681775</v>
+        <v>5.688586</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4281,25 +4281,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>-0.007965</v>
+        <v>-0.0015279999999999998</v>
       </c>
       <c r="F57" s="7">
-        <v>-0.009294</v>
+        <v>-0.016789000000000002</v>
       </c>
       <c r="G57" s="7">
-        <v>0.144004</v>
+        <v>0.141898</v>
       </c>
       <c r="H57" s="7">
-        <v>0.071418</v>
+        <v>0.06820999999999999</v>
       </c>
       <c r="I57" s="7">
-        <v>0.34731900000000004</v>
+        <v>0.34482100000000004</v>
       </c>
       <c r="J57" s="7">
-        <v>1.3690950000000002</v>
+        <v>1.362002</v>
       </c>
       <c r="K57" s="7">
-        <v>3.509952</v>
+        <v>3.4964479999999996</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4316,25 +4316,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.045791000000000005</v>
+        <v>0.036783</v>
       </c>
       <c r="F58" s="7">
-        <v>0.056164</v>
+        <v>0.052049000000000005</v>
       </c>
       <c r="G58" s="7">
-        <v>0.33859</v>
+        <v>0.33525799999999994</v>
       </c>
       <c r="H58" s="7">
-        <v>0.254278</v>
+        <v>0.24898499999999998</v>
       </c>
       <c r="I58" s="7">
-        <v>0.552991</v>
+        <v>0.550994</v>
       </c>
       <c r="J58" s="7">
-        <v>3.142323</v>
+        <v>3.124844</v>
       </c>
       <c r="K58" s="7">
-        <v>9.625465</v>
+        <v>9.58063</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4351,25 +4351,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.05079500000000001</v>
+        <v>0.04155300000000001</v>
       </c>
       <c r="F59" s="7">
-        <v>0.060014000000000005</v>
+        <v>0.055119999999999995</v>
       </c>
       <c r="G59" s="7">
-        <v>0.367256</v>
+        <v>0.36384500000000003</v>
       </c>
       <c r="H59" s="7">
-        <v>0.286992</v>
+        <v>0.280893</v>
       </c>
       <c r="I59" s="7">
-        <v>0.553989</v>
+        <v>0.554722</v>
       </c>
       <c r="J59" s="7">
-        <v>3.1402069999999997</v>
+        <v>3.1205860000000003</v>
       </c>
       <c r="K59" s="7">
-        <v>10.714579</v>
+        <v>10.659063000000002</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4386,25 +4386,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.036969</v>
+        <v>0.041219</v>
       </c>
       <c r="F60" s="7">
-        <v>-0.00931</v>
+        <v>-0.019821</v>
       </c>
       <c r="G60" s="7">
-        <v>0.296734</v>
+        <v>0.291169</v>
       </c>
       <c r="H60" s="7">
-        <v>0.223532</v>
+        <v>0.21851199999999998</v>
       </c>
       <c r="I60" s="7">
-        <v>0.39333799999999997</v>
+        <v>0.38974200000000003</v>
       </c>
       <c r="J60" s="7">
-        <v>2.425071</v>
+        <v>2.411019</v>
       </c>
       <c r="K60" s="7">
-        <v>12.867198</v>
+        <v>12.810302</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4421,25 +4421,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0</v>
+        <v>0.048749</v>
       </c>
       <c r="F61" s="7">
-        <v>0</v>
+        <v>0.051254999999999995</v>
       </c>
       <c r="G61" s="7">
-        <v>0</v>
+        <v>0.24749600000000002</v>
       </c>
       <c r="H61" s="7">
-        <v>0</v>
+        <v>0.194375</v>
       </c>
       <c r="I61" s="7">
-        <v>0</v>
+        <v>0.45241</v>
       </c>
       <c r="J61" s="7">
-        <v>0</v>
+        <v>2.418535</v>
       </c>
       <c r="K61" s="7">
-        <v>0</v>
+        <v>7.601464</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4456,25 +4456,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.02129</v>
+        <v>0.007446</v>
       </c>
       <c r="F62" s="7">
-        <v>-0.040362</v>
+        <v>-0.057418</v>
       </c>
       <c r="G62" s="7">
-        <v>0.252511</v>
+        <v>0.236479</v>
       </c>
       <c r="H62" s="7">
-        <v>0.185779</v>
+        <v>0.172068</v>
       </c>
       <c r="I62" s="7">
-        <v>0.334563</v>
+        <v>0.332804</v>
       </c>
       <c r="J62" s="7">
-        <v>2.114838</v>
+        <v>2.078821</v>
       </c>
       <c r="K62" s="7">
-        <v>12.342362000000001</v>
+        <v>12.188082999999999</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4491,25 +4491,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.014098</v>
+        <v>0.015242</v>
       </c>
       <c r="F63" s="7">
-        <v>0.014116</v>
+        <v>0.008796</v>
       </c>
       <c r="G63" s="7">
-        <v>0.19418500000000002</v>
+        <v>0.192411</v>
       </c>
       <c r="H63" s="7">
-        <v>0.099709</v>
+        <v>0.097527</v>
       </c>
       <c r="I63" s="7">
-        <v>0.389378</v>
+        <v>0.38624899999999995</v>
       </c>
       <c r="J63" s="7">
-        <v>1.931583</v>
+        <v>1.925766</v>
       </c>
       <c r="K63" s="7">
-        <v>4.669900999999999</v>
+        <v>4.658652</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4526,25 +4526,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.021257</v>
+        <v>0.024725</v>
       </c>
       <c r="F64" s="7">
-        <v>0.007461</v>
+        <v>0.011711000000000001</v>
       </c>
       <c r="G64" s="7">
-        <v>0.216553</v>
+        <v>0.21323899999999998</v>
       </c>
       <c r="H64" s="7">
-        <v>0.167597</v>
+        <v>0.16635999999999998</v>
       </c>
       <c r="I64" s="7">
-        <v>0.404931</v>
+        <v>0.402406</v>
       </c>
       <c r="J64" s="7">
-        <v>2.033862</v>
+        <v>2.030649</v>
       </c>
       <c r="K64" s="7">
-        <v>6.22729</v>
+        <v>6.219638</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4561,25 +4561,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.01771</v>
+        <v>0.015854999999999998</v>
       </c>
       <c r="F65" s="7">
-        <v>0.037298</v>
+        <v>0.033031000000000005</v>
       </c>
       <c r="G65" s="7">
-        <v>0.104042</v>
+        <v>0.103817</v>
       </c>
       <c r="H65" s="7">
-        <v>0.068754</v>
+        <v>0.068575</v>
       </c>
       <c r="I65" s="7">
-        <v>0.295451</v>
+        <v>0.292993</v>
       </c>
       <c r="J65" s="7">
-        <v>2.024171</v>
+        <v>2.023665</v>
       </c>
       <c r="K65" s="7">
-        <v>5.243887999999999</v>
+        <v>5.2428420000000004</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4596,25 +4596,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.015823</v>
+        <v>0.017338</v>
       </c>
       <c r="F66" s="7">
-        <v>0.030098</v>
+        <v>0.028843999999999998</v>
       </c>
       <c r="G66" s="7">
-        <v>0.099552</v>
+        <v>0.09521800000000001</v>
       </c>
       <c r="H66" s="7">
-        <v>0.05362</v>
+        <v>0.05267</v>
       </c>
       <c r="I66" s="7">
-        <v>0.30933700000000003</v>
+        <v>0.307579</v>
       </c>
       <c r="J66" s="7">
-        <v>2.200319</v>
+        <v>2.1974359999999997</v>
       </c>
       <c r="K66" s="7">
-        <v>6.667615</v>
+        <v>6.660706</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4631,25 +4631,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.025893000000000003</v>
+        <v>0.019936</v>
       </c>
       <c r="F67" s="7">
-        <v>0.036303</v>
+        <v>0.032889</v>
       </c>
       <c r="G67" s="7">
-        <v>0.280532</v>
+        <v>0.26705100000000004</v>
       </c>
       <c r="H67" s="7">
-        <v>0.21448499999999998</v>
+        <v>0.20775200000000002</v>
       </c>
       <c r="I67" s="7">
-        <v>0.552148</v>
+        <v>0.5454399999999999</v>
       </c>
       <c r="J67" s="7">
-        <v>2.538419</v>
+        <v>2.5188040000000003</v>
       </c>
       <c r="K67" s="7">
-        <v>9.362066</v>
+        <v>9.304623</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4666,25 +4666,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.017055</v>
+        <v>0.017143</v>
       </c>
       <c r="F68" s="7">
-        <v>0.031616</v>
+        <v>0.030257</v>
       </c>
       <c r="G68" s="7">
-        <v>0.099048</v>
+        <v>0.094945</v>
       </c>
       <c r="H68" s="7">
-        <v>0.05837</v>
+        <v>0.057347999999999996</v>
       </c>
       <c r="I68" s="7">
-        <v>0.286914</v>
+        <v>0.285059</v>
       </c>
       <c r="J68" s="7">
-        <v>2.020664</v>
+        <v>2.017747</v>
       </c>
       <c r="K68" s="7">
-        <v>6.0640089999999995</v>
+        <v>6.057188</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4701,25 +4701,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.020817000000000002</v>
+        <v>0.021023999999999998</v>
       </c>
       <c r="F69" s="7">
-        <v>0.035964</v>
+        <v>0.032065</v>
       </c>
       <c r="G69" s="7">
-        <v>0.229564</v>
+        <v>0.229112</v>
       </c>
       <c r="H69" s="7">
-        <v>0.139092</v>
+        <v>0.13719699999999999</v>
       </c>
       <c r="I69" s="7">
-        <v>0.451471</v>
+        <v>0.450547</v>
       </c>
       <c r="J69" s="7">
-        <v>2.219671</v>
+        <v>2.214314</v>
       </c>
       <c r="K69" s="7">
-        <v>5.535878</v>
+        <v>5.525004</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4736,25 +4736,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.031432</v>
+        <v>0.03144</v>
       </c>
       <c r="F70" s="7">
-        <v>0.094375</v>
+        <v>0.092288</v>
       </c>
       <c r="G70" s="7">
-        <v>0.19994399999999998</v>
+        <v>0.19994199999999998</v>
       </c>
       <c r="H70" s="7">
-        <v>0.140783</v>
+        <v>0.141959</v>
       </c>
       <c r="I70" s="7">
-        <v>0.477121</v>
+        <v>0.47685099999999997</v>
       </c>
       <c r="J70" s="7">
-        <v>2.3562469999999998</v>
+        <v>2.359708</v>
       </c>
       <c r="K70" s="7">
-        <v>4.075906</v>
+        <v>4.0811399999999995</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4771,25 +4771,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.286835</v>
+        <v>0.274556</v>
       </c>
       <c r="F71" s="7">
-        <v>0.288307</v>
+        <v>0.32195700000000005</v>
       </c>
       <c r="G71" s="7">
-        <v>0.309585</v>
+        <v>0.32494999999999996</v>
       </c>
       <c r="H71" s="7">
-        <v>0.30187200000000003</v>
+        <v>0.296713</v>
       </c>
       <c r="I71" s="7">
-        <v>0.725534</v>
+        <v>0.692299</v>
       </c>
       <c r="J71" s="7">
-        <v>4.170237</v>
+        <v>4.149749</v>
       </c>
       <c r="K71" s="7">
-        <v>9.181673</v>
+        <v>9.141327</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4806,25 +4806,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.039582</v>
+        <v>0.033020999999999995</v>
       </c>
       <c r="F72" s="7">
-        <v>0.079162</v>
+        <v>0.07547100000000001</v>
       </c>
       <c r="G72" s="7">
-        <v>0.250518</v>
+        <v>0.248554</v>
       </c>
       <c r="H72" s="7">
-        <v>0.159514</v>
+        <v>0.157604</v>
       </c>
       <c r="I72" s="7">
-        <v>0.45061100000000004</v>
+        <v>0.447168</v>
       </c>
       <c r="J72" s="7">
-        <v>1.919296</v>
+        <v>1.914485</v>
       </c>
       <c r="K72" s="7">
-        <v>4.717973</v>
+        <v>4.70855</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4841,25 +4841,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.033885</v>
+        <v>0.036536</v>
       </c>
       <c r="F73" s="7">
-        <v>0.000202</v>
+        <v>0.001089</v>
       </c>
       <c r="G73" s="7">
-        <v>0.06725500000000001</v>
+        <v>0.065755</v>
       </c>
       <c r="H73" s="7">
-        <v>0.023323</v>
+        <v>0.024541</v>
       </c>
       <c r="I73" s="7">
-        <v>0.281129</v>
+        <v>0.282151</v>
       </c>
       <c r="J73" s="7">
-        <v>2.006256</v>
+        <v>2.009835</v>
       </c>
       <c r="K73" s="7">
-        <v>6.1055280000000005</v>
+        <v>6.113988000000001</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4876,25 +4876,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.049737</v>
+        <v>0.043322</v>
       </c>
       <c r="F74" s="7">
-        <v>-0.003293</v>
+        <v>-0.014910000000000001</v>
       </c>
       <c r="G74" s="7">
-        <v>0.33246400000000004</v>
+        <v>0.32356699999999994</v>
       </c>
       <c r="H74" s="7">
-        <v>0.244167</v>
+        <v>0.235976</v>
       </c>
       <c r="I74" s="7">
-        <v>0.35756</v>
+        <v>0.355768</v>
       </c>
       <c r="J74" s="7">
-        <v>2.51883</v>
+        <v>2.495665</v>
       </c>
       <c r="K74" s="7">
-        <v>14.75824</v>
+        <v>14.654499000000001</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4911,25 +4911,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.016017999999999998</v>
+        <v>0.019142</v>
       </c>
       <c r="F75" s="7">
-        <v>0.021707</v>
+        <v>0.014895</v>
       </c>
       <c r="G75" s="7">
-        <v>0.175699</v>
+        <v>0.17631799999999997</v>
       </c>
       <c r="H75" s="7">
-        <v>0.062408</v>
+        <v>0.061487</v>
       </c>
       <c r="I75" s="7">
-        <v>0.41357900000000003</v>
+        <v>0.40940800000000005</v>
       </c>
       <c r="J75" s="7">
-        <v>1.8050739999999998</v>
+        <v>1.8026410000000002</v>
       </c>
       <c r="K75" s="7">
-        <v>3.699744</v>
+        <v>3.695668</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4946,25 +4946,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.02149</v>
+        <v>0.021795</v>
       </c>
       <c r="F76" s="7">
-        <v>0.034933</v>
+        <v>0.030725</v>
       </c>
       <c r="G76" s="7">
-        <v>0.232042</v>
+        <v>0.231648</v>
       </c>
       <c r="H76" s="7">
-        <v>0.13934100000000002</v>
+        <v>0.137341</v>
       </c>
       <c r="I76" s="7">
-        <v>0.45860300000000004</v>
+        <v>0.45738300000000004</v>
       </c>
       <c r="J76" s="7">
-        <v>2.258077</v>
+        <v>2.2523589999999998</v>
       </c>
       <c r="K76" s="7">
-        <v>5.6234079999999995</v>
+        <v>5.611783</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4981,25 +4981,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.031788</v>
+        <v>0.033126</v>
       </c>
       <c r="F77" s="7">
-        <v>0.037221000000000004</v>
+        <v>0.044042000000000005</v>
       </c>
       <c r="G77" s="7">
-        <v>0.324223</v>
+        <v>0.320809</v>
       </c>
       <c r="H77" s="7">
-        <v>0.23095400000000002</v>
+        <v>0.23220500000000002</v>
       </c>
       <c r="I77" s="7">
-        <v>0.424592</v>
+        <v>0.419895</v>
       </c>
       <c r="J77" s="7">
-        <v>1.9381720000000002</v>
+        <v>1.9411580000000002</v>
       </c>
       <c r="K77" s="7">
-        <v>5.5743920000000005</v>
+        <v>5.581073</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5037,25 +5037,25 @@
         <v>4</v>
       </c>
       <c r="E79" s="7">
-        <v>0.064651</v>
+        <v>0.06723</v>
       </c>
       <c r="F79" s="7">
-        <v>0.114234</v>
+        <v>0.110011</v>
       </c>
       <c r="G79" s="7">
-        <v>0.39584899999999995</v>
+        <v>0.38047600000000004</v>
       </c>
       <c r="H79" s="7">
-        <v>0.306537</v>
+        <v>0.302191</v>
       </c>
       <c r="I79" s="7">
-        <v>0.6955979999999999</v>
+        <v>0.690696</v>
       </c>
       <c r="J79" s="7">
-        <v>2.9432530000000003</v>
+        <v>2.9301369999999998</v>
       </c>
       <c r="K79" s="7">
-        <v>8.654570999999999</v>
+        <v>8.622456</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5072,25 +5072,25 @@
         <v>5</v>
       </c>
       <c r="E80" s="7">
-        <v>0.063596</v>
+        <v>0.060122</v>
       </c>
       <c r="F80" s="7">
-        <v>0.098531</v>
+        <v>0.085216</v>
       </c>
       <c r="G80" s="7">
-        <v>0.252257</v>
+        <v>0.242654</v>
       </c>
       <c r="H80" s="7">
-        <v>0.21223299999999998</v>
+        <v>0.203018</v>
       </c>
       <c r="I80" s="7">
-        <v>0.446274</v>
+        <v>0.43414</v>
       </c>
       <c r="J80" s="7">
-        <v>2.632027</v>
+        <v>2.604418</v>
       </c>
       <c r="K80" s="7">
-        <v>8.324459000000001</v>
+        <v>8.253579</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5107,25 +5107,25 @@
         <v>6</v>
       </c>
       <c r="E81" s="7">
-        <v>0.023451</v>
+        <v>0.01905</v>
       </c>
       <c r="F81" s="7">
-        <v>0.017825</v>
+        <v>0.007653999999999999</v>
       </c>
       <c r="G81" s="7">
-        <v>0.323007</v>
+        <v>0.31404699999999997</v>
       </c>
       <c r="H81" s="7">
-        <v>0.262571</v>
+        <v>0.254066</v>
       </c>
       <c r="I81" s="7">
-        <v>0.371479</v>
+        <v>0.359279</v>
       </c>
       <c r="J81" s="7">
-        <v>2.2443459999999997</v>
+        <v>2.2224909999999998</v>
       </c>
       <c r="K81" s="7">
-        <v>11.149213</v>
+        <v>11.067372</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5142,25 +5142,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.041524</v>
+        <v>0.038997000000000004</v>
       </c>
       <c r="F82" s="7">
-        <v>0.078207</v>
+        <v>0.072941</v>
       </c>
       <c r="G82" s="7">
-        <v>0.206972</v>
+        <v>0.20298</v>
       </c>
       <c r="H82" s="7">
-        <v>0.147639</v>
+        <v>0.144108</v>
       </c>
       <c r="I82" s="7">
-        <v>0.393712</v>
+        <v>0.389151</v>
       </c>
       <c r="J82" s="7">
-        <v>1.8517789999999998</v>
+        <v>1.843005</v>
       </c>
       <c r="K82" s="7">
-        <v>4.490777</v>
+        <v>4.473882</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5177,25 +5177,25 @@
         <v>4</v>
       </c>
       <c r="E83" s="7">
-        <v>0.014658</v>
+        <v>0.017647</v>
       </c>
       <c r="F83" s="7">
-        <v>0.016473</v>
+        <v>0.008005</v>
       </c>
       <c r="G83" s="7">
-        <v>0.147678</v>
+        <v>0.144929</v>
       </c>
       <c r="H83" s="7">
-        <v>0.058421</v>
+        <v>0.054721</v>
       </c>
       <c r="I83" s="7">
-        <v>0.383907</v>
+        <v>0.377127</v>
       </c>
       <c r="J83" s="7">
-        <v>1.51047</v>
+        <v>1.501695</v>
       </c>
       <c r="K83" s="7">
-        <v>3.133302</v>
+        <v>3.1188540000000002</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5212,25 +5212,25 @@
         <v>5</v>
       </c>
       <c r="E84" s="7">
-        <v>0.078764</v>
+        <v>0.075582</v>
       </c>
       <c r="F84" s="7">
-        <v>0.10027100000000001</v>
+        <v>0.08869300000000001</v>
       </c>
       <c r="G84" s="7">
-        <v>0.27314</v>
+        <v>0.26212</v>
       </c>
       <c r="H84" s="7">
-        <v>0.23654</v>
+        <v>0.226339</v>
       </c>
       <c r="I84" s="7">
-        <v>0.451553</v>
+        <v>0.43649</v>
       </c>
       <c r="J84" s="7">
-        <v>2.6699349999999997</v>
+        <v>2.639656</v>
       </c>
       <c r="K84" s="7">
-        <v>9.476219</v>
+        <v>9.389787</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5247,22 +5247,22 @@
         <v>6</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.0075509999999999996</v>
+        <v>-0.00434</v>
       </c>
       <c r="F85" s="7">
-        <v>-0.082394</v>
+        <v>-0.073447</v>
       </c>
       <c r="G85" s="7">
-        <v>0.117407</v>
+        <v>0.092095</v>
       </c>
       <c r="H85" s="7">
-        <v>0.038556</v>
+        <v>0.035863</v>
       </c>
       <c r="I85" s="7">
-        <v>0.68513</v>
+        <v>0.675981</v>
       </c>
       <c r="J85" s="7">
-        <v>3.817053</v>
+        <v>3.804562</v>
       </c>
       <c r="K85" s="7"/>
     </row>
@@ -5280,19 +5280,19 @@
         <v>2</v>
       </c>
       <c r="E86" s="7">
-        <v>0.031083</v>
+        <v>0.031248</v>
       </c>
       <c r="F86" s="7">
-        <v>0.093568</v>
+        <v>0.091761</v>
       </c>
       <c r="G86" s="7">
-        <v>0.19636299999999998</v>
+        <v>0.196627</v>
       </c>
       <c r="H86" s="7">
-        <v>0.13902699999999998</v>
+        <v>0.14041499999999998</v>
       </c>
       <c r="I86" s="7">
-        <v>0.46353099999999997</v>
+        <v>0.46352899999999997</v>
       </c>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5311,22 +5311,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.023825</v>
+        <v>0.026445</v>
       </c>
       <c r="F87" s="7">
-        <v>0.027098</v>
+        <v>0.029971</v>
       </c>
       <c r="G87" s="7">
-        <v>0.284157</v>
+        <v>0.286399</v>
       </c>
       <c r="H87" s="7">
-        <v>0.220532</v>
+        <v>0.22014399999999998</v>
       </c>
       <c r="I87" s="7">
-        <v>0.49331899999999995</v>
+        <v>0.480366</v>
       </c>
       <c r="J87" s="7">
-        <v>2.6540179999999998</v>
+        <v>2.652858</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5344,22 +5344,22 @@
         <v>6</v>
       </c>
       <c r="E88" s="7">
-        <v>0.15713</v>
+        <v>0.145556</v>
       </c>
       <c r="F88" s="7">
-        <v>0.306308</v>
+        <v>0.289813</v>
       </c>
       <c r="G88" s="7">
-        <v>0.406761</v>
+        <v>0.41178800000000004</v>
       </c>
       <c r="H88" s="7">
-        <v>0.424854</v>
+        <v>0.412822</v>
       </c>
       <c r="I88" s="7">
-        <v>0.748698</v>
+        <v>0.734138</v>
       </c>
       <c r="J88" s="7">
-        <v>4.419172</v>
+        <v>4.373413</v>
       </c>
       <c r="K88" s="7"/>
     </row>
@@ -5377,25 +5377,25 @@
         <v>7</v>
       </c>
       <c r="E89" s="7">
-        <v>0.000656</v>
+        <v>0.002473</v>
       </c>
       <c r="F89" s="7">
-        <v>-0.061748000000000004</v>
+        <v>-0.050621</v>
       </c>
       <c r="G89" s="7">
-        <v>0.189081</v>
+        <v>0.163188</v>
       </c>
       <c r="H89" s="7">
-        <v>0.10228300000000001</v>
+        <v>0.10111</v>
       </c>
       <c r="I89" s="7">
-        <v>0.682458</v>
+        <v>0.680201</v>
       </c>
       <c r="J89" s="7">
-        <v>4.240361</v>
+        <v>4.234782</v>
       </c>
       <c r="K89" s="7">
-        <v>13.784734</v>
+        <v>13.768995</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5412,25 +5412,25 @@
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>0.029946</v>
+        <v>0.031025999999999998</v>
       </c>
       <c r="F90" s="7">
-        <v>0.091892</v>
+        <v>0.09129</v>
       </c>
       <c r="G90" s="7">
-        <v>0.200186</v>
+        <v>0.20160699999999998</v>
       </c>
       <c r="H90" s="7">
-        <v>0.143633</v>
+        <v>0.145696</v>
       </c>
       <c r="I90" s="7">
-        <v>0.540219</v>
+        <v>0.539122</v>
       </c>
       <c r="J90" s="7">
-        <v>2.438753</v>
+        <v>2.4449549999999998</v>
       </c>
       <c r="K90" s="7">
-        <v>4.336857</v>
+        <v>4.346483</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5447,25 +5447,25 @@
         <v>5</v>
       </c>
       <c r="E91" s="7">
-        <v>0.009871</v>
+        <v>0.014119</v>
       </c>
       <c r="F91" s="7">
-        <v>0.012942</v>
+        <v>0.008069</v>
       </c>
       <c r="G91" s="7">
-        <v>0.173677</v>
+        <v>0.173658</v>
       </c>
       <c r="H91" s="7">
-        <v>0.09229599999999999</v>
+        <v>0.09263400000000001</v>
       </c>
       <c r="I91" s="7">
-        <v>0.32235100000000005</v>
+        <v>0.320751</v>
       </c>
       <c r="J91" s="7">
-        <v>2.094258</v>
+        <v>2.0952129999999998</v>
       </c>
       <c r="K91" s="7">
-        <v>5.397384</v>
+        <v>5.399360000000001</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5482,22 +5482,22 @@
         <v>6</v>
       </c>
       <c r="E92" s="7">
-        <v>0.011895</v>
+        <v>0.017819</v>
       </c>
       <c r="F92" s="7">
-        <v>0.005191</v>
+        <v>0.010557</v>
       </c>
       <c r="G92" s="7">
-        <v>0.251189</v>
+        <v>0.254383</v>
       </c>
       <c r="H92" s="7">
-        <v>0.184708</v>
+        <v>0.185492</v>
       </c>
       <c r="I92" s="7">
-        <v>0.38894100000000004</v>
+        <v>0.39502299999999996</v>
       </c>
       <c r="J92" s="7">
-        <v>2.502858</v>
+        <v>2.5051740000000002</v>
       </c>
       <c r="K92" s="7"/>
     </row>
@@ -5515,25 +5515,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.011278999999999999</v>
+        <v>0.017227</v>
       </c>
       <c r="F93" s="7">
-        <v>0.012768</v>
+        <v>0.008916</v>
       </c>
       <c r="G93" s="7">
-        <v>0.21151599999999998</v>
+        <v>0.21502600000000002</v>
       </c>
       <c r="H93" s="7">
-        <v>0.106983</v>
+        <v>0.10862999999999999</v>
       </c>
       <c r="I93" s="7">
-        <v>0.36641100000000004</v>
+        <v>0.366012</v>
       </c>
       <c r="J93" s="7">
-        <v>1.9580099999999998</v>
+        <v>1.962411</v>
       </c>
       <c r="K93" s="7">
-        <v>4.932243000000001</v>
+        <v>4.9410680000000005</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5550,25 +5550,25 @@
         <v>5</v>
       </c>
       <c r="E94" s="7">
-        <v>0.040412</v>
+        <v>0.034659</v>
       </c>
       <c r="F94" s="7">
-        <v>0.07596599999999999</v>
+        <v>0.072816</v>
       </c>
       <c r="G94" s="7">
-        <v>0.22851600000000002</v>
+        <v>0.23018999999999998</v>
       </c>
       <c r="H94" s="7">
-        <v>0.155144</v>
+        <v>0.156286</v>
       </c>
       <c r="I94" s="7">
-        <v>0.374987</v>
+        <v>0.378116</v>
       </c>
       <c r="J94" s="7">
-        <v>1.923162</v>
+        <v>1.9260519999999999</v>
       </c>
       <c r="K94" s="7">
-        <v>4.707688</v>
+        <v>4.713329</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5585,25 +5585,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.011368</v>
+        <v>0.009132</v>
       </c>
       <c r="F95" s="7">
-        <v>0.010679000000000001</v>
+        <v>0.003956</v>
       </c>
       <c r="G95" s="7">
-        <v>0.27911400000000003</v>
+        <v>0.269721</v>
       </c>
       <c r="H95" s="7">
-        <v>0.18174800000000002</v>
+        <v>0.177014</v>
       </c>
       <c r="I95" s="7">
-        <v>0.474032</v>
+        <v>0.464405</v>
       </c>
       <c r="J95" s="7">
-        <v>2.74938</v>
+        <v>2.7343599999999997</v>
       </c>
       <c r="K95" s="7">
-        <v>8.255761</v>
+        <v>8.218683</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5620,25 +5620,25 @@
         <v>4</v>
       </c>
       <c r="E96" s="7">
-        <v>0.010538</v>
+        <v>0.012712000000000001</v>
       </c>
       <c r="F96" s="7">
-        <v>0.017924</v>
+        <v>0.011039</v>
       </c>
       <c r="G96" s="7">
-        <v>0.179934</v>
+        <v>0.180888</v>
       </c>
       <c r="H96" s="7">
-        <v>0.056563999999999996</v>
+        <v>0.054599</v>
       </c>
       <c r="I96" s="7">
-        <v>0.42034</v>
+        <v>0.41407299999999997</v>
       </c>
       <c r="J96" s="7">
-        <v>1.3471389999999999</v>
+        <v>1.342775</v>
       </c>
       <c r="K96" s="7">
-        <v>2.753509</v>
+        <v>2.7465300000000004</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5655,25 +5655,25 @@
         <v>7</v>
       </c>
       <c r="E97" s="7">
-        <v>0.0012540000000000001</v>
+        <v>-0.0010299999999999999</v>
       </c>
       <c r="F97" s="7">
-        <v>-0.027895</v>
+        <v>-0.040633</v>
       </c>
       <c r="G97" s="7">
-        <v>0.33043700000000004</v>
+        <v>0.320407</v>
       </c>
       <c r="H97" s="7">
-        <v>0.233607</v>
+        <v>0.225934</v>
       </c>
       <c r="I97" s="7">
-        <v>0.377879</v>
+        <v>0.367106</v>
       </c>
       <c r="J97" s="7">
-        <v>2.672459</v>
+        <v>2.649617</v>
       </c>
       <c r="K97" s="7">
-        <v>14.660592</v>
+        <v>14.563184000000001</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5690,25 +5690,25 @@
         <v>6</v>
       </c>
       <c r="E98" s="7">
-        <v>0.01802</v>
+        <v>0.007844</v>
       </c>
       <c r="F98" s="7">
-        <v>-0.018867000000000002</v>
+        <v>-0.036095999999999996</v>
       </c>
       <c r="G98" s="7">
-        <v>0.448035</v>
+        <v>0.427913</v>
       </c>
       <c r="H98" s="7">
-        <v>0.243356</v>
+        <v>0.22784300000000002</v>
       </c>
       <c r="I98" s="7">
-        <v>0.501799</v>
+        <v>0.479337</v>
       </c>
       <c r="J98" s="7">
-        <v>3.846717</v>
+        <v>3.786246</v>
       </c>
       <c r="K98" s="7">
-        <v>19.402707</v>
+        <v>19.148148000000003</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5725,25 +5725,25 @@
         <v>4</v>
       </c>
       <c r="E99" s="7">
-        <v>0.014022</v>
+        <v>0.012889</v>
       </c>
       <c r="F99" s="7">
-        <v>0.037374</v>
+        <v>0.031166</v>
       </c>
       <c r="G99" s="7">
-        <v>0.31275</v>
+        <v>0.308216</v>
       </c>
       <c r="H99" s="7">
-        <v>0.224451</v>
+        <v>0.221472</v>
       </c>
       <c r="I99" s="7">
-        <v>0.5285329999999999</v>
+        <v>0.523487</v>
       </c>
       <c r="J99" s="7">
-        <v>3.3761309999999995</v>
+        <v>3.365482</v>
       </c>
       <c r="K99" s="7">
-        <v>9.204613</v>
+        <v>9.179779</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5760,25 +5760,25 @@
         <v>6</v>
       </c>
       <c r="E100" s="7">
-        <v>0.019507</v>
+        <v>0.016816</v>
       </c>
       <c r="F100" s="7">
-        <v>0.040542999999999996</v>
+        <v>0.040544000000000004</v>
       </c>
       <c r="G100" s="7">
-        <v>0.10504899999999999</v>
+        <v>0.10448700000000001</v>
       </c>
       <c r="H100" s="7">
-        <v>0.067448</v>
+        <v>0.067183</v>
       </c>
       <c r="I100" s="7">
-        <v>0.273504</v>
+        <v>0.271908</v>
       </c>
       <c r="J100" s="7">
-        <v>1.9577330000000002</v>
+        <v>1.9569990000000002</v>
       </c>
       <c r="K100" s="7">
-        <v>5.668884</v>
+        <v>5.66723</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5795,25 +5795,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.010212</v>
+        <v>0.008577</v>
       </c>
       <c r="F101" s="7">
-        <v>0.027625999999999998</v>
+        <v>0.020467</v>
       </c>
       <c r="G101" s="7">
-        <v>0.380124</v>
+        <v>0.373818</v>
       </c>
       <c r="H101" s="7">
-        <v>0.23150300000000001</v>
+        <v>0.227299</v>
       </c>
       <c r="I101" s="7">
-        <v>0.560175</v>
+        <v>0.554411</v>
       </c>
       <c r="J101" s="7">
-        <v>3.490896</v>
+        <v>3.475566</v>
       </c>
       <c r="K101" s="7">
-        <v>12.15544</v>
+        <v>12.110532000000001</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5830,25 +5830,25 @@
         <v>5</v>
       </c>
       <c r="E102" s="7">
-        <v>0.06855</v>
+        <v>0.061415</v>
       </c>
       <c r="F102" s="7">
-        <v>0.093073</v>
+        <v>0.09024900000000001</v>
       </c>
       <c r="G102" s="7">
-        <v>0.43919600000000003</v>
+        <v>0.44383</v>
       </c>
       <c r="H102" s="7">
-        <v>0.362827</v>
+        <v>0.36086399999999996</v>
       </c>
       <c r="I102" s="7">
-        <v>0.688698</v>
+        <v>0.690557</v>
       </c>
       <c r="J102" s="7">
-        <v>3.7492059999999996</v>
+        <v>3.742366</v>
       </c>
       <c r="K102" s="7">
-        <v>11.910079000000001</v>
+        <v>11.891485</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5865,25 +5865,25 @@
         <v>2</v>
       </c>
       <c r="E103" s="7">
-        <v>0.028713000000000002</v>
+        <v>0.027067</v>
       </c>
       <c r="F103" s="7">
-        <v>0.085952</v>
+        <v>0.08177899999999999</v>
       </c>
       <c r="G103" s="7">
-        <v>0.26898900000000003</v>
+        <v>0.267487</v>
       </c>
       <c r="H103" s="7">
-        <v>0.17252199999999998</v>
+        <v>0.17119199999999998</v>
       </c>
       <c r="I103" s="7">
-        <v>0.565891</v>
+        <v>0.561897</v>
       </c>
       <c r="J103" s="7">
-        <v>3.1315269999999997</v>
+        <v>3.126843</v>
       </c>
       <c r="K103" s="7">
-        <v>5.754278</v>
+        <v>5.74662</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5900,25 +5900,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.072039</v>
+        <v>0.065084</v>
       </c>
       <c r="F104" s="7">
-        <v>0.085509</v>
+        <v>0.08177899999999999</v>
       </c>
       <c r="G104" s="7">
-        <v>0.462431</v>
+        <v>0.46630499999999997</v>
       </c>
       <c r="H104" s="7">
-        <v>0.38748600000000005</v>
+        <v>0.384014</v>
       </c>
       <c r="I104" s="7">
-        <v>0.69171</v>
+        <v>0.691948</v>
       </c>
       <c r="J104" s="7">
-        <v>3.661246</v>
+        <v>3.649581</v>
       </c>
       <c r="K104" s="7">
-        <v>14.095837</v>
+        <v>14.058060000000001</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5935,25 +5935,25 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.01583</v>
+        <v>0.013824000000000001</v>
       </c>
       <c r="F105" s="7">
-        <v>0.02988</v>
+        <v>0.0296</v>
       </c>
       <c r="G105" s="7">
-        <v>0.100168</v>
+        <v>0.09852</v>
       </c>
       <c r="H105" s="7">
-        <v>0.055490000000000005</v>
+        <v>0.054946999999999996</v>
       </c>
       <c r="I105" s="7">
-        <v>0.30342800000000003</v>
+        <v>0.301773</v>
       </c>
       <c r="J105" s="7">
-        <v>2.072295</v>
+        <v>2.070717</v>
       </c>
       <c r="K105" s="7">
-        <v>6.0679</v>
+        <v>6.0642700000000005</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5970,19 +5970,19 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0</v>
+        <v>0.047618999999999995</v>
       </c>
       <c r="F106" s="7">
-        <v>0</v>
+        <v>0.045004</v>
       </c>
       <c r="G106" s="7">
-        <v>0</v>
+        <v>0.225168</v>
       </c>
       <c r="H106" s="7">
-        <v>0</v>
+        <v>0.172777</v>
       </c>
       <c r="I106" s="7">
-        <v>0</v>
+        <v>0.423542</v>
       </c>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -6001,22 +6001,22 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.213123</v>
+        <v>0.196664</v>
       </c>
       <c r="F107" s="7">
-        <v>0.306742</v>
+        <v>0.307365</v>
       </c>
       <c r="G107" s="7">
-        <v>0.461659</v>
+        <v>0.45948</v>
       </c>
       <c r="H107" s="7">
-        <v>0.432359</v>
+        <v>0.422607</v>
       </c>
       <c r="I107" s="7">
-        <v>0.8749020000000001</v>
+        <v>0.8463379999999999</v>
       </c>
       <c r="J107" s="7">
-        <v>4.7287110000000006</v>
+        <v>4.689707</v>
       </c>
       <c r="K107" s="7"/>
     </row>
@@ -6034,25 +6034,25 @@
         <v>6</v>
       </c>
       <c r="E108" s="7">
-        <v>0.0067090000000000006</v>
+        <v>0.0059099999999999995</v>
       </c>
       <c r="F108" s="7">
-        <v>-0.049015</v>
+        <v>-0.042701</v>
       </c>
       <c r="G108" s="7">
-        <v>0.211698</v>
+        <v>0.184574</v>
       </c>
       <c r="H108" s="7">
-        <v>0.13669900000000001</v>
+        <v>0.133988</v>
       </c>
       <c r="I108" s="7">
-        <v>0.7402549999999999</v>
+        <v>0.731327</v>
       </c>
       <c r="J108" s="7">
-        <v>4.983346</v>
+        <v>4.969074</v>
       </c>
       <c r="K108" s="7">
-        <v>15.927918</v>
+        <v>15.887541</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6069,25 +6069,25 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.013153</v>
+        <v>0.016634</v>
       </c>
       <c r="F109" s="7">
-        <v>0.037714</v>
+        <v>0.033302</v>
       </c>
       <c r="G109" s="7">
-        <v>0.185363</v>
+        <v>0.182981</v>
       </c>
       <c r="H109" s="7">
-        <v>0.084497</v>
+        <v>0.082906</v>
       </c>
       <c r="I109" s="7">
-        <v>0.463673</v>
+        <v>0.459998</v>
       </c>
       <c r="J109" s="7">
-        <v>2.096996</v>
+        <v>2.092453</v>
       </c>
       <c r="K109" s="7">
-        <v>3.913506</v>
+        <v>3.906298</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6104,25 +6104,25 @@
         <v>6</v>
       </c>
       <c r="E110" s="7">
-        <v>0.016431</v>
+        <v>0.013238000000000002</v>
       </c>
       <c r="F110" s="7">
-        <v>0.023690000000000003</v>
+        <v>0.023007</v>
       </c>
       <c r="G110" s="7">
-        <v>0.127127</v>
+        <v>0.123878</v>
       </c>
       <c r="H110" s="7">
-        <v>0.06223</v>
+        <v>0.061255</v>
       </c>
       <c r="I110" s="7">
-        <v>0.331339</v>
+        <v>0.33075200000000005</v>
       </c>
       <c r="J110" s="7">
-        <v>2.1712000000000002</v>
+        <v>2.168289</v>
       </c>
       <c r="K110" s="7">
-        <v>6.500951</v>
+        <v>6.494065000000001</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6139,25 +6139,25 @@
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>0.044659000000000004</v>
+        <v>0.036799</v>
       </c>
       <c r="F111" s="7">
-        <v>0.095183</v>
+        <v>0.09178599999999999</v>
       </c>
       <c r="G111" s="7">
-        <v>0.241404</v>
+        <v>0.24043299999999998</v>
       </c>
       <c r="H111" s="7">
-        <v>0.183671</v>
+        <v>0.182503</v>
       </c>
       <c r="I111" s="7">
-        <v>0.486804</v>
+        <v>0.47853</v>
       </c>
       <c r="J111" s="7">
-        <v>2.132251</v>
+        <v>2.129162</v>
       </c>
       <c r="K111" s="7">
-        <v>5.624756</v>
+        <v>5.618223</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6174,25 +6174,25 @@
         <v>5</v>
       </c>
       <c r="E112" s="7">
-        <v>0.026217999999999998</v>
+        <v>0.020149</v>
       </c>
       <c r="F112" s="7">
-        <v>0.021386</v>
+        <v>0.013848000000000001</v>
       </c>
       <c r="G112" s="7">
-        <v>0.279337</v>
+        <v>0.27413</v>
       </c>
       <c r="H112" s="7">
-        <v>0.18006699999999998</v>
+        <v>0.17376999999999998</v>
       </c>
       <c r="I112" s="7">
-        <v>0.538899</v>
+        <v>0.533056</v>
       </c>
       <c r="J112" s="7">
-        <v>3.4008839999999996</v>
+        <v>3.377398</v>
       </c>
       <c r="K112" s="7">
-        <v>14.752756</v>
+        <v>14.668688</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6209,25 +6209,25 @@
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>0.025949</v>
+        <v>0.025585</v>
       </c>
       <c r="F113" s="7">
-        <v>0.079349</v>
+        <v>0.075415</v>
       </c>
       <c r="G113" s="7">
-        <v>0.23469</v>
+        <v>0.23295300000000002</v>
       </c>
       <c r="H113" s="7">
-        <v>0.151548</v>
+        <v>0.15079</v>
       </c>
       <c r="I113" s="7">
-        <v>0.523249</v>
+        <v>0.5205449999999999</v>
       </c>
       <c r="J113" s="7">
-        <v>3.242919</v>
+        <v>3.240126</v>
       </c>
       <c r="K113" s="7">
-        <v>6.278378</v>
+        <v>6.273587</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6244,25 +6244,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.058871</v>
+        <v>0.046801</v>
       </c>
       <c r="F114" s="7">
-        <v>0.097956</v>
+        <v>0.08739000000000001</v>
       </c>
       <c r="G114" s="7">
-        <v>0.36335700000000004</v>
+        <v>0.35850099999999996</v>
       </c>
       <c r="H114" s="7">
-        <v>0.291751</v>
+        <v>0.282158</v>
       </c>
       <c r="I114" s="7">
-        <v>0.579165</v>
+        <v>0.568872</v>
       </c>
       <c r="J114" s="7">
-        <v>3.5975479999999997</v>
+        <v>3.563404</v>
       </c>
       <c r="K114" s="7">
-        <v>17.057682</v>
+        <v>16.923576</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6279,25 +6279,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.016411</v>
+        <v>0.006634999999999999</v>
       </c>
       <c r="F115" s="7">
-        <v>-0.0045119999999999995</v>
+        <v>-0.020358</v>
       </c>
       <c r="G115" s="7">
-        <v>0.305828</v>
+        <v>0.29121400000000003</v>
       </c>
       <c r="H115" s="7">
-        <v>0.210237</v>
+        <v>0.19715</v>
       </c>
       <c r="I115" s="7">
-        <v>0.508135</v>
+        <v>0.494621</v>
       </c>
       <c r="J115" s="7">
-        <v>3.1550580000000004</v>
+        <v>3.110127</v>
       </c>
       <c r="K115" s="7">
-        <v>22.284792000000003</v>
+        <v>22.032999</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6314,25 +6314,25 @@
         <v>6</v>
       </c>
       <c r="E116" s="7">
-        <v>0.024607</v>
+        <v>0.024916999999999998</v>
       </c>
       <c r="F116" s="7">
-        <v>0.043515</v>
+        <v>0.036822</v>
       </c>
       <c r="G116" s="7">
-        <v>0.350199</v>
+        <v>0.347769</v>
       </c>
       <c r="H116" s="7">
-        <v>0.256866</v>
+        <v>0.24997499999999997</v>
       </c>
       <c r="I116" s="7">
-        <v>0.520692</v>
+        <v>0.521002</v>
       </c>
       <c r="J116" s="7">
-        <v>2.690516</v>
+        <v>2.6702850000000002</v>
       </c>
       <c r="K116" s="7">
-        <v>15.875006</v>
+        <v>15.782494999999999</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6349,25 +6349,25 @@
         <v>5</v>
       </c>
       <c r="E117" s="7">
-        <v>0.044635999999999995</v>
+        <v>0.032570999999999996</v>
       </c>
       <c r="F117" s="7">
-        <v>0.109381</v>
+        <v>0.101397</v>
       </c>
       <c r="G117" s="7">
-        <v>0.358964</v>
+        <v>0.355242</v>
       </c>
       <c r="H117" s="7">
-        <v>0.291799</v>
+        <v>0.284394</v>
       </c>
       <c r="I117" s="7">
-        <v>0.655258</v>
+        <v>0.646343</v>
       </c>
       <c r="J117" s="7">
-        <v>3.3372590000000004</v>
+        <v>3.3123989999999996</v>
       </c>
       <c r="K117" s="7">
-        <v>12.471387</v>
+        <v>12.394174</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6384,25 +6384,25 @@
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>0.013456999999999998</v>
+        <v>0.016289</v>
       </c>
       <c r="F118" s="7">
-        <v>0.038646</v>
+        <v>0.0339</v>
       </c>
       <c r="G118" s="7">
-        <v>0.18303899999999998</v>
+        <v>0.180614</v>
       </c>
       <c r="H118" s="7">
-        <v>0.07867099999999999</v>
+        <v>0.076864</v>
       </c>
       <c r="I118" s="7">
-        <v>0.434562</v>
+        <v>0.430419</v>
       </c>
       <c r="J118" s="7">
-        <v>1.881464</v>
+        <v>1.876636</v>
       </c>
       <c r="K118" s="7">
-        <v>3.704986</v>
+        <v>3.6971030000000003</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6419,25 +6419,25 @@
         <v>6</v>
       </c>
       <c r="E119" s="7">
-        <v>0.033431</v>
+        <v>0.036253</v>
       </c>
       <c r="F119" s="7">
-        <v>0.051523000000000006</v>
+        <v>0.052579</v>
       </c>
       <c r="G119" s="7">
-        <v>0.319982</v>
+        <v>0.32081000000000004</v>
       </c>
       <c r="H119" s="7">
-        <v>0.22933800000000001</v>
+        <v>0.22806200000000001</v>
       </c>
       <c r="I119" s="7">
-        <v>0.632235</v>
+        <v>0.63544</v>
       </c>
       <c r="J119" s="7">
-        <v>3.518162</v>
+        <v>3.513471</v>
       </c>
       <c r="K119" s="7">
-        <v>16.325743</v>
+        <v>16.307755999999998</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6454,25 +6454,25 @@
         <v>5</v>
       </c>
       <c r="E120" s="7">
-        <v>0.004072</v>
+        <v>0.004532</v>
       </c>
       <c r="F120" s="7">
-        <v>0.009351</v>
+        <v>0.008732</v>
       </c>
       <c r="G120" s="7">
-        <v>0.20715399999999998</v>
+        <v>0.208049</v>
       </c>
       <c r="H120" s="7">
-        <v>0.119485</v>
+        <v>0.119323</v>
       </c>
       <c r="I120" s="7">
-        <v>0.443167</v>
+        <v>0.443309</v>
       </c>
       <c r="J120" s="7">
-        <v>2.488077</v>
+        <v>2.487575</v>
       </c>
       <c r="K120" s="7">
-        <v>8.894639</v>
+        <v>8.893215</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6489,25 +6489,25 @@
         <v>6</v>
       </c>
       <c r="E121" s="7">
-        <v>0.021869</v>
+        <v>0.034872</v>
       </c>
       <c r="F121" s="7">
-        <v>-0.01765</v>
+        <v>-0.01722</v>
       </c>
       <c r="G121" s="7">
-        <v>0.21049199999999998</v>
+        <v>0.2065</v>
       </c>
       <c r="H121" s="7">
-        <v>0.165903</v>
+        <v>0.168326</v>
       </c>
       <c r="I121" s="7">
-        <v>0.43593699999999996</v>
+        <v>0.440033</v>
       </c>
       <c r="J121" s="7">
-        <v>3.31893</v>
+        <v>3.327907</v>
       </c>
       <c r="K121" s="7">
-        <v>18.125269</v>
+        <v>18.165021</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6524,25 +6524,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.015639</v>
+        <v>0.015484</v>
       </c>
       <c r="F122" s="7">
-        <v>0.037745</v>
+        <v>0.032623</v>
       </c>
       <c r="G122" s="7">
-        <v>0.220973</v>
+        <v>0.218813</v>
       </c>
       <c r="H122" s="7">
-        <v>0.132404</v>
+        <v>0.129793</v>
       </c>
       <c r="I122" s="7">
-        <v>0.475742</v>
+        <v>0.471607</v>
       </c>
       <c r="J122" s="7">
-        <v>2.325893</v>
+        <v>2.318223</v>
       </c>
       <c r="K122" s="7">
-        <v>6.013034</v>
+        <v>5.996862</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6559,25 +6559,25 @@
         <v>4</v>
       </c>
       <c r="E123" s="7">
-        <v>0.017772</v>
+        <v>0.016587</v>
       </c>
       <c r="F123" s="7">
-        <v>0.037624</v>
+        <v>0.032712</v>
       </c>
       <c r="G123" s="7">
-        <v>0.192154</v>
+        <v>0.18938300000000002</v>
       </c>
       <c r="H123" s="7">
-        <v>0.118713</v>
+        <v>0.11622199999999999</v>
       </c>
       <c r="I123" s="7">
-        <v>0.430362</v>
+        <v>0.42621200000000004</v>
       </c>
       <c r="J123" s="7">
-        <v>1.977321</v>
+        <v>1.9706899999999998</v>
       </c>
       <c r="K123" s="7">
-        <v>6.068363000000001</v>
+        <v>6.052621</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6594,16 +6594,16 @@
         <v>6</v>
       </c>
       <c r="E124" s="7">
-        <v>0.007916</v>
+        <v>0.005174</v>
       </c>
       <c r="F124" s="7">
-        <v>-0.064683</v>
+        <v>-0.057404000000000004</v>
       </c>
       <c r="G124" s="7">
-        <v>0.199425</v>
+        <v>0.170592</v>
       </c>
       <c r="H124" s="7">
-        <v>0.142075</v>
+        <v>0.137134</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
@@ -6623,25 +6623,25 @@
         <v>4</v>
       </c>
       <c r="E125" s="7">
-        <v>0.016901</v>
+        <v>0.016876</v>
       </c>
       <c r="F125" s="7">
-        <v>0.018668</v>
+        <v>0.012747</v>
       </c>
       <c r="G125" s="7">
-        <v>0.257703</v>
+        <v>0.253043</v>
       </c>
       <c r="H125" s="7">
-        <v>0.167114</v>
+        <v>0.165191</v>
       </c>
       <c r="I125" s="7">
-        <v>0.506068</v>
+        <v>0.50209</v>
       </c>
       <c r="J125" s="7">
-        <v>2.058821</v>
+        <v>2.053781</v>
       </c>
       <c r="K125" s="7">
-        <v>6.539583</v>
+        <v>6.5271609999999995</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6658,16 +6658,16 @@
         <v>6</v>
       </c>
       <c r="E126" s="7">
-        <v>0.104795</v>
+        <v>0.088271</v>
       </c>
       <c r="F126" s="7">
-        <v>0.150263</v>
+        <v>0.143884</v>
       </c>
       <c r="G126" s="7">
-        <v>0.48344000000000004</v>
+        <v>0.47690699999999997</v>
       </c>
       <c r="H126" s="7">
-        <v>0.410465</v>
+        <v>0.401076</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
@@ -6687,25 +6687,25 @@
         <v>7</v>
       </c>
       <c r="E127" s="7">
-        <v>0.030912000000000002</v>
+        <v>0.025362</v>
       </c>
       <c r="F127" s="7">
-        <v>0.021955</v>
+        <v>0.009606</v>
       </c>
       <c r="G127" s="7">
-        <v>0.267636</v>
+        <v>0.258171</v>
       </c>
       <c r="H127" s="7">
-        <v>0.145693</v>
+        <v>0.136662</v>
       </c>
       <c r="I127" s="7">
-        <v>0.40936500000000003</v>
+        <v>0.397752</v>
       </c>
       <c r="J127" s="7">
-        <v>2.423554</v>
+        <v>2.396569</v>
       </c>
       <c r="K127" s="7">
-        <v>9.338033000000001</v>
+        <v>9.256545</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6722,25 +6722,25 @@
         <v>5</v>
       </c>
       <c r="E128" s="7">
-        <v>0.013927</v>
+        <v>0.010751</v>
       </c>
       <c r="F128" s="7">
-        <v>0.02183</v>
+        <v>0.018804</v>
       </c>
       <c r="G128" s="7">
-        <v>0.092797</v>
+        <v>0.089613</v>
       </c>
       <c r="H128" s="7">
-        <v>0.053295</v>
+        <v>0.051232</v>
       </c>
       <c r="I128" s="7">
-        <v>0.28549</v>
+        <v>0.27997900000000003</v>
       </c>
       <c r="J128" s="7">
-        <v>1.961002</v>
+        <v>1.955203</v>
       </c>
       <c r="K128" s="7">
-        <v>5.486681</v>
+        <v>5.473978</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6757,25 +6757,25 @@
         <v>4</v>
       </c>
       <c r="E129" s="7">
-        <v>0.016274</v>
+        <v>0.018918</v>
       </c>
       <c r="F129" s="7">
-        <v>0.010501</v>
+        <v>0.000254</v>
       </c>
       <c r="G129" s="7">
-        <v>0.156779</v>
+        <v>0.153459</v>
       </c>
       <c r="H129" s="7">
-        <v>0.057826</v>
+        <v>0.052861000000000005</v>
       </c>
       <c r="I129" s="7">
-        <v>0.391331</v>
+        <v>0.382746</v>
       </c>
       <c r="J129" s="7">
-        <v>1.581946</v>
+        <v>1.5698269999999999</v>
       </c>
       <c r="K129" s="7">
-        <v>3.379273</v>
+        <v>3.358719</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6792,25 +6792,25 @@
         <v>6</v>
       </c>
       <c r="E130" s="7">
-        <v>0.011781</v>
+        <v>0.012248000000000002</v>
       </c>
       <c r="F130" s="7">
-        <v>-0.00471</v>
+        <v>-0.011433</v>
       </c>
       <c r="G130" s="7">
-        <v>0.33683599999999997</v>
+        <v>0.325857</v>
       </c>
       <c r="H130" s="7">
-        <v>0.246794</v>
+        <v>0.240957</v>
       </c>
       <c r="I130" s="7">
-        <v>0.463319</v>
+        <v>0.457384</v>
       </c>
       <c r="J130" s="7">
-        <v>2.7553789999999996</v>
+        <v>2.737799</v>
       </c>
       <c r="K130" s="7">
-        <v>14.151288999999998</v>
+        <v>14.08036</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6827,25 +6827,25 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.015983</v>
+        <v>0.013852</v>
       </c>
       <c r="F131" s="7">
-        <v>0.023788999999999998</v>
+        <v>0.022561</v>
       </c>
       <c r="G131" s="7">
-        <v>0.084558</v>
+        <v>0.081467</v>
       </c>
       <c r="H131" s="7">
-        <v>0.047821999999999996</v>
+        <v>0.047261</v>
       </c>
       <c r="I131" s="7">
-        <v>0.270082</v>
+        <v>0.268489</v>
       </c>
       <c r="J131" s="7">
-        <v>1.985444</v>
+        <v>1.983845</v>
       </c>
       <c r="K131" s="7">
-        <v>6.213452</v>
+        <v>6.209588999999999</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6904,19 +6904,19 @@
         <v>4</v>
       </c>
       <c r="E134" s="7">
-        <v>0.12965</v>
+        <v>0.138051</v>
       </c>
       <c r="F134" s="7">
-        <v>0.178249</v>
+        <v>0.21361</v>
       </c>
       <c r="G134" s="7">
-        <v>0.318855</v>
+        <v>0.344628</v>
       </c>
       <c r="H134" s="7">
-        <v>0.332502</v>
+        <v>0.345417</v>
       </c>
       <c r="I134" s="7">
-        <v>0.739105</v>
+        <v>0.6988509999999999</v>
       </c>
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
@@ -6935,25 +6935,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.010073</v>
+        <v>0.015691</v>
       </c>
       <c r="F135" s="7">
-        <v>0.004072</v>
+        <v>0.000054999999999999995</v>
       </c>
       <c r="G135" s="7">
-        <v>0.18252300000000002</v>
+        <v>0.18284099999999998</v>
       </c>
       <c r="H135" s="7">
-        <v>0.08628999999999999</v>
+        <v>0.086098</v>
       </c>
       <c r="I135" s="7">
-        <v>0.397844</v>
+        <v>0.395845</v>
       </c>
       <c r="J135" s="7">
-        <v>1.5014969999999999</v>
+        <v>1.501053</v>
       </c>
       <c r="K135" s="7">
-        <v>3.755454</v>
+        <v>3.7546109999999997</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6970,25 +6970,25 @@
         <v>3</v>
       </c>
       <c r="E136" s="7">
-        <v>0.031596</v>
+        <v>0.031383999999999995</v>
       </c>
       <c r="F136" s="7">
-        <v>0.08848</v>
+        <v>0.086543</v>
       </c>
       <c r="G136" s="7">
-        <v>0.191309</v>
+        <v>0.189864</v>
       </c>
       <c r="H136" s="7">
-        <v>0.136212</v>
+        <v>0.137576</v>
       </c>
       <c r="I136" s="7">
-        <v>0.46002699999999996</v>
+        <v>0.460137</v>
       </c>
       <c r="J136" s="7">
-        <v>2.316489</v>
+        <v>2.320471</v>
       </c>
       <c r="K136" s="7">
-        <v>3.89045</v>
+        <v>3.896322</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7005,25 +7005,25 @@
         <v>6</v>
       </c>
       <c r="E137" s="7">
-        <v>0.048007</v>
+        <v>0.047208</v>
       </c>
       <c r="F137" s="7">
-        <v>0.05769199999999999</v>
+        <v>0.051778000000000005</v>
       </c>
       <c r="G137" s="7">
-        <v>0.275214</v>
+        <v>0.27409300000000003</v>
       </c>
       <c r="H137" s="7">
-        <v>0.20420200000000002</v>
+        <v>0.20198</v>
       </c>
       <c r="I137" s="7">
-        <v>0.45317999999999997</v>
+        <v>0.449944</v>
       </c>
       <c r="J137" s="7">
-        <v>2.8020389999999997</v>
+        <v>2.795024</v>
       </c>
       <c r="K137" s="7">
-        <v>8.040839</v>
+        <v>8.024158</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7040,25 +7040,25 @@
         <v>4</v>
       </c>
       <c r="E138" s="7">
-        <v>0.011833</v>
+        <v>0.017295</v>
       </c>
       <c r="F138" s="7">
-        <v>0.0052829999999999995</v>
+        <v>-0.001791</v>
       </c>
       <c r="G138" s="7">
-        <v>0.168077</v>
+        <v>0.167504</v>
       </c>
       <c r="H138" s="7">
-        <v>0.08180799999999999</v>
+        <v>0.08051</v>
       </c>
       <c r="I138" s="7">
-        <v>0.34956000000000004</v>
+        <v>0.347057</v>
       </c>
       <c r="J138" s="7">
-        <v>1.062494</v>
+        <v>1.060019</v>
       </c>
       <c r="K138" s="7">
-        <v>2.437813</v>
+        <v>2.433688</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7075,25 +7075,25 @@
         <v>6</v>
       </c>
       <c r="E139" s="7">
-        <v>0.047143</v>
+        <v>0.045191</v>
       </c>
       <c r="F139" s="7">
-        <v>0.075753</v>
+        <v>0.071463</v>
       </c>
       <c r="G139" s="7">
-        <v>0.215456</v>
+        <v>0.207888</v>
       </c>
       <c r="H139" s="7">
-        <v>0.17843499999999998</v>
+        <v>0.17252099999999998</v>
       </c>
       <c r="I139" s="7">
-        <v>0.43213700000000005</v>
+        <v>0.42322400000000004</v>
       </c>
       <c r="J139" s="7">
-        <v>2.9943049999999998</v>
+        <v>2.9742610000000003</v>
       </c>
       <c r="K139" s="7">
-        <v>9.468066</v>
+        <v>9.415536</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -7110,25 +7110,25 @@
         <v>4</v>
       </c>
       <c r="E140" s="7">
-        <v>0.033285999999999996</v>
+        <v>0.033574</v>
       </c>
       <c r="F140" s="7">
-        <v>0.054154</v>
+        <v>0.049074</v>
       </c>
       <c r="G140" s="7">
-        <v>0.19415400000000002</v>
+        <v>0.19216</v>
       </c>
       <c r="H140" s="7">
-        <v>0.123836</v>
+        <v>0.12214900000000001</v>
       </c>
       <c r="I140" s="7">
-        <v>0.43491</v>
+        <v>0.431286</v>
       </c>
       <c r="J140" s="7">
-        <v>2.203356</v>
+        <v>2.198546</v>
       </c>
       <c r="K140" s="7">
-        <v>4.218872</v>
+        <v>4.211036</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7145,19 +7145,19 @@
         <v>6</v>
       </c>
       <c r="E141" s="7">
-        <v>0.18736</v>
+        <v>0.182407</v>
       </c>
       <c r="F141" s="7">
-        <v>0.23769600000000002</v>
+        <v>0.250202</v>
       </c>
       <c r="G141" s="7">
-        <v>0.400117</v>
+        <v>0.41924700000000004</v>
       </c>
       <c r="H141" s="7">
         <v>0.344711</v>
       </c>
       <c r="I141" s="7">
-        <v>0.8870359999999999</v>
+        <v>0.854532</v>
       </c>
       <c r="J141" s="7">
         <v>5.762248</v>
@@ -7178,22 +7178,22 @@
         <v>4</v>
       </c>
       <c r="E142" s="7">
-        <v>0.222594</v>
+        <v>0.048504</v>
       </c>
       <c r="F142" s="7">
-        <v>0.19456900000000002</v>
+        <v>0.025354</v>
       </c>
       <c r="G142" s="7">
-        <v>0.422487</v>
+        <v>0.20755700000000002</v>
       </c>
       <c r="H142" s="7">
-        <v>0.335108</v>
+        <v>0.139746</v>
       </c>
       <c r="I142" s="7">
-        <v>0.7981870000000001</v>
+        <v>0.5341400000000001</v>
       </c>
       <c r="J142" s="7">
-        <v>5.773391</v>
+        <v>4.782261</v>
       </c>
       <c r="K142" s="7"/>
     </row>
@@ -7211,25 +7211,25 @@
         <v>3</v>
       </c>
       <c r="E143" s="7">
-        <v>0.012538</v>
+        <v>0.015151</v>
       </c>
       <c r="F143" s="7">
-        <v>0.012593</v>
+        <v>0.008559</v>
       </c>
       <c r="G143" s="7">
-        <v>0.166024</v>
+        <v>0.16401</v>
       </c>
       <c r="H143" s="7">
-        <v>0.09592700000000001</v>
+        <v>0.095244</v>
       </c>
       <c r="I143" s="7">
-        <v>0.36060200000000003</v>
+        <v>0.356952</v>
       </c>
       <c r="J143" s="7">
-        <v>1.64197</v>
+        <v>1.640324</v>
       </c>
       <c r="K143" s="7">
-        <v>3.61251</v>
+        <v>3.609636</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7246,25 +7246,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.032368</v>
+        <v>0.028098</v>
       </c>
       <c r="F144" s="7">
-        <v>0.063497</v>
+        <v>0.061406</v>
       </c>
       <c r="G144" s="7">
-        <v>0.20069199999999998</v>
+        <v>0.19888899999999998</v>
       </c>
       <c r="H144" s="7">
-        <v>0.134484</v>
+        <v>0.133746</v>
       </c>
       <c r="I144" s="7">
-        <v>0.353374</v>
+        <v>0.35196399999999994</v>
       </c>
       <c r="J144" s="7">
-        <v>1.573811</v>
+        <v>1.5721379999999998</v>
       </c>
       <c r="K144" s="7">
-        <v>4.490035</v>
+        <v>4.486466</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7281,25 +7281,25 @@
         <v>5</v>
       </c>
       <c r="E145" s="7">
-        <v>0.087625</v>
+        <v>0.08816800000000001</v>
       </c>
       <c r="F145" s="7">
-        <v>0.018698</v>
+        <v>0.012841</v>
       </c>
       <c r="G145" s="7">
-        <v>0.301944</v>
+        <v>0.320237</v>
       </c>
       <c r="H145" s="7">
-        <v>0.194004</v>
+        <v>0.193781</v>
       </c>
       <c r="I145" s="7">
-        <v>0.37067700000000003</v>
+        <v>0.367751</v>
       </c>
       <c r="J145" s="7">
-        <v>3.194305</v>
+        <v>3.19352</v>
       </c>
       <c r="K145" s="7">
-        <v>13.749145</v>
+        <v>13.746385</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7316,25 +7316,25 @@
         <v>5</v>
       </c>
       <c r="E146" s="7">
-        <v>0.011664</v>
+        <v>-0.004059</v>
       </c>
       <c r="F146" s="7">
-        <v>0.11717499999999999</v>
+        <v>0.09768800000000001</v>
       </c>
       <c r="G146" s="7">
-        <v>0.27788</v>
+        <v>0.260434</v>
       </c>
       <c r="H146" s="7">
-        <v>0.291831</v>
+        <v>0.27426100000000003</v>
       </c>
       <c r="I146" s="7">
-        <v>0.263066</v>
+        <v>0.24296700000000002</v>
       </c>
       <c r="J146" s="7">
-        <v>3.3491649999999997</v>
+        <v>3.2900139999999998</v>
       </c>
       <c r="K146" s="7">
-        <v>10.993034999999999</v>
+        <v>10.829924</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7351,25 +7351,25 @@
         <v>3</v>
       </c>
       <c r="E147" s="7">
-        <v>0.026307</v>
+        <v>0.023947</v>
       </c>
       <c r="F147" s="7">
-        <v>0.06575</v>
+        <v>0.054416</v>
       </c>
       <c r="G147" s="7">
-        <v>0.324505</v>
+        <v>0.315642</v>
       </c>
       <c r="H147" s="7">
-        <v>0.220523</v>
+        <v>0.213278</v>
       </c>
       <c r="I147" s="7">
-        <v>0.574442</v>
+        <v>0.56665</v>
       </c>
       <c r="J147" s="7">
-        <v>2.960464</v>
+        <v>2.9369549999999998</v>
       </c>
       <c r="K147" s="7">
-        <v>8.244589</v>
+        <v>8.189715</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7386,25 +7386,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.014914</v>
+        <v>0.015195</v>
       </c>
       <c r="F148" s="7">
-        <v>0.007130999999999999</v>
+        <v>0.0019270000000000001</v>
       </c>
       <c r="G148" s="7">
-        <v>0.26815</v>
+        <v>0.26193500000000003</v>
       </c>
       <c r="H148" s="7">
-        <v>0.185834</v>
+        <v>0.183051</v>
       </c>
       <c r="I148" s="7">
-        <v>0.500519</v>
+        <v>0.496583</v>
       </c>
       <c r="J148" s="7">
-        <v>3.414482</v>
+        <v>3.404121</v>
       </c>
       <c r="K148" s="7">
-        <v>9.463268000000001</v>
+        <v>9.438711</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7421,25 +7421,25 @@
         <v>3</v>
       </c>
       <c r="E149" s="7">
-        <v>0.026520000000000002</v>
+        <v>0.028086000000000003</v>
       </c>
       <c r="F149" s="7">
-        <v>0.08588699999999999</v>
+        <v>0.08698399999999999</v>
       </c>
       <c r="G149" s="7">
-        <v>0.355544</v>
+        <v>0.35316699999999995</v>
       </c>
       <c r="H149" s="7">
-        <v>0.291817</v>
+        <v>0.294723</v>
       </c>
       <c r="I149" s="7">
-        <v>0.62419</v>
+        <v>0.623858</v>
       </c>
       <c r="J149" s="7">
-        <v>3.151195</v>
+        <v>3.1605329999999996</v>
       </c>
       <c r="K149" s="7">
-        <v>9.54463</v>
+        <v>9.568349</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7456,25 +7456,25 @@
         <v>4</v>
       </c>
       <c r="E150" s="7">
-        <v>0.02879</v>
+        <v>0.029553</v>
       </c>
       <c r="F150" s="7">
-        <v>0.07581500000000001</v>
+        <v>0.075779</v>
       </c>
       <c r="G150" s="7">
-        <v>0.210064</v>
+        <v>0.21018799999999999</v>
       </c>
       <c r="H150" s="7">
-        <v>0.150876</v>
+        <v>0.152506</v>
       </c>
       <c r="I150" s="7">
-        <v>0.4625</v>
+        <v>0.46123800000000004</v>
       </c>
       <c r="J150" s="7">
-        <v>2.280572</v>
+        <v>2.28522</v>
       </c>
       <c r="K150" s="7">
-        <v>6.521617</v>
+        <v>6.532272000000001</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7491,25 +7491,25 @@
         <v>4</v>
       </c>
       <c r="E151" s="7">
-        <v>-0.8830079999999999</v>
+        <v>0.024548999999999998</v>
       </c>
       <c r="F151" s="7">
-        <v>-0.8840699999999999</v>
+        <v>0.014894000000000001</v>
       </c>
       <c r="G151" s="7">
-        <v>-0.859382</v>
+        <v>0.21942399999999998</v>
       </c>
       <c r="H151" s="7">
-        <v>-0.868668</v>
+        <v>0.14741300000000002</v>
       </c>
       <c r="I151" s="7">
-        <v>-0.8212090000000001</v>
+        <v>0.56392</v>
       </c>
       <c r="J151" s="7">
-        <v>-0.506678</v>
+        <v>3.310021</v>
       </c>
       <c r="K151" s="7">
-        <v>0.208477</v>
+        <v>9.558138</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7526,25 +7526,25 @@
         <v>4</v>
       </c>
       <c r="E152" s="7">
-        <v>0.040113</v>
+        <v>0.034023</v>
       </c>
       <c r="F152" s="7">
-        <v>0.077623</v>
+        <v>0.073597</v>
       </c>
       <c r="G152" s="7">
-        <v>0.204206</v>
+        <v>0.202027</v>
       </c>
       <c r="H152" s="7">
-        <v>0.16032800000000003</v>
+        <v>0.158339</v>
       </c>
       <c r="I152" s="7">
-        <v>0.40315100000000004</v>
+        <v>0.400394</v>
       </c>
       <c r="J152" s="7">
-        <v>1.623239</v>
+        <v>1.6187440000000002</v>
       </c>
       <c r="K152" s="7">
-        <v>4.302044</v>
+        <v>4.292959</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7561,25 +7561,25 @@
         <v>5</v>
       </c>
       <c r="E153" s="7">
-        <v>0.078861</v>
+        <v>0.062763</v>
       </c>
       <c r="F153" s="7">
-        <v>0.127135</v>
+        <v>0.115939</v>
       </c>
       <c r="G153" s="7">
-        <v>0.35525</v>
+        <v>0.345279</v>
       </c>
       <c r="H153" s="7">
-        <v>0.306604</v>
+        <v>0.296101</v>
       </c>
       <c r="I153" s="7">
-        <v>0.599489</v>
+        <v>0.5852040000000001</v>
       </c>
       <c r="J153" s="7">
-        <v>3.067812</v>
+        <v>3.0351139999999996</v>
       </c>
       <c r="K153" s="7">
-        <v>8.806662</v>
+        <v>8.727834</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7596,25 +7596,25 @@
         <v>7</v>
       </c>
       <c r="E154" s="7">
-        <v>0.069814</v>
+        <v>0.056393000000000006</v>
       </c>
       <c r="F154" s="7">
-        <v>0.122052</v>
+        <v>0.112125</v>
       </c>
       <c r="G154" s="7">
-        <v>0.32718400000000003</v>
+        <v>0.318612</v>
       </c>
       <c r="H154" s="7">
-        <v>0.273984</v>
+        <v>0.265335</v>
       </c>
       <c r="I154" s="7">
-        <v>0.581986</v>
+        <v>0.5693</v>
       </c>
       <c r="J154" s="7">
-        <v>2.929647</v>
+        <v>2.902969</v>
       </c>
       <c r="K154" s="7">
-        <v>7.55683</v>
+        <v>7.4987390000000005</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7631,25 +7631,25 @@
         <v>3</v>
       </c>
       <c r="E155" s="7">
-        <v>0.027604000000000004</v>
+        <v>0.026602999999999998</v>
       </c>
       <c r="F155" s="7">
-        <v>0.069226</v>
+        <v>0.06429</v>
       </c>
       <c r="G155" s="7">
-        <v>0.207162</v>
+        <v>0.205703</v>
       </c>
       <c r="H155" s="7">
-        <v>0.139046</v>
+        <v>0.139208</v>
       </c>
       <c r="I155" s="7">
-        <v>0.472887</v>
+        <v>0.470955</v>
       </c>
       <c r="J155" s="7">
-        <v>2.9699919999999995</v>
+        <v>2.970559</v>
       </c>
       <c r="K155" s="7">
-        <v>5.116113</v>
+        <v>5.116987</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7666,22 +7666,22 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.09620699999999999</v>
+        <v>0.09032400000000002</v>
       </c>
       <c r="F156" s="7">
-        <v>0.056554</v>
+        <v>0.054382</v>
       </c>
       <c r="G156" s="7">
-        <v>0.261996</v>
+        <v>0.263627</v>
       </c>
       <c r="H156" s="7">
-        <v>0.18905899999999998</v>
+        <v>0.188621</v>
       </c>
       <c r="I156" s="7">
-        <v>0.537497</v>
+        <v>0.5328309999999999</v>
       </c>
       <c r="J156" s="7">
-        <v>3.57347</v>
+        <v>3.5717849999999998</v>
       </c>
       <c r="K156" s="7"/>
     </row>
@@ -7699,16 +7699,16 @@
         <v>4</v>
       </c>
       <c r="E157" s="7">
-        <v>0</v>
+        <v>0.04101200000000001</v>
       </c>
       <c r="F157" s="7">
-        <v>0</v>
+        <v>0.072827</v>
       </c>
       <c r="G157" s="7">
-        <v>0</v>
+        <v>0.279866</v>
       </c>
       <c r="H157" s="7">
-        <v>0</v>
+        <v>0.21933</v>
       </c>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
@@ -7728,22 +7728,22 @@
         <v>6</v>
       </c>
       <c r="E158" s="7">
-        <v>0.046583</v>
+        <v>0.046485000000000005</v>
       </c>
       <c r="F158" s="7">
-        <v>0.050811999999999996</v>
+        <v>0.05008</v>
       </c>
       <c r="G158" s="7">
-        <v>0.27119</v>
+        <v>0.267305</v>
       </c>
       <c r="H158" s="7">
-        <v>0.22061599999999998</v>
+        <v>0.214527</v>
       </c>
       <c r="I158" s="7">
-        <v>0.44292299999999996</v>
+        <v>0.433147</v>
       </c>
       <c r="J158" s="7">
-        <v>1.808639</v>
+        <v>1.79463</v>
       </c>
       <c r="K158" s="7"/>
     </row>
@@ -7761,25 +7761,25 @@
         <v>3</v>
       </c>
       <c r="E159" s="7">
-        <v>0.047264</v>
+        <v>0.041609999999999994</v>
       </c>
       <c r="F159" s="7">
-        <v>0.093193</v>
+        <v>0.08875899999999999</v>
       </c>
       <c r="G159" s="7">
-        <v>0.270343</v>
+        <v>0.268237</v>
       </c>
       <c r="H159" s="7">
-        <v>0.19668</v>
+        <v>0.19463</v>
       </c>
       <c r="I159" s="7">
-        <v>0.543343</v>
+        <v>0.539745</v>
       </c>
       <c r="J159" s="7">
-        <v>2.595087</v>
+        <v>2.588929</v>
       </c>
       <c r="K159" s="7">
-        <v>6.532895</v>
+        <v>6.519991999999999</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7796,25 +7796,25 @@
         <v>3</v>
       </c>
       <c r="E160" s="7">
-        <v>0.051483999999999995</v>
+        <v>0.046332000000000005</v>
       </c>
       <c r="F160" s="7">
-        <v>0.097981</v>
+        <v>0.093692</v>
       </c>
       <c r="G160" s="7">
-        <v>0.26643100000000003</v>
+        <v>0.264483</v>
       </c>
       <c r="H160" s="7">
-        <v>0.19934100000000002</v>
+        <v>0.197182</v>
       </c>
       <c r="I160" s="7">
-        <v>0.504888</v>
+        <v>0.501058</v>
       </c>
       <c r="J160" s="7">
-        <v>2.3904009999999998</v>
+        <v>2.384299</v>
       </c>
       <c r="K160" s="7">
-        <v>6.05914</v>
+        <v>6.0464340000000005</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7831,25 +7831,25 @@
         <v>3</v>
       </c>
       <c r="E161" s="7">
-        <v>0.04367</v>
+        <v>0.037202</v>
       </c>
       <c r="F161" s="7">
-        <v>0.079376</v>
+        <v>0.077376</v>
       </c>
       <c r="G161" s="7">
-        <v>0.234701</v>
+        <v>0.232366</v>
       </c>
       <c r="H161" s="7">
-        <v>0.162311</v>
+        <v>0.16064299999999998</v>
       </c>
       <c r="I161" s="7">
-        <v>0.440512</v>
+        <v>0.43811900000000004</v>
       </c>
       <c r="J161" s="7">
-        <v>1.961265</v>
+        <v>1.957016</v>
       </c>
       <c r="K161" s="7">
-        <v>5.122421</v>
+        <v>5.1136360000000005</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7866,22 +7866,22 @@
         <v>5</v>
       </c>
       <c r="E162" s="7">
-        <v>0.16416599999999998</v>
+        <v>0.155687</v>
       </c>
       <c r="F162" s="7">
-        <v>0.247238</v>
+        <v>0.246863</v>
       </c>
       <c r="G162" s="7">
-        <v>0.380162</v>
+        <v>0.39237900000000003</v>
       </c>
       <c r="H162" s="7">
-        <v>0.359578</v>
+        <v>0.353576</v>
       </c>
       <c r="I162" s="7">
-        <v>0.7558199999999999</v>
+        <v>0.7397589999999999</v>
       </c>
       <c r="J162" s="7">
-        <v>4.367052</v>
+        <v>4.3433589999999995</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7899,25 +7899,25 @@
         <v>4</v>
       </c>
       <c r="E163" s="7">
-        <v>0.019523</v>
+        <v>0.020505</v>
       </c>
       <c r="F163" s="7">
-        <v>0.021174</v>
+        <v>0.015341</v>
       </c>
       <c r="G163" s="7">
-        <v>0.214759</v>
+        <v>0.211817</v>
       </c>
       <c r="H163" s="7">
-        <v>0.108725</v>
+        <v>0.10627700000000001</v>
       </c>
       <c r="I163" s="7">
-        <v>0.420169</v>
+        <v>0.41647399999999996</v>
       </c>
       <c r="J163" s="7">
-        <v>2.0380789999999998</v>
+        <v>2.031371</v>
       </c>
       <c r="K163" s="7">
-        <v>5.651938</v>
+        <v>5.63725</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7934,22 +7934,22 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.031428</v>
+        <v>0.030462</v>
       </c>
       <c r="F164" s="7">
-        <v>0.082524</v>
+        <v>0.079917</v>
       </c>
       <c r="G164" s="7">
-        <v>0.222938</v>
+        <v>0.22303599999999998</v>
       </c>
       <c r="H164" s="7">
-        <v>0.16648700000000002</v>
+        <v>0.16761299999999998</v>
       </c>
       <c r="I164" s="7">
-        <v>0.532464</v>
+        <v>0.528026</v>
       </c>
       <c r="J164" s="7">
-        <v>3.289482</v>
+        <v>3.293623</v>
       </c>
       <c r="K164" s="7"/>
     </row>
@@ -7967,22 +7967,22 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.014787</v>
+        <v>0.016871</v>
       </c>
       <c r="F165" s="7">
-        <v>-0.002606</v>
+        <v>0.006444999999999999</v>
       </c>
       <c r="G165" s="7">
-        <v>0.125836</v>
+        <v>0.113644</v>
       </c>
       <c r="H165" s="7">
-        <v>0.084558</v>
+        <v>0.081577</v>
       </c>
       <c r="I165" s="7">
-        <v>0.40989800000000004</v>
+        <v>0.404721</v>
       </c>
       <c r="J165" s="7">
-        <v>2.6482170000000003</v>
+        <v>2.638193</v>
       </c>
       <c r="K165" s="7"/>
     </row>
@@ -8000,25 +8000,25 @@
         <v>5</v>
       </c>
       <c r="E166" s="7">
-        <v>0.07817199999999999</v>
+        <v>0.065946</v>
       </c>
       <c r="F166" s="7">
-        <v>0.129811</v>
+        <v>0.12734199999999998</v>
       </c>
       <c r="G166" s="7">
-        <v>0.39309499999999997</v>
+        <v>0.388183</v>
       </c>
       <c r="H166" s="7">
-        <v>0.31204699999999996</v>
+        <v>0.30787600000000004</v>
       </c>
       <c r="I166" s="7">
-        <v>0.663535</v>
+        <v>0.6603279999999999</v>
       </c>
       <c r="J166" s="7">
-        <v>2.637522</v>
+        <v>2.625957</v>
       </c>
       <c r="K166" s="7">
-        <v>8.972858</v>
+        <v>8.941151</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8035,25 +8035,25 @@
         <v>6</v>
       </c>
       <c r="E167" s="7">
-        <v>0.045678</v>
+        <v>0.039852</v>
       </c>
       <c r="F167" s="7">
-        <v>0.043510999999999994</v>
+        <v>0.039771</v>
       </c>
       <c r="G167" s="7">
-        <v>0.410624</v>
+        <v>0.409724</v>
       </c>
       <c r="H167" s="7">
-        <v>0.3191</v>
+        <v>0.314548</v>
       </c>
       <c r="I167" s="7">
-        <v>0.605798</v>
+        <v>0.607727</v>
       </c>
       <c r="J167" s="7">
-        <v>2.028403</v>
+        <v>2.017953</v>
       </c>
       <c r="K167" s="7">
-        <v>3.7188369999999997</v>
+        <v>3.702553</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8070,25 +8070,25 @@
         <v>6</v>
       </c>
       <c r="E168" s="7">
-        <v>0.032146</v>
+        <v>0.030158</v>
       </c>
       <c r="F168" s="7">
-        <v>0.008911</v>
+        <v>0.001613</v>
       </c>
       <c r="G168" s="7">
-        <v>0.362622</v>
+        <v>0.355403</v>
       </c>
       <c r="H168" s="7">
-        <v>0.264211</v>
+        <v>0.257702</v>
       </c>
       <c r="I168" s="7">
-        <v>0.450514</v>
+        <v>0.445681</v>
       </c>
       <c r="J168" s="7">
-        <v>2.764961</v>
+        <v>2.745577</v>
       </c>
       <c r="K168" s="7">
-        <v>15.699813999999998</v>
+        <v>15.613833</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8105,25 +8105,25 @@
         <v>3</v>
       </c>
       <c r="E169" s="7">
-        <v>0.012239</v>
+        <v>0.015028999999999999</v>
       </c>
       <c r="F169" s="7">
-        <v>0.013229</v>
+        <v>0.007327</v>
       </c>
       <c r="G169" s="7">
-        <v>0.147729</v>
+        <v>0.145778</v>
       </c>
       <c r="H169" s="7">
-        <v>0.054872</v>
+        <v>0.052602</v>
       </c>
       <c r="I169" s="7">
-        <v>0.391772</v>
+        <v>0.387064</v>
       </c>
       <c r="J169" s="7">
-        <v>1.90905</v>
+        <v>1.9027889999999998</v>
       </c>
       <c r="K169" s="7">
-        <v>3.9661579999999996</v>
+        <v>3.955471</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8140,25 +8140,25 @@
         <v>3</v>
       </c>
       <c r="E170" s="7">
-        <v>0.04796</v>
+        <v>0.035535000000000004</v>
       </c>
       <c r="F170" s="7">
-        <v>0.09298999999999999</v>
+        <v>0.089344</v>
       </c>
       <c r="G170" s="7">
-        <v>0.272007</v>
+        <v>0.270225</v>
       </c>
       <c r="H170" s="7">
-        <v>0.18941</v>
+        <v>0.187502</v>
       </c>
       <c r="I170" s="7">
-        <v>0.467392</v>
+        <v>0.465135</v>
       </c>
       <c r="J170" s="7">
-        <v>2.023643</v>
+        <v>2.018794</v>
       </c>
       <c r="K170" s="7">
-        <v>5.510168</v>
+        <v>5.49973</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -8175,25 +8175,25 @@
         <v>5</v>
       </c>
       <c r="E171" s="7">
-        <v>0.025219000000000002</v>
+        <v>0.02331</v>
       </c>
       <c r="F171" s="7">
-        <v>0.062453</v>
+        <v>0.061898</v>
       </c>
       <c r="G171" s="7">
-        <v>0.126855</v>
+        <v>0.126358</v>
       </c>
       <c r="H171" s="7">
-        <v>0.09280300000000001</v>
+        <v>0.09315699999999999</v>
       </c>
       <c r="I171" s="7">
-        <v>0.297546</v>
+        <v>0.29675999999999997</v>
       </c>
       <c r="J171" s="7">
-        <v>1.967778</v>
+        <v>1.96874</v>
       </c>
       <c r="K171" s="7">
-        <v>5.4814430000000005</v>
+        <v>5.483545</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -8210,22 +8210,22 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.0037419999999999997</v>
+        <v>0.002852</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.06479</v>
+        <v>-0.055614</v>
       </c>
       <c r="G172" s="7">
-        <v>0.179334</v>
+        <v>0.149961</v>
       </c>
       <c r="H172" s="7">
-        <v>0.11463100000000001</v>
+        <v>0.11104599999999999</v>
       </c>
       <c r="I172" s="7">
-        <v>0.6541459999999999</v>
+        <v>0.6445059999999999</v>
       </c>
       <c r="J172" s="7">
-        <v>4.707169</v>
+        <v>4.688816</v>
       </c>
       <c r="K172" s="7"/>
     </row>
@@ -8243,22 +8243,22 @@
         <v>6</v>
       </c>
       <c r="E173" s="7">
-        <v>0.036828</v>
+        <v>0.032757</v>
       </c>
       <c r="F173" s="7">
-        <v>0.033676</v>
+        <v>0.032358</v>
       </c>
       <c r="G173" s="7">
-        <v>0.289399</v>
+        <v>0.289039</v>
       </c>
       <c r="H173" s="7">
-        <v>0.228818</v>
+        <v>0.22453399999999998</v>
       </c>
       <c r="I173" s="7">
-        <v>0.447776</v>
+        <v>0.44278300000000004</v>
       </c>
       <c r="J173" s="7">
-        <v>2.411468</v>
+        <v>2.399573</v>
       </c>
       <c r="K173" s="7"/>
     </row>
@@ -8276,16 +8276,16 @@
         <v>7</v>
       </c>
       <c r="E174" s="7">
-        <v>0.115255</v>
+        <v>0.155122</v>
       </c>
       <c r="F174" s="7">
-        <v>0.036094</v>
+        <v>0.110859</v>
       </c>
       <c r="G174" s="7">
-        <v>0.655033</v>
+        <v>0.658762</v>
       </c>
       <c r="H174" s="7">
-        <v>0.174707</v>
+        <v>0.206186</v>
       </c>
       <c r="I174" s="7"/>
       <c r="J174" s="7"/>
@@ -8305,25 +8305,25 @@
         <v>6</v>
       </c>
       <c r="E175" s="7">
-        <v>-0.007699</v>
+        <v>-0.004225</v>
       </c>
       <c r="F175" s="7">
-        <v>-0.07591</v>
+        <v>-0.064605</v>
       </c>
       <c r="G175" s="7">
-        <v>0.156049</v>
+        <v>0.13198600000000002</v>
       </c>
       <c r="H175" s="7">
-        <v>0.073944</v>
+        <v>0.073509</v>
       </c>
       <c r="I175" s="7">
-        <v>0.603329</v>
+        <v>0.59553</v>
       </c>
       <c r="J175" s="7">
-        <v>4.075471</v>
+        <v>4.073416</v>
       </c>
       <c r="K175" s="7">
-        <v>13.177304</v>
+        <v>13.171563</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8340,25 +8340,25 @@
         <v>4</v>
       </c>
       <c r="E176" s="7">
-        <v>0.021465</v>
+        <v>0.023254</v>
       </c>
       <c r="F176" s="7">
-        <v>0.020999</v>
+        <v>0.014068</v>
       </c>
       <c r="G176" s="7">
-        <v>0.233187</v>
+        <v>0.230275</v>
       </c>
       <c r="H176" s="7">
-        <v>0.122458</v>
+        <v>0.11931699999999999</v>
       </c>
       <c r="I176" s="7">
-        <v>0.447744</v>
+        <v>0.442729</v>
       </c>
       <c r="J176" s="7">
-        <v>2.073493</v>
+        <v>2.0648929999999996</v>
       </c>
       <c r="K176" s="7">
-        <v>5.404484999999999</v>
+        <v>5.386564</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8375,25 +8375,25 @@
         <v>5</v>
       </c>
       <c r="E177" s="7">
-        <v>0.033105</v>
+        <v>0.032618</v>
       </c>
       <c r="F177" s="7">
-        <v>0.039058999999999996</v>
+        <v>0.031661</v>
       </c>
       <c r="G177" s="7">
-        <v>0.33462400000000003</v>
+        <v>0.33193399999999995</v>
       </c>
       <c r="H177" s="7">
-        <v>0.238578</v>
+        <v>0.234728</v>
       </c>
       <c r="I177" s="7">
-        <v>0.446537</v>
+        <v>0.443109</v>
       </c>
       <c r="J177" s="7">
-        <v>2.6662310000000002</v>
+        <v>2.654835</v>
       </c>
       <c r="K177" s="7">
-        <v>10.503025000000001</v>
+        <v>10.467268999999998</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8410,25 +8410,25 @@
         <v>5</v>
       </c>
       <c r="E178" s="7">
-        <v>0.017602</v>
+        <v>0.015288</v>
       </c>
       <c r="F178" s="7">
-        <v>0.035768</v>
+        <v>0.034892</v>
       </c>
       <c r="G178" s="7">
-        <v>0.103742</v>
+        <v>0.10097400000000001</v>
       </c>
       <c r="H178" s="7">
-        <v>0.063491</v>
+        <v>0.062762</v>
       </c>
       <c r="I178" s="7">
-        <v>0.303978</v>
+        <v>0.302756</v>
       </c>
       <c r="J178" s="7">
-        <v>2.049383</v>
+        <v>2.047294</v>
       </c>
       <c r="K178" s="7">
-        <v>6.23476</v>
+        <v>6.229804000000001</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8445,25 +8445,25 @@
         <v>6</v>
       </c>
       <c r="E179" s="7">
-        <v>0.061238</v>
+        <v>0.062067</v>
       </c>
       <c r="F179" s="7">
-        <v>0.068566</v>
+        <v>0.074415</v>
       </c>
       <c r="G179" s="7">
-        <v>0.293812</v>
+        <v>0.29608799999999996</v>
       </c>
       <c r="H179" s="7">
-        <v>0.227926</v>
+        <v>0.227563</v>
       </c>
       <c r="I179" s="7">
-        <v>0.562852</v>
+        <v>0.559346</v>
       </c>
       <c r="J179" s="7">
-        <v>2.89017</v>
+        <v>2.8890179999999996</v>
       </c>
       <c r="K179" s="7">
-        <v>12.461357</v>
+        <v>12.457372</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8480,25 +8480,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.039051</v>
+        <v>0.038181</v>
       </c>
       <c r="F180" s="7">
-        <v>0.049808000000000005</v>
+        <v>0.042621</v>
       </c>
       <c r="G180" s="7">
-        <v>0.407273</v>
+        <v>0.400821</v>
       </c>
       <c r="H180" s="7">
-        <v>0.287418</v>
+        <v>0.282728</v>
       </c>
       <c r="I180" s="7">
-        <v>0.555167</v>
+        <v>0.550424</v>
       </c>
       <c r="J180" s="7">
-        <v>3.132844</v>
+        <v>3.11779</v>
       </c>
       <c r="K180" s="7">
-        <v>17.325542</v>
+        <v>17.258789999999998</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8515,25 +8515,25 @@
         <v>6</v>
       </c>
       <c r="E181" s="7">
-        <v>0.035526</v>
+        <v>0.035145</v>
       </c>
       <c r="F181" s="7">
-        <v>0.04474</v>
+        <v>0.040295</v>
       </c>
       <c r="G181" s="7">
-        <v>0.365475</v>
+        <v>0.361976</v>
       </c>
       <c r="H181" s="7">
-        <v>0.23845300000000003</v>
+        <v>0.236078</v>
       </c>
       <c r="I181" s="7">
-        <v>0.51681</v>
+        <v>0.516782</v>
       </c>
       <c r="J181" s="7">
-        <v>3.0437169999999996</v>
+        <v>3.035962</v>
       </c>
       <c r="K181" s="7">
-        <v>12.891545</v>
+        <v>12.864903</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8550,25 +8550,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.036815</v>
+        <v>0.035789</v>
       </c>
       <c r="F182" s="7">
-        <v>0.049958999999999996</v>
+        <v>0.043825</v>
       </c>
       <c r="G182" s="7">
-        <v>0.323585</v>
+        <v>0.317582</v>
       </c>
       <c r="H182" s="7">
-        <v>0.208067</v>
+        <v>0.204378</v>
       </c>
       <c r="I182" s="7">
-        <v>0.540702</v>
+        <v>0.535752</v>
       </c>
       <c r="J182" s="7">
-        <v>3.3669619999999996</v>
+        <v>3.353629</v>
       </c>
       <c r="K182" s="7">
-        <v>11.336166</v>
+        <v>11.298502000000001</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8585,25 +8585,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.093004</v>
+        <v>0.092822</v>
       </c>
       <c r="F183" s="7">
-        <v>0.09373</v>
+        <v>0.109872</v>
       </c>
       <c r="G183" s="7">
-        <v>0.19277999999999998</v>
+        <v>0.195738</v>
       </c>
       <c r="H183" s="7">
-        <v>0.160887</v>
+        <v>0.16181</v>
       </c>
       <c r="I183" s="7">
-        <v>0.558578</v>
+        <v>0.546846</v>
       </c>
       <c r="J183" s="7">
-        <v>3.3351699999999997</v>
+        <v>3.338619</v>
       </c>
       <c r="K183" s="7">
-        <v>8.776950000000001</v>
+        <v>8.784729</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8620,25 +8620,25 @@
         <v>2</v>
       </c>
       <c r="E184" s="7">
-        <v>0.027995000000000003</v>
+        <v>0.027751</v>
       </c>
       <c r="F184" s="7">
-        <v>0.075333</v>
+        <v>0.07106</v>
       </c>
       <c r="G184" s="7">
-        <v>0.21317</v>
+        <v>0.210984</v>
       </c>
       <c r="H184" s="7">
-        <v>0.143621</v>
+        <v>0.142512</v>
       </c>
       <c r="I184" s="7">
-        <v>0.49003300000000005</v>
+        <v>0.48735999999999996</v>
       </c>
       <c r="J184" s="7">
-        <v>3.340026</v>
+        <v>3.33582</v>
       </c>
       <c r="K184" s="7">
-        <v>6.352485000000001</v>
+        <v>6.3453610000000005</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8655,25 +8655,25 @@
         <v>4</v>
       </c>
       <c r="E185" s="7">
-        <v>0.031875</v>
+        <v>0.032509</v>
       </c>
       <c r="F185" s="7">
-        <v>0.011056</v>
+        <v>0.009760999999999999</v>
       </c>
       <c r="G185" s="7">
-        <v>0.171727</v>
+        <v>0.1704</v>
       </c>
       <c r="H185" s="7">
-        <v>0.173842</v>
+        <v>0.17210999999999999</v>
       </c>
       <c r="I185" s="7">
-        <v>0.34292700000000004</v>
+        <v>0.340193</v>
       </c>
       <c r="J185" s="7">
-        <v>2.3707149999999997</v>
+        <v>2.365739</v>
       </c>
       <c r="K185" s="7">
-        <v>3.9434570000000004</v>
+        <v>3.9361599999999997</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8690,25 +8690,25 @@
         <v>6</v>
       </c>
       <c r="E186" s="7">
-        <v>0.10889900000000001</v>
+        <v>0.098685</v>
       </c>
       <c r="F186" s="7">
-        <v>0.172742</v>
+        <v>0.174089</v>
       </c>
       <c r="G186" s="7">
-        <v>0.515495</v>
+        <v>0.5231439999999999</v>
       </c>
       <c r="H186" s="7">
-        <v>0.41460299999999994</v>
+        <v>0.415122</v>
       </c>
       <c r="I186" s="7">
-        <v>0.732419</v>
+        <v>0.73238</v>
       </c>
       <c r="J186" s="7">
-        <v>3.457245</v>
+        <v>3.458879</v>
       </c>
       <c r="K186" s="7">
-        <v>13.676544</v>
+        <v>13.681927</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8725,25 +8725,25 @@
         <v>3</v>
       </c>
       <c r="E187" s="7">
-        <v>0.030779</v>
+        <v>0.030816</v>
       </c>
       <c r="F187" s="7">
-        <v>0.08914799999999999</v>
+        <v>0.087103</v>
       </c>
       <c r="G187" s="7">
-        <v>0.193038</v>
+        <v>0.192813</v>
       </c>
       <c r="H187" s="7">
-        <v>0.13409100000000002</v>
+        <v>0.135112</v>
       </c>
       <c r="I187" s="7">
-        <v>0.45404200000000006</v>
+        <v>0.453705</v>
       </c>
       <c r="J187" s="7">
-        <v>1.773243</v>
+        <v>1.7757409999999998</v>
       </c>
       <c r="K187" s="7">
-        <v>3.8451190000000004</v>
+        <v>3.849484</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,25 +8760,25 @@
         <v>5</v>
       </c>
       <c r="E188" s="7">
-        <v>0.09307800000000001</v>
+        <v>0.086035</v>
       </c>
       <c r="F188" s="7">
-        <v>0.13978400000000002</v>
+        <v>0.140724</v>
       </c>
       <c r="G188" s="7">
-        <v>0.39109499999999997</v>
+        <v>0.396357</v>
       </c>
       <c r="H188" s="7">
-        <v>0.313575</v>
+        <v>0.31495999999999996</v>
       </c>
       <c r="I188" s="7">
-        <v>0.6554559999999999</v>
+        <v>0.6574890000000001</v>
       </c>
       <c r="J188" s="7">
-        <v>3.1422809999999997</v>
+        <v>3.146649</v>
       </c>
       <c r="K188" s="7">
-        <v>11.644495999999998</v>
+        <v>11.657828</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8795,25 +8795,25 @@
         <v>2</v>
       </c>
       <c r="E189" s="7">
-        <v>0.030868000000000003</v>
+        <v>0.030945</v>
       </c>
       <c r="F189" s="7">
-        <v>0.08931599999999999</v>
+        <v>0.08727299999999999</v>
       </c>
       <c r="G189" s="7">
-        <v>0.190549</v>
+        <v>0.190423</v>
       </c>
       <c r="H189" s="7">
-        <v>0.133704</v>
+        <v>0.134746</v>
       </c>
       <c r="I189" s="7">
-        <v>0.44903</v>
+        <v>0.448704</v>
       </c>
       <c r="J189" s="7">
-        <v>1.8602809999999999</v>
+        <v>1.862909</v>
       </c>
       <c r="K189" s="7">
-        <v>3.3491699999999995</v>
+        <v>3.353165</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8830,25 +8830,25 @@
         <v>2</v>
       </c>
       <c r="E190" s="7">
-        <v>0.030518999999999998</v>
+        <v>0.024744000000000002</v>
       </c>
       <c r="F190" s="7">
-        <v>0.065786</v>
+        <v>0.064378</v>
       </c>
       <c r="G190" s="7">
-        <v>0.155254</v>
+        <v>0.15513</v>
       </c>
       <c r="H190" s="7">
-        <v>0.108653</v>
+        <v>0.109557</v>
       </c>
       <c r="I190" s="7">
-        <v>0.37975099999999995</v>
+        <v>0.377914</v>
       </c>
       <c r="J190" s="7">
-        <v>1.999019</v>
+        <v>2.0014629999999998</v>
       </c>
       <c r="K190" s="7">
-        <v>3.329893</v>
+        <v>3.333421</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8865,19 +8865,19 @@
         <v>6</v>
       </c>
       <c r="E191" s="7">
-        <v>0.10678900000000001</v>
+        <v>0.154658</v>
       </c>
       <c r="F191" s="7">
-        <v>0.024428000000000002</v>
+        <v>0.09974</v>
       </c>
       <c r="G191" s="7">
-        <v>0.610657</v>
+        <v>0.615398</v>
       </c>
       <c r="H191" s="7">
-        <v>0.15143399999999999</v>
+        <v>0.181518</v>
       </c>
       <c r="I191" s="7">
-        <v>1.699682</v>
+        <v>1.7559790000000002</v>
       </c>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
@@ -8896,25 +8896,25 @@
         <v>6</v>
       </c>
       <c r="E192" s="7">
-        <v>-0.000421</v>
+        <v>0.0018859999999999999</v>
       </c>
       <c r="F192" s="7">
-        <v>-0.064904</v>
+        <v>-0.054150000000000004</v>
       </c>
       <c r="G192" s="7">
-        <v>0.166846</v>
+        <v>0.143002</v>
       </c>
       <c r="H192" s="7">
-        <v>0.088857</v>
+        <v>0.08881299999999999</v>
       </c>
       <c r="I192" s="7">
-        <v>0.626717</v>
+        <v>0.62197</v>
       </c>
       <c r="J192" s="7">
-        <v>3.9794009999999997</v>
+        <v>3.9791969999999997</v>
       </c>
       <c r="K192" s="7">
-        <v>12.959602</v>
+        <v>12.959031</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8931,25 +8931,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>-0.012662</v>
+        <v>-0.007904</v>
       </c>
       <c r="F193" s="7">
-        <v>-0.08192500000000001</v>
+        <v>-0.070871</v>
       </c>
       <c r="G193" s="7">
-        <v>0.128872</v>
+        <v>0.10359199999999999</v>
       </c>
       <c r="H193" s="7">
-        <v>0.055686</v>
+        <v>0.054405</v>
       </c>
       <c r="I193" s="7">
-        <v>0.590443</v>
+        <v>0.580344</v>
       </c>
       <c r="J193" s="7">
-        <v>3.872587</v>
+        <v>3.866672</v>
       </c>
       <c r="K193" s="7">
-        <v>12.653413</v>
+        <v>12.63684</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8966,25 +8966,25 @@
         <v>4</v>
       </c>
       <c r="E194" s="7">
-        <v>0.019584</v>
+        <v>0.018506</v>
       </c>
       <c r="F194" s="7">
-        <v>0.036534</v>
+        <v>0.029459</v>
       </c>
       <c r="G194" s="7">
-        <v>0.252979</v>
+        <v>0.250405</v>
       </c>
       <c r="H194" s="7">
-        <v>0.14771900000000002</v>
+        <v>0.14386200000000002</v>
       </c>
       <c r="I194" s="7">
-        <v>0.47499800000000003</v>
+        <v>0.471976</v>
       </c>
       <c r="J194" s="7">
-        <v>1.853034</v>
+        <v>1.843448</v>
       </c>
       <c r="K194" s="7">
-        <v>5.060494</v>
+        <v>5.040131</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -9001,25 +9001,25 @@
         <v>4</v>
       </c>
       <c r="E195" s="7">
-        <v>0.020630000000000003</v>
+        <v>0.022527</v>
       </c>
       <c r="F195" s="7">
-        <v>0.036709</v>
+        <v>0.031757</v>
       </c>
       <c r="G195" s="7">
-        <v>0.20874600000000001</v>
+        <v>0.20738800000000002</v>
       </c>
       <c r="H195" s="7">
-        <v>0.116278</v>
+        <v>0.11412499999999999</v>
       </c>
       <c r="I195" s="7">
-        <v>0.435875</v>
+        <v>0.433654</v>
       </c>
       <c r="J195" s="7">
-        <v>2.261059</v>
+        <v>2.254768</v>
       </c>
       <c r="K195" s="7">
-        <v>5.541378999999999</v>
+        <v>5.52876</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9036,25 +9036,25 @@
         <v>6</v>
       </c>
       <c r="E196" s="7">
-        <v>0.016737</v>
+        <v>0.014480999999999999</v>
       </c>
       <c r="F196" s="7">
-        <v>0.031027</v>
+        <v>0.028769</v>
       </c>
       <c r="G196" s="7">
-        <v>0.103768</v>
+        <v>0.103345</v>
       </c>
       <c r="H196" s="7">
-        <v>0.059457</v>
+        <v>0.058682</v>
       </c>
       <c r="I196" s="7">
-        <v>0.315774</v>
+        <v>0.312022</v>
       </c>
       <c r="J196" s="7">
-        <v>2.157538</v>
+        <v>2.155229</v>
       </c>
       <c r="K196" s="7">
-        <v>6.450005999999999</v>
+        <v>6.444557</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9071,25 +9071,25 @@
         <v>3</v>
       </c>
       <c r="E197" s="7">
-        <v>0.039965</v>
+        <v>0.032158</v>
       </c>
       <c r="F197" s="7">
-        <v>0.104057</v>
+        <v>0.09568199999999999</v>
       </c>
       <c r="G197" s="7">
-        <v>0.281491</v>
+        <v>0.27645</v>
       </c>
       <c r="H197" s="7">
-        <v>0.21804600000000002</v>
+        <v>0.21090599999999998</v>
       </c>
       <c r="I197" s="7">
-        <v>0.47886</v>
+        <v>0.470553</v>
       </c>
       <c r="J197" s="7">
-        <v>1.645094</v>
+        <v>1.629589</v>
       </c>
       <c r="K197" s="7">
-        <v>3.7844779999999996</v>
+        <v>3.7564319999999998</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9106,25 +9106,25 @@
         <v>3</v>
       </c>
       <c r="E198" s="7">
-        <v>0.041665</v>
+        <v>0.035599</v>
       </c>
       <c r="F198" s="7">
-        <v>0.080826</v>
+        <v>0.077491</v>
       </c>
       <c r="G198" s="7">
-        <v>0.25176</v>
+        <v>0.250201</v>
       </c>
       <c r="H198" s="7">
-        <v>0.159323</v>
+        <v>0.157938</v>
       </c>
       <c r="I198" s="7">
-        <v>0.45406100000000005</v>
+        <v>0.45142000000000004</v>
       </c>
       <c r="J198" s="7">
-        <v>1.882922</v>
+        <v>1.87948</v>
       </c>
       <c r="K198" s="7">
-        <v>4.671722</v>
+        <v>4.664949</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9141,25 +9141,25 @@
         <v>4</v>
       </c>
       <c r="E199" s="7">
-        <v>0.023413</v>
+        <v>0.02464</v>
       </c>
       <c r="F199" s="7">
-        <v>0.038378999999999996</v>
+        <v>0.033687999999999996</v>
       </c>
       <c r="G199" s="7">
-        <v>0.23459700000000003</v>
+        <v>0.233451</v>
       </c>
       <c r="H199" s="7">
-        <v>0.142394</v>
+        <v>0.139825</v>
       </c>
       <c r="I199" s="7">
-        <v>0.464575</v>
+        <v>0.462095</v>
       </c>
       <c r="J199" s="7">
-        <v>2.150809</v>
+        <v>2.143723</v>
       </c>
       <c r="K199" s="7">
-        <v>5.084269</v>
+        <v>5.0705860000000005</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9176,25 +9176,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.014431000000000001</v>
+        <v>0.024207</v>
       </c>
       <c r="F200" s="7">
-        <v>-0.011895</v>
+        <v>-0.013635</v>
       </c>
       <c r="G200" s="7">
-        <v>0.289836</v>
+        <v>0.291616</v>
       </c>
       <c r="H200" s="7">
-        <v>0.236489</v>
+        <v>0.237257</v>
       </c>
       <c r="I200" s="7">
-        <v>0.417333</v>
+        <v>0.42013300000000003</v>
       </c>
       <c r="J200" s="7">
-        <v>3.645329</v>
+        <v>3.648215</v>
       </c>
       <c r="K200" s="7">
-        <v>20.932371</v>
+        <v>20.945997000000002</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9211,16 +9211,16 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.06692300000000001</v>
+        <v>0.061413</v>
       </c>
       <c r="F201" s="7">
-        <v>0.057876000000000004</v>
+        <v>0.052344999999999996</v>
       </c>
       <c r="G201" s="7">
-        <v>0.294896</v>
+        <v>0.292692</v>
       </c>
       <c r="H201" s="7">
-        <v>0.233246</v>
+        <v>0.22880199999999998</v>
       </c>
       <c r="I201" s="7"/>
       <c r="J201" s="7"/>
@@ -9240,25 +9240,25 @@
         <v>6</v>
       </c>
       <c r="E202" s="7">
-        <v>0.057077</v>
+        <v>0.043681</v>
       </c>
       <c r="F202" s="7">
-        <v>0.006422</v>
+        <v>-0.008912</v>
       </c>
       <c r="G202" s="7">
-        <v>0.257972</v>
+        <v>0.243388</v>
       </c>
       <c r="H202" s="7">
-        <v>0.135518</v>
+        <v>0.121172</v>
       </c>
       <c r="I202" s="7">
-        <v>0.381875</v>
+        <v>0.35830399999999996</v>
       </c>
       <c r="J202" s="7">
-        <v>2.312464</v>
+        <v>2.270615</v>
       </c>
       <c r="K202" s="7">
-        <v>10.145323</v>
+        <v>10.004513</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9275,25 +9275,25 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.080456</v>
+        <v>0.065497</v>
       </c>
       <c r="F203" s="7">
-        <v>0.097719</v>
+        <v>0.08612299999999999</v>
       </c>
       <c r="G203" s="7">
-        <v>0.35608199999999995</v>
+        <v>0.351566</v>
       </c>
       <c r="H203" s="7">
-        <v>0.24502600000000002</v>
+        <v>0.23292300000000002</v>
       </c>
       <c r="I203" s="7">
-        <v>0.49697</v>
+        <v>0.47751699999999997</v>
       </c>
       <c r="J203" s="7">
-        <v>2.579357</v>
+        <v>2.544562</v>
       </c>
       <c r="K203" s="7">
-        <v>9.443709</v>
+        <v>9.342186</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9310,25 +9310,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.013931</v>
+        <v>0.016440999999999997</v>
       </c>
       <c r="F204" s="7">
-        <v>-0.002076</v>
+        <v>0.014113</v>
       </c>
       <c r="G204" s="7">
-        <v>0.18274</v>
+        <v>0.18395299999999998</v>
       </c>
       <c r="H204" s="7">
-        <v>0.10213900000000001</v>
+        <v>0.103642</v>
       </c>
       <c r="I204" s="7">
-        <v>0.6036090000000001</v>
+        <v>0.59328</v>
       </c>
       <c r="J204" s="7">
-        <v>2.9005470000000004</v>
+        <v>2.905868</v>
       </c>
       <c r="K204" s="7">
-        <v>6.45064</v>
+        <v>6.460804</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9345,25 +9345,25 @@
         <v>3</v>
       </c>
       <c r="E205" s="7">
-        <v>0.008546</v>
+        <v>0.012699</v>
       </c>
       <c r="F205" s="7">
-        <v>0.026621000000000002</v>
+        <v>0.020268</v>
       </c>
       <c r="G205" s="7">
-        <v>0.163469</v>
+        <v>0.163125</v>
       </c>
       <c r="H205" s="7">
-        <v>0.06142</v>
+        <v>0.059584</v>
       </c>
       <c r="I205" s="7">
-        <v>0.392065</v>
+        <v>0.387833</v>
       </c>
       <c r="J205" s="7">
-        <v>1.6607370000000001</v>
+        <v>1.656135</v>
       </c>
       <c r="K205" s="7">
-        <v>3.678761</v>
+        <v>3.670668</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9380,16 +9380,16 @@
         <v>6</v>
       </c>
       <c r="E206" s="7">
-        <v>0</v>
+        <v>0.024222999999999998</v>
       </c>
       <c r="F206" s="7">
-        <v>0</v>
+        <v>-0.012654</v>
       </c>
       <c r="G206" s="7">
-        <v>0</v>
+        <v>0.310276</v>
       </c>
       <c r="H206" s="7">
-        <v>0</v>
+        <v>0.24435199999999999</v>
       </c>
       <c r="I206" s="7"/>
       <c r="J206" s="7"/>
@@ -9409,25 +9409,25 @@
         <v>5</v>
       </c>
       <c r="E207" s="7">
-        <v>0.022054999999999998</v>
+        <v>0.020232</v>
       </c>
       <c r="F207" s="7">
-        <v>0.038696</v>
+        <v>0.036987</v>
       </c>
       <c r="G207" s="7">
-        <v>0.11275600000000001</v>
+        <v>0.109267</v>
       </c>
       <c r="H207" s="7">
-        <v>0.071925</v>
+        <v>0.070926</v>
       </c>
       <c r="I207" s="7">
-        <v>0.317233</v>
+        <v>0.314451</v>
       </c>
       <c r="J207" s="7">
-        <v>1.9496289999999998</v>
+        <v>1.946878</v>
       </c>
       <c r="K207" s="7">
-        <v>5.28602</v>
+        <v>5.280157</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9444,25 +9444,25 @@
         <v>4</v>
       </c>
       <c r="E208" s="7">
-        <v>0.011321000000000001</v>
+        <v>0.016964999999999997</v>
       </c>
       <c r="F208" s="7">
-        <v>0.010887</v>
+        <v>0.006788</v>
       </c>
       <c r="G208" s="7">
-        <v>0.209935</v>
+        <v>0.213197</v>
       </c>
       <c r="H208" s="7">
-        <v>0.104239</v>
+        <v>0.105665</v>
       </c>
       <c r="I208" s="7">
-        <v>0.361777</v>
+        <v>0.36114199999999996</v>
       </c>
       <c r="J208" s="7">
-        <v>1.9525919999999999</v>
+        <v>1.956405</v>
       </c>
       <c r="K208" s="7">
-        <v>4.913919</v>
+        <v>4.921557</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9476,28 +9476,28 @@
         <v>26</v>
       </c>
       <c r="D209" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E209" s="7">
-        <v>0.010034000000000001</v>
+        <v>0.008813</v>
       </c>
       <c r="F209" s="7">
-        <v>0.013471</v>
+        <v>0.007712</v>
       </c>
       <c r="G209" s="7">
-        <v>0.268774</v>
+        <v>0.26008400000000004</v>
       </c>
       <c r="H209" s="7">
-        <v>0.18330100000000002</v>
+        <v>0.17940699999999998</v>
       </c>
       <c r="I209" s="7">
-        <v>0.46083199999999996</v>
+        <v>0.452637</v>
       </c>
       <c r="J209" s="7">
-        <v>2.715074</v>
+        <v>2.7028480000000004</v>
       </c>
       <c r="K209" s="7">
-        <v>7.961425</v>
+        <v>7.931934</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9514,25 +9514,25 @@
         <v>6</v>
       </c>
       <c r="E210" s="7">
-        <v>0.007229</v>
+        <v>0.0039700000000000004</v>
       </c>
       <c r="F210" s="7">
-        <v>-0.001015</v>
+        <v>-0.009599</v>
       </c>
       <c r="G210" s="7">
-        <v>0.32866100000000004</v>
+        <v>0.314484</v>
       </c>
       <c r="H210" s="7">
-        <v>0.191506</v>
+        <v>0.184371</v>
       </c>
       <c r="I210" s="7">
-        <v>0.47751699999999997</v>
+        <v>0.46539400000000003</v>
       </c>
       <c r="J210" s="7">
-        <v>2.703824</v>
+        <v>2.681644</v>
       </c>
       <c r="K210" s="7">
-        <v>9.663008999999999</v>
+        <v>9.599155</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9549,25 +9549,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.009941</v>
+        <v>0.013241000000000001</v>
       </c>
       <c r="F211" s="7">
-        <v>0.015269</v>
+        <v>0.009582</v>
       </c>
       <c r="G211" s="7">
-        <v>0.18601299999999998</v>
+        <v>0.18945900000000002</v>
       </c>
       <c r="H211" s="7">
-        <v>0.050479</v>
+        <v>0.049645</v>
       </c>
       <c r="I211" s="7">
-        <v>0.385662</v>
+        <v>0.380849</v>
       </c>
       <c r="J211" s="7">
-        <v>1.499095</v>
+        <v>1.4971100000000002</v>
       </c>
       <c r="K211" s="7">
-        <v>2.940221</v>
+        <v>2.9370920000000003</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9584,25 +9584,25 @@
         <v>6</v>
       </c>
       <c r="E212" s="7">
-        <v>0.0021279999999999997</v>
+        <v>-0.000274</v>
       </c>
       <c r="F212" s="7">
-        <v>-0.030822</v>
+        <v>-0.043616999999999996</v>
       </c>
       <c r="G212" s="7">
-        <v>0.326359</v>
+        <v>0.316191</v>
       </c>
       <c r="H212" s="7">
-        <v>0.23040400000000003</v>
+        <v>0.22263100000000002</v>
       </c>
       <c r="I212" s="7">
-        <v>0.37058</v>
+        <v>0.35967799999999994</v>
       </c>
       <c r="J212" s="7">
-        <v>2.639205</v>
+        <v>2.6162150000000004</v>
       </c>
       <c r="K212" s="7">
-        <v>14.48031</v>
+        <v>14.382517</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9619,25 +9619,25 @@
         <v>4</v>
       </c>
       <c r="E213" s="7">
-        <v>0.02786</v>
+        <v>0.026871999999999997</v>
       </c>
       <c r="F213" s="7">
-        <v>0.044381000000000004</v>
+        <v>0.039958</v>
       </c>
       <c r="G213" s="7">
-        <v>0.266108</v>
+        <v>0.263605</v>
       </c>
       <c r="H213" s="7">
-        <v>0.192029</v>
+        <v>0.1895</v>
       </c>
       <c r="I213" s="7">
-        <v>0.491459</v>
+        <v>0.491</v>
       </c>
       <c r="J213" s="7">
-        <v>1.876685</v>
+        <v>1.870582</v>
       </c>
       <c r="K213" s="7">
-        <v>5.506653</v>
+        <v>5.492848</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9654,25 +9654,25 @@
         <v>3</v>
       </c>
       <c r="E214" s="7">
-        <v>0.040597</v>
+        <v>0.03209</v>
       </c>
       <c r="F214" s="7">
-        <v>0.107489</v>
+        <v>0.10508100000000001</v>
       </c>
       <c r="G214" s="7">
-        <v>0.284465</v>
+        <v>0.285356</v>
       </c>
       <c r="H214" s="7">
-        <v>0.208074</v>
+        <v>0.207328</v>
       </c>
       <c r="I214" s="7">
-        <v>0.488548</v>
+        <v>0.48832000000000003</v>
       </c>
       <c r="J214" s="7">
-        <v>1.957874</v>
+        <v>1.956047</v>
       </c>
       <c r="K214" s="7">
-        <v>5.145752</v>
+        <v>5.141955</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9689,25 +9689,25 @@
         <v>4</v>
       </c>
       <c r="E215" s="7">
-        <v>0.042168000000000004</v>
+        <v>0.033064</v>
       </c>
       <c r="F215" s="7">
-        <v>0.10024699999999999</v>
+        <v>0.097316</v>
       </c>
       <c r="G215" s="7">
-        <v>0.362819</v>
+        <v>0.36236199999999996</v>
       </c>
       <c r="H215" s="7">
-        <v>0.290448</v>
+        <v>0.28692</v>
       </c>
       <c r="I215" s="7">
-        <v>0.603766</v>
+        <v>0.5910150000000001</v>
       </c>
       <c r="J215" s="7">
-        <v>3.236136</v>
+        <v>3.2245530000000002</v>
       </c>
       <c r="K215" s="7">
-        <v>9.983712</v>
+        <v>9.953681</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9724,25 +9724,25 @@
         <v>6</v>
       </c>
       <c r="E216" s="7">
-        <v>-0.003387</v>
+        <v>0.00006</v>
       </c>
       <c r="F216" s="7">
-        <v>-0.070283</v>
+        <v>-0.058813000000000004</v>
       </c>
       <c r="G216" s="7">
-        <v>0.16930199999999998</v>
+        <v>0.143633</v>
       </c>
       <c r="H216" s="7">
-        <v>0.09361499999999999</v>
+        <v>0.093437</v>
       </c>
       <c r="I216" s="7">
-        <v>0.6587139999999999</v>
+        <v>0.653389</v>
       </c>
       <c r="J216" s="7">
-        <v>4.161843</v>
+        <v>4.161004</v>
       </c>
       <c r="K216" s="7">
-        <v>13.280916999999999</v>
+        <v>13.278595000000001</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9759,25 +9759,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.045860000000000005</v>
+        <v>0.04125</v>
       </c>
       <c r="F217" s="7">
-        <v>0.059953000000000006</v>
+        <v>0.049908</v>
       </c>
       <c r="G217" s="7">
-        <v>0.219793</v>
+        <v>0.211064</v>
       </c>
       <c r="H217" s="7">
-        <v>0.160442</v>
+        <v>0.15192</v>
       </c>
       <c r="I217" s="7">
-        <v>0.419078</v>
+        <v>0.40740000000000004</v>
       </c>
       <c r="J217" s="7">
-        <v>2.531943</v>
+        <v>2.506004</v>
       </c>
       <c r="K217" s="7">
-        <v>7.341481</v>
+        <v>7.280221</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9794,25 +9794,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.092592</v>
+        <v>0.08488200000000001</v>
       </c>
       <c r="F218" s="7">
-        <v>0.149226</v>
+        <v>0.144905</v>
       </c>
       <c r="G218" s="7">
-        <v>0.487663</v>
+        <v>0.496774</v>
       </c>
       <c r="H218" s="7">
-        <v>0.40171599999999996</v>
+        <v>0.39935699999999996</v>
       </c>
       <c r="I218" s="7">
-        <v>0.675697</v>
+        <v>0.684706</v>
       </c>
       <c r="J218" s="7">
-        <v>2.9280720000000002</v>
+        <v>2.92146</v>
       </c>
       <c r="K218" s="7">
-        <v>10.145278</v>
+        <v>10.126517</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9829,25 +9829,25 @@
         <v>5</v>
       </c>
       <c r="E219" s="7">
-        <v>0.022253</v>
+        <v>0.020064000000000002</v>
       </c>
       <c r="F219" s="7">
-        <v>0.038546</v>
+        <v>0.039376</v>
       </c>
       <c r="G219" s="7">
-        <v>0.085274</v>
+        <v>0.08495599999999999</v>
       </c>
       <c r="H219" s="7">
-        <v>0.05904</v>
+        <v>0.059359</v>
       </c>
       <c r="I219" s="7">
-        <v>0.224939</v>
+        <v>0.22395800000000002</v>
       </c>
       <c r="J219" s="7">
-        <v>1.798296</v>
+        <v>1.7991409999999999</v>
       </c>
       <c r="K219" s="7">
-        <v>5.261551</v>
+        <v>5.263442</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9864,25 +9864,25 @@
         <v>4</v>
       </c>
       <c r="E220" s="7">
-        <v>0.040332999999999994</v>
+        <v>0.03084</v>
       </c>
       <c r="F220" s="7">
-        <v>0.117172</v>
+        <v>0.111036</v>
       </c>
       <c r="G220" s="7">
-        <v>0.35895699999999997</v>
+        <v>0.35698599999999997</v>
       </c>
       <c r="H220" s="7">
-        <v>0.275762</v>
+        <v>0.271368</v>
       </c>
       <c r="I220" s="7">
-        <v>0.6252</v>
+        <v>0.615245</v>
       </c>
       <c r="J220" s="7">
-        <v>3.362223</v>
+        <v>3.347199</v>
       </c>
       <c r="K220" s="7">
-        <v>10.420746</v>
+        <v>10.381412000000001</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9899,25 +9899,25 @@
         <v>5</v>
       </c>
       <c r="E221" s="7">
-        <v>0.09712300000000001</v>
+        <v>0.08752900000000001</v>
       </c>
       <c r="F221" s="7">
-        <v>0.13872</v>
+        <v>0.133411</v>
       </c>
       <c r="G221" s="7">
-        <v>0.458836</v>
+        <v>0.461822</v>
       </c>
       <c r="H221" s="7">
-        <v>0.36288200000000004</v>
+        <v>0.357558</v>
       </c>
       <c r="I221" s="7">
-        <v>0.656537</v>
+        <v>0.6557219999999999</v>
       </c>
       <c r="J221" s="7">
-        <v>4.169154</v>
+        <v>4.148959</v>
       </c>
       <c r="K221" s="7">
-        <v>14.158783000000001</v>
+        <v>14.099561000000001</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -9934,19 +9934,19 @@
         <v>4</v>
       </c>
       <c r="E222" s="7">
-        <v>0.053873</v>
+        <v>0.049079</v>
       </c>
       <c r="F222" s="7">
-        <v>0.075999</v>
+        <v>0.075218</v>
       </c>
       <c r="G222" s="7">
-        <v>0.277455</v>
+        <v>0.27417400000000003</v>
       </c>
       <c r="H222" s="7">
-        <v>0.213114</v>
+        <v>0.21076899999999998</v>
       </c>
       <c r="I222" s="7">
-        <v>0.533703</v>
+        <v>0.531911</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -9965,16 +9965,16 @@
         <v>6</v>
       </c>
       <c r="E223" s="7">
-        <v>0.121861</v>
+        <v>0.15162599999999998</v>
       </c>
       <c r="F223" s="7">
-        <v>0.077246</v>
+        <v>0.15823299999999998</v>
       </c>
       <c r="G223" s="7">
-        <v>0.7253820000000001</v>
+        <v>0.6883830000000001</v>
       </c>
       <c r="H223" s="7">
-        <v>0.241325</v>
+        <v>0.269047</v>
       </c>
       <c r="I223" s="7"/>
       <c r="J223" s="7"/>
@@ -9994,7 +9994,7 @@
         <v>6</v>
       </c>
       <c r="E224" s="7">
-        <v>0.0736</v>
+        <v>0.063854</v>
       </c>
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
@@ -10017,22 +10017,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.060485</v>
+        <v>0.076554</v>
       </c>
       <c r="F225" s="7">
-        <v>-0.004724</v>
+        <v>0.035883</v>
       </c>
       <c r="G225" s="7">
-        <v>0.423425</v>
+        <v>0.3933</v>
       </c>
       <c r="H225" s="7">
-        <v>0.15981</v>
+        <v>0.172058</v>
       </c>
       <c r="I225" s="7">
-        <v>1.192696</v>
+        <v>1.188223</v>
       </c>
       <c r="J225" s="7">
-        <v>4.828397</v>
+        <v>4.889951</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10050,25 +10050,25 @@
         <v>4</v>
       </c>
       <c r="E226" s="7">
-        <v>0.031415</v>
+        <v>0.031423</v>
       </c>
       <c r="F226" s="7">
-        <v>0.09801299999999999</v>
+        <v>0.096274</v>
       </c>
       <c r="G226" s="7">
-        <v>0.196527</v>
+        <v>0.19653500000000002</v>
       </c>
       <c r="H226" s="7">
-        <v>0.13906000000000002</v>
+        <v>0.140228</v>
       </c>
       <c r="I226" s="7">
-        <v>0.437616</v>
+        <v>0.43761099999999997</v>
       </c>
       <c r="J226" s="7">
-        <v>1.660523</v>
+        <v>1.663252</v>
       </c>
       <c r="K226" s="7">
-        <v>2.73747</v>
+        <v>2.741303</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -10085,19 +10085,19 @@
         <v>2</v>
       </c>
       <c r="E227" s="7">
-        <v>0.029169</v>
+        <v>0.029142</v>
       </c>
       <c r="F227" s="7">
-        <v>0.08343099999999999</v>
+        <v>0.081293</v>
       </c>
       <c r="G227" s="7">
-        <v>0.18615700000000002</v>
+        <v>0.186022</v>
       </c>
       <c r="H227" s="7">
-        <v>0.129242</v>
+        <v>0.13026</v>
       </c>
       <c r="I227" s="7">
-        <v>0.44297800000000004</v>
+        <v>0.44259</v>
       </c>
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
@@ -10116,22 +10116,22 @@
         <v>6</v>
       </c>
       <c r="E228" s="7">
-        <v>0.091267</v>
+        <v>0.0722</v>
       </c>
       <c r="F228" s="7">
-        <v>0.126633</v>
+        <v>0.109778</v>
       </c>
       <c r="G228" s="7">
-        <v>0.344174</v>
+        <v>0.337937</v>
       </c>
       <c r="H228" s="7">
-        <v>0.31343499999999996</v>
+        <v>0.29462299999999997</v>
       </c>
       <c r="I228" s="7">
-        <v>0.453693</v>
+        <v>0.43616</v>
       </c>
       <c r="J228" s="7">
-        <v>2.7981599999999998</v>
+        <v>2.743761</v>
       </c>
       <c r="K228" s="7"/>
     </row>
@@ -10149,19 +10149,19 @@
         <v>5</v>
       </c>
       <c r="E229" s="7">
-        <v>0.071666</v>
+        <v>0.08755399999999999</v>
       </c>
       <c r="F229" s="7">
-        <v>-0.001903</v>
+        <v>0.051481000000000006</v>
       </c>
       <c r="G229" s="7">
-        <v>0.41910200000000003</v>
+        <v>0.40382199999999996</v>
       </c>
       <c r="H229" s="7">
-        <v>0.182905</v>
+        <v>0.201116</v>
       </c>
       <c r="I229" s="7">
-        <v>1.113215</v>
+        <v>1.117594</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10201,25 +10201,25 @@
         <v>4</v>
       </c>
       <c r="E231" s="7">
-        <v>0.019077</v>
+        <v>0.020829</v>
       </c>
       <c r="F231" s="7">
-        <v>0.040042999999999995</v>
+        <v>0.035288</v>
       </c>
       <c r="G231" s="7">
-        <v>0.213172</v>
+        <v>0.21123799999999998</v>
       </c>
       <c r="H231" s="7">
-        <v>0.11921200000000001</v>
+        <v>0.11709699999999999</v>
       </c>
       <c r="I231" s="7">
-        <v>0.43955599999999995</v>
+        <v>0.43705700000000003</v>
       </c>
       <c r="J231" s="7">
-        <v>2.226549</v>
+        <v>2.220452</v>
       </c>
       <c r="K231" s="7">
-        <v>5.624427</v>
+        <v>5.61191</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -10236,25 +10236,25 @@
         <v>3</v>
       </c>
       <c r="E232" s="7">
-        <v>0.040209</v>
+        <v>0.033742999999999995</v>
       </c>
       <c r="F232" s="7">
-        <v>0.08076900000000001</v>
+        <v>0.077267</v>
       </c>
       <c r="G232" s="7">
-        <v>0.24574100000000001</v>
+        <v>0.24378599999999997</v>
       </c>
       <c r="H232" s="7">
-        <v>0.159582</v>
+        <v>0.157642</v>
       </c>
       <c r="I232" s="7">
-        <v>0.43999000000000005</v>
+        <v>0.436614</v>
       </c>
       <c r="J232" s="7">
-        <v>1.912712</v>
+        <v>1.9078389999999998</v>
       </c>
       <c r="K232" s="7">
-        <v>4.610447</v>
+        <v>4.6010610000000005</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -10271,19 +10271,19 @@
         <v>3</v>
       </c>
       <c r="E233" s="7">
-        <v>0.087484</v>
+        <v>0.082951</v>
       </c>
       <c r="F233" s="7">
-        <v>0.14052699999999999</v>
+        <v>0.142213</v>
       </c>
       <c r="G233" s="7">
-        <v>0.29181799999999997</v>
+        <v>0.298591</v>
       </c>
       <c r="H233" s="7">
-        <v>0.256718</v>
+        <v>0.25516500000000003</v>
       </c>
       <c r="I233" s="7">
-        <v>0.578533</v>
+        <v>0.572572</v>
       </c>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
@@ -10302,7 +10302,7 @@
         <v>2</v>
       </c>
       <c r="E234" s="7">
-        <v>0.037302</v>
+        <v>0.037468</v>
       </c>
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
@@ -10325,19 +10325,19 @@
         <v>5</v>
       </c>
       <c r="E235" s="7">
-        <v>0.143083</v>
+        <v>0.103446</v>
       </c>
       <c r="F235" s="7">
-        <v>0.238085</v>
+        <v>0.191409</v>
       </c>
       <c r="G235" s="7">
-        <v>0.483051</v>
+        <v>0.45252899999999996</v>
       </c>
       <c r="H235" s="7">
-        <v>0.451331</v>
+        <v>0.411698</v>
       </c>
       <c r="I235" s="7">
-        <v>0.6448999999999999</v>
+        <v>0.598873</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10356,19 +10356,19 @@
         <v>5</v>
       </c>
       <c r="E236" s="7">
-        <v>0.08103099999999999</v>
+        <v>0.07115</v>
       </c>
       <c r="F236" s="7">
-        <v>0.115658</v>
+        <v>0.11308</v>
       </c>
       <c r="G236" s="7">
-        <v>0.32146399999999997</v>
+        <v>0.325823</v>
       </c>
       <c r="H236" s="7">
-        <v>0.269617</v>
+        <v>0.26615500000000003</v>
       </c>
       <c r="I236" s="7">
-        <v>0.543999</v>
+        <v>0.5364909999999999</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10387,25 +10387,25 @@
         <v>4</v>
       </c>
       <c r="E237" s="7">
-        <v>0.037017</v>
+        <v>0.034992</v>
       </c>
       <c r="F237" s="7">
-        <v>0.06895</v>
+        <v>0.063881</v>
       </c>
       <c r="G237" s="7">
-        <v>0.200581</v>
+        <v>0.19738399999999998</v>
       </c>
       <c r="H237" s="7">
-        <v>0.131693</v>
+        <v>0.129129</v>
       </c>
       <c r="I237" s="7">
-        <v>0.379429</v>
+        <v>0.376304</v>
       </c>
       <c r="J237" s="7">
-        <v>1.8634469999999999</v>
+        <v>1.85696</v>
       </c>
       <c r="K237" s="7">
-        <v>4.40825</v>
+        <v>4.3959980000000005</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10422,19 +10422,19 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.017322999999999998</v>
+        <v>0.02358</v>
       </c>
       <c r="F238" s="7">
-        <v>0.021613000000000004</v>
+        <v>0.017447999999999998</v>
       </c>
       <c r="G238" s="7">
-        <v>0.266501</v>
+        <v>0.266436</v>
       </c>
       <c r="H238" s="7">
-        <v>0.194527</v>
+        <v>0.193294</v>
       </c>
       <c r="I238" s="7">
-        <v>0.444975</v>
+        <v>0.44359099999999996</v>
       </c>
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
@@ -10453,19 +10453,19 @@
         <v>4</v>
       </c>
       <c r="E239" s="7">
-        <v>0.020943</v>
+        <v>0.016616</v>
       </c>
       <c r="F239" s="7">
-        <v>0.04600799999999999</v>
+        <v>0.033659</v>
       </c>
       <c r="G239" s="7">
-        <v>0.202482</v>
+        <v>0.19565200000000002</v>
       </c>
       <c r="H239" s="7">
-        <v>0.123268</v>
+        <v>0.11570499999999999</v>
       </c>
       <c r="I239" s="7">
-        <v>0.464835</v>
+        <v>0.455778</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10484,19 +10484,19 @@
         <v>2</v>
       </c>
       <c r="E240" s="7">
-        <v>0.033978</v>
+        <v>0.033885</v>
       </c>
       <c r="F240" s="7">
-        <v>0.096547</v>
+        <v>0.09422499999999999</v>
       </c>
       <c r="G240" s="7">
-        <v>0.199297</v>
+        <v>0.19893899999999998</v>
       </c>
       <c r="H240" s="7">
-        <v>0.143866</v>
+        <v>0.14472200000000002</v>
       </c>
       <c r="I240" s="7">
-        <v>0.47034</v>
+        <v>0.46995800000000004</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10515,25 +10515,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.006604</v>
+        <v>0.004425</v>
       </c>
       <c r="F241" s="7">
-        <v>-0.056177000000000005</v>
+        <v>-0.048811</v>
       </c>
       <c r="G241" s="7">
-        <v>0.19320900000000002</v>
+        <v>0.163309</v>
       </c>
       <c r="H241" s="7">
-        <v>0.109574</v>
+        <v>0.105458</v>
       </c>
       <c r="I241" s="7">
-        <v>0.668309</v>
+        <v>0.6573739999999999</v>
       </c>
       <c r="J241" s="7">
-        <v>4.279398</v>
+        <v>4.259814</v>
       </c>
       <c r="K241" s="7">
-        <v>13.649549</v>
+        <v>13.595207</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10550,14 +10550,14 @@
         <v>3</v>
       </c>
       <c r="E242" s="7">
-        <v>0.004377</v>
+        <v>0.009541</v>
       </c>
       <c r="F242" s="7">
-        <v>0.016084</v>
+        <v>0.008361</v>
       </c>
       <c r="G242" s="7"/>
       <c r="H242" s="7">
-        <v>0.048777999999999995</v>
+        <v>0.046073</v>
       </c>
       <c r="I242" s="7"/>
       <c r="J242" s="7"/>
@@ -10577,19 +10577,19 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.176157</v>
+        <v>0.158348</v>
       </c>
       <c r="F243" s="7">
-        <v>0.281292</v>
+        <v>0.267316</v>
       </c>
       <c r="G243" s="7">
-        <v>0.434379</v>
+        <v>0.431319</v>
       </c>
       <c r="H243" s="7">
-        <v>0.39429499999999995</v>
+        <v>0.377564</v>
       </c>
       <c r="I243" s="7">
-        <v>0.7392319999999999</v>
+        <v>0.7129420000000001</v>
       </c>
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
@@ -10608,19 +10608,19 @@
         <v>5</v>
       </c>
       <c r="E244" s="7">
-        <v>0.04577899999999999</v>
+        <v>0.050076</v>
       </c>
       <c r="F244" s="7">
-        <v>0.03159</v>
+        <v>0.035806</v>
       </c>
       <c r="G244" s="7">
-        <v>0.252631</v>
+        <v>0.254967</v>
       </c>
       <c r="H244" s="7">
-        <v>0.19841</v>
+        <v>0.19775099999999998</v>
       </c>
       <c r="I244" s="7">
-        <v>0.451753</v>
+        <v>0.44839599999999996</v>
       </c>
       <c r="J244" s="7"/>
       <c r="K244" s="7"/>
@@ -10639,25 +10639,25 @@
         <v>6</v>
       </c>
       <c r="E245" s="7">
-        <v>0.019143</v>
+        <v>0.017387</v>
       </c>
       <c r="F245" s="7">
-        <v>0.037459</v>
+        <v>0.037993</v>
       </c>
       <c r="G245" s="7">
-        <v>0.089673</v>
+        <v>0.08886799999999999</v>
       </c>
       <c r="H245" s="7">
-        <v>0.061775000000000004</v>
+        <v>0.06178</v>
       </c>
       <c r="I245" s="7">
-        <v>0.227527</v>
+        <v>0.226444</v>
       </c>
       <c r="J245" s="7">
-        <v>1.812638</v>
+        <v>1.812652</v>
       </c>
       <c r="K245" s="7">
-        <v>5.772797000000001</v>
+        <v>5.772831999999999</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10674,25 +10674,25 @@
         <v>4</v>
       </c>
       <c r="E246" s="7">
-        <v>0.018931</v>
+        <v>0.017734</v>
       </c>
       <c r="F246" s="7">
-        <v>0.053914</v>
+        <v>0.049224</v>
       </c>
       <c r="G246" s="7">
-        <v>0.23505700000000002</v>
+        <v>0.228806</v>
       </c>
       <c r="H246" s="7">
-        <v>0.096625</v>
+        <v>0.09498200000000001</v>
       </c>
       <c r="I246" s="7">
-        <v>0.262018</v>
+        <v>0.255503</v>
       </c>
       <c r="J246" s="7">
-        <v>1.920434</v>
+        <v>1.916059</v>
       </c>
       <c r="K246" s="7">
-        <v>5.821384</v>
+        <v>5.811165</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10709,25 +10709,25 @@
         <v>6</v>
       </c>
       <c r="E247" s="7">
-        <v>0.015498000000000001</v>
+        <v>0.018591</v>
       </c>
       <c r="F247" s="7">
-        <v>-0.014732</v>
+        <v>-0.021771</v>
       </c>
       <c r="G247" s="7">
-        <v>0.308402</v>
+        <v>0.302356</v>
       </c>
       <c r="H247" s="7">
-        <v>0.225356</v>
+        <v>0.220697</v>
       </c>
       <c r="I247" s="7">
-        <v>0.430358</v>
+        <v>0.425845</v>
       </c>
       <c r="J247" s="7">
-        <v>2.732139</v>
+        <v>2.717949</v>
       </c>
       <c r="K247" s="7">
-        <v>14.690931</v>
+        <v>14.631273</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10744,25 +10744,25 @@
         <v>3</v>
       </c>
       <c r="E248" s="7">
-        <v>0.047417</v>
+        <v>0.036946</v>
       </c>
       <c r="F248" s="7">
-        <v>0.086012</v>
+        <v>0.084173</v>
       </c>
       <c r="G248" s="7">
-        <v>0.244119</v>
+        <v>0.24084</v>
       </c>
       <c r="H248" s="7">
-        <v>0.171037</v>
+        <v>0.169024</v>
       </c>
       <c r="I248" s="7">
-        <v>0.453127</v>
+        <v>0.44982700000000003</v>
       </c>
       <c r="J248" s="7">
-        <v>1.9296309999999999</v>
+        <v>1.9245949999999998</v>
       </c>
       <c r="K248" s="7">
-        <v>4.671596</v>
+        <v>4.661846</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10779,25 +10779,25 @@
         <v>4</v>
       </c>
       <c r="E249" s="7">
-        <v>0.006991000000000001</v>
+        <v>0.012179</v>
       </c>
       <c r="F249" s="7">
-        <v>0.0032500000000000003</v>
+        <v>-0.003218</v>
       </c>
       <c r="G249" s="7">
-        <v>0.182995</v>
+        <v>0.181894</v>
       </c>
       <c r="H249" s="7">
-        <v>0.08410500000000001</v>
+        <v>0.08172399999999999</v>
       </c>
       <c r="I249" s="7">
-        <v>0.374975</v>
+        <v>0.37166499999999997</v>
       </c>
       <c r="J249" s="7">
-        <v>1.521359</v>
+        <v>1.515822</v>
       </c>
       <c r="K249" s="7">
-        <v>3.8200510000000003</v>
+        <v>3.8094650000000003</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10814,25 +10814,25 @@
         <v>2</v>
       </c>
       <c r="E250" s="7">
-        <v>0.027564</v>
+        <v>0.027108</v>
       </c>
       <c r="F250" s="7">
-        <v>0.081613</v>
+        <v>0.07732</v>
       </c>
       <c r="G250" s="7">
-        <v>0.21592099999999997</v>
+        <v>0.21488</v>
       </c>
       <c r="H250" s="7">
-        <v>0.14533300000000002</v>
+        <v>0.144414</v>
       </c>
       <c r="I250" s="7">
-        <v>0.507746</v>
+        <v>0.504516</v>
       </c>
       <c r="J250" s="7">
-        <v>4.28424</v>
+        <v>4.280003</v>
       </c>
       <c r="K250" s="7">
-        <v>7.196811</v>
+        <v>7.190239</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10849,25 +10849,25 @@
         <v>4</v>
       </c>
       <c r="E251" s="7">
-        <v>0.018444000000000002</v>
+        <v>0.020274999999999998</v>
       </c>
       <c r="F251" s="7">
-        <v>0.035717</v>
+        <v>0.030441</v>
       </c>
       <c r="G251" s="7">
-        <v>0.27792100000000003</v>
+        <v>0.274521</v>
       </c>
       <c r="H251" s="7">
-        <v>0.201109</v>
+        <v>0.198638</v>
       </c>
       <c r="I251" s="7">
-        <v>0.498899</v>
+        <v>0.49608800000000003</v>
       </c>
       <c r="J251" s="7">
-        <v>3.191484</v>
+        <v>3.182859</v>
       </c>
       <c r="K251" s="7">
-        <v>8.640585999999999</v>
+        <v>8.620749</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10884,25 +10884,25 @@
         <v>5</v>
       </c>
       <c r="E252" s="7">
-        <v>0.016399</v>
+        <v>0.020589</v>
       </c>
       <c r="F252" s="7">
-        <v>0.021141999999999998</v>
+        <v>0.016734</v>
       </c>
       <c r="G252" s="7">
-        <v>0.291449</v>
+        <v>0.289657</v>
       </c>
       <c r="H252" s="7">
-        <v>0.214815</v>
+        <v>0.21329399999999998</v>
       </c>
       <c r="I252" s="7">
-        <v>0.49304499999999996</v>
+        <v>0.49203600000000003</v>
       </c>
       <c r="J252" s="7">
-        <v>3.6954629999999997</v>
+        <v>3.6895830000000003</v>
       </c>
       <c r="K252" s="7">
-        <v>11.582431</v>
+        <v>11.566674</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10919,25 +10919,25 @@
         <v>6</v>
       </c>
       <c r="E253" s="7">
-        <v>0.011955</v>
+        <v>0.017283</v>
       </c>
       <c r="F253" s="7">
-        <v>-0.004366</v>
+        <v>-0.008773999999999999</v>
       </c>
       <c r="G253" s="7">
-        <v>0.309755</v>
+        <v>0.306714</v>
       </c>
       <c r="H253" s="7">
-        <v>0.226906</v>
+        <v>0.225247</v>
       </c>
       <c r="I253" s="7">
-        <v>0.444443</v>
+        <v>0.444624</v>
       </c>
       <c r="J253" s="7">
-        <v>3.220371</v>
+        <v>3.214665</v>
       </c>
       <c r="K253" s="7">
-        <v>14.128672</v>
+        <v>14.108218999999998</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10954,25 +10954,25 @@
         <v>3</v>
       </c>
       <c r="E254" s="7">
-        <v>0.053226</v>
+        <v>0.045956000000000004</v>
       </c>
       <c r="F254" s="7">
-        <v>0.09369999999999999</v>
+        <v>0.089335</v>
       </c>
       <c r="G254" s="7">
-        <v>0.24320799999999998</v>
+        <v>0.241459</v>
       </c>
       <c r="H254" s="7">
-        <v>0.190882</v>
+        <v>0.18864599999999998</v>
       </c>
       <c r="I254" s="7">
-        <v>0.46492100000000003</v>
+        <v>0.45992600000000006</v>
       </c>
       <c r="J254" s="7">
-        <v>2.194751</v>
+        <v>2.188753</v>
       </c>
       <c r="K254" s="7">
-        <v>5.697457000000001</v>
+        <v>5.684882</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10989,25 +10989,25 @@
         <v>5</v>
       </c>
       <c r="E255" s="7">
-        <v>0.075711</v>
+        <v>0.06610100000000001</v>
       </c>
       <c r="F255" s="7">
-        <v>0.11363300000000001</v>
+        <v>0.105498</v>
       </c>
       <c r="G255" s="7">
-        <v>0.33761899999999995</v>
+        <v>0.334121</v>
       </c>
       <c r="H255" s="7">
-        <v>0.27105</v>
+        <v>0.264821</v>
       </c>
       <c r="I255" s="7">
-        <v>0.533532</v>
+        <v>0.526942</v>
       </c>
       <c r="J255" s="7">
-        <v>3.268186</v>
+        <v>3.24727</v>
       </c>
       <c r="K255" s="7">
-        <v>10.247247</v>
+        <v>10.192129999999999</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11024,25 +11024,25 @@
         <v>6</v>
       </c>
       <c r="E256" s="7">
-        <v>0.082622</v>
+        <v>0.07222</v>
       </c>
       <c r="F256" s="7">
-        <v>0.116971</v>
+        <v>0.108539</v>
       </c>
       <c r="G256" s="7">
-        <v>0.36318100000000003</v>
+        <v>0.35969700000000004</v>
       </c>
       <c r="H256" s="7">
-        <v>0.294784</v>
+        <v>0.287851</v>
       </c>
       <c r="I256" s="7">
-        <v>0.538543</v>
+        <v>0.532464</v>
       </c>
       <c r="J256" s="7">
-        <v>3.4669869999999996</v>
+        <v>3.443066</v>
       </c>
       <c r="K256" s="7">
-        <v>11.390264</v>
+        <v>11.323913</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11059,25 +11059,25 @@
         <v>4</v>
       </c>
       <c r="E257" s="7">
-        <v>0.008178999999999999</v>
+        <v>0.012988</v>
       </c>
       <c r="F257" s="7">
-        <v>0.010256000000000001</v>
+        <v>0.005370000000000001</v>
       </c>
       <c r="G257" s="7">
-        <v>0.165628</v>
+        <v>0.1643</v>
       </c>
       <c r="H257" s="7">
-        <v>0.076474</v>
+        <v>0.07485699999999999</v>
       </c>
       <c r="I257" s="7">
-        <v>0.370428</v>
+        <v>0.367705</v>
       </c>
       <c r="J257" s="7">
-        <v>1.8609809999999998</v>
+        <v>1.8566820000000002</v>
       </c>
       <c r="K257" s="7">
-        <v>5.031392</v>
+        <v>5.02233</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11094,25 +11094,25 @@
         <v>4</v>
       </c>
       <c r="E258" s="7">
-        <v>0.031232000000000003</v>
+        <v>0.027522</v>
       </c>
       <c r="F258" s="7">
-        <v>0.030654</v>
+        <v>0.030271</v>
       </c>
       <c r="G258" s="7">
-        <v>0.252402</v>
+        <v>0.243248</v>
       </c>
       <c r="H258" s="7">
-        <v>0.18570799999999998</v>
+        <v>0.18152200000000002</v>
       </c>
       <c r="I258" s="7">
-        <v>0.533531</v>
+        <v>0.526099</v>
       </c>
       <c r="J258" s="7">
-        <v>2.844431</v>
+        <v>2.830859</v>
       </c>
       <c r="K258" s="7">
-        <v>6.188227</v>
+        <v>6.162851000000001</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11129,25 +11129,25 @@
         <v>4</v>
       </c>
       <c r="E259" s="7">
-        <v>0.025844</v>
+        <v>0.023812000000000003</v>
       </c>
       <c r="F259" s="7">
-        <v>0.035706</v>
+        <v>0.036633</v>
       </c>
       <c r="G259" s="7">
-        <v>0.230687</v>
+        <v>0.223294</v>
       </c>
       <c r="H259" s="7">
-        <v>0.167758</v>
+        <v>0.165499</v>
       </c>
       <c r="I259" s="7">
-        <v>0.5163150000000001</v>
+        <v>0.512453</v>
       </c>
       <c r="J259" s="7">
-        <v>2.7965269999999998</v>
+        <v>2.789183</v>
       </c>
       <c r="K259" s="7">
-        <v>5.341385</v>
+        <v>5.329117999999999</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11164,25 +11164,25 @@
         <v>5</v>
       </c>
       <c r="E260" s="7">
-        <v>0.036798000000000004</v>
+        <v>0.031953</v>
       </c>
       <c r="F260" s="7">
-        <v>0.028371</v>
+        <v>0.027169</v>
       </c>
       <c r="G260" s="7">
-        <v>0.28674299999999997</v>
+        <v>0.278537</v>
       </c>
       <c r="H260" s="7">
-        <v>0.210339</v>
+        <v>0.204627</v>
       </c>
       <c r="I260" s="7">
-        <v>0.5445519999999999</v>
+        <v>0.535133</v>
       </c>
       <c r="J260" s="7">
-        <v>2.867189</v>
+        <v>2.848938</v>
       </c>
       <c r="K260" s="7">
-        <v>7.483936</v>
+        <v>7.443898000000001</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11199,25 +11199,25 @@
         <v>6</v>
       </c>
       <c r="E261" s="7">
-        <v>-0.00010800000000000001</v>
+        <v>0.0018470000000000001</v>
       </c>
       <c r="F261" s="7">
-        <v>-0.062675</v>
+        <v>-0.051143999999999995</v>
       </c>
       <c r="G261" s="7">
-        <v>0.17677199999999998</v>
+        <v>0.150937</v>
       </c>
       <c r="H261" s="7">
-        <v>0.101537</v>
+        <v>0.100731</v>
       </c>
       <c r="I261" s="7">
-        <v>0.662751</v>
+        <v>0.660412</v>
       </c>
       <c r="J261" s="7">
-        <v>4.166752</v>
+        <v>4.162973</v>
       </c>
       <c r="K261" s="7">
-        <v>13.505902</v>
+        <v>13.495291</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -11234,25 +11234,25 @@
         <v>2</v>
       </c>
       <c r="E262" s="7">
-        <v>0.045298</v>
+        <v>0.042895</v>
       </c>
       <c r="F262" s="7">
-        <v>0.099234</v>
+        <v>0.097416</v>
       </c>
       <c r="G262" s="7">
-        <v>0.217027</v>
+        <v>0.218305</v>
       </c>
       <c r="H262" s="7">
-        <v>0.171736</v>
+        <v>0.174472</v>
       </c>
       <c r="I262" s="7">
-        <v>0.45063400000000003</v>
+        <v>0.449195</v>
       </c>
       <c r="J262" s="7">
-        <v>2.506425</v>
+        <v>2.514611</v>
       </c>
       <c r="K262" s="7">
-        <v>4.569877</v>
+        <v>4.5828809999999995</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -11269,25 +11269,25 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.08882999999999999</v>
+        <v>0.100085</v>
       </c>
       <c r="F263" s="7">
-        <v>0.060916</v>
+        <v>0.078684</v>
       </c>
       <c r="G263" s="7">
-        <v>0.241955</v>
+        <v>0.23706</v>
       </c>
       <c r="H263" s="7">
-        <v>0.18438400000000002</v>
+        <v>0.18767</v>
       </c>
       <c r="I263" s="7">
-        <v>0.686047</v>
+        <v>0.6796939999999999</v>
       </c>
       <c r="J263" s="7">
-        <v>4.561116</v>
+        <v>4.576544999999999</v>
       </c>
       <c r="K263" s="7">
-        <v>21.023912999999997</v>
+        <v>21.085018</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -11304,10 +11304,10 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0</v>
+        <v>0.003667</v>
       </c>
       <c r="F264" s="7">
-        <v>0</v>
+        <v>-0.050656999999999994</v>
       </c>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
@@ -11329,22 +11329,22 @@
         <v>3</v>
       </c>
       <c r="E265" s="7">
-        <v>0.051193</v>
+        <v>0.046414</v>
       </c>
       <c r="F265" s="7">
-        <v>0.097871</v>
+        <v>0.093766</v>
       </c>
       <c r="G265" s="7">
-        <v>0.27103</v>
+        <v>0.269343</v>
       </c>
       <c r="H265" s="7">
-        <v>0.20247099999999998</v>
+        <v>0.200667</v>
       </c>
       <c r="I265" s="7">
-        <v>0.516271</v>
+        <v>0.512901</v>
       </c>
       <c r="J265" s="7">
-        <v>2.413582</v>
+        <v>2.408459</v>
       </c>
       <c r="K265" s="7"/>
     </row>
@@ -11362,22 +11362,22 @@
         <v>3</v>
       </c>
       <c r="E266" s="7">
-        <v>0.007307</v>
+        <v>0.007463</v>
       </c>
       <c r="F266" s="7">
-        <v>0.03463</v>
+        <v>0.030255999999999998</v>
       </c>
       <c r="G266" s="7">
-        <v>0.12456899999999999</v>
+        <v>0.12181900000000001</v>
       </c>
       <c r="H266" s="7">
-        <v>0.067457</v>
+        <v>0.065714</v>
       </c>
       <c r="I266" s="7">
-        <v>0.44329999999999997</v>
+        <v>0.433482</v>
       </c>
       <c r="J266" s="7">
-        <v>2.6612810000000002</v>
+        <v>2.6553050000000002</v>
       </c>
       <c r="K266" s="7"/>
     </row>
@@ -11395,19 +11395,19 @@
         <v>5</v>
       </c>
       <c r="E267" s="7">
-        <v>-0.021059</v>
+        <v>-0.015088999999999998</v>
       </c>
       <c r="F267" s="7">
-        <v>-0.050969</v>
+        <v>-0.049643</v>
       </c>
       <c r="G267" s="7">
-        <v>0.293963</v>
+        <v>0.278638</v>
       </c>
       <c r="H267" s="7">
-        <v>0.16659600000000002</v>
+        <v>0.162103</v>
       </c>
       <c r="I267" s="7">
-        <v>0.361163</v>
+        <v>0.34977800000000003</v>
       </c>
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
@@ -11447,22 +11447,22 @@
         <v>6</v>
       </c>
       <c r="E269" s="7">
-        <v>0.158241</v>
+        <v>0.134917</v>
       </c>
       <c r="F269" s="7">
-        <v>0.209558</v>
+        <v>0.179403</v>
       </c>
       <c r="G269" s="7">
-        <v>0.31600100000000003</v>
+        <v>0.299298</v>
       </c>
       <c r="H269" s="7">
-        <v>0.289664</v>
+        <v>0.263025</v>
       </c>
       <c r="I269" s="7">
-        <v>0.55304</v>
+        <v>0.507497</v>
       </c>
       <c r="J269" s="7">
-        <v>3.696307</v>
+        <v>3.5993020000000002</v>
       </c>
       <c r="K269" s="7"/>
     </row>
@@ -11480,19 +11480,19 @@
         <v>6</v>
       </c>
       <c r="E270" s="7">
-        <v>0.043333</v>
+        <v>0.049193</v>
       </c>
       <c r="F270" s="7">
-        <v>0.061822</v>
+        <v>0.070635</v>
       </c>
       <c r="G270" s="7">
-        <v>0.180992</v>
+        <v>0.18541799999999997</v>
       </c>
       <c r="H270" s="7">
-        <v>0.15929000000000001</v>
+        <v>0.166357</v>
       </c>
       <c r="I270" s="7">
-        <v>0.290392</v>
+        <v>0.29698399999999997</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11511,19 +11511,19 @@
         <v>2</v>
       </c>
       <c r="E271" s="7">
-        <v>0.032358</v>
+        <v>0.03246</v>
       </c>
       <c r="F271" s="7">
-        <v>0.09877599999999999</v>
+        <v>0.09695999999999999</v>
       </c>
       <c r="G271" s="7">
-        <v>0.20693799999999998</v>
+        <v>0.20722100000000002</v>
       </c>
       <c r="H271" s="7">
-        <v>0.146407</v>
+        <v>0.147783</v>
       </c>
       <c r="I271" s="7">
-        <v>0.481427</v>
+        <v>0.481449</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11542,22 +11542,22 @@
         <v>2</v>
       </c>
       <c r="E272" s="7">
-        <v>0.019252000000000002</v>
+        <v>0.020612</v>
       </c>
       <c r="F272" s="7">
-        <v>0.05110699999999999</v>
+        <v>0.04966</v>
       </c>
       <c r="G272" s="7">
-        <v>0.189929</v>
+        <v>0.19031800000000001</v>
       </c>
       <c r="H272" s="7">
-        <v>0.132752</v>
+        <v>0.1335</v>
       </c>
       <c r="I272" s="7">
-        <v>0.467667</v>
+        <v>0.464207</v>
       </c>
       <c r="J272" s="7">
-        <v>3.092785</v>
+        <v>3.0954880000000005</v>
       </c>
       <c r="K272" s="7"/>
     </row>
@@ -11575,22 +11575,22 @@
         <v>5</v>
       </c>
       <c r="E273" s="7">
-        <v>-0.004986</v>
+        <v>-0.00146</v>
       </c>
       <c r="F273" s="7">
-        <v>-0.026646999999999997</v>
+        <v>-0.031971</v>
       </c>
       <c r="G273" s="7">
-        <v>0.186515</v>
+        <v>0.182719</v>
       </c>
       <c r="H273" s="7">
-        <v>0.12481500000000001</v>
+        <v>0.121928</v>
       </c>
       <c r="I273" s="7">
-        <v>0.499569</v>
+        <v>0.49378700000000003</v>
       </c>
       <c r="J273" s="7">
-        <v>2.786825</v>
+        <v>2.777104</v>
       </c>
       <c r="K273" s="7"/>
     </row>
@@ -11608,19 +11608,19 @@
         <v>5</v>
       </c>
       <c r="E274" s="7">
-        <v>0.044818</v>
+        <v>0.034127</v>
       </c>
       <c r="F274" s="7">
-        <v>0.09254899999999999</v>
+        <v>0.07433</v>
       </c>
       <c r="G274" s="7">
-        <v>0.24741800000000003</v>
+        <v>0.236622</v>
       </c>
       <c r="H274" s="7">
-        <v>0.173863</v>
+        <v>0.161109</v>
       </c>
       <c r="I274" s="7">
-        <v>0.514316</v>
+        <v>0.495626</v>
       </c>
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
@@ -11660,19 +11660,19 @@
         <v>5</v>
       </c>
       <c r="E276" s="7">
-        <v>0.050339999999999996</v>
+        <v>0.040873999999999994</v>
       </c>
       <c r="F276" s="7">
-        <v>0.043959</v>
+        <v>0.022557</v>
       </c>
       <c r="G276" s="7">
-        <v>0.18825299999999998</v>
+        <v>0.179375</v>
       </c>
       <c r="H276" s="7">
-        <v>0.173303</v>
+        <v>0.154584</v>
       </c>
       <c r="I276" s="7">
-        <v>0.45740400000000003</v>
+        <v>0.441295</v>
       </c>
       <c r="J276" s="7"/>
       <c r="K276" s="7"/>
@@ -11691,19 +11691,19 @@
         <v>4</v>
       </c>
       <c r="E277" s="7">
-        <v>0.041481000000000004</v>
+        <v>0.045675</v>
       </c>
       <c r="F277" s="7">
-        <v>0.037761</v>
+        <v>0.039102</v>
       </c>
       <c r="G277" s="7">
-        <v>0.304499</v>
+        <v>0.30371400000000004</v>
       </c>
       <c r="H277" s="7">
-        <v>0.23694500000000002</v>
+        <v>0.235294</v>
       </c>
       <c r="I277" s="7">
-        <v>0.347851</v>
+        <v>0.345797</v>
       </c>
       <c r="J277" s="7"/>
       <c r="K277" s="7"/>
@@ -11722,19 +11722,19 @@
         <v>5</v>
       </c>
       <c r="E278" s="7">
-        <v>0.057159</v>
+        <v>0.055303000000000005</v>
       </c>
       <c r="F278" s="7">
-        <v>0.067199</v>
+        <v>0.05845500000000001</v>
       </c>
       <c r="G278" s="7">
-        <v>0.276286</v>
+        <v>0.272354</v>
       </c>
       <c r="H278" s="7">
-        <v>0.225969</v>
+        <v>0.230184</v>
       </c>
       <c r="I278" s="7">
-        <v>0.36433</v>
+        <v>0.338489</v>
       </c>
       <c r="J278" s="7"/>
       <c r="K278" s="7"/>
@@ -11753,19 +11753,19 @@
         <v>6</v>
       </c>
       <c r="E279" s="7">
-        <v>0.167021</v>
+        <v>0.133902</v>
       </c>
       <c r="F279" s="7">
-        <v>0.220716</v>
+        <v>0.176114</v>
       </c>
       <c r="G279" s="7">
-        <v>0.405562</v>
+        <v>0.386054</v>
       </c>
       <c r="H279" s="7">
-        <v>0.417778</v>
+        <v>0.38378799999999996</v>
       </c>
       <c r="I279" s="7">
-        <v>0.6031920000000001</v>
+        <v>0.5682659999999999</v>
       </c>
       <c r="J279" s="7"/>
       <c r="K279" s="7"/>
@@ -11784,22 +11784,22 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0.008214</v>
+        <v>0.012774</v>
       </c>
       <c r="F280" s="7">
-        <v>0.008912999999999999</v>
+        <v>0.007187</v>
       </c>
       <c r="G280" s="7">
-        <v>0.188149</v>
+        <v>0.187718</v>
       </c>
       <c r="H280" s="7">
-        <v>0.129415</v>
+        <v>0.129575</v>
       </c>
       <c r="I280" s="7">
-        <v>0.47775799999999996</v>
+        <v>0.476071</v>
       </c>
       <c r="J280" s="7">
-        <v>3.015668</v>
+        <v>3.016236</v>
       </c>
       <c r="K280" s="7"/>
     </row>
@@ -11817,25 +11817,25 @@
         <v>5</v>
       </c>
       <c r="E281" s="7">
-        <v>0.052531999999999995</v>
+        <v>0.047429</v>
       </c>
       <c r="F281" s="7">
-        <v>0.113611</v>
+        <v>0.107206</v>
       </c>
       <c r="G281" s="7">
-        <v>0.369569</v>
+        <v>0.366141</v>
       </c>
       <c r="H281" s="7">
-        <v>0.256009</v>
+        <v>0.249148</v>
       </c>
       <c r="I281" s="7">
-        <v>0.581738</v>
+        <v>0.569802</v>
       </c>
       <c r="J281" s="7">
-        <v>2.6891149999999997</v>
+        <v>2.668962</v>
       </c>
       <c r="K281" s="7">
-        <v>6.809689</v>
+        <v>6.767027000000001</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11852,25 +11852,25 @@
         <v>2</v>
       </c>
       <c r="E282" s="7">
-        <v>0.033627</v>
+        <v>0.031056</v>
       </c>
       <c r="F282" s="7">
-        <v>0.09201100000000001</v>
+        <v>0.08886200000000001</v>
       </c>
       <c r="G282" s="7">
-        <v>0.202807</v>
+        <v>0.202159</v>
       </c>
       <c r="H282" s="7">
-        <v>0.14282</v>
+        <v>0.143271</v>
       </c>
       <c r="I282" s="7">
-        <v>0.47476</v>
+        <v>0.473706</v>
       </c>
       <c r="J282" s="7">
-        <v>2.219804</v>
+        <v>2.221073</v>
       </c>
       <c r="K282" s="7">
-        <v>4.169218</v>
+        <v>4.1712560000000005</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11887,25 +11887,25 @@
         <v>6</v>
       </c>
       <c r="E283" s="7">
-        <v>0.014644999999999998</v>
+        <v>0.014719</v>
       </c>
       <c r="F283" s="7">
-        <v>0.012424999999999999</v>
+        <v>0.017601</v>
       </c>
       <c r="G283" s="7">
-        <v>0.11376599999999999</v>
+        <v>0.111958</v>
       </c>
       <c r="H283" s="7">
-        <v>0.055739000000000004</v>
+        <v>0.053994</v>
       </c>
       <c r="I283" s="7">
-        <v>0.293423</v>
+        <v>0.289464</v>
       </c>
       <c r="J283" s="7">
-        <v>1.749785</v>
+        <v>1.745241</v>
       </c>
       <c r="K283" s="7">
-        <v>5.113805</v>
+        <v>5.103702</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11922,25 +11922,25 @@
         <v>6</v>
       </c>
       <c r="E284" s="7">
-        <v>0.019044000000000002</v>
+        <v>0.023114</v>
       </c>
       <c r="F284" s="7">
-        <v>-0.011054999999999999</v>
+        <v>-0.016822999999999998</v>
       </c>
       <c r="G284" s="7">
-        <v>0.293975</v>
+        <v>0.28985099999999997</v>
       </c>
       <c r="H284" s="7">
-        <v>0.222831</v>
+        <v>0.22076</v>
       </c>
       <c r="I284" s="7">
-        <v>0.377552</v>
+        <v>0.37274</v>
       </c>
       <c r="J284" s="7">
-        <v>2.384734</v>
+        <v>2.3790020000000003</v>
       </c>
       <c r="K284" s="7">
-        <v>12.514166</v>
+        <v>12.491278</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11957,25 +11957,25 @@
         <v>4</v>
       </c>
       <c r="E285" s="7">
-        <v>0.018359</v>
+        <v>0.027746</v>
       </c>
       <c r="F285" s="7">
-        <v>0.010823000000000001</v>
+        <v>0.007436000000000001</v>
       </c>
       <c r="G285" s="7">
-        <v>0.184373</v>
+        <v>0.188604</v>
       </c>
       <c r="H285" s="7">
-        <v>0.059137</v>
+        <v>0.059339</v>
       </c>
       <c r="I285" s="7">
-        <v>0.37571</v>
+        <v>0.372729</v>
       </c>
       <c r="J285" s="7">
-        <v>1.712939</v>
+        <v>1.7134559999999999</v>
       </c>
       <c r="K285" s="7">
-        <v>3.660353</v>
+        <v>3.6612400000000003</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -11992,25 +11992,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>0.063501</v>
+        <v>0.054653</v>
       </c>
       <c r="F286" s="7">
-        <v>0.11683500000000001</v>
+        <v>0.10191900000000001</v>
       </c>
       <c r="G286" s="7">
-        <v>0.364094</v>
+        <v>0.35940300000000003</v>
       </c>
       <c r="H286" s="7">
-        <v>0.25806799999999996</v>
+        <v>0.246792</v>
       </c>
       <c r="I286" s="7">
-        <v>0.513127</v>
+        <v>0.501639</v>
       </c>
       <c r="J286" s="7">
-        <v>2.871532</v>
+        <v>2.83683</v>
       </c>
       <c r="K286" s="7">
-        <v>10.447902</v>
+        <v>10.345291</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12027,25 +12027,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.027454</v>
+        <v>0.026484</v>
       </c>
       <c r="F287" s="7">
-        <v>0.076303</v>
+        <v>0.072729</v>
       </c>
       <c r="G287" s="7">
-        <v>0.204996</v>
+        <v>0.204482</v>
       </c>
       <c r="H287" s="7">
-        <v>0.151978</v>
+        <v>0.152202</v>
       </c>
       <c r="I287" s="7">
-        <v>0.464034</v>
+        <v>0.46354799999999996</v>
       </c>
       <c r="J287" s="7">
-        <v>2.9686660000000002</v>
+        <v>2.9694369999999997</v>
       </c>
       <c r="K287" s="7">
-        <v>5.333149</v>
+        <v>5.3343799999999995</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12062,25 +12062,25 @@
         <v>3</v>
       </c>
       <c r="E288" s="7">
-        <v>0.024579</v>
+        <v>0.026131</v>
       </c>
       <c r="F288" s="7">
-        <v>0.072033</v>
+        <v>0.068141</v>
       </c>
       <c r="G288" s="7">
-        <v>0.184332</v>
+        <v>0.18290299999999998</v>
       </c>
       <c r="H288" s="7">
-        <v>0.114211</v>
+        <v>0.11417899999999999</v>
       </c>
       <c r="I288" s="7">
-        <v>0.450601</v>
+        <v>0.448696</v>
       </c>
       <c r="J288" s="7">
-        <v>2.308982</v>
+        <v>2.308885</v>
       </c>
       <c r="K288" s="7">
-        <v>4.22752</v>
+        <v>4.227368</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12097,25 +12097,25 @@
         <v>5</v>
       </c>
       <c r="E289" s="7">
-        <v>0.017738</v>
+        <v>0.015912</v>
       </c>
       <c r="F289" s="7">
-        <v>0.026646999999999997</v>
+        <v>0.02629</v>
       </c>
       <c r="G289" s="7">
-        <v>0.084082</v>
+        <v>0.08250400000000001</v>
       </c>
       <c r="H289" s="7">
-        <v>0.045031999999999996</v>
+        <v>0.044755</v>
       </c>
       <c r="I289" s="7">
-        <v>0.267026</v>
+        <v>0.265464</v>
       </c>
       <c r="J289" s="7">
-        <v>1.8863740000000002</v>
+        <v>1.88561</v>
       </c>
       <c r="K289" s="7">
-        <v>5.770678</v>
+        <v>5.768886</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12132,25 +12132,25 @@
         <v>3</v>
       </c>
       <c r="E290" s="7">
-        <v>0.019051</v>
+        <v>0.022795999999999997</v>
       </c>
       <c r="F290" s="7">
-        <v>0.044977</v>
+        <v>0.044557</v>
       </c>
       <c r="G290" s="7">
-        <v>0.223721</v>
+        <v>0.22959700000000002</v>
       </c>
       <c r="H290" s="7">
-        <v>0.069161</v>
+        <v>0.07016700000000001</v>
       </c>
       <c r="I290" s="7">
-        <v>0.41779200000000005</v>
+        <v>0.417602</v>
       </c>
       <c r="J290" s="7">
-        <v>1.974391</v>
+        <v>1.97719</v>
       </c>
       <c r="K290" s="7">
-        <v>3.632832</v>
+        <v>3.63719</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12167,25 +12167,25 @@
         <v>5</v>
       </c>
       <c r="E291" s="7">
-        <v>0.039428</v>
+        <v>0.04211</v>
       </c>
       <c r="F291" s="7">
-        <v>0.068145</v>
+        <v>0.06423899999999999</v>
       </c>
       <c r="G291" s="7">
-        <v>0.265945</v>
+        <v>0.266302</v>
       </c>
       <c r="H291" s="7">
-        <v>0.191956</v>
+        <v>0.19189399999999998</v>
       </c>
       <c r="I291" s="7">
-        <v>0.511834</v>
+        <v>0.510699</v>
       </c>
       <c r="J291" s="7">
-        <v>2.63448</v>
+        <v>2.634293</v>
       </c>
       <c r="K291" s="7">
-        <v>9.469075</v>
+        <v>9.468537</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12202,25 +12202,25 @@
         <v>6</v>
       </c>
       <c r="E292" s="7">
-        <v>-0.009575</v>
+        <v>-0.005397</v>
       </c>
       <c r="F292" s="7">
-        <v>-0.07789</v>
+        <v>-0.067192</v>
       </c>
       <c r="G292" s="7">
-        <v>0.152238</v>
+        <v>0.127246</v>
       </c>
       <c r="H292" s="7">
-        <v>0.06340900000000001</v>
+        <v>0.062686</v>
       </c>
       <c r="I292" s="7">
-        <v>0.615455</v>
+        <v>0.606322</v>
       </c>
       <c r="J292" s="7">
-        <v>4.1687970000000005</v>
+        <v>4.165283</v>
       </c>
       <c r="K292" s="7">
-        <v>13.452620999999999</v>
+        <v>13.442795</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12237,25 +12237,25 @@
         <v>3</v>
       </c>
       <c r="E293" s="7">
-        <v>0.054376</v>
+        <v>0.042379</v>
       </c>
       <c r="F293" s="7">
-        <v>0.101005</v>
+        <v>0.09729900000000001</v>
       </c>
       <c r="G293" s="7">
-        <v>0.28945</v>
+        <v>0.288003</v>
       </c>
       <c r="H293" s="7">
-        <v>0.19567</v>
+        <v>0.194041</v>
       </c>
       <c r="I293" s="7">
-        <v>0.49160600000000004</v>
+        <v>0.48950499999999997</v>
       </c>
       <c r="J293" s="7">
-        <v>1.460028</v>
+        <v>1.456678</v>
       </c>
       <c r="K293" s="7">
-        <v>3.777515</v>
+        <v>3.771008</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12272,25 +12272,25 @@
         <v>6</v>
       </c>
       <c r="E294" s="7">
-        <v>0.040498000000000006</v>
+        <v>0.048041</v>
       </c>
       <c r="F294" s="7">
-        <v>0.01824</v>
+        <v>0.015498000000000001</v>
       </c>
       <c r="G294" s="7">
-        <v>0.296988</v>
+        <v>0.293094</v>
       </c>
       <c r="H294" s="7">
-        <v>0.20404599999999998</v>
+        <v>0.204466</v>
       </c>
       <c r="I294" s="7">
-        <v>0.524084</v>
+        <v>0.526169</v>
       </c>
       <c r="J294" s="7">
-        <v>2.451488</v>
+        <v>2.4526920000000003</v>
       </c>
       <c r="K294" s="7">
-        <v>10.518831</v>
+        <v>10.52285</v>
       </c>
     </row>
     <row r="295" spans="1:11" x14ac:dyDescent="0.25">
@@ -12307,25 +12307,25 @@
         <v>6</v>
       </c>
       <c r="E295" s="7">
-        <v>0.037271</v>
+        <v>0.048243</v>
       </c>
       <c r="F295" s="7">
-        <v>-0.013481</v>
+        <v>0.013505</v>
       </c>
       <c r="G295" s="7">
-        <v>0.28671</v>
+        <v>0.269449</v>
       </c>
       <c r="H295" s="7">
-        <v>0.154556</v>
+        <v>0.16176100000000002</v>
       </c>
       <c r="I295" s="7">
-        <v>0.874092</v>
+        <v>0.881174</v>
       </c>
       <c r="J295" s="7">
-        <v>4.3656880000000005</v>
+        <v>4.3991739999999995</v>
       </c>
       <c r="K295" s="7">
-        <v>8.767116999999999</v>
+        <v>8.828071999999999</v>
       </c>
     </row>
     <row r="296" spans="1:11" x14ac:dyDescent="0.25">
@@ -12342,25 +12342,25 @@
         <v>6</v>
       </c>
       <c r="E296" s="7">
-        <v>0.103904</v>
+        <v>0.1259</v>
       </c>
       <c r="F296" s="7">
-        <v>0.12986599999999998</v>
+        <v>0.149337</v>
       </c>
       <c r="G296" s="7">
-        <v>0.328776</v>
+        <v>0.360832</v>
       </c>
       <c r="H296" s="7">
-        <v>0.25264600000000004</v>
+        <v>0.276641</v>
       </c>
       <c r="I296" s="7">
-        <v>0.49445900000000004</v>
+        <v>0.526576</v>
       </c>
       <c r="J296" s="7">
-        <v>2.625403</v>
+        <v>2.694848</v>
       </c>
       <c r="K296" s="7">
-        <v>9.897442</v>
+        <v>10.106183</v>
       </c>
     </row>
     <row r="297" spans="1:11" x14ac:dyDescent="0.25">
@@ -12377,25 +12377,25 @@
         <v>6</v>
       </c>
       <c r="E297" s="7">
-        <v>0.061047000000000004</v>
+        <v>0.056336000000000004</v>
       </c>
       <c r="F297" s="7">
-        <v>0.015363</v>
+        <v>0.004472</v>
       </c>
       <c r="G297" s="7">
-        <v>0.359373</v>
+        <v>0.352118</v>
       </c>
       <c r="H297" s="7">
-        <v>0.256907</v>
+        <v>0.24912800000000002</v>
       </c>
       <c r="I297" s="7">
-        <v>0.392104</v>
+        <v>0.390187</v>
       </c>
       <c r="J297" s="7">
-        <v>2.51514</v>
+        <v>2.493386</v>
       </c>
       <c r="K297" s="7">
-        <v>12.696942</v>
+        <v>12.612176999999999</v>
       </c>
     </row>
     <row r="298" spans="1:11" x14ac:dyDescent="0.25">
@@ -12412,25 +12412,25 @@
         <v>4</v>
       </c>
       <c r="E298" s="7">
-        <v>0.046934</v>
+        <v>0.04785999999999999</v>
       </c>
       <c r="F298" s="7">
-        <v>0.07815699999999999</v>
+        <v>0.077043</v>
       </c>
       <c r="G298" s="7">
-        <v>0.25688700000000003</v>
+        <v>0.262556</v>
       </c>
       <c r="H298" s="7">
-        <v>0.195596</v>
+        <v>0.198446</v>
       </c>
       <c r="I298" s="7">
-        <v>0.545201</v>
+        <v>0.546213</v>
       </c>
       <c r="J298" s="7">
-        <v>2.542033</v>
+        <v>2.550474</v>
       </c>
       <c r="K298" s="7">
-        <v>6.4364729999999994</v>
+        <v>6.4541949999999995</v>
       </c>
     </row>
     <row r="299" spans="1:11" x14ac:dyDescent="0.25">
@@ -12447,25 +12447,25 @@
         <v>5</v>
       </c>
       <c r="E299" s="7">
-        <v>0.065179</v>
+        <v>0.054107</v>
       </c>
       <c r="F299" s="7">
-        <v>0.091879</v>
+        <v>0.08276</v>
       </c>
       <c r="G299" s="7">
-        <v>0.33265700000000004</v>
+        <v>0.329561</v>
       </c>
       <c r="H299" s="7">
-        <v>0.236268</v>
+        <v>0.22858499999999998</v>
       </c>
       <c r="I299" s="7">
-        <v>0.531691</v>
+        <v>0.520806</v>
       </c>
       <c r="J299" s="7">
-        <v>2.925384</v>
+        <v>2.9009910000000003</v>
       </c>
       <c r="K299" s="7">
-        <v>8.738185</v>
+        <v>8.677669</v>
       </c>
     </row>
     <row r="300" spans="1:11" x14ac:dyDescent="0.25">
@@ -12482,25 +12482,25 @@
         <v>4</v>
       </c>
       <c r="E300" s="7">
-        <v>0.044827000000000006</v>
+        <v>0.040505000000000006</v>
       </c>
       <c r="F300" s="7">
-        <v>0.075118</v>
+        <v>0.068412</v>
       </c>
       <c r="G300" s="7">
-        <v>0.268772</v>
+        <v>0.265321</v>
       </c>
       <c r="H300" s="7">
-        <v>0.152318</v>
+        <v>0.14722200000000002</v>
       </c>
       <c r="I300" s="7">
-        <v>0.41783299999999995</v>
+        <v>0.411584</v>
       </c>
       <c r="J300" s="7">
-        <v>1.6019919999999999</v>
+        <v>1.5904839999999998</v>
       </c>
       <c r="K300" s="7">
-        <v>4.233722</v>
+        <v>4.210575</v>
       </c>
     </row>
     <row r="301" spans="1:11" x14ac:dyDescent="0.25">
@@ -12517,25 +12517,25 @@
         <v>4</v>
       </c>
       <c r="E301" s="7">
-        <v>0.012565999999999999</v>
+        <v>0.016575</v>
       </c>
       <c r="F301" s="7">
-        <v>0.010845</v>
+        <v>0.007811</v>
       </c>
       <c r="G301" s="7">
-        <v>0.208856</v>
+        <v>0.20756699999999997</v>
       </c>
       <c r="H301" s="7">
-        <v>0.062804</v>
+        <v>0.061575</v>
       </c>
       <c r="I301" s="7">
-        <v>0.38406</v>
+        <v>0.38008699999999995</v>
       </c>
       <c r="J301" s="7">
-        <v>1.7635740000000002</v>
+        <v>1.7603790000000001</v>
       </c>
       <c r="K301" s="7">
-        <v>4.837552</v>
+        <v>4.830802</v>
       </c>
     </row>
     <row r="302" spans="1:11" x14ac:dyDescent="0.25">
@@ -12552,25 +12552,25 @@
         <v>6</v>
       </c>
       <c r="E302" s="7">
-        <v>0.046191</v>
+        <v>0.033159</v>
       </c>
       <c r="F302" s="7">
-        <v>0.04366</v>
+        <v>0.032232</v>
       </c>
       <c r="G302" s="7">
-        <v>0.370928</v>
+        <v>0.36209600000000003</v>
       </c>
       <c r="H302" s="7">
-        <v>0.283814</v>
+        <v>0.271924</v>
       </c>
       <c r="I302" s="7">
-        <v>0.522646</v>
+        <v>0.5206620000000001</v>
       </c>
       <c r="J302" s="7">
-        <v>3.4899169999999997</v>
+        <v>3.448334</v>
       </c>
       <c r="K302" s="7">
-        <v>15.706840999999999</v>
+        <v>15.552112999999999</v>
       </c>
     </row>
     <row r="303" spans="1:11" x14ac:dyDescent="0.25">
@@ -12587,25 +12587,25 @@
         <v>5</v>
       </c>
       <c r="E303" s="7">
-        <v>0.050391000000000005</v>
+        <v>0.040819999999999995</v>
       </c>
       <c r="F303" s="7">
-        <v>0.059668</v>
+        <v>0.054796</v>
       </c>
       <c r="G303" s="7">
-        <v>0.36154000000000003</v>
+        <v>0.35802500000000004</v>
       </c>
       <c r="H303" s="7">
-        <v>0.288236</v>
+        <v>0.282111</v>
       </c>
       <c r="I303" s="7">
-        <v>0.550328</v>
+        <v>0.550725</v>
       </c>
       <c r="J303" s="7">
-        <v>3.1600979999999996</v>
+        <v>3.1403179999999997</v>
       </c>
       <c r="K303" s="7">
-        <v>10.828843999999998</v>
+        <v>10.7726</v>
       </c>
     </row>
     <row r="304" spans="1:11" x14ac:dyDescent="0.25">
@@ -12622,25 +12622,25 @@
         <v>4</v>
       </c>
       <c r="E304" s="7">
-        <v>0.044517</v>
+        <v>0.035865999999999995</v>
       </c>
       <c r="F304" s="7">
-        <v>0.053415</v>
+        <v>0.049618999999999996</v>
       </c>
       <c r="G304" s="7">
-        <v>0.331541</v>
+        <v>0.3271</v>
       </c>
       <c r="H304" s="7">
-        <v>0.24882200000000002</v>
+        <v>0.243307</v>
       </c>
       <c r="I304" s="7">
-        <v>0.5496139999999999</v>
+        <v>0.546946</v>
       </c>
       <c r="J304" s="7">
-        <v>3.180365</v>
+        <v>3.1619029999999997</v>
       </c>
       <c r="K304" s="7">
-        <v>9.769259</v>
+        <v>9.721698</v>
       </c>
     </row>
     <row r="305" spans="1:11" x14ac:dyDescent="0.25">
@@ -12657,25 +12657,25 @@
         <v>2</v>
       </c>
       <c r="E305" s="7">
-        <v>0.027756</v>
+        <v>0.029775</v>
       </c>
       <c r="F305" s="7">
-        <v>0.09106</v>
+        <v>0.089224</v>
       </c>
       <c r="G305" s="7">
-        <v>0.22575199999999998</v>
+        <v>0.22665500000000002</v>
       </c>
       <c r="H305" s="7">
-        <v>0.155102</v>
+        <v>0.156518</v>
       </c>
       <c r="I305" s="7">
-        <v>0.504068</v>
+        <v>0.505595</v>
       </c>
       <c r="J305" s="7">
-        <v>2.823677</v>
+        <v>2.8283620000000003</v>
       </c>
       <c r="K305" s="7">
-        <v>5.145271</v>
+        <v>5.152800999999999</v>
       </c>
     </row>
     <row r="306" spans="1:11" x14ac:dyDescent="0.25">
@@ -12692,25 +12692,25 @@
         <v>5</v>
       </c>
       <c r="E306" s="7">
-        <v>0.071393</v>
+        <v>0.056359000000000006</v>
       </c>
       <c r="F306" s="7">
-        <v>0.11071099999999999</v>
+        <v>0.10269299999999999</v>
       </c>
       <c r="G306" s="7">
-        <v>0.39759700000000003</v>
+        <v>0.39453000000000005</v>
       </c>
       <c r="H306" s="7">
-        <v>0.30987</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="I306" s="7">
-        <v>0.6569320000000001</v>
+        <v>0.64711</v>
       </c>
       <c r="J306" s="7">
-        <v>3.2869729999999997</v>
+        <v>3.263178</v>
       </c>
       <c r="K306" s="7">
-        <v>9.995854000000001</v>
+        <v>9.934821</v>
       </c>
     </row>
     <row r="307" spans="1:11" x14ac:dyDescent="0.25">
@@ -12727,25 +12727,25 @@
         <v>6</v>
       </c>
       <c r="E307" s="7">
-        <v>0.080129</v>
+        <v>0.064385</v>
       </c>
       <c r="F307" s="7">
-        <v>0.10952999999999999</v>
+        <v>0.10139300000000001</v>
       </c>
       <c r="G307" s="7">
-        <v>0.43011000000000005</v>
+        <v>0.425441</v>
       </c>
       <c r="H307" s="7">
-        <v>0.336628</v>
+        <v>0.327611</v>
       </c>
       <c r="I307" s="7">
-        <v>0.713605</v>
+        <v>0.702072</v>
       </c>
       <c r="J307" s="7">
-        <v>3.555788</v>
+        <v>3.525055</v>
       </c>
       <c r="K307" s="7">
-        <v>12.800123000000001</v>
+        <v>12.707028000000001</v>
       </c>
     </row>
     <row r="308" spans="1:11" x14ac:dyDescent="0.25">
@@ -12762,25 +12762,25 @@
         <v>6</v>
       </c>
       <c r="E308" s="7">
-        <v>0.072505</v>
+        <v>0.06334100000000001</v>
       </c>
       <c r="F308" s="7">
-        <v>0.131327</v>
+        <v>0.116711</v>
       </c>
       <c r="G308" s="7">
-        <v>0.427224</v>
+        <v>0.417427</v>
       </c>
       <c r="H308" s="7">
-        <v>0.347413</v>
+        <v>0.33421999999999996</v>
       </c>
       <c r="I308" s="7">
-        <v>0.576864</v>
+        <v>0.5601550000000001</v>
       </c>
       <c r="J308" s="7">
-        <v>2.39654</v>
+        <v>2.3632839999999997</v>
       </c>
       <c r="K308" s="7">
-        <v>9.061947</v>
+        <v>8.963428</v>
       </c>
     </row>
     <row r="309" spans="1:11" x14ac:dyDescent="0.25">
@@ -12797,22 +12797,22 @@
         <v>4</v>
       </c>
       <c r="E309" s="7">
-        <v>0.20754999999999998</v>
+        <v>0.196386</v>
       </c>
       <c r="F309" s="7">
-        <v>0.282152</v>
+        <v>0.287814</v>
       </c>
       <c r="G309" s="7">
-        <v>0.380307</v>
+        <v>0.385661</v>
       </c>
       <c r="H309" s="7">
-        <v>0.35314999999999996</v>
+        <v>0.346252</v>
       </c>
       <c r="I309" s="7">
-        <v>0.7371460000000001</v>
+        <v>0.719902</v>
       </c>
       <c r="J309" s="7">
-        <v>3.802998</v>
+        <v>3.778514</v>
       </c>
       <c r="K309" s="7"/>
     </row>
@@ -12830,25 +12830,25 @@
         <v>5</v>
       </c>
       <c r="E310" s="7">
-        <v>0.043833000000000004</v>
+        <v>0.04460600000000001</v>
       </c>
       <c r="F310" s="7">
-        <v>0.040818</v>
+        <v>0.041422</v>
       </c>
       <c r="G310" s="7">
-        <v>0.324897</v>
+        <v>0.32804099999999997</v>
       </c>
       <c r="H310" s="7">
-        <v>0.211357</v>
+        <v>0.21080200000000002</v>
       </c>
       <c r="I310" s="7">
-        <v>0.45199199999999995</v>
+        <v>0.44717599999999996</v>
       </c>
       <c r="J310" s="7">
-        <v>2.511331</v>
+        <v>2.509724</v>
       </c>
       <c r="K310" s="7">
-        <v>11.494644000000001</v>
+        <v>11.488925</v>
       </c>
     </row>
     <row r="311" spans="1:11" x14ac:dyDescent="0.25">
@@ -12865,25 +12865,25 @@
         <v>6</v>
       </c>
       <c r="E311" s="7">
-        <v>0.021845</v>
+        <v>0.019541</v>
       </c>
       <c r="F311" s="7">
-        <v>0.03863</v>
+        <v>0.039432</v>
       </c>
       <c r="G311" s="7">
-        <v>0.08441599999999999</v>
+        <v>0.08392799999999999</v>
       </c>
       <c r="H311" s="7">
-        <v>0.058938</v>
+        <v>0.059210000000000006</v>
       </c>
       <c r="I311" s="7">
-        <v>0.229458</v>
+        <v>0.228295</v>
       </c>
       <c r="J311" s="7">
-        <v>1.790725</v>
+        <v>1.791439</v>
       </c>
       <c r="K311" s="7">
-        <v>5.538482</v>
+        <v>5.540156</v>
       </c>
     </row>
     <row r="312" spans="1:11" x14ac:dyDescent="0.25">
@@ -12900,25 +12900,25 @@
         <v>6</v>
       </c>
       <c r="E312" s="7">
-        <v>0.004357</v>
+        <v>0.001721</v>
       </c>
       <c r="F312" s="7">
-        <v>0.0030559999999999997</v>
+        <v>-0.0017150000000000002</v>
       </c>
       <c r="G312" s="7">
-        <v>0.209084</v>
+        <v>0.208686</v>
       </c>
       <c r="H312" s="7">
-        <v>0.105974</v>
+        <v>0.09796300000000001</v>
       </c>
       <c r="I312" s="7">
-        <v>0.438917</v>
+        <v>0.40946899999999997</v>
       </c>
       <c r="J312" s="7">
-        <v>2.265341</v>
+        <v>2.241689</v>
       </c>
       <c r="K312" s="7">
-        <v>7.627854</v>
+        <v>7.565359</v>
       </c>
     </row>
     <row r="313" spans="1:11" x14ac:dyDescent="0.25">
@@ -12935,25 +12935,25 @@
         <v>3</v>
       </c>
       <c r="E313" s="7">
-        <v>0.032972</v>
+        <v>0.031644</v>
       </c>
       <c r="F313" s="7">
-        <v>0.086621</v>
+        <v>0.08458500000000001</v>
       </c>
       <c r="G313" s="7">
-        <v>0.225546</v>
+        <v>0.222824</v>
       </c>
       <c r="H313" s="7">
-        <v>0.16239</v>
+        <v>0.16105699999999998</v>
       </c>
       <c r="I313" s="7">
-        <v>0.466226</v>
+        <v>0.462899</v>
       </c>
       <c r="J313" s="7">
-        <v>2.037872</v>
+        <v>2.034388</v>
       </c>
       <c r="K313" s="7">
-        <v>5.337408</v>
+        <v>5.33014</v>
       </c>
     </row>
     <row r="314" spans="1:11" x14ac:dyDescent="0.25">
@@ -12970,25 +12970,25 @@
         <v>3</v>
       </c>
       <c r="E314" s="7">
-        <v>0.015643</v>
+        <v>0.019844</v>
       </c>
       <c r="F314" s="7">
-        <v>0.023780000000000003</v>
+        <v>0.018722000000000003</v>
       </c>
       <c r="G314" s="7">
-        <v>0.151319</v>
+        <v>0.15398</v>
       </c>
       <c r="H314" s="7">
-        <v>0.046502999999999996</v>
+        <v>0.046388</v>
       </c>
       <c r="I314" s="7">
-        <v>0.38633</v>
+        <v>0.383386</v>
       </c>
       <c r="J314" s="7">
-        <v>1.0579479999999999</v>
+        <v>1.057723</v>
       </c>
       <c r="K314" s="7">
-        <v>2.12844</v>
+        <v>2.128097</v>
       </c>
     </row>
   </sheetData>

--- a/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
+++ b/app/fonlar/getiri/emeklilik-fonlari-getiri/data/emeklilik-fonlari-getiri.xlsx
@@ -19,7 +19,7 @@
     <t>Dışa Aktarım Tarihi:</t>
   </si>
   <si>
-    <t>14.05.2026 21:28:14</t>
+    <t>15.05.2026 18:50:37</t>
   </si>
   <si>
     <t>Toplam Kayıt Sayısı:</t>
@@ -2496,25 +2496,25 @@
         <v>4</v>
       </c>
       <c r="E6" s="7">
-        <v>0.020655999999999997</v>
+        <v>0.014994</v>
       </c>
       <c r="F6" s="7">
-        <v>0.033801</v>
+        <v>0.035062</v>
       </c>
       <c r="G6" s="7">
-        <v>0.211974</v>
+        <v>0.212449</v>
       </c>
       <c r="H6" s="7">
-        <v>0.117658</v>
+        <v>0.119022</v>
       </c>
       <c r="I6" s="7">
-        <v>0.43826</v>
+        <v>0.436445</v>
       </c>
       <c r="J6" s="7">
-        <v>2.233576</v>
+        <v>2.237522</v>
       </c>
       <c r="K6" s="7">
-        <v>5.725983</v>
+        <v>5.734190999999999</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -2531,25 +2531,25 @@
         <v>6</v>
       </c>
       <c r="E7" s="7">
-        <v>0.094871</v>
+        <v>0.088284</v>
       </c>
       <c r="F7" s="7">
-        <v>0.11196300000000001</v>
+        <v>0.12300900000000001</v>
       </c>
       <c r="G7" s="7">
-        <v>0.16547</v>
+        <v>0.203152</v>
       </c>
       <c r="H7" s="7">
-        <v>0.13107</v>
+        <v>0.14230600000000002</v>
       </c>
       <c r="I7" s="7">
-        <v>0.470998</v>
+        <v>0.479232</v>
       </c>
       <c r="J7" s="7">
-        <v>2.915127</v>
+        <v>2.954017</v>
       </c>
       <c r="K7" s="7">
-        <v>5.720612999999999</v>
+        <v>5.787371</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2566,25 +2566,25 @@
         <v>3</v>
       </c>
       <c r="E8" s="7">
-        <v>0.01542</v>
+        <v>0.002862</v>
       </c>
       <c r="F8" s="7">
-        <v>0.015537</v>
+        <v>0.012117</v>
       </c>
       <c r="G8" s="7">
-        <v>0.160215</v>
+        <v>0.153691</v>
       </c>
       <c r="H8" s="7">
-        <v>0.060823999999999996</v>
+        <v>0.057252</v>
       </c>
       <c r="I8" s="7">
-        <v>0.389451</v>
+        <v>0.383231</v>
       </c>
       <c r="J8" s="7">
-        <v>1.790425</v>
+        <v>1.781029</v>
       </c>
       <c r="K8" s="7">
-        <v>3.578269</v>
+        <v>3.562853</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -2601,25 +2601,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="7">
-        <v>0.038133</v>
+        <v>0.036723</v>
       </c>
       <c r="F9" s="7">
-        <v>0.042096999999999996</v>
+        <v>0.048731</v>
       </c>
       <c r="G9" s="7">
-        <v>0.334445</v>
+        <v>0.34647399999999995</v>
       </c>
       <c r="H9" s="7">
-        <v>0.269434</v>
+        <v>0.277515</v>
       </c>
       <c r="I9" s="7">
-        <v>0.5288309999999999</v>
+        <v>0.525942</v>
       </c>
       <c r="J9" s="7">
-        <v>2.992582</v>
+        <v>3.017997</v>
       </c>
       <c r="K9" s="7">
-        <v>10.380018</v>
+        <v>10.452459</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -2636,25 +2636,25 @@
         <v>6</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.010363</v>
+        <v>-0.021419</v>
       </c>
       <c r="F10" s="7">
-        <v>-0.07707499999999999</v>
+        <v>-0.078727</v>
       </c>
       <c r="G10" s="7">
-        <v>0.09890399999999999</v>
+        <v>0.111012</v>
       </c>
       <c r="H10" s="7">
-        <v>0.050789999999999995</v>
+        <v>0.048909</v>
       </c>
       <c r="I10" s="7">
-        <v>0.560421</v>
+        <v>0.567279</v>
       </c>
       <c r="J10" s="7">
-        <v>4.074175</v>
+        <v>4.065091</v>
       </c>
       <c r="K10" s="7">
-        <v>13.221871</v>
+        <v>13.19641</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -2671,25 +2671,25 @@
         <v>6</v>
       </c>
       <c r="E11" s="7">
-        <v>0.037932</v>
+        <v>0.038683999999999996</v>
       </c>
       <c r="F11" s="7">
-        <v>0.039367</v>
+        <v>0.047714</v>
       </c>
       <c r="G11" s="7">
-        <v>0.39021</v>
+        <v>0.40605800000000003</v>
       </c>
       <c r="H11" s="7">
-        <v>0.311977</v>
+        <v>0.322513</v>
       </c>
       <c r="I11" s="7">
-        <v>0.545792</v>
+        <v>0.553485</v>
       </c>
       <c r="J11" s="7">
-        <v>2.535066</v>
+        <v>2.5634550000000003</v>
       </c>
       <c r="K11" s="7">
-        <v>12.622046000000001</v>
+        <v>12.731442999999999</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -2706,25 +2706,25 @@
         <v>3</v>
       </c>
       <c r="E12" s="7">
-        <v>0.029859</v>
+        <v>0.026418</v>
       </c>
       <c r="F12" s="7">
-        <v>0.068462</v>
+        <v>0.069015</v>
       </c>
       <c r="G12" s="7">
-        <v>0.25712399999999996</v>
+        <v>0.25738700000000003</v>
       </c>
       <c r="H12" s="7">
-        <v>0.16034800000000002</v>
+        <v>0.16094899999999998</v>
       </c>
       <c r="I12" s="7">
-        <v>0.47856099999999996</v>
+        <v>0.47759999999999997</v>
       </c>
       <c r="J12" s="7">
-        <v>2.6034699999999997</v>
+        <v>2.605335</v>
       </c>
       <c r="K12" s="7">
-        <v>4.5595229999999995</v>
+        <v>4.5624009999999995</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2741,25 +2741,25 @@
         <v>6</v>
       </c>
       <c r="E13" s="7">
-        <v>0.030361</v>
+        <v>0.029054000000000003</v>
       </c>
       <c r="F13" s="7">
-        <v>0.03872</v>
+        <v>0.048097</v>
       </c>
       <c r="G13" s="7">
-        <v>0.431406</v>
+        <v>0.451805</v>
       </c>
       <c r="H13" s="7">
-        <v>0.313654</v>
+        <v>0.325514</v>
       </c>
       <c r="I13" s="7">
-        <v>0.5500849999999999</v>
+        <v>0.557681</v>
       </c>
       <c r="J13" s="7">
-        <v>2.689647</v>
+        <v>2.722957</v>
       </c>
       <c r="K13" s="7">
-        <v>10.447648</v>
+        <v>10.550995</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -2776,25 +2776,25 @@
         <v>5</v>
       </c>
       <c r="E14" s="7">
-        <v>0.027707000000000002</v>
+        <v>0.020904</v>
       </c>
       <c r="F14" s="7">
-        <v>0.014162</v>
+        <v>0.020519</v>
       </c>
       <c r="G14" s="7">
-        <v>0.261057</v>
+        <v>0.277785</v>
       </c>
       <c r="H14" s="7">
-        <v>0.193981</v>
+        <v>0.201466</v>
       </c>
       <c r="I14" s="7">
-        <v>0.45217799999999997</v>
+        <v>0.466146</v>
       </c>
       <c r="J14" s="7">
-        <v>2.566045</v>
+        <v>2.588399</v>
       </c>
       <c r="K14" s="7">
-        <v>8.018871</v>
+        <v>8.075405</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -2811,25 +2811,25 @@
         <v>4</v>
       </c>
       <c r="E15" s="7">
-        <v>0.014542999999999999</v>
+        <v>0.007548</v>
       </c>
       <c r="F15" s="7">
-        <v>0.020571000000000002</v>
+        <v>0.020447000000000003</v>
       </c>
       <c r="G15" s="7">
-        <v>0.19528500000000001</v>
+        <v>0.194296</v>
       </c>
       <c r="H15" s="7">
-        <v>0.09052099999999999</v>
+        <v>0.090388</v>
       </c>
       <c r="I15" s="7">
-        <v>0.39299799999999996</v>
+        <v>0.391011</v>
       </c>
       <c r="J15" s="7">
-        <v>2.014271</v>
+        <v>2.013903</v>
       </c>
       <c r="K15" s="7">
-        <v>5.544328</v>
+        <v>5.54353</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -2846,25 +2846,25 @@
         <v>2</v>
       </c>
       <c r="E16" s="7">
-        <v>0.030364</v>
+        <v>0.026646</v>
       </c>
       <c r="F16" s="7">
-        <v>0.086328</v>
+        <v>0.087039</v>
       </c>
       <c r="G16" s="7">
-        <v>0.22738499999999998</v>
+        <v>0.22549</v>
       </c>
       <c r="H16" s="7">
-        <v>0.155422</v>
+        <v>0.156179</v>
       </c>
       <c r="I16" s="7">
-        <v>0.5050209999999999</v>
+        <v>0.503885</v>
       </c>
       <c r="J16" s="7">
-        <v>2.801939</v>
+        <v>2.8044290000000003</v>
       </c>
       <c r="K16" s="7">
-        <v>5.097401</v>
+        <v>5.101395</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2881,25 +2881,25 @@
         <v>3</v>
       </c>
       <c r="E17" s="7">
-        <v>0.029660000000000002</v>
+        <v>0.027468</v>
       </c>
       <c r="F17" s="7">
-        <v>0.075106</v>
+        <v>0.077308</v>
       </c>
       <c r="G17" s="7">
-        <v>0.20718699999999998</v>
+        <v>0.207674</v>
       </c>
       <c r="H17" s="7">
-        <v>0.148775</v>
+        <v>0.151128</v>
       </c>
       <c r="I17" s="7">
-        <v>0.414225</v>
+        <v>0.41682600000000003</v>
       </c>
       <c r="J17" s="7">
-        <v>1.795967</v>
+        <v>1.801695</v>
       </c>
       <c r="K17" s="7">
-        <v>4.570882</v>
+        <v>4.582294</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2916,25 +2916,25 @@
         <v>6</v>
       </c>
       <c r="E18" s="7">
-        <v>-0.000841</v>
+        <v>-0.010809</v>
       </c>
       <c r="F18" s="7">
-        <v>-0.05867</v>
+        <v>-0.059581</v>
       </c>
       <c r="G18" s="7">
-        <v>0.150045</v>
+        <v>0.162502</v>
       </c>
       <c r="H18" s="7">
-        <v>0.078709</v>
+        <v>0.077664</v>
       </c>
       <c r="I18" s="7">
-        <v>0.679279</v>
+        <v>0.683894</v>
       </c>
       <c r="J18" s="7">
-        <v>4.8609919999999995</v>
+        <v>4.855314</v>
       </c>
       <c r="K18" s="7">
-        <v>15.517076</v>
+        <v>15.501076000000001</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -2951,25 +2951,25 @@
         <v>6</v>
       </c>
       <c r="E19" s="7">
-        <v>0.041035</v>
+        <v>0.043001</v>
       </c>
       <c r="F19" s="7">
-        <v>0.045988</v>
+        <v>0.051372999999999995</v>
       </c>
       <c r="G19" s="7">
-        <v>0.279481</v>
+        <v>0.296954</v>
       </c>
       <c r="H19" s="7">
-        <v>0.14644500000000002</v>
+        <v>0.152347</v>
       </c>
       <c r="I19" s="7">
-        <v>0.44242800000000004</v>
+        <v>0.45063499999999995</v>
       </c>
       <c r="J19" s="7">
-        <v>2.330935</v>
+        <v>2.348082</v>
       </c>
       <c r="K19" s="7">
-        <v>7.048695</v>
+        <v>7.090127</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2986,25 +2986,25 @@
         <v>3</v>
       </c>
       <c r="E20" s="7">
-        <v>0.035663</v>
+        <v>0.039754</v>
       </c>
       <c r="F20" s="7">
-        <v>0.09562799999999999</v>
+        <v>0.10243000000000001</v>
       </c>
       <c r="G20" s="7">
-        <v>0.266696</v>
+        <v>0.27495</v>
       </c>
       <c r="H20" s="7">
-        <v>0.116947</v>
+        <v>0.12388</v>
       </c>
       <c r="I20" s="7">
-        <v>0.457571</v>
+        <v>0.467822</v>
       </c>
       <c r="J20" s="7">
-        <v>1.612406</v>
+        <v>1.6286230000000002</v>
       </c>
       <c r="K20" s="7">
-        <v>4.257523</v>
+        <v>4.29016</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -3021,25 +3021,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="7">
-        <v>0.029763</v>
+        <v>0.027603</v>
       </c>
       <c r="F21" s="7">
-        <v>0.090406</v>
+        <v>0.09323100000000001</v>
       </c>
       <c r="G21" s="7">
-        <v>0.230988</v>
+        <v>0.233955</v>
       </c>
       <c r="H21" s="7">
-        <v>0.16886600000000002</v>
+        <v>0.171893</v>
       </c>
       <c r="I21" s="7">
-        <v>0.435676</v>
+        <v>0.44055700000000003</v>
       </c>
       <c r="J21" s="7">
-        <v>2.078247</v>
+        <v>2.08622</v>
       </c>
       <c r="K21" s="7">
-        <v>5.061406</v>
+        <v>5.077106</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -3056,25 +3056,25 @@
         <v>6</v>
       </c>
       <c r="E22" s="7">
-        <v>0.074552</v>
+        <v>0.076572</v>
       </c>
       <c r="F22" s="7">
-        <v>0.10754799999999999</v>
+        <v>0.11754899999999999</v>
       </c>
       <c r="G22" s="7">
-        <v>0.381113</v>
+        <v>0.40794600000000003</v>
       </c>
       <c r="H22" s="7">
-        <v>0.313956</v>
+        <v>0.32582</v>
       </c>
       <c r="I22" s="7">
-        <v>0.592186</v>
+        <v>0.605999</v>
       </c>
       <c r="J22" s="7">
-        <v>3.050812</v>
+        <v>3.087387</v>
       </c>
       <c r="K22" s="7">
-        <v>11.020942999999999</v>
+        <v>11.129482000000001</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -3091,25 +3091,25 @@
         <v>3</v>
       </c>
       <c r="E23" s="7">
-        <v>0.030417</v>
+        <v>0.030451000000000002</v>
       </c>
       <c r="F23" s="7">
-        <v>0.081509</v>
+        <v>0.08290800000000001</v>
       </c>
       <c r="G23" s="7">
-        <v>0.18694299999999997</v>
+        <v>0.185632</v>
       </c>
       <c r="H23" s="7">
-        <v>0.135206</v>
+        <v>0.136675</v>
       </c>
       <c r="I23" s="7">
-        <v>0.40713900000000003</v>
+        <v>0.40820999999999996</v>
       </c>
       <c r="J23" s="7">
-        <v>2.354451</v>
+        <v>2.3587919999999998</v>
       </c>
       <c r="K23" s="7">
-        <v>5.027335</v>
+        <v>5.035135</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -3126,25 +3126,25 @@
         <v>3</v>
       </c>
       <c r="E24" s="7">
-        <v>0.015124</v>
+        <v>0.004225</v>
       </c>
       <c r="F24" s="7">
-        <v>0.015347999999999999</v>
+        <v>0.013635</v>
       </c>
       <c r="G24" s="7">
-        <v>0.151297</v>
+        <v>0.14674099999999998</v>
       </c>
       <c r="H24" s="7">
-        <v>0.046931</v>
+        <v>0.045166000000000005</v>
       </c>
       <c r="I24" s="7">
-        <v>0.377604</v>
+        <v>0.375998</v>
       </c>
       <c r="J24" s="7">
-        <v>1.6135480000000002</v>
+        <v>1.6091399999999998</v>
       </c>
       <c r="K24" s="7">
-        <v>3.436396</v>
+        <v>3.428913</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -3161,25 +3161,25 @@
         <v>6</v>
       </c>
       <c r="E25" s="7">
-        <v>0.016696</v>
+        <v>0.010987</v>
       </c>
       <c r="F25" s="7">
-        <v>0.031318</v>
+        <v>0.032264</v>
       </c>
       <c r="G25" s="7">
-        <v>0.12349199999999999</v>
+        <v>0.12385199999999999</v>
       </c>
       <c r="H25" s="7">
-        <v>0.063999</v>
+        <v>0.064976</v>
       </c>
       <c r="I25" s="7">
-        <v>0.332988</v>
+        <v>0.33317</v>
       </c>
       <c r="J25" s="7">
-        <v>2.0412690000000002</v>
+        <v>2.044061</v>
       </c>
       <c r="K25" s="7">
-        <v>6.359114</v>
+        <v>6.36587</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -3196,25 +3196,25 @@
         <v>6</v>
       </c>
       <c r="E26" s="7">
-        <v>0.015470999999999999</v>
+        <v>0.005056000000000001</v>
       </c>
       <c r="F26" s="7">
-        <v>0.019370000000000002</v>
+        <v>0.020379</v>
       </c>
       <c r="G26" s="7">
-        <v>0.11583199999999999</v>
+        <v>0.114625</v>
       </c>
       <c r="H26" s="7">
-        <v>0.061581000000000004</v>
+        <v>0.06263200000000001</v>
       </c>
       <c r="I26" s="7">
-        <v>0.319787</v>
+        <v>0.31073</v>
       </c>
       <c r="J26" s="7">
-        <v>2.0865549999999997</v>
+        <v>2.08961</v>
       </c>
       <c r="K26" s="7">
-        <v>5.557449</v>
+        <v>5.563939</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -3231,25 +3231,25 @@
         <v>6</v>
       </c>
       <c r="E27" s="7">
-        <v>0.026810999999999998</v>
+        <v>0.021304</v>
       </c>
       <c r="F27" s="7">
-        <v>-0.017363</v>
+        <v>-0.01264</v>
       </c>
       <c r="G27" s="7">
-        <v>0.278856</v>
+        <v>0.292906</v>
       </c>
       <c r="H27" s="7">
-        <v>0.22367</v>
+        <v>0.229551</v>
       </c>
       <c r="I27" s="7">
-        <v>0.379295</v>
+        <v>0.38819499999999996</v>
       </c>
       <c r="J27" s="7">
-        <v>3.073997</v>
+        <v>3.093578</v>
       </c>
       <c r="K27" s="7">
-        <v>16.155577</v>
+        <v>16.238033</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -3266,25 +3266,25 @@
         <v>5</v>
       </c>
       <c r="E28" s="7">
-        <v>0.058266</v>
+        <v>0.047734</v>
       </c>
       <c r="F28" s="7">
-        <v>0.057795</v>
+        <v>0.066364</v>
       </c>
       <c r="G28" s="7">
-        <v>0.160246</v>
+        <v>0.18619</v>
       </c>
       <c r="H28" s="7">
-        <v>0.125593</v>
+        <v>0.134711</v>
       </c>
       <c r="I28" s="7">
-        <v>0.397196</v>
+        <v>0.399674</v>
       </c>
       <c r="J28" s="7">
-        <v>2.529902</v>
+        <v>2.558497</v>
       </c>
       <c r="K28" s="7">
-        <v>8.004658</v>
+        <v>8.077602</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -3301,25 +3301,25 @@
         <v>2</v>
       </c>
       <c r="E29" s="7">
-        <v>0.023124</v>
+        <v>0.019012</v>
       </c>
       <c r="F29" s="7">
-        <v>0.045011</v>
+        <v>0.045884999999999995</v>
       </c>
       <c r="G29" s="7">
-        <v>0.177714</v>
+        <v>0.17702400000000001</v>
       </c>
       <c r="H29" s="7">
-        <v>0.11166999999999999</v>
+        <v>0.112599</v>
       </c>
       <c r="I29" s="7">
-        <v>0.400439</v>
+        <v>0.400796</v>
       </c>
       <c r="J29" s="7">
-        <v>2.396021</v>
+        <v>2.39886</v>
       </c>
       <c r="K29" s="7">
-        <v>4.602839</v>
+        <v>4.607521</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3336,25 +3336,25 @@
         <v>5</v>
       </c>
       <c r="E30" s="7">
-        <v>0.032129</v>
+        <v>0.026722000000000003</v>
       </c>
       <c r="F30" s="7">
-        <v>0.012541</v>
+        <v>0.01539</v>
       </c>
       <c r="G30" s="7">
-        <v>0.223751</v>
+        <v>0.23123100000000002</v>
       </c>
       <c r="H30" s="7">
-        <v>0.176883</v>
+        <v>0.18019400000000002</v>
       </c>
       <c r="I30" s="7">
-        <v>0.377794</v>
+        <v>0.382408</v>
       </c>
       <c r="J30" s="7">
-        <v>2.9634500000000004</v>
+        <v>2.974602</v>
       </c>
       <c r="K30" s="7">
-        <v>9.610966</v>
+        <v>9.640823000000001</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -3371,25 +3371,25 @@
         <v>6</v>
       </c>
       <c r="E31" s="7">
-        <v>0.042823</v>
+        <v>0.039124</v>
       </c>
       <c r="F31" s="7">
-        <v>-0.016268</v>
+        <v>-0.007802</v>
       </c>
       <c r="G31" s="7">
-        <v>0.315874</v>
+        <v>0.334771</v>
       </c>
       <c r="H31" s="7">
-        <v>0.234024</v>
+        <v>0.24464300000000003</v>
       </c>
       <c r="I31" s="7">
-        <v>0.347651</v>
+        <v>0.354124</v>
       </c>
       <c r="J31" s="7">
-        <v>2.461935</v>
+        <v>2.491727</v>
       </c>
       <c r="K31" s="7">
-        <v>14.448904</v>
+        <v>14.581852</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3406,25 +3406,25 @@
         <v>2</v>
       </c>
       <c r="E32" s="7">
-        <v>0.030042</v>
+        <v>0.029754999999999997</v>
       </c>
       <c r="F32" s="7">
-        <v>0.08585100000000001</v>
+        <v>0.086874</v>
       </c>
       <c r="G32" s="7">
-        <v>0.19513000000000003</v>
+        <v>0.192121</v>
       </c>
       <c r="H32" s="7">
-        <v>0.130436</v>
+        <v>0.131501</v>
       </c>
       <c r="I32" s="7">
-        <v>0.448164</v>
+        <v>0.447888</v>
       </c>
       <c r="J32" s="7">
-        <v>2.167104</v>
+        <v>2.170087</v>
       </c>
       <c r="K32" s="7">
-        <v>3.7584410000000004</v>
+        <v>3.762924</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -3441,25 +3441,25 @@
         <v>6</v>
       </c>
       <c r="E33" s="7">
-        <v>0.020323</v>
+        <v>0.014529</v>
       </c>
       <c r="F33" s="7">
-        <v>-0.008365000000000001</v>
+        <v>-0.0012989999999999998</v>
       </c>
       <c r="G33" s="7">
-        <v>0.28474299999999997</v>
+        <v>0.302782</v>
       </c>
       <c r="H33" s="7">
-        <v>0.198512</v>
+        <v>0.20705300000000001</v>
       </c>
       <c r="I33" s="7">
-        <v>0.400194</v>
+        <v>0.410916</v>
       </c>
       <c r="J33" s="7">
-        <v>3.3292759999999997</v>
+        <v>3.360126</v>
       </c>
       <c r="K33" s="7">
-        <v>16.441612</v>
+        <v>16.565898999999998</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -3476,25 +3476,25 @@
         <v>5</v>
       </c>
       <c r="E34" s="7">
-        <v>0.059632</v>
+        <v>0.062937</v>
       </c>
       <c r="F34" s="7">
-        <v>0.106192</v>
+        <v>0.11381999999999999</v>
       </c>
       <c r="G34" s="7">
-        <v>0.39900399999999997</v>
+        <v>0.41287999999999997</v>
       </c>
       <c r="H34" s="7">
-        <v>0.30949000000000004</v>
+        <v>0.31852</v>
       </c>
       <c r="I34" s="7">
-        <v>0.644071</v>
+        <v>0.653772</v>
       </c>
       <c r="J34" s="7">
-        <v>3.2753840000000003</v>
+        <v>3.304866</v>
       </c>
       <c r="K34" s="7">
-        <v>9.951131</v>
+        <v>10.026647</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -3511,25 +3511,25 @@
         <v>6</v>
       </c>
       <c r="E35" s="7">
-        <v>0.06472800000000001</v>
+        <v>0.069507</v>
       </c>
       <c r="F35" s="7">
-        <v>0.103497</v>
+        <v>0.113682</v>
       </c>
       <c r="G35" s="7">
-        <v>0.42563</v>
+        <v>0.448365</v>
       </c>
       <c r="H35" s="7">
-        <v>0.328001</v>
+        <v>0.34025700000000003</v>
       </c>
       <c r="I35" s="7">
-        <v>0.706202</v>
+        <v>0.720276</v>
       </c>
       <c r="J35" s="7">
-        <v>3.524756</v>
+        <v>3.566517</v>
       </c>
       <c r="K35" s="7">
-        <v>12.592235</v>
+        <v>12.717682</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -3546,25 +3546,25 @@
         <v>6</v>
       </c>
       <c r="E36" s="7">
-        <v>0.012683</v>
+        <v>0.0070220000000000005</v>
       </c>
       <c r="F36" s="7">
-        <v>-0.010883</v>
+        <v>-0.003886</v>
       </c>
       <c r="G36" s="7">
-        <v>0.289251</v>
+        <v>0.307259</v>
       </c>
       <c r="H36" s="7">
-        <v>0.204988</v>
+        <v>0.21351199999999998</v>
       </c>
       <c r="I36" s="7">
-        <v>0.412748</v>
+        <v>0.423491</v>
       </c>
       <c r="J36" s="7">
-        <v>3.3890429999999996</v>
+        <v>3.420089</v>
       </c>
       <c r="K36" s="7">
-        <v>16.913638000000002</v>
+        <v>17.040347999999998</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -3581,25 +3581,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="7">
-        <v>0.021505</v>
+        <v>0.016312</v>
       </c>
       <c r="F37" s="7">
-        <v>0.008239999999999999</v>
+        <v>0.013713999999999999</v>
       </c>
       <c r="G37" s="7">
-        <v>0.297196</v>
+        <v>0.31072500000000003</v>
       </c>
       <c r="H37" s="7">
-        <v>0.197468</v>
+        <v>0.20396899999999998</v>
       </c>
       <c r="I37" s="7">
-        <v>0.44445999999999997</v>
+        <v>0.453224</v>
       </c>
       <c r="J37" s="7">
-        <v>3.5122780000000002</v>
+        <v>3.5367759999999997</v>
       </c>
       <c r="K37" s="7">
-        <v>15.551261</v>
+        <v>15.641123</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -3616,25 +3616,25 @@
         <v>4</v>
       </c>
       <c r="E38" s="7">
-        <v>0.021653</v>
+        <v>0.01755</v>
       </c>
       <c r="F38" s="7">
-        <v>0.010383</v>
+        <v>0.014593</v>
       </c>
       <c r="G38" s="7">
-        <v>0.259006</v>
+        <v>0.270023</v>
       </c>
       <c r="H38" s="7">
-        <v>0.174713</v>
+        <v>0.179607</v>
       </c>
       <c r="I38" s="7">
-        <v>0.44210900000000003</v>
+        <v>0.448071</v>
       </c>
       <c r="J38" s="7">
-        <v>3.414476</v>
+        <v>3.4328680000000005</v>
       </c>
       <c r="K38" s="7">
-        <v>11.572294</v>
+        <v>11.624674</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -3651,25 +3651,25 @@
         <v>2</v>
       </c>
       <c r="E39" s="7">
-        <v>0.020981999999999997</v>
+        <v>0.017069</v>
       </c>
       <c r="F39" s="7">
-        <v>0.055617</v>
+        <v>0.056216999999999996</v>
       </c>
       <c r="G39" s="7">
-        <v>0.196133</v>
+        <v>0.19536</v>
       </c>
       <c r="H39" s="7">
-        <v>0.132284</v>
+        <v>0.132928</v>
       </c>
       <c r="I39" s="7">
-        <v>0.45426900000000003</v>
+        <v>0.454166</v>
       </c>
       <c r="J39" s="7">
-        <v>2.959013</v>
+        <v>2.961265</v>
       </c>
       <c r="K39" s="7">
-        <v>5.728944</v>
+        <v>5.732773</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -3686,25 +3686,25 @@
         <v>6</v>
       </c>
       <c r="E40" s="7">
-        <v>0.049532999999999994</v>
+        <v>0.046805000000000006</v>
       </c>
       <c r="F40" s="7">
-        <v>0.116016</v>
+        <v>0.124032</v>
       </c>
       <c r="G40" s="7">
-        <v>0.37331600000000004</v>
+        <v>0.389913</v>
       </c>
       <c r="H40" s="7">
-        <v>0.277459</v>
+        <v>0.28663299999999997</v>
       </c>
       <c r="I40" s="7">
-        <v>0.589095</v>
+        <v>0.603311</v>
       </c>
       <c r="J40" s="7">
-        <v>3.4410030000000003</v>
+        <v>3.472899</v>
       </c>
       <c r="K40" s="7">
-        <v>11.832989</v>
+        <v>11.925155</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -3721,25 +3721,25 @@
         <v>5</v>
       </c>
       <c r="E41" s="7">
-        <v>0.039091999999999995</v>
+        <v>0.034926</v>
       </c>
       <c r="F41" s="7">
-        <v>0.10230800000000001</v>
+        <v>0.10758100000000001</v>
       </c>
       <c r="G41" s="7">
-        <v>0.334557</v>
+        <v>0.345131</v>
       </c>
       <c r="H41" s="7">
-        <v>0.246464</v>
+        <v>0.252427</v>
       </c>
       <c r="I41" s="7">
-        <v>0.566978</v>
+        <v>0.577765</v>
       </c>
       <c r="J41" s="7">
-        <v>3.226633</v>
+        <v>3.2468540000000004</v>
       </c>
       <c r="K41" s="7">
-        <v>10.070484</v>
+        <v>10.123446</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
@@ -3756,25 +3756,25 @@
         <v>5</v>
       </c>
       <c r="E42" s="7">
-        <v>0.04441900000000001</v>
+        <v>0.043046</v>
       </c>
       <c r="F42" s="7">
-        <v>0.054664000000000004</v>
+        <v>0.061596000000000005</v>
       </c>
       <c r="G42" s="7">
-        <v>0.35531399999999996</v>
+        <v>0.367057</v>
       </c>
       <c r="H42" s="7">
-        <v>0.27979299999999996</v>
+        <v>0.288204</v>
       </c>
       <c r="I42" s="7">
-        <v>0.551196</v>
+        <v>0.554798</v>
       </c>
       <c r="J42" s="7">
-        <v>3.037532</v>
+        <v>3.064069</v>
       </c>
       <c r="K42" s="7">
-        <v>10.827215</v>
+        <v>10.904952000000002</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -3791,25 +3791,25 @@
         <v>6</v>
       </c>
       <c r="E43" s="7">
-        <v>0.009926</v>
+        <v>0.006214</v>
       </c>
       <c r="F43" s="7">
-        <v>-0.016546</v>
+        <v>-0.009597</v>
       </c>
       <c r="G43" s="7">
-        <v>0.297964</v>
+        <v>0.31455500000000003</v>
       </c>
       <c r="H43" s="7">
-        <v>0.20904499999999998</v>
+        <v>0.217588</v>
       </c>
       <c r="I43" s="7">
-        <v>0.418997</v>
+        <v>0.427389</v>
       </c>
       <c r="J43" s="7">
-        <v>3.845773</v>
+        <v>3.880011</v>
       </c>
       <c r="K43" s="7">
-        <v>21.145262</v>
+        <v>21.30173</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -3826,25 +3826,25 @@
         <v>2</v>
       </c>
       <c r="E44" s="7">
-        <v>0.030363</v>
+        <v>0.026522</v>
       </c>
       <c r="F44" s="7">
-        <v>0.064013</v>
+        <v>0.064357</v>
       </c>
       <c r="G44" s="7">
-        <v>0.20434000000000002</v>
+        <v>0.202565</v>
       </c>
       <c r="H44" s="7">
-        <v>0.132982</v>
+        <v>0.133349</v>
       </c>
       <c r="I44" s="7">
-        <v>0.47216299999999994</v>
+        <v>0.471676</v>
       </c>
       <c r="J44" s="7">
-        <v>2.490832</v>
+        <v>2.491961</v>
       </c>
       <c r="K44" s="7">
-        <v>4.500407</v>
+        <v>4.502185</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3861,25 +3861,25 @@
         <v>4</v>
       </c>
       <c r="E45" s="7">
-        <v>0.034032</v>
+        <v>0.034398</v>
       </c>
       <c r="F45" s="7">
-        <v>0.050786</v>
+        <v>0.057995</v>
       </c>
       <c r="G45" s="7">
-        <v>0.32055100000000003</v>
+        <v>0.332694</v>
       </c>
       <c r="H45" s="7">
-        <v>0.23693799999999998</v>
+        <v>0.245425</v>
       </c>
       <c r="I45" s="7">
-        <v>0.546156</v>
+        <v>0.5542560000000001</v>
       </c>
       <c r="J45" s="7">
-        <v>3.148385</v>
+        <v>3.176848</v>
       </c>
       <c r="K45" s="7">
-        <v>9.513394</v>
+        <v>9.58553</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3896,25 +3896,25 @@
         <v>5</v>
       </c>
       <c r="E46" s="7">
-        <v>0.040351</v>
+        <v>0.037946</v>
       </c>
       <c r="F46" s="7">
-        <v>0.10702099999999999</v>
+        <v>0.113051</v>
       </c>
       <c r="G46" s="7">
-        <v>0.357046</v>
+        <v>0.370047</v>
       </c>
       <c r="H46" s="7">
-        <v>0.284726</v>
+        <v>0.291725</v>
       </c>
       <c r="I46" s="7">
-        <v>0.588225</v>
+        <v>0.601961</v>
       </c>
       <c r="J46" s="7">
-        <v>3.620534</v>
+        <v>3.645705</v>
       </c>
       <c r="K46" s="7">
-        <v>10.361732</v>
+        <v>10.423627</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3931,25 +3931,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="7">
-        <v>0.051980000000000005</v>
+        <v>0.049264999999999996</v>
       </c>
       <c r="F47" s="7">
-        <v>0.100834</v>
+        <v>0.10794000000000001</v>
       </c>
       <c r="G47" s="7">
-        <v>0.371265</v>
+        <v>0.387345</v>
       </c>
       <c r="H47" s="7">
-        <v>0.29025</v>
+        <v>0.298579</v>
       </c>
       <c r="I47" s="7">
-        <v>0.579518</v>
+        <v>0.589285</v>
       </c>
       <c r="J47" s="7">
-        <v>3.646063</v>
+        <v>3.676057</v>
       </c>
       <c r="K47" s="7">
-        <v>13.196632999999999</v>
+        <v>13.288285</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -3966,25 +3966,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.027195</v>
+        <v>-0.032428</v>
       </c>
       <c r="F48" s="7">
-        <v>-0.057493999999999996</v>
+        <v>-0.05588</v>
       </c>
       <c r="G48" s="7">
-        <v>0.18062899999999998</v>
+        <v>0.180687</v>
       </c>
       <c r="H48" s="7">
-        <v>0.13018000000000002</v>
+        <v>0.13211499999999998</v>
       </c>
       <c r="I48" s="7">
-        <v>0.34307699999999997</v>
+        <v>0.34036900000000003</v>
       </c>
       <c r="J48" s="7">
-        <v>1.5955840000000001</v>
+        <v>1.600027</v>
       </c>
       <c r="K48" s="7">
-        <v>10.056227</v>
+        <v>10.075154</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -4001,25 +4001,25 @@
         <v>6</v>
       </c>
       <c r="E49" s="7">
-        <v>0.033739</v>
+        <v>0.033984</v>
       </c>
       <c r="F49" s="7">
-        <v>0.033654</v>
+        <v>0.04216</v>
       </c>
       <c r="G49" s="7">
-        <v>0.37065</v>
+        <v>0.38683500000000004</v>
       </c>
       <c r="H49" s="7">
-        <v>0.277129</v>
+        <v>0.287638</v>
       </c>
       <c r="I49" s="7">
-        <v>0.536937</v>
+        <v>0.545385</v>
       </c>
       <c r="J49" s="7">
-        <v>3.5004090000000003</v>
+        <v>3.537441</v>
       </c>
       <c r="K49" s="7">
-        <v>15.738533</v>
+        <v>15.876267</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4036,25 +4036,25 @@
         <v>6</v>
       </c>
       <c r="E50" s="7">
-        <v>0.076028</v>
+        <v>0.070534</v>
       </c>
       <c r="F50" s="7">
-        <v>0.096678</v>
+        <v>0.105516</v>
       </c>
       <c r="G50" s="7">
-        <v>0.200402</v>
+        <v>0.227321</v>
       </c>
       <c r="H50" s="7">
-        <v>0.16005299999999997</v>
+        <v>0.16940100000000002</v>
       </c>
       <c r="I50" s="7">
-        <v>0.48136</v>
+        <v>0.48247799999999996</v>
       </c>
       <c r="J50" s="7">
-        <v>3.041953</v>
+        <v>3.0745240000000003</v>
       </c>
       <c r="K50" s="7">
-        <v>9.306658</v>
+        <v>9.389711</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4071,25 +4071,25 @@
         <v>5</v>
       </c>
       <c r="E51" s="7">
-        <v>0.021658</v>
+        <v>0.015714</v>
       </c>
       <c r="F51" s="7">
-        <v>0.0024560000000000003</v>
+        <v>0.005750999999999999</v>
       </c>
       <c r="G51" s="7">
-        <v>0.224827</v>
+        <v>0.231323</v>
       </c>
       <c r="H51" s="7">
-        <v>0.141859</v>
+        <v>0.145612</v>
       </c>
       <c r="I51" s="7">
-        <v>0.353466</v>
+        <v>0.35609</v>
       </c>
       <c r="J51" s="7">
-        <v>2.4618979999999997</v>
+        <v>2.473279</v>
       </c>
       <c r="K51" s="7">
-        <v>7.984983</v>
+        <v>8.01452</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -4106,25 +4106,25 @@
         <v>6</v>
       </c>
       <c r="E52" s="7">
-        <v>0.047759</v>
+        <v>0.048319</v>
       </c>
       <c r="F52" s="7">
-        <v>0.013139000000000001</v>
+        <v>0.020051</v>
       </c>
       <c r="G52" s="7">
-        <v>0.35090699999999997</v>
+        <v>0.37068100000000004</v>
       </c>
       <c r="H52" s="7">
-        <v>0.246636</v>
+        <v>0.25514</v>
       </c>
       <c r="I52" s="7">
-        <v>0.45651400000000003</v>
+        <v>0.467031</v>
       </c>
       <c r="J52" s="7">
-        <v>2.615986</v>
+        <v>2.640653</v>
       </c>
       <c r="K52" s="7">
-        <v>11.122031999999999</v>
+        <v>11.204726</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4141,25 +4141,25 @@
         <v>5</v>
       </c>
       <c r="E53" s="7">
-        <v>0.015164</v>
+        <v>0.009252</v>
       </c>
       <c r="F53" s="7">
-        <v>0.027709</v>
+        <v>0.028873000000000003</v>
       </c>
       <c r="G53" s="7">
-        <v>0.09934699999999999</v>
+        <v>0.101648</v>
       </c>
       <c r="H53" s="7">
-        <v>0.057276999999999995</v>
+        <v>0.058475</v>
       </c>
       <c r="I53" s="7">
-        <v>0.324754</v>
+        <v>0.324973</v>
       </c>
       <c r="J53" s="7">
-        <v>2.102999</v>
+        <v>2.1065139999999998</v>
       </c>
       <c r="K53" s="7">
-        <v>6.391439</v>
+        <v>6.399813</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4176,25 +4176,25 @@
         <v>6</v>
       </c>
       <c r="E54" s="7">
-        <v>0.015811</v>
+        <v>0.012475</v>
       </c>
       <c r="F54" s="7">
-        <v>0.0334</v>
+        <v>0.034378</v>
       </c>
       <c r="G54" s="7">
-        <v>0.09798899999999999</v>
+        <v>0.099407</v>
       </c>
       <c r="H54" s="7">
-        <v>0.061757</v>
+        <v>0.062761</v>
       </c>
       <c r="I54" s="7">
-        <v>0.292993</v>
+        <v>0.293479</v>
       </c>
       <c r="J54" s="7">
-        <v>2.027528</v>
+        <v>2.030393</v>
       </c>
       <c r="K54" s="7">
-        <v>6.217287</v>
+        <v>6.224115</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -4211,25 +4211,25 @@
         <v>6</v>
       </c>
       <c r="E55" s="7">
-        <v>0.001545</v>
+        <v>-0.008994</v>
       </c>
       <c r="F55" s="7">
-        <v>-0.055507999999999995</v>
+        <v>-0.056488</v>
       </c>
       <c r="G55" s="7">
-        <v>0.149868</v>
+        <v>0.166712</v>
       </c>
       <c r="H55" s="7">
-        <v>0.093919</v>
+        <v>0.09278399999999999</v>
       </c>
       <c r="I55" s="7">
-        <v>0.649637</v>
+        <v>0.6465089999999999</v>
       </c>
       <c r="J55" s="7">
-        <v>4.006455</v>
+        <v>4.001259</v>
       </c>
       <c r="K55" s="7">
-        <v>12.905939</v>
+        <v>12.891506</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -4246,25 +4246,25 @@
         <v>4</v>
       </c>
       <c r="E56" s="7">
-        <v>0.026962</v>
+        <v>0.021177</v>
       </c>
       <c r="F56" s="7">
-        <v>0.053132</v>
+        <v>0.055675999999999996</v>
       </c>
       <c r="G56" s="7">
-        <v>0.25871099999999997</v>
+        <v>0.263902</v>
       </c>
       <c r="H56" s="7">
-        <v>0.165932</v>
+        <v>0.168749</v>
       </c>
       <c r="I56" s="7">
-        <v>0.469318</v>
+        <v>0.473001</v>
       </c>
       <c r="J56" s="7">
-        <v>2.119869</v>
+        <v>2.127406</v>
       </c>
       <c r="K56" s="7">
-        <v>5.688586</v>
+        <v>5.704745</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -4281,25 +4281,25 @@
         <v>4</v>
       </c>
       <c r="E57" s="7">
-        <v>-0.0015279999999999998</v>
+        <v>-0.010824</v>
       </c>
       <c r="F57" s="7">
-        <v>-0.016789000000000002</v>
+        <v>-0.017048</v>
       </c>
       <c r="G57" s="7">
-        <v>0.141898</v>
+        <v>0.141828</v>
       </c>
       <c r="H57" s="7">
-        <v>0.06820999999999999</v>
+        <v>0.067928</v>
       </c>
       <c r="I57" s="7">
-        <v>0.34482100000000004</v>
+        <v>0.34774700000000003</v>
       </c>
       <c r="J57" s="7">
-        <v>1.362002</v>
+        <v>1.36138</v>
       </c>
       <c r="K57" s="7">
-        <v>3.4964479999999996</v>
+        <v>3.495264</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -4316,25 +4316,25 @@
         <v>4</v>
       </c>
       <c r="E58" s="7">
-        <v>0.036783</v>
+        <v>0.037921</v>
       </c>
       <c r="F58" s="7">
-        <v>0.052049000000000005</v>
+        <v>0.059427</v>
       </c>
       <c r="G58" s="7">
-        <v>0.33525799999999994</v>
+        <v>0.345675</v>
       </c>
       <c r="H58" s="7">
-        <v>0.24898499999999998</v>
+        <v>0.257744</v>
       </c>
       <c r="I58" s="7">
-        <v>0.550994</v>
+        <v>0.558963</v>
       </c>
       <c r="J58" s="7">
-        <v>3.124844</v>
+        <v>3.153772</v>
       </c>
       <c r="K58" s="7">
-        <v>9.58063</v>
+        <v>9.654833</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4351,25 +4351,25 @@
         <v>5</v>
       </c>
       <c r="E59" s="7">
-        <v>0.04155300000000001</v>
+        <v>0.042903000000000004</v>
       </c>
       <c r="F59" s="7">
-        <v>0.055119999999999995</v>
+        <v>0.063528</v>
       </c>
       <c r="G59" s="7">
-        <v>0.36384500000000003</v>
+        <v>0.377997</v>
       </c>
       <c r="H59" s="7">
-        <v>0.280893</v>
+        <v>0.29109999999999997</v>
       </c>
       <c r="I59" s="7">
-        <v>0.554722</v>
+        <v>0.5597610000000001</v>
       </c>
       <c r="J59" s="7">
-        <v>3.1205860000000003</v>
+        <v>3.153423</v>
       </c>
       <c r="K59" s="7">
-        <v>10.659063000000002</v>
+        <v>10.751975999999999</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -4386,25 +4386,25 @@
         <v>6</v>
       </c>
       <c r="E60" s="7">
-        <v>0.041219</v>
+        <v>0.035019999999999996</v>
       </c>
       <c r="F60" s="7">
-        <v>-0.019821</v>
+        <v>-0.016777</v>
       </c>
       <c r="G60" s="7">
-        <v>0.291169</v>
+        <v>0.307172</v>
       </c>
       <c r="H60" s="7">
-        <v>0.21851199999999998</v>
+        <v>0.22229700000000002</v>
       </c>
       <c r="I60" s="7">
-        <v>0.38974200000000003</v>
+        <v>0.39387700000000003</v>
       </c>
       <c r="J60" s="7">
-        <v>2.411019</v>
+        <v>2.4216130000000002</v>
       </c>
       <c r="K60" s="7">
-        <v>12.810302</v>
+        <v>12.853197</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -4421,25 +4421,25 @@
         <v>5</v>
       </c>
       <c r="E61" s="7">
-        <v>0.048749</v>
+        <v>0.047050999999999996</v>
       </c>
       <c r="F61" s="7">
-        <v>0.051254999999999995</v>
+        <v>0.06061</v>
       </c>
       <c r="G61" s="7">
-        <v>0.24749600000000002</v>
+        <v>0.277051</v>
       </c>
       <c r="H61" s="7">
-        <v>0.194375</v>
+        <v>0.205004</v>
       </c>
       <c r="I61" s="7">
-        <v>0.45241</v>
+        <v>0.460645</v>
       </c>
       <c r="J61" s="7">
-        <v>2.418535</v>
+        <v>2.448958</v>
       </c>
       <c r="K61" s="7">
-        <v>7.601464</v>
+        <v>7.678012</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -4456,25 +4456,25 @@
         <v>7</v>
       </c>
       <c r="E62" s="7">
-        <v>0.007446</v>
+        <v>0.001017</v>
       </c>
       <c r="F62" s="7">
-        <v>-0.057418</v>
+        <v>-0.056079</v>
       </c>
       <c r="G62" s="7">
-        <v>0.236479</v>
+        <v>0.240202</v>
       </c>
       <c r="H62" s="7">
-        <v>0.172068</v>
+        <v>0.173732</v>
       </c>
       <c r="I62" s="7">
-        <v>0.332804</v>
+        <v>0.33109</v>
       </c>
       <c r="J62" s="7">
-        <v>2.078821</v>
+        <v>2.083194</v>
       </c>
       <c r="K62" s="7">
-        <v>12.188082999999999</v>
+        <v>12.206813</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -4491,25 +4491,25 @@
         <v>4</v>
       </c>
       <c r="E63" s="7">
-        <v>0.015242</v>
+        <v>0.008023</v>
       </c>
       <c r="F63" s="7">
-        <v>0.008796</v>
+        <v>0.009521</v>
       </c>
       <c r="G63" s="7">
-        <v>0.192411</v>
+        <v>0.192497</v>
       </c>
       <c r="H63" s="7">
-        <v>0.097527</v>
+        <v>0.098315</v>
       </c>
       <c r="I63" s="7">
-        <v>0.38624899999999995</v>
+        <v>0.387101</v>
       </c>
       <c r="J63" s="7">
-        <v>1.925766</v>
+        <v>1.927869</v>
       </c>
       <c r="K63" s="7">
-        <v>4.658652</v>
+        <v>4.662717</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -4526,25 +4526,25 @@
         <v>3</v>
       </c>
       <c r="E64" s="7">
-        <v>0.024725</v>
+        <v>0.019775</v>
       </c>
       <c r="F64" s="7">
-        <v>0.011711000000000001</v>
+        <v>0.014467</v>
       </c>
       <c r="G64" s="7">
-        <v>0.21323899999999998</v>
+        <v>0.22827000000000003</v>
       </c>
       <c r="H64" s="7">
-        <v>0.16635999999999998</v>
+        <v>0.16953700000000002</v>
       </c>
       <c r="I64" s="7">
-        <v>0.402406</v>
+        <v>0.40695</v>
       </c>
       <c r="J64" s="7">
-        <v>2.030649</v>
+        <v>2.038904</v>
       </c>
       <c r="K64" s="7">
-        <v>6.219638</v>
+        <v>6.239302</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4561,25 +4561,25 @@
         <v>5</v>
       </c>
       <c r="E65" s="7">
-        <v>0.015854999999999998</v>
+        <v>0.013175</v>
       </c>
       <c r="F65" s="7">
-        <v>0.033031000000000005</v>
+        <v>0.034601</v>
       </c>
       <c r="G65" s="7">
-        <v>0.103817</v>
+        <v>0.104504</v>
       </c>
       <c r="H65" s="7">
-        <v>0.068575</v>
+        <v>0.070199</v>
       </c>
       <c r="I65" s="7">
-        <v>0.292993</v>
+        <v>0.29652</v>
       </c>
       <c r="J65" s="7">
-        <v>2.023665</v>
+        <v>2.02826</v>
       </c>
       <c r="K65" s="7">
-        <v>5.2428420000000004</v>
+        <v>5.252331000000001</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4596,25 +4596,25 @@
         <v>6</v>
       </c>
       <c r="E66" s="7">
-        <v>0.017338</v>
+        <v>0.008174</v>
       </c>
       <c r="F66" s="7">
-        <v>0.028843999999999998</v>
+        <v>0.029341</v>
       </c>
       <c r="G66" s="7">
-        <v>0.09521800000000001</v>
+        <v>0.09672800000000001</v>
       </c>
       <c r="H66" s="7">
-        <v>0.05267</v>
+        <v>0.053179</v>
       </c>
       <c r="I66" s="7">
-        <v>0.307579</v>
+        <v>0.306041</v>
       </c>
       <c r="J66" s="7">
-        <v>2.1974359999999997</v>
+        <v>2.198982</v>
       </c>
       <c r="K66" s="7">
-        <v>6.660706</v>
+        <v>6.664412</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4631,25 +4631,25 @@
         <v>5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.019936</v>
+        <v>0.014474</v>
       </c>
       <c r="F67" s="7">
-        <v>0.032889</v>
+        <v>0.033798</v>
       </c>
       <c r="G67" s="7">
-        <v>0.26705100000000004</v>
+        <v>0.274085</v>
       </c>
       <c r="H67" s="7">
-        <v>0.20775200000000002</v>
+        <v>0.208815</v>
       </c>
       <c r="I67" s="7">
-        <v>0.5454399999999999</v>
+        <v>0.539</v>
       </c>
       <c r="J67" s="7">
-        <v>2.5188040000000003</v>
+        <v>2.521901</v>
       </c>
       <c r="K67" s="7">
-        <v>9.304623</v>
+        <v>9.313695000000001</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -4666,25 +4666,25 @@
         <v>6</v>
       </c>
       <c r="E68" s="7">
-        <v>0.017143</v>
+        <v>0.009325</v>
       </c>
       <c r="F68" s="7">
-        <v>0.030257</v>
+        <v>0.030817</v>
       </c>
       <c r="G68" s="7">
-        <v>0.094945</v>
+        <v>0.09593600000000001</v>
       </c>
       <c r="H68" s="7">
-        <v>0.057347999999999996</v>
+        <v>0.057923</v>
       </c>
       <c r="I68" s="7">
-        <v>0.285059</v>
+        <v>0.28143799999999997</v>
       </c>
       <c r="J68" s="7">
-        <v>2.017747</v>
+        <v>2.019387</v>
       </c>
       <c r="K68" s="7">
-        <v>6.057188</v>
+        <v>6.0610230000000005</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -4701,25 +4701,25 @@
         <v>4</v>
       </c>
       <c r="E69" s="7">
-        <v>0.021023999999999998</v>
+        <v>0.013592</v>
       </c>
       <c r="F69" s="7">
-        <v>0.032065</v>
+        <v>0.032423</v>
       </c>
       <c r="G69" s="7">
-        <v>0.229112</v>
+        <v>0.228529</v>
       </c>
       <c r="H69" s="7">
-        <v>0.13719699999999999</v>
+        <v>0.137591</v>
       </c>
       <c r="I69" s="7">
-        <v>0.450547</v>
+        <v>0.451415</v>
       </c>
       <c r="J69" s="7">
-        <v>2.214314</v>
+        <v>2.215428</v>
       </c>
       <c r="K69" s="7">
-        <v>5.525004</v>
+        <v>5.527265</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4736,25 +4736,25 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>0.03144</v>
+        <v>0.031464</v>
       </c>
       <c r="F70" s="7">
-        <v>0.092288</v>
+        <v>0.09343</v>
       </c>
       <c r="G70" s="7">
-        <v>0.19994199999999998</v>
+        <v>0.19750199999999998</v>
       </c>
       <c r="H70" s="7">
-        <v>0.141959</v>
+        <v>0.143153</v>
       </c>
       <c r="I70" s="7">
-        <v>0.47685099999999997</v>
+        <v>0.476605</v>
       </c>
       <c r="J70" s="7">
-        <v>2.359708</v>
+        <v>2.36322</v>
       </c>
       <c r="K70" s="7">
-        <v>4.0811399999999995</v>
+        <v>4.0864519999999995</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -4771,25 +4771,25 @@
         <v>6</v>
       </c>
       <c r="E71" s="7">
-        <v>0.274556</v>
+        <v>0.23991900000000002</v>
       </c>
       <c r="F71" s="7">
-        <v>0.32195700000000005</v>
+        <v>0.328847</v>
       </c>
       <c r="G71" s="7">
-        <v>0.32494999999999996</v>
+        <v>0.375415</v>
       </c>
       <c r="H71" s="7">
-        <v>0.296713</v>
+        <v>0.303471</v>
       </c>
       <c r="I71" s="7">
-        <v>0.692299</v>
+        <v>0.678828</v>
       </c>
       <c r="J71" s="7">
-        <v>4.149749</v>
+        <v>4.176589</v>
       </c>
       <c r="K71" s="7">
-        <v>9.141327</v>
+        <v>9.194184</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4806,25 +4806,25 @@
         <v>3</v>
       </c>
       <c r="E72" s="7">
-        <v>0.033020999999999995</v>
+        <v>0.03191</v>
       </c>
       <c r="F72" s="7">
-        <v>0.07547100000000001</v>
+        <v>0.077489</v>
       </c>
       <c r="G72" s="7">
-        <v>0.248554</v>
+        <v>0.25166499999999997</v>
       </c>
       <c r="H72" s="7">
-        <v>0.157604</v>
+        <v>0.159775</v>
       </c>
       <c r="I72" s="7">
-        <v>0.447168</v>
+        <v>0.44893700000000003</v>
       </c>
       <c r="J72" s="7">
-        <v>1.914485</v>
+        <v>1.9199529999999998</v>
       </c>
       <c r="K72" s="7">
-        <v>4.70855</v>
+        <v>4.71926</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4841,25 +4841,25 @@
         <v>6</v>
       </c>
       <c r="E73" s="7">
-        <v>0.036536</v>
+        <v>0.028277999999999998</v>
       </c>
       <c r="F73" s="7">
-        <v>0.001089</v>
+        <v>0.0046700000000000005</v>
       </c>
       <c r="G73" s="7">
-        <v>0.065755</v>
+        <v>0.070471</v>
       </c>
       <c r="H73" s="7">
-        <v>0.024541</v>
+        <v>0.028205</v>
       </c>
       <c r="I73" s="7">
-        <v>0.282151</v>
+        <v>0.285524</v>
       </c>
       <c r="J73" s="7">
-        <v>2.009835</v>
+        <v>2.020599</v>
       </c>
       <c r="K73" s="7">
-        <v>6.113988000000001</v>
+        <v>6.139429</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4876,25 +4876,25 @@
         <v>6</v>
       </c>
       <c r="E74" s="7">
-        <v>0.043322</v>
+        <v>0.039577</v>
       </c>
       <c r="F74" s="7">
-        <v>-0.014910000000000001</v>
+        <v>-0.00645</v>
       </c>
       <c r="G74" s="7">
-        <v>0.32356699999999994</v>
+        <v>0.342757</v>
       </c>
       <c r="H74" s="7">
-        <v>0.235976</v>
+        <v>0.24659099999999998</v>
       </c>
       <c r="I74" s="7">
-        <v>0.355768</v>
+        <v>0.36247</v>
       </c>
       <c r="J74" s="7">
-        <v>2.495665</v>
+        <v>2.525687</v>
       </c>
       <c r="K74" s="7">
-        <v>14.654499000000001</v>
+        <v>14.788945000000002</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4911,25 +4911,25 @@
         <v>3</v>
       </c>
       <c r="E75" s="7">
-        <v>0.019142</v>
+        <v>0.007496</v>
       </c>
       <c r="F75" s="7">
-        <v>0.014895</v>
+        <v>0.01085</v>
       </c>
       <c r="G75" s="7">
-        <v>0.17631799999999997</v>
+        <v>0.170047</v>
       </c>
       <c r="H75" s="7">
-        <v>0.061487</v>
+        <v>0.057256</v>
       </c>
       <c r="I75" s="7">
-        <v>0.40940800000000005</v>
+        <v>0.40531599999999995</v>
       </c>
       <c r="J75" s="7">
-        <v>1.8026410000000002</v>
+        <v>1.79147</v>
       </c>
       <c r="K75" s="7">
-        <v>3.695668</v>
+        <v>3.6769510000000003</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4946,25 +4946,25 @@
         <v>4</v>
       </c>
       <c r="E76" s="7">
-        <v>0.021795</v>
+        <v>0.014991</v>
       </c>
       <c r="F76" s="7">
-        <v>0.030725</v>
+        <v>0.031821</v>
       </c>
       <c r="G76" s="7">
-        <v>0.231648</v>
+        <v>0.23209599999999997</v>
       </c>
       <c r="H76" s="7">
-        <v>0.137341</v>
+        <v>0.13855</v>
       </c>
       <c r="I76" s="7">
-        <v>0.45738300000000004</v>
+        <v>0.45937399999999995</v>
       </c>
       <c r="J76" s="7">
-        <v>2.2523589999999998</v>
+        <v>2.2558160000000003</v>
       </c>
       <c r="K76" s="7">
-        <v>5.611783</v>
+        <v>5.618810999999999</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4981,25 +4981,25 @@
         <v>5</v>
       </c>
       <c r="E77" s="7">
-        <v>0.033126</v>
+        <v>0.029608</v>
       </c>
       <c r="F77" s="7">
-        <v>0.044042000000000005</v>
+        <v>0.042177</v>
       </c>
       <c r="G77" s="7">
-        <v>0.320809</v>
+        <v>0.328078</v>
       </c>
       <c r="H77" s="7">
-        <v>0.23220500000000002</v>
+        <v>0.230005</v>
       </c>
       <c r="I77" s="7">
-        <v>0.419895</v>
+        <v>0.417504</v>
       </c>
       <c r="J77" s="7">
-        <v>1.9411580000000002</v>
+        <v>1.935905</v>
       </c>
       <c r="K77" s="7">
-        <v>5.581073</v>
+        <v>5.569319</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5037,25 +5037,25 @@
         <v>4</v>
       </c>
       <c r="E79" s="7">
-        <v>0.06723</v>
+        <v>0.063137</v>
       </c>
       <c r="F79" s="7">
-        <v>0.110011</v>
+        <v>0.116435</v>
       </c>
       <c r="G79" s="7">
-        <v>0.38047600000000004</v>
+        <v>0.383776</v>
       </c>
       <c r="H79" s="7">
-        <v>0.302191</v>
+        <v>0.309727</v>
       </c>
       <c r="I79" s="7">
-        <v>0.690696</v>
+        <v>0.688129</v>
       </c>
       <c r="J79" s="7">
-        <v>2.9301369999999998</v>
+        <v>2.9528820000000002</v>
       </c>
       <c r="K79" s="7">
-        <v>8.622456</v>
+        <v>8.678144999999999</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5072,25 +5072,25 @@
         <v>5</v>
       </c>
       <c r="E80" s="7">
-        <v>0.060122</v>
+        <v>0.061807</v>
       </c>
       <c r="F80" s="7">
-        <v>0.085216</v>
+        <v>0.091201</v>
       </c>
       <c r="G80" s="7">
-        <v>0.242654</v>
+        <v>0.25660299999999997</v>
       </c>
       <c r="H80" s="7">
-        <v>0.203018</v>
+        <v>0.20965399999999998</v>
       </c>
       <c r="I80" s="7">
-        <v>0.43414</v>
+        <v>0.441736</v>
       </c>
       <c r="J80" s="7">
-        <v>2.604418</v>
+        <v>2.624298</v>
       </c>
       <c r="K80" s="7">
-        <v>8.253579</v>
+        <v>8.304616</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5107,25 +5107,25 @@
         <v>6</v>
       </c>
       <c r="E81" s="7">
-        <v>0.01905</v>
+        <v>0.015993999999999998</v>
       </c>
       <c r="F81" s="7">
-        <v>0.007653999999999999</v>
+        <v>0.013186999999999999</v>
       </c>
       <c r="G81" s="7">
-        <v>0.31404699999999997</v>
+        <v>0.328284</v>
       </c>
       <c r="H81" s="7">
-        <v>0.254066</v>
+        <v>0.26095199999999996</v>
       </c>
       <c r="I81" s="7">
-        <v>0.359279</v>
+        <v>0.36168300000000003</v>
       </c>
       <c r="J81" s="7">
-        <v>2.2224909999999998</v>
+        <v>2.240184</v>
       </c>
       <c r="K81" s="7">
-        <v>11.067372</v>
+        <v>11.133629</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5142,25 +5142,25 @@
         <v>4</v>
       </c>
       <c r="E82" s="7">
-        <v>0.038997000000000004</v>
+        <v>0.039224999999999996</v>
       </c>
       <c r="F82" s="7">
-        <v>0.072941</v>
+        <v>0.076122</v>
       </c>
       <c r="G82" s="7">
-        <v>0.20298</v>
+        <v>0.207458</v>
       </c>
       <c r="H82" s="7">
-        <v>0.144108</v>
+        <v>0.1475</v>
       </c>
       <c r="I82" s="7">
-        <v>0.389151</v>
+        <v>0.394916</v>
       </c>
       <c r="J82" s="7">
-        <v>1.843005</v>
+        <v>1.8514340000000002</v>
       </c>
       <c r="K82" s="7">
-        <v>4.473882</v>
+        <v>4.490112</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5177,25 +5177,25 @@
         <v>4</v>
       </c>
       <c r="E83" s="7">
-        <v>0.017647</v>
+        <v>0.006802</v>
       </c>
       <c r="F83" s="7">
-        <v>0.008005</v>
+        <v>0.005417</v>
       </c>
       <c r="G83" s="7">
-        <v>0.144929</v>
+        <v>0.138939</v>
       </c>
       <c r="H83" s="7">
-        <v>0.054721</v>
+        <v>0.052013</v>
       </c>
       <c r="I83" s="7">
-        <v>0.377127</v>
+        <v>0.373813</v>
       </c>
       <c r="J83" s="7">
-        <v>1.501695</v>
+        <v>1.4952709999999998</v>
       </c>
       <c r="K83" s="7">
-        <v>3.1188540000000002</v>
+        <v>3.108279</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5212,25 +5212,25 @@
         <v>5</v>
       </c>
       <c r="E84" s="7">
-        <v>0.075582</v>
+        <v>0.076067</v>
       </c>
       <c r="F84" s="7">
-        <v>0.08869300000000001</v>
+        <v>0.09533200000000001</v>
       </c>
       <c r="G84" s="7">
-        <v>0.26212</v>
+        <v>0.279737</v>
       </c>
       <c r="H84" s="7">
-        <v>0.226339</v>
+        <v>0.233816</v>
       </c>
       <c r="I84" s="7">
-        <v>0.43649</v>
+        <v>0.441274</v>
       </c>
       <c r="J84" s="7">
-        <v>2.639656</v>
+        <v>2.661849</v>
       </c>
       <c r="K84" s="7">
-        <v>9.389787</v>
+        <v>9.45314</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5247,22 +5247,22 @@
         <v>6</v>
       </c>
       <c r="E85" s="7">
-        <v>-0.00434</v>
+        <v>-0.015361</v>
       </c>
       <c r="F85" s="7">
-        <v>-0.073447</v>
+        <v>-0.074529</v>
       </c>
       <c r="G85" s="7">
-        <v>0.092095</v>
+        <v>0.10819000000000001</v>
       </c>
       <c r="H85" s="7">
-        <v>0.035863</v>
+        <v>0.034654</v>
       </c>
       <c r="I85" s="7">
-        <v>0.675981</v>
+        <v>0.676824</v>
       </c>
       <c r="J85" s="7">
-        <v>3.804562</v>
+        <v>3.798953</v>
       </c>
       <c r="K85" s="7"/>
     </row>
@@ -5280,19 +5280,19 @@
         <v>2</v>
       </c>
       <c r="E86" s="7">
-        <v>0.031248</v>
+        <v>0.031283</v>
       </c>
       <c r="F86" s="7">
-        <v>0.091761</v>
+        <v>0.09288</v>
       </c>
       <c r="G86" s="7">
-        <v>0.196627</v>
+        <v>0.194283</v>
       </c>
       <c r="H86" s="7">
-        <v>0.14041499999999998</v>
+        <v>0.14158400000000002</v>
       </c>
       <c r="I86" s="7">
-        <v>0.46352899999999997</v>
+        <v>0.46352</v>
       </c>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
@@ -5311,22 +5311,22 @@
         <v>6</v>
       </c>
       <c r="E87" s="7">
-        <v>0.026445</v>
+        <v>0.024971999999999998</v>
       </c>
       <c r="F87" s="7">
-        <v>0.029971</v>
+        <v>0.039485</v>
       </c>
       <c r="G87" s="7">
-        <v>0.286399</v>
+        <v>0.31681899999999996</v>
       </c>
       <c r="H87" s="7">
-        <v>0.22014399999999998</v>
+        <v>0.231414</v>
       </c>
       <c r="I87" s="7">
-        <v>0.480366</v>
+        <v>0.48903199999999997</v>
       </c>
       <c r="J87" s="7">
-        <v>2.652858</v>
+        <v>2.686597</v>
       </c>
       <c r="K87" s="7"/>
     </row>
@@ -5344,22 +5344,22 @@
         <v>6</v>
       </c>
       <c r="E88" s="7">
-        <v>0.145556</v>
+        <v>0.160385</v>
       </c>
       <c r="F88" s="7">
-        <v>0.289813</v>
+        <v>0.317544</v>
       </c>
       <c r="G88" s="7">
-        <v>0.41178800000000004</v>
+        <v>0.474161</v>
       </c>
       <c r="H88" s="7">
-        <v>0.412822</v>
+        <v>0.44319699999999995</v>
       </c>
       <c r="I88" s="7">
-        <v>0.734138</v>
+        <v>0.777697</v>
       </c>
       <c r="J88" s="7">
-        <v>4.373413</v>
+        <v>4.488938999999999</v>
       </c>
       <c r="K88" s="7"/>
     </row>
@@ -5377,25 +5377,25 @@
         <v>7</v>
       </c>
       <c r="E89" s="7">
-        <v>0.002473</v>
+        <v>-0.006866</v>
       </c>
       <c r="F89" s="7">
-        <v>-0.050621</v>
+        <v>-0.051418</v>
       </c>
       <c r="G89" s="7">
-        <v>0.163188</v>
+        <v>0.173379</v>
       </c>
       <c r="H89" s="7">
-        <v>0.10111</v>
+        <v>0.100185</v>
       </c>
       <c r="I89" s="7">
-        <v>0.680201</v>
+        <v>0.678831</v>
       </c>
       <c r="J89" s="7">
-        <v>4.234782</v>
+        <v>4.230385999999999</v>
       </c>
       <c r="K89" s="7">
-        <v>13.768995</v>
+        <v>13.756592000000001</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5412,25 +5412,25 @@
         <v>3</v>
       </c>
       <c r="E90" s="7">
-        <v>0.031025999999999998</v>
+        <v>0.029645</v>
       </c>
       <c r="F90" s="7">
-        <v>0.09129</v>
+        <v>0.09308</v>
       </c>
       <c r="G90" s="7">
-        <v>0.20160699999999998</v>
+        <v>0.200539</v>
       </c>
       <c r="H90" s="7">
-        <v>0.145696</v>
+        <v>0.147574</v>
       </c>
       <c r="I90" s="7">
-        <v>0.539122</v>
+        <v>0.545987</v>
       </c>
       <c r="J90" s="7">
-        <v>2.4449549999999998</v>
+        <v>2.450604</v>
       </c>
       <c r="K90" s="7">
-        <v>4.346483</v>
+        <v>4.355249</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -5447,25 +5447,25 @@
         <v>5</v>
       </c>
       <c r="E91" s="7">
-        <v>0.014119</v>
+        <v>0.007868</v>
       </c>
       <c r="F91" s="7">
-        <v>0.008069</v>
+        <v>0.008895</v>
       </c>
       <c r="G91" s="7">
-        <v>0.173658</v>
+        <v>0.17283300000000001</v>
       </c>
       <c r="H91" s="7">
-        <v>0.09263400000000001</v>
+        <v>0.093529</v>
       </c>
       <c r="I91" s="7">
-        <v>0.320751</v>
+        <v>0.32276400000000005</v>
       </c>
       <c r="J91" s="7">
-        <v>2.0952129999999998</v>
+        <v>2.09775</v>
       </c>
       <c r="K91" s="7">
-        <v>5.399360000000001</v>
+        <v>5.404605</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -5482,22 +5482,22 @@
         <v>6</v>
       </c>
       <c r="E92" s="7">
-        <v>0.017819</v>
+        <v>0.017672</v>
       </c>
       <c r="F92" s="7">
-        <v>0.010557</v>
+        <v>0.017587</v>
       </c>
       <c r="G92" s="7">
-        <v>0.254383</v>
+        <v>0.268432</v>
       </c>
       <c r="H92" s="7">
-        <v>0.185492</v>
+        <v>0.193739</v>
       </c>
       <c r="I92" s="7">
-        <v>0.39502299999999996</v>
+        <v>0.413113</v>
       </c>
       <c r="J92" s="7">
-        <v>2.5051740000000002</v>
+        <v>2.5295609999999997</v>
       </c>
       <c r="K92" s="7"/>
     </row>
@@ -5515,25 +5515,25 @@
         <v>5</v>
       </c>
       <c r="E93" s="7">
-        <v>0.017227</v>
+        <v>0.010479</v>
       </c>
       <c r="F93" s="7">
-        <v>0.008916</v>
+        <v>0.009949</v>
       </c>
       <c r="G93" s="7">
-        <v>0.21502600000000002</v>
+        <v>0.21540199999999998</v>
       </c>
       <c r="H93" s="7">
-        <v>0.10862999999999999</v>
+        <v>0.109765</v>
       </c>
       <c r="I93" s="7">
-        <v>0.366012</v>
+        <v>0.37067900000000004</v>
       </c>
       <c r="J93" s="7">
-        <v>1.962411</v>
+        <v>1.965444</v>
       </c>
       <c r="K93" s="7">
-        <v>4.9410680000000005</v>
+        <v>4.947151</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -5550,25 +5550,25 @@
         <v>5</v>
       </c>
       <c r="E94" s="7">
-        <v>0.034659</v>
+        <v>0.034189</v>
       </c>
       <c r="F94" s="7">
-        <v>0.072816</v>
+        <v>0.075785</v>
       </c>
       <c r="G94" s="7">
-        <v>0.23018999999999998</v>
+        <v>0.232065</v>
       </c>
       <c r="H94" s="7">
-        <v>0.156286</v>
+        <v>0.15948600000000002</v>
       </c>
       <c r="I94" s="7">
-        <v>0.378116</v>
+        <v>0.37994799999999995</v>
       </c>
       <c r="J94" s="7">
-        <v>1.9260519999999999</v>
+        <v>1.9341480000000002</v>
       </c>
       <c r="K94" s="7">
-        <v>4.713329</v>
+        <v>4.729138</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -5585,25 +5585,25 @@
         <v>4</v>
       </c>
       <c r="E95" s="7">
-        <v>0.009132</v>
+        <v>0.00685</v>
       </c>
       <c r="F95" s="7">
-        <v>0.003956</v>
+        <v>0.008147999999999999</v>
       </c>
       <c r="G95" s="7">
-        <v>0.269721</v>
+        <v>0.27608499999999997</v>
       </c>
       <c r="H95" s="7">
-        <v>0.177014</v>
+        <v>0.18192799999999998</v>
       </c>
       <c r="I95" s="7">
-        <v>0.464405</v>
+        <v>0.467705</v>
       </c>
       <c r="J95" s="7">
-        <v>2.7343599999999997</v>
+        <v>2.749952</v>
       </c>
       <c r="K95" s="7">
-        <v>8.218683</v>
+        <v>8.257172</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -5620,25 +5620,25 @@
         <v>4</v>
       </c>
       <c r="E96" s="7">
-        <v>0.012712000000000001</v>
+        <v>0.003267</v>
       </c>
       <c r="F96" s="7">
-        <v>0.011039</v>
+        <v>0.009126</v>
       </c>
       <c r="G96" s="7">
-        <v>0.180888</v>
+        <v>0.17702</v>
       </c>
       <c r="H96" s="7">
-        <v>0.054599</v>
+        <v>0.052604</v>
       </c>
       <c r="I96" s="7">
-        <v>0.41407299999999997</v>
+        <v>0.414281</v>
       </c>
       <c r="J96" s="7">
-        <v>1.342775</v>
+        <v>1.3383420000000001</v>
       </c>
       <c r="K96" s="7">
-        <v>2.7465300000000004</v>
+        <v>2.739441</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -5655,25 +5655,25 @@
         <v>7</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.0010299999999999999</v>
+        <v>-0.005082</v>
       </c>
       <c r="F97" s="7">
-        <v>-0.040633</v>
+        <v>-0.035041</v>
       </c>
       <c r="G97" s="7">
-        <v>0.320407</v>
+        <v>0.333352</v>
       </c>
       <c r="H97" s="7">
-        <v>0.225934</v>
+        <v>0.23308</v>
       </c>
       <c r="I97" s="7">
-        <v>0.367106</v>
+        <v>0.37109400000000003</v>
       </c>
       <c r="J97" s="7">
-        <v>2.649617</v>
+        <v>2.67089</v>
       </c>
       <c r="K97" s="7">
-        <v>14.563184000000001</v>
+        <v>14.6539</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -5690,25 +5690,25 @@
         <v>6</v>
       </c>
       <c r="E98" s="7">
-        <v>0.007844</v>
+        <v>0.000237</v>
       </c>
       <c r="F98" s="7">
-        <v>-0.036095999999999996</v>
+        <v>-0.028421</v>
       </c>
       <c r="G98" s="7">
-        <v>0.427913</v>
+        <v>0.443891</v>
       </c>
       <c r="H98" s="7">
-        <v>0.22784300000000002</v>
+        <v>0.23762</v>
       </c>
       <c r="I98" s="7">
-        <v>0.479337</v>
+        <v>0.490428</v>
       </c>
       <c r="J98" s="7">
-        <v>3.786246</v>
+        <v>3.8243579999999997</v>
       </c>
       <c r="K98" s="7">
-        <v>19.148148000000003</v>
+        <v>19.308585</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -5725,25 +5725,25 @@
         <v>4</v>
       </c>
       <c r="E99" s="7">
-        <v>0.012889</v>
+        <v>0.010728</v>
       </c>
       <c r="F99" s="7">
-        <v>0.031166</v>
+        <v>0.035417000000000004</v>
       </c>
       <c r="G99" s="7">
-        <v>0.308216</v>
+        <v>0.315007</v>
       </c>
       <c r="H99" s="7">
-        <v>0.221472</v>
+        <v>0.226506</v>
       </c>
       <c r="I99" s="7">
-        <v>0.523487</v>
+        <v>0.525266</v>
       </c>
       <c r="J99" s="7">
-        <v>3.365482</v>
+        <v>3.3834750000000002</v>
       </c>
       <c r="K99" s="7">
-        <v>9.179779</v>
+        <v>9.221738</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -5760,25 +5760,25 @@
         <v>6</v>
       </c>
       <c r="E100" s="7">
-        <v>0.016816</v>
+        <v>0.013987000000000001</v>
       </c>
       <c r="F100" s="7">
-        <v>0.040544000000000004</v>
+        <v>0.041361999999999996</v>
       </c>
       <c r="G100" s="7">
-        <v>0.10448700000000001</v>
+        <v>0.106422</v>
       </c>
       <c r="H100" s="7">
-        <v>0.067183</v>
+        <v>0.068022</v>
       </c>
       <c r="I100" s="7">
-        <v>0.271908</v>
+        <v>0.272466</v>
       </c>
       <c r="J100" s="7">
-        <v>1.9569990000000002</v>
+        <v>1.959325</v>
       </c>
       <c r="K100" s="7">
-        <v>5.66723</v>
+        <v>5.672473</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5795,25 +5795,25 @@
         <v>5</v>
       </c>
       <c r="E101" s="7">
-        <v>0.008577</v>
+        <v>0.006396</v>
       </c>
       <c r="F101" s="7">
-        <v>0.020467</v>
+        <v>0.025089</v>
       </c>
       <c r="G101" s="7">
-        <v>0.373818</v>
+        <v>0.382893</v>
       </c>
       <c r="H101" s="7">
-        <v>0.227299</v>
+        <v>0.23285799999999998</v>
       </c>
       <c r="I101" s="7">
-        <v>0.554411</v>
+        <v>0.556678</v>
       </c>
       <c r="J101" s="7">
-        <v>3.475566</v>
+        <v>3.495838</v>
       </c>
       <c r="K101" s="7">
-        <v>12.110532000000001</v>
+        <v>12.169916</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5830,25 +5830,25 @@
         <v>5</v>
       </c>
       <c r="E102" s="7">
-        <v>0.061415</v>
+        <v>0.063185</v>
       </c>
       <c r="F102" s="7">
-        <v>0.09024900000000001</v>
+        <v>0.097853</v>
       </c>
       <c r="G102" s="7">
-        <v>0.44383</v>
+        <v>0.46219299999999996</v>
       </c>
       <c r="H102" s="7">
-        <v>0.36086399999999996</v>
+        <v>0.370356</v>
       </c>
       <c r="I102" s="7">
-        <v>0.690557</v>
+        <v>0.704576</v>
       </c>
       <c r="J102" s="7">
-        <v>3.742366</v>
+        <v>3.7754450000000004</v>
       </c>
       <c r="K102" s="7">
-        <v>11.891485</v>
+        <v>11.981406</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -5865,25 +5865,25 @@
         <v>2</v>
       </c>
       <c r="E103" s="7">
-        <v>0.027067</v>
+        <v>0.024931000000000002</v>
       </c>
       <c r="F103" s="7">
-        <v>0.08177899999999999</v>
+        <v>0.08289999999999999</v>
       </c>
       <c r="G103" s="7">
-        <v>0.267487</v>
+        <v>0.267136</v>
       </c>
       <c r="H103" s="7">
-        <v>0.17119199999999998</v>
+        <v>0.172406</v>
       </c>
       <c r="I103" s="7">
-        <v>0.561897</v>
+        <v>0.561421</v>
       </c>
       <c r="J103" s="7">
-        <v>3.126843</v>
+        <v>3.13112</v>
       </c>
       <c r="K103" s="7">
-        <v>5.74662</v>
+        <v>5.7536130000000005</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5900,25 +5900,25 @@
         <v>6</v>
       </c>
       <c r="E104" s="7">
-        <v>0.065084</v>
+        <v>0.067481</v>
       </c>
       <c r="F104" s="7">
-        <v>0.08177899999999999</v>
+        <v>0.089716</v>
       </c>
       <c r="G104" s="7">
-        <v>0.46630499999999997</v>
+        <v>0.487287</v>
       </c>
       <c r="H104" s="7">
-        <v>0.384014</v>
+        <v>0.394167</v>
       </c>
       <c r="I104" s="7">
-        <v>0.691948</v>
+        <v>0.705619</v>
       </c>
       <c r="J104" s="7">
-        <v>3.649581</v>
+        <v>3.6836919999999997</v>
       </c>
       <c r="K104" s="7">
-        <v>14.058060000000001</v>
+        <v>14.168531</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -5935,25 +5935,25 @@
         <v>6</v>
       </c>
       <c r="E105" s="7">
-        <v>0.013824000000000001</v>
+        <v>0.008477</v>
       </c>
       <c r="F105" s="7">
-        <v>0.0296</v>
+        <v>0.030794000000000002</v>
       </c>
       <c r="G105" s="7">
-        <v>0.09852</v>
+        <v>0.10135999999999999</v>
       </c>
       <c r="H105" s="7">
-        <v>0.054946999999999996</v>
+        <v>0.05617200000000001</v>
       </c>
       <c r="I105" s="7">
-        <v>0.301773</v>
+        <v>0.302726</v>
       </c>
       <c r="J105" s="7">
-        <v>2.070717</v>
+        <v>2.07428</v>
       </c>
       <c r="K105" s="7">
-        <v>6.0642700000000005</v>
+        <v>6.0724670000000005</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -5970,19 +5970,19 @@
         <v>6</v>
       </c>
       <c r="E106" s="7">
-        <v>0.047618999999999995</v>
+        <v>0.037843</v>
       </c>
       <c r="F106" s="7">
-        <v>0.045004</v>
+        <v>0.051024</v>
       </c>
       <c r="G106" s="7">
-        <v>0.225168</v>
+        <v>0.248997</v>
       </c>
       <c r="H106" s="7">
-        <v>0.172777</v>
+        <v>0.17953399999999997</v>
       </c>
       <c r="I106" s="7">
-        <v>0.423542</v>
+        <v>0.43174300000000004</v>
       </c>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -6001,22 +6001,22 @@
         <v>6</v>
       </c>
       <c r="E107" s="7">
-        <v>0.196664</v>
+        <v>0.187167</v>
       </c>
       <c r="F107" s="7">
-        <v>0.307365</v>
+        <v>0.31732299999999997</v>
       </c>
       <c r="G107" s="7">
-        <v>0.45948</v>
+        <v>0.494549</v>
       </c>
       <c r="H107" s="7">
-        <v>0.422607</v>
+        <v>0.433442</v>
       </c>
       <c r="I107" s="7">
-        <v>0.8463379999999999</v>
+        <v>0.845649</v>
       </c>
       <c r="J107" s="7">
-        <v>4.689707</v>
+        <v>4.733044</v>
       </c>
       <c r="K107" s="7"/>
     </row>
@@ -6034,25 +6034,25 @@
         <v>6</v>
       </c>
       <c r="E108" s="7">
-        <v>0.0059099999999999995</v>
+        <v>-0.002533</v>
       </c>
       <c r="F108" s="7">
-        <v>-0.042701</v>
+        <v>-0.04260100000000001</v>
       </c>
       <c r="G108" s="7">
-        <v>0.184574</v>
+        <v>0.199465</v>
       </c>
       <c r="H108" s="7">
-        <v>0.133988</v>
+        <v>0.134106</v>
       </c>
       <c r="I108" s="7">
-        <v>0.731327</v>
+        <v>0.734049</v>
       </c>
       <c r="J108" s="7">
-        <v>4.969074</v>
+        <v>4.969696</v>
       </c>
       <c r="K108" s="7">
-        <v>15.887541</v>
+        <v>15.889299000000001</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -6069,25 +6069,25 @@
         <v>3</v>
       </c>
       <c r="E109" s="7">
-        <v>0.016634</v>
+        <v>0.004307</v>
       </c>
       <c r="F109" s="7">
-        <v>0.033302</v>
+        <v>0.03093</v>
       </c>
       <c r="G109" s="7">
-        <v>0.182981</v>
+        <v>0.177376</v>
       </c>
       <c r="H109" s="7">
-        <v>0.082906</v>
+        <v>0.08041999999999999</v>
       </c>
       <c r="I109" s="7">
-        <v>0.459998</v>
+        <v>0.456803</v>
       </c>
       <c r="J109" s="7">
-        <v>2.092453</v>
+        <v>2.085354</v>
       </c>
       <c r="K109" s="7">
-        <v>3.906298</v>
+        <v>3.895036</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -6104,25 +6104,25 @@
         <v>6</v>
       </c>
       <c r="E110" s="7">
-        <v>0.013238000000000002</v>
+        <v>0.007692</v>
       </c>
       <c r="F110" s="7">
-        <v>0.023007</v>
+        <v>0.023866000000000002</v>
       </c>
       <c r="G110" s="7">
-        <v>0.123878</v>
+        <v>0.125497</v>
       </c>
       <c r="H110" s="7">
-        <v>0.061255</v>
+        <v>0.062146999999999994</v>
       </c>
       <c r="I110" s="7">
-        <v>0.33075200000000005</v>
+        <v>0.330986</v>
       </c>
       <c r="J110" s="7">
-        <v>2.168289</v>
+        <v>2.17095</v>
       </c>
       <c r="K110" s="7">
-        <v>6.494065000000001</v>
+        <v>6.500361000000001</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -6139,25 +6139,25 @@
         <v>3</v>
       </c>
       <c r="E111" s="7">
-        <v>0.036799</v>
+        <v>0.040027</v>
       </c>
       <c r="F111" s="7">
-        <v>0.09178599999999999</v>
+        <v>0.095284</v>
       </c>
       <c r="G111" s="7">
-        <v>0.24043299999999998</v>
+        <v>0.24425999999999998</v>
       </c>
       <c r="H111" s="7">
-        <v>0.182503</v>
+        <v>0.186292</v>
       </c>
       <c r="I111" s="7">
-        <v>0.47853</v>
+        <v>0.478592</v>
       </c>
       <c r="J111" s="7">
-        <v>2.129162</v>
+        <v>2.139188</v>
       </c>
       <c r="K111" s="7">
-        <v>5.618223</v>
+        <v>5.6394269999999995</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -6174,25 +6174,25 @@
         <v>5</v>
       </c>
       <c r="E112" s="7">
-        <v>0.020149</v>
+        <v>0.023955999999999998</v>
       </c>
       <c r="F112" s="7">
-        <v>0.013848000000000001</v>
+        <v>0.021192000000000003</v>
       </c>
       <c r="G112" s="7">
-        <v>0.27413</v>
+        <v>0.286653</v>
       </c>
       <c r="H112" s="7">
-        <v>0.17376999999999998</v>
+        <v>0.182272</v>
       </c>
       <c r="I112" s="7">
-        <v>0.533056</v>
+        <v>0.5392600000000001</v>
       </c>
       <c r="J112" s="7">
-        <v>3.377398</v>
+        <v>3.409106</v>
       </c>
       <c r="K112" s="7">
-        <v>14.668688</v>
+        <v>14.782183999999999</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -6209,25 +6209,25 @@
         <v>3</v>
       </c>
       <c r="E113" s="7">
-        <v>0.025585</v>
+        <v>0.021976</v>
       </c>
       <c r="F113" s="7">
-        <v>0.075415</v>
+        <v>0.074852</v>
       </c>
       <c r="G113" s="7">
-        <v>0.23295300000000002</v>
+        <v>0.228661</v>
       </c>
       <c r="H113" s="7">
-        <v>0.15079</v>
+        <v>0.15018800000000002</v>
       </c>
       <c r="I113" s="7">
-        <v>0.5205449999999999</v>
+        <v>0.51817</v>
       </c>
       <c r="J113" s="7">
-        <v>3.240126</v>
+        <v>3.2379059999999997</v>
       </c>
       <c r="K113" s="7">
-        <v>6.273587</v>
+        <v>6.269779</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -6244,25 +6244,25 @@
         <v>6</v>
       </c>
       <c r="E114" s="7">
-        <v>0.046801</v>
+        <v>0.046802</v>
       </c>
       <c r="F114" s="7">
-        <v>0.08739000000000001</v>
+        <v>0.09375299999999999</v>
       </c>
       <c r="G114" s="7">
-        <v>0.35850099999999996</v>
+        <v>0.37493299999999996</v>
       </c>
       <c r="H114" s="7">
-        <v>0.282158</v>
+        <v>0.289659</v>
       </c>
       <c r="I114" s="7">
-        <v>0.568872</v>
+        <v>0.571971</v>
       </c>
       <c r="J114" s="7">
-        <v>3.563404</v>
+        <v>3.590104</v>
       </c>
       <c r="K114" s="7">
-        <v>16.923576</v>
+        <v>17.028444</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -6279,25 +6279,25 @@
         <v>6</v>
       </c>
       <c r="E115" s="7">
-        <v>0.006634999999999999</v>
+        <v>0.006594</v>
       </c>
       <c r="F115" s="7">
-        <v>-0.020358</v>
+        <v>-0.012575000000000001</v>
       </c>
       <c r="G115" s="7">
-        <v>0.29121400000000003</v>
+        <v>0.311006</v>
       </c>
       <c r="H115" s="7">
-        <v>0.19715</v>
+        <v>0.206661</v>
       </c>
       <c r="I115" s="7">
-        <v>0.494621</v>
+        <v>0.496355</v>
       </c>
       <c r="J115" s="7">
-        <v>3.110127</v>
+        <v>3.14278</v>
       </c>
       <c r="K115" s="7">
-        <v>22.032999</v>
+        <v>22.215988000000003</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -6314,25 +6314,25 @@
         <v>6</v>
       </c>
       <c r="E116" s="7">
-        <v>0.024916999999999998</v>
+        <v>0.030278999999999997</v>
       </c>
       <c r="F116" s="7">
-        <v>0.036822</v>
+        <v>0.047158</v>
       </c>
       <c r="G116" s="7">
-        <v>0.347769</v>
+        <v>0.36926400000000004</v>
       </c>
       <c r="H116" s="7">
-        <v>0.24997499999999997</v>
+        <v>0.26243700000000003</v>
       </c>
       <c r="I116" s="7">
-        <v>0.521002</v>
+        <v>0.525605</v>
       </c>
       <c r="J116" s="7">
-        <v>2.6702850000000002</v>
+        <v>2.706875</v>
       </c>
       <c r="K116" s="7">
-        <v>15.782494999999999</v>
+        <v>15.949808</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -6349,25 +6349,25 @@
         <v>5</v>
       </c>
       <c r="E117" s="7">
-        <v>0.032570999999999996</v>
+        <v>0.035969</v>
       </c>
       <c r="F117" s="7">
-        <v>0.101397</v>
+        <v>0.107688</v>
       </c>
       <c r="G117" s="7">
-        <v>0.355242</v>
+        <v>0.368157</v>
       </c>
       <c r="H117" s="7">
-        <v>0.284394</v>
+        <v>0.291731</v>
       </c>
       <c r="I117" s="7">
-        <v>0.646343</v>
+        <v>0.650163</v>
       </c>
       <c r="J117" s="7">
-        <v>3.3123989999999996</v>
+        <v>3.337031</v>
       </c>
       <c r="K117" s="7">
-        <v>12.394174</v>
+        <v>12.47068</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -6384,25 +6384,25 @@
         <v>3</v>
       </c>
       <c r="E118" s="7">
-        <v>0.016289</v>
+        <v>0.004106</v>
       </c>
       <c r="F118" s="7">
-        <v>0.0339</v>
+        <v>0.031779</v>
       </c>
       <c r="G118" s="7">
-        <v>0.180614</v>
+        <v>0.175643</v>
       </c>
       <c r="H118" s="7">
-        <v>0.076864</v>
+        <v>0.074656</v>
       </c>
       <c r="I118" s="7">
-        <v>0.430419</v>
+        <v>0.427753</v>
       </c>
       <c r="J118" s="7">
-        <v>1.876636</v>
+        <v>1.870736</v>
       </c>
       <c r="K118" s="7">
-        <v>3.6971030000000003</v>
+        <v>3.6874700000000002</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -6419,25 +6419,25 @@
         <v>6</v>
       </c>
       <c r="E119" s="7">
-        <v>0.036253</v>
+        <v>0.036637</v>
       </c>
       <c r="F119" s="7">
-        <v>0.052579</v>
+        <v>0.057359</v>
       </c>
       <c r="G119" s="7">
-        <v>0.32081000000000004</v>
+        <v>0.338337</v>
       </c>
       <c r="H119" s="7">
-        <v>0.22806200000000001</v>
+        <v>0.233639</v>
       </c>
       <c r="I119" s="7">
-        <v>0.63544</v>
+        <v>0.632968</v>
       </c>
       <c r="J119" s="7">
-        <v>3.513471</v>
+        <v>3.5339679999999998</v>
       </c>
       <c r="K119" s="7">
-        <v>16.307755999999998</v>
+        <v>16.386358</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -6454,25 +6454,25 @@
         <v>5</v>
       </c>
       <c r="E120" s="7">
-        <v>0.004532</v>
+        <v>0.005027</v>
       </c>
       <c r="F120" s="7">
-        <v>0.008732</v>
+        <v>0.015290999999999999</v>
       </c>
       <c r="G120" s="7">
-        <v>0.208049</v>
+        <v>0.213859</v>
       </c>
       <c r="H120" s="7">
-        <v>0.119323</v>
+        <v>0.126602</v>
       </c>
       <c r="I120" s="7">
-        <v>0.443309</v>
+        <v>0.438267</v>
       </c>
       <c r="J120" s="7">
-        <v>2.487575</v>
+        <v>2.510253</v>
       </c>
       <c r="K120" s="7">
-        <v>8.893215</v>
+        <v>8.957545</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -6489,25 +6489,25 @@
         <v>6</v>
       </c>
       <c r="E121" s="7">
-        <v>0.034872</v>
+        <v>0.033765</v>
       </c>
       <c r="F121" s="7">
-        <v>-0.01722</v>
+        <v>-0.009077</v>
       </c>
       <c r="G121" s="7">
-        <v>0.2065</v>
+        <v>0.22642800000000002</v>
       </c>
       <c r="H121" s="7">
-        <v>0.168326</v>
+        <v>0.178007</v>
       </c>
       <c r="I121" s="7">
-        <v>0.440033</v>
+        <v>0.44475000000000003</v>
       </c>
       <c r="J121" s="7">
-        <v>3.327907</v>
+        <v>3.3637689999999996</v>
       </c>
       <c r="K121" s="7">
-        <v>18.165021</v>
+        <v>18.323826</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -6524,25 +6524,25 @@
         <v>4</v>
       </c>
       <c r="E122" s="7">
-        <v>0.015484</v>
+        <v>0.009844</v>
       </c>
       <c r="F122" s="7">
-        <v>0.032623</v>
+        <v>0.03563</v>
       </c>
       <c r="G122" s="7">
-        <v>0.218813</v>
+        <v>0.221899</v>
       </c>
       <c r="H122" s="7">
-        <v>0.129793</v>
+        <v>0.133082</v>
       </c>
       <c r="I122" s="7">
-        <v>0.471607</v>
+        <v>0.471186</v>
       </c>
       <c r="J122" s="7">
-        <v>2.318223</v>
+        <v>2.327885</v>
       </c>
       <c r="K122" s="7">
-        <v>5.996862</v>
+        <v>6.017233999999999</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -6559,25 +6559,25 @@
         <v>4</v>
       </c>
       <c r="E123" s="7">
-        <v>0.016587</v>
+        <v>0.012639000000000001</v>
       </c>
       <c r="F123" s="7">
-        <v>0.032712</v>
+        <v>0.036419</v>
       </c>
       <c r="G123" s="7">
-        <v>0.18938300000000002</v>
+        <v>0.193472</v>
       </c>
       <c r="H123" s="7">
-        <v>0.11622199999999999</v>
+        <v>0.120228</v>
       </c>
       <c r="I123" s="7">
-        <v>0.42621200000000004</v>
+        <v>0.423894</v>
       </c>
       <c r="J123" s="7">
-        <v>1.9706899999999998</v>
+        <v>1.981353</v>
       </c>
       <c r="K123" s="7">
-        <v>6.052621</v>
+        <v>6.077935999999999</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -6594,16 +6594,16 @@
         <v>6</v>
       </c>
       <c r="E124" s="7">
-        <v>0.005174</v>
+        <v>-0.0024</v>
       </c>
       <c r="F124" s="7">
-        <v>-0.057404000000000004</v>
+        <v>-0.056963</v>
       </c>
       <c r="G124" s="7">
-        <v>0.170592</v>
+        <v>0.18448799999999999</v>
       </c>
       <c r="H124" s="7">
-        <v>0.137134</v>
+        <v>0.137666</v>
       </c>
       <c r="I124" s="7"/>
       <c r="J124" s="7"/>
@@ -6623,25 +6623,25 @@
         <v>4</v>
       </c>
       <c r="E125" s="7">
-        <v>0.016876</v>
+        <v>0.014724</v>
       </c>
       <c r="F125" s="7">
-        <v>0.012747</v>
+        <v>0.015826</v>
       </c>
       <c r="G125" s="7">
-        <v>0.253043</v>
+        <v>0.259609</v>
       </c>
       <c r="H125" s="7">
-        <v>0.165191</v>
+        <v>0.168734</v>
       </c>
       <c r="I125" s="7">
-        <v>0.50209</v>
+        <v>0.500065</v>
       </c>
       <c r="J125" s="7">
-        <v>2.053781</v>
+        <v>2.063066</v>
       </c>
       <c r="K125" s="7">
-        <v>6.5271609999999995</v>
+        <v>6.550048</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -6658,16 +6658,16 @@
         <v>6</v>
       </c>
       <c r="E126" s="7">
-        <v>0.088271</v>
+        <v>0.091033</v>
       </c>
       <c r="F126" s="7">
-        <v>0.143884</v>
+        <v>0.152188</v>
       </c>
       <c r="G126" s="7">
-        <v>0.47690699999999997</v>
+        <v>0.503752</v>
       </c>
       <c r="H126" s="7">
-        <v>0.401076</v>
+        <v>0.411247</v>
       </c>
       <c r="I126" s="7"/>
       <c r="J126" s="7"/>
@@ -6687,25 +6687,25 @@
         <v>7</v>
       </c>
       <c r="E127" s="7">
-        <v>0.025362</v>
+        <v>0.025955</v>
       </c>
       <c r="F127" s="7">
-        <v>0.009606</v>
+        <v>0.017249</v>
       </c>
       <c r="G127" s="7">
-        <v>0.258171</v>
+        <v>0.273824</v>
       </c>
       <c r="H127" s="7">
-        <v>0.136662</v>
+        <v>0.145267</v>
       </c>
       <c r="I127" s="7">
-        <v>0.397752</v>
+        <v>0.402909</v>
       </c>
       <c r="J127" s="7">
-        <v>2.396569</v>
+        <v>2.422282</v>
       </c>
       <c r="K127" s="7">
-        <v>9.256545</v>
+        <v>9.334189</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -6722,25 +6722,25 @@
         <v>5</v>
       </c>
       <c r="E128" s="7">
-        <v>0.010751</v>
+        <v>0.0025819999999999997</v>
       </c>
       <c r="F128" s="7">
-        <v>0.018804</v>
+        <v>0.019615</v>
       </c>
       <c r="G128" s="7">
-        <v>0.089613</v>
+        <v>0.089343</v>
       </c>
       <c r="H128" s="7">
-        <v>0.051232</v>
+        <v>0.052069000000000004</v>
       </c>
       <c r="I128" s="7">
-        <v>0.27997900000000003</v>
+        <v>0.27598</v>
       </c>
       <c r="J128" s="7">
-        <v>1.955203</v>
+        <v>1.9575550000000002</v>
       </c>
       <c r="K128" s="7">
-        <v>5.473978</v>
+        <v>5.479129</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -6757,25 +6757,25 @@
         <v>4</v>
       </c>
       <c r="E129" s="7">
-        <v>0.018918</v>
+        <v>0.008413</v>
       </c>
       <c r="F129" s="7">
-        <v>0.000254</v>
+        <v>-0.000473</v>
       </c>
       <c r="G129" s="7">
-        <v>0.153459</v>
+        <v>0.149709</v>
       </c>
       <c r="H129" s="7">
-        <v>0.052861000000000005</v>
+        <v>0.052095</v>
       </c>
       <c r="I129" s="7">
-        <v>0.382746</v>
+        <v>0.383658</v>
       </c>
       <c r="J129" s="7">
-        <v>1.5698269999999999</v>
+        <v>1.5679580000000002</v>
       </c>
       <c r="K129" s="7">
-        <v>3.358719</v>
+        <v>3.355549</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -6792,25 +6792,25 @@
         <v>6</v>
       </c>
       <c r="E130" s="7">
-        <v>0.012248000000000002</v>
+        <v>0.010204999999999999</v>
       </c>
       <c r="F130" s="7">
-        <v>-0.011433</v>
+        <v>-0.003633</v>
       </c>
       <c r="G130" s="7">
-        <v>0.325857</v>
+        <v>0.34379</v>
       </c>
       <c r="H130" s="7">
-        <v>0.240957</v>
+        <v>0.25074799999999997</v>
       </c>
       <c r="I130" s="7">
-        <v>0.457384</v>
+        <v>0.466135</v>
       </c>
       <c r="J130" s="7">
-        <v>2.737799</v>
+        <v>2.767289</v>
       </c>
       <c r="K130" s="7">
-        <v>14.08036</v>
+        <v>14.19934</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -6827,25 +6827,25 @@
         <v>4</v>
       </c>
       <c r="E131" s="7">
-        <v>0.013852</v>
+        <v>0.00728</v>
       </c>
       <c r="F131" s="7">
-        <v>0.022561</v>
+        <v>0.024089999999999997</v>
       </c>
       <c r="G131" s="7">
-        <v>0.081467</v>
+        <v>0.08412800000000001</v>
       </c>
       <c r="H131" s="7">
-        <v>0.047261</v>
+        <v>0.048826999999999995</v>
       </c>
       <c r="I131" s="7">
-        <v>0.268489</v>
+        <v>0.269776</v>
       </c>
       <c r="J131" s="7">
-        <v>1.983845</v>
+        <v>1.9883080000000002</v>
       </c>
       <c r="K131" s="7">
-        <v>6.209588999999999</v>
+        <v>6.220372</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -6904,19 +6904,19 @@
         <v>4</v>
       </c>
       <c r="E134" s="7">
-        <v>0.138051</v>
+        <v>0.115164</v>
       </c>
       <c r="F134" s="7">
-        <v>0.21361</v>
+        <v>0.212087</v>
       </c>
       <c r="G134" s="7">
-        <v>0.344628</v>
+        <v>0.394486</v>
       </c>
       <c r="H134" s="7">
-        <v>0.345417</v>
+        <v>0.343729</v>
       </c>
       <c r="I134" s="7">
-        <v>0.6988509999999999</v>
+        <v>0.69562</v>
       </c>
       <c r="J134" s="7"/>
       <c r="K134" s="7"/>
@@ -6935,25 +6935,25 @@
         <v>4</v>
       </c>
       <c r="E135" s="7">
-        <v>0.015691</v>
+        <v>0.005559</v>
       </c>
       <c r="F135" s="7">
-        <v>0.000054999999999999995</v>
+        <v>-0.001596</v>
       </c>
       <c r="G135" s="7">
-        <v>0.18284099999999998</v>
+        <v>0.18036100000000002</v>
       </c>
       <c r="H135" s="7">
-        <v>0.086098</v>
+        <v>0.084304</v>
       </c>
       <c r="I135" s="7">
-        <v>0.395845</v>
+        <v>0.395569</v>
       </c>
       <c r="J135" s="7">
-        <v>1.501053</v>
+        <v>1.4969229999999998</v>
       </c>
       <c r="K135" s="7">
-        <v>3.7546109999999997</v>
+        <v>3.746759</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -6970,25 +6970,25 @@
         <v>3</v>
       </c>
       <c r="E136" s="7">
-        <v>0.031383999999999995</v>
+        <v>0.032099</v>
       </c>
       <c r="F136" s="7">
-        <v>0.086543</v>
+        <v>0.087979</v>
       </c>
       <c r="G136" s="7">
-        <v>0.189864</v>
+        <v>0.187725</v>
       </c>
       <c r="H136" s="7">
-        <v>0.137576</v>
+        <v>0.139079</v>
       </c>
       <c r="I136" s="7">
-        <v>0.460137</v>
+        <v>0.460269</v>
       </c>
       <c r="J136" s="7">
-        <v>2.320471</v>
+        <v>2.324857</v>
       </c>
       <c r="K136" s="7">
-        <v>3.896322</v>
+        <v>3.9027890000000003</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -7005,25 +7005,25 @@
         <v>6</v>
       </c>
       <c r="E137" s="7">
-        <v>0.047208</v>
+        <v>0.043826000000000004</v>
       </c>
       <c r="F137" s="7">
-        <v>0.051778000000000005</v>
+        <v>0.05428</v>
       </c>
       <c r="G137" s="7">
-        <v>0.27409300000000003</v>
+        <v>0.281423</v>
       </c>
       <c r="H137" s="7">
-        <v>0.20198</v>
+        <v>0.204839</v>
       </c>
       <c r="I137" s="7">
-        <v>0.449944</v>
+        <v>0.45362499999999994</v>
       </c>
       <c r="J137" s="7">
-        <v>2.795024</v>
+        <v>2.804052</v>
       </c>
       <c r="K137" s="7">
-        <v>8.024158</v>
+        <v>8.045626</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -7040,25 +7040,25 @@
         <v>4</v>
       </c>
       <c r="E138" s="7">
-        <v>0.017295</v>
+        <v>0.008098</v>
       </c>
       <c r="F138" s="7">
-        <v>-0.001791</v>
+        <v>-0.002231</v>
       </c>
       <c r="G138" s="7">
-        <v>0.167504</v>
+        <v>0.16614</v>
       </c>
       <c r="H138" s="7">
-        <v>0.08051</v>
+        <v>0.080034</v>
       </c>
       <c r="I138" s="7">
-        <v>0.347057</v>
+        <v>0.34884</v>
       </c>
       <c r="J138" s="7">
-        <v>1.060019</v>
+        <v>1.0591110000000001</v>
       </c>
       <c r="K138" s="7">
-        <v>2.433688</v>
+        <v>2.432174</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -7075,25 +7075,25 @@
         <v>6</v>
       </c>
       <c r="E139" s="7">
-        <v>0.045191</v>
+        <v>0.046459</v>
       </c>
       <c r="F139" s="7">
-        <v>0.071463</v>
+        <v>0.078457</v>
       </c>
       <c r="G139" s="7">
-        <v>0.207888</v>
+        <v>0.220277</v>
       </c>
       <c r="H139" s="7">
-        <v>0.17252099999999998</v>
+        <v>0.18017499999999997</v>
       </c>
       <c r="I139" s="7">
-        <v>0.42322400000000004</v>
+        <v>0.430178</v>
       </c>
       <c r="J139" s="7">
-        <v>2.9742610000000003</v>
+        <v>3.0002050000000002</v>
       </c>
       <c r="K139" s="7">
-        <v>9.415536</v>
+        <v>9.483528</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -7110,25 +7110,25 @@
         <v>4</v>
       </c>
       <c r="E140" s="7">
-        <v>0.033574</v>
+        <v>0.029272999999999997</v>
       </c>
       <c r="F140" s="7">
-        <v>0.049074</v>
+        <v>0.050058</v>
       </c>
       <c r="G140" s="7">
-        <v>0.19216</v>
+        <v>0.19202100000000002</v>
       </c>
       <c r="H140" s="7">
-        <v>0.12214900000000001</v>
+        <v>0.123201</v>
       </c>
       <c r="I140" s="7">
-        <v>0.431286</v>
+        <v>0.43168599999999996</v>
       </c>
       <c r="J140" s="7">
-        <v>2.198546</v>
+        <v>2.2015450000000003</v>
       </c>
       <c r="K140" s="7">
-        <v>4.211036</v>
+        <v>4.215922</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -7145,22 +7145,22 @@
         <v>6</v>
       </c>
       <c r="E141" s="7">
-        <v>0.182407</v>
+        <v>0.17345400000000002</v>
       </c>
       <c r="F141" s="7">
-        <v>0.250202</v>
+        <v>0.261627</v>
       </c>
       <c r="G141" s="7">
-        <v>0.41924700000000004</v>
+        <v>0.445588</v>
       </c>
       <c r="H141" s="7">
-        <v>0.344711</v>
+        <v>0.356999</v>
       </c>
       <c r="I141" s="7">
-        <v>0.854532</v>
+        <v>0.856826</v>
       </c>
       <c r="J141" s="7">
-        <v>5.762248</v>
+        <v>5.824045</v>
       </c>
       <c r="K141" s="7"/>
     </row>
@@ -7178,22 +7178,22 @@
         <v>4</v>
       </c>
       <c r="E142" s="7">
-        <v>0.048504</v>
+        <v>0.047375999999999995</v>
       </c>
       <c r="F142" s="7">
-        <v>0.025354</v>
+        <v>0.034259</v>
       </c>
       <c r="G142" s="7">
-        <v>0.20755700000000002</v>
+        <v>0.22662</v>
       </c>
       <c r="H142" s="7">
-        <v>0.139746</v>
+        <v>0.149644</v>
       </c>
       <c r="I142" s="7">
-        <v>0.5341400000000001</v>
+        <v>0.549685</v>
       </c>
       <c r="J142" s="7">
-        <v>4.782261</v>
+        <v>4.832477</v>
       </c>
       <c r="K142" s="7"/>
     </row>
@@ -7211,25 +7211,25 @@
         <v>3</v>
       </c>
       <c r="E143" s="7">
-        <v>0.015151</v>
+        <v>0.007234000000000001</v>
       </c>
       <c r="F143" s="7">
-        <v>0.008559</v>
+        <v>0.006986</v>
       </c>
       <c r="G143" s="7">
-        <v>0.16401</v>
+        <v>0.16122499999999998</v>
       </c>
       <c r="H143" s="7">
-        <v>0.095244</v>
+        <v>0.093537</v>
       </c>
       <c r="I143" s="7">
-        <v>0.356952</v>
+        <v>0.34945</v>
       </c>
       <c r="J143" s="7">
-        <v>1.640324</v>
+        <v>1.636207</v>
       </c>
       <c r="K143" s="7">
-        <v>3.609636</v>
+        <v>3.60245</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -7246,25 +7246,25 @@
         <v>3</v>
       </c>
       <c r="E144" s="7">
-        <v>0.028098</v>
+        <v>0.029476</v>
       </c>
       <c r="F144" s="7">
-        <v>0.061406</v>
+        <v>0.06433799999999999</v>
       </c>
       <c r="G144" s="7">
-        <v>0.19888899999999998</v>
+        <v>0.202273</v>
       </c>
       <c r="H144" s="7">
-        <v>0.133746</v>
+        <v>0.136878</v>
       </c>
       <c r="I144" s="7">
-        <v>0.35196399999999994</v>
+        <v>0.355001</v>
       </c>
       <c r="J144" s="7">
-        <v>1.5721379999999998</v>
+        <v>1.579243</v>
       </c>
       <c r="K144" s="7">
-        <v>4.486466</v>
+        <v>4.50162</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -7281,25 +7281,25 @@
         <v>5</v>
       </c>
       <c r="E145" s="7">
-        <v>0.08816800000000001</v>
+        <v>0.08923</v>
       </c>
       <c r="F145" s="7">
-        <v>0.012841</v>
+        <v>0.017712000000000002</v>
       </c>
       <c r="G145" s="7">
-        <v>0.320237</v>
+        <v>0.337826</v>
       </c>
       <c r="H145" s="7">
-        <v>0.193781</v>
+        <v>0.199522</v>
       </c>
       <c r="I145" s="7">
-        <v>0.367751</v>
+        <v>0.37348</v>
       </c>
       <c r="J145" s="7">
-        <v>3.19352</v>
+        <v>3.2136869999999997</v>
       </c>
       <c r="K145" s="7">
-        <v>13.746385</v>
+        <v>13.817304</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -7316,25 +7316,25 @@
         <v>5</v>
       </c>
       <c r="E146" s="7">
-        <v>-0.004059</v>
+        <v>0.001587</v>
       </c>
       <c r="F146" s="7">
-        <v>0.09768800000000001</v>
+        <v>0.103893</v>
       </c>
       <c r="G146" s="7">
-        <v>0.260434</v>
+        <v>0.267224</v>
       </c>
       <c r="H146" s="7">
-        <v>0.27426100000000003</v>
+        <v>0.281464</v>
       </c>
       <c r="I146" s="7">
-        <v>0.24296700000000002</v>
+        <v>0.247281</v>
       </c>
       <c r="J146" s="7">
-        <v>3.2900139999999998</v>
+        <v>3.314264</v>
       </c>
       <c r="K146" s="7">
-        <v>10.829924</v>
+        <v>10.896795</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -7351,25 +7351,25 @@
         <v>3</v>
       </c>
       <c r="E147" s="7">
-        <v>0.023947</v>
+        <v>0.022608000000000003</v>
       </c>
       <c r="F147" s="7">
-        <v>0.054416</v>
+        <v>0.060265000000000006</v>
       </c>
       <c r="G147" s="7">
-        <v>0.315642</v>
+        <v>0.32738599999999995</v>
       </c>
       <c r="H147" s="7">
-        <v>0.213278</v>
+        <v>0.220008</v>
       </c>
       <c r="I147" s="7">
-        <v>0.56665</v>
+        <v>0.585114</v>
       </c>
       <c r="J147" s="7">
-        <v>2.9369549999999998</v>
+        <v>2.958793</v>
       </c>
       <c r="K147" s="7">
-        <v>8.189715</v>
+        <v>8.240689</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -7386,25 +7386,25 @@
         <v>4</v>
       </c>
       <c r="E148" s="7">
-        <v>0.015195</v>
+        <v>0.01262</v>
       </c>
       <c r="F148" s="7">
-        <v>0.0019270000000000001</v>
+        <v>0.005661</v>
       </c>
       <c r="G148" s="7">
-        <v>0.26193500000000003</v>
+        <v>0.268034</v>
       </c>
       <c r="H148" s="7">
-        <v>0.183051</v>
+        <v>0.18746</v>
       </c>
       <c r="I148" s="7">
-        <v>0.496583</v>
+        <v>0.5000990000000001</v>
       </c>
       <c r="J148" s="7">
-        <v>3.404121</v>
+        <v>3.4205349999999997</v>
       </c>
       <c r="K148" s="7">
-        <v>9.438711</v>
+        <v>9.477616000000001</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -7421,25 +7421,25 @@
         <v>3</v>
       </c>
       <c r="E149" s="7">
-        <v>0.028086000000000003</v>
+        <v>0.026475</v>
       </c>
       <c r="F149" s="7">
-        <v>0.08698399999999999</v>
+        <v>0.091074</v>
       </c>
       <c r="G149" s="7">
-        <v>0.35316699999999995</v>
+        <v>0.381748</v>
       </c>
       <c r="H149" s="7">
-        <v>0.294723</v>
+        <v>0.299593</v>
       </c>
       <c r="I149" s="7">
-        <v>0.623858</v>
+        <v>0.6292179999999999</v>
       </c>
       <c r="J149" s="7">
-        <v>3.1605329999999996</v>
+        <v>3.176184</v>
       </c>
       <c r="K149" s="7">
-        <v>9.568349</v>
+        <v>9.608106</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -7456,25 +7456,25 @@
         <v>4</v>
       </c>
       <c r="E150" s="7">
-        <v>0.029553</v>
+        <v>0.025118</v>
       </c>
       <c r="F150" s="7">
-        <v>0.075779</v>
+        <v>0.076416</v>
       </c>
       <c r="G150" s="7">
-        <v>0.21018799999999999</v>
+        <v>0.211846</v>
       </c>
       <c r="H150" s="7">
-        <v>0.152506</v>
+        <v>0.153189</v>
       </c>
       <c r="I150" s="7">
-        <v>0.46123800000000004</v>
+        <v>0.460799</v>
       </c>
       <c r="J150" s="7">
-        <v>2.28522</v>
+        <v>2.287165</v>
       </c>
       <c r="K150" s="7">
-        <v>6.532272000000001</v>
+        <v>6.536732</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -7491,25 +7491,25 @@
         <v>4</v>
       </c>
       <c r="E151" s="7">
-        <v>0.024548999999999998</v>
+        <v>0.017255</v>
       </c>
       <c r="F151" s="7">
-        <v>0.014894000000000001</v>
+        <v>0.015553999999999998</v>
       </c>
       <c r="G151" s="7">
-        <v>0.21942399999999998</v>
+        <v>0.229791</v>
       </c>
       <c r="H151" s="7">
-        <v>0.14741300000000002</v>
+        <v>0.14815899999999999</v>
       </c>
       <c r="I151" s="7">
-        <v>0.56392</v>
+        <v>0.57302</v>
       </c>
       <c r="J151" s="7">
-        <v>3.310021</v>
+        <v>3.3128219999999997</v>
       </c>
       <c r="K151" s="7">
-        <v>9.558138</v>
+        <v>9.565</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -7526,25 +7526,25 @@
         <v>4</v>
       </c>
       <c r="E152" s="7">
-        <v>0.034023</v>
+        <v>0.037307</v>
       </c>
       <c r="F152" s="7">
-        <v>0.073597</v>
+        <v>0.076951</v>
       </c>
       <c r="G152" s="7">
-        <v>0.202027</v>
+        <v>0.206419</v>
       </c>
       <c r="H152" s="7">
-        <v>0.158339</v>
+        <v>0.161958</v>
       </c>
       <c r="I152" s="7">
-        <v>0.400394</v>
+        <v>0.404356</v>
       </c>
       <c r="J152" s="7">
-        <v>1.6187440000000002</v>
+        <v>1.6269239999999998</v>
       </c>
       <c r="K152" s="7">
-        <v>4.292959</v>
+        <v>4.3094920000000005</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -7561,25 +7561,25 @@
         <v>5</v>
       </c>
       <c r="E153" s="7">
-        <v>0.062763</v>
+        <v>0.069247</v>
       </c>
       <c r="F153" s="7">
-        <v>0.115939</v>
+        <v>0.125382</v>
       </c>
       <c r="G153" s="7">
-        <v>0.345279</v>
+        <v>0.367705</v>
       </c>
       <c r="H153" s="7">
-        <v>0.296101</v>
+        <v>0.30707</v>
       </c>
       <c r="I153" s="7">
-        <v>0.5852040000000001</v>
+        <v>0.596834</v>
       </c>
       <c r="J153" s="7">
-        <v>3.0351139999999996</v>
+        <v>3.069262</v>
       </c>
       <c r="K153" s="7">
-        <v>8.727834</v>
+        <v>8.810157</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -7596,25 +7596,25 @@
         <v>7</v>
       </c>
       <c r="E154" s="7">
-        <v>0.056393000000000006</v>
+        <v>0.061925</v>
       </c>
       <c r="F154" s="7">
-        <v>0.112125</v>
+        <v>0.12025499999999999</v>
       </c>
       <c r="G154" s="7">
-        <v>0.318612</v>
+        <v>0.33647</v>
       </c>
       <c r="H154" s="7">
-        <v>0.265335</v>
+        <v>0.274586</v>
       </c>
       <c r="I154" s="7">
-        <v>0.5693</v>
+        <v>0.578984</v>
       </c>
       <c r="J154" s="7">
-        <v>2.902969</v>
+        <v>2.931504</v>
       </c>
       <c r="K154" s="7">
-        <v>7.4987390000000005</v>
+        <v>7.560873</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -7631,25 +7631,25 @@
         <v>3</v>
       </c>
       <c r="E155" s="7">
-        <v>0.026602999999999998</v>
+        <v>0.025362</v>
       </c>
       <c r="F155" s="7">
-        <v>0.06429</v>
+        <v>0.06537799999999999</v>
       </c>
       <c r="G155" s="7">
-        <v>0.205703</v>
+        <v>0.204287</v>
       </c>
       <c r="H155" s="7">
-        <v>0.139208</v>
+        <v>0.140372</v>
       </c>
       <c r="I155" s="7">
-        <v>0.470955</v>
+        <v>0.47115</v>
       </c>
       <c r="J155" s="7">
-        <v>2.970559</v>
+        <v>2.974615</v>
       </c>
       <c r="K155" s="7">
-        <v>5.116987</v>
+        <v>5.123236</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -7666,22 +7666,22 @@
         <v>3</v>
       </c>
       <c r="E156" s="7">
-        <v>0.09032400000000002</v>
+        <v>0.09274900000000001</v>
       </c>
       <c r="F156" s="7">
-        <v>0.054382</v>
+        <v>0.059787</v>
       </c>
       <c r="G156" s="7">
-        <v>0.263627</v>
+        <v>0.278405</v>
       </c>
       <c r="H156" s="7">
-        <v>0.188621</v>
+        <v>0.194714</v>
       </c>
       <c r="I156" s="7">
-        <v>0.5328309999999999</v>
+        <v>0.5390849999999999</v>
       </c>
       <c r="J156" s="7">
-        <v>3.5717849999999998</v>
+        <v>3.59522</v>
       </c>
       <c r="K156" s="7"/>
     </row>
@@ -7699,16 +7699,16 @@
         <v>4</v>
       </c>
       <c r="E157" s="7">
-        <v>0.04101200000000001</v>
+        <v>0.038224999999999995</v>
       </c>
       <c r="F157" s="7">
-        <v>0.072827</v>
+        <v>0.07535599999999999</v>
       </c>
       <c r="G157" s="7">
-        <v>0.279866</v>
+        <v>0.28532</v>
       </c>
       <c r="H157" s="7">
-        <v>0.21933</v>
+        <v>0.222204</v>
       </c>
       <c r="I157" s="7"/>
       <c r="J157" s="7"/>
@@ -7728,22 +7728,22 @@
         <v>6</v>
       </c>
       <c r="E158" s="7">
-        <v>0.046485000000000005</v>
+        <v>0.041822</v>
       </c>
       <c r="F158" s="7">
-        <v>0.05008</v>
+        <v>0.059036</v>
       </c>
       <c r="G158" s="7">
-        <v>0.267305</v>
+        <v>0.289721</v>
       </c>
       <c r="H158" s="7">
-        <v>0.214527</v>
+        <v>0.22488600000000003</v>
       </c>
       <c r="I158" s="7">
-        <v>0.433147</v>
+        <v>0.443786</v>
       </c>
       <c r="J158" s="7">
-        <v>1.79463</v>
+        <v>1.818465</v>
       </c>
       <c r="K158" s="7"/>
     </row>
@@ -7761,25 +7761,25 @@
         <v>3</v>
       </c>
       <c r="E159" s="7">
-        <v>0.041609999999999994</v>
+        <v>0.041047</v>
       </c>
       <c r="F159" s="7">
-        <v>0.08875899999999999</v>
+        <v>0.09164</v>
       </c>
       <c r="G159" s="7">
-        <v>0.268237</v>
+        <v>0.271968</v>
       </c>
       <c r="H159" s="7">
-        <v>0.19463</v>
+        <v>0.197791</v>
       </c>
       <c r="I159" s="7">
-        <v>0.539745</v>
+        <v>0.54352</v>
       </c>
       <c r="J159" s="7">
-        <v>2.588929</v>
+        <v>2.598426</v>
       </c>
       <c r="K159" s="7">
-        <v>6.519991999999999</v>
+        <v>6.539890000000001</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -7796,25 +7796,25 @@
         <v>3</v>
       </c>
       <c r="E160" s="7">
-        <v>0.046332000000000005</v>
+        <v>0.045517</v>
       </c>
       <c r="F160" s="7">
-        <v>0.093692</v>
+        <v>0.096922</v>
       </c>
       <c r="G160" s="7">
-        <v>0.264483</v>
+        <v>0.269218</v>
       </c>
       <c r="H160" s="7">
-        <v>0.197182</v>
+        <v>0.200718</v>
       </c>
       <c r="I160" s="7">
-        <v>0.501058</v>
+        <v>0.504938</v>
       </c>
       <c r="J160" s="7">
-        <v>2.384299</v>
+        <v>2.394294</v>
       </c>
       <c r="K160" s="7">
-        <v>6.0464340000000005</v>
+        <v>6.067245000000001</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -7831,25 +7831,25 @@
         <v>3</v>
       </c>
       <c r="E161" s="7">
-        <v>0.037202</v>
+        <v>0.037214</v>
       </c>
       <c r="F161" s="7">
-        <v>0.077376</v>
+        <v>0.079823</v>
       </c>
       <c r="G161" s="7">
-        <v>0.232366</v>
+        <v>0.23611100000000002</v>
       </c>
       <c r="H161" s="7">
-        <v>0.16064299999999998</v>
+        <v>0.163279</v>
       </c>
       <c r="I161" s="7">
-        <v>0.43811900000000004</v>
+        <v>0.44079</v>
       </c>
       <c r="J161" s="7">
-        <v>1.957016</v>
+        <v>1.963733</v>
       </c>
       <c r="K161" s="7">
-        <v>5.1136360000000005</v>
+        <v>5.127522</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -7866,22 +7866,22 @@
         <v>5</v>
       </c>
       <c r="E162" s="7">
-        <v>0.155687</v>
+        <v>0.156729</v>
       </c>
       <c r="F162" s="7">
-        <v>0.246863</v>
+        <v>0.266205</v>
       </c>
       <c r="G162" s="7">
-        <v>0.39237900000000003</v>
+        <v>0.448085</v>
       </c>
       <c r="H162" s="7">
-        <v>0.353576</v>
+        <v>0.374573</v>
       </c>
       <c r="I162" s="7">
-        <v>0.7397589999999999</v>
+        <v>0.748894</v>
       </c>
       <c r="J162" s="7">
-        <v>4.3433589999999995</v>
+        <v>4.426247</v>
       </c>
       <c r="K162" s="7"/>
     </row>
@@ -7899,25 +7899,25 @@
         <v>4</v>
       </c>
       <c r="E163" s="7">
-        <v>0.020505</v>
+        <v>0.013018</v>
       </c>
       <c r="F163" s="7">
-        <v>0.015341</v>
+        <v>0.015275</v>
       </c>
       <c r="G163" s="7">
-        <v>0.211817</v>
+        <v>0.211452</v>
       </c>
       <c r="H163" s="7">
-        <v>0.10627700000000001</v>
+        <v>0.106205</v>
       </c>
       <c r="I163" s="7">
-        <v>0.41647399999999996</v>
+        <v>0.41271599999999997</v>
       </c>
       <c r="J163" s="7">
-        <v>2.031371</v>
+        <v>2.031173</v>
       </c>
       <c r="K163" s="7">
-        <v>5.63725</v>
+        <v>5.636818</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -7934,22 +7934,22 @@
         <v>4</v>
       </c>
       <c r="E164" s="7">
-        <v>0.030462</v>
+        <v>0.029769</v>
       </c>
       <c r="F164" s="7">
-        <v>0.079917</v>
+        <v>0.08100500000000001</v>
       </c>
       <c r="G164" s="7">
-        <v>0.22303599999999998</v>
+        <v>0.2231</v>
       </c>
       <c r="H164" s="7">
-        <v>0.16761299999999998</v>
+        <v>0.16878900000000002</v>
       </c>
       <c r="I164" s="7">
-        <v>0.528026</v>
+        <v>0.529266</v>
       </c>
       <c r="J164" s="7">
-        <v>3.293623</v>
+        <v>3.2979469999999997</v>
       </c>
       <c r="K164" s="7"/>
     </row>
@@ -7967,22 +7967,22 @@
         <v>6</v>
       </c>
       <c r="E165" s="7">
-        <v>0.016871</v>
+        <v>0.00662</v>
       </c>
       <c r="F165" s="7">
-        <v>0.006444999999999999</v>
+        <v>0.012675</v>
       </c>
       <c r="G165" s="7">
-        <v>0.113644</v>
+        <v>0.133817</v>
       </c>
       <c r="H165" s="7">
-        <v>0.081577</v>
+        <v>0.08827199999999999</v>
       </c>
       <c r="I165" s="7">
-        <v>0.404721</v>
+        <v>0.40149700000000005</v>
       </c>
       <c r="J165" s="7">
-        <v>2.638193</v>
+        <v>2.660713</v>
       </c>
       <c r="K165" s="7"/>
     </row>
@@ -8000,25 +8000,25 @@
         <v>5</v>
       </c>
       <c r="E166" s="7">
-        <v>0.065946</v>
+        <v>0.072451</v>
       </c>
       <c r="F166" s="7">
-        <v>0.12734199999999998</v>
+        <v>0.13995100000000002</v>
       </c>
       <c r="G166" s="7">
-        <v>0.388183</v>
+        <v>0.41287599999999997</v>
       </c>
       <c r="H166" s="7">
-        <v>0.30787600000000004</v>
+        <v>0.32250300000000004</v>
       </c>
       <c r="I166" s="7">
-        <v>0.6603279999999999</v>
+        <v>0.6786329999999999</v>
       </c>
       <c r="J166" s="7">
-        <v>2.625957</v>
+        <v>2.666511</v>
       </c>
       <c r="K166" s="7">
-        <v>8.941151</v>
+        <v>9.052337</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -8035,25 +8035,25 @@
         <v>6</v>
       </c>
       <c r="E167" s="7">
-        <v>0.039852</v>
+        <v>0.035977999999999996</v>
       </c>
       <c r="F167" s="7">
-        <v>0.039771</v>
+        <v>0.045776000000000004</v>
       </c>
       <c r="G167" s="7">
-        <v>0.409724</v>
+        <v>0.426364</v>
       </c>
       <c r="H167" s="7">
-        <v>0.314548</v>
+        <v>0.32214</v>
       </c>
       <c r="I167" s="7">
-        <v>0.607727</v>
+        <v>0.614328</v>
       </c>
       <c r="J167" s="7">
-        <v>2.017953</v>
+        <v>2.035384</v>
       </c>
       <c r="K167" s="7">
-        <v>3.702553</v>
+        <v>3.729713</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -8070,25 +8070,25 @@
         <v>6</v>
       </c>
       <c r="E168" s="7">
-        <v>0.030158</v>
+        <v>0.026307</v>
       </c>
       <c r="F168" s="7">
-        <v>0.001613</v>
+        <v>0.008394</v>
       </c>
       <c r="G168" s="7">
-        <v>0.355403</v>
+        <v>0.373354</v>
       </c>
       <c r="H168" s="7">
-        <v>0.257702</v>
+        <v>0.266217</v>
       </c>
       <c r="I168" s="7">
-        <v>0.445681</v>
+        <v>0.45199599999999995</v>
       </c>
       <c r="J168" s="7">
-        <v>2.745577</v>
+        <v>2.7709339999999996</v>
       </c>
       <c r="K168" s="7">
-        <v>15.613833</v>
+        <v>15.726305</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -8105,25 +8105,25 @@
         <v>3</v>
       </c>
       <c r="E169" s="7">
-        <v>0.015028999999999999</v>
+        <v>0.0032740000000000004</v>
       </c>
       <c r="F169" s="7">
-        <v>0.007327</v>
+        <v>0.005013999999999999</v>
       </c>
       <c r="G169" s="7">
-        <v>0.145778</v>
+        <v>0.140037</v>
       </c>
       <c r="H169" s="7">
-        <v>0.052602</v>
+        <v>0.05018500000000001</v>
       </c>
       <c r="I169" s="7">
-        <v>0.387064</v>
+        <v>0.383537</v>
       </c>
       <c r="J169" s="7">
-        <v>1.9027889999999998</v>
+        <v>1.896125</v>
       </c>
       <c r="K169" s="7">
-        <v>3.955471</v>
+        <v>3.9440929999999996</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -8140,25 +8140,25 @@
         <v>3</v>
       </c>
       <c r="E170" s="7">
-        <v>0.035535000000000004</v>
+        <v>0.036695000000000005</v>
       </c>
       <c r="F170" s="7">
-        <v>0.089344</v>
+        <v>0.092697</v>
       </c>
       <c r="G170" s="7">
-        <v>0.270225</v>
+        <v>0.276095</v>
       </c>
       <c r="H170" s="7">
-        <v>0.187502</v>
+        <v>0.191157</v>
       </c>
       <c r="I170" s="7">
-        <v>0.465135</v>
+        <v>0.469534</v>
       </c>
       <c r="J170" s="7">
-        <v>2.018794</v>
+        <v>2.028085</v>
       </c>
       <c r="K170" s="7">
-        <v>5.49973</v>
+        <v>5.519734</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -8175,25 +8175,25 @@
         <v>5</v>
       </c>
       <c r="E171" s="7">
-        <v>0.02331</v>
+        <v>0.02226</v>
       </c>
       <c r="F171" s="7">
-        <v>0.061898</v>
+        <v>0.062761</v>
       </c>
       <c r="G171" s="7">
-        <v>0.126358</v>
+        <v>0.126434</v>
       </c>
       <c r="H171" s="7">
-        <v>0.09315699999999999</v>
+        <v>0.094045</v>
       </c>
       <c r="I171" s="7">
-        <v>0.29675999999999997</v>
+        <v>0.297653</v>
       </c>
       <c r="J171" s="7">
-        <v>1.96874</v>
+        <v>1.9711519999999998</v>
       </c>
       <c r="K171" s="7">
-        <v>5.483545</v>
+        <v>5.488810999999999</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -8210,22 +8210,22 @@
         <v>6</v>
       </c>
       <c r="E172" s="7">
-        <v>0.002852</v>
+        <v>-0.006313</v>
       </c>
       <c r="F172" s="7">
-        <v>-0.055614</v>
+        <v>-0.056559</v>
       </c>
       <c r="G172" s="7">
-        <v>0.149961</v>
+        <v>0.16183</v>
       </c>
       <c r="H172" s="7">
-        <v>0.11104599999999999</v>
+        <v>0.10993399999999999</v>
       </c>
       <c r="I172" s="7">
-        <v>0.6445059999999999</v>
+        <v>0.6419360000000001</v>
       </c>
       <c r="J172" s="7">
-        <v>4.688816</v>
+        <v>4.683122</v>
       </c>
       <c r="K172" s="7"/>
     </row>
@@ -8243,22 +8243,22 @@
         <v>6</v>
       </c>
       <c r="E173" s="7">
-        <v>0.032757</v>
+        <v>0.02993</v>
       </c>
       <c r="F173" s="7">
-        <v>0.032358</v>
+        <v>0.04041</v>
       </c>
       <c r="G173" s="7">
-        <v>0.289039</v>
+        <v>0.311351</v>
       </c>
       <c r="H173" s="7">
-        <v>0.22453399999999998</v>
+        <v>0.23408400000000001</v>
       </c>
       <c r="I173" s="7">
-        <v>0.44278300000000004</v>
+        <v>0.45177</v>
       </c>
       <c r="J173" s="7">
-        <v>2.399573</v>
+        <v>2.426087</v>
       </c>
       <c r="K173" s="7"/>
     </row>
@@ -8276,16 +8276,16 @@
         <v>7</v>
       </c>
       <c r="E174" s="7">
-        <v>0.155122</v>
+        <v>0.11681100000000001</v>
       </c>
       <c r="F174" s="7">
-        <v>0.110859</v>
+        <v>0.10871600000000001</v>
       </c>
       <c r="G174" s="7">
-        <v>0.658762</v>
+        <v>0.6900759999999999</v>
       </c>
       <c r="H174" s="7">
-        <v>0.206186</v>
+        <v>0.20385999999999999</v>
       </c>
       <c r="I174" s="7"/>
       <c r="J174" s="7"/>
@@ -8305,25 +8305,25 @@
         <v>6</v>
       </c>
       <c r="E175" s="7">
-        <v>-0.004225</v>
+        <v>-0.014445</v>
       </c>
       <c r="F175" s="7">
-        <v>-0.064605</v>
+        <v>-0.06595</v>
       </c>
       <c r="G175" s="7">
-        <v>0.13198600000000002</v>
+        <v>0.143703</v>
       </c>
       <c r="H175" s="7">
-        <v>0.073509</v>
+        <v>0.071966</v>
       </c>
       <c r="I175" s="7">
-        <v>0.59553</v>
+        <v>0.597938</v>
       </c>
       <c r="J175" s="7">
-        <v>4.073416</v>
+        <v>4.066120000000001</v>
       </c>
       <c r="K175" s="7">
-        <v>13.171563</v>
+        <v>13.151185</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -8340,25 +8340,25 @@
         <v>4</v>
       </c>
       <c r="E176" s="7">
-        <v>0.023254</v>
+        <v>0.014494</v>
       </c>
       <c r="F176" s="7">
-        <v>0.014068</v>
+        <v>0.014025000000000001</v>
       </c>
       <c r="G176" s="7">
-        <v>0.230275</v>
+        <v>0.23081600000000002</v>
       </c>
       <c r="H176" s="7">
-        <v>0.11931699999999999</v>
+        <v>0.119269</v>
       </c>
       <c r="I176" s="7">
-        <v>0.442729</v>
+        <v>0.442504</v>
       </c>
       <c r="J176" s="7">
-        <v>2.0648929999999996</v>
+        <v>2.064762</v>
       </c>
       <c r="K176" s="7">
-        <v>5.386564</v>
+        <v>5.386291</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -8375,25 +8375,25 @@
         <v>5</v>
       </c>
       <c r="E177" s="7">
-        <v>0.032618</v>
+        <v>0.029491</v>
       </c>
       <c r="F177" s="7">
-        <v>0.031661</v>
+        <v>0.036938</v>
       </c>
       <c r="G177" s="7">
-        <v>0.33193399999999995</v>
+        <v>0.345324</v>
       </c>
       <c r="H177" s="7">
-        <v>0.234728</v>
+        <v>0.24104299999999998</v>
       </c>
       <c r="I177" s="7">
-        <v>0.443109</v>
+        <v>0.45110799999999995</v>
       </c>
       <c r="J177" s="7">
-        <v>2.654835</v>
+        <v>2.673529</v>
       </c>
       <c r="K177" s="7">
-        <v>10.467268999999998</v>
+        <v>10.525922000000001</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -8410,25 +8410,25 @@
         <v>5</v>
       </c>
       <c r="E178" s="7">
-        <v>0.015288</v>
+        <v>0.008754999999999999</v>
       </c>
       <c r="F178" s="7">
-        <v>0.034892</v>
+        <v>0.035901</v>
       </c>
       <c r="G178" s="7">
-        <v>0.10097400000000001</v>
+        <v>0.102075</v>
       </c>
       <c r="H178" s="7">
-        <v>0.062762</v>
+        <v>0.063799</v>
       </c>
       <c r="I178" s="7">
-        <v>0.302756</v>
+        <v>0.30089</v>
       </c>
       <c r="J178" s="7">
-        <v>2.047294</v>
+        <v>2.050266</v>
       </c>
       <c r="K178" s="7">
-        <v>6.229804000000001</v>
+        <v>6.236853999999999</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -8445,25 +8445,25 @@
         <v>6</v>
       </c>
       <c r="E179" s="7">
-        <v>0.062067</v>
+        <v>0.057434000000000006</v>
       </c>
       <c r="F179" s="7">
-        <v>0.074415</v>
+        <v>0.082857</v>
       </c>
       <c r="G179" s="7">
-        <v>0.29608799999999996</v>
+        <v>0.32175800000000004</v>
       </c>
       <c r="H179" s="7">
-        <v>0.227563</v>
+        <v>0.237208</v>
       </c>
       <c r="I179" s="7">
-        <v>0.559346</v>
+        <v>0.568839</v>
       </c>
       <c r="J179" s="7">
-        <v>2.8890179999999996</v>
+        <v>2.919575</v>
       </c>
       <c r="K179" s="7">
-        <v>12.457372</v>
+        <v>12.563111</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -8480,25 +8480,25 @@
         <v>6</v>
       </c>
       <c r="E180" s="7">
-        <v>0.038181</v>
+        <v>0.035796999999999995</v>
       </c>
       <c r="F180" s="7">
-        <v>0.042621</v>
+        <v>0.049517</v>
       </c>
       <c r="G180" s="7">
-        <v>0.400821</v>
+        <v>0.420533</v>
       </c>
       <c r="H180" s="7">
-        <v>0.282728</v>
+        <v>0.291213</v>
       </c>
       <c r="I180" s="7">
-        <v>0.550424</v>
+        <v>0.556904</v>
       </c>
       <c r="J180" s="7">
-        <v>3.11779</v>
+        <v>3.1450270000000002</v>
       </c>
       <c r="K180" s="7">
-        <v>17.258789999999998</v>
+        <v>17.379564000000002</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -8515,25 +8515,25 @@
         <v>6</v>
       </c>
       <c r="E181" s="7">
-        <v>0.035145</v>
+        <v>0.031172</v>
       </c>
       <c r="F181" s="7">
-        <v>0.040295</v>
+        <v>0.04506</v>
       </c>
       <c r="G181" s="7">
-        <v>0.361976</v>
+        <v>0.37628999999999996</v>
       </c>
       <c r="H181" s="7">
-        <v>0.236078</v>
+        <v>0.24173999999999998</v>
       </c>
       <c r="I181" s="7">
-        <v>0.516782</v>
+        <v>0.520724</v>
       </c>
       <c r="J181" s="7">
-        <v>3.035962</v>
+        <v>3.054447</v>
       </c>
       <c r="K181" s="7">
-        <v>12.864903</v>
+        <v>12.928406</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -8550,25 +8550,25 @@
         <v>4</v>
       </c>
       <c r="E182" s="7">
-        <v>0.035789</v>
+        <v>0.030078999999999998</v>
       </c>
       <c r="F182" s="7">
-        <v>0.043825</v>
+        <v>0.046218</v>
       </c>
       <c r="G182" s="7">
-        <v>0.317582</v>
+        <v>0.324027</v>
       </c>
       <c r="H182" s="7">
-        <v>0.204378</v>
+        <v>0.207139</v>
       </c>
       <c r="I182" s="7">
-        <v>0.535752</v>
+        <v>0.535765</v>
       </c>
       <c r="J182" s="7">
-        <v>3.353629</v>
+        <v>3.363607</v>
       </c>
       <c r="K182" s="7">
-        <v>11.298502000000001</v>
+        <v>11.326688999999998</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -8585,25 +8585,25 @@
         <v>6</v>
       </c>
       <c r="E183" s="7">
-        <v>0.092822</v>
+        <v>0.084555</v>
       </c>
       <c r="F183" s="7">
-        <v>0.109872</v>
+        <v>0.11627499999999999</v>
       </c>
       <c r="G183" s="7">
-        <v>0.195738</v>
+        <v>0.221811</v>
       </c>
       <c r="H183" s="7">
-        <v>0.16181</v>
+        <v>0.16851400000000002</v>
       </c>
       <c r="I183" s="7">
-        <v>0.546846</v>
+        <v>0.548537</v>
       </c>
       <c r="J183" s="7">
-        <v>3.338619</v>
+        <v>3.363652</v>
       </c>
       <c r="K183" s="7">
-        <v>8.784729</v>
+        <v>8.841185000000001</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -8620,25 +8620,25 @@
         <v>2</v>
       </c>
       <c r="E184" s="7">
-        <v>0.027751</v>
+        <v>0.023833000000000003</v>
       </c>
       <c r="F184" s="7">
-        <v>0.07106</v>
+        <v>0.07142</v>
       </c>
       <c r="G184" s="7">
-        <v>0.210984</v>
+        <v>0.208507</v>
       </c>
       <c r="H184" s="7">
-        <v>0.142512</v>
+        <v>0.142897</v>
       </c>
       <c r="I184" s="7">
-        <v>0.48735999999999996</v>
+        <v>0.486166</v>
       </c>
       <c r="J184" s="7">
-        <v>3.33582</v>
+        <v>3.3372789999999997</v>
       </c>
       <c r="K184" s="7">
-        <v>6.3453610000000005</v>
+        <v>6.347831</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -8655,25 +8655,25 @@
         <v>4</v>
       </c>
       <c r="E185" s="7">
-        <v>0.032509</v>
+        <v>0.026628</v>
       </c>
       <c r="F185" s="7">
-        <v>0.009760999999999999</v>
+        <v>0.012121</v>
       </c>
       <c r="G185" s="7">
-        <v>0.1704</v>
+        <v>0.17767</v>
       </c>
       <c r="H185" s="7">
-        <v>0.17210999999999999</v>
+        <v>0.174849</v>
       </c>
       <c r="I185" s="7">
-        <v>0.340193</v>
+        <v>0.341781</v>
       </c>
       <c r="J185" s="7">
-        <v>2.365739</v>
+        <v>2.373606</v>
       </c>
       <c r="K185" s="7">
-        <v>3.9361599999999997</v>
+        <v>3.947698</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -8690,25 +8690,25 @@
         <v>6</v>
       </c>
       <c r="E186" s="7">
-        <v>0.098685</v>
+        <v>0.10780300000000001</v>
       </c>
       <c r="F186" s="7">
-        <v>0.174089</v>
+        <v>0.18820900000000002</v>
       </c>
       <c r="G186" s="7">
-        <v>0.5231439999999999</v>
+        <v>0.554882</v>
       </c>
       <c r="H186" s="7">
-        <v>0.415122</v>
+        <v>0.43213999999999997</v>
       </c>
       <c r="I186" s="7">
-        <v>0.73238</v>
+        <v>0.753635</v>
       </c>
       <c r="J186" s="7">
-        <v>3.458879</v>
+        <v>3.512502</v>
       </c>
       <c r="K186" s="7">
-        <v>13.681927</v>
+        <v>13.858494</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -8725,25 +8725,25 @@
         <v>3</v>
       </c>
       <c r="E187" s="7">
-        <v>0.030816</v>
+        <v>0.030556999999999997</v>
       </c>
       <c r="F187" s="7">
-        <v>0.087103</v>
+        <v>0.088002</v>
       </c>
       <c r="G187" s="7">
-        <v>0.192813</v>
+        <v>0.19032900000000003</v>
       </c>
       <c r="H187" s="7">
-        <v>0.135112</v>
+        <v>0.136051</v>
       </c>
       <c r="I187" s="7">
-        <v>0.453705</v>
+        <v>0.45321100000000003</v>
       </c>
       <c r="J187" s="7">
-        <v>1.7757409999999998</v>
+        <v>1.7780369999999999</v>
       </c>
       <c r="K187" s="7">
-        <v>3.849484</v>
+        <v>3.8534949999999997</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,25 +8760,25 @@
         <v>5</v>
       </c>
       <c r="E188" s="7">
-        <v>0.086035</v>
+        <v>0.092184</v>
       </c>
       <c r="F188" s="7">
-        <v>0.140724</v>
+        <v>0.151625</v>
       </c>
       <c r="G188" s="7">
-        <v>0.396357</v>
+        <v>0.41509599999999997</v>
       </c>
       <c r="H188" s="7">
-        <v>0.31495999999999996</v>
+        <v>0.32752699999999996</v>
       </c>
       <c r="I188" s="7">
-        <v>0.6574890000000001</v>
+        <v>0.6721699999999999</v>
       </c>
       <c r="J188" s="7">
-        <v>3.146649</v>
+        <v>3.1862779999999997</v>
       </c>
       <c r="K188" s="7">
-        <v>11.657828</v>
+        <v>11.778796</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -8795,25 +8795,25 @@
         <v>2</v>
       </c>
       <c r="E189" s="7">
-        <v>0.030945</v>
+        <v>0.030674999999999997</v>
       </c>
       <c r="F189" s="7">
-        <v>0.08727299999999999</v>
+        <v>0.088162</v>
       </c>
       <c r="G189" s="7">
-        <v>0.190423</v>
+        <v>0.18796800000000002</v>
       </c>
       <c r="H189" s="7">
-        <v>0.134746</v>
+        <v>0.135673</v>
       </c>
       <c r="I189" s="7">
-        <v>0.448704</v>
+        <v>0.448834</v>
       </c>
       <c r="J189" s="7">
-        <v>1.862909</v>
+        <v>1.865249</v>
       </c>
       <c r="K189" s="7">
-        <v>3.353165</v>
+        <v>3.356724</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -8830,25 +8830,25 @@
         <v>2</v>
       </c>
       <c r="E190" s="7">
-        <v>0.024744000000000002</v>
+        <v>0.024944</v>
       </c>
       <c r="F190" s="7">
-        <v>0.064378</v>
+        <v>0.065245</v>
       </c>
       <c r="G190" s="7">
-        <v>0.15513</v>
+        <v>0.152965</v>
       </c>
       <c r="H190" s="7">
-        <v>0.109557</v>
+        <v>0.11045999999999999</v>
       </c>
       <c r="I190" s="7">
-        <v>0.377914</v>
+        <v>0.3779</v>
       </c>
       <c r="J190" s="7">
-        <v>2.0014629999999998</v>
+        <v>2.003907</v>
       </c>
       <c r="K190" s="7">
-        <v>3.333421</v>
+        <v>3.33695</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -8865,19 +8865,19 @@
         <v>6</v>
       </c>
       <c r="E191" s="7">
-        <v>0.154658</v>
+        <v>0.09077500000000001</v>
       </c>
       <c r="F191" s="7">
-        <v>0.09974</v>
+        <v>0.082387</v>
       </c>
       <c r="G191" s="7">
-        <v>0.615398</v>
+        <v>0.632368</v>
       </c>
       <c r="H191" s="7">
-        <v>0.181518</v>
+        <v>0.16287400000000002</v>
       </c>
       <c r="I191" s="7">
-        <v>1.7559790000000002</v>
+        <v>1.7502760000000002</v>
       </c>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
@@ -8896,25 +8896,25 @@
         <v>6</v>
       </c>
       <c r="E192" s="7">
-        <v>0.0018859999999999999</v>
+        <v>-0.006807</v>
       </c>
       <c r="F192" s="7">
-        <v>-0.054150000000000004</v>
+        <v>-0.054798</v>
       </c>
       <c r="G192" s="7">
-        <v>0.143002</v>
+        <v>0.155014</v>
       </c>
       <c r="H192" s="7">
-        <v>0.08881299999999999</v>
+        <v>0.08806599999999999</v>
       </c>
       <c r="I192" s="7">
-        <v>0.62197</v>
+        <v>0.623923</v>
       </c>
       <c r="J192" s="7">
-        <v>3.9791969999999997</v>
+        <v>3.975784</v>
       </c>
       <c r="K192" s="7">
-        <v>12.959031</v>
+        <v>12.949462</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -8931,25 +8931,25 @@
         <v>6</v>
       </c>
       <c r="E193" s="7">
-        <v>-0.007904</v>
+        <v>-0.019638</v>
       </c>
       <c r="F193" s="7">
-        <v>-0.070871</v>
+        <v>-0.072605</v>
       </c>
       <c r="G193" s="7">
-        <v>0.10359199999999999</v>
+        <v>0.11427799999999999</v>
       </c>
       <c r="H193" s="7">
-        <v>0.054405</v>
+        <v>0.052438000000000005</v>
       </c>
       <c r="I193" s="7">
-        <v>0.580344</v>
+        <v>0.583743</v>
       </c>
       <c r="J193" s="7">
-        <v>3.866672</v>
+        <v>3.8575920000000004</v>
       </c>
       <c r="K193" s="7">
-        <v>12.63684</v>
+        <v>12.611396</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -8966,25 +8966,25 @@
         <v>4</v>
       </c>
       <c r="E194" s="7">
-        <v>0.018506</v>
+        <v>0.010536</v>
       </c>
       <c r="F194" s="7">
-        <v>0.029459</v>
+        <v>0.029719000000000002</v>
       </c>
       <c r="G194" s="7">
-        <v>0.250405</v>
+        <v>0.25211</v>
       </c>
       <c r="H194" s="7">
-        <v>0.14386200000000002</v>
+        <v>0.144151</v>
       </c>
       <c r="I194" s="7">
-        <v>0.471976</v>
+        <v>0.472481</v>
       </c>
       <c r="J194" s="7">
-        <v>1.843448</v>
+        <v>1.844167</v>
       </c>
       <c r="K194" s="7">
-        <v>5.040131</v>
+        <v>5.041657</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -9001,25 +9001,25 @@
         <v>4</v>
       </c>
       <c r="E195" s="7">
-        <v>0.022527</v>
+        <v>0.017396000000000002</v>
       </c>
       <c r="F195" s="7">
-        <v>0.031757</v>
+        <v>0.033506999999999995</v>
       </c>
       <c r="G195" s="7">
-        <v>0.20738800000000002</v>
+        <v>0.20858100000000002</v>
       </c>
       <c r="H195" s="7">
-        <v>0.11412499999999999</v>
+        <v>0.116015</v>
       </c>
       <c r="I195" s="7">
-        <v>0.433654</v>
+        <v>0.430982</v>
       </c>
       <c r="J195" s="7">
-        <v>2.254768</v>
+        <v>2.2602889999999998</v>
       </c>
       <c r="K195" s="7">
-        <v>5.52876</v>
+        <v>5.539835</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -9036,25 +9036,25 @@
         <v>6</v>
       </c>
       <c r="E196" s="7">
-        <v>0.014480999999999999</v>
+        <v>0.008409999999999999</v>
       </c>
       <c r="F196" s="7">
-        <v>0.028769</v>
+        <v>0.030312000000000002</v>
       </c>
       <c r="G196" s="7">
-        <v>0.103345</v>
+        <v>0.103801</v>
       </c>
       <c r="H196" s="7">
-        <v>0.058682</v>
+        <v>0.060270000000000004</v>
       </c>
       <c r="I196" s="7">
-        <v>0.312022</v>
+        <v>0.310628</v>
       </c>
       <c r="J196" s="7">
-        <v>2.155229</v>
+        <v>2.1599619999999997</v>
       </c>
       <c r="K196" s="7">
-        <v>6.444557</v>
+        <v>6.455724</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -9071,25 +9071,25 @@
         <v>3</v>
       </c>
       <c r="E197" s="7">
-        <v>0.032158</v>
+        <v>0.031674</v>
       </c>
       <c r="F197" s="7">
-        <v>0.09568199999999999</v>
+        <v>0.098218</v>
       </c>
       <c r="G197" s="7">
-        <v>0.27645</v>
+        <v>0.279575</v>
       </c>
       <c r="H197" s="7">
-        <v>0.21090599999999998</v>
+        <v>0.21370799999999998</v>
       </c>
       <c r="I197" s="7">
-        <v>0.470553</v>
+        <v>0.47543799999999997</v>
       </c>
       <c r="J197" s="7">
-        <v>1.629589</v>
+        <v>1.6356739999999999</v>
       </c>
       <c r="K197" s="7">
-        <v>3.7564319999999998</v>
+        <v>3.7674380000000003</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -9106,25 +9106,25 @@
         <v>3</v>
       </c>
       <c r="E198" s="7">
-        <v>0.035599</v>
+        <v>0.034473</v>
       </c>
       <c r="F198" s="7">
-        <v>0.077491</v>
+        <v>0.079737</v>
       </c>
       <c r="G198" s="7">
-        <v>0.250201</v>
+        <v>0.25325600000000004</v>
       </c>
       <c r="H198" s="7">
-        <v>0.157938</v>
+        <v>0.160352</v>
       </c>
       <c r="I198" s="7">
-        <v>0.45142000000000004</v>
+        <v>0.453433</v>
       </c>
       <c r="J198" s="7">
-        <v>1.87948</v>
+        <v>1.885482</v>
       </c>
       <c r="K198" s="7">
-        <v>4.664949</v>
+        <v>4.6767579999999995</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -9141,25 +9141,25 @@
         <v>4</v>
       </c>
       <c r="E199" s="7">
-        <v>0.02464</v>
+        <v>0.016635999999999998</v>
       </c>
       <c r="F199" s="7">
-        <v>0.033687999999999996</v>
+        <v>0.034491</v>
       </c>
       <c r="G199" s="7">
-        <v>0.233451</v>
+        <v>0.233322</v>
       </c>
       <c r="H199" s="7">
-        <v>0.139825</v>
+        <v>0.140711</v>
       </c>
       <c r="I199" s="7">
-        <v>0.462095</v>
+        <v>0.464064</v>
       </c>
       <c r="J199" s="7">
-        <v>2.143723</v>
+        <v>2.146166</v>
       </c>
       <c r="K199" s="7">
-        <v>5.0705860000000005</v>
+        <v>5.075304</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -9176,25 +9176,25 @@
         <v>6</v>
       </c>
       <c r="E200" s="7">
-        <v>0.024207</v>
+        <v>0.0181</v>
       </c>
       <c r="F200" s="7">
-        <v>-0.013635</v>
+        <v>-0.008354</v>
       </c>
       <c r="G200" s="7">
-        <v>0.291616</v>
+        <v>0.30656300000000003</v>
       </c>
       <c r="H200" s="7">
-        <v>0.237257</v>
+        <v>0.24388200000000002</v>
       </c>
       <c r="I200" s="7">
-        <v>0.42013300000000003</v>
+        <v>0.43135100000000004</v>
       </c>
       <c r="J200" s="7">
-        <v>3.648215</v>
+        <v>3.673101</v>
       </c>
       <c r="K200" s="7">
-        <v>20.945997000000002</v>
+        <v>21.063494000000002</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -9211,16 +9211,16 @@
         <v>5</v>
       </c>
       <c r="E201" s="7">
-        <v>0.061413</v>
+        <v>0.056377</v>
       </c>
       <c r="F201" s="7">
-        <v>0.052344999999999996</v>
+        <v>0.059413</v>
       </c>
       <c r="G201" s="7">
-        <v>0.292692</v>
+        <v>0.307862</v>
       </c>
       <c r="H201" s="7">
-        <v>0.22880199999999998</v>
+        <v>0.23705500000000002</v>
       </c>
       <c r="I201" s="7"/>
       <c r="J201" s="7"/>
@@ -9240,25 +9240,25 @@
         <v>6</v>
       </c>
       <c r="E202" s="7">
-        <v>0.043681</v>
+        <v>0.035651999999999996</v>
       </c>
       <c r="F202" s="7">
-        <v>-0.008912</v>
+        <v>-0.004546</v>
       </c>
       <c r="G202" s="7">
-        <v>0.243388</v>
+        <v>0.264872</v>
       </c>
       <c r="H202" s="7">
-        <v>0.121172</v>
+        <v>0.126111</v>
       </c>
       <c r="I202" s="7">
-        <v>0.35830399999999996</v>
+        <v>0.361702</v>
       </c>
       <c r="J202" s="7">
-        <v>2.270615</v>
+        <v>2.285023</v>
       </c>
       <c r="K202" s="7">
-        <v>10.004513</v>
+        <v>10.052992</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -9275,25 +9275,25 @@
         <v>6</v>
       </c>
       <c r="E203" s="7">
-        <v>0.065497</v>
+        <v>0.087016</v>
       </c>
       <c r="F203" s="7">
-        <v>0.08612299999999999</v>
+        <v>0.113553</v>
       </c>
       <c r="G203" s="7">
-        <v>0.351566</v>
+        <v>0.39637300000000003</v>
       </c>
       <c r="H203" s="7">
-        <v>0.23292300000000002</v>
+        <v>0.264061</v>
       </c>
       <c r="I203" s="7">
-        <v>0.47751699999999997</v>
+        <v>0.511653</v>
       </c>
       <c r="J203" s="7">
-        <v>2.544562</v>
+        <v>2.63408</v>
       </c>
       <c r="K203" s="7">
-        <v>9.342186</v>
+        <v>9.603378</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -9310,25 +9310,25 @@
         <v>5</v>
       </c>
       <c r="E204" s="7">
-        <v>0.016440999999999997</v>
+        <v>0.009911999999999999</v>
       </c>
       <c r="F204" s="7">
-        <v>0.014113</v>
+        <v>0.011022</v>
       </c>
       <c r="G204" s="7">
-        <v>0.18395299999999998</v>
+        <v>0.200379</v>
       </c>
       <c r="H204" s="7">
-        <v>0.103642</v>
+        <v>0.10027799999999999</v>
       </c>
       <c r="I204" s="7">
-        <v>0.59328</v>
+        <v>0.59251</v>
       </c>
       <c r="J204" s="7">
-        <v>2.905868</v>
+        <v>2.893962</v>
       </c>
       <c r="K204" s="7">
-        <v>6.460804</v>
+        <v>6.4380619999999995</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -9345,25 +9345,25 @@
         <v>3</v>
       </c>
       <c r="E205" s="7">
-        <v>0.012699</v>
+        <v>0.000567</v>
       </c>
       <c r="F205" s="7">
-        <v>0.020268</v>
+        <v>0.017346999999999998</v>
       </c>
       <c r="G205" s="7">
-        <v>0.163125</v>
+        <v>0.15653499999999998</v>
       </c>
       <c r="H205" s="7">
-        <v>0.059584</v>
+        <v>0.056551</v>
       </c>
       <c r="I205" s="7">
-        <v>0.387833</v>
+        <v>0.383988</v>
       </c>
       <c r="J205" s="7">
-        <v>1.656135</v>
+        <v>1.64853</v>
       </c>
       <c r="K205" s="7">
-        <v>3.670668</v>
+        <v>3.657296</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -9380,16 +9380,16 @@
         <v>6</v>
       </c>
       <c r="E206" s="7">
-        <v>0.024222999999999998</v>
+        <v>0.017705</v>
       </c>
       <c r="F206" s="7">
-        <v>-0.012654</v>
+        <v>-0.008511999999999999</v>
       </c>
       <c r="G206" s="7">
-        <v>0.310276</v>
+        <v>0.323979</v>
       </c>
       <c r="H206" s="7">
-        <v>0.24435199999999999</v>
+        <v>0.249573</v>
       </c>
       <c r="I206" s="7"/>
       <c r="J206" s="7"/>
@@ -9409,25 +9409,25 @@
         <v>5</v>
       </c>
       <c r="E207" s="7">
-        <v>0.020232</v>
+        <v>0.01444</v>
       </c>
       <c r="F207" s="7">
-        <v>0.036987</v>
+        <v>0.038058</v>
       </c>
       <c r="G207" s="7">
-        <v>0.109267</v>
+        <v>0.10995200000000001</v>
       </c>
       <c r="H207" s="7">
-        <v>0.070926</v>
+        <v>0.072031</v>
       </c>
       <c r="I207" s="7">
-        <v>0.314451</v>
+        <v>0.31032699999999996</v>
       </c>
       <c r="J207" s="7">
-        <v>1.946878</v>
+        <v>1.9499199999999999</v>
       </c>
       <c r="K207" s="7">
-        <v>5.280157</v>
+        <v>5.2866409999999995</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -9444,25 +9444,25 @@
         <v>4</v>
       </c>
       <c r="E208" s="7">
-        <v>0.016964999999999997</v>
+        <v>0.011045000000000001</v>
       </c>
       <c r="F208" s="7">
-        <v>0.006788</v>
+        <v>0.008363</v>
       </c>
       <c r="G208" s="7">
-        <v>0.213197</v>
+        <v>0.214214</v>
       </c>
       <c r="H208" s="7">
-        <v>0.105665</v>
+        <v>0.107394</v>
       </c>
       <c r="I208" s="7">
-        <v>0.36114199999999996</v>
+        <v>0.36600900000000003</v>
       </c>
       <c r="J208" s="7">
-        <v>1.956405</v>
+        <v>1.9610290000000001</v>
       </c>
       <c r="K208" s="7">
-        <v>4.921557</v>
+        <v>4.9308179999999995</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -9479,25 +9479,25 @@
         <v>5</v>
       </c>
       <c r="E209" s="7">
-        <v>0.008813</v>
+        <v>0.00839</v>
       </c>
       <c r="F209" s="7">
-        <v>0.007712</v>
+        <v>0.013124</v>
       </c>
       <c r="G209" s="7">
-        <v>0.26008400000000004</v>
+        <v>0.267527</v>
       </c>
       <c r="H209" s="7">
-        <v>0.17940699999999998</v>
+        <v>0.18574000000000002</v>
       </c>
       <c r="I209" s="7">
-        <v>0.452637</v>
+        <v>0.459438</v>
       </c>
       <c r="J209" s="7">
-        <v>2.7028480000000004</v>
+        <v>2.7227319999999997</v>
       </c>
       <c r="K209" s="7">
-        <v>7.931934</v>
+        <v>7.979896</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -9514,25 +9514,25 @@
         <v>6</v>
       </c>
       <c r="E210" s="7">
-        <v>0.0039700000000000004</v>
+        <v>0.0029070000000000003</v>
       </c>
       <c r="F210" s="7">
-        <v>-0.009599</v>
+        <v>-0.0039700000000000004</v>
       </c>
       <c r="G210" s="7">
-        <v>0.314484</v>
+        <v>0.326476</v>
       </c>
       <c r="H210" s="7">
-        <v>0.184371</v>
+        <v>0.191103</v>
       </c>
       <c r="I210" s="7">
-        <v>0.46539400000000003</v>
+        <v>0.47149</v>
       </c>
       <c r="J210" s="7">
-        <v>2.681644</v>
+        <v>2.70257</v>
       </c>
       <c r="K210" s="7">
-        <v>9.599155</v>
+        <v>9.659398</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -9549,25 +9549,25 @@
         <v>3</v>
       </c>
       <c r="E211" s="7">
-        <v>0.013241000000000001</v>
+        <v>0.005071</v>
       </c>
       <c r="F211" s="7">
-        <v>0.009582</v>
+        <v>0.009177999999999999</v>
       </c>
       <c r="G211" s="7">
-        <v>0.18945900000000002</v>
+        <v>0.187736</v>
       </c>
       <c r="H211" s="7">
-        <v>0.049645</v>
+        <v>0.049225000000000005</v>
       </c>
       <c r="I211" s="7">
-        <v>0.380849</v>
+        <v>0.38331200000000004</v>
       </c>
       <c r="J211" s="7">
-        <v>1.4971100000000002</v>
+        <v>1.496109</v>
       </c>
       <c r="K211" s="7">
-        <v>2.9370920000000003</v>
+        <v>2.935514</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -9584,25 +9584,25 @@
         <v>6</v>
       </c>
       <c r="E212" s="7">
-        <v>-0.000274</v>
+        <v>-0.0044280000000000005</v>
       </c>
       <c r="F212" s="7">
-        <v>-0.043616999999999996</v>
+        <v>-0.038155</v>
       </c>
       <c r="G212" s="7">
-        <v>0.316191</v>
+        <v>0.32887500000000003</v>
       </c>
       <c r="H212" s="7">
-        <v>0.22263100000000002</v>
+        <v>0.229614</v>
       </c>
       <c r="I212" s="7">
-        <v>0.35967799999999994</v>
+        <v>0.363425</v>
       </c>
       <c r="J212" s="7">
-        <v>2.6162150000000004</v>
+        <v>2.636869</v>
       </c>
       <c r="K212" s="7">
-        <v>14.382517</v>
+        <v>14.470374999999999</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -9619,25 +9619,25 @@
         <v>4</v>
       </c>
       <c r="E213" s="7">
-        <v>0.026871999999999997</v>
+        <v>0.019865</v>
       </c>
       <c r="F213" s="7">
-        <v>0.039958</v>
+        <v>0.040086000000000004</v>
       </c>
       <c r="G213" s="7">
-        <v>0.263605</v>
+        <v>0.265592</v>
       </c>
       <c r="H213" s="7">
-        <v>0.1895</v>
+        <v>0.189645</v>
       </c>
       <c r="I213" s="7">
-        <v>0.491</v>
+        <v>0.49040700000000004</v>
       </c>
       <c r="J213" s="7">
-        <v>1.870582</v>
+        <v>1.870933</v>
       </c>
       <c r="K213" s="7">
-        <v>5.492848</v>
+        <v>5.493643</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -9654,25 +9654,25 @@
         <v>3</v>
       </c>
       <c r="E214" s="7">
-        <v>0.03209</v>
+        <v>0.032221</v>
       </c>
       <c r="F214" s="7">
-        <v>0.10508100000000001</v>
+        <v>0.10734500000000001</v>
       </c>
       <c r="G214" s="7">
-        <v>0.285356</v>
+        <v>0.289198</v>
       </c>
       <c r="H214" s="7">
-        <v>0.207328</v>
+        <v>0.209802</v>
       </c>
       <c r="I214" s="7">
-        <v>0.48832000000000003</v>
+        <v>0.488431</v>
       </c>
       <c r="J214" s="7">
-        <v>1.956047</v>
+        <v>1.962103</v>
       </c>
       <c r="K214" s="7">
-        <v>5.141955</v>
+        <v>5.154538</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -9689,25 +9689,25 @@
         <v>4</v>
       </c>
       <c r="E215" s="7">
-        <v>0.033064</v>
+        <v>0.034243</v>
       </c>
       <c r="F215" s="7">
-        <v>0.097316</v>
+        <v>0.102708</v>
       </c>
       <c r="G215" s="7">
-        <v>0.36236199999999996</v>
+        <v>0.377461</v>
       </c>
       <c r="H215" s="7">
-        <v>0.28692</v>
+        <v>0.293244</v>
       </c>
       <c r="I215" s="7">
-        <v>0.5910150000000001</v>
+        <v>0.59506</v>
       </c>
       <c r="J215" s="7">
-        <v>3.2245530000000002</v>
+        <v>3.245313</v>
       </c>
       <c r="K215" s="7">
-        <v>9.953681</v>
+        <v>10.007508</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -9724,25 +9724,25 @@
         <v>6</v>
       </c>
       <c r="E216" s="7">
-        <v>0.00006</v>
+        <v>-0.010238</v>
       </c>
       <c r="F216" s="7">
-        <v>-0.058813000000000004</v>
+        <v>-0.060149999999999995</v>
       </c>
       <c r="G216" s="7">
-        <v>0.143633</v>
+        <v>0.156086</v>
       </c>
       <c r="H216" s="7">
-        <v>0.093437</v>
+        <v>0.091884</v>
       </c>
       <c r="I216" s="7">
-        <v>0.653389</v>
+        <v>0.6529349999999999</v>
       </c>
       <c r="J216" s="7">
-        <v>4.161004</v>
+        <v>4.153673</v>
       </c>
       <c r="K216" s="7">
-        <v>13.278595000000001</v>
+        <v>13.258313000000001</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -9759,25 +9759,25 @@
         <v>4</v>
       </c>
       <c r="E217" s="7">
-        <v>0.04125</v>
+        <v>0.040368</v>
       </c>
       <c r="F217" s="7">
-        <v>0.049908</v>
+        <v>0.055696</v>
       </c>
       <c r="G217" s="7">
-        <v>0.211064</v>
+        <v>0.224283</v>
       </c>
       <c r="H217" s="7">
-        <v>0.15192</v>
+        <v>0.15827</v>
       </c>
       <c r="I217" s="7">
-        <v>0.40740000000000004</v>
+        <v>0.414431</v>
       </c>
       <c r="J217" s="7">
-        <v>2.506004</v>
+        <v>2.525331</v>
       </c>
       <c r="K217" s="7">
-        <v>7.280221</v>
+        <v>7.325865</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -9794,25 +9794,25 @@
         <v>5</v>
       </c>
       <c r="E218" s="7">
-        <v>0.08488200000000001</v>
+        <v>0.09431300000000001</v>
       </c>
       <c r="F218" s="7">
-        <v>0.144905</v>
+        <v>0.16398</v>
       </c>
       <c r="G218" s="7">
-        <v>0.496774</v>
+        <v>0.542539</v>
       </c>
       <c r="H218" s="7">
-        <v>0.39935699999999996</v>
+        <v>0.42267200000000005</v>
       </c>
       <c r="I218" s="7">
-        <v>0.684706</v>
+        <v>0.71001</v>
       </c>
       <c r="J218" s="7">
-        <v>2.92146</v>
+        <v>2.986797</v>
       </c>
       <c r="K218" s="7">
-        <v>10.126517</v>
+        <v>10.311899</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -9829,25 +9829,25 @@
         <v>5</v>
       </c>
       <c r="E219" s="7">
-        <v>0.020064000000000002</v>
+        <v>0.017603</v>
       </c>
       <c r="F219" s="7">
-        <v>0.039376</v>
+        <v>0.039721</v>
       </c>
       <c r="G219" s="7">
-        <v>0.08495599999999999</v>
+        <v>0.085245</v>
       </c>
       <c r="H219" s="7">
-        <v>0.059359</v>
+        <v>0.059711</v>
       </c>
       <c r="I219" s="7">
-        <v>0.22395800000000002</v>
+        <v>0.224712</v>
       </c>
       <c r="J219" s="7">
-        <v>1.7991409999999999</v>
+        <v>1.80007</v>
       </c>
       <c r="K219" s="7">
-        <v>5.263442</v>
+        <v>5.265522</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -9864,25 +9864,25 @@
         <v>4</v>
       </c>
       <c r="E220" s="7">
-        <v>0.03084</v>
+        <v>0.033229</v>
       </c>
       <c r="F220" s="7">
-        <v>0.111036</v>
+        <v>0.117354</v>
       </c>
       <c r="G220" s="7">
-        <v>0.35698599999999997</v>
+        <v>0.371066</v>
       </c>
       <c r="H220" s="7">
-        <v>0.271368</v>
+        <v>0.278598</v>
       </c>
       <c r="I220" s="7">
-        <v>0.615245</v>
+        <v>0.621899</v>
       </c>
       <c r="J220" s="7">
-        <v>3.347199</v>
+        <v>3.3719200000000003</v>
       </c>
       <c r="K220" s="7">
-        <v>10.381412000000001</v>
+        <v>10.446133</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -9899,25 +9899,25 @@
         <v>5</v>
       </c>
       <c r="E221" s="7">
-        <v>0.08752900000000001</v>
+        <v>0.09301500000000001</v>
       </c>
       <c r="F221" s="7">
-        <v>0.133411</v>
+        <v>0.146872</v>
       </c>
       <c r="G221" s="7">
-        <v>0.461822</v>
+        <v>0.49120600000000003</v>
       </c>
       <c r="H221" s="7">
-        <v>0.357558</v>
+        <v>0.373681</v>
       </c>
       <c r="I221" s="7">
-        <v>0.6557219999999999</v>
+        <v>0.675153</v>
       </c>
       <c r="J221" s="7">
-        <v>4.148959</v>
+        <v>4.210111</v>
       </c>
       <c r="K221" s="7">
-        <v>14.099561000000001</v>
+        <v>14.278892</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -9934,19 +9934,19 @@
         <v>4</v>
       </c>
       <c r="E222" s="7">
-        <v>0.049079</v>
+        <v>0.049178</v>
       </c>
       <c r="F222" s="7">
-        <v>0.075218</v>
+        <v>0.08032199999999999</v>
       </c>
       <c r="G222" s="7">
-        <v>0.27417400000000003</v>
+        <v>0.285646</v>
       </c>
       <c r="H222" s="7">
-        <v>0.21076899999999998</v>
+        <v>0.21651700000000002</v>
       </c>
       <c r="I222" s="7">
-        <v>0.531911</v>
+        <v>0.53639</v>
       </c>
       <c r="J222" s="7"/>
       <c r="K222" s="7"/>
@@ -9965,16 +9965,16 @@
         <v>6</v>
       </c>
       <c r="E223" s="7">
-        <v>0.15162599999999998</v>
+        <v>0.130803</v>
       </c>
       <c r="F223" s="7">
-        <v>0.15823299999999998</v>
+        <v>0.165577</v>
       </c>
       <c r="G223" s="7">
-        <v>0.6883830000000001</v>
+        <v>0.7135630000000001</v>
       </c>
       <c r="H223" s="7">
-        <v>0.269047</v>
+        <v>0.277093</v>
       </c>
       <c r="I223" s="7"/>
       <c r="J223" s="7"/>
@@ -9994,7 +9994,7 @@
         <v>6</v>
       </c>
       <c r="E224" s="7">
-        <v>0.063854</v>
+        <v>0.068382</v>
       </c>
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
@@ -10017,22 +10017,22 @@
         <v>6</v>
       </c>
       <c r="E225" s="7">
-        <v>0.076554</v>
+        <v>0.059029</v>
       </c>
       <c r="F225" s="7">
-        <v>0.035883</v>
+        <v>0.036713</v>
       </c>
       <c r="G225" s="7">
-        <v>0.3933</v>
+        <v>0.410022</v>
       </c>
       <c r="H225" s="7">
-        <v>0.172058</v>
+        <v>0.172998</v>
       </c>
       <c r="I225" s="7">
-        <v>1.188223</v>
+        <v>1.198016</v>
       </c>
       <c r="J225" s="7">
-        <v>4.889951</v>
+        <v>4.89467</v>
       </c>
       <c r="K225" s="7"/>
     </row>
@@ -10050,25 +10050,25 @@
         <v>4</v>
       </c>
       <c r="E226" s="7">
-        <v>0.031423</v>
+        <v>0.031431</v>
       </c>
       <c r="F226" s="7">
-        <v>0.096274</v>
+        <v>0.09739800000000001</v>
       </c>
       <c r="G226" s="7">
-        <v>0.19653500000000002</v>
+        <v>0.19405999999999998</v>
       </c>
       <c r="H226" s="7">
-        <v>0.140228</v>
+        <v>0.141396</v>
       </c>
       <c r="I226" s="7">
-        <v>0.43761099999999997</v>
+        <v>0.438005</v>
       </c>
       <c r="J226" s="7">
-        <v>1.663252</v>
+        <v>1.6659800000000002</v>
       </c>
       <c r="K226" s="7">
-        <v>2.741303</v>
+        <v>2.745136</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -10085,19 +10085,19 @@
         <v>2</v>
       </c>
       <c r="E227" s="7">
-        <v>0.029142</v>
+        <v>0.028878</v>
       </c>
       <c r="F227" s="7">
-        <v>0.081293</v>
+        <v>0.082218</v>
       </c>
       <c r="G227" s="7">
-        <v>0.186022</v>
+        <v>0.18368700000000002</v>
       </c>
       <c r="H227" s="7">
-        <v>0.13026</v>
+        <v>0.131227</v>
       </c>
       <c r="I227" s="7">
-        <v>0.44259</v>
+        <v>0.442325</v>
       </c>
       <c r="J227" s="7"/>
       <c r="K227" s="7"/>
@@ -10116,22 +10116,22 @@
         <v>6</v>
       </c>
       <c r="E228" s="7">
-        <v>0.0722</v>
+        <v>0.08072599999999999</v>
       </c>
       <c r="F228" s="7">
-        <v>0.109778</v>
+        <v>0.126892</v>
       </c>
       <c r="G228" s="7">
-        <v>0.337937</v>
+        <v>0.372902</v>
       </c>
       <c r="H228" s="7">
-        <v>0.29462299999999997</v>
+        <v>0.314588</v>
       </c>
       <c r="I228" s="7">
-        <v>0.43616</v>
+        <v>0.462631</v>
       </c>
       <c r="J228" s="7">
-        <v>2.743761</v>
+        <v>2.801495</v>
       </c>
       <c r="K228" s="7"/>
     </row>
@@ -10149,19 +10149,19 @@
         <v>5</v>
       </c>
       <c r="E229" s="7">
-        <v>0.08755399999999999</v>
+        <v>0.068783</v>
       </c>
       <c r="F229" s="7">
-        <v>0.051481000000000006</v>
+        <v>0.048421000000000006</v>
       </c>
       <c r="G229" s="7">
-        <v>0.40382199999999996</v>
+        <v>0.42931199999999997</v>
       </c>
       <c r="H229" s="7">
-        <v>0.201116</v>
+        <v>0.197621</v>
       </c>
       <c r="I229" s="7">
-        <v>1.117594</v>
+        <v>1.135203</v>
       </c>
       <c r="J229" s="7"/>
       <c r="K229" s="7"/>
@@ -10201,25 +10201,25 @@
         <v>4</v>
       </c>
       <c r="E231" s="7">
-        <v>0.020829</v>
+        <v>0.015297</v>
       </c>
       <c r="F231" s="7">
-        <v>0.035288</v>
+        <v>0.036632</v>
       </c>
       <c r="G231" s="7">
-        <v>0.21123799999999998</v>
+        <v>0.211392</v>
       </c>
       <c r="H231" s="7">
-        <v>0.11709699999999999</v>
+        <v>0.118547</v>
       </c>
       <c r="I231" s="7">
-        <v>0.43705700000000003</v>
+        <v>0.43391599999999997</v>
       </c>
       <c r="J231" s="7">
-        <v>2.220452</v>
+        <v>2.224632</v>
       </c>
       <c r="K231" s="7">
-        <v>5.61191</v>
+        <v>5.6204920000000005</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -10236,25 +10236,25 @@
         <v>3</v>
       </c>
       <c r="E232" s="7">
-        <v>0.033742999999999995</v>
+        <v>0.03282</v>
       </c>
       <c r="F232" s="7">
-        <v>0.077267</v>
+        <v>0.079375</v>
       </c>
       <c r="G232" s="7">
-        <v>0.24378599999999997</v>
+        <v>0.24672</v>
       </c>
       <c r="H232" s="7">
-        <v>0.157642</v>
+        <v>0.159907</v>
       </c>
       <c r="I232" s="7">
-        <v>0.436614</v>
+        <v>0.438565</v>
       </c>
       <c r="J232" s="7">
-        <v>1.9078389999999998</v>
+        <v>1.913529</v>
       </c>
       <c r="K232" s="7">
-        <v>4.6010610000000005</v>
+        <v>4.6120209999999995</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -10271,19 +10271,19 @@
         <v>3</v>
       </c>
       <c r="E233" s="7">
-        <v>0.082951</v>
+        <v>0.083099</v>
       </c>
       <c r="F233" s="7">
-        <v>0.142213</v>
+        <v>0.150255</v>
       </c>
       <c r="G233" s="7">
-        <v>0.298591</v>
+        <v>0.324262</v>
       </c>
       <c r="H233" s="7">
-        <v>0.25516500000000003</v>
+        <v>0.264003</v>
       </c>
       <c r="I233" s="7">
-        <v>0.572572</v>
+        <v>0.5785669999999999</v>
       </c>
       <c r="J233" s="7"/>
       <c r="K233" s="7"/>
@@ -10302,7 +10302,7 @@
         <v>2</v>
       </c>
       <c r="E234" s="7">
-        <v>0.037468</v>
+        <v>0.03599</v>
       </c>
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
@@ -10325,19 +10325,19 @@
         <v>5</v>
       </c>
       <c r="E235" s="7">
-        <v>0.103446</v>
+        <v>0.10177</v>
       </c>
       <c r="F235" s="7">
-        <v>0.191409</v>
+        <v>0.20599699999999999</v>
       </c>
       <c r="G235" s="7">
-        <v>0.45252899999999996</v>
+        <v>0.495432</v>
       </c>
       <c r="H235" s="7">
-        <v>0.411698</v>
+        <v>0.428983</v>
       </c>
       <c r="I235" s="7">
-        <v>0.598873</v>
+        <v>0.626814</v>
       </c>
       <c r="J235" s="7"/>
       <c r="K235" s="7"/>
@@ -10356,19 +10356,19 @@
         <v>5</v>
       </c>
       <c r="E236" s="7">
-        <v>0.07115</v>
+        <v>0.06903</v>
       </c>
       <c r="F236" s="7">
-        <v>0.11308</v>
+        <v>0.12095700000000001</v>
       </c>
       <c r="G236" s="7">
-        <v>0.325823</v>
+        <v>0.348335</v>
       </c>
       <c r="H236" s="7">
-        <v>0.26615500000000003</v>
+        <v>0.275115</v>
       </c>
       <c r="I236" s="7">
-        <v>0.5364909999999999</v>
+        <v>0.546218</v>
       </c>
       <c r="J236" s="7"/>
       <c r="K236" s="7"/>
@@ -10387,25 +10387,25 @@
         <v>4</v>
       </c>
       <c r="E237" s="7">
-        <v>0.034992</v>
+        <v>0.035539999999999995</v>
       </c>
       <c r="F237" s="7">
-        <v>0.063881</v>
+        <v>0.067394</v>
       </c>
       <c r="G237" s="7">
-        <v>0.19738399999999998</v>
+        <v>0.201157</v>
       </c>
       <c r="H237" s="7">
-        <v>0.129129</v>
+        <v>0.132857</v>
       </c>
       <c r="I237" s="7">
-        <v>0.376304</v>
+        <v>0.38245399999999996</v>
       </c>
       <c r="J237" s="7">
-        <v>1.85696</v>
+        <v>1.866393</v>
       </c>
       <c r="K237" s="7">
-        <v>4.3959980000000005</v>
+        <v>4.4138139999999995</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -10422,19 +10422,19 @@
         <v>3</v>
       </c>
       <c r="E238" s="7">
-        <v>0.02358</v>
+        <v>0.019133</v>
       </c>
       <c r="F238" s="7">
-        <v>0.017447999999999998</v>
+        <v>0.021757</v>
       </c>
       <c r="G238" s="7">
-        <v>0.266436</v>
+        <v>0.276057</v>
       </c>
       <c r="H238" s="7">
-        <v>0.193294</v>
+        <v>0.19834800000000002</v>
       </c>
       <c r="I238" s="7">
-        <v>0.44359099999999996</v>
+        <v>0.449381</v>
       </c>
       <c r="J238" s="7"/>
       <c r="K238" s="7"/>
@@ -10453,19 +10453,19 @@
         <v>4</v>
       </c>
       <c r="E239" s="7">
-        <v>0.016616</v>
+        <v>0.008715</v>
       </c>
       <c r="F239" s="7">
-        <v>0.033659</v>
+        <v>0.030843</v>
       </c>
       <c r="G239" s="7">
-        <v>0.19565200000000002</v>
+        <v>0.19203399999999998</v>
       </c>
       <c r="H239" s="7">
-        <v>0.11570499999999999</v>
+        <v>0.112666</v>
       </c>
       <c r="I239" s="7">
-        <v>0.455778</v>
+        <v>0.451277</v>
       </c>
       <c r="J239" s="7"/>
       <c r="K239" s="7"/>
@@ -10484,19 +10484,19 @@
         <v>2</v>
       </c>
       <c r="E240" s="7">
-        <v>0.033885</v>
+        <v>0.033059</v>
       </c>
       <c r="F240" s="7">
-        <v>0.09422499999999999</v>
+        <v>0.095111</v>
       </c>
       <c r="G240" s="7">
-        <v>0.19893899999999998</v>
+        <v>0.196514</v>
       </c>
       <c r="H240" s="7">
-        <v>0.14472200000000002</v>
+        <v>0.145649</v>
       </c>
       <c r="I240" s="7">
-        <v>0.46995800000000004</v>
+        <v>0.469668</v>
       </c>
       <c r="J240" s="7"/>
       <c r="K240" s="7"/>
@@ -10515,25 +10515,25 @@
         <v>6</v>
       </c>
       <c r="E241" s="7">
-        <v>0.004425</v>
+        <v>-0.003196</v>
       </c>
       <c r="F241" s="7">
-        <v>-0.048811</v>
+        <v>-0.048648</v>
       </c>
       <c r="G241" s="7">
-        <v>0.163309</v>
+        <v>0.176342</v>
       </c>
       <c r="H241" s="7">
-        <v>0.105458</v>
+        <v>0.105646</v>
       </c>
       <c r="I241" s="7">
-        <v>0.6573739999999999</v>
+        <v>0.664362</v>
       </c>
       <c r="J241" s="7">
-        <v>4.259814</v>
+        <v>4.260712</v>
       </c>
       <c r="K241" s="7">
-        <v>13.595207</v>
+        <v>13.597697</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -10547,17 +10547,17 @@
         <v>23</v>
       </c>
       <c r="D242" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E242" s="7">
-        <v>0.009541</v>
+        <v>-0.001337</v>
       </c>
       <c r="F242" s="7">
-        <v>0.008361</v>
+        <v>0.006923</v>
       </c>
       <c r="G242" s="7"/>
       <c r="H242" s="7">
-        <v>0.046073</v>
+        <v>0.044581</v>
       </c>
       <c r="I242" s="7"/>
       <c r="J242" s="7"/>
@@ -10577,19 +10577,19 @@
         <v>6</v>
       </c>
       <c r="E243" s="7">
-        <v>0.158348</v>
+        <v>0.166784</v>
       </c>
       <c r="F243" s="7">
-        <v>0.267316</v>
+        <v>0.29130500000000004</v>
       </c>
       <c r="G243" s="7">
-        <v>0.431319</v>
+        <v>0.486102</v>
       </c>
       <c r="H243" s="7">
-        <v>0.377564</v>
+        <v>0.40364</v>
       </c>
       <c r="I243" s="7">
-        <v>0.7129420000000001</v>
+        <v>0.739495</v>
       </c>
       <c r="J243" s="7"/>
       <c r="K243" s="7"/>
@@ -10608,19 +10608,19 @@
         <v>5</v>
       </c>
       <c r="E244" s="7">
-        <v>0.050076</v>
+        <v>0.0463</v>
       </c>
       <c r="F244" s="7">
-        <v>0.035806</v>
+        <v>0.043618</v>
       </c>
       <c r="G244" s="7">
-        <v>0.254967</v>
+        <v>0.28136099999999997</v>
       </c>
       <c r="H244" s="7">
-        <v>0.19775099999999998</v>
+        <v>0.206785</v>
       </c>
       <c r="I244" s="7">
-        <v>0.44839599999999996</v>
+        <v>0.455345</v>
       </c>
       <c r="J244" s="7"/>
       <c r="K244" s="7"/>
@@ -10639,25 +10639,25 @@
         <v>6</v>
       </c>
       <c r="E245" s="7">
-        <v>0.017387</v>
+        <v>0.014539</v>
       </c>
       <c r="F245" s="7">
-        <v>0.037993</v>
+        <v>0.038956</v>
       </c>
       <c r="G245" s="7">
-        <v>0.08886799999999999</v>
+        <v>0.090313</v>
       </c>
       <c r="H245" s="7">
-        <v>0.06178</v>
+        <v>0.062766</v>
       </c>
       <c r="I245" s="7">
-        <v>0.226444</v>
+        <v>0.227879</v>
       </c>
       <c r="J245" s="7">
-        <v>1.812652</v>
+        <v>1.8152629999999998</v>
       </c>
       <c r="K245" s="7">
-        <v>5.772831999999999</v>
+        <v>5.779119</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -10674,25 +10674,25 @@
         <v>4</v>
       </c>
       <c r="E246" s="7">
-        <v>0.017734</v>
+        <v>0.015657</v>
       </c>
       <c r="F246" s="7">
-        <v>0.049224</v>
+        <v>0.051011</v>
       </c>
       <c r="G246" s="7">
-        <v>0.228806</v>
+        <v>0.228031</v>
       </c>
       <c r="H246" s="7">
-        <v>0.09498200000000001</v>
+        <v>0.096846</v>
       </c>
       <c r="I246" s="7">
-        <v>0.255503</v>
+        <v>0.260664</v>
       </c>
       <c r="J246" s="7">
-        <v>1.916059</v>
+        <v>1.921025</v>
       </c>
       <c r="K246" s="7">
-        <v>5.811165</v>
+        <v>5.822763999999999</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -10709,25 +10709,25 @@
         <v>6</v>
       </c>
       <c r="E247" s="7">
-        <v>0.018591</v>
+        <v>0.017636</v>
       </c>
       <c r="F247" s="7">
-        <v>-0.021771</v>
+        <v>-0.01398</v>
       </c>
       <c r="G247" s="7">
-        <v>0.302356</v>
+        <v>0.32293999999999995</v>
       </c>
       <c r="H247" s="7">
-        <v>0.220697</v>
+        <v>0.23041899999999998</v>
       </c>
       <c r="I247" s="7">
-        <v>0.425845</v>
+        <v>0.43075</v>
       </c>
       <c r="J247" s="7">
-        <v>2.717949</v>
+        <v>2.747561</v>
       </c>
       <c r="K247" s="7">
-        <v>14.631273</v>
+        <v>14.75577</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -10747,22 +10747,22 @@
         <v>0.036946</v>
       </c>
       <c r="F248" s="7">
-        <v>0.084173</v>
+        <v>0.086616</v>
       </c>
       <c r="G248" s="7">
-        <v>0.24084</v>
+        <v>0.24394</v>
       </c>
       <c r="H248" s="7">
-        <v>0.169024</v>
+        <v>0.171659</v>
       </c>
       <c r="I248" s="7">
-        <v>0.44982700000000003</v>
+        <v>0.45268</v>
       </c>
       <c r="J248" s="7">
-        <v>1.9245949999999998</v>
+        <v>1.9311859999999998</v>
       </c>
       <c r="K248" s="7">
-        <v>4.661846</v>
+        <v>4.674606</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -10779,25 +10779,25 @@
         <v>4</v>
       </c>
       <c r="E249" s="7">
-        <v>0.012179</v>
+        <v>0.003533</v>
       </c>
       <c r="F249" s="7">
-        <v>-0.003218</v>
+        <v>-0.0034899999999999996</v>
       </c>
       <c r="G249" s="7">
-        <v>0.181894</v>
+        <v>0.18239799999999998</v>
       </c>
       <c r="H249" s="7">
-        <v>0.08172399999999999</v>
+        <v>0.08142899999999999</v>
       </c>
       <c r="I249" s="7">
-        <v>0.37166499999999997</v>
+        <v>0.370948</v>
       </c>
       <c r="J249" s="7">
-        <v>1.515822</v>
+        <v>1.515136</v>
       </c>
       <c r="K249" s="7">
-        <v>3.8094650000000003</v>
+        <v>3.808153</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -10814,25 +10814,25 @@
         <v>2</v>
       </c>
       <c r="E250" s="7">
-        <v>0.027108</v>
+        <v>0.023083</v>
       </c>
       <c r="F250" s="7">
-        <v>0.07732</v>
+        <v>0.077528</v>
       </c>
       <c r="G250" s="7">
-        <v>0.21488</v>
+        <v>0.21227000000000001</v>
       </c>
       <c r="H250" s="7">
-        <v>0.144414</v>
+        <v>0.144636</v>
       </c>
       <c r="I250" s="7">
-        <v>0.504516</v>
+        <v>0.503446</v>
       </c>
       <c r="J250" s="7">
-        <v>4.280003</v>
+        <v>4.281023</v>
       </c>
       <c r="K250" s="7">
-        <v>7.190239</v>
+        <v>7.191821</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -10849,25 +10849,25 @@
         <v>4</v>
       </c>
       <c r="E251" s="7">
-        <v>0.020274999999999998</v>
+        <v>0.017301999999999998</v>
       </c>
       <c r="F251" s="7">
-        <v>0.030441</v>
+        <v>0.03375</v>
       </c>
       <c r="G251" s="7">
-        <v>0.274521</v>
+        <v>0.281371</v>
       </c>
       <c r="H251" s="7">
-        <v>0.198638</v>
+        <v>0.202487</v>
       </c>
       <c r="I251" s="7">
-        <v>0.49608800000000003</v>
+        <v>0.49801</v>
       </c>
       <c r="J251" s="7">
-        <v>3.182859</v>
+        <v>3.196292</v>
       </c>
       <c r="K251" s="7">
-        <v>8.620749</v>
+        <v>8.651645</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -10884,25 +10884,25 @@
         <v>5</v>
       </c>
       <c r="E252" s="7">
-        <v>0.020589</v>
+        <v>0.017833</v>
       </c>
       <c r="F252" s="7">
-        <v>0.016734</v>
+        <v>0.021082999999999998</v>
       </c>
       <c r="G252" s="7">
-        <v>0.289657</v>
+        <v>0.300558</v>
       </c>
       <c r="H252" s="7">
-        <v>0.21329399999999998</v>
+        <v>0.218484</v>
       </c>
       <c r="I252" s="7">
-        <v>0.49203600000000003</v>
+        <v>0.49438099999999996</v>
       </c>
       <c r="J252" s="7">
-        <v>3.6895830000000003</v>
+        <v>3.709642</v>
       </c>
       <c r="K252" s="7">
-        <v>11.566674</v>
+        <v>11.620426</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -10919,25 +10919,25 @@
         <v>6</v>
       </c>
       <c r="E253" s="7">
-        <v>0.017283</v>
+        <v>0.016341</v>
       </c>
       <c r="F253" s="7">
-        <v>-0.008773999999999999</v>
+        <v>-0.002089</v>
       </c>
       <c r="G253" s="7">
-        <v>0.306714</v>
+        <v>0.32620800000000005</v>
       </c>
       <c r="H253" s="7">
-        <v>0.225247</v>
+        <v>0.23351</v>
       </c>
       <c r="I253" s="7">
-        <v>0.444624</v>
+        <v>0.44978900000000005</v>
       </c>
       <c r="J253" s="7">
-        <v>3.214665</v>
+        <v>3.243091</v>
       </c>
       <c r="K253" s="7">
-        <v>14.108218999999998</v>
+        <v>14.210115</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -10954,25 +10954,25 @@
         <v>3</v>
       </c>
       <c r="E254" s="7">
-        <v>0.045956000000000004</v>
+        <v>0.04584800000000001</v>
       </c>
       <c r="F254" s="7">
-        <v>0.089335</v>
+        <v>0.092989</v>
       </c>
       <c r="G254" s="7">
-        <v>0.241459</v>
+        <v>0.247187</v>
       </c>
       <c r="H254" s="7">
-        <v>0.18864599999999998</v>
+        <v>0.192633</v>
       </c>
       <c r="I254" s="7">
-        <v>0.45992600000000006</v>
+        <v>0.465045</v>
       </c>
       <c r="J254" s="7">
-        <v>2.188753</v>
+        <v>2.199449</v>
       </c>
       <c r="K254" s="7">
-        <v>5.684882</v>
+        <v>5.707305</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -10989,25 +10989,25 @@
         <v>5</v>
       </c>
       <c r="E255" s="7">
-        <v>0.06610100000000001</v>
+        <v>0.06868400000000001</v>
       </c>
       <c r="F255" s="7">
-        <v>0.105498</v>
+        <v>0.11371700000000001</v>
       </c>
       <c r="G255" s="7">
-        <v>0.334121</v>
+        <v>0.35159999999999997</v>
       </c>
       <c r="H255" s="7">
-        <v>0.264821</v>
+        <v>0.274224</v>
       </c>
       <c r="I255" s="7">
-        <v>0.526942</v>
+        <v>0.5360779999999999</v>
       </c>
       <c r="J255" s="7">
-        <v>3.24727</v>
+        <v>3.2788459999999997</v>
       </c>
       <c r="K255" s="7">
-        <v>10.192129999999999</v>
+        <v>10.275338</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -11024,25 +11024,25 @@
         <v>6</v>
       </c>
       <c r="E256" s="7">
-        <v>0.07222</v>
+        <v>0.075073</v>
       </c>
       <c r="F256" s="7">
-        <v>0.108539</v>
+        <v>0.118018</v>
       </c>
       <c r="G256" s="7">
-        <v>0.35969700000000004</v>
+        <v>0.38167</v>
       </c>
       <c r="H256" s="7">
-        <v>0.287851</v>
+        <v>0.298863</v>
       </c>
       <c r="I256" s="7">
-        <v>0.532464</v>
+        <v>0.543109</v>
       </c>
       <c r="J256" s="7">
-        <v>3.443066</v>
+        <v>3.4810570000000003</v>
       </c>
       <c r="K256" s="7">
-        <v>11.323913</v>
+        <v>11.429290000000002</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -11059,25 +11059,25 @@
         <v>4</v>
       </c>
       <c r="E257" s="7">
-        <v>0.012988</v>
+        <v>0.004744</v>
       </c>
       <c r="F257" s="7">
-        <v>0.005370000000000001</v>
+        <v>0.004571</v>
       </c>
       <c r="G257" s="7">
-        <v>0.1643</v>
+        <v>0.162792</v>
       </c>
       <c r="H257" s="7">
-        <v>0.07485699999999999</v>
+        <v>0.074002</v>
       </c>
       <c r="I257" s="7">
-        <v>0.367705</v>
+        <v>0.35952300000000004</v>
       </c>
       <c r="J257" s="7">
-        <v>1.8566820000000002</v>
+        <v>1.8544100000000001</v>
       </c>
       <c r="K257" s="7">
-        <v>5.02233</v>
+        <v>5.01754</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -11094,25 +11094,25 @@
         <v>4</v>
       </c>
       <c r="E258" s="7">
-        <v>0.027522</v>
+        <v>0.024622</v>
       </c>
       <c r="F258" s="7">
-        <v>0.030271</v>
+        <v>0.033564</v>
       </c>
       <c r="G258" s="7">
-        <v>0.243248</v>
+        <v>0.251595</v>
       </c>
       <c r="H258" s="7">
-        <v>0.18152200000000002</v>
+        <v>0.18529900000000002</v>
       </c>
       <c r="I258" s="7">
-        <v>0.526099</v>
+        <v>0.528864</v>
       </c>
       <c r="J258" s="7">
-        <v>2.830859</v>
+        <v>2.8431040000000003</v>
       </c>
       <c r="K258" s="7">
-        <v>6.162851000000001</v>
+        <v>6.185747</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -11129,25 +11129,25 @@
         <v>4</v>
       </c>
       <c r="E259" s="7">
-        <v>0.023812000000000003</v>
+        <v>0.02094</v>
       </c>
       <c r="F259" s="7">
-        <v>0.036633</v>
+        <v>0.038798</v>
       </c>
       <c r="G259" s="7">
-        <v>0.223294</v>
+        <v>0.22776700000000002</v>
       </c>
       <c r="H259" s="7">
-        <v>0.165499</v>
+        <v>0.167933</v>
       </c>
       <c r="I259" s="7">
-        <v>0.512453</v>
+        <v>0.51451</v>
       </c>
       <c r="J259" s="7">
-        <v>2.789183</v>
+        <v>2.7970960000000002</v>
       </c>
       <c r="K259" s="7">
-        <v>5.329117999999999</v>
+        <v>5.342335</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -11164,25 +11164,25 @@
         <v>5</v>
       </c>
       <c r="E260" s="7">
-        <v>0.031953</v>
+        <v>0.028838</v>
       </c>
       <c r="F260" s="7">
-        <v>0.027169</v>
+        <v>0.031711</v>
       </c>
       <c r="G260" s="7">
-        <v>0.278537</v>
+        <v>0.291568</v>
       </c>
       <c r="H260" s="7">
-        <v>0.204627</v>
+        <v>0.209954</v>
       </c>
       <c r="I260" s="7">
-        <v>0.535133</v>
+        <v>0.539922</v>
       </c>
       <c r="J260" s="7">
-        <v>2.848938</v>
+        <v>2.8659570000000003</v>
       </c>
       <c r="K260" s="7">
-        <v>7.443898000000001</v>
+        <v>7.481235000000001</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -11199,25 +11199,25 @@
         <v>6</v>
       </c>
       <c r="E261" s="7">
-        <v>0.0018470000000000001</v>
+        <v>-0.007323</v>
       </c>
       <c r="F261" s="7">
-        <v>-0.051143999999999995</v>
+        <v>-0.051982</v>
       </c>
       <c r="G261" s="7">
-        <v>0.150937</v>
+        <v>0.16234400000000002</v>
       </c>
       <c r="H261" s="7">
-        <v>0.100731</v>
+        <v>0.09975899999999999</v>
       </c>
       <c r="I261" s="7">
-        <v>0.660412</v>
+        <v>0.659135</v>
       </c>
       <c r="J261" s="7">
-        <v>4.162973</v>
+        <v>4.15841</v>
       </c>
       <c r="K261" s="7">
-        <v>13.495291</v>
+        <v>13.482481</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -11234,25 +11234,25 @@
         <v>2</v>
       </c>
       <c r="E262" s="7">
-        <v>0.042895</v>
+        <v>0.047087000000000004</v>
       </c>
       <c r="F262" s="7">
-        <v>0.097416</v>
+        <v>0.09967000000000001</v>
       </c>
       <c r="G262" s="7">
-        <v>0.218305</v>
+        <v>0.221203</v>
       </c>
       <c r="H262" s="7">
-        <v>0.174472</v>
+        <v>0.176884</v>
       </c>
       <c r="I262" s="7">
-        <v>0.449195</v>
+        <v>0.450726</v>
       </c>
       <c r="J262" s="7">
-        <v>2.514611</v>
+        <v>2.521831</v>
       </c>
       <c r="K262" s="7">
-        <v>4.5828809999999995</v>
+        <v>4.594348</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -11269,25 +11269,25 @@
         <v>6</v>
       </c>
       <c r="E263" s="7">
-        <v>0.100085</v>
+        <v>0.085594</v>
       </c>
       <c r="F263" s="7">
-        <v>0.078684</v>
+        <v>0.085161</v>
       </c>
       <c r="G263" s="7">
-        <v>0.23706</v>
+        <v>0.264243</v>
       </c>
       <c r="H263" s="7">
-        <v>0.18767</v>
+        <v>0.194802</v>
       </c>
       <c r="I263" s="7">
-        <v>0.6796939999999999</v>
+        <v>0.687186</v>
       </c>
       <c r="J263" s="7">
-        <v>4.576544999999999</v>
+        <v>4.610029</v>
       </c>
       <c r="K263" s="7">
-        <v>21.085018</v>
+        <v>21.217626</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -11304,7 +11304,7 @@
         <v>6</v>
       </c>
       <c r="E264" s="7">
-        <v>0.003667</v>
+        <v>-0.005545</v>
       </c>
       <c r="F264" s="7">
         <v>-0.050656999999999994</v>
@@ -11329,22 +11329,22 @@
         <v>3</v>
       </c>
       <c r="E265" s="7">
-        <v>0.046414</v>
+        <v>0.045885999999999996</v>
       </c>
       <c r="F265" s="7">
-        <v>0.093766</v>
+        <v>0.097278</v>
       </c>
       <c r="G265" s="7">
-        <v>0.269343</v>
+        <v>0.274708</v>
       </c>
       <c r="H265" s="7">
-        <v>0.200667</v>
+        <v>0.204522</v>
       </c>
       <c r="I265" s="7">
-        <v>0.512901</v>
+        <v>0.5170790000000001</v>
       </c>
       <c r="J265" s="7">
-        <v>2.408459</v>
+        <v>2.419402</v>
       </c>
       <c r="K265" s="7"/>
     </row>
@@ -11362,22 +11362,22 @@
         <v>3</v>
       </c>
       <c r="E266" s="7">
-        <v>0.007463</v>
+        <v>0.006463</v>
       </c>
       <c r="F266" s="7">
-        <v>0.030255999999999998</v>
+        <v>0.033064</v>
       </c>
       <c r="G266" s="7">
-        <v>0.12181900000000001</v>
+        <v>0.12806800000000002</v>
       </c>
       <c r="H266" s="7">
-        <v>0.065714</v>
+        <v>0.068618</v>
       </c>
       <c r="I266" s="7">
-        <v>0.433482</v>
+        <v>0.436017</v>
       </c>
       <c r="J266" s="7">
-        <v>2.6553050000000002</v>
+        <v>2.6652649999999998</v>
       </c>
       <c r="K266" s="7"/>
     </row>
@@ -11395,19 +11395,19 @@
         <v>5</v>
       </c>
       <c r="E267" s="7">
-        <v>-0.015088999999999998</v>
+        <v>-0.020491000000000002</v>
       </c>
       <c r="F267" s="7">
-        <v>-0.049643</v>
+        <v>-0.042155</v>
       </c>
       <c r="G267" s="7">
-        <v>0.278638</v>
+        <v>0.299379</v>
       </c>
       <c r="H267" s="7">
-        <v>0.162103</v>
+        <v>0.17125900000000002</v>
       </c>
       <c r="I267" s="7">
-        <v>0.34977800000000003</v>
+        <v>0.354146</v>
       </c>
       <c r="J267" s="7"/>
       <c r="K267" s="7"/>
@@ -11447,22 +11447,22 @@
         <v>6</v>
       </c>
       <c r="E269" s="7">
-        <v>0.134917</v>
+        <v>0.145809</v>
       </c>
       <c r="F269" s="7">
-        <v>0.179403</v>
+        <v>0.21037099999999997</v>
       </c>
       <c r="G269" s="7">
-        <v>0.299298</v>
+        <v>0.359881</v>
       </c>
       <c r="H269" s="7">
-        <v>0.263025</v>
+        <v>0.296189</v>
       </c>
       <c r="I269" s="7">
-        <v>0.507497</v>
+        <v>0.546304</v>
       </c>
       <c r="J269" s="7">
-        <v>3.5993020000000002</v>
+        <v>3.7200689999999996</v>
       </c>
       <c r="K269" s="7"/>
     </row>
@@ -11480,19 +11480,19 @@
         <v>6</v>
       </c>
       <c r="E270" s="7">
-        <v>0.049193</v>
+        <v>0.041048999999999995</v>
       </c>
       <c r="F270" s="7">
-        <v>0.070635</v>
+        <v>0.065364</v>
       </c>
       <c r="G270" s="7">
-        <v>0.18541799999999997</v>
+        <v>0.186721</v>
       </c>
       <c r="H270" s="7">
-        <v>0.166357</v>
+        <v>0.16061499999999998</v>
       </c>
       <c r="I270" s="7">
-        <v>0.29698399999999997</v>
+        <v>0.289458</v>
       </c>
       <c r="J270" s="7"/>
       <c r="K270" s="7"/>
@@ -11511,19 +11511,19 @@
         <v>2</v>
       </c>
       <c r="E271" s="7">
-        <v>0.03246</v>
+        <v>0.032564</v>
       </c>
       <c r="F271" s="7">
-        <v>0.09695999999999999</v>
+        <v>0.098203</v>
       </c>
       <c r="G271" s="7">
-        <v>0.20722100000000002</v>
+        <v>0.20481000000000002</v>
       </c>
       <c r="H271" s="7">
-        <v>0.147783</v>
+        <v>0.149083</v>
       </c>
       <c r="I271" s="7">
-        <v>0.481449</v>
+        <v>0.481372</v>
       </c>
       <c r="J271" s="7"/>
       <c r="K271" s="7"/>
@@ -11542,22 +11542,22 @@
         <v>2</v>
       </c>
       <c r="E272" s="7">
-        <v>0.020612</v>
+        <v>0.019257</v>
       </c>
       <c r="F272" s="7">
-        <v>0.04966</v>
+        <v>0.050919</v>
       </c>
       <c r="G272" s="7">
-        <v>0.19031800000000001</v>
+        <v>0.188267</v>
       </c>
       <c r="H272" s="7">
-        <v>0.1335</v>
+        <v>0.134859</v>
       </c>
       <c r="I272" s="7">
-        <v>0.464207</v>
+        <v>0.465835</v>
       </c>
       <c r="J272" s="7">
-        <v>3.0954880000000005</v>
+        <v>3.1004009999999997</v>
       </c>
       <c r="K272" s="7"/>
     </row>
@@ -11575,22 +11575,22 @@
         <v>5</v>
       </c>
       <c r="E273" s="7">
-        <v>-0.00146</v>
+        <v>-0.0009429999999999999</v>
       </c>
       <c r="F273" s="7">
-        <v>-0.031971</v>
+        <v>-0.028363999999999997</v>
       </c>
       <c r="G273" s="7">
-        <v>0.182719</v>
+        <v>0.194165</v>
       </c>
       <c r="H273" s="7">
-        <v>0.121928</v>
+        <v>0.126109</v>
       </c>
       <c r="I273" s="7">
-        <v>0.49378700000000003</v>
+        <v>0.502219</v>
       </c>
       <c r="J273" s="7">
-        <v>2.777104</v>
+        <v>2.7911810000000004</v>
       </c>
       <c r="K273" s="7"/>
     </row>
@@ -11608,19 +11608,19 @@
         <v>5</v>
       </c>
       <c r="E274" s="7">
-        <v>0.034127</v>
+        <v>0.034461</v>
       </c>
       <c r="F274" s="7">
-        <v>0.07433</v>
+        <v>0.076526</v>
       </c>
       <c r="G274" s="7">
-        <v>0.236622</v>
+        <v>0.242732</v>
       </c>
       <c r="H274" s="7">
-        <v>0.161109</v>
+        <v>0.163483</v>
       </c>
       <c r="I274" s="7">
-        <v>0.495626</v>
+        <v>0.49666200000000005</v>
       </c>
       <c r="J274" s="7"/>
       <c r="K274" s="7"/>
@@ -11660,19 +11660,19 @@
         <v>5</v>
       </c>
       <c r="E276" s="7">
-        <v>0.040873999999999994</v>
+        <v>0.024377</v>
       </c>
       <c r="F276" s="7">
-        <v>0.022557</v>
+        <v>0.02215</v>
       </c>
       <c r="G276" s="7">
-        <v>0.179375</v>
+        <v>0.182797</v>
       </c>
       <c r="H276" s="7">
-        <v>0.154584</v>
+        <v>0.154124</v>
       </c>
       <c r="I276" s="7">
-        <v>0.441295</v>
+        <v>0.449186</v>
       </c>
       <c r="J276" s="7"/>
       <c r="K276" s="7"/>
@@ -11691,19 +11691,19 @@
         <v>4</v>
       </c>
       <c r="E277" s="7">
-        <v>0.045675</v>
+        <v>0.040881999999999995</v>
       </c>
       <c r="F277" s="7">
-        <v>0.039102</v>
+        <v>0.042099000000000004</v>
       </c>
       <c r="G277" s="7">
-        <v>0.30371400000000004</v>
+        <v>0.31933</v>
       </c>
       <c r="H277" s="7">
-        <v>0.235294</v>
+        <v>0.23885699999999999</v>
       </c>
       <c r="I277" s="7">
-        <v>0.345797</v>
+        <v>0.35868099999999997</v>
       </c>
       <c r="J277" s="7"/>
       <c r="K277" s="7"/>
@@ -11722,19 +11722,19 @@
         <v>5</v>
       </c>
       <c r="E278" s="7">
-        <v>0.055303000000000005</v>
+        <v>0.049405000000000004</v>
       </c>
       <c r="F278" s="7">
-        <v>0.05845500000000001</v>
+        <v>0.052836999999999995</v>
       </c>
       <c r="G278" s="7">
-        <v>0.272354</v>
+        <v>0.262471</v>
       </c>
       <c r="H278" s="7">
-        <v>0.230184</v>
+        <v>0.22365500000000002</v>
       </c>
       <c r="I278" s="7">
-        <v>0.338489</v>
+        <v>0.329114</v>
       </c>
       <c r="J278" s="7"/>
       <c r="K278" s="7"/>
@@ -11753,19 +11753,19 @@
         <v>6</v>
       </c>
       <c r="E279" s="7">
-        <v>0.133902</v>
+        <v>0.152291</v>
       </c>
       <c r="F279" s="7">
-        <v>0.176114</v>
+        <v>0.200834</v>
       </c>
       <c r="G279" s="7">
-        <v>0.386054</v>
+        <v>0.435604</v>
       </c>
       <c r="H279" s="7">
-        <v>0.38378799999999996</v>
+        <v>0.41287300000000005</v>
       </c>
       <c r="I279" s="7">
-        <v>0.5682659999999999</v>
+        <v>0.607342</v>
       </c>
       <c r="J279" s="7"/>
       <c r="K279" s="7"/>
@@ -11784,22 +11784,22 @@
         <v>3</v>
       </c>
       <c r="E280" s="7">
-        <v>0.012774</v>
+        <v>0.011174</v>
       </c>
       <c r="F280" s="7">
-        <v>0.007187</v>
+        <v>0.009569</v>
       </c>
       <c r="G280" s="7">
-        <v>0.187718</v>
+        <v>0.188387</v>
       </c>
       <c r="H280" s="7">
-        <v>0.129575</v>
+        <v>0.132247</v>
       </c>
       <c r="I280" s="7">
-        <v>0.476071</v>
+        <v>0.48049</v>
       </c>
       <c r="J280" s="7">
-        <v>3.016236</v>
+        <v>3.025735</v>
       </c>
       <c r="K280" s="7"/>
     </row>
@@ -11817,25 +11817,25 @@
         <v>5</v>
       </c>
       <c r="E281" s="7">
-        <v>0.047429</v>
+        <v>0.04765</v>
       </c>
       <c r="F281" s="7">
-        <v>0.107206</v>
+        <v>0.109637</v>
       </c>
       <c r="G281" s="7">
-        <v>0.366141</v>
+        <v>0.376376</v>
       </c>
       <c r="H281" s="7">
-        <v>0.249148</v>
+        <v>0.25189</v>
       </c>
       <c r="I281" s="7">
-        <v>0.569802</v>
+        <v>0.572048</v>
       </c>
       <c r="J281" s="7">
-        <v>2.668962</v>
+        <v>2.677017</v>
       </c>
       <c r="K281" s="7">
-        <v>6.767027000000001</v>
+        <v>6.784077999999999</v>
       </c>
     </row>
     <row r="282" spans="1:11" x14ac:dyDescent="0.25">
@@ -11852,25 +11852,25 @@
         <v>2</v>
       </c>
       <c r="E282" s="7">
-        <v>0.031056</v>
+        <v>0.03042</v>
       </c>
       <c r="F282" s="7">
-        <v>0.08886200000000001</v>
+        <v>0.08936899999999999</v>
       </c>
       <c r="G282" s="7">
-        <v>0.202159</v>
+        <v>0.19922399999999998</v>
       </c>
       <c r="H282" s="7">
-        <v>0.143271</v>
+        <v>0.14380300000000001</v>
       </c>
       <c r="I282" s="7">
-        <v>0.473706</v>
+        <v>0.47273400000000004</v>
       </c>
       <c r="J282" s="7">
-        <v>2.221073</v>
+        <v>2.2225729999999997</v>
       </c>
       <c r="K282" s="7">
-        <v>4.1712560000000005</v>
+        <v>4.173663</v>
       </c>
     </row>
     <row r="283" spans="1:11" x14ac:dyDescent="0.25">
@@ -11887,25 +11887,25 @@
         <v>6</v>
       </c>
       <c r="E283" s="7">
-        <v>0.014719</v>
+        <v>0.0069099999999999995</v>
       </c>
       <c r="F283" s="7">
-        <v>0.017601</v>
+        <v>0.023836</v>
       </c>
       <c r="G283" s="7">
-        <v>0.111958</v>
+        <v>0.121124</v>
       </c>
       <c r="H283" s="7">
-        <v>0.053994</v>
+        <v>0.060452000000000006</v>
       </c>
       <c r="I283" s="7">
-        <v>0.289464</v>
+        <v>0.298045</v>
       </c>
       <c r="J283" s="7">
-        <v>1.745241</v>
+        <v>1.7620609999999999</v>
       </c>
       <c r="K283" s="7">
-        <v>5.103702</v>
+        <v>5.1410990000000005</v>
       </c>
     </row>
     <row r="284" spans="1:11" x14ac:dyDescent="0.25">
@@ -11922,25 +11922,25 @@
         <v>6</v>
       </c>
       <c r="E284" s="7">
-        <v>0.023114</v>
+        <v>0.017781</v>
       </c>
       <c r="F284" s="7">
-        <v>-0.016822999999999998</v>
+        <v>-0.013726</v>
       </c>
       <c r="G284" s="7">
-        <v>0.28985099999999997</v>
+        <v>0.306598</v>
       </c>
       <c r="H284" s="7">
-        <v>0.22076</v>
+        <v>0.224606</v>
       </c>
       <c r="I284" s="7">
-        <v>0.37274</v>
+        <v>0.37351999999999996</v>
       </c>
       <c r="J284" s="7">
-        <v>2.3790020000000003</v>
+        <v>2.389645</v>
       </c>
       <c r="K284" s="7">
-        <v>12.491278</v>
+        <v>12.533774000000001</v>
       </c>
     </row>
     <row r="285" spans="1:11" x14ac:dyDescent="0.25">
@@ -11957,25 +11957,25 @@
         <v>4</v>
       </c>
       <c r="E285" s="7">
-        <v>0.027746</v>
+        <v>0.018449</v>
       </c>
       <c r="F285" s="7">
-        <v>0.007436000000000001</v>
+        <v>0.008714</v>
       </c>
       <c r="G285" s="7">
-        <v>0.188604</v>
+        <v>0.191073</v>
       </c>
       <c r="H285" s="7">
-        <v>0.059339</v>
+        <v>0.060683</v>
       </c>
       <c r="I285" s="7">
-        <v>0.372729</v>
+        <v>0.373567</v>
       </c>
       <c r="J285" s="7">
-        <v>1.7134559999999999</v>
+        <v>1.7168979999999998</v>
       </c>
       <c r="K285" s="7">
-        <v>3.6612400000000003</v>
+        <v>3.6671530000000003</v>
       </c>
     </row>
     <row r="286" spans="1:11" x14ac:dyDescent="0.25">
@@ -11992,25 +11992,25 @@
         <v>6</v>
       </c>
       <c r="E286" s="7">
-        <v>0.054653</v>
+        <v>0.058075999999999996</v>
       </c>
       <c r="F286" s="7">
-        <v>0.10191900000000001</v>
+        <v>0.108377</v>
       </c>
       <c r="G286" s="7">
-        <v>0.35940300000000003</v>
+        <v>0.37649900000000003</v>
       </c>
       <c r="H286" s="7">
-        <v>0.246792</v>
+        <v>0.254099</v>
       </c>
       <c r="I286" s="7">
-        <v>0.501639</v>
+        <v>0.511471</v>
       </c>
       <c r="J286" s="7">
-        <v>2.83683</v>
+        <v>2.859316</v>
       </c>
       <c r="K286" s="7">
-        <v>10.345291</v>
+        <v>10.411782</v>
       </c>
     </row>
     <row r="287" spans="1:11" x14ac:dyDescent="0.25">
@@ -12027,25 +12027,25 @@
         <v>3</v>
       </c>
       <c r="E287" s="7">
-        <v>0.026484</v>
+        <v>0.025415</v>
       </c>
       <c r="F287" s="7">
-        <v>0.072729</v>
+        <v>0.074606</v>
       </c>
       <c r="G287" s="7">
-        <v>0.204482</v>
+        <v>0.20340499999999997</v>
       </c>
       <c r="H287" s="7">
-        <v>0.152202</v>
+        <v>0.154218</v>
       </c>
       <c r="I287" s="7">
-        <v>0.46354799999999996</v>
+        <v>0.465754</v>
       </c>
       <c r="J287" s="7">
-        <v>2.9694369999999997</v>
+        <v>2.9763830000000002</v>
       </c>
       <c r="K287" s="7">
-        <v>5.3343799999999995</v>
+        <v>5.345465000000001</v>
       </c>
     </row>
     <row r="288" spans="1:11" x14ac:dyDescent="0.25">
@@ -12062,25 +12062,25 @@
         <v>3</v>
       </c>
       <c r="E288" s="7">
-        <v>0.026131</v>
+        <v>0.023011</v>
       </c>
       <c r="F288" s="7">
-        <v>0.068141</v>
+        <v>0.068777</v>
       </c>
       <c r="G288" s="7">
-        <v>0.18290299999999998</v>
+        <v>0.18005700000000002</v>
       </c>
       <c r="H288" s="7">
-        <v>0.11417899999999999</v>
+        <v>0.11484299999999999</v>
       </c>
       <c r="I288" s="7">
-        <v>0.448696</v>
+        <v>0.448369</v>
       </c>
       <c r="J288" s="7">
-        <v>2.308885</v>
+        <v>2.310857</v>
       </c>
       <c r="K288" s="7">
-        <v>4.227368</v>
+        <v>4.2304829999999995</v>
       </c>
     </row>
     <row r="289" spans="1:11" x14ac:dyDescent="0.25">
@@ -12097,25 +12097,25 @@
         <v>5</v>
       </c>
       <c r="E289" s="7">
-        <v>0.015912</v>
+        <v>0.009069</v>
       </c>
       <c r="F289" s="7">
-        <v>0.02629</v>
+        <v>0.02667</v>
       </c>
       <c r="G289" s="7">
-        <v>0.08250400000000001</v>
+        <v>0.084117</v>
       </c>
       <c r="H289" s="7">
-        <v>0.044755</v>
+        <v>0.045141999999999995</v>
       </c>
       <c r="I289" s="7">
-        <v>0.265464</v>
+        <v>0.264745</v>
       </c>
       <c r="J289" s="7">
-        <v>1.88561</v>
+        <v>1.886678</v>
       </c>
       <c r="K289" s="7">
-        <v>5.768886</v>
+        <v>5.7713909999999995</v>
       </c>
     </row>
     <row r="290" spans="1:11" x14ac:dyDescent="0.25">
@@ -12132,25 +12132,25 @@
         <v>3</v>
       </c>
       <c r="E290" s="7">
-        <v>0.022795999999999997</v>
+        <v>0.019196</v>
       </c>
       <c r="F290" s="7">
-        <v>0.044557</v>
+        <v>0.04633</v>
       </c>
       <c r="G290" s="7">
-        <v>0.22959700000000002</v>
+        <v>0.22954799999999997</v>
       </c>
       <c r="H290" s="7">
-        <v>0.07016700000000001</v>
+        <v>0.071984</v>
       </c>
       <c r="I290" s="7">
-        <v>0.417602</v>
+        <v>0.418662</v>
       </c>
       <c r="J290" s="7">
-        <v>1.97719</v>
+        <v>1.982243</v>
       </c>
       <c r="K290" s="7">
-        <v>3.63719</v>
+        <v>3.645061</v>
       </c>
     </row>
     <row r="291" spans="1:11" x14ac:dyDescent="0.25">
@@ -12167,25 +12167,25 @@
         <v>5</v>
       </c>
       <c r="E291" s="7">
-        <v>0.04211</v>
+        <v>0.040465</v>
       </c>
       <c r="F291" s="7">
-        <v>0.06423899999999999</v>
+        <v>0.067297</v>
       </c>
       <c r="G291" s="7">
-        <v>0.266302</v>
+        <v>0.270594</v>
       </c>
       <c r="H291" s="7">
-        <v>0.19189399999999998</v>
+        <v>0.19532</v>
       </c>
       <c r="I291" s="7">
-        <v>0.510699</v>
+        <v>0.515093</v>
       </c>
       <c r="J291" s="7">
-        <v>2.634293</v>
+        <v>2.644738</v>
       </c>
       <c r="K291" s="7">
-        <v>9.468537</v>
+        <v>9.498624</v>
       </c>
     </row>
     <row r="292" spans="1:11" x14ac:dyDescent="0.25">
@@ -12202,25 +12202,25 @@
         <v>6</v>
       </c>
       <c r="E292" s="7">
-        <v>-0.005397</v>
+        <v>-0.015781</v>
       </c>
       <c r="F292" s="7">
-        <v>-0.067192</v>
+        <v>-0.068563</v>
       </c>
       <c r="G292" s="7">
-        <v>0.127246</v>
+        <v>0.13889200000000002</v>
       </c>
       <c r="H292" s="7">
-        <v>0.062686</v>
+        <v>0.061124</v>
       </c>
       <c r="I292" s="7">
-        <v>0.606322</v>
+        <v>0.612437</v>
       </c>
       <c r="J292" s="7">
-        <v>4.165283</v>
+        <v>4.157691</v>
       </c>
       <c r="K292" s="7">
-        <v>13.442795</v>
+        <v>13.421566</v>
       </c>
     </row>
     <row r="293" spans="1:11" x14ac:dyDescent="0.25">
@@ -12237,25 +12237,25 @@
         <v>3</v>
       </c>
       <c r="E293" s="7">
-        <v>0.042379</v>
+        <v>0.043502</v>
       </c>
       <c r="F293" s="7">
-        <v>0.09729900000000001</v>
+        <v>0.101143</v>
       </c>
       <c r="G293" s="7">
-        <v>0.288003</v>
+        <v>0.294199</v>
       </c>
       <c r="H293" s="7">
-        <v>0.194041</v>
+        <v>0.19822299999999998</v>
       </c>
       <c r="I293" s="7">
-        <v>0.48950499999999997</v>
+        <v>0.494405</v>
       </c>
       <c r="J293" s="7">
-        <v>1.456678</v>
+        <v>1.4652830000000001</v>
       </c>
       <c r="K293" s="7">
-        <v>3.771008</v>
+        <v>3.787719</v>
       </c>
     </row>
     <row r="294" spans="1:11" x14ac:dyDescent="0.25">
@@ -12272,25 +12272,25 @@
     